--- a/ICT-RFA-RFI-lists-New.xlsx
+++ b/ICT-RFA-RFI-lists-New.xlsx
@@ -9,9 +9,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project Airport\LTIA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C0C2DFB-B61C-4FFB-8BE7-78404970B7BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1845AA21-5882-4350-9D4D-1CBC789B9D62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="506" activeTab="1" xr2:uid="{CCA8147E-0981-4321-B87F-440A52C0DA59}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="506" xr2:uid="{CCA8147E-0981-4321-B87F-440A52C0DA59}"/>
   </bookViews>
   <sheets>
     <sheet name="RFA" sheetId="1" r:id="rId1"/>
@@ -26,12 +26,12 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Need ReSub (RFA-SDS)'!$A$6:$R$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">RFA!$A$6:$AE$137</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'RFA-SDS'!$A$6:$AD$34</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">RFI!$A$6:$Z$126</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">RFI!$A$6:$Z$127</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Need ReSub (RFA)'!$A$1:$S$77</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'Need ReSub (RFA-SDS)'!$A$1:$R$62</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">RFA!$A$1:$AE$137,RFA!$I$139:$R$145,RFA!$C$139:$F$149,RFA!$C$151:$F$154,RFA!$C$156:$F$167</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'RFA-SDS'!$A$1:$AD$41,'RFA-SDS'!$H$43:$Q$49,'RFA-SDS'!$C$43:$E$47,'RFA-SDS'!$C$49:$E$52</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">RFI!$A$1:$Z$128,RFI!$H$130:$Q$134,RFI!$C$130:$E$135,RFI!$C$137:$E$140</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">RFI!$A$1:$Z$129,RFI!$H$131:$Q$135,RFI!$C$131:$E$136,RFI!$C$138:$E$141</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">RFA!$4:$5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'RFA-SDS'!$4:$5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">RFI!$4:$5</definedName>
@@ -78,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3419" uniqueCount="1058">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3423" uniqueCount="1061">
   <si>
     <t>TT</t>
   </si>
@@ -5019,6 +5019,15 @@
   </si>
   <si>
     <t>10/9/2026 Update</t>
+  </si>
+  <si>
+    <t>LTIA-5.11-LTICT-80000 -RFI-0037A</t>
+  </si>
+  <si>
+    <t>Proposed construction drawing naming convention.</t>
+  </si>
+  <si>
+    <t>Đề xuất nguyên tắc đặt tên bản vẽ thi công.</t>
   </si>
 </sst>
 </file>
@@ -7455,23 +7464,233 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="51" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="52" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="55" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="55" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -7479,266 +7698,56 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="51" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="52" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="45" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="55" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="55" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="53" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="47" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="45" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -8269,6 +8278,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C724CDAB-378C-47DB-9F45-08EE3BFB6E8B}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:AI167"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75"/>
   <cols>
@@ -8314,7 +8324,7 @@
       </c>
       <c r="J1" s="176">
         <f ca="1">TODAY()</f>
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="K1" s="131"/>
       <c r="L1" s="197"/>
@@ -8401,92 +8411,92 @@
       <c r="AE3" s="159"/>
     </row>
     <row r="4" spans="1:35" s="5" customFormat="1" ht="36" customHeight="1" thickBot="1">
-      <c r="A4" s="408" t="s">
+      <c r="A4" s="397" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="348" t="s">
+      <c r="B4" s="407" t="s">
         <v>515</v>
       </c>
-      <c r="C4" s="414" t="s">
+      <c r="C4" s="403" t="s">
         <v>45</v>
       </c>
-      <c r="D4" s="366" t="s">
+      <c r="D4" s="364" t="s">
         <v>95</v>
       </c>
-      <c r="E4" s="369" t="s">
+      <c r="E4" s="362" t="s">
         <v>46</v>
       </c>
-      <c r="F4" s="412" t="s">
+      <c r="F4" s="399" t="s">
         <v>47</v>
       </c>
-      <c r="G4" s="369" t="s">
+      <c r="G4" s="362" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="410" t="s">
+      <c r="H4" s="401" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="366" t="s">
+      <c r="I4" s="364" t="s">
         <v>48</v>
       </c>
-      <c r="J4" s="366" t="s">
+      <c r="J4" s="364" t="s">
         <v>49</v>
       </c>
-      <c r="K4" s="369" t="s">
+      <c r="K4" s="362" t="s">
         <v>78</v>
       </c>
-      <c r="L4" s="366" t="s">
+      <c r="L4" s="364" t="s">
         <v>80</v>
       </c>
-      <c r="M4" s="364" t="s">
+      <c r="M4" s="366" t="s">
         <v>53</v>
       </c>
-      <c r="N4" s="365"/>
-      <c r="O4" s="364" t="s">
+      <c r="N4" s="367"/>
+      <c r="O4" s="366" t="s">
         <v>55</v>
       </c>
-      <c r="P4" s="365"/>
+      <c r="P4" s="367"/>
       <c r="Q4" s="368" t="s">
         <v>72</v>
       </c>
-      <c r="R4" s="365"/>
-      <c r="S4" s="364" t="s">
+      <c r="R4" s="367"/>
+      <c r="S4" s="366" t="s">
         <v>53</v>
       </c>
-      <c r="T4" s="364"/>
-      <c r="U4" s="365"/>
+      <c r="T4" s="366"/>
+      <c r="U4" s="367"/>
       <c r="V4" s="368" t="s">
         <v>55</v>
       </c>
-      <c r="W4" s="364"/>
-      <c r="X4" s="365"/>
-      <c r="Y4" s="371" t="s">
+      <c r="W4" s="366"/>
+      <c r="X4" s="367"/>
+      <c r="Y4" s="393" t="s">
         <v>72</v>
       </c>
-      <c r="Z4" s="372"/>
-      <c r="AA4" s="359" t="s">
+      <c r="Z4" s="427"/>
+      <c r="AA4" s="426" t="s">
         <v>112</v>
       </c>
-      <c r="AB4" s="360"/>
-      <c r="AC4" s="360"/>
-      <c r="AD4" s="361"/>
-      <c r="AE4" s="369" t="s">
+      <c r="AB4" s="395"/>
+      <c r="AC4" s="395"/>
+      <c r="AD4" s="396"/>
+      <c r="AE4" s="362" t="s">
         <v>79</v>
       </c>
       <c r="AG4" s="236"/>
     </row>
     <row r="5" spans="1:35" ht="78.75">
-      <c r="A5" s="409"/>
-      <c r="B5" s="349"/>
-      <c r="C5" s="415"/>
-      <c r="D5" s="367"/>
-      <c r="E5" s="370"/>
-      <c r="F5" s="413"/>
-      <c r="G5" s="370"/>
-      <c r="H5" s="411"/>
-      <c r="I5" s="367"/>
-      <c r="J5" s="367"/>
-      <c r="K5" s="370"/>
-      <c r="L5" s="367"/>
+      <c r="A5" s="398"/>
+      <c r="B5" s="408"/>
+      <c r="C5" s="404"/>
+      <c r="D5" s="365"/>
+      <c r="E5" s="369"/>
+      <c r="F5" s="400"/>
+      <c r="G5" s="369"/>
+      <c r="H5" s="402"/>
+      <c r="I5" s="365"/>
+      <c r="J5" s="365"/>
+      <c r="K5" s="369"/>
+      <c r="L5" s="365"/>
       <c r="M5" s="79" t="s">
         <v>52</v>
       </c>
@@ -8541,14 +8551,14 @@
       <c r="AD5" s="336" t="s">
         <v>118</v>
       </c>
-      <c r="AE5" s="416"/>
-      <c r="AG5" s="369" t="s">
+      <c r="AE5" s="363"/>
+      <c r="AG5" s="362" t="s">
         <v>119</v>
       </c>
-      <c r="AH5" s="369" t="s">
+      <c r="AH5" s="362" t="s">
         <v>120</v>
       </c>
-      <c r="AI5" s="369" t="s">
+      <c r="AI5" s="362" t="s">
         <v>121</v>
       </c>
     </row>
@@ -8584,11 +8594,11 @@
       <c r="AC6" s="86"/>
       <c r="AD6" s="86"/>
       <c r="AE6" s="74"/>
-      <c r="AG6" s="407"/>
-      <c r="AH6" s="407"/>
-      <c r="AI6" s="407"/>
-    </row>
-    <row r="7" spans="1:35" s="9" customFormat="1" ht="47.25">
+      <c r="AG6" s="409"/>
+      <c r="AH6" s="409"/>
+      <c r="AI6" s="409"/>
+    </row>
+    <row r="7" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
       <c r="A7" s="33">
         <f t="shared" ref="A7:A38" si="0">A6+1</f>
         <v>1</v>
@@ -8708,7 +8718,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:35" s="9" customFormat="1" ht="47.25">
+    <row r="8" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
       <c r="A8" s="33">
         <f t="shared" si="0"/>
         <v>2</v>
@@ -8824,7 +8834,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:35" s="9" customFormat="1" ht="47.25">
+    <row r="9" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
       <c r="A9" s="33">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -8940,7 +8950,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:35" s="9" customFormat="1" ht="47.25">
+    <row r="10" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
       <c r="A10" s="33">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -9058,7 +9068,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:35" s="9" customFormat="1" ht="47.25">
+    <row r="11" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
       <c r="A11" s="33">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -9176,7 +9186,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:35" s="9" customFormat="1" ht="47.25">
+    <row r="12" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
       <c r="A12" s="33">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -9294,7 +9304,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:35" s="9" customFormat="1" ht="47.25">
+    <row r="13" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
       <c r="A13" s="33">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -9412,7 +9422,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:35" s="9" customFormat="1" ht="47.25">
+    <row r="14" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
       <c r="A14" s="33">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -9505,7 +9515,7 @@
       </c>
       <c r="AD14" s="337">
         <f t="shared" ca="1" si="7"/>
-        <v>841</v>
+        <v>844</v>
       </c>
       <c r="AE14" s="92"/>
       <c r="AG14" s="238" t="str">
@@ -9528,7 +9538,7 @@
         <v>YES</v>
       </c>
     </row>
-    <row r="15" spans="1:35" s="9" customFormat="1" ht="63">
+    <row r="15" spans="1:35" s="9" customFormat="1" ht="63" hidden="1">
       <c r="A15" s="33">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -9621,7 +9631,7 @@
       </c>
       <c r="AD15" s="337">
         <f t="shared" ca="1" si="7"/>
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="AE15" s="92"/>
       <c r="AG15" s="238" t="str">
@@ -9644,7 +9654,7 @@
         <v>YES</v>
       </c>
     </row>
-    <row r="16" spans="1:35" s="9" customFormat="1" ht="47.25">
+    <row r="16" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
       <c r="A16" s="33">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -9762,7 +9772,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:35" s="9" customFormat="1" ht="47.25">
+    <row r="17" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
       <c r="A17" s="33">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -9878,7 +9888,7 @@
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:35" s="9" customFormat="1" ht="47.25">
+    <row r="18" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
       <c r="A18" s="33">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -9996,7 +10006,7 @@
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:35" s="9" customFormat="1" ht="47.25">
+    <row r="19" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
       <c r="A19" s="33">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -10114,7 +10124,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:35" s="9" customFormat="1" ht="47.25">
+    <row r="20" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
       <c r="A20" s="33">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -10230,7 +10240,7 @@
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:35" s="9" customFormat="1" ht="47.25">
+    <row r="21" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
       <c r="A21" s="33">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -10348,7 +10358,7 @@
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:35" s="9" customFormat="1" ht="47.25">
+    <row r="22" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
       <c r="A22" s="33">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -10466,7 +10476,7 @@
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:35" s="9" customFormat="1" ht="47.25">
+    <row r="23" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
       <c r="A23" s="33">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -10582,7 +10592,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:35" s="9" customFormat="1" ht="47.25">
+    <row r="24" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
       <c r="A24" s="33">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -10702,7 +10712,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:35" s="9" customFormat="1" ht="63">
+    <row r="25" spans="1:35" s="9" customFormat="1" ht="63" hidden="1">
       <c r="A25" s="33">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -10818,7 +10828,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:35" s="9" customFormat="1" ht="47.25">
+    <row r="26" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
       <c r="A26" s="33">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -10934,7 +10944,7 @@
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:35" s="9" customFormat="1" ht="47.25">
+    <row r="27" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
       <c r="A27" s="33">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -11052,7 +11062,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" spans="1:35" s="9" customFormat="1" ht="47.25">
+    <row r="28" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
       <c r="A28" s="33">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -11170,7 +11180,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:35" s="9" customFormat="1" ht="47.25">
+    <row r="29" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
       <c r="A29" s="33">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -11286,7 +11296,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:35" s="9" customFormat="1" ht="47.25">
+    <row r="30" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
       <c r="A30" s="33">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -11404,7 +11414,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:35" s="9" customFormat="1" ht="47.25">
+    <row r="31" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
       <c r="A31" s="33">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -11522,7 +11532,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" spans="1:35" s="9" customFormat="1" ht="47.25">
+    <row r="32" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
       <c r="A32" s="33">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -11638,7 +11648,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" spans="1:35" s="9" customFormat="1" ht="47.25">
+    <row r="33" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
       <c r="A33" s="33">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -11756,7 +11766,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:35" s="9" customFormat="1" ht="47.25">
+    <row r="34" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
       <c r="A34" s="33">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -11872,7 +11882,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:35" s="9" customFormat="1" ht="47.25">
+    <row r="35" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
       <c r="A35" s="33">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -11988,7 +11998,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:35" s="9" customFormat="1" ht="47.25">
+    <row r="36" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
       <c r="A36" s="33">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -12104,7 +12114,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="1:35" s="9" customFormat="1" ht="47.25">
+    <row r="37" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
       <c r="A37" s="33">
         <f t="shared" si="0"/>
         <v>31</v>
@@ -12220,7 +12230,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="1:35" s="9" customFormat="1" ht="47.25">
+    <row r="38" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
       <c r="A38" s="33">
         <f t="shared" si="0"/>
         <v>32</v>
@@ -12336,7 +12346,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:35" s="9" customFormat="1" ht="63">
+    <row r="39" spans="1:35" s="9" customFormat="1" ht="63" hidden="1">
       <c r="A39" s="33">
         <f t="shared" ref="A39:A70" si="10">A38+1</f>
         <v>33</v>
@@ -12452,7 +12462,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:35" s="9" customFormat="1" ht="47.25">
+    <row r="40" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
       <c r="A40" s="33">
         <f t="shared" si="10"/>
         <v>34</v>
@@ -12568,7 +12578,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:35" s="9" customFormat="1" ht="47.25">
+    <row r="41" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
       <c r="A41" s="33">
         <f t="shared" si="10"/>
         <v>35</v>
@@ -12684,7 +12694,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="1:35" s="9" customFormat="1" ht="47.25">
+    <row r="42" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
       <c r="A42" s="33">
         <f t="shared" si="10"/>
         <v>36</v>
@@ -12800,7 +12810,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="1:35" s="9" customFormat="1" ht="47.25">
+    <row r="43" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
       <c r="A43" s="33">
         <f t="shared" si="10"/>
         <v>37</v>
@@ -12916,7 +12926,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:35" s="9" customFormat="1" ht="47.25">
+    <row r="44" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
       <c r="A44" s="33">
         <f t="shared" si="10"/>
         <v>38</v>
@@ -13009,7 +13019,7 @@
       </c>
       <c r="AD44" s="337">
         <f t="shared" ca="1" si="13"/>
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="AE44" s="92"/>
       <c r="AG44" s="238" t="str">
@@ -13032,7 +13042,7 @@
         <v>YES</v>
       </c>
     </row>
-    <row r="45" spans="1:35" s="9" customFormat="1" ht="94.5">
+    <row r="45" spans="1:35" s="9" customFormat="1" ht="94.5" hidden="1">
       <c r="A45" s="33">
         <f t="shared" si="10"/>
         <v>39</v>
@@ -13150,7 +13160,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="1:35" s="9" customFormat="1" ht="47.25">
+    <row r="46" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
       <c r="A46" s="33">
         <f t="shared" si="10"/>
         <v>40</v>
@@ -13243,7 +13253,7 @@
       </c>
       <c r="AD46" s="337">
         <f t="shared" ca="1" si="13"/>
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="AE46" s="92"/>
       <c r="AG46" s="238" t="str">
@@ -13266,7 +13276,7 @@
         <v>YES</v>
       </c>
     </row>
-    <row r="47" spans="1:35" s="9" customFormat="1" ht="47.25">
+    <row r="47" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
       <c r="A47" s="33">
         <f t="shared" si="10"/>
         <v>41</v>
@@ -13382,7 +13392,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:35" s="9" customFormat="1" ht="47.25">
+    <row r="48" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
       <c r="A48" s="33">
         <f t="shared" si="10"/>
         <v>42</v>
@@ -13498,7 +13508,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:35" s="9" customFormat="1" ht="94.5">
+    <row r="49" spans="1:35" s="9" customFormat="1" ht="94.5" hidden="1">
       <c r="A49" s="33">
         <f t="shared" si="10"/>
         <v>43</v>
@@ -13616,7 +13626,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:35" s="9" customFormat="1" ht="78.75">
+    <row r="50" spans="1:35" s="9" customFormat="1" ht="78.75" hidden="1">
       <c r="A50" s="33">
         <f t="shared" si="10"/>
         <v>44</v>
@@ -13709,7 +13719,7 @@
       </c>
       <c r="AD50" s="337">
         <f t="shared" ca="1" si="13"/>
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="AE50" s="92"/>
       <c r="AG50" s="238" t="str">
@@ -13732,7 +13742,7 @@
         <v>YES</v>
       </c>
     </row>
-    <row r="51" spans="1:35" s="9" customFormat="1" ht="47.25">
+    <row r="51" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
       <c r="A51" s="33">
         <f t="shared" si="10"/>
         <v>45</v>
@@ -13760,7 +13770,7 @@
       <c r="I51" s="138"/>
       <c r="J51" s="164">
         <f t="shared" ca="1" si="3"/>
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="K51" s="47"/>
       <c r="L51" s="164" t="s">
@@ -13822,7 +13832,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="1:35" s="9" customFormat="1" ht="63">
+    <row r="52" spans="1:35" s="9" customFormat="1" ht="63" hidden="1">
       <c r="A52" s="33">
         <f t="shared" si="10"/>
         <v>46</v>
@@ -13940,7 +13950,7 @@
         <v/>
       </c>
     </row>
-    <row r="53" spans="1:35" s="9" customFormat="1" ht="47.25">
+    <row r="53" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
       <c r="A53" s="33">
         <f t="shared" si="10"/>
         <v>47</v>
@@ -14058,7 +14068,7 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="1:35" s="9" customFormat="1" ht="47.25">
+    <row r="54" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
       <c r="A54" s="33">
         <f t="shared" si="10"/>
         <v>48</v>
@@ -14174,7 +14184,7 @@
         <v/>
       </c>
     </row>
-    <row r="55" spans="1:35" s="9" customFormat="1" ht="47.25">
+    <row r="55" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
       <c r="A55" s="33">
         <f t="shared" si="10"/>
         <v>49</v>
@@ -14290,7 +14300,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="1:35" s="9" customFormat="1" ht="47.25">
+    <row r="56" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
       <c r="A56" s="33">
         <f t="shared" si="10"/>
         <v>50</v>
@@ -14408,7 +14418,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="1:35" s="9" customFormat="1" ht="47.25">
+    <row r="57" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
       <c r="A57" s="33">
         <f t="shared" si="10"/>
         <v>51</v>
@@ -14524,7 +14534,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="1:35" s="9" customFormat="1" ht="47.25">
+    <row r="58" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
       <c r="A58" s="33">
         <f t="shared" si="10"/>
         <v>52</v>
@@ -14617,7 +14627,7 @@
       </c>
       <c r="AD58" s="337">
         <f t="shared" ca="1" si="13"/>
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="AE58" s="92"/>
       <c r="AG58" s="238" t="str">
@@ -14640,7 +14650,7 @@
         <v>YES</v>
       </c>
     </row>
-    <row r="59" spans="1:35" s="9" customFormat="1" ht="47.25">
+    <row r="59" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
       <c r="A59" s="33">
         <f t="shared" si="10"/>
         <v>53</v>
@@ -14668,7 +14678,7 @@
       <c r="I59" s="138"/>
       <c r="J59" s="164">
         <f t="shared" ca="1" si="3"/>
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="K59" s="47"/>
       <c r="L59" s="164" t="s">
@@ -14730,7 +14740,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:35" s="9" customFormat="1" ht="47.25">
+    <row r="60" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
       <c r="A60" s="33">
         <f t="shared" si="10"/>
         <v>54</v>
@@ -14823,7 +14833,7 @@
       </c>
       <c r="AD60" s="337">
         <f t="shared" ca="1" si="13"/>
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="AE60" s="92" t="s">
         <v>878</v>
@@ -14848,7 +14858,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:35" s="9" customFormat="1" ht="47.25">
+    <row r="61" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
       <c r="A61" s="33">
         <f t="shared" si="10"/>
         <v>55</v>
@@ -14941,7 +14951,7 @@
       </c>
       <c r="AD61" s="337">
         <f t="shared" ca="1" si="13"/>
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="AE61" s="92"/>
       <c r="AG61" s="238" t="str">
@@ -14964,7 +14974,7 @@
         <v>YES</v>
       </c>
     </row>
-    <row r="62" spans="1:35" s="9" customFormat="1" ht="78.75">
+    <row r="62" spans="1:35" s="9" customFormat="1" ht="78.75" hidden="1">
       <c r="A62" s="33">
         <f t="shared" si="10"/>
         <v>56</v>
@@ -15082,7 +15092,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="1:35" s="9" customFormat="1" ht="47.25">
+    <row r="63" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
       <c r="A63" s="33">
         <f t="shared" si="10"/>
         <v>57</v>
@@ -15200,7 +15210,7 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="1:35" s="9" customFormat="1" ht="47.25">
+    <row r="64" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
       <c r="A64" s="33">
         <f t="shared" si="10"/>
         <v>58</v>
@@ -15318,7 +15328,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="1:35" s="9" customFormat="1" ht="47.25">
+    <row r="65" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
       <c r="A65" s="33">
         <f t="shared" si="10"/>
         <v>59</v>
@@ -15436,7 +15446,7 @@
         <v/>
       </c>
     </row>
-    <row r="66" spans="1:35" s="9" customFormat="1" ht="94.5">
+    <row r="66" spans="1:35" s="9" customFormat="1" ht="94.5" hidden="1">
       <c r="A66" s="33">
         <f t="shared" si="10"/>
         <v>60</v>
@@ -15554,7 +15564,7 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="1:35" s="9" customFormat="1" ht="78.75">
+    <row r="67" spans="1:35" s="9" customFormat="1" ht="78.75" hidden="1">
       <c r="A67" s="33">
         <f t="shared" si="10"/>
         <v>61</v>
@@ -15670,7 +15680,7 @@
         <v/>
       </c>
     </row>
-    <row r="68" spans="1:35" s="9" customFormat="1" ht="47.25">
+    <row r="68" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
       <c r="A68" s="33">
         <f t="shared" si="10"/>
         <v>62</v>
@@ -15761,7 +15771,7 @@
       </c>
       <c r="AD68" s="337">
         <f t="shared" ca="1" si="13"/>
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="AE68" s="92"/>
       <c r="AG68" s="238" t="str">
@@ -15784,7 +15794,7 @@
         <v>YES</v>
       </c>
     </row>
-    <row r="69" spans="1:35" s="9" customFormat="1" ht="47.25">
+    <row r="69" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
       <c r="A69" s="33">
         <f>A68+1</f>
         <v>63</v>
@@ -15892,7 +15902,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="1:35" s="9" customFormat="1" ht="47.25">
+    <row r="70" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
       <c r="A70" s="33">
         <f t="shared" si="10"/>
         <v>64</v>
@@ -16008,7 +16018,7 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="1:35" s="9" customFormat="1" ht="47.25">
+    <row r="71" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
       <c r="A71" s="33">
         <f t="shared" ref="A71:A135" si="19">A70+1</f>
         <v>65</v>
@@ -16124,7 +16134,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="1:35" s="9" customFormat="1" ht="47.25">
+    <row r="72" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
       <c r="A72" s="33">
         <f t="shared" si="19"/>
         <v>66</v>
@@ -16240,7 +16250,7 @@
         <v/>
       </c>
     </row>
-    <row r="73" spans="1:35" s="9" customFormat="1" ht="47.25">
+    <row r="73" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
       <c r="A73" s="33">
         <f t="shared" si="19"/>
         <v>67</v>
@@ -16356,7 +16366,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:35" s="9" customFormat="1" ht="47.25">
+    <row r="74" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
       <c r="A74" s="33">
         <f t="shared" si="19"/>
         <v>68</v>
@@ -16474,7 +16484,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:35" s="9" customFormat="1" ht="47.25">
+    <row r="75" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
       <c r="A75" s="33">
         <f t="shared" si="19"/>
         <v>69</v>
@@ -16592,7 +16602,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="1:35" s="9" customFormat="1" ht="63">
+    <row r="76" spans="1:35" s="9" customFormat="1" ht="63" hidden="1">
       <c r="A76" s="33">
         <f t="shared" si="19"/>
         <v>70</v>
@@ -16710,7 +16720,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="1:35" s="9" customFormat="1" ht="47.25">
+    <row r="77" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
       <c r="A77" s="33">
         <f t="shared" si="19"/>
         <v>71</v>
@@ -16828,7 +16838,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:35" s="9" customFormat="1" ht="47.25">
+    <row r="78" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
       <c r="A78" s="33">
         <f t="shared" si="19"/>
         <v>72</v>
@@ -16944,7 +16954,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:35" s="9" customFormat="1" ht="141.75">
+    <row r="79" spans="1:35" s="9" customFormat="1" ht="141.75" hidden="1">
       <c r="A79" s="33">
         <f t="shared" si="19"/>
         <v>73</v>
@@ -17054,7 +17064,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:35" s="9" customFormat="1" ht="141.75">
+    <row r="80" spans="1:35" s="9" customFormat="1" ht="141.75" hidden="1">
       <c r="A80" s="33">
         <f t="shared" si="19"/>
         <v>74</v>
@@ -17164,7 +17174,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:35" s="9" customFormat="1" ht="126">
+    <row r="81" spans="1:35" s="9" customFormat="1" ht="126" hidden="1">
       <c r="A81" s="33">
         <f t="shared" si="19"/>
         <v>75</v>
@@ -17270,7 +17280,7 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="1:35" s="9" customFormat="1" ht="63">
+    <row r="82" spans="1:35" s="9" customFormat="1" ht="63" hidden="1">
       <c r="A82" s="33">
         <f t="shared" si="19"/>
         <v>76</v>
@@ -17386,7 +17396,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="1:35" s="9" customFormat="1" ht="63">
+    <row r="83" spans="1:35" s="9" customFormat="1" ht="63" hidden="1">
       <c r="A83" s="33">
         <f t="shared" si="19"/>
         <v>77</v>
@@ -17475,7 +17485,7 @@
         <v/>
       </c>
     </row>
-    <row r="84" spans="1:35" s="9" customFormat="1" ht="141.75">
+    <row r="84" spans="1:35" s="9" customFormat="1" ht="141.75" hidden="1">
       <c r="A84" s="33">
         <f t="shared" si="19"/>
         <v>78</v>
@@ -17585,7 +17595,7 @@
         <v/>
       </c>
     </row>
-    <row r="85" spans="1:35" s="9" customFormat="1" ht="110.25">
+    <row r="85" spans="1:35" s="9" customFormat="1" ht="110.25" hidden="1">
       <c r="A85" s="33">
         <f t="shared" si="19"/>
         <v>79</v>
@@ -17703,7 +17713,7 @@
         <v/>
       </c>
     </row>
-    <row r="86" spans="1:35" s="9" customFormat="1" ht="47.25">
+    <row r="86" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
       <c r="A86" s="33">
         <f t="shared" si="19"/>
         <v>80</v>
@@ -17813,7 +17823,7 @@
         <v/>
       </c>
     </row>
-    <row r="87" spans="1:35" s="9" customFormat="1" ht="47.25">
+    <row r="87" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
       <c r="A87" s="33">
         <f t="shared" si="19"/>
         <v>81</v>
@@ -17906,7 +17916,7 @@
         <v/>
       </c>
     </row>
-    <row r="88" spans="1:35" s="9" customFormat="1" ht="47.25">
+    <row r="88" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
       <c r="A88" s="33">
         <f t="shared" si="19"/>
         <v>82</v>
@@ -18018,7 +18028,7 @@
         <v/>
       </c>
     </row>
-    <row r="89" spans="1:35" s="9" customFormat="1" ht="47.25">
+    <row r="89" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
       <c r="A89" s="33">
         <f t="shared" si="19"/>
         <v>83</v>
@@ -18130,7 +18140,7 @@
         <v/>
       </c>
     </row>
-    <row r="90" spans="1:35" s="9" customFormat="1" ht="47.25">
+    <row r="90" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
       <c r="A90" s="33">
         <f t="shared" si="19"/>
         <v>84</v>
@@ -18242,7 +18252,7 @@
         <v/>
       </c>
     </row>
-    <row r="91" spans="1:35" s="9" customFormat="1" ht="47.25">
+    <row r="91" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
       <c r="A91" s="33">
         <f t="shared" si="19"/>
         <v>85</v>
@@ -18354,7 +18364,7 @@
         <v/>
       </c>
     </row>
-    <row r="92" spans="1:35" s="9" customFormat="1" ht="47.25">
+    <row r="92" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
       <c r="A92" s="33">
         <f t="shared" si="19"/>
         <v>86</v>
@@ -18383,11 +18393,11 @@
       <c r="I92" s="138"/>
       <c r="J92" s="164">
         <f t="shared" ca="1" si="27"/>
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="K92" s="47">
         <f t="shared" ca="1" si="28"/>
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="L92" s="164" t="s">
         <v>1004</v>
@@ -18452,7 +18462,7 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="1:35" s="9" customFormat="1" ht="63">
+    <row r="93" spans="1:35" s="9" customFormat="1" ht="63" hidden="1">
       <c r="A93" s="33">
         <f t="shared" si="19"/>
         <v>87</v>
@@ -18485,11 +18495,11 @@
       </c>
       <c r="J93" s="164">
         <f t="shared" ca="1" si="27"/>
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="K93" s="47">
         <f t="shared" ca="1" si="28"/>
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="L93" s="164" t="s">
         <v>13</v>
@@ -18554,7 +18564,7 @@
         <v/>
       </c>
     </row>
-    <row r="94" spans="1:35" s="9" customFormat="1" ht="177.75" customHeight="1">
+    <row r="94" spans="1:35" s="9" customFormat="1" ht="177.75" hidden="1" customHeight="1">
       <c r="A94" s="33">
         <f t="shared" si="19"/>
         <v>88</v>
@@ -18664,7 +18674,7 @@
         <v>YES</v>
       </c>
     </row>
-    <row r="95" spans="1:35" s="9" customFormat="1" ht="78.75">
+    <row r="95" spans="1:35" s="9" customFormat="1" ht="78.75" hidden="1">
       <c r="A95" s="33">
         <f t="shared" si="19"/>
         <v>89</v>
@@ -18753,7 +18763,7 @@
         <v/>
       </c>
     </row>
-    <row r="96" spans="1:35" s="9" customFormat="1" ht="47.25">
+    <row r="96" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
       <c r="A96" s="33">
         <f t="shared" si="19"/>
         <v>90</v>
@@ -18863,7 +18873,7 @@
         <v>YES</v>
       </c>
     </row>
-    <row r="97" spans="1:35" s="9" customFormat="1" ht="78.75">
+    <row r="97" spans="1:35" s="9" customFormat="1" ht="78.75" hidden="1">
       <c r="A97" s="33">
         <f t="shared" si="19"/>
         <v>91</v>
@@ -18971,7 +18981,7 @@
         <v>YES</v>
       </c>
     </row>
-    <row r="98" spans="1:35" s="9" customFormat="1" ht="47.25">
+    <row r="98" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
       <c r="A98" s="33">
         <f t="shared" si="19"/>
         <v>92</v>
@@ -19079,7 +19089,7 @@
         <v>YES</v>
       </c>
     </row>
-    <row r="99" spans="1:35" s="9" customFormat="1" ht="47.25">
+    <row r="99" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
       <c r="A99" s="33">
         <f t="shared" si="19"/>
         <v>93</v>
@@ -19191,7 +19201,7 @@
         <v/>
       </c>
     </row>
-    <row r="100" spans="1:35" s="9" customFormat="1" ht="47.25">
+    <row r="100" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
       <c r="A100" s="33">
         <f t="shared" si="19"/>
         <v>94</v>
@@ -19299,7 +19309,7 @@
         <v/>
       </c>
     </row>
-    <row r="101" spans="1:35" s="9" customFormat="1" ht="78.75">
+    <row r="101" spans="1:35" s="9" customFormat="1" ht="78.75" hidden="1">
       <c r="A101" s="33">
         <f t="shared" si="19"/>
         <v>95</v>
@@ -19405,7 +19415,7 @@
         <v>YES</v>
       </c>
     </row>
-    <row r="102" spans="1:35" s="9" customFormat="1" ht="78.75">
+    <row r="102" spans="1:35" s="9" customFormat="1" ht="78.75" hidden="1">
       <c r="A102" s="33">
         <f t="shared" si="19"/>
         <v>96</v>
@@ -19497,7 +19507,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:35" s="9" customFormat="1" ht="63">
+    <row r="103" spans="1:35" s="9" customFormat="1" ht="63" hidden="1">
       <c r="A103" s="33">
         <f t="shared" si="19"/>
         <v>97</v>
@@ -19609,7 +19619,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:35" s="9" customFormat="1" ht="63">
+    <row r="104" spans="1:35" s="9" customFormat="1" ht="63" hidden="1">
       <c r="A104" s="33">
         <f t="shared" si="19"/>
         <v>98</v>
@@ -19721,7 +19731,7 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="1:35" s="9" customFormat="1" ht="63">
+    <row r="105" spans="1:35" s="9" customFormat="1" ht="63" hidden="1">
       <c r="A105" s="33">
         <f t="shared" si="19"/>
         <v>99</v>
@@ -19833,7 +19843,7 @@
         <v/>
       </c>
     </row>
-    <row r="106" spans="1:35" s="9" customFormat="1" ht="47.25">
+    <row r="106" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
       <c r="A106" s="33">
         <f t="shared" si="19"/>
         <v>100</v>
@@ -19941,7 +19951,7 @@
         <v/>
       </c>
     </row>
-    <row r="107" spans="1:35" s="9" customFormat="1" ht="63">
+    <row r="107" spans="1:35" s="9" customFormat="1" ht="63" hidden="1">
       <c r="A107" s="33">
         <f t="shared" si="19"/>
         <v>101</v>
@@ -20032,7 +20042,7 @@
         <v/>
       </c>
     </row>
-    <row r="108" spans="1:35" s="9" customFormat="1" ht="47.25">
+    <row r="108" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
       <c r="A108" s="33">
         <f t="shared" si="19"/>
         <v>102</v>
@@ -20138,7 +20148,7 @@
         <v>YES</v>
       </c>
     </row>
-    <row r="109" spans="1:35" s="9" customFormat="1" ht="63">
+    <row r="109" spans="1:35" s="9" customFormat="1" ht="63" hidden="1">
       <c r="A109" s="33">
         <f t="shared" si="19"/>
         <v>103</v>
@@ -20246,7 +20256,7 @@
         <v/>
       </c>
     </row>
-    <row r="110" spans="1:35" s="9" customFormat="1" ht="47.25">
+    <row r="110" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
       <c r="A110" s="33">
         <f t="shared" si="19"/>
         <v>104</v>
@@ -20350,7 +20360,7 @@
         <v/>
       </c>
     </row>
-    <row r="111" spans="1:35" s="9" customFormat="1" ht="63">
+    <row r="111" spans="1:35" s="9" customFormat="1" ht="63" hidden="1">
       <c r="A111" s="33">
         <f t="shared" si="19"/>
         <v>105</v>
@@ -20381,11 +20391,11 @@
       <c r="I111" s="23"/>
       <c r="J111" s="164">
         <f t="shared" ca="1" si="30"/>
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="K111" s="47">
         <f t="shared" ca="1" si="31"/>
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="L111" s="164" t="s">
         <v>13</v>
@@ -20448,7 +20458,7 @@
         <v/>
       </c>
     </row>
-    <row r="112" spans="1:35" s="9" customFormat="1" ht="47.25">
+    <row r="112" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
       <c r="A112" s="33">
         <f t="shared" si="19"/>
         <v>106</v>
@@ -20554,7 +20564,7 @@
         <v>YES</v>
       </c>
     </row>
-    <row r="113" spans="1:35" s="9" customFormat="1" ht="110.25">
+    <row r="113" spans="1:35" s="9" customFormat="1" ht="110.25" hidden="1">
       <c r="A113" s="33">
         <f t="shared" si="19"/>
         <v>107</v>
@@ -20660,7 +20670,7 @@
         <v/>
       </c>
     </row>
-    <row r="114" spans="1:35" s="9" customFormat="1" ht="47.25">
+    <row r="114" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
       <c r="A114" s="33">
         <f t="shared" si="19"/>
         <v>108</v>
@@ -20766,7 +20776,7 @@
         <v/>
       </c>
     </row>
-    <row r="115" spans="1:35" s="9" customFormat="1" ht="63">
+    <row r="115" spans="1:35" s="9" customFormat="1" ht="63" hidden="1">
       <c r="A115" s="33">
         <f t="shared" si="19"/>
         <v>109</v>
@@ -20874,7 +20884,7 @@
         <v/>
       </c>
     </row>
-    <row r="116" spans="1:35" s="9" customFormat="1" ht="63">
+    <row r="116" spans="1:35" s="9" customFormat="1" ht="63" hidden="1">
       <c r="A116" s="33">
         <f t="shared" si="19"/>
         <v>110</v>
@@ -20986,7 +20996,7 @@
         <v/>
       </c>
     </row>
-    <row r="117" spans="1:35" s="9" customFormat="1" ht="94.5">
+    <row r="117" spans="1:35" s="9" customFormat="1" ht="94.5" hidden="1">
       <c r="A117" s="33">
         <f t="shared" si="19"/>
         <v>111</v>
@@ -21015,11 +21025,11 @@
       <c r="I117" s="138"/>
       <c r="J117" s="164">
         <f t="shared" ca="1" si="30"/>
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="K117" s="47">
         <f t="shared" ca="1" si="31"/>
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="L117" s="164" t="s">
         <v>1004</v>
@@ -21082,7 +21092,7 @@
         <v/>
       </c>
     </row>
-    <row r="118" spans="1:35" s="9" customFormat="1" ht="78.75">
+    <row r="118" spans="1:35" s="9" customFormat="1" ht="78.75" hidden="1">
       <c r="A118" s="33">
         <f t="shared" si="19"/>
         <v>112</v>
@@ -21174,7 +21184,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:35" s="9" customFormat="1" ht="47.25">
+    <row r="119" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
       <c r="A119" s="33">
         <f t="shared" si="19"/>
         <v>113</v>
@@ -21280,7 +21290,7 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:35" s="9" customFormat="1" ht="63">
+    <row r="120" spans="1:35" s="9" customFormat="1" ht="63" hidden="1">
       <c r="A120" s="33">
         <f t="shared" si="19"/>
         <v>114</v>
@@ -21386,7 +21396,7 @@
         <v>YES</v>
       </c>
     </row>
-    <row r="121" spans="1:35" s="9" customFormat="1" ht="63">
+    <row r="121" spans="1:35" s="9" customFormat="1" ht="63" hidden="1">
       <c r="A121" s="33">
         <f t="shared" si="19"/>
         <v>115</v>
@@ -21478,7 +21488,7 @@
         <v/>
       </c>
     </row>
-    <row r="122" spans="1:35" s="9" customFormat="1" ht="63">
+    <row r="122" spans="1:35" s="9" customFormat="1" ht="63" hidden="1">
       <c r="A122" s="33">
         <f t="shared" si="19"/>
         <v>116</v>
@@ -21582,7 +21592,7 @@
         <v>YES</v>
       </c>
     </row>
-    <row r="123" spans="1:35" s="9" customFormat="1" ht="110.25">
+    <row r="123" spans="1:35" s="9" customFormat="1" ht="110.25" hidden="1">
       <c r="A123" s="33">
         <f t="shared" si="19"/>
         <v>117</v>
@@ -21706,11 +21716,11 @@
         <v>3</v>
       </c>
       <c r="J124" s="164">
-        <f t="shared" ca="1" si="30"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="K124" s="47">
-        <f t="shared" ca="1" si="31"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="L124" s="164"/>
@@ -21733,8 +21743,12 @@
       <c r="U124" s="188">
         <v>46303</v>
       </c>
-      <c r="V124" s="29"/>
-      <c r="W124" s="188"/>
+      <c r="V124" s="29">
+        <v>46275</v>
+      </c>
+      <c r="W124" s="188">
+        <v>46304</v>
+      </c>
       <c r="X124" s="235" t="s">
         <v>240</v>
       </c>
@@ -21776,7 +21790,7 @@
         <v/>
       </c>
     </row>
-    <row r="125" spans="1:35" s="9" customFormat="1" ht="47.25">
+    <row r="125" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
       <c r="A125" s="33">
         <f t="shared" si="19"/>
         <v>119</v>
@@ -21882,7 +21896,7 @@
         <v/>
       </c>
     </row>
-    <row r="126" spans="1:35" s="9" customFormat="1" ht="110.25">
+    <row r="126" spans="1:35" s="9" customFormat="1" ht="110.25" hidden="1">
       <c r="A126" s="33">
         <f t="shared" si="19"/>
         <v>120</v>
@@ -21988,7 +22002,7 @@
         <v>YES</v>
       </c>
     </row>
-    <row r="127" spans="1:35" s="9" customFormat="1" ht="78.75">
+    <row r="127" spans="1:35" s="9" customFormat="1" ht="78.75" hidden="1">
       <c r="A127" s="33">
         <f t="shared" si="19"/>
         <v>121</v>
@@ -22088,7 +22102,7 @@
         <v/>
       </c>
     </row>
-    <row r="128" spans="1:35" s="9" customFormat="1" ht="47.25">
+    <row r="128" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
       <c r="A128" s="33">
         <f t="shared" si="19"/>
         <v>122</v>
@@ -22119,7 +22133,7 @@
       <c r="I128" s="138"/>
       <c r="J128" s="164">
         <f t="shared" ca="1" si="30"/>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K128" s="47">
         <f t="shared" ca="1" si="31"/>
@@ -22176,7 +22190,7 @@
         <v/>
       </c>
     </row>
-    <row r="129" spans="1:35" s="9" customFormat="1" ht="47.25">
+    <row r="129" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
       <c r="A129" s="33">
         <f t="shared" si="19"/>
         <v>123</v>
@@ -22207,7 +22221,7 @@
       <c r="I129" s="138"/>
       <c r="J129" s="164">
         <f t="shared" ca="1" si="30"/>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K129" s="47">
         <f t="shared" ca="1" si="31"/>
@@ -22264,7 +22278,7 @@
         <v/>
       </c>
     </row>
-    <row r="130" spans="1:35" s="9" customFormat="1" ht="47.25">
+    <row r="130" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
       <c r="A130" s="33">
         <f t="shared" si="19"/>
         <v>124</v>
@@ -22295,7 +22309,7 @@
       <c r="I130" s="138"/>
       <c r="J130" s="164">
         <f t="shared" ca="1" si="30"/>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K130" s="47">
         <f t="shared" ca="1" si="31"/>
@@ -22352,7 +22366,7 @@
         <v/>
       </c>
     </row>
-    <row r="131" spans="1:35" s="9" customFormat="1" ht="47.25">
+    <row r="131" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
       <c r="A131" s="33">
         <f t="shared" si="19"/>
         <v>125</v>
@@ -22383,7 +22397,7 @@
       <c r="I131" s="138"/>
       <c r="J131" s="164">
         <f t="shared" ca="1" si="30"/>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K131" s="47">
         <f t="shared" ca="1" si="31"/>
@@ -22440,7 +22454,7 @@
         <v/>
       </c>
     </row>
-    <row r="132" spans="1:35" s="9" customFormat="1" ht="47.25">
+    <row r="132" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
       <c r="A132" s="33">
         <f t="shared" si="19"/>
         <v>126</v>
@@ -22471,7 +22485,7 @@
       <c r="I132" s="138"/>
       <c r="J132" s="164">
         <f t="shared" ca="1" si="30"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K132" s="47">
         <f t="shared" ca="1" si="31"/>
@@ -22528,7 +22542,7 @@
         <v/>
       </c>
     </row>
-    <row r="133" spans="1:35" s="9" customFormat="1" ht="47.25">
+    <row r="133" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
       <c r="A133" s="33">
         <f t="shared" si="19"/>
         <v>127</v>
@@ -22559,7 +22573,7 @@
       <c r="I133" s="138"/>
       <c r="J133" s="164">
         <f t="shared" ca="1" si="30"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K133" s="47">
         <f t="shared" ca="1" si="31"/>
@@ -22616,7 +22630,7 @@
         <v/>
       </c>
     </row>
-    <row r="134" spans="1:35" s="9" customFormat="1" ht="47.25">
+    <row r="134" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
       <c r="A134" s="33">
         <f t="shared" si="19"/>
         <v>128</v>
@@ -22647,7 +22661,7 @@
       <c r="I134" s="138"/>
       <c r="J134" s="164">
         <f t="shared" ca="1" si="30"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K134" s="47">
         <f t="shared" ca="1" si="31"/>
@@ -22704,7 +22718,7 @@
         <v/>
       </c>
     </row>
-    <row r="135" spans="1:35" s="9" customFormat="1" ht="47.25">
+    <row r="135" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
       <c r="A135" s="33">
         <f t="shared" si="19"/>
         <v>129</v>
@@ -22735,7 +22749,7 @@
       <c r="I135" s="138"/>
       <c r="J135" s="164">
         <f t="shared" ca="1" si="30"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K135" s="47">
         <f t="shared" ca="1" si="31"/>
@@ -22792,7 +22806,7 @@
         <v/>
       </c>
     </row>
-    <row r="136" spans="1:35" s="9" customFormat="1">
+    <row r="136" spans="1:35" s="9" customFormat="1" hidden="1">
       <c r="A136" s="33"/>
       <c r="B136" s="330"/>
       <c r="C136" s="164"/>
@@ -22834,7 +22848,7 @@
         <v/>
       </c>
     </row>
-    <row r="137" spans="1:35" s="9" customFormat="1" ht="16.5" thickBot="1">
+    <row r="137" spans="1:35" s="9" customFormat="1" ht="16.5" hidden="1" thickBot="1">
       <c r="A137" s="347"/>
       <c r="B137" s="338"/>
       <c r="C137" s="178"/>
@@ -22883,29 +22897,29 @@
       <c r="C139" s="166" t="s">
         <v>20</v>
       </c>
-      <c r="D139" s="376" t="s">
+      <c r="D139" s="405" t="s">
         <v>21</v>
       </c>
-      <c r="E139" s="376"/>
-      <c r="F139" s="377"/>
+      <c r="E139" s="405"/>
+      <c r="F139" s="406"/>
       <c r="G139" s="46"/>
       <c r="H139" s="68"/>
-      <c r="I139" s="356" t="s">
+      <c r="I139" s="357" t="s">
         <v>14</v>
       </c>
-      <c r="J139" s="357"/>
-      <c r="K139" s="357"/>
-      <c r="L139" s="357"/>
-      <c r="M139" s="357"/>
-      <c r="N139" s="358"/>
-      <c r="O139" s="362" t="s">
+      <c r="J139" s="358"/>
+      <c r="K139" s="358"/>
+      <c r="L139" s="358"/>
+      <c r="M139" s="358"/>
+      <c r="N139" s="359"/>
+      <c r="O139" s="360" t="s">
         <v>7</v>
       </c>
-      <c r="P139" s="363"/>
-      <c r="Q139" s="362" t="s">
+      <c r="P139" s="361"/>
+      <c r="Q139" s="360" t="s">
         <v>109</v>
       </c>
-      <c r="R139" s="363"/>
+      <c r="R139" s="361"/>
       <c r="S139" s="1"/>
       <c r="T139" s="1"/>
       <c r="U139" s="140"/>
@@ -22927,26 +22941,26 @@
       <c r="C140" s="167" t="s">
         <v>109</v>
       </c>
-      <c r="D140" s="354" t="s">
+      <c r="D140" s="424" t="s">
         <v>111</v>
       </c>
-      <c r="E140" s="354"/>
-      <c r="F140" s="355"/>
+      <c r="E140" s="424"/>
+      <c r="F140" s="425"/>
       <c r="G140" s="46"/>
       <c r="H140" s="46"/>
-      <c r="I140" s="356" t="s">
+      <c r="I140" s="357" t="s">
         <v>19</v>
       </c>
-      <c r="J140" s="357"/>
-      <c r="K140" s="357"/>
-      <c r="L140" s="358"/>
+      <c r="J140" s="358"/>
+      <c r="K140" s="358"/>
+      <c r="L140" s="359"/>
       <c r="M140" s="105">
         <f t="shared" ref="M140:M145" ca="1" si="84">N140/$N$140</f>
         <v>1</v>
       </c>
       <c r="N140" s="106">
         <f ca="1">SUM($N$141:$N$145)</f>
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="O140" s="102" t="s">
         <v>15</v>
@@ -22983,22 +22997,22 @@
       <c r="C141" s="167" t="s">
         <v>22</v>
       </c>
-      <c r="D141" s="354" t="s">
+      <c r="D141" s="424" t="s">
         <v>23</v>
       </c>
-      <c r="E141" s="354"/>
-      <c r="F141" s="355"/>
+      <c r="E141" s="424"/>
+      <c r="F141" s="425"/>
       <c r="G141" s="70"/>
       <c r="H141" s="6"/>
-      <c r="I141" s="379" t="s">
+      <c r="I141" s="373" t="s">
         <v>66</v>
       </c>
-      <c r="J141" s="380"/>
-      <c r="K141" s="380"/>
-      <c r="L141" s="381"/>
+      <c r="J141" s="374"/>
+      <c r="K141" s="374"/>
+      <c r="L141" s="375"/>
       <c r="M141" s="107">
         <f t="shared" ca="1" si="84"/>
-        <v>0.50370370370370365</v>
+        <v>0.5074626865671642</v>
       </c>
       <c r="N141" s="108">
         <f>COUNTIF($I$7:$I$137,"A")</f>
@@ -23041,21 +23055,21 @@
       <c r="C142" s="167" t="s">
         <v>24</v>
       </c>
-      <c r="D142" s="354" t="s">
+      <c r="D142" s="424" t="s">
         <v>25</v>
       </c>
-      <c r="E142" s="354"/>
-      <c r="F142" s="355"/>
+      <c r="E142" s="424"/>
+      <c r="F142" s="425"/>
       <c r="H142" s="6"/>
-      <c r="I142" s="382" t="s">
+      <c r="I142" s="376" t="s">
         <v>67</v>
       </c>
-      <c r="J142" s="383"/>
-      <c r="K142" s="383"/>
-      <c r="L142" s="384"/>
+      <c r="J142" s="377"/>
+      <c r="K142" s="377"/>
+      <c r="L142" s="378"/>
       <c r="M142" s="109">
         <f t="shared" ca="1" si="84"/>
-        <v>0.1037037037037037</v>
+        <v>0.1044776119402985</v>
       </c>
       <c r="N142" s="110">
         <f>COUNTIF($I$7:$I$137,"B")</f>
@@ -23098,22 +23112,22 @@
       <c r="C143" s="167" t="s">
         <v>26</v>
       </c>
-      <c r="D143" s="354" t="s">
+      <c r="D143" s="424" t="s">
         <v>27</v>
       </c>
-      <c r="E143" s="354"/>
-      <c r="F143" s="355"/>
+      <c r="E143" s="424"/>
+      <c r="F143" s="425"/>
       <c r="G143" s="71"/>
       <c r="H143" s="6"/>
-      <c r="I143" s="385" t="s">
+      <c r="I143" s="379" t="s">
         <v>68</v>
       </c>
-      <c r="J143" s="386"/>
-      <c r="K143" s="386"/>
-      <c r="L143" s="387"/>
+      <c r="J143" s="380"/>
+      <c r="K143" s="380"/>
+      <c r="L143" s="381"/>
       <c r="M143" s="111">
         <f t="shared" ca="1" si="84"/>
-        <v>0.2</v>
+        <v>0.20149253731343283</v>
       </c>
       <c r="N143" s="112">
         <f>COUNTIF($I$7:$I$137,"C")</f>
@@ -23156,29 +23170,29 @@
       <c r="C144" s="168" t="s">
         <v>28</v>
       </c>
-      <c r="D144" s="354" t="s">
+      <c r="D144" s="424" t="s">
         <v>29</v>
       </c>
-      <c r="E144" s="354"/>
-      <c r="F144" s="355"/>
+      <c r="E144" s="424"/>
+      <c r="F144" s="425"/>
       <c r="G144" s="72"/>
-      <c r="I144" s="388" t="s">
+      <c r="I144" s="382" t="s">
         <v>70</v>
       </c>
-      <c r="J144" s="389"/>
-      <c r="K144" s="389"/>
-      <c r="L144" s="390"/>
+      <c r="J144" s="383"/>
+      <c r="K144" s="383"/>
+      <c r="L144" s="384"/>
       <c r="M144" s="114">
         <f t="shared" ca="1" si="84"/>
-        <v>8.1481481481481488E-2</v>
+        <v>7.4626865671641784E-2</v>
       </c>
       <c r="N144" s="115">
         <f ca="1">SUM(O144:P144)</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O144" s="98">
         <f ca="1">COUNTIFS($J$7:$J$137,"&lt;=21",$V$7:$V$137,"",$L$7:$L$137,"&lt;&gt;X")</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P144" s="50">
         <f ca="1">COUNTIFS($J$7:$J$137,"&gt;21",$V$7:$V$137,"",$L$7:$L$137,"&lt;&gt;X")</f>
@@ -23215,21 +23229,21 @@
       <c r="C145" s="168" t="s">
         <v>30</v>
       </c>
-      <c r="D145" s="354" t="s">
+      <c r="D145" s="424" t="s">
         <v>31</v>
       </c>
-      <c r="E145" s="354"/>
-      <c r="F145" s="355"/>
+      <c r="E145" s="424"/>
+      <c r="F145" s="425"/>
       <c r="H145" s="6"/>
-      <c r="I145" s="391" t="s">
+      <c r="I145" s="354" t="s">
         <v>71</v>
       </c>
-      <c r="J145" s="392"/>
-      <c r="K145" s="392"/>
-      <c r="L145" s="393"/>
+      <c r="J145" s="355"/>
+      <c r="K145" s="355"/>
+      <c r="L145" s="356"/>
       <c r="M145" s="113">
         <f t="shared" ca="1" si="84"/>
-        <v>0.1111111111111111</v>
+        <v>0.11194029850746269</v>
       </c>
       <c r="N145" s="97">
         <f>COUNTIFS($L$7:$L$137,"X")</f>
@@ -23246,11 +23260,11 @@
       <c r="C146" s="168" t="s">
         <v>32</v>
       </c>
-      <c r="D146" s="354" t="s">
+      <c r="D146" s="424" t="s">
         <v>33</v>
       </c>
-      <c r="E146" s="354"/>
-      <c r="F146" s="355"/>
+      <c r="E146" s="424"/>
+      <c r="F146" s="425"/>
       <c r="H146" s="1" t="s">
         <v>11</v>
       </c>
@@ -23259,11 +23273,11 @@
       <c r="C147" s="167" t="s">
         <v>34</v>
       </c>
-      <c r="D147" s="354" t="s">
+      <c r="D147" s="424" t="s">
         <v>35</v>
       </c>
-      <c r="E147" s="354"/>
-      <c r="F147" s="355"/>
+      <c r="E147" s="424"/>
+      <c r="F147" s="425"/>
       <c r="H147" s="13"/>
       <c r="I147" s="141"/>
       <c r="J147" s="141"/>
@@ -23291,14 +23305,14 @@
       <c r="AI147" s="1"/>
     </row>
     <row r="148" spans="1:35">
-      <c r="C148" s="394" t="s">
+      <c r="C148" s="385" t="s">
         <v>75</v>
       </c>
-      <c r="D148" s="350" t="s">
+      <c r="D148" s="387" t="s">
         <v>76</v>
       </c>
-      <c r="E148" s="350"/>
-      <c r="F148" s="351"/>
+      <c r="E148" s="387"/>
+      <c r="F148" s="388"/>
       <c r="H148" s="13"/>
       <c r="J148" s="141"/>
       <c r="K148" s="13"/>
@@ -23325,10 +23339,10 @@
       <c r="AI148" s="1"/>
     </row>
     <row r="149" spans="1:35" ht="16.5" thickBot="1">
-      <c r="C149" s="395"/>
-      <c r="D149" s="352"/>
-      <c r="E149" s="352"/>
-      <c r="F149" s="353"/>
+      <c r="C149" s="386"/>
+      <c r="D149" s="389"/>
+      <c r="E149" s="389"/>
+      <c r="F149" s="390"/>
       <c r="H149" s="13"/>
       <c r="I149" s="141"/>
       <c r="J149" s="141"/>
@@ -23383,12 +23397,12 @@
       <c r="AI150" s="1"/>
     </row>
     <row r="151" spans="1:35">
-      <c r="C151" s="378" t="s">
+      <c r="C151" s="372" t="s">
         <v>41</v>
       </c>
-      <c r="D151" s="378"/>
-      <c r="E151" s="378"/>
-      <c r="F151" s="378"/>
+      <c r="D151" s="372"/>
+      <c r="E151" s="372"/>
+      <c r="F151" s="372"/>
       <c r="H151" s="13"/>
       <c r="I151" s="141"/>
       <c r="J151" s="141"/>
@@ -23419,11 +23433,11 @@
       <c r="C152" s="169" t="s">
         <v>8</v>
       </c>
-      <c r="D152" s="396" t="s">
+      <c r="D152" s="412" t="s">
         <v>91</v>
       </c>
-      <c r="E152" s="396"/>
-      <c r="F152" s="396"/>
+      <c r="E152" s="412"/>
+      <c r="F152" s="412"/>
       <c r="H152" s="13"/>
       <c r="I152" s="141"/>
       <c r="J152" s="141"/>
@@ -23454,11 +23468,11 @@
       <c r="C153" s="169" t="s">
         <v>8</v>
       </c>
-      <c r="D153" s="396" t="s">
+      <c r="D153" s="412" t="s">
         <v>92</v>
       </c>
-      <c r="E153" s="396"/>
-      <c r="F153" s="396"/>
+      <c r="E153" s="412"/>
+      <c r="F153" s="412"/>
       <c r="H153" s="13"/>
       <c r="I153" s="141"/>
       <c r="J153" s="141"/>
@@ -23489,11 +23503,11 @@
       <c r="C154" s="169" t="s">
         <v>8</v>
       </c>
-      <c r="D154" s="396" t="s">
+      <c r="D154" s="412" t="s">
         <v>93</v>
       </c>
-      <c r="E154" s="396"/>
-      <c r="F154" s="396"/>
+      <c r="E154" s="412"/>
+      <c r="F154" s="412"/>
       <c r="H154" s="13"/>
       <c r="I154" s="141"/>
       <c r="J154" s="141"/>
@@ -23548,12 +23562,12 @@
       <c r="AI155" s="1"/>
     </row>
     <row r="156" spans="1:35" ht="16.5" thickBot="1">
-      <c r="C156" s="402" t="s">
+      <c r="C156" s="416" t="s">
         <v>96</v>
       </c>
-      <c r="D156" s="403"/>
-      <c r="E156" s="403"/>
-      <c r="F156" s="404"/>
+      <c r="D156" s="417"/>
+      <c r="E156" s="417"/>
+      <c r="F156" s="418"/>
       <c r="H156" s="13"/>
       <c r="I156" s="141"/>
       <c r="J156" s="141"/>
@@ -23584,11 +23598,11 @@
       <c r="C157" s="212" t="s">
         <v>81</v>
       </c>
-      <c r="D157" s="405" t="s">
+      <c r="D157" s="419" t="s">
         <v>97</v>
       </c>
-      <c r="E157" s="405"/>
-      <c r="F157" s="406"/>
+      <c r="E157" s="419"/>
+      <c r="F157" s="420"/>
       <c r="H157" s="13"/>
       <c r="I157" s="141"/>
       <c r="J157" s="141"/>
@@ -23619,109 +23633,157 @@
       <c r="C158" s="213" t="s">
         <v>82</v>
       </c>
-      <c r="D158" s="397" t="s">
+      <c r="D158" s="410" t="s">
         <v>98</v>
       </c>
-      <c r="E158" s="397"/>
-      <c r="F158" s="398"/>
+      <c r="E158" s="410"/>
+      <c r="F158" s="411"/>
     </row>
     <row r="159" spans="1:35">
       <c r="C159" s="213" t="s">
         <v>83</v>
       </c>
-      <c r="D159" s="397" t="s">
+      <c r="D159" s="410" t="s">
         <v>99</v>
       </c>
-      <c r="E159" s="397"/>
-      <c r="F159" s="398"/>
+      <c r="E159" s="410"/>
+      <c r="F159" s="411"/>
     </row>
     <row r="160" spans="1:35">
       <c r="C160" s="214" t="s">
         <v>84</v>
       </c>
-      <c r="D160" s="397" t="s">
+      <c r="D160" s="410" t="s">
         <v>100</v>
       </c>
-      <c r="E160" s="397"/>
-      <c r="F160" s="398"/>
+      <c r="E160" s="410"/>
+      <c r="F160" s="411"/>
     </row>
     <row r="161" spans="3:6">
       <c r="C161" s="214" t="s">
         <v>85</v>
       </c>
-      <c r="D161" s="397" t="s">
+      <c r="D161" s="410" t="s">
         <v>101</v>
       </c>
-      <c r="E161" s="397"/>
-      <c r="F161" s="398"/>
+      <c r="E161" s="410"/>
+      <c r="F161" s="411"/>
     </row>
     <row r="162" spans="3:6" ht="18.75">
       <c r="C162" s="214" t="s">
         <v>86</v>
       </c>
-      <c r="D162" s="397" t="s">
+      <c r="D162" s="410" t="s">
         <v>102</v>
       </c>
-      <c r="E162" s="397"/>
-      <c r="F162" s="398"/>
+      <c r="E162" s="410"/>
+      <c r="F162" s="411"/>
     </row>
     <row r="163" spans="3:6" ht="18.75">
       <c r="C163" s="213" t="s">
         <v>87</v>
       </c>
-      <c r="D163" s="397" t="s">
+      <c r="D163" s="410" t="s">
         <v>103</v>
       </c>
-      <c r="E163" s="397"/>
-      <c r="F163" s="398"/>
+      <c r="E163" s="410"/>
+      <c r="F163" s="411"/>
     </row>
     <row r="164" spans="3:6">
       <c r="C164" s="215" t="s">
         <v>88</v>
       </c>
-      <c r="D164" s="399" t="s">
+      <c r="D164" s="413" t="s">
         <v>104</v>
       </c>
-      <c r="E164" s="400"/>
-      <c r="F164" s="401"/>
+      <c r="E164" s="414"/>
+      <c r="F164" s="415"/>
     </row>
     <row r="165" spans="3:6" ht="18.75">
       <c r="C165" s="215" t="s">
         <v>89</v>
       </c>
-      <c r="D165" s="397" t="s">
+      <c r="D165" s="410" t="s">
         <v>105</v>
       </c>
-      <c r="E165" s="397"/>
-      <c r="F165" s="398"/>
+      <c r="E165" s="410"/>
+      <c r="F165" s="411"/>
     </row>
     <row r="166" spans="3:6">
       <c r="C166" s="213" t="s">
         <v>90</v>
       </c>
-      <c r="D166" s="397" t="s">
+      <c r="D166" s="410" t="s">
         <v>106</v>
       </c>
-      <c r="E166" s="397"/>
-      <c r="F166" s="398"/>
+      <c r="E166" s="410"/>
+      <c r="F166" s="411"/>
     </row>
     <row r="167" spans="3:6" ht="16.5" thickBot="1">
       <c r="C167" s="216" t="s">
         <v>94</v>
       </c>
-      <c r="D167" s="373" t="s">
+      <c r="D167" s="421" t="s">
         <v>107</v>
       </c>
-      <c r="E167" s="374"/>
-      <c r="F167" s="375"/>
+      <c r="E167" s="422"/>
+      <c r="F167" s="423"/>
     </row>
   </sheetData>
   <autoFilter ref="A6:AE137" xr:uid="{C724CDAB-378C-47DB-9F45-08EE3BFB6E8B}">
+    <filterColumn colId="4">
+      <filters>
+        <filter val="LTIA-5.10-VIETUR-70000-RFA-MAS-0821"/>
+      </filters>
+    </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A7:AE69">
       <sortCondition ref="T6:T69"/>
     </sortState>
   </autoFilter>
   <mergeCells count="59">
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="D148:F149"/>
+    <mergeCell ref="D140:F140"/>
+    <mergeCell ref="I140:L140"/>
+    <mergeCell ref="AA4:AD4"/>
+    <mergeCell ref="Q139:R139"/>
+    <mergeCell ref="D145:F145"/>
+    <mergeCell ref="D146:F146"/>
+    <mergeCell ref="D147:F147"/>
+    <mergeCell ref="S4:U4"/>
+    <mergeCell ref="L4:L5"/>
+    <mergeCell ref="Q4:R4"/>
+    <mergeCell ref="K4:K5"/>
+    <mergeCell ref="Y4:Z4"/>
+    <mergeCell ref="D167:F167"/>
+    <mergeCell ref="D139:F139"/>
+    <mergeCell ref="C151:F151"/>
+    <mergeCell ref="O139:P139"/>
+    <mergeCell ref="I139:N139"/>
+    <mergeCell ref="I141:L141"/>
+    <mergeCell ref="I142:L142"/>
+    <mergeCell ref="I143:L143"/>
+    <mergeCell ref="I144:L144"/>
+    <mergeCell ref="I145:L145"/>
+    <mergeCell ref="C148:C149"/>
+    <mergeCell ref="D141:F141"/>
+    <mergeCell ref="D142:F142"/>
+    <mergeCell ref="D143:F143"/>
+    <mergeCell ref="D144:F144"/>
+    <mergeCell ref="D152:F152"/>
+    <mergeCell ref="D166:F166"/>
+    <mergeCell ref="D153:F153"/>
+    <mergeCell ref="D154:F154"/>
+    <mergeCell ref="D161:F161"/>
+    <mergeCell ref="D162:F162"/>
+    <mergeCell ref="D163:F163"/>
+    <mergeCell ref="D164:F164"/>
+    <mergeCell ref="D165:F165"/>
+    <mergeCell ref="C156:F156"/>
+    <mergeCell ref="D157:F157"/>
+    <mergeCell ref="D158:F158"/>
+    <mergeCell ref="D159:F159"/>
+    <mergeCell ref="D160:F160"/>
     <mergeCell ref="AG5:AG6"/>
     <mergeCell ref="AH5:AH6"/>
     <mergeCell ref="AI5:AI6"/>
@@ -23738,49 +23800,6 @@
     <mergeCell ref="V4:X4"/>
     <mergeCell ref="M4:N4"/>
     <mergeCell ref="O4:P4"/>
-    <mergeCell ref="D166:F166"/>
-    <mergeCell ref="D153:F153"/>
-    <mergeCell ref="D154:F154"/>
-    <mergeCell ref="D161:F161"/>
-    <mergeCell ref="D162:F162"/>
-    <mergeCell ref="D163:F163"/>
-    <mergeCell ref="D164:F164"/>
-    <mergeCell ref="D165:F165"/>
-    <mergeCell ref="C156:F156"/>
-    <mergeCell ref="D157:F157"/>
-    <mergeCell ref="D158:F158"/>
-    <mergeCell ref="D159:F159"/>
-    <mergeCell ref="D160:F160"/>
-    <mergeCell ref="D167:F167"/>
-    <mergeCell ref="D139:F139"/>
-    <mergeCell ref="C151:F151"/>
-    <mergeCell ref="O139:P139"/>
-    <mergeCell ref="I139:N139"/>
-    <mergeCell ref="I141:L141"/>
-    <mergeCell ref="I142:L142"/>
-    <mergeCell ref="I143:L143"/>
-    <mergeCell ref="I144:L144"/>
-    <mergeCell ref="I145:L145"/>
-    <mergeCell ref="C148:C149"/>
-    <mergeCell ref="D141:F141"/>
-    <mergeCell ref="D142:F142"/>
-    <mergeCell ref="D143:F143"/>
-    <mergeCell ref="D144:F144"/>
-    <mergeCell ref="D152:F152"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="D148:F149"/>
-    <mergeCell ref="D140:F140"/>
-    <mergeCell ref="I140:L140"/>
-    <mergeCell ref="AA4:AD4"/>
-    <mergeCell ref="Q139:R139"/>
-    <mergeCell ref="D145:F145"/>
-    <mergeCell ref="D146:F146"/>
-    <mergeCell ref="D147:F147"/>
-    <mergeCell ref="S4:U4"/>
-    <mergeCell ref="L4:L5"/>
-    <mergeCell ref="Q4:R4"/>
-    <mergeCell ref="K4:K5"/>
-    <mergeCell ref="Y4:Z4"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="A7:AE137 AG7:AI137">
@@ -24360,7 +24379,7 @@
       </c>
       <c r="I1" s="176">
         <f ca="1">TODAY()</f>
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="J1" s="131"/>
       <c r="K1" s="197"/>
@@ -24445,88 +24464,88 @@
       <c r="AD3" s="159"/>
     </row>
     <row r="4" spans="1:35" s="5" customFormat="1" ht="36" customHeight="1" thickBot="1">
-      <c r="A4" s="408" t="s">
+      <c r="A4" s="397" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="348" t="s">
+      <c r="B4" s="407" t="s">
         <v>515</v>
       </c>
-      <c r="C4" s="414" t="s">
+      <c r="C4" s="403" t="s">
         <v>45</v>
       </c>
-      <c r="D4" s="369" t="s">
+      <c r="D4" s="362" t="s">
         <v>46</v>
       </c>
-      <c r="E4" s="412" t="s">
+      <c r="E4" s="399" t="s">
         <v>47</v>
       </c>
-      <c r="F4" s="369" t="s">
+      <c r="F4" s="362" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="410" t="s">
+      <c r="G4" s="401" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="366" t="s">
+      <c r="H4" s="364" t="s">
         <v>48</v>
       </c>
-      <c r="I4" s="366" t="s">
+      <c r="I4" s="364" t="s">
         <v>49</v>
       </c>
-      <c r="J4" s="369" t="s">
+      <c r="J4" s="362" t="s">
         <v>78</v>
       </c>
-      <c r="K4" s="366" t="s">
+      <c r="K4" s="364" t="s">
         <v>80</v>
       </c>
-      <c r="L4" s="364" t="s">
+      <c r="L4" s="366" t="s">
         <v>53</v>
       </c>
-      <c r="M4" s="365"/>
+      <c r="M4" s="367"/>
       <c r="N4" s="368" t="s">
         <v>55</v>
       </c>
-      <c r="O4" s="365"/>
+      <c r="O4" s="367"/>
       <c r="P4" s="368" t="s">
         <v>72</v>
       </c>
-      <c r="Q4" s="365"/>
-      <c r="R4" s="364" t="s">
+      <c r="Q4" s="367"/>
+      <c r="R4" s="366" t="s">
         <v>53</v>
       </c>
-      <c r="S4" s="364"/>
-      <c r="T4" s="365"/>
+      <c r="S4" s="366"/>
+      <c r="T4" s="367"/>
       <c r="U4" s="368" t="s">
         <v>55</v>
       </c>
-      <c r="V4" s="364"/>
-      <c r="W4" s="365"/>
-      <c r="X4" s="371" t="s">
+      <c r="V4" s="366"/>
+      <c r="W4" s="367"/>
+      <c r="X4" s="393" t="s">
         <v>72</v>
       </c>
-      <c r="Y4" s="417"/>
-      <c r="Z4" s="371" t="s">
+      <c r="Y4" s="394"/>
+      <c r="Z4" s="393" t="s">
         <v>112</v>
       </c>
-      <c r="AA4" s="360"/>
-      <c r="AB4" s="360"/>
-      <c r="AC4" s="361"/>
-      <c r="AD4" s="369" t="s">
+      <c r="AA4" s="395"/>
+      <c r="AB4" s="395"/>
+      <c r="AC4" s="396"/>
+      <c r="AD4" s="362" t="s">
         <v>79</v>
       </c>
       <c r="AG4" s="236"/>
     </row>
     <row r="5" spans="1:35" ht="78.75">
-      <c r="A5" s="409"/>
-      <c r="B5" s="349"/>
-      <c r="C5" s="415"/>
-      <c r="D5" s="370"/>
-      <c r="E5" s="413"/>
-      <c r="F5" s="370"/>
-      <c r="G5" s="411"/>
-      <c r="H5" s="367"/>
-      <c r="I5" s="367"/>
-      <c r="J5" s="370"/>
-      <c r="K5" s="367"/>
+      <c r="A5" s="398"/>
+      <c r="B5" s="408"/>
+      <c r="C5" s="404"/>
+      <c r="D5" s="369"/>
+      <c r="E5" s="400"/>
+      <c r="F5" s="369"/>
+      <c r="G5" s="402"/>
+      <c r="H5" s="365"/>
+      <c r="I5" s="365"/>
+      <c r="J5" s="369"/>
+      <c r="K5" s="365"/>
       <c r="L5" s="79" t="s">
         <v>52</v>
       </c>
@@ -24581,14 +24600,14 @@
       <c r="AC5" s="250" t="s">
         <v>118</v>
       </c>
-      <c r="AD5" s="416"/>
-      <c r="AG5" s="422" t="s">
+      <c r="AD5" s="363"/>
+      <c r="AG5" s="348" t="s">
         <v>119</v>
       </c>
-      <c r="AH5" s="424" t="s">
+      <c r="AH5" s="350" t="s">
         <v>120</v>
       </c>
-      <c r="AI5" s="426" t="s">
+      <c r="AI5" s="352" t="s">
         <v>121</v>
       </c>
     </row>
@@ -24623,9 +24642,9 @@
       <c r="AB6" s="86"/>
       <c r="AC6" s="86"/>
       <c r="AD6" s="74"/>
-      <c r="AG6" s="423"/>
-      <c r="AH6" s="425"/>
-      <c r="AI6" s="427"/>
+      <c r="AG6" s="349"/>
+      <c r="AH6" s="351"/>
+      <c r="AI6" s="353"/>
     </row>
     <row r="7" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A7" s="33">
@@ -25301,7 +25320,7 @@
       </c>
       <c r="AC12" s="183">
         <f t="shared" ca="1" si="7"/>
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="AD12" s="92"/>
       <c r="AG12" s="238" t="str">
@@ -25527,7 +25546,7 @@
       </c>
       <c r="AC14" s="183">
         <f t="shared" ca="1" si="7"/>
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="AD14" s="92"/>
       <c r="AG14" s="238" t="str">
@@ -25753,7 +25772,7 @@
       </c>
       <c r="AC16" s="183">
         <f t="shared" ca="1" si="7"/>
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="AD16" s="92"/>
       <c r="AG16" s="238" t="str">
@@ -25776,7 +25795,7 @@
         <v>YES</v>
       </c>
     </row>
-    <row r="17" spans="1:35" s="9" customFormat="1" ht="110.25">
+    <row r="17" spans="1:35" s="9" customFormat="1" ht="94.5">
       <c r="A17" s="33">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -25866,7 +25885,7 @@
       </c>
       <c r="AC17" s="183">
         <f t="shared" ca="1" si="7"/>
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="AD17" s="92"/>
       <c r="AG17" s="238" t="str">
@@ -25979,7 +25998,7 @@
       </c>
       <c r="AC18" s="183">
         <f t="shared" ca="1" si="7"/>
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="AD18" s="92"/>
       <c r="AG18" s="238" t="str">
@@ -26554,7 +26573,7 @@
       </c>
       <c r="AC23" s="183">
         <f t="shared" ca="1" si="7"/>
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="AD23" s="92"/>
       <c r="AG23" s="238" t="str">
@@ -26667,7 +26686,7 @@
       </c>
       <c r="AC24" s="183">
         <f t="shared" ca="1" si="7"/>
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="AD24" s="92"/>
       <c r="AG24" s="238" t="str">
@@ -26778,7 +26797,7 @@
       </c>
       <c r="AC25" s="183">
         <f t="shared" ca="1" si="7"/>
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="AD25" s="92" t="s">
         <v>887</v>
@@ -26893,7 +26912,7 @@
       </c>
       <c r="AC26" s="183">
         <f t="shared" ca="1" si="7"/>
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="AD26" s="92"/>
       <c r="AG26" s="238" t="str">
@@ -27006,7 +27025,7 @@
       </c>
       <c r="AC27" s="183">
         <f t="shared" ca="1" si="7"/>
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="AD27" s="92"/>
       <c r="AG27" s="238" t="str">
@@ -27325,7 +27344,7 @@
       </c>
       <c r="AC30" s="183">
         <f t="shared" ca="1" si="7"/>
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="AD30" s="92" t="s">
         <v>593</v>
@@ -27380,11 +27399,11 @@
       </c>
       <c r="I31" s="164">
         <f ca="1">IF(ISBLANK($V31),_xlfn.DAYS($I$1,$T31),_xlfn.DAYS($V31,$T31))</f>
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="J31" s="47">
         <f t="shared" ca="1" si="4"/>
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="K31" s="164"/>
       <c r="L31" s="54" t="s">
@@ -27783,7 +27802,7 @@
       <c r="H35" s="138"/>
       <c r="I35" s="164">
         <f t="shared" ca="1" si="10"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J35" s="47">
         <f t="shared" ca="1" si="4"/>
@@ -27979,11 +27998,11 @@
       </c>
       <c r="I37" s="164">
         <f t="shared" ca="1" si="10"/>
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J37" s="47">
         <f t="shared" ca="1" si="4"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K37" s="164"/>
       <c r="L37" s="54" t="s">
@@ -28177,7 +28196,7 @@
       <c r="H39" s="138"/>
       <c r="I39" s="164">
         <f t="shared" ca="1" si="10"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J39" s="47">
         <f t="shared" ca="1" si="4"/>
@@ -28323,28 +28342,28 @@
       <c r="C43" s="166" t="s">
         <v>20</v>
       </c>
-      <c r="D43" s="376" t="s">
+      <c r="D43" s="405" t="s">
         <v>21</v>
       </c>
-      <c r="E43" s="377"/>
+      <c r="E43" s="406"/>
       <c r="F43" s="46"/>
       <c r="G43" s="46"/>
-      <c r="H43" s="356" t="s">
+      <c r="H43" s="357" t="s">
         <v>14</v>
       </c>
-      <c r="I43" s="357"/>
-      <c r="J43" s="357"/>
-      <c r="K43" s="357"/>
-      <c r="L43" s="357"/>
-      <c r="M43" s="358"/>
-      <c r="N43" s="362" t="s">
+      <c r="I43" s="358"/>
+      <c r="J43" s="358"/>
+      <c r="K43" s="358"/>
+      <c r="L43" s="358"/>
+      <c r="M43" s="359"/>
+      <c r="N43" s="360" t="s">
         <v>7</v>
       </c>
-      <c r="O43" s="363"/>
-      <c r="P43" s="362" t="s">
+      <c r="O43" s="361"/>
+      <c r="P43" s="360" t="s">
         <v>109</v>
       </c>
-      <c r="Q43" s="363"/>
+      <c r="Q43" s="361"/>
       <c r="R43" s="1"/>
       <c r="S43" s="1"/>
       <c r="T43" s="140"/>
@@ -28364,17 +28383,17 @@
       <c r="C44" s="195" t="s">
         <v>109</v>
       </c>
-      <c r="D44" s="420" t="s">
+      <c r="D44" s="391" t="s">
         <v>111</v>
       </c>
-      <c r="E44" s="421"/>
+      <c r="E44" s="392"/>
       <c r="F44" s="46"/>
-      <c r="H44" s="356" t="s">
+      <c r="H44" s="357" t="s">
         <v>18</v>
       </c>
-      <c r="I44" s="357"/>
-      <c r="J44" s="357"/>
-      <c r="K44" s="358"/>
+      <c r="I44" s="358"/>
+      <c r="J44" s="358"/>
+      <c r="K44" s="359"/>
       <c r="L44" s="105">
         <f ca="1">M44/$M$44</f>
         <v>1</v>
@@ -28416,18 +28435,18 @@
       <c r="C45" s="195" t="s">
         <v>36</v>
       </c>
-      <c r="D45" s="418" t="s">
+      <c r="D45" s="370" t="s">
         <v>37</v>
       </c>
-      <c r="E45" s="419"/>
+      <c r="E45" s="371"/>
       <c r="F45" s="69"/>
       <c r="G45" s="6"/>
-      <c r="H45" s="379" t="s">
+      <c r="H45" s="373" t="s">
         <v>66</v>
       </c>
-      <c r="I45" s="380"/>
-      <c r="J45" s="380"/>
-      <c r="K45" s="381"/>
+      <c r="I45" s="374"/>
+      <c r="J45" s="374"/>
+      <c r="K45" s="375"/>
       <c r="L45" s="107">
         <f ca="1">M45/$M$44</f>
         <v>2.8571428571428571E-2</v>
@@ -28468,21 +28487,21 @@
       <c r="AI45" s="11"/>
     </row>
     <row r="46" spans="1:35">
-      <c r="C46" s="394" t="s">
+      <c r="C46" s="385" t="s">
         <v>75</v>
       </c>
-      <c r="D46" s="350" t="s">
+      <c r="D46" s="387" t="s">
         <v>76</v>
       </c>
-      <c r="E46" s="351"/>
+      <c r="E46" s="388"/>
       <c r="F46" s="70"/>
       <c r="G46" s="6"/>
-      <c r="H46" s="382" t="s">
+      <c r="H46" s="376" t="s">
         <v>67</v>
       </c>
-      <c r="I46" s="383"/>
-      <c r="J46" s="383"/>
-      <c r="K46" s="384"/>
+      <c r="I46" s="377"/>
+      <c r="J46" s="377"/>
+      <c r="K46" s="378"/>
       <c r="L46" s="109">
         <f t="shared" ref="L46:L49" ca="1" si="21">M46/$M$44</f>
         <v>0.5714285714285714</v>
@@ -28523,17 +28542,17 @@
       <c r="AI46" s="11"/>
     </row>
     <row r="47" spans="1:35" ht="16.5" thickBot="1">
-      <c r="C47" s="395"/>
-      <c r="D47" s="352"/>
-      <c r="E47" s="353"/>
+      <c r="C47" s="386"/>
+      <c r="D47" s="389"/>
+      <c r="E47" s="390"/>
       <c r="F47" s="71"/>
       <c r="G47" s="6"/>
-      <c r="H47" s="385" t="s">
+      <c r="H47" s="379" t="s">
         <v>68</v>
       </c>
-      <c r="I47" s="386"/>
-      <c r="J47" s="386"/>
-      <c r="K47" s="387"/>
+      <c r="I47" s="380"/>
+      <c r="J47" s="380"/>
+      <c r="K47" s="381"/>
       <c r="L47" s="111">
         <f t="shared" ca="1" si="21"/>
         <v>0.22857142857142856</v>
@@ -28576,12 +28595,12 @@
     <row r="48" spans="1:35">
       <c r="F48" s="72"/>
       <c r="G48" s="6"/>
-      <c r="H48" s="388" t="s">
+      <c r="H48" s="382" t="s">
         <v>70</v>
       </c>
-      <c r="I48" s="389"/>
-      <c r="J48" s="389"/>
-      <c r="K48" s="390"/>
+      <c r="I48" s="383"/>
+      <c r="J48" s="383"/>
+      <c r="K48" s="384"/>
       <c r="L48" s="114">
         <f t="shared" ca="1" si="21"/>
         <v>0.11428571428571428</v>
@@ -28624,17 +28643,17 @@
       <c r="AI48" s="11"/>
     </row>
     <row r="49" spans="3:17" ht="16.5" thickBot="1">
-      <c r="C49" s="378" t="s">
+      <c r="C49" s="372" t="s">
         <v>41</v>
       </c>
-      <c r="D49" s="378"/>
-      <c r="E49" s="378"/>
-      <c r="H49" s="391" t="s">
+      <c r="D49" s="372"/>
+      <c r="E49" s="372"/>
+      <c r="H49" s="354" t="s">
         <v>71</v>
       </c>
-      <c r="I49" s="392"/>
-      <c r="J49" s="392"/>
-      <c r="K49" s="393"/>
+      <c r="I49" s="355"/>
+      <c r="J49" s="355"/>
+      <c r="K49" s="356"/>
       <c r="L49" s="113">
         <f t="shared" ca="1" si="21"/>
         <v>5.7142857142857141E-2</v>
@@ -28679,6 +28698,27 @@
     </sortState>
   </autoFilter>
   <mergeCells count="37">
+    <mergeCell ref="P43:Q43"/>
+    <mergeCell ref="X4:Y4"/>
+    <mergeCell ref="Z4:AC4"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D43:E43"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="D45:E45"/>
+    <mergeCell ref="C49:E49"/>
+    <mergeCell ref="H45:K45"/>
+    <mergeCell ref="H46:K46"/>
+    <mergeCell ref="H43:M43"/>
+    <mergeCell ref="H47:K47"/>
+    <mergeCell ref="H48:K48"/>
+    <mergeCell ref="C46:C47"/>
+    <mergeCell ref="D46:E47"/>
+    <mergeCell ref="D44:E44"/>
     <mergeCell ref="AG5:AG6"/>
     <mergeCell ref="AH5:AH6"/>
     <mergeCell ref="AI5:AI6"/>
@@ -28695,27 +28735,6 @@
     <mergeCell ref="K4:K5"/>
     <mergeCell ref="P4:Q4"/>
     <mergeCell ref="J4:J5"/>
-    <mergeCell ref="D45:E45"/>
-    <mergeCell ref="C49:E49"/>
-    <mergeCell ref="H45:K45"/>
-    <mergeCell ref="H46:K46"/>
-    <mergeCell ref="H43:M43"/>
-    <mergeCell ref="H47:K47"/>
-    <mergeCell ref="H48:K48"/>
-    <mergeCell ref="C46:C47"/>
-    <mergeCell ref="D46:E47"/>
-    <mergeCell ref="D44:E44"/>
-    <mergeCell ref="P43:Q43"/>
-    <mergeCell ref="X4:Y4"/>
-    <mergeCell ref="Z4:AC4"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D43:E43"/>
-    <mergeCell ref="B4:B5"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="A7:AD41 AG7:AI41">
@@ -28889,7 +28908,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C184EF3E-84BF-4DCF-951B-B90EB4B9D23F}">
-  <dimension ref="A1:Z140"/>
+  <dimension ref="A1:Z141"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" customWidth="1"/>
@@ -28928,7 +28947,7 @@
       </c>
       <c r="I1" s="176">
         <f ca="1">TODAY()</f>
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="J1" s="131"/>
       <c r="K1" s="197"/>
@@ -28999,81 +29018,81 @@
       <c r="Z3" s="159"/>
     </row>
     <row r="4" spans="1:26" s="5" customFormat="1" ht="35.1" customHeight="1" thickBot="1">
-      <c r="A4" s="348" t="s">
+      <c r="A4" s="407" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="348" t="s">
+      <c r="B4" s="407" t="s">
         <v>515</v>
       </c>
-      <c r="C4" s="414" t="s">
+      <c r="C4" s="403" t="s">
         <v>45</v>
       </c>
-      <c r="D4" s="369" t="s">
+      <c r="D4" s="362" t="s">
         <v>46</v>
       </c>
-      <c r="E4" s="437" t="s">
+      <c r="E4" s="428" t="s">
         <v>47</v>
       </c>
-      <c r="F4" s="369" t="s">
+      <c r="F4" s="362" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="439" t="s">
+      <c r="G4" s="430" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="366" t="s">
+      <c r="H4" s="364" t="s">
         <v>48</v>
       </c>
-      <c r="I4" s="441" t="s">
+      <c r="I4" s="432" t="s">
         <v>49</v>
       </c>
-      <c r="J4" s="369" t="s">
+      <c r="J4" s="362" t="s">
         <v>78</v>
       </c>
-      <c r="K4" s="366" t="s">
+      <c r="K4" s="364" t="s">
         <v>80</v>
       </c>
       <c r="L4" s="368" t="s">
         <v>53</v>
       </c>
-      <c r="M4" s="365"/>
+      <c r="M4" s="367"/>
       <c r="N4" s="368" t="s">
         <v>55</v>
       </c>
-      <c r="O4" s="365"/>
+      <c r="O4" s="367"/>
       <c r="P4" s="368" t="s">
         <v>72</v>
       </c>
-      <c r="Q4" s="365"/>
-      <c r="R4" s="364" t="s">
+      <c r="Q4" s="367"/>
+      <c r="R4" s="366" t="s">
         <v>53</v>
       </c>
-      <c r="S4" s="364"/>
-      <c r="T4" s="365"/>
+      <c r="S4" s="366"/>
+      <c r="T4" s="367"/>
       <c r="U4" s="368" t="s">
         <v>55</v>
       </c>
-      <c r="V4" s="364"/>
-      <c r="W4" s="364"/>
-      <c r="X4" s="371" t="s">
+      <c r="V4" s="366"/>
+      <c r="W4" s="366"/>
+      <c r="X4" s="393" t="s">
         <v>72</v>
       </c>
-      <c r="Y4" s="372"/>
-      <c r="Z4" s="365" t="s">
+      <c r="Y4" s="427"/>
+      <c r="Z4" s="367" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="72" customHeight="1">
-      <c r="A5" s="349"/>
-      <c r="B5" s="349"/>
-      <c r="C5" s="415"/>
-      <c r="D5" s="370"/>
-      <c r="E5" s="438"/>
-      <c r="F5" s="370"/>
-      <c r="G5" s="440"/>
-      <c r="H5" s="367"/>
-      <c r="I5" s="442"/>
-      <c r="J5" s="370"/>
-      <c r="K5" s="367"/>
+      <c r="A5" s="408"/>
+      <c r="B5" s="408"/>
+      <c r="C5" s="404"/>
+      <c r="D5" s="369"/>
+      <c r="E5" s="429"/>
+      <c r="F5" s="369"/>
+      <c r="G5" s="431"/>
+      <c r="H5" s="365"/>
+      <c r="I5" s="433"/>
+      <c r="J5" s="369"/>
+      <c r="K5" s="365"/>
       <c r="L5" s="79" t="s">
         <v>52</v>
       </c>
@@ -29116,7 +29135,7 @@
       <c r="Y5" s="260" t="s">
         <v>114</v>
       </c>
-      <c r="Z5" s="416"/>
+      <c r="Z5" s="363"/>
     </row>
     <row r="6" spans="1:26" ht="15" customHeight="1" thickBot="1">
       <c r="A6" s="78"/>
@@ -31673,11 +31692,11 @@
       <c r="H39" s="138"/>
       <c r="I39" s="164">
         <f t="shared" ca="1" si="9"/>
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="J39" s="47">
         <f t="shared" ca="1" si="10"/>
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="K39" s="164"/>
       <c r="L39" s="40"/>
@@ -34079,11 +34098,11 @@
       </c>
       <c r="I70" s="164">
         <f t="shared" ref="I70:I78" ca="1" si="14">IF(ISBLANK($V70),_xlfn.DAYS($I$1,$T70),_xlfn.DAYS($V70,$T70))</f>
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="J70" s="47">
         <f t="shared" ref="J70:J78" ca="1" si="15">IF(($I70-21)&gt;0,$I70-21,0)</f>
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="K70" s="164"/>
       <c r="L70" s="40"/>
@@ -34800,7 +34819,7 @@
         <v>628</v>
       </c>
       <c r="E80" s="174">
-        <f t="shared" ref="E80:E126" si="23">IF($T80=0,$S80+22,$T80+21)</f>
+        <f t="shared" ref="E80:E127" si="23">IF($T80=0,$S80+22,$T80+21)</f>
         <v>45945</v>
       </c>
       <c r="F80" s="31" t="s">
@@ -34813,11 +34832,11 @@
         <v>6</v>
       </c>
       <c r="I80" s="164">
-        <f t="shared" ref="I80:I126" si="24">IF(ISBLANK($V80),_xlfn.DAYS($I$1,$T80),_xlfn.DAYS($V80,$T80))</f>
+        <f t="shared" ref="I80:I127" si="24">IF(ISBLANK($V80),_xlfn.DAYS($I$1,$T80),_xlfn.DAYS($V80,$T80))</f>
         <v>6</v>
       </c>
       <c r="J80" s="47">
-        <f t="shared" ref="J80:J126" si="25">IF(($I80-21)&gt;0,$I80-21,0)</f>
+        <f t="shared" ref="J80:J127" si="25">IF(($I80-21)&gt;0,$I80-21,0)</f>
         <v>0</v>
       </c>
       <c r="K80" s="164"/>
@@ -35160,7 +35179,7 @@
     </row>
     <row r="85" spans="1:26" s="9" customFormat="1" ht="47.25">
       <c r="A85" s="33">
-        <f t="shared" ref="A85:A126" si="29">A84+1</f>
+        <f t="shared" ref="A85:A127" si="29">A84+1</f>
         <v>79</v>
       </c>
       <c r="B85" s="33" t="str">
@@ -36037,11 +36056,11 @@
       <c r="H97" s="138"/>
       <c r="I97" s="164">
         <f t="shared" ca="1" si="24"/>
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="J97" s="47">
         <f t="shared" ca="1" si="25"/>
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="K97" s="164"/>
       <c r="L97" s="40" t="s">
@@ -37157,11 +37176,11 @@
       <c r="H112" s="138"/>
       <c r="I112" s="164">
         <f t="shared" ca="1" si="24"/>
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="J112" s="47">
         <f t="shared" ca="1" si="25"/>
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="K112" s="164" t="s">
         <v>13</v>
@@ -37224,11 +37243,11 @@
       </c>
       <c r="I113" s="164">
         <f t="shared" ca="1" si="24"/>
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="J113" s="47">
         <f t="shared" ca="1" si="25"/>
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K113" s="164"/>
       <c r="L113" s="40" t="s">
@@ -37360,11 +37379,11 @@
       <c r="H115" s="138"/>
       <c r="I115" s="164">
         <f t="shared" ca="1" si="24"/>
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="J115" s="47">
         <f t="shared" ca="1" si="25"/>
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K115" s="164"/>
       <c r="L115" s="40" t="s">
@@ -38028,7 +38047,7 @@
       <c r="H125" s="138"/>
       <c r="I125" s="164">
         <f t="shared" ca="1" si="24"/>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J125" s="47">
         <f t="shared" ca="1" si="25"/>
@@ -38087,7 +38106,7 @@
       <c r="H126" s="138"/>
       <c r="I126" s="164">
         <f t="shared" ca="1" si="24"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J126" s="47">
         <f t="shared" ca="1" si="25"/>
@@ -38118,135 +38137,146 @@
       <c r="Y126" s="19"/>
       <c r="Z126" s="92"/>
     </row>
-    <row r="127" spans="1:26" s="9" customFormat="1">
-      <c r="A127" s="23"/>
-      <c r="B127" s="33"/>
-      <c r="C127" s="137"/>
-      <c r="D127" s="25"/>
-      <c r="E127" s="174"/>
-      <c r="F127" s="31"/>
-      <c r="G127" s="21"/>
+    <row r="127" spans="1:26" s="9" customFormat="1" ht="31.5">
+      <c r="A127" s="33">
+        <f t="shared" si="29"/>
+        <v>121</v>
+      </c>
+      <c r="B127" s="33" t="str">
+        <f t="shared" ref="B127" si="58">MID(D127, FIND("-", D127) + 1, 4)</f>
+        <v>5.11</v>
+      </c>
+      <c r="C127" s="164"/>
+      <c r="D127" s="25" t="s">
+        <v>1058</v>
+      </c>
+      <c r="E127" s="174">
+        <f t="shared" si="23"/>
+        <v>46325</v>
+      </c>
+      <c r="F127" s="31" t="s">
+        <v>1059</v>
+      </c>
+      <c r="G127" s="21" t="s">
+        <v>1060</v>
+      </c>
       <c r="H127" s="138"/>
-      <c r="I127" s="177"/>
-      <c r="J127" s="48"/>
-      <c r="K127" s="177"/>
-      <c r="L127" s="59"/>
-      <c r="M127" s="60"/>
-      <c r="N127" s="61"/>
-      <c r="O127" s="144"/>
-      <c r="P127" s="146"/>
-      <c r="Q127" s="152"/>
-      <c r="R127" s="27"/>
-      <c r="S127" s="27"/>
-      <c r="T127" s="187"/>
+      <c r="I127" s="164">
+        <f t="shared" ca="1" si="24"/>
+        <v>3</v>
+      </c>
+      <c r="J127" s="47">
+        <f t="shared" ca="1" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="K127" s="164"/>
+      <c r="L127" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="M127" s="41"/>
+      <c r="N127" s="40"/>
+      <c r="O127" s="41"/>
+      <c r="P127" s="40"/>
+      <c r="Q127" s="154"/>
+      <c r="R127" s="27">
+        <v>46304</v>
+      </c>
+      <c r="S127" s="27">
+        <v>46304</v>
+      </c>
+      <c r="T127" s="188">
+        <v>46304</v>
+      </c>
       <c r="U127" s="29"/>
-      <c r="V127" s="188"/>
+      <c r="V127" s="211"/>
       <c r="W127" s="235"/>
       <c r="X127" s="230"/>
       <c r="Y127" s="19"/>
       <c r="Z127" s="92"/>
     </row>
-    <row r="128" spans="1:26" s="9" customFormat="1" ht="16.5" thickBot="1">
-      <c r="A128" s="24"/>
-      <c r="B128" s="329"/>
-      <c r="C128" s="165"/>
-      <c r="D128" s="45"/>
-      <c r="E128" s="175"/>
-      <c r="F128" s="32"/>
-      <c r="G128" s="22"/>
-      <c r="H128" s="139"/>
-      <c r="I128" s="178"/>
-      <c r="J128" s="49"/>
-      <c r="K128" s="178"/>
-      <c r="L128" s="62"/>
-      <c r="M128" s="63"/>
-      <c r="N128" s="64"/>
-      <c r="O128" s="145"/>
-      <c r="P128" s="147"/>
-      <c r="Q128" s="153"/>
-      <c r="R128" s="44"/>
-      <c r="S128" s="44"/>
-      <c r="T128" s="189"/>
-      <c r="U128" s="43"/>
-      <c r="V128" s="194"/>
-      <c r="W128" s="258"/>
-      <c r="X128" s="232"/>
-      <c r="Y128" s="20"/>
-      <c r="Z128" s="93"/>
-    </row>
-    <row r="129" spans="3:25" ht="16.5" thickBot="1"/>
-    <row r="130" spans="3:25" ht="16.5" thickBot="1">
-      <c r="C130" s="207" t="s">
+    <row r="128" spans="1:26" s="9" customFormat="1">
+      <c r="A128" s="23"/>
+      <c r="B128" s="33"/>
+      <c r="C128" s="137"/>
+      <c r="D128" s="25"/>
+      <c r="E128" s="174"/>
+      <c r="F128" s="31"/>
+      <c r="G128" s="21"/>
+      <c r="H128" s="138"/>
+      <c r="I128" s="177"/>
+      <c r="J128" s="48"/>
+      <c r="K128" s="177"/>
+      <c r="L128" s="59"/>
+      <c r="M128" s="60"/>
+      <c r="N128" s="61"/>
+      <c r="O128" s="144"/>
+      <c r="P128" s="146"/>
+      <c r="Q128" s="152"/>
+      <c r="R128" s="27"/>
+      <c r="S128" s="27"/>
+      <c r="T128" s="187"/>
+      <c r="U128" s="29"/>
+      <c r="V128" s="188"/>
+      <c r="W128" s="235"/>
+      <c r="X128" s="230"/>
+      <c r="Y128" s="19"/>
+      <c r="Z128" s="92"/>
+    </row>
+    <row r="129" spans="1:26" s="9" customFormat="1" ht="16.5" thickBot="1">
+      <c r="A129" s="24"/>
+      <c r="B129" s="329"/>
+      <c r="C129" s="165"/>
+      <c r="D129" s="45"/>
+      <c r="E129" s="175"/>
+      <c r="F129" s="32"/>
+      <c r="G129" s="22"/>
+      <c r="H129" s="139"/>
+      <c r="I129" s="178"/>
+      <c r="J129" s="49"/>
+      <c r="K129" s="178"/>
+      <c r="L129" s="62"/>
+      <c r="M129" s="63"/>
+      <c r="N129" s="64"/>
+      <c r="O129" s="145"/>
+      <c r="P129" s="147"/>
+      <c r="Q129" s="153"/>
+      <c r="R129" s="44"/>
+      <c r="S129" s="44"/>
+      <c r="T129" s="189"/>
+      <c r="U129" s="43"/>
+      <c r="V129" s="194"/>
+      <c r="W129" s="258"/>
+      <c r="X129" s="232"/>
+      <c r="Y129" s="20"/>
+      <c r="Z129" s="93"/>
+    </row>
+    <row r="130" spans="1:26" ht="16.5" thickBot="1"/>
+    <row r="131" spans="1:26" ht="16.5" thickBot="1">
+      <c r="C131" s="207" t="s">
         <v>38</v>
       </c>
-      <c r="D130" s="428" t="s">
+      <c r="D131" s="441" t="s">
         <v>39</v>
       </c>
-      <c r="E130" s="429"/>
-      <c r="F130" s="46"/>
-      <c r="G130" s="68"/>
-      <c r="H130" s="356" t="s">
+      <c r="E131" s="442"/>
+      <c r="F131" s="46"/>
+      <c r="G131" s="68"/>
+      <c r="H131" s="357" t="s">
         <v>14</v>
       </c>
-      <c r="I130" s="357"/>
-      <c r="J130" s="357"/>
-      <c r="K130" s="357"/>
-      <c r="L130" s="357"/>
-      <c r="M130" s="358"/>
-      <c r="N130" s="362" t="s">
+      <c r="I131" s="358"/>
+      <c r="J131" s="358"/>
+      <c r="K131" s="358"/>
+      <c r="L131" s="358"/>
+      <c r="M131" s="359"/>
+      <c r="N131" s="360" t="s">
         <v>7</v>
       </c>
-      <c r="O130" s="363"/>
-      <c r="P130" s="362" t="s">
+      <c r="O131" s="361"/>
+      <c r="P131" s="360" t="s">
         <v>110</v>
       </c>
-      <c r="Q130" s="363"/>
-      <c r="R130" s="1"/>
-      <c r="S130" s="1"/>
-      <c r="T130" s="140"/>
-      <c r="U130" s="1"/>
-      <c r="W130" s="11"/>
-      <c r="X130" s="11"/>
-      <c r="Y130" s="11"/>
-    </row>
-    <row r="131" spans="3:25" ht="16.5" customHeight="1" thickBot="1">
-      <c r="C131" s="208" t="s">
-        <v>74</v>
-      </c>
-      <c r="D131" s="435" t="s">
-        <v>77</v>
-      </c>
-      <c r="E131" s="436"/>
-      <c r="F131" s="46"/>
-      <c r="G131" s="46"/>
-      <c r="H131" s="430" t="s">
-        <v>17</v>
-      </c>
-      <c r="I131" s="431"/>
-      <c r="J131" s="130"/>
-      <c r="K131" s="210"/>
-      <c r="L131" s="117">
-        <f ca="1">M131/$M$131</f>
-        <v>1</v>
-      </c>
-      <c r="M131" s="104">
-        <f ca="1">SUM($M$132:$M$134)</f>
-        <v>124</v>
-      </c>
-      <c r="N131" s="118" t="s">
-        <v>15</v>
-      </c>
-      <c r="O131" s="119" t="s">
-        <v>16</v>
-      </c>
-      <c r="P131" s="117">
-        <f ca="1">Q131/$Q$131</f>
-        <v>1</v>
-      </c>
-      <c r="Q131" s="104">
-        <f ca="1">SUM(Q132:Q133)</f>
-        <v>106</v>
-      </c>
+      <c r="Q131" s="361"/>
       <c r="R131" s="1"/>
       <c r="S131" s="1"/>
       <c r="T131" s="140"/>
@@ -38255,45 +38285,43 @@
       <c r="X131" s="11"/>
       <c r="Y131" s="11"/>
     </row>
-    <row r="132" spans="3:25">
-      <c r="C132" s="394" t="s">
-        <v>6</v>
-      </c>
-      <c r="D132" s="435" t="s">
-        <v>40</v>
-      </c>
-      <c r="E132" s="436"/>
-      <c r="F132" s="69"/>
-      <c r="G132" s="6"/>
-      <c r="H132" s="432" t="s">
-        <v>69</v>
-      </c>
-      <c r="I132" s="433"/>
-      <c r="J132" s="433"/>
-      <c r="K132" s="434"/>
-      <c r="L132" s="122">
-        <f t="shared" ref="L132:L134" ca="1" si="58">M132/$M$131</f>
-        <v>0.83064516129032262</v>
-      </c>
-      <c r="M132" s="123">
-        <f>COUNTIF($H$7:$H$128,"RFCS")</f>
-        <v>103</v>
-      </c>
-      <c r="N132" s="121">
-        <f ca="1">COUNTIFS($I$7:$I$128,"&lt;=21",$H$7:$H$128,"RFCS")</f>
-        <v>61</v>
-      </c>
-      <c r="O132" s="120">
-        <f ca="1">COUNTIFS($I$7:$I$128,"&gt;21",$H$7:$H$128,"RFCS")</f>
-        <v>41</v>
-      </c>
-      <c r="P132" s="122">
-        <f ca="1">Q132/$Q$131</f>
-        <v>0.64150943396226412</v>
-      </c>
-      <c r="Q132" s="123">
-        <f>COUNTIF($Q$7:$Q$128,"RBE") + COUNTIF($Q$7:$Q$128,"SUP")</f>
-        <v>68</v>
+    <row r="132" spans="1:26" ht="16.5" customHeight="1" thickBot="1">
+      <c r="C132" s="208" t="s">
+        <v>74</v>
+      </c>
+      <c r="D132" s="439" t="s">
+        <v>77</v>
+      </c>
+      <c r="E132" s="440"/>
+      <c r="F132" s="46"/>
+      <c r="G132" s="46"/>
+      <c r="H132" s="434" t="s">
+        <v>17</v>
+      </c>
+      <c r="I132" s="435"/>
+      <c r="J132" s="130"/>
+      <c r="K132" s="210"/>
+      <c r="L132" s="117">
+        <f ca="1">M132/$M$132</f>
+        <v>1</v>
+      </c>
+      <c r="M132" s="104">
+        <f ca="1">SUM($M$133:$M$135)</f>
+        <v>125</v>
+      </c>
+      <c r="N132" s="118" t="s">
+        <v>15</v>
+      </c>
+      <c r="O132" s="119" t="s">
+        <v>16</v>
+      </c>
+      <c r="P132" s="117">
+        <f ca="1">Q132/$Q$132</f>
+        <v>1</v>
+      </c>
+      <c r="Q132" s="104">
+        <f ca="1">SUM(Q133:Q134)</f>
+        <v>107</v>
       </c>
       <c r="R132" s="1"/>
       <c r="S132" s="1"/>
@@ -38303,45 +38331,47 @@
       <c r="X132" s="11"/>
       <c r="Y132" s="11"/>
     </row>
-    <row r="133" spans="3:25">
-      <c r="C133" s="394"/>
-      <c r="D133" s="435"/>
-      <c r="E133" s="436"/>
-      <c r="F133" s="72"/>
+    <row r="133" spans="1:26">
+      <c r="C133" s="385" t="s">
+        <v>6</v>
+      </c>
+      <c r="D133" s="439" t="s">
+        <v>40</v>
+      </c>
+      <c r="E133" s="440"/>
+      <c r="F133" s="69"/>
       <c r="G133" s="6"/>
-      <c r="H133" s="388" t="s">
-        <v>70</v>
-      </c>
-      <c r="I133" s="389"/>
-      <c r="J133" s="389"/>
-      <c r="K133" s="390"/>
-      <c r="L133" s="124">
-        <f t="shared" ca="1" si="58"/>
-        <v>5.6451612903225805E-2</v>
-      </c>
-      <c r="M133" s="125">
-        <f ca="1">SUM(N133:O133)</f>
-        <v>7</v>
-      </c>
-      <c r="N133" s="98">
-        <f ca="1">COUNTIFS($I$7:$I$128,"&lt;=21",$U$7:$U$128,"",$K$7:$K$128,"&lt;&gt;X")</f>
-        <v>2</v>
-      </c>
-      <c r="O133" s="50">
-        <f ca="1">COUNTIFS($I$7:$I$128,"&gt;21",$U$7:$U$128,"",$K$7:$K$128,"&lt;&gt;X")</f>
-        <v>5</v>
-      </c>
-      <c r="P133" s="124">
-        <f ca="1">Q133/$Q$131</f>
-        <v>0.35849056603773582</v>
-      </c>
-      <c r="Q133" s="125">
-        <f ca="1">COUNTIFS($I$7:$I$128,"&gt;=0",$P$7:$P$128,"",$K$7:$K$128,"&lt;&gt;X")</f>
-        <v>38</v>
-      </c>
-      <c r="R133" s="1" t="s">
-        <v>10</v>
-      </c>
+      <c r="H133" s="436" t="s">
+        <v>69</v>
+      </c>
+      <c r="I133" s="437"/>
+      <c r="J133" s="437"/>
+      <c r="K133" s="438"/>
+      <c r="L133" s="122">
+        <f t="shared" ref="L133:L135" ca="1" si="59">M133/$M$132</f>
+        <v>0.82399999999999995</v>
+      </c>
+      <c r="M133" s="123">
+        <f>COUNTIF($H$7:$H$129,"RFCS")</f>
+        <v>103</v>
+      </c>
+      <c r="N133" s="121">
+        <f ca="1">COUNTIFS($I$7:$I$129,"&lt;=21",$H$7:$H$129,"RFCS")</f>
+        <v>61</v>
+      </c>
+      <c r="O133" s="120">
+        <f ca="1">COUNTIFS($I$7:$I$129,"&gt;21",$H$7:$H$129,"RFCS")</f>
+        <v>41</v>
+      </c>
+      <c r="P133" s="122">
+        <f ca="1">Q133/$Q$132</f>
+        <v>0.63551401869158874</v>
+      </c>
+      <c r="Q133" s="123">
+        <f>COUNTIF($Q$7:$Q$129,"RBE") + COUNTIF($Q$7:$Q$129,"SUP")</f>
+        <v>68</v>
+      </c>
+      <c r="R133" s="1"/>
       <c r="S133" s="1"/>
       <c r="T133" s="140"/>
       <c r="U133" s="1"/>
@@ -38349,76 +38379,138 @@
       <c r="X133" s="11"/>
       <c r="Y133" s="11"/>
     </row>
-    <row r="134" spans="3:25" ht="16.5" thickBot="1">
-      <c r="C134" s="394" t="s">
+    <row r="134" spans="1:26">
+      <c r="C134" s="385"/>
+      <c r="D134" s="439"/>
+      <c r="E134" s="440"/>
+      <c r="F134" s="72"/>
+      <c r="G134" s="6"/>
+      <c r="H134" s="382" t="s">
+        <v>70</v>
+      </c>
+      <c r="I134" s="383"/>
+      <c r="J134" s="383"/>
+      <c r="K134" s="384"/>
+      <c r="L134" s="124">
+        <f t="shared" ca="1" si="59"/>
+        <v>6.4000000000000001E-2</v>
+      </c>
+      <c r="M134" s="125">
+        <f ca="1">SUM(N134:O134)</f>
+        <v>8</v>
+      </c>
+      <c r="N134" s="98">
+        <f ca="1">COUNTIFS($I$7:$I$129,"&lt;=21",$U$7:$U$129,"",$K$7:$K$129,"&lt;&gt;X")</f>
+        <v>3</v>
+      </c>
+      <c r="O134" s="50">
+        <f ca="1">COUNTIFS($I$7:$I$129,"&gt;21",$U$7:$U$129,"",$K$7:$K$129,"&lt;&gt;X")</f>
+        <v>5</v>
+      </c>
+      <c r="P134" s="124">
+        <f ca="1">Q134/$Q$132</f>
+        <v>0.3644859813084112</v>
+      </c>
+      <c r="Q134" s="125">
+        <f ca="1">COUNTIFS($I$7:$I$129,"&gt;=0",$P$7:$P$129,"",$K$7:$K$129,"&lt;&gt;X")</f>
+        <v>39</v>
+      </c>
+      <c r="R134" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="S134" s="1"/>
+      <c r="T134" s="140"/>
+      <c r="U134" s="1"/>
+      <c r="W134" s="11"/>
+      <c r="X134" s="11"/>
+      <c r="Y134" s="11"/>
+    </row>
+    <row r="135" spans="1:26" ht="16.5" thickBot="1">
+      <c r="C135" s="385" t="s">
         <v>75</v>
       </c>
-      <c r="D134" s="350" t="s">
+      <c r="D135" s="387" t="s">
         <v>76</v>
       </c>
-      <c r="E134" s="351"/>
-      <c r="H134" s="391" t="s">
+      <c r="E135" s="388"/>
+      <c r="H135" s="354" t="s">
         <v>71</v>
       </c>
-      <c r="I134" s="392"/>
-      <c r="J134" s="392"/>
-      <c r="K134" s="393"/>
-      <c r="L134" s="126">
-        <f t="shared" ca="1" si="58"/>
-        <v>0.11290322580645161</v>
-      </c>
-      <c r="M134" s="116">
-        <f>COUNTIFS($K$7:$K$128,"X")</f>
+      <c r="I135" s="355"/>
+      <c r="J135" s="355"/>
+      <c r="K135" s="356"/>
+      <c r="L135" s="126">
+        <f t="shared" ca="1" si="59"/>
+        <v>0.112</v>
+      </c>
+      <c r="M135" s="116">
+        <f>COUNTIFS($K$7:$K$129,"X")</f>
         <v>14</v>
       </c>
-      <c r="N134" s="99"/>
-      <c r="O134" s="51"/>
-      <c r="P134" s="223"/>
-      <c r="Q134" s="224"/>
-    </row>
-    <row r="135" spans="3:25" ht="16.5" thickBot="1">
-      <c r="C135" s="395"/>
-      <c r="D135" s="352"/>
-      <c r="E135" s="353"/>
-    </row>
-    <row r="137" spans="3:25">
-      <c r="C137" s="378" t="s">
+      <c r="N135" s="99"/>
+      <c r="O135" s="51"/>
+      <c r="P135" s="223"/>
+      <c r="Q135" s="224"/>
+    </row>
+    <row r="136" spans="1:26" ht="16.5" thickBot="1">
+      <c r="C136" s="386"/>
+      <c r="D136" s="389"/>
+      <c r="E136" s="390"/>
+    </row>
+    <row r="138" spans="1:26">
+      <c r="C138" s="372" t="s">
         <v>41</v>
       </c>
-      <c r="D137" s="378"/>
-      <c r="E137" s="378"/>
-    </row>
-    <row r="138" spans="3:25">
-      <c r="C138" s="169" t="s">
-        <v>8</v>
-      </c>
-      <c r="D138" s="1" t="s">
+      <c r="D138" s="372"/>
+      <c r="E138" s="372"/>
+    </row>
+    <row r="139" spans="1:26">
+      <c r="C139" s="169" t="s">
+        <v>8</v>
+      </c>
+      <c r="D139" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="139" spans="3:25">
-      <c r="C139" s="169" t="s">
-        <v>8</v>
-      </c>
-      <c r="D139" s="127" t="s">
+    <row r="140" spans="1:26">
+      <c r="C140" s="169" t="s">
+        <v>8</v>
+      </c>
+      <c r="D140" s="127" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="140" spans="3:25">
-      <c r="C140" s="169" t="s">
-        <v>8</v>
-      </c>
-      <c r="D140" s="1" t="s">
+    <row r="141" spans="1:26">
+      <c r="C141" s="169" t="s">
+        <v>8</v>
+      </c>
+      <c r="D141" s="1" t="s">
         <v>44</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A6:Z126" xr:uid="{C184EF3E-84BF-4DCF-951B-B90EB4B9D23F}">
+  <autoFilter ref="A6:Z127" xr:uid="{C184EF3E-84BF-4DCF-951B-B90EB4B9D23F}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A7:Z32">
       <sortCondition ref="S6"/>
     </sortState>
   </autoFilter>
   <mergeCells count="32">
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="P131:Q131"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="D131:E131"/>
+    <mergeCell ref="H131:M131"/>
+    <mergeCell ref="N131:O131"/>
+    <mergeCell ref="H132:I132"/>
+    <mergeCell ref="C138:E138"/>
+    <mergeCell ref="H133:K133"/>
+    <mergeCell ref="H134:K134"/>
+    <mergeCell ref="H135:K135"/>
+    <mergeCell ref="D132:E132"/>
+    <mergeCell ref="C133:C134"/>
+    <mergeCell ref="D133:E134"/>
+    <mergeCell ref="C135:C136"/>
+    <mergeCell ref="D135:E136"/>
     <mergeCell ref="Z4:Z5"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="D4:D5"/>
@@ -38435,25 +38527,9 @@
     <mergeCell ref="K4:K5"/>
     <mergeCell ref="P4:Q4"/>
     <mergeCell ref="X4:Y4"/>
-    <mergeCell ref="H131:I131"/>
-    <mergeCell ref="C137:E137"/>
-    <mergeCell ref="H132:K132"/>
-    <mergeCell ref="H133:K133"/>
-    <mergeCell ref="H134:K134"/>
-    <mergeCell ref="D131:E131"/>
-    <mergeCell ref="C132:C133"/>
-    <mergeCell ref="D132:E133"/>
-    <mergeCell ref="C134:C135"/>
-    <mergeCell ref="D134:E135"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="P130:Q130"/>
-    <mergeCell ref="J4:J5"/>
-    <mergeCell ref="D130:E130"/>
-    <mergeCell ref="H130:M130"/>
-    <mergeCell ref="N130:O130"/>
   </mergeCells>
   <phoneticPr fontId="71"/>
-  <conditionalFormatting sqref="A7:Z128">
+  <conditionalFormatting sqref="A7:Z129">
     <cfRule type="expression" dxfId="4" priority="1">
       <formula>$K7="X"</formula>
     </cfRule>
@@ -38598,9 +38674,9 @@
     <hyperlink ref="O43" r:id="rId125" xr:uid="{0E3F3A7F-DA9A-49F8-A93F-8337122FAE1A}"/>
     <hyperlink ref="N41" r:id="rId126" xr:uid="{3405D711-BDD4-4069-A376-D6B961D87010}"/>
     <hyperlink ref="N43" r:id="rId127" xr:uid="{525398A7-A7B1-41B1-88A2-7E7F9115541E}"/>
-    <hyperlink ref="C138" r:id="rId128" xr:uid="{F06CE902-4089-4B08-A7E9-420A16C9FF0E}"/>
-    <hyperlink ref="C139" r:id="rId129" xr:uid="{6D322F1B-B574-40E7-BED0-14ED893C19C5}"/>
-    <hyperlink ref="C140" r:id="rId130" xr:uid="{1845DEB0-969B-4FE7-B52A-52C25D3EC72E}"/>
+    <hyperlink ref="C139" r:id="rId128" xr:uid="{F06CE902-4089-4B08-A7E9-420A16C9FF0E}"/>
+    <hyperlink ref="C140" r:id="rId129" xr:uid="{6D322F1B-B574-40E7-BED0-14ED893C19C5}"/>
+    <hyperlink ref="C141" r:id="rId130" xr:uid="{1845DEB0-969B-4FE7-B52A-52C25D3EC72E}"/>
     <hyperlink ref="N42" r:id="rId131" xr:uid="{95D9F3CF-8EC0-4C96-9F49-34E6585C583B}"/>
     <hyperlink ref="L44" r:id="rId132" xr:uid="{255E79C1-4568-41F7-B71E-8301B034AA56}"/>
     <hyperlink ref="P8" r:id="rId133" xr:uid="{4339778F-2FA8-45DA-BD1F-0684B78D35ED}"/>
@@ -38945,9 +39021,10 @@
     <hyperlink ref="L125" r:id="rId472" xr:uid="{2E6A3E6B-ABC8-4AE9-B1DE-8F7C56644B00}"/>
     <hyperlink ref="N124" r:id="rId473" xr:uid="{F03DC946-218B-485F-BFEB-FBD9AEF00913}"/>
     <hyperlink ref="L126" r:id="rId474" xr:uid="{3EB8572D-FD0D-4865-AF14-84A4ECCCC02A}"/>
+    <hyperlink ref="L127" r:id="rId475" xr:uid="{E41605CA-C2E5-494D-8E08-2F89092E4322}"/>
   </hyperlinks>
   <pageMargins left="0.25" right="0.17" top="0.5" bottom="0.25" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="28" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId475"/>
+  <pageSetup paperSize="9" scale="28" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId476"/>
 </worksheet>
 </file>
 
@@ -39032,19 +39109,19 @@
       <c r="S3" s="281"/>
     </row>
     <row r="4" spans="1:25" ht="36" customHeight="1" thickBot="1">
-      <c r="A4" s="408" t="s">
+      <c r="A4" s="397" t="s">
         <v>123</v>
       </c>
-      <c r="B4" s="366" t="s">
+      <c r="B4" s="364" t="s">
         <v>45</v>
       </c>
-      <c r="C4" s="366" t="s">
+      <c r="C4" s="364" t="s">
         <v>95</v>
       </c>
-      <c r="D4" s="366" t="s">
+      <c r="D4" s="364" t="s">
         <v>46</v>
       </c>
-      <c r="E4" s="369" t="s">
+      <c r="E4" s="362" t="s">
         <v>4</v>
       </c>
       <c r="F4" s="449" t="s">
@@ -39073,12 +39150,12 @@
       <c r="S4" s="448"/>
     </row>
     <row r="5" spans="1:25" ht="78.75">
-      <c r="A5" s="409"/>
-      <c r="B5" s="367"/>
-      <c r="C5" s="367"/>
-      <c r="D5" s="367"/>
-      <c r="E5" s="370"/>
-      <c r="F5" s="411"/>
+      <c r="A5" s="398"/>
+      <c r="B5" s="365"/>
+      <c r="C5" s="365"/>
+      <c r="D5" s="365"/>
+      <c r="E5" s="369"/>
+      <c r="F5" s="402"/>
       <c r="G5" s="283" t="s">
         <v>56</v>
       </c>
@@ -39266,7 +39343,7 @@
 _xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(D7),RFA!$E:$E,RFA!$AD:$AD,""),
 IF(_xlpm.x=0,"",_xlpm.x)
 )</f>
-        <v>841</v>
+        <v>844</v>
       </c>
     </row>
     <row r="8" spans="1:25" ht="45">
@@ -39327,7 +39404,7 @@
       </c>
       <c r="S8" s="279">
         <f ca="1"/>
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="Y8" t="s">
         <v>125</v>
@@ -39392,7 +39469,7 @@
       </c>
       <c r="S9" s="279">
         <f ca="1"/>
-        <v>504</v>
+        <v>507</v>
       </c>
     </row>
     <row r="10" spans="1:25" ht="45">
@@ -39453,7 +39530,7 @@
       </c>
       <c r="S10" s="279">
         <f ca="1"/>
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="11" spans="1:25" ht="75">
@@ -39514,7 +39591,7 @@
       </c>
       <c r="S11" s="279">
         <f ca="1"/>
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="12" spans="1:25" ht="45">
@@ -39575,7 +39652,7 @@
       </c>
       <c r="S12" s="279">
         <f ca="1"/>
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="13" spans="1:25" ht="45">
@@ -39636,7 +39713,7 @@
       </c>
       <c r="S13" s="279">
         <f ca="1"/>
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="14" spans="1:25" ht="45">
@@ -39697,7 +39774,7 @@
       </c>
       <c r="S14" s="279">
         <f ca="1"/>
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15" spans="1:25" ht="60">
@@ -40411,16 +40488,16 @@
       <c r="R3" s="281"/>
     </row>
     <row r="4" spans="1:18" ht="16.5" thickBot="1">
-      <c r="A4" s="408" t="s">
+      <c r="A4" s="397" t="s">
         <v>123</v>
       </c>
-      <c r="B4" s="366" t="s">
+      <c r="B4" s="364" t="s">
         <v>45</v>
       </c>
-      <c r="C4" s="366" t="s">
+      <c r="C4" s="364" t="s">
         <v>46</v>
       </c>
-      <c r="D4" s="364" t="s">
+      <c r="D4" s="366" t="s">
         <v>4</v>
       </c>
       <c r="E4" s="449" t="s">
@@ -40449,11 +40526,11 @@
       <c r="R4" s="448"/>
     </row>
     <row r="5" spans="1:18" ht="78.75">
-      <c r="A5" s="409"/>
-      <c r="B5" s="367"/>
-      <c r="C5" s="367"/>
-      <c r="D5" s="440"/>
-      <c r="E5" s="370"/>
+      <c r="A5" s="398"/>
+      <c r="B5" s="365"/>
+      <c r="C5" s="365"/>
+      <c r="D5" s="431"/>
+      <c r="E5" s="369"/>
       <c r="F5" s="283" t="s">
         <v>56</v>
       </c>
@@ -40589,7 +40666,7 @@
       </c>
       <c r="R7" s="279" cm="1">
         <f t="array" aca="1" ref="R7:R18" ca="1">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$AC:$AC,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
-        <v>541</v>
+        <v>544</v>
       </c>
     </row>
     <row r="8" spans="1:18" ht="30">
@@ -40647,7 +40724,7 @@
       </c>
       <c r="R8" s="279">
         <f ca="1"/>
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="45">
@@ -40705,7 +40782,7 @@
       </c>
       <c r="R9" s="279">
         <f ca="1"/>
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="105">
@@ -40764,7 +40841,7 @@
       </c>
       <c r="R10" s="279">
         <f ca="1"/>
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="45">
@@ -40822,7 +40899,7 @@
       </c>
       <c r="R11" s="279">
         <f ca="1"/>
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="12" spans="1:18" ht="45">
@@ -40881,7 +40958,7 @@
       </c>
       <c r="R12" s="279">
         <f ca="1"/>
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="75">
@@ -40939,7 +41016,7 @@
       </c>
       <c r="R13" s="279">
         <f ca="1"/>
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="14" spans="1:18" ht="60">
@@ -40997,7 +41074,7 @@
       </c>
       <c r="R14" s="279">
         <f ca="1"/>
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="15" spans="1:18" ht="45">
@@ -41055,7 +41132,7 @@
       </c>
       <c r="R15" s="279">
         <f ca="1"/>
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="45">
@@ -41113,7 +41190,7 @@
       </c>
       <c r="R16" s="279">
         <f ca="1"/>
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="17" spans="1:18" ht="60">
@@ -41229,7 +41306,7 @@
       </c>
       <c r="R18" s="279">
         <f ca="1"/>
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
   </sheetData>
@@ -41287,19 +41364,19 @@
     <row r="3" spans="1:4" ht="15.75">
       <c r="A3" s="319">
         <f ca="1">MAX('Need ReSub (RFA)'!S7:S76)</f>
-        <v>841</v>
+        <v>844</v>
       </c>
       <c r="B3" s="319">
         <f ca="1">AVERAGEIF('Need ReSub (RFA)'!S7:S76,"&lt;&gt;0")</f>
-        <v>449.25</v>
+        <v>452.25</v>
       </c>
       <c r="C3" s="319">
         <f ca="1">MAX(_xlfn.ANCHORARRAY('Need ReSub (RFA-SDS)'!R7))</f>
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="D3" s="319">
         <f ca="1">AVERAGEIF(_xlfn.ANCHORARRAY('Need ReSub (RFA-SDS)'!R7),"&lt;&gt;0")</f>
-        <v>333.16666666666669</v>
+        <v>335.91666666666669</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -41308,10 +41385,10 @@
 Furthermore, the RFA (SDS) is as follows:
 Avarage :  " &amp; ROUND($D$3,0) &amp; " days
 Maimum :  " &amp; ROUND($C$3,0) &amp; " days"</f>
-        <v>In the RFA process, the average number of days elapsed since responding to an unapproved RFA was 449 days, with a maximum of 841 days, indicating that delays in the RFA approval process are contributing to delays in construction work.
+        <v>In the RFA process, the average number of days elapsed since responding to an unapproved RFA was 452 days, with a maximum of 844 days, indicating that delays in the RFA approval process are contributing to delays in construction work.
 Furthermore, the RFA (SDS) is as follows:
-Avarage :  333 days
-Maimum :  541 days</v>
+Avarage :  336 days
+Maimum :  544 days</v>
       </c>
       <c r="B5" s="452"/>
     </row>

--- a/ICT-RFA-RFI-lists-New.xlsx
+++ b/ICT-RFA-RFI-lists-New.xlsx
@@ -9,7 +9,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project Airport\LTIA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1845AA21-5882-4350-9D4D-1CBC789B9D62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBFC37CA-3DD4-4461-98C4-97E18107EF83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="506" xr2:uid="{CCA8147E-0981-4321-B87F-440A52C0DA59}"/>
   </bookViews>
@@ -30,7 +30,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Need ReSub (RFA)'!$A$1:$S$77</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'Need ReSub (RFA-SDS)'!$A$1:$R$62</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">RFA!$A$1:$AE$137,RFA!$I$139:$R$145,RFA!$C$139:$F$149,RFA!$C$151:$F$154,RFA!$C$156:$F$167</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'RFA-SDS'!$A$1:$AD$41,'RFA-SDS'!$H$43:$Q$49,'RFA-SDS'!$C$43:$E$47,'RFA-SDS'!$C$49:$E$52</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'RFA-SDS'!$A$1:$AD$42,'RFA-SDS'!$H$44:$Q$50,'RFA-SDS'!$C$44:$E$48,'RFA-SDS'!$C$50:$E$53</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">RFI!$A$1:$Z$129,RFI!$H$131:$Q$135,RFI!$C$131:$E$136,RFI!$C$138:$E$141</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">RFA!$4:$5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'RFA-SDS'!$4:$5</definedName>
@@ -78,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3423" uniqueCount="1061">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3430" uniqueCount="1066">
   <si>
     <t>TT</t>
   </si>
@@ -5028,6 +5028,22 @@
   </si>
   <si>
     <t>Đề xuất nguyên tắc đặt tên bản vẽ thi công.</t>
+  </si>
+  <si>
+    <t>LTIA-5.10-VIETUR-80000-RFA-SDS-0493</t>
+  </si>
+  <si>
+    <t>Construction design drawing of  ICT system – part.1: ICT systems for GF, 3F, FLB Technical Room Drawing</t>
+  </si>
+  <si>
+    <t>Bản vẽ TKTC cho hệ thống ICT – phần 1 – Hệ thống ICT cho Bản Vẽ Phòng Kỹ Thuật Tầng GF, Tầng 3, FLB</t>
+  </si>
+  <si>
+    <t>10/12/2026: Đã comment</t>
+  </si>
+  <si>
+    <t>10/12/2026: Đã comment
+10/13/2026: Đã gửi comment qua CNC</t>
   </si>
 </sst>
 </file>
@@ -8278,7 +8294,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C724CDAB-378C-47DB-9F45-08EE3BFB6E8B}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:AI167"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75"/>
   <cols>
@@ -8301,7 +8316,7 @@
     <col min="24" max="28" width="16.42578125" style="6" customWidth="1"/>
     <col min="29" max="29" width="18.42578125" style="6" customWidth="1"/>
     <col min="30" max="30" width="16.42578125" style="6" customWidth="1"/>
-    <col min="31" max="31" width="37.140625" style="160" customWidth="1"/>
+    <col min="31" max="31" width="40.140625" style="160" customWidth="1"/>
     <col min="32" max="32" width="9.140625" style="1"/>
     <col min="33" max="33" width="18.42578125" style="219" customWidth="1"/>
     <col min="34" max="35" width="18.42578125" style="6" customWidth="1"/>
@@ -8324,7 +8339,7 @@
       </c>
       <c r="J1" s="176">
         <f ca="1">TODAY()</f>
-        <v>46307</v>
+        <v>46309</v>
       </c>
       <c r="K1" s="131"/>
       <c r="L1" s="197"/>
@@ -8598,7 +8613,7 @@
       <c r="AH6" s="409"/>
       <c r="AI6" s="409"/>
     </row>
-    <row r="7" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
+    <row r="7" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A7" s="33">
         <f t="shared" ref="A7:A38" si="0">A6+1</f>
         <v>1</v>
@@ -8718,7 +8733,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
+    <row r="8" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A8" s="33">
         <f t="shared" si="0"/>
         <v>2</v>
@@ -8834,7 +8849,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
+    <row r="9" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A9" s="33">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -8950,7 +8965,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
+    <row r="10" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A10" s="33">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -9068,7 +9083,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
+    <row r="11" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A11" s="33">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -9186,7 +9201,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
+    <row r="12" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A12" s="33">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -9304,7 +9319,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
+    <row r="13" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A13" s="33">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -9422,7 +9437,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
+    <row r="14" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A14" s="33">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -9515,7 +9530,7 @@
       </c>
       <c r="AD14" s="337">
         <f t="shared" ca="1" si="7"/>
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="AE14" s="92"/>
       <c r="AG14" s="238" t="str">
@@ -9538,7 +9553,7 @@
         <v>YES</v>
       </c>
     </row>
-    <row r="15" spans="1:35" s="9" customFormat="1" ht="63" hidden="1">
+    <row r="15" spans="1:35" s="9" customFormat="1" ht="63">
       <c r="A15" s="33">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -9631,7 +9646,7 @@
       </c>
       <c r="AD15" s="337">
         <f t="shared" ca="1" si="7"/>
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="AE15" s="92"/>
       <c r="AG15" s="238" t="str">
@@ -9654,7 +9669,7 @@
         <v>YES</v>
       </c>
     </row>
-    <row r="16" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
+    <row r="16" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A16" s="33">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -9772,7 +9787,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
+    <row r="17" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A17" s="33">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -9888,7 +9903,7 @@
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
+    <row r="18" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A18" s="33">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -10006,7 +10021,7 @@
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
+    <row r="19" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A19" s="33">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -10124,7 +10139,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
+    <row r="20" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A20" s="33">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -10240,7 +10255,7 @@
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
+    <row r="21" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A21" s="33">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -10358,7 +10373,7 @@
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
+    <row r="22" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A22" s="33">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -10476,7 +10491,7 @@
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
+    <row r="23" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A23" s="33">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -10592,7 +10607,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
+    <row r="24" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A24" s="33">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -10712,7 +10727,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:35" s="9" customFormat="1" ht="63" hidden="1">
+    <row r="25" spans="1:35" s="9" customFormat="1" ht="63">
       <c r="A25" s="33">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -10828,7 +10843,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
+    <row r="26" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A26" s="33">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -10944,7 +10959,7 @@
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
+    <row r="27" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A27" s="33">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -11062,7 +11077,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
+    <row r="28" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A28" s="33">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -11180,7 +11195,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
+    <row r="29" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A29" s="33">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -11296,7 +11311,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
+    <row r="30" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A30" s="33">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -11414,7 +11429,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
+    <row r="31" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A31" s="33">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -11532,7 +11547,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
+    <row r="32" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A32" s="33">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -11648,7 +11663,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
+    <row r="33" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A33" s="33">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -11766,7 +11781,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
+    <row r="34" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A34" s="33">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -11882,7 +11897,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
+    <row r="35" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A35" s="33">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -11998,7 +12013,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
+    <row r="36" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A36" s="33">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -12114,7 +12129,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
+    <row r="37" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A37" s="33">
         <f t="shared" si="0"/>
         <v>31</v>
@@ -12230,7 +12245,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
+    <row r="38" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A38" s="33">
         <f t="shared" si="0"/>
         <v>32</v>
@@ -12346,7 +12361,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:35" s="9" customFormat="1" ht="63" hidden="1">
+    <row r="39" spans="1:35" s="9" customFormat="1" ht="63">
       <c r="A39" s="33">
         <f t="shared" ref="A39:A70" si="10">A38+1</f>
         <v>33</v>
@@ -12462,7 +12477,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
+    <row r="40" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A40" s="33">
         <f t="shared" si="10"/>
         <v>34</v>
@@ -12578,7 +12593,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
+    <row r="41" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A41" s="33">
         <f t="shared" si="10"/>
         <v>35</v>
@@ -12694,7 +12709,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
+    <row r="42" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A42" s="33">
         <f t="shared" si="10"/>
         <v>36</v>
@@ -12810,7 +12825,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
+    <row r="43" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A43" s="33">
         <f t="shared" si="10"/>
         <v>37</v>
@@ -12926,7 +12941,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
+    <row r="44" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A44" s="33">
         <f t="shared" si="10"/>
         <v>38</v>
@@ -13019,7 +13034,7 @@
       </c>
       <c r="AD44" s="337">
         <f t="shared" ca="1" si="13"/>
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="AE44" s="92"/>
       <c r="AG44" s="238" t="str">
@@ -13042,7 +13057,7 @@
         <v>YES</v>
       </c>
     </row>
-    <row r="45" spans="1:35" s="9" customFormat="1" ht="94.5" hidden="1">
+    <row r="45" spans="1:35" s="9" customFormat="1" ht="94.5">
       <c r="A45" s="33">
         <f t="shared" si="10"/>
         <v>39</v>
@@ -13160,7 +13175,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
+    <row r="46" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A46" s="33">
         <f t="shared" si="10"/>
         <v>40</v>
@@ -13253,7 +13268,7 @@
       </c>
       <c r="AD46" s="337">
         <f t="shared" ca="1" si="13"/>
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AE46" s="92"/>
       <c r="AG46" s="238" t="str">
@@ -13276,7 +13291,7 @@
         <v>YES</v>
       </c>
     </row>
-    <row r="47" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
+    <row r="47" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A47" s="33">
         <f t="shared" si="10"/>
         <v>41</v>
@@ -13392,7 +13407,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
+    <row r="48" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A48" s="33">
         <f t="shared" si="10"/>
         <v>42</v>
@@ -13508,7 +13523,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:35" s="9" customFormat="1" ht="94.5" hidden="1">
+    <row r="49" spans="1:35" s="9" customFormat="1" ht="94.5">
       <c r="A49" s="33">
         <f t="shared" si="10"/>
         <v>43</v>
@@ -13626,7 +13641,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:35" s="9" customFormat="1" ht="78.75" hidden="1">
+    <row r="50" spans="1:35" s="9" customFormat="1" ht="78.75">
       <c r="A50" s="33">
         <f t="shared" si="10"/>
         <v>44</v>
@@ -13719,7 +13734,7 @@
       </c>
       <c r="AD50" s="337">
         <f t="shared" ca="1" si="13"/>
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AE50" s="92"/>
       <c r="AG50" s="238" t="str">
@@ -13742,7 +13757,7 @@
         <v>YES</v>
       </c>
     </row>
-    <row r="51" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
+    <row r="51" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A51" s="33">
         <f t="shared" si="10"/>
         <v>45</v>
@@ -13770,7 +13785,7 @@
       <c r="I51" s="138"/>
       <c r="J51" s="164">
         <f t="shared" ca="1" si="3"/>
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="K51" s="47"/>
       <c r="L51" s="164" t="s">
@@ -13832,7 +13847,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="1:35" s="9" customFormat="1" ht="63" hidden="1">
+    <row r="52" spans="1:35" s="9" customFormat="1" ht="63">
       <c r="A52" s="33">
         <f t="shared" si="10"/>
         <v>46</v>
@@ -13950,7 +13965,7 @@
         <v/>
       </c>
     </row>
-    <row r="53" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
+    <row r="53" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A53" s="33">
         <f t="shared" si="10"/>
         <v>47</v>
@@ -14068,7 +14083,7 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
+    <row r="54" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A54" s="33">
         <f t="shared" si="10"/>
         <v>48</v>
@@ -14184,7 +14199,7 @@
         <v/>
       </c>
     </row>
-    <row r="55" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
+    <row r="55" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A55" s="33">
         <f t="shared" si="10"/>
         <v>49</v>
@@ -14300,7 +14315,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
+    <row r="56" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A56" s="33">
         <f t="shared" si="10"/>
         <v>50</v>
@@ -14418,7 +14433,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
+    <row r="57" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A57" s="33">
         <f t="shared" si="10"/>
         <v>51</v>
@@ -14534,7 +14549,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
+    <row r="58" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A58" s="33">
         <f t="shared" si="10"/>
         <v>52</v>
@@ -14627,7 +14642,7 @@
       </c>
       <c r="AD58" s="337">
         <f t="shared" ca="1" si="13"/>
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AE58" s="92"/>
       <c r="AG58" s="238" t="str">
@@ -14650,7 +14665,7 @@
         <v>YES</v>
       </c>
     </row>
-    <row r="59" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
+    <row r="59" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A59" s="33">
         <f t="shared" si="10"/>
         <v>53</v>
@@ -14678,7 +14693,7 @@
       <c r="I59" s="138"/>
       <c r="J59" s="164">
         <f t="shared" ca="1" si="3"/>
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K59" s="47"/>
       <c r="L59" s="164" t="s">
@@ -14740,7 +14755,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
+    <row r="60" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A60" s="33">
         <f t="shared" si="10"/>
         <v>54</v>
@@ -14833,7 +14848,7 @@
       </c>
       <c r="AD60" s="337">
         <f t="shared" ca="1" si="13"/>
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AE60" s="92" t="s">
         <v>878</v>
@@ -14858,7 +14873,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
+    <row r="61" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A61" s="33">
         <f t="shared" si="10"/>
         <v>55</v>
@@ -14951,7 +14966,7 @@
       </c>
       <c r="AD61" s="337">
         <f t="shared" ca="1" si="13"/>
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AE61" s="92"/>
       <c r="AG61" s="238" t="str">
@@ -14974,7 +14989,7 @@
         <v>YES</v>
       </c>
     </row>
-    <row r="62" spans="1:35" s="9" customFormat="1" ht="78.75" hidden="1">
+    <row r="62" spans="1:35" s="9" customFormat="1" ht="78.75">
       <c r="A62" s="33">
         <f t="shared" si="10"/>
         <v>56</v>
@@ -15092,7 +15107,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
+    <row r="63" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A63" s="33">
         <f t="shared" si="10"/>
         <v>57</v>
@@ -15210,7 +15225,7 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
+    <row r="64" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A64" s="33">
         <f t="shared" si="10"/>
         <v>58</v>
@@ -15328,7 +15343,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
+    <row r="65" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A65" s="33">
         <f t="shared" si="10"/>
         <v>59</v>
@@ -15446,7 +15461,7 @@
         <v/>
       </c>
     </row>
-    <row r="66" spans="1:35" s="9" customFormat="1" ht="94.5" hidden="1">
+    <row r="66" spans="1:35" s="9" customFormat="1" ht="94.5">
       <c r="A66" s="33">
         <f t="shared" si="10"/>
         <v>60</v>
@@ -15564,7 +15579,7 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="1:35" s="9" customFormat="1" ht="78.75" hidden="1">
+    <row r="67" spans="1:35" s="9" customFormat="1" ht="78.75">
       <c r="A67" s="33">
         <f t="shared" si="10"/>
         <v>61</v>
@@ -15680,7 +15695,7 @@
         <v/>
       </c>
     </row>
-    <row r="68" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
+    <row r="68" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A68" s="33">
         <f t="shared" si="10"/>
         <v>62</v>
@@ -15771,7 +15786,7 @@
       </c>
       <c r="AD68" s="337">
         <f t="shared" ca="1" si="13"/>
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AE68" s="92"/>
       <c r="AG68" s="238" t="str">
@@ -15794,7 +15809,7 @@
         <v>YES</v>
       </c>
     </row>
-    <row r="69" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
+    <row r="69" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A69" s="33">
         <f>A68+1</f>
         <v>63</v>
@@ -15902,7 +15917,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
+    <row r="70" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A70" s="33">
         <f t="shared" si="10"/>
         <v>64</v>
@@ -16018,7 +16033,7 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
+    <row r="71" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A71" s="33">
         <f t="shared" ref="A71:A135" si="19">A70+1</f>
         <v>65</v>
@@ -16134,7 +16149,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
+    <row r="72" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A72" s="33">
         <f t="shared" si="19"/>
         <v>66</v>
@@ -16250,7 +16265,7 @@
         <v/>
       </c>
     </row>
-    <row r="73" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
+    <row r="73" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A73" s="33">
         <f t="shared" si="19"/>
         <v>67</v>
@@ -16366,7 +16381,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
+    <row r="74" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A74" s="33">
         <f t="shared" si="19"/>
         <v>68</v>
@@ -16484,7 +16499,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
+    <row r="75" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A75" s="33">
         <f t="shared" si="19"/>
         <v>69</v>
@@ -16602,7 +16617,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="1:35" s="9" customFormat="1" ht="63" hidden="1">
+    <row r="76" spans="1:35" s="9" customFormat="1" ht="63">
       <c r="A76" s="33">
         <f t="shared" si="19"/>
         <v>70</v>
@@ -16720,7 +16735,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
+    <row r="77" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A77" s="33">
         <f t="shared" si="19"/>
         <v>71</v>
@@ -16838,7 +16853,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
+    <row r="78" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A78" s="33">
         <f t="shared" si="19"/>
         <v>72</v>
@@ -16954,7 +16969,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:35" s="9" customFormat="1" ht="141.75" hidden="1">
+    <row r="79" spans="1:35" s="9" customFormat="1" ht="141.75">
       <c r="A79" s="33">
         <f t="shared" si="19"/>
         <v>73</v>
@@ -17064,7 +17079,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:35" s="9" customFormat="1" ht="141.75" hidden="1">
+    <row r="80" spans="1:35" s="9" customFormat="1" ht="141.75">
       <c r="A80" s="33">
         <f t="shared" si="19"/>
         <v>74</v>
@@ -17174,7 +17189,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:35" s="9" customFormat="1" ht="126" hidden="1">
+    <row r="81" spans="1:35" s="9" customFormat="1" ht="126">
       <c r="A81" s="33">
         <f t="shared" si="19"/>
         <v>75</v>
@@ -17280,7 +17295,7 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="1:35" s="9" customFormat="1" ht="63" hidden="1">
+    <row r="82" spans="1:35" s="9" customFormat="1" ht="63">
       <c r="A82" s="33">
         <f t="shared" si="19"/>
         <v>76</v>
@@ -17396,7 +17411,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="1:35" s="9" customFormat="1" ht="63" hidden="1">
+    <row r="83" spans="1:35" s="9" customFormat="1" ht="63">
       <c r="A83" s="33">
         <f t="shared" si="19"/>
         <v>77</v>
@@ -17485,7 +17500,7 @@
         <v/>
       </c>
     </row>
-    <row r="84" spans="1:35" s="9" customFormat="1" ht="141.75" hidden="1">
+    <row r="84" spans="1:35" s="9" customFormat="1" ht="141.75">
       <c r="A84" s="33">
         <f t="shared" si="19"/>
         <v>78</v>
@@ -17595,7 +17610,7 @@
         <v/>
       </c>
     </row>
-    <row r="85" spans="1:35" s="9" customFormat="1" ht="110.25" hidden="1">
+    <row r="85" spans="1:35" s="9" customFormat="1" ht="110.25">
       <c r="A85" s="33">
         <f t="shared" si="19"/>
         <v>79</v>
@@ -17713,7 +17728,7 @@
         <v/>
       </c>
     </row>
-    <row r="86" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
+    <row r="86" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A86" s="33">
         <f t="shared" si="19"/>
         <v>80</v>
@@ -17823,7 +17838,7 @@
         <v/>
       </c>
     </row>
-    <row r="87" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
+    <row r="87" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A87" s="33">
         <f t="shared" si="19"/>
         <v>81</v>
@@ -17916,7 +17931,7 @@
         <v/>
       </c>
     </row>
-    <row r="88" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
+    <row r="88" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A88" s="33">
         <f t="shared" si="19"/>
         <v>82</v>
@@ -18028,7 +18043,7 @@
         <v/>
       </c>
     </row>
-    <row r="89" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
+    <row r="89" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A89" s="33">
         <f t="shared" si="19"/>
         <v>83</v>
@@ -18140,7 +18155,7 @@
         <v/>
       </c>
     </row>
-    <row r="90" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
+    <row r="90" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A90" s="33">
         <f t="shared" si="19"/>
         <v>84</v>
@@ -18252,7 +18267,7 @@
         <v/>
       </c>
     </row>
-    <row r="91" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
+    <row r="91" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A91" s="33">
         <f t="shared" si="19"/>
         <v>85</v>
@@ -18364,7 +18379,7 @@
         <v/>
       </c>
     </row>
-    <row r="92" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
+    <row r="92" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A92" s="33">
         <f t="shared" si="19"/>
         <v>86</v>
@@ -18393,11 +18408,11 @@
       <c r="I92" s="138"/>
       <c r="J92" s="164">
         <f t="shared" ca="1" si="27"/>
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="K92" s="47">
         <f t="shared" ca="1" si="28"/>
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="L92" s="164" t="s">
         <v>1004</v>
@@ -18462,7 +18477,7 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="1:35" s="9" customFormat="1" ht="63" hidden="1">
+    <row r="93" spans="1:35" s="9" customFormat="1" ht="63">
       <c r="A93" s="33">
         <f t="shared" si="19"/>
         <v>87</v>
@@ -18495,11 +18510,11 @@
       </c>
       <c r="J93" s="164">
         <f t="shared" ca="1" si="27"/>
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="K93" s="47">
         <f t="shared" ca="1" si="28"/>
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="L93" s="164" t="s">
         <v>13</v>
@@ -18564,7 +18579,7 @@
         <v/>
       </c>
     </row>
-    <row r="94" spans="1:35" s="9" customFormat="1" ht="177.75" hidden="1" customHeight="1">
+    <row r="94" spans="1:35" s="9" customFormat="1" ht="177.75" customHeight="1">
       <c r="A94" s="33">
         <f t="shared" si="19"/>
         <v>88</v>
@@ -18674,7 +18689,7 @@
         <v>YES</v>
       </c>
     </row>
-    <row r="95" spans="1:35" s="9" customFormat="1" ht="78.75" hidden="1">
+    <row r="95" spans="1:35" s="9" customFormat="1" ht="78.75">
       <c r="A95" s="33">
         <f t="shared" si="19"/>
         <v>89</v>
@@ -18763,7 +18778,7 @@
         <v/>
       </c>
     </row>
-    <row r="96" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
+    <row r="96" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A96" s="33">
         <f t="shared" si="19"/>
         <v>90</v>
@@ -18873,7 +18888,7 @@
         <v>YES</v>
       </c>
     </row>
-    <row r="97" spans="1:35" s="9" customFormat="1" ht="78.75" hidden="1">
+    <row r="97" spans="1:35" s="9" customFormat="1" ht="78.75">
       <c r="A97" s="33">
         <f t="shared" si="19"/>
         <v>91</v>
@@ -18981,7 +18996,7 @@
         <v>YES</v>
       </c>
     </row>
-    <row r="98" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
+    <row r="98" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A98" s="33">
         <f t="shared" si="19"/>
         <v>92</v>
@@ -19089,7 +19104,7 @@
         <v>YES</v>
       </c>
     </row>
-    <row r="99" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
+    <row r="99" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A99" s="33">
         <f t="shared" si="19"/>
         <v>93</v>
@@ -19201,7 +19216,7 @@
         <v/>
       </c>
     </row>
-    <row r="100" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
+    <row r="100" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A100" s="33">
         <f t="shared" si="19"/>
         <v>94</v>
@@ -19309,7 +19324,7 @@
         <v/>
       </c>
     </row>
-    <row r="101" spans="1:35" s="9" customFormat="1" ht="78.75" hidden="1">
+    <row r="101" spans="1:35" s="9" customFormat="1" ht="78.75">
       <c r="A101" s="33">
         <f t="shared" si="19"/>
         <v>95</v>
@@ -19415,7 +19430,7 @@
         <v>YES</v>
       </c>
     </row>
-    <row r="102" spans="1:35" s="9" customFormat="1" ht="78.75" hidden="1">
+    <row r="102" spans="1:35" s="9" customFormat="1" ht="78.75">
       <c r="A102" s="33">
         <f t="shared" si="19"/>
         <v>96</v>
@@ -19507,7 +19522,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:35" s="9" customFormat="1" ht="63" hidden="1">
+    <row r="103" spans="1:35" s="9" customFormat="1" ht="63">
       <c r="A103" s="33">
         <f t="shared" si="19"/>
         <v>97</v>
@@ -19619,7 +19634,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:35" s="9" customFormat="1" ht="63" hidden="1">
+    <row r="104" spans="1:35" s="9" customFormat="1" ht="63">
       <c r="A104" s="33">
         <f t="shared" si="19"/>
         <v>98</v>
@@ -19731,7 +19746,7 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="1:35" s="9" customFormat="1" ht="63" hidden="1">
+    <row r="105" spans="1:35" s="9" customFormat="1" ht="63">
       <c r="A105" s="33">
         <f t="shared" si="19"/>
         <v>99</v>
@@ -19843,7 +19858,7 @@
         <v/>
       </c>
     </row>
-    <row r="106" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
+    <row r="106" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A106" s="33">
         <f t="shared" si="19"/>
         <v>100</v>
@@ -19951,7 +19966,7 @@
         <v/>
       </c>
     </row>
-    <row r="107" spans="1:35" s="9" customFormat="1" ht="63" hidden="1">
+    <row r="107" spans="1:35" s="9" customFormat="1" ht="63">
       <c r="A107" s="33">
         <f t="shared" si="19"/>
         <v>101</v>
@@ -20042,7 +20057,7 @@
         <v/>
       </c>
     </row>
-    <row r="108" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
+    <row r="108" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A108" s="33">
         <f t="shared" si="19"/>
         <v>102</v>
@@ -20148,7 +20163,7 @@
         <v>YES</v>
       </c>
     </row>
-    <row r="109" spans="1:35" s="9" customFormat="1" ht="63" hidden="1">
+    <row r="109" spans="1:35" s="9" customFormat="1" ht="63">
       <c r="A109" s="33">
         <f t="shared" si="19"/>
         <v>103</v>
@@ -20256,7 +20271,7 @@
         <v/>
       </c>
     </row>
-    <row r="110" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
+    <row r="110" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A110" s="33">
         <f t="shared" si="19"/>
         <v>104</v>
@@ -20360,7 +20375,7 @@
         <v/>
       </c>
     </row>
-    <row r="111" spans="1:35" s="9" customFormat="1" ht="63" hidden="1">
+    <row r="111" spans="1:35" s="9" customFormat="1" ht="63">
       <c r="A111" s="33">
         <f t="shared" si="19"/>
         <v>105</v>
@@ -20391,11 +20406,11 @@
       <c r="I111" s="23"/>
       <c r="J111" s="164">
         <f t="shared" ca="1" si="30"/>
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="K111" s="47">
         <f t="shared" ca="1" si="31"/>
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="L111" s="164" t="s">
         <v>13</v>
@@ -20458,7 +20473,7 @@
         <v/>
       </c>
     </row>
-    <row r="112" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
+    <row r="112" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A112" s="33">
         <f t="shared" si="19"/>
         <v>106</v>
@@ -20564,7 +20579,7 @@
         <v>YES</v>
       </c>
     </row>
-    <row r="113" spans="1:35" s="9" customFormat="1" ht="110.25" hidden="1">
+    <row r="113" spans="1:35" s="9" customFormat="1" ht="110.25">
       <c r="A113" s="33">
         <f t="shared" si="19"/>
         <v>107</v>
@@ -20670,7 +20685,7 @@
         <v/>
       </c>
     </row>
-    <row r="114" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
+    <row r="114" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A114" s="33">
         <f t="shared" si="19"/>
         <v>108</v>
@@ -20776,7 +20791,7 @@
         <v/>
       </c>
     </row>
-    <row r="115" spans="1:35" s="9" customFormat="1" ht="63" hidden="1">
+    <row r="115" spans="1:35" s="9" customFormat="1" ht="63">
       <c r="A115" s="33">
         <f t="shared" si="19"/>
         <v>109</v>
@@ -20884,7 +20899,7 @@
         <v/>
       </c>
     </row>
-    <row r="116" spans="1:35" s="9" customFormat="1" ht="63" hidden="1">
+    <row r="116" spans="1:35" s="9" customFormat="1" ht="63">
       <c r="A116" s="33">
         <f t="shared" si="19"/>
         <v>110</v>
@@ -20996,7 +21011,7 @@
         <v/>
       </c>
     </row>
-    <row r="117" spans="1:35" s="9" customFormat="1" ht="94.5" hidden="1">
+    <row r="117" spans="1:35" s="9" customFormat="1" ht="94.5">
       <c r="A117" s="33">
         <f t="shared" si="19"/>
         <v>111</v>
@@ -21025,11 +21040,11 @@
       <c r="I117" s="138"/>
       <c r="J117" s="164">
         <f t="shared" ca="1" si="30"/>
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K117" s="47">
         <f t="shared" ca="1" si="31"/>
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="L117" s="164" t="s">
         <v>1004</v>
@@ -21092,7 +21107,7 @@
         <v/>
       </c>
     </row>
-    <row r="118" spans="1:35" s="9" customFormat="1" ht="78.75" hidden="1">
+    <row r="118" spans="1:35" s="9" customFormat="1" ht="78.75">
       <c r="A118" s="33">
         <f t="shared" si="19"/>
         <v>112</v>
@@ -21184,7 +21199,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
+    <row r="119" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A119" s="33">
         <f t="shared" si="19"/>
         <v>113</v>
@@ -21290,7 +21305,7 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:35" s="9" customFormat="1" ht="63" hidden="1">
+    <row r="120" spans="1:35" s="9" customFormat="1" ht="63">
       <c r="A120" s="33">
         <f t="shared" si="19"/>
         <v>114</v>
@@ -21396,7 +21411,7 @@
         <v>YES</v>
       </c>
     </row>
-    <row r="121" spans="1:35" s="9" customFormat="1" ht="63" hidden="1">
+    <row r="121" spans="1:35" s="9" customFormat="1" ht="63">
       <c r="A121" s="33">
         <f t="shared" si="19"/>
         <v>115</v>
@@ -21488,7 +21503,7 @@
         <v/>
       </c>
     </row>
-    <row r="122" spans="1:35" s="9" customFormat="1" ht="63" hidden="1">
+    <row r="122" spans="1:35" s="9" customFormat="1" ht="63">
       <c r="A122" s="33">
         <f t="shared" si="19"/>
         <v>116</v>
@@ -21592,7 +21607,7 @@
         <v>YES</v>
       </c>
     </row>
-    <row r="123" spans="1:35" s="9" customFormat="1" ht="110.25" hidden="1">
+    <row r="123" spans="1:35" s="9" customFormat="1" ht="110.25">
       <c r="A123" s="33">
         <f t="shared" si="19"/>
         <v>117</v>
@@ -21790,7 +21805,7 @@
         <v/>
       </c>
     </row>
-    <row r="125" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
+    <row r="125" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A125" s="33">
         <f t="shared" si="19"/>
         <v>119</v>
@@ -21896,7 +21911,7 @@
         <v/>
       </c>
     </row>
-    <row r="126" spans="1:35" s="9" customFormat="1" ht="110.25" hidden="1">
+    <row r="126" spans="1:35" s="9" customFormat="1" ht="110.25">
       <c r="A126" s="33">
         <f t="shared" si="19"/>
         <v>120</v>
@@ -22002,7 +22017,7 @@
         <v>YES</v>
       </c>
     </row>
-    <row r="127" spans="1:35" s="9" customFormat="1" ht="78.75" hidden="1">
+    <row r="127" spans="1:35" s="9" customFormat="1" ht="78.75">
       <c r="A127" s="33">
         <f t="shared" si="19"/>
         <v>121</v>
@@ -22102,7 +22117,7 @@
         <v/>
       </c>
     </row>
-    <row r="128" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
+    <row r="128" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A128" s="33">
         <f t="shared" si="19"/>
         <v>122</v>
@@ -22133,7 +22148,7 @@
       <c r="I128" s="138"/>
       <c r="J128" s="164">
         <f t="shared" ca="1" si="30"/>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K128" s="47">
         <f t="shared" ca="1" si="31"/>
@@ -22190,7 +22205,7 @@
         <v/>
       </c>
     </row>
-    <row r="129" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
+    <row r="129" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A129" s="33">
         <f t="shared" si="19"/>
         <v>123</v>
@@ -22221,7 +22236,7 @@
       <c r="I129" s="138"/>
       <c r="J129" s="164">
         <f t="shared" ca="1" si="30"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K129" s="47">
         <f t="shared" ca="1" si="31"/>
@@ -22257,7 +22272,9 @@
       <c r="AB129" s="229"/>
       <c r="AC129" s="229"/>
       <c r="AD129" s="337"/>
-      <c r="AE129" s="92"/>
+      <c r="AE129" s="92" t="s">
+        <v>1064</v>
+      </c>
       <c r="AG129" s="238" t="str">
         <f t="shared" si="75"/>
         <v>LTIA-5.11- LTICT- 72100-RFA-MSS-0002</v>
@@ -22278,7 +22295,7 @@
         <v/>
       </c>
     </row>
-    <row r="130" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
+    <row r="130" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A130" s="33">
         <f t="shared" si="19"/>
         <v>124</v>
@@ -22309,7 +22326,7 @@
       <c r="I130" s="138"/>
       <c r="J130" s="164">
         <f t="shared" ca="1" si="30"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K130" s="47">
         <f t="shared" ca="1" si="31"/>
@@ -22366,7 +22383,7 @@
         <v/>
       </c>
     </row>
-    <row r="131" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
+    <row r="131" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A131" s="33">
         <f t="shared" si="19"/>
         <v>125</v>
@@ -22397,7 +22414,7 @@
       <c r="I131" s="138"/>
       <c r="J131" s="164">
         <f t="shared" ca="1" si="30"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K131" s="47">
         <f t="shared" ca="1" si="31"/>
@@ -22433,7 +22450,9 @@
       <c r="AB131" s="229"/>
       <c r="AC131" s="229"/>
       <c r="AD131" s="337"/>
-      <c r="AE131" s="92"/>
+      <c r="AE131" s="92" t="s">
+        <v>1065</v>
+      </c>
       <c r="AG131" s="238" t="str">
         <f t="shared" si="75"/>
         <v>LTIA-5.11-LTICT- 72120 -RFA-MSS-0004</v>
@@ -22454,7 +22473,7 @@
         <v/>
       </c>
     </row>
-    <row r="132" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
+    <row r="132" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A132" s="33">
         <f t="shared" si="19"/>
         <v>126</v>
@@ -22485,7 +22504,7 @@
       <c r="I132" s="138"/>
       <c r="J132" s="164">
         <f t="shared" ca="1" si="30"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K132" s="47">
         <f t="shared" ca="1" si="31"/>
@@ -22521,7 +22540,9 @@
       <c r="AB132" s="229"/>
       <c r="AC132" s="229"/>
       <c r="AD132" s="337"/>
-      <c r="AE132" s="92"/>
+      <c r="AE132" s="92" t="s">
+        <v>1065</v>
+      </c>
       <c r="AG132" s="238" t="str">
         <f t="shared" si="75"/>
         <v>LTIA-5.11-LTICT-70100-RFA-MSS-0007</v>
@@ -22542,7 +22563,7 @@
         <v/>
       </c>
     </row>
-    <row r="133" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
+    <row r="133" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A133" s="33">
         <f t="shared" si="19"/>
         <v>127</v>
@@ -22573,7 +22594,7 @@
       <c r="I133" s="138"/>
       <c r="J133" s="164">
         <f t="shared" ca="1" si="30"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K133" s="47">
         <f t="shared" ca="1" si="31"/>
@@ -22630,7 +22651,7 @@
         <v/>
       </c>
     </row>
-    <row r="134" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
+    <row r="134" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A134" s="33">
         <f t="shared" si="19"/>
         <v>128</v>
@@ -22661,7 +22682,7 @@
       <c r="I134" s="138"/>
       <c r="J134" s="164">
         <f t="shared" ca="1" si="30"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K134" s="47">
         <f t="shared" ca="1" si="31"/>
@@ -22718,7 +22739,7 @@
         <v/>
       </c>
     </row>
-    <row r="135" spans="1:35" s="9" customFormat="1" ht="47.25" hidden="1">
+    <row r="135" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A135" s="33">
         <f t="shared" si="19"/>
         <v>129</v>
@@ -22749,7 +22770,7 @@
       <c r="I135" s="138"/>
       <c r="J135" s="164">
         <f t="shared" ca="1" si="30"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K135" s="47">
         <f t="shared" ca="1" si="31"/>
@@ -22806,7 +22827,7 @@
         <v/>
       </c>
     </row>
-    <row r="136" spans="1:35" s="9" customFormat="1" hidden="1">
+    <row r="136" spans="1:35" s="9" customFormat="1">
       <c r="A136" s="33"/>
       <c r="B136" s="330"/>
       <c r="C136" s="164"/>
@@ -22848,7 +22869,7 @@
         <v/>
       </c>
     </row>
-    <row r="137" spans="1:35" s="9" customFormat="1" ht="16.5" hidden="1" thickBot="1">
+    <row r="137" spans="1:35" s="9" customFormat="1" ht="16.5" thickBot="1">
       <c r="A137" s="347"/>
       <c r="B137" s="338"/>
       <c r="C137" s="178"/>
@@ -23731,11 +23752,6 @@
     </row>
   </sheetData>
   <autoFilter ref="A6:AE137" xr:uid="{C724CDAB-378C-47DB-9F45-08EE3BFB6E8B}">
-    <filterColumn colId="4">
-      <filters>
-        <filter val="LTIA-5.10-VIETUR-70000-RFA-MAS-0821"/>
-      </filters>
-    </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A7:AE69">
       <sortCondition ref="T6:T69"/>
     </sortState>
@@ -24335,7 +24351,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D8E8261-1CEF-42DB-8488-C430D415EC88}">
-  <dimension ref="A1:AI52"/>
+  <dimension ref="A1:AI53"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" customWidth="1"/>
@@ -24379,7 +24395,7 @@
       </c>
       <c r="I1" s="176">
         <f ca="1">TODAY()</f>
-        <v>46307</v>
+        <v>46309</v>
       </c>
       <c r="J1" s="131"/>
       <c r="K1" s="197"/>
@@ -24648,7 +24664,7 @@
     </row>
     <row r="7" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A7" s="33">
-        <f t="shared" ref="A7:A39" si="0">A6+1</f>
+        <f t="shared" ref="A7:A40" si="0">A6+1</f>
         <v>1</v>
       </c>
       <c r="B7" s="33" t="str">
@@ -24662,7 +24678,7 @@
         <v>519</v>
       </c>
       <c r="E7" s="174">
-        <f t="shared" ref="E7:E39" si="2">IF($T7=0,$S7+22,$T7+21)</f>
+        <f t="shared" ref="E7:E40" si="2">IF($T7=0,$S7+22,$T7+21)</f>
         <v>45490</v>
       </c>
       <c r="F7" s="30" t="s">
@@ -24748,8 +24764,8 @@
       <c r="AH7" s="242" t="b" cm="1">
         <f t="array" ref="AH7">$D7=_xlfn.XLOOKUP(
 AG7,
-_xlfn._xlws.FILTER($AG$7:$AG$4868,$K$7:$K$4868&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4868,$K$7:$K$4868&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4869,$K$7:$K$4869&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4869,$K$7:$K$4869&lt;&gt;"X"),
 "",
 0,
 -1
@@ -24794,7 +24810,7 @@
         <v>25</v>
       </c>
       <c r="J8" s="47">
-        <f t="shared" ref="J8:J39" si="4">IF(($I8-21)&gt;0,$I8-21,0)</f>
+        <f t="shared" ref="J8:J40" si="4">IF(($I8-21)&gt;0,$I8-21,0)</f>
         <v>4</v>
       </c>
       <c r="K8" s="164"/>
@@ -24841,14 +24857,14 @@
         <v>45674</v>
       </c>
       <c r="Z8" s="29">
-        <f t="shared" ref="Z8:Z41" si="5">IF(AND($Q8="",$H8=""),"",IF(OR($Q8="B",$Q8="C"),IF($Y8&lt;&gt;"",$Y8+7,IF($X8&lt;&gt;"",$X8+8,"")),IF($Q8="",IF(OR($H8="B",$H8="C"),IF($V8&lt;&gt;"",$V8+7,IF($U8&lt;&gt;"",$U8+8,""))),"")))</f>
+        <f t="shared" ref="Z8:Z42" si="5">IF(AND($Q8="",$H8=""),"",IF(OR($Q8="B",$Q8="C"),IF($Y8&lt;&gt;"",$Y8+7,IF($X8&lt;&gt;"",$X8+8,"")),IF($Q8="",IF(OR($H8="B",$H8="C"),IF($V8&lt;&gt;"",$V8+7,IF($U8&lt;&gt;"",$U8+8,""))),"")))</f>
         <v>45681</v>
       </c>
       <c r="AA8" s="229">
         <v>45850</v>
       </c>
       <c r="AB8" s="229" t="str">
-        <f t="shared" ref="AB8:AB39" si="6">IF(OR($Q8="B",$Q8="C"),IF($Z8="","",IF($AA8="",IF($Z8&gt;=$I$1,"In progress","Not submit yet"),IF($Z8&gt;=$AA8,"Timely Response","Late Resubmission"))),"")</f>
+        <f t="shared" ref="AB8:AB40" si="6">IF(OR($Q8="B",$Q8="C"),IF($Z8="","",IF($AA8="",IF($Z8&gt;=$I$1,"In progress","Not submit yet"),IF($Z8&gt;=$AA8,"Timely Response","Late Resubmission"))),"")</f>
         <v>Late Resubmission</v>
       </c>
       <c r="AC8" s="183">
@@ -24857,14 +24873,14 @@
       </c>
       <c r="AD8" s="92"/>
       <c r="AG8" s="238" t="str">
-        <f t="shared" ref="AG8:AG39" si="8">IF(AND(RIGHT($D8,1)&gt;="A",RIGHT($D8,1)&lt;="Z"),LEFT($D8,LEN($D8)-1),$D8)</f>
+        <f t="shared" ref="AG8:AG40" si="8">IF(AND(RIGHT($D8,1)&gt;="A",RIGHT($D8,1)&lt;="Z"),LEFT($D8,LEN($D8)-1),$D8)</f>
         <v>LTIA-5.10-VIETUR-80000-RFA-SDS-0122</v>
       </c>
       <c r="AH8" s="243" t="b" cm="1">
         <f t="array" ref="AH8">$D8=_xlfn.XLOOKUP(
 AG8,
-_xlfn._xlws.FILTER($AG$7:$AG$4868,$K$7:$K$4868&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4868,$K$7:$K$4868&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4869,$K$7:$K$4869&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4869,$K$7:$K$4869&lt;&gt;"X"),
 "",
 0,
 -1
@@ -24985,8 +25001,8 @@
       <c r="AH9" s="243" t="b" cm="1">
         <f t="array" ref="AH9">$D9=_xlfn.XLOOKUP(
 AG9,
-_xlfn._xlws.FILTER($AG$7:$AG$4868,$K$7:$K$4868&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4868,$K$7:$K$4868&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4869,$K$7:$K$4869&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4869,$K$7:$K$4869&lt;&gt;"X"),
 "",
 0,
 -1
@@ -25100,8 +25116,8 @@
       <c r="AH10" s="243" t="b" cm="1">
         <f t="array" ref="AH10">$D10=_xlfn.XLOOKUP(
 AG10,
-_xlfn._xlws.FILTER($AG$7:$AG$4868,$K$7:$K$4868&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4868,$K$7:$K$4868&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4869,$K$7:$K$4869&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4869,$K$7:$K$4869&lt;&gt;"X"),
 "",
 0,
 -1
@@ -25217,8 +25233,8 @@
       <c r="AH11" s="243" t="b" cm="1">
         <f t="array" ref="AH11">$D11=_xlfn.XLOOKUP(
 AG11,
-_xlfn._xlws.FILTER($AG$7:$AG$4868,$K$7:$K$4868&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4868,$K$7:$K$4868&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4869,$K$7:$K$4869&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4869,$K$7:$K$4869&lt;&gt;"X"),
 "",
 0,
 -1
@@ -25320,7 +25336,7 @@
       </c>
       <c r="AC12" s="183">
         <f t="shared" ca="1" si="7"/>
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="AD12" s="92"/>
       <c r="AG12" s="238" t="str">
@@ -25330,8 +25346,8 @@
       <c r="AH12" s="243" t="b" cm="1">
         <f t="array" ref="AH12">$D12=_xlfn.XLOOKUP(
 AG12,
-_xlfn._xlws.FILTER($AG$7:$AG$4868,$K$7:$K$4868&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4868,$K$7:$K$4868&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4869,$K$7:$K$4869&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4869,$K$7:$K$4869&lt;&gt;"X"),
 "",
 0,
 -1
@@ -25443,8 +25459,8 @@
       <c r="AH13" s="243" t="b" cm="1">
         <f t="array" ref="AH13">$D13=_xlfn.XLOOKUP(
 AG13,
-_xlfn._xlws.FILTER($AG$7:$AG$4868,$K$7:$K$4868&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4868,$K$7:$K$4868&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4869,$K$7:$K$4869&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4869,$K$7:$K$4869&lt;&gt;"X"),
 "",
 0,
 -1
@@ -25485,7 +25501,7 @@
         <v>2</v>
       </c>
       <c r="I14" s="164">
-        <f t="shared" ref="I14:I39" si="10">IF(ISBLANK($V14),_xlfn.DAYS($I$1,$T14),_xlfn.DAYS($V14,$T14))</f>
+        <f t="shared" ref="I14:I40" si="10">IF(ISBLANK($V14),_xlfn.DAYS($I$1,$T14),_xlfn.DAYS($V14,$T14))</f>
         <v>25</v>
       </c>
       <c r="J14" s="47">
@@ -25546,7 +25562,7 @@
       </c>
       <c r="AC14" s="183">
         <f t="shared" ca="1" si="7"/>
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="AD14" s="92"/>
       <c r="AG14" s="238" t="str">
@@ -25556,8 +25572,8 @@
       <c r="AH14" s="243" t="b" cm="1">
         <f t="array" ref="AH14">$D14=_xlfn.XLOOKUP(
 AG14,
-_xlfn._xlws.FILTER($AG$7:$AG$4868,$K$7:$K$4868&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4868,$K$7:$K$4868&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4869,$K$7:$K$4869&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4869,$K$7:$K$4869&lt;&gt;"X"),
 "",
 0,
 -1
@@ -25669,8 +25685,8 @@
       <c r="AH15" s="243" t="b" cm="1">
         <f t="array" ref="AH15">$D15=_xlfn.XLOOKUP(
 AG15,
-_xlfn._xlws.FILTER($AG$7:$AG$4868,$K$7:$K$4868&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4868,$K$7:$K$4868&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4869,$K$7:$K$4869&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4869,$K$7:$K$4869&lt;&gt;"X"),
 "",
 0,
 -1
@@ -25772,7 +25788,7 @@
       </c>
       <c r="AC16" s="183">
         <f t="shared" ca="1" si="7"/>
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AD16" s="92"/>
       <c r="AG16" s="238" t="str">
@@ -25782,8 +25798,8 @@
       <c r="AH16" s="243" t="b" cm="1">
         <f t="array" ref="AH16">$D16=_xlfn.XLOOKUP(
 AG16,
-_xlfn._xlws.FILTER($AG$7:$AG$4868,$K$7:$K$4868&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4868,$K$7:$K$4868&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4869,$K$7:$K$4869&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4869,$K$7:$K$4869&lt;&gt;"X"),
 "",
 0,
 -1
@@ -25885,7 +25901,7 @@
       </c>
       <c r="AC17" s="183">
         <f t="shared" ca="1" si="7"/>
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AD17" s="92"/>
       <c r="AG17" s="238" t="str">
@@ -25895,8 +25911,8 @@
       <c r="AH17" s="243" t="b" cm="1">
         <f t="array" ref="AH17">$D17=_xlfn.XLOOKUP(
 AG17,
-_xlfn._xlws.FILTER($AG$7:$AG$4868,$K$7:$K$4868&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4868,$K$7:$K$4868&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4869,$K$7:$K$4869&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4869,$K$7:$K$4869&lt;&gt;"X"),
 "",
 0,
 -1
@@ -25998,7 +26014,7 @@
       </c>
       <c r="AC18" s="183">
         <f t="shared" ca="1" si="7"/>
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AD18" s="92"/>
       <c r="AG18" s="238" t="str">
@@ -26008,8 +26024,8 @@
       <c r="AH18" s="243" t="b" cm="1">
         <f t="array" ref="AH18">$D18=_xlfn.XLOOKUP(
 AG18,
-_xlfn._xlws.FILTER($AG$7:$AG$4868,$K$7:$K$4868&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4868,$K$7:$K$4868&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4869,$K$7:$K$4869&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4869,$K$7:$K$4869&lt;&gt;"X"),
 "",
 0,
 -1
@@ -26123,8 +26139,8 @@
       <c r="AH19" s="243" t="b" cm="1">
         <f t="array" ref="AH19">$D19=_xlfn.XLOOKUP(
 AG19,
-_xlfn._xlws.FILTER($AG$7:$AG$4868,$K$7:$K$4868&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4868,$K$7:$K$4868&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4869,$K$7:$K$4869&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4869,$K$7:$K$4869&lt;&gt;"X"),
 "",
 0,
 -1
@@ -26238,8 +26254,8 @@
       <c r="AH20" s="243" t="b" cm="1">
         <f t="array" ref="AH20">$D20=_xlfn.XLOOKUP(
 AG20,
-_xlfn._xlws.FILTER($AG$7:$AG$4868,$K$7:$K$4868&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4868,$K$7:$K$4868&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4869,$K$7:$K$4869&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4869,$K$7:$K$4869&lt;&gt;"X"),
 "",
 0,
 -1
@@ -26355,8 +26371,8 @@
       <c r="AH21" s="243" t="b" cm="1">
         <f t="array" ref="AH21">$D21=_xlfn.XLOOKUP(
 AG21,
-_xlfn._xlws.FILTER($AG$7:$AG$4868,$K$7:$K$4868&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4868,$K$7:$K$4868&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4869,$K$7:$K$4869&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4869,$K$7:$K$4869&lt;&gt;"X"),
 "",
 0,
 -1
@@ -26470,8 +26486,8 @@
       <c r="AH22" s="243" t="b" cm="1">
         <f t="array" ref="AH22">$D22=_xlfn.XLOOKUP(
 AG22,
-_xlfn._xlws.FILTER($AG$7:$AG$4868,$K$7:$K$4868&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4868,$K$7:$K$4868&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4869,$K$7:$K$4869&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4869,$K$7:$K$4869&lt;&gt;"X"),
 "",
 0,
 -1
@@ -26573,7 +26589,7 @@
       </c>
       <c r="AC23" s="183">
         <f t="shared" ca="1" si="7"/>
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AD23" s="92"/>
       <c r="AG23" s="238" t="str">
@@ -26583,8 +26599,8 @@
       <c r="AH23" s="243" t="b" cm="1">
         <f t="array" ref="AH23">$D23=_xlfn.XLOOKUP(
 AG23,
-_xlfn._xlws.FILTER($AG$7:$AG$4868,$K$7:$K$4868&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4868,$K$7:$K$4868&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4869,$K$7:$K$4869&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4869,$K$7:$K$4869&lt;&gt;"X"),
 "",
 0,
 -1
@@ -26686,7 +26702,7 @@
       </c>
       <c r="AC24" s="183">
         <f t="shared" ca="1" si="7"/>
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AD24" s="92"/>
       <c r="AG24" s="238" t="str">
@@ -26696,8 +26712,8 @@
       <c r="AH24" s="243" t="b" cm="1">
         <f t="array" ref="AH24">$D24=_xlfn.XLOOKUP(
 AG24,
-_xlfn._xlws.FILTER($AG$7:$AG$4868,$K$7:$K$4868&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4868,$K$7:$K$4868&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4869,$K$7:$K$4869&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4869,$K$7:$K$4869&lt;&gt;"X"),
 "",
 0,
 -1
@@ -26797,7 +26813,7 @@
       </c>
       <c r="AC25" s="183">
         <f t="shared" ca="1" si="7"/>
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AD25" s="92" t="s">
         <v>887</v>
@@ -26809,8 +26825,8 @@
       <c r="AH25" s="243" t="b" cm="1">
         <f t="array" ref="AH25">$D25=_xlfn.XLOOKUP(
 AG25,
-_xlfn._xlws.FILTER($AG$7:$AG$4868,$K$7:$K$4868&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4868,$K$7:$K$4868&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4869,$K$7:$K$4869&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4869,$K$7:$K$4869&lt;&gt;"X"),
 "",
 0,
 -1
@@ -26912,7 +26928,7 @@
       </c>
       <c r="AC26" s="183">
         <f t="shared" ca="1" si="7"/>
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AD26" s="92"/>
       <c r="AG26" s="238" t="str">
@@ -26922,8 +26938,8 @@
       <c r="AH26" s="243" t="b" cm="1">
         <f t="array" ref="AH26">$D26=_xlfn.XLOOKUP(
 AG26,
-_xlfn._xlws.FILTER($AG$7:$AG$4868,$K$7:$K$4868&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4868,$K$7:$K$4868&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4869,$K$7:$K$4869&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4869,$K$7:$K$4869&lt;&gt;"X"),
 "",
 0,
 -1
@@ -27025,7 +27041,7 @@
       </c>
       <c r="AC27" s="183">
         <f t="shared" ca="1" si="7"/>
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AD27" s="92"/>
       <c r="AG27" s="238" t="str">
@@ -27035,8 +27051,8 @@
       <c r="AH27" s="243" t="b" cm="1">
         <f t="array" ref="AH27">$D27=_xlfn.XLOOKUP(
 AG27,
-_xlfn._xlws.FILTER($AG$7:$AG$4868,$K$7:$K$4868&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4868,$K$7:$K$4868&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4869,$K$7:$K$4869&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4869,$K$7:$K$4869&lt;&gt;"X"),
 "",
 0,
 -1
@@ -27150,8 +27166,8 @@
       <c r="AH28" s="243" t="b" cm="1">
         <f t="array" ref="AH28">$D28=_xlfn.XLOOKUP(
 AG28,
-_xlfn._xlws.FILTER($AG$7:$AG$4868,$K$7:$K$4868&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4868,$K$7:$K$4868&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4869,$K$7:$K$4869&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4869,$K$7:$K$4869&lt;&gt;"X"),
 "",
 0,
 -1
@@ -27241,8 +27257,8 @@
       <c r="AH29" s="243" t="b" cm="1">
         <f t="array" ref="AH29">$D29=_xlfn.XLOOKUP(
 AG29,
-_xlfn._xlws.FILTER($AG$7:$AG$4868,$K$7:$K$4868&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4868,$K$7:$K$4868&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4869,$K$7:$K$4869&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4869,$K$7:$K$4869&lt;&gt;"X"),
 "",
 0,
 -1
@@ -27344,7 +27360,7 @@
       </c>
       <c r="AC30" s="183">
         <f t="shared" ca="1" si="7"/>
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AD30" s="92" t="s">
         <v>593</v>
@@ -27356,8 +27372,8 @@
       <c r="AH30" s="243" t="b" cm="1">
         <f t="array" ref="AH30">$D30=_xlfn.XLOOKUP(
 AG30,
-_xlfn._xlws.FILTER($AG$7:$AG$4868,$K$7:$K$4868&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4868,$K$7:$K$4868&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4869,$K$7:$K$4869&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4869,$K$7:$K$4869&lt;&gt;"X"),
 "",
 0,
 -1
@@ -27399,11 +27415,11 @@
       </c>
       <c r="I31" s="164">
         <f ca="1">IF(ISBLANK($V31),_xlfn.DAYS($I$1,$T31),_xlfn.DAYS($V31,$T31))</f>
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="J31" s="47">
         <f t="shared" ca="1" si="4"/>
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="K31" s="164"/>
       <c r="L31" s="54" t="s">
@@ -27453,8 +27469,8 @@
       <c r="AH31" s="243" t="b" cm="1">
         <f t="array" ref="AH31">$D31=_xlfn.XLOOKUP(
 AG31,
-_xlfn._xlws.FILTER($AG$7:$AG$4868,$K$7:$K$4868&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4868,$K$7:$K$4868&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4869,$K$7:$K$4869&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4869,$K$7:$K$4869&lt;&gt;"X"),
 "",
 0,
 -1
@@ -27570,8 +27586,8 @@
       <c r="AH32" s="243" t="b" cm="1">
         <f t="array" ref="AH32">$D32=_xlfn.XLOOKUP(
 AG32,
-_xlfn._xlws.FILTER($AG$7:$AG$4868,$K$7:$K$4868&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4868,$K$7:$K$4868&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4869,$K$7:$K$4869&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4869,$K$7:$K$4869&lt;&gt;"X"),
 "",
 0,
 -1
@@ -27675,8 +27691,8 @@
       <c r="AH33" s="243" t="b" cm="1">
         <f t="array" ref="AH33">$D33=_xlfn.XLOOKUP(
 AG33,
-_xlfn._xlws.FILTER($AG$7:$AG$4868,$K$7:$K$4868&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4868,$K$7:$K$4868&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4869,$K$7:$K$4869&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4869,$K$7:$K$4869&lt;&gt;"X"),
 "",
 0,
 -1
@@ -27761,8 +27777,8 @@
       <c r="AH34" s="243" t="b" cm="1">
         <f t="array" ref="AH34">$D34=_xlfn.XLOOKUP(
 AG34,
-_xlfn._xlws.FILTER($AG$7:$AG$4868,$K$7:$K$4868&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4868,$K$7:$K$4868&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4869,$K$7:$K$4869&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4869,$K$7:$K$4869&lt;&gt;"X"),
 "",
 0,
 -1
@@ -27802,7 +27818,7 @@
       <c r="H35" s="138"/>
       <c r="I35" s="164">
         <f t="shared" ca="1" si="10"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J35" s="47">
         <f t="shared" ca="1" si="4"/>
@@ -27854,8 +27870,8 @@
       <c r="AH35" s="243" t="b" cm="1">
         <f t="array" ref="AH35">$D35=_xlfn.XLOOKUP(
 AG35,
-_xlfn._xlws.FILTER($AG$7:$AG$4868,$K$7:$K$4868&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4868,$K$7:$K$4868&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4869,$K$7:$K$4869&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4869,$K$7:$K$4869&lt;&gt;"X"),
 "",
 0,
 -1
@@ -27957,8 +27973,8 @@
       <c r="AH36" s="243" t="b" cm="1">
         <f t="array" ref="AH36">$D36=_xlfn.XLOOKUP(
 AG36,
-_xlfn._xlws.FILTER($AG$7:$AG$4868,$K$7:$K$4868&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4868,$K$7:$K$4868&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4869,$K$7:$K$4869&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4869,$K$7:$K$4869&lt;&gt;"X"),
 "",
 0,
 -1
@@ -27998,11 +28014,11 @@
       </c>
       <c r="I37" s="164">
         <f t="shared" ca="1" si="10"/>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J37" s="47">
         <f t="shared" ca="1" si="4"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K37" s="164"/>
       <c r="L37" s="54" t="s">
@@ -28052,8 +28068,8 @@
       <c r="AH37" s="243" t="b" cm="1">
         <f t="array" ref="AH37">$D37=_xlfn.XLOOKUP(
 AG37,
-_xlfn._xlws.FILTER($AG$7:$AG$4868,$K$7:$K$4868&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4868,$K$7:$K$4868&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4869,$K$7:$K$4869&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4869,$K$7:$K$4869&lt;&gt;"X"),
 "",
 0,
 -1
@@ -28155,8 +28171,8 @@
       <c r="AH38" s="243" t="b" cm="1">
         <f t="array" ref="AH38">$D38=_xlfn.XLOOKUP(
 AG38,
-_xlfn._xlws.FILTER($AG$7:$AG$4868,$K$7:$K$4868&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4868,$K$7:$K$4868&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4869,$K$7:$K$4869&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4869,$K$7:$K$4869&lt;&gt;"X"),
 "",
 0,
 -1
@@ -28196,7 +28212,7 @@
       <c r="H39" s="138"/>
       <c r="I39" s="164">
         <f t="shared" ca="1" si="10"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J39" s="47">
         <f t="shared" ca="1" si="4"/>
@@ -28248,8 +28264,8 @@
       <c r="AH39" s="243" t="b" cm="1">
         <f t="array" ref="AH39">$D39=_xlfn.XLOOKUP(
 AG39,
-_xlfn._xlws.FILTER($AG$7:$AG$4868,$K$7:$K$4868&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4868,$K$7:$K$4868&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4869,$K$7:$K$4869&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4869,$K$7:$K$4869&lt;&gt;"X"),
 "",
 0,
 -1
@@ -28261,30 +28277,59 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:35" s="9" customFormat="1">
-      <c r="A40" s="23"/>
-      <c r="B40" s="33"/>
-      <c r="C40" s="137"/>
-      <c r="D40" s="25"/>
-      <c r="E40" s="174"/>
-      <c r="F40" s="31"/>
-      <c r="G40" s="21"/>
+    <row r="40" spans="1:35" s="9" customFormat="1" ht="63">
+      <c r="A40" s="33">
+        <f t="shared" si="0"/>
+        <v>34</v>
+      </c>
+      <c r="B40" s="33" t="str">
+        <f t="shared" ref="B40" si="21">MID(D40, FIND("-", D40) + 1, 4)</f>
+        <v>5.10</v>
+      </c>
+      <c r="C40" s="164"/>
+      <c r="D40" s="25" t="s">
+        <v>1061</v>
+      </c>
+      <c r="E40" s="174">
+        <f t="shared" si="2"/>
+        <v>46330</v>
+      </c>
+      <c r="F40" s="31" t="s">
+        <v>1062</v>
+      </c>
+      <c r="G40" s="21" t="s">
+        <v>1063</v>
+      </c>
       <c r="H40" s="138"/>
-      <c r="I40" s="177"/>
-      <c r="J40" s="47"/>
+      <c r="I40" s="164">
+        <f t="shared" ca="1" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="J40" s="47">
+        <f t="shared" ca="1" si="4"/>
+        <v>0</v>
+      </c>
       <c r="K40" s="164"/>
-      <c r="L40" s="52"/>
-      <c r="M40" s="66"/>
+      <c r="L40" s="54" t="s">
+        <v>8</v>
+      </c>
+      <c r="M40" s="65"/>
       <c r="N40" s="40"/>
-      <c r="O40" s="37"/>
-      <c r="P40" s="17"/>
-      <c r="Q40" s="183"/>
-      <c r="R40" s="27"/>
-      <c r="S40" s="27"/>
-      <c r="T40" s="187"/>
+      <c r="O40" s="41"/>
+      <c r="P40" s="40"/>
+      <c r="Q40" s="155"/>
+      <c r="R40" s="27">
+        <v>46309</v>
+      </c>
+      <c r="S40" s="27">
+        <v>46309</v>
+      </c>
+      <c r="T40" s="188">
+        <v>46309</v>
+      </c>
       <c r="U40" s="29"/>
       <c r="V40" s="188"/>
-      <c r="W40" s="227"/>
+      <c r="W40" s="235"/>
       <c r="X40" s="230"/>
       <c r="Y40" s="227"/>
       <c r="Z40" s="29" t="str">
@@ -28292,130 +28337,138 @@
         <v/>
       </c>
       <c r="AA40" s="229"/>
-      <c r="AB40" s="229"/>
-      <c r="AC40" s="19"/>
+      <c r="AB40" s="229" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="AC40" s="183" t="str">
+        <f t="shared" ref="AC40" si="22">IF(AB40="Late Resubmission",IF(AA40="","",AA40-Z40),IF(AB40="Not submit yet",IF(Z40="","",$I$1-Z40),""))</f>
+        <v/>
+      </c>
       <c r="AD40" s="92"/>
-      <c r="AG40" s="238"/>
-      <c r="AH40" s="243"/>
-      <c r="AI40" s="75"/>
-    </row>
-    <row r="41" spans="1:35" s="9" customFormat="1" ht="16.5" thickBot="1">
-      <c r="A41" s="24"/>
-      <c r="B41" s="329"/>
-      <c r="C41" s="165"/>
-      <c r="D41" s="45"/>
-      <c r="E41" s="175"/>
-      <c r="F41" s="32"/>
-      <c r="G41" s="22"/>
-      <c r="H41" s="139"/>
-      <c r="I41" s="178"/>
-      <c r="J41" s="132"/>
-      <c r="K41" s="199"/>
-      <c r="L41" s="53"/>
-      <c r="M41" s="67"/>
-      <c r="N41" s="18"/>
-      <c r="O41" s="38"/>
-      <c r="P41" s="18"/>
-      <c r="Q41" s="184"/>
-      <c r="R41" s="44"/>
-      <c r="S41" s="44"/>
-      <c r="T41" s="189"/>
-      <c r="U41" s="43"/>
-      <c r="V41" s="194"/>
-      <c r="W41" s="228"/>
-      <c r="X41" s="232"/>
-      <c r="Y41" s="228"/>
-      <c r="Z41" s="43" t="str">
+      <c r="AG40" s="238" t="str">
+        <f t="shared" si="8"/>
+        <v>LTIA-5.10-VIETUR-80000-RFA-SDS-0493</v>
+      </c>
+      <c r="AH40" s="243" t="b" cm="1">
+        <f t="array" ref="AH40">$D40=_xlfn.XLOOKUP(
+AG40,
+_xlfn._xlws.FILTER($AG$7:$AG$4869,$K$7:$K$4869&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4869,$K$7:$K$4869&lt;&gt;"X"),
+"",
+0,
+-1
+)</f>
+        <v>1</v>
+      </c>
+      <c r="AI40" s="75" t="str">
+        <f>IF(AND($AH40,OR($Q40="B",$Q40="C")),"YES","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" spans="1:35" s="9" customFormat="1">
+      <c r="A41" s="23"/>
+      <c r="B41" s="33"/>
+      <c r="C41" s="137"/>
+      <c r="D41" s="25"/>
+      <c r="E41" s="174"/>
+      <c r="F41" s="31"/>
+      <c r="G41" s="21"/>
+      <c r="H41" s="138"/>
+      <c r="I41" s="177"/>
+      <c r="J41" s="47"/>
+      <c r="K41" s="164"/>
+      <c r="L41" s="52"/>
+      <c r="M41" s="66"/>
+      <c r="N41" s="40"/>
+      <c r="O41" s="37"/>
+      <c r="P41" s="17"/>
+      <c r="Q41" s="183"/>
+      <c r="R41" s="27"/>
+      <c r="S41" s="27"/>
+      <c r="T41" s="187"/>
+      <c r="U41" s="29"/>
+      <c r="V41" s="188"/>
+      <c r="W41" s="227"/>
+      <c r="X41" s="230"/>
+      <c r="Y41" s="227"/>
+      <c r="Z41" s="29" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AA41" s="233"/>
-      <c r="AB41" s="233"/>
-      <c r="AC41" s="20"/>
-      <c r="AD41" s="93"/>
-      <c r="AG41" s="239"/>
-      <c r="AH41" s="244"/>
-      <c r="AI41" s="241"/>
-    </row>
-    <row r="42" spans="1:35" ht="16.5" thickBot="1"/>
-    <row r="43" spans="1:35" ht="16.5" thickBot="1">
-      <c r="C43" s="166" t="s">
+      <c r="AA41" s="229"/>
+      <c r="AB41" s="229"/>
+      <c r="AC41" s="19"/>
+      <c r="AD41" s="92"/>
+      <c r="AG41" s="238"/>
+      <c r="AH41" s="243"/>
+      <c r="AI41" s="75"/>
+    </row>
+    <row r="42" spans="1:35" s="9" customFormat="1" ht="16.5" thickBot="1">
+      <c r="A42" s="24"/>
+      <c r="B42" s="329"/>
+      <c r="C42" s="165"/>
+      <c r="D42" s="45"/>
+      <c r="E42" s="175"/>
+      <c r="F42" s="32"/>
+      <c r="G42" s="22"/>
+      <c r="H42" s="139"/>
+      <c r="I42" s="178"/>
+      <c r="J42" s="132"/>
+      <c r="K42" s="199"/>
+      <c r="L42" s="53"/>
+      <c r="M42" s="67"/>
+      <c r="N42" s="18"/>
+      <c r="O42" s="38"/>
+      <c r="P42" s="18"/>
+      <c r="Q42" s="184"/>
+      <c r="R42" s="44"/>
+      <c r="S42" s="44"/>
+      <c r="T42" s="189"/>
+      <c r="U42" s="43"/>
+      <c r="V42" s="194"/>
+      <c r="W42" s="228"/>
+      <c r="X42" s="232"/>
+      <c r="Y42" s="228"/>
+      <c r="Z42" s="43" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="AA42" s="233"/>
+      <c r="AB42" s="233"/>
+      <c r="AC42" s="20"/>
+      <c r="AD42" s="93"/>
+      <c r="AG42" s="239"/>
+      <c r="AH42" s="244"/>
+      <c r="AI42" s="241"/>
+    </row>
+    <row r="43" spans="1:35" ht="16.5" thickBot="1"/>
+    <row r="44" spans="1:35" ht="16.5" thickBot="1">
+      <c r="C44" s="166" t="s">
         <v>20</v>
       </c>
-      <c r="D43" s="405" t="s">
+      <c r="D44" s="405" t="s">
         <v>21</v>
       </c>
-      <c r="E43" s="406"/>
-      <c r="F43" s="46"/>
-      <c r="G43" s="46"/>
-      <c r="H43" s="357" t="s">
+      <c r="E44" s="406"/>
+      <c r="F44" s="46"/>
+      <c r="G44" s="46"/>
+      <c r="H44" s="357" t="s">
         <v>14</v>
-      </c>
-      <c r="I43" s="358"/>
-      <c r="J43" s="358"/>
-      <c r="K43" s="358"/>
-      <c r="L43" s="358"/>
-      <c r="M43" s="359"/>
-      <c r="N43" s="360" t="s">
-        <v>7</v>
-      </c>
-      <c r="O43" s="361"/>
-      <c r="P43" s="360" t="s">
-        <v>109</v>
-      </c>
-      <c r="Q43" s="361"/>
-      <c r="R43" s="1"/>
-      <c r="S43" s="1"/>
-      <c r="T43" s="140"/>
-      <c r="U43" s="1"/>
-      <c r="W43" s="11"/>
-      <c r="X43" s="11"/>
-      <c r="Y43" s="11"/>
-      <c r="Z43" s="11"/>
-      <c r="AA43" s="11"/>
-      <c r="AB43" s="11"/>
-      <c r="AC43" s="11"/>
-      <c r="AG43" s="11"/>
-      <c r="AH43" s="11"/>
-      <c r="AI43" s="11"/>
-    </row>
-    <row r="44" spans="1:35" ht="16.5" thickBot="1">
-      <c r="C44" s="195" t="s">
-        <v>109</v>
-      </c>
-      <c r="D44" s="391" t="s">
-        <v>111</v>
-      </c>
-      <c r="E44" s="392"/>
-      <c r="F44" s="46"/>
-      <c r="H44" s="357" t="s">
-        <v>18</v>
       </c>
       <c r="I44" s="358"/>
       <c r="J44" s="358"/>
-      <c r="K44" s="359"/>
-      <c r="L44" s="105">
-        <f ca="1">M44/$M$44</f>
-        <v>1</v>
-      </c>
-      <c r="M44" s="106">
-        <f ca="1">SUM($M$45:$M$49)</f>
-        <v>35</v>
-      </c>
-      <c r="N44" s="102" t="s">
-        <v>15</v>
-      </c>
-      <c r="O44" s="103" t="s">
-        <v>16</v>
-      </c>
-      <c r="P44" s="105">
-        <f ca="1">Q44/$Q$44</f>
-        <v>1</v>
-      </c>
-      <c r="Q44" s="220">
-        <f ca="1">SUM(Q45:Q48)</f>
-        <v>31</v>
-      </c>
+      <c r="K44" s="358"/>
+      <c r="L44" s="358"/>
+      <c r="M44" s="359"/>
+      <c r="N44" s="360" t="s">
+        <v>7</v>
+      </c>
+      <c r="O44" s="361"/>
+      <c r="P44" s="360" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q44" s="361"/>
       <c r="R44" s="1"/>
       <c r="S44" s="1"/>
       <c r="T44" s="140"/>
@@ -28431,45 +28484,42 @@
       <c r="AH44" s="11"/>
       <c r="AI44" s="11"/>
     </row>
-    <row r="45" spans="1:35">
+    <row r="45" spans="1:35" ht="16.5" thickBot="1">
       <c r="C45" s="195" t="s">
+        <v>109</v>
+      </c>
+      <c r="D45" s="391" t="s">
+        <v>111</v>
+      </c>
+      <c r="E45" s="392"/>
+      <c r="F45" s="46"/>
+      <c r="H45" s="357" t="s">
+        <v>18</v>
+      </c>
+      <c r="I45" s="358"/>
+      <c r="J45" s="358"/>
+      <c r="K45" s="359"/>
+      <c r="L45" s="105">
+        <f ca="1">M45/$M$45</f>
+        <v>1</v>
+      </c>
+      <c r="M45" s="106">
+        <f ca="1">SUM($M$46:$M$50)</f>
         <v>36</v>
       </c>
-      <c r="D45" s="370" t="s">
-        <v>37</v>
-      </c>
-      <c r="E45" s="371"/>
-      <c r="F45" s="69"/>
-      <c r="G45" s="6"/>
-      <c r="H45" s="373" t="s">
-        <v>66</v>
-      </c>
-      <c r="I45" s="374"/>
-      <c r="J45" s="374"/>
-      <c r="K45" s="375"/>
-      <c r="L45" s="107">
-        <f ca="1">M45/$M$44</f>
-        <v>2.8571428571428571E-2</v>
-      </c>
-      <c r="M45" s="108">
-        <f>COUNTIF($H$7:$H$41,"A")</f>
+      <c r="N45" s="102" t="s">
+        <v>15</v>
+      </c>
+      <c r="O45" s="103" t="s">
+        <v>16</v>
+      </c>
+      <c r="P45" s="105">
+        <f ca="1">Q45/$Q$45</f>
         <v>1</v>
       </c>
-      <c r="N45" s="100">
-        <f ca="1">COUNTIFS($I$7:$I$41,"&lt;=21",$H$7:$H$41,"A")</f>
-        <v>1</v>
-      </c>
-      <c r="O45" s="101">
-        <f ca="1">COUNTIFS($I$7:$I$41,"&gt;21",$H$7:$H$41,"A")</f>
-        <v>0</v>
-      </c>
-      <c r="P45" s="107">
-        <f ca="1">Q45/$Q$44</f>
-        <v>3.2258064516129031E-2</v>
-      </c>
-      <c r="Q45" s="108">
-        <f>COUNTIF($Q$7:$Q$41,"A")</f>
-        <v>1</v>
+      <c r="Q45" s="220">
+        <f ca="1">SUM(Q46:Q49)</f>
+        <v>32</v>
       </c>
       <c r="R45" s="1"/>
       <c r="S45" s="1"/>
@@ -28487,44 +28537,44 @@
       <c r="AI45" s="11"/>
     </row>
     <row r="46" spans="1:35">
-      <c r="C46" s="385" t="s">
-        <v>75</v>
-      </c>
-      <c r="D46" s="387" t="s">
-        <v>76</v>
-      </c>
-      <c r="E46" s="388"/>
-      <c r="F46" s="70"/>
+      <c r="C46" s="195" t="s">
+        <v>36</v>
+      </c>
+      <c r="D46" s="370" t="s">
+        <v>37</v>
+      </c>
+      <c r="E46" s="371"/>
+      <c r="F46" s="69"/>
       <c r="G46" s="6"/>
-      <c r="H46" s="376" t="s">
-        <v>67</v>
-      </c>
-      <c r="I46" s="377"/>
-      <c r="J46" s="377"/>
-      <c r="K46" s="378"/>
-      <c r="L46" s="109">
-        <f t="shared" ref="L46:L49" ca="1" si="21">M46/$M$44</f>
-        <v>0.5714285714285714</v>
-      </c>
-      <c r="M46" s="110">
-        <f>COUNTIF($H$7:$H$41,"B")</f>
-        <v>20</v>
-      </c>
-      <c r="N46" s="98">
-        <f ca="1">COUNTIFS($I$7:$I$41,"&lt;=21",$H$7:$H$41,"B")</f>
-        <v>8</v>
-      </c>
-      <c r="O46" s="50">
-        <f ca="1">COUNTIFS($I$7:$I$41,"&gt;21",$H$7:$H$41,"B")</f>
-        <v>12</v>
-      </c>
-      <c r="P46" s="109">
-        <f t="shared" ref="P46:P48" ca="1" si="22">Q46/$Q$44</f>
-        <v>0.64516129032258063</v>
-      </c>
-      <c r="Q46" s="110">
-        <f>COUNTIF($Q$7:$Q$41,"B")</f>
-        <v>20</v>
+      <c r="H46" s="373" t="s">
+        <v>66</v>
+      </c>
+      <c r="I46" s="374"/>
+      <c r="J46" s="374"/>
+      <c r="K46" s="375"/>
+      <c r="L46" s="107">
+        <f ca="1">M46/$M$45</f>
+        <v>2.7777777777777776E-2</v>
+      </c>
+      <c r="M46" s="108">
+        <f>COUNTIF($H$7:$H$42,"A")</f>
+        <v>1</v>
+      </c>
+      <c r="N46" s="100">
+        <f ca="1">COUNTIFS($I$7:$I$42,"&lt;=21",$H$7:$H$42,"A")</f>
+        <v>1</v>
+      </c>
+      <c r="O46" s="101">
+        <f ca="1">COUNTIFS($I$7:$I$42,"&gt;21",$H$7:$H$42,"A")</f>
+        <v>0</v>
+      </c>
+      <c r="P46" s="107">
+        <f ca="1">Q46/$Q$45</f>
+        <v>3.125E-2</v>
+      </c>
+      <c r="Q46" s="108">
+        <f>COUNTIF($Q$7:$Q$42,"A")</f>
+        <v>1</v>
       </c>
       <c r="R46" s="1"/>
       <c r="S46" s="1"/>
@@ -28541,41 +28591,45 @@
       <c r="AH46" s="11"/>
       <c r="AI46" s="11"/>
     </row>
-    <row r="47" spans="1:35" ht="16.5" thickBot="1">
-      <c r="C47" s="386"/>
-      <c r="D47" s="389"/>
-      <c r="E47" s="390"/>
-      <c r="F47" s="71"/>
+    <row r="47" spans="1:35">
+      <c r="C47" s="385" t="s">
+        <v>75</v>
+      </c>
+      <c r="D47" s="387" t="s">
+        <v>76</v>
+      </c>
+      <c r="E47" s="388"/>
+      <c r="F47" s="70"/>
       <c r="G47" s="6"/>
-      <c r="H47" s="379" t="s">
-        <v>68</v>
-      </c>
-      <c r="I47" s="380"/>
-      <c r="J47" s="380"/>
-      <c r="K47" s="381"/>
-      <c r="L47" s="111">
-        <f t="shared" ca="1" si="21"/>
-        <v>0.22857142857142856</v>
-      </c>
-      <c r="M47" s="112">
-        <f>COUNTIF($H$7:$H$41,"C")</f>
-        <v>8</v>
+      <c r="H47" s="376" t="s">
+        <v>67</v>
+      </c>
+      <c r="I47" s="377"/>
+      <c r="J47" s="377"/>
+      <c r="K47" s="378"/>
+      <c r="L47" s="109">
+        <f t="shared" ref="L47:L50" ca="1" si="23">M47/$M$45</f>
+        <v>0.55555555555555558</v>
+      </c>
+      <c r="M47" s="110">
+        <f>COUNTIF($H$7:$H$42,"B")</f>
+        <v>20</v>
       </c>
       <c r="N47" s="98">
-        <f ca="1">COUNTIFS($I$7:$I$41,"&lt;=21",$H$7:$H$41,"C")</f>
-        <v>3</v>
+        <f ca="1">COUNTIFS($I$7:$I$42,"&lt;=21",$H$7:$H$42,"B")</f>
+        <v>8</v>
       </c>
       <c r="O47" s="50">
-        <f ca="1">COUNTIFS($I$7:$I$41,"&gt;21",$H$7:$H$41,"C")</f>
-        <v>5</v>
-      </c>
-      <c r="P47" s="111">
-        <f t="shared" ca="1" si="22"/>
-        <v>9.6774193548387094E-2</v>
-      </c>
-      <c r="Q47" s="112">
-        <f>COUNTIF($Q$7:$Q$41,"C")</f>
-        <v>3</v>
+        <f ca="1">COUNTIFS($I$7:$I$42,"&gt;21",$H$7:$H$42,"B")</f>
+        <v>12</v>
+      </c>
+      <c r="P47" s="109">
+        <f t="shared" ref="P47:P49" ca="1" si="24">Q47/$Q$45</f>
+        <v>0.625</v>
+      </c>
+      <c r="Q47" s="110">
+        <f>COUNTIF($Q$7:$Q$42,"B")</f>
+        <v>20</v>
       </c>
       <c r="R47" s="1"/>
       <c r="S47" s="1"/>
@@ -28592,42 +28646,43 @@
       <c r="AH47" s="11"/>
       <c r="AI47" s="11"/>
     </row>
-    <row r="48" spans="1:35">
-      <c r="F48" s="72"/>
+    <row r="48" spans="1:35" ht="16.5" thickBot="1">
+      <c r="C48" s="386"/>
+      <c r="D48" s="389"/>
+      <c r="E48" s="390"/>
+      <c r="F48" s="71"/>
       <c r="G48" s="6"/>
-      <c r="H48" s="382" t="s">
-        <v>70</v>
-      </c>
-      <c r="I48" s="383"/>
-      <c r="J48" s="383"/>
-      <c r="K48" s="384"/>
-      <c r="L48" s="114">
-        <f t="shared" ca="1" si="21"/>
-        <v>0.11428571428571428</v>
-      </c>
-      <c r="M48" s="115">
-        <f ca="1">SUM(N48:O48)</f>
-        <v>4</v>
+      <c r="H48" s="379" t="s">
+        <v>68</v>
+      </c>
+      <c r="I48" s="380"/>
+      <c r="J48" s="380"/>
+      <c r="K48" s="381"/>
+      <c r="L48" s="111">
+        <f t="shared" ca="1" si="23"/>
+        <v>0.22222222222222221</v>
+      </c>
+      <c r="M48" s="112">
+        <f>COUNTIF($H$7:$H$42,"C")</f>
+        <v>8</v>
       </c>
       <c r="N48" s="98">
-        <f ca="1">COUNTIFS($I$7:$I$41,"&lt;=21",$U$7:$U$41,"",$K$7:$K$41,"&lt;&gt;X")</f>
-        <v>2</v>
+        <f ca="1">COUNTIFS($I$7:$I$42,"&lt;=21",$H$7:$H$42,"C")</f>
+        <v>3</v>
       </c>
       <c r="O48" s="50">
-        <f ca="1">COUNTIFS($I$7:$I$41,"&gt;21",$U$7:$U$41,"",$K$7:$K$41,"&lt;&gt;X")</f>
-        <v>2</v>
-      </c>
-      <c r="P48" s="114">
-        <f t="shared" ca="1" si="22"/>
-        <v>0.22580645161290322</v>
-      </c>
-      <c r="Q48" s="115">
-        <f ca="1">COUNTIFS($I$7:$I$41,"&gt;=0",$P$7:$P$41,"",$K$7:$K$41,"&lt;&gt;X")</f>
-        <v>7</v>
-      </c>
-      <c r="R48" s="1" t="s">
-        <v>10</v>
-      </c>
+        <f ca="1">COUNTIFS($I$7:$I$42,"&gt;21",$H$7:$H$42,"C")</f>
+        <v>5</v>
+      </c>
+      <c r="P48" s="111">
+        <f t="shared" ca="1" si="24"/>
+        <v>9.375E-2</v>
+      </c>
+      <c r="Q48" s="112">
+        <f>COUNTIF($Q$7:$Q$42,"C")</f>
+        <v>3</v>
+      </c>
+      <c r="R48" s="1"/>
       <c r="S48" s="1"/>
       <c r="T48" s="140"/>
       <c r="U48" s="1"/>
@@ -28642,52 +28697,102 @@
       <c r="AH48" s="11"/>
       <c r="AI48" s="11"/>
     </row>
-    <row r="49" spans="3:17" ht="16.5" thickBot="1">
-      <c r="C49" s="372" t="s">
+    <row r="49" spans="3:35">
+      <c r="F49" s="72"/>
+      <c r="G49" s="6"/>
+      <c r="H49" s="382" t="s">
+        <v>70</v>
+      </c>
+      <c r="I49" s="383"/>
+      <c r="J49" s="383"/>
+      <c r="K49" s="384"/>
+      <c r="L49" s="114">
+        <f t="shared" ca="1" si="23"/>
+        <v>0.1388888888888889</v>
+      </c>
+      <c r="M49" s="115">
+        <f ca="1">SUM(N49:O49)</f>
+        <v>5</v>
+      </c>
+      <c r="N49" s="98">
+        <f ca="1">COUNTIFS($I$7:$I$42,"&lt;=21",$U$7:$U$42,"",$K$7:$K$42,"&lt;&gt;X")</f>
+        <v>3</v>
+      </c>
+      <c r="O49" s="50">
+        <f ca="1">COUNTIFS($I$7:$I$42,"&gt;21",$U$7:$U$42,"",$K$7:$K$42,"&lt;&gt;X")</f>
+        <v>2</v>
+      </c>
+      <c r="P49" s="114">
+        <f t="shared" ca="1" si="24"/>
+        <v>0.25</v>
+      </c>
+      <c r="Q49" s="115">
+        <f ca="1">COUNTIFS($I$7:$I$42,"&gt;=0",$P$7:$P$42,"",$K$7:$K$42,"&lt;&gt;X")</f>
+        <v>8</v>
+      </c>
+      <c r="R49" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="S49" s="1"/>
+      <c r="T49" s="140"/>
+      <c r="U49" s="1"/>
+      <c r="W49" s="11"/>
+      <c r="X49" s="11"/>
+      <c r="Y49" s="11"/>
+      <c r="Z49" s="11"/>
+      <c r="AA49" s="11"/>
+      <c r="AB49" s="11"/>
+      <c r="AC49" s="11"/>
+      <c r="AG49" s="11"/>
+      <c r="AH49" s="11"/>
+      <c r="AI49" s="11"/>
+    </row>
+    <row r="50" spans="3:35" ht="16.5" thickBot="1">
+      <c r="C50" s="372" t="s">
         <v>41</v>
       </c>
-      <c r="D49" s="372"/>
-      <c r="E49" s="372"/>
-      <c r="H49" s="354" t="s">
+      <c r="D50" s="372"/>
+      <c r="E50" s="372"/>
+      <c r="H50" s="354" t="s">
         <v>71</v>
       </c>
-      <c r="I49" s="355"/>
-      <c r="J49" s="355"/>
-      <c r="K49" s="356"/>
-      <c r="L49" s="113">
-        <f t="shared" ca="1" si="21"/>
-        <v>5.7142857142857141E-2</v>
-      </c>
-      <c r="M49" s="97">
-        <f>COUNTIFS($K$7:$K$41,"X")</f>
+      <c r="I50" s="355"/>
+      <c r="J50" s="355"/>
+      <c r="K50" s="356"/>
+      <c r="L50" s="113">
+        <f t="shared" ca="1" si="23"/>
+        <v>5.5555555555555552E-2</v>
+      </c>
+      <c r="M50" s="97">
+        <f>COUNTIFS($K$7:$K$42,"X")</f>
         <v>2</v>
       </c>
-      <c r="N49" s="99"/>
-      <c r="O49" s="51"/>
-      <c r="P49" s="221"/>
-      <c r="Q49" s="222"/>
-    </row>
-    <row r="50" spans="3:17">
-      <c r="C50" s="169" t="s">
-        <v>8</v>
-      </c>
-      <c r="D50" s="1" t="s">
+      <c r="N50" s="99"/>
+      <c r="O50" s="51"/>
+      <c r="P50" s="221"/>
+      <c r="Q50" s="222"/>
+    </row>
+    <row r="51" spans="3:35">
+      <c r="C51" s="169" t="s">
+        <v>8</v>
+      </c>
+      <c r="D51" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="51" spans="3:17">
-      <c r="C51" s="169" t="s">
-        <v>8</v>
-      </c>
-      <c r="D51" s="127" t="s">
+    <row r="52" spans="3:35">
+      <c r="C52" s="169" t="s">
+        <v>8</v>
+      </c>
+      <c r="D52" s="127" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="52" spans="3:17">
-      <c r="C52" s="169" t="s">
-        <v>8</v>
-      </c>
-      <c r="D52" s="1" t="s">
+    <row r="53" spans="3:35">
+      <c r="C53" s="169" t="s">
+        <v>8</v>
+      </c>
+      <c r="D53" s="1" t="s">
         <v>44</v>
       </c>
     </row>
@@ -28698,7 +28803,7 @@
     </sortState>
   </autoFilter>
   <mergeCells count="37">
-    <mergeCell ref="P43:Q43"/>
+    <mergeCell ref="P44:Q44"/>
     <mergeCell ref="X4:Y4"/>
     <mergeCell ref="Z4:AC4"/>
     <mergeCell ref="A4:A5"/>
@@ -28707,24 +28812,24 @@
     <mergeCell ref="F4:F5"/>
     <mergeCell ref="G4:G5"/>
     <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D43:E43"/>
+    <mergeCell ref="D44:E44"/>
     <mergeCell ref="B4:B5"/>
+    <mergeCell ref="D46:E46"/>
+    <mergeCell ref="C50:E50"/>
+    <mergeCell ref="H46:K46"/>
+    <mergeCell ref="H47:K47"/>
+    <mergeCell ref="H44:M44"/>
+    <mergeCell ref="H48:K48"/>
+    <mergeCell ref="H49:K49"/>
+    <mergeCell ref="C47:C48"/>
+    <mergeCell ref="D47:E48"/>
     <mergeCell ref="D45:E45"/>
-    <mergeCell ref="C49:E49"/>
-    <mergeCell ref="H45:K45"/>
-    <mergeCell ref="H46:K46"/>
-    <mergeCell ref="H43:M43"/>
-    <mergeCell ref="H47:K47"/>
-    <mergeCell ref="H48:K48"/>
-    <mergeCell ref="C46:C47"/>
-    <mergeCell ref="D46:E47"/>
-    <mergeCell ref="D44:E44"/>
     <mergeCell ref="AG5:AG6"/>
     <mergeCell ref="AH5:AH6"/>
     <mergeCell ref="AI5:AI6"/>
-    <mergeCell ref="H49:K49"/>
-    <mergeCell ref="H44:K44"/>
-    <mergeCell ref="N43:O43"/>
+    <mergeCell ref="H50:K50"/>
+    <mergeCell ref="H45:K45"/>
+    <mergeCell ref="N44:O44"/>
     <mergeCell ref="AD4:AD5"/>
     <mergeCell ref="H4:H5"/>
     <mergeCell ref="I4:I5"/>
@@ -28737,7 +28842,7 @@
     <mergeCell ref="J4:J5"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
-  <conditionalFormatting sqref="A7:AD41 AG7:AI41">
+  <conditionalFormatting sqref="A7:AD42 AG7:AI42">
     <cfRule type="expression" dxfId="11" priority="1">
       <formula>$K7="X"</formula>
     </cfRule>
@@ -28863,9 +28968,9 @@
     <hyperlink ref="O24" r:id="rId100" xr:uid="{26FEB876-D8E0-4A23-A9C5-C07952F599D7}"/>
     <hyperlink ref="O27" r:id="rId101" xr:uid="{51C15339-30E0-4EDA-A35A-162E28AC0D63}"/>
     <hyperlink ref="O33" r:id="rId102" xr:uid="{7E0883C0-4918-4433-937B-70D3D155F955}"/>
-    <hyperlink ref="C50" r:id="rId103" xr:uid="{BDBBB1AA-41DD-4769-B198-E0D4B6B569E2}"/>
-    <hyperlink ref="C51" r:id="rId104" xr:uid="{174B2EE8-A853-4328-A727-C5D3FC38F2B6}"/>
-    <hyperlink ref="C52" r:id="rId105" xr:uid="{6C349E79-11FF-4195-90FE-DE817F5EBEF8}"/>
+    <hyperlink ref="C51" r:id="rId103" xr:uid="{BDBBB1AA-41DD-4769-B198-E0D4B6B569E2}"/>
+    <hyperlink ref="C52" r:id="rId104" xr:uid="{174B2EE8-A853-4328-A727-C5D3FC38F2B6}"/>
+    <hyperlink ref="C53" r:id="rId105" xr:uid="{6C349E79-11FF-4195-90FE-DE817F5EBEF8}"/>
     <hyperlink ref="P7" r:id="rId106" xr:uid="{20D7A9F2-B509-4410-8C53-729666C026F8}"/>
     <hyperlink ref="P8" r:id="rId107" xr:uid="{BC5C2D57-7ED0-43E0-8C7C-0DF13280AE79}"/>
     <hyperlink ref="P9" r:id="rId108" xr:uid="{49C5EB74-800E-4CE6-82D1-E75C20991765}"/>
@@ -28900,9 +29005,10 @@
     <hyperlink ref="L39" r:id="rId137" xr:uid="{1260CC6F-397A-4689-AF30-C6ECD668430C}"/>
     <hyperlink ref="N36" r:id="rId138" xr:uid="{A9162BCC-A67F-4960-972B-2EF68F29EB50}"/>
     <hyperlink ref="N38" r:id="rId139" xr:uid="{DBAA5DC8-908C-4ABF-AC05-BCE08D8BBB73}"/>
+    <hyperlink ref="L40" r:id="rId140" xr:uid="{95929207-D5E2-4FFA-94DE-6961D7557694}"/>
   </hyperlinks>
   <pageMargins left="0.25" right="0.17" top="0.5" bottom="0.25" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="29" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId140"/>
+  <pageSetup paperSize="9" scale="29" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId141"/>
 </worksheet>
 </file>
 
@@ -28947,7 +29053,7 @@
       </c>
       <c r="I1" s="176">
         <f ca="1">TODAY()</f>
-        <v>46307</v>
+        <v>46309</v>
       </c>
       <c r="J1" s="131"/>
       <c r="K1" s="197"/>
@@ -31692,11 +31798,11 @@
       <c r="H39" s="138"/>
       <c r="I39" s="164">
         <f t="shared" ca="1" si="9"/>
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="J39" s="47">
         <f t="shared" ca="1" si="10"/>
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="K39" s="164"/>
       <c r="L39" s="40"/>
@@ -34098,11 +34204,11 @@
       </c>
       <c r="I70" s="164">
         <f t="shared" ref="I70:I78" ca="1" si="14">IF(ISBLANK($V70),_xlfn.DAYS($I$1,$T70),_xlfn.DAYS($V70,$T70))</f>
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="J70" s="47">
         <f t="shared" ref="J70:J78" ca="1" si="15">IF(($I70-21)&gt;0,$I70-21,0)</f>
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K70" s="164"/>
       <c r="L70" s="40"/>
@@ -36056,11 +36162,11 @@
       <c r="H97" s="138"/>
       <c r="I97" s="164">
         <f t="shared" ca="1" si="24"/>
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="J97" s="47">
         <f t="shared" ca="1" si="25"/>
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K97" s="164"/>
       <c r="L97" s="40" t="s">
@@ -37176,11 +37282,11 @@
       <c r="H112" s="138"/>
       <c r="I112" s="164">
         <f t="shared" ca="1" si="24"/>
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="J112" s="47">
         <f t="shared" ca="1" si="25"/>
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="K112" s="164" t="s">
         <v>13</v>
@@ -37243,11 +37349,11 @@
       </c>
       <c r="I113" s="164">
         <f t="shared" ca="1" si="24"/>
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="J113" s="47">
         <f t="shared" ca="1" si="25"/>
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="K113" s="164"/>
       <c r="L113" s="40" t="s">
@@ -37379,11 +37485,11 @@
       <c r="H115" s="138"/>
       <c r="I115" s="164">
         <f t="shared" ca="1" si="24"/>
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="J115" s="47">
         <f t="shared" ca="1" si="25"/>
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="K115" s="164"/>
       <c r="L115" s="40" t="s">
@@ -38047,7 +38153,7 @@
       <c r="H125" s="138"/>
       <c r="I125" s="164">
         <f t="shared" ca="1" si="24"/>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J125" s="47">
         <f t="shared" ca="1" si="25"/>
@@ -38106,7 +38212,7 @@
       <c r="H126" s="138"/>
       <c r="I126" s="164">
         <f t="shared" ca="1" si="24"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J126" s="47">
         <f t="shared" ca="1" si="25"/>
@@ -38163,7 +38269,7 @@
       <c r="H127" s="138"/>
       <c r="I127" s="164">
         <f t="shared" ca="1" si="24"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J127" s="47">
         <f t="shared" ca="1" si="25"/>
@@ -39343,7 +39449,7 @@
 _xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(D7),RFA!$E:$E,RFA!$AD:$AD,""),
 IF(_xlpm.x=0,"",_xlpm.x)
 )</f>
-        <v>844</v>
+        <v>846</v>
       </c>
     </row>
     <row r="8" spans="1:25" ht="45">
@@ -39404,7 +39510,7 @@
       </c>
       <c r="S8" s="279">
         <f ca="1"/>
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="Y8" t="s">
         <v>125</v>
@@ -39469,7 +39575,7 @@
       </c>
       <c r="S9" s="279">
         <f ca="1"/>
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="10" spans="1:25" ht="45">
@@ -39530,7 +39636,7 @@
       </c>
       <c r="S10" s="279">
         <f ca="1"/>
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="11" spans="1:25" ht="75">
@@ -39591,7 +39697,7 @@
       </c>
       <c r="S11" s="279">
         <f ca="1"/>
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="12" spans="1:25" ht="45">
@@ -39652,7 +39758,7 @@
       </c>
       <c r="S12" s="279">
         <f ca="1"/>
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="13" spans="1:25" ht="45">
@@ -39713,7 +39819,7 @@
       </c>
       <c r="S13" s="279">
         <f ca="1"/>
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="14" spans="1:25" ht="45">
@@ -39774,7 +39880,7 @@
       </c>
       <c r="S14" s="279">
         <f ca="1"/>
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="15" spans="1:25" ht="60">
@@ -40605,7 +40711,7 @@
 PAS</v>
       </c>
       <c r="C7" s="282" t="str" cm="1">
-        <f t="array" ref="C7:C18">_xlfn._xlws.FILTER('RFA-SDS'!$D$5:$D$4868,'RFA-SDS'!$AI$5:$AI$4868="YES","")</f>
+        <f t="array" ref="C7:C18">_xlfn._xlws.FILTER('RFA-SDS'!$D$5:$D$4869,'RFA-SDS'!$AI$5:$AI$4869="YES","")</f>
         <v>LTIA-5.10-VIETUR-80000-RFA-SDS-0214</v>
       </c>
       <c r="D7" s="303" t="str" cm="1">
@@ -40666,7 +40772,7 @@
       </c>
       <c r="R7" s="279" cm="1">
         <f t="array" aca="1" ref="R7:R18" ca="1">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$AC:$AC,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="8" spans="1:18" ht="30">
@@ -40724,7 +40830,7 @@
       </c>
       <c r="R8" s="279">
         <f ca="1"/>
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="45">
@@ -40782,7 +40888,7 @@
       </c>
       <c r="R9" s="279">
         <f ca="1"/>
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="105">
@@ -40841,7 +40947,7 @@
       </c>
       <c r="R10" s="279">
         <f ca="1"/>
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="45">
@@ -40899,7 +41005,7 @@
       </c>
       <c r="R11" s="279">
         <f ca="1"/>
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="12" spans="1:18" ht="45">
@@ -40958,7 +41064,7 @@
       </c>
       <c r="R12" s="279">
         <f ca="1"/>
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="75">
@@ -41016,7 +41122,7 @@
       </c>
       <c r="R13" s="279">
         <f ca="1"/>
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="14" spans="1:18" ht="60">
@@ -41074,7 +41180,7 @@
       </c>
       <c r="R14" s="279">
         <f ca="1"/>
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="15" spans="1:18" ht="45">
@@ -41132,7 +41238,7 @@
       </c>
       <c r="R15" s="279">
         <f ca="1"/>
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="45">
@@ -41190,7 +41296,7 @@
       </c>
       <c r="R16" s="279">
         <f ca="1"/>
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="17" spans="1:18" ht="60">
@@ -41306,7 +41412,7 @@
       </c>
       <c r="R18" s="279">
         <f ca="1"/>
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
   </sheetData>
@@ -41364,19 +41470,19 @@
     <row r="3" spans="1:4" ht="15.75">
       <c r="A3" s="319">
         <f ca="1">MAX('Need ReSub (RFA)'!S7:S76)</f>
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="B3" s="319">
         <f ca="1">AVERAGEIF('Need ReSub (RFA)'!S7:S76,"&lt;&gt;0")</f>
-        <v>452.25</v>
+        <v>454.25</v>
       </c>
       <c r="C3" s="319">
         <f ca="1">MAX(_xlfn.ANCHORARRAY('Need ReSub (RFA-SDS)'!R7))</f>
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="D3" s="319">
         <f ca="1">AVERAGEIF(_xlfn.ANCHORARRAY('Need ReSub (RFA-SDS)'!R7),"&lt;&gt;0")</f>
-        <v>335.91666666666669</v>
+        <v>337.75</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -41385,10 +41491,10 @@
 Furthermore, the RFA (SDS) is as follows:
 Avarage :  " &amp; ROUND($D$3,0) &amp; " days
 Maimum :  " &amp; ROUND($C$3,0) &amp; " days"</f>
-        <v>In the RFA process, the average number of days elapsed since responding to an unapproved RFA was 452 days, with a maximum of 844 days, indicating that delays in the RFA approval process are contributing to delays in construction work.
+        <v>In the RFA process, the average number of days elapsed since responding to an unapproved RFA was 454 days, with a maximum of 846 days, indicating that delays in the RFA approval process are contributing to delays in construction work.
 Furthermore, the RFA (SDS) is as follows:
-Avarage :  336 days
-Maimum :  544 days</v>
+Avarage :  338 days
+Maimum :  546 days</v>
       </c>
       <c r="B5" s="452"/>
     </row>

--- a/ICT-RFA-RFI-lists-New.xlsx
+++ b/ICT-RFA-RFI-lists-New.xlsx
@@ -9,7 +9,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project Airport\LTIA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBFC37CA-3DD4-4461-98C4-97E18107EF83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFF966B9-3B1C-40EB-9BCA-4855061DB119}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="506" xr2:uid="{CCA8147E-0981-4321-B87F-440A52C0DA59}"/>
   </bookViews>
@@ -78,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3430" uniqueCount="1066">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3436" uniqueCount="1068">
   <si>
     <t>TT</t>
   </si>
@@ -4716,9 +4716,6 @@
     <t>Đề nghị phê duyệt bổ sung thêm nhãn hiệu cho giá đỡ thiết bị (giá đỡ đầu Beam) của hệ thống báo cháy</t>
   </si>
   <si>
-    <t>LTIA-5.11-LTICT-RFA-OTH-0012</t>
-  </si>
-  <si>
     <t>Request for Approval of Proposed Motorcycle Parking Card Printing Options.</t>
   </si>
   <si>
@@ -5044,6 +5041,15 @@
   <si>
     <t>10/12/2026: Đã comment
 10/13/2026: Đã gửi comment qua CNC</t>
+  </si>
+  <si>
+    <t>10/14/2026: Đã ký RFCS</t>
+  </si>
+  <si>
+    <t>10/14/2026: Đã ký A</t>
+  </si>
+  <si>
+    <t>LTIA-5.11-LTICT- 71110 -RFA-OTH-0012</t>
   </si>
 </sst>
 </file>
@@ -7480,6 +7486,228 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="51" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="52" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="55" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="55" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -7498,227 +7726,32 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="53" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="47" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="45" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="51" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="52" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="55" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="55" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="58" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -7737,33 +7770,6 @@
     </xf>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="45" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="53" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="47" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -8426,92 +8432,92 @@
       <c r="AE3" s="159"/>
     </row>
     <row r="4" spans="1:35" s="5" customFormat="1" ht="36" customHeight="1" thickBot="1">
-      <c r="A4" s="397" t="s">
+      <c r="A4" s="408" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="407" t="s">
+      <c r="B4" s="348" t="s">
         <v>515</v>
       </c>
-      <c r="C4" s="403" t="s">
+      <c r="C4" s="414" t="s">
         <v>45</v>
       </c>
-      <c r="D4" s="364" t="s">
+      <c r="D4" s="366" t="s">
         <v>95</v>
       </c>
-      <c r="E4" s="362" t="s">
+      <c r="E4" s="369" t="s">
         <v>46</v>
       </c>
-      <c r="F4" s="399" t="s">
+      <c r="F4" s="412" t="s">
         <v>47</v>
       </c>
-      <c r="G4" s="362" t="s">
+      <c r="G4" s="369" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="401" t="s">
+      <c r="H4" s="410" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="364" t="s">
+      <c r="I4" s="366" t="s">
         <v>48</v>
       </c>
-      <c r="J4" s="364" t="s">
+      <c r="J4" s="366" t="s">
         <v>49</v>
       </c>
-      <c r="K4" s="362" t="s">
+      <c r="K4" s="369" t="s">
         <v>78</v>
       </c>
-      <c r="L4" s="364" t="s">
+      <c r="L4" s="366" t="s">
         <v>80</v>
       </c>
-      <c r="M4" s="366" t="s">
+      <c r="M4" s="364" t="s">
         <v>53</v>
       </c>
-      <c r="N4" s="367"/>
-      <c r="O4" s="366" t="s">
+      <c r="N4" s="365"/>
+      <c r="O4" s="364" t="s">
         <v>55</v>
       </c>
-      <c r="P4" s="367"/>
+      <c r="P4" s="365"/>
       <c r="Q4" s="368" t="s">
         <v>72</v>
       </c>
-      <c r="R4" s="367"/>
-      <c r="S4" s="366" t="s">
+      <c r="R4" s="365"/>
+      <c r="S4" s="364" t="s">
         <v>53</v>
       </c>
-      <c r="T4" s="366"/>
-      <c r="U4" s="367"/>
+      <c r="T4" s="364"/>
+      <c r="U4" s="365"/>
       <c r="V4" s="368" t="s">
         <v>55</v>
       </c>
-      <c r="W4" s="366"/>
-      <c r="X4" s="367"/>
-      <c r="Y4" s="393" t="s">
+      <c r="W4" s="364"/>
+      <c r="X4" s="365"/>
+      <c r="Y4" s="371" t="s">
         <v>72</v>
       </c>
-      <c r="Z4" s="427"/>
-      <c r="AA4" s="426" t="s">
+      <c r="Z4" s="372"/>
+      <c r="AA4" s="359" t="s">
         <v>112</v>
       </c>
-      <c r="AB4" s="395"/>
-      <c r="AC4" s="395"/>
-      <c r="AD4" s="396"/>
-      <c r="AE4" s="362" t="s">
+      <c r="AB4" s="360"/>
+      <c r="AC4" s="360"/>
+      <c r="AD4" s="361"/>
+      <c r="AE4" s="369" t="s">
         <v>79</v>
       </c>
       <c r="AG4" s="236"/>
     </row>
     <row r="5" spans="1:35" ht="78.75">
-      <c r="A5" s="398"/>
-      <c r="B5" s="408"/>
-      <c r="C5" s="404"/>
-      <c r="D5" s="365"/>
-      <c r="E5" s="369"/>
-      <c r="F5" s="400"/>
-      <c r="G5" s="369"/>
-      <c r="H5" s="402"/>
-      <c r="I5" s="365"/>
-      <c r="J5" s="365"/>
-      <c r="K5" s="369"/>
-      <c r="L5" s="365"/>
+      <c r="A5" s="409"/>
+      <c r="B5" s="349"/>
+      <c r="C5" s="415"/>
+      <c r="D5" s="367"/>
+      <c r="E5" s="370"/>
+      <c r="F5" s="413"/>
+      <c r="G5" s="370"/>
+      <c r="H5" s="411"/>
+      <c r="I5" s="367"/>
+      <c r="J5" s="367"/>
+      <c r="K5" s="370"/>
+      <c r="L5" s="367"/>
       <c r="M5" s="79" t="s">
         <v>52</v>
       </c>
@@ -8566,14 +8572,14 @@
       <c r="AD5" s="336" t="s">
         <v>118</v>
       </c>
-      <c r="AE5" s="363"/>
-      <c r="AG5" s="362" t="s">
+      <c r="AE5" s="416"/>
+      <c r="AG5" s="369" t="s">
         <v>119</v>
       </c>
-      <c r="AH5" s="362" t="s">
+      <c r="AH5" s="369" t="s">
         <v>120</v>
       </c>
-      <c r="AI5" s="362" t="s">
+      <c r="AI5" s="369" t="s">
         <v>121</v>
       </c>
     </row>
@@ -8609,9 +8615,9 @@
       <c r="AC6" s="86"/>
       <c r="AD6" s="86"/>
       <c r="AE6" s="74"/>
-      <c r="AG6" s="409"/>
-      <c r="AH6" s="409"/>
-      <c r="AI6" s="409"/>
+      <c r="AG6" s="407"/>
+      <c r="AH6" s="407"/>
+      <c r="AI6" s="407"/>
     </row>
     <row r="7" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A7" s="33">
@@ -14841,14 +14847,16 @@
         <f t="shared" si="5"/>
         <v>46092</v>
       </c>
-      <c r="AB60" s="229"/>
+      <c r="AB60" s="229">
+        <v>46295</v>
+      </c>
       <c r="AC60" s="229" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v>Not submit yet</v>
+        <f t="shared" si="12"/>
+        <v>Late Resubmission</v>
       </c>
       <c r="AD60" s="337">
-        <f t="shared" ca="1" si="13"/>
-        <v>217</v>
+        <f t="shared" si="13"/>
+        <v>203</v>
       </c>
       <c r="AE60" s="92" t="s">
         <v>878</v>
@@ -16969,7 +16977,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:35" s="9" customFormat="1" ht="141.75">
+    <row r="79" spans="1:35" s="9" customFormat="1" ht="126">
       <c r="A79" s="33">
         <f t="shared" si="19"/>
         <v>73</v>
@@ -17079,7 +17087,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:35" s="9" customFormat="1" ht="141.75">
+    <row r="80" spans="1:35" s="9" customFormat="1" ht="126">
       <c r="A80" s="33">
         <f t="shared" si="19"/>
         <v>74</v>
@@ -17189,7 +17197,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:35" s="9" customFormat="1" ht="126">
+    <row r="81" spans="1:35" s="9" customFormat="1" ht="110.25">
       <c r="A81" s="33">
         <f t="shared" si="19"/>
         <v>75</v>
@@ -17295,7 +17303,7 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="1:35" s="9" customFormat="1" ht="63">
+    <row r="82" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A82" s="33">
         <f t="shared" si="19"/>
         <v>76</v>
@@ -17610,7 +17618,7 @@
         <v/>
       </c>
     </row>
-    <row r="85" spans="1:35" s="9" customFormat="1" ht="110.25">
+    <row r="85" spans="1:35" s="9" customFormat="1" ht="94.5">
       <c r="A85" s="33">
         <f t="shared" si="19"/>
         <v>79</v>
@@ -18415,7 +18423,7 @@
         <v>128</v>
       </c>
       <c r="L92" s="164" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="M92" s="40" t="s">
         <v>8</v>
@@ -19944,7 +19952,7 @@
         <v/>
       </c>
       <c r="AE106" s="92" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="AG106" s="238" t="str">
         <f t="shared" si="14"/>
@@ -20249,7 +20257,7 @@
         <v/>
       </c>
       <c r="AE109" s="92" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="AG109" s="238" t="str">
         <f t="shared" si="14"/>
@@ -20451,7 +20459,7 @@
         <v/>
       </c>
       <c r="AE111" s="92" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="AG111" s="238" t="str">
         <f t="shared" si="14"/>
@@ -20602,7 +20610,7 @@
         <v>46234</v>
       </c>
       <c r="G113" s="31" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="H113" s="21" t="s">
         <v>924</v>
@@ -20769,7 +20777,7 @@
         <v/>
       </c>
       <c r="AE114" s="92" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="AG114" s="238" t="str">
         <f t="shared" si="14"/>
@@ -20877,7 +20885,7 @@
         <v/>
       </c>
       <c r="AE115" s="92" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="AG115" s="238" t="str">
         <f t="shared" si="14"/>
@@ -20989,7 +20997,7 @@
         <v/>
       </c>
       <c r="AE116" s="92" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="AG116" s="238" t="str">
         <f t="shared" si="14"/>
@@ -21047,7 +21055,7 @@
         <v>41</v>
       </c>
       <c r="L117" s="164" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="M117" s="40" t="s">
         <v>8</v>
@@ -21085,7 +21093,7 @@
         <v/>
       </c>
       <c r="AE117" s="92" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="AG117" s="238" t="str">
         <f t="shared" si="14"/>
@@ -21215,17 +21223,17 @@
         <v>28</v>
       </c>
       <c r="E119" s="25" t="s">
-        <v>965</v>
+        <v>1067</v>
       </c>
       <c r="F119" s="174">
         <f t="shared" si="29"/>
         <v>46275</v>
       </c>
       <c r="G119" s="31" t="s">
+        <v>965</v>
+      </c>
+      <c r="H119" s="21" t="s">
         <v>966</v>
-      </c>
-      <c r="H119" s="21" t="s">
-        <v>967</v>
       </c>
       <c r="I119" s="138" t="s">
         <v>3</v>
@@ -21273,7 +21281,9 @@
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="AB119" s="229"/>
+      <c r="AB119" s="229">
+        <v>46301</v>
+      </c>
       <c r="AC119" s="229" t="str">
         <f t="shared" si="22"/>
         <v/>
@@ -21283,11 +21293,11 @@
         <v/>
       </c>
       <c r="AE119" s="92" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="AG119" s="238" t="str">
         <f t="shared" si="14"/>
-        <v>LTIA-5.11-LTICT-RFA-OTH-0012</v>
+        <v>LTIA-5.11-LTICT- 71110 -RFA-OTH-0012</v>
       </c>
       <c r="AH119" s="243" t="b" cm="1">
         <f t="array" ref="AH119">$E119=_xlfn.XLOOKUP(
@@ -21298,7 +21308,7 @@
 0,
 -1
 )</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI119" s="75" t="str">
         <f t="shared" si="24"/>
@@ -21321,17 +21331,17 @@
         <v>28</v>
       </c>
       <c r="E120" s="25" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="F120" s="174">
         <f t="shared" si="29"/>
         <v>46276</v>
       </c>
       <c r="G120" s="31" t="s">
+        <v>968</v>
+      </c>
+      <c r="H120" s="21" t="s">
         <v>969</v>
-      </c>
-      <c r="H120" s="21" t="s">
-        <v>970</v>
       </c>
       <c r="I120" s="138" t="s">
         <v>1</v>
@@ -21389,7 +21399,7 @@
         <v/>
       </c>
       <c r="AE120" s="92" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="AG120" s="238" t="str">
         <f t="shared" si="14"/>
@@ -21427,7 +21437,7 @@
         <v>28</v>
       </c>
       <c r="E121" s="25" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="F121" s="174">
         <f t="shared" si="29"/>
@@ -21481,7 +21491,7 @@
         <v/>
       </c>
       <c r="AE121" s="92" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="AG121" s="238" t="str">
         <f t="shared" si="14"/>
@@ -21519,7 +21529,7 @@
         <v>28</v>
       </c>
       <c r="E122" s="25" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="F122" s="174">
         <f t="shared" si="29"/>
@@ -21623,14 +21633,14 @@
         <v>28</v>
       </c>
       <c r="E123" s="25" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="F123" s="174">
         <f t="shared" si="29"/>
         <v>46293</v>
       </c>
       <c r="G123" s="31" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="H123" s="21" t="s">
         <v>924</v>
@@ -21677,7 +21687,7 @@
         <v/>
       </c>
       <c r="AE123" s="92" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="AG123" s="238" t="str">
         <f t="shared" si="14"/>
@@ -21715,17 +21725,17 @@
         <v>30</v>
       </c>
       <c r="E124" s="25" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="F124" s="174">
         <f t="shared" si="29"/>
         <v>46324</v>
       </c>
       <c r="G124" s="31" t="s">
+        <v>982</v>
+      </c>
+      <c r="H124" s="21" t="s">
         <v>983</v>
-      </c>
-      <c r="H124" s="21" t="s">
-        <v>984</v>
       </c>
       <c r="I124" s="138" t="s">
         <v>3</v>
@@ -21783,7 +21793,7 @@
         <v/>
       </c>
       <c r="AE124" s="92" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="AG124" s="238" t="str">
         <f t="shared" si="14"/>
@@ -21821,14 +21831,14 @@
         <v>30</v>
       </c>
       <c r="E125" s="25" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="F125" s="174">
         <f t="shared" si="29"/>
         <v>46310</v>
       </c>
       <c r="G125" s="31" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="H125" s="21" t="s">
         <v>776</v>
@@ -21889,7 +21899,7 @@
         <v/>
       </c>
       <c r="AE125" s="92" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="AG125" s="238" t="str">
         <f t="shared" ref="AG125:AG135" si="75">IF(AND(RIGHT($E125,1)&gt;="A",RIGHT($E125,1)&lt;="Z"),LEFT($E125,LEN($E125)-1),$E125)</f>
@@ -21927,14 +21937,14 @@
         <v>28</v>
       </c>
       <c r="E126" s="25" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="F126" s="174">
         <f t="shared" si="29"/>
         <v>46310</v>
       </c>
       <c r="G126" s="31" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="H126" s="21" t="s">
         <v>924</v>
@@ -21995,7 +22005,7 @@
         <v/>
       </c>
       <c r="AE126" s="92" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="AG126" s="238" t="str">
         <f t="shared" si="75"/>
@@ -22095,7 +22105,7 @@
       <c r="AC127" s="229"/>
       <c r="AD127" s="337"/>
       <c r="AE127" s="92" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="AG127" s="238" t="str">
         <f t="shared" si="75"/>
@@ -22133,17 +22143,17 @@
         <v>30</v>
       </c>
       <c r="E128" s="25" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="F128" s="174">
         <f t="shared" si="29"/>
         <v>46316</v>
       </c>
       <c r="G128" s="31" t="s">
+        <v>1006</v>
+      </c>
+      <c r="H128" s="21" t="s">
         <v>1007</v>
-      </c>
-      <c r="H128" s="21" t="s">
-        <v>1008</v>
       </c>
       <c r="I128" s="138"/>
       <c r="J128" s="164">
@@ -22221,17 +22231,17 @@
         <v>32</v>
       </c>
       <c r="E129" s="25" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="F129" s="174">
         <f t="shared" si="29"/>
         <v>46319</v>
       </c>
       <c r="G129" s="31" t="s">
+        <v>1028</v>
+      </c>
+      <c r="H129" s="21" t="s">
         <v>1029</v>
-      </c>
-      <c r="H129" s="21" t="s">
-        <v>1030</v>
       </c>
       <c r="I129" s="138"/>
       <c r="J129" s="164">
@@ -22273,7 +22283,7 @@
       <c r="AC129" s="229"/>
       <c r="AD129" s="337"/>
       <c r="AE129" s="92" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="AG129" s="238" t="str">
         <f t="shared" si="75"/>
@@ -22311,17 +22321,17 @@
         <v>32</v>
       </c>
       <c r="E130" s="25" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="F130" s="174">
         <f t="shared" si="29"/>
         <v>46321</v>
       </c>
       <c r="G130" s="31" t="s">
+        <v>1033</v>
+      </c>
+      <c r="H130" s="21" t="s">
         <v>1034</v>
-      </c>
-      <c r="H130" s="21" t="s">
-        <v>1035</v>
       </c>
       <c r="I130" s="138"/>
       <c r="J130" s="164">
@@ -22399,17 +22409,17 @@
         <v>32</v>
       </c>
       <c r="E131" s="25" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="F131" s="174">
         <f t="shared" si="29"/>
         <v>46321</v>
       </c>
       <c r="G131" s="31" t="s">
+        <v>1037</v>
+      </c>
+      <c r="H131" s="21" t="s">
         <v>1038</v>
-      </c>
-      <c r="H131" s="21" t="s">
-        <v>1039</v>
       </c>
       <c r="I131" s="138"/>
       <c r="J131" s="164">
@@ -22451,7 +22461,7 @@
       <c r="AC131" s="229"/>
       <c r="AD131" s="337"/>
       <c r="AE131" s="92" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="AG131" s="238" t="str">
         <f t="shared" si="75"/>
@@ -22489,17 +22499,17 @@
         <v>32</v>
       </c>
       <c r="E132" s="25" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="F132" s="174">
         <f t="shared" si="29"/>
         <v>46322</v>
       </c>
       <c r="G132" s="31" t="s">
+        <v>1040</v>
+      </c>
+      <c r="H132" s="21" t="s">
         <v>1041</v>
-      </c>
-      <c r="H132" s="21" t="s">
-        <v>1042</v>
       </c>
       <c r="I132" s="138"/>
       <c r="J132" s="164">
@@ -22541,7 +22551,7 @@
       <c r="AC132" s="229"/>
       <c r="AD132" s="337"/>
       <c r="AE132" s="92" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="AG132" s="238" t="str">
         <f t="shared" si="75"/>
@@ -22579,17 +22589,17 @@
         <v>32</v>
       </c>
       <c r="E133" s="25" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="F133" s="174">
         <f t="shared" si="29"/>
         <v>46322</v>
       </c>
       <c r="G133" s="31" t="s">
+        <v>1043</v>
+      </c>
+      <c r="H133" s="21" t="s">
         <v>1044</v>
-      </c>
-      <c r="H133" s="21" t="s">
-        <v>1045</v>
       </c>
       <c r="I133" s="138"/>
       <c r="J133" s="164">
@@ -22667,17 +22677,17 @@
         <v>32</v>
       </c>
       <c r="E134" s="25" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="F134" s="174">
         <f t="shared" si="29"/>
         <v>46322</v>
       </c>
       <c r="G134" s="31" t="s">
+        <v>1046</v>
+      </c>
+      <c r="H134" s="21" t="s">
         <v>1047</v>
-      </c>
-      <c r="H134" s="21" t="s">
-        <v>1048</v>
       </c>
       <c r="I134" s="138"/>
       <c r="J134" s="164">
@@ -22755,19 +22765,21 @@
         <v>28</v>
       </c>
       <c r="E135" s="25" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="F135" s="174">
         <f t="shared" si="29"/>
         <v>46322</v>
       </c>
       <c r="G135" s="31" t="s">
+        <v>1049</v>
+      </c>
+      <c r="H135" s="21" t="s">
         <v>1050</v>
       </c>
-      <c r="H135" s="21" t="s">
-        <v>1051</v>
-      </c>
-      <c r="I135" s="138"/>
+      <c r="I135" s="138" t="s">
+        <v>3</v>
+      </c>
       <c r="J135" s="164">
         <f t="shared" ca="1" si="30"/>
         <v>8</v>
@@ -22796,17 +22808,21 @@
       </c>
       <c r="V135" s="29"/>
       <c r="W135" s="188"/>
-      <c r="X135" s="235"/>
+      <c r="X135" s="235" t="s">
+        <v>240</v>
+      </c>
       <c r="Y135" s="230"/>
       <c r="Z135" s="227"/>
-      <c r="AA135" s="29" t="str">
+      <c r="AA135" s="29" t="b">
         <f t="shared" si="68"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AB135" s="229"/>
       <c r="AC135" s="229"/>
       <c r="AD135" s="337"/>
-      <c r="AE135" s="92"/>
+      <c r="AE135" s="92" t="s">
+        <v>1066</v>
+      </c>
       <c r="AG135" s="238" t="str">
         <f t="shared" si="75"/>
         <v>LTIA-5.11-LTICT- 71110 -RFA-OTH-0012</v>
@@ -22918,29 +22934,29 @@
       <c r="C139" s="166" t="s">
         <v>20</v>
       </c>
-      <c r="D139" s="405" t="s">
+      <c r="D139" s="376" t="s">
         <v>21</v>
       </c>
-      <c r="E139" s="405"/>
-      <c r="F139" s="406"/>
+      <c r="E139" s="376"/>
+      <c r="F139" s="377"/>
       <c r="G139" s="46"/>
       <c r="H139" s="68"/>
-      <c r="I139" s="357" t="s">
+      <c r="I139" s="356" t="s">
         <v>14</v>
       </c>
-      <c r="J139" s="358"/>
-      <c r="K139" s="358"/>
-      <c r="L139" s="358"/>
-      <c r="M139" s="358"/>
-      <c r="N139" s="359"/>
-      <c r="O139" s="360" t="s">
+      <c r="J139" s="357"/>
+      <c r="K139" s="357"/>
+      <c r="L139" s="357"/>
+      <c r="M139" s="357"/>
+      <c r="N139" s="358"/>
+      <c r="O139" s="362" t="s">
         <v>7</v>
       </c>
-      <c r="P139" s="361"/>
-      <c r="Q139" s="360" t="s">
+      <c r="P139" s="363"/>
+      <c r="Q139" s="362" t="s">
         <v>109</v>
       </c>
-      <c r="R139" s="361"/>
+      <c r="R139" s="363"/>
       <c r="S139" s="1"/>
       <c r="T139" s="1"/>
       <c r="U139" s="140"/>
@@ -22962,26 +22978,26 @@
       <c r="C140" s="167" t="s">
         <v>109</v>
       </c>
-      <c r="D140" s="424" t="s">
+      <c r="D140" s="354" t="s">
         <v>111</v>
       </c>
-      <c r="E140" s="424"/>
-      <c r="F140" s="425"/>
+      <c r="E140" s="354"/>
+      <c r="F140" s="355"/>
       <c r="G140" s="46"/>
       <c r="H140" s="46"/>
-      <c r="I140" s="357" t="s">
+      <c r="I140" s="356" t="s">
         <v>19</v>
       </c>
-      <c r="J140" s="358"/>
-      <c r="K140" s="358"/>
-      <c r="L140" s="359"/>
+      <c r="J140" s="357"/>
+      <c r="K140" s="357"/>
+      <c r="L140" s="358"/>
       <c r="M140" s="105">
         <f t="shared" ref="M140:M145" ca="1" si="84">N140/$N$140</f>
         <v>1</v>
       </c>
       <c r="N140" s="106">
         <f ca="1">SUM($N$141:$N$145)</f>
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O140" s="102" t="s">
         <v>15</v>
@@ -23018,30 +23034,30 @@
       <c r="C141" s="167" t="s">
         <v>22</v>
       </c>
-      <c r="D141" s="424" t="s">
+      <c r="D141" s="354" t="s">
         <v>23</v>
       </c>
-      <c r="E141" s="424"/>
-      <c r="F141" s="425"/>
+      <c r="E141" s="354"/>
+      <c r="F141" s="355"/>
       <c r="G141" s="70"/>
       <c r="H141" s="6"/>
-      <c r="I141" s="373" t="s">
+      <c r="I141" s="379" t="s">
         <v>66</v>
       </c>
-      <c r="J141" s="374"/>
-      <c r="K141" s="374"/>
-      <c r="L141" s="375"/>
+      <c r="J141" s="380"/>
+      <c r="K141" s="380"/>
+      <c r="L141" s="381"/>
       <c r="M141" s="107">
         <f t="shared" ca="1" si="84"/>
-        <v>0.5074626865671642</v>
+        <v>0.51111111111111107</v>
       </c>
       <c r="N141" s="108">
         <f>COUNTIF($I$7:$I$137,"A")</f>
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="O141" s="100">
         <f ca="1">COUNTIFS($J$7:$J$137,"&lt;=21",$I$7:$I$137,"A")</f>
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="P141" s="101">
         <f ca="1">COUNTIFS($J$7:$J$137,"&gt;21",$I$7:$I$137,"A")</f>
@@ -23076,21 +23092,21 @@
       <c r="C142" s="167" t="s">
         <v>24</v>
       </c>
-      <c r="D142" s="424" t="s">
+      <c r="D142" s="354" t="s">
         <v>25</v>
       </c>
-      <c r="E142" s="424"/>
-      <c r="F142" s="425"/>
+      <c r="E142" s="354"/>
+      <c r="F142" s="355"/>
       <c r="H142" s="6"/>
-      <c r="I142" s="376" t="s">
+      <c r="I142" s="382" t="s">
         <v>67</v>
       </c>
-      <c r="J142" s="377"/>
-      <c r="K142" s="377"/>
-      <c r="L142" s="378"/>
+      <c r="J142" s="383"/>
+      <c r="K142" s="383"/>
+      <c r="L142" s="384"/>
       <c r="M142" s="109">
         <f t="shared" ca="1" si="84"/>
-        <v>0.1044776119402985</v>
+        <v>0.1037037037037037</v>
       </c>
       <c r="N142" s="110">
         <f>COUNTIF($I$7:$I$137,"B")</f>
@@ -23133,22 +23149,22 @@
       <c r="C143" s="167" t="s">
         <v>26</v>
       </c>
-      <c r="D143" s="424" t="s">
+      <c r="D143" s="354" t="s">
         <v>27</v>
       </c>
-      <c r="E143" s="424"/>
-      <c r="F143" s="425"/>
+      <c r="E143" s="354"/>
+      <c r="F143" s="355"/>
       <c r="G143" s="71"/>
       <c r="H143" s="6"/>
-      <c r="I143" s="379" t="s">
+      <c r="I143" s="385" t="s">
         <v>68</v>
       </c>
-      <c r="J143" s="380"/>
-      <c r="K143" s="380"/>
-      <c r="L143" s="381"/>
+      <c r="J143" s="386"/>
+      <c r="K143" s="386"/>
+      <c r="L143" s="387"/>
       <c r="M143" s="111">
         <f t="shared" ca="1" si="84"/>
-        <v>0.20149253731343283</v>
+        <v>0.2</v>
       </c>
       <c r="N143" s="112">
         <f>COUNTIF($I$7:$I$137,"C")</f>
@@ -23191,21 +23207,21 @@
       <c r="C144" s="168" t="s">
         <v>28</v>
       </c>
-      <c r="D144" s="424" t="s">
+      <c r="D144" s="354" t="s">
         <v>29</v>
       </c>
-      <c r="E144" s="424"/>
-      <c r="F144" s="425"/>
+      <c r="E144" s="354"/>
+      <c r="F144" s="355"/>
       <c r="G144" s="72"/>
-      <c r="I144" s="382" t="s">
+      <c r="I144" s="388" t="s">
         <v>70</v>
       </c>
-      <c r="J144" s="383"/>
-      <c r="K144" s="383"/>
-      <c r="L144" s="384"/>
+      <c r="J144" s="389"/>
+      <c r="K144" s="389"/>
+      <c r="L144" s="390"/>
       <c r="M144" s="114">
         <f t="shared" ca="1" si="84"/>
-        <v>7.4626865671641784E-2</v>
+        <v>7.407407407407407E-2</v>
       </c>
       <c r="N144" s="115">
         <f ca="1">SUM(O144:P144)</f>
@@ -23250,21 +23266,21 @@
       <c r="C145" s="168" t="s">
         <v>30</v>
       </c>
-      <c r="D145" s="424" t="s">
+      <c r="D145" s="354" t="s">
         <v>31</v>
       </c>
-      <c r="E145" s="424"/>
-      <c r="F145" s="425"/>
+      <c r="E145" s="354"/>
+      <c r="F145" s="355"/>
       <c r="H145" s="6"/>
-      <c r="I145" s="354" t="s">
+      <c r="I145" s="391" t="s">
         <v>71</v>
       </c>
-      <c r="J145" s="355"/>
-      <c r="K145" s="355"/>
-      <c r="L145" s="356"/>
+      <c r="J145" s="392"/>
+      <c r="K145" s="392"/>
+      <c r="L145" s="393"/>
       <c r="M145" s="113">
         <f t="shared" ca="1" si="84"/>
-        <v>0.11194029850746269</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="N145" s="97">
         <f>COUNTIFS($L$7:$L$137,"X")</f>
@@ -23281,11 +23297,11 @@
       <c r="C146" s="168" t="s">
         <v>32</v>
       </c>
-      <c r="D146" s="424" t="s">
+      <c r="D146" s="354" t="s">
         <v>33</v>
       </c>
-      <c r="E146" s="424"/>
-      <c r="F146" s="425"/>
+      <c r="E146" s="354"/>
+      <c r="F146" s="355"/>
       <c r="H146" s="1" t="s">
         <v>11</v>
       </c>
@@ -23294,11 +23310,11 @@
       <c r="C147" s="167" t="s">
         <v>34</v>
       </c>
-      <c r="D147" s="424" t="s">
+      <c r="D147" s="354" t="s">
         <v>35</v>
       </c>
-      <c r="E147" s="424"/>
-      <c r="F147" s="425"/>
+      <c r="E147" s="354"/>
+      <c r="F147" s="355"/>
       <c r="H147" s="13"/>
       <c r="I147" s="141"/>
       <c r="J147" s="141"/>
@@ -23326,14 +23342,14 @@
       <c r="AI147" s="1"/>
     </row>
     <row r="148" spans="1:35">
-      <c r="C148" s="385" t="s">
+      <c r="C148" s="394" t="s">
         <v>75</v>
       </c>
-      <c r="D148" s="387" t="s">
+      <c r="D148" s="350" t="s">
         <v>76</v>
       </c>
-      <c r="E148" s="387"/>
-      <c r="F148" s="388"/>
+      <c r="E148" s="350"/>
+      <c r="F148" s="351"/>
       <c r="H148" s="13"/>
       <c r="J148" s="141"/>
       <c r="K148" s="13"/>
@@ -23360,10 +23376,10 @@
       <c r="AI148" s="1"/>
     </row>
     <row r="149" spans="1:35" ht="16.5" thickBot="1">
-      <c r="C149" s="386"/>
-      <c r="D149" s="389"/>
-      <c r="E149" s="389"/>
-      <c r="F149" s="390"/>
+      <c r="C149" s="395"/>
+      <c r="D149" s="352"/>
+      <c r="E149" s="352"/>
+      <c r="F149" s="353"/>
       <c r="H149" s="13"/>
       <c r="I149" s="141"/>
       <c r="J149" s="141"/>
@@ -23418,12 +23434,12 @@
       <c r="AI150" s="1"/>
     </row>
     <row r="151" spans="1:35">
-      <c r="C151" s="372" t="s">
+      <c r="C151" s="378" t="s">
         <v>41</v>
       </c>
-      <c r="D151" s="372"/>
-      <c r="E151" s="372"/>
-      <c r="F151" s="372"/>
+      <c r="D151" s="378"/>
+      <c r="E151" s="378"/>
+      <c r="F151" s="378"/>
       <c r="H151" s="13"/>
       <c r="I151" s="141"/>
       <c r="J151" s="141"/>
@@ -23454,11 +23470,11 @@
       <c r="C152" s="169" t="s">
         <v>8</v>
       </c>
-      <c r="D152" s="412" t="s">
+      <c r="D152" s="396" t="s">
         <v>91</v>
       </c>
-      <c r="E152" s="412"/>
-      <c r="F152" s="412"/>
+      <c r="E152" s="396"/>
+      <c r="F152" s="396"/>
       <c r="H152" s="13"/>
       <c r="I152" s="141"/>
       <c r="J152" s="141"/>
@@ -23489,11 +23505,11 @@
       <c r="C153" s="169" t="s">
         <v>8</v>
       </c>
-      <c r="D153" s="412" t="s">
+      <c r="D153" s="396" t="s">
         <v>92</v>
       </c>
-      <c r="E153" s="412"/>
-      <c r="F153" s="412"/>
+      <c r="E153" s="396"/>
+      <c r="F153" s="396"/>
       <c r="H153" s="13"/>
       <c r="I153" s="141"/>
       <c r="J153" s="141"/>
@@ -23524,11 +23540,11 @@
       <c r="C154" s="169" t="s">
         <v>8</v>
       </c>
-      <c r="D154" s="412" t="s">
+      <c r="D154" s="396" t="s">
         <v>93</v>
       </c>
-      <c r="E154" s="412"/>
-      <c r="F154" s="412"/>
+      <c r="E154" s="396"/>
+      <c r="F154" s="396"/>
       <c r="H154" s="13"/>
       <c r="I154" s="141"/>
       <c r="J154" s="141"/>
@@ -23583,12 +23599,12 @@
       <c r="AI155" s="1"/>
     </row>
     <row r="156" spans="1:35" ht="16.5" thickBot="1">
-      <c r="C156" s="416" t="s">
+      <c r="C156" s="402" t="s">
         <v>96</v>
       </c>
-      <c r="D156" s="417"/>
-      <c r="E156" s="417"/>
-      <c r="F156" s="418"/>
+      <c r="D156" s="403"/>
+      <c r="E156" s="403"/>
+      <c r="F156" s="404"/>
       <c r="H156" s="13"/>
       <c r="I156" s="141"/>
       <c r="J156" s="141"/>
@@ -23619,11 +23635,11 @@
       <c r="C157" s="212" t="s">
         <v>81</v>
       </c>
-      <c r="D157" s="419" t="s">
+      <c r="D157" s="405" t="s">
         <v>97</v>
       </c>
-      <c r="E157" s="419"/>
-      <c r="F157" s="420"/>
+      <c r="E157" s="405"/>
+      <c r="F157" s="406"/>
       <c r="H157" s="13"/>
       <c r="I157" s="141"/>
       <c r="J157" s="141"/>
@@ -23654,101 +23670,101 @@
       <c r="C158" s="213" t="s">
         <v>82</v>
       </c>
-      <c r="D158" s="410" t="s">
+      <c r="D158" s="397" t="s">
         <v>98</v>
       </c>
-      <c r="E158" s="410"/>
-      <c r="F158" s="411"/>
+      <c r="E158" s="397"/>
+      <c r="F158" s="398"/>
     </row>
     <row r="159" spans="1:35">
       <c r="C159" s="213" t="s">
         <v>83</v>
       </c>
-      <c r="D159" s="410" t="s">
+      <c r="D159" s="397" t="s">
         <v>99</v>
       </c>
-      <c r="E159" s="410"/>
-      <c r="F159" s="411"/>
+      <c r="E159" s="397"/>
+      <c r="F159" s="398"/>
     </row>
     <row r="160" spans="1:35">
       <c r="C160" s="214" t="s">
         <v>84</v>
       </c>
-      <c r="D160" s="410" t="s">
+      <c r="D160" s="397" t="s">
         <v>100</v>
       </c>
-      <c r="E160" s="410"/>
-      <c r="F160" s="411"/>
+      <c r="E160" s="397"/>
+      <c r="F160" s="398"/>
     </row>
     <row r="161" spans="3:6">
       <c r="C161" s="214" t="s">
         <v>85</v>
       </c>
-      <c r="D161" s="410" t="s">
+      <c r="D161" s="397" t="s">
         <v>101</v>
       </c>
-      <c r="E161" s="410"/>
-      <c r="F161" s="411"/>
+      <c r="E161" s="397"/>
+      <c r="F161" s="398"/>
     </row>
     <row r="162" spans="3:6" ht="18.75">
       <c r="C162" s="214" t="s">
         <v>86</v>
       </c>
-      <c r="D162" s="410" t="s">
+      <c r="D162" s="397" t="s">
         <v>102</v>
       </c>
-      <c r="E162" s="410"/>
-      <c r="F162" s="411"/>
+      <c r="E162" s="397"/>
+      <c r="F162" s="398"/>
     </row>
     <row r="163" spans="3:6" ht="18.75">
       <c r="C163" s="213" t="s">
         <v>87</v>
       </c>
-      <c r="D163" s="410" t="s">
+      <c r="D163" s="397" t="s">
         <v>103</v>
       </c>
-      <c r="E163" s="410"/>
-      <c r="F163" s="411"/>
+      <c r="E163" s="397"/>
+      <c r="F163" s="398"/>
     </row>
     <row r="164" spans="3:6">
       <c r="C164" s="215" t="s">
         <v>88</v>
       </c>
-      <c r="D164" s="413" t="s">
+      <c r="D164" s="399" t="s">
         <v>104</v>
       </c>
-      <c r="E164" s="414"/>
-      <c r="F164" s="415"/>
+      <c r="E164" s="400"/>
+      <c r="F164" s="401"/>
     </row>
     <row r="165" spans="3:6" ht="18.75">
       <c r="C165" s="215" t="s">
         <v>89</v>
       </c>
-      <c r="D165" s="410" t="s">
+      <c r="D165" s="397" t="s">
         <v>105</v>
       </c>
-      <c r="E165" s="410"/>
-      <c r="F165" s="411"/>
+      <c r="E165" s="397"/>
+      <c r="F165" s="398"/>
     </row>
     <row r="166" spans="3:6">
       <c r="C166" s="213" t="s">
         <v>90</v>
       </c>
-      <c r="D166" s="410" t="s">
+      <c r="D166" s="397" t="s">
         <v>106</v>
       </c>
-      <c r="E166" s="410"/>
-      <c r="F166" s="411"/>
+      <c r="E166" s="397"/>
+      <c r="F166" s="398"/>
     </row>
     <row r="167" spans="3:6" ht="16.5" thickBot="1">
       <c r="C167" s="216" t="s">
         <v>94</v>
       </c>
-      <c r="D167" s="421" t="s">
+      <c r="D167" s="373" t="s">
         <v>107</v>
       </c>
-      <c r="E167" s="422"/>
-      <c r="F167" s="423"/>
+      <c r="E167" s="374"/>
+      <c r="F167" s="375"/>
     </row>
   </sheetData>
   <autoFilter ref="A6:AE137" xr:uid="{C724CDAB-378C-47DB-9F45-08EE3BFB6E8B}">
@@ -23757,20 +23773,35 @@
     </sortState>
   </autoFilter>
   <mergeCells count="59">
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="D148:F149"/>
-    <mergeCell ref="D140:F140"/>
-    <mergeCell ref="I140:L140"/>
-    <mergeCell ref="AA4:AD4"/>
-    <mergeCell ref="Q139:R139"/>
-    <mergeCell ref="D145:F145"/>
-    <mergeCell ref="D146:F146"/>
-    <mergeCell ref="D147:F147"/>
-    <mergeCell ref="S4:U4"/>
-    <mergeCell ref="L4:L5"/>
-    <mergeCell ref="Q4:R4"/>
-    <mergeCell ref="K4:K5"/>
-    <mergeCell ref="Y4:Z4"/>
+    <mergeCell ref="AG5:AG6"/>
+    <mergeCell ref="AH5:AH6"/>
+    <mergeCell ref="AI5:AI6"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="AE4:AE5"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="V4:X4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="O4:P4"/>
+    <mergeCell ref="D166:F166"/>
+    <mergeCell ref="D153:F153"/>
+    <mergeCell ref="D154:F154"/>
+    <mergeCell ref="D161:F161"/>
+    <mergeCell ref="D162:F162"/>
+    <mergeCell ref="D163:F163"/>
+    <mergeCell ref="D164:F164"/>
+    <mergeCell ref="D165:F165"/>
+    <mergeCell ref="C156:F156"/>
+    <mergeCell ref="D157:F157"/>
+    <mergeCell ref="D158:F158"/>
+    <mergeCell ref="D159:F159"/>
+    <mergeCell ref="D160:F160"/>
     <mergeCell ref="D167:F167"/>
     <mergeCell ref="D139:F139"/>
     <mergeCell ref="C151:F151"/>
@@ -23787,35 +23818,20 @@
     <mergeCell ref="D143:F143"/>
     <mergeCell ref="D144:F144"/>
     <mergeCell ref="D152:F152"/>
-    <mergeCell ref="D166:F166"/>
-    <mergeCell ref="D153:F153"/>
-    <mergeCell ref="D154:F154"/>
-    <mergeCell ref="D161:F161"/>
-    <mergeCell ref="D162:F162"/>
-    <mergeCell ref="D163:F163"/>
-    <mergeCell ref="D164:F164"/>
-    <mergeCell ref="D165:F165"/>
-    <mergeCell ref="C156:F156"/>
-    <mergeCell ref="D157:F157"/>
-    <mergeCell ref="D158:F158"/>
-    <mergeCell ref="D159:F159"/>
-    <mergeCell ref="D160:F160"/>
-    <mergeCell ref="AG5:AG6"/>
-    <mergeCell ref="AH5:AH6"/>
-    <mergeCell ref="AI5:AI6"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="I4:I5"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="H4:H5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="AE4:AE5"/>
-    <mergeCell ref="J4:J5"/>
-    <mergeCell ref="V4:X4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="O4:P4"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="D148:F149"/>
+    <mergeCell ref="D140:F140"/>
+    <mergeCell ref="I140:L140"/>
+    <mergeCell ref="AA4:AD4"/>
+    <mergeCell ref="Q139:R139"/>
+    <mergeCell ref="D145:F145"/>
+    <mergeCell ref="D146:F146"/>
+    <mergeCell ref="D147:F147"/>
+    <mergeCell ref="S4:U4"/>
+    <mergeCell ref="L4:L5"/>
+    <mergeCell ref="Q4:R4"/>
+    <mergeCell ref="K4:K5"/>
+    <mergeCell ref="Y4:Z4"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="A7:AE137 AG7:AI137">
@@ -24480,88 +24496,88 @@
       <c r="AD3" s="159"/>
     </row>
     <row r="4" spans="1:35" s="5" customFormat="1" ht="36" customHeight="1" thickBot="1">
-      <c r="A4" s="397" t="s">
+      <c r="A4" s="408" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="407" t="s">
+      <c r="B4" s="348" t="s">
         <v>515</v>
       </c>
-      <c r="C4" s="403" t="s">
+      <c r="C4" s="414" t="s">
         <v>45</v>
       </c>
-      <c r="D4" s="362" t="s">
+      <c r="D4" s="369" t="s">
         <v>46</v>
       </c>
-      <c r="E4" s="399" t="s">
+      <c r="E4" s="412" t="s">
         <v>47</v>
       </c>
-      <c r="F4" s="362" t="s">
+      <c r="F4" s="369" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="401" t="s">
+      <c r="G4" s="410" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="364" t="s">
+      <c r="H4" s="366" t="s">
         <v>48</v>
       </c>
-      <c r="I4" s="364" t="s">
+      <c r="I4" s="366" t="s">
         <v>49</v>
       </c>
-      <c r="J4" s="362" t="s">
+      <c r="J4" s="369" t="s">
         <v>78</v>
       </c>
-      <c r="K4" s="364" t="s">
+      <c r="K4" s="366" t="s">
         <v>80</v>
       </c>
-      <c r="L4" s="366" t="s">
+      <c r="L4" s="364" t="s">
         <v>53</v>
       </c>
-      <c r="M4" s="367"/>
+      <c r="M4" s="365"/>
       <c r="N4" s="368" t="s">
         <v>55</v>
       </c>
-      <c r="O4" s="367"/>
+      <c r="O4" s="365"/>
       <c r="P4" s="368" t="s">
         <v>72</v>
       </c>
-      <c r="Q4" s="367"/>
-      <c r="R4" s="366" t="s">
+      <c r="Q4" s="365"/>
+      <c r="R4" s="364" t="s">
         <v>53</v>
       </c>
-      <c r="S4" s="366"/>
-      <c r="T4" s="367"/>
+      <c r="S4" s="364"/>
+      <c r="T4" s="365"/>
       <c r="U4" s="368" t="s">
         <v>55</v>
       </c>
-      <c r="V4" s="366"/>
-      <c r="W4" s="367"/>
-      <c r="X4" s="393" t="s">
+      <c r="V4" s="364"/>
+      <c r="W4" s="365"/>
+      <c r="X4" s="371" t="s">
         <v>72</v>
       </c>
-      <c r="Y4" s="394"/>
-      <c r="Z4" s="393" t="s">
+      <c r="Y4" s="417"/>
+      <c r="Z4" s="371" t="s">
         <v>112</v>
       </c>
-      <c r="AA4" s="395"/>
-      <c r="AB4" s="395"/>
-      <c r="AC4" s="396"/>
-      <c r="AD4" s="362" t="s">
+      <c r="AA4" s="360"/>
+      <c r="AB4" s="360"/>
+      <c r="AC4" s="361"/>
+      <c r="AD4" s="369" t="s">
         <v>79</v>
       </c>
       <c r="AG4" s="236"/>
     </row>
     <row r="5" spans="1:35" ht="78.75">
-      <c r="A5" s="398"/>
-      <c r="B5" s="408"/>
-      <c r="C5" s="404"/>
-      <c r="D5" s="369"/>
-      <c r="E5" s="400"/>
-      <c r="F5" s="369"/>
-      <c r="G5" s="402"/>
-      <c r="H5" s="365"/>
-      <c r="I5" s="365"/>
-      <c r="J5" s="369"/>
-      <c r="K5" s="365"/>
+      <c r="A5" s="409"/>
+      <c r="B5" s="349"/>
+      <c r="C5" s="415"/>
+      <c r="D5" s="370"/>
+      <c r="E5" s="413"/>
+      <c r="F5" s="370"/>
+      <c r="G5" s="411"/>
+      <c r="H5" s="367"/>
+      <c r="I5" s="367"/>
+      <c r="J5" s="370"/>
+      <c r="K5" s="367"/>
       <c r="L5" s="79" t="s">
         <v>52</v>
       </c>
@@ -24616,14 +24632,14 @@
       <c r="AC5" s="250" t="s">
         <v>118</v>
       </c>
-      <c r="AD5" s="363"/>
-      <c r="AG5" s="348" t="s">
+      <c r="AD5" s="416"/>
+      <c r="AG5" s="422" t="s">
         <v>119</v>
       </c>
-      <c r="AH5" s="350" t="s">
+      <c r="AH5" s="424" t="s">
         <v>120</v>
       </c>
-      <c r="AI5" s="352" t="s">
+      <c r="AI5" s="426" t="s">
         <v>121</v>
       </c>
     </row>
@@ -24658,9 +24674,9 @@
       <c r="AB6" s="86"/>
       <c r="AC6" s="86"/>
       <c r="AD6" s="74"/>
-      <c r="AG6" s="349"/>
-      <c r="AH6" s="351"/>
-      <c r="AI6" s="353"/>
+      <c r="AG6" s="423"/>
+      <c r="AH6" s="425"/>
+      <c r="AI6" s="427"/>
     </row>
     <row r="7" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A7" s="33">
@@ -25811,7 +25827,7 @@
         <v>YES</v>
       </c>
     </row>
-    <row r="17" spans="1:35" s="9" customFormat="1" ht="94.5">
+    <row r="17" spans="1:35" s="9" customFormat="1" ht="110.25">
       <c r="A17" s="33">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -27248,7 +27264,7 @@
         <v/>
       </c>
       <c r="AD29" s="92" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="AG29" s="238" t="str">
         <f t="shared" si="8"/>
@@ -27803,14 +27819,14 @@
         <v>197</v>
       </c>
       <c r="D35" s="25" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="E35" s="174">
         <f t="shared" si="2"/>
         <v>46325</v>
       </c>
       <c r="F35" s="31" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="G35" s="21" t="s">
         <v>600</v>
@@ -27861,7 +27877,7 @@
         <v/>
       </c>
       <c r="AD35" s="92" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="AG35" s="238" t="str">
         <f t="shared" si="8"/>
@@ -27903,10 +27919,10 @@
         <v>46302</v>
       </c>
       <c r="F36" s="31" t="s">
+        <v>984</v>
+      </c>
+      <c r="G36" s="21" t="s">
         <v>985</v>
-      </c>
-      <c r="G36" s="21" t="s">
-        <v>986</v>
       </c>
       <c r="H36" s="138" t="s">
         <v>1</v>
@@ -27964,7 +27980,7 @@
         <v/>
       </c>
       <c r="AD36" s="92" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="AG36" s="238" t="str">
         <f t="shared" si="8"/>
@@ -27997,17 +28013,17 @@
       </c>
       <c r="C37" s="164"/>
       <c r="D37" s="25" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E37" s="174">
         <f t="shared" si="2"/>
         <v>46302</v>
       </c>
       <c r="F37" s="31" t="s">
+        <v>987</v>
+      </c>
+      <c r="G37" s="21" t="s">
         <v>988</v>
-      </c>
-      <c r="G37" s="21" t="s">
-        <v>989</v>
       </c>
       <c r="H37" s="138" t="s">
         <v>1</v>
@@ -28059,7 +28075,7 @@
         <v/>
       </c>
       <c r="AD37" s="92" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="AG37" s="238" t="str">
         <f t="shared" si="8"/>
@@ -28094,17 +28110,17 @@
         <v>372</v>
       </c>
       <c r="D38" s="25" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="E38" s="174">
         <f t="shared" si="2"/>
         <v>46304</v>
       </c>
       <c r="F38" s="31" t="s">
+        <v>990</v>
+      </c>
+      <c r="G38" s="21" t="s">
         <v>991</v>
-      </c>
-      <c r="G38" s="21" t="s">
-        <v>992</v>
       </c>
       <c r="H38" s="138" t="s">
         <v>1</v>
@@ -28162,7 +28178,7 @@
         <v/>
       </c>
       <c r="AD38" s="92" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="AG38" s="238" t="str">
         <f t="shared" si="8"/>
@@ -28197,14 +28213,14 @@
         <v>197</v>
       </c>
       <c r="D39" s="25" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="E39" s="174">
         <f t="shared" si="2"/>
         <v>46325</v>
       </c>
       <c r="F39" s="31" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="G39" s="21" t="s">
         <v>588</v>
@@ -28255,7 +28271,7 @@
         <v/>
       </c>
       <c r="AD39" s="92" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="AG39" s="238" t="str">
         <f t="shared" si="8"/>
@@ -28288,17 +28304,17 @@
       </c>
       <c r="C40" s="164"/>
       <c r="D40" s="25" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="E40" s="174">
         <f t="shared" si="2"/>
         <v>46330</v>
       </c>
       <c r="F40" s="31" t="s">
+        <v>1061</v>
+      </c>
+      <c r="G40" s="21" t="s">
         <v>1062</v>
-      </c>
-      <c r="G40" s="21" t="s">
-        <v>1063</v>
       </c>
       <c r="H40" s="138"/>
       <c r="I40" s="164">
@@ -28447,28 +28463,28 @@
       <c r="C44" s="166" t="s">
         <v>20</v>
       </c>
-      <c r="D44" s="405" t="s">
+      <c r="D44" s="376" t="s">
         <v>21</v>
       </c>
-      <c r="E44" s="406"/>
+      <c r="E44" s="377"/>
       <c r="F44" s="46"/>
       <c r="G44" s="46"/>
-      <c r="H44" s="357" t="s">
+      <c r="H44" s="356" t="s">
         <v>14</v>
       </c>
-      <c r="I44" s="358"/>
-      <c r="J44" s="358"/>
-      <c r="K44" s="358"/>
-      <c r="L44" s="358"/>
-      <c r="M44" s="359"/>
-      <c r="N44" s="360" t="s">
+      <c r="I44" s="357"/>
+      <c r="J44" s="357"/>
+      <c r="K44" s="357"/>
+      <c r="L44" s="357"/>
+      <c r="M44" s="358"/>
+      <c r="N44" s="362" t="s">
         <v>7</v>
       </c>
-      <c r="O44" s="361"/>
-      <c r="P44" s="360" t="s">
+      <c r="O44" s="363"/>
+      <c r="P44" s="362" t="s">
         <v>109</v>
       </c>
-      <c r="Q44" s="361"/>
+      <c r="Q44" s="363"/>
       <c r="R44" s="1"/>
       <c r="S44" s="1"/>
       <c r="T44" s="140"/>
@@ -28488,17 +28504,17 @@
       <c r="C45" s="195" t="s">
         <v>109</v>
       </c>
-      <c r="D45" s="391" t="s">
+      <c r="D45" s="420" t="s">
         <v>111</v>
       </c>
-      <c r="E45" s="392"/>
+      <c r="E45" s="421"/>
       <c r="F45" s="46"/>
-      <c r="H45" s="357" t="s">
+      <c r="H45" s="356" t="s">
         <v>18</v>
       </c>
-      <c r="I45" s="358"/>
-      <c r="J45" s="358"/>
-      <c r="K45" s="359"/>
+      <c r="I45" s="357"/>
+      <c r="J45" s="357"/>
+      <c r="K45" s="358"/>
       <c r="L45" s="105">
         <f ca="1">M45/$M$45</f>
         <v>1</v>
@@ -28540,18 +28556,18 @@
       <c r="C46" s="195" t="s">
         <v>36</v>
       </c>
-      <c r="D46" s="370" t="s">
+      <c r="D46" s="418" t="s">
         <v>37</v>
       </c>
-      <c r="E46" s="371"/>
+      <c r="E46" s="419"/>
       <c r="F46" s="69"/>
       <c r="G46" s="6"/>
-      <c r="H46" s="373" t="s">
+      <c r="H46" s="379" t="s">
         <v>66</v>
       </c>
-      <c r="I46" s="374"/>
-      <c r="J46" s="374"/>
-      <c r="K46" s="375"/>
+      <c r="I46" s="380"/>
+      <c r="J46" s="380"/>
+      <c r="K46" s="381"/>
       <c r="L46" s="107">
         <f ca="1">M46/$M$45</f>
         <v>2.7777777777777776E-2</v>
@@ -28592,21 +28608,21 @@
       <c r="AI46" s="11"/>
     </row>
     <row r="47" spans="1:35">
-      <c r="C47" s="385" t="s">
+      <c r="C47" s="394" t="s">
         <v>75</v>
       </c>
-      <c r="D47" s="387" t="s">
+      <c r="D47" s="350" t="s">
         <v>76</v>
       </c>
-      <c r="E47" s="388"/>
+      <c r="E47" s="351"/>
       <c r="F47" s="70"/>
       <c r="G47" s="6"/>
-      <c r="H47" s="376" t="s">
+      <c r="H47" s="382" t="s">
         <v>67</v>
       </c>
-      <c r="I47" s="377"/>
-      <c r="J47" s="377"/>
-      <c r="K47" s="378"/>
+      <c r="I47" s="383"/>
+      <c r="J47" s="383"/>
+      <c r="K47" s="384"/>
       <c r="L47" s="109">
         <f t="shared" ref="L47:L50" ca="1" si="23">M47/$M$45</f>
         <v>0.55555555555555558</v>
@@ -28647,17 +28663,17 @@
       <c r="AI47" s="11"/>
     </row>
     <row r="48" spans="1:35" ht="16.5" thickBot="1">
-      <c r="C48" s="386"/>
-      <c r="D48" s="389"/>
-      <c r="E48" s="390"/>
+      <c r="C48" s="395"/>
+      <c r="D48" s="352"/>
+      <c r="E48" s="353"/>
       <c r="F48" s="71"/>
       <c r="G48" s="6"/>
-      <c r="H48" s="379" t="s">
+      <c r="H48" s="385" t="s">
         <v>68</v>
       </c>
-      <c r="I48" s="380"/>
-      <c r="J48" s="380"/>
-      <c r="K48" s="381"/>
+      <c r="I48" s="386"/>
+      <c r="J48" s="386"/>
+      <c r="K48" s="387"/>
       <c r="L48" s="111">
         <f t="shared" ca="1" si="23"/>
         <v>0.22222222222222221</v>
@@ -28700,12 +28716,12 @@
     <row r="49" spans="3:35">
       <c r="F49" s="72"/>
       <c r="G49" s="6"/>
-      <c r="H49" s="382" t="s">
+      <c r="H49" s="388" t="s">
         <v>70</v>
       </c>
-      <c r="I49" s="383"/>
-      <c r="J49" s="383"/>
-      <c r="K49" s="384"/>
+      <c r="I49" s="389"/>
+      <c r="J49" s="389"/>
+      <c r="K49" s="390"/>
       <c r="L49" s="114">
         <f t="shared" ca="1" si="23"/>
         <v>0.1388888888888889</v>
@@ -28748,17 +28764,17 @@
       <c r="AI49" s="11"/>
     </row>
     <row r="50" spans="3:35" ht="16.5" thickBot="1">
-      <c r="C50" s="372" t="s">
+      <c r="C50" s="378" t="s">
         <v>41</v>
       </c>
-      <c r="D50" s="372"/>
-      <c r="E50" s="372"/>
-      <c r="H50" s="354" t="s">
+      <c r="D50" s="378"/>
+      <c r="E50" s="378"/>
+      <c r="H50" s="391" t="s">
         <v>71</v>
       </c>
-      <c r="I50" s="355"/>
-      <c r="J50" s="355"/>
-      <c r="K50" s="356"/>
+      <c r="I50" s="392"/>
+      <c r="J50" s="392"/>
+      <c r="K50" s="393"/>
       <c r="L50" s="113">
         <f t="shared" ca="1" si="23"/>
         <v>5.5555555555555552E-2</v>
@@ -28803,27 +28819,6 @@
     </sortState>
   </autoFilter>
   <mergeCells count="37">
-    <mergeCell ref="P44:Q44"/>
-    <mergeCell ref="X4:Y4"/>
-    <mergeCell ref="Z4:AC4"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D44:E44"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="D46:E46"/>
-    <mergeCell ref="C50:E50"/>
-    <mergeCell ref="H46:K46"/>
-    <mergeCell ref="H47:K47"/>
-    <mergeCell ref="H44:M44"/>
-    <mergeCell ref="H48:K48"/>
-    <mergeCell ref="H49:K49"/>
-    <mergeCell ref="C47:C48"/>
-    <mergeCell ref="D47:E48"/>
-    <mergeCell ref="D45:E45"/>
     <mergeCell ref="AG5:AG6"/>
     <mergeCell ref="AH5:AH6"/>
     <mergeCell ref="AI5:AI6"/>
@@ -28840,6 +28835,27 @@
     <mergeCell ref="K4:K5"/>
     <mergeCell ref="P4:Q4"/>
     <mergeCell ref="J4:J5"/>
+    <mergeCell ref="D46:E46"/>
+    <mergeCell ref="C50:E50"/>
+    <mergeCell ref="H46:K46"/>
+    <mergeCell ref="H47:K47"/>
+    <mergeCell ref="H44:M44"/>
+    <mergeCell ref="H48:K48"/>
+    <mergeCell ref="H49:K49"/>
+    <mergeCell ref="C47:C48"/>
+    <mergeCell ref="D47:E48"/>
+    <mergeCell ref="D45:E45"/>
+    <mergeCell ref="P44:Q44"/>
+    <mergeCell ref="X4:Y4"/>
+    <mergeCell ref="Z4:AC4"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D44:E44"/>
+    <mergeCell ref="B4:B5"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="A7:AD42 AG7:AI42">
@@ -29124,81 +29140,81 @@
       <c r="Z3" s="159"/>
     </row>
     <row r="4" spans="1:26" s="5" customFormat="1" ht="35.1" customHeight="1" thickBot="1">
-      <c r="A4" s="407" t="s">
+      <c r="A4" s="348" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="407" t="s">
+      <c r="B4" s="348" t="s">
         <v>515</v>
       </c>
-      <c r="C4" s="403" t="s">
+      <c r="C4" s="414" t="s">
         <v>45</v>
       </c>
-      <c r="D4" s="362" t="s">
+      <c r="D4" s="369" t="s">
         <v>46</v>
       </c>
-      <c r="E4" s="428" t="s">
+      <c r="E4" s="437" t="s">
         <v>47</v>
       </c>
-      <c r="F4" s="362" t="s">
+      <c r="F4" s="369" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="430" t="s">
+      <c r="G4" s="439" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="364" t="s">
+      <c r="H4" s="366" t="s">
         <v>48</v>
       </c>
-      <c r="I4" s="432" t="s">
+      <c r="I4" s="441" t="s">
         <v>49</v>
       </c>
-      <c r="J4" s="362" t="s">
+      <c r="J4" s="369" t="s">
         <v>78</v>
       </c>
-      <c r="K4" s="364" t="s">
+      <c r="K4" s="366" t="s">
         <v>80</v>
       </c>
       <c r="L4" s="368" t="s">
         <v>53</v>
       </c>
-      <c r="M4" s="367"/>
+      <c r="M4" s="365"/>
       <c r="N4" s="368" t="s">
         <v>55</v>
       </c>
-      <c r="O4" s="367"/>
+      <c r="O4" s="365"/>
       <c r="P4" s="368" t="s">
         <v>72</v>
       </c>
-      <c r="Q4" s="367"/>
-      <c r="R4" s="366" t="s">
+      <c r="Q4" s="365"/>
+      <c r="R4" s="364" t="s">
         <v>53</v>
       </c>
-      <c r="S4" s="366"/>
-      <c r="T4" s="367"/>
+      <c r="S4" s="364"/>
+      <c r="T4" s="365"/>
       <c r="U4" s="368" t="s">
         <v>55</v>
       </c>
-      <c r="V4" s="366"/>
-      <c r="W4" s="366"/>
-      <c r="X4" s="393" t="s">
+      <c r="V4" s="364"/>
+      <c r="W4" s="364"/>
+      <c r="X4" s="371" t="s">
         <v>72</v>
       </c>
-      <c r="Y4" s="427"/>
-      <c r="Z4" s="367" t="s">
+      <c r="Y4" s="372"/>
+      <c r="Z4" s="365" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="72" customHeight="1">
-      <c r="A5" s="408"/>
-      <c r="B5" s="408"/>
-      <c r="C5" s="404"/>
-      <c r="D5" s="369"/>
-      <c r="E5" s="429"/>
-      <c r="F5" s="369"/>
-      <c r="G5" s="431"/>
-      <c r="H5" s="365"/>
-      <c r="I5" s="433"/>
-      <c r="J5" s="369"/>
-      <c r="K5" s="365"/>
+      <c r="A5" s="349"/>
+      <c r="B5" s="349"/>
+      <c r="C5" s="415"/>
+      <c r="D5" s="370"/>
+      <c r="E5" s="438"/>
+      <c r="F5" s="370"/>
+      <c r="G5" s="440"/>
+      <c r="H5" s="367"/>
+      <c r="I5" s="442"/>
+      <c r="J5" s="370"/>
+      <c r="K5" s="367"/>
       <c r="L5" s="79" t="s">
         <v>52</v>
       </c>
@@ -29241,7 +29257,7 @@
       <c r="Y5" s="260" t="s">
         <v>114</v>
       </c>
-      <c r="Z5" s="363"/>
+      <c r="Z5" s="416"/>
     </row>
     <row r="6" spans="1:26" ht="15" customHeight="1" thickBot="1">
       <c r="A6" s="78"/>
@@ -34234,7 +34250,7 @@
       <c r="X70" s="230"/>
       <c r="Y70" s="19"/>
       <c r="Z70" s="92" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="71" spans="1:26" s="9" customFormat="1" ht="47.25">
@@ -37383,7 +37399,7 @@
       <c r="X113" s="230"/>
       <c r="Y113" s="19"/>
       <c r="Z113" s="92" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="114" spans="1:26" s="9" customFormat="1" ht="63">
@@ -37655,7 +37671,7 @@
       <c r="X117" s="230"/>
       <c r="Y117" s="19"/>
       <c r="Z117" s="92" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="118" spans="1:26" s="9" customFormat="1" ht="94.5">
@@ -37712,7 +37728,7 @@
       <c r="X118" s="230"/>
       <c r="Y118" s="19"/>
       <c r="Z118" s="92" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
     </row>
     <row r="119" spans="1:26" s="9" customFormat="1" ht="63">
@@ -37783,7 +37799,7 @@
       <c r="X119" s="230"/>
       <c r="Y119" s="19"/>
       <c r="Z119" s="92" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="120" spans="1:26" s="9" customFormat="1" ht="110.25">
@@ -37854,7 +37870,7 @@
       <c r="X120" s="230"/>
       <c r="Y120" s="19"/>
       <c r="Z120" s="92" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="121" spans="1:26" s="9" customFormat="1" ht="141.75">
@@ -37920,12 +37936,12 @@
         <v>46274</v>
       </c>
       <c r="W121" s="235" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="X121" s="230"/>
       <c r="Y121" s="19"/>
       <c r="Z121" s="92" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="122" spans="1:26" s="9" customFormat="1" ht="31.5">
@@ -37994,7 +38010,7 @@
       <c r="X122" s="230"/>
       <c r="Y122" s="19"/>
       <c r="Z122" s="92" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="123" spans="1:26" s="9" customFormat="1" ht="47.25">
@@ -38010,17 +38026,17 @@
         <v>131</v>
       </c>
       <c r="D123" s="25" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="E123" s="174">
         <f t="shared" si="23"/>
         <v>46280</v>
       </c>
       <c r="F123" s="31" t="s">
+        <v>971</v>
+      </c>
+      <c r="G123" s="21" t="s">
         <v>972</v>
-      </c>
-      <c r="G123" s="21" t="s">
-        <v>973</v>
       </c>
       <c r="H123" s="138"/>
       <c r="I123" s="164"/>
@@ -38067,17 +38083,17 @@
         <v>131</v>
       </c>
       <c r="D124" s="25" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="E124" s="174">
         <f t="shared" si="23"/>
         <v>46314</v>
       </c>
       <c r="F124" s="31" t="s">
+        <v>971</v>
+      </c>
+      <c r="G124" s="21" t="s">
         <v>972</v>
-      </c>
-      <c r="G124" s="21" t="s">
-        <v>973</v>
       </c>
       <c r="H124" s="138" t="s">
         <v>6</v>
@@ -38122,7 +38138,7 @@
       <c r="X124" s="230"/>
       <c r="Y124" s="19"/>
       <c r="Z124" s="92" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="125" spans="1:26" s="9" customFormat="1" ht="63">
@@ -38138,19 +38154,21 @@
         <v>131</v>
       </c>
       <c r="D125" s="25" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="E125" s="174">
         <f t="shared" si="23"/>
         <v>46316</v>
       </c>
       <c r="F125" s="31" t="s">
+        <v>1009</v>
+      </c>
+      <c r="G125" s="21" t="s">
         <v>1010</v>
       </c>
-      <c r="G125" s="21" t="s">
-        <v>1011</v>
-      </c>
-      <c r="H125" s="138"/>
+      <c r="H125" s="138" t="s">
+        <v>6</v>
+      </c>
       <c r="I125" s="164">
         <f t="shared" ca="1" si="24"/>
         <v>14</v>
@@ -38179,10 +38197,14 @@
       </c>
       <c r="U125" s="29"/>
       <c r="V125" s="211"/>
-      <c r="W125" s="235"/>
+      <c r="W125" s="235" t="s">
+        <v>240</v>
+      </c>
       <c r="X125" s="230"/>
       <c r="Y125" s="19"/>
-      <c r="Z125" s="92"/>
+      <c r="Z125" s="92" t="s">
+        <v>1065</v>
+      </c>
     </row>
     <row r="126" spans="1:26" s="9" customFormat="1" ht="78.75">
       <c r="A126" s="33">
@@ -38197,17 +38219,17 @@
         <v>621</v>
       </c>
       <c r="D126" s="25" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="E126" s="174">
         <f t="shared" si="23"/>
         <v>46323</v>
       </c>
       <c r="F126" s="31" t="s">
+        <v>1052</v>
+      </c>
+      <c r="G126" s="21" t="s">
         <v>1053</v>
-      </c>
-      <c r="G126" s="21" t="s">
-        <v>1054</v>
       </c>
       <c r="H126" s="138"/>
       <c r="I126" s="164">
@@ -38254,17 +38276,17 @@
       </c>
       <c r="C127" s="164"/>
       <c r="D127" s="25" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="E127" s="174">
         <f t="shared" si="23"/>
         <v>46325</v>
       </c>
       <c r="F127" s="31" t="s">
+        <v>1058</v>
+      </c>
+      <c r="G127" s="21" t="s">
         <v>1059</v>
-      </c>
-      <c r="G127" s="21" t="s">
-        <v>1060</v>
       </c>
       <c r="H127" s="138"/>
       <c r="I127" s="164">
@@ -38361,28 +38383,28 @@
       <c r="C131" s="207" t="s">
         <v>38</v>
       </c>
-      <c r="D131" s="441" t="s">
+      <c r="D131" s="428" t="s">
         <v>39</v>
       </c>
-      <c r="E131" s="442"/>
+      <c r="E131" s="429"/>
       <c r="F131" s="46"/>
       <c r="G131" s="68"/>
-      <c r="H131" s="357" t="s">
+      <c r="H131" s="356" t="s">
         <v>14</v>
       </c>
-      <c r="I131" s="358"/>
-      <c r="J131" s="358"/>
-      <c r="K131" s="358"/>
-      <c r="L131" s="358"/>
-      <c r="M131" s="359"/>
-      <c r="N131" s="360" t="s">
+      <c r="I131" s="357"/>
+      <c r="J131" s="357"/>
+      <c r="K131" s="357"/>
+      <c r="L131" s="357"/>
+      <c r="M131" s="358"/>
+      <c r="N131" s="362" t="s">
         <v>7</v>
       </c>
-      <c r="O131" s="361"/>
-      <c r="P131" s="360" t="s">
+      <c r="O131" s="363"/>
+      <c r="P131" s="362" t="s">
         <v>110</v>
       </c>
-      <c r="Q131" s="361"/>
+      <c r="Q131" s="363"/>
       <c r="R131" s="1"/>
       <c r="S131" s="1"/>
       <c r="T131" s="140"/>
@@ -38395,16 +38417,16 @@
       <c r="C132" s="208" t="s">
         <v>74</v>
       </c>
-      <c r="D132" s="439" t="s">
+      <c r="D132" s="435" t="s">
         <v>77</v>
       </c>
-      <c r="E132" s="440"/>
+      <c r="E132" s="436"/>
       <c r="F132" s="46"/>
       <c r="G132" s="46"/>
-      <c r="H132" s="434" t="s">
+      <c r="H132" s="430" t="s">
         <v>17</v>
       </c>
-      <c r="I132" s="435"/>
+      <c r="I132" s="431"/>
       <c r="J132" s="130"/>
       <c r="K132" s="210"/>
       <c r="L132" s="117">
@@ -38413,7 +38435,7 @@
       </c>
       <c r="M132" s="104">
         <f ca="1">SUM($M$133:$M$135)</f>
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="N132" s="118" t="s">
         <v>15</v>
@@ -38438,32 +38460,32 @@
       <c r="Y132" s="11"/>
     </row>
     <row r="133" spans="1:26">
-      <c r="C133" s="385" t="s">
+      <c r="C133" s="394" t="s">
         <v>6</v>
       </c>
-      <c r="D133" s="439" t="s">
+      <c r="D133" s="435" t="s">
         <v>40</v>
       </c>
-      <c r="E133" s="440"/>
+      <c r="E133" s="436"/>
       <c r="F133" s="69"/>
       <c r="G133" s="6"/>
-      <c r="H133" s="436" t="s">
+      <c r="H133" s="432" t="s">
         <v>69</v>
       </c>
-      <c r="I133" s="437"/>
-      <c r="J133" s="437"/>
-      <c r="K133" s="438"/>
+      <c r="I133" s="433"/>
+      <c r="J133" s="433"/>
+      <c r="K133" s="434"/>
       <c r="L133" s="122">
         <f t="shared" ref="L133:L135" ca="1" si="59">M133/$M$132</f>
-        <v>0.82399999999999995</v>
+        <v>0.82539682539682535</v>
       </c>
       <c r="M133" s="123">
         <f>COUNTIF($H$7:$H$129,"RFCS")</f>
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N133" s="121">
         <f ca="1">COUNTIFS($I$7:$I$129,"&lt;=21",$H$7:$H$129,"RFCS")</f>
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="O133" s="120">
         <f ca="1">COUNTIFS($I$7:$I$129,"&gt;21",$H$7:$H$129,"RFCS")</f>
@@ -38486,20 +38508,20 @@
       <c r="Y133" s="11"/>
     </row>
     <row r="134" spans="1:26">
-      <c r="C134" s="385"/>
-      <c r="D134" s="439"/>
-      <c r="E134" s="440"/>
+      <c r="C134" s="394"/>
+      <c r="D134" s="435"/>
+      <c r="E134" s="436"/>
       <c r="F134" s="72"/>
       <c r="G134" s="6"/>
-      <c r="H134" s="382" t="s">
+      <c r="H134" s="388" t="s">
         <v>70</v>
       </c>
-      <c r="I134" s="383"/>
-      <c r="J134" s="383"/>
-      <c r="K134" s="384"/>
+      <c r="I134" s="389"/>
+      <c r="J134" s="389"/>
+      <c r="K134" s="390"/>
       <c r="L134" s="124">
         <f t="shared" ca="1" si="59"/>
-        <v>6.4000000000000001E-2</v>
+        <v>6.3492063492063489E-2</v>
       </c>
       <c r="M134" s="125">
         <f ca="1">SUM(N134:O134)</f>
@@ -38532,22 +38554,22 @@
       <c r="Y134" s="11"/>
     </row>
     <row r="135" spans="1:26" ht="16.5" thickBot="1">
-      <c r="C135" s="385" t="s">
+      <c r="C135" s="394" t="s">
         <v>75</v>
       </c>
-      <c r="D135" s="387" t="s">
+      <c r="D135" s="350" t="s">
         <v>76</v>
       </c>
-      <c r="E135" s="388"/>
-      <c r="H135" s="354" t="s">
+      <c r="E135" s="351"/>
+      <c r="H135" s="391" t="s">
         <v>71</v>
       </c>
-      <c r="I135" s="355"/>
-      <c r="J135" s="355"/>
-      <c r="K135" s="356"/>
+      <c r="I135" s="392"/>
+      <c r="J135" s="392"/>
+      <c r="K135" s="393"/>
       <c r="L135" s="126">
         <f t="shared" ca="1" si="59"/>
-        <v>0.112</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="M135" s="116">
         <f>COUNTIFS($K$7:$K$129,"X")</f>
@@ -38559,16 +38581,16 @@
       <c r="Q135" s="224"/>
     </row>
     <row r="136" spans="1:26" ht="16.5" thickBot="1">
-      <c r="C136" s="386"/>
-      <c r="D136" s="389"/>
-      <c r="E136" s="390"/>
+      <c r="C136" s="395"/>
+      <c r="D136" s="352"/>
+      <c r="E136" s="353"/>
     </row>
     <row r="138" spans="1:26">
-      <c r="C138" s="372" t="s">
+      <c r="C138" s="378" t="s">
         <v>41</v>
       </c>
-      <c r="D138" s="372"/>
-      <c r="E138" s="372"/>
+      <c r="D138" s="378"/>
+      <c r="E138" s="378"/>
     </row>
     <row r="139" spans="1:26">
       <c r="C139" s="169" t="s">
@@ -38601,22 +38623,6 @@
     </sortState>
   </autoFilter>
   <mergeCells count="32">
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="P131:Q131"/>
-    <mergeCell ref="J4:J5"/>
-    <mergeCell ref="D131:E131"/>
-    <mergeCell ref="H131:M131"/>
-    <mergeCell ref="N131:O131"/>
-    <mergeCell ref="H132:I132"/>
-    <mergeCell ref="C138:E138"/>
-    <mergeCell ref="H133:K133"/>
-    <mergeCell ref="H134:K134"/>
-    <mergeCell ref="H135:K135"/>
-    <mergeCell ref="D132:E132"/>
-    <mergeCell ref="C133:C134"/>
-    <mergeCell ref="D133:E134"/>
-    <mergeCell ref="C135:C136"/>
-    <mergeCell ref="D135:E136"/>
     <mergeCell ref="Z4:Z5"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="D4:D5"/>
@@ -38633,6 +38639,22 @@
     <mergeCell ref="K4:K5"/>
     <mergeCell ref="P4:Q4"/>
     <mergeCell ref="X4:Y4"/>
+    <mergeCell ref="H132:I132"/>
+    <mergeCell ref="C138:E138"/>
+    <mergeCell ref="H133:K133"/>
+    <mergeCell ref="H134:K134"/>
+    <mergeCell ref="H135:K135"/>
+    <mergeCell ref="D132:E132"/>
+    <mergeCell ref="C133:C134"/>
+    <mergeCell ref="D133:E134"/>
+    <mergeCell ref="C135:C136"/>
+    <mergeCell ref="D135:E136"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="P131:Q131"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="D131:E131"/>
+    <mergeCell ref="H131:M131"/>
+    <mergeCell ref="N131:O131"/>
   </mergeCells>
   <phoneticPr fontId="71"/>
   <conditionalFormatting sqref="A7:Z129">
@@ -39215,19 +39237,19 @@
       <c r="S3" s="281"/>
     </row>
     <row r="4" spans="1:25" ht="36" customHeight="1" thickBot="1">
-      <c r="A4" s="397" t="s">
+      <c r="A4" s="408" t="s">
         <v>123</v>
       </c>
-      <c r="B4" s="364" t="s">
+      <c r="B4" s="366" t="s">
         <v>45</v>
       </c>
-      <c r="C4" s="364" t="s">
+      <c r="C4" s="366" t="s">
         <v>95</v>
       </c>
-      <c r="D4" s="364" t="s">
+      <c r="D4" s="366" t="s">
         <v>46</v>
       </c>
-      <c r="E4" s="362" t="s">
+      <c r="E4" s="369" t="s">
         <v>4</v>
       </c>
       <c r="F4" s="449" t="s">
@@ -39256,12 +39278,12 @@
       <c r="S4" s="448"/>
     </row>
     <row r="5" spans="1:25" ht="78.75">
-      <c r="A5" s="398"/>
-      <c r="B5" s="365"/>
-      <c r="C5" s="365"/>
-      <c r="D5" s="365"/>
-      <c r="E5" s="369"/>
-      <c r="F5" s="402"/>
+      <c r="A5" s="409"/>
+      <c r="B5" s="367"/>
+      <c r="C5" s="367"/>
+      <c r="D5" s="367"/>
+      <c r="E5" s="370"/>
+      <c r="F5" s="411"/>
       <c r="G5" s="283" t="s">
         <v>56</v>
       </c>
@@ -40594,16 +40616,16 @@
       <c r="R3" s="281"/>
     </row>
     <row r="4" spans="1:18" ht="16.5" thickBot="1">
-      <c r="A4" s="397" t="s">
+      <c r="A4" s="408" t="s">
         <v>123</v>
       </c>
-      <c r="B4" s="364" t="s">
+      <c r="B4" s="366" t="s">
         <v>45</v>
       </c>
-      <c r="C4" s="364" t="s">
+      <c r="C4" s="366" t="s">
         <v>46</v>
       </c>
-      <c r="D4" s="366" t="s">
+      <c r="D4" s="364" t="s">
         <v>4</v>
       </c>
       <c r="E4" s="449" t="s">
@@ -40632,11 +40654,11 @@
       <c r="R4" s="448"/>
     </row>
     <row r="5" spans="1:18" ht="78.75">
-      <c r="A5" s="398"/>
-      <c r="B5" s="365"/>
-      <c r="C5" s="365"/>
-      <c r="D5" s="431"/>
-      <c r="E5" s="369"/>
+      <c r="A5" s="409"/>
+      <c r="B5" s="367"/>
+      <c r="C5" s="367"/>
+      <c r="D5" s="440"/>
+      <c r="E5" s="370"/>
       <c r="F5" s="283" t="s">
         <v>56</v>
       </c>

--- a/ICT-RFA-RFI-lists-New.xlsx
+++ b/ICT-RFA-RFI-lists-New.xlsx
@@ -9,9 +9,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project Airport\LTIA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFF966B9-3B1C-40EB-9BCA-4855061DB119}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6757417F-F15B-4A0C-8DF6-754F72477F39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="506" xr2:uid="{CCA8147E-0981-4321-B87F-440A52C0DA59}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="506" activeTab="2" xr2:uid="{CCA8147E-0981-4321-B87F-440A52C0DA59}"/>
   </bookViews>
   <sheets>
     <sheet name="RFA" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="4">'Need ReSub (RFA-SDS)'!$A$1:$R$62</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">RFA!$A$1:$AE$137,RFA!$I$139:$R$145,RFA!$C$139:$F$149,RFA!$C$151:$F$154,RFA!$C$156:$F$167</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'RFA-SDS'!$A$1:$AD$42,'RFA-SDS'!$H$44:$Q$50,'RFA-SDS'!$C$44:$E$48,'RFA-SDS'!$C$50:$E$53</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">RFI!$A$1:$Z$129,RFI!$H$131:$Q$135,RFI!$C$131:$E$136,RFI!$C$138:$E$141</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">RFI!$A$1:$Z$130,RFI!$H$132:$Q$136,RFI!$C$132:$E$137,RFI!$C$139:$E$142</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">RFA!$4:$5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'RFA-SDS'!$4:$5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">RFI!$4:$5</definedName>
@@ -78,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3436" uniqueCount="1068">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3441" uniqueCount="1071">
   <si>
     <t>TT</t>
   </si>
@@ -5050,6 +5050,15 @@
   </si>
   <si>
     <t>LTIA-5.11-LTICT- 71110 -RFA-OTH-0012</t>
+  </si>
+  <si>
+    <t>LTIA-5.11-LTICT-72190-RFI-0039</t>
+  </si>
+  <si>
+    <t>Recommendations regarding the replacement of the converter model in the Smart Parking system</t>
+  </si>
+  <si>
+    <t>Kiến nghị thay đổi mã hiệu media converter cho hệ thống Smart Parking</t>
   </si>
 </sst>
 </file>
@@ -7487,6 +7496,180 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="51" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="52" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="55" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="55" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -7504,21 +7687,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="51" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="52" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -7528,248 +7696,89 @@
     <xf numFmtId="1" fontId="2" fillId="0" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="55" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="55" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="45" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="53" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="47" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="45" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -8432,92 +8441,92 @@
       <c r="AE3" s="159"/>
     </row>
     <row r="4" spans="1:35" s="5" customFormat="1" ht="36" customHeight="1" thickBot="1">
-      <c r="A4" s="408" t="s">
+      <c r="A4" s="350" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="348" t="s">
+      <c r="B4" s="406" t="s">
         <v>515</v>
       </c>
-      <c r="C4" s="414" t="s">
+      <c r="C4" s="359" t="s">
         <v>45</v>
       </c>
-      <c r="D4" s="366" t="s">
+      <c r="D4" s="352" t="s">
         <v>95</v>
       </c>
-      <c r="E4" s="369" t="s">
+      <c r="E4" s="348" t="s">
         <v>46</v>
       </c>
-      <c r="F4" s="412" t="s">
+      <c r="F4" s="357" t="s">
         <v>47</v>
       </c>
-      <c r="G4" s="369" t="s">
+      <c r="G4" s="348" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="410" t="s">
+      <c r="H4" s="355" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="366" t="s">
+      <c r="I4" s="352" t="s">
         <v>48</v>
       </c>
-      <c r="J4" s="366" t="s">
+      <c r="J4" s="352" t="s">
         <v>49</v>
       </c>
-      <c r="K4" s="369" t="s">
+      <c r="K4" s="348" t="s">
         <v>78</v>
       </c>
-      <c r="L4" s="366" t="s">
+      <c r="L4" s="352" t="s">
         <v>80</v>
       </c>
-      <c r="M4" s="364" t="s">
+      <c r="M4" s="363" t="s">
         <v>53</v>
       </c>
-      <c r="N4" s="365"/>
-      <c r="O4" s="364" t="s">
+      <c r="N4" s="364"/>
+      <c r="O4" s="363" t="s">
         <v>55</v>
       </c>
-      <c r="P4" s="365"/>
-      <c r="Q4" s="368" t="s">
+      <c r="P4" s="364"/>
+      <c r="Q4" s="362" t="s">
         <v>72</v>
       </c>
-      <c r="R4" s="365"/>
-      <c r="S4" s="364" t="s">
+      <c r="R4" s="364"/>
+      <c r="S4" s="363" t="s">
         <v>53</v>
       </c>
-      <c r="T4" s="364"/>
-      <c r="U4" s="365"/>
-      <c r="V4" s="368" t="s">
+      <c r="T4" s="363"/>
+      <c r="U4" s="364"/>
+      <c r="V4" s="362" t="s">
         <v>55</v>
       </c>
-      <c r="W4" s="364"/>
-      <c r="X4" s="365"/>
-      <c r="Y4" s="371" t="s">
+      <c r="W4" s="363"/>
+      <c r="X4" s="364"/>
+      <c r="Y4" s="415" t="s">
         <v>72</v>
       </c>
-      <c r="Z4" s="372"/>
-      <c r="AA4" s="359" t="s">
+      <c r="Z4" s="416"/>
+      <c r="AA4" s="412" t="s">
         <v>112</v>
       </c>
-      <c r="AB4" s="360"/>
-      <c r="AC4" s="360"/>
-      <c r="AD4" s="361"/>
-      <c r="AE4" s="369" t="s">
+      <c r="AB4" s="413"/>
+      <c r="AC4" s="413"/>
+      <c r="AD4" s="414"/>
+      <c r="AE4" s="348" t="s">
         <v>79</v>
       </c>
       <c r="AG4" s="236"/>
     </row>
     <row r="5" spans="1:35" ht="78.75">
-      <c r="A5" s="409"/>
-      <c r="B5" s="349"/>
-      <c r="C5" s="415"/>
-      <c r="D5" s="367"/>
-      <c r="E5" s="370"/>
-      <c r="F5" s="413"/>
-      <c r="G5" s="370"/>
-      <c r="H5" s="411"/>
-      <c r="I5" s="367"/>
-      <c r="J5" s="367"/>
-      <c r="K5" s="370"/>
-      <c r="L5" s="367"/>
+      <c r="A5" s="351"/>
+      <c r="B5" s="407"/>
+      <c r="C5" s="360"/>
+      <c r="D5" s="353"/>
+      <c r="E5" s="354"/>
+      <c r="F5" s="358"/>
+      <c r="G5" s="354"/>
+      <c r="H5" s="356"/>
+      <c r="I5" s="353"/>
+      <c r="J5" s="353"/>
+      <c r="K5" s="354"/>
+      <c r="L5" s="353"/>
       <c r="M5" s="79" t="s">
         <v>52</v>
       </c>
@@ -8572,14 +8581,14 @@
       <c r="AD5" s="336" t="s">
         <v>118</v>
       </c>
-      <c r="AE5" s="416"/>
-      <c r="AG5" s="369" t="s">
+      <c r="AE5" s="361"/>
+      <c r="AG5" s="348" t="s">
         <v>119</v>
       </c>
-      <c r="AH5" s="369" t="s">
+      <c r="AH5" s="348" t="s">
         <v>120</v>
       </c>
-      <c r="AI5" s="369" t="s">
+      <c r="AI5" s="348" t="s">
         <v>121</v>
       </c>
     </row>
@@ -8615,9 +8624,9 @@
       <c r="AC6" s="86"/>
       <c r="AD6" s="86"/>
       <c r="AE6" s="74"/>
-      <c r="AG6" s="407"/>
-      <c r="AH6" s="407"/>
-      <c r="AI6" s="407"/>
+      <c r="AG6" s="349"/>
+      <c r="AH6" s="349"/>
+      <c r="AI6" s="349"/>
     </row>
     <row r="7" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A7" s="33">
@@ -22934,29 +22943,29 @@
       <c r="C139" s="166" t="s">
         <v>20</v>
       </c>
-      <c r="D139" s="376" t="s">
+      <c r="D139" s="379" t="s">
         <v>21</v>
       </c>
-      <c r="E139" s="376"/>
-      <c r="F139" s="377"/>
+      <c r="E139" s="379"/>
+      <c r="F139" s="380"/>
       <c r="G139" s="46"/>
       <c r="H139" s="68"/>
-      <c r="I139" s="356" t="s">
+      <c r="I139" s="384" t="s">
         <v>14</v>
       </c>
-      <c r="J139" s="357"/>
-      <c r="K139" s="357"/>
-      <c r="L139" s="357"/>
-      <c r="M139" s="357"/>
-      <c r="N139" s="358"/>
-      <c r="O139" s="362" t="s">
+      <c r="J139" s="385"/>
+      <c r="K139" s="385"/>
+      <c r="L139" s="385"/>
+      <c r="M139" s="385"/>
+      <c r="N139" s="386"/>
+      <c r="O139" s="382" t="s">
         <v>7</v>
       </c>
-      <c r="P139" s="363"/>
-      <c r="Q139" s="362" t="s">
+      <c r="P139" s="383"/>
+      <c r="Q139" s="382" t="s">
         <v>109</v>
       </c>
-      <c r="R139" s="363"/>
+      <c r="R139" s="383"/>
       <c r="S139" s="1"/>
       <c r="T139" s="1"/>
       <c r="U139" s="140"/>
@@ -22978,19 +22987,19 @@
       <c r="C140" s="167" t="s">
         <v>109</v>
       </c>
-      <c r="D140" s="354" t="s">
+      <c r="D140" s="404" t="s">
         <v>111</v>
       </c>
-      <c r="E140" s="354"/>
-      <c r="F140" s="355"/>
+      <c r="E140" s="404"/>
+      <c r="F140" s="405"/>
       <c r="G140" s="46"/>
       <c r="H140" s="46"/>
-      <c r="I140" s="356" t="s">
+      <c r="I140" s="384" t="s">
         <v>19</v>
       </c>
-      <c r="J140" s="357"/>
-      <c r="K140" s="357"/>
-      <c r="L140" s="358"/>
+      <c r="J140" s="385"/>
+      <c r="K140" s="385"/>
+      <c r="L140" s="386"/>
       <c r="M140" s="105">
         <f t="shared" ref="M140:M145" ca="1" si="84">N140/$N$140</f>
         <v>1</v>
@@ -23034,19 +23043,19 @@
       <c r="C141" s="167" t="s">
         <v>22</v>
       </c>
-      <c r="D141" s="354" t="s">
+      <c r="D141" s="404" t="s">
         <v>23</v>
       </c>
-      <c r="E141" s="354"/>
-      <c r="F141" s="355"/>
+      <c r="E141" s="404"/>
+      <c r="F141" s="405"/>
       <c r="G141" s="70"/>
       <c r="H141" s="6"/>
-      <c r="I141" s="379" t="s">
+      <c r="I141" s="387" t="s">
         <v>66</v>
       </c>
-      <c r="J141" s="380"/>
-      <c r="K141" s="380"/>
-      <c r="L141" s="381"/>
+      <c r="J141" s="388"/>
+      <c r="K141" s="388"/>
+      <c r="L141" s="389"/>
       <c r="M141" s="107">
         <f t="shared" ca="1" si="84"/>
         <v>0.51111111111111107</v>
@@ -23092,18 +23101,18 @@
       <c r="C142" s="167" t="s">
         <v>24</v>
       </c>
-      <c r="D142" s="354" t="s">
+      <c r="D142" s="404" t="s">
         <v>25</v>
       </c>
-      <c r="E142" s="354"/>
-      <c r="F142" s="355"/>
+      <c r="E142" s="404"/>
+      <c r="F142" s="405"/>
       <c r="H142" s="6"/>
-      <c r="I142" s="382" t="s">
+      <c r="I142" s="390" t="s">
         <v>67</v>
       </c>
-      <c r="J142" s="383"/>
-      <c r="K142" s="383"/>
-      <c r="L142" s="384"/>
+      <c r="J142" s="391"/>
+      <c r="K142" s="391"/>
+      <c r="L142" s="392"/>
       <c r="M142" s="109">
         <f t="shared" ca="1" si="84"/>
         <v>0.1037037037037037</v>
@@ -23149,19 +23158,19 @@
       <c r="C143" s="167" t="s">
         <v>26</v>
       </c>
-      <c r="D143" s="354" t="s">
+      <c r="D143" s="404" t="s">
         <v>27</v>
       </c>
-      <c r="E143" s="354"/>
-      <c r="F143" s="355"/>
+      <c r="E143" s="404"/>
+      <c r="F143" s="405"/>
       <c r="G143" s="71"/>
       <c r="H143" s="6"/>
-      <c r="I143" s="385" t="s">
+      <c r="I143" s="393" t="s">
         <v>68</v>
       </c>
-      <c r="J143" s="386"/>
-      <c r="K143" s="386"/>
-      <c r="L143" s="387"/>
+      <c r="J143" s="394"/>
+      <c r="K143" s="394"/>
+      <c r="L143" s="395"/>
       <c r="M143" s="111">
         <f t="shared" ca="1" si="84"/>
         <v>0.2</v>
@@ -23207,18 +23216,18 @@
       <c r="C144" s="168" t="s">
         <v>28</v>
       </c>
-      <c r="D144" s="354" t="s">
+      <c r="D144" s="404" t="s">
         <v>29</v>
       </c>
-      <c r="E144" s="354"/>
-      <c r="F144" s="355"/>
+      <c r="E144" s="404"/>
+      <c r="F144" s="405"/>
       <c r="G144" s="72"/>
-      <c r="I144" s="388" t="s">
+      <c r="I144" s="396" t="s">
         <v>70</v>
       </c>
-      <c r="J144" s="389"/>
-      <c r="K144" s="389"/>
-      <c r="L144" s="390"/>
+      <c r="J144" s="397"/>
+      <c r="K144" s="397"/>
+      <c r="L144" s="398"/>
       <c r="M144" s="114">
         <f t="shared" ca="1" si="84"/>
         <v>7.407407407407407E-2</v>
@@ -23266,18 +23275,18 @@
       <c r="C145" s="168" t="s">
         <v>30</v>
       </c>
-      <c r="D145" s="354" t="s">
+      <c r="D145" s="404" t="s">
         <v>31</v>
       </c>
-      <c r="E145" s="354"/>
-      <c r="F145" s="355"/>
+      <c r="E145" s="404"/>
+      <c r="F145" s="405"/>
       <c r="H145" s="6"/>
-      <c r="I145" s="391" t="s">
+      <c r="I145" s="399" t="s">
         <v>71</v>
       </c>
-      <c r="J145" s="392"/>
-      <c r="K145" s="392"/>
-      <c r="L145" s="393"/>
+      <c r="J145" s="400"/>
+      <c r="K145" s="400"/>
+      <c r="L145" s="401"/>
       <c r="M145" s="113">
         <f t="shared" ca="1" si="84"/>
         <v>0.1111111111111111</v>
@@ -23297,11 +23306,11 @@
       <c r="C146" s="168" t="s">
         <v>32</v>
       </c>
-      <c r="D146" s="354" t="s">
+      <c r="D146" s="404" t="s">
         <v>33</v>
       </c>
-      <c r="E146" s="354"/>
-      <c r="F146" s="355"/>
+      <c r="E146" s="404"/>
+      <c r="F146" s="405"/>
       <c r="H146" s="1" t="s">
         <v>11</v>
       </c>
@@ -23310,11 +23319,11 @@
       <c r="C147" s="167" t="s">
         <v>34</v>
       </c>
-      <c r="D147" s="354" t="s">
+      <c r="D147" s="404" t="s">
         <v>35</v>
       </c>
-      <c r="E147" s="354"/>
-      <c r="F147" s="355"/>
+      <c r="E147" s="404"/>
+      <c r="F147" s="405"/>
       <c r="H147" s="13"/>
       <c r="I147" s="141"/>
       <c r="J147" s="141"/>
@@ -23342,14 +23351,14 @@
       <c r="AI147" s="1"/>
     </row>
     <row r="148" spans="1:35">
-      <c r="C148" s="394" t="s">
+      <c r="C148" s="402" t="s">
         <v>75</v>
       </c>
-      <c r="D148" s="350" t="s">
+      <c r="D148" s="408" t="s">
         <v>76</v>
       </c>
-      <c r="E148" s="350"/>
-      <c r="F148" s="351"/>
+      <c r="E148" s="408"/>
+      <c r="F148" s="409"/>
       <c r="H148" s="13"/>
       <c r="J148" s="141"/>
       <c r="K148" s="13"/>
@@ -23376,10 +23385,10 @@
       <c r="AI148" s="1"/>
     </row>
     <row r="149" spans="1:35" ht="16.5" thickBot="1">
-      <c r="C149" s="395"/>
-      <c r="D149" s="352"/>
-      <c r="E149" s="352"/>
-      <c r="F149" s="353"/>
+      <c r="C149" s="403"/>
+      <c r="D149" s="410"/>
+      <c r="E149" s="410"/>
+      <c r="F149" s="411"/>
       <c r="H149" s="13"/>
       <c r="I149" s="141"/>
       <c r="J149" s="141"/>
@@ -23434,12 +23443,12 @@
       <c r="AI150" s="1"/>
     </row>
     <row r="151" spans="1:35">
-      <c r="C151" s="378" t="s">
+      <c r="C151" s="381" t="s">
         <v>41</v>
       </c>
-      <c r="D151" s="378"/>
-      <c r="E151" s="378"/>
-      <c r="F151" s="378"/>
+      <c r="D151" s="381"/>
+      <c r="E151" s="381"/>
+      <c r="F151" s="381"/>
       <c r="H151" s="13"/>
       <c r="I151" s="141"/>
       <c r="J151" s="141"/>
@@ -23470,11 +23479,11 @@
       <c r="C152" s="169" t="s">
         <v>8</v>
       </c>
-      <c r="D152" s="396" t="s">
+      <c r="D152" s="367" t="s">
         <v>91</v>
       </c>
-      <c r="E152" s="396"/>
-      <c r="F152" s="396"/>
+      <c r="E152" s="367"/>
+      <c r="F152" s="367"/>
       <c r="H152" s="13"/>
       <c r="I152" s="141"/>
       <c r="J152" s="141"/>
@@ -23505,11 +23514,11 @@
       <c r="C153" s="169" t="s">
         <v>8</v>
       </c>
-      <c r="D153" s="396" t="s">
+      <c r="D153" s="367" t="s">
         <v>92</v>
       </c>
-      <c r="E153" s="396"/>
-      <c r="F153" s="396"/>
+      <c r="E153" s="367"/>
+      <c r="F153" s="367"/>
       <c r="H153" s="13"/>
       <c r="I153" s="141"/>
       <c r="J153" s="141"/>
@@ -23540,11 +23549,11 @@
       <c r="C154" s="169" t="s">
         <v>8</v>
       </c>
-      <c r="D154" s="396" t="s">
+      <c r="D154" s="367" t="s">
         <v>93</v>
       </c>
-      <c r="E154" s="396"/>
-      <c r="F154" s="396"/>
+      <c r="E154" s="367"/>
+      <c r="F154" s="367"/>
       <c r="H154" s="13"/>
       <c r="I154" s="141"/>
       <c r="J154" s="141"/>
@@ -23599,12 +23608,12 @@
       <c r="AI155" s="1"/>
     </row>
     <row r="156" spans="1:35" ht="16.5" thickBot="1">
-      <c r="C156" s="402" t="s">
+      <c r="C156" s="371" t="s">
         <v>96</v>
       </c>
-      <c r="D156" s="403"/>
-      <c r="E156" s="403"/>
-      <c r="F156" s="404"/>
+      <c r="D156" s="372"/>
+      <c r="E156" s="372"/>
+      <c r="F156" s="373"/>
       <c r="H156" s="13"/>
       <c r="I156" s="141"/>
       <c r="J156" s="141"/>
@@ -23635,11 +23644,11 @@
       <c r="C157" s="212" t="s">
         <v>81</v>
       </c>
-      <c r="D157" s="405" t="s">
+      <c r="D157" s="374" t="s">
         <v>97</v>
       </c>
-      <c r="E157" s="405"/>
-      <c r="F157" s="406"/>
+      <c r="E157" s="374"/>
+      <c r="F157" s="375"/>
       <c r="H157" s="13"/>
       <c r="I157" s="141"/>
       <c r="J157" s="141"/>
@@ -23670,101 +23679,101 @@
       <c r="C158" s="213" t="s">
         <v>82</v>
       </c>
-      <c r="D158" s="397" t="s">
+      <c r="D158" s="365" t="s">
         <v>98</v>
       </c>
-      <c r="E158" s="397"/>
-      <c r="F158" s="398"/>
+      <c r="E158" s="365"/>
+      <c r="F158" s="366"/>
     </row>
     <row r="159" spans="1:35">
       <c r="C159" s="213" t="s">
         <v>83</v>
       </c>
-      <c r="D159" s="397" t="s">
+      <c r="D159" s="365" t="s">
         <v>99</v>
       </c>
-      <c r="E159" s="397"/>
-      <c r="F159" s="398"/>
+      <c r="E159" s="365"/>
+      <c r="F159" s="366"/>
     </row>
     <row r="160" spans="1:35">
       <c r="C160" s="214" t="s">
         <v>84</v>
       </c>
-      <c r="D160" s="397" t="s">
+      <c r="D160" s="365" t="s">
         <v>100</v>
       </c>
-      <c r="E160" s="397"/>
-      <c r="F160" s="398"/>
+      <c r="E160" s="365"/>
+      <c r="F160" s="366"/>
     </row>
     <row r="161" spans="3:6">
       <c r="C161" s="214" t="s">
         <v>85</v>
       </c>
-      <c r="D161" s="397" t="s">
+      <c r="D161" s="365" t="s">
         <v>101</v>
       </c>
-      <c r="E161" s="397"/>
-      <c r="F161" s="398"/>
+      <c r="E161" s="365"/>
+      <c r="F161" s="366"/>
     </row>
     <row r="162" spans="3:6" ht="18.75">
       <c r="C162" s="214" t="s">
         <v>86</v>
       </c>
-      <c r="D162" s="397" t="s">
+      <c r="D162" s="365" t="s">
         <v>102</v>
       </c>
-      <c r="E162" s="397"/>
-      <c r="F162" s="398"/>
+      <c r="E162" s="365"/>
+      <c r="F162" s="366"/>
     </row>
     <row r="163" spans="3:6" ht="18.75">
       <c r="C163" s="213" t="s">
         <v>87</v>
       </c>
-      <c r="D163" s="397" t="s">
+      <c r="D163" s="365" t="s">
         <v>103</v>
       </c>
-      <c r="E163" s="397"/>
-      <c r="F163" s="398"/>
+      <c r="E163" s="365"/>
+      <c r="F163" s="366"/>
     </row>
     <row r="164" spans="3:6">
       <c r="C164" s="215" t="s">
         <v>88</v>
       </c>
-      <c r="D164" s="399" t="s">
+      <c r="D164" s="368" t="s">
         <v>104</v>
       </c>
-      <c r="E164" s="400"/>
-      <c r="F164" s="401"/>
+      <c r="E164" s="369"/>
+      <c r="F164" s="370"/>
     </row>
     <row r="165" spans="3:6" ht="18.75">
       <c r="C165" s="215" t="s">
         <v>89</v>
       </c>
-      <c r="D165" s="397" t="s">
+      <c r="D165" s="365" t="s">
         <v>105</v>
       </c>
-      <c r="E165" s="397"/>
-      <c r="F165" s="398"/>
+      <c r="E165" s="365"/>
+      <c r="F165" s="366"/>
     </row>
     <row r="166" spans="3:6">
       <c r="C166" s="213" t="s">
         <v>90</v>
       </c>
-      <c r="D166" s="397" t="s">
+      <c r="D166" s="365" t="s">
         <v>106</v>
       </c>
-      <c r="E166" s="397"/>
-      <c r="F166" s="398"/>
+      <c r="E166" s="365"/>
+      <c r="F166" s="366"/>
     </row>
     <row r="167" spans="3:6" ht="16.5" thickBot="1">
       <c r="C167" s="216" t="s">
         <v>94</v>
       </c>
-      <c r="D167" s="373" t="s">
+      <c r="D167" s="376" t="s">
         <v>107</v>
       </c>
-      <c r="E167" s="374"/>
-      <c r="F167" s="375"/>
+      <c r="E167" s="377"/>
+      <c r="F167" s="378"/>
     </row>
   </sheetData>
   <autoFilter ref="A6:AE137" xr:uid="{C724CDAB-378C-47DB-9F45-08EE3BFB6E8B}">
@@ -23773,6 +23782,49 @@
     </sortState>
   </autoFilter>
   <mergeCells count="59">
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="D148:F149"/>
+    <mergeCell ref="D140:F140"/>
+    <mergeCell ref="I140:L140"/>
+    <mergeCell ref="AA4:AD4"/>
+    <mergeCell ref="Q139:R139"/>
+    <mergeCell ref="D145:F145"/>
+    <mergeCell ref="D146:F146"/>
+    <mergeCell ref="D147:F147"/>
+    <mergeCell ref="S4:U4"/>
+    <mergeCell ref="L4:L5"/>
+    <mergeCell ref="Q4:R4"/>
+    <mergeCell ref="K4:K5"/>
+    <mergeCell ref="Y4:Z4"/>
+    <mergeCell ref="D167:F167"/>
+    <mergeCell ref="D139:F139"/>
+    <mergeCell ref="C151:F151"/>
+    <mergeCell ref="O139:P139"/>
+    <mergeCell ref="I139:N139"/>
+    <mergeCell ref="I141:L141"/>
+    <mergeCell ref="I142:L142"/>
+    <mergeCell ref="I143:L143"/>
+    <mergeCell ref="I144:L144"/>
+    <mergeCell ref="I145:L145"/>
+    <mergeCell ref="C148:C149"/>
+    <mergeCell ref="D141:F141"/>
+    <mergeCell ref="D142:F142"/>
+    <mergeCell ref="D143:F143"/>
+    <mergeCell ref="D144:F144"/>
+    <mergeCell ref="D152:F152"/>
+    <mergeCell ref="D166:F166"/>
+    <mergeCell ref="D153:F153"/>
+    <mergeCell ref="D154:F154"/>
+    <mergeCell ref="D161:F161"/>
+    <mergeCell ref="D162:F162"/>
+    <mergeCell ref="D163:F163"/>
+    <mergeCell ref="D164:F164"/>
+    <mergeCell ref="D165:F165"/>
+    <mergeCell ref="C156:F156"/>
+    <mergeCell ref="D157:F157"/>
+    <mergeCell ref="D158:F158"/>
+    <mergeCell ref="D159:F159"/>
+    <mergeCell ref="D160:F160"/>
     <mergeCell ref="AG5:AG6"/>
     <mergeCell ref="AH5:AH6"/>
     <mergeCell ref="AI5:AI6"/>
@@ -23789,49 +23841,6 @@
     <mergeCell ref="V4:X4"/>
     <mergeCell ref="M4:N4"/>
     <mergeCell ref="O4:P4"/>
-    <mergeCell ref="D166:F166"/>
-    <mergeCell ref="D153:F153"/>
-    <mergeCell ref="D154:F154"/>
-    <mergeCell ref="D161:F161"/>
-    <mergeCell ref="D162:F162"/>
-    <mergeCell ref="D163:F163"/>
-    <mergeCell ref="D164:F164"/>
-    <mergeCell ref="D165:F165"/>
-    <mergeCell ref="C156:F156"/>
-    <mergeCell ref="D157:F157"/>
-    <mergeCell ref="D158:F158"/>
-    <mergeCell ref="D159:F159"/>
-    <mergeCell ref="D160:F160"/>
-    <mergeCell ref="D167:F167"/>
-    <mergeCell ref="D139:F139"/>
-    <mergeCell ref="C151:F151"/>
-    <mergeCell ref="O139:P139"/>
-    <mergeCell ref="I139:N139"/>
-    <mergeCell ref="I141:L141"/>
-    <mergeCell ref="I142:L142"/>
-    <mergeCell ref="I143:L143"/>
-    <mergeCell ref="I144:L144"/>
-    <mergeCell ref="I145:L145"/>
-    <mergeCell ref="C148:C149"/>
-    <mergeCell ref="D141:F141"/>
-    <mergeCell ref="D142:F142"/>
-    <mergeCell ref="D143:F143"/>
-    <mergeCell ref="D144:F144"/>
-    <mergeCell ref="D152:F152"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="D148:F149"/>
-    <mergeCell ref="D140:F140"/>
-    <mergeCell ref="I140:L140"/>
-    <mergeCell ref="AA4:AD4"/>
-    <mergeCell ref="Q139:R139"/>
-    <mergeCell ref="D145:F145"/>
-    <mergeCell ref="D146:F146"/>
-    <mergeCell ref="D147:F147"/>
-    <mergeCell ref="S4:U4"/>
-    <mergeCell ref="L4:L5"/>
-    <mergeCell ref="Q4:R4"/>
-    <mergeCell ref="K4:K5"/>
-    <mergeCell ref="Y4:Z4"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="A7:AE137 AG7:AI137">
@@ -24496,88 +24505,88 @@
       <c r="AD3" s="159"/>
     </row>
     <row r="4" spans="1:35" s="5" customFormat="1" ht="36" customHeight="1" thickBot="1">
-      <c r="A4" s="408" t="s">
+      <c r="A4" s="350" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="348" t="s">
+      <c r="B4" s="406" t="s">
         <v>515</v>
       </c>
-      <c r="C4" s="414" t="s">
+      <c r="C4" s="359" t="s">
         <v>45</v>
       </c>
-      <c r="D4" s="369" t="s">
+      <c r="D4" s="348" t="s">
         <v>46</v>
       </c>
-      <c r="E4" s="412" t="s">
+      <c r="E4" s="357" t="s">
         <v>47</v>
       </c>
-      <c r="F4" s="369" t="s">
+      <c r="F4" s="348" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="410" t="s">
+      <c r="G4" s="355" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="366" t="s">
+      <c r="H4" s="352" t="s">
         <v>48</v>
       </c>
-      <c r="I4" s="366" t="s">
+      <c r="I4" s="352" t="s">
         <v>49</v>
       </c>
-      <c r="J4" s="369" t="s">
+      <c r="J4" s="348" t="s">
         <v>78</v>
       </c>
-      <c r="K4" s="366" t="s">
+      <c r="K4" s="352" t="s">
         <v>80</v>
       </c>
-      <c r="L4" s="364" t="s">
+      <c r="L4" s="363" t="s">
         <v>53</v>
       </c>
-      <c r="M4" s="365"/>
-      <c r="N4" s="368" t="s">
+      <c r="M4" s="364"/>
+      <c r="N4" s="362" t="s">
         <v>55</v>
       </c>
-      <c r="O4" s="365"/>
-      <c r="P4" s="368" t="s">
+      <c r="O4" s="364"/>
+      <c r="P4" s="362" t="s">
         <v>72</v>
       </c>
-      <c r="Q4" s="365"/>
-      <c r="R4" s="364" t="s">
+      <c r="Q4" s="364"/>
+      <c r="R4" s="363" t="s">
         <v>53</v>
       </c>
-      <c r="S4" s="364"/>
-      <c r="T4" s="365"/>
-      <c r="U4" s="368" t="s">
+      <c r="S4" s="363"/>
+      <c r="T4" s="364"/>
+      <c r="U4" s="362" t="s">
         <v>55</v>
       </c>
-      <c r="V4" s="364"/>
-      <c r="W4" s="365"/>
-      <c r="X4" s="371" t="s">
+      <c r="V4" s="363"/>
+      <c r="W4" s="364"/>
+      <c r="X4" s="415" t="s">
         <v>72</v>
       </c>
-      <c r="Y4" s="417"/>
-      <c r="Z4" s="371" t="s">
+      <c r="Y4" s="427"/>
+      <c r="Z4" s="415" t="s">
         <v>112</v>
       </c>
-      <c r="AA4" s="360"/>
-      <c r="AB4" s="360"/>
-      <c r="AC4" s="361"/>
-      <c r="AD4" s="369" t="s">
+      <c r="AA4" s="413"/>
+      <c r="AB4" s="413"/>
+      <c r="AC4" s="414"/>
+      <c r="AD4" s="348" t="s">
         <v>79</v>
       </c>
       <c r="AG4" s="236"/>
     </row>
     <row r="5" spans="1:35" ht="78.75">
-      <c r="A5" s="409"/>
-      <c r="B5" s="349"/>
-      <c r="C5" s="415"/>
-      <c r="D5" s="370"/>
-      <c r="E5" s="413"/>
-      <c r="F5" s="370"/>
-      <c r="G5" s="411"/>
-      <c r="H5" s="367"/>
-      <c r="I5" s="367"/>
-      <c r="J5" s="370"/>
-      <c r="K5" s="367"/>
+      <c r="A5" s="351"/>
+      <c r="B5" s="407"/>
+      <c r="C5" s="360"/>
+      <c r="D5" s="354"/>
+      <c r="E5" s="358"/>
+      <c r="F5" s="354"/>
+      <c r="G5" s="356"/>
+      <c r="H5" s="353"/>
+      <c r="I5" s="353"/>
+      <c r="J5" s="354"/>
+      <c r="K5" s="353"/>
       <c r="L5" s="79" t="s">
         <v>52</v>
       </c>
@@ -24632,14 +24641,14 @@
       <c r="AC5" s="250" t="s">
         <v>118</v>
       </c>
-      <c r="AD5" s="416"/>
-      <c r="AG5" s="422" t="s">
+      <c r="AD5" s="361"/>
+      <c r="AG5" s="417" t="s">
         <v>119</v>
       </c>
-      <c r="AH5" s="424" t="s">
+      <c r="AH5" s="419" t="s">
         <v>120</v>
       </c>
-      <c r="AI5" s="426" t="s">
+      <c r="AI5" s="421" t="s">
         <v>121</v>
       </c>
     </row>
@@ -24674,9 +24683,9 @@
       <c r="AB6" s="86"/>
       <c r="AC6" s="86"/>
       <c r="AD6" s="74"/>
-      <c r="AG6" s="423"/>
-      <c r="AH6" s="425"/>
-      <c r="AI6" s="427"/>
+      <c r="AG6" s="418"/>
+      <c r="AH6" s="420"/>
+      <c r="AI6" s="422"/>
     </row>
     <row r="7" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A7" s="33">
@@ -28463,28 +28472,28 @@
       <c r="C44" s="166" t="s">
         <v>20</v>
       </c>
-      <c r="D44" s="376" t="s">
+      <c r="D44" s="379" t="s">
         <v>21</v>
       </c>
-      <c r="E44" s="377"/>
+      <c r="E44" s="380"/>
       <c r="F44" s="46"/>
       <c r="G44" s="46"/>
-      <c r="H44" s="356" t="s">
+      <c r="H44" s="384" t="s">
         <v>14</v>
       </c>
-      <c r="I44" s="357"/>
-      <c r="J44" s="357"/>
-      <c r="K44" s="357"/>
-      <c r="L44" s="357"/>
-      <c r="M44" s="358"/>
-      <c r="N44" s="362" t="s">
+      <c r="I44" s="385"/>
+      <c r="J44" s="385"/>
+      <c r="K44" s="385"/>
+      <c r="L44" s="385"/>
+      <c r="M44" s="386"/>
+      <c r="N44" s="382" t="s">
         <v>7</v>
       </c>
-      <c r="O44" s="363"/>
-      <c r="P44" s="362" t="s">
+      <c r="O44" s="383"/>
+      <c r="P44" s="382" t="s">
         <v>109</v>
       </c>
-      <c r="Q44" s="363"/>
+      <c r="Q44" s="383"/>
       <c r="R44" s="1"/>
       <c r="S44" s="1"/>
       <c r="T44" s="140"/>
@@ -28504,17 +28513,17 @@
       <c r="C45" s="195" t="s">
         <v>109</v>
       </c>
-      <c r="D45" s="420" t="s">
+      <c r="D45" s="425" t="s">
         <v>111</v>
       </c>
-      <c r="E45" s="421"/>
+      <c r="E45" s="426"/>
       <c r="F45" s="46"/>
-      <c r="H45" s="356" t="s">
+      <c r="H45" s="384" t="s">
         <v>18</v>
       </c>
-      <c r="I45" s="357"/>
-      <c r="J45" s="357"/>
-      <c r="K45" s="358"/>
+      <c r="I45" s="385"/>
+      <c r="J45" s="385"/>
+      <c r="K45" s="386"/>
       <c r="L45" s="105">
         <f ca="1">M45/$M$45</f>
         <v>1</v>
@@ -28556,18 +28565,18 @@
       <c r="C46" s="195" t="s">
         <v>36</v>
       </c>
-      <c r="D46" s="418" t="s">
+      <c r="D46" s="423" t="s">
         <v>37</v>
       </c>
-      <c r="E46" s="419"/>
+      <c r="E46" s="424"/>
       <c r="F46" s="69"/>
       <c r="G46" s="6"/>
-      <c r="H46" s="379" t="s">
+      <c r="H46" s="387" t="s">
         <v>66</v>
       </c>
-      <c r="I46" s="380"/>
-      <c r="J46" s="380"/>
-      <c r="K46" s="381"/>
+      <c r="I46" s="388"/>
+      <c r="J46" s="388"/>
+      <c r="K46" s="389"/>
       <c r="L46" s="107">
         <f ca="1">M46/$M$45</f>
         <v>2.7777777777777776E-2</v>
@@ -28608,21 +28617,21 @@
       <c r="AI46" s="11"/>
     </row>
     <row r="47" spans="1:35">
-      <c r="C47" s="394" t="s">
+      <c r="C47" s="402" t="s">
         <v>75</v>
       </c>
-      <c r="D47" s="350" t="s">
+      <c r="D47" s="408" t="s">
         <v>76</v>
       </c>
-      <c r="E47" s="351"/>
+      <c r="E47" s="409"/>
       <c r="F47" s="70"/>
       <c r="G47" s="6"/>
-      <c r="H47" s="382" t="s">
+      <c r="H47" s="390" t="s">
         <v>67</v>
       </c>
-      <c r="I47" s="383"/>
-      <c r="J47" s="383"/>
-      <c r="K47" s="384"/>
+      <c r="I47" s="391"/>
+      <c r="J47" s="391"/>
+      <c r="K47" s="392"/>
       <c r="L47" s="109">
         <f t="shared" ref="L47:L50" ca="1" si="23">M47/$M$45</f>
         <v>0.55555555555555558</v>
@@ -28663,17 +28672,17 @@
       <c r="AI47" s="11"/>
     </row>
     <row r="48" spans="1:35" ht="16.5" thickBot="1">
-      <c r="C48" s="395"/>
-      <c r="D48" s="352"/>
-      <c r="E48" s="353"/>
+      <c r="C48" s="403"/>
+      <c r="D48" s="410"/>
+      <c r="E48" s="411"/>
       <c r="F48" s="71"/>
       <c r="G48" s="6"/>
-      <c r="H48" s="385" t="s">
+      <c r="H48" s="393" t="s">
         <v>68</v>
       </c>
-      <c r="I48" s="386"/>
-      <c r="J48" s="386"/>
-      <c r="K48" s="387"/>
+      <c r="I48" s="394"/>
+      <c r="J48" s="394"/>
+      <c r="K48" s="395"/>
       <c r="L48" s="111">
         <f t="shared" ca="1" si="23"/>
         <v>0.22222222222222221</v>
@@ -28716,12 +28725,12 @@
     <row r="49" spans="3:35">
       <c r="F49" s="72"/>
       <c r="G49" s="6"/>
-      <c r="H49" s="388" t="s">
+      <c r="H49" s="396" t="s">
         <v>70</v>
       </c>
-      <c r="I49" s="389"/>
-      <c r="J49" s="389"/>
-      <c r="K49" s="390"/>
+      <c r="I49" s="397"/>
+      <c r="J49" s="397"/>
+      <c r="K49" s="398"/>
       <c r="L49" s="114">
         <f t="shared" ca="1" si="23"/>
         <v>0.1388888888888889</v>
@@ -28764,17 +28773,17 @@
       <c r="AI49" s="11"/>
     </row>
     <row r="50" spans="3:35" ht="16.5" thickBot="1">
-      <c r="C50" s="378" t="s">
+      <c r="C50" s="381" t="s">
         <v>41</v>
       </c>
-      <c r="D50" s="378"/>
-      <c r="E50" s="378"/>
-      <c r="H50" s="391" t="s">
+      <c r="D50" s="381"/>
+      <c r="E50" s="381"/>
+      <c r="H50" s="399" t="s">
         <v>71</v>
       </c>
-      <c r="I50" s="392"/>
-      <c r="J50" s="392"/>
-      <c r="K50" s="393"/>
+      <c r="I50" s="400"/>
+      <c r="J50" s="400"/>
+      <c r="K50" s="401"/>
       <c r="L50" s="113">
         <f t="shared" ca="1" si="23"/>
         <v>5.5555555555555552E-2</v>
@@ -28819,6 +28828,27 @@
     </sortState>
   </autoFilter>
   <mergeCells count="37">
+    <mergeCell ref="P44:Q44"/>
+    <mergeCell ref="X4:Y4"/>
+    <mergeCell ref="Z4:AC4"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D44:E44"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="D46:E46"/>
+    <mergeCell ref="C50:E50"/>
+    <mergeCell ref="H46:K46"/>
+    <mergeCell ref="H47:K47"/>
+    <mergeCell ref="H44:M44"/>
+    <mergeCell ref="H48:K48"/>
+    <mergeCell ref="H49:K49"/>
+    <mergeCell ref="C47:C48"/>
+    <mergeCell ref="D47:E48"/>
+    <mergeCell ref="D45:E45"/>
     <mergeCell ref="AG5:AG6"/>
     <mergeCell ref="AH5:AH6"/>
     <mergeCell ref="AI5:AI6"/>
@@ -28835,27 +28865,6 @@
     <mergeCell ref="K4:K5"/>
     <mergeCell ref="P4:Q4"/>
     <mergeCell ref="J4:J5"/>
-    <mergeCell ref="D46:E46"/>
-    <mergeCell ref="C50:E50"/>
-    <mergeCell ref="H46:K46"/>
-    <mergeCell ref="H47:K47"/>
-    <mergeCell ref="H44:M44"/>
-    <mergeCell ref="H48:K48"/>
-    <mergeCell ref="H49:K49"/>
-    <mergeCell ref="C47:C48"/>
-    <mergeCell ref="D47:E48"/>
-    <mergeCell ref="D45:E45"/>
-    <mergeCell ref="P44:Q44"/>
-    <mergeCell ref="X4:Y4"/>
-    <mergeCell ref="Z4:AC4"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D44:E44"/>
-    <mergeCell ref="B4:B5"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="A7:AD42 AG7:AI42">
@@ -29030,7 +29039,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C184EF3E-84BF-4DCF-951B-B90EB4B9D23F}">
-  <dimension ref="A1:Z141"/>
+  <dimension ref="A1:Z142"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" customWidth="1"/>
@@ -29140,81 +29149,81 @@
       <c r="Z3" s="159"/>
     </row>
     <row r="4" spans="1:26" s="5" customFormat="1" ht="35.1" customHeight="1" thickBot="1">
-      <c r="A4" s="348" t="s">
+      <c r="A4" s="406" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="348" t="s">
+      <c r="B4" s="406" t="s">
         <v>515</v>
       </c>
-      <c r="C4" s="414" t="s">
+      <c r="C4" s="359" t="s">
         <v>45</v>
       </c>
-      <c r="D4" s="369" t="s">
+      <c r="D4" s="348" t="s">
         <v>46</v>
       </c>
-      <c r="E4" s="437" t="s">
+      <c r="E4" s="428" t="s">
         <v>47</v>
       </c>
-      <c r="F4" s="369" t="s">
+      <c r="F4" s="348" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="439" t="s">
+      <c r="G4" s="430" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="366" t="s">
+      <c r="H4" s="352" t="s">
         <v>48</v>
       </c>
-      <c r="I4" s="441" t="s">
+      <c r="I4" s="432" t="s">
         <v>49</v>
       </c>
-      <c r="J4" s="369" t="s">
+      <c r="J4" s="348" t="s">
         <v>78</v>
       </c>
-      <c r="K4" s="366" t="s">
+      <c r="K4" s="352" t="s">
         <v>80</v>
       </c>
-      <c r="L4" s="368" t="s">
+      <c r="L4" s="362" t="s">
         <v>53</v>
       </c>
-      <c r="M4" s="365"/>
-      <c r="N4" s="368" t="s">
+      <c r="M4" s="364"/>
+      <c r="N4" s="362" t="s">
         <v>55</v>
       </c>
-      <c r="O4" s="365"/>
-      <c r="P4" s="368" t="s">
+      <c r="O4" s="364"/>
+      <c r="P4" s="362" t="s">
         <v>72</v>
       </c>
-      <c r="Q4" s="365"/>
-      <c r="R4" s="364" t="s">
+      <c r="Q4" s="364"/>
+      <c r="R4" s="363" t="s">
         <v>53</v>
       </c>
-      <c r="S4" s="364"/>
-      <c r="T4" s="365"/>
-      <c r="U4" s="368" t="s">
+      <c r="S4" s="363"/>
+      <c r="T4" s="364"/>
+      <c r="U4" s="362" t="s">
         <v>55</v>
       </c>
-      <c r="V4" s="364"/>
-      <c r="W4" s="364"/>
-      <c r="X4" s="371" t="s">
+      <c r="V4" s="363"/>
+      <c r="W4" s="363"/>
+      <c r="X4" s="415" t="s">
         <v>72</v>
       </c>
-      <c r="Y4" s="372"/>
-      <c r="Z4" s="365" t="s">
+      <c r="Y4" s="416"/>
+      <c r="Z4" s="364" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="72" customHeight="1">
-      <c r="A5" s="349"/>
-      <c r="B5" s="349"/>
-      <c r="C5" s="415"/>
-      <c r="D5" s="370"/>
-      <c r="E5" s="438"/>
-      <c r="F5" s="370"/>
-      <c r="G5" s="440"/>
-      <c r="H5" s="367"/>
-      <c r="I5" s="442"/>
-      <c r="J5" s="370"/>
-      <c r="K5" s="367"/>
+      <c r="A5" s="407"/>
+      <c r="B5" s="407"/>
+      <c r="C5" s="360"/>
+      <c r="D5" s="354"/>
+      <c r="E5" s="429"/>
+      <c r="F5" s="354"/>
+      <c r="G5" s="431"/>
+      <c r="H5" s="353"/>
+      <c r="I5" s="433"/>
+      <c r="J5" s="354"/>
+      <c r="K5" s="353"/>
       <c r="L5" s="79" t="s">
         <v>52</v>
       </c>
@@ -29257,7 +29266,7 @@
       <c r="Y5" s="260" t="s">
         <v>114</v>
       </c>
-      <c r="Z5" s="416"/>
+      <c r="Z5" s="361"/>
     </row>
     <row r="6" spans="1:26" ht="15" customHeight="1" thickBot="1">
       <c r="A6" s="78"/>
@@ -34941,7 +34950,7 @@
         <v>628</v>
       </c>
       <c r="E80" s="174">
-        <f t="shared" ref="E80:E127" si="23">IF($T80=0,$S80+22,$T80+21)</f>
+        <f t="shared" ref="E80:E128" si="23">IF($T80=0,$S80+22,$T80+21)</f>
         <v>45945</v>
       </c>
       <c r="F80" s="31" t="s">
@@ -34954,11 +34963,11 @@
         <v>6</v>
       </c>
       <c r="I80" s="164">
-        <f t="shared" ref="I80:I127" si="24">IF(ISBLANK($V80),_xlfn.DAYS($I$1,$T80),_xlfn.DAYS($V80,$T80))</f>
+        <f t="shared" ref="I80:I128" si="24">IF(ISBLANK($V80),_xlfn.DAYS($I$1,$T80),_xlfn.DAYS($V80,$T80))</f>
         <v>6</v>
       </c>
       <c r="J80" s="47">
-        <f t="shared" ref="J80:J127" si="25">IF(($I80-21)&gt;0,$I80-21,0)</f>
+        <f t="shared" ref="J80:J128" si="25">IF(($I80-21)&gt;0,$I80-21,0)</f>
         <v>0</v>
       </c>
       <c r="K80" s="164"/>
@@ -35301,7 +35310,7 @@
     </row>
     <row r="85" spans="1:26" s="9" customFormat="1" ht="47.25">
       <c r="A85" s="33">
-        <f t="shared" ref="A85:A127" si="29">A84+1</f>
+        <f t="shared" ref="A85:A128" si="29">A84+1</f>
         <v>79</v>
       </c>
       <c r="B85" s="33" t="str">
@@ -38322,135 +38331,148 @@
       <c r="Y127" s="19"/>
       <c r="Z127" s="92"/>
     </row>
-    <row r="128" spans="1:26" s="9" customFormat="1">
-      <c r="A128" s="23"/>
-      <c r="B128" s="33"/>
-      <c r="C128" s="137"/>
-      <c r="D128" s="25"/>
-      <c r="E128" s="174"/>
-      <c r="F128" s="31"/>
-      <c r="G128" s="21"/>
+    <row r="128" spans="1:26" s="9" customFormat="1" ht="47.25">
+      <c r="A128" s="33">
+        <f t="shared" si="29"/>
+        <v>122</v>
+      </c>
+      <c r="B128" s="33" t="str">
+        <f t="shared" ref="B128" si="59">MID(D128, FIND("-", D128) + 1, 4)</f>
+        <v>5.11</v>
+      </c>
+      <c r="C128" s="164" t="s">
+        <v>621</v>
+      </c>
+      <c r="D128" s="25" t="s">
+        <v>1068</v>
+      </c>
+      <c r="E128" s="174">
+        <f t="shared" si="23"/>
+        <v>46330</v>
+      </c>
+      <c r="F128" s="31" t="s">
+        <v>1069</v>
+      </c>
+      <c r="G128" s="21" t="s">
+        <v>1070</v>
+      </c>
       <c r="H128" s="138"/>
-      <c r="I128" s="177"/>
-      <c r="J128" s="48"/>
-      <c r="K128" s="177"/>
-      <c r="L128" s="59"/>
-      <c r="M128" s="60"/>
-      <c r="N128" s="61"/>
-      <c r="O128" s="144"/>
-      <c r="P128" s="146"/>
-      <c r="Q128" s="152"/>
-      <c r="R128" s="27"/>
-      <c r="S128" s="27"/>
-      <c r="T128" s="187"/>
+      <c r="I128" s="164">
+        <f t="shared" ca="1" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="J128" s="47">
+        <f t="shared" ca="1" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="K128" s="164"/>
+      <c r="L128" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="M128" s="41"/>
+      <c r="N128" s="40"/>
+      <c r="O128" s="41"/>
+      <c r="P128" s="40"/>
+      <c r="Q128" s="154"/>
+      <c r="R128" s="27">
+        <v>46309</v>
+      </c>
+      <c r="S128" s="27">
+        <v>46309</v>
+      </c>
+      <c r="T128" s="188">
+        <v>46309</v>
+      </c>
       <c r="U128" s="29"/>
-      <c r="V128" s="188"/>
+      <c r="V128" s="211"/>
       <c r="W128" s="235"/>
       <c r="X128" s="230"/>
       <c r="Y128" s="19"/>
       <c r="Z128" s="92"/>
     </row>
-    <row r="129" spans="1:26" s="9" customFormat="1" ht="16.5" thickBot="1">
-      <c r="A129" s="24"/>
-      <c r="B129" s="329"/>
-      <c r="C129" s="165"/>
-      <c r="D129" s="45"/>
-      <c r="E129" s="175"/>
-      <c r="F129" s="32"/>
-      <c r="G129" s="22"/>
-      <c r="H129" s="139"/>
-      <c r="I129" s="178"/>
-      <c r="J129" s="49"/>
-      <c r="K129" s="178"/>
-      <c r="L129" s="62"/>
-      <c r="M129" s="63"/>
-      <c r="N129" s="64"/>
-      <c r="O129" s="145"/>
-      <c r="P129" s="147"/>
-      <c r="Q129" s="153"/>
-      <c r="R129" s="44"/>
-      <c r="S129" s="44"/>
-      <c r="T129" s="189"/>
-      <c r="U129" s="43"/>
-      <c r="V129" s="194"/>
-      <c r="W129" s="258"/>
-      <c r="X129" s="232"/>
-      <c r="Y129" s="20"/>
-      <c r="Z129" s="93"/>
-    </row>
-    <row r="130" spans="1:26" ht="16.5" thickBot="1"/>
-    <row r="131" spans="1:26" ht="16.5" thickBot="1">
-      <c r="C131" s="207" t="s">
+    <row r="129" spans="1:26" s="9" customFormat="1">
+      <c r="A129" s="23"/>
+      <c r="B129" s="33"/>
+      <c r="C129" s="137"/>
+      <c r="D129" s="25"/>
+      <c r="E129" s="174"/>
+      <c r="F129" s="31"/>
+      <c r="G129" s="21"/>
+      <c r="H129" s="138"/>
+      <c r="I129" s="177"/>
+      <c r="J129" s="48"/>
+      <c r="K129" s="177"/>
+      <c r="L129" s="59"/>
+      <c r="M129" s="60"/>
+      <c r="N129" s="61"/>
+      <c r="O129" s="144"/>
+      <c r="P129" s="146"/>
+      <c r="Q129" s="152"/>
+      <c r="R129" s="27"/>
+      <c r="S129" s="27"/>
+      <c r="T129" s="187"/>
+      <c r="U129" s="29"/>
+      <c r="V129" s="188"/>
+      <c r="W129" s="235"/>
+      <c r="X129" s="230"/>
+      <c r="Y129" s="19"/>
+      <c r="Z129" s="92"/>
+    </row>
+    <row r="130" spans="1:26" s="9" customFormat="1" ht="16.5" thickBot="1">
+      <c r="A130" s="24"/>
+      <c r="B130" s="329"/>
+      <c r="C130" s="165"/>
+      <c r="D130" s="45"/>
+      <c r="E130" s="175"/>
+      <c r="F130" s="32"/>
+      <c r="G130" s="22"/>
+      <c r="H130" s="139"/>
+      <c r="I130" s="178"/>
+      <c r="J130" s="49"/>
+      <c r="K130" s="178"/>
+      <c r="L130" s="62"/>
+      <c r="M130" s="63"/>
+      <c r="N130" s="64"/>
+      <c r="O130" s="145"/>
+      <c r="P130" s="147"/>
+      <c r="Q130" s="153"/>
+      <c r="R130" s="44"/>
+      <c r="S130" s="44"/>
+      <c r="T130" s="189"/>
+      <c r="U130" s="43"/>
+      <c r="V130" s="194"/>
+      <c r="W130" s="258"/>
+      <c r="X130" s="232"/>
+      <c r="Y130" s="20"/>
+      <c r="Z130" s="93"/>
+    </row>
+    <row r="131" spans="1:26" ht="16.5" thickBot="1"/>
+    <row r="132" spans="1:26" ht="16.5" thickBot="1">
+      <c r="C132" s="207" t="s">
         <v>38</v>
       </c>
-      <c r="D131" s="428" t="s">
+      <c r="D132" s="441" t="s">
         <v>39</v>
       </c>
-      <c r="E131" s="429"/>
-      <c r="F131" s="46"/>
-      <c r="G131" s="68"/>
-      <c r="H131" s="356" t="s">
+      <c r="E132" s="442"/>
+      <c r="F132" s="46"/>
+      <c r="G132" s="68"/>
+      <c r="H132" s="384" t="s">
         <v>14</v>
       </c>
-      <c r="I131" s="357"/>
-      <c r="J131" s="357"/>
-      <c r="K131" s="357"/>
-      <c r="L131" s="357"/>
-      <c r="M131" s="358"/>
-      <c r="N131" s="362" t="s">
+      <c r="I132" s="385"/>
+      <c r="J132" s="385"/>
+      <c r="K132" s="385"/>
+      <c r="L132" s="385"/>
+      <c r="M132" s="386"/>
+      <c r="N132" s="382" t="s">
         <v>7</v>
       </c>
-      <c r="O131" s="363"/>
-      <c r="P131" s="362" t="s">
+      <c r="O132" s="383"/>
+      <c r="P132" s="382" t="s">
         <v>110</v>
       </c>
-      <c r="Q131" s="363"/>
-      <c r="R131" s="1"/>
-      <c r="S131" s="1"/>
-      <c r="T131" s="140"/>
-      <c r="U131" s="1"/>
-      <c r="W131" s="11"/>
-      <c r="X131" s="11"/>
-      <c r="Y131" s="11"/>
-    </row>
-    <row r="132" spans="1:26" ht="16.5" customHeight="1" thickBot="1">
-      <c r="C132" s="208" t="s">
-        <v>74</v>
-      </c>
-      <c r="D132" s="435" t="s">
-        <v>77</v>
-      </c>
-      <c r="E132" s="436"/>
-      <c r="F132" s="46"/>
-      <c r="G132" s="46"/>
-      <c r="H132" s="430" t="s">
-        <v>17</v>
-      </c>
-      <c r="I132" s="431"/>
-      <c r="J132" s="130"/>
-      <c r="K132" s="210"/>
-      <c r="L132" s="117">
-        <f ca="1">M132/$M$132</f>
-        <v>1</v>
-      </c>
-      <c r="M132" s="104">
-        <f ca="1">SUM($M$133:$M$135)</f>
-        <v>126</v>
-      </c>
-      <c r="N132" s="118" t="s">
-        <v>15</v>
-      </c>
-      <c r="O132" s="119" t="s">
-        <v>16</v>
-      </c>
-      <c r="P132" s="117">
-        <f ca="1">Q132/$Q$132</f>
-        <v>1</v>
-      </c>
-      <c r="Q132" s="104">
-        <f ca="1">SUM(Q133:Q134)</f>
-        <v>107</v>
-      </c>
+      <c r="Q132" s="383"/>
       <c r="R132" s="1"/>
       <c r="S132" s="1"/>
       <c r="T132" s="140"/>
@@ -38459,45 +38481,43 @@
       <c r="X132" s="11"/>
       <c r="Y132" s="11"/>
     </row>
-    <row r="133" spans="1:26">
-      <c r="C133" s="394" t="s">
-        <v>6</v>
-      </c>
-      <c r="D133" s="435" t="s">
-        <v>40</v>
-      </c>
-      <c r="E133" s="436"/>
-      <c r="F133" s="69"/>
-      <c r="G133" s="6"/>
-      <c r="H133" s="432" t="s">
-        <v>69</v>
-      </c>
-      <c r="I133" s="433"/>
-      <c r="J133" s="433"/>
-      <c r="K133" s="434"/>
-      <c r="L133" s="122">
-        <f t="shared" ref="L133:L135" ca="1" si="59">M133/$M$132</f>
-        <v>0.82539682539682535</v>
-      </c>
-      <c r="M133" s="123">
-        <f>COUNTIF($H$7:$H$129,"RFCS")</f>
-        <v>104</v>
-      </c>
-      <c r="N133" s="121">
-        <f ca="1">COUNTIFS($I$7:$I$129,"&lt;=21",$H$7:$H$129,"RFCS")</f>
-        <v>62</v>
-      </c>
-      <c r="O133" s="120">
-        <f ca="1">COUNTIFS($I$7:$I$129,"&gt;21",$H$7:$H$129,"RFCS")</f>
-        <v>41</v>
-      </c>
-      <c r="P133" s="122">
-        <f ca="1">Q133/$Q$132</f>
-        <v>0.63551401869158874</v>
-      </c>
-      <c r="Q133" s="123">
-        <f>COUNTIF($Q$7:$Q$129,"RBE") + COUNTIF($Q$7:$Q$129,"SUP")</f>
-        <v>68</v>
+    <row r="133" spans="1:26" ht="16.5" customHeight="1" thickBot="1">
+      <c r="C133" s="208" t="s">
+        <v>74</v>
+      </c>
+      <c r="D133" s="439" t="s">
+        <v>77</v>
+      </c>
+      <c r="E133" s="440"/>
+      <c r="F133" s="46"/>
+      <c r="G133" s="46"/>
+      <c r="H133" s="434" t="s">
+        <v>17</v>
+      </c>
+      <c r="I133" s="435"/>
+      <c r="J133" s="130"/>
+      <c r="K133" s="210"/>
+      <c r="L133" s="117">
+        <f ca="1">M133/$M$133</f>
+        <v>1</v>
+      </c>
+      <c r="M133" s="104">
+        <f ca="1">SUM($M$134:$M$136)</f>
+        <v>127</v>
+      </c>
+      <c r="N133" s="118" t="s">
+        <v>15</v>
+      </c>
+      <c r="O133" s="119" t="s">
+        <v>16</v>
+      </c>
+      <c r="P133" s="117">
+        <f ca="1">Q133/$Q$133</f>
+        <v>1</v>
+      </c>
+      <c r="Q133" s="104">
+        <f ca="1">SUM(Q134:Q135)</f>
+        <v>108</v>
       </c>
       <c r="R133" s="1"/>
       <c r="S133" s="1"/>
@@ -38508,44 +38528,46 @@
       <c r="Y133" s="11"/>
     </row>
     <row r="134" spans="1:26">
-      <c r="C134" s="394"/>
-      <c r="D134" s="435"/>
-      <c r="E134" s="436"/>
-      <c r="F134" s="72"/>
+      <c r="C134" s="402" t="s">
+        <v>6</v>
+      </c>
+      <c r="D134" s="439" t="s">
+        <v>40</v>
+      </c>
+      <c r="E134" s="440"/>
+      <c r="F134" s="69"/>
       <c r="G134" s="6"/>
-      <c r="H134" s="388" t="s">
-        <v>70</v>
-      </c>
-      <c r="I134" s="389"/>
-      <c r="J134" s="389"/>
-      <c r="K134" s="390"/>
-      <c r="L134" s="124">
-        <f t="shared" ca="1" si="59"/>
-        <v>6.3492063492063489E-2</v>
-      </c>
-      <c r="M134" s="125">
-        <f ca="1">SUM(N134:O134)</f>
-        <v>8</v>
-      </c>
-      <c r="N134" s="98">
-        <f ca="1">COUNTIFS($I$7:$I$129,"&lt;=21",$U$7:$U$129,"",$K$7:$K$129,"&lt;&gt;X")</f>
-        <v>3</v>
-      </c>
-      <c r="O134" s="50">
-        <f ca="1">COUNTIFS($I$7:$I$129,"&gt;21",$U$7:$U$129,"",$K$7:$K$129,"&lt;&gt;X")</f>
-        <v>5</v>
-      </c>
-      <c r="P134" s="124">
-        <f ca="1">Q134/$Q$132</f>
-        <v>0.3644859813084112</v>
-      </c>
-      <c r="Q134" s="125">
-        <f ca="1">COUNTIFS($I$7:$I$129,"&gt;=0",$P$7:$P$129,"",$K$7:$K$129,"&lt;&gt;X")</f>
-        <v>39</v>
-      </c>
-      <c r="R134" s="1" t="s">
-        <v>10</v>
-      </c>
+      <c r="H134" s="436" t="s">
+        <v>69</v>
+      </c>
+      <c r="I134" s="437"/>
+      <c r="J134" s="437"/>
+      <c r="K134" s="438"/>
+      <c r="L134" s="122">
+        <f t="shared" ref="L134:L136" ca="1" si="60">M134/$M$133</f>
+        <v>0.81889763779527558</v>
+      </c>
+      <c r="M134" s="123">
+        <f>COUNTIF($H$7:$H$130,"RFCS")</f>
+        <v>104</v>
+      </c>
+      <c r="N134" s="121">
+        <f ca="1">COUNTIFS($I$7:$I$130,"&lt;=21",$H$7:$H$130,"RFCS")</f>
+        <v>62</v>
+      </c>
+      <c r="O134" s="120">
+        <f ca="1">COUNTIFS($I$7:$I$130,"&gt;21",$H$7:$H$130,"RFCS")</f>
+        <v>41</v>
+      </c>
+      <c r="P134" s="122">
+        <f ca="1">Q134/$Q$133</f>
+        <v>0.62962962962962965</v>
+      </c>
+      <c r="Q134" s="123">
+        <f>COUNTIF($Q$7:$Q$130,"RBE") + COUNTIF($Q$7:$Q$130,"SUP")</f>
+        <v>68</v>
+      </c>
+      <c r="R134" s="1"/>
       <c r="S134" s="1"/>
       <c r="T134" s="140"/>
       <c r="U134" s="1"/>
@@ -38553,66 +38575,112 @@
       <c r="X134" s="11"/>
       <c r="Y134" s="11"/>
     </row>
-    <row r="135" spans="1:26" ht="16.5" thickBot="1">
-      <c r="C135" s="394" t="s">
+    <row r="135" spans="1:26">
+      <c r="C135" s="402"/>
+      <c r="D135" s="439"/>
+      <c r="E135" s="440"/>
+      <c r="F135" s="72"/>
+      <c r="G135" s="6"/>
+      <c r="H135" s="396" t="s">
+        <v>70</v>
+      </c>
+      <c r="I135" s="397"/>
+      <c r="J135" s="397"/>
+      <c r="K135" s="398"/>
+      <c r="L135" s="124">
+        <f t="shared" ca="1" si="60"/>
+        <v>7.0866141732283464E-2</v>
+      </c>
+      <c r="M135" s="125">
+        <f ca="1">SUM(N135:O135)</f>
+        <v>9</v>
+      </c>
+      <c r="N135" s="98">
+        <f ca="1">COUNTIFS($I$7:$I$130,"&lt;=21",$U$7:$U$130,"",$K$7:$K$130,"&lt;&gt;X")</f>
+        <v>4</v>
+      </c>
+      <c r="O135" s="50">
+        <f ca="1">COUNTIFS($I$7:$I$130,"&gt;21",$U$7:$U$130,"",$K$7:$K$130,"&lt;&gt;X")</f>
+        <v>5</v>
+      </c>
+      <c r="P135" s="124">
+        <f ca="1">Q135/$Q$133</f>
+        <v>0.37037037037037035</v>
+      </c>
+      <c r="Q135" s="125">
+        <f ca="1">COUNTIFS($I$7:$I$130,"&gt;=0",$P$7:$P$130,"",$K$7:$K$130,"&lt;&gt;X")</f>
+        <v>40</v>
+      </c>
+      <c r="R135" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="S135" s="1"/>
+      <c r="T135" s="140"/>
+      <c r="U135" s="1"/>
+      <c r="W135" s="11"/>
+      <c r="X135" s="11"/>
+      <c r="Y135" s="11"/>
+    </row>
+    <row r="136" spans="1:26" ht="16.5" thickBot="1">
+      <c r="C136" s="402" t="s">
         <v>75</v>
       </c>
-      <c r="D135" s="350" t="s">
+      <c r="D136" s="408" t="s">
         <v>76</v>
       </c>
-      <c r="E135" s="351"/>
-      <c r="H135" s="391" t="s">
+      <c r="E136" s="409"/>
+      <c r="H136" s="399" t="s">
         <v>71</v>
       </c>
-      <c r="I135" s="392"/>
-      <c r="J135" s="392"/>
-      <c r="K135" s="393"/>
-      <c r="L135" s="126">
-        <f t="shared" ca="1" si="59"/>
-        <v>0.1111111111111111</v>
-      </c>
-      <c r="M135" s="116">
-        <f>COUNTIFS($K$7:$K$129,"X")</f>
+      <c r="I136" s="400"/>
+      <c r="J136" s="400"/>
+      <c r="K136" s="401"/>
+      <c r="L136" s="126">
+        <f t="shared" ca="1" si="60"/>
+        <v>0.11023622047244094</v>
+      </c>
+      <c r="M136" s="116">
+        <f>COUNTIFS($K$7:$K$130,"X")</f>
         <v>14</v>
       </c>
-      <c r="N135" s="99"/>
-      <c r="O135" s="51"/>
-      <c r="P135" s="223"/>
-      <c r="Q135" s="224"/>
-    </row>
-    <row r="136" spans="1:26" ht="16.5" thickBot="1">
-      <c r="C136" s="395"/>
-      <c r="D136" s="352"/>
-      <c r="E136" s="353"/>
-    </row>
-    <row r="138" spans="1:26">
-      <c r="C138" s="378" t="s">
+      <c r="N136" s="99"/>
+      <c r="O136" s="51"/>
+      <c r="P136" s="223"/>
+      <c r="Q136" s="224"/>
+    </row>
+    <row r="137" spans="1:26" ht="16.5" thickBot="1">
+      <c r="C137" s="403"/>
+      <c r="D137" s="410"/>
+      <c r="E137" s="411"/>
+    </row>
+    <row r="139" spans="1:26">
+      <c r="C139" s="381" t="s">
         <v>41</v>
       </c>
-      <c r="D138" s="378"/>
-      <c r="E138" s="378"/>
-    </row>
-    <row r="139" spans="1:26">
-      <c r="C139" s="169" t="s">
-        <v>8</v>
-      </c>
-      <c r="D139" s="1" t="s">
-        <v>42</v>
-      </c>
+      <c r="D139" s="381"/>
+      <c r="E139" s="381"/>
     </row>
     <row r="140" spans="1:26">
       <c r="C140" s="169" t="s">
         <v>8</v>
       </c>
-      <c r="D140" s="127" t="s">
-        <v>43</v>
+      <c r="D140" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="141" spans="1:26">
       <c r="C141" s="169" t="s">
         <v>8</v>
       </c>
-      <c r="D141" s="1" t="s">
+      <c r="D141" s="127" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="142" spans="1:26">
+      <c r="C142" s="169" t="s">
+        <v>8</v>
+      </c>
+      <c r="D142" s="1" t="s">
         <v>44</v>
       </c>
     </row>
@@ -38623,6 +38691,22 @@
     </sortState>
   </autoFilter>
   <mergeCells count="32">
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="P132:Q132"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="D132:E132"/>
+    <mergeCell ref="H132:M132"/>
+    <mergeCell ref="N132:O132"/>
+    <mergeCell ref="H133:I133"/>
+    <mergeCell ref="C139:E139"/>
+    <mergeCell ref="H134:K134"/>
+    <mergeCell ref="H135:K135"/>
+    <mergeCell ref="H136:K136"/>
+    <mergeCell ref="D133:E133"/>
+    <mergeCell ref="C134:C135"/>
+    <mergeCell ref="D134:E135"/>
+    <mergeCell ref="C136:C137"/>
+    <mergeCell ref="D136:E137"/>
     <mergeCell ref="Z4:Z5"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="D4:D5"/>
@@ -38639,25 +38723,9 @@
     <mergeCell ref="K4:K5"/>
     <mergeCell ref="P4:Q4"/>
     <mergeCell ref="X4:Y4"/>
-    <mergeCell ref="H132:I132"/>
-    <mergeCell ref="C138:E138"/>
-    <mergeCell ref="H133:K133"/>
-    <mergeCell ref="H134:K134"/>
-    <mergeCell ref="H135:K135"/>
-    <mergeCell ref="D132:E132"/>
-    <mergeCell ref="C133:C134"/>
-    <mergeCell ref="D133:E134"/>
-    <mergeCell ref="C135:C136"/>
-    <mergeCell ref="D135:E136"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="P131:Q131"/>
-    <mergeCell ref="J4:J5"/>
-    <mergeCell ref="D131:E131"/>
-    <mergeCell ref="H131:M131"/>
-    <mergeCell ref="N131:O131"/>
   </mergeCells>
   <phoneticPr fontId="71"/>
-  <conditionalFormatting sqref="A7:Z129">
+  <conditionalFormatting sqref="A7:Z130">
     <cfRule type="expression" dxfId="4" priority="1">
       <formula>$K7="X"</formula>
     </cfRule>
@@ -38802,9 +38870,9 @@
     <hyperlink ref="O43" r:id="rId125" xr:uid="{0E3F3A7F-DA9A-49F8-A93F-8337122FAE1A}"/>
     <hyperlink ref="N41" r:id="rId126" xr:uid="{3405D711-BDD4-4069-A376-D6B961D87010}"/>
     <hyperlink ref="N43" r:id="rId127" xr:uid="{525398A7-A7B1-41B1-88A2-7E7F9115541E}"/>
-    <hyperlink ref="C139" r:id="rId128" xr:uid="{F06CE902-4089-4B08-A7E9-420A16C9FF0E}"/>
-    <hyperlink ref="C140" r:id="rId129" xr:uid="{6D322F1B-B574-40E7-BED0-14ED893C19C5}"/>
-    <hyperlink ref="C141" r:id="rId130" xr:uid="{1845DEB0-969B-4FE7-B52A-52C25D3EC72E}"/>
+    <hyperlink ref="C140" r:id="rId128" xr:uid="{F06CE902-4089-4B08-A7E9-420A16C9FF0E}"/>
+    <hyperlink ref="C141" r:id="rId129" xr:uid="{6D322F1B-B574-40E7-BED0-14ED893C19C5}"/>
+    <hyperlink ref="C142" r:id="rId130" xr:uid="{1845DEB0-969B-4FE7-B52A-52C25D3EC72E}"/>
     <hyperlink ref="N42" r:id="rId131" xr:uid="{95D9F3CF-8EC0-4C96-9F49-34E6585C583B}"/>
     <hyperlink ref="L44" r:id="rId132" xr:uid="{255E79C1-4568-41F7-B71E-8301B034AA56}"/>
     <hyperlink ref="P8" r:id="rId133" xr:uid="{4339778F-2FA8-45DA-BD1F-0684B78D35ED}"/>
@@ -39150,9 +39218,10 @@
     <hyperlink ref="N124" r:id="rId473" xr:uid="{F03DC946-218B-485F-BFEB-FBD9AEF00913}"/>
     <hyperlink ref="L126" r:id="rId474" xr:uid="{3EB8572D-FD0D-4865-AF14-84A4ECCCC02A}"/>
     <hyperlink ref="L127" r:id="rId475" xr:uid="{E41605CA-C2E5-494D-8E08-2F89092E4322}"/>
+    <hyperlink ref="L128" r:id="rId476" xr:uid="{EEC0D82E-190C-4F0D-80DD-BE42DD4F1D56}"/>
   </hyperlinks>
   <pageMargins left="0.25" right="0.17" top="0.5" bottom="0.25" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="28" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId476"/>
+  <pageSetup paperSize="9" scale="28" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId477"/>
 </worksheet>
 </file>
 
@@ -39237,19 +39306,19 @@
       <c r="S3" s="281"/>
     </row>
     <row r="4" spans="1:25" ht="36" customHeight="1" thickBot="1">
-      <c r="A4" s="408" t="s">
+      <c r="A4" s="350" t="s">
         <v>123</v>
       </c>
-      <c r="B4" s="366" t="s">
+      <c r="B4" s="352" t="s">
         <v>45</v>
       </c>
-      <c r="C4" s="366" t="s">
+      <c r="C4" s="352" t="s">
         <v>95</v>
       </c>
-      <c r="D4" s="366" t="s">
+      <c r="D4" s="352" t="s">
         <v>46</v>
       </c>
-      <c r="E4" s="369" t="s">
+      <c r="E4" s="348" t="s">
         <v>4</v>
       </c>
       <c r="F4" s="449" t="s">
@@ -39278,12 +39347,12 @@
       <c r="S4" s="448"/>
     </row>
     <row r="5" spans="1:25" ht="78.75">
-      <c r="A5" s="409"/>
-      <c r="B5" s="367"/>
-      <c r="C5" s="367"/>
-      <c r="D5" s="367"/>
-      <c r="E5" s="370"/>
-      <c r="F5" s="411"/>
+      <c r="A5" s="351"/>
+      <c r="B5" s="353"/>
+      <c r="C5" s="353"/>
+      <c r="D5" s="353"/>
+      <c r="E5" s="354"/>
+      <c r="F5" s="356"/>
       <c r="G5" s="283" t="s">
         <v>56</v>
       </c>
@@ -40616,16 +40685,16 @@
       <c r="R3" s="281"/>
     </row>
     <row r="4" spans="1:18" ht="16.5" thickBot="1">
-      <c r="A4" s="408" t="s">
+      <c r="A4" s="350" t="s">
         <v>123</v>
       </c>
-      <c r="B4" s="366" t="s">
+      <c r="B4" s="352" t="s">
         <v>45</v>
       </c>
-      <c r="C4" s="366" t="s">
+      <c r="C4" s="352" t="s">
         <v>46</v>
       </c>
-      <c r="D4" s="364" t="s">
+      <c r="D4" s="363" t="s">
         <v>4</v>
       </c>
       <c r="E4" s="449" t="s">
@@ -40654,11 +40723,11 @@
       <c r="R4" s="448"/>
     </row>
     <row r="5" spans="1:18" ht="78.75">
-      <c r="A5" s="409"/>
-      <c r="B5" s="367"/>
-      <c r="C5" s="367"/>
-      <c r="D5" s="440"/>
-      <c r="E5" s="370"/>
+      <c r="A5" s="351"/>
+      <c r="B5" s="353"/>
+      <c r="C5" s="353"/>
+      <c r="D5" s="431"/>
+      <c r="E5" s="354"/>
       <c r="F5" s="283" t="s">
         <v>56</v>
       </c>

--- a/ICT-RFA-RFI-lists-New.xlsx
+++ b/ICT-RFA-RFI-lists-New.xlsx
@@ -9,9 +9,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project Airport\LTIA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6757417F-F15B-4A0C-8DF6-754F72477F39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E58510BE-229C-4BD8-B416-72158A7B789B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="506" activeTab="2" xr2:uid="{CCA8147E-0981-4321-B87F-440A52C0DA59}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="506" xr2:uid="{CCA8147E-0981-4321-B87F-440A52C0DA59}"/>
   </bookViews>
   <sheets>
     <sheet name="RFA" sheetId="1" r:id="rId1"/>
@@ -24,12 +24,12 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Need ReSub (RFA)'!$A$6:$S$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Need ReSub (RFA-SDS)'!$A$6:$R$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">RFA!$A$6:$AE$137</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">RFA!$A$6:$AE$141</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'RFA-SDS'!$A$6:$AD$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">RFI!$A$6:$Z$127</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Need ReSub (RFA)'!$A$1:$S$77</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'Need ReSub (RFA-SDS)'!$A$1:$R$62</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RFA!$A$1:$AE$137,RFA!$I$139:$R$145,RFA!$C$139:$F$149,RFA!$C$151:$F$154,RFA!$C$156:$F$167</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RFA!$A$1:$AE$141,RFA!$I$143:$R$149,RFA!$C$143:$F$153,RFA!$C$155:$F$158,RFA!$C$160:$F$171</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'RFA-SDS'!$A$1:$AD$42,'RFA-SDS'!$H$44:$Q$50,'RFA-SDS'!$C$44:$E$48,'RFA-SDS'!$C$50:$E$53</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">RFI!$A$1:$Z$130,RFI!$H$132:$Q$136,RFI!$C$132:$E$137,RFI!$C$139:$E$142</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">RFA!$4:$5</definedName>
@@ -78,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3441" uniqueCount="1071">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3469" uniqueCount="1088">
   <si>
     <t>TT</t>
   </si>
@@ -5015,9 +5015,6 @@
 10/8/2026 Đã ký A</t>
   </si>
   <si>
-    <t>10/9/2026 Update</t>
-  </si>
-  <si>
     <t>LTIA-5.11-LTICT-80000 -RFI-0037A</t>
   </si>
   <si>
@@ -5043,12 +5040,6 @@
 10/13/2026: Đã gửi comment qua CNC</t>
   </si>
   <si>
-    <t>10/14/2026: Đã ký RFCS</t>
-  </si>
-  <si>
-    <t>10/14/2026: Đã ký A</t>
-  </si>
-  <si>
     <t>LTIA-5.11-LTICT- 71110 -RFA-OTH-0012</t>
   </si>
   <si>
@@ -5059,6 +5050,73 @@
   </si>
   <si>
     <t>Kiến nghị thay đổi mã hiệu media converter cho hệ thống Smart Parking</t>
+  </si>
+  <si>
+    <t>10/9/2026 Update
+10/13/2026: Đã comment và gửi CNC</t>
+  </si>
+  <si>
+    <t>10/13/2026: Đã comment và gửi CNC
+10/14/2026: Đã ký RFCS</t>
+  </si>
+  <si>
+    <t>10/13/2026: Đã comment và gửi CNC
+10/14/2026: Đã ký A</t>
+  </si>
+  <si>
+    <t>101/14/2026: Đã comment</t>
+  </si>
+  <si>
+    <t>10/14/2026: Đã comment và gửi CNC
+10/14/2026: Đã ký RFCS</t>
+  </si>
+  <si>
+    <t>10/12/2026: Đã comment
+10/13/2026: Đã gửi comment qua CNC
+10/14/2026: Đã ký C</t>
+  </si>
+  <si>
+    <t>LTIA-5.11-LTICT-72040-RFA-MSS-0008</t>
+  </si>
+  <si>
+    <t>Request for Approval of the Method Statement for Data Communication Hardware system (DCH)</t>
+  </si>
+  <si>
+    <t>Yêu cầu phê duyệt Biện pháp thi công cho hệ thống Thiết bị phần cứng truyền thông dữ liệu (DCH) </t>
+  </si>
+  <si>
+    <t>LTIA-5.11-LTICT-72020-RFA-MSS-0009</t>
+  </si>
+  <si>
+    <t>Request for Approval of the Method Statement for Data Communication Network System (DNE)</t>
+  </si>
+  <si>
+    <t>Yêu cầu phê duyệt Biện pháp thi công cho hệ thống Thiết bị mạng truyền thông dữ liệu (DNE)</t>
+  </si>
+  <si>
+    <t>LTIA-5.11-LTICT-72170-RFA-MSS-0010</t>
+  </si>
+  <si>
+    <t>Request for Approval of the Method Statement for Video Wall SystemRequest for Approval of the Method Statement for Video Wall System</t>
+  </si>
+  <si>
+    <t>Yêu cầu phê duyệt Biện pháp thi công cho hệ thống màn hình hiển thị (Video wall)</t>
+  </si>
+  <si>
+    <t>VW</t>
+  </si>
+  <si>
+    <t>LTIA-5.11-LTICT-70000-RFA-MSS-0011</t>
+  </si>
+  <si>
+    <t>Request for Approval of the Method Statement for Wireless Data Network Equipment (WDNE) and Telephone Over IP (TOIP) System</t>
+  </si>
+  <si>
+    <t>Yêu cầu phê duyệt Biện pháp thi công cho hệ thống Thiết bị mạng truyền thông dữ liệu không dây (WDNE)và hệ thống Hệ thống điện thoại IP (TOIP)</t>
+  </si>
+  <si>
+    <t>WDNE
+TOIP</t>
   </si>
 </sst>
 </file>
@@ -7496,7 +7554,181 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="51" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="52" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="55" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="55" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -7507,15 +7739,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="43" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -7537,170 +7760,20 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="51" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="52" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="55" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="55" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -7720,20 +7793,32 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="53" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="47" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="45" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="58" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -7752,33 +7837,6 @@
     </xf>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="45" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="53" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="47" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -8309,7 +8367,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C724CDAB-378C-47DB-9F45-08EE3BFB6E8B}">
-  <dimension ref="A1:AI167"/>
+  <dimension ref="A1:AI171"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" customWidth="1"/>
@@ -8441,92 +8499,92 @@
       <c r="AE3" s="159"/>
     </row>
     <row r="4" spans="1:35" s="5" customFormat="1" ht="36" customHeight="1" thickBot="1">
-      <c r="A4" s="350" t="s">
+      <c r="A4" s="408" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="406" t="s">
+      <c r="B4" s="348" t="s">
         <v>515</v>
       </c>
-      <c r="C4" s="359" t="s">
+      <c r="C4" s="414" t="s">
         <v>45</v>
       </c>
-      <c r="D4" s="352" t="s">
+      <c r="D4" s="366" t="s">
         <v>95</v>
       </c>
-      <c r="E4" s="348" t="s">
+      <c r="E4" s="369" t="s">
         <v>46</v>
       </c>
-      <c r="F4" s="357" t="s">
+      <c r="F4" s="412" t="s">
         <v>47</v>
       </c>
-      <c r="G4" s="348" t="s">
+      <c r="G4" s="369" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="355" t="s">
+      <c r="H4" s="410" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="352" t="s">
+      <c r="I4" s="366" t="s">
         <v>48</v>
       </c>
-      <c r="J4" s="352" t="s">
+      <c r="J4" s="366" t="s">
         <v>49</v>
       </c>
-      <c r="K4" s="348" t="s">
+      <c r="K4" s="369" t="s">
         <v>78</v>
       </c>
-      <c r="L4" s="352" t="s">
+      <c r="L4" s="366" t="s">
         <v>80</v>
       </c>
-      <c r="M4" s="363" t="s">
+      <c r="M4" s="364" t="s">
         <v>53</v>
       </c>
-      <c r="N4" s="364"/>
-      <c r="O4" s="363" t="s">
+      <c r="N4" s="365"/>
+      <c r="O4" s="364" t="s">
         <v>55</v>
       </c>
-      <c r="P4" s="364"/>
-      <c r="Q4" s="362" t="s">
+      <c r="P4" s="365"/>
+      <c r="Q4" s="368" t="s">
         <v>72</v>
       </c>
-      <c r="R4" s="364"/>
-      <c r="S4" s="363" t="s">
+      <c r="R4" s="365"/>
+      <c r="S4" s="364" t="s">
         <v>53</v>
       </c>
-      <c r="T4" s="363"/>
-      <c r="U4" s="364"/>
-      <c r="V4" s="362" t="s">
+      <c r="T4" s="364"/>
+      <c r="U4" s="365"/>
+      <c r="V4" s="368" t="s">
         <v>55</v>
       </c>
-      <c r="W4" s="363"/>
-      <c r="X4" s="364"/>
-      <c r="Y4" s="415" t="s">
+      <c r="W4" s="364"/>
+      <c r="X4" s="365"/>
+      <c r="Y4" s="371" t="s">
         <v>72</v>
       </c>
-      <c r="Z4" s="416"/>
-      <c r="AA4" s="412" t="s">
+      <c r="Z4" s="372"/>
+      <c r="AA4" s="359" t="s">
         <v>112</v>
       </c>
-      <c r="AB4" s="413"/>
-      <c r="AC4" s="413"/>
-      <c r="AD4" s="414"/>
-      <c r="AE4" s="348" t="s">
+      <c r="AB4" s="360"/>
+      <c r="AC4" s="360"/>
+      <c r="AD4" s="361"/>
+      <c r="AE4" s="369" t="s">
         <v>79</v>
       </c>
       <c r="AG4" s="236"/>
     </row>
     <row r="5" spans="1:35" ht="78.75">
-      <c r="A5" s="351"/>
-      <c r="B5" s="407"/>
-      <c r="C5" s="360"/>
-      <c r="D5" s="353"/>
-      <c r="E5" s="354"/>
-      <c r="F5" s="358"/>
-      <c r="G5" s="354"/>
-      <c r="H5" s="356"/>
-      <c r="I5" s="353"/>
-      <c r="J5" s="353"/>
-      <c r="K5" s="354"/>
-      <c r="L5" s="353"/>
+      <c r="A5" s="409"/>
+      <c r="B5" s="349"/>
+      <c r="C5" s="415"/>
+      <c r="D5" s="367"/>
+      <c r="E5" s="370"/>
+      <c r="F5" s="413"/>
+      <c r="G5" s="370"/>
+      <c r="H5" s="411"/>
+      <c r="I5" s="367"/>
+      <c r="J5" s="367"/>
+      <c r="K5" s="370"/>
+      <c r="L5" s="367"/>
       <c r="M5" s="79" t="s">
         <v>52</v>
       </c>
@@ -8581,14 +8639,14 @@
       <c r="AD5" s="336" t="s">
         <v>118</v>
       </c>
-      <c r="AE5" s="361"/>
-      <c r="AG5" s="348" t="s">
+      <c r="AE5" s="416"/>
+      <c r="AG5" s="369" t="s">
         <v>119</v>
       </c>
-      <c r="AH5" s="348" t="s">
+      <c r="AH5" s="369" t="s">
         <v>120</v>
       </c>
-      <c r="AI5" s="348" t="s">
+      <c r="AI5" s="369" t="s">
         <v>121</v>
       </c>
     </row>
@@ -8624,9 +8682,9 @@
       <c r="AC6" s="86"/>
       <c r="AD6" s="86"/>
       <c r="AE6" s="74"/>
-      <c r="AG6" s="349"/>
-      <c r="AH6" s="349"/>
-      <c r="AI6" s="349"/>
+      <c r="AG6" s="407"/>
+      <c r="AH6" s="407"/>
+      <c r="AI6" s="407"/>
     </row>
     <row r="7" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A7" s="33">
@@ -8735,8 +8793,8 @@
       <c r="AH7" s="242" t="b" cm="1">
         <f t="array" ref="AH7">$E7=_xlfn.XLOOKUP(
 AG7,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -8851,8 +8909,8 @@
       <c r="AH8" s="243" t="b" cm="1">
         <f t="array" ref="AH8">$E8=_xlfn.XLOOKUP(
 AG8,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -8967,8 +9025,8 @@
       <c r="AH9" s="243" t="b" cm="1">
         <f t="array" ref="AH9">$E9=_xlfn.XLOOKUP(
 AG9,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -9085,8 +9143,8 @@
       <c r="AH10" s="243" t="b" cm="1">
         <f t="array" ref="AH10">$E10=_xlfn.XLOOKUP(
 AG10,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -9203,8 +9261,8 @@
       <c r="AH11" s="243" t="b" cm="1">
         <f t="array" ref="AH11">$E11=_xlfn.XLOOKUP(
 AG11,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -9321,8 +9379,8 @@
       <c r="AH12" s="243" t="b" cm="1">
         <f t="array" ref="AH12">$E12=_xlfn.XLOOKUP(
 AG12,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -9439,8 +9497,8 @@
       <c r="AH13" s="243" t="b" cm="1">
         <f t="array" ref="AH13">$E13=_xlfn.XLOOKUP(
 AG13,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -9555,8 +9613,8 @@
       <c r="AH14" s="243" t="b" cm="1">
         <f t="array" ref="AH14">$E14=_xlfn.XLOOKUP(
 AG14,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -9671,8 +9729,8 @@
       <c r="AH15" s="243" t="b" cm="1">
         <f t="array" ref="AH15">$E15=_xlfn.XLOOKUP(
 AG15,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -9789,8 +9847,8 @@
       <c r="AH16" s="243" t="b" cm="1">
         <f t="array" ref="AH16">$E16=_xlfn.XLOOKUP(
 AG16,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -9905,8 +9963,8 @@
       <c r="AH17" s="243" t="b" cm="1">
         <f t="array" ref="AH17">$E17=_xlfn.XLOOKUP(
 AG17,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -10023,8 +10081,8 @@
       <c r="AH18" s="243" t="b" cm="1">
         <f t="array" ref="AH18">$E18=_xlfn.XLOOKUP(
 AG18,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -10141,8 +10199,8 @@
       <c r="AH19" s="243" t="b" cm="1">
         <f t="array" ref="AH19">$E19=_xlfn.XLOOKUP(
 AG19,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -10257,8 +10315,8 @@
       <c r="AH20" s="243" t="b" cm="1">
         <f t="array" ref="AH20">$E20=_xlfn.XLOOKUP(
 AG20,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -10375,8 +10433,8 @@
       <c r="AH21" s="243" t="b" cm="1">
         <f t="array" ref="AH21">$E21=_xlfn.XLOOKUP(
 AG21,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -10493,8 +10551,8 @@
       <c r="AH22" s="243" t="b" cm="1">
         <f t="array" ref="AH22">$E22=_xlfn.XLOOKUP(
 AG22,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -10609,8 +10667,8 @@
       <c r="AH23" s="243" t="b" cm="1">
         <f t="array" ref="AH23">$E23=_xlfn.XLOOKUP(
 AG23,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -10729,8 +10787,8 @@
       <c r="AH24" s="243" t="b" cm="1">
         <f t="array" ref="AH24">$E24=_xlfn.XLOOKUP(
 AG24,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -10845,8 +10903,8 @@
       <c r="AH25" s="243" t="b" cm="1">
         <f t="array" ref="AH25">$E25=_xlfn.XLOOKUP(
 AG25,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -10961,8 +11019,8 @@
       <c r="AH26" s="243" t="b" cm="1">
         <f t="array" ref="AH26">$E26=_xlfn.XLOOKUP(
 AG26,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -11079,8 +11137,8 @@
       <c r="AH27" s="243" t="b" cm="1">
         <f t="array" ref="AH27">$E27=_xlfn.XLOOKUP(
 AG27,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -11197,8 +11255,8 @@
       <c r="AH28" s="243" t="b" cm="1">
         <f t="array" ref="AH28">$E28=_xlfn.XLOOKUP(
 AG28,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -11313,8 +11371,8 @@
       <c r="AH29" s="243" t="b" cm="1">
         <f t="array" ref="AH29">$E29=_xlfn.XLOOKUP(
 AG29,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -11431,8 +11489,8 @@
       <c r="AH30" s="243" t="b" cm="1">
         <f t="array" ref="AH30">$E30=_xlfn.XLOOKUP(
 AG30,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -11549,8 +11607,8 @@
       <c r="AH31" s="243" t="b" cm="1">
         <f t="array" ref="AH31">$E31=_xlfn.XLOOKUP(
 AG31,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -11665,8 +11723,8 @@
       <c r="AH32" s="243" t="b" cm="1">
         <f t="array" ref="AH32">$E32=_xlfn.XLOOKUP(
 AG32,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -11783,8 +11841,8 @@
       <c r="AH33" s="243" t="b" cm="1">
         <f t="array" ref="AH33">$E33=_xlfn.XLOOKUP(
 AG33,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -11899,8 +11957,8 @@
       <c r="AH34" s="243" t="b" cm="1">
         <f t="array" ref="AH34">$E34=_xlfn.XLOOKUP(
 AG34,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -12015,8 +12073,8 @@
       <c r="AH35" s="243" t="b" cm="1">
         <f t="array" ref="AH35">$E35=_xlfn.XLOOKUP(
 AG35,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -12131,8 +12189,8 @@
       <c r="AH36" s="243" t="b" cm="1">
         <f t="array" ref="AH36">$E36=_xlfn.XLOOKUP(
 AG36,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -12247,8 +12305,8 @@
       <c r="AH37" s="243" t="b" cm="1">
         <f t="array" ref="AH37">$E37=_xlfn.XLOOKUP(
 AG37,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -12363,8 +12421,8 @@
       <c r="AH38" s="243" t="b" cm="1">
         <f t="array" ref="AH38">$E38=_xlfn.XLOOKUP(
 AG38,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -12479,8 +12537,8 @@
       <c r="AH39" s="243" t="b" cm="1">
         <f t="array" ref="AH39">$E39=_xlfn.XLOOKUP(
 AG39,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -12595,8 +12653,8 @@
       <c r="AH40" s="243" t="b" cm="1">
         <f t="array" ref="AH40">$E40=_xlfn.XLOOKUP(
 AG40,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -12711,8 +12769,8 @@
       <c r="AH41" s="243" t="b" cm="1">
         <f t="array" ref="AH41">$E41=_xlfn.XLOOKUP(
 AG41,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -12827,8 +12885,8 @@
       <c r="AH42" s="243" t="b" cm="1">
         <f t="array" ref="AH42">$E42=_xlfn.XLOOKUP(
 AG42,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -12943,8 +13001,8 @@
       <c r="AH43" s="243" t="b" cm="1">
         <f t="array" ref="AH43">$E43=_xlfn.XLOOKUP(
 AG43,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -13059,8 +13117,8 @@
       <c r="AH44" s="243" t="b" cm="1">
         <f t="array" ref="AH44">$E44=_xlfn.XLOOKUP(
 AG44,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -13177,8 +13235,8 @@
       <c r="AH45" s="243" t="b" cm="1">
         <f t="array" ref="AH45">$E45=_xlfn.XLOOKUP(
 AG45,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -13293,8 +13351,8 @@
       <c r="AH46" s="243" t="b" cm="1">
         <f t="array" ref="AH46">$E46=_xlfn.XLOOKUP(
 AG46,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -13409,8 +13467,8 @@
       <c r="AH47" s="243" t="b" cm="1">
         <f t="array" ref="AH47">$E47=_xlfn.XLOOKUP(
 AG47,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -13525,8 +13583,8 @@
       <c r="AH48" s="243" t="b" cm="1">
         <f t="array" ref="AH48">$E48=_xlfn.XLOOKUP(
 AG48,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -13643,8 +13701,8 @@
       <c r="AH49" s="243" t="b" cm="1">
         <f t="array" ref="AH49">$E49=_xlfn.XLOOKUP(
 AG49,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -13759,8 +13817,8 @@
       <c r="AH50" s="243" t="b" cm="1">
         <f t="array" ref="AH50">$E50=_xlfn.XLOOKUP(
 AG50,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -13849,8 +13907,8 @@
       <c r="AH51" s="243" t="b" cm="1">
         <f t="array" ref="AH51">$E51=_xlfn.XLOOKUP(
 AG51,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -13967,8 +14025,8 @@
       <c r="AH52" s="243" t="b" cm="1">
         <f t="array" ref="AH52">$E52=_xlfn.XLOOKUP(
 AG52,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -14085,8 +14143,8 @@
       <c r="AH53" s="243" t="b" cm="1">
         <f t="array" ref="AH53">$E53=_xlfn.XLOOKUP(
 AG53,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -14201,8 +14259,8 @@
       <c r="AH54" s="243" t="b" cm="1">
         <f t="array" ref="AH54">$E54=_xlfn.XLOOKUP(
 AG54,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -14317,8 +14375,8 @@
       <c r="AH55" s="243" t="b" cm="1">
         <f t="array" ref="AH55">$E55=_xlfn.XLOOKUP(
 AG55,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -14435,8 +14493,8 @@
       <c r="AH56" s="243" t="b" cm="1">
         <f t="array" ref="AH56">$E56=_xlfn.XLOOKUP(
 AG56,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -14551,8 +14609,8 @@
       <c r="AH57" s="243" t="b" cm="1">
         <f t="array" ref="AH57">$E57=_xlfn.XLOOKUP(
 AG57,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -14667,8 +14725,8 @@
       <c r="AH58" s="243" t="b" cm="1">
         <f t="array" ref="AH58">$E58=_xlfn.XLOOKUP(
 AG58,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -14757,8 +14815,8 @@
       <c r="AH59" s="243" t="b" cm="1">
         <f t="array" ref="AH59">$E59=_xlfn.XLOOKUP(
 AG59,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -14877,8 +14935,8 @@
       <c r="AH60" s="243" t="b" cm="1">
         <f t="array" ref="AH60">$E60=_xlfn.XLOOKUP(
 AG60,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -14993,8 +15051,8 @@
       <c r="AH61" s="243" t="b" cm="1">
         <f t="array" ref="AH61">$E61=_xlfn.XLOOKUP(
 AG61,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -15111,8 +15169,8 @@
       <c r="AH62" s="243" t="b" cm="1">
         <f t="array" ref="AH62">$E62=_xlfn.XLOOKUP(
 AG62,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -15229,8 +15287,8 @@
       <c r="AH63" s="243" t="b" cm="1">
         <f t="array" ref="AH63">$E63=_xlfn.XLOOKUP(
 AG63,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -15347,8 +15405,8 @@
       <c r="AH64" s="243" t="b" cm="1">
         <f t="array" ref="AH64">$E64=_xlfn.XLOOKUP(
 AG64,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -15465,8 +15523,8 @@
       <c r="AH65" s="243" t="b" cm="1">
         <f t="array" ref="AH65">$E65=_xlfn.XLOOKUP(
 AG65,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -15583,8 +15641,8 @@
       <c r="AH66" s="243" t="b" cm="1">
         <f t="array" ref="AH66">$E66=_xlfn.XLOOKUP(
 AG66,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -15699,8 +15757,8 @@
       <c r="AH67" s="243" t="b" cm="1">
         <f t="array" ref="AH67">$E67=_xlfn.XLOOKUP(
 AG67,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -15813,8 +15871,8 @@
       <c r="AH68" s="243" t="b" cm="1">
         <f t="array" ref="AH68">$E68=_xlfn.XLOOKUP(
 AG68,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -15921,8 +15979,8 @@
       <c r="AH69" s="243" t="b" cm="1">
         <f t="array" ref="AH69">$E69=_xlfn.XLOOKUP(
 AG69,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -16037,8 +16095,8 @@
       <c r="AH70" s="243" t="b" cm="1">
         <f t="array" ref="AH70">$E70=_xlfn.XLOOKUP(
 AG70,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -16052,7 +16110,7 @@
     </row>
     <row r="71" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A71" s="33">
-        <f t="shared" ref="A71:A135" si="19">A70+1</f>
+        <f t="shared" ref="A71:A139" si="19">A70+1</f>
         <v>65</v>
       </c>
       <c r="B71" s="330" t="str">
@@ -16153,8 +16211,8 @@
       <c r="AH71" s="243" t="b" cm="1">
         <f t="array" ref="AH71">$E71=_xlfn.XLOOKUP(
 AG71,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -16269,8 +16327,8 @@
       <c r="AH72" s="243" t="b" cm="1">
         <f t="array" ref="AH72">$E72=_xlfn.XLOOKUP(
 AG72,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -16385,8 +16443,8 @@
       <c r="AH73" s="243" t="b" cm="1">
         <f t="array" ref="AH73">$E73=_xlfn.XLOOKUP(
 AG73,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -16503,8 +16561,8 @@
       <c r="AH74" s="243" t="b" cm="1">
         <f t="array" ref="AH74">$E74=_xlfn.XLOOKUP(
 AG74,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -16621,8 +16679,8 @@
       <c r="AH75" s="243" t="b" cm="1">
         <f t="array" ref="AH75">$E75=_xlfn.XLOOKUP(
 AG75,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -16739,8 +16797,8 @@
       <c r="AH76" s="243" t="b" cm="1">
         <f t="array" ref="AH76">$E76=_xlfn.XLOOKUP(
 AG76,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -16857,8 +16915,8 @@
       <c r="AH77" s="243" t="b" cm="1">
         <f t="array" ref="AH77">$E77=_xlfn.XLOOKUP(
 AG77,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -16973,8 +17031,8 @@
       <c r="AH78" s="243" t="b" cm="1">
         <f t="array" ref="AH78">$E78=_xlfn.XLOOKUP(
 AG78,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -17083,8 +17141,8 @@
       <c r="AH79" s="243" t="b" cm="1">
         <f t="array" ref="AH79">$E79=_xlfn.XLOOKUP(
 AG79,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -17193,8 +17251,8 @@
       <c r="AH80" s="243" t="b" cm="1">
         <f t="array" ref="AH80">$E80=_xlfn.XLOOKUP(
 AG80,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -17299,8 +17357,8 @@
       <c r="AH81" s="243" t="b" cm="1">
         <f t="array" ref="AH81">$E81=_xlfn.XLOOKUP(
 AG81,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -17415,8 +17473,8 @@
       <c r="AH82" s="243" t="b" cm="1">
         <f t="array" ref="AH82">$E82=_xlfn.XLOOKUP(
 AG82,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -17504,8 +17562,8 @@
       <c r="AH83" s="243" t="b" cm="1">
         <f t="array" ref="AH83">$E83=_xlfn.XLOOKUP(
 AG83,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -17614,8 +17672,8 @@
       <c r="AH84" s="243" t="b" cm="1">
         <f t="array" ref="AH84">$E84=_xlfn.XLOOKUP(
 AG84,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -17732,8 +17790,8 @@
       <c r="AH85" s="243" t="b" cm="1">
         <f t="array" ref="AH85">$E85=_xlfn.XLOOKUP(
 AG85,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -17842,8 +17900,8 @@
       <c r="AH86" s="243" t="b" cm="1">
         <f t="array" ref="AH86">$E86=_xlfn.XLOOKUP(
 AG86,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -17935,8 +17993,8 @@
       <c r="AH87" s="243" t="b" cm="1">
         <f t="array" ref="AH87">$E87=_xlfn.XLOOKUP(
 AG87,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -18047,8 +18105,8 @@
       <c r="AH88" s="243" t="b" cm="1">
         <f t="array" ref="AH88">$E88=_xlfn.XLOOKUP(
 AG88,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -18159,8 +18217,8 @@
       <c r="AH89" s="243" t="b" cm="1">
         <f t="array" ref="AH89">$E89=_xlfn.XLOOKUP(
 AG89,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -18271,8 +18329,8 @@
       <c r="AH90" s="243" t="b" cm="1">
         <f t="array" ref="AH90">$E90=_xlfn.XLOOKUP(
 AG90,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -18383,8 +18441,8 @@
       <c r="AH91" s="243" t="b" cm="1">
         <f t="array" ref="AH91">$E91=_xlfn.XLOOKUP(
 AG91,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -18481,8 +18539,8 @@
       <c r="AH92" s="243" t="b" cm="1">
         <f t="array" ref="AH92">$E92=_xlfn.XLOOKUP(
 AG92,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -18583,8 +18641,8 @@
       <c r="AH93" s="243" t="b" cm="1">
         <f t="array" ref="AH93">$E93=_xlfn.XLOOKUP(
 AG93,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -18693,8 +18751,8 @@
       <c r="AH94" s="243" t="b" cm="1">
         <f t="array" ref="AH94">$E94=_xlfn.XLOOKUP(
 AG94,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -18782,8 +18840,8 @@
       <c r="AH95" s="243" t="b" cm="1">
         <f t="array" ref="AH95">$E95=_xlfn.XLOOKUP(
 AG95,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -18814,7 +18872,7 @@
         <v>811</v>
       </c>
       <c r="F96" s="174">
-        <f t="shared" ref="F96:F135" si="29">IF($U96=0,$T96+22,$U96+21)</f>
+        <f t="shared" ref="F96:F139" si="29">IF($U96=0,$T96+22,$U96+21)</f>
         <v>46078</v>
       </c>
       <c r="G96" s="31" t="s">
@@ -18827,11 +18885,11 @@
         <v>1</v>
       </c>
       <c r="J96" s="164">
-        <f t="shared" ref="J96:J135" si="30">IF(ISBLANK($W96),_xlfn.DAYS($J$1,$U96),_xlfn.DAYS($W96,$U96))</f>
+        <f t="shared" ref="J96:J139" si="30">IF(ISBLANK($W96),_xlfn.DAYS($J$1,$U96),_xlfn.DAYS($W96,$U96))</f>
         <v>48</v>
       </c>
       <c r="K96" s="47">
-        <f t="shared" ref="K96:K135" si="31">IF(($J96-21)&gt;0,$J96-21,0)</f>
+        <f t="shared" ref="K96:K139" si="31">IF(($J96-21)&gt;0,$J96-21,0)</f>
         <v>27</v>
       </c>
       <c r="L96" s="164"/>
@@ -18892,8 +18950,8 @@
       <c r="AH96" s="243" t="b" cm="1">
         <f t="array" ref="AH96">$E96=_xlfn.XLOOKUP(
 AG96,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -19000,8 +19058,8 @@
       <c r="AH97" s="243" t="b" cm="1">
         <f t="array" ref="AH97">$E97=_xlfn.XLOOKUP(
 AG97,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -19108,8 +19166,8 @@
       <c r="AH98" s="243" t="b" cm="1">
         <f t="array" ref="AH98">$E98=_xlfn.XLOOKUP(
 AG98,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -19220,8 +19278,8 @@
       <c r="AH99" s="243" t="b" cm="1">
         <f t="array" ref="AH99">$E99=_xlfn.XLOOKUP(
 AG99,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -19328,8 +19386,8 @@
       <c r="AH100" s="243" t="b" cm="1">
         <f t="array" ref="AH100">$E100=_xlfn.XLOOKUP(
 AG100,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -19434,8 +19492,8 @@
       <c r="AH101" s="243" t="b" cm="1">
         <f t="array" ref="AH101">$E101=_xlfn.XLOOKUP(
 AG101,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -19526,8 +19584,8 @@
       <c r="AH102" s="243" t="b" cm="1">
         <f t="array" ref="AH102">$E102=_xlfn.XLOOKUP(
 AG102,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -19638,8 +19696,8 @@
       <c r="AH103" s="243" t="b" cm="1">
         <f t="array" ref="AH103">$E103=_xlfn.XLOOKUP(
 AG103,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -19750,8 +19808,8 @@
       <c r="AH104" s="243" t="b" cm="1">
         <f t="array" ref="AH104">$E104=_xlfn.XLOOKUP(
 AG104,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -19862,8 +19920,8 @@
       <c r="AH105" s="243" t="b" cm="1">
         <f t="array" ref="AH105">$E105=_xlfn.XLOOKUP(
 AG105,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -19970,8 +20028,8 @@
       <c r="AH106" s="243" t="b" cm="1">
         <f t="array" ref="AH106">$E106=_xlfn.XLOOKUP(
 AG106,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -20061,8 +20119,8 @@
       <c r="AH107" s="243" t="b" cm="1">
         <f t="array" ref="AH107">$E107=_xlfn.XLOOKUP(
 AG107,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -20167,8 +20225,8 @@
       <c r="AH108" s="243" t="b" cm="1">
         <f t="array" ref="AH108">$E108=_xlfn.XLOOKUP(
 AG108,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -20275,8 +20333,8 @@
       <c r="AH109" s="243" t="b" cm="1">
         <f t="array" ref="AH109">$E109=_xlfn.XLOOKUP(
 AG109,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -20379,8 +20437,8 @@
       <c r="AH110" s="243" t="b" cm="1">
         <f t="array" ref="AH110">$E110=_xlfn.XLOOKUP(
 AG110,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -20477,8 +20535,8 @@
       <c r="AH111" s="243" t="b" cm="1">
         <f t="array" ref="AH111">$E111=_xlfn.XLOOKUP(
 AG111,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -20583,8 +20641,8 @@
       <c r="AH112" s="243" t="b" cm="1">
         <f t="array" ref="AH112">$E112=_xlfn.XLOOKUP(
 AG112,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -20689,8 +20747,8 @@
       <c r="AH113" s="243" t="b" cm="1">
         <f t="array" ref="AH113">$E113=_xlfn.XLOOKUP(
 AG113,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -20795,8 +20853,8 @@
       <c r="AH114" s="243" t="b" cm="1">
         <f t="array" ref="AH114">$E114=_xlfn.XLOOKUP(
 AG114,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -20903,8 +20961,8 @@
       <c r="AH115" s="243" t="b" cm="1">
         <f t="array" ref="AH115">$E115=_xlfn.XLOOKUP(
 AG115,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -21015,8 +21073,8 @@
       <c r="AH116" s="243" t="b" cm="1">
         <f t="array" ref="AH116">$E116=_xlfn.XLOOKUP(
 AG116,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -21111,8 +21169,8 @@
       <c r="AH117" s="243" t="b" cm="1">
         <f t="array" ref="AH117">$E117=_xlfn.XLOOKUP(
 AG117,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -21203,8 +21261,8 @@
       <c r="AH118" s="243" t="b" cm="1">
         <f t="array" ref="AH118">$E118=_xlfn.XLOOKUP(
 AG118,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -21232,7 +21290,7 @@
         <v>28</v>
       </c>
       <c r="E119" s="25" t="s">
-        <v>1067</v>
+        <v>1064</v>
       </c>
       <c r="F119" s="174">
         <f t="shared" si="29"/>
@@ -21311,8 +21369,8 @@
       <c r="AH119" s="243" t="b" cm="1">
         <f t="array" ref="AH119">$E119=_xlfn.XLOOKUP(
 AG119,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -21417,8 +21475,8 @@
       <c r="AH120" s="243" t="b" cm="1">
         <f t="array" ref="AH120">$E120=_xlfn.XLOOKUP(
 AG120,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -21509,8 +21567,8 @@
       <c r="AH121" s="243" t="b" cm="1">
         <f t="array" ref="AH121">$E121=_xlfn.XLOOKUP(
 AG121,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -21593,7 +21651,7 @@
       <c r="Y122" s="230"/>
       <c r="Z122" s="227"/>
       <c r="AA122" s="29">
-        <f t="shared" ref="AA122:AA137" si="68">IF(AND($R122="",$I122=""),"",IF(OR($R122="B",$R122="C"),IF($Z122&lt;&gt;"",$Z122+7,IF($Y122&lt;&gt;"",$Y122+8,"")),IF($R122="",IF(OR($I122="B",$I122="C"),IF($W122&lt;&gt;"",$W122+7,IF($V122&lt;&gt;"",$V122+8,""))),"")))</f>
+        <f t="shared" ref="AA122:AA141" si="68">IF(AND($R122="",$I122=""),"",IF(OR($R122="B",$R122="C"),IF($Z122&lt;&gt;"",$Z122+7,IF($Y122&lt;&gt;"",$Y122+8,"")),IF($R122="",IF(OR($I122="B",$I122="C"),IF($W122&lt;&gt;"",$W122+7,IF($V122&lt;&gt;"",$V122+8,""))),"")))</f>
         <v>46286</v>
       </c>
       <c r="AB122" s="229"/>
@@ -21613,8 +21671,8 @@
       <c r="AH122" s="243" t="b" cm="1">
         <f t="array" ref="AH122">$E122=_xlfn.XLOOKUP(
 AG122,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -21705,8 +21763,8 @@
       <c r="AH123" s="243" t="b" cm="1">
         <f t="array" ref="AH123">$E123=_xlfn.XLOOKUP(
 AG123,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -21811,8 +21869,8 @@
       <c r="AH124" s="243" t="b" cm="1">
         <f t="array" ref="AH124">$E124=_xlfn.XLOOKUP(
 AG124,
-_xlfn._xlws.FILTER($AG$7:$AG$4572,$L$7:$L$4572&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4572,$L$7:$L$4572&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
 "",
 0,
 -1
@@ -21820,7 +21878,7 @@
         <v>1</v>
       </c>
       <c r="AI124" s="75" t="str">
-        <f t="shared" ref="AI124:AI137" si="74">IF($AH124,IF(OR($R124="B",$R124="C"),"YES",IF($R124="",IF(OR($I124="B",$I124="C"),"YES",""),"")),"")</f>
+        <f t="shared" ref="AI124:AI141" si="74">IF($AH124,IF(OR($R124="B",$R124="C"),"YES",IF($R124="",IF(OR($I124="B",$I124="C"),"YES",""),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -21911,14 +21969,14 @@
         <v>1024</v>
       </c>
       <c r="AG125" s="238" t="str">
-        <f t="shared" ref="AG125:AG135" si="75">IF(AND(RIGHT($E125,1)&gt;="A",RIGHT($E125,1)&lt;="Z"),LEFT($E125,LEN($E125)-1),$E125)</f>
+        <f t="shared" ref="AG125:AG139" si="75">IF(AND(RIGHT($E125,1)&gt;="A",RIGHT($E125,1)&lt;="Z"),LEFT($E125,LEN($E125)-1),$E125)</f>
         <v xml:space="preserve"> LTIA-5.11-LTICT-71110-RFA-MAS-0021</v>
       </c>
       <c r="AH125" s="243" t="b" cm="1">
         <f t="array" ref="AH125">$E125=_xlfn.XLOOKUP(
 AG125,
-_xlfn._xlws.FILTER($AG$7:$AG$4573,$L$7:$L$4573&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4573,$L$7:$L$4573&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -22023,8 +22081,8 @@
       <c r="AH126" s="243" t="b" cm="1">
         <f t="array" ref="AH126">$E126=_xlfn.XLOOKUP(
 AG126,
-_xlfn._xlws.FILTER($AG$7:$AG$4573,$L$7:$L$4573&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4573,$L$7:$L$4573&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -22123,8 +22181,8 @@
       <c r="AH127" s="243" t="b" cm="1">
         <f t="array" ref="AH127">$E127=_xlfn.XLOOKUP(
 AG127,
-_xlfn._xlws.FILTER($AG$7:$AG$4573,$L$7:$L$4573&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4573,$L$7:$L$4573&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -22211,8 +22269,8 @@
       <c r="AH128" s="243" t="b" cm="1">
         <f t="array" ref="AH128">$E128=_xlfn.XLOOKUP(
 AG128,
-_xlfn._xlws.FILTER($AG$7:$AG$4573,$L$7:$L$4573&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4573,$L$7:$L$4573&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -22292,7 +22350,7 @@
       <c r="AC129" s="229"/>
       <c r="AD129" s="337"/>
       <c r="AE129" s="92" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="AG129" s="238" t="str">
         <f t="shared" si="75"/>
@@ -22301,8 +22359,8 @@
       <c r="AH129" s="243" t="b" cm="1">
         <f t="array" ref="AH129">$E129=_xlfn.XLOOKUP(
 AG129,
-_xlfn._xlws.FILTER($AG$7:$AG$4573,$L$7:$L$4573&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4573,$L$7:$L$4573&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -22389,8 +22447,8 @@
       <c r="AH130" s="243" t="b" cm="1">
         <f t="array" ref="AH130">$E130=_xlfn.XLOOKUP(
 AG130,
-_xlfn._xlws.FILTER($AG$7:$AG$4573,$L$7:$L$4573&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4573,$L$7:$L$4573&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -22470,7 +22528,7 @@
       <c r="AC131" s="229"/>
       <c r="AD131" s="337"/>
       <c r="AE131" s="92" t="s">
-        <v>1064</v>
+        <v>1073</v>
       </c>
       <c r="AG131" s="238" t="str">
         <f t="shared" si="75"/>
@@ -22479,8 +22537,8 @@
       <c r="AH131" s="243" t="b" cm="1">
         <f t="array" ref="AH131">$E131=_xlfn.XLOOKUP(
 AG131,
-_xlfn._xlws.FILTER($AG$7:$AG$4573,$L$7:$L$4573&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4573,$L$7:$L$4573&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -22560,7 +22618,7 @@
       <c r="AC132" s="229"/>
       <c r="AD132" s="337"/>
       <c r="AE132" s="92" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="AG132" s="238" t="str">
         <f t="shared" si="75"/>
@@ -22569,8 +22627,8 @@
       <c r="AH132" s="243" t="b" cm="1">
         <f t="array" ref="AH132">$E132=_xlfn.XLOOKUP(
 AG132,
-_xlfn._xlws.FILTER($AG$7:$AG$4573,$L$7:$L$4573&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4573,$L$7:$L$4573&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -22657,8 +22715,8 @@
       <c r="AH133" s="243" t="b" cm="1">
         <f t="array" ref="AH133">$E133=_xlfn.XLOOKUP(
 AG133,
-_xlfn._xlws.FILTER($AG$7:$AG$4573,$L$7:$L$4573&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4573,$L$7:$L$4573&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -22745,8 +22803,8 @@
       <c r="AH134" s="243" t="b" cm="1">
         <f t="array" ref="AH134">$E134=_xlfn.XLOOKUP(
 AG134,
-_xlfn._xlws.FILTER($AG$7:$AG$4573,$L$7:$L$4573&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4573,$L$7:$L$4573&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -22764,7 +22822,7 @@
         <v>129</v>
       </c>
       <c r="B135" s="330" t="str">
-        <f t="shared" ref="B135" si="83">MID(E135, FIND("-", E135) + 1, 4)</f>
+        <f t="shared" ref="B135:B136" si="83">MID(E135, FIND("-", E135) + 1, 4)</f>
         <v>5.11</v>
       </c>
       <c r="C135" s="164" t="s">
@@ -22830,7 +22888,7 @@
       <c r="AC135" s="229"/>
       <c r="AD135" s="337"/>
       <c r="AE135" s="92" t="s">
-        <v>1066</v>
+        <v>1070</v>
       </c>
       <c r="AG135" s="238" t="str">
         <f t="shared" si="75"/>
@@ -22839,8 +22897,8 @@
       <c r="AH135" s="243" t="b" cm="1">
         <f t="array" ref="AH135">$E135=_xlfn.XLOOKUP(
 AG135,
-_xlfn._xlws.FILTER($AG$7:$AG$4573,$L$7:$L$4573&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4573,$L$7:$L$4573&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -22852,28 +22910,61 @@
         <v/>
       </c>
     </row>
-    <row r="136" spans="1:35" s="9" customFormat="1">
-      <c r="A136" s="33"/>
-      <c r="B136" s="330"/>
-      <c r="C136" s="164"/>
-      <c r="D136" s="137"/>
-      <c r="E136" s="25"/>
-      <c r="F136" s="174"/>
-      <c r="G136" s="31"/>
-      <c r="H136" s="21"/>
+    <row r="136" spans="1:35" s="9" customFormat="1" ht="47.25">
+      <c r="A136" s="33">
+        <f t="shared" si="19"/>
+        <v>130</v>
+      </c>
+      <c r="B136" s="330" t="str">
+        <f t="shared" si="83"/>
+        <v>5.11</v>
+      </c>
+      <c r="C136" s="164" t="s">
+        <v>751</v>
+      </c>
+      <c r="D136" s="137" t="s">
+        <v>32</v>
+      </c>
+      <c r="E136" s="25" t="s">
+        <v>1074</v>
+      </c>
+      <c r="F136" s="174">
+        <f t="shared" si="29"/>
+        <v>46330</v>
+      </c>
+      <c r="G136" s="31" t="s">
+        <v>1075</v>
+      </c>
+      <c r="H136" s="21" t="s">
+        <v>1076</v>
+      </c>
       <c r="I136" s="138"/>
-      <c r="J136" s="164"/>
-      <c r="K136" s="47"/>
+      <c r="J136" s="164">
+        <f t="shared" ca="1" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="K136" s="47">
+        <f t="shared" ca="1" si="31"/>
+        <v>0</v>
+      </c>
       <c r="L136" s="164"/>
-      <c r="M136" s="40"/>
+      <c r="M136" s="40" t="s">
+        <v>8</v>
+      </c>
       <c r="N136" s="41"/>
       <c r="O136" s="40"/>
       <c r="P136" s="41"/>
       <c r="Q136" s="40"/>
       <c r="R136" s="155"/>
-      <c r="S136" s="27"/>
-      <c r="T136" s="27"/>
-      <c r="U136" s="188"/>
+      <c r="S136" s="27">
+        <v>46309</v>
+      </c>
+      <c r="T136" s="27">
+        <v>46309</v>
+      </c>
+      <c r="U136" s="188">
+        <v>46309</v>
+      </c>
       <c r="V136" s="29"/>
       <c r="W136" s="188"/>
       <c r="X136" s="235"/>
@@ -22887,314 +22978,404 @@
       <c r="AC136" s="229"/>
       <c r="AD136" s="337"/>
       <c r="AE136" s="92"/>
-      <c r="AG136" s="238"/>
-      <c r="AH136" s="243"/>
+      <c r="AG136" s="238" t="str">
+        <f t="shared" si="75"/>
+        <v>LTIA-5.11-LTICT-72040-RFA-MSS-0008</v>
+      </c>
+      <c r="AH136" s="243" t="b" cm="1">
+        <f t="array" ref="AH136">$E136=_xlfn.XLOOKUP(
+AG136,
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+"",
+0,
+-1
+)</f>
+        <v>1</v>
+      </c>
       <c r="AI136" s="75" t="str">
         <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
-    <row r="137" spans="1:35" s="9" customFormat="1" ht="16.5" thickBot="1">
-      <c r="A137" s="347"/>
-      <c r="B137" s="338"/>
-      <c r="C137" s="178"/>
-      <c r="D137" s="139"/>
-      <c r="E137" s="339"/>
-      <c r="F137" s="340"/>
-      <c r="G137" s="32"/>
-      <c r="H137" s="22"/>
-      <c r="I137" s="139"/>
-      <c r="J137" s="178"/>
-      <c r="K137" s="49"/>
-      <c r="L137" s="178"/>
-      <c r="M137" s="341"/>
-      <c r="N137" s="342"/>
-      <c r="O137" s="341"/>
-      <c r="P137" s="342"/>
-      <c r="Q137" s="341"/>
-      <c r="R137" s="343"/>
-      <c r="S137" s="344"/>
-      <c r="T137" s="344"/>
-      <c r="U137" s="345"/>
-      <c r="V137" s="232"/>
-      <c r="W137" s="345"/>
-      <c r="X137" s="258"/>
-      <c r="Y137" s="232"/>
-      <c r="Z137" s="228"/>
-      <c r="AA137" s="232" t="str">
+    <row r="137" spans="1:35" s="9" customFormat="1" ht="47.25">
+      <c r="A137" s="33">
+        <f t="shared" si="19"/>
+        <v>131</v>
+      </c>
+      <c r="B137" s="330" t="str">
+        <f t="shared" ref="B137" si="84">MID(E137, FIND("-", E137) + 1, 4)</f>
+        <v>5.11</v>
+      </c>
+      <c r="C137" s="164" t="s">
+        <v>342</v>
+      </c>
+      <c r="D137" s="137" t="s">
+        <v>32</v>
+      </c>
+      <c r="E137" s="25" t="s">
+        <v>1077</v>
+      </c>
+      <c r="F137" s="174">
+        <f t="shared" si="29"/>
+        <v>46330</v>
+      </c>
+      <c r="G137" s="31" t="s">
+        <v>1078</v>
+      </c>
+      <c r="H137" s="21" t="s">
+        <v>1079</v>
+      </c>
+      <c r="I137" s="138"/>
+      <c r="J137" s="164">
+        <f t="shared" ca="1" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="K137" s="47">
+        <f t="shared" ca="1" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="L137" s="164"/>
+      <c r="M137" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="N137" s="41"/>
+      <c r="O137" s="40"/>
+      <c r="P137" s="41"/>
+      <c r="Q137" s="40"/>
+      <c r="R137" s="155"/>
+      <c r="S137" s="27">
+        <v>46309</v>
+      </c>
+      <c r="T137" s="27">
+        <v>46309</v>
+      </c>
+      <c r="U137" s="188">
+        <v>46309</v>
+      </c>
+      <c r="V137" s="29"/>
+      <c r="W137" s="188"/>
+      <c r="X137" s="235"/>
+      <c r="Y137" s="230"/>
+      <c r="Z137" s="227"/>
+      <c r="AA137" s="29" t="str">
         <f t="shared" si="68"/>
         <v/>
       </c>
-      <c r="AB137" s="233"/>
-      <c r="AC137" s="233"/>
-      <c r="AD137" s="346"/>
-      <c r="AE137" s="93"/>
-      <c r="AG137" s="239"/>
-      <c r="AH137" s="244"/>
-      <c r="AI137" s="241" t="str">
+      <c r="AB137" s="229"/>
+      <c r="AC137" s="229"/>
+      <c r="AD137" s="337"/>
+      <c r="AE137" s="92"/>
+      <c r="AG137" s="238" t="str">
+        <f t="shared" si="75"/>
+        <v>LTIA-5.11-LTICT-72020-RFA-MSS-0009</v>
+      </c>
+      <c r="AH137" s="243" t="b" cm="1">
+        <f t="array" ref="AH137">$E137=_xlfn.XLOOKUP(
+AG137,
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+"",
+0,
+-1
+)</f>
+        <v>1</v>
+      </c>
+      <c r="AI137" s="75" t="str">
         <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
-    <row r="138" spans="1:35" ht="16.5" thickBot="1"/>
-    <row r="139" spans="1:35" ht="16.5" thickBot="1">
-      <c r="A139" s="128"/>
-      <c r="B139" s="128"/>
-      <c r="C139" s="166" t="s">
+    <row r="138" spans="1:35" s="9" customFormat="1" ht="78.75">
+      <c r="A138" s="33">
+        <f t="shared" si="19"/>
+        <v>132</v>
+      </c>
+      <c r="B138" s="330" t="str">
+        <f t="shared" ref="B138" si="85">MID(E138, FIND("-", E138) + 1, 4)</f>
+        <v>5.11</v>
+      </c>
+      <c r="C138" s="164" t="s">
+        <v>1083</v>
+      </c>
+      <c r="D138" s="137" t="s">
+        <v>32</v>
+      </c>
+      <c r="E138" s="25" t="s">
+        <v>1080</v>
+      </c>
+      <c r="F138" s="174">
+        <f t="shared" si="29"/>
+        <v>46330</v>
+      </c>
+      <c r="G138" s="31" t="s">
+        <v>1081</v>
+      </c>
+      <c r="H138" s="21" t="s">
+        <v>1082</v>
+      </c>
+      <c r="I138" s="138"/>
+      <c r="J138" s="164">
+        <f t="shared" ca="1" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="K138" s="47">
+        <f t="shared" ca="1" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="L138" s="164"/>
+      <c r="M138" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="N138" s="41"/>
+      <c r="O138" s="40"/>
+      <c r="P138" s="41"/>
+      <c r="Q138" s="40"/>
+      <c r="R138" s="155"/>
+      <c r="S138" s="27">
+        <v>46309</v>
+      </c>
+      <c r="T138" s="27">
+        <v>46309</v>
+      </c>
+      <c r="U138" s="188">
+        <v>46309</v>
+      </c>
+      <c r="V138" s="29"/>
+      <c r="W138" s="188"/>
+      <c r="X138" s="235"/>
+      <c r="Y138" s="230"/>
+      <c r="Z138" s="227"/>
+      <c r="AA138" s="29" t="str">
+        <f t="shared" si="68"/>
+        <v/>
+      </c>
+      <c r="AB138" s="229"/>
+      <c r="AC138" s="229"/>
+      <c r="AD138" s="337"/>
+      <c r="AE138" s="92"/>
+      <c r="AG138" s="238" t="str">
+        <f t="shared" si="75"/>
+        <v>LTIA-5.11-LTICT-72170-RFA-MSS-0010</v>
+      </c>
+      <c r="AH138" s="243" t="b" cm="1">
+        <f t="array" ref="AH138">$E138=_xlfn.XLOOKUP(
+AG138,
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+"",
+0,
+-1
+)</f>
+        <v>1</v>
+      </c>
+      <c r="AI138" s="75" t="str">
+        <f t="shared" si="74"/>
+        <v/>
+      </c>
+    </row>
+    <row r="139" spans="1:35" s="9" customFormat="1" ht="78.75">
+      <c r="A139" s="33">
+        <f t="shared" si="19"/>
+        <v>133</v>
+      </c>
+      <c r="B139" s="330" t="str">
+        <f t="shared" ref="B139" si="86">MID(E139, FIND("-", E139) + 1, 4)</f>
+        <v>5.11</v>
+      </c>
+      <c r="C139" s="164" t="s">
+        <v>1087</v>
+      </c>
+      <c r="D139" s="137" t="s">
+        <v>32</v>
+      </c>
+      <c r="E139" s="25" t="s">
+        <v>1084</v>
+      </c>
+      <c r="F139" s="174">
+        <f t="shared" si="29"/>
+        <v>46330</v>
+      </c>
+      <c r="G139" s="31" t="s">
+        <v>1085</v>
+      </c>
+      <c r="H139" s="21" t="s">
+        <v>1086</v>
+      </c>
+      <c r="I139" s="138"/>
+      <c r="J139" s="164">
+        <f t="shared" ca="1" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="K139" s="47">
+        <f t="shared" ca="1" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="L139" s="164"/>
+      <c r="M139" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="N139" s="41"/>
+      <c r="O139" s="40"/>
+      <c r="P139" s="41"/>
+      <c r="Q139" s="40"/>
+      <c r="R139" s="155"/>
+      <c r="S139" s="27">
+        <v>46309</v>
+      </c>
+      <c r="T139" s="27">
+        <v>46309</v>
+      </c>
+      <c r="U139" s="188">
+        <v>46309</v>
+      </c>
+      <c r="V139" s="29"/>
+      <c r="W139" s="188"/>
+      <c r="X139" s="235"/>
+      <c r="Y139" s="230"/>
+      <c r="Z139" s="227"/>
+      <c r="AA139" s="29" t="str">
+        <f t="shared" si="68"/>
+        <v/>
+      </c>
+      <c r="AB139" s="229"/>
+      <c r="AC139" s="229"/>
+      <c r="AD139" s="337"/>
+      <c r="AE139" s="92"/>
+      <c r="AG139" s="238" t="str">
+        <f t="shared" si="75"/>
+        <v>LTIA-5.11-LTICT-70000-RFA-MSS-0011</v>
+      </c>
+      <c r="AH139" s="243" t="b" cm="1">
+        <f t="array" ref="AH139">$E139=_xlfn.XLOOKUP(
+AG139,
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+"",
+0,
+-1
+)</f>
+        <v>1</v>
+      </c>
+      <c r="AI139" s="75" t="str">
+        <f t="shared" si="74"/>
+        <v/>
+      </c>
+    </row>
+    <row r="140" spans="1:35" s="9" customFormat="1">
+      <c r="A140" s="33"/>
+      <c r="B140" s="330"/>
+      <c r="C140" s="164"/>
+      <c r="D140" s="137"/>
+      <c r="E140" s="25"/>
+      <c r="F140" s="174"/>
+      <c r="G140" s="31"/>
+      <c r="H140" s="21"/>
+      <c r="I140" s="138"/>
+      <c r="J140" s="164"/>
+      <c r="K140" s="47"/>
+      <c r="L140" s="164"/>
+      <c r="M140" s="40"/>
+      <c r="N140" s="41"/>
+      <c r="O140" s="40"/>
+      <c r="P140" s="41"/>
+      <c r="Q140" s="40"/>
+      <c r="R140" s="155"/>
+      <c r="S140" s="27"/>
+      <c r="T140" s="27"/>
+      <c r="U140" s="188"/>
+      <c r="V140" s="29"/>
+      <c r="W140" s="188"/>
+      <c r="X140" s="235"/>
+      <c r="Y140" s="230"/>
+      <c r="Z140" s="227"/>
+      <c r="AA140" s="29" t="str">
+        <f t="shared" si="68"/>
+        <v/>
+      </c>
+      <c r="AB140" s="229"/>
+      <c r="AC140" s="229"/>
+      <c r="AD140" s="337"/>
+      <c r="AE140" s="92"/>
+      <c r="AG140" s="238"/>
+      <c r="AH140" s="243"/>
+      <c r="AI140" s="75" t="str">
+        <f t="shared" si="74"/>
+        <v/>
+      </c>
+    </row>
+    <row r="141" spans="1:35" s="9" customFormat="1" ht="16.5" thickBot="1">
+      <c r="A141" s="347"/>
+      <c r="B141" s="338"/>
+      <c r="C141" s="178"/>
+      <c r="D141" s="139"/>
+      <c r="E141" s="339"/>
+      <c r="F141" s="340"/>
+      <c r="G141" s="32"/>
+      <c r="H141" s="22"/>
+      <c r="I141" s="139"/>
+      <c r="J141" s="178"/>
+      <c r="K141" s="49"/>
+      <c r="L141" s="178"/>
+      <c r="M141" s="341"/>
+      <c r="N141" s="342"/>
+      <c r="O141" s="341"/>
+      <c r="P141" s="342"/>
+      <c r="Q141" s="341"/>
+      <c r="R141" s="343"/>
+      <c r="S141" s="344"/>
+      <c r="T141" s="344"/>
+      <c r="U141" s="345"/>
+      <c r="V141" s="232"/>
+      <c r="W141" s="345"/>
+      <c r="X141" s="258"/>
+      <c r="Y141" s="232"/>
+      <c r="Z141" s="228"/>
+      <c r="AA141" s="232" t="str">
+        <f t="shared" si="68"/>
+        <v/>
+      </c>
+      <c r="AB141" s="233"/>
+      <c r="AC141" s="233"/>
+      <c r="AD141" s="346"/>
+      <c r="AE141" s="93"/>
+      <c r="AG141" s="239"/>
+      <c r="AH141" s="244"/>
+      <c r="AI141" s="241" t="str">
+        <f t="shared" si="74"/>
+        <v/>
+      </c>
+    </row>
+    <row r="142" spans="1:35" ht="16.5" thickBot="1"/>
+    <row r="143" spans="1:35" ht="16.5" thickBot="1">
+      <c r="A143" s="128"/>
+      <c r="B143" s="128"/>
+      <c r="C143" s="166" t="s">
         <v>20</v>
       </c>
-      <c r="D139" s="379" t="s">
+      <c r="D143" s="376" t="s">
         <v>21</v>
       </c>
-      <c r="E139" s="379"/>
-      <c r="F139" s="380"/>
-      <c r="G139" s="46"/>
-      <c r="H139" s="68"/>
-      <c r="I139" s="384" t="s">
+      <c r="E143" s="376"/>
+      <c r="F143" s="377"/>
+      <c r="G143" s="46"/>
+      <c r="H143" s="68"/>
+      <c r="I143" s="356" t="s">
         <v>14</v>
       </c>
-      <c r="J139" s="385"/>
-      <c r="K139" s="385"/>
-      <c r="L139" s="385"/>
-      <c r="M139" s="385"/>
-      <c r="N139" s="386"/>
-      <c r="O139" s="382" t="s">
+      <c r="J143" s="357"/>
+      <c r="K143" s="357"/>
+      <c r="L143" s="357"/>
+      <c r="M143" s="357"/>
+      <c r="N143" s="358"/>
+      <c r="O143" s="362" t="s">
         <v>7</v>
       </c>
-      <c r="P139" s="383"/>
-      <c r="Q139" s="382" t="s">
+      <c r="P143" s="363"/>
+      <c r="Q143" s="362" t="s">
         <v>109</v>
       </c>
-      <c r="R139" s="383"/>
-      <c r="S139" s="1"/>
-      <c r="T139" s="1"/>
-      <c r="U139" s="140"/>
-      <c r="V139" s="1"/>
-      <c r="X139" s="11"/>
-      <c r="Y139" s="11"/>
-      <c r="Z139" s="11"/>
-      <c r="AA139" s="11"/>
-      <c r="AB139" s="11"/>
-      <c r="AC139" s="11"/>
-      <c r="AD139" s="11"/>
-      <c r="AG139" s="11"/>
-      <c r="AH139" s="11"/>
-      <c r="AI139" s="11"/>
-    </row>
-    <row r="140" spans="1:35" ht="16.5" thickBot="1">
-      <c r="A140" s="128"/>
-      <c r="B140" s="128"/>
-      <c r="C140" s="167" t="s">
-        <v>109</v>
-      </c>
-      <c r="D140" s="404" t="s">
-        <v>111</v>
-      </c>
-      <c r="E140" s="404"/>
-      <c r="F140" s="405"/>
-      <c r="G140" s="46"/>
-      <c r="H140" s="46"/>
-      <c r="I140" s="384" t="s">
-        <v>19</v>
-      </c>
-      <c r="J140" s="385"/>
-      <c r="K140" s="385"/>
-      <c r="L140" s="386"/>
-      <c r="M140" s="105">
-        <f t="shared" ref="M140:M145" ca="1" si="84">N140/$N$140</f>
-        <v>1</v>
-      </c>
-      <c r="N140" s="106">
-        <f ca="1">SUM($N$141:$N$145)</f>
-        <v>135</v>
-      </c>
-      <c r="O140" s="102" t="s">
-        <v>15</v>
-      </c>
-      <c r="P140" s="103" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q140" s="105">
-        <f ca="1">R140/$R$140</f>
-        <v>1</v>
-      </c>
-      <c r="R140" s="220">
-        <f ca="1">SUM(R141:R144)</f>
-        <v>117</v>
-      </c>
-      <c r="S140" s="1"/>
-      <c r="T140" s="1"/>
-      <c r="U140" s="140"/>
-      <c r="V140" s="1"/>
-      <c r="X140" s="11"/>
-      <c r="Y140" s="11"/>
-      <c r="Z140" s="11"/>
-      <c r="AA140" s="11"/>
-      <c r="AB140" s="11"/>
-      <c r="AC140" s="11"/>
-      <c r="AD140" s="11"/>
-      <c r="AG140" s="11"/>
-      <c r="AH140" s="11"/>
-      <c r="AI140" s="11"/>
-    </row>
-    <row r="141" spans="1:35">
-      <c r="A141" s="128"/>
-      <c r="B141" s="128"/>
-      <c r="C141" s="167" t="s">
-        <v>22</v>
-      </c>
-      <c r="D141" s="404" t="s">
-        <v>23</v>
-      </c>
-      <c r="E141" s="404"/>
-      <c r="F141" s="405"/>
-      <c r="G141" s="70"/>
-      <c r="H141" s="6"/>
-      <c r="I141" s="387" t="s">
-        <v>66</v>
-      </c>
-      <c r="J141" s="388"/>
-      <c r="K141" s="388"/>
-      <c r="L141" s="389"/>
-      <c r="M141" s="107">
-        <f t="shared" ca="1" si="84"/>
-        <v>0.51111111111111107</v>
-      </c>
-      <c r="N141" s="108">
-        <f>COUNTIF($I$7:$I$137,"A")</f>
-        <v>69</v>
-      </c>
-      <c r="O141" s="100">
-        <f ca="1">COUNTIFS($J$7:$J$137,"&lt;=21",$I$7:$I$137,"A")</f>
-        <v>56</v>
-      </c>
-      <c r="P141" s="101">
-        <f ca="1">COUNTIFS($J$7:$J$137,"&gt;21",$I$7:$I$137,"A")</f>
-        <v>12</v>
-      </c>
-      <c r="Q141" s="107">
-        <f ca="1">R141/$R$140</f>
-        <v>0.42735042735042733</v>
-      </c>
-      <c r="R141" s="108">
-        <f>COUNTIF($R$7:$R$137,"A")</f>
-        <v>50</v>
-      </c>
-      <c r="S141" s="1"/>
-      <c r="T141" s="1"/>
-      <c r="U141" s="140"/>
-      <c r="V141" s="1"/>
-      <c r="X141" s="11"/>
-      <c r="Y141" s="11"/>
-      <c r="Z141" s="11"/>
-      <c r="AA141" s="11"/>
-      <c r="AB141" s="11"/>
-      <c r="AC141" s="11"/>
-      <c r="AD141" s="11"/>
-      <c r="AG141" s="11"/>
-      <c r="AH141" s="11"/>
-      <c r="AI141" s="11"/>
-    </row>
-    <row r="142" spans="1:35">
-      <c r="A142" s="128"/>
-      <c r="B142" s="128"/>
-      <c r="C142" s="167" t="s">
-        <v>24</v>
-      </c>
-      <c r="D142" s="404" t="s">
-        <v>25</v>
-      </c>
-      <c r="E142" s="404"/>
-      <c r="F142" s="405"/>
-      <c r="H142" s="6"/>
-      <c r="I142" s="390" t="s">
-        <v>67</v>
-      </c>
-      <c r="J142" s="391"/>
-      <c r="K142" s="391"/>
-      <c r="L142" s="392"/>
-      <c r="M142" s="109">
-        <f t="shared" ca="1" si="84"/>
-        <v>0.1037037037037037</v>
-      </c>
-      <c r="N142" s="110">
-        <f>COUNTIF($I$7:$I$137,"B")</f>
-        <v>14</v>
-      </c>
-      <c r="O142" s="98">
-        <f ca="1">COUNTIFS($J$7:$J$137,"&lt;=21",$I$7:$I$137,"B")</f>
-        <v>7</v>
-      </c>
-      <c r="P142" s="50">
-        <f ca="1">COUNTIFS($J$7:$J$137,"&gt;21",$I$7:$I$137,"B")</f>
-        <v>7</v>
-      </c>
-      <c r="Q142" s="109">
-        <f t="shared" ref="Q142:Q144" ca="1" si="85">R142/$R$140</f>
-        <v>7.6923076923076927E-2</v>
-      </c>
-      <c r="R142" s="110">
-        <f>COUNTIF($R$7:$R$137,"B")</f>
-        <v>9</v>
-      </c>
-      <c r="S142" s="1"/>
-      <c r="T142" s="1"/>
-      <c r="U142" s="140"/>
-      <c r="V142" s="1"/>
-      <c r="X142" s="11"/>
-      <c r="Y142" s="11"/>
-      <c r="Z142" s="11"/>
-      <c r="AA142" s="11"/>
-      <c r="AB142" s="11"/>
-      <c r="AC142" s="11"/>
-      <c r="AD142" s="11"/>
-      <c r="AG142" s="11"/>
-      <c r="AH142" s="11"/>
-      <c r="AI142" s="11"/>
-    </row>
-    <row r="143" spans="1:35">
-      <c r="A143" s="129"/>
-      <c r="B143" s="129"/>
-      <c r="C143" s="167" t="s">
-        <v>26</v>
-      </c>
-      <c r="D143" s="404" t="s">
-        <v>27</v>
-      </c>
-      <c r="E143" s="404"/>
-      <c r="F143" s="405"/>
-      <c r="G143" s="71"/>
-      <c r="H143" s="6"/>
-      <c r="I143" s="393" t="s">
-        <v>68</v>
-      </c>
-      <c r="J143" s="394"/>
-      <c r="K143" s="394"/>
-      <c r="L143" s="395"/>
-      <c r="M143" s="111">
-        <f t="shared" ca="1" si="84"/>
-        <v>0.2</v>
-      </c>
-      <c r="N143" s="112">
-        <f>COUNTIF($I$7:$I$137,"C")</f>
-        <v>27</v>
-      </c>
-      <c r="O143" s="98">
-        <f ca="1">COUNTIFS($J$7:$J$137,"&lt;=21",$I$7:$I$137,"C")</f>
-        <v>13</v>
-      </c>
-      <c r="P143" s="50">
-        <f ca="1">COUNTIFS($J$7:$J$137,"&gt;21",$I$7:$I$137,"C")</f>
-        <v>14</v>
-      </c>
-      <c r="Q143" s="111">
-        <f t="shared" ca="1" si="85"/>
-        <v>0.14529914529914531</v>
-      </c>
-      <c r="R143" s="112">
-        <f>COUNTIF($R$7:$R$137,"C")</f>
-        <v>17</v>
-      </c>
+      <c r="R143" s="363"/>
       <c r="S143" s="1"/>
       <c r="T143" s="1"/>
       <c r="U143" s="140"/>
@@ -23210,51 +23391,48 @@
       <c r="AH143" s="11"/>
       <c r="AI143" s="11"/>
     </row>
-    <row r="144" spans="1:35">
-      <c r="A144" s="129"/>
-      <c r="B144" s="129"/>
-      <c r="C144" s="168" t="s">
-        <v>28</v>
-      </c>
-      <c r="D144" s="404" t="s">
-        <v>29</v>
-      </c>
-      <c r="E144" s="404"/>
-      <c r="F144" s="405"/>
-      <c r="G144" s="72"/>
-      <c r="I144" s="396" t="s">
-        <v>70</v>
-      </c>
-      <c r="J144" s="397"/>
-      <c r="K144" s="397"/>
-      <c r="L144" s="398"/>
-      <c r="M144" s="114">
-        <f t="shared" ca="1" si="84"/>
-        <v>7.407407407407407E-2</v>
-      </c>
-      <c r="N144" s="115">
-        <f ca="1">SUM(O144:P144)</f>
-        <v>10</v>
-      </c>
-      <c r="O144" s="98">
-        <f ca="1">COUNTIFS($J$7:$J$137,"&lt;=21",$V$7:$V$137,"",$L$7:$L$137,"&lt;&gt;X")</f>
-        <v>8</v>
-      </c>
-      <c r="P144" s="50">
-        <f ca="1">COUNTIFS($J$7:$J$137,"&gt;21",$V$7:$V$137,"",$L$7:$L$137,"&lt;&gt;X")</f>
-        <v>2</v>
-      </c>
-      <c r="Q144" s="114">
-        <f t="shared" ca="1" si="85"/>
-        <v>0.3504273504273504</v>
-      </c>
-      <c r="R144" s="115">
-        <f ca="1">COUNTIFS($J$7:$J$137,"&gt;=0",$Q$7:$Q$137,"",$L$7:$L$137,"&lt;&gt;X")</f>
-        <v>41</v>
-      </c>
-      <c r="S144" s="1" t="s">
-        <v>10</v>
-      </c>
+    <row r="144" spans="1:35" ht="16.5" thickBot="1">
+      <c r="A144" s="128"/>
+      <c r="B144" s="128"/>
+      <c r="C144" s="167" t="s">
+        <v>109</v>
+      </c>
+      <c r="D144" s="354" t="s">
+        <v>111</v>
+      </c>
+      <c r="E144" s="354"/>
+      <c r="F144" s="355"/>
+      <c r="G144" s="46"/>
+      <c r="H144" s="46"/>
+      <c r="I144" s="356" t="s">
+        <v>19</v>
+      </c>
+      <c r="J144" s="357"/>
+      <c r="K144" s="357"/>
+      <c r="L144" s="358"/>
+      <c r="M144" s="105">
+        <f t="shared" ref="M144:M149" ca="1" si="87">N144/$N$144</f>
+        <v>1</v>
+      </c>
+      <c r="N144" s="106">
+        <f ca="1">SUM($N$145:$N$149)</f>
+        <v>139</v>
+      </c>
+      <c r="O144" s="102" t="s">
+        <v>15</v>
+      </c>
+      <c r="P144" s="103" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q144" s="105">
+        <f ca="1">R144/$R$144</f>
+        <v>1</v>
+      </c>
+      <c r="R144" s="220">
+        <f ca="1">SUM(R145:R148)</f>
+        <v>121</v>
+      </c>
+      <c r="S144" s="1"/>
       <c r="T144" s="1"/>
       <c r="U144" s="140"/>
       <c r="V144" s="1"/>
@@ -23269,186 +23447,293 @@
       <c r="AH144" s="11"/>
       <c r="AI144" s="11"/>
     </row>
-    <row r="145" spans="1:35" ht="16.5" thickBot="1">
-      <c r="A145" s="129"/>
-      <c r="B145" s="129"/>
-      <c r="C145" s="168" t="s">
-        <v>30</v>
-      </c>
-      <c r="D145" s="404" t="s">
-        <v>31</v>
-      </c>
-      <c r="E145" s="404"/>
-      <c r="F145" s="405"/>
+    <row r="145" spans="1:35">
+      <c r="A145" s="128"/>
+      <c r="B145" s="128"/>
+      <c r="C145" s="167" t="s">
+        <v>22</v>
+      </c>
+      <c r="D145" s="354" t="s">
+        <v>23</v>
+      </c>
+      <c r="E145" s="354"/>
+      <c r="F145" s="355"/>
+      <c r="G145" s="70"/>
       <c r="H145" s="6"/>
-      <c r="I145" s="399" t="s">
-        <v>71</v>
-      </c>
-      <c r="J145" s="400"/>
-      <c r="K145" s="400"/>
-      <c r="L145" s="401"/>
-      <c r="M145" s="113">
-        <f t="shared" ca="1" si="84"/>
-        <v>0.1111111111111111</v>
-      </c>
-      <c r="N145" s="97">
-        <f>COUNTIFS($L$7:$L$137,"X")</f>
-        <v>15</v>
-      </c>
-      <c r="O145" s="99"/>
-      <c r="P145" s="51"/>
-      <c r="Q145" s="221"/>
-      <c r="R145" s="222"/>
+      <c r="I145" s="379" t="s">
+        <v>66</v>
+      </c>
+      <c r="J145" s="380"/>
+      <c r="K145" s="380"/>
+      <c r="L145" s="381"/>
+      <c r="M145" s="107">
+        <f t="shared" ca="1" si="87"/>
+        <v>0.49640287769784175</v>
+      </c>
+      <c r="N145" s="108">
+        <f>COUNTIF($I$7:$I$141,"A")</f>
+        <v>69</v>
+      </c>
+      <c r="O145" s="100">
+        <f ca="1">COUNTIFS($J$7:$J$141,"&lt;=21",$I$7:$I$141,"A")</f>
+        <v>56</v>
+      </c>
+      <c r="P145" s="101">
+        <f ca="1">COUNTIFS($J$7:$J$141,"&gt;21",$I$7:$I$141,"A")</f>
+        <v>12</v>
+      </c>
+      <c r="Q145" s="107">
+        <f ca="1">R145/$R$144</f>
+        <v>0.41322314049586778</v>
+      </c>
+      <c r="R145" s="108">
+        <f>COUNTIF($R$7:$R$141,"A")</f>
+        <v>50</v>
+      </c>
+      <c r="S145" s="1"/>
+      <c r="T145" s="1"/>
+      <c r="U145" s="140"/>
+      <c r="V145" s="1"/>
+      <c r="X145" s="11"/>
+      <c r="Y145" s="11"/>
+      <c r="Z145" s="11"/>
+      <c r="AA145" s="11"/>
+      <c r="AB145" s="11"/>
+      <c r="AC145" s="11"/>
+      <c r="AD145" s="11"/>
+      <c r="AG145" s="11"/>
+      <c r="AH145" s="11"/>
+      <c r="AI145" s="11"/>
     </row>
     <row r="146" spans="1:35">
       <c r="A146" s="128"/>
       <c r="B146" s="128"/>
-      <c r="C146" s="168" t="s">
-        <v>32</v>
-      </c>
-      <c r="D146" s="404" t="s">
-        <v>33</v>
-      </c>
-      <c r="E146" s="404"/>
-      <c r="F146" s="405"/>
-      <c r="H146" s="1" t="s">
-        <v>11</v>
-      </c>
+      <c r="C146" s="167" t="s">
+        <v>24</v>
+      </c>
+      <c r="D146" s="354" t="s">
+        <v>25</v>
+      </c>
+      <c r="E146" s="354"/>
+      <c r="F146" s="355"/>
+      <c r="H146" s="6"/>
+      <c r="I146" s="382" t="s">
+        <v>67</v>
+      </c>
+      <c r="J146" s="383"/>
+      <c r="K146" s="383"/>
+      <c r="L146" s="384"/>
+      <c r="M146" s="109">
+        <f t="shared" ca="1" si="87"/>
+        <v>0.10071942446043165</v>
+      </c>
+      <c r="N146" s="110">
+        <f>COUNTIF($I$7:$I$141,"B")</f>
+        <v>14</v>
+      </c>
+      <c r="O146" s="98">
+        <f ca="1">COUNTIFS($J$7:$J$141,"&lt;=21",$I$7:$I$141,"B")</f>
+        <v>7</v>
+      </c>
+      <c r="P146" s="50">
+        <f ca="1">COUNTIFS($J$7:$J$141,"&gt;21",$I$7:$I$141,"B")</f>
+        <v>7</v>
+      </c>
+      <c r="Q146" s="109">
+        <f t="shared" ref="Q146:Q148" ca="1" si="88">R146/$R$144</f>
+        <v>7.43801652892562E-2</v>
+      </c>
+      <c r="R146" s="110">
+        <f>COUNTIF($R$7:$R$141,"B")</f>
+        <v>9</v>
+      </c>
+      <c r="S146" s="1"/>
+      <c r="T146" s="1"/>
+      <c r="U146" s="140"/>
+      <c r="V146" s="1"/>
+      <c r="X146" s="11"/>
+      <c r="Y146" s="11"/>
+      <c r="Z146" s="11"/>
+      <c r="AA146" s="11"/>
+      <c r="AB146" s="11"/>
+      <c r="AC146" s="11"/>
+      <c r="AD146" s="11"/>
+      <c r="AG146" s="11"/>
+      <c r="AH146" s="11"/>
+      <c r="AI146" s="11"/>
     </row>
     <row r="147" spans="1:35">
+      <c r="A147" s="129"/>
+      <c r="B147" s="129"/>
       <c r="C147" s="167" t="s">
-        <v>34</v>
-      </c>
-      <c r="D147" s="404" t="s">
-        <v>35</v>
-      </c>
-      <c r="E147" s="404"/>
-      <c r="F147" s="405"/>
-      <c r="H147" s="13"/>
-      <c r="I147" s="141"/>
-      <c r="J147" s="141"/>
-      <c r="K147" s="13"/>
-      <c r="L147" s="141"/>
-      <c r="M147" s="6"/>
-      <c r="N147" s="6"/>
-      <c r="O147" s="6"/>
-      <c r="P147" s="6"/>
-      <c r="Q147" s="6"/>
-      <c r="S147" s="6"/>
+        <v>26</v>
+      </c>
+      <c r="D147" s="354" t="s">
+        <v>27</v>
+      </c>
+      <c r="E147" s="354"/>
+      <c r="F147" s="355"/>
+      <c r="G147" s="71"/>
+      <c r="H147" s="6"/>
+      <c r="I147" s="385" t="s">
+        <v>68</v>
+      </c>
+      <c r="J147" s="386"/>
+      <c r="K147" s="386"/>
+      <c r="L147" s="387"/>
+      <c r="M147" s="111">
+        <f t="shared" ca="1" si="87"/>
+        <v>0.19424460431654678</v>
+      </c>
+      <c r="N147" s="112">
+        <f>COUNTIF($I$7:$I$141,"C")</f>
+        <v>27</v>
+      </c>
+      <c r="O147" s="98">
+        <f ca="1">COUNTIFS($J$7:$J$141,"&lt;=21",$I$7:$I$141,"C")</f>
+        <v>13</v>
+      </c>
+      <c r="P147" s="50">
+        <f ca="1">COUNTIFS($J$7:$J$141,"&gt;21",$I$7:$I$141,"C")</f>
+        <v>14</v>
+      </c>
+      <c r="Q147" s="111">
+        <f t="shared" ca="1" si="88"/>
+        <v>0.14049586776859505</v>
+      </c>
+      <c r="R147" s="112">
+        <f>COUNTIF($R$7:$R$141,"C")</f>
+        <v>17</v>
+      </c>
+      <c r="S147" s="1"/>
       <c r="T147" s="1"/>
       <c r="U147" s="140"/>
       <c r="V147" s="1"/>
-      <c r="W147" s="140"/>
-      <c r="X147" s="1"/>
-      <c r="Y147" s="1"/>
-      <c r="Z147" s="1"/>
-      <c r="AA147" s="1"/>
-      <c r="AB147" s="1"/>
-      <c r="AC147" s="1"/>
-      <c r="AD147" s="1"/>
-      <c r="AG147" s="160"/>
-      <c r="AH147" s="1"/>
-      <c r="AI147" s="1"/>
+      <c r="X147" s="11"/>
+      <c r="Y147" s="11"/>
+      <c r="Z147" s="11"/>
+      <c r="AA147" s="11"/>
+      <c r="AB147" s="11"/>
+      <c r="AC147" s="11"/>
+      <c r="AD147" s="11"/>
+      <c r="AG147" s="11"/>
+      <c r="AH147" s="11"/>
+      <c r="AI147" s="11"/>
     </row>
     <row r="148" spans="1:35">
-      <c r="C148" s="402" t="s">
-        <v>75</v>
-      </c>
-      <c r="D148" s="408" t="s">
-        <v>76</v>
-      </c>
-      <c r="E148" s="408"/>
-      <c r="F148" s="409"/>
-      <c r="H148" s="13"/>
-      <c r="J148" s="141"/>
-      <c r="K148" s="13"/>
-      <c r="L148" s="141"/>
-      <c r="M148" s="6"/>
-      <c r="N148" s="6"/>
-      <c r="O148" s="6"/>
-      <c r="P148" s="6"/>
-      <c r="Q148" s="6"/>
-      <c r="S148" s="6"/>
+      <c r="A148" s="129"/>
+      <c r="B148" s="129"/>
+      <c r="C148" s="168" t="s">
+        <v>28</v>
+      </c>
+      <c r="D148" s="354" t="s">
+        <v>29</v>
+      </c>
+      <c r="E148" s="354"/>
+      <c r="F148" s="355"/>
+      <c r="G148" s="72"/>
+      <c r="I148" s="388" t="s">
+        <v>70</v>
+      </c>
+      <c r="J148" s="389"/>
+      <c r="K148" s="389"/>
+      <c r="L148" s="390"/>
+      <c r="M148" s="114">
+        <f t="shared" ca="1" si="87"/>
+        <v>0.10071942446043165</v>
+      </c>
+      <c r="N148" s="115">
+        <f ca="1">SUM(O148:P148)</f>
+        <v>14</v>
+      </c>
+      <c r="O148" s="98">
+        <f ca="1">COUNTIFS($J$7:$J$141,"&lt;=21",$V$7:$V$141,"",$L$7:$L$141,"&lt;&gt;X")</f>
+        <v>12</v>
+      </c>
+      <c r="P148" s="50">
+        <f ca="1">COUNTIFS($J$7:$J$141,"&gt;21",$V$7:$V$141,"",$L$7:$L$141,"&lt;&gt;X")</f>
+        <v>2</v>
+      </c>
+      <c r="Q148" s="114">
+        <f t="shared" ca="1" si="88"/>
+        <v>0.37190082644628097</v>
+      </c>
+      <c r="R148" s="115">
+        <f ca="1">COUNTIFS($J$7:$J$141,"&gt;=0",$Q$7:$Q$141,"",$L$7:$L$141,"&lt;&gt;X")</f>
+        <v>45</v>
+      </c>
+      <c r="S148" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="T148" s="1"/>
       <c r="U148" s="140"/>
       <c r="V148" s="1"/>
-      <c r="W148" s="140"/>
-      <c r="X148" s="1"/>
-      <c r="Y148" s="1"/>
-      <c r="Z148" s="1"/>
-      <c r="AA148" s="1"/>
-      <c r="AB148" s="1"/>
-      <c r="AC148" s="1"/>
-      <c r="AD148" s="1"/>
-      <c r="AG148" s="160"/>
-      <c r="AH148" s="1"/>
-      <c r="AI148" s="1"/>
+      <c r="X148" s="11"/>
+      <c r="Y148" s="11"/>
+      <c r="Z148" s="11"/>
+      <c r="AA148" s="11"/>
+      <c r="AB148" s="11"/>
+      <c r="AC148" s="11"/>
+      <c r="AD148" s="11"/>
+      <c r="AG148" s="11"/>
+      <c r="AH148" s="11"/>
+      <c r="AI148" s="11"/>
     </row>
     <row r="149" spans="1:35" ht="16.5" thickBot="1">
-      <c r="C149" s="403"/>
-      <c r="D149" s="410"/>
-      <c r="E149" s="410"/>
-      <c r="F149" s="411"/>
-      <c r="H149" s="13"/>
-      <c r="I149" s="141"/>
-      <c r="J149" s="141"/>
-      <c r="K149" s="13"/>
-      <c r="L149" s="141"/>
-      <c r="M149" s="6"/>
-      <c r="N149" s="6"/>
-      <c r="O149" s="6"/>
-      <c r="P149" s="6"/>
-      <c r="Q149" s="6"/>
-      <c r="S149" s="6"/>
-      <c r="T149" s="1"/>
-      <c r="U149" s="140"/>
-      <c r="V149" s="1"/>
-      <c r="W149" s="140"/>
-      <c r="X149" s="1"/>
-      <c r="Y149" s="1"/>
-      <c r="Z149" s="1"/>
-      <c r="AA149" s="1"/>
-      <c r="AB149" s="1"/>
-      <c r="AC149" s="1"/>
-      <c r="AD149" s="1"/>
-      <c r="AG149" s="160"/>
-      <c r="AH149" s="1"/>
-      <c r="AI149" s="1"/>
+      <c r="A149" s="129"/>
+      <c r="B149" s="129"/>
+      <c r="C149" s="168" t="s">
+        <v>30</v>
+      </c>
+      <c r="D149" s="354" t="s">
+        <v>31</v>
+      </c>
+      <c r="E149" s="354"/>
+      <c r="F149" s="355"/>
+      <c r="H149" s="6"/>
+      <c r="I149" s="391" t="s">
+        <v>71</v>
+      </c>
+      <c r="J149" s="392"/>
+      <c r="K149" s="392"/>
+      <c r="L149" s="393"/>
+      <c r="M149" s="113">
+        <f t="shared" ca="1" si="87"/>
+        <v>0.1079136690647482</v>
+      </c>
+      <c r="N149" s="97">
+        <f>COUNTIFS($L$7:$L$141,"X")</f>
+        <v>15</v>
+      </c>
+      <c r="O149" s="99"/>
+      <c r="P149" s="51"/>
+      <c r="Q149" s="221"/>
+      <c r="R149" s="222"/>
     </row>
     <row r="150" spans="1:35">
-      <c r="H150" s="13"/>
-      <c r="I150" s="141"/>
-      <c r="J150" s="141"/>
-      <c r="K150" s="13"/>
-      <c r="L150" s="141"/>
-      <c r="M150" s="6"/>
-      <c r="N150" s="6"/>
-      <c r="O150" s="6"/>
-      <c r="P150" s="6"/>
-      <c r="Q150" s="6"/>
-      <c r="S150" s="6"/>
-      <c r="T150" s="1"/>
-      <c r="U150" s="140"/>
-      <c r="V150" s="1"/>
-      <c r="W150" s="140"/>
-      <c r="X150" s="1"/>
-      <c r="Y150" s="1"/>
-      <c r="Z150" s="1"/>
-      <c r="AA150" s="1"/>
-      <c r="AB150" s="1"/>
-      <c r="AC150" s="1"/>
-      <c r="AD150" s="1"/>
-      <c r="AG150" s="160"/>
-      <c r="AH150" s="1"/>
-      <c r="AI150" s="1"/>
+      <c r="A150" s="128"/>
+      <c r="B150" s="128"/>
+      <c r="C150" s="168" t="s">
+        <v>32</v>
+      </c>
+      <c r="D150" s="354" t="s">
+        <v>33</v>
+      </c>
+      <c r="E150" s="354"/>
+      <c r="F150" s="355"/>
+      <c r="H150" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="151" spans="1:35">
-      <c r="C151" s="381" t="s">
-        <v>41</v>
-      </c>
-      <c r="D151" s="381"/>
-      <c r="E151" s="381"/>
-      <c r="F151" s="381"/>
+      <c r="C151" s="167" t="s">
+        <v>34</v>
+      </c>
+      <c r="D151" s="354" t="s">
+        <v>35</v>
+      </c>
+      <c r="E151" s="354"/>
+      <c r="F151" s="355"/>
       <c r="H151" s="13"/>
       <c r="I151" s="141"/>
       <c r="J151" s="141"/>
@@ -23476,16 +23761,15 @@
       <c r="AI151" s="1"/>
     </row>
     <row r="152" spans="1:35">
-      <c r="C152" s="169" t="s">
-        <v>8</v>
-      </c>
-      <c r="D152" s="367" t="s">
-        <v>91</v>
-      </c>
-      <c r="E152" s="367"/>
-      <c r="F152" s="367"/>
+      <c r="C152" s="394" t="s">
+        <v>75</v>
+      </c>
+      <c r="D152" s="350" t="s">
+        <v>76</v>
+      </c>
+      <c r="E152" s="350"/>
+      <c r="F152" s="351"/>
       <c r="H152" s="13"/>
-      <c r="I152" s="141"/>
       <c r="J152" s="141"/>
       <c r="K152" s="13"/>
       <c r="L152" s="141"/>
@@ -23510,15 +23794,11 @@
       <c r="AH152" s="1"/>
       <c r="AI152" s="1"/>
     </row>
-    <row r="153" spans="1:35">
-      <c r="C153" s="169" t="s">
-        <v>8</v>
-      </c>
-      <c r="D153" s="367" t="s">
-        <v>92</v>
-      </c>
-      <c r="E153" s="367"/>
-      <c r="F153" s="367"/>
+    <row r="153" spans="1:35" ht="16.5" thickBot="1">
+      <c r="C153" s="395"/>
+      <c r="D153" s="352"/>
+      <c r="E153" s="352"/>
+      <c r="F153" s="353"/>
       <c r="H153" s="13"/>
       <c r="I153" s="141"/>
       <c r="J153" s="141"/>
@@ -23546,14 +23826,6 @@
       <c r="AI153" s="1"/>
     </row>
     <row r="154" spans="1:35">
-      <c r="C154" s="169" t="s">
-        <v>8</v>
-      </c>
-      <c r="D154" s="367" t="s">
-        <v>93</v>
-      </c>
-      <c r="E154" s="367"/>
-      <c r="F154" s="367"/>
       <c r="H154" s="13"/>
       <c r="I154" s="141"/>
       <c r="J154" s="141"/>
@@ -23580,7 +23852,13 @@
       <c r="AH154" s="1"/>
       <c r="AI154" s="1"/>
     </row>
-    <row r="155" spans="1:35" ht="16.5" thickBot="1">
+    <row r="155" spans="1:35">
+      <c r="C155" s="378" t="s">
+        <v>41</v>
+      </c>
+      <c r="D155" s="378"/>
+      <c r="E155" s="378"/>
+      <c r="F155" s="378"/>
       <c r="H155" s="13"/>
       <c r="I155" s="141"/>
       <c r="J155" s="141"/>
@@ -23607,13 +23885,15 @@
       <c r="AH155" s="1"/>
       <c r="AI155" s="1"/>
     </row>
-    <row r="156" spans="1:35" ht="16.5" thickBot="1">
-      <c r="C156" s="371" t="s">
-        <v>96</v>
-      </c>
-      <c r="D156" s="372"/>
-      <c r="E156" s="372"/>
-      <c r="F156" s="373"/>
+    <row r="156" spans="1:35">
+      <c r="C156" s="169" t="s">
+        <v>8</v>
+      </c>
+      <c r="D156" s="396" t="s">
+        <v>91</v>
+      </c>
+      <c r="E156" s="396"/>
+      <c r="F156" s="396"/>
       <c r="H156" s="13"/>
       <c r="I156" s="141"/>
       <c r="J156" s="141"/>
@@ -23641,14 +23921,14 @@
       <c r="AI156" s="1"/>
     </row>
     <row r="157" spans="1:35">
-      <c r="C157" s="212" t="s">
-        <v>81</v>
-      </c>
-      <c r="D157" s="374" t="s">
-        <v>97</v>
-      </c>
-      <c r="E157" s="374"/>
-      <c r="F157" s="375"/>
+      <c r="C157" s="169" t="s">
+        <v>8</v>
+      </c>
+      <c r="D157" s="396" t="s">
+        <v>92</v>
+      </c>
+      <c r="E157" s="396"/>
+      <c r="F157" s="396"/>
       <c r="H157" s="13"/>
       <c r="I157" s="141"/>
       <c r="J157" s="141"/>
@@ -23676,155 +23956,242 @@
       <c r="AI157" s="1"/>
     </row>
     <row r="158" spans="1:35">
-      <c r="C158" s="213" t="s">
+      <c r="C158" s="169" t="s">
+        <v>8</v>
+      </c>
+      <c r="D158" s="396" t="s">
+        <v>93</v>
+      </c>
+      <c r="E158" s="396"/>
+      <c r="F158" s="396"/>
+      <c r="H158" s="13"/>
+      <c r="I158" s="141"/>
+      <c r="J158" s="141"/>
+      <c r="K158" s="13"/>
+      <c r="L158" s="141"/>
+      <c r="M158" s="6"/>
+      <c r="N158" s="6"/>
+      <c r="O158" s="6"/>
+      <c r="P158" s="6"/>
+      <c r="Q158" s="6"/>
+      <c r="S158" s="6"/>
+      <c r="T158" s="1"/>
+      <c r="U158" s="140"/>
+      <c r="V158" s="1"/>
+      <c r="W158" s="140"/>
+      <c r="X158" s="1"/>
+      <c r="Y158" s="1"/>
+      <c r="Z158" s="1"/>
+      <c r="AA158" s="1"/>
+      <c r="AB158" s="1"/>
+      <c r="AC158" s="1"/>
+      <c r="AD158" s="1"/>
+      <c r="AG158" s="160"/>
+      <c r="AH158" s="1"/>
+      <c r="AI158" s="1"/>
+    </row>
+    <row r="159" spans="1:35" ht="16.5" thickBot="1">
+      <c r="H159" s="13"/>
+      <c r="I159" s="141"/>
+      <c r="J159" s="141"/>
+      <c r="K159" s="13"/>
+      <c r="L159" s="141"/>
+      <c r="M159" s="6"/>
+      <c r="N159" s="6"/>
+      <c r="O159" s="6"/>
+      <c r="P159" s="6"/>
+      <c r="Q159" s="6"/>
+      <c r="S159" s="6"/>
+      <c r="T159" s="1"/>
+      <c r="U159" s="140"/>
+      <c r="V159" s="1"/>
+      <c r="W159" s="140"/>
+      <c r="X159" s="1"/>
+      <c r="Y159" s="1"/>
+      <c r="Z159" s="1"/>
+      <c r="AA159" s="1"/>
+      <c r="AB159" s="1"/>
+      <c r="AC159" s="1"/>
+      <c r="AD159" s="1"/>
+      <c r="AG159" s="160"/>
+      <c r="AH159" s="1"/>
+      <c r="AI159" s="1"/>
+    </row>
+    <row r="160" spans="1:35" ht="16.5" thickBot="1">
+      <c r="C160" s="402" t="s">
+        <v>96</v>
+      </c>
+      <c r="D160" s="403"/>
+      <c r="E160" s="403"/>
+      <c r="F160" s="404"/>
+      <c r="H160" s="13"/>
+      <c r="I160" s="141"/>
+      <c r="J160" s="141"/>
+      <c r="K160" s="13"/>
+      <c r="L160" s="141"/>
+      <c r="M160" s="6"/>
+      <c r="N160" s="6"/>
+      <c r="O160" s="6"/>
+      <c r="P160" s="6"/>
+      <c r="Q160" s="6"/>
+      <c r="S160" s="6"/>
+      <c r="T160" s="1"/>
+      <c r="U160" s="140"/>
+      <c r="V160" s="1"/>
+      <c r="W160" s="140"/>
+      <c r="X160" s="1"/>
+      <c r="Y160" s="1"/>
+      <c r="Z160" s="1"/>
+      <c r="AA160" s="1"/>
+      <c r="AB160" s="1"/>
+      <c r="AC160" s="1"/>
+      <c r="AD160" s="1"/>
+      <c r="AG160" s="160"/>
+      <c r="AH160" s="1"/>
+      <c r="AI160" s="1"/>
+    </row>
+    <row r="161" spans="3:35">
+      <c r="C161" s="212" t="s">
+        <v>81</v>
+      </c>
+      <c r="D161" s="405" t="s">
+        <v>97</v>
+      </c>
+      <c r="E161" s="405"/>
+      <c r="F161" s="406"/>
+      <c r="H161" s="13"/>
+      <c r="I161" s="141"/>
+      <c r="J161" s="141"/>
+      <c r="K161" s="13"/>
+      <c r="L161" s="141"/>
+      <c r="M161" s="6"/>
+      <c r="N161" s="6"/>
+      <c r="O161" s="6"/>
+      <c r="P161" s="6"/>
+      <c r="Q161" s="6"/>
+      <c r="S161" s="6"/>
+      <c r="T161" s="1"/>
+      <c r="U161" s="140"/>
+      <c r="V161" s="1"/>
+      <c r="W161" s="140"/>
+      <c r="X161" s="1"/>
+      <c r="Y161" s="1"/>
+      <c r="Z161" s="1"/>
+      <c r="AA161" s="1"/>
+      <c r="AB161" s="1"/>
+      <c r="AC161" s="1"/>
+      <c r="AD161" s="1"/>
+      <c r="AG161" s="160"/>
+      <c r="AH161" s="1"/>
+      <c r="AI161" s="1"/>
+    </row>
+    <row r="162" spans="3:35">
+      <c r="C162" s="213" t="s">
         <v>82</v>
       </c>
-      <c r="D158" s="365" t="s">
+      <c r="D162" s="397" t="s">
         <v>98</v>
       </c>
-      <c r="E158" s="365"/>
-      <c r="F158" s="366"/>
-    </row>
-    <row r="159" spans="1:35">
-      <c r="C159" s="213" t="s">
+      <c r="E162" s="397"/>
+      <c r="F162" s="398"/>
+    </row>
+    <row r="163" spans="3:35">
+      <c r="C163" s="213" t="s">
         <v>83</v>
       </c>
-      <c r="D159" s="365" t="s">
+      <c r="D163" s="397" t="s">
         <v>99</v>
       </c>
-      <c r="E159" s="365"/>
-      <c r="F159" s="366"/>
-    </row>
-    <row r="160" spans="1:35">
-      <c r="C160" s="214" t="s">
+      <c r="E163" s="397"/>
+      <c r="F163" s="398"/>
+    </row>
+    <row r="164" spans="3:35">
+      <c r="C164" s="214" t="s">
         <v>84</v>
       </c>
-      <c r="D160" s="365" t="s">
+      <c r="D164" s="397" t="s">
         <v>100</v>
       </c>
-      <c r="E160" s="365"/>
-      <c r="F160" s="366"/>
-    </row>
-    <row r="161" spans="3:6">
-      <c r="C161" s="214" t="s">
+      <c r="E164" s="397"/>
+      <c r="F164" s="398"/>
+    </row>
+    <row r="165" spans="3:35">
+      <c r="C165" s="214" t="s">
         <v>85</v>
       </c>
-      <c r="D161" s="365" t="s">
+      <c r="D165" s="397" t="s">
         <v>101</v>
       </c>
-      <c r="E161" s="365"/>
-      <c r="F161" s="366"/>
-    </row>
-    <row r="162" spans="3:6" ht="18.75">
-      <c r="C162" s="214" t="s">
+      <c r="E165" s="397"/>
+      <c r="F165" s="398"/>
+    </row>
+    <row r="166" spans="3:35" ht="18.75">
+      <c r="C166" s="214" t="s">
         <v>86</v>
       </c>
-      <c r="D162" s="365" t="s">
+      <c r="D166" s="397" t="s">
         <v>102</v>
       </c>
-      <c r="E162" s="365"/>
-      <c r="F162" s="366"/>
-    </row>
-    <row r="163" spans="3:6" ht="18.75">
-      <c r="C163" s="213" t="s">
+      <c r="E166" s="397"/>
+      <c r="F166" s="398"/>
+    </row>
+    <row r="167" spans="3:35" ht="18.75">
+      <c r="C167" s="213" t="s">
         <v>87</v>
       </c>
-      <c r="D163" s="365" t="s">
+      <c r="D167" s="397" t="s">
         <v>103</v>
       </c>
-      <c r="E163" s="365"/>
-      <c r="F163" s="366"/>
-    </row>
-    <row r="164" spans="3:6">
-      <c r="C164" s="215" t="s">
+      <c r="E167" s="397"/>
+      <c r="F167" s="398"/>
+    </row>
+    <row r="168" spans="3:35">
+      <c r="C168" s="215" t="s">
         <v>88</v>
       </c>
-      <c r="D164" s="368" t="s">
+      <c r="D168" s="399" t="s">
         <v>104</v>
       </c>
-      <c r="E164" s="369"/>
-      <c r="F164" s="370"/>
-    </row>
-    <row r="165" spans="3:6" ht="18.75">
-      <c r="C165" s="215" t="s">
+      <c r="E168" s="400"/>
+      <c r="F168" s="401"/>
+    </row>
+    <row r="169" spans="3:35" ht="18.75">
+      <c r="C169" s="215" t="s">
         <v>89</v>
       </c>
-      <c r="D165" s="365" t="s">
+      <c r="D169" s="397" t="s">
         <v>105</v>
       </c>
-      <c r="E165" s="365"/>
-      <c r="F165" s="366"/>
-    </row>
-    <row r="166" spans="3:6">
-      <c r="C166" s="213" t="s">
+      <c r="E169" s="397"/>
+      <c r="F169" s="398"/>
+    </row>
+    <row r="170" spans="3:35">
+      <c r="C170" s="213" t="s">
         <v>90</v>
       </c>
-      <c r="D166" s="365" t="s">
+      <c r="D170" s="397" t="s">
         <v>106</v>
       </c>
-      <c r="E166" s="365"/>
-      <c r="F166" s="366"/>
-    </row>
-    <row r="167" spans="3:6" ht="16.5" thickBot="1">
-      <c r="C167" s="216" t="s">
+      <c r="E170" s="397"/>
+      <c r="F170" s="398"/>
+    </row>
+    <row r="171" spans="3:35" ht="16.5" thickBot="1">
+      <c r="C171" s="216" t="s">
         <v>94</v>
       </c>
-      <c r="D167" s="376" t="s">
+      <c r="D171" s="373" t="s">
         <v>107</v>
       </c>
-      <c r="E167" s="377"/>
-      <c r="F167" s="378"/>
+      <c r="E171" s="374"/>
+      <c r="F171" s="375"/>
     </row>
   </sheetData>
-  <autoFilter ref="A6:AE137" xr:uid="{C724CDAB-378C-47DB-9F45-08EE3BFB6E8B}">
+  <autoFilter ref="A6:AE141" xr:uid="{C724CDAB-378C-47DB-9F45-08EE3BFB6E8B}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A7:AE69">
       <sortCondition ref="T6:T69"/>
     </sortState>
   </autoFilter>
   <mergeCells count="59">
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="D148:F149"/>
-    <mergeCell ref="D140:F140"/>
-    <mergeCell ref="I140:L140"/>
-    <mergeCell ref="AA4:AD4"/>
-    <mergeCell ref="Q139:R139"/>
-    <mergeCell ref="D145:F145"/>
-    <mergeCell ref="D146:F146"/>
-    <mergeCell ref="D147:F147"/>
-    <mergeCell ref="S4:U4"/>
-    <mergeCell ref="L4:L5"/>
-    <mergeCell ref="Q4:R4"/>
-    <mergeCell ref="K4:K5"/>
-    <mergeCell ref="Y4:Z4"/>
-    <mergeCell ref="D167:F167"/>
-    <mergeCell ref="D139:F139"/>
-    <mergeCell ref="C151:F151"/>
-    <mergeCell ref="O139:P139"/>
-    <mergeCell ref="I139:N139"/>
-    <mergeCell ref="I141:L141"/>
-    <mergeCell ref="I142:L142"/>
-    <mergeCell ref="I143:L143"/>
-    <mergeCell ref="I144:L144"/>
-    <mergeCell ref="I145:L145"/>
-    <mergeCell ref="C148:C149"/>
-    <mergeCell ref="D141:F141"/>
-    <mergeCell ref="D142:F142"/>
-    <mergeCell ref="D143:F143"/>
-    <mergeCell ref="D144:F144"/>
-    <mergeCell ref="D152:F152"/>
-    <mergeCell ref="D166:F166"/>
-    <mergeCell ref="D153:F153"/>
-    <mergeCell ref="D154:F154"/>
-    <mergeCell ref="D161:F161"/>
-    <mergeCell ref="D162:F162"/>
-    <mergeCell ref="D163:F163"/>
-    <mergeCell ref="D164:F164"/>
-    <mergeCell ref="D165:F165"/>
-    <mergeCell ref="C156:F156"/>
-    <mergeCell ref="D157:F157"/>
-    <mergeCell ref="D158:F158"/>
-    <mergeCell ref="D159:F159"/>
-    <mergeCell ref="D160:F160"/>
     <mergeCell ref="AG5:AG6"/>
     <mergeCell ref="AH5:AH6"/>
     <mergeCell ref="AI5:AI6"/>
@@ -23841,9 +24208,52 @@
     <mergeCell ref="V4:X4"/>
     <mergeCell ref="M4:N4"/>
     <mergeCell ref="O4:P4"/>
+    <mergeCell ref="D170:F170"/>
+    <mergeCell ref="D157:F157"/>
+    <mergeCell ref="D158:F158"/>
+    <mergeCell ref="D165:F165"/>
+    <mergeCell ref="D166:F166"/>
+    <mergeCell ref="D167:F167"/>
+    <mergeCell ref="D168:F168"/>
+    <mergeCell ref="D169:F169"/>
+    <mergeCell ref="C160:F160"/>
+    <mergeCell ref="D161:F161"/>
+    <mergeCell ref="D162:F162"/>
+    <mergeCell ref="D163:F163"/>
+    <mergeCell ref="D164:F164"/>
+    <mergeCell ref="D171:F171"/>
+    <mergeCell ref="D143:F143"/>
+    <mergeCell ref="C155:F155"/>
+    <mergeCell ref="O143:P143"/>
+    <mergeCell ref="I143:N143"/>
+    <mergeCell ref="I145:L145"/>
+    <mergeCell ref="I146:L146"/>
+    <mergeCell ref="I147:L147"/>
+    <mergeCell ref="I148:L148"/>
+    <mergeCell ref="I149:L149"/>
+    <mergeCell ref="C152:C153"/>
+    <mergeCell ref="D145:F145"/>
+    <mergeCell ref="D146:F146"/>
+    <mergeCell ref="D147:F147"/>
+    <mergeCell ref="D148:F148"/>
+    <mergeCell ref="D156:F156"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="D152:F153"/>
+    <mergeCell ref="D144:F144"/>
+    <mergeCell ref="I144:L144"/>
+    <mergeCell ref="AA4:AD4"/>
+    <mergeCell ref="Q143:R143"/>
+    <mergeCell ref="D149:F149"/>
+    <mergeCell ref="D150:F150"/>
+    <mergeCell ref="D151:F151"/>
+    <mergeCell ref="S4:U4"/>
+    <mergeCell ref="L4:L5"/>
+    <mergeCell ref="Q4:R4"/>
+    <mergeCell ref="K4:K5"/>
+    <mergeCell ref="Y4:Z4"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
-  <conditionalFormatting sqref="A7:AE137 AG7:AI137">
+  <conditionalFormatting sqref="A7:AE141 AG7:AI141">
     <cfRule type="expression" dxfId="18" priority="15" stopIfTrue="1">
       <formula>$L7="X"</formula>
     </cfRule>
@@ -24103,9 +24513,9 @@
     <hyperlink ref="P66" r:id="rId234" xr:uid="{943197F0-AD92-4E20-ACB9-85E2FC8AC2B6}"/>
     <hyperlink ref="P68" r:id="rId235" xr:uid="{B8D8E563-954E-4146-81D8-6B9C7FA5754F}"/>
     <hyperlink ref="P69" r:id="rId236" xr:uid="{B36E752F-3B1E-43A8-9FDB-009F10632DBE}"/>
-    <hyperlink ref="C152" r:id="rId237" xr:uid="{8E310CD5-A28F-4463-BCF0-54C44E66ED53}"/>
-    <hyperlink ref="C153" r:id="rId238" xr:uid="{5182D641-FE70-4AC5-A684-B03DCC409CD2}"/>
-    <hyperlink ref="C154" r:id="rId239" xr:uid="{1AA76CB8-C0E3-43B4-9061-99A680A3D3C7}"/>
+    <hyperlink ref="C156" r:id="rId237" xr:uid="{8E310CD5-A28F-4463-BCF0-54C44E66ED53}"/>
+    <hyperlink ref="C157" r:id="rId238" xr:uid="{5182D641-FE70-4AC5-A684-B03DCC409CD2}"/>
+    <hyperlink ref="C158" r:id="rId239" xr:uid="{1AA76CB8-C0E3-43B4-9061-99A680A3D3C7}"/>
     <hyperlink ref="Q7" r:id="rId240" xr:uid="{D3D10629-3F3E-4216-8F11-F525BC7A698A}"/>
     <hyperlink ref="Q8" r:id="rId241" xr:uid="{91F15092-AC5D-4C7E-9E23-E3913E29C1F3}"/>
     <hyperlink ref="Q9" r:id="rId242" xr:uid="{381D2B0A-72F0-4FCE-A724-4D1E565A253A}"/>
@@ -24365,9 +24775,13 @@
     <hyperlink ref="M133" r:id="rId496" xr:uid="{ECCF68AE-AB34-47D5-8D2A-7325D8660689}"/>
     <hyperlink ref="M134" r:id="rId497" xr:uid="{CB8AF97E-9DC3-471D-83EC-AD597E73F69A}"/>
     <hyperlink ref="M135" r:id="rId498" xr:uid="{80B00F06-D45F-42B9-8E93-41FF6E915245}"/>
+    <hyperlink ref="M136" r:id="rId499" xr:uid="{E9C2C5E6-4341-4C30-94FD-9FFC2168AE7E}"/>
+    <hyperlink ref="M137" r:id="rId500" xr:uid="{796282C8-8FC2-4043-A523-A0A91C9DD849}"/>
+    <hyperlink ref="M138" r:id="rId501" xr:uid="{24F8F9C1-0497-4EC1-849F-4BFB6EF701D0}"/>
+    <hyperlink ref="M139" r:id="rId502" xr:uid="{D1C7F371-1906-4C4E-9D64-07CD74AF282A}"/>
   </hyperlinks>
   <pageMargins left="0.25" right="0.17" top="0.5" bottom="0.25" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="28" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId499"/>
+  <pageSetup paperSize="9" scale="28" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId503"/>
   <colBreaks count="1" manualBreakCount="1">
     <brk id="30" max="564" man="1"/>
   </colBreaks>
@@ -24397,7 +24811,7 @@
     <col min="23" max="27" width="16.42578125" style="6" customWidth="1"/>
     <col min="28" max="28" width="18.42578125" style="6" customWidth="1"/>
     <col min="29" max="29" width="16.42578125" style="6" customWidth="1"/>
-    <col min="30" max="30" width="35.28515625" style="160" customWidth="1"/>
+    <col min="30" max="30" width="42.7109375" style="160" customWidth="1"/>
     <col min="31" max="31" width="9.140625" style="1"/>
     <col min="32" max="32" width="9.140625" style="1" customWidth="1"/>
     <col min="33" max="33" width="18.42578125" style="219" customWidth="1"/>
@@ -24505,88 +24919,88 @@
       <c r="AD3" s="159"/>
     </row>
     <row r="4" spans="1:35" s="5" customFormat="1" ht="36" customHeight="1" thickBot="1">
-      <c r="A4" s="350" t="s">
+      <c r="A4" s="408" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="406" t="s">
+      <c r="B4" s="348" t="s">
         <v>515</v>
       </c>
-      <c r="C4" s="359" t="s">
+      <c r="C4" s="414" t="s">
         <v>45</v>
       </c>
-      <c r="D4" s="348" t="s">
+      <c r="D4" s="369" t="s">
         <v>46</v>
       </c>
-      <c r="E4" s="357" t="s">
+      <c r="E4" s="412" t="s">
         <v>47</v>
       </c>
-      <c r="F4" s="348" t="s">
+      <c r="F4" s="369" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="355" t="s">
+      <c r="G4" s="410" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="352" t="s">
+      <c r="H4" s="366" t="s">
         <v>48</v>
       </c>
-      <c r="I4" s="352" t="s">
+      <c r="I4" s="366" t="s">
         <v>49</v>
       </c>
-      <c r="J4" s="348" t="s">
+      <c r="J4" s="369" t="s">
         <v>78</v>
       </c>
-      <c r="K4" s="352" t="s">
+      <c r="K4" s="366" t="s">
         <v>80</v>
       </c>
-      <c r="L4" s="363" t="s">
+      <c r="L4" s="364" t="s">
         <v>53</v>
       </c>
-      <c r="M4" s="364"/>
-      <c r="N4" s="362" t="s">
+      <c r="M4" s="365"/>
+      <c r="N4" s="368" t="s">
         <v>55</v>
       </c>
-      <c r="O4" s="364"/>
-      <c r="P4" s="362" t="s">
+      <c r="O4" s="365"/>
+      <c r="P4" s="368" t="s">
         <v>72</v>
       </c>
-      <c r="Q4" s="364"/>
-      <c r="R4" s="363" t="s">
+      <c r="Q4" s="365"/>
+      <c r="R4" s="364" t="s">
         <v>53</v>
       </c>
-      <c r="S4" s="363"/>
-      <c r="T4" s="364"/>
-      <c r="U4" s="362" t="s">
+      <c r="S4" s="364"/>
+      <c r="T4" s="365"/>
+      <c r="U4" s="368" t="s">
         <v>55</v>
       </c>
-      <c r="V4" s="363"/>
-      <c r="W4" s="364"/>
-      <c r="X4" s="415" t="s">
+      <c r="V4" s="364"/>
+      <c r="W4" s="365"/>
+      <c r="X4" s="371" t="s">
         <v>72</v>
       </c>
-      <c r="Y4" s="427"/>
-      <c r="Z4" s="415" t="s">
+      <c r="Y4" s="417"/>
+      <c r="Z4" s="371" t="s">
         <v>112</v>
       </c>
-      <c r="AA4" s="413"/>
-      <c r="AB4" s="413"/>
-      <c r="AC4" s="414"/>
-      <c r="AD4" s="348" t="s">
+      <c r="AA4" s="360"/>
+      <c r="AB4" s="360"/>
+      <c r="AC4" s="361"/>
+      <c r="AD4" s="369" t="s">
         <v>79</v>
       </c>
       <c r="AG4" s="236"/>
     </row>
     <row r="5" spans="1:35" ht="78.75">
-      <c r="A5" s="351"/>
-      <c r="B5" s="407"/>
-      <c r="C5" s="360"/>
-      <c r="D5" s="354"/>
-      <c r="E5" s="358"/>
-      <c r="F5" s="354"/>
-      <c r="G5" s="356"/>
-      <c r="H5" s="353"/>
-      <c r="I5" s="353"/>
-      <c r="J5" s="354"/>
-      <c r="K5" s="353"/>
+      <c r="A5" s="409"/>
+      <c r="B5" s="349"/>
+      <c r="C5" s="415"/>
+      <c r="D5" s="370"/>
+      <c r="E5" s="413"/>
+      <c r="F5" s="370"/>
+      <c r="G5" s="411"/>
+      <c r="H5" s="367"/>
+      <c r="I5" s="367"/>
+      <c r="J5" s="370"/>
+      <c r="K5" s="367"/>
       <c r="L5" s="79" t="s">
         <v>52</v>
       </c>
@@ -24641,14 +25055,14 @@
       <c r="AC5" s="250" t="s">
         <v>118</v>
       </c>
-      <c r="AD5" s="361"/>
-      <c r="AG5" s="417" t="s">
+      <c r="AD5" s="416"/>
+      <c r="AG5" s="422" t="s">
         <v>119</v>
       </c>
-      <c r="AH5" s="419" t="s">
+      <c r="AH5" s="424" t="s">
         <v>120</v>
       </c>
-      <c r="AI5" s="421" t="s">
+      <c r="AI5" s="426" t="s">
         <v>121</v>
       </c>
     </row>
@@ -24683,9 +25097,9 @@
       <c r="AB6" s="86"/>
       <c r="AC6" s="86"/>
       <c r="AD6" s="74"/>
-      <c r="AG6" s="418"/>
-      <c r="AH6" s="420"/>
-      <c r="AI6" s="422"/>
+      <c r="AG6" s="423"/>
+      <c r="AH6" s="425"/>
+      <c r="AI6" s="427"/>
     </row>
     <row r="7" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A7" s="33">
@@ -27886,7 +28300,7 @@
         <v/>
       </c>
       <c r="AD35" s="92" t="s">
-        <v>1056</v>
+        <v>1068</v>
       </c>
       <c r="AG35" s="238" t="str">
         <f t="shared" si="8"/>
@@ -28280,7 +28694,7 @@
         <v/>
       </c>
       <c r="AD39" s="92" t="s">
-        <v>1056</v>
+        <v>1068</v>
       </c>
       <c r="AG39" s="238" t="str">
         <f t="shared" si="8"/>
@@ -28313,17 +28727,17 @@
       </c>
       <c r="C40" s="164"/>
       <c r="D40" s="25" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="E40" s="174">
         <f t="shared" si="2"/>
         <v>46330</v>
       </c>
       <c r="F40" s="31" t="s">
+        <v>1060</v>
+      </c>
+      <c r="G40" s="21" t="s">
         <v>1061</v>
-      </c>
-      <c r="G40" s="21" t="s">
-        <v>1062</v>
       </c>
       <c r="H40" s="138"/>
       <c r="I40" s="164">
@@ -28472,28 +28886,28 @@
       <c r="C44" s="166" t="s">
         <v>20</v>
       </c>
-      <c r="D44" s="379" t="s">
+      <c r="D44" s="376" t="s">
         <v>21</v>
       </c>
-      <c r="E44" s="380"/>
+      <c r="E44" s="377"/>
       <c r="F44" s="46"/>
       <c r="G44" s="46"/>
-      <c r="H44" s="384" t="s">
+      <c r="H44" s="356" t="s">
         <v>14</v>
       </c>
-      <c r="I44" s="385"/>
-      <c r="J44" s="385"/>
-      <c r="K44" s="385"/>
-      <c r="L44" s="385"/>
-      <c r="M44" s="386"/>
-      <c r="N44" s="382" t="s">
+      <c r="I44" s="357"/>
+      <c r="J44" s="357"/>
+      <c r="K44" s="357"/>
+      <c r="L44" s="357"/>
+      <c r="M44" s="358"/>
+      <c r="N44" s="362" t="s">
         <v>7</v>
       </c>
-      <c r="O44" s="383"/>
-      <c r="P44" s="382" t="s">
+      <c r="O44" s="363"/>
+      <c r="P44" s="362" t="s">
         <v>109</v>
       </c>
-      <c r="Q44" s="383"/>
+      <c r="Q44" s="363"/>
       <c r="R44" s="1"/>
       <c r="S44" s="1"/>
       <c r="T44" s="140"/>
@@ -28513,17 +28927,17 @@
       <c r="C45" s="195" t="s">
         <v>109</v>
       </c>
-      <c r="D45" s="425" t="s">
+      <c r="D45" s="420" t="s">
         <v>111</v>
       </c>
-      <c r="E45" s="426"/>
+      <c r="E45" s="421"/>
       <c r="F45" s="46"/>
-      <c r="H45" s="384" t="s">
+      <c r="H45" s="356" t="s">
         <v>18</v>
       </c>
-      <c r="I45" s="385"/>
-      <c r="J45" s="385"/>
-      <c r="K45" s="386"/>
+      <c r="I45" s="357"/>
+      <c r="J45" s="357"/>
+      <c r="K45" s="358"/>
       <c r="L45" s="105">
         <f ca="1">M45/$M$45</f>
         <v>1</v>
@@ -28565,18 +28979,18 @@
       <c r="C46" s="195" t="s">
         <v>36</v>
       </c>
-      <c r="D46" s="423" t="s">
+      <c r="D46" s="418" t="s">
         <v>37</v>
       </c>
-      <c r="E46" s="424"/>
+      <c r="E46" s="419"/>
       <c r="F46" s="69"/>
       <c r="G46" s="6"/>
-      <c r="H46" s="387" t="s">
+      <c r="H46" s="379" t="s">
         <v>66</v>
       </c>
-      <c r="I46" s="388"/>
-      <c r="J46" s="388"/>
-      <c r="K46" s="389"/>
+      <c r="I46" s="380"/>
+      <c r="J46" s="380"/>
+      <c r="K46" s="381"/>
       <c r="L46" s="107">
         <f ca="1">M46/$M$45</f>
         <v>2.7777777777777776E-2</v>
@@ -28617,21 +29031,21 @@
       <c r="AI46" s="11"/>
     </row>
     <row r="47" spans="1:35">
-      <c r="C47" s="402" t="s">
+      <c r="C47" s="394" t="s">
         <v>75</v>
       </c>
-      <c r="D47" s="408" t="s">
+      <c r="D47" s="350" t="s">
         <v>76</v>
       </c>
-      <c r="E47" s="409"/>
+      <c r="E47" s="351"/>
       <c r="F47" s="70"/>
       <c r="G47" s="6"/>
-      <c r="H47" s="390" t="s">
+      <c r="H47" s="382" t="s">
         <v>67</v>
       </c>
-      <c r="I47" s="391"/>
-      <c r="J47" s="391"/>
-      <c r="K47" s="392"/>
+      <c r="I47" s="383"/>
+      <c r="J47" s="383"/>
+      <c r="K47" s="384"/>
       <c r="L47" s="109">
         <f t="shared" ref="L47:L50" ca="1" si="23">M47/$M$45</f>
         <v>0.55555555555555558</v>
@@ -28672,17 +29086,17 @@
       <c r="AI47" s="11"/>
     </row>
     <row r="48" spans="1:35" ht="16.5" thickBot="1">
-      <c r="C48" s="403"/>
-      <c r="D48" s="410"/>
-      <c r="E48" s="411"/>
+      <c r="C48" s="395"/>
+      <c r="D48" s="352"/>
+      <c r="E48" s="353"/>
       <c r="F48" s="71"/>
       <c r="G48" s="6"/>
-      <c r="H48" s="393" t="s">
+      <c r="H48" s="385" t="s">
         <v>68</v>
       </c>
-      <c r="I48" s="394"/>
-      <c r="J48" s="394"/>
-      <c r="K48" s="395"/>
+      <c r="I48" s="386"/>
+      <c r="J48" s="386"/>
+      <c r="K48" s="387"/>
       <c r="L48" s="111">
         <f t="shared" ca="1" si="23"/>
         <v>0.22222222222222221</v>
@@ -28725,12 +29139,12 @@
     <row r="49" spans="3:35">
       <c r="F49" s="72"/>
       <c r="G49" s="6"/>
-      <c r="H49" s="396" t="s">
+      <c r="H49" s="388" t="s">
         <v>70</v>
       </c>
-      <c r="I49" s="397"/>
-      <c r="J49" s="397"/>
-      <c r="K49" s="398"/>
+      <c r="I49" s="389"/>
+      <c r="J49" s="389"/>
+      <c r="K49" s="390"/>
       <c r="L49" s="114">
         <f t="shared" ca="1" si="23"/>
         <v>0.1388888888888889</v>
@@ -28773,17 +29187,17 @@
       <c r="AI49" s="11"/>
     </row>
     <row r="50" spans="3:35" ht="16.5" thickBot="1">
-      <c r="C50" s="381" t="s">
+      <c r="C50" s="378" t="s">
         <v>41</v>
       </c>
-      <c r="D50" s="381"/>
-      <c r="E50" s="381"/>
-      <c r="H50" s="399" t="s">
+      <c r="D50" s="378"/>
+      <c r="E50" s="378"/>
+      <c r="H50" s="391" t="s">
         <v>71</v>
       </c>
-      <c r="I50" s="400"/>
-      <c r="J50" s="400"/>
-      <c r="K50" s="401"/>
+      <c r="I50" s="392"/>
+      <c r="J50" s="392"/>
+      <c r="K50" s="393"/>
       <c r="L50" s="113">
         <f t="shared" ca="1" si="23"/>
         <v>5.5555555555555552E-2</v>
@@ -28828,27 +29242,6 @@
     </sortState>
   </autoFilter>
   <mergeCells count="37">
-    <mergeCell ref="P44:Q44"/>
-    <mergeCell ref="X4:Y4"/>
-    <mergeCell ref="Z4:AC4"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D44:E44"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="D46:E46"/>
-    <mergeCell ref="C50:E50"/>
-    <mergeCell ref="H46:K46"/>
-    <mergeCell ref="H47:K47"/>
-    <mergeCell ref="H44:M44"/>
-    <mergeCell ref="H48:K48"/>
-    <mergeCell ref="H49:K49"/>
-    <mergeCell ref="C47:C48"/>
-    <mergeCell ref="D47:E48"/>
-    <mergeCell ref="D45:E45"/>
     <mergeCell ref="AG5:AG6"/>
     <mergeCell ref="AH5:AH6"/>
     <mergeCell ref="AI5:AI6"/>
@@ -28865,6 +29258,27 @@
     <mergeCell ref="K4:K5"/>
     <mergeCell ref="P4:Q4"/>
     <mergeCell ref="J4:J5"/>
+    <mergeCell ref="D46:E46"/>
+    <mergeCell ref="C50:E50"/>
+    <mergeCell ref="H46:K46"/>
+    <mergeCell ref="H47:K47"/>
+    <mergeCell ref="H44:M44"/>
+    <mergeCell ref="H48:K48"/>
+    <mergeCell ref="H49:K49"/>
+    <mergeCell ref="C47:C48"/>
+    <mergeCell ref="D47:E48"/>
+    <mergeCell ref="D45:E45"/>
+    <mergeCell ref="P44:Q44"/>
+    <mergeCell ref="X4:Y4"/>
+    <mergeCell ref="Z4:AC4"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D44:E44"/>
+    <mergeCell ref="B4:B5"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="A7:AD42 AG7:AI42">
@@ -29149,81 +29563,81 @@
       <c r="Z3" s="159"/>
     </row>
     <row r="4" spans="1:26" s="5" customFormat="1" ht="35.1" customHeight="1" thickBot="1">
-      <c r="A4" s="406" t="s">
+      <c r="A4" s="348" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="406" t="s">
+      <c r="B4" s="348" t="s">
         <v>515</v>
       </c>
-      <c r="C4" s="359" t="s">
+      <c r="C4" s="414" t="s">
         <v>45</v>
       </c>
-      <c r="D4" s="348" t="s">
+      <c r="D4" s="369" t="s">
         <v>46</v>
       </c>
-      <c r="E4" s="428" t="s">
+      <c r="E4" s="437" t="s">
         <v>47</v>
       </c>
-      <c r="F4" s="348" t="s">
+      <c r="F4" s="369" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="430" t="s">
+      <c r="G4" s="439" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="352" t="s">
+      <c r="H4" s="366" t="s">
         <v>48</v>
       </c>
-      <c r="I4" s="432" t="s">
+      <c r="I4" s="441" t="s">
         <v>49</v>
       </c>
-      <c r="J4" s="348" t="s">
+      <c r="J4" s="369" t="s">
         <v>78</v>
       </c>
-      <c r="K4" s="352" t="s">
+      <c r="K4" s="366" t="s">
         <v>80</v>
       </c>
-      <c r="L4" s="362" t="s">
+      <c r="L4" s="368" t="s">
         <v>53</v>
       </c>
-      <c r="M4" s="364"/>
-      <c r="N4" s="362" t="s">
+      <c r="M4" s="365"/>
+      <c r="N4" s="368" t="s">
         <v>55</v>
       </c>
-      <c r="O4" s="364"/>
-      <c r="P4" s="362" t="s">
+      <c r="O4" s="365"/>
+      <c r="P4" s="368" t="s">
         <v>72</v>
       </c>
-      <c r="Q4" s="364"/>
-      <c r="R4" s="363" t="s">
+      <c r="Q4" s="365"/>
+      <c r="R4" s="364" t="s">
         <v>53</v>
       </c>
-      <c r="S4" s="363"/>
-      <c r="T4" s="364"/>
-      <c r="U4" s="362" t="s">
+      <c r="S4" s="364"/>
+      <c r="T4" s="365"/>
+      <c r="U4" s="368" t="s">
         <v>55</v>
       </c>
-      <c r="V4" s="363"/>
-      <c r="W4" s="363"/>
-      <c r="X4" s="415" t="s">
+      <c r="V4" s="364"/>
+      <c r="W4" s="364"/>
+      <c r="X4" s="371" t="s">
         <v>72</v>
       </c>
-      <c r="Y4" s="416"/>
-      <c r="Z4" s="364" t="s">
+      <c r="Y4" s="372"/>
+      <c r="Z4" s="365" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="72" customHeight="1">
-      <c r="A5" s="407"/>
-      <c r="B5" s="407"/>
-      <c r="C5" s="360"/>
-      <c r="D5" s="354"/>
-      <c r="E5" s="429"/>
-      <c r="F5" s="354"/>
-      <c r="G5" s="431"/>
-      <c r="H5" s="353"/>
-      <c r="I5" s="433"/>
-      <c r="J5" s="354"/>
-      <c r="K5" s="353"/>
+      <c r="A5" s="349"/>
+      <c r="B5" s="349"/>
+      <c r="C5" s="415"/>
+      <c r="D5" s="370"/>
+      <c r="E5" s="438"/>
+      <c r="F5" s="370"/>
+      <c r="G5" s="440"/>
+      <c r="H5" s="367"/>
+      <c r="I5" s="442"/>
+      <c r="J5" s="370"/>
+      <c r="K5" s="367"/>
       <c r="L5" s="79" t="s">
         <v>52</v>
       </c>
@@ -29266,7 +29680,7 @@
       <c r="Y5" s="260" t="s">
         <v>114</v>
       </c>
-      <c r="Z5" s="361"/>
+      <c r="Z5" s="416"/>
     </row>
     <row r="6" spans="1:26" ht="15" customHeight="1" thickBot="1">
       <c r="A6" s="78"/>
@@ -38212,7 +38626,7 @@
       <c r="X125" s="230"/>
       <c r="Y125" s="19"/>
       <c r="Z125" s="92" t="s">
-        <v>1065</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="126" spans="1:26" s="9" customFormat="1" ht="78.75">
@@ -38240,7 +38654,9 @@
       <c r="G126" s="21" t="s">
         <v>1053</v>
       </c>
-      <c r="H126" s="138"/>
+      <c r="H126" s="138" t="s">
+        <v>6</v>
+      </c>
       <c r="I126" s="164">
         <f t="shared" ca="1" si="24"/>
         <v>7</v>
@@ -38269,10 +38685,14 @@
       </c>
       <c r="U126" s="29"/>
       <c r="V126" s="211"/>
-      <c r="W126" s="235"/>
+      <c r="W126" s="235" t="s">
+        <v>240</v>
+      </c>
       <c r="X126" s="230"/>
       <c r="Y126" s="19"/>
-      <c r="Z126" s="92"/>
+      <c r="Z126" s="92" t="s">
+        <v>1072</v>
+      </c>
     </row>
     <row r="127" spans="1:26" s="9" customFormat="1" ht="31.5">
       <c r="A127" s="33">
@@ -38285,17 +38705,17 @@
       </c>
       <c r="C127" s="164"/>
       <c r="D127" s="25" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="E127" s="174">
         <f t="shared" si="23"/>
         <v>46325</v>
       </c>
       <c r="F127" s="31" t="s">
+        <v>1057</v>
+      </c>
+      <c r="G127" s="21" t="s">
         <v>1058</v>
-      </c>
-      <c r="G127" s="21" t="s">
-        <v>1059</v>
       </c>
       <c r="H127" s="138"/>
       <c r="I127" s="164">
@@ -38329,7 +38749,9 @@
       <c r="W127" s="235"/>
       <c r="X127" s="230"/>
       <c r="Y127" s="19"/>
-      <c r="Z127" s="92"/>
+      <c r="Z127" s="92" t="s">
+        <v>1071</v>
+      </c>
     </row>
     <row r="128" spans="1:26" s="9" customFormat="1" ht="47.25">
       <c r="A128" s="33">
@@ -38344,17 +38766,17 @@
         <v>621</v>
       </c>
       <c r="D128" s="25" t="s">
-        <v>1068</v>
+        <v>1065</v>
       </c>
       <c r="E128" s="174">
         <f t="shared" si="23"/>
         <v>46330</v>
       </c>
       <c r="F128" s="31" t="s">
-        <v>1069</v>
+        <v>1066</v>
       </c>
       <c r="G128" s="21" t="s">
-        <v>1070</v>
+        <v>1067</v>
       </c>
       <c r="H128" s="138"/>
       <c r="I128" s="164">
@@ -38451,28 +38873,28 @@
       <c r="C132" s="207" t="s">
         <v>38</v>
       </c>
-      <c r="D132" s="441" t="s">
+      <c r="D132" s="428" t="s">
         <v>39</v>
       </c>
-      <c r="E132" s="442"/>
+      <c r="E132" s="429"/>
       <c r="F132" s="46"/>
       <c r="G132" s="68"/>
-      <c r="H132" s="384" t="s">
+      <c r="H132" s="356" t="s">
         <v>14</v>
       </c>
-      <c r="I132" s="385"/>
-      <c r="J132" s="385"/>
-      <c r="K132" s="385"/>
-      <c r="L132" s="385"/>
-      <c r="M132" s="386"/>
-      <c r="N132" s="382" t="s">
+      <c r="I132" s="357"/>
+      <c r="J132" s="357"/>
+      <c r="K132" s="357"/>
+      <c r="L132" s="357"/>
+      <c r="M132" s="358"/>
+      <c r="N132" s="362" t="s">
         <v>7</v>
       </c>
-      <c r="O132" s="383"/>
-      <c r="P132" s="382" t="s">
+      <c r="O132" s="363"/>
+      <c r="P132" s="362" t="s">
         <v>110</v>
       </c>
-      <c r="Q132" s="383"/>
+      <c r="Q132" s="363"/>
       <c r="R132" s="1"/>
       <c r="S132" s="1"/>
       <c r="T132" s="140"/>
@@ -38485,16 +38907,16 @@
       <c r="C133" s="208" t="s">
         <v>74</v>
       </c>
-      <c r="D133" s="439" t="s">
+      <c r="D133" s="435" t="s">
         <v>77</v>
       </c>
-      <c r="E133" s="440"/>
+      <c r="E133" s="436"/>
       <c r="F133" s="46"/>
       <c r="G133" s="46"/>
-      <c r="H133" s="434" t="s">
+      <c r="H133" s="430" t="s">
         <v>17</v>
       </c>
-      <c r="I133" s="435"/>
+      <c r="I133" s="431"/>
       <c r="J133" s="130"/>
       <c r="K133" s="210"/>
       <c r="L133" s="117">
@@ -38503,7 +38925,7 @@
       </c>
       <c r="M133" s="104">
         <f ca="1">SUM($M$134:$M$136)</f>
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="N133" s="118" t="s">
         <v>15</v>
@@ -38528,32 +38950,32 @@
       <c r="Y133" s="11"/>
     </row>
     <row r="134" spans="1:26">
-      <c r="C134" s="402" t="s">
+      <c r="C134" s="394" t="s">
         <v>6</v>
       </c>
-      <c r="D134" s="439" t="s">
+      <c r="D134" s="435" t="s">
         <v>40</v>
       </c>
-      <c r="E134" s="440"/>
+      <c r="E134" s="436"/>
       <c r="F134" s="69"/>
       <c r="G134" s="6"/>
-      <c r="H134" s="436" t="s">
+      <c r="H134" s="432" t="s">
         <v>69</v>
       </c>
-      <c r="I134" s="437"/>
-      <c r="J134" s="437"/>
-      <c r="K134" s="438"/>
+      <c r="I134" s="433"/>
+      <c r="J134" s="433"/>
+      <c r="K134" s="434"/>
       <c r="L134" s="122">
         <f t="shared" ref="L134:L136" ca="1" si="60">M134/$M$133</f>
-        <v>0.81889763779527558</v>
+        <v>0.8203125</v>
       </c>
       <c r="M134" s="123">
         <f>COUNTIF($H$7:$H$130,"RFCS")</f>
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="N134" s="121">
         <f ca="1">COUNTIFS($I$7:$I$130,"&lt;=21",$H$7:$H$130,"RFCS")</f>
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="O134" s="120">
         <f ca="1">COUNTIFS($I$7:$I$130,"&gt;21",$H$7:$H$130,"RFCS")</f>
@@ -38576,20 +38998,20 @@
       <c r="Y134" s="11"/>
     </row>
     <row r="135" spans="1:26">
-      <c r="C135" s="402"/>
-      <c r="D135" s="439"/>
-      <c r="E135" s="440"/>
+      <c r="C135" s="394"/>
+      <c r="D135" s="435"/>
+      <c r="E135" s="436"/>
       <c r="F135" s="72"/>
       <c r="G135" s="6"/>
-      <c r="H135" s="396" t="s">
+      <c r="H135" s="388" t="s">
         <v>70</v>
       </c>
-      <c r="I135" s="397"/>
-      <c r="J135" s="397"/>
-      <c r="K135" s="398"/>
+      <c r="I135" s="389"/>
+      <c r="J135" s="389"/>
+      <c r="K135" s="390"/>
       <c r="L135" s="124">
         <f t="shared" ca="1" si="60"/>
-        <v>7.0866141732283464E-2</v>
+        <v>7.03125E-2</v>
       </c>
       <c r="M135" s="125">
         <f ca="1">SUM(N135:O135)</f>
@@ -38622,22 +39044,22 @@
       <c r="Y135" s="11"/>
     </row>
     <row r="136" spans="1:26" ht="16.5" thickBot="1">
-      <c r="C136" s="402" t="s">
+      <c r="C136" s="394" t="s">
         <v>75</v>
       </c>
-      <c r="D136" s="408" t="s">
+      <c r="D136" s="350" t="s">
         <v>76</v>
       </c>
-      <c r="E136" s="409"/>
-      <c r="H136" s="399" t="s">
+      <c r="E136" s="351"/>
+      <c r="H136" s="391" t="s">
         <v>71</v>
       </c>
-      <c r="I136" s="400"/>
-      <c r="J136" s="400"/>
-      <c r="K136" s="401"/>
+      <c r="I136" s="392"/>
+      <c r="J136" s="392"/>
+      <c r="K136" s="393"/>
       <c r="L136" s="126">
         <f t="shared" ca="1" si="60"/>
-        <v>0.11023622047244094</v>
+        <v>0.109375</v>
       </c>
       <c r="M136" s="116">
         <f>COUNTIFS($K$7:$K$130,"X")</f>
@@ -38649,16 +39071,16 @@
       <c r="Q136" s="224"/>
     </row>
     <row r="137" spans="1:26" ht="16.5" thickBot="1">
-      <c r="C137" s="403"/>
-      <c r="D137" s="410"/>
-      <c r="E137" s="411"/>
+      <c r="C137" s="395"/>
+      <c r="D137" s="352"/>
+      <c r="E137" s="353"/>
     </row>
     <row r="139" spans="1:26">
-      <c r="C139" s="381" t="s">
+      <c r="C139" s="378" t="s">
         <v>41</v>
       </c>
-      <c r="D139" s="381"/>
-      <c r="E139" s="381"/>
+      <c r="D139" s="378"/>
+      <c r="E139" s="378"/>
     </row>
     <row r="140" spans="1:26">
       <c r="C140" s="169" t="s">
@@ -38691,22 +39113,6 @@
     </sortState>
   </autoFilter>
   <mergeCells count="32">
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="P132:Q132"/>
-    <mergeCell ref="J4:J5"/>
-    <mergeCell ref="D132:E132"/>
-    <mergeCell ref="H132:M132"/>
-    <mergeCell ref="N132:O132"/>
-    <mergeCell ref="H133:I133"/>
-    <mergeCell ref="C139:E139"/>
-    <mergeCell ref="H134:K134"/>
-    <mergeCell ref="H135:K135"/>
-    <mergeCell ref="H136:K136"/>
-    <mergeCell ref="D133:E133"/>
-    <mergeCell ref="C134:C135"/>
-    <mergeCell ref="D134:E135"/>
-    <mergeCell ref="C136:C137"/>
-    <mergeCell ref="D136:E137"/>
     <mergeCell ref="Z4:Z5"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="D4:D5"/>
@@ -38723,6 +39129,22 @@
     <mergeCell ref="K4:K5"/>
     <mergeCell ref="P4:Q4"/>
     <mergeCell ref="X4:Y4"/>
+    <mergeCell ref="H133:I133"/>
+    <mergeCell ref="C139:E139"/>
+    <mergeCell ref="H134:K134"/>
+    <mergeCell ref="H135:K135"/>
+    <mergeCell ref="H136:K136"/>
+    <mergeCell ref="D133:E133"/>
+    <mergeCell ref="C134:C135"/>
+    <mergeCell ref="D134:E135"/>
+    <mergeCell ref="C136:C137"/>
+    <mergeCell ref="D136:E137"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="P132:Q132"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="D132:E132"/>
+    <mergeCell ref="H132:M132"/>
+    <mergeCell ref="N132:O132"/>
   </mergeCells>
   <phoneticPr fontId="71"/>
   <conditionalFormatting sqref="A7:Z130">
@@ -39306,19 +39728,19 @@
       <c r="S3" s="281"/>
     </row>
     <row r="4" spans="1:25" ht="36" customHeight="1" thickBot="1">
-      <c r="A4" s="350" t="s">
+      <c r="A4" s="408" t="s">
         <v>123</v>
       </c>
-      <c r="B4" s="352" t="s">
+      <c r="B4" s="366" t="s">
         <v>45</v>
       </c>
-      <c r="C4" s="352" t="s">
+      <c r="C4" s="366" t="s">
         <v>95</v>
       </c>
-      <c r="D4" s="352" t="s">
+      <c r="D4" s="366" t="s">
         <v>46</v>
       </c>
-      <c r="E4" s="348" t="s">
+      <c r="E4" s="369" t="s">
         <v>4</v>
       </c>
       <c r="F4" s="449" t="s">
@@ -39347,12 +39769,12 @@
       <c r="S4" s="448"/>
     </row>
     <row r="5" spans="1:25" ht="78.75">
-      <c r="A5" s="351"/>
-      <c r="B5" s="353"/>
-      <c r="C5" s="353"/>
-      <c r="D5" s="353"/>
-      <c r="E5" s="354"/>
-      <c r="F5" s="356"/>
+      <c r="A5" s="409"/>
+      <c r="B5" s="367"/>
+      <c r="C5" s="367"/>
+      <c r="D5" s="367"/>
+      <c r="E5" s="370"/>
+      <c r="F5" s="411"/>
       <c r="G5" s="283" t="s">
         <v>56</v>
       </c>
@@ -39434,7 +39856,7 @@
         <v>MAS</v>
       </c>
       <c r="D7" s="282" t="str" cm="1">
-        <f t="array" ref="D7:D24">_xlfn._xlws.FILTER(RFA!$E$5:$E$4572, RFA!$AI$5:$AI$4572="YES","")</f>
+        <f t="array" ref="D7:D24">_xlfn._xlws.FILTER(RFA!$E$5:$E$4576, RFA!$AI$5:$AI$4576="YES","")</f>
         <v>LTIA-5.10-VIETUR-70000-RFA-MAS-0088A</v>
       </c>
       <c r="E7" s="303" t="str" cm="1">
@@ -40685,16 +41107,16 @@
       <c r="R3" s="281"/>
     </row>
     <row r="4" spans="1:18" ht="16.5" thickBot="1">
-      <c r="A4" s="350" t="s">
+      <c r="A4" s="408" t="s">
         <v>123</v>
       </c>
-      <c r="B4" s="352" t="s">
+      <c r="B4" s="366" t="s">
         <v>45</v>
       </c>
-      <c r="C4" s="352" t="s">
+      <c r="C4" s="366" t="s">
         <v>46</v>
       </c>
-      <c r="D4" s="363" t="s">
+      <c r="D4" s="364" t="s">
         <v>4</v>
       </c>
       <c r="E4" s="449" t="s">
@@ -40723,11 +41145,11 @@
       <c r="R4" s="448"/>
     </row>
     <row r="5" spans="1:18" ht="78.75">
-      <c r="A5" s="351"/>
-      <c r="B5" s="353"/>
-      <c r="C5" s="353"/>
-      <c r="D5" s="431"/>
-      <c r="E5" s="354"/>
+      <c r="A5" s="409"/>
+      <c r="B5" s="367"/>
+      <c r="C5" s="367"/>
+      <c r="D5" s="440"/>
+      <c r="E5" s="370"/>
       <c r="F5" s="283" t="s">
         <v>56</v>
       </c>

--- a/ICT-RFA-RFI-lists-New.xlsx
+++ b/ICT-RFA-RFI-lists-New.xlsx
@@ -9,7 +9,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project Airport\LTIA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E58510BE-229C-4BD8-B416-72158A7B789B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01F0DF36-5C6D-488E-8CE1-E9A935FF3051}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="506" xr2:uid="{CCA8147E-0981-4321-B87F-440A52C0DA59}"/>
   </bookViews>
@@ -24,12 +24,12 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Need ReSub (RFA)'!$A$6:$S$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Need ReSub (RFA-SDS)'!$A$6:$R$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">RFA!$A$6:$AE$141</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">RFA!$A$6:$AE$142</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'RFA-SDS'!$A$6:$AD$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">RFI!$A$6:$Z$127</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Need ReSub (RFA)'!$A$1:$S$77</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'Need ReSub (RFA-SDS)'!$A$1:$R$62</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RFA!$A$1:$AE$141,RFA!$I$143:$R$149,RFA!$C$143:$F$153,RFA!$C$155:$F$158,RFA!$C$160:$F$171</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RFA!$A$1:$AE$142,RFA!$I$144:$R$150,RFA!$C$144:$F$154,RFA!$C$156:$F$159,RFA!$C$161:$F$172</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'RFA-SDS'!$A$1:$AD$42,'RFA-SDS'!$H$44:$Q$50,'RFA-SDS'!$C$44:$E$48,'RFA-SDS'!$C$50:$E$53</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">RFI!$A$1:$Z$130,RFI!$H$132:$Q$136,RFI!$C$132:$E$137,RFI!$C$139:$E$142</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">RFA!$4:$5</definedName>
@@ -78,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3469" uniqueCount="1088">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3475" uniqueCount="1091">
   <si>
     <t>TT</t>
   </si>
@@ -5117,6 +5117,15 @@
   <si>
     <t>WDNE
 TOIP</t>
+  </si>
+  <si>
+    <t>LTIA-5.10-VIETUR-70000-RFA-OTH-0767</t>
+  </si>
+  <si>
+    <t>Request for Approval of the Pre-Completion Inspection, Testing, and Operation Procedure for the Border Gate Security System (IMM)</t>
+  </si>
+  <si>
+    <t>Đề nghị phê duyệt Quy trình kiểm tra trước khi hoàn thành, thử nghiệm, vận hành hệ thống An ninh Cửa Khẩu</t>
   </si>
 </sst>
 </file>
@@ -7554,6 +7563,180 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="51" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="52" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="55" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="55" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -7571,21 +7754,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="51" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="52" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -7595,248 +7763,89 @@
     <xf numFmtId="1" fontId="2" fillId="0" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="55" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="55" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="45" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="53" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="47" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="45" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -8367,7 +8376,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C724CDAB-378C-47DB-9F45-08EE3BFB6E8B}">
-  <dimension ref="A1:AI171"/>
+  <dimension ref="A1:AI172"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" customWidth="1"/>
@@ -8412,7 +8421,7 @@
       </c>
       <c r="J1" s="176">
         <f ca="1">TODAY()</f>
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="K1" s="131"/>
       <c r="L1" s="197"/>
@@ -8499,92 +8508,92 @@
       <c r="AE3" s="159"/>
     </row>
     <row r="4" spans="1:35" s="5" customFormat="1" ht="36" customHeight="1" thickBot="1">
-      <c r="A4" s="408" t="s">
+      <c r="A4" s="350" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="348" t="s">
+      <c r="B4" s="406" t="s">
         <v>515</v>
       </c>
-      <c r="C4" s="414" t="s">
+      <c r="C4" s="359" t="s">
         <v>45</v>
       </c>
-      <c r="D4" s="366" t="s">
+      <c r="D4" s="352" t="s">
         <v>95</v>
       </c>
-      <c r="E4" s="369" t="s">
+      <c r="E4" s="348" t="s">
         <v>46</v>
       </c>
-      <c r="F4" s="412" t="s">
+      <c r="F4" s="357" t="s">
         <v>47</v>
       </c>
-      <c r="G4" s="369" t="s">
+      <c r="G4" s="348" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="410" t="s">
+      <c r="H4" s="355" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="366" t="s">
+      <c r="I4" s="352" t="s">
         <v>48</v>
       </c>
-      <c r="J4" s="366" t="s">
+      <c r="J4" s="352" t="s">
         <v>49</v>
       </c>
-      <c r="K4" s="369" t="s">
+      <c r="K4" s="348" t="s">
         <v>78</v>
       </c>
-      <c r="L4" s="366" t="s">
+      <c r="L4" s="352" t="s">
         <v>80</v>
       </c>
-      <c r="M4" s="364" t="s">
+      <c r="M4" s="363" t="s">
         <v>53</v>
       </c>
-      <c r="N4" s="365"/>
-      <c r="O4" s="364" t="s">
+      <c r="N4" s="364"/>
+      <c r="O4" s="363" t="s">
         <v>55</v>
       </c>
-      <c r="P4" s="365"/>
-      <c r="Q4" s="368" t="s">
+      <c r="P4" s="364"/>
+      <c r="Q4" s="362" t="s">
         <v>72</v>
       </c>
-      <c r="R4" s="365"/>
-      <c r="S4" s="364" t="s">
+      <c r="R4" s="364"/>
+      <c r="S4" s="363" t="s">
         <v>53</v>
       </c>
-      <c r="T4" s="364"/>
-      <c r="U4" s="365"/>
-      <c r="V4" s="368" t="s">
+      <c r="T4" s="363"/>
+      <c r="U4" s="364"/>
+      <c r="V4" s="362" t="s">
         <v>55</v>
       </c>
-      <c r="W4" s="364"/>
-      <c r="X4" s="365"/>
-      <c r="Y4" s="371" t="s">
+      <c r="W4" s="363"/>
+      <c r="X4" s="364"/>
+      <c r="Y4" s="415" t="s">
         <v>72</v>
       </c>
-      <c r="Z4" s="372"/>
-      <c r="AA4" s="359" t="s">
+      <c r="Z4" s="416"/>
+      <c r="AA4" s="412" t="s">
         <v>112</v>
       </c>
-      <c r="AB4" s="360"/>
-      <c r="AC4" s="360"/>
-      <c r="AD4" s="361"/>
-      <c r="AE4" s="369" t="s">
+      <c r="AB4" s="413"/>
+      <c r="AC4" s="413"/>
+      <c r="AD4" s="414"/>
+      <c r="AE4" s="348" t="s">
         <v>79</v>
       </c>
       <c r="AG4" s="236"/>
     </row>
     <row r="5" spans="1:35" ht="78.75">
-      <c r="A5" s="409"/>
-      <c r="B5" s="349"/>
-      <c r="C5" s="415"/>
-      <c r="D5" s="367"/>
-      <c r="E5" s="370"/>
-      <c r="F5" s="413"/>
-      <c r="G5" s="370"/>
-      <c r="H5" s="411"/>
-      <c r="I5" s="367"/>
-      <c r="J5" s="367"/>
-      <c r="K5" s="370"/>
-      <c r="L5" s="367"/>
+      <c r="A5" s="351"/>
+      <c r="B5" s="407"/>
+      <c r="C5" s="360"/>
+      <c r="D5" s="353"/>
+      <c r="E5" s="354"/>
+      <c r="F5" s="358"/>
+      <c r="G5" s="354"/>
+      <c r="H5" s="356"/>
+      <c r="I5" s="353"/>
+      <c r="J5" s="353"/>
+      <c r="K5" s="354"/>
+      <c r="L5" s="353"/>
       <c r="M5" s="79" t="s">
         <v>52</v>
       </c>
@@ -8639,14 +8648,14 @@
       <c r="AD5" s="336" t="s">
         <v>118</v>
       </c>
-      <c r="AE5" s="416"/>
-      <c r="AG5" s="369" t="s">
+      <c r="AE5" s="361"/>
+      <c r="AG5" s="348" t="s">
         <v>119</v>
       </c>
-      <c r="AH5" s="369" t="s">
+      <c r="AH5" s="348" t="s">
         <v>120</v>
       </c>
-      <c r="AI5" s="369" t="s">
+      <c r="AI5" s="348" t="s">
         <v>121</v>
       </c>
     </row>
@@ -8682,9 +8691,9 @@
       <c r="AC6" s="86"/>
       <c r="AD6" s="86"/>
       <c r="AE6" s="74"/>
-      <c r="AG6" s="407"/>
-      <c r="AH6" s="407"/>
-      <c r="AI6" s="407"/>
+      <c r="AG6" s="349"/>
+      <c r="AH6" s="349"/>
+      <c r="AI6" s="349"/>
     </row>
     <row r="7" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A7" s="33">
@@ -8793,8 +8802,8 @@
       <c r="AH7" s="242" t="b" cm="1">
         <f t="array" ref="AH7">$E7=_xlfn.XLOOKUP(
 AG7,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -8909,8 +8918,8 @@
       <c r="AH8" s="243" t="b" cm="1">
         <f t="array" ref="AH8">$E8=_xlfn.XLOOKUP(
 AG8,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -9025,8 +9034,8 @@
       <c r="AH9" s="243" t="b" cm="1">
         <f t="array" ref="AH9">$E9=_xlfn.XLOOKUP(
 AG9,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -9143,8 +9152,8 @@
       <c r="AH10" s="243" t="b" cm="1">
         <f t="array" ref="AH10">$E10=_xlfn.XLOOKUP(
 AG10,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -9261,8 +9270,8 @@
       <c r="AH11" s="243" t="b" cm="1">
         <f t="array" ref="AH11">$E11=_xlfn.XLOOKUP(
 AG11,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -9379,8 +9388,8 @@
       <c r="AH12" s="243" t="b" cm="1">
         <f t="array" ref="AH12">$E12=_xlfn.XLOOKUP(
 AG12,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -9497,8 +9506,8 @@
       <c r="AH13" s="243" t="b" cm="1">
         <f t="array" ref="AH13">$E13=_xlfn.XLOOKUP(
 AG13,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -9603,7 +9612,7 @@
       </c>
       <c r="AD14" s="337">
         <f t="shared" ca="1" si="7"/>
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="AE14" s="92"/>
       <c r="AG14" s="238" t="str">
@@ -9613,8 +9622,8 @@
       <c r="AH14" s="243" t="b" cm="1">
         <f t="array" ref="AH14">$E14=_xlfn.XLOOKUP(
 AG14,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -9719,7 +9728,7 @@
       </c>
       <c r="AD15" s="337">
         <f t="shared" ca="1" si="7"/>
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="AE15" s="92"/>
       <c r="AG15" s="238" t="str">
@@ -9729,8 +9738,8 @@
       <c r="AH15" s="243" t="b" cm="1">
         <f t="array" ref="AH15">$E15=_xlfn.XLOOKUP(
 AG15,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -9847,8 +9856,8 @@
       <c r="AH16" s="243" t="b" cm="1">
         <f t="array" ref="AH16">$E16=_xlfn.XLOOKUP(
 AG16,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -9963,8 +9972,8 @@
       <c r="AH17" s="243" t="b" cm="1">
         <f t="array" ref="AH17">$E17=_xlfn.XLOOKUP(
 AG17,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -10081,8 +10090,8 @@
       <c r="AH18" s="243" t="b" cm="1">
         <f t="array" ref="AH18">$E18=_xlfn.XLOOKUP(
 AG18,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -10199,8 +10208,8 @@
       <c r="AH19" s="243" t="b" cm="1">
         <f t="array" ref="AH19">$E19=_xlfn.XLOOKUP(
 AG19,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -10315,8 +10324,8 @@
       <c r="AH20" s="243" t="b" cm="1">
         <f t="array" ref="AH20">$E20=_xlfn.XLOOKUP(
 AG20,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -10433,8 +10442,8 @@
       <c r="AH21" s="243" t="b" cm="1">
         <f t="array" ref="AH21">$E21=_xlfn.XLOOKUP(
 AG21,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -10551,8 +10560,8 @@
       <c r="AH22" s="243" t="b" cm="1">
         <f t="array" ref="AH22">$E22=_xlfn.XLOOKUP(
 AG22,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -10667,8 +10676,8 @@
       <c r="AH23" s="243" t="b" cm="1">
         <f t="array" ref="AH23">$E23=_xlfn.XLOOKUP(
 AG23,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -10787,8 +10796,8 @@
       <c r="AH24" s="243" t="b" cm="1">
         <f t="array" ref="AH24">$E24=_xlfn.XLOOKUP(
 AG24,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -10903,8 +10912,8 @@
       <c r="AH25" s="243" t="b" cm="1">
         <f t="array" ref="AH25">$E25=_xlfn.XLOOKUP(
 AG25,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -11019,8 +11028,8 @@
       <c r="AH26" s="243" t="b" cm="1">
         <f t="array" ref="AH26">$E26=_xlfn.XLOOKUP(
 AG26,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -11137,8 +11146,8 @@
       <c r="AH27" s="243" t="b" cm="1">
         <f t="array" ref="AH27">$E27=_xlfn.XLOOKUP(
 AG27,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -11255,8 +11264,8 @@
       <c r="AH28" s="243" t="b" cm="1">
         <f t="array" ref="AH28">$E28=_xlfn.XLOOKUP(
 AG28,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -11371,8 +11380,8 @@
       <c r="AH29" s="243" t="b" cm="1">
         <f t="array" ref="AH29">$E29=_xlfn.XLOOKUP(
 AG29,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -11489,8 +11498,8 @@
       <c r="AH30" s="243" t="b" cm="1">
         <f t="array" ref="AH30">$E30=_xlfn.XLOOKUP(
 AG30,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -11607,8 +11616,8 @@
       <c r="AH31" s="243" t="b" cm="1">
         <f t="array" ref="AH31">$E31=_xlfn.XLOOKUP(
 AG31,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -11723,8 +11732,8 @@
       <c r="AH32" s="243" t="b" cm="1">
         <f t="array" ref="AH32">$E32=_xlfn.XLOOKUP(
 AG32,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -11841,8 +11850,8 @@
       <c r="AH33" s="243" t="b" cm="1">
         <f t="array" ref="AH33">$E33=_xlfn.XLOOKUP(
 AG33,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -11957,8 +11966,8 @@
       <c r="AH34" s="243" t="b" cm="1">
         <f t="array" ref="AH34">$E34=_xlfn.XLOOKUP(
 AG34,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -12073,8 +12082,8 @@
       <c r="AH35" s="243" t="b" cm="1">
         <f t="array" ref="AH35">$E35=_xlfn.XLOOKUP(
 AG35,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -12189,8 +12198,8 @@
       <c r="AH36" s="243" t="b" cm="1">
         <f t="array" ref="AH36">$E36=_xlfn.XLOOKUP(
 AG36,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -12305,8 +12314,8 @@
       <c r="AH37" s="243" t="b" cm="1">
         <f t="array" ref="AH37">$E37=_xlfn.XLOOKUP(
 AG37,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -12421,8 +12430,8 @@
       <c r="AH38" s="243" t="b" cm="1">
         <f t="array" ref="AH38">$E38=_xlfn.XLOOKUP(
 AG38,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -12537,8 +12546,8 @@
       <c r="AH39" s="243" t="b" cm="1">
         <f t="array" ref="AH39">$E39=_xlfn.XLOOKUP(
 AG39,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -12653,8 +12662,8 @@
       <c r="AH40" s="243" t="b" cm="1">
         <f t="array" ref="AH40">$E40=_xlfn.XLOOKUP(
 AG40,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -12769,8 +12778,8 @@
       <c r="AH41" s="243" t="b" cm="1">
         <f t="array" ref="AH41">$E41=_xlfn.XLOOKUP(
 AG41,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -12885,8 +12894,8 @@
       <c r="AH42" s="243" t="b" cm="1">
         <f t="array" ref="AH42">$E42=_xlfn.XLOOKUP(
 AG42,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -13001,8 +13010,8 @@
       <c r="AH43" s="243" t="b" cm="1">
         <f t="array" ref="AH43">$E43=_xlfn.XLOOKUP(
 AG43,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -13107,7 +13116,7 @@
       </c>
       <c r="AD44" s="337">
         <f t="shared" ca="1" si="13"/>
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AE44" s="92"/>
       <c r="AG44" s="238" t="str">
@@ -13117,8 +13126,8 @@
       <c r="AH44" s="243" t="b" cm="1">
         <f t="array" ref="AH44">$E44=_xlfn.XLOOKUP(
 AG44,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -13235,8 +13244,8 @@
       <c r="AH45" s="243" t="b" cm="1">
         <f t="array" ref="AH45">$E45=_xlfn.XLOOKUP(
 AG45,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -13341,7 +13350,7 @@
       </c>
       <c r="AD46" s="337">
         <f t="shared" ca="1" si="13"/>
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AE46" s="92"/>
       <c r="AG46" s="238" t="str">
@@ -13351,8 +13360,8 @@
       <c r="AH46" s="243" t="b" cm="1">
         <f t="array" ref="AH46">$E46=_xlfn.XLOOKUP(
 AG46,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -13467,8 +13476,8 @@
       <c r="AH47" s="243" t="b" cm="1">
         <f t="array" ref="AH47">$E47=_xlfn.XLOOKUP(
 AG47,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -13583,8 +13592,8 @@
       <c r="AH48" s="243" t="b" cm="1">
         <f t="array" ref="AH48">$E48=_xlfn.XLOOKUP(
 AG48,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -13701,8 +13710,8 @@
       <c r="AH49" s="243" t="b" cm="1">
         <f t="array" ref="AH49">$E49=_xlfn.XLOOKUP(
 AG49,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -13807,7 +13816,7 @@
       </c>
       <c r="AD50" s="337">
         <f t="shared" ca="1" si="13"/>
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AE50" s="92"/>
       <c r="AG50" s="238" t="str">
@@ -13817,8 +13826,8 @@
       <c r="AH50" s="243" t="b" cm="1">
         <f t="array" ref="AH50">$E50=_xlfn.XLOOKUP(
 AG50,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -13858,7 +13867,7 @@
       <c r="I51" s="138"/>
       <c r="J51" s="164">
         <f t="shared" ca="1" si="3"/>
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="K51" s="47"/>
       <c r="L51" s="164" t="s">
@@ -13907,8 +13916,8 @@
       <c r="AH51" s="243" t="b" cm="1">
         <f t="array" ref="AH51">$E51=_xlfn.XLOOKUP(
 AG51,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -14025,8 +14034,8 @@
       <c r="AH52" s="243" t="b" cm="1">
         <f t="array" ref="AH52">$E52=_xlfn.XLOOKUP(
 AG52,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -14143,8 +14152,8 @@
       <c r="AH53" s="243" t="b" cm="1">
         <f t="array" ref="AH53">$E53=_xlfn.XLOOKUP(
 AG53,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -14259,8 +14268,8 @@
       <c r="AH54" s="243" t="b" cm="1">
         <f t="array" ref="AH54">$E54=_xlfn.XLOOKUP(
 AG54,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -14375,8 +14384,8 @@
       <c r="AH55" s="243" t="b" cm="1">
         <f t="array" ref="AH55">$E55=_xlfn.XLOOKUP(
 AG55,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -14493,8 +14502,8 @@
       <c r="AH56" s="243" t="b" cm="1">
         <f t="array" ref="AH56">$E56=_xlfn.XLOOKUP(
 AG56,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -14609,8 +14618,8 @@
       <c r="AH57" s="243" t="b" cm="1">
         <f t="array" ref="AH57">$E57=_xlfn.XLOOKUP(
 AG57,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -14715,7 +14724,7 @@
       </c>
       <c r="AD58" s="337">
         <f t="shared" ca="1" si="13"/>
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AE58" s="92"/>
       <c r="AG58" s="238" t="str">
@@ -14725,8 +14734,8 @@
       <c r="AH58" s="243" t="b" cm="1">
         <f t="array" ref="AH58">$E58=_xlfn.XLOOKUP(
 AG58,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -14766,7 +14775,7 @@
       <c r="I59" s="138"/>
       <c r="J59" s="164">
         <f t="shared" ca="1" si="3"/>
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K59" s="47"/>
       <c r="L59" s="164" t="s">
@@ -14815,8 +14824,8 @@
       <c r="AH59" s="243" t="b" cm="1">
         <f t="array" ref="AH59">$E59=_xlfn.XLOOKUP(
 AG59,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -14935,8 +14944,8 @@
       <c r="AH60" s="243" t="b" cm="1">
         <f t="array" ref="AH60">$E60=_xlfn.XLOOKUP(
 AG60,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -15041,7 +15050,7 @@
       </c>
       <c r="AD61" s="337">
         <f t="shared" ca="1" si="13"/>
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AE61" s="92"/>
       <c r="AG61" s="238" t="str">
@@ -15051,8 +15060,8 @@
       <c r="AH61" s="243" t="b" cm="1">
         <f t="array" ref="AH61">$E61=_xlfn.XLOOKUP(
 AG61,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -15169,8 +15178,8 @@
       <c r="AH62" s="243" t="b" cm="1">
         <f t="array" ref="AH62">$E62=_xlfn.XLOOKUP(
 AG62,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -15287,8 +15296,8 @@
       <c r="AH63" s="243" t="b" cm="1">
         <f t="array" ref="AH63">$E63=_xlfn.XLOOKUP(
 AG63,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -15405,8 +15414,8 @@
       <c r="AH64" s="243" t="b" cm="1">
         <f t="array" ref="AH64">$E64=_xlfn.XLOOKUP(
 AG64,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -15523,8 +15532,8 @@
       <c r="AH65" s="243" t="b" cm="1">
         <f t="array" ref="AH65">$E65=_xlfn.XLOOKUP(
 AG65,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -15641,8 +15650,8 @@
       <c r="AH66" s="243" t="b" cm="1">
         <f t="array" ref="AH66">$E66=_xlfn.XLOOKUP(
 AG66,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -15757,8 +15766,8 @@
       <c r="AH67" s="243" t="b" cm="1">
         <f t="array" ref="AH67">$E67=_xlfn.XLOOKUP(
 AG67,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -15861,7 +15870,7 @@
       </c>
       <c r="AD68" s="337">
         <f t="shared" ca="1" si="13"/>
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AE68" s="92"/>
       <c r="AG68" s="238" t="str">
@@ -15871,8 +15880,8 @@
       <c r="AH68" s="243" t="b" cm="1">
         <f t="array" ref="AH68">$E68=_xlfn.XLOOKUP(
 AG68,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -15979,8 +15988,8 @@
       <c r="AH69" s="243" t="b" cm="1">
         <f t="array" ref="AH69">$E69=_xlfn.XLOOKUP(
 AG69,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -16095,8 +16104,8 @@
       <c r="AH70" s="243" t="b" cm="1">
         <f t="array" ref="AH70">$E70=_xlfn.XLOOKUP(
 AG70,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -16110,7 +16119,7 @@
     </row>
     <row r="71" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A71" s="33">
-        <f t="shared" ref="A71:A139" si="19">A70+1</f>
+        <f t="shared" ref="A71:A140" si="19">A70+1</f>
         <v>65</v>
       </c>
       <c r="B71" s="330" t="str">
@@ -16211,8 +16220,8 @@
       <c r="AH71" s="243" t="b" cm="1">
         <f t="array" ref="AH71">$E71=_xlfn.XLOOKUP(
 AG71,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -16327,8 +16336,8 @@
       <c r="AH72" s="243" t="b" cm="1">
         <f t="array" ref="AH72">$E72=_xlfn.XLOOKUP(
 AG72,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -16443,8 +16452,8 @@
       <c r="AH73" s="243" t="b" cm="1">
         <f t="array" ref="AH73">$E73=_xlfn.XLOOKUP(
 AG73,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -16561,8 +16570,8 @@
       <c r="AH74" s="243" t="b" cm="1">
         <f t="array" ref="AH74">$E74=_xlfn.XLOOKUP(
 AG74,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -16679,8 +16688,8 @@
       <c r="AH75" s="243" t="b" cm="1">
         <f t="array" ref="AH75">$E75=_xlfn.XLOOKUP(
 AG75,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -16797,8 +16806,8 @@
       <c r="AH76" s="243" t="b" cm="1">
         <f t="array" ref="AH76">$E76=_xlfn.XLOOKUP(
 AG76,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -16915,8 +16924,8 @@
       <c r="AH77" s="243" t="b" cm="1">
         <f t="array" ref="AH77">$E77=_xlfn.XLOOKUP(
 AG77,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -17031,8 +17040,8 @@
       <c r="AH78" s="243" t="b" cm="1">
         <f t="array" ref="AH78">$E78=_xlfn.XLOOKUP(
 AG78,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -17141,8 +17150,8 @@
       <c r="AH79" s="243" t="b" cm="1">
         <f t="array" ref="AH79">$E79=_xlfn.XLOOKUP(
 AG79,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -17251,8 +17260,8 @@
       <c r="AH80" s="243" t="b" cm="1">
         <f t="array" ref="AH80">$E80=_xlfn.XLOOKUP(
 AG80,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -17357,8 +17366,8 @@
       <c r="AH81" s="243" t="b" cm="1">
         <f t="array" ref="AH81">$E81=_xlfn.XLOOKUP(
 AG81,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -17473,8 +17482,8 @@
       <c r="AH82" s="243" t="b" cm="1">
         <f t="array" ref="AH82">$E82=_xlfn.XLOOKUP(
 AG82,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -17562,8 +17571,8 @@
       <c r="AH83" s="243" t="b" cm="1">
         <f t="array" ref="AH83">$E83=_xlfn.XLOOKUP(
 AG83,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -17672,8 +17681,8 @@
       <c r="AH84" s="243" t="b" cm="1">
         <f t="array" ref="AH84">$E84=_xlfn.XLOOKUP(
 AG84,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -17790,8 +17799,8 @@
       <c r="AH85" s="243" t="b" cm="1">
         <f t="array" ref="AH85">$E85=_xlfn.XLOOKUP(
 AG85,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -17900,8 +17909,8 @@
       <c r="AH86" s="243" t="b" cm="1">
         <f t="array" ref="AH86">$E86=_xlfn.XLOOKUP(
 AG86,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -17993,8 +18002,8 @@
       <c r="AH87" s="243" t="b" cm="1">
         <f t="array" ref="AH87">$E87=_xlfn.XLOOKUP(
 AG87,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -18105,8 +18114,8 @@
       <c r="AH88" s="243" t="b" cm="1">
         <f t="array" ref="AH88">$E88=_xlfn.XLOOKUP(
 AG88,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -18217,8 +18226,8 @@
       <c r="AH89" s="243" t="b" cm="1">
         <f t="array" ref="AH89">$E89=_xlfn.XLOOKUP(
 AG89,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -18329,8 +18338,8 @@
       <c r="AH90" s="243" t="b" cm="1">
         <f t="array" ref="AH90">$E90=_xlfn.XLOOKUP(
 AG90,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -18441,8 +18450,8 @@
       <c r="AH91" s="243" t="b" cm="1">
         <f t="array" ref="AH91">$E91=_xlfn.XLOOKUP(
 AG91,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -18483,11 +18492,11 @@
       <c r="I92" s="138"/>
       <c r="J92" s="164">
         <f t="shared" ca="1" si="27"/>
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K92" s="47">
         <f t="shared" ca="1" si="28"/>
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="L92" s="164" t="s">
         <v>1003</v>
@@ -18539,8 +18548,8 @@
       <c r="AH92" s="243" t="b" cm="1">
         <f t="array" ref="AH92">$E92=_xlfn.XLOOKUP(
 AG92,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -18585,11 +18594,11 @@
       </c>
       <c r="J93" s="164">
         <f t="shared" ca="1" si="27"/>
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="K93" s="47">
         <f t="shared" ca="1" si="28"/>
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L93" s="164" t="s">
         <v>13</v>
@@ -18641,8 +18650,8 @@
       <c r="AH93" s="243" t="b" cm="1">
         <f t="array" ref="AH93">$E93=_xlfn.XLOOKUP(
 AG93,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -18751,8 +18760,8 @@
       <c r="AH94" s="243" t="b" cm="1">
         <f t="array" ref="AH94">$E94=_xlfn.XLOOKUP(
 AG94,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -18840,8 +18849,8 @@
       <c r="AH95" s="243" t="b" cm="1">
         <f t="array" ref="AH95">$E95=_xlfn.XLOOKUP(
 AG95,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -18872,7 +18881,7 @@
         <v>811</v>
       </c>
       <c r="F96" s="174">
-        <f t="shared" ref="F96:F139" si="29">IF($U96=0,$T96+22,$U96+21)</f>
+        <f t="shared" ref="F96:F140" si="29">IF($U96=0,$T96+22,$U96+21)</f>
         <v>46078</v>
       </c>
       <c r="G96" s="31" t="s">
@@ -18885,11 +18894,11 @@
         <v>1</v>
       </c>
       <c r="J96" s="164">
-        <f t="shared" ref="J96:J139" si="30">IF(ISBLANK($W96),_xlfn.DAYS($J$1,$U96),_xlfn.DAYS($W96,$U96))</f>
+        <f t="shared" ref="J96:J140" si="30">IF(ISBLANK($W96),_xlfn.DAYS($J$1,$U96),_xlfn.DAYS($W96,$U96))</f>
         <v>48</v>
       </c>
       <c r="K96" s="47">
-        <f t="shared" ref="K96:K139" si="31">IF(($J96-21)&gt;0,$J96-21,0)</f>
+        <f t="shared" ref="K96:K140" si="31">IF(($J96-21)&gt;0,$J96-21,0)</f>
         <v>27</v>
       </c>
       <c r="L96" s="164"/>
@@ -18950,8 +18959,8 @@
       <c r="AH96" s="243" t="b" cm="1">
         <f t="array" ref="AH96">$E96=_xlfn.XLOOKUP(
 AG96,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -19058,8 +19067,8 @@
       <c r="AH97" s="243" t="b" cm="1">
         <f t="array" ref="AH97">$E97=_xlfn.XLOOKUP(
 AG97,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -19166,8 +19175,8 @@
       <c r="AH98" s="243" t="b" cm="1">
         <f t="array" ref="AH98">$E98=_xlfn.XLOOKUP(
 AG98,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -19278,8 +19287,8 @@
       <c r="AH99" s="243" t="b" cm="1">
         <f t="array" ref="AH99">$E99=_xlfn.XLOOKUP(
 AG99,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -19386,8 +19395,8 @@
       <c r="AH100" s="243" t="b" cm="1">
         <f t="array" ref="AH100">$E100=_xlfn.XLOOKUP(
 AG100,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -19492,8 +19501,8 @@
       <c r="AH101" s="243" t="b" cm="1">
         <f t="array" ref="AH101">$E101=_xlfn.XLOOKUP(
 AG101,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -19584,8 +19593,8 @@
       <c r="AH102" s="243" t="b" cm="1">
         <f t="array" ref="AH102">$E102=_xlfn.XLOOKUP(
 AG102,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -19696,8 +19705,8 @@
       <c r="AH103" s="243" t="b" cm="1">
         <f t="array" ref="AH103">$E103=_xlfn.XLOOKUP(
 AG103,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -19808,8 +19817,8 @@
       <c r="AH104" s="243" t="b" cm="1">
         <f t="array" ref="AH104">$E104=_xlfn.XLOOKUP(
 AG104,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -19920,8 +19929,8 @@
       <c r="AH105" s="243" t="b" cm="1">
         <f t="array" ref="AH105">$E105=_xlfn.XLOOKUP(
 AG105,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -20028,8 +20037,8 @@
       <c r="AH106" s="243" t="b" cm="1">
         <f t="array" ref="AH106">$E106=_xlfn.XLOOKUP(
 AG106,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -20119,8 +20128,8 @@
       <c r="AH107" s="243" t="b" cm="1">
         <f t="array" ref="AH107">$E107=_xlfn.XLOOKUP(
 AG107,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -20225,8 +20234,8 @@
       <c r="AH108" s="243" t="b" cm="1">
         <f t="array" ref="AH108">$E108=_xlfn.XLOOKUP(
 AG108,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -20333,8 +20342,8 @@
       <c r="AH109" s="243" t="b" cm="1">
         <f t="array" ref="AH109">$E109=_xlfn.XLOOKUP(
 AG109,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -20437,8 +20446,8 @@
       <c r="AH110" s="243" t="b" cm="1">
         <f t="array" ref="AH110">$E110=_xlfn.XLOOKUP(
 AG110,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -20481,11 +20490,11 @@
       <c r="I111" s="23"/>
       <c r="J111" s="164">
         <f t="shared" ca="1" si="30"/>
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K111" s="47">
         <f t="shared" ca="1" si="31"/>
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L111" s="164" t="s">
         <v>13</v>
@@ -20535,8 +20544,8 @@
       <c r="AH111" s="243" t="b" cm="1">
         <f t="array" ref="AH111">$E111=_xlfn.XLOOKUP(
 AG111,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -20641,8 +20650,8 @@
       <c r="AH112" s="243" t="b" cm="1">
         <f t="array" ref="AH112">$E112=_xlfn.XLOOKUP(
 AG112,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -20747,8 +20756,8 @@
       <c r="AH113" s="243" t="b" cm="1">
         <f t="array" ref="AH113">$E113=_xlfn.XLOOKUP(
 AG113,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -20853,8 +20862,8 @@
       <c r="AH114" s="243" t="b" cm="1">
         <f t="array" ref="AH114">$E114=_xlfn.XLOOKUP(
 AG114,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -20961,8 +20970,8 @@
       <c r="AH115" s="243" t="b" cm="1">
         <f t="array" ref="AH115">$E115=_xlfn.XLOOKUP(
 AG115,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -21073,8 +21082,8 @@
       <c r="AH116" s="243" t="b" cm="1">
         <f t="array" ref="AH116">$E116=_xlfn.XLOOKUP(
 AG116,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -21115,11 +21124,11 @@
       <c r="I117" s="138"/>
       <c r="J117" s="164">
         <f t="shared" ca="1" si="30"/>
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K117" s="47">
         <f t="shared" ca="1" si="31"/>
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L117" s="164" t="s">
         <v>1003</v>
@@ -21169,8 +21178,8 @@
       <c r="AH117" s="243" t="b" cm="1">
         <f t="array" ref="AH117">$E117=_xlfn.XLOOKUP(
 AG117,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -21261,8 +21270,8 @@
       <c r="AH118" s="243" t="b" cm="1">
         <f t="array" ref="AH118">$E118=_xlfn.XLOOKUP(
 AG118,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -21369,8 +21378,8 @@
       <c r="AH119" s="243" t="b" cm="1">
         <f t="array" ref="AH119">$E119=_xlfn.XLOOKUP(
 AG119,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -21475,8 +21484,8 @@
       <c r="AH120" s="243" t="b" cm="1">
         <f t="array" ref="AH120">$E120=_xlfn.XLOOKUP(
 AG120,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -21567,8 +21576,8 @@
       <c r="AH121" s="243" t="b" cm="1">
         <f t="array" ref="AH121">$E121=_xlfn.XLOOKUP(
 AG121,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -21651,7 +21660,7 @@
       <c r="Y122" s="230"/>
       <c r="Z122" s="227"/>
       <c r="AA122" s="29">
-        <f t="shared" ref="AA122:AA141" si="68">IF(AND($R122="",$I122=""),"",IF(OR($R122="B",$R122="C"),IF($Z122&lt;&gt;"",$Z122+7,IF($Y122&lt;&gt;"",$Y122+8,"")),IF($R122="",IF(OR($I122="B",$I122="C"),IF($W122&lt;&gt;"",$W122+7,IF($V122&lt;&gt;"",$V122+8,""))),"")))</f>
+        <f t="shared" ref="AA122:AA142" si="68">IF(AND($R122="",$I122=""),"",IF(OR($R122="B",$R122="C"),IF($Z122&lt;&gt;"",$Z122+7,IF($Y122&lt;&gt;"",$Y122+8,"")),IF($R122="",IF(OR($I122="B",$I122="C"),IF($W122&lt;&gt;"",$W122+7,IF($V122&lt;&gt;"",$V122+8,""))),"")))</f>
         <v>46286</v>
       </c>
       <c r="AB122" s="229"/>
@@ -21671,8 +21680,8 @@
       <c r="AH122" s="243" t="b" cm="1">
         <f t="array" ref="AH122">$E122=_xlfn.XLOOKUP(
 AG122,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -21763,8 +21772,8 @@
       <c r="AH123" s="243" t="b" cm="1">
         <f t="array" ref="AH123">$E123=_xlfn.XLOOKUP(
 AG123,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
 0,
 -1
@@ -21869,112 +21878,6 @@
       <c r="AH124" s="243" t="b" cm="1">
         <f t="array" ref="AH124">$E124=_xlfn.XLOOKUP(
 AG124,
-_xlfn._xlws.FILTER($AG$7:$AG$4576,$L$7:$L$4576&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4576,$L$7:$L$4576&lt;&gt;"X"),
-"",
-0,
--1
-)</f>
-        <v>1</v>
-      </c>
-      <c r="AI124" s="75" t="str">
-        <f t="shared" ref="AI124:AI141" si="74">IF($AH124,IF(OR($R124="B",$R124="C"),"YES",IF($R124="",IF(OR($I124="B",$I124="C"),"YES",""),"")),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="125" spans="1:35" s="9" customFormat="1" ht="47.25">
-      <c r="A125" s="33">
-        <f t="shared" si="19"/>
-        <v>119</v>
-      </c>
-      <c r="B125" s="330" t="str">
-        <f t="shared" si="72"/>
-        <v>5.11</v>
-      </c>
-      <c r="C125" s="164" t="s">
-        <v>656</v>
-      </c>
-      <c r="D125" s="137" t="s">
-        <v>30</v>
-      </c>
-      <c r="E125" s="25" t="s">
-        <v>997</v>
-      </c>
-      <c r="F125" s="174">
-        <f t="shared" si="29"/>
-        <v>46310</v>
-      </c>
-      <c r="G125" s="31" t="s">
-        <v>998</v>
-      </c>
-      <c r="H125" s="21" t="s">
-        <v>776</v>
-      </c>
-      <c r="I125" s="138" t="s">
-        <v>3</v>
-      </c>
-      <c r="J125" s="164">
-        <f t="shared" si="30"/>
-        <v>11</v>
-      </c>
-      <c r="K125" s="47">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="L125" s="164"/>
-      <c r="M125" s="40" t="s">
-        <v>8</v>
-      </c>
-      <c r="N125" s="41"/>
-      <c r="O125" s="40" t="s">
-        <v>8</v>
-      </c>
-      <c r="P125" s="41"/>
-      <c r="Q125" s="40"/>
-      <c r="R125" s="155"/>
-      <c r="S125" s="27">
-        <v>46289</v>
-      </c>
-      <c r="T125" s="27">
-        <v>46289</v>
-      </c>
-      <c r="U125" s="188">
-        <v>46289</v>
-      </c>
-      <c r="V125" s="29">
-        <v>46297</v>
-      </c>
-      <c r="W125" s="188">
-        <v>46300</v>
-      </c>
-      <c r="X125" s="235" t="s">
-        <v>240</v>
-      </c>
-      <c r="Y125" s="230"/>
-      <c r="Z125" s="227"/>
-      <c r="AA125" s="29" t="b">
-        <f t="shared" si="68"/>
-        <v>0</v>
-      </c>
-      <c r="AB125" s="229"/>
-      <c r="AC125" s="229" t="str">
-        <f t="shared" si="22"/>
-        <v/>
-      </c>
-      <c r="AD125" s="337" t="str">
-        <f t="shared" si="73"/>
-        <v/>
-      </c>
-      <c r="AE125" s="92" t="s">
-        <v>1024</v>
-      </c>
-      <c r="AG125" s="238" t="str">
-        <f t="shared" ref="AG125:AG139" si="75">IF(AND(RIGHT($E125,1)&gt;="A",RIGHT($E125,1)&lt;="Z"),LEFT($E125,LEN($E125)-1),$E125)</f>
-        <v xml:space="preserve"> LTIA-5.11-LTICT-71110-RFA-MAS-0021</v>
-      </c>
-      <c r="AH125" s="243" t="b" cm="1">
-        <f t="array" ref="AH125">$E125=_xlfn.XLOOKUP(
-AG125,
 _xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
 _xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
 "",
@@ -21983,6 +21886,112 @@
 )</f>
         <v>1</v>
       </c>
+      <c r="AI124" s="75" t="str">
+        <f t="shared" ref="AI124:AI142" si="74">IF($AH124,IF(OR($R124="B",$R124="C"),"YES",IF($R124="",IF(OR($I124="B",$I124="C"),"YES",""),"")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="125" spans="1:35" s="9" customFormat="1" ht="47.25">
+      <c r="A125" s="33">
+        <f t="shared" si="19"/>
+        <v>119</v>
+      </c>
+      <c r="B125" s="330" t="str">
+        <f t="shared" si="72"/>
+        <v>5.11</v>
+      </c>
+      <c r="C125" s="164" t="s">
+        <v>656</v>
+      </c>
+      <c r="D125" s="137" t="s">
+        <v>30</v>
+      </c>
+      <c r="E125" s="25" t="s">
+        <v>997</v>
+      </c>
+      <c r="F125" s="174">
+        <f t="shared" si="29"/>
+        <v>46310</v>
+      </c>
+      <c r="G125" s="31" t="s">
+        <v>998</v>
+      </c>
+      <c r="H125" s="21" t="s">
+        <v>776</v>
+      </c>
+      <c r="I125" s="138" t="s">
+        <v>3</v>
+      </c>
+      <c r="J125" s="164">
+        <f t="shared" si="30"/>
+        <v>11</v>
+      </c>
+      <c r="K125" s="47">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="L125" s="164"/>
+      <c r="M125" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="N125" s="41"/>
+      <c r="O125" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="P125" s="41"/>
+      <c r="Q125" s="40"/>
+      <c r="R125" s="155"/>
+      <c r="S125" s="27">
+        <v>46289</v>
+      </c>
+      <c r="T125" s="27">
+        <v>46289</v>
+      </c>
+      <c r="U125" s="188">
+        <v>46289</v>
+      </c>
+      <c r="V125" s="29">
+        <v>46297</v>
+      </c>
+      <c r="W125" s="188">
+        <v>46300</v>
+      </c>
+      <c r="X125" s="235" t="s">
+        <v>240</v>
+      </c>
+      <c r="Y125" s="230"/>
+      <c r="Z125" s="227"/>
+      <c r="AA125" s="29" t="b">
+        <f t="shared" si="68"/>
+        <v>0</v>
+      </c>
+      <c r="AB125" s="229"/>
+      <c r="AC125" s="229" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="AD125" s="337" t="str">
+        <f t="shared" si="73"/>
+        <v/>
+      </c>
+      <c r="AE125" s="92" t="s">
+        <v>1024</v>
+      </c>
+      <c r="AG125" s="238" t="str">
+        <f t="shared" ref="AG125:AG140" si="75">IF(AND(RIGHT($E125,1)&gt;="A",RIGHT($E125,1)&lt;="Z"),LEFT($E125,LEN($E125)-1),$E125)</f>
+        <v xml:space="preserve"> LTIA-5.11-LTICT-71110-RFA-MAS-0021</v>
+      </c>
+      <c r="AH125" s="243" t="b" cm="1">
+        <f t="array" ref="AH125">$E125=_xlfn.XLOOKUP(
+AG125,
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
+"",
+0,
+-1
+)</f>
+        <v>1</v>
+      </c>
       <c r="AI125" s="75" t="str">
         <f t="shared" si="74"/>
         <v/>
@@ -22081,8 +22090,8 @@
       <c r="AH126" s="243" t="b" cm="1">
         <f t="array" ref="AH126">$E126=_xlfn.XLOOKUP(
 AG126,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -22181,8 +22190,8 @@
       <c r="AH127" s="243" t="b" cm="1">
         <f t="array" ref="AH127">$E127=_xlfn.XLOOKUP(
 AG127,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -22225,7 +22234,7 @@
       <c r="I128" s="138"/>
       <c r="J128" s="164">
         <f t="shared" ca="1" si="30"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K128" s="47">
         <f t="shared" ca="1" si="31"/>
@@ -22269,8 +22278,8 @@
       <c r="AH128" s="243" t="b" cm="1">
         <f t="array" ref="AH128">$E128=_xlfn.XLOOKUP(
 AG128,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -22313,7 +22322,7 @@
       <c r="I129" s="138"/>
       <c r="J129" s="164">
         <f t="shared" ca="1" si="30"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K129" s="47">
         <f t="shared" ca="1" si="31"/>
@@ -22359,8 +22368,8 @@
       <c r="AH129" s="243" t="b" cm="1">
         <f t="array" ref="AH129">$E129=_xlfn.XLOOKUP(
 AG129,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -22403,7 +22412,7 @@
       <c r="I130" s="138"/>
       <c r="J130" s="164">
         <f t="shared" ca="1" si="30"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K130" s="47">
         <f t="shared" ca="1" si="31"/>
@@ -22447,8 +22456,8 @@
       <c r="AH130" s="243" t="b" cm="1">
         <f t="array" ref="AH130">$E130=_xlfn.XLOOKUP(
 AG130,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -22491,7 +22500,7 @@
       <c r="I131" s="138"/>
       <c r="J131" s="164">
         <f t="shared" ca="1" si="30"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K131" s="47">
         <f t="shared" ca="1" si="31"/>
@@ -22537,8 +22546,8 @@
       <c r="AH131" s="243" t="b" cm="1">
         <f t="array" ref="AH131">$E131=_xlfn.XLOOKUP(
 AG131,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -22581,7 +22590,7 @@
       <c r="I132" s="138"/>
       <c r="J132" s="164">
         <f t="shared" ca="1" si="30"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K132" s="47">
         <f t="shared" ca="1" si="31"/>
@@ -22627,8 +22636,8 @@
       <c r="AH132" s="243" t="b" cm="1">
         <f t="array" ref="AH132">$E132=_xlfn.XLOOKUP(
 AG132,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -22671,7 +22680,7 @@
       <c r="I133" s="138"/>
       <c r="J133" s="164">
         <f t="shared" ca="1" si="30"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K133" s="47">
         <f t="shared" ca="1" si="31"/>
@@ -22715,8 +22724,8 @@
       <c r="AH133" s="243" t="b" cm="1">
         <f t="array" ref="AH133">$E133=_xlfn.XLOOKUP(
 AG133,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -22759,7 +22768,7 @@
       <c r="I134" s="138"/>
       <c r="J134" s="164">
         <f t="shared" ca="1" si="30"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K134" s="47">
         <f t="shared" ca="1" si="31"/>
@@ -22803,8 +22812,8 @@
       <c r="AH134" s="243" t="b" cm="1">
         <f t="array" ref="AH134">$E134=_xlfn.XLOOKUP(
 AG134,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -22849,7 +22858,7 @@
       </c>
       <c r="J135" s="164">
         <f t="shared" ca="1" si="30"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K135" s="47">
         <f t="shared" ca="1" si="31"/>
@@ -22897,8 +22906,8 @@
       <c r="AH135" s="243" t="b" cm="1">
         <f t="array" ref="AH135">$E135=_xlfn.XLOOKUP(
 AG135,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -22941,7 +22950,7 @@
       <c r="I136" s="138"/>
       <c r="J136" s="164">
         <f t="shared" ca="1" si="30"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K136" s="47">
         <f t="shared" ca="1" si="31"/>
@@ -22985,8 +22994,8 @@
       <c r="AH136" s="243" t="b" cm="1">
         <f t="array" ref="AH136">$E136=_xlfn.XLOOKUP(
 AG136,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -23029,7 +23038,7 @@
       <c r="I137" s="138"/>
       <c r="J137" s="164">
         <f t="shared" ca="1" si="30"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K137" s="47">
         <f t="shared" ca="1" si="31"/>
@@ -23073,8 +23082,8 @@
       <c r="AH137" s="243" t="b" cm="1">
         <f t="array" ref="AH137">$E137=_xlfn.XLOOKUP(
 AG137,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -23117,7 +23126,7 @@
       <c r="I138" s="138"/>
       <c r="J138" s="164">
         <f t="shared" ca="1" si="30"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K138" s="47">
         <f t="shared" ca="1" si="31"/>
@@ -23161,8 +23170,8 @@
       <c r="AH138" s="243" t="b" cm="1">
         <f t="array" ref="AH138">$E138=_xlfn.XLOOKUP(
 AG138,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -23205,7 +23214,7 @@
       <c r="I139" s="138"/>
       <c r="J139" s="164">
         <f t="shared" ca="1" si="30"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K139" s="47">
         <f t="shared" ca="1" si="31"/>
@@ -23249,8 +23258,8 @@
       <c r="AH139" s="243" t="b" cm="1">
         <f t="array" ref="AH139">$E139=_xlfn.XLOOKUP(
 AG139,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -23262,28 +23271,61 @@
         <v/>
       </c>
     </row>
-    <row r="140" spans="1:35" s="9" customFormat="1">
-      <c r="A140" s="33"/>
-      <c r="B140" s="330"/>
-      <c r="C140" s="164"/>
-      <c r="D140" s="137"/>
-      <c r="E140" s="25"/>
-      <c r="F140" s="174"/>
-      <c r="G140" s="31"/>
-      <c r="H140" s="21"/>
+    <row r="140" spans="1:35" s="9" customFormat="1" ht="63">
+      <c r="A140" s="33">
+        <f t="shared" si="19"/>
+        <v>134</v>
+      </c>
+      <c r="B140" s="330" t="str">
+        <f t="shared" ref="B140" si="87">MID(E140, FIND("-", E140) + 1, 4)</f>
+        <v>5.10</v>
+      </c>
+      <c r="C140" s="164" t="s">
+        <v>180</v>
+      </c>
+      <c r="D140" s="137" t="s">
+        <v>32</v>
+      </c>
+      <c r="E140" s="25" t="s">
+        <v>1088</v>
+      </c>
+      <c r="F140" s="174">
+        <f t="shared" si="29"/>
+        <v>46331</v>
+      </c>
+      <c r="G140" s="31" t="s">
+        <v>1089</v>
+      </c>
+      <c r="H140" s="21" t="s">
+        <v>1090</v>
+      </c>
       <c r="I140" s="138"/>
-      <c r="J140" s="164"/>
-      <c r="K140" s="47"/>
+      <c r="J140" s="164">
+        <f t="shared" ca="1" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="K140" s="47">
+        <f t="shared" ca="1" si="31"/>
+        <v>0</v>
+      </c>
       <c r="L140" s="164"/>
-      <c r="M140" s="40"/>
+      <c r="M140" s="40" t="s">
+        <v>8</v>
+      </c>
       <c r="N140" s="41"/>
       <c r="O140" s="40"/>
       <c r="P140" s="41"/>
       <c r="Q140" s="40"/>
       <c r="R140" s="155"/>
-      <c r="S140" s="27"/>
-      <c r="T140" s="27"/>
-      <c r="U140" s="188"/>
+      <c r="S140" s="27">
+        <v>46310</v>
+      </c>
+      <c r="T140" s="27">
+        <v>46310</v>
+      </c>
+      <c r="U140" s="188">
+        <v>46310</v>
+      </c>
       <c r="V140" s="29"/>
       <c r="W140" s="188"/>
       <c r="X140" s="235"/>
@@ -23297,141 +23339,140 @@
       <c r="AC140" s="229"/>
       <c r="AD140" s="337"/>
       <c r="AE140" s="92"/>
-      <c r="AG140" s="238"/>
-      <c r="AH140" s="243"/>
+      <c r="AG140" s="238" t="str">
+        <f t="shared" si="75"/>
+        <v>LTIA-5.10-VIETUR-70000-RFA-OTH-0767</v>
+      </c>
+      <c r="AH140" s="243" t="b" cm="1">
+        <f t="array" ref="AH140">$E140=_xlfn.XLOOKUP(
+AG140,
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
+"",
+0,
+-1
+)</f>
+        <v>1</v>
+      </c>
       <c r="AI140" s="75" t="str">
         <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
-    <row r="141" spans="1:35" s="9" customFormat="1" ht="16.5" thickBot="1">
-      <c r="A141" s="347"/>
-      <c r="B141" s="338"/>
-      <c r="C141" s="178"/>
-      <c r="D141" s="139"/>
-      <c r="E141" s="339"/>
-      <c r="F141" s="340"/>
-      <c r="G141" s="32"/>
-      <c r="H141" s="22"/>
-      <c r="I141" s="139"/>
-      <c r="J141" s="178"/>
-      <c r="K141" s="49"/>
-      <c r="L141" s="178"/>
-      <c r="M141" s="341"/>
-      <c r="N141" s="342"/>
-      <c r="O141" s="341"/>
-      <c r="P141" s="342"/>
-      <c r="Q141" s="341"/>
-      <c r="R141" s="343"/>
-      <c r="S141" s="344"/>
-      <c r="T141" s="344"/>
-      <c r="U141" s="345"/>
-      <c r="V141" s="232"/>
-      <c r="W141" s="345"/>
-      <c r="X141" s="258"/>
-      <c r="Y141" s="232"/>
-      <c r="Z141" s="228"/>
-      <c r="AA141" s="232" t="str">
+    <row r="141" spans="1:35" s="9" customFormat="1">
+      <c r="A141" s="33"/>
+      <c r="B141" s="330"/>
+      <c r="C141" s="164"/>
+      <c r="D141" s="137"/>
+      <c r="E141" s="25"/>
+      <c r="F141" s="174"/>
+      <c r="G141" s="31"/>
+      <c r="H141" s="21"/>
+      <c r="I141" s="138"/>
+      <c r="J141" s="164"/>
+      <c r="K141" s="47"/>
+      <c r="L141" s="164"/>
+      <c r="M141" s="40"/>
+      <c r="N141" s="41"/>
+      <c r="O141" s="40"/>
+      <c r="P141" s="41"/>
+      <c r="Q141" s="40"/>
+      <c r="R141" s="155"/>
+      <c r="S141" s="27"/>
+      <c r="T141" s="27"/>
+      <c r="U141" s="188"/>
+      <c r="V141" s="29"/>
+      <c r="W141" s="188"/>
+      <c r="X141" s="235"/>
+      <c r="Y141" s="230"/>
+      <c r="Z141" s="227"/>
+      <c r="AA141" s="29" t="str">
         <f t="shared" si="68"/>
         <v/>
       </c>
-      <c r="AB141" s="233"/>
-      <c r="AC141" s="233"/>
-      <c r="AD141" s="346"/>
-      <c r="AE141" s="93"/>
-      <c r="AG141" s="239"/>
-      <c r="AH141" s="244"/>
-      <c r="AI141" s="241" t="str">
+      <c r="AB141" s="229"/>
+      <c r="AC141" s="229"/>
+      <c r="AD141" s="337"/>
+      <c r="AE141" s="92"/>
+      <c r="AG141" s="238"/>
+      <c r="AH141" s="243"/>
+      <c r="AI141" s="75" t="str">
         <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
-    <row r="142" spans="1:35" ht="16.5" thickBot="1"/>
-    <row r="143" spans="1:35" ht="16.5" thickBot="1">
-      <c r="A143" s="128"/>
-      <c r="B143" s="128"/>
-      <c r="C143" s="166" t="s">
-        <v>20</v>
-      </c>
-      <c r="D143" s="376" t="s">
-        <v>21</v>
-      </c>
-      <c r="E143" s="376"/>
-      <c r="F143" s="377"/>
-      <c r="G143" s="46"/>
-      <c r="H143" s="68"/>
-      <c r="I143" s="356" t="s">
-        <v>14</v>
-      </c>
-      <c r="J143" s="357"/>
-      <c r="K143" s="357"/>
-      <c r="L143" s="357"/>
-      <c r="M143" s="357"/>
-      <c r="N143" s="358"/>
-      <c r="O143" s="362" t="s">
-        <v>7</v>
-      </c>
-      <c r="P143" s="363"/>
-      <c r="Q143" s="362" t="s">
-        <v>109</v>
-      </c>
-      <c r="R143" s="363"/>
-      <c r="S143" s="1"/>
-      <c r="T143" s="1"/>
-      <c r="U143" s="140"/>
-      <c r="V143" s="1"/>
-      <c r="X143" s="11"/>
-      <c r="Y143" s="11"/>
-      <c r="Z143" s="11"/>
-      <c r="AA143" s="11"/>
-      <c r="AB143" s="11"/>
-      <c r="AC143" s="11"/>
-      <c r="AD143" s="11"/>
-      <c r="AG143" s="11"/>
-      <c r="AH143" s="11"/>
-      <c r="AI143" s="11"/>
-    </row>
+    <row r="142" spans="1:35" s="9" customFormat="1" ht="16.5" thickBot="1">
+      <c r="A142" s="347"/>
+      <c r="B142" s="338"/>
+      <c r="C142" s="178"/>
+      <c r="D142" s="139"/>
+      <c r="E142" s="339"/>
+      <c r="F142" s="340"/>
+      <c r="G142" s="32"/>
+      <c r="H142" s="22"/>
+      <c r="I142" s="139"/>
+      <c r="J142" s="178"/>
+      <c r="K142" s="49"/>
+      <c r="L142" s="178"/>
+      <c r="M142" s="341"/>
+      <c r="N142" s="342"/>
+      <c r="O142" s="341"/>
+      <c r="P142" s="342"/>
+      <c r="Q142" s="341"/>
+      <c r="R142" s="343"/>
+      <c r="S142" s="344"/>
+      <c r="T142" s="344"/>
+      <c r="U142" s="345"/>
+      <c r="V142" s="232"/>
+      <c r="W142" s="345"/>
+      <c r="X142" s="258"/>
+      <c r="Y142" s="232"/>
+      <c r="Z142" s="228"/>
+      <c r="AA142" s="232" t="str">
+        <f t="shared" si="68"/>
+        <v/>
+      </c>
+      <c r="AB142" s="233"/>
+      <c r="AC142" s="233"/>
+      <c r="AD142" s="346"/>
+      <c r="AE142" s="93"/>
+      <c r="AG142" s="239"/>
+      <c r="AH142" s="244"/>
+      <c r="AI142" s="241" t="str">
+        <f t="shared" si="74"/>
+        <v/>
+      </c>
+    </row>
+    <row r="143" spans="1:35" ht="16.5" thickBot="1"/>
     <row r="144" spans="1:35" ht="16.5" thickBot="1">
       <c r="A144" s="128"/>
       <c r="B144" s="128"/>
-      <c r="C144" s="167" t="s">
+      <c r="C144" s="166" t="s">
+        <v>20</v>
+      </c>
+      <c r="D144" s="379" t="s">
+        <v>21</v>
+      </c>
+      <c r="E144" s="379"/>
+      <c r="F144" s="380"/>
+      <c r="G144" s="46"/>
+      <c r="H144" s="68"/>
+      <c r="I144" s="384" t="s">
+        <v>14</v>
+      </c>
+      <c r="J144" s="385"/>
+      <c r="K144" s="385"/>
+      <c r="L144" s="385"/>
+      <c r="M144" s="385"/>
+      <c r="N144" s="386"/>
+      <c r="O144" s="382" t="s">
+        <v>7</v>
+      </c>
+      <c r="P144" s="383"/>
+      <c r="Q144" s="382" t="s">
         <v>109</v>
       </c>
-      <c r="D144" s="354" t="s">
-        <v>111</v>
-      </c>
-      <c r="E144" s="354"/>
-      <c r="F144" s="355"/>
-      <c r="G144" s="46"/>
-      <c r="H144" s="46"/>
-      <c r="I144" s="356" t="s">
-        <v>19</v>
-      </c>
-      <c r="J144" s="357"/>
-      <c r="K144" s="357"/>
-      <c r="L144" s="358"/>
-      <c r="M144" s="105">
-        <f t="shared" ref="M144:M149" ca="1" si="87">N144/$N$144</f>
-        <v>1</v>
-      </c>
-      <c r="N144" s="106">
-        <f ca="1">SUM($N$145:$N$149)</f>
-        <v>139</v>
-      </c>
-      <c r="O144" s="102" t="s">
-        <v>15</v>
-      </c>
-      <c r="P144" s="103" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q144" s="105">
-        <f ca="1">R144/$R$144</f>
-        <v>1</v>
-      </c>
-      <c r="R144" s="220">
-        <f ca="1">SUM(R145:R148)</f>
-        <v>121</v>
-      </c>
+      <c r="R144" s="383"/>
       <c r="S144" s="1"/>
       <c r="T144" s="1"/>
       <c r="U144" s="140"/>
@@ -23447,48 +23488,46 @@
       <c r="AH144" s="11"/>
       <c r="AI144" s="11"/>
     </row>
-    <row r="145" spans="1:35">
+    <row r="145" spans="1:35" ht="16.5" thickBot="1">
       <c r="A145" s="128"/>
       <c r="B145" s="128"/>
       <c r="C145" s="167" t="s">
-        <v>22</v>
-      </c>
-      <c r="D145" s="354" t="s">
-        <v>23</v>
-      </c>
-      <c r="E145" s="354"/>
-      <c r="F145" s="355"/>
-      <c r="G145" s="70"/>
-      <c r="H145" s="6"/>
-      <c r="I145" s="379" t="s">
-        <v>66</v>
-      </c>
-      <c r="J145" s="380"/>
-      <c r="K145" s="380"/>
-      <c r="L145" s="381"/>
-      <c r="M145" s="107">
-        <f t="shared" ca="1" si="87"/>
-        <v>0.49640287769784175</v>
-      </c>
-      <c r="N145" s="108">
-        <f>COUNTIF($I$7:$I$141,"A")</f>
-        <v>69</v>
-      </c>
-      <c r="O145" s="100">
-        <f ca="1">COUNTIFS($J$7:$J$141,"&lt;=21",$I$7:$I$141,"A")</f>
-        <v>56</v>
-      </c>
-      <c r="P145" s="101">
-        <f ca="1">COUNTIFS($J$7:$J$141,"&gt;21",$I$7:$I$141,"A")</f>
-        <v>12</v>
-      </c>
-      <c r="Q145" s="107">
-        <f ca="1">R145/$R$144</f>
-        <v>0.41322314049586778</v>
-      </c>
-      <c r="R145" s="108">
-        <f>COUNTIF($R$7:$R$141,"A")</f>
-        <v>50</v>
+        <v>109</v>
+      </c>
+      <c r="D145" s="404" t="s">
+        <v>111</v>
+      </c>
+      <c r="E145" s="404"/>
+      <c r="F145" s="405"/>
+      <c r="G145" s="46"/>
+      <c r="H145" s="46"/>
+      <c r="I145" s="384" t="s">
+        <v>19</v>
+      </c>
+      <c r="J145" s="385"/>
+      <c r="K145" s="385"/>
+      <c r="L145" s="386"/>
+      <c r="M145" s="105">
+        <f t="shared" ref="M145:M150" ca="1" si="88">N145/$N$145</f>
+        <v>1</v>
+      </c>
+      <c r="N145" s="106">
+        <f ca="1">SUM($N$146:$N$150)</f>
+        <v>140</v>
+      </c>
+      <c r="O145" s="102" t="s">
+        <v>15</v>
+      </c>
+      <c r="P145" s="103" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q145" s="105">
+        <f ca="1">R145/$R$145</f>
+        <v>1</v>
+      </c>
+      <c r="R145" s="220">
+        <f ca="1">SUM(R146:R149)</f>
+        <v>122</v>
       </c>
       <c r="S145" s="1"/>
       <c r="T145" s="1"/>
@@ -23509,43 +23548,44 @@
       <c r="A146" s="128"/>
       <c r="B146" s="128"/>
       <c r="C146" s="167" t="s">
-        <v>24</v>
-      </c>
-      <c r="D146" s="354" t="s">
-        <v>25</v>
-      </c>
-      <c r="E146" s="354"/>
-      <c r="F146" s="355"/>
+        <v>22</v>
+      </c>
+      <c r="D146" s="404" t="s">
+        <v>23</v>
+      </c>
+      <c r="E146" s="404"/>
+      <c r="F146" s="405"/>
+      <c r="G146" s="70"/>
       <c r="H146" s="6"/>
-      <c r="I146" s="382" t="s">
-        <v>67</v>
-      </c>
-      <c r="J146" s="383"/>
-      <c r="K146" s="383"/>
-      <c r="L146" s="384"/>
-      <c r="M146" s="109">
-        <f t="shared" ca="1" si="87"/>
-        <v>0.10071942446043165</v>
-      </c>
-      <c r="N146" s="110">
-        <f>COUNTIF($I$7:$I$141,"B")</f>
-        <v>14</v>
-      </c>
-      <c r="O146" s="98">
-        <f ca="1">COUNTIFS($J$7:$J$141,"&lt;=21",$I$7:$I$141,"B")</f>
-        <v>7</v>
-      </c>
-      <c r="P146" s="50">
-        <f ca="1">COUNTIFS($J$7:$J$141,"&gt;21",$I$7:$I$141,"B")</f>
-        <v>7</v>
-      </c>
-      <c r="Q146" s="109">
-        <f t="shared" ref="Q146:Q148" ca="1" si="88">R146/$R$144</f>
-        <v>7.43801652892562E-2</v>
-      </c>
-      <c r="R146" s="110">
-        <f>COUNTIF($R$7:$R$141,"B")</f>
-        <v>9</v>
+      <c r="I146" s="387" t="s">
+        <v>66</v>
+      </c>
+      <c r="J146" s="388"/>
+      <c r="K146" s="388"/>
+      <c r="L146" s="389"/>
+      <c r="M146" s="107">
+        <f t="shared" ca="1" si="88"/>
+        <v>0.49285714285714288</v>
+      </c>
+      <c r="N146" s="108">
+        <f>COUNTIF($I$7:$I$142,"A")</f>
+        <v>69</v>
+      </c>
+      <c r="O146" s="100">
+        <f ca="1">COUNTIFS($J$7:$J$142,"&lt;=21",$I$7:$I$142,"A")</f>
+        <v>56</v>
+      </c>
+      <c r="P146" s="101">
+        <f ca="1">COUNTIFS($J$7:$J$142,"&gt;21",$I$7:$I$142,"A")</f>
+        <v>12</v>
+      </c>
+      <c r="Q146" s="107">
+        <f ca="1">R146/$R$145</f>
+        <v>0.4098360655737705</v>
+      </c>
+      <c r="R146" s="108">
+        <f>COUNTIF($R$7:$R$142,"A")</f>
+        <v>50</v>
       </c>
       <c r="S146" s="1"/>
       <c r="T146" s="1"/>
@@ -23563,47 +23603,46 @@
       <c r="AI146" s="11"/>
     </row>
     <row r="147" spans="1:35">
-      <c r="A147" s="129"/>
-      <c r="B147" s="129"/>
+      <c r="A147" s="128"/>
+      <c r="B147" s="128"/>
       <c r="C147" s="167" t="s">
-        <v>26</v>
-      </c>
-      <c r="D147" s="354" t="s">
-        <v>27</v>
-      </c>
-      <c r="E147" s="354"/>
-      <c r="F147" s="355"/>
-      <c r="G147" s="71"/>
+        <v>24</v>
+      </c>
+      <c r="D147" s="404" t="s">
+        <v>25</v>
+      </c>
+      <c r="E147" s="404"/>
+      <c r="F147" s="405"/>
       <c r="H147" s="6"/>
-      <c r="I147" s="385" t="s">
-        <v>68</v>
-      </c>
-      <c r="J147" s="386"/>
-      <c r="K147" s="386"/>
-      <c r="L147" s="387"/>
-      <c r="M147" s="111">
-        <f t="shared" ca="1" si="87"/>
-        <v>0.19424460431654678</v>
-      </c>
-      <c r="N147" s="112">
-        <f>COUNTIF($I$7:$I$141,"C")</f>
-        <v>27</v>
+      <c r="I147" s="390" t="s">
+        <v>67</v>
+      </c>
+      <c r="J147" s="391"/>
+      <c r="K147" s="391"/>
+      <c r="L147" s="392"/>
+      <c r="M147" s="109">
+        <f t="shared" ca="1" si="88"/>
+        <v>0.1</v>
+      </c>
+      <c r="N147" s="110">
+        <f>COUNTIF($I$7:$I$142,"B")</f>
+        <v>14</v>
       </c>
       <c r="O147" s="98">
-        <f ca="1">COUNTIFS($J$7:$J$141,"&lt;=21",$I$7:$I$141,"C")</f>
-        <v>13</v>
+        <f ca="1">COUNTIFS($J$7:$J$142,"&lt;=21",$I$7:$I$142,"B")</f>
+        <v>7</v>
       </c>
       <c r="P147" s="50">
-        <f ca="1">COUNTIFS($J$7:$J$141,"&gt;21",$I$7:$I$141,"C")</f>
-        <v>14</v>
-      </c>
-      <c r="Q147" s="111">
-        <f t="shared" ca="1" si="88"/>
-        <v>0.14049586776859505</v>
-      </c>
-      <c r="R147" s="112">
-        <f>COUNTIF($R$7:$R$141,"C")</f>
-        <v>17</v>
+        <f ca="1">COUNTIFS($J$7:$J$142,"&gt;21",$I$7:$I$142,"B")</f>
+        <v>7</v>
+      </c>
+      <c r="Q147" s="109">
+        <f t="shared" ref="Q147:Q149" ca="1" si="89">R147/$R$145</f>
+        <v>7.3770491803278687E-2</v>
+      </c>
+      <c r="R147" s="110">
+        <f>COUNTIF($R$7:$R$142,"B")</f>
+        <v>9</v>
       </c>
       <c r="S147" s="1"/>
       <c r="T147" s="1"/>
@@ -23623,48 +23662,47 @@
     <row r="148" spans="1:35">
       <c r="A148" s="129"/>
       <c r="B148" s="129"/>
-      <c r="C148" s="168" t="s">
-        <v>28</v>
-      </c>
-      <c r="D148" s="354" t="s">
-        <v>29</v>
-      </c>
-      <c r="E148" s="354"/>
-      <c r="F148" s="355"/>
-      <c r="G148" s="72"/>
-      <c r="I148" s="388" t="s">
-        <v>70</v>
-      </c>
-      <c r="J148" s="389"/>
-      <c r="K148" s="389"/>
-      <c r="L148" s="390"/>
-      <c r="M148" s="114">
-        <f t="shared" ca="1" si="87"/>
-        <v>0.10071942446043165</v>
-      </c>
-      <c r="N148" s="115">
-        <f ca="1">SUM(O148:P148)</f>
+      <c r="C148" s="167" t="s">
+        <v>26</v>
+      </c>
+      <c r="D148" s="404" t="s">
+        <v>27</v>
+      </c>
+      <c r="E148" s="404"/>
+      <c r="F148" s="405"/>
+      <c r="G148" s="71"/>
+      <c r="H148" s="6"/>
+      <c r="I148" s="393" t="s">
+        <v>68</v>
+      </c>
+      <c r="J148" s="394"/>
+      <c r="K148" s="394"/>
+      <c r="L148" s="395"/>
+      <c r="M148" s="111">
+        <f t="shared" ca="1" si="88"/>
+        <v>0.19285714285714287</v>
+      </c>
+      <c r="N148" s="112">
+        <f>COUNTIF($I$7:$I$142,"C")</f>
+        <v>27</v>
+      </c>
+      <c r="O148" s="98">
+        <f ca="1">COUNTIFS($J$7:$J$142,"&lt;=21",$I$7:$I$142,"C")</f>
+        <v>13</v>
+      </c>
+      <c r="P148" s="50">
+        <f ca="1">COUNTIFS($J$7:$J$142,"&gt;21",$I$7:$I$142,"C")</f>
         <v>14</v>
       </c>
-      <c r="O148" s="98">
-        <f ca="1">COUNTIFS($J$7:$J$141,"&lt;=21",$V$7:$V$141,"",$L$7:$L$141,"&lt;&gt;X")</f>
-        <v>12</v>
-      </c>
-      <c r="P148" s="50">
-        <f ca="1">COUNTIFS($J$7:$J$141,"&gt;21",$V$7:$V$141,"",$L$7:$L$141,"&lt;&gt;X")</f>
-        <v>2</v>
-      </c>
-      <c r="Q148" s="114">
-        <f t="shared" ca="1" si="88"/>
-        <v>0.37190082644628097</v>
-      </c>
-      <c r="R148" s="115">
-        <f ca="1">COUNTIFS($J$7:$J$141,"&gt;=0",$Q$7:$Q$141,"",$L$7:$L$141,"&lt;&gt;X")</f>
-        <v>45</v>
-      </c>
-      <c r="S148" s="1" t="s">
-        <v>10</v>
-      </c>
+      <c r="Q148" s="111">
+        <f t="shared" ca="1" si="89"/>
+        <v>0.13934426229508196</v>
+      </c>
+      <c r="R148" s="112">
+        <f>COUNTIF($R$7:$R$142,"C")</f>
+        <v>17</v>
+      </c>
+      <c r="S148" s="1"/>
       <c r="T148" s="1"/>
       <c r="U148" s="140"/>
       <c r="V148" s="1"/>
@@ -23679,97 +23717,122 @@
       <c r="AH148" s="11"/>
       <c r="AI148" s="11"/>
     </row>
-    <row r="149" spans="1:35" ht="16.5" thickBot="1">
+    <row r="149" spans="1:35">
       <c r="A149" s="129"/>
       <c r="B149" s="129"/>
       <c r="C149" s="168" t="s">
+        <v>28</v>
+      </c>
+      <c r="D149" s="404" t="s">
+        <v>29</v>
+      </c>
+      <c r="E149" s="404"/>
+      <c r="F149" s="405"/>
+      <c r="G149" s="72"/>
+      <c r="I149" s="396" t="s">
+        <v>70</v>
+      </c>
+      <c r="J149" s="397"/>
+      <c r="K149" s="397"/>
+      <c r="L149" s="398"/>
+      <c r="M149" s="114">
+        <f t="shared" ca="1" si="88"/>
+        <v>0.10714285714285714</v>
+      </c>
+      <c r="N149" s="115">
+        <f ca="1">SUM(O149:P149)</f>
+        <v>15</v>
+      </c>
+      <c r="O149" s="98">
+        <f ca="1">COUNTIFS($J$7:$J$142,"&lt;=21",$V$7:$V$142,"",$L$7:$L$142,"&lt;&gt;X")</f>
+        <v>13</v>
+      </c>
+      <c r="P149" s="50">
+        <f ca="1">COUNTIFS($J$7:$J$142,"&gt;21",$V$7:$V$142,"",$L$7:$L$142,"&lt;&gt;X")</f>
+        <v>2</v>
+      </c>
+      <c r="Q149" s="114">
+        <f t="shared" ca="1" si="89"/>
+        <v>0.37704918032786883</v>
+      </c>
+      <c r="R149" s="115">
+        <f ca="1">COUNTIFS($J$7:$J$142,"&gt;=0",$Q$7:$Q$142,"",$L$7:$L$142,"&lt;&gt;X")</f>
+        <v>46</v>
+      </c>
+      <c r="S149" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="T149" s="1"/>
+      <c r="U149" s="140"/>
+      <c r="V149" s="1"/>
+      <c r="X149" s="11"/>
+      <c r="Y149" s="11"/>
+      <c r="Z149" s="11"/>
+      <c r="AA149" s="11"/>
+      <c r="AB149" s="11"/>
+      <c r="AC149" s="11"/>
+      <c r="AD149" s="11"/>
+      <c r="AG149" s="11"/>
+      <c r="AH149" s="11"/>
+      <c r="AI149" s="11"/>
+    </row>
+    <row r="150" spans="1:35" ht="16.5" thickBot="1">
+      <c r="A150" s="129"/>
+      <c r="B150" s="129"/>
+      <c r="C150" s="168" t="s">
         <v>30</v>
       </c>
-      <c r="D149" s="354" t="s">
+      <c r="D150" s="404" t="s">
         <v>31</v>
       </c>
-      <c r="E149" s="354"/>
-      <c r="F149" s="355"/>
-      <c r="H149" s="6"/>
-      <c r="I149" s="391" t="s">
+      <c r="E150" s="404"/>
+      <c r="F150" s="405"/>
+      <c r="H150" s="6"/>
+      <c r="I150" s="399" t="s">
         <v>71</v>
       </c>
-      <c r="J149" s="392"/>
-      <c r="K149" s="392"/>
-      <c r="L149" s="393"/>
-      <c r="M149" s="113">
-        <f t="shared" ca="1" si="87"/>
-        <v>0.1079136690647482</v>
-      </c>
-      <c r="N149" s="97">
-        <f>COUNTIFS($L$7:$L$141,"X")</f>
+      <c r="J150" s="400"/>
+      <c r="K150" s="400"/>
+      <c r="L150" s="401"/>
+      <c r="M150" s="113">
+        <f t="shared" ca="1" si="88"/>
+        <v>0.10714285714285714</v>
+      </c>
+      <c r="N150" s="97">
+        <f>COUNTIFS($L$7:$L$142,"X")</f>
         <v>15</v>
       </c>
-      <c r="O149" s="99"/>
-      <c r="P149" s="51"/>
-      <c r="Q149" s="221"/>
-      <c r="R149" s="222"/>
-    </row>
-    <row r="150" spans="1:35">
-      <c r="A150" s="128"/>
-      <c r="B150" s="128"/>
-      <c r="C150" s="168" t="s">
+      <c r="O150" s="99"/>
+      <c r="P150" s="51"/>
+      <c r="Q150" s="221"/>
+      <c r="R150" s="222"/>
+    </row>
+    <row r="151" spans="1:35">
+      <c r="A151" s="128"/>
+      <c r="B151" s="128"/>
+      <c r="C151" s="168" t="s">
         <v>32</v>
       </c>
-      <c r="D150" s="354" t="s">
+      <c r="D151" s="404" t="s">
         <v>33</v>
       </c>
-      <c r="E150" s="354"/>
-      <c r="F150" s="355"/>
-      <c r="H150" s="1" t="s">
+      <c r="E151" s="404"/>
+      <c r="F151" s="405"/>
+      <c r="H151" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="151" spans="1:35">
-      <c r="C151" s="167" t="s">
+    <row r="152" spans="1:35">
+      <c r="C152" s="167" t="s">
         <v>34</v>
       </c>
-      <c r="D151" s="354" t="s">
+      <c r="D152" s="404" t="s">
         <v>35</v>
       </c>
-      <c r="E151" s="354"/>
-      <c r="F151" s="355"/>
-      <c r="H151" s="13"/>
-      <c r="I151" s="141"/>
-      <c r="J151" s="141"/>
-      <c r="K151" s="13"/>
-      <c r="L151" s="141"/>
-      <c r="M151" s="6"/>
-      <c r="N151" s="6"/>
-      <c r="O151" s="6"/>
-      <c r="P151" s="6"/>
-      <c r="Q151" s="6"/>
-      <c r="S151" s="6"/>
-      <c r="T151" s="1"/>
-      <c r="U151" s="140"/>
-      <c r="V151" s="1"/>
-      <c r="W151" s="140"/>
-      <c r="X151" s="1"/>
-      <c r="Y151" s="1"/>
-      <c r="Z151" s="1"/>
-      <c r="AA151" s="1"/>
-      <c r="AB151" s="1"/>
-      <c r="AC151" s="1"/>
-      <c r="AD151" s="1"/>
-      <c r="AG151" s="160"/>
-      <c r="AH151" s="1"/>
-      <c r="AI151" s="1"/>
-    </row>
-    <row r="152" spans="1:35">
-      <c r="C152" s="394" t="s">
-        <v>75</v>
-      </c>
-      <c r="D152" s="350" t="s">
-        <v>76</v>
-      </c>
-      <c r="E152" s="350"/>
-      <c r="F152" s="351"/>
+      <c r="E152" s="404"/>
+      <c r="F152" s="405"/>
       <c r="H152" s="13"/>
+      <c r="I152" s="141"/>
       <c r="J152" s="141"/>
       <c r="K152" s="13"/>
       <c r="L152" s="141"/>
@@ -23794,13 +23857,16 @@
       <c r="AH152" s="1"/>
       <c r="AI152" s="1"/>
     </row>
-    <row r="153" spans="1:35" ht="16.5" thickBot="1">
-      <c r="C153" s="395"/>
-      <c r="D153" s="352"/>
-      <c r="E153" s="352"/>
-      <c r="F153" s="353"/>
+    <row r="153" spans="1:35">
+      <c r="C153" s="402" t="s">
+        <v>75</v>
+      </c>
+      <c r="D153" s="408" t="s">
+        <v>76</v>
+      </c>
+      <c r="E153" s="408"/>
+      <c r="F153" s="409"/>
       <c r="H153" s="13"/>
-      <c r="I153" s="141"/>
       <c r="J153" s="141"/>
       <c r="K153" s="13"/>
       <c r="L153" s="141"/>
@@ -23825,7 +23891,11 @@
       <c r="AH153" s="1"/>
       <c r="AI153" s="1"/>
     </row>
-    <row r="154" spans="1:35">
+    <row r="154" spans="1:35" ht="16.5" thickBot="1">
+      <c r="C154" s="403"/>
+      <c r="D154" s="410"/>
+      <c r="E154" s="410"/>
+      <c r="F154" s="411"/>
       <c r="H154" s="13"/>
       <c r="I154" s="141"/>
       <c r="J154" s="141"/>
@@ -23853,12 +23923,6 @@
       <c r="AI154" s="1"/>
     </row>
     <row r="155" spans="1:35">
-      <c r="C155" s="378" t="s">
-        <v>41</v>
-      </c>
-      <c r="D155" s="378"/>
-      <c r="E155" s="378"/>
-      <c r="F155" s="378"/>
       <c r="H155" s="13"/>
       <c r="I155" s="141"/>
       <c r="J155" s="141"/>
@@ -23886,14 +23950,12 @@
       <c r="AI155" s="1"/>
     </row>
     <row r="156" spans="1:35">
-      <c r="C156" s="169" t="s">
-        <v>8</v>
-      </c>
-      <c r="D156" s="396" t="s">
-        <v>91</v>
-      </c>
-      <c r="E156" s="396"/>
-      <c r="F156" s="396"/>
+      <c r="C156" s="381" t="s">
+        <v>41</v>
+      </c>
+      <c r="D156" s="381"/>
+      <c r="E156" s="381"/>
+      <c r="F156" s="381"/>
       <c r="H156" s="13"/>
       <c r="I156" s="141"/>
       <c r="J156" s="141"/>
@@ -23924,11 +23986,11 @@
       <c r="C157" s="169" t="s">
         <v>8</v>
       </c>
-      <c r="D157" s="396" t="s">
-        <v>92</v>
-      </c>
-      <c r="E157" s="396"/>
-      <c r="F157" s="396"/>
+      <c r="D157" s="367" t="s">
+        <v>91</v>
+      </c>
+      <c r="E157" s="367"/>
+      <c r="F157" s="367"/>
       <c r="H157" s="13"/>
       <c r="I157" s="141"/>
       <c r="J157" s="141"/>
@@ -23959,11 +24021,11 @@
       <c r="C158" s="169" t="s">
         <v>8</v>
       </c>
-      <c r="D158" s="396" t="s">
-        <v>93</v>
-      </c>
-      <c r="E158" s="396"/>
-      <c r="F158" s="396"/>
+      <c r="D158" s="367" t="s">
+        <v>92</v>
+      </c>
+      <c r="E158" s="367"/>
+      <c r="F158" s="367"/>
       <c r="H158" s="13"/>
       <c r="I158" s="141"/>
       <c r="J158" s="141"/>
@@ -23990,7 +24052,15 @@
       <c r="AH158" s="1"/>
       <c r="AI158" s="1"/>
     </row>
-    <row r="159" spans="1:35" ht="16.5" thickBot="1">
+    <row r="159" spans="1:35">
+      <c r="C159" s="169" t="s">
+        <v>8</v>
+      </c>
+      <c r="D159" s="367" t="s">
+        <v>93</v>
+      </c>
+      <c r="E159" s="367"/>
+      <c r="F159" s="367"/>
       <c r="H159" s="13"/>
       <c r="I159" s="141"/>
       <c r="J159" s="141"/>
@@ -24018,12 +24088,6 @@
       <c r="AI159" s="1"/>
     </row>
     <row r="160" spans="1:35" ht="16.5" thickBot="1">
-      <c r="C160" s="402" t="s">
-        <v>96</v>
-      </c>
-      <c r="D160" s="403"/>
-      <c r="E160" s="403"/>
-      <c r="F160" s="404"/>
       <c r="H160" s="13"/>
       <c r="I160" s="141"/>
       <c r="J160" s="141"/>
@@ -24050,15 +24114,13 @@
       <c r="AH160" s="1"/>
       <c r="AI160" s="1"/>
     </row>
-    <row r="161" spans="3:35">
-      <c r="C161" s="212" t="s">
-        <v>81</v>
-      </c>
-      <c r="D161" s="405" t="s">
-        <v>97</v>
-      </c>
-      <c r="E161" s="405"/>
-      <c r="F161" s="406"/>
+    <row r="161" spans="3:35" ht="16.5" thickBot="1">
+      <c r="C161" s="371" t="s">
+        <v>96</v>
+      </c>
+      <c r="D161" s="372"/>
+      <c r="E161" s="372"/>
+      <c r="F161" s="373"/>
       <c r="H161" s="13"/>
       <c r="I161" s="141"/>
       <c r="J161" s="141"/>
@@ -24086,112 +24148,190 @@
       <c r="AI161" s="1"/>
     </row>
     <row r="162" spans="3:35">
-      <c r="C162" s="213" t="s">
-        <v>82</v>
-      </c>
-      <c r="D162" s="397" t="s">
-        <v>98</v>
-      </c>
-      <c r="E162" s="397"/>
-      <c r="F162" s="398"/>
+      <c r="C162" s="212" t="s">
+        <v>81</v>
+      </c>
+      <c r="D162" s="374" t="s">
+        <v>97</v>
+      </c>
+      <c r="E162" s="374"/>
+      <c r="F162" s="375"/>
+      <c r="H162" s="13"/>
+      <c r="I162" s="141"/>
+      <c r="J162" s="141"/>
+      <c r="K162" s="13"/>
+      <c r="L162" s="141"/>
+      <c r="M162" s="6"/>
+      <c r="N162" s="6"/>
+      <c r="O162" s="6"/>
+      <c r="P162" s="6"/>
+      <c r="Q162" s="6"/>
+      <c r="S162" s="6"/>
+      <c r="T162" s="1"/>
+      <c r="U162" s="140"/>
+      <c r="V162" s="1"/>
+      <c r="W162" s="140"/>
+      <c r="X162" s="1"/>
+      <c r="Y162" s="1"/>
+      <c r="Z162" s="1"/>
+      <c r="AA162" s="1"/>
+      <c r="AB162" s="1"/>
+      <c r="AC162" s="1"/>
+      <c r="AD162" s="1"/>
+      <c r="AG162" s="160"/>
+      <c r="AH162" s="1"/>
+      <c r="AI162" s="1"/>
     </row>
     <row r="163" spans="3:35">
       <c r="C163" s="213" t="s">
+        <v>82</v>
+      </c>
+      <c r="D163" s="365" t="s">
+        <v>98</v>
+      </c>
+      <c r="E163" s="365"/>
+      <c r="F163" s="366"/>
+    </row>
+    <row r="164" spans="3:35">
+      <c r="C164" s="213" t="s">
         <v>83</v>
       </c>
-      <c r="D163" s="397" t="s">
+      <c r="D164" s="365" t="s">
         <v>99</v>
       </c>
-      <c r="E163" s="397"/>
-      <c r="F163" s="398"/>
-    </row>
-    <row r="164" spans="3:35">
-      <c r="C164" s="214" t="s">
-        <v>84</v>
-      </c>
-      <c r="D164" s="397" t="s">
-        <v>100</v>
-      </c>
-      <c r="E164" s="397"/>
-      <c r="F164" s="398"/>
+      <c r="E164" s="365"/>
+      <c r="F164" s="366"/>
     </row>
     <row r="165" spans="3:35">
       <c r="C165" s="214" t="s">
+        <v>84</v>
+      </c>
+      <c r="D165" s="365" t="s">
+        <v>100</v>
+      </c>
+      <c r="E165" s="365"/>
+      <c r="F165" s="366"/>
+    </row>
+    <row r="166" spans="3:35">
+      <c r="C166" s="214" t="s">
         <v>85</v>
       </c>
-      <c r="D165" s="397" t="s">
+      <c r="D166" s="365" t="s">
         <v>101</v>
       </c>
-      <c r="E165" s="397"/>
-      <c r="F165" s="398"/>
-    </row>
-    <row r="166" spans="3:35" ht="18.75">
-      <c r="C166" s="214" t="s">
+      <c r="E166" s="365"/>
+      <c r="F166" s="366"/>
+    </row>
+    <row r="167" spans="3:35" ht="18.75">
+      <c r="C167" s="214" t="s">
         <v>86</v>
       </c>
-      <c r="D166" s="397" t="s">
+      <c r="D167" s="365" t="s">
         <v>102</v>
       </c>
-      <c r="E166" s="397"/>
-      <c r="F166" s="398"/>
-    </row>
-    <row r="167" spans="3:35" ht="18.75">
-      <c r="C167" s="213" t="s">
+      <c r="E167" s="365"/>
+      <c r="F167" s="366"/>
+    </row>
+    <row r="168" spans="3:35" ht="18.75">
+      <c r="C168" s="213" t="s">
         <v>87</v>
       </c>
-      <c r="D167" s="397" t="s">
+      <c r="D168" s="365" t="s">
         <v>103</v>
       </c>
-      <c r="E167" s="397"/>
-      <c r="F167" s="398"/>
-    </row>
-    <row r="168" spans="3:35">
-      <c r="C168" s="215" t="s">
+      <c r="E168" s="365"/>
+      <c r="F168" s="366"/>
+    </row>
+    <row r="169" spans="3:35">
+      <c r="C169" s="215" t="s">
         <v>88</v>
       </c>
-      <c r="D168" s="399" t="s">
+      <c r="D169" s="368" t="s">
         <v>104</v>
       </c>
-      <c r="E168" s="400"/>
-      <c r="F168" s="401"/>
-    </row>
-    <row r="169" spans="3:35" ht="18.75">
-      <c r="C169" s="215" t="s">
+      <c r="E169" s="369"/>
+      <c r="F169" s="370"/>
+    </row>
+    <row r="170" spans="3:35" ht="18.75">
+      <c r="C170" s="215" t="s">
         <v>89</v>
       </c>
-      <c r="D169" s="397" t="s">
+      <c r="D170" s="365" t="s">
         <v>105</v>
       </c>
-      <c r="E169" s="397"/>
-      <c r="F169" s="398"/>
-    </row>
-    <row r="170" spans="3:35">
-      <c r="C170" s="213" t="s">
+      <c r="E170" s="365"/>
+      <c r="F170" s="366"/>
+    </row>
+    <row r="171" spans="3:35">
+      <c r="C171" s="213" t="s">
         <v>90</v>
       </c>
-      <c r="D170" s="397" t="s">
+      <c r="D171" s="365" t="s">
         <v>106</v>
       </c>
-      <c r="E170" s="397"/>
-      <c r="F170" s="398"/>
-    </row>
-    <row r="171" spans="3:35" ht="16.5" thickBot="1">
-      <c r="C171" s="216" t="s">
+      <c r="E171" s="365"/>
+      <c r="F171" s="366"/>
+    </row>
+    <row r="172" spans="3:35" ht="16.5" thickBot="1">
+      <c r="C172" s="216" t="s">
         <v>94</v>
       </c>
-      <c r="D171" s="373" t="s">
+      <c r="D172" s="376" t="s">
         <v>107</v>
       </c>
-      <c r="E171" s="374"/>
-      <c r="F171" s="375"/>
+      <c r="E172" s="377"/>
+      <c r="F172" s="378"/>
     </row>
   </sheetData>
-  <autoFilter ref="A6:AE141" xr:uid="{C724CDAB-378C-47DB-9F45-08EE3BFB6E8B}">
+  <autoFilter ref="A6:AE142" xr:uid="{C724CDAB-378C-47DB-9F45-08EE3BFB6E8B}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A7:AE69">
       <sortCondition ref="T6:T69"/>
     </sortState>
   </autoFilter>
   <mergeCells count="59">
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="D153:F154"/>
+    <mergeCell ref="D145:F145"/>
+    <mergeCell ref="I145:L145"/>
+    <mergeCell ref="AA4:AD4"/>
+    <mergeCell ref="Q144:R144"/>
+    <mergeCell ref="D150:F150"/>
+    <mergeCell ref="D151:F151"/>
+    <mergeCell ref="D152:F152"/>
+    <mergeCell ref="S4:U4"/>
+    <mergeCell ref="L4:L5"/>
+    <mergeCell ref="Q4:R4"/>
+    <mergeCell ref="K4:K5"/>
+    <mergeCell ref="Y4:Z4"/>
+    <mergeCell ref="D172:F172"/>
+    <mergeCell ref="D144:F144"/>
+    <mergeCell ref="C156:F156"/>
+    <mergeCell ref="O144:P144"/>
+    <mergeCell ref="I144:N144"/>
+    <mergeCell ref="I146:L146"/>
+    <mergeCell ref="I147:L147"/>
+    <mergeCell ref="I148:L148"/>
+    <mergeCell ref="I149:L149"/>
+    <mergeCell ref="I150:L150"/>
+    <mergeCell ref="C153:C154"/>
+    <mergeCell ref="D146:F146"/>
+    <mergeCell ref="D147:F147"/>
+    <mergeCell ref="D148:F148"/>
+    <mergeCell ref="D149:F149"/>
+    <mergeCell ref="D157:F157"/>
+    <mergeCell ref="D171:F171"/>
+    <mergeCell ref="D158:F158"/>
+    <mergeCell ref="D159:F159"/>
+    <mergeCell ref="D166:F166"/>
+    <mergeCell ref="D167:F167"/>
+    <mergeCell ref="D168:F168"/>
+    <mergeCell ref="D169:F169"/>
+    <mergeCell ref="D170:F170"/>
+    <mergeCell ref="C161:F161"/>
+    <mergeCell ref="D162:F162"/>
+    <mergeCell ref="D163:F163"/>
+    <mergeCell ref="D164:F164"/>
+    <mergeCell ref="D165:F165"/>
     <mergeCell ref="AG5:AG6"/>
     <mergeCell ref="AH5:AH6"/>
     <mergeCell ref="AI5:AI6"/>
@@ -24208,52 +24348,9 @@
     <mergeCell ref="V4:X4"/>
     <mergeCell ref="M4:N4"/>
     <mergeCell ref="O4:P4"/>
-    <mergeCell ref="D170:F170"/>
-    <mergeCell ref="D157:F157"/>
-    <mergeCell ref="D158:F158"/>
-    <mergeCell ref="D165:F165"/>
-    <mergeCell ref="D166:F166"/>
-    <mergeCell ref="D167:F167"/>
-    <mergeCell ref="D168:F168"/>
-    <mergeCell ref="D169:F169"/>
-    <mergeCell ref="C160:F160"/>
-    <mergeCell ref="D161:F161"/>
-    <mergeCell ref="D162:F162"/>
-    <mergeCell ref="D163:F163"/>
-    <mergeCell ref="D164:F164"/>
-    <mergeCell ref="D171:F171"/>
-    <mergeCell ref="D143:F143"/>
-    <mergeCell ref="C155:F155"/>
-    <mergeCell ref="O143:P143"/>
-    <mergeCell ref="I143:N143"/>
-    <mergeCell ref="I145:L145"/>
-    <mergeCell ref="I146:L146"/>
-    <mergeCell ref="I147:L147"/>
-    <mergeCell ref="I148:L148"/>
-    <mergeCell ref="I149:L149"/>
-    <mergeCell ref="C152:C153"/>
-    <mergeCell ref="D145:F145"/>
-    <mergeCell ref="D146:F146"/>
-    <mergeCell ref="D147:F147"/>
-    <mergeCell ref="D148:F148"/>
-    <mergeCell ref="D156:F156"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="D152:F153"/>
-    <mergeCell ref="D144:F144"/>
-    <mergeCell ref="I144:L144"/>
-    <mergeCell ref="AA4:AD4"/>
-    <mergeCell ref="Q143:R143"/>
-    <mergeCell ref="D149:F149"/>
-    <mergeCell ref="D150:F150"/>
-    <mergeCell ref="D151:F151"/>
-    <mergeCell ref="S4:U4"/>
-    <mergeCell ref="L4:L5"/>
-    <mergeCell ref="Q4:R4"/>
-    <mergeCell ref="K4:K5"/>
-    <mergeCell ref="Y4:Z4"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
-  <conditionalFormatting sqref="A7:AE141 AG7:AI141">
+  <conditionalFormatting sqref="A7:AE142 AG7:AI142">
     <cfRule type="expression" dxfId="18" priority="15" stopIfTrue="1">
       <formula>$L7="X"</formula>
     </cfRule>
@@ -24513,9 +24610,9 @@
     <hyperlink ref="P66" r:id="rId234" xr:uid="{943197F0-AD92-4E20-ACB9-85E2FC8AC2B6}"/>
     <hyperlink ref="P68" r:id="rId235" xr:uid="{B8D8E563-954E-4146-81D8-6B9C7FA5754F}"/>
     <hyperlink ref="P69" r:id="rId236" xr:uid="{B36E752F-3B1E-43A8-9FDB-009F10632DBE}"/>
-    <hyperlink ref="C156" r:id="rId237" xr:uid="{8E310CD5-A28F-4463-BCF0-54C44E66ED53}"/>
-    <hyperlink ref="C157" r:id="rId238" xr:uid="{5182D641-FE70-4AC5-A684-B03DCC409CD2}"/>
-    <hyperlink ref="C158" r:id="rId239" xr:uid="{1AA76CB8-C0E3-43B4-9061-99A680A3D3C7}"/>
+    <hyperlink ref="C157" r:id="rId237" xr:uid="{8E310CD5-A28F-4463-BCF0-54C44E66ED53}"/>
+    <hyperlink ref="C158" r:id="rId238" xr:uid="{5182D641-FE70-4AC5-A684-B03DCC409CD2}"/>
+    <hyperlink ref="C159" r:id="rId239" xr:uid="{1AA76CB8-C0E3-43B4-9061-99A680A3D3C7}"/>
     <hyperlink ref="Q7" r:id="rId240" xr:uid="{D3D10629-3F3E-4216-8F11-F525BC7A698A}"/>
     <hyperlink ref="Q8" r:id="rId241" xr:uid="{91F15092-AC5D-4C7E-9E23-E3913E29C1F3}"/>
     <hyperlink ref="Q9" r:id="rId242" xr:uid="{381D2B0A-72F0-4FCE-A724-4D1E565A253A}"/>
@@ -24779,9 +24876,10 @@
     <hyperlink ref="M137" r:id="rId500" xr:uid="{796282C8-8FC2-4043-A523-A0A91C9DD849}"/>
     <hyperlink ref="M138" r:id="rId501" xr:uid="{24F8F9C1-0497-4EC1-849F-4BFB6EF701D0}"/>
     <hyperlink ref="M139" r:id="rId502" xr:uid="{D1C7F371-1906-4C4E-9D64-07CD74AF282A}"/>
+    <hyperlink ref="M140" r:id="rId503" xr:uid="{1BAE53B4-41B2-4955-9719-066BE2284B9D}"/>
   </hyperlinks>
   <pageMargins left="0.25" right="0.17" top="0.5" bottom="0.25" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="28" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId503"/>
+  <pageSetup paperSize="9" scale="28" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId504"/>
   <colBreaks count="1" manualBreakCount="1">
     <brk id="30" max="564" man="1"/>
   </colBreaks>
@@ -24834,7 +24932,7 @@
       </c>
       <c r="I1" s="176">
         <f ca="1">TODAY()</f>
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="J1" s="131"/>
       <c r="K1" s="197"/>
@@ -24919,88 +25017,88 @@
       <c r="AD3" s="159"/>
     </row>
     <row r="4" spans="1:35" s="5" customFormat="1" ht="36" customHeight="1" thickBot="1">
-      <c r="A4" s="408" t="s">
+      <c r="A4" s="350" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="348" t="s">
+      <c r="B4" s="406" t="s">
         <v>515</v>
       </c>
-      <c r="C4" s="414" t="s">
+      <c r="C4" s="359" t="s">
         <v>45</v>
       </c>
-      <c r="D4" s="369" t="s">
+      <c r="D4" s="348" t="s">
         <v>46</v>
       </c>
-      <c r="E4" s="412" t="s">
+      <c r="E4" s="357" t="s">
         <v>47</v>
       </c>
-      <c r="F4" s="369" t="s">
+      <c r="F4" s="348" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="410" t="s">
+      <c r="G4" s="355" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="366" t="s">
+      <c r="H4" s="352" t="s">
         <v>48</v>
       </c>
-      <c r="I4" s="366" t="s">
+      <c r="I4" s="352" t="s">
         <v>49</v>
       </c>
-      <c r="J4" s="369" t="s">
+      <c r="J4" s="348" t="s">
         <v>78</v>
       </c>
-      <c r="K4" s="366" t="s">
+      <c r="K4" s="352" t="s">
         <v>80</v>
       </c>
-      <c r="L4" s="364" t="s">
+      <c r="L4" s="363" t="s">
         <v>53</v>
       </c>
-      <c r="M4" s="365"/>
-      <c r="N4" s="368" t="s">
+      <c r="M4" s="364"/>
+      <c r="N4" s="362" t="s">
         <v>55</v>
       </c>
-      <c r="O4" s="365"/>
-      <c r="P4" s="368" t="s">
+      <c r="O4" s="364"/>
+      <c r="P4" s="362" t="s">
         <v>72</v>
       </c>
-      <c r="Q4" s="365"/>
-      <c r="R4" s="364" t="s">
+      <c r="Q4" s="364"/>
+      <c r="R4" s="363" t="s">
         <v>53</v>
       </c>
-      <c r="S4" s="364"/>
-      <c r="T4" s="365"/>
-      <c r="U4" s="368" t="s">
+      <c r="S4" s="363"/>
+      <c r="T4" s="364"/>
+      <c r="U4" s="362" t="s">
         <v>55</v>
       </c>
-      <c r="V4" s="364"/>
-      <c r="W4" s="365"/>
-      <c r="X4" s="371" t="s">
+      <c r="V4" s="363"/>
+      <c r="W4" s="364"/>
+      <c r="X4" s="415" t="s">
         <v>72</v>
       </c>
-      <c r="Y4" s="417"/>
-      <c r="Z4" s="371" t="s">
+      <c r="Y4" s="427"/>
+      <c r="Z4" s="415" t="s">
         <v>112</v>
       </c>
-      <c r="AA4" s="360"/>
-      <c r="AB4" s="360"/>
-      <c r="AC4" s="361"/>
-      <c r="AD4" s="369" t="s">
+      <c r="AA4" s="413"/>
+      <c r="AB4" s="413"/>
+      <c r="AC4" s="414"/>
+      <c r="AD4" s="348" t="s">
         <v>79</v>
       </c>
       <c r="AG4" s="236"/>
     </row>
     <row r="5" spans="1:35" ht="78.75">
-      <c r="A5" s="409"/>
-      <c r="B5" s="349"/>
-      <c r="C5" s="415"/>
-      <c r="D5" s="370"/>
-      <c r="E5" s="413"/>
-      <c r="F5" s="370"/>
-      <c r="G5" s="411"/>
-      <c r="H5" s="367"/>
-      <c r="I5" s="367"/>
-      <c r="J5" s="370"/>
-      <c r="K5" s="367"/>
+      <c r="A5" s="351"/>
+      <c r="B5" s="407"/>
+      <c r="C5" s="360"/>
+      <c r="D5" s="354"/>
+      <c r="E5" s="358"/>
+      <c r="F5" s="354"/>
+      <c r="G5" s="356"/>
+      <c r="H5" s="353"/>
+      <c r="I5" s="353"/>
+      <c r="J5" s="354"/>
+      <c r="K5" s="353"/>
       <c r="L5" s="79" t="s">
         <v>52</v>
       </c>
@@ -25055,14 +25153,14 @@
       <c r="AC5" s="250" t="s">
         <v>118</v>
       </c>
-      <c r="AD5" s="416"/>
-      <c r="AG5" s="422" t="s">
+      <c r="AD5" s="361"/>
+      <c r="AG5" s="417" t="s">
         <v>119</v>
       </c>
-      <c r="AH5" s="424" t="s">
+      <c r="AH5" s="419" t="s">
         <v>120</v>
       </c>
-      <c r="AI5" s="426" t="s">
+      <c r="AI5" s="421" t="s">
         <v>121</v>
       </c>
     </row>
@@ -25097,9 +25195,9 @@
       <c r="AB6" s="86"/>
       <c r="AC6" s="86"/>
       <c r="AD6" s="74"/>
-      <c r="AG6" s="423"/>
-      <c r="AH6" s="425"/>
-      <c r="AI6" s="427"/>
+      <c r="AG6" s="418"/>
+      <c r="AH6" s="420"/>
+      <c r="AI6" s="422"/>
     </row>
     <row r="7" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A7" s="33">
@@ -25775,7 +25873,7 @@
       </c>
       <c r="AC12" s="183">
         <f t="shared" ca="1" si="7"/>
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AD12" s="92"/>
       <c r="AG12" s="238" t="str">
@@ -26001,7 +26099,7 @@
       </c>
       <c r="AC14" s="183">
         <f t="shared" ca="1" si="7"/>
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AD14" s="92"/>
       <c r="AG14" s="238" t="str">
@@ -26227,7 +26325,7 @@
       </c>
       <c r="AC16" s="183">
         <f t="shared" ca="1" si="7"/>
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AD16" s="92"/>
       <c r="AG16" s="238" t="str">
@@ -26340,7 +26438,7 @@
       </c>
       <c r="AC17" s="183">
         <f t="shared" ca="1" si="7"/>
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AD17" s="92"/>
       <c r="AG17" s="238" t="str">
@@ -26453,7 +26551,7 @@
       </c>
       <c r="AC18" s="183">
         <f t="shared" ca="1" si="7"/>
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AD18" s="92"/>
       <c r="AG18" s="238" t="str">
@@ -27028,7 +27126,7 @@
       </c>
       <c r="AC23" s="183">
         <f t="shared" ca="1" si="7"/>
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AD23" s="92"/>
       <c r="AG23" s="238" t="str">
@@ -27141,7 +27239,7 @@
       </c>
       <c r="AC24" s="183">
         <f t="shared" ca="1" si="7"/>
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AD24" s="92"/>
       <c r="AG24" s="238" t="str">
@@ -27252,7 +27350,7 @@
       </c>
       <c r="AC25" s="183">
         <f t="shared" ca="1" si="7"/>
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AD25" s="92" t="s">
         <v>887</v>
@@ -27367,7 +27465,7 @@
       </c>
       <c r="AC26" s="183">
         <f t="shared" ca="1" si="7"/>
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AD26" s="92"/>
       <c r="AG26" s="238" t="str">
@@ -27480,7 +27578,7 @@
       </c>
       <c r="AC27" s="183">
         <f t="shared" ca="1" si="7"/>
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AD27" s="92"/>
       <c r="AG27" s="238" t="str">
@@ -27799,7 +27897,7 @@
       </c>
       <c r="AC30" s="183">
         <f t="shared" ca="1" si="7"/>
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AD30" s="92" t="s">
         <v>593</v>
@@ -27854,11 +27952,11 @@
       </c>
       <c r="I31" s="164">
         <f ca="1">IF(ISBLANK($V31),_xlfn.DAYS($I$1,$T31),_xlfn.DAYS($V31,$T31))</f>
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="J31" s="47">
         <f t="shared" ca="1" si="4"/>
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K31" s="164"/>
       <c r="L31" s="54" t="s">
@@ -28257,7 +28355,7 @@
       <c r="H35" s="138"/>
       <c r="I35" s="164">
         <f t="shared" ca="1" si="10"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J35" s="47">
         <f t="shared" ca="1" si="4"/>
@@ -28453,11 +28551,11 @@
       </c>
       <c r="I37" s="164">
         <f t="shared" ca="1" si="10"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J37" s="47">
         <f t="shared" ca="1" si="4"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K37" s="164"/>
       <c r="L37" s="54" t="s">
@@ -28651,7 +28749,7 @@
       <c r="H39" s="138"/>
       <c r="I39" s="164">
         <f t="shared" ca="1" si="10"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J39" s="47">
         <f t="shared" ca="1" si="4"/>
@@ -28742,7 +28840,7 @@
       <c r="H40" s="138"/>
       <c r="I40" s="164">
         <f t="shared" ca="1" si="10"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J40" s="47">
         <f t="shared" ca="1" si="4"/>
@@ -28886,28 +28984,28 @@
       <c r="C44" s="166" t="s">
         <v>20</v>
       </c>
-      <c r="D44" s="376" t="s">
+      <c r="D44" s="379" t="s">
         <v>21</v>
       </c>
-      <c r="E44" s="377"/>
+      <c r="E44" s="380"/>
       <c r="F44" s="46"/>
       <c r="G44" s="46"/>
-      <c r="H44" s="356" t="s">
+      <c r="H44" s="384" t="s">
         <v>14</v>
       </c>
-      <c r="I44" s="357"/>
-      <c r="J44" s="357"/>
-      <c r="K44" s="357"/>
-      <c r="L44" s="357"/>
-      <c r="M44" s="358"/>
-      <c r="N44" s="362" t="s">
+      <c r="I44" s="385"/>
+      <c r="J44" s="385"/>
+      <c r="K44" s="385"/>
+      <c r="L44" s="385"/>
+      <c r="M44" s="386"/>
+      <c r="N44" s="382" t="s">
         <v>7</v>
       </c>
-      <c r="O44" s="363"/>
-      <c r="P44" s="362" t="s">
+      <c r="O44" s="383"/>
+      <c r="P44" s="382" t="s">
         <v>109</v>
       </c>
-      <c r="Q44" s="363"/>
+      <c r="Q44" s="383"/>
       <c r="R44" s="1"/>
       <c r="S44" s="1"/>
       <c r="T44" s="140"/>
@@ -28927,17 +29025,17 @@
       <c r="C45" s="195" t="s">
         <v>109</v>
       </c>
-      <c r="D45" s="420" t="s">
+      <c r="D45" s="425" t="s">
         <v>111</v>
       </c>
-      <c r="E45" s="421"/>
+      <c r="E45" s="426"/>
       <c r="F45" s="46"/>
-      <c r="H45" s="356" t="s">
+      <c r="H45" s="384" t="s">
         <v>18</v>
       </c>
-      <c r="I45" s="357"/>
-      <c r="J45" s="357"/>
-      <c r="K45" s="358"/>
+      <c r="I45" s="385"/>
+      <c r="J45" s="385"/>
+      <c r="K45" s="386"/>
       <c r="L45" s="105">
         <f ca="1">M45/$M$45</f>
         <v>1</v>
@@ -28979,18 +29077,18 @@
       <c r="C46" s="195" t="s">
         <v>36</v>
       </c>
-      <c r="D46" s="418" t="s">
+      <c r="D46" s="423" t="s">
         <v>37</v>
       </c>
-      <c r="E46" s="419"/>
+      <c r="E46" s="424"/>
       <c r="F46" s="69"/>
       <c r="G46" s="6"/>
-      <c r="H46" s="379" t="s">
+      <c r="H46" s="387" t="s">
         <v>66</v>
       </c>
-      <c r="I46" s="380"/>
-      <c r="J46" s="380"/>
-      <c r="K46" s="381"/>
+      <c r="I46" s="388"/>
+      <c r="J46" s="388"/>
+      <c r="K46" s="389"/>
       <c r="L46" s="107">
         <f ca="1">M46/$M$45</f>
         <v>2.7777777777777776E-2</v>
@@ -29031,21 +29129,21 @@
       <c r="AI46" s="11"/>
     </row>
     <row r="47" spans="1:35">
-      <c r="C47" s="394" t="s">
+      <c r="C47" s="402" t="s">
         <v>75</v>
       </c>
-      <c r="D47" s="350" t="s">
+      <c r="D47" s="408" t="s">
         <v>76</v>
       </c>
-      <c r="E47" s="351"/>
+      <c r="E47" s="409"/>
       <c r="F47" s="70"/>
       <c r="G47" s="6"/>
-      <c r="H47" s="382" t="s">
+      <c r="H47" s="390" t="s">
         <v>67</v>
       </c>
-      <c r="I47" s="383"/>
-      <c r="J47" s="383"/>
-      <c r="K47" s="384"/>
+      <c r="I47" s="391"/>
+      <c r="J47" s="391"/>
+      <c r="K47" s="392"/>
       <c r="L47" s="109">
         <f t="shared" ref="L47:L50" ca="1" si="23">M47/$M$45</f>
         <v>0.55555555555555558</v>
@@ -29086,17 +29184,17 @@
       <c r="AI47" s="11"/>
     </row>
     <row r="48" spans="1:35" ht="16.5" thickBot="1">
-      <c r="C48" s="395"/>
-      <c r="D48" s="352"/>
-      <c r="E48" s="353"/>
+      <c r="C48" s="403"/>
+      <c r="D48" s="410"/>
+      <c r="E48" s="411"/>
       <c r="F48" s="71"/>
       <c r="G48" s="6"/>
-      <c r="H48" s="385" t="s">
+      <c r="H48" s="393" t="s">
         <v>68</v>
       </c>
-      <c r="I48" s="386"/>
-      <c r="J48" s="386"/>
-      <c r="K48" s="387"/>
+      <c r="I48" s="394"/>
+      <c r="J48" s="394"/>
+      <c r="K48" s="395"/>
       <c r="L48" s="111">
         <f t="shared" ca="1" si="23"/>
         <v>0.22222222222222221</v>
@@ -29139,12 +29237,12 @@
     <row r="49" spans="3:35">
       <c r="F49" s="72"/>
       <c r="G49" s="6"/>
-      <c r="H49" s="388" t="s">
+      <c r="H49" s="396" t="s">
         <v>70</v>
       </c>
-      <c r="I49" s="389"/>
-      <c r="J49" s="389"/>
-      <c r="K49" s="390"/>
+      <c r="I49" s="397"/>
+      <c r="J49" s="397"/>
+      <c r="K49" s="398"/>
       <c r="L49" s="114">
         <f t="shared" ca="1" si="23"/>
         <v>0.1388888888888889</v>
@@ -29187,17 +29285,17 @@
       <c r="AI49" s="11"/>
     </row>
     <row r="50" spans="3:35" ht="16.5" thickBot="1">
-      <c r="C50" s="378" t="s">
+      <c r="C50" s="381" t="s">
         <v>41</v>
       </c>
-      <c r="D50" s="378"/>
-      <c r="E50" s="378"/>
-      <c r="H50" s="391" t="s">
+      <c r="D50" s="381"/>
+      <c r="E50" s="381"/>
+      <c r="H50" s="399" t="s">
         <v>71</v>
       </c>
-      <c r="I50" s="392"/>
-      <c r="J50" s="392"/>
-      <c r="K50" s="393"/>
+      <c r="I50" s="400"/>
+      <c r="J50" s="400"/>
+      <c r="K50" s="401"/>
       <c r="L50" s="113">
         <f t="shared" ca="1" si="23"/>
         <v>5.5555555555555552E-2</v>
@@ -29242,6 +29340,27 @@
     </sortState>
   </autoFilter>
   <mergeCells count="37">
+    <mergeCell ref="P44:Q44"/>
+    <mergeCell ref="X4:Y4"/>
+    <mergeCell ref="Z4:AC4"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D44:E44"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="D46:E46"/>
+    <mergeCell ref="C50:E50"/>
+    <mergeCell ref="H46:K46"/>
+    <mergeCell ref="H47:K47"/>
+    <mergeCell ref="H44:M44"/>
+    <mergeCell ref="H48:K48"/>
+    <mergeCell ref="H49:K49"/>
+    <mergeCell ref="C47:C48"/>
+    <mergeCell ref="D47:E48"/>
+    <mergeCell ref="D45:E45"/>
     <mergeCell ref="AG5:AG6"/>
     <mergeCell ref="AH5:AH6"/>
     <mergeCell ref="AI5:AI6"/>
@@ -29258,27 +29377,6 @@
     <mergeCell ref="K4:K5"/>
     <mergeCell ref="P4:Q4"/>
     <mergeCell ref="J4:J5"/>
-    <mergeCell ref="D46:E46"/>
-    <mergeCell ref="C50:E50"/>
-    <mergeCell ref="H46:K46"/>
-    <mergeCell ref="H47:K47"/>
-    <mergeCell ref="H44:M44"/>
-    <mergeCell ref="H48:K48"/>
-    <mergeCell ref="H49:K49"/>
-    <mergeCell ref="C47:C48"/>
-    <mergeCell ref="D47:E48"/>
-    <mergeCell ref="D45:E45"/>
-    <mergeCell ref="P44:Q44"/>
-    <mergeCell ref="X4:Y4"/>
-    <mergeCell ref="Z4:AC4"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D44:E44"/>
-    <mergeCell ref="B4:B5"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="A7:AD42 AG7:AI42">
@@ -29492,7 +29590,7 @@
       </c>
       <c r="I1" s="176">
         <f ca="1">TODAY()</f>
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="J1" s="131"/>
       <c r="K1" s="197"/>
@@ -29563,81 +29661,81 @@
       <c r="Z3" s="159"/>
     </row>
     <row r="4" spans="1:26" s="5" customFormat="1" ht="35.1" customHeight="1" thickBot="1">
-      <c r="A4" s="348" t="s">
+      <c r="A4" s="406" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="348" t="s">
+      <c r="B4" s="406" t="s">
         <v>515</v>
       </c>
-      <c r="C4" s="414" t="s">
+      <c r="C4" s="359" t="s">
         <v>45</v>
       </c>
-      <c r="D4" s="369" t="s">
+      <c r="D4" s="348" t="s">
         <v>46</v>
       </c>
-      <c r="E4" s="437" t="s">
+      <c r="E4" s="428" t="s">
         <v>47</v>
       </c>
-      <c r="F4" s="369" t="s">
+      <c r="F4" s="348" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="439" t="s">
+      <c r="G4" s="430" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="366" t="s">
+      <c r="H4" s="352" t="s">
         <v>48</v>
       </c>
-      <c r="I4" s="441" t="s">
+      <c r="I4" s="432" t="s">
         <v>49</v>
       </c>
-      <c r="J4" s="369" t="s">
+      <c r="J4" s="348" t="s">
         <v>78</v>
       </c>
-      <c r="K4" s="366" t="s">
+      <c r="K4" s="352" t="s">
         <v>80</v>
       </c>
-      <c r="L4" s="368" t="s">
+      <c r="L4" s="362" t="s">
         <v>53</v>
       </c>
-      <c r="M4" s="365"/>
-      <c r="N4" s="368" t="s">
+      <c r="M4" s="364"/>
+      <c r="N4" s="362" t="s">
         <v>55</v>
       </c>
-      <c r="O4" s="365"/>
-      <c r="P4" s="368" t="s">
+      <c r="O4" s="364"/>
+      <c r="P4" s="362" t="s">
         <v>72</v>
       </c>
-      <c r="Q4" s="365"/>
-      <c r="R4" s="364" t="s">
+      <c r="Q4" s="364"/>
+      <c r="R4" s="363" t="s">
         <v>53</v>
       </c>
-      <c r="S4" s="364"/>
-      <c r="T4" s="365"/>
-      <c r="U4" s="368" t="s">
+      <c r="S4" s="363"/>
+      <c r="T4" s="364"/>
+      <c r="U4" s="362" t="s">
         <v>55</v>
       </c>
-      <c r="V4" s="364"/>
-      <c r="W4" s="364"/>
-      <c r="X4" s="371" t="s">
+      <c r="V4" s="363"/>
+      <c r="W4" s="363"/>
+      <c r="X4" s="415" t="s">
         <v>72</v>
       </c>
-      <c r="Y4" s="372"/>
-      <c r="Z4" s="365" t="s">
+      <c r="Y4" s="416"/>
+      <c r="Z4" s="364" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="72" customHeight="1">
-      <c r="A5" s="349"/>
-      <c r="B5" s="349"/>
-      <c r="C5" s="415"/>
-      <c r="D5" s="370"/>
-      <c r="E5" s="438"/>
-      <c r="F5" s="370"/>
-      <c r="G5" s="440"/>
-      <c r="H5" s="367"/>
-      <c r="I5" s="442"/>
-      <c r="J5" s="370"/>
-      <c r="K5" s="367"/>
+      <c r="A5" s="407"/>
+      <c r="B5" s="407"/>
+      <c r="C5" s="360"/>
+      <c r="D5" s="354"/>
+      <c r="E5" s="429"/>
+      <c r="F5" s="354"/>
+      <c r="G5" s="431"/>
+      <c r="H5" s="353"/>
+      <c r="I5" s="433"/>
+      <c r="J5" s="354"/>
+      <c r="K5" s="353"/>
       <c r="L5" s="79" t="s">
         <v>52</v>
       </c>
@@ -29680,7 +29778,7 @@
       <c r="Y5" s="260" t="s">
         <v>114</v>
       </c>
-      <c r="Z5" s="416"/>
+      <c r="Z5" s="361"/>
     </row>
     <row r="6" spans="1:26" ht="15" customHeight="1" thickBot="1">
       <c r="A6" s="78"/>
@@ -32237,11 +32335,11 @@
       <c r="H39" s="138"/>
       <c r="I39" s="164">
         <f t="shared" ca="1" si="9"/>
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="J39" s="47">
         <f t="shared" ca="1" si="10"/>
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="K39" s="164"/>
       <c r="L39" s="40"/>
@@ -34643,11 +34741,11 @@
       </c>
       <c r="I70" s="164">
         <f t="shared" ref="I70:I78" ca="1" si="14">IF(ISBLANK($V70),_xlfn.DAYS($I$1,$T70),_xlfn.DAYS($V70,$T70))</f>
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="J70" s="47">
         <f t="shared" ref="J70:J78" ca="1" si="15">IF(($I70-21)&gt;0,$I70-21,0)</f>
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K70" s="164"/>
       <c r="L70" s="40"/>
@@ -36601,11 +36699,11 @@
       <c r="H97" s="138"/>
       <c r="I97" s="164">
         <f t="shared" ca="1" si="24"/>
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="J97" s="47">
         <f t="shared" ca="1" si="25"/>
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K97" s="164"/>
       <c r="L97" s="40" t="s">
@@ -37721,11 +37819,11 @@
       <c r="H112" s="138"/>
       <c r="I112" s="164">
         <f t="shared" ca="1" si="24"/>
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="J112" s="47">
         <f t="shared" ca="1" si="25"/>
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K112" s="164" t="s">
         <v>13</v>
@@ -37788,11 +37886,11 @@
       </c>
       <c r="I113" s="164">
         <f t="shared" ca="1" si="24"/>
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J113" s="47">
         <f t="shared" ca="1" si="25"/>
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K113" s="164"/>
       <c r="L113" s="40" t="s">
@@ -37924,11 +38022,11 @@
       <c r="H115" s="138"/>
       <c r="I115" s="164">
         <f t="shared" ca="1" si="24"/>
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J115" s="47">
         <f t="shared" ca="1" si="25"/>
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K115" s="164"/>
       <c r="L115" s="40" t="s">
@@ -38594,7 +38692,7 @@
       </c>
       <c r="I125" s="164">
         <f t="shared" ca="1" si="24"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J125" s="47">
         <f t="shared" ca="1" si="25"/>
@@ -38659,7 +38757,7 @@
       </c>
       <c r="I126" s="164">
         <f t="shared" ca="1" si="24"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J126" s="47">
         <f t="shared" ca="1" si="25"/>
@@ -38720,7 +38818,7 @@
       <c r="H127" s="138"/>
       <c r="I127" s="164">
         <f t="shared" ca="1" si="24"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J127" s="47">
         <f t="shared" ca="1" si="25"/>
@@ -38781,7 +38879,7 @@
       <c r="H128" s="138"/>
       <c r="I128" s="164">
         <f t="shared" ca="1" si="24"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J128" s="47">
         <f t="shared" ca="1" si="25"/>
@@ -38873,28 +38971,28 @@
       <c r="C132" s="207" t="s">
         <v>38</v>
       </c>
-      <c r="D132" s="428" t="s">
+      <c r="D132" s="441" t="s">
         <v>39</v>
       </c>
-      <c r="E132" s="429"/>
+      <c r="E132" s="442"/>
       <c r="F132" s="46"/>
       <c r="G132" s="68"/>
-      <c r="H132" s="356" t="s">
+      <c r="H132" s="384" t="s">
         <v>14</v>
       </c>
-      <c r="I132" s="357"/>
-      <c r="J132" s="357"/>
-      <c r="K132" s="357"/>
-      <c r="L132" s="357"/>
-      <c r="M132" s="358"/>
-      <c r="N132" s="362" t="s">
+      <c r="I132" s="385"/>
+      <c r="J132" s="385"/>
+      <c r="K132" s="385"/>
+      <c r="L132" s="385"/>
+      <c r="M132" s="386"/>
+      <c r="N132" s="382" t="s">
         <v>7</v>
       </c>
-      <c r="O132" s="363"/>
-      <c r="P132" s="362" t="s">
+      <c r="O132" s="383"/>
+      <c r="P132" s="382" t="s">
         <v>110</v>
       </c>
-      <c r="Q132" s="363"/>
+      <c r="Q132" s="383"/>
       <c r="R132" s="1"/>
       <c r="S132" s="1"/>
       <c r="T132" s="140"/>
@@ -38907,16 +39005,16 @@
       <c r="C133" s="208" t="s">
         <v>74</v>
       </c>
-      <c r="D133" s="435" t="s">
+      <c r="D133" s="439" t="s">
         <v>77</v>
       </c>
-      <c r="E133" s="436"/>
+      <c r="E133" s="440"/>
       <c r="F133" s="46"/>
       <c r="G133" s="46"/>
-      <c r="H133" s="430" t="s">
+      <c r="H133" s="434" t="s">
         <v>17</v>
       </c>
-      <c r="I133" s="431"/>
+      <c r="I133" s="435"/>
       <c r="J133" s="130"/>
       <c r="K133" s="210"/>
       <c r="L133" s="117">
@@ -38950,21 +39048,21 @@
       <c r="Y133" s="11"/>
     </row>
     <row r="134" spans="1:26">
-      <c r="C134" s="394" t="s">
+      <c r="C134" s="402" t="s">
         <v>6</v>
       </c>
-      <c r="D134" s="435" t="s">
+      <c r="D134" s="439" t="s">
         <v>40</v>
       </c>
-      <c r="E134" s="436"/>
+      <c r="E134" s="440"/>
       <c r="F134" s="69"/>
       <c r="G134" s="6"/>
-      <c r="H134" s="432" t="s">
+      <c r="H134" s="436" t="s">
         <v>69</v>
       </c>
-      <c r="I134" s="433"/>
-      <c r="J134" s="433"/>
-      <c r="K134" s="434"/>
+      <c r="I134" s="437"/>
+      <c r="J134" s="437"/>
+      <c r="K134" s="438"/>
       <c r="L134" s="122">
         <f t="shared" ref="L134:L136" ca="1" si="60">M134/$M$133</f>
         <v>0.8203125</v>
@@ -38998,17 +39096,17 @@
       <c r="Y134" s="11"/>
     </row>
     <row r="135" spans="1:26">
-      <c r="C135" s="394"/>
-      <c r="D135" s="435"/>
-      <c r="E135" s="436"/>
+      <c r="C135" s="402"/>
+      <c r="D135" s="439"/>
+      <c r="E135" s="440"/>
       <c r="F135" s="72"/>
       <c r="G135" s="6"/>
-      <c r="H135" s="388" t="s">
+      <c r="H135" s="396" t="s">
         <v>70</v>
       </c>
-      <c r="I135" s="389"/>
-      <c r="J135" s="389"/>
-      <c r="K135" s="390"/>
+      <c r="I135" s="397"/>
+      <c r="J135" s="397"/>
+      <c r="K135" s="398"/>
       <c r="L135" s="124">
         <f t="shared" ca="1" si="60"/>
         <v>7.03125E-2</v>
@@ -39044,19 +39142,19 @@
       <c r="Y135" s="11"/>
     </row>
     <row r="136" spans="1:26" ht="16.5" thickBot="1">
-      <c r="C136" s="394" t="s">
+      <c r="C136" s="402" t="s">
         <v>75</v>
       </c>
-      <c r="D136" s="350" t="s">
+      <c r="D136" s="408" t="s">
         <v>76</v>
       </c>
-      <c r="E136" s="351"/>
-      <c r="H136" s="391" t="s">
+      <c r="E136" s="409"/>
+      <c r="H136" s="399" t="s">
         <v>71</v>
       </c>
-      <c r="I136" s="392"/>
-      <c r="J136" s="392"/>
-      <c r="K136" s="393"/>
+      <c r="I136" s="400"/>
+      <c r="J136" s="400"/>
+      <c r="K136" s="401"/>
       <c r="L136" s="126">
         <f t="shared" ca="1" si="60"/>
         <v>0.109375</v>
@@ -39071,16 +39169,16 @@
       <c r="Q136" s="224"/>
     </row>
     <row r="137" spans="1:26" ht="16.5" thickBot="1">
-      <c r="C137" s="395"/>
-      <c r="D137" s="352"/>
-      <c r="E137" s="353"/>
+      <c r="C137" s="403"/>
+      <c r="D137" s="410"/>
+      <c r="E137" s="411"/>
     </row>
     <row r="139" spans="1:26">
-      <c r="C139" s="378" t="s">
+      <c r="C139" s="381" t="s">
         <v>41</v>
       </c>
-      <c r="D139" s="378"/>
-      <c r="E139" s="378"/>
+      <c r="D139" s="381"/>
+      <c r="E139" s="381"/>
     </row>
     <row r="140" spans="1:26">
       <c r="C140" s="169" t="s">
@@ -39113,6 +39211,22 @@
     </sortState>
   </autoFilter>
   <mergeCells count="32">
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="P132:Q132"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="D132:E132"/>
+    <mergeCell ref="H132:M132"/>
+    <mergeCell ref="N132:O132"/>
+    <mergeCell ref="H133:I133"/>
+    <mergeCell ref="C139:E139"/>
+    <mergeCell ref="H134:K134"/>
+    <mergeCell ref="H135:K135"/>
+    <mergeCell ref="H136:K136"/>
+    <mergeCell ref="D133:E133"/>
+    <mergeCell ref="C134:C135"/>
+    <mergeCell ref="D134:E135"/>
+    <mergeCell ref="C136:C137"/>
+    <mergeCell ref="D136:E137"/>
     <mergeCell ref="Z4:Z5"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="D4:D5"/>
@@ -39129,22 +39243,6 @@
     <mergeCell ref="K4:K5"/>
     <mergeCell ref="P4:Q4"/>
     <mergeCell ref="X4:Y4"/>
-    <mergeCell ref="H133:I133"/>
-    <mergeCell ref="C139:E139"/>
-    <mergeCell ref="H134:K134"/>
-    <mergeCell ref="H135:K135"/>
-    <mergeCell ref="H136:K136"/>
-    <mergeCell ref="D133:E133"/>
-    <mergeCell ref="C134:C135"/>
-    <mergeCell ref="D134:E135"/>
-    <mergeCell ref="C136:C137"/>
-    <mergeCell ref="D136:E137"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="P132:Q132"/>
-    <mergeCell ref="J4:J5"/>
-    <mergeCell ref="D132:E132"/>
-    <mergeCell ref="H132:M132"/>
-    <mergeCell ref="N132:O132"/>
   </mergeCells>
   <phoneticPr fontId="71"/>
   <conditionalFormatting sqref="A7:Z130">
@@ -39728,19 +39826,19 @@
       <c r="S3" s="281"/>
     </row>
     <row r="4" spans="1:25" ht="36" customHeight="1" thickBot="1">
-      <c r="A4" s="408" t="s">
+      <c r="A4" s="350" t="s">
         <v>123</v>
       </c>
-      <c r="B4" s="366" t="s">
+      <c r="B4" s="352" t="s">
         <v>45</v>
       </c>
-      <c r="C4" s="366" t="s">
+      <c r="C4" s="352" t="s">
         <v>95</v>
       </c>
-      <c r="D4" s="366" t="s">
+      <c r="D4" s="352" t="s">
         <v>46</v>
       </c>
-      <c r="E4" s="369" t="s">
+      <c r="E4" s="348" t="s">
         <v>4</v>
       </c>
       <c r="F4" s="449" t="s">
@@ -39769,12 +39867,12 @@
       <c r="S4" s="448"/>
     </row>
     <row r="5" spans="1:25" ht="78.75">
-      <c r="A5" s="409"/>
-      <c r="B5" s="367"/>
-      <c r="C5" s="367"/>
-      <c r="D5" s="367"/>
-      <c r="E5" s="370"/>
-      <c r="F5" s="411"/>
+      <c r="A5" s="351"/>
+      <c r="B5" s="353"/>
+      <c r="C5" s="353"/>
+      <c r="D5" s="353"/>
+      <c r="E5" s="354"/>
+      <c r="F5" s="356"/>
       <c r="G5" s="283" t="s">
         <v>56</v>
       </c>
@@ -39856,7 +39954,7 @@
         <v>MAS</v>
       </c>
       <c r="D7" s="282" t="str" cm="1">
-        <f t="array" ref="D7:D24">_xlfn._xlws.FILTER(RFA!$E$5:$E$4576, RFA!$AI$5:$AI$4576="YES","")</f>
+        <f t="array" ref="D7:D24">_xlfn._xlws.FILTER(RFA!$E$5:$E$4577, RFA!$AI$5:$AI$4577="YES","")</f>
         <v>LTIA-5.10-VIETUR-70000-RFA-MAS-0088A</v>
       </c>
       <c r="E7" s="303" t="str" cm="1">
@@ -39962,7 +40060,7 @@
 _xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(D7),RFA!$E:$E,RFA!$AD:$AD,""),
 IF(_xlpm.x=0,"",_xlpm.x)
 )</f>
-        <v>846</v>
+        <v>847</v>
       </c>
     </row>
     <row r="8" spans="1:25" ht="45">
@@ -40023,7 +40121,7 @@
       </c>
       <c r="S8" s="279">
         <f ca="1"/>
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="Y8" t="s">
         <v>125</v>
@@ -40088,7 +40186,7 @@
       </c>
       <c r="S9" s="279">
         <f ca="1"/>
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="10" spans="1:25" ht="45">
@@ -40149,7 +40247,7 @@
       </c>
       <c r="S10" s="279">
         <f ca="1"/>
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="11" spans="1:25" ht="75">
@@ -40210,7 +40308,7 @@
       </c>
       <c r="S11" s="279">
         <f ca="1"/>
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="12" spans="1:25" ht="45">
@@ -40271,7 +40369,7 @@
       </c>
       <c r="S12" s="279">
         <f ca="1"/>
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="13" spans="1:25" ht="45">
@@ -40332,7 +40430,7 @@
       </c>
       <c r="S13" s="279">
         <f ca="1"/>
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="14" spans="1:25" ht="45">
@@ -40393,7 +40491,7 @@
       </c>
       <c r="S14" s="279">
         <f ca="1"/>
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="15" spans="1:25" ht="60">
@@ -41107,16 +41205,16 @@
       <c r="R3" s="281"/>
     </row>
     <row r="4" spans="1:18" ht="16.5" thickBot="1">
-      <c r="A4" s="408" t="s">
+      <c r="A4" s="350" t="s">
         <v>123</v>
       </c>
-      <c r="B4" s="366" t="s">
+      <c r="B4" s="352" t="s">
         <v>45</v>
       </c>
-      <c r="C4" s="366" t="s">
+      <c r="C4" s="352" t="s">
         <v>46</v>
       </c>
-      <c r="D4" s="364" t="s">
+      <c r="D4" s="363" t="s">
         <v>4</v>
       </c>
       <c r="E4" s="449" t="s">
@@ -41145,11 +41243,11 @@
       <c r="R4" s="448"/>
     </row>
     <row r="5" spans="1:18" ht="78.75">
-      <c r="A5" s="409"/>
-      <c r="B5" s="367"/>
-      <c r="C5" s="367"/>
-      <c r="D5" s="440"/>
-      <c r="E5" s="370"/>
+      <c r="A5" s="351"/>
+      <c r="B5" s="353"/>
+      <c r="C5" s="353"/>
+      <c r="D5" s="431"/>
+      <c r="E5" s="354"/>
       <c r="F5" s="283" t="s">
         <v>56</v>
       </c>
@@ -41285,7 +41383,7 @@
       </c>
       <c r="R7" s="279" cm="1">
         <f t="array" aca="1" ref="R7:R18" ca="1">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$AC:$AC,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="8" spans="1:18" ht="30">
@@ -41343,7 +41441,7 @@
       </c>
       <c r="R8" s="279">
         <f ca="1"/>
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="45">
@@ -41401,7 +41499,7 @@
       </c>
       <c r="R9" s="279">
         <f ca="1"/>
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="105">
@@ -41460,7 +41558,7 @@
       </c>
       <c r="R10" s="279">
         <f ca="1"/>
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="45">
@@ -41518,7 +41616,7 @@
       </c>
       <c r="R11" s="279">
         <f ca="1"/>
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="12" spans="1:18" ht="45">
@@ -41577,7 +41675,7 @@
       </c>
       <c r="R12" s="279">
         <f ca="1"/>
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="75">
@@ -41635,7 +41733,7 @@
       </c>
       <c r="R13" s="279">
         <f ca="1"/>
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="14" spans="1:18" ht="60">
@@ -41693,7 +41791,7 @@
       </c>
       <c r="R14" s="279">
         <f ca="1"/>
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="15" spans="1:18" ht="45">
@@ -41751,7 +41849,7 @@
       </c>
       <c r="R15" s="279">
         <f ca="1"/>
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="45">
@@ -41809,7 +41907,7 @@
       </c>
       <c r="R16" s="279">
         <f ca="1"/>
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="17" spans="1:18" ht="60">
@@ -41925,7 +42023,7 @@
       </c>
       <c r="R18" s="279">
         <f ca="1"/>
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
   </sheetData>
@@ -41983,19 +42081,19 @@
     <row r="3" spans="1:4" ht="15.75">
       <c r="A3" s="319">
         <f ca="1">MAX('Need ReSub (RFA)'!S7:S76)</f>
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="B3" s="319">
         <f ca="1">AVERAGEIF('Need ReSub (RFA)'!S7:S76,"&lt;&gt;0")</f>
-        <v>454.25</v>
+        <v>455.25</v>
       </c>
       <c r="C3" s="319">
         <f ca="1">MAX(_xlfn.ANCHORARRAY('Need ReSub (RFA-SDS)'!R7))</f>
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="D3" s="319">
         <f ca="1">AVERAGEIF(_xlfn.ANCHORARRAY('Need ReSub (RFA-SDS)'!R7),"&lt;&gt;0")</f>
-        <v>337.75</v>
+        <v>338.66666666666669</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -42004,10 +42102,10 @@
 Furthermore, the RFA (SDS) is as follows:
 Avarage :  " &amp; ROUND($D$3,0) &amp; " days
 Maimum :  " &amp; ROUND($C$3,0) &amp; " days"</f>
-        <v>In the RFA process, the average number of days elapsed since responding to an unapproved RFA was 454 days, with a maximum of 846 days, indicating that delays in the RFA approval process are contributing to delays in construction work.
+        <v>In the RFA process, the average number of days elapsed since responding to an unapproved RFA was 455 days, with a maximum of 847 days, indicating that delays in the RFA approval process are contributing to delays in construction work.
 Furthermore, the RFA (SDS) is as follows:
-Avarage :  338 days
-Maimum :  546 days</v>
+Avarage :  339 days
+Maimum :  547 days</v>
       </c>
       <c r="B5" s="452"/>
     </row>

--- a/ICT-RFA-RFI-lists-New.xlsx
+++ b/ICT-RFA-RFI-lists-New.xlsx
@@ -9,7 +9,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project Airport\LTIA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01F0DF36-5C6D-488E-8CE1-E9A935FF3051}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{550F1BD5-7A77-46C2-9DF2-894155E4FCF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="506" xr2:uid="{CCA8147E-0981-4321-B87F-440A52C0DA59}"/>
   </bookViews>
@@ -24,14 +24,14 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Need ReSub (RFA)'!$A$6:$S$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Need ReSub (RFA-SDS)'!$A$6:$R$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">RFA!$A$6:$AE$142</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">RFA!$A$6:$AE$143</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'RFA-SDS'!$A$6:$AD$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">RFI!$A$6:$Z$127</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Need ReSub (RFA)'!$A$1:$S$77</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'Need ReSub (RFA-SDS)'!$A$1:$R$62</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RFA!$A$1:$AE$142,RFA!$I$144:$R$150,RFA!$C$144:$F$154,RFA!$C$156:$F$159,RFA!$C$161:$F$172</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RFA!$A$1:$AE$143,RFA!$I$145:$R$151,RFA!$C$145:$F$155,RFA!$C$157:$F$160,RFA!$C$162:$F$173</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'RFA-SDS'!$A$1:$AD$42,'RFA-SDS'!$H$44:$Q$50,'RFA-SDS'!$C$44:$E$48,'RFA-SDS'!$C$50:$E$53</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">RFI!$A$1:$Z$130,RFI!$H$132:$Q$136,RFI!$C$132:$E$137,RFI!$C$139:$E$142</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">RFI!$A$1:$Z$131,RFI!$H$133:$Q$137,RFI!$C$133:$E$138,RFI!$C$140:$E$143</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">RFA!$4:$5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'RFA-SDS'!$4:$5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">RFI!$4:$5</definedName>
@@ -78,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3475" uniqueCount="1091">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3487" uniqueCount="1097">
   <si>
     <t>TT</t>
   </si>
@@ -5126,6 +5126,24 @@
   </si>
   <si>
     <t>Đề nghị phê duyệt Quy trình kiểm tra trước khi hoàn thành, thử nghiệm, vận hành hệ thống An ninh Cửa Khẩu</t>
+  </si>
+  <si>
+    <t>LTIA-5.10-VIETUR-70000-RFI-1025</t>
+  </si>
+  <si>
+    <t>Clarify the information about equipping Access control system (ACS) for door positions at: SSE-FD Room, FLB05, and FLB16</t>
+  </si>
+  <si>
+    <t>Làm rõ thông tin về việc trang bị ACS cho các vị trí cửa tại: Phòng SSE-FD, FLB05 và FLB16</t>
+  </si>
+  <si>
+    <t>LTIA-5.11-LTICT-72020-RFA-OTH-0009A</t>
+  </si>
+  <si>
+    <t>Request for Approval of the Network Architecture and IP-VLAN Planning</t>
+  </si>
+  <si>
+    <t>Đề nghị phê duyệt kiến trúc mạng và quy hoạch IP-VLAN</t>
   </si>
 </sst>
 </file>
@@ -7562,9 +7580,147 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="45" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="53" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="47" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="51" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="52" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -7574,15 +7730,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="43" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -7595,24 +7742,6 @@
     <xf numFmtId="0" fontId="58" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -7661,24 +7790,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="51" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="52" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -7706,54 +7817,12 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -7763,12 +7832,6 @@
     <xf numFmtId="1" fontId="2" fillId="0" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -7801,51 +7864,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="45" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="53" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="47" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -8376,7 +8394,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C724CDAB-378C-47DB-9F45-08EE3BFB6E8B}">
-  <dimension ref="A1:AI172"/>
+  <dimension ref="A1:AI173"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" customWidth="1"/>
@@ -8421,7 +8439,7 @@
       </c>
       <c r="J1" s="176">
         <f ca="1">TODAY()</f>
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="K1" s="131"/>
       <c r="L1" s="197"/>
@@ -8508,92 +8526,92 @@
       <c r="AE3" s="159"/>
     </row>
     <row r="4" spans="1:35" s="5" customFormat="1" ht="36" customHeight="1" thickBot="1">
-      <c r="A4" s="350" t="s">
+      <c r="A4" s="396" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="406" t="s">
+      <c r="B4" s="350" t="s">
         <v>515</v>
       </c>
-      <c r="C4" s="359" t="s">
+      <c r="C4" s="364" t="s">
         <v>45</v>
       </c>
-      <c r="D4" s="352" t="s">
+      <c r="D4" s="358" t="s">
         <v>95</v>
       </c>
-      <c r="E4" s="348" t="s">
+      <c r="E4" s="352" t="s">
         <v>46</v>
       </c>
-      <c r="F4" s="357" t="s">
+      <c r="F4" s="400" t="s">
         <v>47</v>
       </c>
-      <c r="G4" s="348" t="s">
+      <c r="G4" s="352" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="355" t="s">
+      <c r="H4" s="398" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="352" t="s">
+      <c r="I4" s="358" t="s">
         <v>48</v>
       </c>
-      <c r="J4" s="352" t="s">
+      <c r="J4" s="358" t="s">
         <v>49</v>
       </c>
-      <c r="K4" s="348" t="s">
+      <c r="K4" s="352" t="s">
         <v>78</v>
       </c>
-      <c r="L4" s="352" t="s">
+      <c r="L4" s="358" t="s">
         <v>80</v>
       </c>
       <c r="M4" s="363" t="s">
         <v>53</v>
       </c>
-      <c r="N4" s="364"/>
+      <c r="N4" s="348"/>
       <c r="O4" s="363" t="s">
         <v>55</v>
       </c>
-      <c r="P4" s="364"/>
+      <c r="P4" s="348"/>
       <c r="Q4" s="362" t="s">
         <v>72</v>
       </c>
-      <c r="R4" s="364"/>
+      <c r="R4" s="348"/>
       <c r="S4" s="363" t="s">
         <v>53</v>
       </c>
       <c r="T4" s="363"/>
-      <c r="U4" s="364"/>
+      <c r="U4" s="348"/>
       <c r="V4" s="362" t="s">
         <v>55</v>
       </c>
       <c r="W4" s="363"/>
-      <c r="X4" s="364"/>
-      <c r="Y4" s="415" t="s">
+      <c r="X4" s="348"/>
+      <c r="Y4" s="366" t="s">
         <v>72</v>
       </c>
-      <c r="Z4" s="416"/>
-      <c r="AA4" s="412" t="s">
+      <c r="Z4" s="367"/>
+      <c r="AA4" s="429" t="s">
         <v>112</v>
       </c>
-      <c r="AB4" s="413"/>
-      <c r="AC4" s="413"/>
-      <c r="AD4" s="414"/>
-      <c r="AE4" s="348" t="s">
+      <c r="AB4" s="430"/>
+      <c r="AC4" s="430"/>
+      <c r="AD4" s="431"/>
+      <c r="AE4" s="352" t="s">
         <v>79</v>
       </c>
       <c r="AG4" s="236"/>
     </row>
     <row r="5" spans="1:35" ht="78.75">
-      <c r="A5" s="351"/>
-      <c r="B5" s="407"/>
-      <c r="C5" s="360"/>
-      <c r="D5" s="353"/>
-      <c r="E5" s="354"/>
-      <c r="F5" s="358"/>
-      <c r="G5" s="354"/>
-      <c r="H5" s="356"/>
-      <c r="I5" s="353"/>
-      <c r="J5" s="353"/>
-      <c r="K5" s="354"/>
-      <c r="L5" s="353"/>
+      <c r="A5" s="397"/>
+      <c r="B5" s="351"/>
+      <c r="C5" s="365"/>
+      <c r="D5" s="359"/>
+      <c r="E5" s="353"/>
+      <c r="F5" s="401"/>
+      <c r="G5" s="353"/>
+      <c r="H5" s="399"/>
+      <c r="I5" s="359"/>
+      <c r="J5" s="359"/>
+      <c r="K5" s="353"/>
+      <c r="L5" s="359"/>
       <c r="M5" s="79" t="s">
         <v>52</v>
       </c>
@@ -8648,14 +8666,14 @@
       <c r="AD5" s="336" t="s">
         <v>118</v>
       </c>
-      <c r="AE5" s="361"/>
-      <c r="AG5" s="348" t="s">
+      <c r="AE5" s="349"/>
+      <c r="AG5" s="352" t="s">
         <v>119</v>
       </c>
-      <c r="AH5" s="348" t="s">
+      <c r="AH5" s="352" t="s">
         <v>120</v>
       </c>
-      <c r="AI5" s="348" t="s">
+      <c r="AI5" s="352" t="s">
         <v>121</v>
       </c>
     </row>
@@ -8691,9 +8709,9 @@
       <c r="AC6" s="86"/>
       <c r="AD6" s="86"/>
       <c r="AE6" s="74"/>
-      <c r="AG6" s="349"/>
-      <c r="AH6" s="349"/>
-      <c r="AI6" s="349"/>
+      <c r="AG6" s="395"/>
+      <c r="AH6" s="395"/>
+      <c r="AI6" s="395"/>
     </row>
     <row r="7" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A7" s="33">
@@ -8802,8 +8820,8 @@
       <c r="AH7" s="242" t="b" cm="1">
         <f t="array" ref="AH7">$E7=_xlfn.XLOOKUP(
 AG7,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -8918,8 +8936,8 @@
       <c r="AH8" s="243" t="b" cm="1">
         <f t="array" ref="AH8">$E8=_xlfn.XLOOKUP(
 AG8,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -9034,8 +9052,8 @@
       <c r="AH9" s="243" t="b" cm="1">
         <f t="array" ref="AH9">$E9=_xlfn.XLOOKUP(
 AG9,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -9152,8 +9170,8 @@
       <c r="AH10" s="243" t="b" cm="1">
         <f t="array" ref="AH10">$E10=_xlfn.XLOOKUP(
 AG10,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -9270,8 +9288,8 @@
       <c r="AH11" s="243" t="b" cm="1">
         <f t="array" ref="AH11">$E11=_xlfn.XLOOKUP(
 AG11,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -9388,8 +9406,8 @@
       <c r="AH12" s="243" t="b" cm="1">
         <f t="array" ref="AH12">$E12=_xlfn.XLOOKUP(
 AG12,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -9506,8 +9524,8 @@
       <c r="AH13" s="243" t="b" cm="1">
         <f t="array" ref="AH13">$E13=_xlfn.XLOOKUP(
 AG13,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -9612,7 +9630,7 @@
       </c>
       <c r="AD14" s="337">
         <f t="shared" ca="1" si="7"/>
-        <v>847</v>
+        <v>851</v>
       </c>
       <c r="AE14" s="92"/>
       <c r="AG14" s="238" t="str">
@@ -9622,8 +9640,8 @@
       <c r="AH14" s="243" t="b" cm="1">
         <f t="array" ref="AH14">$E14=_xlfn.XLOOKUP(
 AG14,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -9728,7 +9746,7 @@
       </c>
       <c r="AD15" s="337">
         <f t="shared" ca="1" si="7"/>
-        <v>812</v>
+        <v>816</v>
       </c>
       <c r="AE15" s="92"/>
       <c r="AG15" s="238" t="str">
@@ -9738,8 +9756,8 @@
       <c r="AH15" s="243" t="b" cm="1">
         <f t="array" ref="AH15">$E15=_xlfn.XLOOKUP(
 AG15,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -9856,8 +9874,8 @@
       <c r="AH16" s="243" t="b" cm="1">
         <f t="array" ref="AH16">$E16=_xlfn.XLOOKUP(
 AG16,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -9972,8 +9990,8 @@
       <c r="AH17" s="243" t="b" cm="1">
         <f t="array" ref="AH17">$E17=_xlfn.XLOOKUP(
 AG17,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -10090,8 +10108,8 @@
       <c r="AH18" s="243" t="b" cm="1">
         <f t="array" ref="AH18">$E18=_xlfn.XLOOKUP(
 AG18,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -10208,8 +10226,8 @@
       <c r="AH19" s="243" t="b" cm="1">
         <f t="array" ref="AH19">$E19=_xlfn.XLOOKUP(
 AG19,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -10324,8 +10342,8 @@
       <c r="AH20" s="243" t="b" cm="1">
         <f t="array" ref="AH20">$E20=_xlfn.XLOOKUP(
 AG20,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -10442,8 +10460,8 @@
       <c r="AH21" s="243" t="b" cm="1">
         <f t="array" ref="AH21">$E21=_xlfn.XLOOKUP(
 AG21,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -10560,8 +10578,8 @@
       <c r="AH22" s="243" t="b" cm="1">
         <f t="array" ref="AH22">$E22=_xlfn.XLOOKUP(
 AG22,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -10676,8 +10694,8 @@
       <c r="AH23" s="243" t="b" cm="1">
         <f t="array" ref="AH23">$E23=_xlfn.XLOOKUP(
 AG23,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -10796,8 +10814,8 @@
       <c r="AH24" s="243" t="b" cm="1">
         <f t="array" ref="AH24">$E24=_xlfn.XLOOKUP(
 AG24,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -10912,8 +10930,8 @@
       <c r="AH25" s="243" t="b" cm="1">
         <f t="array" ref="AH25">$E25=_xlfn.XLOOKUP(
 AG25,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -11028,8 +11046,8 @@
       <c r="AH26" s="243" t="b" cm="1">
         <f t="array" ref="AH26">$E26=_xlfn.XLOOKUP(
 AG26,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -11146,8 +11164,8 @@
       <c r="AH27" s="243" t="b" cm="1">
         <f t="array" ref="AH27">$E27=_xlfn.XLOOKUP(
 AG27,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -11264,8 +11282,8 @@
       <c r="AH28" s="243" t="b" cm="1">
         <f t="array" ref="AH28">$E28=_xlfn.XLOOKUP(
 AG28,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -11380,8 +11398,8 @@
       <c r="AH29" s="243" t="b" cm="1">
         <f t="array" ref="AH29">$E29=_xlfn.XLOOKUP(
 AG29,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -11498,8 +11516,8 @@
       <c r="AH30" s="243" t="b" cm="1">
         <f t="array" ref="AH30">$E30=_xlfn.XLOOKUP(
 AG30,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -11616,8 +11634,8 @@
       <c r="AH31" s="243" t="b" cm="1">
         <f t="array" ref="AH31">$E31=_xlfn.XLOOKUP(
 AG31,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -11732,8 +11750,8 @@
       <c r="AH32" s="243" t="b" cm="1">
         <f t="array" ref="AH32">$E32=_xlfn.XLOOKUP(
 AG32,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -11850,8 +11868,8 @@
       <c r="AH33" s="243" t="b" cm="1">
         <f t="array" ref="AH33">$E33=_xlfn.XLOOKUP(
 AG33,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -11966,8 +11984,8 @@
       <c r="AH34" s="243" t="b" cm="1">
         <f t="array" ref="AH34">$E34=_xlfn.XLOOKUP(
 AG34,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -12082,8 +12100,8 @@
       <c r="AH35" s="243" t="b" cm="1">
         <f t="array" ref="AH35">$E35=_xlfn.XLOOKUP(
 AG35,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -12198,8 +12216,8 @@
       <c r="AH36" s="243" t="b" cm="1">
         <f t="array" ref="AH36">$E36=_xlfn.XLOOKUP(
 AG36,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -12314,8 +12332,8 @@
       <c r="AH37" s="243" t="b" cm="1">
         <f t="array" ref="AH37">$E37=_xlfn.XLOOKUP(
 AG37,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -12430,8 +12448,8 @@
       <c r="AH38" s="243" t="b" cm="1">
         <f t="array" ref="AH38">$E38=_xlfn.XLOOKUP(
 AG38,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -12546,8 +12564,8 @@
       <c r="AH39" s="243" t="b" cm="1">
         <f t="array" ref="AH39">$E39=_xlfn.XLOOKUP(
 AG39,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -12662,8 +12680,8 @@
       <c r="AH40" s="243" t="b" cm="1">
         <f t="array" ref="AH40">$E40=_xlfn.XLOOKUP(
 AG40,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -12778,8 +12796,8 @@
       <c r="AH41" s="243" t="b" cm="1">
         <f t="array" ref="AH41">$E41=_xlfn.XLOOKUP(
 AG41,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -12894,8 +12912,8 @@
       <c r="AH42" s="243" t="b" cm="1">
         <f t="array" ref="AH42">$E42=_xlfn.XLOOKUP(
 AG42,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -13010,8 +13028,8 @@
       <c r="AH43" s="243" t="b" cm="1">
         <f t="array" ref="AH43">$E43=_xlfn.XLOOKUP(
 AG43,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -13116,7 +13134,7 @@
       </c>
       <c r="AD44" s="337">
         <f t="shared" ca="1" si="13"/>
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="AE44" s="92"/>
       <c r="AG44" s="238" t="str">
@@ -13126,8 +13144,8 @@
       <c r="AH44" s="243" t="b" cm="1">
         <f t="array" ref="AH44">$E44=_xlfn.XLOOKUP(
 AG44,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -13244,8 +13262,8 @@
       <c r="AH45" s="243" t="b" cm="1">
         <f t="array" ref="AH45">$E45=_xlfn.XLOOKUP(
 AG45,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -13350,7 +13368,7 @@
       </c>
       <c r="AD46" s="337">
         <f t="shared" ca="1" si="13"/>
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="AE46" s="92"/>
       <c r="AG46" s="238" t="str">
@@ -13360,8 +13378,8 @@
       <c r="AH46" s="243" t="b" cm="1">
         <f t="array" ref="AH46">$E46=_xlfn.XLOOKUP(
 AG46,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -13476,8 +13494,8 @@
       <c r="AH47" s="243" t="b" cm="1">
         <f t="array" ref="AH47">$E47=_xlfn.XLOOKUP(
 AG47,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -13592,8 +13610,8 @@
       <c r="AH48" s="243" t="b" cm="1">
         <f t="array" ref="AH48">$E48=_xlfn.XLOOKUP(
 AG48,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -13710,8 +13728,8 @@
       <c r="AH49" s="243" t="b" cm="1">
         <f t="array" ref="AH49">$E49=_xlfn.XLOOKUP(
 AG49,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -13816,7 +13834,7 @@
       </c>
       <c r="AD50" s="337">
         <f t="shared" ca="1" si="13"/>
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="AE50" s="92"/>
       <c r="AG50" s="238" t="str">
@@ -13826,8 +13844,8 @@
       <c r="AH50" s="243" t="b" cm="1">
         <f t="array" ref="AH50">$E50=_xlfn.XLOOKUP(
 AG50,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -13867,7 +13885,7 @@
       <c r="I51" s="138"/>
       <c r="J51" s="164">
         <f t="shared" ca="1" si="3"/>
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="K51" s="47"/>
       <c r="L51" s="164" t="s">
@@ -13916,8 +13934,8 @@
       <c r="AH51" s="243" t="b" cm="1">
         <f t="array" ref="AH51">$E51=_xlfn.XLOOKUP(
 AG51,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -14034,8 +14052,8 @@
       <c r="AH52" s="243" t="b" cm="1">
         <f t="array" ref="AH52">$E52=_xlfn.XLOOKUP(
 AG52,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -14152,8 +14170,8 @@
       <c r="AH53" s="243" t="b" cm="1">
         <f t="array" ref="AH53">$E53=_xlfn.XLOOKUP(
 AG53,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -14268,8 +14286,8 @@
       <c r="AH54" s="243" t="b" cm="1">
         <f t="array" ref="AH54">$E54=_xlfn.XLOOKUP(
 AG54,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -14384,8 +14402,8 @@
       <c r="AH55" s="243" t="b" cm="1">
         <f t="array" ref="AH55">$E55=_xlfn.XLOOKUP(
 AG55,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -14502,8 +14520,8 @@
       <c r="AH56" s="243" t="b" cm="1">
         <f t="array" ref="AH56">$E56=_xlfn.XLOOKUP(
 AG56,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -14618,8 +14636,8 @@
       <c r="AH57" s="243" t="b" cm="1">
         <f t="array" ref="AH57">$E57=_xlfn.XLOOKUP(
 AG57,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -14724,7 +14742,7 @@
       </c>
       <c r="AD58" s="337">
         <f t="shared" ca="1" si="13"/>
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="AE58" s="92"/>
       <c r="AG58" s="238" t="str">
@@ -14734,8 +14752,8 @@
       <c r="AH58" s="243" t="b" cm="1">
         <f t="array" ref="AH58">$E58=_xlfn.XLOOKUP(
 AG58,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -14775,7 +14793,7 @@
       <c r="I59" s="138"/>
       <c r="J59" s="164">
         <f t="shared" ca="1" si="3"/>
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="K59" s="47"/>
       <c r="L59" s="164" t="s">
@@ -14824,8 +14842,8 @@
       <c r="AH59" s="243" t="b" cm="1">
         <f t="array" ref="AH59">$E59=_xlfn.XLOOKUP(
 AG59,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -14944,8 +14962,8 @@
       <c r="AH60" s="243" t="b" cm="1">
         <f t="array" ref="AH60">$E60=_xlfn.XLOOKUP(
 AG60,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -15050,7 +15068,7 @@
       </c>
       <c r="AD61" s="337">
         <f t="shared" ca="1" si="13"/>
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="AE61" s="92"/>
       <c r="AG61" s="238" t="str">
@@ -15060,8 +15078,8 @@
       <c r="AH61" s="243" t="b" cm="1">
         <f t="array" ref="AH61">$E61=_xlfn.XLOOKUP(
 AG61,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -15178,8 +15196,8 @@
       <c r="AH62" s="243" t="b" cm="1">
         <f t="array" ref="AH62">$E62=_xlfn.XLOOKUP(
 AG62,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -15296,8 +15314,8 @@
       <c r="AH63" s="243" t="b" cm="1">
         <f t="array" ref="AH63">$E63=_xlfn.XLOOKUP(
 AG63,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -15414,8 +15432,8 @@
       <c r="AH64" s="243" t="b" cm="1">
         <f t="array" ref="AH64">$E64=_xlfn.XLOOKUP(
 AG64,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -15532,8 +15550,8 @@
       <c r="AH65" s="243" t="b" cm="1">
         <f t="array" ref="AH65">$E65=_xlfn.XLOOKUP(
 AG65,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -15650,8 +15668,8 @@
       <c r="AH66" s="243" t="b" cm="1">
         <f t="array" ref="AH66">$E66=_xlfn.XLOOKUP(
 AG66,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -15766,8 +15784,8 @@
       <c r="AH67" s="243" t="b" cm="1">
         <f t="array" ref="AH67">$E67=_xlfn.XLOOKUP(
 AG67,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -15870,7 +15888,7 @@
       </c>
       <c r="AD68" s="337">
         <f t="shared" ca="1" si="13"/>
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="AE68" s="92"/>
       <c r="AG68" s="238" t="str">
@@ -15880,8 +15898,8 @@
       <c r="AH68" s="243" t="b" cm="1">
         <f t="array" ref="AH68">$E68=_xlfn.XLOOKUP(
 AG68,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -15988,8 +16006,8 @@
       <c r="AH69" s="243" t="b" cm="1">
         <f t="array" ref="AH69">$E69=_xlfn.XLOOKUP(
 AG69,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -16104,8 +16122,8 @@
       <c r="AH70" s="243" t="b" cm="1">
         <f t="array" ref="AH70">$E70=_xlfn.XLOOKUP(
 AG70,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -16119,7 +16137,7 @@
     </row>
     <row r="71" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A71" s="33">
-        <f t="shared" ref="A71:A140" si="19">A70+1</f>
+        <f t="shared" ref="A71:A141" si="19">A70+1</f>
         <v>65</v>
       </c>
       <c r="B71" s="330" t="str">
@@ -16220,8 +16238,8 @@
       <c r="AH71" s="243" t="b" cm="1">
         <f t="array" ref="AH71">$E71=_xlfn.XLOOKUP(
 AG71,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -16336,8 +16354,8 @@
       <c r="AH72" s="243" t="b" cm="1">
         <f t="array" ref="AH72">$E72=_xlfn.XLOOKUP(
 AG72,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -16452,8 +16470,8 @@
       <c r="AH73" s="243" t="b" cm="1">
         <f t="array" ref="AH73">$E73=_xlfn.XLOOKUP(
 AG73,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -16570,8 +16588,8 @@
       <c r="AH74" s="243" t="b" cm="1">
         <f t="array" ref="AH74">$E74=_xlfn.XLOOKUP(
 AG74,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -16688,8 +16706,8 @@
       <c r="AH75" s="243" t="b" cm="1">
         <f t="array" ref="AH75">$E75=_xlfn.XLOOKUP(
 AG75,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -16806,8 +16824,8 @@
       <c r="AH76" s="243" t="b" cm="1">
         <f t="array" ref="AH76">$E76=_xlfn.XLOOKUP(
 AG76,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -16924,8 +16942,8 @@
       <c r="AH77" s="243" t="b" cm="1">
         <f t="array" ref="AH77">$E77=_xlfn.XLOOKUP(
 AG77,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -17040,8 +17058,8 @@
       <c r="AH78" s="243" t="b" cm="1">
         <f t="array" ref="AH78">$E78=_xlfn.XLOOKUP(
 AG78,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -17150,8 +17168,8 @@
       <c r="AH79" s="243" t="b" cm="1">
         <f t="array" ref="AH79">$E79=_xlfn.XLOOKUP(
 AG79,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -17260,8 +17278,8 @@
       <c r="AH80" s="243" t="b" cm="1">
         <f t="array" ref="AH80">$E80=_xlfn.XLOOKUP(
 AG80,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -17366,8 +17384,8 @@
       <c r="AH81" s="243" t="b" cm="1">
         <f t="array" ref="AH81">$E81=_xlfn.XLOOKUP(
 AG81,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -17482,8 +17500,8 @@
       <c r="AH82" s="243" t="b" cm="1">
         <f t="array" ref="AH82">$E82=_xlfn.XLOOKUP(
 AG82,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -17571,8 +17589,8 @@
       <c r="AH83" s="243" t="b" cm="1">
         <f t="array" ref="AH83">$E83=_xlfn.XLOOKUP(
 AG83,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -17681,8 +17699,8 @@
       <c r="AH84" s="243" t="b" cm="1">
         <f t="array" ref="AH84">$E84=_xlfn.XLOOKUP(
 AG84,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -17799,8 +17817,8 @@
       <c r="AH85" s="243" t="b" cm="1">
         <f t="array" ref="AH85">$E85=_xlfn.XLOOKUP(
 AG85,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -17909,8 +17927,8 @@
       <c r="AH86" s="243" t="b" cm="1">
         <f t="array" ref="AH86">$E86=_xlfn.XLOOKUP(
 AG86,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -18002,8 +18020,8 @@
       <c r="AH87" s="243" t="b" cm="1">
         <f t="array" ref="AH87">$E87=_xlfn.XLOOKUP(
 AG87,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -18114,8 +18132,8 @@
       <c r="AH88" s="243" t="b" cm="1">
         <f t="array" ref="AH88">$E88=_xlfn.XLOOKUP(
 AG88,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -18226,8 +18244,8 @@
       <c r="AH89" s="243" t="b" cm="1">
         <f t="array" ref="AH89">$E89=_xlfn.XLOOKUP(
 AG89,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -18338,8 +18356,8 @@
       <c r="AH90" s="243" t="b" cm="1">
         <f t="array" ref="AH90">$E90=_xlfn.XLOOKUP(
 AG90,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -18450,8 +18468,8 @@
       <c r="AH91" s="243" t="b" cm="1">
         <f t="array" ref="AH91">$E91=_xlfn.XLOOKUP(
 AG91,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -18492,11 +18510,11 @@
       <c r="I92" s="138"/>
       <c r="J92" s="164">
         <f t="shared" ca="1" si="27"/>
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="K92" s="47">
         <f t="shared" ca="1" si="28"/>
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="L92" s="164" t="s">
         <v>1003</v>
@@ -18548,8 +18566,8 @@
       <c r="AH92" s="243" t="b" cm="1">
         <f t="array" ref="AH92">$E92=_xlfn.XLOOKUP(
 AG92,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -18594,11 +18612,11 @@
       </c>
       <c r="J93" s="164">
         <f t="shared" ca="1" si="27"/>
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="K93" s="47">
         <f t="shared" ca="1" si="28"/>
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="L93" s="164" t="s">
         <v>13</v>
@@ -18650,8 +18668,8 @@
       <c r="AH93" s="243" t="b" cm="1">
         <f t="array" ref="AH93">$E93=_xlfn.XLOOKUP(
 AG93,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -18760,8 +18778,8 @@
       <c r="AH94" s="243" t="b" cm="1">
         <f t="array" ref="AH94">$E94=_xlfn.XLOOKUP(
 AG94,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -18849,8 +18867,8 @@
       <c r="AH95" s="243" t="b" cm="1">
         <f t="array" ref="AH95">$E95=_xlfn.XLOOKUP(
 AG95,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -18881,7 +18899,7 @@
         <v>811</v>
       </c>
       <c r="F96" s="174">
-        <f t="shared" ref="F96:F140" si="29">IF($U96=0,$T96+22,$U96+21)</f>
+        <f t="shared" ref="F96:F141" si="29">IF($U96=0,$T96+22,$U96+21)</f>
         <v>46078</v>
       </c>
       <c r="G96" s="31" t="s">
@@ -18894,11 +18912,11 @@
         <v>1</v>
       </c>
       <c r="J96" s="164">
-        <f t="shared" ref="J96:J140" si="30">IF(ISBLANK($W96),_xlfn.DAYS($J$1,$U96),_xlfn.DAYS($W96,$U96))</f>
+        <f t="shared" ref="J96:J141" si="30">IF(ISBLANK($W96),_xlfn.DAYS($J$1,$U96),_xlfn.DAYS($W96,$U96))</f>
         <v>48</v>
       </c>
       <c r="K96" s="47">
-        <f t="shared" ref="K96:K140" si="31">IF(($J96-21)&gt;0,$J96-21,0)</f>
+        <f t="shared" ref="K96:K141" si="31">IF(($J96-21)&gt;0,$J96-21,0)</f>
         <v>27</v>
       </c>
       <c r="L96" s="164"/>
@@ -18959,8 +18977,8 @@
       <c r="AH96" s="243" t="b" cm="1">
         <f t="array" ref="AH96">$E96=_xlfn.XLOOKUP(
 AG96,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -19067,8 +19085,8 @@
       <c r="AH97" s="243" t="b" cm="1">
         <f t="array" ref="AH97">$E97=_xlfn.XLOOKUP(
 AG97,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -19175,8 +19193,8 @@
       <c r="AH98" s="243" t="b" cm="1">
         <f t="array" ref="AH98">$E98=_xlfn.XLOOKUP(
 AG98,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -19287,8 +19305,8 @@
       <c r="AH99" s="243" t="b" cm="1">
         <f t="array" ref="AH99">$E99=_xlfn.XLOOKUP(
 AG99,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -19395,8 +19413,8 @@
       <c r="AH100" s="243" t="b" cm="1">
         <f t="array" ref="AH100">$E100=_xlfn.XLOOKUP(
 AG100,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -19501,8 +19519,8 @@
       <c r="AH101" s="243" t="b" cm="1">
         <f t="array" ref="AH101">$E101=_xlfn.XLOOKUP(
 AG101,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -19593,8 +19611,8 @@
       <c r="AH102" s="243" t="b" cm="1">
         <f t="array" ref="AH102">$E102=_xlfn.XLOOKUP(
 AG102,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -19705,8 +19723,8 @@
       <c r="AH103" s="243" t="b" cm="1">
         <f t="array" ref="AH103">$E103=_xlfn.XLOOKUP(
 AG103,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -19817,8 +19835,8 @@
       <c r="AH104" s="243" t="b" cm="1">
         <f t="array" ref="AH104">$E104=_xlfn.XLOOKUP(
 AG104,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -19929,8 +19947,8 @@
       <c r="AH105" s="243" t="b" cm="1">
         <f t="array" ref="AH105">$E105=_xlfn.XLOOKUP(
 AG105,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -20037,8 +20055,8 @@
       <c r="AH106" s="243" t="b" cm="1">
         <f t="array" ref="AH106">$E106=_xlfn.XLOOKUP(
 AG106,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -20128,8 +20146,8 @@
       <c r="AH107" s="243" t="b" cm="1">
         <f t="array" ref="AH107">$E107=_xlfn.XLOOKUP(
 AG107,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -20150,7 +20168,9 @@
         <f t="shared" ref="B108" si="39">MID(E108, FIND("-", E108) + 1, 4)</f>
         <v>5.11</v>
       </c>
-      <c r="C108" s="164"/>
+      <c r="C108" s="164" t="s">
+        <v>342</v>
+      </c>
       <c r="D108" s="137" t="s">
         <v>28</v>
       </c>
@@ -20215,7 +20235,9 @@
         <f t="shared" si="21"/>
         <v>46226</v>
       </c>
-      <c r="AB108" s="229"/>
+      <c r="AB108" s="229">
+        <v>46312</v>
+      </c>
       <c r="AC108" s="229" t="str">
         <f t="shared" si="22"/>
         <v/>
@@ -20234,8 +20256,8 @@
       <c r="AH108" s="243" t="b" cm="1">
         <f t="array" ref="AH108">$E108=_xlfn.XLOOKUP(
 AG108,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -20342,8 +20364,8 @@
       <c r="AH109" s="243" t="b" cm="1">
         <f t="array" ref="AH109">$E109=_xlfn.XLOOKUP(
 AG109,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -20446,8 +20468,8 @@
       <c r="AH110" s="243" t="b" cm="1">
         <f t="array" ref="AH110">$E110=_xlfn.XLOOKUP(
 AG110,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -20490,11 +20512,11 @@
       <c r="I111" s="23"/>
       <c r="J111" s="164">
         <f t="shared" ca="1" si="30"/>
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="K111" s="47">
         <f t="shared" ca="1" si="31"/>
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="L111" s="164" t="s">
         <v>13</v>
@@ -20544,8 +20566,8 @@
       <c r="AH111" s="243" t="b" cm="1">
         <f t="array" ref="AH111">$E111=_xlfn.XLOOKUP(
 AG111,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -20650,8 +20672,8 @@
       <c r="AH112" s="243" t="b" cm="1">
         <f t="array" ref="AH112">$E112=_xlfn.XLOOKUP(
 AG112,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -20756,8 +20778,8 @@
       <c r="AH113" s="243" t="b" cm="1">
         <f t="array" ref="AH113">$E113=_xlfn.XLOOKUP(
 AG113,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -20862,8 +20884,8 @@
       <c r="AH114" s="243" t="b" cm="1">
         <f t="array" ref="AH114">$E114=_xlfn.XLOOKUP(
 AG114,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -20970,8 +20992,8 @@
       <c r="AH115" s="243" t="b" cm="1">
         <f t="array" ref="AH115">$E115=_xlfn.XLOOKUP(
 AG115,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -21082,8 +21104,8 @@
       <c r="AH116" s="243" t="b" cm="1">
         <f t="array" ref="AH116">$E116=_xlfn.XLOOKUP(
 AG116,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -21124,11 +21146,11 @@
       <c r="I117" s="138"/>
       <c r="J117" s="164">
         <f t="shared" ca="1" si="30"/>
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K117" s="47">
         <f t="shared" ca="1" si="31"/>
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="L117" s="164" t="s">
         <v>1003</v>
@@ -21178,8 +21200,8 @@
       <c r="AH117" s="243" t="b" cm="1">
         <f t="array" ref="AH117">$E117=_xlfn.XLOOKUP(
 AG117,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -21270,8 +21292,8 @@
       <c r="AH118" s="243" t="b" cm="1">
         <f t="array" ref="AH118">$E118=_xlfn.XLOOKUP(
 AG118,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -21378,8 +21400,8 @@
       <c r="AH119" s="243" t="b" cm="1">
         <f t="array" ref="AH119">$E119=_xlfn.XLOOKUP(
 AG119,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -21484,8 +21506,8 @@
       <c r="AH120" s="243" t="b" cm="1">
         <f t="array" ref="AH120">$E120=_xlfn.XLOOKUP(
 AG120,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -21576,8 +21598,8 @@
       <c r="AH121" s="243" t="b" cm="1">
         <f t="array" ref="AH121">$E121=_xlfn.XLOOKUP(
 AG121,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -21660,7 +21682,7 @@
       <c r="Y122" s="230"/>
       <c r="Z122" s="227"/>
       <c r="AA122" s="29">
-        <f t="shared" ref="AA122:AA142" si="68">IF(AND($R122="",$I122=""),"",IF(OR($R122="B",$R122="C"),IF($Z122&lt;&gt;"",$Z122+7,IF($Y122&lt;&gt;"",$Y122+8,"")),IF($R122="",IF(OR($I122="B",$I122="C"),IF($W122&lt;&gt;"",$W122+7,IF($V122&lt;&gt;"",$V122+8,""))),"")))</f>
+        <f t="shared" ref="AA122:AA143" si="68">IF(AND($R122="",$I122=""),"",IF(OR($R122="B",$R122="C"),IF($Z122&lt;&gt;"",$Z122+7,IF($Y122&lt;&gt;"",$Y122+8,"")),IF($R122="",IF(OR($I122="B",$I122="C"),IF($W122&lt;&gt;"",$W122+7,IF($V122&lt;&gt;"",$V122+8,""))),"")))</f>
         <v>46286</v>
       </c>
       <c r="AB122" s="229"/>
@@ -21680,8 +21702,8 @@
       <c r="AH122" s="243" t="b" cm="1">
         <f t="array" ref="AH122">$E122=_xlfn.XLOOKUP(
 AG122,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -21772,8 +21794,8 @@
       <c r="AH123" s="243" t="b" cm="1">
         <f t="array" ref="AH123">$E123=_xlfn.XLOOKUP(
 AG123,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
 0,
 -1
@@ -21878,112 +21900,6 @@
       <c r="AH124" s="243" t="b" cm="1">
         <f t="array" ref="AH124">$E124=_xlfn.XLOOKUP(
 AG124,
-_xlfn._xlws.FILTER($AG$7:$AG$4577,$L$7:$L$4577&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4577,$L$7:$L$4577&lt;&gt;"X"),
-"",
-0,
--1
-)</f>
-        <v>1</v>
-      </c>
-      <c r="AI124" s="75" t="str">
-        <f t="shared" ref="AI124:AI142" si="74">IF($AH124,IF(OR($R124="B",$R124="C"),"YES",IF($R124="",IF(OR($I124="B",$I124="C"),"YES",""),"")),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="125" spans="1:35" s="9" customFormat="1" ht="47.25">
-      <c r="A125" s="33">
-        <f t="shared" si="19"/>
-        <v>119</v>
-      </c>
-      <c r="B125" s="330" t="str">
-        <f t="shared" si="72"/>
-        <v>5.11</v>
-      </c>
-      <c r="C125" s="164" t="s">
-        <v>656</v>
-      </c>
-      <c r="D125" s="137" t="s">
-        <v>30</v>
-      </c>
-      <c r="E125" s="25" t="s">
-        <v>997</v>
-      </c>
-      <c r="F125" s="174">
-        <f t="shared" si="29"/>
-        <v>46310</v>
-      </c>
-      <c r="G125" s="31" t="s">
-        <v>998</v>
-      </c>
-      <c r="H125" s="21" t="s">
-        <v>776</v>
-      </c>
-      <c r="I125" s="138" t="s">
-        <v>3</v>
-      </c>
-      <c r="J125" s="164">
-        <f t="shared" si="30"/>
-        <v>11</v>
-      </c>
-      <c r="K125" s="47">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="L125" s="164"/>
-      <c r="M125" s="40" t="s">
-        <v>8</v>
-      </c>
-      <c r="N125" s="41"/>
-      <c r="O125" s="40" t="s">
-        <v>8</v>
-      </c>
-      <c r="P125" s="41"/>
-      <c r="Q125" s="40"/>
-      <c r="R125" s="155"/>
-      <c r="S125" s="27">
-        <v>46289</v>
-      </c>
-      <c r="T125" s="27">
-        <v>46289</v>
-      </c>
-      <c r="U125" s="188">
-        <v>46289</v>
-      </c>
-      <c r="V125" s="29">
-        <v>46297</v>
-      </c>
-      <c r="W125" s="188">
-        <v>46300</v>
-      </c>
-      <c r="X125" s="235" t="s">
-        <v>240</v>
-      </c>
-      <c r="Y125" s="230"/>
-      <c r="Z125" s="227"/>
-      <c r="AA125" s="29" t="b">
-        <f t="shared" si="68"/>
-        <v>0</v>
-      </c>
-      <c r="AB125" s="229"/>
-      <c r="AC125" s="229" t="str">
-        <f t="shared" si="22"/>
-        <v/>
-      </c>
-      <c r="AD125" s="337" t="str">
-        <f t="shared" si="73"/>
-        <v/>
-      </c>
-      <c r="AE125" s="92" t="s">
-        <v>1024</v>
-      </c>
-      <c r="AG125" s="238" t="str">
-        <f t="shared" ref="AG125:AG140" si="75">IF(AND(RIGHT($E125,1)&gt;="A",RIGHT($E125,1)&lt;="Z"),LEFT($E125,LEN($E125)-1),$E125)</f>
-        <v xml:space="preserve"> LTIA-5.11-LTICT-71110-RFA-MAS-0021</v>
-      </c>
-      <c r="AH125" s="243" t="b" cm="1">
-        <f t="array" ref="AH125">$E125=_xlfn.XLOOKUP(
-AG125,
 _xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
 _xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
 "",
@@ -21992,6 +21908,112 @@
 )</f>
         <v>1</v>
       </c>
+      <c r="AI124" s="75" t="str">
+        <f t="shared" ref="AI124:AI143" si="74">IF($AH124,IF(OR($R124="B",$R124="C"),"YES",IF($R124="",IF(OR($I124="B",$I124="C"),"YES",""),"")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="125" spans="1:35" s="9" customFormat="1" ht="47.25">
+      <c r="A125" s="33">
+        <f t="shared" si="19"/>
+        <v>119</v>
+      </c>
+      <c r="B125" s="330" t="str">
+        <f t="shared" si="72"/>
+        <v>5.11</v>
+      </c>
+      <c r="C125" s="164" t="s">
+        <v>656</v>
+      </c>
+      <c r="D125" s="137" t="s">
+        <v>30</v>
+      </c>
+      <c r="E125" s="25" t="s">
+        <v>997</v>
+      </c>
+      <c r="F125" s="174">
+        <f t="shared" si="29"/>
+        <v>46310</v>
+      </c>
+      <c r="G125" s="31" t="s">
+        <v>998</v>
+      </c>
+      <c r="H125" s="21" t="s">
+        <v>776</v>
+      </c>
+      <c r="I125" s="138" t="s">
+        <v>3</v>
+      </c>
+      <c r="J125" s="164">
+        <f t="shared" si="30"/>
+        <v>11</v>
+      </c>
+      <c r="K125" s="47">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="L125" s="164"/>
+      <c r="M125" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="N125" s="41"/>
+      <c r="O125" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="P125" s="41"/>
+      <c r="Q125" s="40"/>
+      <c r="R125" s="155"/>
+      <c r="S125" s="27">
+        <v>46289</v>
+      </c>
+      <c r="T125" s="27">
+        <v>46289</v>
+      </c>
+      <c r="U125" s="188">
+        <v>46289</v>
+      </c>
+      <c r="V125" s="29">
+        <v>46297</v>
+      </c>
+      <c r="W125" s="188">
+        <v>46300</v>
+      </c>
+      <c r="X125" s="235" t="s">
+        <v>240</v>
+      </c>
+      <c r="Y125" s="230"/>
+      <c r="Z125" s="227"/>
+      <c r="AA125" s="29" t="b">
+        <f t="shared" si="68"/>
+        <v>0</v>
+      </c>
+      <c r="AB125" s="229"/>
+      <c r="AC125" s="229" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="AD125" s="337" t="str">
+        <f t="shared" si="73"/>
+        <v/>
+      </c>
+      <c r="AE125" s="92" t="s">
+        <v>1024</v>
+      </c>
+      <c r="AG125" s="238" t="str">
+        <f t="shared" ref="AG125:AG141" si="75">IF(AND(RIGHT($E125,1)&gt;="A",RIGHT($E125,1)&lt;="Z"),LEFT($E125,LEN($E125)-1),$E125)</f>
+        <v xml:space="preserve"> LTIA-5.11-LTICT-71110-RFA-MAS-0021</v>
+      </c>
+      <c r="AH125" s="243" t="b" cm="1">
+        <f t="array" ref="AH125">$E125=_xlfn.XLOOKUP(
+AG125,
+_xlfn._xlws.FILTER($AG$7:$AG$4579,$L$7:$L$4579&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4579,$L$7:$L$4579&lt;&gt;"X"),
+"",
+0,
+-1
+)</f>
+        <v>1</v>
+      </c>
       <c r="AI125" s="75" t="str">
         <f t="shared" si="74"/>
         <v/>
@@ -22090,8 +22112,8 @@
       <c r="AH126" s="243" t="b" cm="1">
         <f t="array" ref="AH126">$E126=_xlfn.XLOOKUP(
 AG126,
-_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4579,$L$7:$L$4579&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4579,$L$7:$L$4579&lt;&gt;"X"),
 "",
 0,
 -1
@@ -22190,8 +22212,8 @@
       <c r="AH127" s="243" t="b" cm="1">
         <f t="array" ref="AH127">$E127=_xlfn.XLOOKUP(
 AG127,
-_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4579,$L$7:$L$4579&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4579,$L$7:$L$4579&lt;&gt;"X"),
 "",
 0,
 -1
@@ -22234,7 +22256,7 @@
       <c r="I128" s="138"/>
       <c r="J128" s="164">
         <f t="shared" ca="1" si="30"/>
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="K128" s="47">
         <f t="shared" ca="1" si="31"/>
@@ -22278,8 +22300,8 @@
       <c r="AH128" s="243" t="b" cm="1">
         <f t="array" ref="AH128">$E128=_xlfn.XLOOKUP(
 AG128,
-_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4579,$L$7:$L$4579&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4579,$L$7:$L$4579&lt;&gt;"X"),
 "",
 0,
 -1
@@ -22322,7 +22344,7 @@
       <c r="I129" s="138"/>
       <c r="J129" s="164">
         <f t="shared" ca="1" si="30"/>
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="K129" s="47">
         <f t="shared" ca="1" si="31"/>
@@ -22368,8 +22390,8 @@
       <c r="AH129" s="243" t="b" cm="1">
         <f t="array" ref="AH129">$E129=_xlfn.XLOOKUP(
 AG129,
-_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4579,$L$7:$L$4579&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4579,$L$7:$L$4579&lt;&gt;"X"),
 "",
 0,
 -1
@@ -22412,7 +22434,7 @@
       <c r="I130" s="138"/>
       <c r="J130" s="164">
         <f t="shared" ca="1" si="30"/>
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K130" s="47">
         <f t="shared" ca="1" si="31"/>
@@ -22456,8 +22478,8 @@
       <c r="AH130" s="243" t="b" cm="1">
         <f t="array" ref="AH130">$E130=_xlfn.XLOOKUP(
 AG130,
-_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4579,$L$7:$L$4579&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4579,$L$7:$L$4579&lt;&gt;"X"),
 "",
 0,
 -1
@@ -22500,7 +22522,7 @@
       <c r="I131" s="138"/>
       <c r="J131" s="164">
         <f t="shared" ca="1" si="30"/>
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K131" s="47">
         <f t="shared" ca="1" si="31"/>
@@ -22546,8 +22568,8 @@
       <c r="AH131" s="243" t="b" cm="1">
         <f t="array" ref="AH131">$E131=_xlfn.XLOOKUP(
 AG131,
-_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4579,$L$7:$L$4579&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4579,$L$7:$L$4579&lt;&gt;"X"),
 "",
 0,
 -1
@@ -22590,7 +22612,7 @@
       <c r="I132" s="138"/>
       <c r="J132" s="164">
         <f t="shared" ca="1" si="30"/>
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="K132" s="47">
         <f t="shared" ca="1" si="31"/>
@@ -22636,8 +22658,8 @@
       <c r="AH132" s="243" t="b" cm="1">
         <f t="array" ref="AH132">$E132=_xlfn.XLOOKUP(
 AG132,
-_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4579,$L$7:$L$4579&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4579,$L$7:$L$4579&lt;&gt;"X"),
 "",
 0,
 -1
@@ -22680,7 +22702,7 @@
       <c r="I133" s="138"/>
       <c r="J133" s="164">
         <f t="shared" ca="1" si="30"/>
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="K133" s="47">
         <f t="shared" ca="1" si="31"/>
@@ -22724,8 +22746,8 @@
       <c r="AH133" s="243" t="b" cm="1">
         <f t="array" ref="AH133">$E133=_xlfn.XLOOKUP(
 AG133,
-_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4579,$L$7:$L$4579&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4579,$L$7:$L$4579&lt;&gt;"X"),
 "",
 0,
 -1
@@ -22768,7 +22790,7 @@
       <c r="I134" s="138"/>
       <c r="J134" s="164">
         <f t="shared" ca="1" si="30"/>
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="K134" s="47">
         <f t="shared" ca="1" si="31"/>
@@ -22812,8 +22834,8 @@
       <c r="AH134" s="243" t="b" cm="1">
         <f t="array" ref="AH134">$E134=_xlfn.XLOOKUP(
 AG134,
-_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4579,$L$7:$L$4579&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4579,$L$7:$L$4579&lt;&gt;"X"),
 "",
 0,
 -1
@@ -22858,7 +22880,7 @@
       </c>
       <c r="J135" s="164">
         <f t="shared" ca="1" si="30"/>
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="K135" s="47">
         <f t="shared" ca="1" si="31"/>
@@ -22906,8 +22928,8 @@
       <c r="AH135" s="243" t="b" cm="1">
         <f t="array" ref="AH135">$E135=_xlfn.XLOOKUP(
 AG135,
-_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4579,$L$7:$L$4579&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4579,$L$7:$L$4579&lt;&gt;"X"),
 "",
 0,
 -1
@@ -22950,7 +22972,7 @@
       <c r="I136" s="138"/>
       <c r="J136" s="164">
         <f t="shared" ca="1" si="30"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K136" s="47">
         <f t="shared" ca="1" si="31"/>
@@ -22994,8 +23016,8 @@
       <c r="AH136" s="243" t="b" cm="1">
         <f t="array" ref="AH136">$E136=_xlfn.XLOOKUP(
 AG136,
-_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4579,$L$7:$L$4579&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4579,$L$7:$L$4579&lt;&gt;"X"),
 "",
 0,
 -1
@@ -23038,7 +23060,7 @@
       <c r="I137" s="138"/>
       <c r="J137" s="164">
         <f t="shared" ca="1" si="30"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K137" s="47">
         <f t="shared" ca="1" si="31"/>
@@ -23082,8 +23104,8 @@
       <c r="AH137" s="243" t="b" cm="1">
         <f t="array" ref="AH137">$E137=_xlfn.XLOOKUP(
 AG137,
-_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4579,$L$7:$L$4579&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4579,$L$7:$L$4579&lt;&gt;"X"),
 "",
 0,
 -1
@@ -23126,7 +23148,7 @@
       <c r="I138" s="138"/>
       <c r="J138" s="164">
         <f t="shared" ca="1" si="30"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K138" s="47">
         <f t="shared" ca="1" si="31"/>
@@ -23170,8 +23192,8 @@
       <c r="AH138" s="243" t="b" cm="1">
         <f t="array" ref="AH138">$E138=_xlfn.XLOOKUP(
 AG138,
-_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4579,$L$7:$L$4579&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4579,$L$7:$L$4579&lt;&gt;"X"),
 "",
 0,
 -1
@@ -23214,7 +23236,7 @@
       <c r="I139" s="138"/>
       <c r="J139" s="164">
         <f t="shared" ca="1" si="30"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K139" s="47">
         <f t="shared" ca="1" si="31"/>
@@ -23258,8 +23280,8 @@
       <c r="AH139" s="243" t="b" cm="1">
         <f t="array" ref="AH139">$E139=_xlfn.XLOOKUP(
 AG139,
-_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4579,$L$7:$L$4579&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4579,$L$7:$L$4579&lt;&gt;"X"),
 "",
 0,
 -1
@@ -23302,7 +23324,7 @@
       <c r="I140" s="138"/>
       <c r="J140" s="164">
         <f t="shared" ca="1" si="30"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K140" s="47">
         <f t="shared" ca="1" si="31"/>
@@ -23346,8 +23368,8 @@
       <c r="AH140" s="243" t="b" cm="1">
         <f t="array" ref="AH140">$E140=_xlfn.XLOOKUP(
 AG140,
-_xlfn._xlws.FILTER($AG$7:$AG$4578,$L$7:$L$4578&lt;&gt;"X"),
-_xlfn._xlws.FILTER($E$7:$E$4578,$L$7:$L$4578&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4579,$L$7:$L$4579&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4579,$L$7:$L$4579&lt;&gt;"X"),
 "",
 0,
 -1
@@ -23359,28 +23381,61 @@
         <v/>
       </c>
     </row>
-    <row r="141" spans="1:35" s="9" customFormat="1">
-      <c r="A141" s="33"/>
-      <c r="B141" s="330"/>
-      <c r="C141" s="164"/>
-      <c r="D141" s="137"/>
-      <c r="E141" s="25"/>
-      <c r="F141" s="174"/>
-      <c r="G141" s="31"/>
-      <c r="H141" s="21"/>
+    <row r="141" spans="1:35" s="9" customFormat="1" ht="47.25">
+      <c r="A141" s="33">
+        <f t="shared" si="19"/>
+        <v>135</v>
+      </c>
+      <c r="B141" s="330" t="str">
+        <f t="shared" ref="B141" si="88">MID(E141, FIND("-", E141) + 1, 4)</f>
+        <v>5.11</v>
+      </c>
+      <c r="C141" s="164" t="s">
+        <v>342</v>
+      </c>
+      <c r="D141" s="137" t="s">
+        <v>28</v>
+      </c>
+      <c r="E141" s="25" t="s">
+        <v>1094</v>
+      </c>
+      <c r="F141" s="174">
+        <f t="shared" si="29"/>
+        <v>46333</v>
+      </c>
+      <c r="G141" s="31" t="s">
+        <v>1095</v>
+      </c>
+      <c r="H141" s="21" t="s">
+        <v>1096</v>
+      </c>
       <c r="I141" s="138"/>
-      <c r="J141" s="164"/>
-      <c r="K141" s="47"/>
+      <c r="J141" s="164">
+        <f t="shared" ca="1" si="30"/>
+        <v>2</v>
+      </c>
+      <c r="K141" s="47">
+        <f t="shared" ca="1" si="31"/>
+        <v>0</v>
+      </c>
       <c r="L141" s="164"/>
-      <c r="M141" s="40"/>
+      <c r="M141" s="40" t="s">
+        <v>8</v>
+      </c>
       <c r="N141" s="41"/>
       <c r="O141" s="40"/>
       <c r="P141" s="41"/>
       <c r="Q141" s="40"/>
       <c r="R141" s="155"/>
-      <c r="S141" s="27"/>
-      <c r="T141" s="27"/>
-      <c r="U141" s="188"/>
+      <c r="S141" s="27">
+        <v>46312</v>
+      </c>
+      <c r="T141" s="27">
+        <v>46312</v>
+      </c>
+      <c r="U141" s="188">
+        <v>46312</v>
+      </c>
       <c r="V141" s="29"/>
       <c r="W141" s="188"/>
       <c r="X141" s="235"/>
@@ -23394,141 +23449,140 @@
       <c r="AC141" s="229"/>
       <c r="AD141" s="337"/>
       <c r="AE141" s="92"/>
-      <c r="AG141" s="238"/>
-      <c r="AH141" s="243"/>
+      <c r="AG141" s="238" t="str">
+        <f t="shared" si="75"/>
+        <v>LTIA-5.11-LTICT-72020-RFA-OTH-0009</v>
+      </c>
+      <c r="AH141" s="243" t="b" cm="1">
+        <f t="array" ref="AH141">$E141=_xlfn.XLOOKUP(
+AG141,
+_xlfn._xlws.FILTER($AG$7:$AG$4579,$L$7:$L$4579&lt;&gt;"X"),
+_xlfn._xlws.FILTER($E$7:$E$4579,$L$7:$L$4579&lt;&gt;"X"),
+"",
+0,
+-1
+)</f>
+        <v>1</v>
+      </c>
       <c r="AI141" s="75" t="str">
         <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
-    <row r="142" spans="1:35" s="9" customFormat="1" ht="16.5" thickBot="1">
-      <c r="A142" s="347"/>
-      <c r="B142" s="338"/>
-      <c r="C142" s="178"/>
-      <c r="D142" s="139"/>
-      <c r="E142" s="339"/>
-      <c r="F142" s="340"/>
-      <c r="G142" s="32"/>
-      <c r="H142" s="22"/>
-      <c r="I142" s="139"/>
-      <c r="J142" s="178"/>
-      <c r="K142" s="49"/>
-      <c r="L142" s="178"/>
-      <c r="M142" s="341"/>
-      <c r="N142" s="342"/>
-      <c r="O142" s="341"/>
-      <c r="P142" s="342"/>
-      <c r="Q142" s="341"/>
-      <c r="R142" s="343"/>
-      <c r="S142" s="344"/>
-      <c r="T142" s="344"/>
-      <c r="U142" s="345"/>
-      <c r="V142" s="232"/>
-      <c r="W142" s="345"/>
-      <c r="X142" s="258"/>
-      <c r="Y142" s="232"/>
-      <c r="Z142" s="228"/>
-      <c r="AA142" s="232" t="str">
+    <row r="142" spans="1:35" s="9" customFormat="1">
+      <c r="A142" s="33"/>
+      <c r="B142" s="330"/>
+      <c r="C142" s="164"/>
+      <c r="D142" s="137"/>
+      <c r="E142" s="25"/>
+      <c r="F142" s="174"/>
+      <c r="G142" s="31"/>
+      <c r="H142" s="21"/>
+      <c r="I142" s="138"/>
+      <c r="J142" s="164"/>
+      <c r="K142" s="47"/>
+      <c r="L142" s="164"/>
+      <c r="M142" s="40"/>
+      <c r="N142" s="41"/>
+      <c r="O142" s="40"/>
+      <c r="P142" s="41"/>
+      <c r="Q142" s="40"/>
+      <c r="R142" s="155"/>
+      <c r="S142" s="27"/>
+      <c r="T142" s="27"/>
+      <c r="U142" s="188"/>
+      <c r="V142" s="29"/>
+      <c r="W142" s="188"/>
+      <c r="X142" s="235"/>
+      <c r="Y142" s="230"/>
+      <c r="Z142" s="227"/>
+      <c r="AA142" s="29" t="str">
         <f t="shared" si="68"/>
         <v/>
       </c>
-      <c r="AB142" s="233"/>
-      <c r="AC142" s="233"/>
-      <c r="AD142" s="346"/>
-      <c r="AE142" s="93"/>
-      <c r="AG142" s="239"/>
-      <c r="AH142" s="244"/>
-      <c r="AI142" s="241" t="str">
+      <c r="AB142" s="229"/>
+      <c r="AC142" s="229"/>
+      <c r="AD142" s="337"/>
+      <c r="AE142" s="92"/>
+      <c r="AG142" s="238"/>
+      <c r="AH142" s="243"/>
+      <c r="AI142" s="75" t="str">
         <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
-    <row r="143" spans="1:35" ht="16.5" thickBot="1"/>
-    <row r="144" spans="1:35" ht="16.5" thickBot="1">
-      <c r="A144" s="128"/>
-      <c r="B144" s="128"/>
-      <c r="C144" s="166" t="s">
-        <v>20</v>
-      </c>
-      <c r="D144" s="379" t="s">
-        <v>21</v>
-      </c>
-      <c r="E144" s="379"/>
-      <c r="F144" s="380"/>
-      <c r="G144" s="46"/>
-      <c r="H144" s="68"/>
-      <c r="I144" s="384" t="s">
-        <v>14</v>
-      </c>
-      <c r="J144" s="385"/>
-      <c r="K144" s="385"/>
-      <c r="L144" s="385"/>
-      <c r="M144" s="385"/>
-      <c r="N144" s="386"/>
-      <c r="O144" s="382" t="s">
-        <v>7</v>
-      </c>
-      <c r="P144" s="383"/>
-      <c r="Q144" s="382" t="s">
-        <v>109</v>
-      </c>
-      <c r="R144" s="383"/>
-      <c r="S144" s="1"/>
-      <c r="T144" s="1"/>
-      <c r="U144" s="140"/>
-      <c r="V144" s="1"/>
-      <c r="X144" s="11"/>
-      <c r="Y144" s="11"/>
-      <c r="Z144" s="11"/>
-      <c r="AA144" s="11"/>
-      <c r="AB144" s="11"/>
-      <c r="AC144" s="11"/>
-      <c r="AD144" s="11"/>
-      <c r="AG144" s="11"/>
-      <c r="AH144" s="11"/>
-      <c r="AI144" s="11"/>
-    </row>
+    <row r="143" spans="1:35" s="9" customFormat="1" ht="16.5" thickBot="1">
+      <c r="A143" s="347"/>
+      <c r="B143" s="338"/>
+      <c r="C143" s="178"/>
+      <c r="D143" s="139"/>
+      <c r="E143" s="339"/>
+      <c r="F143" s="340"/>
+      <c r="G143" s="32"/>
+      <c r="H143" s="22"/>
+      <c r="I143" s="139"/>
+      <c r="J143" s="178"/>
+      <c r="K143" s="49"/>
+      <c r="L143" s="178"/>
+      <c r="M143" s="341"/>
+      <c r="N143" s="342"/>
+      <c r="O143" s="341"/>
+      <c r="P143" s="342"/>
+      <c r="Q143" s="341"/>
+      <c r="R143" s="343"/>
+      <c r="S143" s="344"/>
+      <c r="T143" s="344"/>
+      <c r="U143" s="345"/>
+      <c r="V143" s="232"/>
+      <c r="W143" s="345"/>
+      <c r="X143" s="258"/>
+      <c r="Y143" s="232"/>
+      <c r="Z143" s="228"/>
+      <c r="AA143" s="232" t="str">
+        <f t="shared" si="68"/>
+        <v/>
+      </c>
+      <c r="AB143" s="233"/>
+      <c r="AC143" s="233"/>
+      <c r="AD143" s="346"/>
+      <c r="AE143" s="93"/>
+      <c r="AG143" s="239"/>
+      <c r="AH143" s="244"/>
+      <c r="AI143" s="241" t="str">
+        <f t="shared" si="74"/>
+        <v/>
+      </c>
+    </row>
+    <row r="144" spans="1:35" ht="16.5" thickBot="1"/>
     <row r="145" spans="1:35" ht="16.5" thickBot="1">
       <c r="A145" s="128"/>
       <c r="B145" s="128"/>
-      <c r="C145" s="167" t="s">
+      <c r="C145" s="166" t="s">
+        <v>20</v>
+      </c>
+      <c r="D145" s="416" t="s">
+        <v>21</v>
+      </c>
+      <c r="E145" s="416"/>
+      <c r="F145" s="417"/>
+      <c r="G145" s="46"/>
+      <c r="H145" s="68"/>
+      <c r="I145" s="392" t="s">
+        <v>14</v>
+      </c>
+      <c r="J145" s="393"/>
+      <c r="K145" s="393"/>
+      <c r="L145" s="393"/>
+      <c r="M145" s="393"/>
+      <c r="N145" s="394"/>
+      <c r="O145" s="388" t="s">
+        <v>7</v>
+      </c>
+      <c r="P145" s="389"/>
+      <c r="Q145" s="388" t="s">
         <v>109</v>
       </c>
-      <c r="D145" s="404" t="s">
-        <v>111</v>
-      </c>
-      <c r="E145" s="404"/>
-      <c r="F145" s="405"/>
-      <c r="G145" s="46"/>
-      <c r="H145" s="46"/>
-      <c r="I145" s="384" t="s">
-        <v>19</v>
-      </c>
-      <c r="J145" s="385"/>
-      <c r="K145" s="385"/>
-      <c r="L145" s="386"/>
-      <c r="M145" s="105">
-        <f t="shared" ref="M145:M150" ca="1" si="88">N145/$N$145</f>
-        <v>1</v>
-      </c>
-      <c r="N145" s="106">
-        <f ca="1">SUM($N$146:$N$150)</f>
-        <v>140</v>
-      </c>
-      <c r="O145" s="102" t="s">
-        <v>15</v>
-      </c>
-      <c r="P145" s="103" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q145" s="105">
-        <f ca="1">R145/$R$145</f>
-        <v>1</v>
-      </c>
-      <c r="R145" s="220">
-        <f ca="1">SUM(R146:R149)</f>
-        <v>122</v>
-      </c>
+      <c r="R145" s="389"/>
       <c r="S145" s="1"/>
       <c r="T145" s="1"/>
       <c r="U145" s="140"/>
@@ -23544,48 +23598,46 @@
       <c r="AH145" s="11"/>
       <c r="AI145" s="11"/>
     </row>
-    <row r="146" spans="1:35">
+    <row r="146" spans="1:35" ht="16.5" thickBot="1">
       <c r="A146" s="128"/>
       <c r="B146" s="128"/>
       <c r="C146" s="167" t="s">
-        <v>22</v>
-      </c>
-      <c r="D146" s="404" t="s">
-        <v>23</v>
-      </c>
-      <c r="E146" s="404"/>
-      <c r="F146" s="405"/>
-      <c r="G146" s="70"/>
-      <c r="H146" s="6"/>
-      <c r="I146" s="387" t="s">
-        <v>66</v>
-      </c>
-      <c r="J146" s="388"/>
-      <c r="K146" s="388"/>
-      <c r="L146" s="389"/>
-      <c r="M146" s="107">
-        <f t="shared" ca="1" si="88"/>
-        <v>0.49285714285714288</v>
-      </c>
-      <c r="N146" s="108">
-        <f>COUNTIF($I$7:$I$142,"A")</f>
-        <v>69</v>
-      </c>
-      <c r="O146" s="100">
-        <f ca="1">COUNTIFS($J$7:$J$142,"&lt;=21",$I$7:$I$142,"A")</f>
-        <v>56</v>
-      </c>
-      <c r="P146" s="101">
-        <f ca="1">COUNTIFS($J$7:$J$142,"&gt;21",$I$7:$I$142,"A")</f>
-        <v>12</v>
-      </c>
-      <c r="Q146" s="107">
-        <f ca="1">R146/$R$145</f>
-        <v>0.4098360655737705</v>
-      </c>
-      <c r="R146" s="108">
-        <f>COUNTIF($R$7:$R$142,"A")</f>
-        <v>50</v>
+        <v>109</v>
+      </c>
+      <c r="D146" s="427" t="s">
+        <v>111</v>
+      </c>
+      <c r="E146" s="427"/>
+      <c r="F146" s="428"/>
+      <c r="G146" s="46"/>
+      <c r="H146" s="46"/>
+      <c r="I146" s="392" t="s">
+        <v>19</v>
+      </c>
+      <c r="J146" s="393"/>
+      <c r="K146" s="393"/>
+      <c r="L146" s="394"/>
+      <c r="M146" s="105">
+        <f t="shared" ref="M146:M151" ca="1" si="89">N146/$N$146</f>
+        <v>1</v>
+      </c>
+      <c r="N146" s="106">
+        <f ca="1">SUM($N$147:$N$151)</f>
+        <v>141</v>
+      </c>
+      <c r="O146" s="102" t="s">
+        <v>15</v>
+      </c>
+      <c r="P146" s="103" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q146" s="105">
+        <f ca="1">R146/$R$146</f>
+        <v>1</v>
+      </c>
+      <c r="R146" s="220">
+        <f ca="1">SUM(R147:R150)</f>
+        <v>123</v>
       </c>
       <c r="S146" s="1"/>
       <c r="T146" s="1"/>
@@ -23606,43 +23658,44 @@
       <c r="A147" s="128"/>
       <c r="B147" s="128"/>
       <c r="C147" s="167" t="s">
-        <v>24</v>
-      </c>
-      <c r="D147" s="404" t="s">
-        <v>25</v>
-      </c>
-      <c r="E147" s="404"/>
-      <c r="F147" s="405"/>
+        <v>22</v>
+      </c>
+      <c r="D147" s="427" t="s">
+        <v>23</v>
+      </c>
+      <c r="E147" s="427"/>
+      <c r="F147" s="428"/>
+      <c r="G147" s="70"/>
       <c r="H147" s="6"/>
-      <c r="I147" s="390" t="s">
-        <v>67</v>
-      </c>
-      <c r="J147" s="391"/>
-      <c r="K147" s="391"/>
-      <c r="L147" s="392"/>
-      <c r="M147" s="109">
-        <f t="shared" ca="1" si="88"/>
-        <v>0.1</v>
-      </c>
-      <c r="N147" s="110">
-        <f>COUNTIF($I$7:$I$142,"B")</f>
-        <v>14</v>
-      </c>
-      <c r="O147" s="98">
-        <f ca="1">COUNTIFS($J$7:$J$142,"&lt;=21",$I$7:$I$142,"B")</f>
-        <v>7</v>
-      </c>
-      <c r="P147" s="50">
-        <f ca="1">COUNTIFS($J$7:$J$142,"&gt;21",$I$7:$I$142,"B")</f>
-        <v>7</v>
-      </c>
-      <c r="Q147" s="109">
-        <f t="shared" ref="Q147:Q149" ca="1" si="89">R147/$R$145</f>
-        <v>7.3770491803278687E-2</v>
-      </c>
-      <c r="R147" s="110">
-        <f>COUNTIF($R$7:$R$142,"B")</f>
-        <v>9</v>
+      <c r="I147" s="418" t="s">
+        <v>66</v>
+      </c>
+      <c r="J147" s="419"/>
+      <c r="K147" s="419"/>
+      <c r="L147" s="420"/>
+      <c r="M147" s="107">
+        <f t="shared" ca="1" si="89"/>
+        <v>0.48936170212765956</v>
+      </c>
+      <c r="N147" s="108">
+        <f>COUNTIF($I$7:$I$143,"A")</f>
+        <v>69</v>
+      </c>
+      <c r="O147" s="100">
+        <f ca="1">COUNTIFS($J$7:$J$143,"&lt;=21",$I$7:$I$143,"A")</f>
+        <v>56</v>
+      </c>
+      <c r="P147" s="101">
+        <f ca="1">COUNTIFS($J$7:$J$143,"&gt;21",$I$7:$I$143,"A")</f>
+        <v>12</v>
+      </c>
+      <c r="Q147" s="107">
+        <f ca="1">R147/$R$146</f>
+        <v>0.4065040650406504</v>
+      </c>
+      <c r="R147" s="108">
+        <f>COUNTIF($R$7:$R$143,"A")</f>
+        <v>50</v>
       </c>
       <c r="S147" s="1"/>
       <c r="T147" s="1"/>
@@ -23660,47 +23713,46 @@
       <c r="AI147" s="11"/>
     </row>
     <row r="148" spans="1:35">
-      <c r="A148" s="129"/>
-      <c r="B148" s="129"/>
+      <c r="A148" s="128"/>
+      <c r="B148" s="128"/>
       <c r="C148" s="167" t="s">
-        <v>26</v>
-      </c>
-      <c r="D148" s="404" t="s">
-        <v>27</v>
-      </c>
-      <c r="E148" s="404"/>
-      <c r="F148" s="405"/>
-      <c r="G148" s="71"/>
+        <v>24</v>
+      </c>
+      <c r="D148" s="427" t="s">
+        <v>25</v>
+      </c>
+      <c r="E148" s="427"/>
+      <c r="F148" s="428"/>
       <c r="H148" s="6"/>
-      <c r="I148" s="393" t="s">
-        <v>68</v>
-      </c>
-      <c r="J148" s="394"/>
-      <c r="K148" s="394"/>
-      <c r="L148" s="395"/>
-      <c r="M148" s="111">
-        <f t="shared" ca="1" si="88"/>
-        <v>0.19285714285714287</v>
-      </c>
-      <c r="N148" s="112">
-        <f>COUNTIF($I$7:$I$142,"C")</f>
-        <v>27</v>
+      <c r="I148" s="421" t="s">
+        <v>67</v>
+      </c>
+      <c r="J148" s="422"/>
+      <c r="K148" s="422"/>
+      <c r="L148" s="423"/>
+      <c r="M148" s="109">
+        <f t="shared" ca="1" si="89"/>
+        <v>9.9290780141843976E-2</v>
+      </c>
+      <c r="N148" s="110">
+        <f>COUNTIF($I$7:$I$143,"B")</f>
+        <v>14</v>
       </c>
       <c r="O148" s="98">
-        <f ca="1">COUNTIFS($J$7:$J$142,"&lt;=21",$I$7:$I$142,"C")</f>
-        <v>13</v>
+        <f ca="1">COUNTIFS($J$7:$J$143,"&lt;=21",$I$7:$I$143,"B")</f>
+        <v>7</v>
       </c>
       <c r="P148" s="50">
-        <f ca="1">COUNTIFS($J$7:$J$142,"&gt;21",$I$7:$I$142,"C")</f>
-        <v>14</v>
-      </c>
-      <c r="Q148" s="111">
-        <f t="shared" ca="1" si="89"/>
-        <v>0.13934426229508196</v>
-      </c>
-      <c r="R148" s="112">
-        <f>COUNTIF($R$7:$R$142,"C")</f>
-        <v>17</v>
+        <f ca="1">COUNTIFS($J$7:$J$143,"&gt;21",$I$7:$I$143,"B")</f>
+        <v>7</v>
+      </c>
+      <c r="Q148" s="109">
+        <f t="shared" ref="Q148:Q150" ca="1" si="90">R148/$R$146</f>
+        <v>7.3170731707317069E-2</v>
+      </c>
+      <c r="R148" s="110">
+        <f>COUNTIF($R$7:$R$143,"B")</f>
+        <v>9</v>
       </c>
       <c r="S148" s="1"/>
       <c r="T148" s="1"/>
@@ -23720,48 +23772,47 @@
     <row r="149" spans="1:35">
       <c r="A149" s="129"/>
       <c r="B149" s="129"/>
-      <c r="C149" s="168" t="s">
-        <v>28</v>
-      </c>
-      <c r="D149" s="404" t="s">
-        <v>29</v>
-      </c>
-      <c r="E149" s="404"/>
-      <c r="F149" s="405"/>
-      <c r="G149" s="72"/>
-      <c r="I149" s="396" t="s">
-        <v>70</v>
-      </c>
-      <c r="J149" s="397"/>
-      <c r="K149" s="397"/>
-      <c r="L149" s="398"/>
-      <c r="M149" s="114">
-        <f t="shared" ca="1" si="88"/>
-        <v>0.10714285714285714</v>
-      </c>
-      <c r="N149" s="115">
-        <f ca="1">SUM(O149:P149)</f>
-        <v>15</v>
+      <c r="C149" s="167" t="s">
+        <v>26</v>
+      </c>
+      <c r="D149" s="427" t="s">
+        <v>27</v>
+      </c>
+      <c r="E149" s="427"/>
+      <c r="F149" s="428"/>
+      <c r="G149" s="71"/>
+      <c r="H149" s="6"/>
+      <c r="I149" s="424" t="s">
+        <v>68</v>
+      </c>
+      <c r="J149" s="425"/>
+      <c r="K149" s="425"/>
+      <c r="L149" s="426"/>
+      <c r="M149" s="111">
+        <f t="shared" ca="1" si="89"/>
+        <v>0.19148936170212766</v>
+      </c>
+      <c r="N149" s="112">
+        <f>COUNTIF($I$7:$I$143,"C")</f>
+        <v>27</v>
       </c>
       <c r="O149" s="98">
-        <f ca="1">COUNTIFS($J$7:$J$142,"&lt;=21",$V$7:$V$142,"",$L$7:$L$142,"&lt;&gt;X")</f>
+        <f ca="1">COUNTIFS($J$7:$J$143,"&lt;=21",$I$7:$I$143,"C")</f>
         <v>13</v>
       </c>
       <c r="P149" s="50">
-        <f ca="1">COUNTIFS($J$7:$J$142,"&gt;21",$V$7:$V$142,"",$L$7:$L$142,"&lt;&gt;X")</f>
-        <v>2</v>
-      </c>
-      <c r="Q149" s="114">
-        <f t="shared" ca="1" si="89"/>
-        <v>0.37704918032786883</v>
-      </c>
-      <c r="R149" s="115">
-        <f ca="1">COUNTIFS($J$7:$J$142,"&gt;=0",$Q$7:$Q$142,"",$L$7:$L$142,"&lt;&gt;X")</f>
-        <v>46</v>
-      </c>
-      <c r="S149" s="1" t="s">
-        <v>10</v>
-      </c>
+        <f ca="1">COUNTIFS($J$7:$J$143,"&gt;21",$I$7:$I$143,"C")</f>
+        <v>14</v>
+      </c>
+      <c r="Q149" s="111">
+        <f t="shared" ca="1" si="90"/>
+        <v>0.13821138211382114</v>
+      </c>
+      <c r="R149" s="112">
+        <f>COUNTIF($R$7:$R$143,"C")</f>
+        <v>17</v>
+      </c>
+      <c r="S149" s="1"/>
       <c r="T149" s="1"/>
       <c r="U149" s="140"/>
       <c r="V149" s="1"/>
@@ -23776,97 +23827,122 @@
       <c r="AH149" s="11"/>
       <c r="AI149" s="11"/>
     </row>
-    <row r="150" spans="1:35" ht="16.5" thickBot="1">
+    <row r="150" spans="1:35">
       <c r="A150" s="129"/>
       <c r="B150" s="129"/>
       <c r="C150" s="168" t="s">
+        <v>28</v>
+      </c>
+      <c r="D150" s="427" t="s">
+        <v>29</v>
+      </c>
+      <c r="E150" s="427"/>
+      <c r="F150" s="428"/>
+      <c r="G150" s="72"/>
+      <c r="I150" s="374" t="s">
+        <v>70</v>
+      </c>
+      <c r="J150" s="375"/>
+      <c r="K150" s="375"/>
+      <c r="L150" s="376"/>
+      <c r="M150" s="114">
+        <f t="shared" ca="1" si="89"/>
+        <v>0.11347517730496454</v>
+      </c>
+      <c r="N150" s="115">
+        <f ca="1">SUM(O150:P150)</f>
+        <v>16</v>
+      </c>
+      <c r="O150" s="98">
+        <f ca="1">COUNTIFS($J$7:$J$143,"&lt;=21",$V$7:$V$143,"",$L$7:$L$143,"&lt;&gt;X")</f>
+        <v>14</v>
+      </c>
+      <c r="P150" s="50">
+        <f ca="1">COUNTIFS($J$7:$J$143,"&gt;21",$V$7:$V$143,"",$L$7:$L$143,"&lt;&gt;X")</f>
+        <v>2</v>
+      </c>
+      <c r="Q150" s="114">
+        <f t="shared" ca="1" si="90"/>
+        <v>0.38211382113821141</v>
+      </c>
+      <c r="R150" s="115">
+        <f ca="1">COUNTIFS($J$7:$J$143,"&gt;=0",$Q$7:$Q$143,"",$L$7:$L$143,"&lt;&gt;X")</f>
+        <v>47</v>
+      </c>
+      <c r="S150" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="T150" s="1"/>
+      <c r="U150" s="140"/>
+      <c r="V150" s="1"/>
+      <c r="X150" s="11"/>
+      <c r="Y150" s="11"/>
+      <c r="Z150" s="11"/>
+      <c r="AA150" s="11"/>
+      <c r="AB150" s="11"/>
+      <c r="AC150" s="11"/>
+      <c r="AD150" s="11"/>
+      <c r="AG150" s="11"/>
+      <c r="AH150" s="11"/>
+      <c r="AI150" s="11"/>
+    </row>
+    <row r="151" spans="1:35" ht="16.5" thickBot="1">
+      <c r="A151" s="129"/>
+      <c r="B151" s="129"/>
+      <c r="C151" s="168" t="s">
         <v>30</v>
       </c>
-      <c r="D150" s="404" t="s">
+      <c r="D151" s="427" t="s">
         <v>31</v>
       </c>
-      <c r="E150" s="404"/>
-      <c r="F150" s="405"/>
-      <c r="H150" s="6"/>
-      <c r="I150" s="399" t="s">
+      <c r="E151" s="427"/>
+      <c r="F151" s="428"/>
+      <c r="H151" s="6"/>
+      <c r="I151" s="377" t="s">
         <v>71</v>
       </c>
-      <c r="J150" s="400"/>
-      <c r="K150" s="400"/>
-      <c r="L150" s="401"/>
-      <c r="M150" s="113">
-        <f t="shared" ca="1" si="88"/>
-        <v>0.10714285714285714</v>
-      </c>
-      <c r="N150" s="97">
-        <f>COUNTIFS($L$7:$L$142,"X")</f>
+      <c r="J151" s="378"/>
+      <c r="K151" s="378"/>
+      <c r="L151" s="379"/>
+      <c r="M151" s="113">
+        <f t="shared" ca="1" si="89"/>
+        <v>0.10638297872340426</v>
+      </c>
+      <c r="N151" s="97">
+        <f>COUNTIFS($L$7:$L$143,"X")</f>
         <v>15</v>
       </c>
-      <c r="O150" s="99"/>
-      <c r="P150" s="51"/>
-      <c r="Q150" s="221"/>
-      <c r="R150" s="222"/>
-    </row>
-    <row r="151" spans="1:35">
-      <c r="A151" s="128"/>
-      <c r="B151" s="128"/>
-      <c r="C151" s="168" t="s">
+      <c r="O151" s="99"/>
+      <c r="P151" s="51"/>
+      <c r="Q151" s="221"/>
+      <c r="R151" s="222"/>
+    </row>
+    <row r="152" spans="1:35">
+      <c r="A152" s="128"/>
+      <c r="B152" s="128"/>
+      <c r="C152" s="168" t="s">
         <v>32</v>
       </c>
-      <c r="D151" s="404" t="s">
+      <c r="D152" s="427" t="s">
         <v>33</v>
       </c>
-      <c r="E151" s="404"/>
-      <c r="F151" s="405"/>
-      <c r="H151" s="1" t="s">
+      <c r="E152" s="427"/>
+      <c r="F152" s="428"/>
+      <c r="H152" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="152" spans="1:35">
-      <c r="C152" s="167" t="s">
+    <row r="153" spans="1:35">
+      <c r="C153" s="167" t="s">
         <v>34</v>
       </c>
-      <c r="D152" s="404" t="s">
+      <c r="D153" s="427" t="s">
         <v>35</v>
       </c>
-      <c r="E152" s="404"/>
-      <c r="F152" s="405"/>
-      <c r="H152" s="13"/>
-      <c r="I152" s="141"/>
-      <c r="J152" s="141"/>
-      <c r="K152" s="13"/>
-      <c r="L152" s="141"/>
-      <c r="M152" s="6"/>
-      <c r="N152" s="6"/>
-      <c r="O152" s="6"/>
-      <c r="P152" s="6"/>
-      <c r="Q152" s="6"/>
-      <c r="S152" s="6"/>
-      <c r="T152" s="1"/>
-      <c r="U152" s="140"/>
-      <c r="V152" s="1"/>
-      <c r="W152" s="140"/>
-      <c r="X152" s="1"/>
-      <c r="Y152" s="1"/>
-      <c r="Z152" s="1"/>
-      <c r="AA152" s="1"/>
-      <c r="AB152" s="1"/>
-      <c r="AC152" s="1"/>
-      <c r="AD152" s="1"/>
-      <c r="AG152" s="160"/>
-      <c r="AH152" s="1"/>
-      <c r="AI152" s="1"/>
-    </row>
-    <row r="153" spans="1:35">
-      <c r="C153" s="402" t="s">
-        <v>75</v>
-      </c>
-      <c r="D153" s="408" t="s">
-        <v>76</v>
-      </c>
-      <c r="E153" s="408"/>
-      <c r="F153" s="409"/>
+      <c r="E153" s="427"/>
+      <c r="F153" s="428"/>
       <c r="H153" s="13"/>
+      <c r="I153" s="141"/>
       <c r="J153" s="141"/>
       <c r="K153" s="13"/>
       <c r="L153" s="141"/>
@@ -23891,13 +23967,16 @@
       <c r="AH153" s="1"/>
       <c r="AI153" s="1"/>
     </row>
-    <row r="154" spans="1:35" ht="16.5" thickBot="1">
-      <c r="C154" s="403"/>
-      <c r="D154" s="410"/>
-      <c r="E154" s="410"/>
-      <c r="F154" s="411"/>
+    <row r="154" spans="1:35">
+      <c r="C154" s="382" t="s">
+        <v>75</v>
+      </c>
+      <c r="D154" s="384" t="s">
+        <v>76</v>
+      </c>
+      <c r="E154" s="384"/>
+      <c r="F154" s="385"/>
       <c r="H154" s="13"/>
-      <c r="I154" s="141"/>
       <c r="J154" s="141"/>
       <c r="K154" s="13"/>
       <c r="L154" s="141"/>
@@ -23922,7 +24001,11 @@
       <c r="AH154" s="1"/>
       <c r="AI154" s="1"/>
     </row>
-    <row r="155" spans="1:35">
+    <row r="155" spans="1:35" ht="16.5" thickBot="1">
+      <c r="C155" s="383"/>
+      <c r="D155" s="386"/>
+      <c r="E155" s="386"/>
+      <c r="F155" s="387"/>
       <c r="H155" s="13"/>
       <c r="I155" s="141"/>
       <c r="J155" s="141"/>
@@ -23950,12 +24033,6 @@
       <c r="AI155" s="1"/>
     </row>
     <row r="156" spans="1:35">
-      <c r="C156" s="381" t="s">
-        <v>41</v>
-      </c>
-      <c r="D156" s="381"/>
-      <c r="E156" s="381"/>
-      <c r="F156" s="381"/>
       <c r="H156" s="13"/>
       <c r="I156" s="141"/>
       <c r="J156" s="141"/>
@@ -23983,14 +24060,12 @@
       <c r="AI156" s="1"/>
     </row>
     <row r="157" spans="1:35">
-      <c r="C157" s="169" t="s">
-        <v>8</v>
-      </c>
-      <c r="D157" s="367" t="s">
-        <v>91</v>
-      </c>
-      <c r="E157" s="367"/>
-      <c r="F157" s="367"/>
+      <c r="C157" s="370" t="s">
+        <v>41</v>
+      </c>
+      <c r="D157" s="370"/>
+      <c r="E157" s="370"/>
+      <c r="F157" s="370"/>
       <c r="H157" s="13"/>
       <c r="I157" s="141"/>
       <c r="J157" s="141"/>
@@ -24021,11 +24096,11 @@
       <c r="C158" s="169" t="s">
         <v>8</v>
       </c>
-      <c r="D158" s="367" t="s">
-        <v>92</v>
-      </c>
-      <c r="E158" s="367"/>
-      <c r="F158" s="367"/>
+      <c r="D158" s="404" t="s">
+        <v>91</v>
+      </c>
+      <c r="E158" s="404"/>
+      <c r="F158" s="404"/>
       <c r="H158" s="13"/>
       <c r="I158" s="141"/>
       <c r="J158" s="141"/>
@@ -24056,11 +24131,11 @@
       <c r="C159" s="169" t="s">
         <v>8</v>
       </c>
-      <c r="D159" s="367" t="s">
-        <v>93</v>
-      </c>
-      <c r="E159" s="367"/>
-      <c r="F159" s="367"/>
+      <c r="D159" s="404" t="s">
+        <v>92</v>
+      </c>
+      <c r="E159" s="404"/>
+      <c r="F159" s="404"/>
       <c r="H159" s="13"/>
       <c r="I159" s="141"/>
       <c r="J159" s="141"/>
@@ -24087,7 +24162,15 @@
       <c r="AH159" s="1"/>
       <c r="AI159" s="1"/>
     </row>
-    <row r="160" spans="1:35" ht="16.5" thickBot="1">
+    <row r="160" spans="1:35">
+      <c r="C160" s="169" t="s">
+        <v>8</v>
+      </c>
+      <c r="D160" s="404" t="s">
+        <v>93</v>
+      </c>
+      <c r="E160" s="404"/>
+      <c r="F160" s="404"/>
       <c r="H160" s="13"/>
       <c r="I160" s="141"/>
       <c r="J160" s="141"/>
@@ -24115,12 +24198,6 @@
       <c r="AI160" s="1"/>
     </row>
     <row r="161" spans="3:35" ht="16.5" thickBot="1">
-      <c r="C161" s="371" t="s">
-        <v>96</v>
-      </c>
-      <c r="D161" s="372"/>
-      <c r="E161" s="372"/>
-      <c r="F161" s="373"/>
       <c r="H161" s="13"/>
       <c r="I161" s="141"/>
       <c r="J161" s="141"/>
@@ -24147,15 +24224,13 @@
       <c r="AH161" s="1"/>
       <c r="AI161" s="1"/>
     </row>
-    <row r="162" spans="3:35">
-      <c r="C162" s="212" t="s">
-        <v>81</v>
-      </c>
-      <c r="D162" s="374" t="s">
-        <v>97</v>
-      </c>
-      <c r="E162" s="374"/>
-      <c r="F162" s="375"/>
+    <row r="162" spans="3:35" ht="16.5" thickBot="1">
+      <c r="C162" s="408" t="s">
+        <v>96</v>
+      </c>
+      <c r="D162" s="409"/>
+      <c r="E162" s="409"/>
+      <c r="F162" s="410"/>
       <c r="H162" s="13"/>
       <c r="I162" s="141"/>
       <c r="J162" s="141"/>
@@ -24183,155 +24258,190 @@
       <c r="AI162" s="1"/>
     </row>
     <row r="163" spans="3:35">
-      <c r="C163" s="213" t="s">
-        <v>82</v>
-      </c>
-      <c r="D163" s="365" t="s">
-        <v>98</v>
-      </c>
-      <c r="E163" s="365"/>
-      <c r="F163" s="366"/>
+      <c r="C163" s="212" t="s">
+        <v>81</v>
+      </c>
+      <c r="D163" s="411" t="s">
+        <v>97</v>
+      </c>
+      <c r="E163" s="411"/>
+      <c r="F163" s="412"/>
+      <c r="H163" s="13"/>
+      <c r="I163" s="141"/>
+      <c r="J163" s="141"/>
+      <c r="K163" s="13"/>
+      <c r="L163" s="141"/>
+      <c r="M163" s="6"/>
+      <c r="N163" s="6"/>
+      <c r="O163" s="6"/>
+      <c r="P163" s="6"/>
+      <c r="Q163" s="6"/>
+      <c r="S163" s="6"/>
+      <c r="T163" s="1"/>
+      <c r="U163" s="140"/>
+      <c r="V163" s="1"/>
+      <c r="W163" s="140"/>
+      <c r="X163" s="1"/>
+      <c r="Y163" s="1"/>
+      <c r="Z163" s="1"/>
+      <c r="AA163" s="1"/>
+      <c r="AB163" s="1"/>
+      <c r="AC163" s="1"/>
+      <c r="AD163" s="1"/>
+      <c r="AG163" s="160"/>
+      <c r="AH163" s="1"/>
+      <c r="AI163" s="1"/>
     </row>
     <row r="164" spans="3:35">
       <c r="C164" s="213" t="s">
+        <v>82</v>
+      </c>
+      <c r="D164" s="402" t="s">
+        <v>98</v>
+      </c>
+      <c r="E164" s="402"/>
+      <c r="F164" s="403"/>
+    </row>
+    <row r="165" spans="3:35">
+      <c r="C165" s="213" t="s">
         <v>83</v>
       </c>
-      <c r="D164" s="365" t="s">
+      <c r="D165" s="402" t="s">
         <v>99</v>
       </c>
-      <c r="E164" s="365"/>
-      <c r="F164" s="366"/>
-    </row>
-    <row r="165" spans="3:35">
-      <c r="C165" s="214" t="s">
-        <v>84</v>
-      </c>
-      <c r="D165" s="365" t="s">
-        <v>100</v>
-      </c>
-      <c r="E165" s="365"/>
-      <c r="F165" s="366"/>
+      <c r="E165" s="402"/>
+      <c r="F165" s="403"/>
     </row>
     <row r="166" spans="3:35">
       <c r="C166" s="214" t="s">
+        <v>84</v>
+      </c>
+      <c r="D166" s="402" t="s">
+        <v>100</v>
+      </c>
+      <c r="E166" s="402"/>
+      <c r="F166" s="403"/>
+    </row>
+    <row r="167" spans="3:35">
+      <c r="C167" s="214" t="s">
         <v>85</v>
       </c>
-      <c r="D166" s="365" t="s">
+      <c r="D167" s="402" t="s">
         <v>101</v>
       </c>
-      <c r="E166" s="365"/>
-      <c r="F166" s="366"/>
-    </row>
-    <row r="167" spans="3:35" ht="18.75">
-      <c r="C167" s="214" t="s">
+      <c r="E167" s="402"/>
+      <c r="F167" s="403"/>
+    </row>
+    <row r="168" spans="3:35" ht="18.75">
+      <c r="C168" s="214" t="s">
         <v>86</v>
       </c>
-      <c r="D167" s="365" t="s">
+      <c r="D168" s="402" t="s">
         <v>102</v>
       </c>
-      <c r="E167" s="365"/>
-      <c r="F167" s="366"/>
-    </row>
-    <row r="168" spans="3:35" ht="18.75">
-      <c r="C168" s="213" t="s">
+      <c r="E168" s="402"/>
+      <c r="F168" s="403"/>
+    </row>
+    <row r="169" spans="3:35" ht="18.75">
+      <c r="C169" s="213" t="s">
         <v>87</v>
       </c>
-      <c r="D168" s="365" t="s">
+      <c r="D169" s="402" t="s">
         <v>103</v>
       </c>
-      <c r="E168" s="365"/>
-      <c r="F168" s="366"/>
-    </row>
-    <row r="169" spans="3:35">
-      <c r="C169" s="215" t="s">
+      <c r="E169" s="402"/>
+      <c r="F169" s="403"/>
+    </row>
+    <row r="170" spans="3:35">
+      <c r="C170" s="215" t="s">
         <v>88</v>
       </c>
-      <c r="D169" s="368" t="s">
+      <c r="D170" s="405" t="s">
         <v>104</v>
       </c>
-      <c r="E169" s="369"/>
-      <c r="F169" s="370"/>
-    </row>
-    <row r="170" spans="3:35" ht="18.75">
-      <c r="C170" s="215" t="s">
+      <c r="E170" s="406"/>
+      <c r="F170" s="407"/>
+    </row>
+    <row r="171" spans="3:35" ht="18.75">
+      <c r="C171" s="215" t="s">
         <v>89</v>
       </c>
-      <c r="D170" s="365" t="s">
+      <c r="D171" s="402" t="s">
         <v>105</v>
       </c>
-      <c r="E170" s="365"/>
-      <c r="F170" s="366"/>
-    </row>
-    <row r="171" spans="3:35">
-      <c r="C171" s="213" t="s">
+      <c r="E171" s="402"/>
+      <c r="F171" s="403"/>
+    </row>
+    <row r="172" spans="3:35">
+      <c r="C172" s="213" t="s">
         <v>90</v>
       </c>
-      <c r="D171" s="365" t="s">
+      <c r="D172" s="402" t="s">
         <v>106</v>
       </c>
-      <c r="E171" s="365"/>
-      <c r="F171" s="366"/>
-    </row>
-    <row r="172" spans="3:35" ht="16.5" thickBot="1">
-      <c r="C172" s="216" t="s">
+      <c r="E172" s="402"/>
+      <c r="F172" s="403"/>
+    </row>
+    <row r="173" spans="3:35" ht="16.5" thickBot="1">
+      <c r="C173" s="216" t="s">
         <v>94</v>
       </c>
-      <c r="D172" s="376" t="s">
+      <c r="D173" s="413" t="s">
         <v>107</v>
       </c>
-      <c r="E172" s="377"/>
-      <c r="F172" s="378"/>
+      <c r="E173" s="414"/>
+      <c r="F173" s="415"/>
     </row>
   </sheetData>
-  <autoFilter ref="A6:AE142" xr:uid="{C724CDAB-378C-47DB-9F45-08EE3BFB6E8B}">
+  <autoFilter ref="A6:AE143" xr:uid="{C724CDAB-378C-47DB-9F45-08EE3BFB6E8B}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A7:AE69">
       <sortCondition ref="T6:T69"/>
     </sortState>
   </autoFilter>
   <mergeCells count="59">
     <mergeCell ref="B4:B5"/>
-    <mergeCell ref="D153:F154"/>
-    <mergeCell ref="D145:F145"/>
-    <mergeCell ref="I145:L145"/>
+    <mergeCell ref="D154:F155"/>
+    <mergeCell ref="D146:F146"/>
+    <mergeCell ref="I146:L146"/>
     <mergeCell ref="AA4:AD4"/>
-    <mergeCell ref="Q144:R144"/>
-    <mergeCell ref="D150:F150"/>
+    <mergeCell ref="Q145:R145"/>
     <mergeCell ref="D151:F151"/>
     <mergeCell ref="D152:F152"/>
+    <mergeCell ref="D153:F153"/>
     <mergeCell ref="S4:U4"/>
     <mergeCell ref="L4:L5"/>
     <mergeCell ref="Q4:R4"/>
     <mergeCell ref="K4:K5"/>
     <mergeCell ref="Y4:Z4"/>
-    <mergeCell ref="D172:F172"/>
-    <mergeCell ref="D144:F144"/>
-    <mergeCell ref="C156:F156"/>
-    <mergeCell ref="O144:P144"/>
-    <mergeCell ref="I144:N144"/>
-    <mergeCell ref="I146:L146"/>
+    <mergeCell ref="D173:F173"/>
+    <mergeCell ref="D145:F145"/>
+    <mergeCell ref="C157:F157"/>
+    <mergeCell ref="O145:P145"/>
+    <mergeCell ref="I145:N145"/>
     <mergeCell ref="I147:L147"/>
     <mergeCell ref="I148:L148"/>
     <mergeCell ref="I149:L149"/>
     <mergeCell ref="I150:L150"/>
-    <mergeCell ref="C153:C154"/>
-    <mergeCell ref="D146:F146"/>
+    <mergeCell ref="I151:L151"/>
+    <mergeCell ref="C154:C155"/>
     <mergeCell ref="D147:F147"/>
     <mergeCell ref="D148:F148"/>
     <mergeCell ref="D149:F149"/>
-    <mergeCell ref="D157:F157"/>
-    <mergeCell ref="D171:F171"/>
+    <mergeCell ref="D150:F150"/>
     <mergeCell ref="D158:F158"/>
+    <mergeCell ref="D172:F172"/>
     <mergeCell ref="D159:F159"/>
-    <mergeCell ref="D166:F166"/>
+    <mergeCell ref="D160:F160"/>
     <mergeCell ref="D167:F167"/>
     <mergeCell ref="D168:F168"/>
     <mergeCell ref="D169:F169"/>
     <mergeCell ref="D170:F170"/>
-    <mergeCell ref="C161:F161"/>
-    <mergeCell ref="D162:F162"/>
+    <mergeCell ref="D171:F171"/>
+    <mergeCell ref="C162:F162"/>
     <mergeCell ref="D163:F163"/>
     <mergeCell ref="D164:F164"/>
     <mergeCell ref="D165:F165"/>
+    <mergeCell ref="D166:F166"/>
     <mergeCell ref="AG5:AG6"/>
     <mergeCell ref="AH5:AH6"/>
     <mergeCell ref="AI5:AI6"/>
@@ -24350,7 +24460,7 @@
     <mergeCell ref="O4:P4"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
-  <conditionalFormatting sqref="A7:AE142 AG7:AI142">
+  <conditionalFormatting sqref="A7:AE143 AG7:AI143">
     <cfRule type="expression" dxfId="18" priority="15" stopIfTrue="1">
       <formula>$L7="X"</formula>
     </cfRule>
@@ -24610,9 +24720,9 @@
     <hyperlink ref="P66" r:id="rId234" xr:uid="{943197F0-AD92-4E20-ACB9-85E2FC8AC2B6}"/>
     <hyperlink ref="P68" r:id="rId235" xr:uid="{B8D8E563-954E-4146-81D8-6B9C7FA5754F}"/>
     <hyperlink ref="P69" r:id="rId236" xr:uid="{B36E752F-3B1E-43A8-9FDB-009F10632DBE}"/>
-    <hyperlink ref="C157" r:id="rId237" xr:uid="{8E310CD5-A28F-4463-BCF0-54C44E66ED53}"/>
-    <hyperlink ref="C158" r:id="rId238" xr:uid="{5182D641-FE70-4AC5-A684-B03DCC409CD2}"/>
-    <hyperlink ref="C159" r:id="rId239" xr:uid="{1AA76CB8-C0E3-43B4-9061-99A680A3D3C7}"/>
+    <hyperlink ref="C158" r:id="rId237" xr:uid="{8E310CD5-A28F-4463-BCF0-54C44E66ED53}"/>
+    <hyperlink ref="C159" r:id="rId238" xr:uid="{5182D641-FE70-4AC5-A684-B03DCC409CD2}"/>
+    <hyperlink ref="C160" r:id="rId239" xr:uid="{1AA76CB8-C0E3-43B4-9061-99A680A3D3C7}"/>
     <hyperlink ref="Q7" r:id="rId240" xr:uid="{D3D10629-3F3E-4216-8F11-F525BC7A698A}"/>
     <hyperlink ref="Q8" r:id="rId241" xr:uid="{91F15092-AC5D-4C7E-9E23-E3913E29C1F3}"/>
     <hyperlink ref="Q9" r:id="rId242" xr:uid="{381D2B0A-72F0-4FCE-A724-4D1E565A253A}"/>
@@ -24877,9 +24987,10 @@
     <hyperlink ref="M138" r:id="rId501" xr:uid="{24F8F9C1-0497-4EC1-849F-4BFB6EF701D0}"/>
     <hyperlink ref="M139" r:id="rId502" xr:uid="{D1C7F371-1906-4C4E-9D64-07CD74AF282A}"/>
     <hyperlink ref="M140" r:id="rId503" xr:uid="{1BAE53B4-41B2-4955-9719-066BE2284B9D}"/>
+    <hyperlink ref="M141" r:id="rId504" xr:uid="{1AD5278F-5E89-48A8-B214-0DE3CB9C250D}"/>
   </hyperlinks>
   <pageMargins left="0.25" right="0.17" top="0.5" bottom="0.25" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="28" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId504"/>
+  <pageSetup paperSize="9" scale="28" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId505"/>
   <colBreaks count="1" manualBreakCount="1">
     <brk id="30" max="564" man="1"/>
   </colBreaks>
@@ -24932,7 +25043,7 @@
       </c>
       <c r="I1" s="176">
         <f ca="1">TODAY()</f>
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="J1" s="131"/>
       <c r="K1" s="197"/>
@@ -25017,88 +25128,88 @@
       <c r="AD3" s="159"/>
     </row>
     <row r="4" spans="1:35" s="5" customFormat="1" ht="36" customHeight="1" thickBot="1">
-      <c r="A4" s="350" t="s">
+      <c r="A4" s="396" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="406" t="s">
+      <c r="B4" s="350" t="s">
         <v>515</v>
       </c>
-      <c r="C4" s="359" t="s">
+      <c r="C4" s="364" t="s">
         <v>45</v>
       </c>
-      <c r="D4" s="348" t="s">
+      <c r="D4" s="352" t="s">
         <v>46</v>
       </c>
-      <c r="E4" s="357" t="s">
+      <c r="E4" s="400" t="s">
         <v>47</v>
       </c>
-      <c r="F4" s="348" t="s">
+      <c r="F4" s="352" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="355" t="s">
+      <c r="G4" s="398" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="352" t="s">
+      <c r="H4" s="358" t="s">
         <v>48</v>
       </c>
-      <c r="I4" s="352" t="s">
+      <c r="I4" s="358" t="s">
         <v>49</v>
       </c>
-      <c r="J4" s="348" t="s">
+      <c r="J4" s="352" t="s">
         <v>78</v>
       </c>
-      <c r="K4" s="352" t="s">
+      <c r="K4" s="358" t="s">
         <v>80</v>
       </c>
       <c r="L4" s="363" t="s">
         <v>53</v>
       </c>
-      <c r="M4" s="364"/>
+      <c r="M4" s="348"/>
       <c r="N4" s="362" t="s">
         <v>55</v>
       </c>
-      <c r="O4" s="364"/>
+      <c r="O4" s="348"/>
       <c r="P4" s="362" t="s">
         <v>72</v>
       </c>
-      <c r="Q4" s="364"/>
+      <c r="Q4" s="348"/>
       <c r="R4" s="363" t="s">
         <v>53</v>
       </c>
       <c r="S4" s="363"/>
-      <c r="T4" s="364"/>
+      <c r="T4" s="348"/>
       <c r="U4" s="362" t="s">
         <v>55</v>
       </c>
       <c r="V4" s="363"/>
-      <c r="W4" s="364"/>
-      <c r="X4" s="415" t="s">
+      <c r="W4" s="348"/>
+      <c r="X4" s="366" t="s">
         <v>72</v>
       </c>
-      <c r="Y4" s="427"/>
-      <c r="Z4" s="415" t="s">
+      <c r="Y4" s="442"/>
+      <c r="Z4" s="366" t="s">
         <v>112</v>
       </c>
-      <c r="AA4" s="413"/>
-      <c r="AB4" s="413"/>
-      <c r="AC4" s="414"/>
-      <c r="AD4" s="348" t="s">
+      <c r="AA4" s="430"/>
+      <c r="AB4" s="430"/>
+      <c r="AC4" s="431"/>
+      <c r="AD4" s="352" t="s">
         <v>79</v>
       </c>
       <c r="AG4" s="236"/>
     </row>
     <row r="5" spans="1:35" ht="78.75">
-      <c r="A5" s="351"/>
-      <c r="B5" s="407"/>
-      <c r="C5" s="360"/>
-      <c r="D5" s="354"/>
-      <c r="E5" s="358"/>
-      <c r="F5" s="354"/>
-      <c r="G5" s="356"/>
-      <c r="H5" s="353"/>
-      <c r="I5" s="353"/>
-      <c r="J5" s="354"/>
-      <c r="K5" s="353"/>
+      <c r="A5" s="397"/>
+      <c r="B5" s="351"/>
+      <c r="C5" s="365"/>
+      <c r="D5" s="353"/>
+      <c r="E5" s="401"/>
+      <c r="F5" s="353"/>
+      <c r="G5" s="399"/>
+      <c r="H5" s="359"/>
+      <c r="I5" s="359"/>
+      <c r="J5" s="353"/>
+      <c r="K5" s="359"/>
       <c r="L5" s="79" t="s">
         <v>52</v>
       </c>
@@ -25153,14 +25264,14 @@
       <c r="AC5" s="250" t="s">
         <v>118</v>
       </c>
-      <c r="AD5" s="361"/>
-      <c r="AG5" s="417" t="s">
+      <c r="AD5" s="349"/>
+      <c r="AG5" s="432" t="s">
         <v>119</v>
       </c>
-      <c r="AH5" s="419" t="s">
+      <c r="AH5" s="434" t="s">
         <v>120</v>
       </c>
-      <c r="AI5" s="421" t="s">
+      <c r="AI5" s="436" t="s">
         <v>121</v>
       </c>
     </row>
@@ -25195,9 +25306,9 @@
       <c r="AB6" s="86"/>
       <c r="AC6" s="86"/>
       <c r="AD6" s="74"/>
-      <c r="AG6" s="418"/>
-      <c r="AH6" s="420"/>
-      <c r="AI6" s="422"/>
+      <c r="AG6" s="433"/>
+      <c r="AH6" s="435"/>
+      <c r="AI6" s="437"/>
     </row>
     <row r="7" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A7" s="33">
@@ -25873,7 +25984,7 @@
       </c>
       <c r="AC12" s="183">
         <f t="shared" ca="1" si="7"/>
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="AD12" s="92"/>
       <c r="AG12" s="238" t="str">
@@ -26099,7 +26210,7 @@
       </c>
       <c r="AC14" s="183">
         <f t="shared" ca="1" si="7"/>
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="AD14" s="92"/>
       <c r="AG14" s="238" t="str">
@@ -26325,7 +26436,7 @@
       </c>
       <c r="AC16" s="183">
         <f t="shared" ca="1" si="7"/>
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="AD16" s="92"/>
       <c r="AG16" s="238" t="str">
@@ -26438,7 +26549,7 @@
       </c>
       <c r="AC17" s="183">
         <f t="shared" ca="1" si="7"/>
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="AD17" s="92"/>
       <c r="AG17" s="238" t="str">
@@ -26551,7 +26662,7 @@
       </c>
       <c r="AC18" s="183">
         <f t="shared" ca="1" si="7"/>
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="AD18" s="92"/>
       <c r="AG18" s="238" t="str">
@@ -27126,7 +27237,7 @@
       </c>
       <c r="AC23" s="183">
         <f t="shared" ca="1" si="7"/>
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="AD23" s="92"/>
       <c r="AG23" s="238" t="str">
@@ -27239,7 +27350,7 @@
       </c>
       <c r="AC24" s="183">
         <f t="shared" ca="1" si="7"/>
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="AD24" s="92"/>
       <c r="AG24" s="238" t="str">
@@ -27350,7 +27461,7 @@
       </c>
       <c r="AC25" s="183">
         <f t="shared" ca="1" si="7"/>
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="AD25" s="92" t="s">
         <v>887</v>
@@ -27465,7 +27576,7 @@
       </c>
       <c r="AC26" s="183">
         <f t="shared" ca="1" si="7"/>
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="AD26" s="92"/>
       <c r="AG26" s="238" t="str">
@@ -27578,7 +27689,7 @@
       </c>
       <c r="AC27" s="183">
         <f t="shared" ca="1" si="7"/>
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="AD27" s="92"/>
       <c r="AG27" s="238" t="str">
@@ -27897,7 +28008,7 @@
       </c>
       <c r="AC30" s="183">
         <f t="shared" ca="1" si="7"/>
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="AD30" s="92" t="s">
         <v>593</v>
@@ -27952,11 +28063,11 @@
       </c>
       <c r="I31" s="164">
         <f ca="1">IF(ISBLANK($V31),_xlfn.DAYS($I$1,$T31),_xlfn.DAYS($V31,$T31))</f>
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="J31" s="47">
         <f t="shared" ca="1" si="4"/>
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="K31" s="164"/>
       <c r="L31" s="54" t="s">
@@ -28355,7 +28466,7 @@
       <c r="H35" s="138"/>
       <c r="I35" s="164">
         <f t="shared" ca="1" si="10"/>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J35" s="47">
         <f t="shared" ca="1" si="4"/>
@@ -28551,11 +28662,11 @@
       </c>
       <c r="I37" s="164">
         <f t="shared" ca="1" si="10"/>
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="J37" s="47">
         <f t="shared" ca="1" si="4"/>
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K37" s="164"/>
       <c r="L37" s="54" t="s">
@@ -28749,7 +28860,7 @@
       <c r="H39" s="138"/>
       <c r="I39" s="164">
         <f t="shared" ca="1" si="10"/>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J39" s="47">
         <f t="shared" ca="1" si="4"/>
@@ -28840,7 +28951,7 @@
       <c r="H40" s="138"/>
       <c r="I40" s="164">
         <f t="shared" ca="1" si="10"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J40" s="47">
         <f t="shared" ca="1" si="4"/>
@@ -28984,28 +29095,28 @@
       <c r="C44" s="166" t="s">
         <v>20</v>
       </c>
-      <c r="D44" s="379" t="s">
+      <c r="D44" s="416" t="s">
         <v>21</v>
       </c>
-      <c r="E44" s="380"/>
+      <c r="E44" s="417"/>
       <c r="F44" s="46"/>
       <c r="G44" s="46"/>
-      <c r="H44" s="384" t="s">
+      <c r="H44" s="392" t="s">
         <v>14</v>
       </c>
-      <c r="I44" s="385"/>
-      <c r="J44" s="385"/>
-      <c r="K44" s="385"/>
-      <c r="L44" s="385"/>
-      <c r="M44" s="386"/>
-      <c r="N44" s="382" t="s">
+      <c r="I44" s="393"/>
+      <c r="J44" s="393"/>
+      <c r="K44" s="393"/>
+      <c r="L44" s="393"/>
+      <c r="M44" s="394"/>
+      <c r="N44" s="388" t="s">
         <v>7</v>
       </c>
-      <c r="O44" s="383"/>
-      <c r="P44" s="382" t="s">
+      <c r="O44" s="389"/>
+      <c r="P44" s="388" t="s">
         <v>109</v>
       </c>
-      <c r="Q44" s="383"/>
+      <c r="Q44" s="389"/>
       <c r="R44" s="1"/>
       <c r="S44" s="1"/>
       <c r="T44" s="140"/>
@@ -29025,17 +29136,17 @@
       <c r="C45" s="195" t="s">
         <v>109</v>
       </c>
-      <c r="D45" s="425" t="s">
+      <c r="D45" s="440" t="s">
         <v>111</v>
       </c>
-      <c r="E45" s="426"/>
+      <c r="E45" s="441"/>
       <c r="F45" s="46"/>
-      <c r="H45" s="384" t="s">
+      <c r="H45" s="392" t="s">
         <v>18</v>
       </c>
-      <c r="I45" s="385"/>
-      <c r="J45" s="385"/>
-      <c r="K45" s="386"/>
+      <c r="I45" s="393"/>
+      <c r="J45" s="393"/>
+      <c r="K45" s="394"/>
       <c r="L45" s="105">
         <f ca="1">M45/$M$45</f>
         <v>1</v>
@@ -29077,18 +29188,18 @@
       <c r="C46" s="195" t="s">
         <v>36</v>
       </c>
-      <c r="D46" s="423" t="s">
+      <c r="D46" s="438" t="s">
         <v>37</v>
       </c>
-      <c r="E46" s="424"/>
+      <c r="E46" s="439"/>
       <c r="F46" s="69"/>
       <c r="G46" s="6"/>
-      <c r="H46" s="387" t="s">
+      <c r="H46" s="418" t="s">
         <v>66</v>
       </c>
-      <c r="I46" s="388"/>
-      <c r="J46" s="388"/>
-      <c r="K46" s="389"/>
+      <c r="I46" s="419"/>
+      <c r="J46" s="419"/>
+      <c r="K46" s="420"/>
       <c r="L46" s="107">
         <f ca="1">M46/$M$45</f>
         <v>2.7777777777777776E-2</v>
@@ -29129,21 +29240,21 @@
       <c r="AI46" s="11"/>
     </row>
     <row r="47" spans="1:35">
-      <c r="C47" s="402" t="s">
+      <c r="C47" s="382" t="s">
         <v>75</v>
       </c>
-      <c r="D47" s="408" t="s">
+      <c r="D47" s="384" t="s">
         <v>76</v>
       </c>
-      <c r="E47" s="409"/>
+      <c r="E47" s="385"/>
       <c r="F47" s="70"/>
       <c r="G47" s="6"/>
-      <c r="H47" s="390" t="s">
+      <c r="H47" s="421" t="s">
         <v>67</v>
       </c>
-      <c r="I47" s="391"/>
-      <c r="J47" s="391"/>
-      <c r="K47" s="392"/>
+      <c r="I47" s="422"/>
+      <c r="J47" s="422"/>
+      <c r="K47" s="423"/>
       <c r="L47" s="109">
         <f t="shared" ref="L47:L50" ca="1" si="23">M47/$M$45</f>
         <v>0.55555555555555558</v>
@@ -29184,17 +29295,17 @@
       <c r="AI47" s="11"/>
     </row>
     <row r="48" spans="1:35" ht="16.5" thickBot="1">
-      <c r="C48" s="403"/>
-      <c r="D48" s="410"/>
-      <c r="E48" s="411"/>
+      <c r="C48" s="383"/>
+      <c r="D48" s="386"/>
+      <c r="E48" s="387"/>
       <c r="F48" s="71"/>
       <c r="G48" s="6"/>
-      <c r="H48" s="393" t="s">
+      <c r="H48" s="424" t="s">
         <v>68</v>
       </c>
-      <c r="I48" s="394"/>
-      <c r="J48" s="394"/>
-      <c r="K48" s="395"/>
+      <c r="I48" s="425"/>
+      <c r="J48" s="425"/>
+      <c r="K48" s="426"/>
       <c r="L48" s="111">
         <f t="shared" ca="1" si="23"/>
         <v>0.22222222222222221</v>
@@ -29237,12 +29348,12 @@
     <row r="49" spans="3:35">
       <c r="F49" s="72"/>
       <c r="G49" s="6"/>
-      <c r="H49" s="396" t="s">
+      <c r="H49" s="374" t="s">
         <v>70</v>
       </c>
-      <c r="I49" s="397"/>
-      <c r="J49" s="397"/>
-      <c r="K49" s="398"/>
+      <c r="I49" s="375"/>
+      <c r="J49" s="375"/>
+      <c r="K49" s="376"/>
       <c r="L49" s="114">
         <f t="shared" ca="1" si="23"/>
         <v>0.1388888888888889</v>
@@ -29285,17 +29396,17 @@
       <c r="AI49" s="11"/>
     </row>
     <row r="50" spans="3:35" ht="16.5" thickBot="1">
-      <c r="C50" s="381" t="s">
+      <c r="C50" s="370" t="s">
         <v>41</v>
       </c>
-      <c r="D50" s="381"/>
-      <c r="E50" s="381"/>
-      <c r="H50" s="399" t="s">
+      <c r="D50" s="370"/>
+      <c r="E50" s="370"/>
+      <c r="H50" s="377" t="s">
         <v>71</v>
       </c>
-      <c r="I50" s="400"/>
-      <c r="J50" s="400"/>
-      <c r="K50" s="401"/>
+      <c r="I50" s="378"/>
+      <c r="J50" s="378"/>
+      <c r="K50" s="379"/>
       <c r="L50" s="113">
         <f t="shared" ca="1" si="23"/>
         <v>5.5555555555555552E-2</v>
@@ -29551,7 +29662,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C184EF3E-84BF-4DCF-951B-B90EB4B9D23F}">
-  <dimension ref="A1:Z142"/>
+  <dimension ref="A1:Z143"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" customWidth="1"/>
@@ -29590,7 +29701,7 @@
       </c>
       <c r="I1" s="176">
         <f ca="1">TODAY()</f>
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="J1" s="131"/>
       <c r="K1" s="197"/>
@@ -29661,81 +29772,81 @@
       <c r="Z3" s="159"/>
     </row>
     <row r="4" spans="1:26" s="5" customFormat="1" ht="35.1" customHeight="1" thickBot="1">
-      <c r="A4" s="406" t="s">
+      <c r="A4" s="350" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="406" t="s">
+      <c r="B4" s="350" t="s">
         <v>515</v>
       </c>
-      <c r="C4" s="359" t="s">
+      <c r="C4" s="364" t="s">
         <v>45</v>
       </c>
-      <c r="D4" s="348" t="s">
+      <c r="D4" s="352" t="s">
         <v>46</v>
       </c>
-      <c r="E4" s="428" t="s">
+      <c r="E4" s="354" t="s">
         <v>47</v>
       </c>
-      <c r="F4" s="348" t="s">
+      <c r="F4" s="352" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="430" t="s">
+      <c r="G4" s="356" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="352" t="s">
+      <c r="H4" s="358" t="s">
         <v>48</v>
       </c>
-      <c r="I4" s="432" t="s">
+      <c r="I4" s="360" t="s">
         <v>49</v>
       </c>
-      <c r="J4" s="348" t="s">
+      <c r="J4" s="352" t="s">
         <v>78</v>
       </c>
-      <c r="K4" s="352" t="s">
+      <c r="K4" s="358" t="s">
         <v>80</v>
       </c>
       <c r="L4" s="362" t="s">
         <v>53</v>
       </c>
-      <c r="M4" s="364"/>
+      <c r="M4" s="348"/>
       <c r="N4" s="362" t="s">
         <v>55</v>
       </c>
-      <c r="O4" s="364"/>
+      <c r="O4" s="348"/>
       <c r="P4" s="362" t="s">
         <v>72</v>
       </c>
-      <c r="Q4" s="364"/>
+      <c r="Q4" s="348"/>
       <c r="R4" s="363" t="s">
         <v>53</v>
       </c>
       <c r="S4" s="363"/>
-      <c r="T4" s="364"/>
+      <c r="T4" s="348"/>
       <c r="U4" s="362" t="s">
         <v>55</v>
       </c>
       <c r="V4" s="363"/>
       <c r="W4" s="363"/>
-      <c r="X4" s="415" t="s">
+      <c r="X4" s="366" t="s">
         <v>72</v>
       </c>
-      <c r="Y4" s="416"/>
-      <c r="Z4" s="364" t="s">
+      <c r="Y4" s="367"/>
+      <c r="Z4" s="348" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="72" customHeight="1">
-      <c r="A5" s="407"/>
-      <c r="B5" s="407"/>
-      <c r="C5" s="360"/>
-      <c r="D5" s="354"/>
-      <c r="E5" s="429"/>
-      <c r="F5" s="354"/>
-      <c r="G5" s="431"/>
-      <c r="H5" s="353"/>
-      <c r="I5" s="433"/>
-      <c r="J5" s="354"/>
-      <c r="K5" s="353"/>
+      <c r="A5" s="351"/>
+      <c r="B5" s="351"/>
+      <c r="C5" s="365"/>
+      <c r="D5" s="353"/>
+      <c r="E5" s="355"/>
+      <c r="F5" s="353"/>
+      <c r="G5" s="357"/>
+      <c r="H5" s="359"/>
+      <c r="I5" s="361"/>
+      <c r="J5" s="353"/>
+      <c r="K5" s="359"/>
       <c r="L5" s="79" t="s">
         <v>52</v>
       </c>
@@ -29778,7 +29889,7 @@
       <c r="Y5" s="260" t="s">
         <v>114</v>
       </c>
-      <c r="Z5" s="361"/>
+      <c r="Z5" s="349"/>
     </row>
     <row r="6" spans="1:26" ht="15" customHeight="1" thickBot="1">
       <c r="A6" s="78"/>
@@ -31605,7 +31716,7 @@
       <c r="Y29" s="19"/>
       <c r="Z29" s="92"/>
     </row>
-    <row r="30" spans="1:26" s="9" customFormat="1" ht="47.25">
+    <row r="30" spans="1:26" s="9" customFormat="1" ht="31.5">
       <c r="A30" s="33">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -32335,11 +32446,11 @@
       <c r="H39" s="138"/>
       <c r="I39" s="164">
         <f t="shared" ca="1" si="9"/>
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="J39" s="47">
         <f t="shared" ca="1" si="10"/>
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="K39" s="164"/>
       <c r="L39" s="40"/>
@@ -33951,7 +34062,7 @@
       </c>
       <c r="Z59" s="92"/>
     </row>
-    <row r="60" spans="1:26" s="9" customFormat="1" ht="63">
+    <row r="60" spans="1:26" s="9" customFormat="1" ht="47.25">
       <c r="A60" s="33">
         <f t="shared" si="0"/>
         <v>54</v>
@@ -34741,11 +34852,11 @@
       </c>
       <c r="I70" s="164">
         <f t="shared" ref="I70:I78" ca="1" si="14">IF(ISBLANK($V70),_xlfn.DAYS($I$1,$T70),_xlfn.DAYS($V70,$T70))</f>
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="J70" s="47">
         <f t="shared" ref="J70:J78" ca="1" si="15">IF(($I70-21)&gt;0,$I70-21,0)</f>
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="K70" s="164"/>
       <c r="L70" s="40"/>
@@ -35462,7 +35573,7 @@
         <v>628</v>
       </c>
       <c r="E80" s="174">
-        <f t="shared" ref="E80:E128" si="23">IF($T80=0,$S80+22,$T80+21)</f>
+        <f t="shared" ref="E80:E129" si="23">IF($T80=0,$S80+22,$T80+21)</f>
         <v>45945</v>
       </c>
       <c r="F80" s="31" t="s">
@@ -35475,11 +35586,11 @@
         <v>6</v>
       </c>
       <c r="I80" s="164">
-        <f t="shared" ref="I80:I128" si="24">IF(ISBLANK($V80),_xlfn.DAYS($I$1,$T80),_xlfn.DAYS($V80,$T80))</f>
+        <f t="shared" ref="I80:I129" si="24">IF(ISBLANK($V80),_xlfn.DAYS($I$1,$T80),_xlfn.DAYS($V80,$T80))</f>
         <v>6</v>
       </c>
       <c r="J80" s="47">
-        <f t="shared" ref="J80:J128" si="25">IF(($I80-21)&gt;0,$I80-21,0)</f>
+        <f t="shared" ref="J80:J129" si="25">IF(($I80-21)&gt;0,$I80-21,0)</f>
         <v>0</v>
       </c>
       <c r="K80" s="164"/>
@@ -35822,7 +35933,7 @@
     </row>
     <row r="85" spans="1:26" s="9" customFormat="1" ht="47.25">
       <c r="A85" s="33">
-        <f t="shared" ref="A85:A128" si="29">A84+1</f>
+        <f t="shared" ref="A85:A129" si="29">A84+1</f>
         <v>79</v>
       </c>
       <c r="B85" s="33" t="str">
@@ -36699,11 +36810,11 @@
       <c r="H97" s="138"/>
       <c r="I97" s="164">
         <f t="shared" ca="1" si="24"/>
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="J97" s="47">
         <f t="shared" ca="1" si="25"/>
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="K97" s="164"/>
       <c r="L97" s="40" t="s">
@@ -37819,11 +37930,11 @@
       <c r="H112" s="138"/>
       <c r="I112" s="164">
         <f t="shared" ca="1" si="24"/>
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="J112" s="47">
         <f t="shared" ca="1" si="25"/>
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="K112" s="164" t="s">
         <v>13</v>
@@ -37886,11 +37997,11 @@
       </c>
       <c r="I113" s="164">
         <f t="shared" ca="1" si="24"/>
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="J113" s="47">
         <f t="shared" ca="1" si="25"/>
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="K113" s="164"/>
       <c r="L113" s="40" t="s">
@@ -38022,11 +38133,11 @@
       <c r="H115" s="138"/>
       <c r="I115" s="164">
         <f t="shared" ca="1" si="24"/>
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="J115" s="47">
         <f t="shared" ca="1" si="25"/>
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="K115" s="164"/>
       <c r="L115" s="40" t="s">
@@ -38692,7 +38803,7 @@
       </c>
       <c r="I125" s="164">
         <f t="shared" ca="1" si="24"/>
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J125" s="47">
         <f t="shared" ca="1" si="25"/>
@@ -38757,7 +38868,7 @@
       </c>
       <c r="I126" s="164">
         <f t="shared" ca="1" si="24"/>
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J126" s="47">
         <f t="shared" ca="1" si="25"/>
@@ -38818,7 +38929,7 @@
       <c r="H127" s="138"/>
       <c r="I127" s="164">
         <f t="shared" ca="1" si="24"/>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J127" s="47">
         <f t="shared" ca="1" si="25"/>
@@ -38879,7 +38990,7 @@
       <c r="H128" s="138"/>
       <c r="I128" s="164">
         <f t="shared" ca="1" si="24"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J128" s="47">
         <f t="shared" ca="1" si="25"/>
@@ -38910,135 +39021,148 @@
       <c r="Y128" s="19"/>
       <c r="Z128" s="92"/>
     </row>
-    <row r="129" spans="1:26" s="9" customFormat="1">
-      <c r="A129" s="23"/>
-      <c r="B129" s="33"/>
-      <c r="C129" s="137"/>
-      <c r="D129" s="25"/>
-      <c r="E129" s="174"/>
-      <c r="F129" s="31"/>
-      <c r="G129" s="21"/>
+    <row r="129" spans="1:26" s="9" customFormat="1" ht="63">
+      <c r="A129" s="33">
+        <f t="shared" si="29"/>
+        <v>123</v>
+      </c>
+      <c r="B129" s="33" t="str">
+        <f t="shared" ref="B129" si="60">MID(D129, FIND("-", D129) + 1, 4)</f>
+        <v>5.10</v>
+      </c>
+      <c r="C129" s="164" t="s">
+        <v>195</v>
+      </c>
+      <c r="D129" s="25" t="s">
+        <v>1091</v>
+      </c>
+      <c r="E129" s="174">
+        <f t="shared" si="23"/>
+        <v>46332</v>
+      </c>
+      <c r="F129" s="31" t="s">
+        <v>1092</v>
+      </c>
+      <c r="G129" s="21" t="s">
+        <v>1093</v>
+      </c>
       <c r="H129" s="138"/>
-      <c r="I129" s="177"/>
-      <c r="J129" s="48"/>
-      <c r="K129" s="177"/>
-      <c r="L129" s="59"/>
-      <c r="M129" s="60"/>
-      <c r="N129" s="61"/>
-      <c r="O129" s="144"/>
-      <c r="P129" s="146"/>
-      <c r="Q129" s="152"/>
-      <c r="R129" s="27"/>
-      <c r="S129" s="27"/>
-      <c r="T129" s="187"/>
+      <c r="I129" s="164">
+        <f t="shared" ca="1" si="24"/>
+        <v>3</v>
+      </c>
+      <c r="J129" s="47">
+        <f t="shared" ca="1" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="K129" s="164"/>
+      <c r="L129" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="M129" s="41"/>
+      <c r="N129" s="40"/>
+      <c r="O129" s="41"/>
+      <c r="P129" s="40"/>
+      <c r="Q129" s="154"/>
+      <c r="R129" s="27">
+        <v>46311</v>
+      </c>
+      <c r="S129" s="27">
+        <v>46311</v>
+      </c>
+      <c r="T129" s="188">
+        <v>46311</v>
+      </c>
       <c r="U129" s="29"/>
-      <c r="V129" s="188"/>
+      <c r="V129" s="211"/>
       <c r="W129" s="235"/>
       <c r="X129" s="230"/>
       <c r="Y129" s="19"/>
       <c r="Z129" s="92"/>
     </row>
-    <row r="130" spans="1:26" s="9" customFormat="1" ht="16.5" thickBot="1">
-      <c r="A130" s="24"/>
-      <c r="B130" s="329"/>
-      <c r="C130" s="165"/>
-      <c r="D130" s="45"/>
-      <c r="E130" s="175"/>
-      <c r="F130" s="32"/>
-      <c r="G130" s="22"/>
-      <c r="H130" s="139"/>
-      <c r="I130" s="178"/>
-      <c r="J130" s="49"/>
-      <c r="K130" s="178"/>
-      <c r="L130" s="62"/>
-      <c r="M130" s="63"/>
-      <c r="N130" s="64"/>
-      <c r="O130" s="145"/>
-      <c r="P130" s="147"/>
-      <c r="Q130" s="153"/>
-      <c r="R130" s="44"/>
-      <c r="S130" s="44"/>
-      <c r="T130" s="189"/>
-      <c r="U130" s="43"/>
-      <c r="V130" s="194"/>
-      <c r="W130" s="258"/>
-      <c r="X130" s="232"/>
-      <c r="Y130" s="20"/>
-      <c r="Z130" s="93"/>
-    </row>
-    <row r="131" spans="1:26" ht="16.5" thickBot="1"/>
-    <row r="132" spans="1:26" ht="16.5" thickBot="1">
-      <c r="C132" s="207" t="s">
+    <row r="130" spans="1:26" s="9" customFormat="1">
+      <c r="A130" s="23"/>
+      <c r="B130" s="33"/>
+      <c r="C130" s="137"/>
+      <c r="D130" s="25"/>
+      <c r="E130" s="174"/>
+      <c r="F130" s="31"/>
+      <c r="G130" s="21"/>
+      <c r="H130" s="138"/>
+      <c r="I130" s="177"/>
+      <c r="J130" s="48"/>
+      <c r="K130" s="177"/>
+      <c r="L130" s="59"/>
+      <c r="M130" s="60"/>
+      <c r="N130" s="61"/>
+      <c r="O130" s="144"/>
+      <c r="P130" s="146"/>
+      <c r="Q130" s="152"/>
+      <c r="R130" s="27"/>
+      <c r="S130" s="27"/>
+      <c r="T130" s="187"/>
+      <c r="U130" s="29"/>
+      <c r="V130" s="188"/>
+      <c r="W130" s="235"/>
+      <c r="X130" s="230"/>
+      <c r="Y130" s="19"/>
+      <c r="Z130" s="92"/>
+    </row>
+    <row r="131" spans="1:26" s="9" customFormat="1" ht="16.5" thickBot="1">
+      <c r="A131" s="24"/>
+      <c r="B131" s="329"/>
+      <c r="C131" s="165"/>
+      <c r="D131" s="45"/>
+      <c r="E131" s="175"/>
+      <c r="F131" s="32"/>
+      <c r="G131" s="22"/>
+      <c r="H131" s="139"/>
+      <c r="I131" s="178"/>
+      <c r="J131" s="49"/>
+      <c r="K131" s="178"/>
+      <c r="L131" s="62"/>
+      <c r="M131" s="63"/>
+      <c r="N131" s="64"/>
+      <c r="O131" s="145"/>
+      <c r="P131" s="147"/>
+      <c r="Q131" s="153"/>
+      <c r="R131" s="44"/>
+      <c r="S131" s="44"/>
+      <c r="T131" s="189"/>
+      <c r="U131" s="43"/>
+      <c r="V131" s="194"/>
+      <c r="W131" s="258"/>
+      <c r="X131" s="232"/>
+      <c r="Y131" s="20"/>
+      <c r="Z131" s="93"/>
+    </row>
+    <row r="132" spans="1:26" ht="16.5" thickBot="1"/>
+    <row r="133" spans="1:26" ht="16.5" thickBot="1">
+      <c r="C133" s="207" t="s">
         <v>38</v>
       </c>
-      <c r="D132" s="441" t="s">
+      <c r="D133" s="390" t="s">
         <v>39</v>
       </c>
-      <c r="E132" s="442"/>
-      <c r="F132" s="46"/>
-      <c r="G132" s="68"/>
-      <c r="H132" s="384" t="s">
+      <c r="E133" s="391"/>
+      <c r="F133" s="46"/>
+      <c r="G133" s="68"/>
+      <c r="H133" s="392" t="s">
         <v>14</v>
       </c>
-      <c r="I132" s="385"/>
-      <c r="J132" s="385"/>
-      <c r="K132" s="385"/>
-      <c r="L132" s="385"/>
-      <c r="M132" s="386"/>
-      <c r="N132" s="382" t="s">
+      <c r="I133" s="393"/>
+      <c r="J133" s="393"/>
+      <c r="K133" s="393"/>
+      <c r="L133" s="393"/>
+      <c r="M133" s="394"/>
+      <c r="N133" s="388" t="s">
         <v>7</v>
       </c>
-      <c r="O132" s="383"/>
-      <c r="P132" s="382" t="s">
+      <c r="O133" s="389"/>
+      <c r="P133" s="388" t="s">
         <v>110</v>
       </c>
-      <c r="Q132" s="383"/>
-      <c r="R132" s="1"/>
-      <c r="S132" s="1"/>
-      <c r="T132" s="140"/>
-      <c r="U132" s="1"/>
-      <c r="W132" s="11"/>
-      <c r="X132" s="11"/>
-      <c r="Y132" s="11"/>
-    </row>
-    <row r="133" spans="1:26" ht="16.5" customHeight="1" thickBot="1">
-      <c r="C133" s="208" t="s">
-        <v>74</v>
-      </c>
-      <c r="D133" s="439" t="s">
-        <v>77</v>
-      </c>
-      <c r="E133" s="440"/>
-      <c r="F133" s="46"/>
-      <c r="G133" s="46"/>
-      <c r="H133" s="434" t="s">
-        <v>17</v>
-      </c>
-      <c r="I133" s="435"/>
-      <c r="J133" s="130"/>
-      <c r="K133" s="210"/>
-      <c r="L133" s="117">
-        <f ca="1">M133/$M$133</f>
-        <v>1</v>
-      </c>
-      <c r="M133" s="104">
-        <f ca="1">SUM($M$134:$M$136)</f>
-        <v>128</v>
-      </c>
-      <c r="N133" s="118" t="s">
-        <v>15</v>
-      </c>
-      <c r="O133" s="119" t="s">
-        <v>16</v>
-      </c>
-      <c r="P133" s="117">
-        <f ca="1">Q133/$Q$133</f>
-        <v>1</v>
-      </c>
-      <c r="Q133" s="104">
-        <f ca="1">SUM(Q134:Q135)</f>
-        <v>108</v>
-      </c>
+      <c r="Q133" s="389"/>
       <c r="R133" s="1"/>
       <c r="S133" s="1"/>
       <c r="T133" s="140"/>
@@ -39047,45 +39171,43 @@
       <c r="X133" s="11"/>
       <c r="Y133" s="11"/>
     </row>
-    <row r="134" spans="1:26">
-      <c r="C134" s="402" t="s">
-        <v>6</v>
-      </c>
-      <c r="D134" s="439" t="s">
-        <v>40</v>
-      </c>
-      <c r="E134" s="440"/>
-      <c r="F134" s="69"/>
-      <c r="G134" s="6"/>
-      <c r="H134" s="436" t="s">
-        <v>69</v>
-      </c>
-      <c r="I134" s="437"/>
-      <c r="J134" s="437"/>
-      <c r="K134" s="438"/>
-      <c r="L134" s="122">
-        <f t="shared" ref="L134:L136" ca="1" si="60">M134/$M$133</f>
-        <v>0.8203125</v>
-      </c>
-      <c r="M134" s="123">
-        <f>COUNTIF($H$7:$H$130,"RFCS")</f>
-        <v>105</v>
-      </c>
-      <c r="N134" s="121">
-        <f ca="1">COUNTIFS($I$7:$I$130,"&lt;=21",$H$7:$H$130,"RFCS")</f>
-        <v>63</v>
-      </c>
-      <c r="O134" s="120">
-        <f ca="1">COUNTIFS($I$7:$I$130,"&gt;21",$H$7:$H$130,"RFCS")</f>
-        <v>41</v>
-      </c>
-      <c r="P134" s="122">
-        <f ca="1">Q134/$Q$133</f>
-        <v>0.62962962962962965</v>
-      </c>
-      <c r="Q134" s="123">
-        <f>COUNTIF($Q$7:$Q$130,"RBE") + COUNTIF($Q$7:$Q$130,"SUP")</f>
-        <v>68</v>
+    <row r="134" spans="1:26" ht="16.5" customHeight="1" thickBot="1">
+      <c r="C134" s="208" t="s">
+        <v>74</v>
+      </c>
+      <c r="D134" s="380" t="s">
+        <v>77</v>
+      </c>
+      <c r="E134" s="381"/>
+      <c r="F134" s="46"/>
+      <c r="G134" s="46"/>
+      <c r="H134" s="368" t="s">
+        <v>17</v>
+      </c>
+      <c r="I134" s="369"/>
+      <c r="J134" s="130"/>
+      <c r="K134" s="210"/>
+      <c r="L134" s="117">
+        <f ca="1">M134/$M$134</f>
+        <v>1</v>
+      </c>
+      <c r="M134" s="104">
+        <f ca="1">SUM($M$135:$M$137)</f>
+        <v>129</v>
+      </c>
+      <c r="N134" s="118" t="s">
+        <v>15</v>
+      </c>
+      <c r="O134" s="119" t="s">
+        <v>16</v>
+      </c>
+      <c r="P134" s="117">
+        <f ca="1">Q134/$Q$134</f>
+        <v>1</v>
+      </c>
+      <c r="Q134" s="104">
+        <f ca="1">SUM(Q135:Q136)</f>
+        <v>109</v>
       </c>
       <c r="R134" s="1"/>
       <c r="S134" s="1"/>
@@ -39096,44 +39218,46 @@
       <c r="Y134" s="11"/>
     </row>
     <row r="135" spans="1:26">
-      <c r="C135" s="402"/>
-      <c r="D135" s="439"/>
-      <c r="E135" s="440"/>
-      <c r="F135" s="72"/>
+      <c r="C135" s="382" t="s">
+        <v>6</v>
+      </c>
+      <c r="D135" s="380" t="s">
+        <v>40</v>
+      </c>
+      <c r="E135" s="381"/>
+      <c r="F135" s="69"/>
       <c r="G135" s="6"/>
-      <c r="H135" s="396" t="s">
-        <v>70</v>
-      </c>
-      <c r="I135" s="397"/>
-      <c r="J135" s="397"/>
-      <c r="K135" s="398"/>
-      <c r="L135" s="124">
-        <f t="shared" ca="1" si="60"/>
-        <v>7.03125E-2</v>
-      </c>
-      <c r="M135" s="125">
-        <f ca="1">SUM(N135:O135)</f>
-        <v>9</v>
-      </c>
-      <c r="N135" s="98">
-        <f ca="1">COUNTIFS($I$7:$I$130,"&lt;=21",$U$7:$U$130,"",$K$7:$K$130,"&lt;&gt;X")</f>
-        <v>4</v>
-      </c>
-      <c r="O135" s="50">
-        <f ca="1">COUNTIFS($I$7:$I$130,"&gt;21",$U$7:$U$130,"",$K$7:$K$130,"&lt;&gt;X")</f>
-        <v>5</v>
-      </c>
-      <c r="P135" s="124">
-        <f ca="1">Q135/$Q$133</f>
-        <v>0.37037037037037035</v>
-      </c>
-      <c r="Q135" s="125">
-        <f ca="1">COUNTIFS($I$7:$I$130,"&gt;=0",$P$7:$P$130,"",$K$7:$K$130,"&lt;&gt;X")</f>
-        <v>40</v>
-      </c>
-      <c r="R135" s="1" t="s">
-        <v>10</v>
-      </c>
+      <c r="H135" s="371" t="s">
+        <v>69</v>
+      </c>
+      <c r="I135" s="372"/>
+      <c r="J135" s="372"/>
+      <c r="K135" s="373"/>
+      <c r="L135" s="122">
+        <f t="shared" ref="L135:L137" ca="1" si="61">M135/$M$134</f>
+        <v>0.81395348837209303</v>
+      </c>
+      <c r="M135" s="123">
+        <f>COUNTIF($H$7:$H$131,"RFCS")</f>
+        <v>105</v>
+      </c>
+      <c r="N135" s="121">
+        <f ca="1">COUNTIFS($I$7:$I$131,"&lt;=21",$H$7:$H$131,"RFCS")</f>
+        <v>63</v>
+      </c>
+      <c r="O135" s="120">
+        <f ca="1">COUNTIFS($I$7:$I$131,"&gt;21",$H$7:$H$131,"RFCS")</f>
+        <v>41</v>
+      </c>
+      <c r="P135" s="122">
+        <f ca="1">Q135/$Q$134</f>
+        <v>0.62385321100917435</v>
+      </c>
+      <c r="Q135" s="123">
+        <f>COUNTIF($Q$7:$Q$131,"RBE") + COUNTIF($Q$7:$Q$131,"SUP")</f>
+        <v>68</v>
+      </c>
+      <c r="R135" s="1"/>
       <c r="S135" s="1"/>
       <c r="T135" s="140"/>
       <c r="U135" s="1"/>
@@ -39141,66 +39265,112 @@
       <c r="X135" s="11"/>
       <c r="Y135" s="11"/>
     </row>
-    <row r="136" spans="1:26" ht="16.5" thickBot="1">
-      <c r="C136" s="402" t="s">
+    <row r="136" spans="1:26">
+      <c r="C136" s="382"/>
+      <c r="D136" s="380"/>
+      <c r="E136" s="381"/>
+      <c r="F136" s="72"/>
+      <c r="G136" s="6"/>
+      <c r="H136" s="374" t="s">
+        <v>70</v>
+      </c>
+      <c r="I136" s="375"/>
+      <c r="J136" s="375"/>
+      <c r="K136" s="376"/>
+      <c r="L136" s="124">
+        <f t="shared" ca="1" si="61"/>
+        <v>7.7519379844961239E-2</v>
+      </c>
+      <c r="M136" s="125">
+        <f ca="1">SUM(N136:O136)</f>
+        <v>10</v>
+      </c>
+      <c r="N136" s="98">
+        <f ca="1">COUNTIFS($I$7:$I$131,"&lt;=21",$U$7:$U$131,"",$K$7:$K$131,"&lt;&gt;X")</f>
+        <v>5</v>
+      </c>
+      <c r="O136" s="50">
+        <f ca="1">COUNTIFS($I$7:$I$131,"&gt;21",$U$7:$U$131,"",$K$7:$K$131,"&lt;&gt;X")</f>
+        <v>5</v>
+      </c>
+      <c r="P136" s="124">
+        <f ca="1">Q136/$Q$134</f>
+        <v>0.37614678899082571</v>
+      </c>
+      <c r="Q136" s="125">
+        <f ca="1">COUNTIFS($I$7:$I$131,"&gt;=0",$P$7:$P$131,"",$K$7:$K$131,"&lt;&gt;X")</f>
+        <v>41</v>
+      </c>
+      <c r="R136" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="S136" s="1"/>
+      <c r="T136" s="140"/>
+      <c r="U136" s="1"/>
+      <c r="W136" s="11"/>
+      <c r="X136" s="11"/>
+      <c r="Y136" s="11"/>
+    </row>
+    <row r="137" spans="1:26" ht="16.5" thickBot="1">
+      <c r="C137" s="382" t="s">
         <v>75</v>
       </c>
-      <c r="D136" s="408" t="s">
+      <c r="D137" s="384" t="s">
         <v>76</v>
       </c>
-      <c r="E136" s="409"/>
-      <c r="H136" s="399" t="s">
+      <c r="E137" s="385"/>
+      <c r="H137" s="377" t="s">
         <v>71</v>
       </c>
-      <c r="I136" s="400"/>
-      <c r="J136" s="400"/>
-      <c r="K136" s="401"/>
-      <c r="L136" s="126">
-        <f t="shared" ca="1" si="60"/>
-        <v>0.109375</v>
-      </c>
-      <c r="M136" s="116">
-        <f>COUNTIFS($K$7:$K$130,"X")</f>
+      <c r="I137" s="378"/>
+      <c r="J137" s="378"/>
+      <c r="K137" s="379"/>
+      <c r="L137" s="126">
+        <f t="shared" ca="1" si="61"/>
+        <v>0.10852713178294573</v>
+      </c>
+      <c r="M137" s="116">
+        <f>COUNTIFS($K$7:$K$131,"X")</f>
         <v>14</v>
       </c>
-      <c r="N136" s="99"/>
-      <c r="O136" s="51"/>
-      <c r="P136" s="223"/>
-      <c r="Q136" s="224"/>
-    </row>
-    <row r="137" spans="1:26" ht="16.5" thickBot="1">
-      <c r="C137" s="403"/>
-      <c r="D137" s="410"/>
-      <c r="E137" s="411"/>
-    </row>
-    <row r="139" spans="1:26">
-      <c r="C139" s="381" t="s">
+      <c r="N137" s="99"/>
+      <c r="O137" s="51"/>
+      <c r="P137" s="223"/>
+      <c r="Q137" s="224"/>
+    </row>
+    <row r="138" spans="1:26" ht="16.5" thickBot="1">
+      <c r="C138" s="383"/>
+      <c r="D138" s="386"/>
+      <c r="E138" s="387"/>
+    </row>
+    <row r="140" spans="1:26">
+      <c r="C140" s="370" t="s">
         <v>41</v>
       </c>
-      <c r="D139" s="381"/>
-      <c r="E139" s="381"/>
-    </row>
-    <row r="140" spans="1:26">
-      <c r="C140" s="169" t="s">
-        <v>8</v>
-      </c>
-      <c r="D140" s="1" t="s">
-        <v>42</v>
-      </c>
+      <c r="D140" s="370"/>
+      <c r="E140" s="370"/>
     </row>
     <row r="141" spans="1:26">
       <c r="C141" s="169" t="s">
         <v>8</v>
       </c>
-      <c r="D141" s="127" t="s">
-        <v>43</v>
+      <c r="D141" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="142" spans="1:26">
       <c r="C142" s="169" t="s">
         <v>8</v>
       </c>
-      <c r="D142" s="1" t="s">
+      <c r="D142" s="127" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="143" spans="1:26">
+      <c r="C143" s="169" t="s">
+        <v>8</v>
+      </c>
+      <c r="D143" s="1" t="s">
         <v>44</v>
       </c>
     </row>
@@ -39212,21 +39382,21 @@
   </autoFilter>
   <mergeCells count="32">
     <mergeCell ref="B4:B5"/>
-    <mergeCell ref="P132:Q132"/>
+    <mergeCell ref="P133:Q133"/>
     <mergeCell ref="J4:J5"/>
-    <mergeCell ref="D132:E132"/>
-    <mergeCell ref="H132:M132"/>
-    <mergeCell ref="N132:O132"/>
-    <mergeCell ref="H133:I133"/>
-    <mergeCell ref="C139:E139"/>
-    <mergeCell ref="H134:K134"/>
+    <mergeCell ref="D133:E133"/>
+    <mergeCell ref="H133:M133"/>
+    <mergeCell ref="N133:O133"/>
+    <mergeCell ref="H134:I134"/>
+    <mergeCell ref="C140:E140"/>
     <mergeCell ref="H135:K135"/>
     <mergeCell ref="H136:K136"/>
-    <mergeCell ref="D133:E133"/>
-    <mergeCell ref="C134:C135"/>
-    <mergeCell ref="D134:E135"/>
-    <mergeCell ref="C136:C137"/>
-    <mergeCell ref="D136:E137"/>
+    <mergeCell ref="H137:K137"/>
+    <mergeCell ref="D134:E134"/>
+    <mergeCell ref="C135:C136"/>
+    <mergeCell ref="D135:E136"/>
+    <mergeCell ref="C137:C138"/>
+    <mergeCell ref="D137:E138"/>
     <mergeCell ref="Z4:Z5"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="D4:D5"/>
@@ -39245,7 +39415,7 @@
     <mergeCell ref="X4:Y4"/>
   </mergeCells>
   <phoneticPr fontId="71"/>
-  <conditionalFormatting sqref="A7:Z130">
+  <conditionalFormatting sqref="A7:Z131">
     <cfRule type="expression" dxfId="4" priority="1">
       <formula>$K7="X"</formula>
     </cfRule>
@@ -39390,9 +39560,9 @@
     <hyperlink ref="O43" r:id="rId125" xr:uid="{0E3F3A7F-DA9A-49F8-A93F-8337122FAE1A}"/>
     <hyperlink ref="N41" r:id="rId126" xr:uid="{3405D711-BDD4-4069-A376-D6B961D87010}"/>
     <hyperlink ref="N43" r:id="rId127" xr:uid="{525398A7-A7B1-41B1-88A2-7E7F9115541E}"/>
-    <hyperlink ref="C140" r:id="rId128" xr:uid="{F06CE902-4089-4B08-A7E9-420A16C9FF0E}"/>
-    <hyperlink ref="C141" r:id="rId129" xr:uid="{6D322F1B-B574-40E7-BED0-14ED893C19C5}"/>
-    <hyperlink ref="C142" r:id="rId130" xr:uid="{1845DEB0-969B-4FE7-B52A-52C25D3EC72E}"/>
+    <hyperlink ref="C141" r:id="rId128" xr:uid="{F06CE902-4089-4B08-A7E9-420A16C9FF0E}"/>
+    <hyperlink ref="C142" r:id="rId129" xr:uid="{6D322F1B-B574-40E7-BED0-14ED893C19C5}"/>
+    <hyperlink ref="C143" r:id="rId130" xr:uid="{1845DEB0-969B-4FE7-B52A-52C25D3EC72E}"/>
     <hyperlink ref="N42" r:id="rId131" xr:uid="{95D9F3CF-8EC0-4C96-9F49-34E6585C583B}"/>
     <hyperlink ref="L44" r:id="rId132" xr:uid="{255E79C1-4568-41F7-B71E-8301B034AA56}"/>
     <hyperlink ref="P8" r:id="rId133" xr:uid="{4339778F-2FA8-45DA-BD1F-0684B78D35ED}"/>
@@ -39739,9 +39909,10 @@
     <hyperlink ref="L126" r:id="rId474" xr:uid="{3EB8572D-FD0D-4865-AF14-84A4ECCCC02A}"/>
     <hyperlink ref="L127" r:id="rId475" xr:uid="{E41605CA-C2E5-494D-8E08-2F89092E4322}"/>
     <hyperlink ref="L128" r:id="rId476" xr:uid="{EEC0D82E-190C-4F0D-80DD-BE42DD4F1D56}"/>
+    <hyperlink ref="L129" r:id="rId477" xr:uid="{090DE60D-6895-4F41-A19F-68068AEBAA0A}"/>
   </hyperlinks>
   <pageMargins left="0.25" right="0.17" top="0.5" bottom="0.25" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="28" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId477"/>
+  <pageSetup paperSize="9" scale="28" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId478"/>
 </worksheet>
 </file>
 
@@ -39826,19 +39997,19 @@
       <c r="S3" s="281"/>
     </row>
     <row r="4" spans="1:25" ht="36" customHeight="1" thickBot="1">
-      <c r="A4" s="350" t="s">
+      <c r="A4" s="396" t="s">
         <v>123</v>
       </c>
-      <c r="B4" s="352" t="s">
+      <c r="B4" s="358" t="s">
         <v>45</v>
       </c>
-      <c r="C4" s="352" t="s">
+      <c r="C4" s="358" t="s">
         <v>95</v>
       </c>
-      <c r="D4" s="352" t="s">
+      <c r="D4" s="358" t="s">
         <v>46</v>
       </c>
-      <c r="E4" s="348" t="s">
+      <c r="E4" s="352" t="s">
         <v>4</v>
       </c>
       <c r="F4" s="449" t="s">
@@ -39867,12 +40038,12 @@
       <c r="S4" s="448"/>
     </row>
     <row r="5" spans="1:25" ht="78.75">
-      <c r="A5" s="351"/>
-      <c r="B5" s="353"/>
-      <c r="C5" s="353"/>
-      <c r="D5" s="353"/>
-      <c r="E5" s="354"/>
-      <c r="F5" s="356"/>
+      <c r="A5" s="397"/>
+      <c r="B5" s="359"/>
+      <c r="C5" s="359"/>
+      <c r="D5" s="359"/>
+      <c r="E5" s="353"/>
+      <c r="F5" s="399"/>
       <c r="G5" s="283" t="s">
         <v>56</v>
       </c>
@@ -39954,7 +40125,7 @@
         <v>MAS</v>
       </c>
       <c r="D7" s="282" t="str" cm="1">
-        <f t="array" ref="D7:D24">_xlfn._xlws.FILTER(RFA!$E$5:$E$4577, RFA!$AI$5:$AI$4577="YES","")</f>
+        <f t="array" ref="D7:D24">_xlfn._xlws.FILTER(RFA!$E$5:$E$4578, RFA!$AI$5:$AI$4578="YES","")</f>
         <v>LTIA-5.10-VIETUR-70000-RFA-MAS-0088A</v>
       </c>
       <c r="E7" s="303" t="str" cm="1">
@@ -40060,7 +40231,7 @@
 _xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(D7),RFA!$E:$E,RFA!$AD:$AD,""),
 IF(_xlpm.x=0,"",_xlpm.x)
 )</f>
-        <v>847</v>
+        <v>851</v>
       </c>
     </row>
     <row r="8" spans="1:25" ht="45">
@@ -40121,7 +40292,7 @@
       </c>
       <c r="S8" s="279">
         <f ca="1"/>
-        <v>812</v>
+        <v>816</v>
       </c>
       <c r="Y8" t="s">
         <v>125</v>
@@ -40186,7 +40357,7 @@
       </c>
       <c r="S9" s="279">
         <f ca="1"/>
-        <v>510</v>
+        <v>514</v>
       </c>
     </row>
     <row r="10" spans="1:25" ht="45">
@@ -40247,7 +40418,7 @@
       </c>
       <c r="S10" s="279">
         <f ca="1"/>
-        <v>391</v>
+        <v>395</v>
       </c>
     </row>
     <row r="11" spans="1:25" ht="75">
@@ -40308,7 +40479,7 @@
       </c>
       <c r="S11" s="279">
         <f ca="1"/>
-        <v>331</v>
+        <v>335</v>
       </c>
     </row>
     <row r="12" spans="1:25" ht="45">
@@ -40369,7 +40540,7 @@
       </c>
       <c r="S12" s="279">
         <f ca="1"/>
-        <v>308</v>
+        <v>312</v>
       </c>
     </row>
     <row r="13" spans="1:25" ht="45">
@@ -40430,7 +40601,7 @@
       </c>
       <c r="S13" s="279">
         <f ca="1"/>
-        <v>303</v>
+        <v>307</v>
       </c>
     </row>
     <row r="14" spans="1:25" ht="45">
@@ -40491,7 +40662,7 @@
       </c>
       <c r="S14" s="279">
         <f ca="1"/>
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="15" spans="1:25" ht="60">
@@ -40808,7 +40979,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="302" t="str">
-        <v/>
+        <v>DNE</v>
       </c>
       <c r="C20" s="13" t="str">
         <v>OTH</v>
@@ -40852,8 +41023,8 @@
       <c r="P20" s="264">
         <v>46226</v>
       </c>
-      <c r="Q20" s="270" t="str">
-        <v/>
+      <c r="Q20" s="270">
+        <v>46312</v>
       </c>
       <c r="R20" s="13" t="str">
         <f ca="1"/>
@@ -41205,13 +41376,13 @@
       <c r="R3" s="281"/>
     </row>
     <row r="4" spans="1:18" ht="16.5" thickBot="1">
-      <c r="A4" s="350" t="s">
+      <c r="A4" s="396" t="s">
         <v>123</v>
       </c>
-      <c r="B4" s="352" t="s">
+      <c r="B4" s="358" t="s">
         <v>45</v>
       </c>
-      <c r="C4" s="352" t="s">
+      <c r="C4" s="358" t="s">
         <v>46</v>
       </c>
       <c r="D4" s="363" t="s">
@@ -41243,11 +41414,11 @@
       <c r="R4" s="448"/>
     </row>
     <row r="5" spans="1:18" ht="78.75">
-      <c r="A5" s="351"/>
-      <c r="B5" s="353"/>
-      <c r="C5" s="353"/>
-      <c r="D5" s="431"/>
-      <c r="E5" s="354"/>
+      <c r="A5" s="397"/>
+      <c r="B5" s="359"/>
+      <c r="C5" s="359"/>
+      <c r="D5" s="357"/>
+      <c r="E5" s="353"/>
       <c r="F5" s="283" t="s">
         <v>56</v>
       </c>
@@ -41383,7 +41554,7 @@
       </c>
       <c r="R7" s="279" cm="1">
         <f t="array" aca="1" ref="R7:R18" ca="1">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$AC:$AC,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
-        <v>547</v>
+        <v>551</v>
       </c>
     </row>
     <row r="8" spans="1:18" ht="30">
@@ -41441,7 +41612,7 @@
       </c>
       <c r="R8" s="279">
         <f ca="1"/>
-        <v>457</v>
+        <v>461</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="45">
@@ -41499,7 +41670,7 @@
       </c>
       <c r="R9" s="279">
         <f ca="1"/>
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="105">
@@ -41558,7 +41729,7 @@
       </c>
       <c r="R10" s="279">
         <f ca="1"/>
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="45">
@@ -41616,7 +41787,7 @@
       </c>
       <c r="R11" s="279">
         <f ca="1"/>
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="12" spans="1:18" ht="45">
@@ -41675,7 +41846,7 @@
       </c>
       <c r="R12" s="279">
         <f ca="1"/>
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="75">
@@ -41733,7 +41904,7 @@
       </c>
       <c r="R13" s="279">
         <f ca="1"/>
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="14" spans="1:18" ht="60">
@@ -41791,7 +41962,7 @@
       </c>
       <c r="R14" s="279">
         <f ca="1"/>
-        <v>273</v>
+        <v>277</v>
       </c>
     </row>
     <row r="15" spans="1:18" ht="45">
@@ -41849,7 +42020,7 @@
       </c>
       <c r="R15" s="279">
         <f ca="1"/>
-        <v>324</v>
+        <v>328</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="45">
@@ -41907,7 +42078,7 @@
       </c>
       <c r="R16" s="279">
         <f ca="1"/>
-        <v>304</v>
+        <v>308</v>
       </c>
     </row>
     <row r="17" spans="1:18" ht="60">
@@ -42023,7 +42194,7 @@
       </c>
       <c r="R18" s="279">
         <f ca="1"/>
-        <v>304</v>
+        <v>308</v>
       </c>
     </row>
   </sheetData>
@@ -42081,19 +42252,19 @@
     <row r="3" spans="1:4" ht="15.75">
       <c r="A3" s="319">
         <f ca="1">MAX('Need ReSub (RFA)'!S7:S76)</f>
-        <v>847</v>
+        <v>851</v>
       </c>
       <c r="B3" s="319">
         <f ca="1">AVERAGEIF('Need ReSub (RFA)'!S7:S76,"&lt;&gt;0")</f>
-        <v>455.25</v>
+        <v>459.25</v>
       </c>
       <c r="C3" s="319">
         <f ca="1">MAX(_xlfn.ANCHORARRAY('Need ReSub (RFA-SDS)'!R7))</f>
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="D3" s="319">
         <f ca="1">AVERAGEIF(_xlfn.ANCHORARRAY('Need ReSub (RFA-SDS)'!R7),"&lt;&gt;0")</f>
-        <v>338.66666666666669</v>
+        <v>342.33333333333331</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -42102,10 +42273,10 @@
 Furthermore, the RFA (SDS) is as follows:
 Avarage :  " &amp; ROUND($D$3,0) &amp; " days
 Maimum :  " &amp; ROUND($C$3,0) &amp; " days"</f>
-        <v>In the RFA process, the average number of days elapsed since responding to an unapproved RFA was 455 days, with a maximum of 847 days, indicating that delays in the RFA approval process are contributing to delays in construction work.
+        <v>In the RFA process, the average number of days elapsed since responding to an unapproved RFA was 459 days, with a maximum of 851 days, indicating that delays in the RFA approval process are contributing to delays in construction work.
 Furthermore, the RFA (SDS) is as follows:
-Avarage :  339 days
-Maimum :  547 days</v>
+Avarage :  342 days
+Maimum :  551 days</v>
       </c>
       <c r="B5" s="452"/>
     </row>

--- a/ICT-RFA-RFI-lists-New.xlsx
+++ b/ICT-RFA-RFI-lists-New.xlsx
@@ -9,9 +9,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project Airport\LTIA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{550F1BD5-7A77-46C2-9DF2-894155E4FCF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79BA979A-7609-4D27-935F-A679DD1F78F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="506" xr2:uid="{CCA8147E-0981-4321-B87F-440A52C0DA59}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="506" activeTab="2" xr2:uid="{CCA8147E-0981-4321-B87F-440A52C0DA59}"/>
   </bookViews>
   <sheets>
     <sheet name="RFA" sheetId="1" r:id="rId1"/>
@@ -78,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3487" uniqueCount="1097">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3493" uniqueCount="1097">
   <si>
     <t>TT</t>
   </si>
@@ -5064,9 +5064,6 @@
 10/14/2026: Đã ký A</t>
   </si>
   <si>
-    <t>101/14/2026: Đã comment</t>
-  </si>
-  <si>
     <t>10/14/2026: Đã comment và gửi CNC
 10/14/2026: Đã ký RFCS</t>
   </si>
@@ -5144,6 +5141,11 @@
   </si>
   <si>
     <t>Đề nghị phê duyệt kiến trúc mạng và quy hoạch IP-VLAN</t>
+  </si>
+  <si>
+    <t>101/14/2026: Đã comment
+10/15/2026 Đã gửi CNC
+10/15/2026: Đã ký RFCS</t>
   </si>
 </sst>
 </file>
@@ -7580,23 +7582,272 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="51" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="52" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="55" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="55" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="53" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="47" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="45" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="58" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -7610,259 +7861,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="45" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="53" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="47" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="51" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="52" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="55" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="55" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -8526,92 +8528,92 @@
       <c r="AE3" s="159"/>
     </row>
     <row r="4" spans="1:35" s="5" customFormat="1" ht="36" customHeight="1" thickBot="1">
-      <c r="A4" s="396" t="s">
+      <c r="A4" s="408" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="350" t="s">
+      <c r="B4" s="348" t="s">
         <v>515</v>
       </c>
-      <c r="C4" s="364" t="s">
+      <c r="C4" s="414" t="s">
         <v>45</v>
       </c>
-      <c r="D4" s="358" t="s">
+      <c r="D4" s="366" t="s">
         <v>95</v>
       </c>
-      <c r="E4" s="352" t="s">
+      <c r="E4" s="369" t="s">
         <v>46</v>
       </c>
-      <c r="F4" s="400" t="s">
+      <c r="F4" s="412" t="s">
         <v>47</v>
       </c>
-      <c r="G4" s="352" t="s">
+      <c r="G4" s="369" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="398" t="s">
+      <c r="H4" s="410" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="358" t="s">
+      <c r="I4" s="366" t="s">
         <v>48</v>
       </c>
-      <c r="J4" s="358" t="s">
+      <c r="J4" s="366" t="s">
         <v>49</v>
       </c>
-      <c r="K4" s="352" t="s">
+      <c r="K4" s="369" t="s">
         <v>78</v>
       </c>
-      <c r="L4" s="358" t="s">
+      <c r="L4" s="366" t="s">
         <v>80</v>
       </c>
-      <c r="M4" s="363" t="s">
+      <c r="M4" s="364" t="s">
         <v>53</v>
       </c>
-      <c r="N4" s="348"/>
-      <c r="O4" s="363" t="s">
+      <c r="N4" s="365"/>
+      <c r="O4" s="364" t="s">
         <v>55</v>
       </c>
-      <c r="P4" s="348"/>
-      <c r="Q4" s="362" t="s">
+      <c r="P4" s="365"/>
+      <c r="Q4" s="368" t="s">
         <v>72</v>
       </c>
-      <c r="R4" s="348"/>
-      <c r="S4" s="363" t="s">
+      <c r="R4" s="365"/>
+      <c r="S4" s="364" t="s">
         <v>53</v>
       </c>
-      <c r="T4" s="363"/>
-      <c r="U4" s="348"/>
-      <c r="V4" s="362" t="s">
+      <c r="T4" s="364"/>
+      <c r="U4" s="365"/>
+      <c r="V4" s="368" t="s">
         <v>55</v>
       </c>
-      <c r="W4" s="363"/>
-      <c r="X4" s="348"/>
-      <c r="Y4" s="366" t="s">
+      <c r="W4" s="364"/>
+      <c r="X4" s="365"/>
+      <c r="Y4" s="371" t="s">
         <v>72</v>
       </c>
-      <c r="Z4" s="367"/>
-      <c r="AA4" s="429" t="s">
+      <c r="Z4" s="372"/>
+      <c r="AA4" s="359" t="s">
         <v>112</v>
       </c>
-      <c r="AB4" s="430"/>
-      <c r="AC4" s="430"/>
-      <c r="AD4" s="431"/>
-      <c r="AE4" s="352" t="s">
+      <c r="AB4" s="360"/>
+      <c r="AC4" s="360"/>
+      <c r="AD4" s="361"/>
+      <c r="AE4" s="369" t="s">
         <v>79</v>
       </c>
       <c r="AG4" s="236"/>
     </row>
     <row r="5" spans="1:35" ht="78.75">
-      <c r="A5" s="397"/>
-      <c r="B5" s="351"/>
-      <c r="C5" s="365"/>
-      <c r="D5" s="359"/>
-      <c r="E5" s="353"/>
-      <c r="F5" s="401"/>
-      <c r="G5" s="353"/>
-      <c r="H5" s="399"/>
-      <c r="I5" s="359"/>
-      <c r="J5" s="359"/>
-      <c r="K5" s="353"/>
-      <c r="L5" s="359"/>
+      <c r="A5" s="409"/>
+      <c r="B5" s="349"/>
+      <c r="C5" s="415"/>
+      <c r="D5" s="367"/>
+      <c r="E5" s="370"/>
+      <c r="F5" s="413"/>
+      <c r="G5" s="370"/>
+      <c r="H5" s="411"/>
+      <c r="I5" s="367"/>
+      <c r="J5" s="367"/>
+      <c r="K5" s="370"/>
+      <c r="L5" s="367"/>
       <c r="M5" s="79" t="s">
         <v>52</v>
       </c>
@@ -8666,14 +8668,14 @@
       <c r="AD5" s="336" t="s">
         <v>118</v>
       </c>
-      <c r="AE5" s="349"/>
-      <c r="AG5" s="352" t="s">
+      <c r="AE5" s="416"/>
+      <c r="AG5" s="369" t="s">
         <v>119</v>
       </c>
-      <c r="AH5" s="352" t="s">
+      <c r="AH5" s="369" t="s">
         <v>120</v>
       </c>
-      <c r="AI5" s="352" t="s">
+      <c r="AI5" s="369" t="s">
         <v>121</v>
       </c>
     </row>
@@ -8709,9 +8711,9 @@
       <c r="AC6" s="86"/>
       <c r="AD6" s="86"/>
       <c r="AE6" s="74"/>
-      <c r="AG6" s="395"/>
-      <c r="AH6" s="395"/>
-      <c r="AI6" s="395"/>
+      <c r="AG6" s="407"/>
+      <c r="AH6" s="407"/>
+      <c r="AI6" s="407"/>
     </row>
     <row r="7" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A7" s="33">
@@ -22559,7 +22561,7 @@
       <c r="AC131" s="229"/>
       <c r="AD131" s="337"/>
       <c r="AE131" s="92" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="AG131" s="238" t="str">
         <f t="shared" si="75"/>
@@ -22879,11 +22881,11 @@
         <v>3</v>
       </c>
       <c r="J135" s="164">
-        <f t="shared" ca="1" si="30"/>
+        <f t="shared" si="30"/>
         <v>13</v>
       </c>
       <c r="K135" s="47">
-        <f t="shared" ca="1" si="31"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="L135" s="164"/>
@@ -22891,7 +22893,9 @@
         <v>8</v>
       </c>
       <c r="N135" s="41"/>
-      <c r="O135" s="40"/>
+      <c r="O135" s="40" t="s">
+        <v>8</v>
+      </c>
       <c r="P135" s="41"/>
       <c r="Q135" s="40"/>
       <c r="R135" s="155"/>
@@ -22904,8 +22908,12 @@
       <c r="U135" s="188">
         <v>46301</v>
       </c>
-      <c r="V135" s="29"/>
-      <c r="W135" s="188"/>
+      <c r="V135" s="29">
+        <v>46311</v>
+      </c>
+      <c r="W135" s="188">
+        <v>46314</v>
+      </c>
       <c r="X135" s="235" t="s">
         <v>240</v>
       </c>
@@ -22957,17 +22965,17 @@
         <v>32</v>
       </c>
       <c r="E136" s="25" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="F136" s="174">
         <f t="shared" si="29"/>
         <v>46330</v>
       </c>
       <c r="G136" s="31" t="s">
+        <v>1074</v>
+      </c>
+      <c r="H136" s="21" t="s">
         <v>1075</v>
-      </c>
-      <c r="H136" s="21" t="s">
-        <v>1076</v>
       </c>
       <c r="I136" s="138"/>
       <c r="J136" s="164">
@@ -23045,17 +23053,17 @@
         <v>32</v>
       </c>
       <c r="E137" s="25" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="F137" s="174">
         <f t="shared" si="29"/>
         <v>46330</v>
       </c>
       <c r="G137" s="31" t="s">
+        <v>1077</v>
+      </c>
+      <c r="H137" s="21" t="s">
         <v>1078</v>
-      </c>
-      <c r="H137" s="21" t="s">
-        <v>1079</v>
       </c>
       <c r="I137" s="138"/>
       <c r="J137" s="164">
@@ -23127,23 +23135,23 @@
         <v>5.11</v>
       </c>
       <c r="C138" s="164" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="D138" s="137" t="s">
         <v>32</v>
       </c>
       <c r="E138" s="25" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="F138" s="174">
         <f t="shared" si="29"/>
         <v>46330</v>
       </c>
       <c r="G138" s="31" t="s">
+        <v>1080</v>
+      </c>
+      <c r="H138" s="21" t="s">
         <v>1081</v>
-      </c>
-      <c r="H138" s="21" t="s">
-        <v>1082</v>
       </c>
       <c r="I138" s="138"/>
       <c r="J138" s="164">
@@ -23215,23 +23223,23 @@
         <v>5.11</v>
       </c>
       <c r="C139" s="164" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="D139" s="137" t="s">
         <v>32</v>
       </c>
       <c r="E139" s="25" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="F139" s="174">
         <f t="shared" si="29"/>
         <v>46330</v>
       </c>
       <c r="G139" s="31" t="s">
+        <v>1084</v>
+      </c>
+      <c r="H139" s="21" t="s">
         <v>1085</v>
-      </c>
-      <c r="H139" s="21" t="s">
-        <v>1086</v>
       </c>
       <c r="I139" s="138"/>
       <c r="J139" s="164">
@@ -23309,17 +23317,17 @@
         <v>32</v>
       </c>
       <c r="E140" s="25" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="F140" s="174">
         <f t="shared" si="29"/>
         <v>46331</v>
       </c>
       <c r="G140" s="31" t="s">
+        <v>1088</v>
+      </c>
+      <c r="H140" s="21" t="s">
         <v>1089</v>
-      </c>
-      <c r="H140" s="21" t="s">
-        <v>1090</v>
       </c>
       <c r="I140" s="138"/>
       <c r="J140" s="164">
@@ -23397,17 +23405,17 @@
         <v>28</v>
       </c>
       <c r="E141" s="25" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="F141" s="174">
         <f t="shared" si="29"/>
         <v>46333</v>
       </c>
       <c r="G141" s="31" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H141" s="21" t="s">
         <v>1095</v>
-      </c>
-      <c r="H141" s="21" t="s">
-        <v>1096</v>
       </c>
       <c r="I141" s="138"/>
       <c r="J141" s="164">
@@ -23560,29 +23568,29 @@
       <c r="C145" s="166" t="s">
         <v>20</v>
       </c>
-      <c r="D145" s="416" t="s">
+      <c r="D145" s="376" t="s">
         <v>21</v>
       </c>
-      <c r="E145" s="416"/>
-      <c r="F145" s="417"/>
+      <c r="E145" s="376"/>
+      <c r="F145" s="377"/>
       <c r="G145" s="46"/>
       <c r="H145" s="68"/>
-      <c r="I145" s="392" t="s">
+      <c r="I145" s="356" t="s">
         <v>14</v>
       </c>
-      <c r="J145" s="393"/>
-      <c r="K145" s="393"/>
-      <c r="L145" s="393"/>
-      <c r="M145" s="393"/>
-      <c r="N145" s="394"/>
-      <c r="O145" s="388" t="s">
+      <c r="J145" s="357"/>
+      <c r="K145" s="357"/>
+      <c r="L145" s="357"/>
+      <c r="M145" s="357"/>
+      <c r="N145" s="358"/>
+      <c r="O145" s="362" t="s">
         <v>7</v>
       </c>
-      <c r="P145" s="389"/>
-      <c r="Q145" s="388" t="s">
+      <c r="P145" s="363"/>
+      <c r="Q145" s="362" t="s">
         <v>109</v>
       </c>
-      <c r="R145" s="389"/>
+      <c r="R145" s="363"/>
       <c r="S145" s="1"/>
       <c r="T145" s="1"/>
       <c r="U145" s="140"/>
@@ -23604,26 +23612,26 @@
       <c r="C146" s="167" t="s">
         <v>109</v>
       </c>
-      <c r="D146" s="427" t="s">
+      <c r="D146" s="354" t="s">
         <v>111</v>
       </c>
-      <c r="E146" s="427"/>
-      <c r="F146" s="428"/>
+      <c r="E146" s="354"/>
+      <c r="F146" s="355"/>
       <c r="G146" s="46"/>
       <c r="H146" s="46"/>
-      <c r="I146" s="392" t="s">
+      <c r="I146" s="356" t="s">
         <v>19</v>
       </c>
-      <c r="J146" s="393"/>
-      <c r="K146" s="393"/>
-      <c r="L146" s="394"/>
+      <c r="J146" s="357"/>
+      <c r="K146" s="357"/>
+      <c r="L146" s="358"/>
       <c r="M146" s="105">
         <f t="shared" ref="M146:M151" ca="1" si="89">N146/$N$146</f>
         <v>1</v>
       </c>
       <c r="N146" s="106">
         <f ca="1">SUM($N$147:$N$151)</f>
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="O146" s="102" t="s">
         <v>15</v>
@@ -23660,22 +23668,22 @@
       <c r="C147" s="167" t="s">
         <v>22</v>
       </c>
-      <c r="D147" s="427" t="s">
+      <c r="D147" s="354" t="s">
         <v>23</v>
       </c>
-      <c r="E147" s="427"/>
-      <c r="F147" s="428"/>
+      <c r="E147" s="354"/>
+      <c r="F147" s="355"/>
       <c r="G147" s="70"/>
       <c r="H147" s="6"/>
-      <c r="I147" s="418" t="s">
+      <c r="I147" s="379" t="s">
         <v>66</v>
       </c>
-      <c r="J147" s="419"/>
-      <c r="K147" s="419"/>
-      <c r="L147" s="420"/>
+      <c r="J147" s="380"/>
+      <c r="K147" s="380"/>
+      <c r="L147" s="381"/>
       <c r="M147" s="107">
         <f t="shared" ca="1" si="89"/>
-        <v>0.48936170212765956</v>
+        <v>0.49285714285714288</v>
       </c>
       <c r="N147" s="108">
         <f>COUNTIF($I$7:$I$143,"A")</f>
@@ -23718,21 +23726,21 @@
       <c r="C148" s="167" t="s">
         <v>24</v>
       </c>
-      <c r="D148" s="427" t="s">
+      <c r="D148" s="354" t="s">
         <v>25</v>
       </c>
-      <c r="E148" s="427"/>
-      <c r="F148" s="428"/>
+      <c r="E148" s="354"/>
+      <c r="F148" s="355"/>
       <c r="H148" s="6"/>
-      <c r="I148" s="421" t="s">
+      <c r="I148" s="382" t="s">
         <v>67</v>
       </c>
-      <c r="J148" s="422"/>
-      <c r="K148" s="422"/>
-      <c r="L148" s="423"/>
+      <c r="J148" s="383"/>
+      <c r="K148" s="383"/>
+      <c r="L148" s="384"/>
       <c r="M148" s="109">
         <f t="shared" ca="1" si="89"/>
-        <v>9.9290780141843976E-2</v>
+        <v>0.1</v>
       </c>
       <c r="N148" s="110">
         <f>COUNTIF($I$7:$I$143,"B")</f>
@@ -23775,22 +23783,22 @@
       <c r="C149" s="167" t="s">
         <v>26</v>
       </c>
-      <c r="D149" s="427" t="s">
+      <c r="D149" s="354" t="s">
         <v>27</v>
       </c>
-      <c r="E149" s="427"/>
-      <c r="F149" s="428"/>
+      <c r="E149" s="354"/>
+      <c r="F149" s="355"/>
       <c r="G149" s="71"/>
       <c r="H149" s="6"/>
-      <c r="I149" s="424" t="s">
+      <c r="I149" s="385" t="s">
         <v>68</v>
       </c>
-      <c r="J149" s="425"/>
-      <c r="K149" s="425"/>
-      <c r="L149" s="426"/>
+      <c r="J149" s="386"/>
+      <c r="K149" s="386"/>
+      <c r="L149" s="387"/>
       <c r="M149" s="111">
         <f t="shared" ca="1" si="89"/>
-        <v>0.19148936170212766</v>
+        <v>0.19285714285714287</v>
       </c>
       <c r="N149" s="112">
         <f>COUNTIF($I$7:$I$143,"C")</f>
@@ -23833,29 +23841,29 @@
       <c r="C150" s="168" t="s">
         <v>28</v>
       </c>
-      <c r="D150" s="427" t="s">
+      <c r="D150" s="354" t="s">
         <v>29</v>
       </c>
-      <c r="E150" s="427"/>
-      <c r="F150" s="428"/>
+      <c r="E150" s="354"/>
+      <c r="F150" s="355"/>
       <c r="G150" s="72"/>
-      <c r="I150" s="374" t="s">
+      <c r="I150" s="388" t="s">
         <v>70</v>
       </c>
-      <c r="J150" s="375"/>
-      <c r="K150" s="375"/>
-      <c r="L150" s="376"/>
+      <c r="J150" s="389"/>
+      <c r="K150" s="389"/>
+      <c r="L150" s="390"/>
       <c r="M150" s="114">
         <f t="shared" ca="1" si="89"/>
-        <v>0.11347517730496454</v>
+        <v>0.10714285714285714</v>
       </c>
       <c r="N150" s="115">
         <f ca="1">SUM(O150:P150)</f>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O150" s="98">
         <f ca="1">COUNTIFS($J$7:$J$143,"&lt;=21",$V$7:$V$143,"",$L$7:$L$143,"&lt;&gt;X")</f>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="P150" s="50">
         <f ca="1">COUNTIFS($J$7:$J$143,"&gt;21",$V$7:$V$143,"",$L$7:$L$143,"&lt;&gt;X")</f>
@@ -23892,21 +23900,21 @@
       <c r="C151" s="168" t="s">
         <v>30</v>
       </c>
-      <c r="D151" s="427" t="s">
+      <c r="D151" s="354" t="s">
         <v>31</v>
       </c>
-      <c r="E151" s="427"/>
-      <c r="F151" s="428"/>
+      <c r="E151" s="354"/>
+      <c r="F151" s="355"/>
       <c r="H151" s="6"/>
-      <c r="I151" s="377" t="s">
+      <c r="I151" s="391" t="s">
         <v>71</v>
       </c>
-      <c r="J151" s="378"/>
-      <c r="K151" s="378"/>
-      <c r="L151" s="379"/>
+      <c r="J151" s="392"/>
+      <c r="K151" s="392"/>
+      <c r="L151" s="393"/>
       <c r="M151" s="113">
         <f t="shared" ca="1" si="89"/>
-        <v>0.10638297872340426</v>
+        <v>0.10714285714285714</v>
       </c>
       <c r="N151" s="97">
         <f>COUNTIFS($L$7:$L$143,"X")</f>
@@ -23923,11 +23931,11 @@
       <c r="C152" s="168" t="s">
         <v>32</v>
       </c>
-      <c r="D152" s="427" t="s">
+      <c r="D152" s="354" t="s">
         <v>33</v>
       </c>
-      <c r="E152" s="427"/>
-      <c r="F152" s="428"/>
+      <c r="E152" s="354"/>
+      <c r="F152" s="355"/>
       <c r="H152" s="1" t="s">
         <v>11</v>
       </c>
@@ -23936,11 +23944,11 @@
       <c r="C153" s="167" t="s">
         <v>34</v>
       </c>
-      <c r="D153" s="427" t="s">
+      <c r="D153" s="354" t="s">
         <v>35</v>
       </c>
-      <c r="E153" s="427"/>
-      <c r="F153" s="428"/>
+      <c r="E153" s="354"/>
+      <c r="F153" s="355"/>
       <c r="H153" s="13"/>
       <c r="I153" s="141"/>
       <c r="J153" s="141"/>
@@ -23968,14 +23976,14 @@
       <c r="AI153" s="1"/>
     </row>
     <row r="154" spans="1:35">
-      <c r="C154" s="382" t="s">
+      <c r="C154" s="394" t="s">
         <v>75</v>
       </c>
-      <c r="D154" s="384" t="s">
+      <c r="D154" s="350" t="s">
         <v>76</v>
       </c>
-      <c r="E154" s="384"/>
-      <c r="F154" s="385"/>
+      <c r="E154" s="350"/>
+      <c r="F154" s="351"/>
       <c r="H154" s="13"/>
       <c r="J154" s="141"/>
       <c r="K154" s="13"/>
@@ -24002,10 +24010,10 @@
       <c r="AI154" s="1"/>
     </row>
     <row r="155" spans="1:35" ht="16.5" thickBot="1">
-      <c r="C155" s="383"/>
-      <c r="D155" s="386"/>
-      <c r="E155" s="386"/>
-      <c r="F155" s="387"/>
+      <c r="C155" s="395"/>
+      <c r="D155" s="352"/>
+      <c r="E155" s="352"/>
+      <c r="F155" s="353"/>
       <c r="H155" s="13"/>
       <c r="I155" s="141"/>
       <c r="J155" s="141"/>
@@ -24060,12 +24068,12 @@
       <c r="AI156" s="1"/>
     </row>
     <row r="157" spans="1:35">
-      <c r="C157" s="370" t="s">
+      <c r="C157" s="378" t="s">
         <v>41</v>
       </c>
-      <c r="D157" s="370"/>
-      <c r="E157" s="370"/>
-      <c r="F157" s="370"/>
+      <c r="D157" s="378"/>
+      <c r="E157" s="378"/>
+      <c r="F157" s="378"/>
       <c r="H157" s="13"/>
       <c r="I157" s="141"/>
       <c r="J157" s="141"/>
@@ -24096,11 +24104,11 @@
       <c r="C158" s="169" t="s">
         <v>8</v>
       </c>
-      <c r="D158" s="404" t="s">
+      <c r="D158" s="396" t="s">
         <v>91</v>
       </c>
-      <c r="E158" s="404"/>
-      <c r="F158" s="404"/>
+      <c r="E158" s="396"/>
+      <c r="F158" s="396"/>
       <c r="H158" s="13"/>
       <c r="I158" s="141"/>
       <c r="J158" s="141"/>
@@ -24131,11 +24139,11 @@
       <c r="C159" s="169" t="s">
         <v>8</v>
       </c>
-      <c r="D159" s="404" t="s">
+      <c r="D159" s="396" t="s">
         <v>92</v>
       </c>
-      <c r="E159" s="404"/>
-      <c r="F159" s="404"/>
+      <c r="E159" s="396"/>
+      <c r="F159" s="396"/>
       <c r="H159" s="13"/>
       <c r="I159" s="141"/>
       <c r="J159" s="141"/>
@@ -24166,11 +24174,11 @@
       <c r="C160" s="169" t="s">
         <v>8</v>
       </c>
-      <c r="D160" s="404" t="s">
+      <c r="D160" s="396" t="s">
         <v>93</v>
       </c>
-      <c r="E160" s="404"/>
-      <c r="F160" s="404"/>
+      <c r="E160" s="396"/>
+      <c r="F160" s="396"/>
       <c r="H160" s="13"/>
       <c r="I160" s="141"/>
       <c r="J160" s="141"/>
@@ -24225,12 +24233,12 @@
       <c r="AI161" s="1"/>
     </row>
     <row r="162" spans="3:35" ht="16.5" thickBot="1">
-      <c r="C162" s="408" t="s">
+      <c r="C162" s="402" t="s">
         <v>96</v>
       </c>
-      <c r="D162" s="409"/>
-      <c r="E162" s="409"/>
-      <c r="F162" s="410"/>
+      <c r="D162" s="403"/>
+      <c r="E162" s="403"/>
+      <c r="F162" s="404"/>
       <c r="H162" s="13"/>
       <c r="I162" s="141"/>
       <c r="J162" s="141"/>
@@ -24261,11 +24269,11 @@
       <c r="C163" s="212" t="s">
         <v>81</v>
       </c>
-      <c r="D163" s="411" t="s">
+      <c r="D163" s="405" t="s">
         <v>97</v>
       </c>
-      <c r="E163" s="411"/>
-      <c r="F163" s="412"/>
+      <c r="E163" s="405"/>
+      <c r="F163" s="406"/>
       <c r="H163" s="13"/>
       <c r="I163" s="141"/>
       <c r="J163" s="141"/>
@@ -24296,101 +24304,101 @@
       <c r="C164" s="213" t="s">
         <v>82</v>
       </c>
-      <c r="D164" s="402" t="s">
+      <c r="D164" s="397" t="s">
         <v>98</v>
       </c>
-      <c r="E164" s="402"/>
-      <c r="F164" s="403"/>
+      <c r="E164" s="397"/>
+      <c r="F164" s="398"/>
     </row>
     <row r="165" spans="3:35">
       <c r="C165" s="213" t="s">
         <v>83</v>
       </c>
-      <c r="D165" s="402" t="s">
+      <c r="D165" s="397" t="s">
         <v>99</v>
       </c>
-      <c r="E165" s="402"/>
-      <c r="F165" s="403"/>
+      <c r="E165" s="397"/>
+      <c r="F165" s="398"/>
     </row>
     <row r="166" spans="3:35">
       <c r="C166" s="214" t="s">
         <v>84</v>
       </c>
-      <c r="D166" s="402" t="s">
+      <c r="D166" s="397" t="s">
         <v>100</v>
       </c>
-      <c r="E166" s="402"/>
-      <c r="F166" s="403"/>
+      <c r="E166" s="397"/>
+      <c r="F166" s="398"/>
     </row>
     <row r="167" spans="3:35">
       <c r="C167" s="214" t="s">
         <v>85</v>
       </c>
-      <c r="D167" s="402" t="s">
+      <c r="D167" s="397" t="s">
         <v>101</v>
       </c>
-      <c r="E167" s="402"/>
-      <c r="F167" s="403"/>
+      <c r="E167" s="397"/>
+      <c r="F167" s="398"/>
     </row>
     <row r="168" spans="3:35" ht="18.75">
       <c r="C168" s="214" t="s">
         <v>86</v>
       </c>
-      <c r="D168" s="402" t="s">
+      <c r="D168" s="397" t="s">
         <v>102</v>
       </c>
-      <c r="E168" s="402"/>
-      <c r="F168" s="403"/>
+      <c r="E168" s="397"/>
+      <c r="F168" s="398"/>
     </row>
     <row r="169" spans="3:35" ht="18.75">
       <c r="C169" s="213" t="s">
         <v>87</v>
       </c>
-      <c r="D169" s="402" t="s">
+      <c r="D169" s="397" t="s">
         <v>103</v>
       </c>
-      <c r="E169" s="402"/>
-      <c r="F169" s="403"/>
+      <c r="E169" s="397"/>
+      <c r="F169" s="398"/>
     </row>
     <row r="170" spans="3:35">
       <c r="C170" s="215" t="s">
         <v>88</v>
       </c>
-      <c r="D170" s="405" t="s">
+      <c r="D170" s="399" t="s">
         <v>104</v>
       </c>
-      <c r="E170" s="406"/>
-      <c r="F170" s="407"/>
+      <c r="E170" s="400"/>
+      <c r="F170" s="401"/>
     </row>
     <row r="171" spans="3:35" ht="18.75">
       <c r="C171" s="215" t="s">
         <v>89</v>
       </c>
-      <c r="D171" s="402" t="s">
+      <c r="D171" s="397" t="s">
         <v>105</v>
       </c>
-      <c r="E171" s="402"/>
-      <c r="F171" s="403"/>
+      <c r="E171" s="397"/>
+      <c r="F171" s="398"/>
     </row>
     <row r="172" spans="3:35">
       <c r="C172" s="213" t="s">
         <v>90</v>
       </c>
-      <c r="D172" s="402" t="s">
+      <c r="D172" s="397" t="s">
         <v>106</v>
       </c>
-      <c r="E172" s="402"/>
-      <c r="F172" s="403"/>
+      <c r="E172" s="397"/>
+      <c r="F172" s="398"/>
     </row>
     <row r="173" spans="3:35" ht="16.5" thickBot="1">
       <c r="C173" s="216" t="s">
         <v>94</v>
       </c>
-      <c r="D173" s="413" t="s">
+      <c r="D173" s="373" t="s">
         <v>107</v>
       </c>
-      <c r="E173" s="414"/>
-      <c r="F173" s="415"/>
+      <c r="E173" s="374"/>
+      <c r="F173" s="375"/>
     </row>
   </sheetData>
   <autoFilter ref="A6:AE143" xr:uid="{C724CDAB-378C-47DB-9F45-08EE3BFB6E8B}">
@@ -24399,20 +24407,35 @@
     </sortState>
   </autoFilter>
   <mergeCells count="59">
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="D154:F155"/>
-    <mergeCell ref="D146:F146"/>
-    <mergeCell ref="I146:L146"/>
-    <mergeCell ref="AA4:AD4"/>
-    <mergeCell ref="Q145:R145"/>
-    <mergeCell ref="D151:F151"/>
-    <mergeCell ref="D152:F152"/>
-    <mergeCell ref="D153:F153"/>
-    <mergeCell ref="S4:U4"/>
-    <mergeCell ref="L4:L5"/>
-    <mergeCell ref="Q4:R4"/>
-    <mergeCell ref="K4:K5"/>
-    <mergeCell ref="Y4:Z4"/>
+    <mergeCell ref="AG5:AG6"/>
+    <mergeCell ref="AH5:AH6"/>
+    <mergeCell ref="AI5:AI6"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="AE4:AE5"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="V4:X4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="O4:P4"/>
+    <mergeCell ref="D172:F172"/>
+    <mergeCell ref="D159:F159"/>
+    <mergeCell ref="D160:F160"/>
+    <mergeCell ref="D167:F167"/>
+    <mergeCell ref="D168:F168"/>
+    <mergeCell ref="D169:F169"/>
+    <mergeCell ref="D170:F170"/>
+    <mergeCell ref="D171:F171"/>
+    <mergeCell ref="C162:F162"/>
+    <mergeCell ref="D163:F163"/>
+    <mergeCell ref="D164:F164"/>
+    <mergeCell ref="D165:F165"/>
+    <mergeCell ref="D166:F166"/>
     <mergeCell ref="D173:F173"/>
     <mergeCell ref="D145:F145"/>
     <mergeCell ref="C157:F157"/>
@@ -24429,35 +24452,20 @@
     <mergeCell ref="D149:F149"/>
     <mergeCell ref="D150:F150"/>
     <mergeCell ref="D158:F158"/>
-    <mergeCell ref="D172:F172"/>
-    <mergeCell ref="D159:F159"/>
-    <mergeCell ref="D160:F160"/>
-    <mergeCell ref="D167:F167"/>
-    <mergeCell ref="D168:F168"/>
-    <mergeCell ref="D169:F169"/>
-    <mergeCell ref="D170:F170"/>
-    <mergeCell ref="D171:F171"/>
-    <mergeCell ref="C162:F162"/>
-    <mergeCell ref="D163:F163"/>
-    <mergeCell ref="D164:F164"/>
-    <mergeCell ref="D165:F165"/>
-    <mergeCell ref="D166:F166"/>
-    <mergeCell ref="AG5:AG6"/>
-    <mergeCell ref="AH5:AH6"/>
-    <mergeCell ref="AI5:AI6"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="I4:I5"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="H4:H5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="AE4:AE5"/>
-    <mergeCell ref="J4:J5"/>
-    <mergeCell ref="V4:X4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="O4:P4"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="D154:F155"/>
+    <mergeCell ref="D146:F146"/>
+    <mergeCell ref="I146:L146"/>
+    <mergeCell ref="AA4:AD4"/>
+    <mergeCell ref="Q145:R145"/>
+    <mergeCell ref="D151:F151"/>
+    <mergeCell ref="D152:F152"/>
+    <mergeCell ref="D153:F153"/>
+    <mergeCell ref="S4:U4"/>
+    <mergeCell ref="L4:L5"/>
+    <mergeCell ref="Q4:R4"/>
+    <mergeCell ref="K4:K5"/>
+    <mergeCell ref="Y4:Z4"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="A7:AE143 AG7:AI143">
@@ -24988,9 +24996,10 @@
     <hyperlink ref="M139" r:id="rId502" xr:uid="{D1C7F371-1906-4C4E-9D64-07CD74AF282A}"/>
     <hyperlink ref="M140" r:id="rId503" xr:uid="{1BAE53B4-41B2-4955-9719-066BE2284B9D}"/>
     <hyperlink ref="M141" r:id="rId504" xr:uid="{1AD5278F-5E89-48A8-B214-0DE3CB9C250D}"/>
+    <hyperlink ref="O135" r:id="rId505" xr:uid="{E415571E-9ABB-4838-B4BB-663A644C52E5}"/>
   </hyperlinks>
   <pageMargins left="0.25" right="0.17" top="0.5" bottom="0.25" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="28" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId505"/>
+  <pageSetup paperSize="9" scale="28" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId506"/>
   <colBreaks count="1" manualBreakCount="1">
     <brk id="30" max="564" man="1"/>
   </colBreaks>
@@ -25128,88 +25137,88 @@
       <c r="AD3" s="159"/>
     </row>
     <row r="4" spans="1:35" s="5" customFormat="1" ht="36" customHeight="1" thickBot="1">
-      <c r="A4" s="396" t="s">
+      <c r="A4" s="408" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="350" t="s">
+      <c r="B4" s="348" t="s">
         <v>515</v>
       </c>
-      <c r="C4" s="364" t="s">
+      <c r="C4" s="414" t="s">
         <v>45</v>
       </c>
-      <c r="D4" s="352" t="s">
+      <c r="D4" s="369" t="s">
         <v>46</v>
       </c>
-      <c r="E4" s="400" t="s">
+      <c r="E4" s="412" t="s">
         <v>47</v>
       </c>
-      <c r="F4" s="352" t="s">
+      <c r="F4" s="369" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="398" t="s">
+      <c r="G4" s="410" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="358" t="s">
+      <c r="H4" s="366" t="s">
         <v>48</v>
       </c>
-      <c r="I4" s="358" t="s">
+      <c r="I4" s="366" t="s">
         <v>49</v>
       </c>
-      <c r="J4" s="352" t="s">
+      <c r="J4" s="369" t="s">
         <v>78</v>
       </c>
-      <c r="K4" s="358" t="s">
+      <c r="K4" s="366" t="s">
         <v>80</v>
       </c>
-      <c r="L4" s="363" t="s">
+      <c r="L4" s="364" t="s">
         <v>53</v>
       </c>
-      <c r="M4" s="348"/>
-      <c r="N4" s="362" t="s">
+      <c r="M4" s="365"/>
+      <c r="N4" s="368" t="s">
         <v>55</v>
       </c>
-      <c r="O4" s="348"/>
-      <c r="P4" s="362" t="s">
+      <c r="O4" s="365"/>
+      <c r="P4" s="368" t="s">
         <v>72</v>
       </c>
-      <c r="Q4" s="348"/>
-      <c r="R4" s="363" t="s">
+      <c r="Q4" s="365"/>
+      <c r="R4" s="364" t="s">
         <v>53</v>
       </c>
-      <c r="S4" s="363"/>
-      <c r="T4" s="348"/>
-      <c r="U4" s="362" t="s">
+      <c r="S4" s="364"/>
+      <c r="T4" s="365"/>
+      <c r="U4" s="368" t="s">
         <v>55</v>
       </c>
-      <c r="V4" s="363"/>
-      <c r="W4" s="348"/>
-      <c r="X4" s="366" t="s">
+      <c r="V4" s="364"/>
+      <c r="W4" s="365"/>
+      <c r="X4" s="371" t="s">
         <v>72</v>
       </c>
-      <c r="Y4" s="442"/>
-      <c r="Z4" s="366" t="s">
+      <c r="Y4" s="417"/>
+      <c r="Z4" s="371" t="s">
         <v>112</v>
       </c>
-      <c r="AA4" s="430"/>
-      <c r="AB4" s="430"/>
-      <c r="AC4" s="431"/>
-      <c r="AD4" s="352" t="s">
+      <c r="AA4" s="360"/>
+      <c r="AB4" s="360"/>
+      <c r="AC4" s="361"/>
+      <c r="AD4" s="369" t="s">
         <v>79</v>
       </c>
       <c r="AG4" s="236"/>
     </row>
     <row r="5" spans="1:35" ht="78.75">
-      <c r="A5" s="397"/>
-      <c r="B5" s="351"/>
-      <c r="C5" s="365"/>
-      <c r="D5" s="353"/>
-      <c r="E5" s="401"/>
-      <c r="F5" s="353"/>
-      <c r="G5" s="399"/>
-      <c r="H5" s="359"/>
-      <c r="I5" s="359"/>
-      <c r="J5" s="353"/>
-      <c r="K5" s="359"/>
+      <c r="A5" s="409"/>
+      <c r="B5" s="349"/>
+      <c r="C5" s="415"/>
+      <c r="D5" s="370"/>
+      <c r="E5" s="413"/>
+      <c r="F5" s="370"/>
+      <c r="G5" s="411"/>
+      <c r="H5" s="367"/>
+      <c r="I5" s="367"/>
+      <c r="J5" s="370"/>
+      <c r="K5" s="367"/>
       <c r="L5" s="79" t="s">
         <v>52</v>
       </c>
@@ -25264,14 +25273,14 @@
       <c r="AC5" s="250" t="s">
         <v>118</v>
       </c>
-      <c r="AD5" s="349"/>
-      <c r="AG5" s="432" t="s">
+      <c r="AD5" s="416"/>
+      <c r="AG5" s="422" t="s">
         <v>119</v>
       </c>
-      <c r="AH5" s="434" t="s">
+      <c r="AH5" s="424" t="s">
         <v>120</v>
       </c>
-      <c r="AI5" s="436" t="s">
+      <c r="AI5" s="426" t="s">
         <v>121</v>
       </c>
     </row>
@@ -25306,9 +25315,9 @@
       <c r="AB6" s="86"/>
       <c r="AC6" s="86"/>
       <c r="AD6" s="74"/>
-      <c r="AG6" s="433"/>
-      <c r="AH6" s="435"/>
-      <c r="AI6" s="437"/>
+      <c r="AG6" s="423"/>
+      <c r="AH6" s="425"/>
+      <c r="AI6" s="427"/>
     </row>
     <row r="7" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A7" s="33">
@@ -29095,28 +29104,28 @@
       <c r="C44" s="166" t="s">
         <v>20</v>
       </c>
-      <c r="D44" s="416" t="s">
+      <c r="D44" s="376" t="s">
         <v>21</v>
       </c>
-      <c r="E44" s="417"/>
+      <c r="E44" s="377"/>
       <c r="F44" s="46"/>
       <c r="G44" s="46"/>
-      <c r="H44" s="392" t="s">
+      <c r="H44" s="356" t="s">
         <v>14</v>
       </c>
-      <c r="I44" s="393"/>
-      <c r="J44" s="393"/>
-      <c r="K44" s="393"/>
-      <c r="L44" s="393"/>
-      <c r="M44" s="394"/>
-      <c r="N44" s="388" t="s">
+      <c r="I44" s="357"/>
+      <c r="J44" s="357"/>
+      <c r="K44" s="357"/>
+      <c r="L44" s="357"/>
+      <c r="M44" s="358"/>
+      <c r="N44" s="362" t="s">
         <v>7</v>
       </c>
-      <c r="O44" s="389"/>
-      <c r="P44" s="388" t="s">
+      <c r="O44" s="363"/>
+      <c r="P44" s="362" t="s">
         <v>109</v>
       </c>
-      <c r="Q44" s="389"/>
+      <c r="Q44" s="363"/>
       <c r="R44" s="1"/>
       <c r="S44" s="1"/>
       <c r="T44" s="140"/>
@@ -29136,17 +29145,17 @@
       <c r="C45" s="195" t="s">
         <v>109</v>
       </c>
-      <c r="D45" s="440" t="s">
+      <c r="D45" s="420" t="s">
         <v>111</v>
       </c>
-      <c r="E45" s="441"/>
+      <c r="E45" s="421"/>
       <c r="F45" s="46"/>
-      <c r="H45" s="392" t="s">
+      <c r="H45" s="356" t="s">
         <v>18</v>
       </c>
-      <c r="I45" s="393"/>
-      <c r="J45" s="393"/>
-      <c r="K45" s="394"/>
+      <c r="I45" s="357"/>
+      <c r="J45" s="357"/>
+      <c r="K45" s="358"/>
       <c r="L45" s="105">
         <f ca="1">M45/$M$45</f>
         <v>1</v>
@@ -29188,18 +29197,18 @@
       <c r="C46" s="195" t="s">
         <v>36</v>
       </c>
-      <c r="D46" s="438" t="s">
+      <c r="D46" s="418" t="s">
         <v>37</v>
       </c>
-      <c r="E46" s="439"/>
+      <c r="E46" s="419"/>
       <c r="F46" s="69"/>
       <c r="G46" s="6"/>
-      <c r="H46" s="418" t="s">
+      <c r="H46" s="379" t="s">
         <v>66</v>
       </c>
-      <c r="I46" s="419"/>
-      <c r="J46" s="419"/>
-      <c r="K46" s="420"/>
+      <c r="I46" s="380"/>
+      <c r="J46" s="380"/>
+      <c r="K46" s="381"/>
       <c r="L46" s="107">
         <f ca="1">M46/$M$45</f>
         <v>2.7777777777777776E-2</v>
@@ -29240,21 +29249,21 @@
       <c r="AI46" s="11"/>
     </row>
     <row r="47" spans="1:35">
-      <c r="C47" s="382" t="s">
+      <c r="C47" s="394" t="s">
         <v>75</v>
       </c>
-      <c r="D47" s="384" t="s">
+      <c r="D47" s="350" t="s">
         <v>76</v>
       </c>
-      <c r="E47" s="385"/>
+      <c r="E47" s="351"/>
       <c r="F47" s="70"/>
       <c r="G47" s="6"/>
-      <c r="H47" s="421" t="s">
+      <c r="H47" s="382" t="s">
         <v>67</v>
       </c>
-      <c r="I47" s="422"/>
-      <c r="J47" s="422"/>
-      <c r="K47" s="423"/>
+      <c r="I47" s="383"/>
+      <c r="J47" s="383"/>
+      <c r="K47" s="384"/>
       <c r="L47" s="109">
         <f t="shared" ref="L47:L50" ca="1" si="23">M47/$M$45</f>
         <v>0.55555555555555558</v>
@@ -29295,17 +29304,17 @@
       <c r="AI47" s="11"/>
     </row>
     <row r="48" spans="1:35" ht="16.5" thickBot="1">
-      <c r="C48" s="383"/>
-      <c r="D48" s="386"/>
-      <c r="E48" s="387"/>
+      <c r="C48" s="395"/>
+      <c r="D48" s="352"/>
+      <c r="E48" s="353"/>
       <c r="F48" s="71"/>
       <c r="G48" s="6"/>
-      <c r="H48" s="424" t="s">
+      <c r="H48" s="385" t="s">
         <v>68</v>
       </c>
-      <c r="I48" s="425"/>
-      <c r="J48" s="425"/>
-      <c r="K48" s="426"/>
+      <c r="I48" s="386"/>
+      <c r="J48" s="386"/>
+      <c r="K48" s="387"/>
       <c r="L48" s="111">
         <f t="shared" ca="1" si="23"/>
         <v>0.22222222222222221</v>
@@ -29348,12 +29357,12 @@
     <row r="49" spans="3:35">
       <c r="F49" s="72"/>
       <c r="G49" s="6"/>
-      <c r="H49" s="374" t="s">
+      <c r="H49" s="388" t="s">
         <v>70</v>
       </c>
-      <c r="I49" s="375"/>
-      <c r="J49" s="375"/>
-      <c r="K49" s="376"/>
+      <c r="I49" s="389"/>
+      <c r="J49" s="389"/>
+      <c r="K49" s="390"/>
       <c r="L49" s="114">
         <f t="shared" ca="1" si="23"/>
         <v>0.1388888888888889</v>
@@ -29396,17 +29405,17 @@
       <c r="AI49" s="11"/>
     </row>
     <row r="50" spans="3:35" ht="16.5" thickBot="1">
-      <c r="C50" s="370" t="s">
+      <c r="C50" s="378" t="s">
         <v>41</v>
       </c>
-      <c r="D50" s="370"/>
-      <c r="E50" s="370"/>
-      <c r="H50" s="377" t="s">
+      <c r="D50" s="378"/>
+      <c r="E50" s="378"/>
+      <c r="H50" s="391" t="s">
         <v>71</v>
       </c>
-      <c r="I50" s="378"/>
-      <c r="J50" s="378"/>
-      <c r="K50" s="379"/>
+      <c r="I50" s="392"/>
+      <c r="J50" s="392"/>
+      <c r="K50" s="393"/>
       <c r="L50" s="113">
         <f t="shared" ca="1" si="23"/>
         <v>5.5555555555555552E-2</v>
@@ -29451,27 +29460,6 @@
     </sortState>
   </autoFilter>
   <mergeCells count="37">
-    <mergeCell ref="P44:Q44"/>
-    <mergeCell ref="X4:Y4"/>
-    <mergeCell ref="Z4:AC4"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D44:E44"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="D46:E46"/>
-    <mergeCell ref="C50:E50"/>
-    <mergeCell ref="H46:K46"/>
-    <mergeCell ref="H47:K47"/>
-    <mergeCell ref="H44:M44"/>
-    <mergeCell ref="H48:K48"/>
-    <mergeCell ref="H49:K49"/>
-    <mergeCell ref="C47:C48"/>
-    <mergeCell ref="D47:E48"/>
-    <mergeCell ref="D45:E45"/>
     <mergeCell ref="AG5:AG6"/>
     <mergeCell ref="AH5:AH6"/>
     <mergeCell ref="AI5:AI6"/>
@@ -29488,6 +29476,27 @@
     <mergeCell ref="K4:K5"/>
     <mergeCell ref="P4:Q4"/>
     <mergeCell ref="J4:J5"/>
+    <mergeCell ref="D46:E46"/>
+    <mergeCell ref="C50:E50"/>
+    <mergeCell ref="H46:K46"/>
+    <mergeCell ref="H47:K47"/>
+    <mergeCell ref="H44:M44"/>
+    <mergeCell ref="H48:K48"/>
+    <mergeCell ref="H49:K49"/>
+    <mergeCell ref="C47:C48"/>
+    <mergeCell ref="D47:E48"/>
+    <mergeCell ref="D45:E45"/>
+    <mergeCell ref="P44:Q44"/>
+    <mergeCell ref="X4:Y4"/>
+    <mergeCell ref="Z4:AC4"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D44:E44"/>
+    <mergeCell ref="B4:B5"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="A7:AD42 AG7:AI42">
@@ -29772,81 +29781,81 @@
       <c r="Z3" s="159"/>
     </row>
     <row r="4" spans="1:26" s="5" customFormat="1" ht="35.1" customHeight="1" thickBot="1">
-      <c r="A4" s="350" t="s">
+      <c r="A4" s="348" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="350" t="s">
+      <c r="B4" s="348" t="s">
         <v>515</v>
       </c>
-      <c r="C4" s="364" t="s">
+      <c r="C4" s="414" t="s">
         <v>45</v>
       </c>
-      <c r="D4" s="352" t="s">
+      <c r="D4" s="369" t="s">
         <v>46</v>
       </c>
-      <c r="E4" s="354" t="s">
+      <c r="E4" s="437" t="s">
         <v>47</v>
       </c>
-      <c r="F4" s="352" t="s">
+      <c r="F4" s="369" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="356" t="s">
+      <c r="G4" s="439" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="358" t="s">
+      <c r="H4" s="366" t="s">
         <v>48</v>
       </c>
-      <c r="I4" s="360" t="s">
+      <c r="I4" s="441" t="s">
         <v>49</v>
       </c>
-      <c r="J4" s="352" t="s">
+      <c r="J4" s="369" t="s">
         <v>78</v>
       </c>
-      <c r="K4" s="358" t="s">
+      <c r="K4" s="366" t="s">
         <v>80</v>
       </c>
-      <c r="L4" s="362" t="s">
+      <c r="L4" s="368" t="s">
         <v>53</v>
       </c>
-      <c r="M4" s="348"/>
-      <c r="N4" s="362" t="s">
+      <c r="M4" s="365"/>
+      <c r="N4" s="368" t="s">
         <v>55</v>
       </c>
-      <c r="O4" s="348"/>
-      <c r="P4" s="362" t="s">
+      <c r="O4" s="365"/>
+      <c r="P4" s="368" t="s">
         <v>72</v>
       </c>
-      <c r="Q4" s="348"/>
-      <c r="R4" s="363" t="s">
+      <c r="Q4" s="365"/>
+      <c r="R4" s="364" t="s">
         <v>53</v>
       </c>
-      <c r="S4" s="363"/>
-      <c r="T4" s="348"/>
-      <c r="U4" s="362" t="s">
+      <c r="S4" s="364"/>
+      <c r="T4" s="365"/>
+      <c r="U4" s="368" t="s">
         <v>55</v>
       </c>
-      <c r="V4" s="363"/>
-      <c r="W4" s="363"/>
-      <c r="X4" s="366" t="s">
+      <c r="V4" s="364"/>
+      <c r="W4" s="364"/>
+      <c r="X4" s="371" t="s">
         <v>72</v>
       </c>
-      <c r="Y4" s="367"/>
-      <c r="Z4" s="348" t="s">
+      <c r="Y4" s="372"/>
+      <c r="Z4" s="365" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="72" customHeight="1">
-      <c r="A5" s="351"/>
-      <c r="B5" s="351"/>
-      <c r="C5" s="365"/>
-      <c r="D5" s="353"/>
-      <c r="E5" s="355"/>
-      <c r="F5" s="353"/>
-      <c r="G5" s="357"/>
-      <c r="H5" s="359"/>
-      <c r="I5" s="361"/>
-      <c r="J5" s="353"/>
-      <c r="K5" s="359"/>
+      <c r="A5" s="349"/>
+      <c r="B5" s="349"/>
+      <c r="C5" s="415"/>
+      <c r="D5" s="370"/>
+      <c r="E5" s="438"/>
+      <c r="F5" s="370"/>
+      <c r="G5" s="440"/>
+      <c r="H5" s="367"/>
+      <c r="I5" s="442"/>
+      <c r="J5" s="370"/>
+      <c r="K5" s="367"/>
       <c r="L5" s="79" t="s">
         <v>52</v>
       </c>
@@ -29889,7 +29898,7 @@
       <c r="Y5" s="260" t="s">
         <v>114</v>
       </c>
-      <c r="Z5" s="349"/>
+      <c r="Z5" s="416"/>
     </row>
     <row r="6" spans="1:26" ht="15" customHeight="1" thickBot="1">
       <c r="A6" s="78"/>
@@ -31716,7 +31725,7 @@
       <c r="Y29" s="19"/>
       <c r="Z29" s="92"/>
     </row>
-    <row r="30" spans="1:26" s="9" customFormat="1" ht="31.5">
+    <row r="30" spans="1:26" s="9" customFormat="1" ht="47.25">
       <c r="A30" s="33">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -34062,7 +34071,7 @@
       </c>
       <c r="Z59" s="92"/>
     </row>
-    <row r="60" spans="1:26" s="9" customFormat="1" ht="47.25">
+    <row r="60" spans="1:26" s="9" customFormat="1" ht="63">
       <c r="A60" s="33">
         <f t="shared" si="0"/>
         <v>54</v>
@@ -38802,11 +38811,11 @@
         <v>6</v>
       </c>
       <c r="I125" s="164">
-        <f t="shared" ca="1" si="24"/>
+        <f t="shared" si="24"/>
         <v>19</v>
       </c>
       <c r="J125" s="47">
-        <f t="shared" ca="1" si="25"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="K125" s="164"/>
@@ -38814,7 +38823,9 @@
         <v>8</v>
       </c>
       <c r="M125" s="41"/>
-      <c r="N125" s="40"/>
+      <c r="N125" s="40" t="s">
+        <v>8</v>
+      </c>
       <c r="O125" s="41"/>
       <c r="P125" s="40"/>
       <c r="Q125" s="154"/>
@@ -38827,8 +38838,12 @@
       <c r="T125" s="188">
         <v>46295</v>
       </c>
-      <c r="U125" s="29"/>
-      <c r="V125" s="211"/>
+      <c r="U125" s="29">
+        <v>46307</v>
+      </c>
+      <c r="V125" s="211">
+        <v>46314</v>
+      </c>
       <c r="W125" s="235" t="s">
         <v>240</v>
       </c>
@@ -38867,11 +38882,11 @@
         <v>6</v>
       </c>
       <c r="I126" s="164">
-        <f t="shared" ca="1" si="24"/>
+        <f t="shared" si="24"/>
         <v>12</v>
       </c>
       <c r="J126" s="47">
-        <f t="shared" ca="1" si="25"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="K126" s="164"/>
@@ -38879,7 +38894,9 @@
         <v>8</v>
       </c>
       <c r="M126" s="41"/>
-      <c r="N126" s="40"/>
+      <c r="N126" s="40" t="s">
+        <v>8</v>
+      </c>
       <c r="O126" s="41"/>
       <c r="P126" s="40"/>
       <c r="Q126" s="154"/>
@@ -38892,18 +38909,22 @@
       <c r="T126" s="188">
         <v>46302</v>
       </c>
-      <c r="U126" s="29"/>
-      <c r="V126" s="211"/>
+      <c r="U126" s="29">
+        <v>46311</v>
+      </c>
+      <c r="V126" s="211">
+        <v>46314</v>
+      </c>
       <c r="W126" s="235" t="s">
         <v>240</v>
       </c>
       <c r="X126" s="230"/>
       <c r="Y126" s="19"/>
       <c r="Z126" s="92" t="s">
-        <v>1072</v>
-      </c>
-    </row>
-    <row r="127" spans="1:26" s="9" customFormat="1" ht="31.5">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="127" spans="1:26" s="9" customFormat="1" ht="47.25">
       <c r="A127" s="33">
         <f t="shared" si="29"/>
         <v>121</v>
@@ -38926,13 +38947,15 @@
       <c r="G127" s="21" t="s">
         <v>1058</v>
       </c>
-      <c r="H127" s="138"/>
+      <c r="H127" s="138" t="s">
+        <v>6</v>
+      </c>
       <c r="I127" s="164">
-        <f t="shared" ca="1" si="24"/>
+        <f t="shared" si="24"/>
         <v>10</v>
       </c>
       <c r="J127" s="47">
-        <f t="shared" ca="1" si="25"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="K127" s="164"/>
@@ -38940,7 +38963,9 @@
         <v>8</v>
       </c>
       <c r="M127" s="41"/>
-      <c r="N127" s="40"/>
+      <c r="N127" s="40" t="s">
+        <v>8</v>
+      </c>
       <c r="O127" s="41"/>
       <c r="P127" s="40"/>
       <c r="Q127" s="154"/>
@@ -38953,13 +38978,19 @@
       <c r="T127" s="188">
         <v>46304</v>
       </c>
-      <c r="U127" s="29"/>
-      <c r="V127" s="211"/>
-      <c r="W127" s="235"/>
+      <c r="U127" s="29">
+        <v>46311</v>
+      </c>
+      <c r="V127" s="211">
+        <v>46314</v>
+      </c>
+      <c r="W127" s="235" t="s">
+        <v>240</v>
+      </c>
       <c r="X127" s="230"/>
       <c r="Y127" s="19"/>
       <c r="Z127" s="92" t="s">
-        <v>1071</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="128" spans="1:26" s="9" customFormat="1" ht="47.25">
@@ -39034,17 +39065,17 @@
         <v>195</v>
       </c>
       <c r="D129" s="25" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="E129" s="174">
         <f t="shared" si="23"/>
         <v>46332</v>
       </c>
       <c r="F129" s="31" t="s">
+        <v>1091</v>
+      </c>
+      <c r="G129" s="21" t="s">
         <v>1092</v>
-      </c>
-      <c r="G129" s="21" t="s">
-        <v>1093</v>
       </c>
       <c r="H129" s="138"/>
       <c r="I129" s="164">
@@ -39141,28 +39172,28 @@
       <c r="C133" s="207" t="s">
         <v>38</v>
       </c>
-      <c r="D133" s="390" t="s">
+      <c r="D133" s="428" t="s">
         <v>39</v>
       </c>
-      <c r="E133" s="391"/>
+      <c r="E133" s="429"/>
       <c r="F133" s="46"/>
       <c r="G133" s="68"/>
-      <c r="H133" s="392" t="s">
+      <c r="H133" s="356" t="s">
         <v>14</v>
       </c>
-      <c r="I133" s="393"/>
-      <c r="J133" s="393"/>
-      <c r="K133" s="393"/>
-      <c r="L133" s="393"/>
-      <c r="M133" s="394"/>
-      <c r="N133" s="388" t="s">
+      <c r="I133" s="357"/>
+      <c r="J133" s="357"/>
+      <c r="K133" s="357"/>
+      <c r="L133" s="357"/>
+      <c r="M133" s="358"/>
+      <c r="N133" s="362" t="s">
         <v>7</v>
       </c>
-      <c r="O133" s="389"/>
-      <c r="P133" s="388" t="s">
+      <c r="O133" s="363"/>
+      <c r="P133" s="362" t="s">
         <v>110</v>
       </c>
-      <c r="Q133" s="389"/>
+      <c r="Q133" s="363"/>
       <c r="R133" s="1"/>
       <c r="S133" s="1"/>
       <c r="T133" s="140"/>
@@ -39175,16 +39206,16 @@
       <c r="C134" s="208" t="s">
         <v>74</v>
       </c>
-      <c r="D134" s="380" t="s">
+      <c r="D134" s="435" t="s">
         <v>77</v>
       </c>
-      <c r="E134" s="381"/>
+      <c r="E134" s="436"/>
       <c r="F134" s="46"/>
       <c r="G134" s="46"/>
-      <c r="H134" s="368" t="s">
+      <c r="H134" s="430" t="s">
         <v>17</v>
       </c>
-      <c r="I134" s="369"/>
+      <c r="I134" s="431"/>
       <c r="J134" s="130"/>
       <c r="K134" s="210"/>
       <c r="L134" s="117">
@@ -39193,7 +39224,7 @@
       </c>
       <c r="M134" s="104">
         <f ca="1">SUM($M$135:$M$137)</f>
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="N134" s="118" t="s">
         <v>15</v>
@@ -39218,32 +39249,32 @@
       <c r="Y134" s="11"/>
     </row>
     <row r="135" spans="1:26">
-      <c r="C135" s="382" t="s">
+      <c r="C135" s="394" t="s">
         <v>6</v>
       </c>
-      <c r="D135" s="380" t="s">
+      <c r="D135" s="435" t="s">
         <v>40</v>
       </c>
-      <c r="E135" s="381"/>
+      <c r="E135" s="436"/>
       <c r="F135" s="69"/>
       <c r="G135" s="6"/>
-      <c r="H135" s="371" t="s">
+      <c r="H135" s="432" t="s">
         <v>69</v>
       </c>
-      <c r="I135" s="372"/>
-      <c r="J135" s="372"/>
-      <c r="K135" s="373"/>
+      <c r="I135" s="433"/>
+      <c r="J135" s="433"/>
+      <c r="K135" s="434"/>
       <c r="L135" s="122">
         <f t="shared" ref="L135:L137" ca="1" si="61">M135/$M$134</f>
-        <v>0.81395348837209303</v>
+        <v>0.83464566929133854</v>
       </c>
       <c r="M135" s="123">
         <f>COUNTIF($H$7:$H$131,"RFCS")</f>
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N135" s="121">
         <f ca="1">COUNTIFS($I$7:$I$131,"&lt;=21",$H$7:$H$131,"RFCS")</f>
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="O135" s="120">
         <f ca="1">COUNTIFS($I$7:$I$131,"&gt;21",$H$7:$H$131,"RFCS")</f>
@@ -39266,28 +39297,28 @@
       <c r="Y135" s="11"/>
     </row>
     <row r="136" spans="1:26">
-      <c r="C136" s="382"/>
-      <c r="D136" s="380"/>
-      <c r="E136" s="381"/>
+      <c r="C136" s="394"/>
+      <c r="D136" s="435"/>
+      <c r="E136" s="436"/>
       <c r="F136" s="72"/>
       <c r="G136" s="6"/>
-      <c r="H136" s="374" t="s">
+      <c r="H136" s="388" t="s">
         <v>70</v>
       </c>
-      <c r="I136" s="375"/>
-      <c r="J136" s="375"/>
-      <c r="K136" s="376"/>
+      <c r="I136" s="389"/>
+      <c r="J136" s="389"/>
+      <c r="K136" s="390"/>
       <c r="L136" s="124">
         <f t="shared" ca="1" si="61"/>
-        <v>7.7519379844961239E-2</v>
+        <v>5.5118110236220472E-2</v>
       </c>
       <c r="M136" s="125">
         <f ca="1">SUM(N136:O136)</f>
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="N136" s="98">
         <f ca="1">COUNTIFS($I$7:$I$131,"&lt;=21",$U$7:$U$131,"",$K$7:$K$131,"&lt;&gt;X")</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O136" s="50">
         <f ca="1">COUNTIFS($I$7:$I$131,"&gt;21",$U$7:$U$131,"",$K$7:$K$131,"&lt;&gt;X")</f>
@@ -39312,22 +39343,22 @@
       <c r="Y136" s="11"/>
     </row>
     <row r="137" spans="1:26" ht="16.5" thickBot="1">
-      <c r="C137" s="382" t="s">
+      <c r="C137" s="394" t="s">
         <v>75</v>
       </c>
-      <c r="D137" s="384" t="s">
+      <c r="D137" s="350" t="s">
         <v>76</v>
       </c>
-      <c r="E137" s="385"/>
-      <c r="H137" s="377" t="s">
+      <c r="E137" s="351"/>
+      <c r="H137" s="391" t="s">
         <v>71</v>
       </c>
-      <c r="I137" s="378"/>
-      <c r="J137" s="378"/>
-      <c r="K137" s="379"/>
+      <c r="I137" s="392"/>
+      <c r="J137" s="392"/>
+      <c r="K137" s="393"/>
       <c r="L137" s="126">
         <f t="shared" ca="1" si="61"/>
-        <v>0.10852713178294573</v>
+        <v>0.11023622047244094</v>
       </c>
       <c r="M137" s="116">
         <f>COUNTIFS($K$7:$K$131,"X")</f>
@@ -39339,16 +39370,16 @@
       <c r="Q137" s="224"/>
     </row>
     <row r="138" spans="1:26" ht="16.5" thickBot="1">
-      <c r="C138" s="383"/>
-      <c r="D138" s="386"/>
-      <c r="E138" s="387"/>
+      <c r="C138" s="395"/>
+      <c r="D138" s="352"/>
+      <c r="E138" s="353"/>
     </row>
     <row r="140" spans="1:26">
-      <c r="C140" s="370" t="s">
+      <c r="C140" s="378" t="s">
         <v>41</v>
       </c>
-      <c r="D140" s="370"/>
-      <c r="E140" s="370"/>
+      <c r="D140" s="378"/>
+      <c r="E140" s="378"/>
     </row>
     <row r="141" spans="1:26">
       <c r="C141" s="169" t="s">
@@ -39381,22 +39412,6 @@
     </sortState>
   </autoFilter>
   <mergeCells count="32">
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="P133:Q133"/>
-    <mergeCell ref="J4:J5"/>
-    <mergeCell ref="D133:E133"/>
-    <mergeCell ref="H133:M133"/>
-    <mergeCell ref="N133:O133"/>
-    <mergeCell ref="H134:I134"/>
-    <mergeCell ref="C140:E140"/>
-    <mergeCell ref="H135:K135"/>
-    <mergeCell ref="H136:K136"/>
-    <mergeCell ref="H137:K137"/>
-    <mergeCell ref="D134:E134"/>
-    <mergeCell ref="C135:C136"/>
-    <mergeCell ref="D135:E136"/>
-    <mergeCell ref="C137:C138"/>
-    <mergeCell ref="D137:E138"/>
     <mergeCell ref="Z4:Z5"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="D4:D5"/>
@@ -39413,6 +39428,22 @@
     <mergeCell ref="K4:K5"/>
     <mergeCell ref="P4:Q4"/>
     <mergeCell ref="X4:Y4"/>
+    <mergeCell ref="H134:I134"/>
+    <mergeCell ref="C140:E140"/>
+    <mergeCell ref="H135:K135"/>
+    <mergeCell ref="H136:K136"/>
+    <mergeCell ref="H137:K137"/>
+    <mergeCell ref="D134:E134"/>
+    <mergeCell ref="C135:C136"/>
+    <mergeCell ref="D135:E136"/>
+    <mergeCell ref="C137:C138"/>
+    <mergeCell ref="D137:E138"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="P133:Q133"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="D133:E133"/>
+    <mergeCell ref="H133:M133"/>
+    <mergeCell ref="N133:O133"/>
   </mergeCells>
   <phoneticPr fontId="71"/>
   <conditionalFormatting sqref="A7:Z131">
@@ -39910,9 +39941,12 @@
     <hyperlink ref="L127" r:id="rId475" xr:uid="{E41605CA-C2E5-494D-8E08-2F89092E4322}"/>
     <hyperlink ref="L128" r:id="rId476" xr:uid="{EEC0D82E-190C-4F0D-80DD-BE42DD4F1D56}"/>
     <hyperlink ref="L129" r:id="rId477" xr:uid="{090DE60D-6895-4F41-A19F-68068AEBAA0A}"/>
+    <hyperlink ref="N126" r:id="rId478" xr:uid="{E0E300E4-A703-49B0-A1DF-0EC9F6DC050D}"/>
+    <hyperlink ref="N127" r:id="rId479" xr:uid="{984FC4EC-B838-4F05-998C-F6897E6C0896}"/>
+    <hyperlink ref="N125" r:id="rId480" xr:uid="{ECB0E570-ED5C-4126-9B31-6711B56E14D0}"/>
   </hyperlinks>
   <pageMargins left="0.25" right="0.17" top="0.5" bottom="0.25" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="28" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId478"/>
+  <pageSetup paperSize="9" scale="28" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId481"/>
 </worksheet>
 </file>
 
@@ -39997,19 +40031,19 @@
       <c r="S3" s="281"/>
     </row>
     <row r="4" spans="1:25" ht="36" customHeight="1" thickBot="1">
-      <c r="A4" s="396" t="s">
+      <c r="A4" s="408" t="s">
         <v>123</v>
       </c>
-      <c r="B4" s="358" t="s">
+      <c r="B4" s="366" t="s">
         <v>45</v>
       </c>
-      <c r="C4" s="358" t="s">
+      <c r="C4" s="366" t="s">
         <v>95</v>
       </c>
-      <c r="D4" s="358" t="s">
+      <c r="D4" s="366" t="s">
         <v>46</v>
       </c>
-      <c r="E4" s="352" t="s">
+      <c r="E4" s="369" t="s">
         <v>4</v>
       </c>
       <c r="F4" s="449" t="s">
@@ -40038,12 +40072,12 @@
       <c r="S4" s="448"/>
     </row>
     <row r="5" spans="1:25" ht="78.75">
-      <c r="A5" s="397"/>
-      <c r="B5" s="359"/>
-      <c r="C5" s="359"/>
-      <c r="D5" s="359"/>
-      <c r="E5" s="353"/>
-      <c r="F5" s="399"/>
+      <c r="A5" s="409"/>
+      <c r="B5" s="367"/>
+      <c r="C5" s="367"/>
+      <c r="D5" s="367"/>
+      <c r="E5" s="370"/>
+      <c r="F5" s="411"/>
       <c r="G5" s="283" t="s">
         <v>56</v>
       </c>
@@ -41376,16 +41410,16 @@
       <c r="R3" s="281"/>
     </row>
     <row r="4" spans="1:18" ht="16.5" thickBot="1">
-      <c r="A4" s="396" t="s">
+      <c r="A4" s="408" t="s">
         <v>123</v>
       </c>
-      <c r="B4" s="358" t="s">
+      <c r="B4" s="366" t="s">
         <v>45</v>
       </c>
-      <c r="C4" s="358" t="s">
+      <c r="C4" s="366" t="s">
         <v>46</v>
       </c>
-      <c r="D4" s="363" t="s">
+      <c r="D4" s="364" t="s">
         <v>4</v>
       </c>
       <c r="E4" s="449" t="s">
@@ -41414,11 +41448,11 @@
       <c r="R4" s="448"/>
     </row>
     <row r="5" spans="1:18" ht="78.75">
-      <c r="A5" s="397"/>
-      <c r="B5" s="359"/>
-      <c r="C5" s="359"/>
-      <c r="D5" s="357"/>
-      <c r="E5" s="353"/>
+      <c r="A5" s="409"/>
+      <c r="B5" s="367"/>
+      <c r="C5" s="367"/>
+      <c r="D5" s="440"/>
+      <c r="E5" s="370"/>
       <c r="F5" s="283" t="s">
         <v>56</v>
       </c>

--- a/ICT-RFA-RFI-lists-New.xlsx
+++ b/ICT-RFA-RFI-lists-New.xlsx
@@ -9,9 +9,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project Airport\LTIA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79BA979A-7609-4D27-935F-A679DD1F78F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BF5D713-AEFB-4B9C-A558-01D45CE3E09E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="506" activeTab="2" xr2:uid="{CCA8147E-0981-4321-B87F-440A52C0DA59}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="506" activeTab="1" xr2:uid="{CCA8147E-0981-4321-B87F-440A52C0DA59}"/>
   </bookViews>
   <sheets>
     <sheet name="RFA" sheetId="1" r:id="rId1"/>
@@ -25,12 +25,12 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Need ReSub (RFA)'!$A$6:$S$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Need ReSub (RFA-SDS)'!$A$6:$R$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">RFA!$A$6:$AE$143</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'RFA-SDS'!$A$6:$AD$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'RFA-SDS'!$A$6:$AD$43</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">RFI!$A$6:$Z$127</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Need ReSub (RFA)'!$A$1:$S$77</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'Need ReSub (RFA-SDS)'!$A$1:$R$62</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">RFA!$A$1:$AE$143,RFA!$I$145:$R$151,RFA!$C$145:$F$155,RFA!$C$157:$F$160,RFA!$C$162:$F$173</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'RFA-SDS'!$A$1:$AD$42,'RFA-SDS'!$H$44:$Q$50,'RFA-SDS'!$C$44:$E$48,'RFA-SDS'!$C$50:$E$53</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'RFA-SDS'!$A$1:$AD$43,'RFA-SDS'!$H$45:$Q$51,'RFA-SDS'!$C$45:$E$49,'RFA-SDS'!$C$51:$E$54</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">RFI!$A$1:$Z$131,RFI!$H$133:$Q$137,RFI!$C$133:$E$138,RFI!$C$140:$E$143</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">RFA!$4:$5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'RFA-SDS'!$4:$5</definedName>
@@ -78,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3493" uniqueCount="1097">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3497" uniqueCount="1099">
   <si>
     <t>TT</t>
   </si>
@@ -5146,6 +5146,12 @@
     <t>101/14/2026: Đã comment
 10/15/2026 Đã gửi CNC
 10/15/2026: Đã ký RFCS</t>
+  </si>
+  <si>
+    <t>LTIA-5.10-VIETUR-80000-RFA-SDS-0222B</t>
+  </si>
+  <si>
+    <t>Construction design drawing of  ICT system – part.1: ICT systems for DATA CENTER 2 (DC2) &amp; TECHNICAL ROOM (EF,BD)</t>
   </si>
 </sst>
 </file>
@@ -7582,12 +7588,114 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="45" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -7600,21 +7708,129 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="53" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="47" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="51" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="52" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="55" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="55" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="51" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="52" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -7624,172 +7840,22 @@
     <xf numFmtId="1" fontId="2" fillId="0" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="55" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="55" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -7804,67 +7870,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="53" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="47" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="45" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -8441,7 +8447,7 @@
       </c>
       <c r="J1" s="176">
         <f ca="1">TODAY()</f>
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="K1" s="131"/>
       <c r="L1" s="197"/>
@@ -8528,92 +8534,92 @@
       <c r="AE3" s="159"/>
     </row>
     <row r="4" spans="1:35" s="5" customFormat="1" ht="36" customHeight="1" thickBot="1">
-      <c r="A4" s="408" t="s">
+      <c r="A4" s="396" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="348" t="s">
+      <c r="B4" s="350" t="s">
         <v>515</v>
       </c>
-      <c r="C4" s="414" t="s">
+      <c r="C4" s="364" t="s">
         <v>45</v>
       </c>
-      <c r="D4" s="366" t="s">
+      <c r="D4" s="358" t="s">
         <v>95</v>
       </c>
-      <c r="E4" s="369" t="s">
+      <c r="E4" s="352" t="s">
         <v>46</v>
       </c>
-      <c r="F4" s="412" t="s">
+      <c r="F4" s="400" t="s">
         <v>47</v>
       </c>
-      <c r="G4" s="369" t="s">
+      <c r="G4" s="352" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="410" t="s">
+      <c r="H4" s="398" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="366" t="s">
+      <c r="I4" s="358" t="s">
         <v>48</v>
       </c>
-      <c r="J4" s="366" t="s">
+      <c r="J4" s="358" t="s">
         <v>49</v>
       </c>
-      <c r="K4" s="369" t="s">
+      <c r="K4" s="352" t="s">
         <v>78</v>
       </c>
-      <c r="L4" s="366" t="s">
+      <c r="L4" s="358" t="s">
         <v>80</v>
       </c>
-      <c r="M4" s="364" t="s">
+      <c r="M4" s="363" t="s">
         <v>53</v>
       </c>
-      <c r="N4" s="365"/>
-      <c r="O4" s="364" t="s">
+      <c r="N4" s="348"/>
+      <c r="O4" s="363" t="s">
         <v>55</v>
       </c>
-      <c r="P4" s="365"/>
-      <c r="Q4" s="368" t="s">
+      <c r="P4" s="348"/>
+      <c r="Q4" s="362" t="s">
         <v>72</v>
       </c>
-      <c r="R4" s="365"/>
-      <c r="S4" s="364" t="s">
+      <c r="R4" s="348"/>
+      <c r="S4" s="363" t="s">
         <v>53</v>
       </c>
-      <c r="T4" s="364"/>
-      <c r="U4" s="365"/>
-      <c r="V4" s="368" t="s">
+      <c r="T4" s="363"/>
+      <c r="U4" s="348"/>
+      <c r="V4" s="362" t="s">
         <v>55</v>
       </c>
-      <c r="W4" s="364"/>
-      <c r="X4" s="365"/>
-      <c r="Y4" s="371" t="s">
+      <c r="W4" s="363"/>
+      <c r="X4" s="348"/>
+      <c r="Y4" s="366" t="s">
         <v>72</v>
       </c>
-      <c r="Z4" s="372"/>
-      <c r="AA4" s="359" t="s">
+      <c r="Z4" s="367"/>
+      <c r="AA4" s="429" t="s">
         <v>112</v>
       </c>
-      <c r="AB4" s="360"/>
-      <c r="AC4" s="360"/>
-      <c r="AD4" s="361"/>
-      <c r="AE4" s="369" t="s">
+      <c r="AB4" s="430"/>
+      <c r="AC4" s="430"/>
+      <c r="AD4" s="431"/>
+      <c r="AE4" s="352" t="s">
         <v>79</v>
       </c>
       <c r="AG4" s="236"/>
     </row>
     <row r="5" spans="1:35" ht="78.75">
-      <c r="A5" s="409"/>
-      <c r="B5" s="349"/>
-      <c r="C5" s="415"/>
-      <c r="D5" s="367"/>
-      <c r="E5" s="370"/>
-      <c r="F5" s="413"/>
-      <c r="G5" s="370"/>
-      <c r="H5" s="411"/>
-      <c r="I5" s="367"/>
-      <c r="J5" s="367"/>
-      <c r="K5" s="370"/>
-      <c r="L5" s="367"/>
+      <c r="A5" s="397"/>
+      <c r="B5" s="351"/>
+      <c r="C5" s="365"/>
+      <c r="D5" s="359"/>
+      <c r="E5" s="353"/>
+      <c r="F5" s="401"/>
+      <c r="G5" s="353"/>
+      <c r="H5" s="399"/>
+      <c r="I5" s="359"/>
+      <c r="J5" s="359"/>
+      <c r="K5" s="353"/>
+      <c r="L5" s="359"/>
       <c r="M5" s="79" t="s">
         <v>52</v>
       </c>
@@ -8668,14 +8674,14 @@
       <c r="AD5" s="336" t="s">
         <v>118</v>
       </c>
-      <c r="AE5" s="416"/>
-      <c r="AG5" s="369" t="s">
+      <c r="AE5" s="349"/>
+      <c r="AG5" s="352" t="s">
         <v>119</v>
       </c>
-      <c r="AH5" s="369" t="s">
+      <c r="AH5" s="352" t="s">
         <v>120</v>
       </c>
-      <c r="AI5" s="369" t="s">
+      <c r="AI5" s="352" t="s">
         <v>121</v>
       </c>
     </row>
@@ -8711,9 +8717,9 @@
       <c r="AC6" s="86"/>
       <c r="AD6" s="86"/>
       <c r="AE6" s="74"/>
-      <c r="AG6" s="407"/>
-      <c r="AH6" s="407"/>
-      <c r="AI6" s="407"/>
+      <c r="AG6" s="395"/>
+      <c r="AH6" s="395"/>
+      <c r="AI6" s="395"/>
     </row>
     <row r="7" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A7" s="33">
@@ -9632,7 +9638,7 @@
       </c>
       <c r="AD14" s="337">
         <f t="shared" ca="1" si="7"/>
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="AE14" s="92"/>
       <c r="AG14" s="238" t="str">
@@ -9748,7 +9754,7 @@
       </c>
       <c r="AD15" s="337">
         <f t="shared" ca="1" si="7"/>
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="AE15" s="92"/>
       <c r="AG15" s="238" t="str">
@@ -13136,7 +13142,7 @@
       </c>
       <c r="AD44" s="337">
         <f t="shared" ca="1" si="13"/>
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AE44" s="92"/>
       <c r="AG44" s="238" t="str">
@@ -13370,7 +13376,7 @@
       </c>
       <c r="AD46" s="337">
         <f t="shared" ca="1" si="13"/>
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AE46" s="92"/>
       <c r="AG46" s="238" t="str">
@@ -13836,7 +13842,7 @@
       </c>
       <c r="AD50" s="337">
         <f t="shared" ca="1" si="13"/>
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AE50" s="92"/>
       <c r="AG50" s="238" t="str">
@@ -13887,7 +13893,7 @@
       <c r="I51" s="138"/>
       <c r="J51" s="164">
         <f t="shared" ca="1" si="3"/>
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="K51" s="47"/>
       <c r="L51" s="164" t="s">
@@ -14744,7 +14750,7 @@
       </c>
       <c r="AD58" s="337">
         <f t="shared" ca="1" si="13"/>
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AE58" s="92"/>
       <c r="AG58" s="238" t="str">
@@ -14795,7 +14801,7 @@
       <c r="I59" s="138"/>
       <c r="J59" s="164">
         <f t="shared" ca="1" si="3"/>
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="K59" s="47"/>
       <c r="L59" s="164" t="s">
@@ -15070,7 +15076,7 @@
       </c>
       <c r="AD61" s="337">
         <f t="shared" ca="1" si="13"/>
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AE61" s="92"/>
       <c r="AG61" s="238" t="str">
@@ -15890,7 +15896,7 @@
       </c>
       <c r="AD68" s="337">
         <f t="shared" ca="1" si="13"/>
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AE68" s="92"/>
       <c r="AG68" s="238" t="str">
@@ -18512,11 +18518,11 @@
       <c r="I92" s="138"/>
       <c r="J92" s="164">
         <f t="shared" ca="1" si="27"/>
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K92" s="47">
         <f t="shared" ca="1" si="28"/>
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L92" s="164" t="s">
         <v>1003</v>
@@ -18614,11 +18620,11 @@
       </c>
       <c r="J93" s="164">
         <f t="shared" ca="1" si="27"/>
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="K93" s="47">
         <f t="shared" ca="1" si="28"/>
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L93" s="164" t="s">
         <v>13</v>
@@ -20514,11 +20520,11 @@
       <c r="I111" s="23"/>
       <c r="J111" s="164">
         <f t="shared" ca="1" si="30"/>
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K111" s="47">
         <f t="shared" ca="1" si="31"/>
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L111" s="164" t="s">
         <v>13</v>
@@ -21148,11 +21154,11 @@
       <c r="I117" s="138"/>
       <c r="J117" s="164">
         <f t="shared" ca="1" si="30"/>
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K117" s="47">
         <f t="shared" ca="1" si="31"/>
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L117" s="164" t="s">
         <v>1003</v>
@@ -22258,7 +22264,7 @@
       <c r="I128" s="138"/>
       <c r="J128" s="164">
         <f t="shared" ca="1" si="30"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K128" s="47">
         <f t="shared" ca="1" si="31"/>
@@ -22346,7 +22352,7 @@
       <c r="I129" s="138"/>
       <c r="J129" s="164">
         <f t="shared" ca="1" si="30"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K129" s="47">
         <f t="shared" ca="1" si="31"/>
@@ -22436,7 +22442,7 @@
       <c r="I130" s="138"/>
       <c r="J130" s="164">
         <f t="shared" ca="1" si="30"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K130" s="47">
         <f t="shared" ca="1" si="31"/>
@@ -22524,7 +22530,7 @@
       <c r="I131" s="138"/>
       <c r="J131" s="164">
         <f t="shared" ca="1" si="30"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K131" s="47">
         <f t="shared" ca="1" si="31"/>
@@ -22614,7 +22620,7 @@
       <c r="I132" s="138"/>
       <c r="J132" s="164">
         <f t="shared" ca="1" si="30"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K132" s="47">
         <f t="shared" ca="1" si="31"/>
@@ -22704,7 +22710,7 @@
       <c r="I133" s="138"/>
       <c r="J133" s="164">
         <f t="shared" ca="1" si="30"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K133" s="47">
         <f t="shared" ca="1" si="31"/>
@@ -22792,7 +22798,7 @@
       <c r="I134" s="138"/>
       <c r="J134" s="164">
         <f t="shared" ca="1" si="30"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K134" s="47">
         <f t="shared" ca="1" si="31"/>
@@ -22980,7 +22986,7 @@
       <c r="I136" s="138"/>
       <c r="J136" s="164">
         <f t="shared" ca="1" si="30"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K136" s="47">
         <f t="shared" ca="1" si="31"/>
@@ -23068,7 +23074,7 @@
       <c r="I137" s="138"/>
       <c r="J137" s="164">
         <f t="shared" ca="1" si="30"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K137" s="47">
         <f t="shared" ca="1" si="31"/>
@@ -23156,7 +23162,7 @@
       <c r="I138" s="138"/>
       <c r="J138" s="164">
         <f t="shared" ca="1" si="30"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K138" s="47">
         <f t="shared" ca="1" si="31"/>
@@ -23244,7 +23250,7 @@
       <c r="I139" s="138"/>
       <c r="J139" s="164">
         <f t="shared" ca="1" si="30"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K139" s="47">
         <f t="shared" ca="1" si="31"/>
@@ -23332,7 +23338,7 @@
       <c r="I140" s="138"/>
       <c r="J140" s="164">
         <f t="shared" ca="1" si="30"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K140" s="47">
         <f t="shared" ca="1" si="31"/>
@@ -23420,7 +23426,7 @@
       <c r="I141" s="138"/>
       <c r="J141" s="164">
         <f t="shared" ca="1" si="30"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K141" s="47">
         <f t="shared" ca="1" si="31"/>
@@ -23568,29 +23574,29 @@
       <c r="C145" s="166" t="s">
         <v>20</v>
       </c>
-      <c r="D145" s="376" t="s">
+      <c r="D145" s="416" t="s">
         <v>21</v>
       </c>
-      <c r="E145" s="376"/>
-      <c r="F145" s="377"/>
+      <c r="E145" s="416"/>
+      <c r="F145" s="417"/>
       <c r="G145" s="46"/>
       <c r="H145" s="68"/>
-      <c r="I145" s="356" t="s">
+      <c r="I145" s="392" t="s">
         <v>14</v>
       </c>
-      <c r="J145" s="357"/>
-      <c r="K145" s="357"/>
-      <c r="L145" s="357"/>
-      <c r="M145" s="357"/>
-      <c r="N145" s="358"/>
-      <c r="O145" s="362" t="s">
+      <c r="J145" s="393"/>
+      <c r="K145" s="393"/>
+      <c r="L145" s="393"/>
+      <c r="M145" s="393"/>
+      <c r="N145" s="394"/>
+      <c r="O145" s="388" t="s">
         <v>7</v>
       </c>
-      <c r="P145" s="363"/>
-      <c r="Q145" s="362" t="s">
+      <c r="P145" s="389"/>
+      <c r="Q145" s="388" t="s">
         <v>109</v>
       </c>
-      <c r="R145" s="363"/>
+      <c r="R145" s="389"/>
       <c r="S145" s="1"/>
       <c r="T145" s="1"/>
       <c r="U145" s="140"/>
@@ -23612,19 +23618,19 @@
       <c r="C146" s="167" t="s">
         <v>109</v>
       </c>
-      <c r="D146" s="354" t="s">
+      <c r="D146" s="427" t="s">
         <v>111</v>
       </c>
-      <c r="E146" s="354"/>
-      <c r="F146" s="355"/>
+      <c r="E146" s="427"/>
+      <c r="F146" s="428"/>
       <c r="G146" s="46"/>
       <c r="H146" s="46"/>
-      <c r="I146" s="356" t="s">
+      <c r="I146" s="392" t="s">
         <v>19</v>
       </c>
-      <c r="J146" s="357"/>
-      <c r="K146" s="357"/>
-      <c r="L146" s="358"/>
+      <c r="J146" s="393"/>
+      <c r="K146" s="393"/>
+      <c r="L146" s="394"/>
       <c r="M146" s="105">
         <f t="shared" ref="M146:M151" ca="1" si="89">N146/$N$146</f>
         <v>1</v>
@@ -23668,19 +23674,19 @@
       <c r="C147" s="167" t="s">
         <v>22</v>
       </c>
-      <c r="D147" s="354" t="s">
+      <c r="D147" s="427" t="s">
         <v>23</v>
       </c>
-      <c r="E147" s="354"/>
-      <c r="F147" s="355"/>
+      <c r="E147" s="427"/>
+      <c r="F147" s="428"/>
       <c r="G147" s="70"/>
       <c r="H147" s="6"/>
-      <c r="I147" s="379" t="s">
+      <c r="I147" s="418" t="s">
         <v>66</v>
       </c>
-      <c r="J147" s="380"/>
-      <c r="K147" s="380"/>
-      <c r="L147" s="381"/>
+      <c r="J147" s="419"/>
+      <c r="K147" s="419"/>
+      <c r="L147" s="420"/>
       <c r="M147" s="107">
         <f t="shared" ca="1" si="89"/>
         <v>0.49285714285714288</v>
@@ -23726,18 +23732,18 @@
       <c r="C148" s="167" t="s">
         <v>24</v>
       </c>
-      <c r="D148" s="354" t="s">
+      <c r="D148" s="427" t="s">
         <v>25</v>
       </c>
-      <c r="E148" s="354"/>
-      <c r="F148" s="355"/>
+      <c r="E148" s="427"/>
+      <c r="F148" s="428"/>
       <c r="H148" s="6"/>
-      <c r="I148" s="382" t="s">
+      <c r="I148" s="421" t="s">
         <v>67</v>
       </c>
-      <c r="J148" s="383"/>
-      <c r="K148" s="383"/>
-      <c r="L148" s="384"/>
+      <c r="J148" s="422"/>
+      <c r="K148" s="422"/>
+      <c r="L148" s="423"/>
       <c r="M148" s="109">
         <f t="shared" ca="1" si="89"/>
         <v>0.1</v>
@@ -23783,19 +23789,19 @@
       <c r="C149" s="167" t="s">
         <v>26</v>
       </c>
-      <c r="D149" s="354" t="s">
+      <c r="D149" s="427" t="s">
         <v>27</v>
       </c>
-      <c r="E149" s="354"/>
-      <c r="F149" s="355"/>
+      <c r="E149" s="427"/>
+      <c r="F149" s="428"/>
       <c r="G149" s="71"/>
       <c r="H149" s="6"/>
-      <c r="I149" s="385" t="s">
+      <c r="I149" s="424" t="s">
         <v>68</v>
       </c>
-      <c r="J149" s="386"/>
-      <c r="K149" s="386"/>
-      <c r="L149" s="387"/>
+      <c r="J149" s="425"/>
+      <c r="K149" s="425"/>
+      <c r="L149" s="426"/>
       <c r="M149" s="111">
         <f t="shared" ca="1" si="89"/>
         <v>0.19285714285714287</v>
@@ -23841,18 +23847,18 @@
       <c r="C150" s="168" t="s">
         <v>28</v>
       </c>
-      <c r="D150" s="354" t="s">
+      <c r="D150" s="427" t="s">
         <v>29</v>
       </c>
-      <c r="E150" s="354"/>
-      <c r="F150" s="355"/>
+      <c r="E150" s="427"/>
+      <c r="F150" s="428"/>
       <c r="G150" s="72"/>
-      <c r="I150" s="388" t="s">
+      <c r="I150" s="374" t="s">
         <v>70</v>
       </c>
-      <c r="J150" s="389"/>
-      <c r="K150" s="389"/>
-      <c r="L150" s="390"/>
+      <c r="J150" s="375"/>
+      <c r="K150" s="375"/>
+      <c r="L150" s="376"/>
       <c r="M150" s="114">
         <f t="shared" ca="1" si="89"/>
         <v>0.10714285714285714</v>
@@ -23900,18 +23906,18 @@
       <c r="C151" s="168" t="s">
         <v>30</v>
       </c>
-      <c r="D151" s="354" t="s">
+      <c r="D151" s="427" t="s">
         <v>31</v>
       </c>
-      <c r="E151" s="354"/>
-      <c r="F151" s="355"/>
+      <c r="E151" s="427"/>
+      <c r="F151" s="428"/>
       <c r="H151" s="6"/>
-      <c r="I151" s="391" t="s">
+      <c r="I151" s="377" t="s">
         <v>71</v>
       </c>
-      <c r="J151" s="392"/>
-      <c r="K151" s="392"/>
-      <c r="L151" s="393"/>
+      <c r="J151" s="378"/>
+      <c r="K151" s="378"/>
+      <c r="L151" s="379"/>
       <c r="M151" s="113">
         <f t="shared" ca="1" si="89"/>
         <v>0.10714285714285714</v>
@@ -23931,11 +23937,11 @@
       <c r="C152" s="168" t="s">
         <v>32</v>
       </c>
-      <c r="D152" s="354" t="s">
+      <c r="D152" s="427" t="s">
         <v>33</v>
       </c>
-      <c r="E152" s="354"/>
-      <c r="F152" s="355"/>
+      <c r="E152" s="427"/>
+      <c r="F152" s="428"/>
       <c r="H152" s="1" t="s">
         <v>11</v>
       </c>
@@ -23944,11 +23950,11 @@
       <c r="C153" s="167" t="s">
         <v>34</v>
       </c>
-      <c r="D153" s="354" t="s">
+      <c r="D153" s="427" t="s">
         <v>35</v>
       </c>
-      <c r="E153" s="354"/>
-      <c r="F153" s="355"/>
+      <c r="E153" s="427"/>
+      <c r="F153" s="428"/>
       <c r="H153" s="13"/>
       <c r="I153" s="141"/>
       <c r="J153" s="141"/>
@@ -23976,14 +23982,14 @@
       <c r="AI153" s="1"/>
     </row>
     <row r="154" spans="1:35">
-      <c r="C154" s="394" t="s">
+      <c r="C154" s="382" t="s">
         <v>75</v>
       </c>
-      <c r="D154" s="350" t="s">
+      <c r="D154" s="384" t="s">
         <v>76</v>
       </c>
-      <c r="E154" s="350"/>
-      <c r="F154" s="351"/>
+      <c r="E154" s="384"/>
+      <c r="F154" s="385"/>
       <c r="H154" s="13"/>
       <c r="J154" s="141"/>
       <c r="K154" s="13"/>
@@ -24010,10 +24016,10 @@
       <c r="AI154" s="1"/>
     </row>
     <row r="155" spans="1:35" ht="16.5" thickBot="1">
-      <c r="C155" s="395"/>
-      <c r="D155" s="352"/>
-      <c r="E155" s="352"/>
-      <c r="F155" s="353"/>
+      <c r="C155" s="383"/>
+      <c r="D155" s="386"/>
+      <c r="E155" s="386"/>
+      <c r="F155" s="387"/>
       <c r="H155" s="13"/>
       <c r="I155" s="141"/>
       <c r="J155" s="141"/>
@@ -24068,12 +24074,12 @@
       <c r="AI156" s="1"/>
     </row>
     <row r="157" spans="1:35">
-      <c r="C157" s="378" t="s">
+      <c r="C157" s="370" t="s">
         <v>41</v>
       </c>
-      <c r="D157" s="378"/>
-      <c r="E157" s="378"/>
-      <c r="F157" s="378"/>
+      <c r="D157" s="370"/>
+      <c r="E157" s="370"/>
+      <c r="F157" s="370"/>
       <c r="H157" s="13"/>
       <c r="I157" s="141"/>
       <c r="J157" s="141"/>
@@ -24104,11 +24110,11 @@
       <c r="C158" s="169" t="s">
         <v>8</v>
       </c>
-      <c r="D158" s="396" t="s">
+      <c r="D158" s="404" t="s">
         <v>91</v>
       </c>
-      <c r="E158" s="396"/>
-      <c r="F158" s="396"/>
+      <c r="E158" s="404"/>
+      <c r="F158" s="404"/>
       <c r="H158" s="13"/>
       <c r="I158" s="141"/>
       <c r="J158" s="141"/>
@@ -24139,11 +24145,11 @@
       <c r="C159" s="169" t="s">
         <v>8</v>
       </c>
-      <c r="D159" s="396" t="s">
+      <c r="D159" s="404" t="s">
         <v>92</v>
       </c>
-      <c r="E159" s="396"/>
-      <c r="F159" s="396"/>
+      <c r="E159" s="404"/>
+      <c r="F159" s="404"/>
       <c r="H159" s="13"/>
       <c r="I159" s="141"/>
       <c r="J159" s="141"/>
@@ -24174,11 +24180,11 @@
       <c r="C160" s="169" t="s">
         <v>8</v>
       </c>
-      <c r="D160" s="396" t="s">
+      <c r="D160" s="404" t="s">
         <v>93</v>
       </c>
-      <c r="E160" s="396"/>
-      <c r="F160" s="396"/>
+      <c r="E160" s="404"/>
+      <c r="F160" s="404"/>
       <c r="H160" s="13"/>
       <c r="I160" s="141"/>
       <c r="J160" s="141"/>
@@ -24233,12 +24239,12 @@
       <c r="AI161" s="1"/>
     </row>
     <row r="162" spans="3:35" ht="16.5" thickBot="1">
-      <c r="C162" s="402" t="s">
+      <c r="C162" s="408" t="s">
         <v>96</v>
       </c>
-      <c r="D162" s="403"/>
-      <c r="E162" s="403"/>
-      <c r="F162" s="404"/>
+      <c r="D162" s="409"/>
+      <c r="E162" s="409"/>
+      <c r="F162" s="410"/>
       <c r="H162" s="13"/>
       <c r="I162" s="141"/>
       <c r="J162" s="141"/>
@@ -24269,11 +24275,11 @@
       <c r="C163" s="212" t="s">
         <v>81</v>
       </c>
-      <c r="D163" s="405" t="s">
+      <c r="D163" s="411" t="s">
         <v>97</v>
       </c>
-      <c r="E163" s="405"/>
-      <c r="F163" s="406"/>
+      <c r="E163" s="411"/>
+      <c r="F163" s="412"/>
       <c r="H163" s="13"/>
       <c r="I163" s="141"/>
       <c r="J163" s="141"/>
@@ -24304,101 +24310,101 @@
       <c r="C164" s="213" t="s">
         <v>82</v>
       </c>
-      <c r="D164" s="397" t="s">
+      <c r="D164" s="402" t="s">
         <v>98</v>
       </c>
-      <c r="E164" s="397"/>
-      <c r="F164" s="398"/>
+      <c r="E164" s="402"/>
+      <c r="F164" s="403"/>
     </row>
     <row r="165" spans="3:35">
       <c r="C165" s="213" t="s">
         <v>83</v>
       </c>
-      <c r="D165" s="397" t="s">
+      <c r="D165" s="402" t="s">
         <v>99</v>
       </c>
-      <c r="E165" s="397"/>
-      <c r="F165" s="398"/>
+      <c r="E165" s="402"/>
+      <c r="F165" s="403"/>
     </row>
     <row r="166" spans="3:35">
       <c r="C166" s="214" t="s">
         <v>84</v>
       </c>
-      <c r="D166" s="397" t="s">
+      <c r="D166" s="402" t="s">
         <v>100</v>
       </c>
-      <c r="E166" s="397"/>
-      <c r="F166" s="398"/>
+      <c r="E166" s="402"/>
+      <c r="F166" s="403"/>
     </row>
     <row r="167" spans="3:35">
       <c r="C167" s="214" t="s">
         <v>85</v>
       </c>
-      <c r="D167" s="397" t="s">
+      <c r="D167" s="402" t="s">
         <v>101</v>
       </c>
-      <c r="E167" s="397"/>
-      <c r="F167" s="398"/>
+      <c r="E167" s="402"/>
+      <c r="F167" s="403"/>
     </row>
     <row r="168" spans="3:35" ht="18.75">
       <c r="C168" s="214" t="s">
         <v>86</v>
       </c>
-      <c r="D168" s="397" t="s">
+      <c r="D168" s="402" t="s">
         <v>102</v>
       </c>
-      <c r="E168" s="397"/>
-      <c r="F168" s="398"/>
+      <c r="E168" s="402"/>
+      <c r="F168" s="403"/>
     </row>
     <row r="169" spans="3:35" ht="18.75">
       <c r="C169" s="213" t="s">
         <v>87</v>
       </c>
-      <c r="D169" s="397" t="s">
+      <c r="D169" s="402" t="s">
         <v>103</v>
       </c>
-      <c r="E169" s="397"/>
-      <c r="F169" s="398"/>
+      <c r="E169" s="402"/>
+      <c r="F169" s="403"/>
     </row>
     <row r="170" spans="3:35">
       <c r="C170" s="215" t="s">
         <v>88</v>
       </c>
-      <c r="D170" s="399" t="s">
+      <c r="D170" s="405" t="s">
         <v>104</v>
       </c>
-      <c r="E170" s="400"/>
-      <c r="F170" s="401"/>
+      <c r="E170" s="406"/>
+      <c r="F170" s="407"/>
     </row>
     <row r="171" spans="3:35" ht="18.75">
       <c r="C171" s="215" t="s">
         <v>89</v>
       </c>
-      <c r="D171" s="397" t="s">
+      <c r="D171" s="402" t="s">
         <v>105</v>
       </c>
-      <c r="E171" s="397"/>
-      <c r="F171" s="398"/>
+      <c r="E171" s="402"/>
+      <c r="F171" s="403"/>
     </row>
     <row r="172" spans="3:35">
       <c r="C172" s="213" t="s">
         <v>90</v>
       </c>
-      <c r="D172" s="397" t="s">
+      <c r="D172" s="402" t="s">
         <v>106</v>
       </c>
-      <c r="E172" s="397"/>
-      <c r="F172" s="398"/>
+      <c r="E172" s="402"/>
+      <c r="F172" s="403"/>
     </row>
     <row r="173" spans="3:35" ht="16.5" thickBot="1">
       <c r="C173" s="216" t="s">
         <v>94</v>
       </c>
-      <c r="D173" s="373" t="s">
+      <c r="D173" s="413" t="s">
         <v>107</v>
       </c>
-      <c r="E173" s="374"/>
-      <c r="F173" s="375"/>
+      <c r="E173" s="414"/>
+      <c r="F173" s="415"/>
     </row>
   </sheetData>
   <autoFilter ref="A6:AE143" xr:uid="{C724CDAB-378C-47DB-9F45-08EE3BFB6E8B}">
@@ -24407,6 +24413,49 @@
     </sortState>
   </autoFilter>
   <mergeCells count="59">
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="D154:F155"/>
+    <mergeCell ref="D146:F146"/>
+    <mergeCell ref="I146:L146"/>
+    <mergeCell ref="AA4:AD4"/>
+    <mergeCell ref="Q145:R145"/>
+    <mergeCell ref="D151:F151"/>
+    <mergeCell ref="D152:F152"/>
+    <mergeCell ref="D153:F153"/>
+    <mergeCell ref="S4:U4"/>
+    <mergeCell ref="L4:L5"/>
+    <mergeCell ref="Q4:R4"/>
+    <mergeCell ref="K4:K5"/>
+    <mergeCell ref="Y4:Z4"/>
+    <mergeCell ref="D173:F173"/>
+    <mergeCell ref="D145:F145"/>
+    <mergeCell ref="C157:F157"/>
+    <mergeCell ref="O145:P145"/>
+    <mergeCell ref="I145:N145"/>
+    <mergeCell ref="I147:L147"/>
+    <mergeCell ref="I148:L148"/>
+    <mergeCell ref="I149:L149"/>
+    <mergeCell ref="I150:L150"/>
+    <mergeCell ref="I151:L151"/>
+    <mergeCell ref="C154:C155"/>
+    <mergeCell ref="D147:F147"/>
+    <mergeCell ref="D148:F148"/>
+    <mergeCell ref="D149:F149"/>
+    <mergeCell ref="D150:F150"/>
+    <mergeCell ref="D158:F158"/>
+    <mergeCell ref="D172:F172"/>
+    <mergeCell ref="D159:F159"/>
+    <mergeCell ref="D160:F160"/>
+    <mergeCell ref="D167:F167"/>
+    <mergeCell ref="D168:F168"/>
+    <mergeCell ref="D169:F169"/>
+    <mergeCell ref="D170:F170"/>
+    <mergeCell ref="D171:F171"/>
+    <mergeCell ref="C162:F162"/>
+    <mergeCell ref="D163:F163"/>
+    <mergeCell ref="D164:F164"/>
+    <mergeCell ref="D165:F165"/>
+    <mergeCell ref="D166:F166"/>
     <mergeCell ref="AG5:AG6"/>
     <mergeCell ref="AH5:AH6"/>
     <mergeCell ref="AI5:AI6"/>
@@ -24423,49 +24472,6 @@
     <mergeCell ref="V4:X4"/>
     <mergeCell ref="M4:N4"/>
     <mergeCell ref="O4:P4"/>
-    <mergeCell ref="D172:F172"/>
-    <mergeCell ref="D159:F159"/>
-    <mergeCell ref="D160:F160"/>
-    <mergeCell ref="D167:F167"/>
-    <mergeCell ref="D168:F168"/>
-    <mergeCell ref="D169:F169"/>
-    <mergeCell ref="D170:F170"/>
-    <mergeCell ref="D171:F171"/>
-    <mergeCell ref="C162:F162"/>
-    <mergeCell ref="D163:F163"/>
-    <mergeCell ref="D164:F164"/>
-    <mergeCell ref="D165:F165"/>
-    <mergeCell ref="D166:F166"/>
-    <mergeCell ref="D173:F173"/>
-    <mergeCell ref="D145:F145"/>
-    <mergeCell ref="C157:F157"/>
-    <mergeCell ref="O145:P145"/>
-    <mergeCell ref="I145:N145"/>
-    <mergeCell ref="I147:L147"/>
-    <mergeCell ref="I148:L148"/>
-    <mergeCell ref="I149:L149"/>
-    <mergeCell ref="I150:L150"/>
-    <mergeCell ref="I151:L151"/>
-    <mergeCell ref="C154:C155"/>
-    <mergeCell ref="D147:F147"/>
-    <mergeCell ref="D148:F148"/>
-    <mergeCell ref="D149:F149"/>
-    <mergeCell ref="D150:F150"/>
-    <mergeCell ref="D158:F158"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="D154:F155"/>
-    <mergeCell ref="D146:F146"/>
-    <mergeCell ref="I146:L146"/>
-    <mergeCell ref="AA4:AD4"/>
-    <mergeCell ref="Q145:R145"/>
-    <mergeCell ref="D151:F151"/>
-    <mergeCell ref="D152:F152"/>
-    <mergeCell ref="D153:F153"/>
-    <mergeCell ref="S4:U4"/>
-    <mergeCell ref="L4:L5"/>
-    <mergeCell ref="Q4:R4"/>
-    <mergeCell ref="K4:K5"/>
-    <mergeCell ref="Y4:Z4"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="A7:AE143 AG7:AI143">
@@ -25008,7 +25014,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D8E8261-1CEF-42DB-8488-C430D415EC88}">
-  <dimension ref="A1:AI53"/>
+  <dimension ref="A1:AI54"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" customWidth="1"/>
@@ -25052,7 +25058,7 @@
       </c>
       <c r="I1" s="176">
         <f ca="1">TODAY()</f>
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="J1" s="131"/>
       <c r="K1" s="197"/>
@@ -25137,88 +25143,88 @@
       <c r="AD3" s="159"/>
     </row>
     <row r="4" spans="1:35" s="5" customFormat="1" ht="36" customHeight="1" thickBot="1">
-      <c r="A4" s="408" t="s">
+      <c r="A4" s="396" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="348" t="s">
+      <c r="B4" s="350" t="s">
         <v>515</v>
       </c>
-      <c r="C4" s="414" t="s">
+      <c r="C4" s="364" t="s">
         <v>45</v>
       </c>
-      <c r="D4" s="369" t="s">
+      <c r="D4" s="352" t="s">
         <v>46</v>
       </c>
-      <c r="E4" s="412" t="s">
+      <c r="E4" s="400" t="s">
         <v>47</v>
       </c>
-      <c r="F4" s="369" t="s">
+      <c r="F4" s="352" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="410" t="s">
+      <c r="G4" s="398" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="366" t="s">
+      <c r="H4" s="358" t="s">
         <v>48</v>
       </c>
-      <c r="I4" s="366" t="s">
+      <c r="I4" s="358" t="s">
         <v>49</v>
       </c>
-      <c r="J4" s="369" t="s">
+      <c r="J4" s="352" t="s">
         <v>78</v>
       </c>
-      <c r="K4" s="366" t="s">
+      <c r="K4" s="358" t="s">
         <v>80</v>
       </c>
-      <c r="L4" s="364" t="s">
+      <c r="L4" s="363" t="s">
         <v>53</v>
       </c>
-      <c r="M4" s="365"/>
-      <c r="N4" s="368" t="s">
+      <c r="M4" s="348"/>
+      <c r="N4" s="362" t="s">
         <v>55</v>
       </c>
-      <c r="O4" s="365"/>
-      <c r="P4" s="368" t="s">
+      <c r="O4" s="348"/>
+      <c r="P4" s="362" t="s">
         <v>72</v>
       </c>
-      <c r="Q4" s="365"/>
-      <c r="R4" s="364" t="s">
+      <c r="Q4" s="348"/>
+      <c r="R4" s="363" t="s">
         <v>53</v>
       </c>
-      <c r="S4" s="364"/>
-      <c r="T4" s="365"/>
-      <c r="U4" s="368" t="s">
+      <c r="S4" s="363"/>
+      <c r="T4" s="348"/>
+      <c r="U4" s="362" t="s">
         <v>55</v>
       </c>
-      <c r="V4" s="364"/>
-      <c r="W4" s="365"/>
-      <c r="X4" s="371" t="s">
+      <c r="V4" s="363"/>
+      <c r="W4" s="348"/>
+      <c r="X4" s="366" t="s">
         <v>72</v>
       </c>
-      <c r="Y4" s="417"/>
-      <c r="Z4" s="371" t="s">
+      <c r="Y4" s="442"/>
+      <c r="Z4" s="366" t="s">
         <v>112</v>
       </c>
-      <c r="AA4" s="360"/>
-      <c r="AB4" s="360"/>
-      <c r="AC4" s="361"/>
-      <c r="AD4" s="369" t="s">
+      <c r="AA4" s="430"/>
+      <c r="AB4" s="430"/>
+      <c r="AC4" s="431"/>
+      <c r="AD4" s="352" t="s">
         <v>79</v>
       </c>
       <c r="AG4" s="236"/>
     </row>
     <row r="5" spans="1:35" ht="78.75">
-      <c r="A5" s="409"/>
-      <c r="B5" s="349"/>
-      <c r="C5" s="415"/>
-      <c r="D5" s="370"/>
-      <c r="E5" s="413"/>
-      <c r="F5" s="370"/>
-      <c r="G5" s="411"/>
-      <c r="H5" s="367"/>
-      <c r="I5" s="367"/>
-      <c r="J5" s="370"/>
-      <c r="K5" s="367"/>
+      <c r="A5" s="397"/>
+      <c r="B5" s="351"/>
+      <c r="C5" s="365"/>
+      <c r="D5" s="353"/>
+      <c r="E5" s="401"/>
+      <c r="F5" s="353"/>
+      <c r="G5" s="399"/>
+      <c r="H5" s="359"/>
+      <c r="I5" s="359"/>
+      <c r="J5" s="353"/>
+      <c r="K5" s="359"/>
       <c r="L5" s="79" t="s">
         <v>52</v>
       </c>
@@ -25273,14 +25279,14 @@
       <c r="AC5" s="250" t="s">
         <v>118</v>
       </c>
-      <c r="AD5" s="416"/>
-      <c r="AG5" s="422" t="s">
+      <c r="AD5" s="349"/>
+      <c r="AG5" s="432" t="s">
         <v>119</v>
       </c>
-      <c r="AH5" s="424" t="s">
+      <c r="AH5" s="434" t="s">
         <v>120</v>
       </c>
-      <c r="AI5" s="426" t="s">
+      <c r="AI5" s="436" t="s">
         <v>121</v>
       </c>
     </row>
@@ -25315,13 +25321,13 @@
       <c r="AB6" s="86"/>
       <c r="AC6" s="86"/>
       <c r="AD6" s="74"/>
-      <c r="AG6" s="423"/>
-      <c r="AH6" s="425"/>
-      <c r="AI6" s="427"/>
+      <c r="AG6" s="433"/>
+      <c r="AH6" s="435"/>
+      <c r="AI6" s="437"/>
     </row>
     <row r="7" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A7" s="33">
-        <f t="shared" ref="A7:A40" si="0">A6+1</f>
+        <f t="shared" ref="A7:A41" si="0">A6+1</f>
         <v>1</v>
       </c>
       <c r="B7" s="33" t="str">
@@ -25335,7 +25341,7 @@
         <v>519</v>
       </c>
       <c r="E7" s="174">
-        <f t="shared" ref="E7:E40" si="2">IF($T7=0,$S7+22,$T7+21)</f>
+        <f t="shared" ref="E7:E41" si="2">IF($T7=0,$S7+22,$T7+21)</f>
         <v>45490</v>
       </c>
       <c r="F7" s="30" t="s">
@@ -25421,8 +25427,8 @@
       <c r="AH7" s="242" t="b" cm="1">
         <f t="array" ref="AH7">$D7=_xlfn.XLOOKUP(
 AG7,
-_xlfn._xlws.FILTER($AG$7:$AG$4869,$K$7:$K$4869&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4869,$K$7:$K$4869&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4870,$K$7:$K$4870&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4870,$K$7:$K$4870&lt;&gt;"X"),
 "",
 0,
 -1
@@ -25467,7 +25473,7 @@
         <v>25</v>
       </c>
       <c r="J8" s="47">
-        <f t="shared" ref="J8:J40" si="4">IF(($I8-21)&gt;0,$I8-21,0)</f>
+        <f t="shared" ref="J8:J41" si="4">IF(($I8-21)&gt;0,$I8-21,0)</f>
         <v>4</v>
       </c>
       <c r="K8" s="164"/>
@@ -25514,14 +25520,14 @@
         <v>45674</v>
       </c>
       <c r="Z8" s="29">
-        <f t="shared" ref="Z8:Z42" si="5">IF(AND($Q8="",$H8=""),"",IF(OR($Q8="B",$Q8="C"),IF($Y8&lt;&gt;"",$Y8+7,IF($X8&lt;&gt;"",$X8+8,"")),IF($Q8="",IF(OR($H8="B",$H8="C"),IF($V8&lt;&gt;"",$V8+7,IF($U8&lt;&gt;"",$U8+8,""))),"")))</f>
+        <f t="shared" ref="Z8:Z43" si="5">IF(AND($Q8="",$H8=""),"",IF(OR($Q8="B",$Q8="C"),IF($Y8&lt;&gt;"",$Y8+7,IF($X8&lt;&gt;"",$X8+8,"")),IF($Q8="",IF(OR($H8="B",$H8="C"),IF($V8&lt;&gt;"",$V8+7,IF($U8&lt;&gt;"",$U8+8,""))),"")))</f>
         <v>45681</v>
       </c>
       <c r="AA8" s="229">
         <v>45850</v>
       </c>
       <c r="AB8" s="229" t="str">
-        <f t="shared" ref="AB8:AB40" si="6">IF(OR($Q8="B",$Q8="C"),IF($Z8="","",IF($AA8="",IF($Z8&gt;=$I$1,"In progress","Not submit yet"),IF($Z8&gt;=$AA8,"Timely Response","Late Resubmission"))),"")</f>
+        <f t="shared" ref="AB8:AB41" si="6">IF(OR($Q8="B",$Q8="C"),IF($Z8="","",IF($AA8="",IF($Z8&gt;=$I$1,"In progress","Not submit yet"),IF($Z8&gt;=$AA8,"Timely Response","Late Resubmission"))),"")</f>
         <v>Late Resubmission</v>
       </c>
       <c r="AC8" s="183">
@@ -25530,14 +25536,14 @@
       </c>
       <c r="AD8" s="92"/>
       <c r="AG8" s="238" t="str">
-        <f t="shared" ref="AG8:AG40" si="8">IF(AND(RIGHT($D8,1)&gt;="A",RIGHT($D8,1)&lt;="Z"),LEFT($D8,LEN($D8)-1),$D8)</f>
+        <f t="shared" ref="AG8:AG41" si="8">IF(AND(RIGHT($D8,1)&gt;="A",RIGHT($D8,1)&lt;="Z"),LEFT($D8,LEN($D8)-1),$D8)</f>
         <v>LTIA-5.10-VIETUR-80000-RFA-SDS-0122</v>
       </c>
       <c r="AH8" s="243" t="b" cm="1">
         <f t="array" ref="AH8">$D8=_xlfn.XLOOKUP(
 AG8,
-_xlfn._xlws.FILTER($AG$7:$AG$4869,$K$7:$K$4869&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4869,$K$7:$K$4869&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4870,$K$7:$K$4870&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4870,$K$7:$K$4870&lt;&gt;"X"),
 "",
 0,
 -1
@@ -25658,8 +25664,8 @@
       <c r="AH9" s="243" t="b" cm="1">
         <f t="array" ref="AH9">$D9=_xlfn.XLOOKUP(
 AG9,
-_xlfn._xlws.FILTER($AG$7:$AG$4869,$K$7:$K$4869&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4869,$K$7:$K$4869&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4870,$K$7:$K$4870&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4870,$K$7:$K$4870&lt;&gt;"X"),
 "",
 0,
 -1
@@ -25773,8 +25779,8 @@
       <c r="AH10" s="243" t="b" cm="1">
         <f t="array" ref="AH10">$D10=_xlfn.XLOOKUP(
 AG10,
-_xlfn._xlws.FILTER($AG$7:$AG$4869,$K$7:$K$4869&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4869,$K$7:$K$4869&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4870,$K$7:$K$4870&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4870,$K$7:$K$4870&lt;&gt;"X"),
 "",
 0,
 -1
@@ -25890,8 +25896,8 @@
       <c r="AH11" s="243" t="b" cm="1">
         <f t="array" ref="AH11">$D11=_xlfn.XLOOKUP(
 AG11,
-_xlfn._xlws.FILTER($AG$7:$AG$4869,$K$7:$K$4869&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4869,$K$7:$K$4869&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4870,$K$7:$K$4870&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4870,$K$7:$K$4870&lt;&gt;"X"),
 "",
 0,
 -1
@@ -25993,7 +25999,7 @@
       </c>
       <c r="AC12" s="183">
         <f t="shared" ca="1" si="7"/>
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AD12" s="92"/>
       <c r="AG12" s="238" t="str">
@@ -26003,8 +26009,8 @@
       <c r="AH12" s="243" t="b" cm="1">
         <f t="array" ref="AH12">$D12=_xlfn.XLOOKUP(
 AG12,
-_xlfn._xlws.FILTER($AG$7:$AG$4869,$K$7:$K$4869&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4869,$K$7:$K$4869&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4870,$K$7:$K$4870&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4870,$K$7:$K$4870&lt;&gt;"X"),
 "",
 0,
 -1
@@ -26116,8 +26122,8 @@
       <c r="AH13" s="243" t="b" cm="1">
         <f t="array" ref="AH13">$D13=_xlfn.XLOOKUP(
 AG13,
-_xlfn._xlws.FILTER($AG$7:$AG$4869,$K$7:$K$4869&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4869,$K$7:$K$4869&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4870,$K$7:$K$4870&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4870,$K$7:$K$4870&lt;&gt;"X"),
 "",
 0,
 -1
@@ -26158,7 +26164,7 @@
         <v>2</v>
       </c>
       <c r="I14" s="164">
-        <f t="shared" ref="I14:I40" si="10">IF(ISBLANK($V14),_xlfn.DAYS($I$1,$T14),_xlfn.DAYS($V14,$T14))</f>
+        <f t="shared" ref="I14:I41" si="10">IF(ISBLANK($V14),_xlfn.DAYS($I$1,$T14),_xlfn.DAYS($V14,$T14))</f>
         <v>25</v>
       </c>
       <c r="J14" s="47">
@@ -26219,7 +26225,7 @@
       </c>
       <c r="AC14" s="183">
         <f t="shared" ca="1" si="7"/>
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AD14" s="92"/>
       <c r="AG14" s="238" t="str">
@@ -26229,8 +26235,8 @@
       <c r="AH14" s="243" t="b" cm="1">
         <f t="array" ref="AH14">$D14=_xlfn.XLOOKUP(
 AG14,
-_xlfn._xlws.FILTER($AG$7:$AG$4869,$K$7:$K$4869&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4869,$K$7:$K$4869&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4870,$K$7:$K$4870&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4870,$K$7:$K$4870&lt;&gt;"X"),
 "",
 0,
 -1
@@ -26342,8 +26348,8 @@
       <c r="AH15" s="243" t="b" cm="1">
         <f t="array" ref="AH15">$D15=_xlfn.XLOOKUP(
 AG15,
-_xlfn._xlws.FILTER($AG$7:$AG$4869,$K$7:$K$4869&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4869,$K$7:$K$4869&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4870,$K$7:$K$4870&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4870,$K$7:$K$4870&lt;&gt;"X"),
 "",
 0,
 -1
@@ -26445,7 +26451,7 @@
       </c>
       <c r="AC16" s="183">
         <f t="shared" ca="1" si="7"/>
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AD16" s="92"/>
       <c r="AG16" s="238" t="str">
@@ -26455,8 +26461,8 @@
       <c r="AH16" s="243" t="b" cm="1">
         <f t="array" ref="AH16">$D16=_xlfn.XLOOKUP(
 AG16,
-_xlfn._xlws.FILTER($AG$7:$AG$4869,$K$7:$K$4869&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4869,$K$7:$K$4869&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4870,$K$7:$K$4870&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4870,$K$7:$K$4870&lt;&gt;"X"),
 "",
 0,
 -1
@@ -26558,7 +26564,7 @@
       </c>
       <c r="AC17" s="183">
         <f t="shared" ca="1" si="7"/>
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AD17" s="92"/>
       <c r="AG17" s="238" t="str">
@@ -26568,8 +26574,8 @@
       <c r="AH17" s="243" t="b" cm="1">
         <f t="array" ref="AH17">$D17=_xlfn.XLOOKUP(
 AG17,
-_xlfn._xlws.FILTER($AG$7:$AG$4869,$K$7:$K$4869&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4869,$K$7:$K$4869&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4870,$K$7:$K$4870&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4870,$K$7:$K$4870&lt;&gt;"X"),
 "",
 0,
 -1
@@ -26671,7 +26677,7 @@
       </c>
       <c r="AC18" s="183">
         <f t="shared" ca="1" si="7"/>
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AD18" s="92"/>
       <c r="AG18" s="238" t="str">
@@ -26681,8 +26687,8 @@
       <c r="AH18" s="243" t="b" cm="1">
         <f t="array" ref="AH18">$D18=_xlfn.XLOOKUP(
 AG18,
-_xlfn._xlws.FILTER($AG$7:$AG$4869,$K$7:$K$4869&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4869,$K$7:$K$4869&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4870,$K$7:$K$4870&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4870,$K$7:$K$4870&lt;&gt;"X"),
 "",
 0,
 -1
@@ -26796,8 +26802,8 @@
       <c r="AH19" s="243" t="b" cm="1">
         <f t="array" ref="AH19">$D19=_xlfn.XLOOKUP(
 AG19,
-_xlfn._xlws.FILTER($AG$7:$AG$4869,$K$7:$K$4869&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4869,$K$7:$K$4869&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4870,$K$7:$K$4870&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4870,$K$7:$K$4870&lt;&gt;"X"),
 "",
 0,
 -1
@@ -26911,8 +26917,8 @@
       <c r="AH20" s="243" t="b" cm="1">
         <f t="array" ref="AH20">$D20=_xlfn.XLOOKUP(
 AG20,
-_xlfn._xlws.FILTER($AG$7:$AG$4869,$K$7:$K$4869&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4869,$K$7:$K$4869&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4870,$K$7:$K$4870&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4870,$K$7:$K$4870&lt;&gt;"X"),
 "",
 0,
 -1
@@ -27028,8 +27034,8 @@
       <c r="AH21" s="243" t="b" cm="1">
         <f t="array" ref="AH21">$D21=_xlfn.XLOOKUP(
 AG21,
-_xlfn._xlws.FILTER($AG$7:$AG$4869,$K$7:$K$4869&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4869,$K$7:$K$4869&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4870,$K$7:$K$4870&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4870,$K$7:$K$4870&lt;&gt;"X"),
 "",
 0,
 -1
@@ -27143,8 +27149,8 @@
       <c r="AH22" s="243" t="b" cm="1">
         <f t="array" ref="AH22">$D22=_xlfn.XLOOKUP(
 AG22,
-_xlfn._xlws.FILTER($AG$7:$AG$4869,$K$7:$K$4869&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4869,$K$7:$K$4869&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4870,$K$7:$K$4870&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4870,$K$7:$K$4870&lt;&gt;"X"),
 "",
 0,
 -1
@@ -27246,7 +27252,7 @@
       </c>
       <c r="AC23" s="183">
         <f t="shared" ca="1" si="7"/>
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AD23" s="92"/>
       <c r="AG23" s="238" t="str">
@@ -27256,8 +27262,8 @@
       <c r="AH23" s="243" t="b" cm="1">
         <f t="array" ref="AH23">$D23=_xlfn.XLOOKUP(
 AG23,
-_xlfn._xlws.FILTER($AG$7:$AG$4869,$K$7:$K$4869&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4869,$K$7:$K$4869&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4870,$K$7:$K$4870&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4870,$K$7:$K$4870&lt;&gt;"X"),
 "",
 0,
 -1
@@ -27359,7 +27365,7 @@
       </c>
       <c r="AC24" s="183">
         <f t="shared" ca="1" si="7"/>
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AD24" s="92"/>
       <c r="AG24" s="238" t="str">
@@ -27369,8 +27375,8 @@
       <c r="AH24" s="243" t="b" cm="1">
         <f t="array" ref="AH24">$D24=_xlfn.XLOOKUP(
 AG24,
-_xlfn._xlws.FILTER($AG$7:$AG$4869,$K$7:$K$4869&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4869,$K$7:$K$4869&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4870,$K$7:$K$4870&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4870,$K$7:$K$4870&lt;&gt;"X"),
 "",
 0,
 -1
@@ -27463,14 +27469,16 @@
         <f t="shared" si="5"/>
         <v>46037</v>
       </c>
-      <c r="AA25" s="229"/>
+      <c r="AA25" s="229">
+        <v>46311</v>
+      </c>
       <c r="AB25" s="229" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v>Not submit yet</v>
+        <f t="shared" si="6"/>
+        <v>Late Resubmission</v>
       </c>
       <c r="AC25" s="183">
-        <f t="shared" ca="1" si="7"/>
-        <v>277</v>
+        <f t="shared" si="7"/>
+        <v>274</v>
       </c>
       <c r="AD25" s="92" t="s">
         <v>887</v>
@@ -27482,240 +27490,240 @@
       <c r="AH25" s="243" t="b" cm="1">
         <f t="array" ref="AH25">$D25=_xlfn.XLOOKUP(
 AG25,
-_xlfn._xlws.FILTER($AG$7:$AG$4869,$K$7:$K$4869&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4869,$K$7:$K$4869&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4870,$K$7:$K$4870&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4870,$K$7:$K$4870&lt;&gt;"X"),
+"",
+0,
+-1
+)</f>
+        <v>0</v>
+      </c>
+      <c r="AI25" s="75" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="1:35" s="9" customFormat="1" ht="47.25">
+      <c r="A26" s="33">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="B26" s="33" t="str">
+        <f t="shared" si="1"/>
+        <v>5.10</v>
+      </c>
+      <c r="C26" s="137" t="s">
+        <v>195</v>
+      </c>
+      <c r="D26" s="25" t="s">
+        <v>582</v>
+      </c>
+      <c r="E26" s="174">
+        <f t="shared" si="2"/>
+        <v>45953</v>
+      </c>
+      <c r="F26" s="31" t="s">
+        <v>583</v>
+      </c>
+      <c r="G26" s="21" t="s">
+        <v>584</v>
+      </c>
+      <c r="H26" s="138" t="s">
+        <v>2</v>
+      </c>
+      <c r="I26" s="164">
+        <f t="shared" si="10"/>
+        <v>13</v>
+      </c>
+      <c r="J26" s="47">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K26" s="164"/>
+      <c r="L26" s="54" t="s">
+        <v>8</v>
+      </c>
+      <c r="M26" s="65" t="s">
+        <v>8</v>
+      </c>
+      <c r="N26" s="40" t="s">
+        <v>12</v>
+      </c>
+      <c r="O26" s="41" t="s">
+        <v>8</v>
+      </c>
+      <c r="P26" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q26" s="155" t="s">
+        <v>2</v>
+      </c>
+      <c r="R26" s="27">
+        <v>45930</v>
+      </c>
+      <c r="S26" s="27">
+        <v>45930</v>
+      </c>
+      <c r="T26" s="188">
+        <v>45932</v>
+      </c>
+      <c r="U26" s="29">
+        <v>45940</v>
+      </c>
+      <c r="V26" s="188">
+        <v>45945</v>
+      </c>
+      <c r="W26" s="235" t="s">
+        <v>581</v>
+      </c>
+      <c r="X26" s="230">
+        <v>45978</v>
+      </c>
+      <c r="Y26" s="227">
+        <v>45979</v>
+      </c>
+      <c r="Z26" s="29">
+        <f t="shared" si="5"/>
+        <v>45986</v>
+      </c>
+      <c r="AA26" s="229"/>
+      <c r="AB26" s="229" t="str">
+        <f t="shared" ca="1" si="6"/>
+        <v>Not submit yet</v>
+      </c>
+      <c r="AC26" s="183">
+        <f t="shared" ca="1" si="7"/>
+        <v>329</v>
+      </c>
+      <c r="AD26" s="92"/>
+      <c r="AG26" s="238" t="str">
+        <f t="shared" si="8"/>
+        <v>LTIA-5.10-VIETUR-80000-RFA-SDS-0371</v>
+      </c>
+      <c r="AH26" s="243" t="b" cm="1">
+        <f t="array" ref="AH26">$D26=_xlfn.XLOOKUP(
+AG26,
+_xlfn._xlws.FILTER($AG$7:$AG$4870,$K$7:$K$4870&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4870,$K$7:$K$4870&lt;&gt;"X"),
 "",
 0,
 -1
 )</f>
         <v>1</v>
       </c>
-      <c r="AI25" s="75" t="str">
+      <c r="AI26" s="75" t="str">
         <f t="shared" si="9"/>
         <v>YES</v>
       </c>
     </row>
-    <row r="26" spans="1:35" s="9" customFormat="1" ht="47.25">
-      <c r="A26" s="33">
+    <row r="27" spans="1:35" s="9" customFormat="1" ht="47.25">
+      <c r="A27" s="33">
         <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="B26" s="33" t="str">
+        <v>21</v>
+      </c>
+      <c r="B27" s="33" t="str">
         <f t="shared" si="1"/>
         <v>5.10</v>
       </c>
-      <c r="C26" s="137" t="s">
-        <v>195</v>
-      </c>
-      <c r="D26" s="25" t="s">
-        <v>582</v>
-      </c>
-      <c r="E26" s="174">
+      <c r="C27" s="137" t="s">
+        <v>131</v>
+      </c>
+      <c r="D27" s="25" t="s">
+        <v>585</v>
+      </c>
+      <c r="E27" s="174">
         <f t="shared" si="2"/>
-        <v>45953</v>
-      </c>
-      <c r="F26" s="31" t="s">
-        <v>583</v>
-      </c>
-      <c r="G26" s="21" t="s">
-        <v>584</v>
-      </c>
-      <c r="H26" s="138" t="s">
+        <v>45982</v>
+      </c>
+      <c r="F27" s="31" t="s">
+        <v>537</v>
+      </c>
+      <c r="G27" s="21" t="s">
+        <v>538</v>
+      </c>
+      <c r="H27" s="138" t="s">
         <v>2</v>
       </c>
-      <c r="I26" s="164">
+      <c r="I27" s="164">
         <f t="shared" si="10"/>
-        <v>13</v>
-      </c>
-      <c r="J26" s="47">
+        <v>19</v>
+      </c>
+      <c r="J27" s="47">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K26" s="164"/>
-      <c r="L26" s="54" t="s">
-        <v>8</v>
-      </c>
-      <c r="M26" s="65" t="s">
-        <v>8</v>
-      </c>
-      <c r="N26" s="40" t="s">
-        <v>12</v>
-      </c>
-      <c r="O26" s="41" t="s">
-        <v>8</v>
-      </c>
-      <c r="P26" s="40" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q26" s="155" t="s">
+      <c r="K27" s="164"/>
+      <c r="L27" s="54" t="s">
+        <v>8</v>
+      </c>
+      <c r="M27" s="65" t="s">
+        <v>8</v>
+      </c>
+      <c r="N27" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="O27" s="41" t="s">
+        <v>8</v>
+      </c>
+      <c r="P27" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q27" s="155" t="s">
         <v>2</v>
       </c>
-      <c r="R26" s="27">
-        <v>45930</v>
-      </c>
-      <c r="S26" s="27">
-        <v>45930</v>
-      </c>
-      <c r="T26" s="188">
-        <v>45932</v>
-      </c>
-      <c r="U26" s="29">
-        <v>45940</v>
-      </c>
-      <c r="V26" s="188">
+      <c r="R27" s="27">
+        <v>45959</v>
+      </c>
+      <c r="S27" s="27">
+        <v>45959</v>
+      </c>
+      <c r="T27" s="188">
+        <v>45961</v>
+      </c>
+      <c r="U27" s="29">
         <v>45945</v>
       </c>
-      <c r="W26" s="235" t="s">
-        <v>581</v>
-      </c>
-      <c r="X26" s="230">
-        <v>45978</v>
-      </c>
-      <c r="Y26" s="227">
-        <v>45979</v>
-      </c>
-      <c r="Z26" s="29">
+      <c r="V27" s="188">
+        <v>45980</v>
+      </c>
+      <c r="W27" s="235" t="s">
+        <v>190</v>
+      </c>
+      <c r="X27" s="230">
+        <v>45995</v>
+      </c>
+      <c r="Y27" s="227">
+        <v>45999</v>
+      </c>
+      <c r="Z27" s="29">
         <f t="shared" si="5"/>
-        <v>45986</v>
-      </c>
-      <c r="AA26" s="229"/>
-      <c r="AB26" s="229" t="str">
+        <v>46006</v>
+      </c>
+      <c r="AA27" s="229"/>
+      <c r="AB27" s="229" t="str">
         <f t="shared" ca="1" si="6"/>
         <v>Not submit yet</v>
       </c>
-      <c r="AC26" s="183">
+      <c r="AC27" s="183">
         <f t="shared" ca="1" si="7"/>
-        <v>328</v>
-      </c>
-      <c r="AD26" s="92"/>
-      <c r="AG26" s="238" t="str">
+        <v>309</v>
+      </c>
+      <c r="AD27" s="92"/>
+      <c r="AG27" s="238" t="str">
         <f t="shared" si="8"/>
-        <v>LTIA-5.10-VIETUR-80000-RFA-SDS-0371</v>
-      </c>
-      <c r="AH26" s="243" t="b" cm="1">
-        <f t="array" ref="AH26">$D26=_xlfn.XLOOKUP(
-AG26,
-_xlfn._xlws.FILTER($AG$7:$AG$4869,$K$7:$K$4869&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4869,$K$7:$K$4869&lt;&gt;"X"),
+        <v>LTIA-5.10-VIETUR-80000-RFA-SDS-0197</v>
+      </c>
+      <c r="AH27" s="243" t="b" cm="1">
+        <f t="array" ref="AH27">$D27=_xlfn.XLOOKUP(
+AG27,
+_xlfn._xlws.FILTER($AG$7:$AG$4870,$K$7:$K$4870&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4870,$K$7:$K$4870&lt;&gt;"X"),
 "",
 0,
 -1
 )</f>
         <v>1</v>
       </c>
-      <c r="AI26" s="75" t="str">
-        <f t="shared" si="9"/>
-        <v>YES</v>
-      </c>
-    </row>
-    <row r="27" spans="1:35" s="9" customFormat="1" ht="47.25">
-      <c r="A27" s="33">
-        <f t="shared" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="B27" s="33" t="str">
-        <f t="shared" si="1"/>
-        <v>5.10</v>
-      </c>
-      <c r="C27" s="137" t="s">
-        <v>131</v>
-      </c>
-      <c r="D27" s="25" t="s">
-        <v>585</v>
-      </c>
-      <c r="E27" s="174">
-        <f t="shared" si="2"/>
-        <v>45982</v>
-      </c>
-      <c r="F27" s="31" t="s">
-        <v>537</v>
-      </c>
-      <c r="G27" s="21" t="s">
-        <v>538</v>
-      </c>
-      <c r="H27" s="138" t="s">
-        <v>2</v>
-      </c>
-      <c r="I27" s="164">
-        <f t="shared" si="10"/>
-        <v>19</v>
-      </c>
-      <c r="J27" s="47">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="K27" s="164"/>
-      <c r="L27" s="54" t="s">
-        <v>8</v>
-      </c>
-      <c r="M27" s="65" t="s">
-        <v>8</v>
-      </c>
-      <c r="N27" s="40" t="s">
-        <v>8</v>
-      </c>
-      <c r="O27" s="41" t="s">
-        <v>8</v>
-      </c>
-      <c r="P27" s="40" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q27" s="155" t="s">
-        <v>2</v>
-      </c>
-      <c r="R27" s="27">
-        <v>45959</v>
-      </c>
-      <c r="S27" s="27">
-        <v>45959</v>
-      </c>
-      <c r="T27" s="188">
-        <v>45961</v>
-      </c>
-      <c r="U27" s="29">
-        <v>45945</v>
-      </c>
-      <c r="V27" s="188">
-        <v>45980</v>
-      </c>
-      <c r="W27" s="235" t="s">
-        <v>190</v>
-      </c>
-      <c r="X27" s="230">
-        <v>45995</v>
-      </c>
-      <c r="Y27" s="227">
-        <v>45999</v>
-      </c>
-      <c r="Z27" s="29">
-        <f t="shared" si="5"/>
-        <v>46006</v>
-      </c>
-      <c r="AA27" s="229"/>
-      <c r="AB27" s="229" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v>Not submit yet</v>
-      </c>
-      <c r="AC27" s="183">
-        <f t="shared" ca="1" si="7"/>
-        <v>308</v>
-      </c>
-      <c r="AD27" s="92"/>
-      <c r="AG27" s="238" t="str">
-        <f t="shared" si="8"/>
-        <v>LTIA-5.10-VIETUR-80000-RFA-SDS-0197</v>
-      </c>
-      <c r="AH27" s="243" t="b" cm="1">
-        <f t="array" ref="AH27">$D27=_xlfn.XLOOKUP(
-AG27,
-_xlfn._xlws.FILTER($AG$7:$AG$4869,$K$7:$K$4869&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4869,$K$7:$K$4869&lt;&gt;"X"),
-"",
-0,
--1
-)</f>
-        <v>1</v>
-      </c>
       <c r="AI27" s="75" t="str">
         <f t="shared" si="9"/>
         <v>YES</v>
@@ -27823,8 +27831,8 @@
       <c r="AH28" s="243" t="b" cm="1">
         <f t="array" ref="AH28">$D28=_xlfn.XLOOKUP(
 AG28,
-_xlfn._xlws.FILTER($AG$7:$AG$4869,$K$7:$K$4869&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4869,$K$7:$K$4869&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4870,$K$7:$K$4870&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4870,$K$7:$K$4870&lt;&gt;"X"),
 "",
 0,
 -1
@@ -27914,8 +27922,8 @@
       <c r="AH29" s="243" t="b" cm="1">
         <f t="array" ref="AH29">$D29=_xlfn.XLOOKUP(
 AG29,
-_xlfn._xlws.FILTER($AG$7:$AG$4869,$K$7:$K$4869&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4869,$K$7:$K$4869&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4870,$K$7:$K$4870&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4870,$K$7:$K$4870&lt;&gt;"X"),
 "",
 0,
 -1
@@ -28017,7 +28025,7 @@
       </c>
       <c r="AC30" s="183">
         <f t="shared" ca="1" si="7"/>
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AD30" s="92" t="s">
         <v>593</v>
@@ -28029,8 +28037,8 @@
       <c r="AH30" s="243" t="b" cm="1">
         <f t="array" ref="AH30">$D30=_xlfn.XLOOKUP(
 AG30,
-_xlfn._xlws.FILTER($AG$7:$AG$4869,$K$7:$K$4869&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4869,$K$7:$K$4869&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4870,$K$7:$K$4870&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4870,$K$7:$K$4870&lt;&gt;"X"),
 "",
 0,
 -1
@@ -28072,11 +28080,11 @@
       </c>
       <c r="I31" s="164">
         <f ca="1">IF(ISBLANK($V31),_xlfn.DAYS($I$1,$T31),_xlfn.DAYS($V31,$T31))</f>
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="J31" s="47">
         <f t="shared" ca="1" si="4"/>
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="K31" s="164"/>
       <c r="L31" s="54" t="s">
@@ -28126,8 +28134,8 @@
       <c r="AH31" s="243" t="b" cm="1">
         <f t="array" ref="AH31">$D31=_xlfn.XLOOKUP(
 AG31,
-_xlfn._xlws.FILTER($AG$7:$AG$4869,$K$7:$K$4869&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4869,$K$7:$K$4869&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4870,$K$7:$K$4870&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4870,$K$7:$K$4870&lt;&gt;"X"),
 "",
 0,
 -1
@@ -28243,8 +28251,8 @@
       <c r="AH32" s="243" t="b" cm="1">
         <f t="array" ref="AH32">$D32=_xlfn.XLOOKUP(
 AG32,
-_xlfn._xlws.FILTER($AG$7:$AG$4869,$K$7:$K$4869&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4869,$K$7:$K$4869&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4870,$K$7:$K$4870&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4870,$K$7:$K$4870&lt;&gt;"X"),
 "",
 0,
 -1
@@ -28348,8 +28356,8 @@
       <c r="AH33" s="243" t="b" cm="1">
         <f t="array" ref="AH33">$D33=_xlfn.XLOOKUP(
 AG33,
-_xlfn._xlws.FILTER($AG$7:$AG$4869,$K$7:$K$4869&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4869,$K$7:$K$4869&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4870,$K$7:$K$4870&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4870,$K$7:$K$4870&lt;&gt;"X"),
 "",
 0,
 -1
@@ -28434,8 +28442,8 @@
       <c r="AH34" s="243" t="b" cm="1">
         <f t="array" ref="AH34">$D34=_xlfn.XLOOKUP(
 AG34,
-_xlfn._xlws.FILTER($AG$7:$AG$4869,$K$7:$K$4869&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4869,$K$7:$K$4869&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4870,$K$7:$K$4870&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4870,$K$7:$K$4870&lt;&gt;"X"),
 "",
 0,
 -1
@@ -28475,7 +28483,7 @@
       <c r="H35" s="138"/>
       <c r="I35" s="164">
         <f t="shared" ca="1" si="10"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J35" s="47">
         <f t="shared" ca="1" si="4"/>
@@ -28527,8 +28535,8 @@
       <c r="AH35" s="243" t="b" cm="1">
         <f t="array" ref="AH35">$D35=_xlfn.XLOOKUP(
 AG35,
-_xlfn._xlws.FILTER($AG$7:$AG$4869,$K$7:$K$4869&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4869,$K$7:$K$4869&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4870,$K$7:$K$4870&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4870,$K$7:$K$4870&lt;&gt;"X"),
 "",
 0,
 -1
@@ -28630,8 +28638,8 @@
       <c r="AH36" s="243" t="b" cm="1">
         <f t="array" ref="AH36">$D36=_xlfn.XLOOKUP(
 AG36,
-_xlfn._xlws.FILTER($AG$7:$AG$4869,$K$7:$K$4869&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4869,$K$7:$K$4869&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4870,$K$7:$K$4870&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4870,$K$7:$K$4870&lt;&gt;"X"),
 "",
 0,
 -1
@@ -28671,11 +28679,11 @@
       </c>
       <c r="I37" s="164">
         <f t="shared" ca="1" si="10"/>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J37" s="47">
         <f t="shared" ca="1" si="4"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K37" s="164"/>
       <c r="L37" s="54" t="s">
@@ -28725,8 +28733,8 @@
       <c r="AH37" s="243" t="b" cm="1">
         <f t="array" ref="AH37">$D37=_xlfn.XLOOKUP(
 AG37,
-_xlfn._xlws.FILTER($AG$7:$AG$4869,$K$7:$K$4869&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4869,$K$7:$K$4869&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4870,$K$7:$K$4870&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4870,$K$7:$K$4870&lt;&gt;"X"),
 "",
 0,
 -1
@@ -28828,8 +28836,8 @@
       <c r="AH38" s="243" t="b" cm="1">
         <f t="array" ref="AH38">$D38=_xlfn.XLOOKUP(
 AG38,
-_xlfn._xlws.FILTER($AG$7:$AG$4869,$K$7:$K$4869&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4869,$K$7:$K$4869&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4870,$K$7:$K$4870&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4870,$K$7:$K$4870&lt;&gt;"X"),
 "",
 0,
 -1
@@ -28869,7 +28877,7 @@
       <c r="H39" s="138"/>
       <c r="I39" s="164">
         <f t="shared" ca="1" si="10"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J39" s="47">
         <f t="shared" ca="1" si="4"/>
@@ -28921,8 +28929,8 @@
       <c r="AH39" s="243" t="b" cm="1">
         <f t="array" ref="AH39">$D39=_xlfn.XLOOKUP(
 AG39,
-_xlfn._xlws.FILTER($AG$7:$AG$4869,$K$7:$K$4869&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4869,$K$7:$K$4869&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4870,$K$7:$K$4870&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4870,$K$7:$K$4870&lt;&gt;"X"),
 "",
 0,
 -1
@@ -28960,7 +28968,7 @@
       <c r="H40" s="138"/>
       <c r="I40" s="164">
         <f t="shared" ca="1" si="10"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J40" s="47">
         <f t="shared" ca="1" si="4"/>
@@ -29010,8 +29018,8 @@
       <c r="AH40" s="243" t="b" cm="1">
         <f t="array" ref="AH40">$D40=_xlfn.XLOOKUP(
 AG40,
-_xlfn._xlws.FILTER($AG$7:$AG$4869,$K$7:$K$4869&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4869,$K$7:$K$4869&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4870,$K$7:$K$4870&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4870,$K$7:$K$4870&lt;&gt;"X"),
 "",
 0,
 -1
@@ -29023,30 +29031,59 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:35" s="9" customFormat="1">
-      <c r="A41" s="23"/>
-      <c r="B41" s="33"/>
-      <c r="C41" s="137"/>
-      <c r="D41" s="25"/>
-      <c r="E41" s="174"/>
-      <c r="F41" s="31"/>
-      <c r="G41" s="21"/>
+    <row r="41" spans="1:35" s="9" customFormat="1" ht="63">
+      <c r="A41" s="33">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="B41" s="33" t="str">
+        <f t="shared" ref="B41" si="23">MID(D41, FIND("-", D41) + 1, 4)</f>
+        <v>5.10</v>
+      </c>
+      <c r="C41" s="164"/>
+      <c r="D41" s="25" t="s">
+        <v>1097</v>
+      </c>
+      <c r="E41" s="174">
+        <f t="shared" si="2"/>
+        <v>46332</v>
+      </c>
+      <c r="F41" s="31" t="s">
+        <v>1098</v>
+      </c>
+      <c r="G41" s="21" t="s">
+        <v>547</v>
+      </c>
       <c r="H41" s="138"/>
-      <c r="I41" s="177"/>
-      <c r="J41" s="47"/>
+      <c r="I41" s="164">
+        <f t="shared" ca="1" si="10"/>
+        <v>4</v>
+      </c>
+      <c r="J41" s="47">
+        <f t="shared" ca="1" si="4"/>
+        <v>0</v>
+      </c>
       <c r="K41" s="164"/>
-      <c r="L41" s="52"/>
-      <c r="M41" s="66"/>
+      <c r="L41" s="54" t="s">
+        <v>8</v>
+      </c>
+      <c r="M41" s="65"/>
       <c r="N41" s="40"/>
-      <c r="O41" s="37"/>
-      <c r="P41" s="17"/>
-      <c r="Q41" s="183"/>
-      <c r="R41" s="27"/>
-      <c r="S41" s="27"/>
-      <c r="T41" s="187"/>
+      <c r="O41" s="41"/>
+      <c r="P41" s="40"/>
+      <c r="Q41" s="155"/>
+      <c r="R41" s="27">
+        <v>46311</v>
+      </c>
+      <c r="S41" s="27">
+        <v>46311</v>
+      </c>
+      <c r="T41" s="188">
+        <v>46311</v>
+      </c>
       <c r="U41" s="29"/>
       <c r="V41" s="188"/>
-      <c r="W41" s="227"/>
+      <c r="W41" s="235"/>
       <c r="X41" s="230"/>
       <c r="Y41" s="227"/>
       <c r="Z41" s="29" t="str">
@@ -29054,130 +29091,138 @@
         <v/>
       </c>
       <c r="AA41" s="229"/>
-      <c r="AB41" s="229"/>
-      <c r="AC41" s="19"/>
+      <c r="AB41" s="229" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="AC41" s="183" t="str">
+        <f t="shared" ref="AC41" si="24">IF(AB41="Late Resubmission",IF(AA41="","",AA41-Z41),IF(AB41="Not submit yet",IF(Z41="","",$I$1-Z41),""))</f>
+        <v/>
+      </c>
       <c r="AD41" s="92"/>
-      <c r="AG41" s="238"/>
-      <c r="AH41" s="243"/>
-      <c r="AI41" s="75"/>
-    </row>
-    <row r="42" spans="1:35" s="9" customFormat="1" ht="16.5" thickBot="1">
-      <c r="A42" s="24"/>
-      <c r="B42" s="329"/>
-      <c r="C42" s="165"/>
-      <c r="D42" s="45"/>
-      <c r="E42" s="175"/>
-      <c r="F42" s="32"/>
-      <c r="G42" s="22"/>
-      <c r="H42" s="139"/>
-      <c r="I42" s="178"/>
-      <c r="J42" s="132"/>
-      <c r="K42" s="199"/>
-      <c r="L42" s="53"/>
-      <c r="M42" s="67"/>
-      <c r="N42" s="18"/>
-      <c r="O42" s="38"/>
-      <c r="P42" s="18"/>
-      <c r="Q42" s="184"/>
-      <c r="R42" s="44"/>
-      <c r="S42" s="44"/>
-      <c r="T42" s="189"/>
-      <c r="U42" s="43"/>
-      <c r="V42" s="194"/>
-      <c r="W42" s="228"/>
-      <c r="X42" s="232"/>
-      <c r="Y42" s="228"/>
-      <c r="Z42" s="43" t="str">
+      <c r="AG41" s="238" t="str">
+        <f t="shared" si="8"/>
+        <v>LTIA-5.10-VIETUR-80000-RFA-SDS-0222</v>
+      </c>
+      <c r="AH41" s="243" t="b" cm="1">
+        <f t="array" ref="AH41">$D41=_xlfn.XLOOKUP(
+AG41,
+_xlfn._xlws.FILTER($AG$7:$AG$4870,$K$7:$K$4870&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4870,$K$7:$K$4870&lt;&gt;"X"),
+"",
+0,
+-1
+)</f>
+        <v>1</v>
+      </c>
+      <c r="AI41" s="75" t="str">
+        <f>IF(AND($AH41,OR($Q41="B",$Q41="C")),"YES","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" spans="1:35" s="9" customFormat="1">
+      <c r="A42" s="23"/>
+      <c r="B42" s="33"/>
+      <c r="C42" s="137"/>
+      <c r="D42" s="25"/>
+      <c r="E42" s="174"/>
+      <c r="F42" s="31"/>
+      <c r="G42" s="21"/>
+      <c r="H42" s="138"/>
+      <c r="I42" s="177"/>
+      <c r="J42" s="47"/>
+      <c r="K42" s="164"/>
+      <c r="L42" s="52"/>
+      <c r="M42" s="66"/>
+      <c r="N42" s="40"/>
+      <c r="O42" s="37"/>
+      <c r="P42" s="17"/>
+      <c r="Q42" s="183"/>
+      <c r="R42" s="27"/>
+      <c r="S42" s="27"/>
+      <c r="T42" s="187"/>
+      <c r="U42" s="29"/>
+      <c r="V42" s="188"/>
+      <c r="W42" s="227"/>
+      <c r="X42" s="230"/>
+      <c r="Y42" s="227"/>
+      <c r="Z42" s="29" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AA42" s="233"/>
-      <c r="AB42" s="233"/>
-      <c r="AC42" s="20"/>
-      <c r="AD42" s="93"/>
-      <c r="AG42" s="239"/>
-      <c r="AH42" s="244"/>
-      <c r="AI42" s="241"/>
-    </row>
-    <row r="43" spans="1:35" ht="16.5" thickBot="1"/>
-    <row r="44" spans="1:35" ht="16.5" thickBot="1">
-      <c r="C44" s="166" t="s">
+      <c r="AA42" s="229"/>
+      <c r="AB42" s="229"/>
+      <c r="AC42" s="19"/>
+      <c r="AD42" s="92"/>
+      <c r="AG42" s="238"/>
+      <c r="AH42" s="243"/>
+      <c r="AI42" s="75"/>
+    </row>
+    <row r="43" spans="1:35" s="9" customFormat="1" ht="16.5" thickBot="1">
+      <c r="A43" s="24"/>
+      <c r="B43" s="329"/>
+      <c r="C43" s="165"/>
+      <c r="D43" s="45"/>
+      <c r="E43" s="175"/>
+      <c r="F43" s="32"/>
+      <c r="G43" s="22"/>
+      <c r="H43" s="139"/>
+      <c r="I43" s="178"/>
+      <c r="J43" s="132"/>
+      <c r="K43" s="199"/>
+      <c r="L43" s="53"/>
+      <c r="M43" s="67"/>
+      <c r="N43" s="18"/>
+      <c r="O43" s="38"/>
+      <c r="P43" s="18"/>
+      <c r="Q43" s="184"/>
+      <c r="R43" s="44"/>
+      <c r="S43" s="44"/>
+      <c r="T43" s="189"/>
+      <c r="U43" s="43"/>
+      <c r="V43" s="194"/>
+      <c r="W43" s="228"/>
+      <c r="X43" s="232"/>
+      <c r="Y43" s="228"/>
+      <c r="Z43" s="43" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="AA43" s="233"/>
+      <c r="AB43" s="233"/>
+      <c r="AC43" s="20"/>
+      <c r="AD43" s="93"/>
+      <c r="AG43" s="239"/>
+      <c r="AH43" s="244"/>
+      <c r="AI43" s="241"/>
+    </row>
+    <row r="44" spans="1:35" ht="16.5" thickBot="1"/>
+    <row r="45" spans="1:35" ht="16.5" thickBot="1">
+      <c r="C45" s="166" t="s">
         <v>20</v>
       </c>
-      <c r="D44" s="376" t="s">
+      <c r="D45" s="416" t="s">
         <v>21</v>
       </c>
-      <c r="E44" s="377"/>
-      <c r="F44" s="46"/>
-      <c r="G44" s="46"/>
-      <c r="H44" s="356" t="s">
+      <c r="E45" s="417"/>
+      <c r="F45" s="46"/>
+      <c r="G45" s="46"/>
+      <c r="H45" s="392" t="s">
         <v>14</v>
       </c>
-      <c r="I44" s="357"/>
-      <c r="J44" s="357"/>
-      <c r="K44" s="357"/>
-      <c r="L44" s="357"/>
-      <c r="M44" s="358"/>
-      <c r="N44" s="362" t="s">
+      <c r="I45" s="393"/>
+      <c r="J45" s="393"/>
+      <c r="K45" s="393"/>
+      <c r="L45" s="393"/>
+      <c r="M45" s="394"/>
+      <c r="N45" s="388" t="s">
         <v>7</v>
       </c>
-      <c r="O44" s="363"/>
-      <c r="P44" s="362" t="s">
+      <c r="O45" s="389"/>
+      <c r="P45" s="388" t="s">
         <v>109</v>
       </c>
-      <c r="Q44" s="363"/>
-      <c r="R44" s="1"/>
-      <c r="S44" s="1"/>
-      <c r="T44" s="140"/>
-      <c r="U44" s="1"/>
-      <c r="W44" s="11"/>
-      <c r="X44" s="11"/>
-      <c r="Y44" s="11"/>
-      <c r="Z44" s="11"/>
-      <c r="AA44" s="11"/>
-      <c r="AB44" s="11"/>
-      <c r="AC44" s="11"/>
-      <c r="AG44" s="11"/>
-      <c r="AH44" s="11"/>
-      <c r="AI44" s="11"/>
-    </row>
-    <row r="45" spans="1:35" ht="16.5" thickBot="1">
-      <c r="C45" s="195" t="s">
-        <v>109</v>
-      </c>
-      <c r="D45" s="420" t="s">
-        <v>111</v>
-      </c>
-      <c r="E45" s="421"/>
-      <c r="F45" s="46"/>
-      <c r="H45" s="356" t="s">
-        <v>18</v>
-      </c>
-      <c r="I45" s="357"/>
-      <c r="J45" s="357"/>
-      <c r="K45" s="358"/>
-      <c r="L45" s="105">
-        <f ca="1">M45/$M$45</f>
-        <v>1</v>
-      </c>
-      <c r="M45" s="106">
-        <f ca="1">SUM($M$46:$M$50)</f>
-        <v>36</v>
-      </c>
-      <c r="N45" s="102" t="s">
-        <v>15</v>
-      </c>
-      <c r="O45" s="103" t="s">
-        <v>16</v>
-      </c>
-      <c r="P45" s="105">
-        <f ca="1">Q45/$Q$45</f>
-        <v>1</v>
-      </c>
-      <c r="Q45" s="220">
-        <f ca="1">SUM(Q46:Q49)</f>
-        <v>32</v>
-      </c>
+      <c r="Q45" s="389"/>
       <c r="R45" s="1"/>
       <c r="S45" s="1"/>
       <c r="T45" s="140"/>
@@ -29193,45 +29238,42 @@
       <c r="AH45" s="11"/>
       <c r="AI45" s="11"/>
     </row>
-    <row r="46" spans="1:35">
+    <row r="46" spans="1:35" ht="16.5" thickBot="1">
       <c r="C46" s="195" t="s">
-        <v>36</v>
-      </c>
-      <c r="D46" s="418" t="s">
+        <v>109</v>
+      </c>
+      <c r="D46" s="440" t="s">
+        <v>111</v>
+      </c>
+      <c r="E46" s="441"/>
+      <c r="F46" s="46"/>
+      <c r="H46" s="392" t="s">
+        <v>18</v>
+      </c>
+      <c r="I46" s="393"/>
+      <c r="J46" s="393"/>
+      <c r="K46" s="394"/>
+      <c r="L46" s="105">
+        <f ca="1">M46/$M$46</f>
+        <v>1</v>
+      </c>
+      <c r="M46" s="106">
+        <f ca="1">SUM($M$47:$M$51)</f>
         <v>37</v>
       </c>
-      <c r="E46" s="419"/>
-      <c r="F46" s="69"/>
-      <c r="G46" s="6"/>
-      <c r="H46" s="379" t="s">
-        <v>66</v>
-      </c>
-      <c r="I46" s="380"/>
-      <c r="J46" s="380"/>
-      <c r="K46" s="381"/>
-      <c r="L46" s="107">
-        <f ca="1">M46/$M$45</f>
-        <v>2.7777777777777776E-2</v>
-      </c>
-      <c r="M46" s="108">
-        <f>COUNTIF($H$7:$H$42,"A")</f>
+      <c r="N46" s="102" t="s">
+        <v>15</v>
+      </c>
+      <c r="O46" s="103" t="s">
+        <v>16</v>
+      </c>
+      <c r="P46" s="105">
+        <f ca="1">Q46/$Q$46</f>
         <v>1</v>
       </c>
-      <c r="N46" s="100">
-        <f ca="1">COUNTIFS($I$7:$I$42,"&lt;=21",$H$7:$H$42,"A")</f>
-        <v>1</v>
-      </c>
-      <c r="O46" s="101">
-        <f ca="1">COUNTIFS($I$7:$I$42,"&gt;21",$H$7:$H$42,"A")</f>
-        <v>0</v>
-      </c>
-      <c r="P46" s="107">
-        <f ca="1">Q46/$Q$45</f>
-        <v>3.125E-2</v>
-      </c>
-      <c r="Q46" s="108">
-        <f>COUNTIF($Q$7:$Q$42,"A")</f>
-        <v>1</v>
+      <c r="Q46" s="220">
+        <f ca="1">SUM(Q47:Q50)</f>
+        <v>33</v>
       </c>
       <c r="R46" s="1"/>
       <c r="S46" s="1"/>
@@ -29249,44 +29291,44 @@
       <c r="AI46" s="11"/>
     </row>
     <row r="47" spans="1:35">
-      <c r="C47" s="394" t="s">
-        <v>75</v>
-      </c>
-      <c r="D47" s="350" t="s">
-        <v>76</v>
-      </c>
-      <c r="E47" s="351"/>
-      <c r="F47" s="70"/>
+      <c r="C47" s="195" t="s">
+        <v>36</v>
+      </c>
+      <c r="D47" s="438" t="s">
+        <v>37</v>
+      </c>
+      <c r="E47" s="439"/>
+      <c r="F47" s="69"/>
       <c r="G47" s="6"/>
-      <c r="H47" s="382" t="s">
-        <v>67</v>
-      </c>
-      <c r="I47" s="383"/>
-      <c r="J47" s="383"/>
-      <c r="K47" s="384"/>
-      <c r="L47" s="109">
-        <f t="shared" ref="L47:L50" ca="1" si="23">M47/$M$45</f>
-        <v>0.55555555555555558</v>
-      </c>
-      <c r="M47" s="110">
-        <f>COUNTIF($H$7:$H$42,"B")</f>
-        <v>20</v>
-      </c>
-      <c r="N47" s="98">
-        <f ca="1">COUNTIFS($I$7:$I$42,"&lt;=21",$H$7:$H$42,"B")</f>
-        <v>8</v>
-      </c>
-      <c r="O47" s="50">
-        <f ca="1">COUNTIFS($I$7:$I$42,"&gt;21",$H$7:$H$42,"B")</f>
-        <v>12</v>
-      </c>
-      <c r="P47" s="109">
-        <f t="shared" ref="P47:P49" ca="1" si="24">Q47/$Q$45</f>
-        <v>0.625</v>
-      </c>
-      <c r="Q47" s="110">
-        <f>COUNTIF($Q$7:$Q$42,"B")</f>
-        <v>20</v>
+      <c r="H47" s="418" t="s">
+        <v>66</v>
+      </c>
+      <c r="I47" s="419"/>
+      <c r="J47" s="419"/>
+      <c r="K47" s="420"/>
+      <c r="L47" s="107">
+        <f ca="1">M47/$M$46</f>
+        <v>2.7027027027027029E-2</v>
+      </c>
+      <c r="M47" s="108">
+        <f>COUNTIF($H$7:$H$43,"A")</f>
+        <v>1</v>
+      </c>
+      <c r="N47" s="100">
+        <f ca="1">COUNTIFS($I$7:$I$43,"&lt;=21",$H$7:$H$43,"A")</f>
+        <v>1</v>
+      </c>
+      <c r="O47" s="101">
+        <f ca="1">COUNTIFS($I$7:$I$43,"&gt;21",$H$7:$H$43,"A")</f>
+        <v>0</v>
+      </c>
+      <c r="P47" s="107">
+        <f ca="1">Q47/$Q$46</f>
+        <v>3.0303030303030304E-2</v>
+      </c>
+      <c r="Q47" s="108">
+        <f>COUNTIF($Q$7:$Q$43,"A")</f>
+        <v>1</v>
       </c>
       <c r="R47" s="1"/>
       <c r="S47" s="1"/>
@@ -29303,41 +29345,45 @@
       <c r="AH47" s="11"/>
       <c r="AI47" s="11"/>
     </row>
-    <row r="48" spans="1:35" ht="16.5" thickBot="1">
-      <c r="C48" s="395"/>
-      <c r="D48" s="352"/>
-      <c r="E48" s="353"/>
-      <c r="F48" s="71"/>
+    <row r="48" spans="1:35">
+      <c r="C48" s="382" t="s">
+        <v>75</v>
+      </c>
+      <c r="D48" s="384" t="s">
+        <v>76</v>
+      </c>
+      <c r="E48" s="385"/>
+      <c r="F48" s="70"/>
       <c r="G48" s="6"/>
-      <c r="H48" s="385" t="s">
-        <v>68</v>
-      </c>
-      <c r="I48" s="386"/>
-      <c r="J48" s="386"/>
-      <c r="K48" s="387"/>
-      <c r="L48" s="111">
-        <f t="shared" ca="1" si="23"/>
-        <v>0.22222222222222221</v>
-      </c>
-      <c r="M48" s="112">
-        <f>COUNTIF($H$7:$H$42,"C")</f>
-        <v>8</v>
+      <c r="H48" s="421" t="s">
+        <v>67</v>
+      </c>
+      <c r="I48" s="422"/>
+      <c r="J48" s="422"/>
+      <c r="K48" s="423"/>
+      <c r="L48" s="109">
+        <f t="shared" ref="L48:L51" ca="1" si="25">M48/$M$46</f>
+        <v>0.54054054054054057</v>
+      </c>
+      <c r="M48" s="110">
+        <f>COUNTIF($H$7:$H$43,"B")</f>
+        <v>20</v>
       </c>
       <c r="N48" s="98">
-        <f ca="1">COUNTIFS($I$7:$I$42,"&lt;=21",$H$7:$H$42,"C")</f>
-        <v>3</v>
+        <f ca="1">COUNTIFS($I$7:$I$43,"&lt;=21",$H$7:$H$43,"B")</f>
+        <v>8</v>
       </c>
       <c r="O48" s="50">
-        <f ca="1">COUNTIFS($I$7:$I$42,"&gt;21",$H$7:$H$42,"C")</f>
-        <v>5</v>
-      </c>
-      <c r="P48" s="111">
-        <f t="shared" ca="1" si="24"/>
-        <v>9.375E-2</v>
-      </c>
-      <c r="Q48" s="112">
-        <f>COUNTIF($Q$7:$Q$42,"C")</f>
-        <v>3</v>
+        <f ca="1">COUNTIFS($I$7:$I$43,"&gt;21",$H$7:$H$43,"B")</f>
+        <v>12</v>
+      </c>
+      <c r="P48" s="109">
+        <f t="shared" ref="P48:P50" ca="1" si="26">Q48/$Q$46</f>
+        <v>0.60606060606060608</v>
+      </c>
+      <c r="Q48" s="110">
+        <f>COUNTIF($Q$7:$Q$43,"B")</f>
+        <v>20</v>
       </c>
       <c r="R48" s="1"/>
       <c r="S48" s="1"/>
@@ -29354,42 +29400,43 @@
       <c r="AH48" s="11"/>
       <c r="AI48" s="11"/>
     </row>
-    <row r="49" spans="3:35">
-      <c r="F49" s="72"/>
+    <row r="49" spans="3:35" ht="16.5" thickBot="1">
+      <c r="C49" s="383"/>
+      <c r="D49" s="386"/>
+      <c r="E49" s="387"/>
+      <c r="F49" s="71"/>
       <c r="G49" s="6"/>
-      <c r="H49" s="388" t="s">
-        <v>70</v>
-      </c>
-      <c r="I49" s="389"/>
-      <c r="J49" s="389"/>
-      <c r="K49" s="390"/>
-      <c r="L49" s="114">
-        <f t="shared" ca="1" si="23"/>
-        <v>0.1388888888888889</v>
-      </c>
-      <c r="M49" s="115">
-        <f ca="1">SUM(N49:O49)</f>
+      <c r="H49" s="424" t="s">
+        <v>68</v>
+      </c>
+      <c r="I49" s="425"/>
+      <c r="J49" s="425"/>
+      <c r="K49" s="426"/>
+      <c r="L49" s="111">
+        <f t="shared" ca="1" si="25"/>
+        <v>0.21621621621621623</v>
+      </c>
+      <c r="M49" s="112">
+        <f>COUNTIF($H$7:$H$43,"C")</f>
+        <v>8</v>
+      </c>
+      <c r="N49" s="98">
+        <f ca="1">COUNTIFS($I$7:$I$43,"&lt;=21",$H$7:$H$43,"C")</f>
+        <v>3</v>
+      </c>
+      <c r="O49" s="50">
+        <f ca="1">COUNTIFS($I$7:$I$43,"&gt;21",$H$7:$H$43,"C")</f>
         <v>5</v>
       </c>
-      <c r="N49" s="98">
-        <f ca="1">COUNTIFS($I$7:$I$42,"&lt;=21",$U$7:$U$42,"",$K$7:$K$42,"&lt;&gt;X")</f>
+      <c r="P49" s="111">
+        <f t="shared" ca="1" si="26"/>
+        <v>9.0909090909090912E-2</v>
+      </c>
+      <c r="Q49" s="112">
+        <f>COUNTIF($Q$7:$Q$43,"C")</f>
         <v>3</v>
       </c>
-      <c r="O49" s="50">
-        <f ca="1">COUNTIFS($I$7:$I$42,"&gt;21",$U$7:$U$42,"",$K$7:$K$42,"&lt;&gt;X")</f>
-        <v>2</v>
-      </c>
-      <c r="P49" s="114">
-        <f t="shared" ca="1" si="24"/>
-        <v>0.25</v>
-      </c>
-      <c r="Q49" s="115">
-        <f ca="1">COUNTIFS($I$7:$I$42,"&gt;=0",$P$7:$P$42,"",$K$7:$K$42,"&lt;&gt;X")</f>
-        <v>8</v>
-      </c>
-      <c r="R49" s="1" t="s">
-        <v>10</v>
-      </c>
+      <c r="R49" s="1"/>
       <c r="S49" s="1"/>
       <c r="T49" s="140"/>
       <c r="U49" s="1"/>
@@ -29404,68 +29451,139 @@
       <c r="AH49" s="11"/>
       <c r="AI49" s="11"/>
     </row>
-    <row r="50" spans="3:35" ht="16.5" thickBot="1">
-      <c r="C50" s="378" t="s">
+    <row r="50" spans="3:35">
+      <c r="F50" s="72"/>
+      <c r="G50" s="6"/>
+      <c r="H50" s="374" t="s">
+        <v>70</v>
+      </c>
+      <c r="I50" s="375"/>
+      <c r="J50" s="375"/>
+      <c r="K50" s="376"/>
+      <c r="L50" s="114">
+        <f t="shared" ca="1" si="25"/>
+        <v>0.16216216216216217</v>
+      </c>
+      <c r="M50" s="115">
+        <f ca="1">SUM(N50:O50)</f>
+        <v>6</v>
+      </c>
+      <c r="N50" s="98">
+        <f ca="1">COUNTIFS($I$7:$I$43,"&lt;=21",$U$7:$U$43,"",$K$7:$K$43,"&lt;&gt;X")</f>
+        <v>4</v>
+      </c>
+      <c r="O50" s="50">
+        <f ca="1">COUNTIFS($I$7:$I$43,"&gt;21",$U$7:$U$43,"",$K$7:$K$43,"&lt;&gt;X")</f>
+        <v>2</v>
+      </c>
+      <c r="P50" s="114">
+        <f t="shared" ca="1" si="26"/>
+        <v>0.27272727272727271</v>
+      </c>
+      <c r="Q50" s="115">
+        <f ca="1">COUNTIFS($I$7:$I$43,"&gt;=0",$P$7:$P$43,"",$K$7:$K$43,"&lt;&gt;X")</f>
+        <v>9</v>
+      </c>
+      <c r="R50" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="S50" s="1"/>
+      <c r="T50" s="140"/>
+      <c r="U50" s="1"/>
+      <c r="W50" s="11"/>
+      <c r="X50" s="11"/>
+      <c r="Y50" s="11"/>
+      <c r="Z50" s="11"/>
+      <c r="AA50" s="11"/>
+      <c r="AB50" s="11"/>
+      <c r="AC50" s="11"/>
+      <c r="AG50" s="11"/>
+      <c r="AH50" s="11"/>
+      <c r="AI50" s="11"/>
+    </row>
+    <row r="51" spans="3:35" ht="16.5" thickBot="1">
+      <c r="C51" s="370" t="s">
         <v>41</v>
       </c>
-      <c r="D50" s="378"/>
-      <c r="E50" s="378"/>
-      <c r="H50" s="391" t="s">
+      <c r="D51" s="370"/>
+      <c r="E51" s="370"/>
+      <c r="H51" s="377" t="s">
         <v>71</v>
       </c>
-      <c r="I50" s="392"/>
-      <c r="J50" s="392"/>
-      <c r="K50" s="393"/>
-      <c r="L50" s="113">
-        <f t="shared" ca="1" si="23"/>
-        <v>5.5555555555555552E-2</v>
-      </c>
-      <c r="M50" s="97">
-        <f>COUNTIFS($K$7:$K$42,"X")</f>
+      <c r="I51" s="378"/>
+      <c r="J51" s="378"/>
+      <c r="K51" s="379"/>
+      <c r="L51" s="113">
+        <f t="shared" ca="1" si="25"/>
+        <v>5.4054054054054057E-2</v>
+      </c>
+      <c r="M51" s="97">
+        <f>COUNTIFS($K$7:$K$43,"X")</f>
         <v>2</v>
       </c>
-      <c r="N50" s="99"/>
-      <c r="O50" s="51"/>
-      <c r="P50" s="221"/>
-      <c r="Q50" s="222"/>
-    </row>
-    <row r="51" spans="3:35">
-      <c r="C51" s="169" t="s">
-        <v>8</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>42</v>
-      </c>
+      <c r="N51" s="99"/>
+      <c r="O51" s="51"/>
+      <c r="P51" s="221"/>
+      <c r="Q51" s="222"/>
     </row>
     <row r="52" spans="3:35">
       <c r="C52" s="169" t="s">
         <v>8</v>
       </c>
-      <c r="D52" s="127" t="s">
-        <v>43</v>
+      <c r="D52" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="53" spans="3:35">
       <c r="C53" s="169" t="s">
         <v>8</v>
       </c>
-      <c r="D53" s="1" t="s">
+      <c r="D53" s="127" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35">
+      <c r="C54" s="169" t="s">
+        <v>8</v>
+      </c>
+      <c r="D54" s="1" t="s">
         <v>44</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A6:AD34" xr:uid="{4D8E8261-1CEF-42DB-8488-C430D415EC88}">
+  <autoFilter ref="A6:AD43" xr:uid="{4D8E8261-1CEF-42DB-8488-C430D415EC88}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A7:AD33">
       <sortCondition ref="S6:S33"/>
     </sortState>
   </autoFilter>
   <mergeCells count="37">
+    <mergeCell ref="P45:Q45"/>
+    <mergeCell ref="X4:Y4"/>
+    <mergeCell ref="Z4:AC4"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D45:E45"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="D47:E47"/>
+    <mergeCell ref="C51:E51"/>
+    <mergeCell ref="H47:K47"/>
+    <mergeCell ref="H48:K48"/>
+    <mergeCell ref="H45:M45"/>
+    <mergeCell ref="H49:K49"/>
+    <mergeCell ref="H50:K50"/>
+    <mergeCell ref="C48:C49"/>
+    <mergeCell ref="D48:E49"/>
+    <mergeCell ref="D46:E46"/>
     <mergeCell ref="AG5:AG6"/>
     <mergeCell ref="AH5:AH6"/>
     <mergeCell ref="AI5:AI6"/>
-    <mergeCell ref="H50:K50"/>
-    <mergeCell ref="H45:K45"/>
-    <mergeCell ref="N44:O44"/>
+    <mergeCell ref="H51:K51"/>
+    <mergeCell ref="H46:K46"/>
+    <mergeCell ref="N45:O45"/>
     <mergeCell ref="AD4:AD5"/>
     <mergeCell ref="H4:H5"/>
     <mergeCell ref="I4:I5"/>
@@ -29476,30 +29594,9 @@
     <mergeCell ref="K4:K5"/>
     <mergeCell ref="P4:Q4"/>
     <mergeCell ref="J4:J5"/>
-    <mergeCell ref="D46:E46"/>
-    <mergeCell ref="C50:E50"/>
-    <mergeCell ref="H46:K46"/>
-    <mergeCell ref="H47:K47"/>
-    <mergeCell ref="H44:M44"/>
-    <mergeCell ref="H48:K48"/>
-    <mergeCell ref="H49:K49"/>
-    <mergeCell ref="C47:C48"/>
-    <mergeCell ref="D47:E48"/>
-    <mergeCell ref="D45:E45"/>
-    <mergeCell ref="P44:Q44"/>
-    <mergeCell ref="X4:Y4"/>
-    <mergeCell ref="Z4:AC4"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D44:E44"/>
-    <mergeCell ref="B4:B5"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
-  <conditionalFormatting sqref="A7:AD42 AG7:AI42">
+  <conditionalFormatting sqref="A7:AD43 AG7:AI43">
     <cfRule type="expression" dxfId="11" priority="1">
       <formula>$K7="X"</formula>
     </cfRule>
@@ -29625,9 +29722,9 @@
     <hyperlink ref="O24" r:id="rId100" xr:uid="{26FEB876-D8E0-4A23-A9C5-C07952F599D7}"/>
     <hyperlink ref="O27" r:id="rId101" xr:uid="{51C15339-30E0-4EDA-A35A-162E28AC0D63}"/>
     <hyperlink ref="O33" r:id="rId102" xr:uid="{7E0883C0-4918-4433-937B-70D3D155F955}"/>
-    <hyperlink ref="C51" r:id="rId103" xr:uid="{BDBBB1AA-41DD-4769-B198-E0D4B6B569E2}"/>
-    <hyperlink ref="C52" r:id="rId104" xr:uid="{174B2EE8-A853-4328-A727-C5D3FC38F2B6}"/>
-    <hyperlink ref="C53" r:id="rId105" xr:uid="{6C349E79-11FF-4195-90FE-DE817F5EBEF8}"/>
+    <hyperlink ref="C52" r:id="rId103" xr:uid="{BDBBB1AA-41DD-4769-B198-E0D4B6B569E2}"/>
+    <hyperlink ref="C53" r:id="rId104" xr:uid="{174B2EE8-A853-4328-A727-C5D3FC38F2B6}"/>
+    <hyperlink ref="C54" r:id="rId105" xr:uid="{6C349E79-11FF-4195-90FE-DE817F5EBEF8}"/>
     <hyperlink ref="P7" r:id="rId106" xr:uid="{20D7A9F2-B509-4410-8C53-729666C026F8}"/>
     <hyperlink ref="P8" r:id="rId107" xr:uid="{BC5C2D57-7ED0-43E0-8C7C-0DF13280AE79}"/>
     <hyperlink ref="P9" r:id="rId108" xr:uid="{49C5EB74-800E-4CE6-82D1-E75C20991765}"/>
@@ -29663,9 +29760,10 @@
     <hyperlink ref="N36" r:id="rId138" xr:uid="{A9162BCC-A67F-4960-972B-2EF68F29EB50}"/>
     <hyperlink ref="N38" r:id="rId139" xr:uid="{DBAA5DC8-908C-4ABF-AC05-BCE08D8BBB73}"/>
     <hyperlink ref="L40" r:id="rId140" xr:uid="{95929207-D5E2-4FFA-94DE-6961D7557694}"/>
+    <hyperlink ref="L41" r:id="rId141" xr:uid="{4C22862D-00A5-4D76-A6A0-23BE29E9D691}"/>
   </hyperlinks>
   <pageMargins left="0.25" right="0.17" top="0.5" bottom="0.25" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="29" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId141"/>
+  <pageSetup paperSize="9" scale="29" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId142"/>
 </worksheet>
 </file>
 
@@ -29710,7 +29808,7 @@
       </c>
       <c r="I1" s="176">
         <f ca="1">TODAY()</f>
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="J1" s="131"/>
       <c r="K1" s="197"/>
@@ -29781,81 +29879,81 @@
       <c r="Z3" s="159"/>
     </row>
     <row r="4" spans="1:26" s="5" customFormat="1" ht="35.1" customHeight="1" thickBot="1">
-      <c r="A4" s="348" t="s">
+      <c r="A4" s="350" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="348" t="s">
+      <c r="B4" s="350" t="s">
         <v>515</v>
       </c>
-      <c r="C4" s="414" t="s">
+      <c r="C4" s="364" t="s">
         <v>45</v>
       </c>
-      <c r="D4" s="369" t="s">
+      <c r="D4" s="352" t="s">
         <v>46</v>
       </c>
-      <c r="E4" s="437" t="s">
+      <c r="E4" s="354" t="s">
         <v>47</v>
       </c>
-      <c r="F4" s="369" t="s">
+      <c r="F4" s="352" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="439" t="s">
+      <c r="G4" s="356" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="366" t="s">
+      <c r="H4" s="358" t="s">
         <v>48</v>
       </c>
-      <c r="I4" s="441" t="s">
+      <c r="I4" s="360" t="s">
         <v>49</v>
       </c>
-      <c r="J4" s="369" t="s">
+      <c r="J4" s="352" t="s">
         <v>78</v>
       </c>
-      <c r="K4" s="366" t="s">
+      <c r="K4" s="358" t="s">
         <v>80</v>
       </c>
-      <c r="L4" s="368" t="s">
+      <c r="L4" s="362" t="s">
         <v>53</v>
       </c>
-      <c r="M4" s="365"/>
-      <c r="N4" s="368" t="s">
+      <c r="M4" s="348"/>
+      <c r="N4" s="362" t="s">
         <v>55</v>
       </c>
-      <c r="O4" s="365"/>
-      <c r="P4" s="368" t="s">
+      <c r="O4" s="348"/>
+      <c r="P4" s="362" t="s">
         <v>72</v>
       </c>
-      <c r="Q4" s="365"/>
-      <c r="R4" s="364" t="s">
+      <c r="Q4" s="348"/>
+      <c r="R4" s="363" t="s">
         <v>53</v>
       </c>
-      <c r="S4" s="364"/>
-      <c r="T4" s="365"/>
-      <c r="U4" s="368" t="s">
+      <c r="S4" s="363"/>
+      <c r="T4" s="348"/>
+      <c r="U4" s="362" t="s">
         <v>55</v>
       </c>
-      <c r="V4" s="364"/>
-      <c r="W4" s="364"/>
-      <c r="X4" s="371" t="s">
+      <c r="V4" s="363"/>
+      <c r="W4" s="363"/>
+      <c r="X4" s="366" t="s">
         <v>72</v>
       </c>
-      <c r="Y4" s="372"/>
-      <c r="Z4" s="365" t="s">
+      <c r="Y4" s="367"/>
+      <c r="Z4" s="348" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="72" customHeight="1">
-      <c r="A5" s="349"/>
-      <c r="B5" s="349"/>
-      <c r="C5" s="415"/>
-      <c r="D5" s="370"/>
-      <c r="E5" s="438"/>
-      <c r="F5" s="370"/>
-      <c r="G5" s="440"/>
-      <c r="H5" s="367"/>
-      <c r="I5" s="442"/>
-      <c r="J5" s="370"/>
-      <c r="K5" s="367"/>
+      <c r="A5" s="351"/>
+      <c r="B5" s="351"/>
+      <c r="C5" s="365"/>
+      <c r="D5" s="353"/>
+      <c r="E5" s="355"/>
+      <c r="F5" s="353"/>
+      <c r="G5" s="357"/>
+      <c r="H5" s="359"/>
+      <c r="I5" s="361"/>
+      <c r="J5" s="353"/>
+      <c r="K5" s="359"/>
       <c r="L5" s="79" t="s">
         <v>52</v>
       </c>
@@ -29898,7 +29996,7 @@
       <c r="Y5" s="260" t="s">
         <v>114</v>
       </c>
-      <c r="Z5" s="416"/>
+      <c r="Z5" s="349"/>
     </row>
     <row r="6" spans="1:26" ht="15" customHeight="1" thickBot="1">
       <c r="A6" s="78"/>
@@ -31725,7 +31823,7 @@
       <c r="Y29" s="19"/>
       <c r="Z29" s="92"/>
     </row>
-    <row r="30" spans="1:26" s="9" customFormat="1" ht="47.25">
+    <row r="30" spans="1:26" s="9" customFormat="1" ht="31.5">
       <c r="A30" s="33">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -32455,11 +32553,11 @@
       <c r="H39" s="138"/>
       <c r="I39" s="164">
         <f t="shared" ca="1" si="9"/>
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="J39" s="47">
         <f t="shared" ca="1" si="10"/>
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="K39" s="164"/>
       <c r="L39" s="40"/>
@@ -34071,7 +34169,7 @@
       </c>
       <c r="Z59" s="92"/>
     </row>
-    <row r="60" spans="1:26" s="9" customFormat="1" ht="63">
+    <row r="60" spans="1:26" s="9" customFormat="1" ht="47.25">
       <c r="A60" s="33">
         <f t="shared" si="0"/>
         <v>54</v>
@@ -34861,11 +34959,11 @@
       </c>
       <c r="I70" s="164">
         <f t="shared" ref="I70:I78" ca="1" si="14">IF(ISBLANK($V70),_xlfn.DAYS($I$1,$T70),_xlfn.DAYS($V70,$T70))</f>
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="J70" s="47">
         <f t="shared" ref="J70:J78" ca="1" si="15">IF(($I70-21)&gt;0,$I70-21,0)</f>
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="K70" s="164"/>
       <c r="L70" s="40"/>
@@ -36819,11 +36917,11 @@
       <c r="H97" s="138"/>
       <c r="I97" s="164">
         <f t="shared" ca="1" si="24"/>
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J97" s="47">
         <f t="shared" ca="1" si="25"/>
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K97" s="164"/>
       <c r="L97" s="40" t="s">
@@ -37939,11 +38037,11 @@
       <c r="H112" s="138"/>
       <c r="I112" s="164">
         <f t="shared" ca="1" si="24"/>
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="J112" s="47">
         <f t="shared" ca="1" si="25"/>
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K112" s="164" t="s">
         <v>13</v>
@@ -38006,11 +38104,11 @@
       </c>
       <c r="I113" s="164">
         <f t="shared" ca="1" si="24"/>
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J113" s="47">
         <f t="shared" ca="1" si="25"/>
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K113" s="164"/>
       <c r="L113" s="40" t="s">
@@ -38142,11 +38240,11 @@
       <c r="H115" s="138"/>
       <c r="I115" s="164">
         <f t="shared" ca="1" si="24"/>
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J115" s="47">
         <f t="shared" ca="1" si="25"/>
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K115" s="164"/>
       <c r="L115" s="40" t="s">
@@ -39021,7 +39119,7 @@
       <c r="H128" s="138"/>
       <c r="I128" s="164">
         <f t="shared" ca="1" si="24"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J128" s="47">
         <f t="shared" ca="1" si="25"/>
@@ -39080,7 +39178,7 @@
       <c r="H129" s="138"/>
       <c r="I129" s="164">
         <f t="shared" ca="1" si="24"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J129" s="47">
         <f t="shared" ca="1" si="25"/>
@@ -39172,28 +39270,28 @@
       <c r="C133" s="207" t="s">
         <v>38</v>
       </c>
-      <c r="D133" s="428" t="s">
+      <c r="D133" s="390" t="s">
         <v>39</v>
       </c>
-      <c r="E133" s="429"/>
+      <c r="E133" s="391"/>
       <c r="F133" s="46"/>
       <c r="G133" s="68"/>
-      <c r="H133" s="356" t="s">
+      <c r="H133" s="392" t="s">
         <v>14</v>
       </c>
-      <c r="I133" s="357"/>
-      <c r="J133" s="357"/>
-      <c r="K133" s="357"/>
-      <c r="L133" s="357"/>
-      <c r="M133" s="358"/>
-      <c r="N133" s="362" t="s">
+      <c r="I133" s="393"/>
+      <c r="J133" s="393"/>
+      <c r="K133" s="393"/>
+      <c r="L133" s="393"/>
+      <c r="M133" s="394"/>
+      <c r="N133" s="388" t="s">
         <v>7</v>
       </c>
-      <c r="O133" s="363"/>
-      <c r="P133" s="362" t="s">
+      <c r="O133" s="389"/>
+      <c r="P133" s="388" t="s">
         <v>110</v>
       </c>
-      <c r="Q133" s="363"/>
+      <c r="Q133" s="389"/>
       <c r="R133" s="1"/>
       <c r="S133" s="1"/>
       <c r="T133" s="140"/>
@@ -39206,16 +39304,16 @@
       <c r="C134" s="208" t="s">
         <v>74</v>
       </c>
-      <c r="D134" s="435" t="s">
+      <c r="D134" s="380" t="s">
         <v>77</v>
       </c>
-      <c r="E134" s="436"/>
+      <c r="E134" s="381"/>
       <c r="F134" s="46"/>
       <c r="G134" s="46"/>
-      <c r="H134" s="430" t="s">
+      <c r="H134" s="368" t="s">
         <v>17</v>
       </c>
-      <c r="I134" s="431"/>
+      <c r="I134" s="369"/>
       <c r="J134" s="130"/>
       <c r="K134" s="210"/>
       <c r="L134" s="117">
@@ -39249,21 +39347,21 @@
       <c r="Y134" s="11"/>
     </row>
     <row r="135" spans="1:26">
-      <c r="C135" s="394" t="s">
+      <c r="C135" s="382" t="s">
         <v>6</v>
       </c>
-      <c r="D135" s="435" t="s">
+      <c r="D135" s="380" t="s">
         <v>40</v>
       </c>
-      <c r="E135" s="436"/>
+      <c r="E135" s="381"/>
       <c r="F135" s="69"/>
       <c r="G135" s="6"/>
-      <c r="H135" s="432" t="s">
+      <c r="H135" s="371" t="s">
         <v>69</v>
       </c>
-      <c r="I135" s="433"/>
-      <c r="J135" s="433"/>
-      <c r="K135" s="434"/>
+      <c r="I135" s="372"/>
+      <c r="J135" s="372"/>
+      <c r="K135" s="373"/>
       <c r="L135" s="122">
         <f t="shared" ref="L135:L137" ca="1" si="61">M135/$M$134</f>
         <v>0.83464566929133854</v>
@@ -39297,17 +39395,17 @@
       <c r="Y135" s="11"/>
     </row>
     <row r="136" spans="1:26">
-      <c r="C136" s="394"/>
-      <c r="D136" s="435"/>
-      <c r="E136" s="436"/>
+      <c r="C136" s="382"/>
+      <c r="D136" s="380"/>
+      <c r="E136" s="381"/>
       <c r="F136" s="72"/>
       <c r="G136" s="6"/>
-      <c r="H136" s="388" t="s">
+      <c r="H136" s="374" t="s">
         <v>70</v>
       </c>
-      <c r="I136" s="389"/>
-      <c r="J136" s="389"/>
-      <c r="K136" s="390"/>
+      <c r="I136" s="375"/>
+      <c r="J136" s="375"/>
+      <c r="K136" s="376"/>
       <c r="L136" s="124">
         <f t="shared" ca="1" si="61"/>
         <v>5.5118110236220472E-2</v>
@@ -39343,19 +39441,19 @@
       <c r="Y136" s="11"/>
     </row>
     <row r="137" spans="1:26" ht="16.5" thickBot="1">
-      <c r="C137" s="394" t="s">
+      <c r="C137" s="382" t="s">
         <v>75</v>
       </c>
-      <c r="D137" s="350" t="s">
+      <c r="D137" s="384" t="s">
         <v>76</v>
       </c>
-      <c r="E137" s="351"/>
-      <c r="H137" s="391" t="s">
+      <c r="E137" s="385"/>
+      <c r="H137" s="377" t="s">
         <v>71</v>
       </c>
-      <c r="I137" s="392"/>
-      <c r="J137" s="392"/>
-      <c r="K137" s="393"/>
+      <c r="I137" s="378"/>
+      <c r="J137" s="378"/>
+      <c r="K137" s="379"/>
       <c r="L137" s="126">
         <f t="shared" ca="1" si="61"/>
         <v>0.11023622047244094</v>
@@ -39370,16 +39468,16 @@
       <c r="Q137" s="224"/>
     </row>
     <row r="138" spans="1:26" ht="16.5" thickBot="1">
-      <c r="C138" s="395"/>
-      <c r="D138" s="352"/>
-      <c r="E138" s="353"/>
+      <c r="C138" s="383"/>
+      <c r="D138" s="386"/>
+      <c r="E138" s="387"/>
     </row>
     <row r="140" spans="1:26">
-      <c r="C140" s="378" t="s">
+      <c r="C140" s="370" t="s">
         <v>41</v>
       </c>
-      <c r="D140" s="378"/>
-      <c r="E140" s="378"/>
+      <c r="D140" s="370"/>
+      <c r="E140" s="370"/>
     </row>
     <row r="141" spans="1:26">
       <c r="C141" s="169" t="s">
@@ -39412,6 +39510,22 @@
     </sortState>
   </autoFilter>
   <mergeCells count="32">
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="P133:Q133"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="D133:E133"/>
+    <mergeCell ref="H133:M133"/>
+    <mergeCell ref="N133:O133"/>
+    <mergeCell ref="H134:I134"/>
+    <mergeCell ref="C140:E140"/>
+    <mergeCell ref="H135:K135"/>
+    <mergeCell ref="H136:K136"/>
+    <mergeCell ref="H137:K137"/>
+    <mergeCell ref="D134:E134"/>
+    <mergeCell ref="C135:C136"/>
+    <mergeCell ref="D135:E136"/>
+    <mergeCell ref="C137:C138"/>
+    <mergeCell ref="D137:E138"/>
     <mergeCell ref="Z4:Z5"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="D4:D5"/>
@@ -39428,22 +39542,6 @@
     <mergeCell ref="K4:K5"/>
     <mergeCell ref="P4:Q4"/>
     <mergeCell ref="X4:Y4"/>
-    <mergeCell ref="H134:I134"/>
-    <mergeCell ref="C140:E140"/>
-    <mergeCell ref="H135:K135"/>
-    <mergeCell ref="H136:K136"/>
-    <mergeCell ref="H137:K137"/>
-    <mergeCell ref="D134:E134"/>
-    <mergeCell ref="C135:C136"/>
-    <mergeCell ref="D135:E136"/>
-    <mergeCell ref="C137:C138"/>
-    <mergeCell ref="D137:E138"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="P133:Q133"/>
-    <mergeCell ref="J4:J5"/>
-    <mergeCell ref="D133:E133"/>
-    <mergeCell ref="H133:M133"/>
-    <mergeCell ref="N133:O133"/>
   </mergeCells>
   <phoneticPr fontId="71"/>
   <conditionalFormatting sqref="A7:Z131">
@@ -40031,19 +40129,19 @@
       <c r="S3" s="281"/>
     </row>
     <row r="4" spans="1:25" ht="36" customHeight="1" thickBot="1">
-      <c r="A4" s="408" t="s">
+      <c r="A4" s="396" t="s">
         <v>123</v>
       </c>
-      <c r="B4" s="366" t="s">
+      <c r="B4" s="358" t="s">
         <v>45</v>
       </c>
-      <c r="C4" s="366" t="s">
+      <c r="C4" s="358" t="s">
         <v>95</v>
       </c>
-      <c r="D4" s="366" t="s">
+      <c r="D4" s="358" t="s">
         <v>46</v>
       </c>
-      <c r="E4" s="369" t="s">
+      <c r="E4" s="352" t="s">
         <v>4</v>
       </c>
       <c r="F4" s="449" t="s">
@@ -40072,12 +40170,12 @@
       <c r="S4" s="448"/>
     </row>
     <row r="5" spans="1:25" ht="78.75">
-      <c r="A5" s="409"/>
-      <c r="B5" s="367"/>
-      <c r="C5" s="367"/>
-      <c r="D5" s="367"/>
-      <c r="E5" s="370"/>
-      <c r="F5" s="411"/>
+      <c r="A5" s="397"/>
+      <c r="B5" s="359"/>
+      <c r="C5" s="359"/>
+      <c r="D5" s="359"/>
+      <c r="E5" s="353"/>
+      <c r="F5" s="399"/>
       <c r="G5" s="283" t="s">
         <v>56</v>
       </c>
@@ -40265,7 +40363,7 @@
 _xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(D7),RFA!$E:$E,RFA!$AD:$AD,""),
 IF(_xlpm.x=0,"",_xlpm.x)
 )</f>
-        <v>851</v>
+        <v>852</v>
       </c>
     </row>
     <row r="8" spans="1:25" ht="45">
@@ -40326,7 +40424,7 @@
       </c>
       <c r="S8" s="279">
         <f ca="1"/>
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="Y8" t="s">
         <v>125</v>
@@ -40391,7 +40489,7 @@
       </c>
       <c r="S9" s="279">
         <f ca="1"/>
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="10" spans="1:25" ht="45">
@@ -40452,7 +40550,7 @@
       </c>
       <c r="S10" s="279">
         <f ca="1"/>
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="11" spans="1:25" ht="75">
@@ -40513,7 +40611,7 @@
       </c>
       <c r="S11" s="279">
         <f ca="1"/>
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="12" spans="1:25" ht="45">
@@ -40574,7 +40672,7 @@
       </c>
       <c r="S12" s="279">
         <f ca="1"/>
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="13" spans="1:25" ht="45">
@@ -40635,7 +40733,7 @@
       </c>
       <c r="S13" s="279">
         <f ca="1"/>
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="14" spans="1:25" ht="45">
@@ -40696,7 +40794,7 @@
       </c>
       <c r="S14" s="279">
         <f ca="1"/>
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="15" spans="1:25" ht="60">
@@ -41410,16 +41508,16 @@
       <c r="R3" s="281"/>
     </row>
     <row r="4" spans="1:18" ht="16.5" thickBot="1">
-      <c r="A4" s="408" t="s">
+      <c r="A4" s="396" t="s">
         <v>123</v>
       </c>
-      <c r="B4" s="366" t="s">
+      <c r="B4" s="358" t="s">
         <v>45</v>
       </c>
-      <c r="C4" s="366" t="s">
+      <c r="C4" s="358" t="s">
         <v>46</v>
       </c>
-      <c r="D4" s="364" t="s">
+      <c r="D4" s="363" t="s">
         <v>4</v>
       </c>
       <c r="E4" s="449" t="s">
@@ -41448,11 +41546,11 @@
       <c r="R4" s="448"/>
     </row>
     <row r="5" spans="1:18" ht="78.75">
-      <c r="A5" s="409"/>
-      <c r="B5" s="367"/>
-      <c r="C5" s="367"/>
-      <c r="D5" s="440"/>
-      <c r="E5" s="370"/>
+      <c r="A5" s="397"/>
+      <c r="B5" s="359"/>
+      <c r="C5" s="359"/>
+      <c r="D5" s="357"/>
+      <c r="E5" s="353"/>
       <c r="F5" s="283" t="s">
         <v>56</v>
       </c>
@@ -41515,11 +41613,11 @@
     </row>
     <row r="7" spans="1:18" ht="75">
       <c r="A7" s="13" cm="1">
-        <f t="array" ref="A7:A18">IF(_xlfn.ANCHORARRAY(C7)="","",_xlfn.SEQUENCE(ROWS(_xlfn.ANCHORARRAY(C7))))</f>
+        <f t="array" ref="A7:A17">IF(_xlfn.ANCHORARRAY(C7)="","",_xlfn.SEQUENCE(ROWS(_xlfn.ANCHORARRAY(C7))))</f>
         <v>1</v>
       </c>
       <c r="B7" s="302" t="str" cm="1">
-        <f t="array" ref="B7:B18">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$C:$C,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
+        <f t="array" ref="B7:B17">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$C:$C,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
         <v>FAS
 SCS
 SCN
@@ -41527,68 +41625,68 @@
 PAS</v>
       </c>
       <c r="C7" s="282" t="str" cm="1">
-        <f t="array" ref="C7:C18">_xlfn._xlws.FILTER('RFA-SDS'!$D$5:$D$4869,'RFA-SDS'!$AI$5:$AI$4869="YES","")</f>
+        <f t="array" ref="C7:C17">_xlfn._xlws.FILTER('RFA-SDS'!$D$5:$D$4870,'RFA-SDS'!$AI$5:$AI$4870="YES","")</f>
         <v>LTIA-5.10-VIETUR-80000-RFA-SDS-0214</v>
       </c>
       <c r="D7" s="303" t="str" cm="1">
-        <f t="array" ref="D7:D18">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$F:$F,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
+        <f t="array" ref="D7:D17">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$F:$F,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
         <v xml:space="preserve">Construction design drawing of  ICT system – part.1: ICT systems for FLB </v>
       </c>
       <c r="E7" s="303" t="str" cm="1">
-        <f t="array" ref="E7:E18">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$G:$G,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
+        <f t="array" ref="E7:E17">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$G:$G,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
         <v>Bản vẽ TKTC cho hệ thống ICT – phần 1 – Hệ thống ICT cho FLB</v>
       </c>
       <c r="F7" s="270" cm="1">
-        <f t="array" ref="F7:F18">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$R:$R,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
+        <f t="array" ref="F7:F17">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$R:$R,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
         <v>45673</v>
       </c>
       <c r="G7" s="270" cm="1">
-        <f t="array" ref="G7:G18">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$S:$S,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
+        <f t="array" ref="G7:G17">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$S:$S,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
         <v>45673</v>
       </c>
       <c r="H7" s="264" cm="1">
-        <f t="array" ref="H7:H18">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$T:$T,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
+        <f t="array" ref="H7:H17">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$T:$T,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
         <v>45699</v>
       </c>
       <c r="I7" s="264" t="str" cm="1">
-        <f t="array" ref="I7:I18">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$H:$H,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
+        <f t="array" ref="I7:I17">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$H:$H,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
         <v>B</v>
       </c>
       <c r="J7" s="270" cm="1">
-        <f t="array" ref="J7:J18">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$U:$U,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
+        <f t="array" ref="J7:J17">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$U:$U,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
         <v>45716</v>
       </c>
       <c r="K7" s="264" cm="1">
-        <f t="array" ref="K7:K18">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$V:$V,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
+        <f t="array" ref="K7:K17">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$V:$V,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
         <v>45741</v>
       </c>
       <c r="L7" s="264" t="str" cm="1">
-        <f t="array" ref="L7:L18">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$Q:$Q,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
+        <f t="array" ref="L7:L17">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$Q:$Q,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
         <v>B</v>
       </c>
       <c r="M7" s="270" cm="1">
-        <f t="array" ref="M7:M18">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$X:$X,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
+        <f t="array" ref="M7:M17">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$X:$X,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
         <v>45756</v>
       </c>
       <c r="N7" s="264" cm="1">
-        <f t="array" ref="N7:N18">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$Y:$Y,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
+        <f t="array" ref="N7:N17">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$Y:$Y,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
         <v>45756</v>
       </c>
       <c r="O7" s="264" cm="1">
-        <f t="array" ref="O7:O18">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$Z:$Z,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
+        <f t="array" ref="O7:O17">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$Z:$Z,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
         <v>45763</v>
       </c>
       <c r="P7" s="270" t="str" cm="1">
-        <f t="array" ref="P7:P18">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$AA:$AA,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
+        <f t="array" ref="P7:P17">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$AA:$AA,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
         <v/>
       </c>
       <c r="Q7" s="13" t="str" cm="1">
-        <f t="array" aca="1" ref="Q7:Q18" ca="1">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$AB:$AB,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
+        <f t="array" aca="1" ref="Q7:Q17" ca="1">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$AB:$AB,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
         <v>Not submit yet</v>
       </c>
       <c r="R7" s="279" cm="1">
-        <f t="array" aca="1" ref="R7:R18" ca="1">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$AC:$AC,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
-        <v>551</v>
+        <f t="array" aca="1" ref="R7:R17" ca="1">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$AC:$AC,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
+        <v>552</v>
       </c>
     </row>
     <row r="8" spans="1:18" ht="30">
@@ -41646,7 +41744,7 @@
       </c>
       <c r="R8" s="279">
         <f ca="1"/>
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="45">
@@ -41704,7 +41802,7 @@
       </c>
       <c r="R9" s="279">
         <f ca="1"/>
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="105">
@@ -41763,7 +41861,7 @@
       </c>
       <c r="R10" s="279">
         <f ca="1"/>
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="45">
@@ -41821,7 +41919,7 @@
       </c>
       <c r="R11" s="279">
         <f ca="1"/>
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="12" spans="1:18" ht="45">
@@ -41880,7 +41978,7 @@
       </c>
       <c r="R12" s="279">
         <f ca="1"/>
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="75">
@@ -41938,7 +42036,7 @@
       </c>
       <c r="R13" s="279">
         <f ca="1"/>
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="14" spans="1:18" ht="60">
@@ -41946,22 +42044,22 @@
         <v>8</v>
       </c>
       <c r="B14" s="302" t="str">
-        <v/>
+        <v>ACS</v>
       </c>
       <c r="C14" s="282" t="str">
-        <v>LTIA-5.10-VIETUR-80000-RFA-SDS-0222A</v>
+        <v>LTIA-5.10-VIETUR-80000-RFA-SDS-0371</v>
       </c>
       <c r="D14" s="303" t="str">
-        <v>Construction design drawing of  ICT system – part.1: ICT systems for DATA CENTER 2 (DC2) &amp; TECHNICAL ROOM (EF,BD)</v>
+        <v xml:space="preserve">Construction design drawing of  ICT system – part.1: ICT systems for Duress Button Drawings. </v>
       </c>
       <c r="E14" s="303" t="str">
-        <v>Bản vẽ TKTC cho hệ thống ICT – phần 1 – Hệ thống ICT cho Trung tâm dữ liệu số 2 (DC2) và Phòng kỹ thuật (EF,BD)</v>
+        <v>Bản vẽ TKTC cho hệ thống ICT – phần 1 – Hệ thống ICT cho hệ thống nút nhấn khẩn cấp.</v>
       </c>
       <c r="F14" s="270">
-        <v>45919</v>
+        <v>45930</v>
       </c>
       <c r="G14" s="270">
-        <v>45919</v>
+        <v>45930</v>
       </c>
       <c r="H14" s="264">
         <v>45932</v>
@@ -41979,13 +42077,13 @@
         <v>B</v>
       </c>
       <c r="M14" s="270">
-        <v>46029</v>
+        <v>45978</v>
       </c>
       <c r="N14" s="264">
-        <v>46030</v>
+        <v>45979</v>
       </c>
       <c r="O14" s="264">
-        <v>46037</v>
+        <v>45986</v>
       </c>
       <c r="P14" s="270" t="str">
         <v/>
@@ -41996,7 +42094,7 @@
       </c>
       <c r="R14" s="279">
         <f ca="1"/>
-        <v>277</v>
+        <v>329</v>
       </c>
     </row>
     <row r="15" spans="1:18" ht="45">
@@ -42004,46 +42102,46 @@
         <v>9</v>
       </c>
       <c r="B15" s="302" t="str">
-        <v>ACS</v>
+        <v>FAS</v>
       </c>
       <c r="C15" s="282" t="str">
-        <v>LTIA-5.10-VIETUR-80000-RFA-SDS-0371</v>
+        <v>LTIA-5.10-VIETUR-80000-RFA-SDS-0197B</v>
       </c>
       <c r="D15" s="303" t="str">
-        <v xml:space="preserve">Construction design drawing of  ICT system – part.1: ICT systems for Duress Button Drawings. </v>
+        <v xml:space="preserve">Construction design drawing of  ICT system – part.1: ICT systems for 3F Level </v>
       </c>
       <c r="E15" s="303" t="str">
-        <v>Bản vẽ TKTC cho hệ thống ICT – phần 1 – Hệ thống ICT cho hệ thống nút nhấn khẩn cấp.</v>
+        <v>Bản vẽ TKTC cho hệ thống ICT – phần 1 – Hệ thống ICT cho tầng 3F</v>
       </c>
       <c r="F15" s="270">
-        <v>45930</v>
+        <v>45959</v>
       </c>
       <c r="G15" s="270">
-        <v>45930</v>
+        <v>45959</v>
       </c>
       <c r="H15" s="264">
-        <v>45932</v>
+        <v>45961</v>
       </c>
       <c r="I15" s="264" t="str">
         <v>B</v>
       </c>
       <c r="J15" s="270">
-        <v>45940</v>
+        <v>45945</v>
       </c>
       <c r="K15" s="264">
-        <v>45945</v>
+        <v>45980</v>
       </c>
       <c r="L15" s="264" t="str">
         <v>B</v>
       </c>
       <c r="M15" s="270">
-        <v>45978</v>
+        <v>45995</v>
       </c>
       <c r="N15" s="264">
-        <v>45979</v>
+        <v>45999</v>
       </c>
       <c r="O15" s="264">
-        <v>45986</v>
+        <v>46006</v>
       </c>
       <c r="P15" s="270" t="str">
         <v/>
@@ -42054,7 +42152,7 @@
       </c>
       <c r="R15" s="279">
         <f ca="1"/>
-        <v>328</v>
+        <v>309</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="45">
@@ -42062,57 +42160,57 @@
         <v>10</v>
       </c>
       <c r="B16" s="302" t="str">
-        <v>FAS</v>
+        <v>PAS</v>
       </c>
       <c r="C16" s="282" t="str">
-        <v>LTIA-5.10-VIETUR-80000-RFA-SDS-0197B</v>
+        <v>LTIA-5.10-VIETUR-80000-RFA-SDS-0394</v>
       </c>
       <c r="D16" s="303" t="str">
-        <v xml:space="preserve">Construction design drawing of  ICT system – part.1: ICT systems for 3F Level </v>
+        <v>Construction design drawing of  ICT system – part.1: ICT systems for Schematic Diagram Public Address System (PAS)</v>
       </c>
       <c r="E16" s="303" t="str">
-        <v>Bản vẽ TKTC cho hệ thống ICT – phần 1 – Hệ thống ICT cho tầng 3F</v>
+        <v>Bản vẽ TKTC cho hệ thống ICT – phần 1 – Hệ thống ICT cho SDNL hệ thống Phát Thanh</v>
       </c>
       <c r="F16" s="270">
-        <v>45959</v>
+        <v>45965</v>
       </c>
       <c r="G16" s="270">
-        <v>45959</v>
+        <v>45965</v>
       </c>
       <c r="H16" s="264">
-        <v>45961</v>
+        <v>45966</v>
       </c>
       <c r="I16" s="264" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
       <c r="J16" s="270">
-        <v>45945</v>
+        <v>45979</v>
       </c>
       <c r="K16" s="264">
-        <v>45980</v>
+        <v>45994</v>
       </c>
       <c r="L16" s="264" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
       <c r="M16" s="270">
-        <v>45995</v>
+        <v>46146</v>
       </c>
       <c r="N16" s="264">
-        <v>45999</v>
+        <v>46136</v>
       </c>
       <c r="O16" s="264">
-        <v>46006</v>
-      </c>
-      <c r="P16" s="270" t="str">
-        <v/>
+        <v>46143</v>
+      </c>
+      <c r="P16" s="270">
+        <v>46268</v>
       </c>
       <c r="Q16" s="13" t="str">
         <f ca="1"/>
-        <v>Not submit yet</v>
+        <v>Late Resubmission</v>
       </c>
       <c r="R16" s="279">
         <f ca="1"/>
-        <v>308</v>
+        <v>125</v>
       </c>
     </row>
     <row r="17" spans="1:18" ht="60">
@@ -42123,114 +42221,57 @@
         <v>PAS</v>
       </c>
       <c r="C17" s="282" t="str">
-        <v>LTIA-5.10-VIETUR-80000-RFA-SDS-0394</v>
+        <v>LTIA-5.10-VIETUR-80000-RFA-SDS-0160B</v>
       </c>
       <c r="D17" s="303" t="str">
-        <v>Construction design drawing of  ICT system – part.1: ICT systems for Schematic Diagram Public Address System (PAS)</v>
+        <v xml:space="preserve">Construction design drawing of  ICT system – part.1: ICT systems for GF Level </v>
       </c>
       <c r="E17" s="303" t="str">
-        <v>Bản vẽ TKTC cho hệ thống ICT – phần 1 – Hệ thống ICT cho SDNL hệ thống Phát Thanh</v>
+        <v>Bản vẽ TKTC cho hệ thống ICT – phần 1 – Hệ thống ICT cho tầng GF</v>
       </c>
       <c r="F17" s="270">
-        <v>45965</v>
+        <v>45972</v>
       </c>
       <c r="G17" s="270">
-        <v>45965</v>
+        <v>45972</v>
       </c>
       <c r="H17" s="264">
-        <v>45966</v>
+        <v>45972</v>
       </c>
       <c r="I17" s="264" t="str">
-        <v>C</v>
+        <v>B</v>
       </c>
       <c r="J17" s="270">
-        <v>45979</v>
+        <v>45982</v>
       </c>
       <c r="K17" s="264">
-        <v>45994</v>
+        <v>45982</v>
       </c>
       <c r="L17" s="264" t="str">
-        <v>C</v>
+        <v>B</v>
       </c>
       <c r="M17" s="270">
-        <v>46146</v>
+        <v>45995</v>
       </c>
       <c r="N17" s="264">
-        <v>46136</v>
+        <v>45999</v>
       </c>
       <c r="O17" s="264">
-        <v>46143</v>
-      </c>
-      <c r="P17" s="270">
-        <v>46268</v>
+        <v>46006</v>
+      </c>
+      <c r="P17" s="270" t="str">
+        <v/>
       </c>
       <c r="Q17" s="13" t="str">
         <f ca="1"/>
-        <v>Late Resubmission</v>
+        <v>Not submit yet</v>
       </c>
       <c r="R17" s="279">
         <f ca="1"/>
-        <v>125</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18" ht="45">
-      <c r="A18" s="13">
-        <v>12</v>
-      </c>
-      <c r="B18" s="302" t="str">
-        <v>PAS</v>
-      </c>
-      <c r="C18" s="282" t="str">
-        <v>LTIA-5.10-VIETUR-80000-RFA-SDS-0160B</v>
-      </c>
-      <c r="D18" s="303" t="str">
-        <v xml:space="preserve">Construction design drawing of  ICT system – part.1: ICT systems for GF Level </v>
-      </c>
-      <c r="E18" s="303" t="str">
-        <v>Bản vẽ TKTC cho hệ thống ICT – phần 1 – Hệ thống ICT cho tầng GF</v>
-      </c>
-      <c r="F18" s="270">
-        <v>45972</v>
-      </c>
-      <c r="G18" s="270">
-        <v>45972</v>
-      </c>
-      <c r="H18" s="264">
-        <v>45972</v>
-      </c>
-      <c r="I18" s="264" t="str">
-        <v>B</v>
-      </c>
-      <c r="J18" s="270">
-        <v>45982</v>
-      </c>
-      <c r="K18" s="264">
-        <v>45982</v>
-      </c>
-      <c r="L18" s="264" t="str">
-        <v>B</v>
-      </c>
-      <c r="M18" s="270">
-        <v>45995</v>
-      </c>
-      <c r="N18" s="264">
-        <v>45999</v>
-      </c>
-      <c r="O18" s="264">
-        <v>46006</v>
-      </c>
-      <c r="P18" s="270" t="str">
-        <v/>
-      </c>
-      <c r="Q18" s="13" t="str">
-        <f ca="1"/>
-        <v>Not submit yet</v>
-      </c>
-      <c r="R18" s="279">
-        <f ca="1"/>
-        <v>308</v>
-      </c>
-    </row>
+        <v>309</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" ht="45"/>
   </sheetData>
   <autoFilter ref="A6:R6" xr:uid="{75733AF3-96C4-423A-BD99-1E08B3C66916}"/>
   <mergeCells count="9">
@@ -42286,19 +42327,19 @@
     <row r="3" spans="1:4" ht="15.75">
       <c r="A3" s="319">
         <f ca="1">MAX('Need ReSub (RFA)'!S7:S76)</f>
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="B3" s="319">
         <f ca="1">AVERAGEIF('Need ReSub (RFA)'!S7:S76,"&lt;&gt;0")</f>
-        <v>459.25</v>
+        <v>460.25</v>
       </c>
       <c r="C3" s="319">
         <f ca="1">MAX(_xlfn.ANCHORARRAY('Need ReSub (RFA-SDS)'!R7))</f>
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="D3" s="319">
         <f ca="1">AVERAGEIF(_xlfn.ANCHORARRAY('Need ReSub (RFA-SDS)'!R7),"&lt;&gt;0")</f>
-        <v>342.33333333333331</v>
+        <v>349.18181818181819</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -42307,10 +42348,10 @@
 Furthermore, the RFA (SDS) is as follows:
 Avarage :  " &amp; ROUND($D$3,0) &amp; " days
 Maimum :  " &amp; ROUND($C$3,0) &amp; " days"</f>
-        <v>In the RFA process, the average number of days elapsed since responding to an unapproved RFA was 459 days, with a maximum of 851 days, indicating that delays in the RFA approval process are contributing to delays in construction work.
+        <v>In the RFA process, the average number of days elapsed since responding to an unapproved RFA was 460 days, with a maximum of 852 days, indicating that delays in the RFA approval process are contributing to delays in construction work.
 Furthermore, the RFA (SDS) is as follows:
-Avarage :  342 days
-Maimum :  551 days</v>
+Avarage :  349 days
+Maimum :  552 days</v>
       </c>
       <c r="B5" s="452"/>
     </row>

--- a/ICT-RFA-RFI-lists-New.xlsx
+++ b/ICT-RFA-RFI-lists-New.xlsx
@@ -9,9 +9,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project Airport\LTIA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BF5D713-AEFB-4B9C-A558-01D45CE3E09E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{458764C3-D111-42DD-B0BC-919B4BC6EA75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="506" activeTab="1" xr2:uid="{CCA8147E-0981-4321-B87F-440A52C0DA59}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="506" activeTab="2" xr2:uid="{CCA8147E-0981-4321-B87F-440A52C0DA59}"/>
   </bookViews>
   <sheets>
     <sheet name="RFA" sheetId="1" r:id="rId1"/>
@@ -78,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3497" uniqueCount="1099">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3507" uniqueCount="1101">
   <si>
     <t>TT</t>
   </si>
@@ -5036,10 +5036,6 @@
     <t>10/12/2026: Đã comment</t>
   </si>
   <si>
-    <t>10/12/2026: Đã comment
-10/13/2026: Đã gửi comment qua CNC</t>
-  </si>
-  <si>
     <t>LTIA-5.11-LTICT- 71110 -RFA-OTH-0012</t>
   </si>
   <si>
@@ -5143,15 +5139,27 @@
     <t>Đề nghị phê duyệt kiến trúc mạng và quy hoạch IP-VLAN</t>
   </si>
   <si>
-    <t>101/14/2026: Đã comment
+    <t>LTIA-5.10-VIETUR-80000-RFA-SDS-0222B</t>
+  </si>
+  <si>
+    <t>Construction design drawing of  ICT system – part.1: ICT systems for DATA CENTER 2 (DC2) &amp; TECHNICAL ROOM (EF,BD)</t>
+  </si>
+  <si>
+    <t>10/19/2026: Đã comment</t>
+  </si>
+  <si>
+    <t>10/12/2026: Đã comment
+10/13/2026: Đã gửi comment qua CNC
+10/19/2026: Đã ký C</t>
+  </si>
+  <si>
+    <t>10/14/2026: Đã comment
 10/15/2026 Đã gửi CNC
 10/15/2026: Đã ký RFCS</t>
   </si>
   <si>
-    <t>LTIA-5.10-VIETUR-80000-RFA-SDS-0222B</t>
-  </si>
-  <si>
-    <t>Construction design drawing of  ICT system – part.1: ICT systems for DATA CENTER 2 (DC2) &amp; TECHNICAL ROOM (EF,BD)</t>
+    <t>10/16/2026: Đã comment và gửi CNC
+10/19/2026: Đã ký RFCS</t>
   </si>
 </sst>
 </file>
@@ -7588,23 +7596,272 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="55" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="51" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="52" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="55" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="53" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="47" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="45" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="58" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -7618,259 +7875,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="45" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="53" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="47" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="51" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="52" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="55" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="55" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -8534,92 +8542,92 @@
       <c r="AE3" s="159"/>
     </row>
     <row r="4" spans="1:35" s="5" customFormat="1" ht="36" customHeight="1" thickBot="1">
-      <c r="A4" s="396" t="s">
+      <c r="A4" s="354" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="350" t="s">
+      <c r="B4" s="366" t="s">
         <v>515</v>
       </c>
-      <c r="C4" s="364" t="s">
+      <c r="C4" s="362" t="s">
         <v>45</v>
       </c>
-      <c r="D4" s="358" t="s">
+      <c r="D4" s="404" t="s">
         <v>95</v>
       </c>
-      <c r="E4" s="352" t="s">
+      <c r="E4" s="356" t="s">
         <v>46</v>
       </c>
-      <c r="F4" s="400" t="s">
+      <c r="F4" s="358" t="s">
         <v>47</v>
       </c>
-      <c r="G4" s="352" t="s">
+      <c r="G4" s="356" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="398" t="s">
+      <c r="H4" s="360" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="358" t="s">
+      <c r="I4" s="404" t="s">
         <v>48</v>
       </c>
-      <c r="J4" s="358" t="s">
+      <c r="J4" s="404" t="s">
         <v>49</v>
       </c>
-      <c r="K4" s="352" t="s">
+      <c r="K4" s="356" t="s">
         <v>78</v>
       </c>
-      <c r="L4" s="358" t="s">
+      <c r="L4" s="404" t="s">
         <v>80</v>
       </c>
-      <c r="M4" s="363" t="s">
+      <c r="M4" s="406" t="s">
         <v>53</v>
       </c>
-      <c r="N4" s="348"/>
-      <c r="O4" s="363" t="s">
+      <c r="N4" s="407"/>
+      <c r="O4" s="406" t="s">
         <v>55</v>
       </c>
-      <c r="P4" s="348"/>
-      <c r="Q4" s="362" t="s">
+      <c r="P4" s="407"/>
+      <c r="Q4" s="408" t="s">
         <v>72</v>
       </c>
-      <c r="R4" s="348"/>
-      <c r="S4" s="363" t="s">
+      <c r="R4" s="407"/>
+      <c r="S4" s="406" t="s">
         <v>53</v>
       </c>
-      <c r="T4" s="363"/>
-      <c r="U4" s="348"/>
-      <c r="V4" s="362" t="s">
+      <c r="T4" s="406"/>
+      <c r="U4" s="407"/>
+      <c r="V4" s="408" t="s">
         <v>55</v>
       </c>
-      <c r="W4" s="363"/>
-      <c r="X4" s="348"/>
-      <c r="Y4" s="366" t="s">
+      <c r="W4" s="406"/>
+      <c r="X4" s="407"/>
+      <c r="Y4" s="350" t="s">
         <v>72</v>
       </c>
-      <c r="Z4" s="367"/>
-      <c r="AA4" s="429" t="s">
+      <c r="Z4" s="412"/>
+      <c r="AA4" s="411" t="s">
         <v>112</v>
       </c>
-      <c r="AB4" s="430"/>
-      <c r="AC4" s="430"/>
-      <c r="AD4" s="431"/>
-      <c r="AE4" s="352" t="s">
+      <c r="AB4" s="352"/>
+      <c r="AC4" s="352"/>
+      <c r="AD4" s="353"/>
+      <c r="AE4" s="356" t="s">
         <v>79</v>
       </c>
       <c r="AG4" s="236"/>
     </row>
     <row r="5" spans="1:35" ht="78.75">
-      <c r="A5" s="397"/>
-      <c r="B5" s="351"/>
-      <c r="C5" s="365"/>
-      <c r="D5" s="359"/>
-      <c r="E5" s="353"/>
-      <c r="F5" s="401"/>
-      <c r="G5" s="353"/>
-      <c r="H5" s="399"/>
-      <c r="I5" s="359"/>
-      <c r="J5" s="359"/>
-      <c r="K5" s="353"/>
-      <c r="L5" s="359"/>
+      <c r="A5" s="355"/>
+      <c r="B5" s="367"/>
+      <c r="C5" s="363"/>
+      <c r="D5" s="405"/>
+      <c r="E5" s="357"/>
+      <c r="F5" s="359"/>
+      <c r="G5" s="357"/>
+      <c r="H5" s="361"/>
+      <c r="I5" s="405"/>
+      <c r="J5" s="405"/>
+      <c r="K5" s="357"/>
+      <c r="L5" s="405"/>
       <c r="M5" s="79" t="s">
         <v>52</v>
       </c>
@@ -8674,14 +8682,14 @@
       <c r="AD5" s="336" t="s">
         <v>118</v>
       </c>
-      <c r="AE5" s="349"/>
-      <c r="AG5" s="352" t="s">
+      <c r="AE5" s="403"/>
+      <c r="AG5" s="356" t="s">
         <v>119</v>
       </c>
-      <c r="AH5" s="352" t="s">
+      <c r="AH5" s="356" t="s">
         <v>120</v>
       </c>
-      <c r="AI5" s="352" t="s">
+      <c r="AI5" s="356" t="s">
         <v>121</v>
       </c>
     </row>
@@ -8717,9 +8725,9 @@
       <c r="AC6" s="86"/>
       <c r="AD6" s="86"/>
       <c r="AE6" s="74"/>
-      <c r="AG6" s="395"/>
-      <c r="AH6" s="395"/>
-      <c r="AI6" s="395"/>
+      <c r="AG6" s="427"/>
+      <c r="AH6" s="427"/>
+      <c r="AI6" s="427"/>
     </row>
     <row r="7" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A7" s="33">
@@ -21329,7 +21337,7 @@
         <v>28</v>
       </c>
       <c r="E119" s="25" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="F119" s="174">
         <f t="shared" si="29"/>
@@ -22478,7 +22486,9 @@
       <c r="AB130" s="229"/>
       <c r="AC130" s="229"/>
       <c r="AD130" s="337"/>
-      <c r="AE130" s="92"/>
+      <c r="AE130" s="92" t="s">
+        <v>1097</v>
+      </c>
       <c r="AG130" s="238" t="str">
         <f t="shared" si="75"/>
         <v>LTIA-5.11-LTICT- 72010 -RFA-MSS-0003</v>
@@ -22527,7 +22537,9 @@
       <c r="H131" s="21" t="s">
         <v>1038</v>
       </c>
-      <c r="I131" s="138"/>
+      <c r="I131" s="138" t="s">
+        <v>1</v>
+      </c>
       <c r="J131" s="164">
         <f t="shared" ca="1" si="30"/>
         <v>15</v>
@@ -22556,7 +22568,9 @@
       </c>
       <c r="V131" s="29"/>
       <c r="W131" s="188"/>
-      <c r="X131" s="235"/>
+      <c r="X131" s="235" t="s">
+        <v>240</v>
+      </c>
       <c r="Y131" s="230"/>
       <c r="Z131" s="227"/>
       <c r="AA131" s="29" t="str">
@@ -22567,7 +22581,7 @@
       <c r="AC131" s="229"/>
       <c r="AD131" s="337"/>
       <c r="AE131" s="92" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="AG131" s="238" t="str">
         <f t="shared" si="75"/>
@@ -22586,7 +22600,7 @@
       </c>
       <c r="AI131" s="75" t="str">
         <f t="shared" si="74"/>
-        <v/>
+        <v>YES</v>
       </c>
     </row>
     <row r="132" spans="1:35" s="9" customFormat="1" ht="47.25">
@@ -22617,7 +22631,9 @@
       <c r="H132" s="21" t="s">
         <v>1041</v>
       </c>
-      <c r="I132" s="138"/>
+      <c r="I132" s="138" t="s">
+        <v>1</v>
+      </c>
       <c r="J132" s="164">
         <f t="shared" ca="1" si="30"/>
         <v>14</v>
@@ -22646,7 +22662,9 @@
       </c>
       <c r="V132" s="29"/>
       <c r="W132" s="188"/>
-      <c r="X132" s="235"/>
+      <c r="X132" s="235" t="s">
+        <v>240</v>
+      </c>
       <c r="Y132" s="230"/>
       <c r="Z132" s="227"/>
       <c r="AA132" s="29" t="str">
@@ -22657,7 +22675,7 @@
       <c r="AC132" s="229"/>
       <c r="AD132" s="337"/>
       <c r="AE132" s="92" t="s">
-        <v>1063</v>
+        <v>1098</v>
       </c>
       <c r="AG132" s="238" t="str">
         <f t="shared" si="75"/>
@@ -22676,7 +22694,7 @@
       </c>
       <c r="AI132" s="75" t="str">
         <f t="shared" si="74"/>
-        <v/>
+        <v>YES</v>
       </c>
     </row>
     <row r="133" spans="1:35" s="9" customFormat="1" ht="47.25">
@@ -22746,7 +22764,9 @@
       <c r="AB133" s="229"/>
       <c r="AC133" s="229"/>
       <c r="AD133" s="337"/>
-      <c r="AE133" s="92"/>
+      <c r="AE133" s="92" t="s">
+        <v>1097</v>
+      </c>
       <c r="AG133" s="238" t="str">
         <f t="shared" si="75"/>
         <v>LTIA-5.11-LTICT- 72190 -RFA-MSS-0005</v>
@@ -22834,7 +22854,9 @@
       <c r="AB134" s="229"/>
       <c r="AC134" s="229"/>
       <c r="AD134" s="337"/>
-      <c r="AE134" s="92"/>
+      <c r="AE134" s="92" t="s">
+        <v>1097</v>
+      </c>
       <c r="AG134" s="238" t="str">
         <f t="shared" si="75"/>
         <v>LTIA-5.11-LTICT- 71110 -RFA-MSS-0006</v>
@@ -22933,7 +22955,7 @@
       <c r="AC135" s="229"/>
       <c r="AD135" s="337"/>
       <c r="AE135" s="92" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="AG135" s="238" t="str">
         <f t="shared" si="75"/>
@@ -22971,17 +22993,17 @@
         <v>32</v>
       </c>
       <c r="E136" s="25" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="F136" s="174">
         <f t="shared" si="29"/>
         <v>46330</v>
       </c>
       <c r="G136" s="31" t="s">
+        <v>1073</v>
+      </c>
+      <c r="H136" s="21" t="s">
         <v>1074</v>
-      </c>
-      <c r="H136" s="21" t="s">
-        <v>1075</v>
       </c>
       <c r="I136" s="138"/>
       <c r="J136" s="164">
@@ -23059,17 +23081,17 @@
         <v>32</v>
       </c>
       <c r="E137" s="25" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="F137" s="174">
         <f t="shared" si="29"/>
         <v>46330</v>
       </c>
       <c r="G137" s="31" t="s">
+        <v>1076</v>
+      </c>
+      <c r="H137" s="21" t="s">
         <v>1077</v>
-      </c>
-      <c r="H137" s="21" t="s">
-        <v>1078</v>
       </c>
       <c r="I137" s="138"/>
       <c r="J137" s="164">
@@ -23141,23 +23163,23 @@
         <v>5.11</v>
       </c>
       <c r="C138" s="164" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="D138" s="137" t="s">
         <v>32</v>
       </c>
       <c r="E138" s="25" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="F138" s="174">
         <f t="shared" si="29"/>
         <v>46330</v>
       </c>
       <c r="G138" s="31" t="s">
+        <v>1079</v>
+      </c>
+      <c r="H138" s="21" t="s">
         <v>1080</v>
-      </c>
-      <c r="H138" s="21" t="s">
-        <v>1081</v>
       </c>
       <c r="I138" s="138"/>
       <c r="J138" s="164">
@@ -23229,23 +23251,23 @@
         <v>5.11</v>
       </c>
       <c r="C139" s="164" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="D139" s="137" t="s">
         <v>32</v>
       </c>
       <c r="E139" s="25" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="F139" s="174">
         <f t="shared" si="29"/>
         <v>46330</v>
       </c>
       <c r="G139" s="31" t="s">
+        <v>1083</v>
+      </c>
+      <c r="H139" s="21" t="s">
         <v>1084</v>
-      </c>
-      <c r="H139" s="21" t="s">
-        <v>1085</v>
       </c>
       <c r="I139" s="138"/>
       <c r="J139" s="164">
@@ -23323,17 +23345,17 @@
         <v>32</v>
       </c>
       <c r="E140" s="25" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="F140" s="174">
         <f t="shared" si="29"/>
         <v>46331</v>
       </c>
       <c r="G140" s="31" t="s">
+        <v>1087</v>
+      </c>
+      <c r="H140" s="21" t="s">
         <v>1088</v>
-      </c>
-      <c r="H140" s="21" t="s">
-        <v>1089</v>
       </c>
       <c r="I140" s="138"/>
       <c r="J140" s="164">
@@ -23411,17 +23433,17 @@
         <v>28</v>
       </c>
       <c r="E141" s="25" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="F141" s="174">
         <f t="shared" si="29"/>
         <v>46333</v>
       </c>
       <c r="G141" s="31" t="s">
+        <v>1093</v>
+      </c>
+      <c r="H141" s="21" t="s">
         <v>1094</v>
-      </c>
-      <c r="H141" s="21" t="s">
-        <v>1095</v>
       </c>
       <c r="I141" s="138"/>
       <c r="J141" s="164">
@@ -23574,29 +23596,29 @@
       <c r="C145" s="166" t="s">
         <v>20</v>
       </c>
-      <c r="D145" s="416" t="s">
+      <c r="D145" s="364" t="s">
         <v>21</v>
       </c>
-      <c r="E145" s="416"/>
-      <c r="F145" s="417"/>
+      <c r="E145" s="364"/>
+      <c r="F145" s="365"/>
       <c r="G145" s="46"/>
       <c r="H145" s="68"/>
-      <c r="I145" s="392" t="s">
+      <c r="I145" s="377" t="s">
         <v>14</v>
       </c>
-      <c r="J145" s="393"/>
-      <c r="K145" s="393"/>
-      <c r="L145" s="393"/>
-      <c r="M145" s="393"/>
-      <c r="N145" s="394"/>
-      <c r="O145" s="388" t="s">
+      <c r="J145" s="378"/>
+      <c r="K145" s="378"/>
+      <c r="L145" s="378"/>
+      <c r="M145" s="378"/>
+      <c r="N145" s="379"/>
+      <c r="O145" s="348" t="s">
         <v>7</v>
       </c>
-      <c r="P145" s="389"/>
-      <c r="Q145" s="388" t="s">
+      <c r="P145" s="349"/>
+      <c r="Q145" s="348" t="s">
         <v>109</v>
       </c>
-      <c r="R145" s="389"/>
+      <c r="R145" s="349"/>
       <c r="S145" s="1"/>
       <c r="T145" s="1"/>
       <c r="U145" s="140"/>
@@ -23618,26 +23640,26 @@
       <c r="C146" s="167" t="s">
         <v>109</v>
       </c>
-      <c r="D146" s="427" t="s">
+      <c r="D146" s="409" t="s">
         <v>111</v>
       </c>
-      <c r="E146" s="427"/>
-      <c r="F146" s="428"/>
+      <c r="E146" s="409"/>
+      <c r="F146" s="410"/>
       <c r="G146" s="46"/>
       <c r="H146" s="46"/>
-      <c r="I146" s="392" t="s">
+      <c r="I146" s="377" t="s">
         <v>19</v>
       </c>
-      <c r="J146" s="393"/>
-      <c r="K146" s="393"/>
-      <c r="L146" s="394"/>
+      <c r="J146" s="378"/>
+      <c r="K146" s="378"/>
+      <c r="L146" s="379"/>
       <c r="M146" s="105">
         <f t="shared" ref="M146:M151" ca="1" si="89">N146/$N$146</f>
         <v>1</v>
       </c>
       <c r="N146" s="106">
         <f ca="1">SUM($N$147:$N$151)</f>
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O146" s="102" t="s">
         <v>15</v>
@@ -23674,22 +23696,22 @@
       <c r="C147" s="167" t="s">
         <v>22</v>
       </c>
-      <c r="D147" s="427" t="s">
+      <c r="D147" s="409" t="s">
         <v>23</v>
       </c>
-      <c r="E147" s="427"/>
-      <c r="F147" s="428"/>
+      <c r="E147" s="409"/>
+      <c r="F147" s="410"/>
       <c r="G147" s="70"/>
       <c r="H147" s="6"/>
-      <c r="I147" s="418" t="s">
+      <c r="I147" s="371" t="s">
         <v>66</v>
       </c>
-      <c r="J147" s="419"/>
-      <c r="K147" s="419"/>
-      <c r="L147" s="420"/>
+      <c r="J147" s="372"/>
+      <c r="K147" s="372"/>
+      <c r="L147" s="373"/>
       <c r="M147" s="107">
         <f t="shared" ca="1" si="89"/>
-        <v>0.49285714285714288</v>
+        <v>0.4859154929577465</v>
       </c>
       <c r="N147" s="108">
         <f>COUNTIF($I$7:$I$143,"A")</f>
@@ -23732,21 +23754,21 @@
       <c r="C148" s="167" t="s">
         <v>24</v>
       </c>
-      <c r="D148" s="427" t="s">
+      <c r="D148" s="409" t="s">
         <v>25</v>
       </c>
-      <c r="E148" s="427"/>
-      <c r="F148" s="428"/>
+      <c r="E148" s="409"/>
+      <c r="F148" s="410"/>
       <c r="H148" s="6"/>
-      <c r="I148" s="421" t="s">
+      <c r="I148" s="374" t="s">
         <v>67</v>
       </c>
-      <c r="J148" s="422"/>
-      <c r="K148" s="422"/>
-      <c r="L148" s="423"/>
+      <c r="J148" s="375"/>
+      <c r="K148" s="375"/>
+      <c r="L148" s="376"/>
       <c r="M148" s="109">
         <f t="shared" ca="1" si="89"/>
-        <v>0.1</v>
+        <v>9.8591549295774641E-2</v>
       </c>
       <c r="N148" s="110">
         <f>COUNTIF($I$7:$I$143,"B")</f>
@@ -23789,30 +23811,30 @@
       <c r="C149" s="167" t="s">
         <v>26</v>
       </c>
-      <c r="D149" s="427" t="s">
+      <c r="D149" s="409" t="s">
         <v>27</v>
       </c>
-      <c r="E149" s="427"/>
-      <c r="F149" s="428"/>
+      <c r="E149" s="409"/>
+      <c r="F149" s="410"/>
       <c r="G149" s="71"/>
       <c r="H149" s="6"/>
-      <c r="I149" s="424" t="s">
+      <c r="I149" s="380" t="s">
         <v>68</v>
       </c>
-      <c r="J149" s="425"/>
-      <c r="K149" s="425"/>
-      <c r="L149" s="426"/>
+      <c r="J149" s="381"/>
+      <c r="K149" s="381"/>
+      <c r="L149" s="382"/>
       <c r="M149" s="111">
         <f t="shared" ca="1" si="89"/>
-        <v>0.19285714285714287</v>
+        <v>0.20422535211267606</v>
       </c>
       <c r="N149" s="112">
         <f>COUNTIF($I$7:$I$143,"C")</f>
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="O149" s="98">
         <f ca="1">COUNTIFS($J$7:$J$143,"&lt;=21",$I$7:$I$143,"C")</f>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="P149" s="50">
         <f ca="1">COUNTIFS($J$7:$J$143,"&gt;21",$I$7:$I$143,"C")</f>
@@ -23847,21 +23869,21 @@
       <c r="C150" s="168" t="s">
         <v>28</v>
       </c>
-      <c r="D150" s="427" t="s">
+      <c r="D150" s="409" t="s">
         <v>29</v>
       </c>
-      <c r="E150" s="427"/>
-      <c r="F150" s="428"/>
+      <c r="E150" s="409"/>
+      <c r="F150" s="410"/>
       <c r="G150" s="72"/>
-      <c r="I150" s="374" t="s">
+      <c r="I150" s="383" t="s">
         <v>70</v>
       </c>
-      <c r="J150" s="375"/>
-      <c r="K150" s="375"/>
-      <c r="L150" s="376"/>
+      <c r="J150" s="384"/>
+      <c r="K150" s="384"/>
+      <c r="L150" s="385"/>
       <c r="M150" s="114">
         <f t="shared" ca="1" si="89"/>
-        <v>0.10714285714285714</v>
+        <v>0.10563380281690141</v>
       </c>
       <c r="N150" s="115">
         <f ca="1">SUM(O150:P150)</f>
@@ -23906,21 +23928,21 @@
       <c r="C151" s="168" t="s">
         <v>30</v>
       </c>
-      <c r="D151" s="427" t="s">
+      <c r="D151" s="409" t="s">
         <v>31</v>
       </c>
-      <c r="E151" s="427"/>
-      <c r="F151" s="428"/>
+      <c r="E151" s="409"/>
+      <c r="F151" s="410"/>
       <c r="H151" s="6"/>
-      <c r="I151" s="377" t="s">
+      <c r="I151" s="400" t="s">
         <v>71</v>
       </c>
-      <c r="J151" s="378"/>
-      <c r="K151" s="378"/>
-      <c r="L151" s="379"/>
+      <c r="J151" s="401"/>
+      <c r="K151" s="401"/>
+      <c r="L151" s="402"/>
       <c r="M151" s="113">
         <f t="shared" ca="1" si="89"/>
-        <v>0.10714285714285714</v>
+        <v>0.10563380281690141</v>
       </c>
       <c r="N151" s="97">
         <f>COUNTIFS($L$7:$L$143,"X")</f>
@@ -23937,11 +23959,11 @@
       <c r="C152" s="168" t="s">
         <v>32</v>
       </c>
-      <c r="D152" s="427" t="s">
+      <c r="D152" s="409" t="s">
         <v>33</v>
       </c>
-      <c r="E152" s="427"/>
-      <c r="F152" s="428"/>
+      <c r="E152" s="409"/>
+      <c r="F152" s="410"/>
       <c r="H152" s="1" t="s">
         <v>11</v>
       </c>
@@ -23950,11 +23972,11 @@
       <c r="C153" s="167" t="s">
         <v>34</v>
       </c>
-      <c r="D153" s="427" t="s">
+      <c r="D153" s="409" t="s">
         <v>35</v>
       </c>
-      <c r="E153" s="427"/>
-      <c r="F153" s="428"/>
+      <c r="E153" s="409"/>
+      <c r="F153" s="410"/>
       <c r="H153" s="13"/>
       <c r="I153" s="141"/>
       <c r="J153" s="141"/>
@@ -23982,14 +24004,14 @@
       <c r="AI153" s="1"/>
     </row>
     <row r="154" spans="1:35">
-      <c r="C154" s="382" t="s">
+      <c r="C154" s="386" t="s">
         <v>75</v>
       </c>
-      <c r="D154" s="384" t="s">
+      <c r="D154" s="388" t="s">
         <v>76</v>
       </c>
-      <c r="E154" s="384"/>
-      <c r="F154" s="385"/>
+      <c r="E154" s="388"/>
+      <c r="F154" s="389"/>
       <c r="H154" s="13"/>
       <c r="J154" s="141"/>
       <c r="K154" s="13"/>
@@ -24016,10 +24038,10 @@
       <c r="AI154" s="1"/>
     </row>
     <row r="155" spans="1:35" ht="16.5" thickBot="1">
-      <c r="C155" s="383"/>
-      <c r="D155" s="386"/>
-      <c r="E155" s="386"/>
-      <c r="F155" s="387"/>
+      <c r="C155" s="387"/>
+      <c r="D155" s="390"/>
+      <c r="E155" s="390"/>
+      <c r="F155" s="391"/>
       <c r="H155" s="13"/>
       <c r="I155" s="141"/>
       <c r="J155" s="141"/>
@@ -24110,11 +24132,11 @@
       <c r="C158" s="169" t="s">
         <v>8</v>
       </c>
-      <c r="D158" s="404" t="s">
+      <c r="D158" s="416" t="s">
         <v>91</v>
       </c>
-      <c r="E158" s="404"/>
-      <c r="F158" s="404"/>
+      <c r="E158" s="416"/>
+      <c r="F158" s="416"/>
       <c r="H158" s="13"/>
       <c r="I158" s="141"/>
       <c r="J158" s="141"/>
@@ -24145,11 +24167,11 @@
       <c r="C159" s="169" t="s">
         <v>8</v>
       </c>
-      <c r="D159" s="404" t="s">
+      <c r="D159" s="416" t="s">
         <v>92</v>
       </c>
-      <c r="E159" s="404"/>
-      <c r="F159" s="404"/>
+      <c r="E159" s="416"/>
+      <c r="F159" s="416"/>
       <c r="H159" s="13"/>
       <c r="I159" s="141"/>
       <c r="J159" s="141"/>
@@ -24180,11 +24202,11 @@
       <c r="C160" s="169" t="s">
         <v>8</v>
       </c>
-      <c r="D160" s="404" t="s">
+      <c r="D160" s="416" t="s">
         <v>93</v>
       </c>
-      <c r="E160" s="404"/>
-      <c r="F160" s="404"/>
+      <c r="E160" s="416"/>
+      <c r="F160" s="416"/>
       <c r="H160" s="13"/>
       <c r="I160" s="141"/>
       <c r="J160" s="141"/>
@@ -24239,12 +24261,12 @@
       <c r="AI161" s="1"/>
     </row>
     <row r="162" spans="3:35" ht="16.5" thickBot="1">
-      <c r="C162" s="408" t="s">
+      <c r="C162" s="422" t="s">
         <v>96</v>
       </c>
-      <c r="D162" s="409"/>
-      <c r="E162" s="409"/>
-      <c r="F162" s="410"/>
+      <c r="D162" s="423"/>
+      <c r="E162" s="423"/>
+      <c r="F162" s="424"/>
       <c r="H162" s="13"/>
       <c r="I162" s="141"/>
       <c r="J162" s="141"/>
@@ -24275,11 +24297,11 @@
       <c r="C163" s="212" t="s">
         <v>81</v>
       </c>
-      <c r="D163" s="411" t="s">
+      <c r="D163" s="425" t="s">
         <v>97</v>
       </c>
-      <c r="E163" s="411"/>
-      <c r="F163" s="412"/>
+      <c r="E163" s="425"/>
+      <c r="F163" s="426"/>
       <c r="H163" s="13"/>
       <c r="I163" s="141"/>
       <c r="J163" s="141"/>
@@ -24310,91 +24332,91 @@
       <c r="C164" s="213" t="s">
         <v>82</v>
       </c>
-      <c r="D164" s="402" t="s">
+      <c r="D164" s="417" t="s">
         <v>98</v>
       </c>
-      <c r="E164" s="402"/>
-      <c r="F164" s="403"/>
+      <c r="E164" s="417"/>
+      <c r="F164" s="418"/>
     </row>
     <row r="165" spans="3:35">
       <c r="C165" s="213" t="s">
         <v>83</v>
       </c>
-      <c r="D165" s="402" t="s">
+      <c r="D165" s="417" t="s">
         <v>99</v>
       </c>
-      <c r="E165" s="402"/>
-      <c r="F165" s="403"/>
+      <c r="E165" s="417"/>
+      <c r="F165" s="418"/>
     </row>
     <row r="166" spans="3:35">
       <c r="C166" s="214" t="s">
         <v>84</v>
       </c>
-      <c r="D166" s="402" t="s">
+      <c r="D166" s="417" t="s">
         <v>100</v>
       </c>
-      <c r="E166" s="402"/>
-      <c r="F166" s="403"/>
+      <c r="E166" s="417"/>
+      <c r="F166" s="418"/>
     </row>
     <row r="167" spans="3:35">
       <c r="C167" s="214" t="s">
         <v>85</v>
       </c>
-      <c r="D167" s="402" t="s">
+      <c r="D167" s="417" t="s">
         <v>101</v>
       </c>
-      <c r="E167" s="402"/>
-      <c r="F167" s="403"/>
+      <c r="E167" s="417"/>
+      <c r="F167" s="418"/>
     </row>
     <row r="168" spans="3:35" ht="18.75">
       <c r="C168" s="214" t="s">
         <v>86</v>
       </c>
-      <c r="D168" s="402" t="s">
+      <c r="D168" s="417" t="s">
         <v>102</v>
       </c>
-      <c r="E168" s="402"/>
-      <c r="F168" s="403"/>
+      <c r="E168" s="417"/>
+      <c r="F168" s="418"/>
     </row>
     <row r="169" spans="3:35" ht="18.75">
       <c r="C169" s="213" t="s">
         <v>87</v>
       </c>
-      <c r="D169" s="402" t="s">
+      <c r="D169" s="417" t="s">
         <v>103</v>
       </c>
-      <c r="E169" s="402"/>
-      <c r="F169" s="403"/>
+      <c r="E169" s="417"/>
+      <c r="F169" s="418"/>
     </row>
     <row r="170" spans="3:35">
       <c r="C170" s="215" t="s">
         <v>88</v>
       </c>
-      <c r="D170" s="405" t="s">
+      <c r="D170" s="419" t="s">
         <v>104</v>
       </c>
-      <c r="E170" s="406"/>
-      <c r="F170" s="407"/>
+      <c r="E170" s="420"/>
+      <c r="F170" s="421"/>
     </row>
     <row r="171" spans="3:35" ht="18.75">
       <c r="C171" s="215" t="s">
         <v>89</v>
       </c>
-      <c r="D171" s="402" t="s">
+      <c r="D171" s="417" t="s">
         <v>105</v>
       </c>
-      <c r="E171" s="402"/>
-      <c r="F171" s="403"/>
+      <c r="E171" s="417"/>
+      <c r="F171" s="418"/>
     </row>
     <row r="172" spans="3:35">
       <c r="C172" s="213" t="s">
         <v>90</v>
       </c>
-      <c r="D172" s="402" t="s">
+      <c r="D172" s="417" t="s">
         <v>106</v>
       </c>
-      <c r="E172" s="402"/>
-      <c r="F172" s="403"/>
+      <c r="E172" s="417"/>
+      <c r="F172" s="418"/>
     </row>
     <row r="173" spans="3:35" ht="16.5" thickBot="1">
       <c r="C173" s="216" t="s">
@@ -24413,20 +24435,35 @@
     </sortState>
   </autoFilter>
   <mergeCells count="59">
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="D154:F155"/>
-    <mergeCell ref="D146:F146"/>
-    <mergeCell ref="I146:L146"/>
-    <mergeCell ref="AA4:AD4"/>
-    <mergeCell ref="Q145:R145"/>
-    <mergeCell ref="D151:F151"/>
-    <mergeCell ref="D152:F152"/>
-    <mergeCell ref="D153:F153"/>
-    <mergeCell ref="S4:U4"/>
-    <mergeCell ref="L4:L5"/>
-    <mergeCell ref="Q4:R4"/>
-    <mergeCell ref="K4:K5"/>
-    <mergeCell ref="Y4:Z4"/>
+    <mergeCell ref="AG5:AG6"/>
+    <mergeCell ref="AH5:AH6"/>
+    <mergeCell ref="AI5:AI6"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="AE4:AE5"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="V4:X4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="O4:P4"/>
+    <mergeCell ref="D172:F172"/>
+    <mergeCell ref="D159:F159"/>
+    <mergeCell ref="D160:F160"/>
+    <mergeCell ref="D167:F167"/>
+    <mergeCell ref="D168:F168"/>
+    <mergeCell ref="D169:F169"/>
+    <mergeCell ref="D170:F170"/>
+    <mergeCell ref="D171:F171"/>
+    <mergeCell ref="C162:F162"/>
+    <mergeCell ref="D163:F163"/>
+    <mergeCell ref="D164:F164"/>
+    <mergeCell ref="D165:F165"/>
+    <mergeCell ref="D166:F166"/>
     <mergeCell ref="D173:F173"/>
     <mergeCell ref="D145:F145"/>
     <mergeCell ref="C157:F157"/>
@@ -24443,35 +24480,20 @@
     <mergeCell ref="D149:F149"/>
     <mergeCell ref="D150:F150"/>
     <mergeCell ref="D158:F158"/>
-    <mergeCell ref="D172:F172"/>
-    <mergeCell ref="D159:F159"/>
-    <mergeCell ref="D160:F160"/>
-    <mergeCell ref="D167:F167"/>
-    <mergeCell ref="D168:F168"/>
-    <mergeCell ref="D169:F169"/>
-    <mergeCell ref="D170:F170"/>
-    <mergeCell ref="D171:F171"/>
-    <mergeCell ref="C162:F162"/>
-    <mergeCell ref="D163:F163"/>
-    <mergeCell ref="D164:F164"/>
-    <mergeCell ref="D165:F165"/>
-    <mergeCell ref="D166:F166"/>
-    <mergeCell ref="AG5:AG6"/>
-    <mergeCell ref="AH5:AH6"/>
-    <mergeCell ref="AI5:AI6"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="I4:I5"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="H4:H5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="AE4:AE5"/>
-    <mergeCell ref="J4:J5"/>
-    <mergeCell ref="V4:X4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="O4:P4"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="D154:F155"/>
+    <mergeCell ref="D146:F146"/>
+    <mergeCell ref="I146:L146"/>
+    <mergeCell ref="AA4:AD4"/>
+    <mergeCell ref="Q145:R145"/>
+    <mergeCell ref="D151:F151"/>
+    <mergeCell ref="D152:F152"/>
+    <mergeCell ref="D153:F153"/>
+    <mergeCell ref="S4:U4"/>
+    <mergeCell ref="L4:L5"/>
+    <mergeCell ref="Q4:R4"/>
+    <mergeCell ref="K4:K5"/>
+    <mergeCell ref="Y4:Z4"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="A7:AE143 AG7:AI143">
@@ -25143,88 +25165,88 @@
       <c r="AD3" s="159"/>
     </row>
     <row r="4" spans="1:35" s="5" customFormat="1" ht="36" customHeight="1" thickBot="1">
-      <c r="A4" s="396" t="s">
+      <c r="A4" s="354" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="350" t="s">
+      <c r="B4" s="366" t="s">
         <v>515</v>
       </c>
-      <c r="C4" s="364" t="s">
+      <c r="C4" s="362" t="s">
         <v>45</v>
       </c>
-      <c r="D4" s="352" t="s">
+      <c r="D4" s="356" t="s">
         <v>46</v>
       </c>
-      <c r="E4" s="400" t="s">
+      <c r="E4" s="358" t="s">
         <v>47</v>
       </c>
-      <c r="F4" s="352" t="s">
+      <c r="F4" s="356" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="398" t="s">
+      <c r="G4" s="360" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="358" t="s">
+      <c r="H4" s="404" t="s">
         <v>48</v>
       </c>
-      <c r="I4" s="358" t="s">
+      <c r="I4" s="404" t="s">
         <v>49</v>
       </c>
-      <c r="J4" s="352" t="s">
+      <c r="J4" s="356" t="s">
         <v>78</v>
       </c>
-      <c r="K4" s="358" t="s">
+      <c r="K4" s="404" t="s">
         <v>80</v>
       </c>
-      <c r="L4" s="363" t="s">
+      <c r="L4" s="406" t="s">
         <v>53</v>
       </c>
-      <c r="M4" s="348"/>
-      <c r="N4" s="362" t="s">
+      <c r="M4" s="407"/>
+      <c r="N4" s="408" t="s">
         <v>55</v>
       </c>
-      <c r="O4" s="348"/>
-      <c r="P4" s="362" t="s">
+      <c r="O4" s="407"/>
+      <c r="P4" s="408" t="s">
         <v>72</v>
       </c>
-      <c r="Q4" s="348"/>
-      <c r="R4" s="363" t="s">
+      <c r="Q4" s="407"/>
+      <c r="R4" s="406" t="s">
         <v>53</v>
       </c>
-      <c r="S4" s="363"/>
-      <c r="T4" s="348"/>
-      <c r="U4" s="362" t="s">
+      <c r="S4" s="406"/>
+      <c r="T4" s="407"/>
+      <c r="U4" s="408" t="s">
         <v>55</v>
       </c>
-      <c r="V4" s="363"/>
-      <c r="W4" s="348"/>
-      <c r="X4" s="366" t="s">
+      <c r="V4" s="406"/>
+      <c r="W4" s="407"/>
+      <c r="X4" s="350" t="s">
         <v>72</v>
       </c>
-      <c r="Y4" s="442"/>
-      <c r="Z4" s="366" t="s">
+      <c r="Y4" s="351"/>
+      <c r="Z4" s="350" t="s">
         <v>112</v>
       </c>
-      <c r="AA4" s="430"/>
-      <c r="AB4" s="430"/>
-      <c r="AC4" s="431"/>
-      <c r="AD4" s="352" t="s">
+      <c r="AA4" s="352"/>
+      <c r="AB4" s="352"/>
+      <c r="AC4" s="353"/>
+      <c r="AD4" s="356" t="s">
         <v>79</v>
       </c>
       <c r="AG4" s="236"/>
     </row>
     <row r="5" spans="1:35" ht="78.75">
-      <c r="A5" s="397"/>
-      <c r="B5" s="351"/>
-      <c r="C5" s="365"/>
-      <c r="D5" s="353"/>
-      <c r="E5" s="401"/>
-      <c r="F5" s="353"/>
-      <c r="G5" s="399"/>
-      <c r="H5" s="359"/>
-      <c r="I5" s="359"/>
-      <c r="J5" s="353"/>
-      <c r="K5" s="359"/>
+      <c r="A5" s="355"/>
+      <c r="B5" s="367"/>
+      <c r="C5" s="363"/>
+      <c r="D5" s="357"/>
+      <c r="E5" s="359"/>
+      <c r="F5" s="357"/>
+      <c r="G5" s="361"/>
+      <c r="H5" s="405"/>
+      <c r="I5" s="405"/>
+      <c r="J5" s="357"/>
+      <c r="K5" s="405"/>
       <c r="L5" s="79" t="s">
         <v>52</v>
       </c>
@@ -25279,14 +25301,14 @@
       <c r="AC5" s="250" t="s">
         <v>118</v>
       </c>
-      <c r="AD5" s="349"/>
-      <c r="AG5" s="432" t="s">
+      <c r="AD5" s="403"/>
+      <c r="AG5" s="394" t="s">
         <v>119</v>
       </c>
-      <c r="AH5" s="434" t="s">
+      <c r="AH5" s="396" t="s">
         <v>120</v>
       </c>
-      <c r="AI5" s="436" t="s">
+      <c r="AI5" s="398" t="s">
         <v>121</v>
       </c>
     </row>
@@ -25321,9 +25343,9 @@
       <c r="AB6" s="86"/>
       <c r="AC6" s="86"/>
       <c r="AD6" s="74"/>
-      <c r="AG6" s="433"/>
-      <c r="AH6" s="435"/>
-      <c r="AI6" s="437"/>
+      <c r="AG6" s="395"/>
+      <c r="AH6" s="397"/>
+      <c r="AI6" s="399"/>
     </row>
     <row r="7" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A7" s="33">
@@ -26474,7 +26496,7 @@
         <v>YES</v>
       </c>
     </row>
-    <row r="17" spans="1:35" s="9" customFormat="1" ht="110.25">
+    <row r="17" spans="1:35" s="9" customFormat="1" ht="94.5">
       <c r="A17" s="33">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -28526,7 +28548,7 @@
         <v/>
       </c>
       <c r="AD35" s="92" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="AG35" s="238" t="str">
         <f t="shared" si="8"/>
@@ -28920,7 +28942,7 @@
         <v/>
       </c>
       <c r="AD39" s="92" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="AG39" s="238" t="str">
         <f t="shared" si="8"/>
@@ -29042,14 +29064,14 @@
       </c>
       <c r="C41" s="164"/>
       <c r="D41" s="25" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
       <c r="E41" s="174">
         <f t="shared" si="2"/>
         <v>46332</v>
       </c>
       <c r="F41" s="31" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="G41" s="21" t="s">
         <v>547</v>
@@ -29201,28 +29223,28 @@
       <c r="C45" s="166" t="s">
         <v>20</v>
       </c>
-      <c r="D45" s="416" t="s">
+      <c r="D45" s="364" t="s">
         <v>21</v>
       </c>
-      <c r="E45" s="417"/>
+      <c r="E45" s="365"/>
       <c r="F45" s="46"/>
       <c r="G45" s="46"/>
-      <c r="H45" s="392" t="s">
+      <c r="H45" s="377" t="s">
         <v>14</v>
       </c>
-      <c r="I45" s="393"/>
-      <c r="J45" s="393"/>
-      <c r="K45" s="393"/>
-      <c r="L45" s="393"/>
-      <c r="M45" s="394"/>
-      <c r="N45" s="388" t="s">
+      <c r="I45" s="378"/>
+      <c r="J45" s="378"/>
+      <c r="K45" s="378"/>
+      <c r="L45" s="378"/>
+      <c r="M45" s="379"/>
+      <c r="N45" s="348" t="s">
         <v>7</v>
       </c>
-      <c r="O45" s="389"/>
-      <c r="P45" s="388" t="s">
+      <c r="O45" s="349"/>
+      <c r="P45" s="348" t="s">
         <v>109</v>
       </c>
-      <c r="Q45" s="389"/>
+      <c r="Q45" s="349"/>
       <c r="R45" s="1"/>
       <c r="S45" s="1"/>
       <c r="T45" s="140"/>
@@ -29242,17 +29264,17 @@
       <c r="C46" s="195" t="s">
         <v>109</v>
       </c>
-      <c r="D46" s="440" t="s">
+      <c r="D46" s="392" t="s">
         <v>111</v>
       </c>
-      <c r="E46" s="441"/>
+      <c r="E46" s="393"/>
       <c r="F46" s="46"/>
-      <c r="H46" s="392" t="s">
+      <c r="H46" s="377" t="s">
         <v>18</v>
       </c>
-      <c r="I46" s="393"/>
-      <c r="J46" s="393"/>
-      <c r="K46" s="394"/>
+      <c r="I46" s="378"/>
+      <c r="J46" s="378"/>
+      <c r="K46" s="379"/>
       <c r="L46" s="105">
         <f ca="1">M46/$M$46</f>
         <v>1</v>
@@ -29294,18 +29316,18 @@
       <c r="C47" s="195" t="s">
         <v>36</v>
       </c>
-      <c r="D47" s="438" t="s">
+      <c r="D47" s="368" t="s">
         <v>37</v>
       </c>
-      <c r="E47" s="439"/>
+      <c r="E47" s="369"/>
       <c r="F47" s="69"/>
       <c r="G47" s="6"/>
-      <c r="H47" s="418" t="s">
+      <c r="H47" s="371" t="s">
         <v>66</v>
       </c>
-      <c r="I47" s="419"/>
-      <c r="J47" s="419"/>
-      <c r="K47" s="420"/>
+      <c r="I47" s="372"/>
+      <c r="J47" s="372"/>
+      <c r="K47" s="373"/>
       <c r="L47" s="107">
         <f ca="1">M47/$M$46</f>
         <v>2.7027027027027029E-2</v>
@@ -29346,21 +29368,21 @@
       <c r="AI47" s="11"/>
     </row>
     <row r="48" spans="1:35">
-      <c r="C48" s="382" t="s">
+      <c r="C48" s="386" t="s">
         <v>75</v>
       </c>
-      <c r="D48" s="384" t="s">
+      <c r="D48" s="388" t="s">
         <v>76</v>
       </c>
-      <c r="E48" s="385"/>
+      <c r="E48" s="389"/>
       <c r="F48" s="70"/>
       <c r="G48" s="6"/>
-      <c r="H48" s="421" t="s">
+      <c r="H48" s="374" t="s">
         <v>67</v>
       </c>
-      <c r="I48" s="422"/>
-      <c r="J48" s="422"/>
-      <c r="K48" s="423"/>
+      <c r="I48" s="375"/>
+      <c r="J48" s="375"/>
+      <c r="K48" s="376"/>
       <c r="L48" s="109">
         <f t="shared" ref="L48:L51" ca="1" si="25">M48/$M$46</f>
         <v>0.54054054054054057</v>
@@ -29401,17 +29423,17 @@
       <c r="AI48" s="11"/>
     </row>
     <row r="49" spans="3:35" ht="16.5" thickBot="1">
-      <c r="C49" s="383"/>
-      <c r="D49" s="386"/>
-      <c r="E49" s="387"/>
+      <c r="C49" s="387"/>
+      <c r="D49" s="390"/>
+      <c r="E49" s="391"/>
       <c r="F49" s="71"/>
       <c r="G49" s="6"/>
-      <c r="H49" s="424" t="s">
+      <c r="H49" s="380" t="s">
         <v>68</v>
       </c>
-      <c r="I49" s="425"/>
-      <c r="J49" s="425"/>
-      <c r="K49" s="426"/>
+      <c r="I49" s="381"/>
+      <c r="J49" s="381"/>
+      <c r="K49" s="382"/>
       <c r="L49" s="111">
         <f t="shared" ca="1" si="25"/>
         <v>0.21621621621621623</v>
@@ -29454,12 +29476,12 @@
     <row r="50" spans="3:35">
       <c r="F50" s="72"/>
       <c r="G50" s="6"/>
-      <c r="H50" s="374" t="s">
+      <c r="H50" s="383" t="s">
         <v>70</v>
       </c>
-      <c r="I50" s="375"/>
-      <c r="J50" s="375"/>
-      <c r="K50" s="376"/>
+      <c r="I50" s="384"/>
+      <c r="J50" s="384"/>
+      <c r="K50" s="385"/>
       <c r="L50" s="114">
         <f t="shared" ca="1" si="25"/>
         <v>0.16216216216216217</v>
@@ -29507,12 +29529,12 @@
       </c>
       <c r="D51" s="370"/>
       <c r="E51" s="370"/>
-      <c r="H51" s="377" t="s">
+      <c r="H51" s="400" t="s">
         <v>71</v>
       </c>
-      <c r="I51" s="378"/>
-      <c r="J51" s="378"/>
-      <c r="K51" s="379"/>
+      <c r="I51" s="401"/>
+      <c r="J51" s="401"/>
+      <c r="K51" s="402"/>
       <c r="L51" s="113">
         <f t="shared" ca="1" si="25"/>
         <v>5.4054054054054057E-2</v>
@@ -29557,27 +29579,6 @@
     </sortState>
   </autoFilter>
   <mergeCells count="37">
-    <mergeCell ref="P45:Q45"/>
-    <mergeCell ref="X4:Y4"/>
-    <mergeCell ref="Z4:AC4"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D45:E45"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="D47:E47"/>
-    <mergeCell ref="C51:E51"/>
-    <mergeCell ref="H47:K47"/>
-    <mergeCell ref="H48:K48"/>
-    <mergeCell ref="H45:M45"/>
-    <mergeCell ref="H49:K49"/>
-    <mergeCell ref="H50:K50"/>
-    <mergeCell ref="C48:C49"/>
-    <mergeCell ref="D48:E49"/>
-    <mergeCell ref="D46:E46"/>
     <mergeCell ref="AG5:AG6"/>
     <mergeCell ref="AH5:AH6"/>
     <mergeCell ref="AI5:AI6"/>
@@ -29594,6 +29595,27 @@
     <mergeCell ref="K4:K5"/>
     <mergeCell ref="P4:Q4"/>
     <mergeCell ref="J4:J5"/>
+    <mergeCell ref="D47:E47"/>
+    <mergeCell ref="C51:E51"/>
+    <mergeCell ref="H47:K47"/>
+    <mergeCell ref="H48:K48"/>
+    <mergeCell ref="H45:M45"/>
+    <mergeCell ref="H49:K49"/>
+    <mergeCell ref="H50:K50"/>
+    <mergeCell ref="C48:C49"/>
+    <mergeCell ref="D48:E49"/>
+    <mergeCell ref="D46:E46"/>
+    <mergeCell ref="P45:Q45"/>
+    <mergeCell ref="X4:Y4"/>
+    <mergeCell ref="Z4:AC4"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D45:E45"/>
+    <mergeCell ref="B4:B5"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="A7:AD43 AG7:AI43">
@@ -29879,81 +29901,81 @@
       <c r="Z3" s="159"/>
     </row>
     <row r="4" spans="1:26" s="5" customFormat="1" ht="35.1" customHeight="1" thickBot="1">
-      <c r="A4" s="350" t="s">
+      <c r="A4" s="366" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="350" t="s">
+      <c r="B4" s="366" t="s">
         <v>515</v>
       </c>
-      <c r="C4" s="364" t="s">
+      <c r="C4" s="362" t="s">
         <v>45</v>
       </c>
-      <c r="D4" s="352" t="s">
+      <c r="D4" s="356" t="s">
         <v>46</v>
       </c>
-      <c r="E4" s="354" t="s">
+      <c r="E4" s="437" t="s">
         <v>47</v>
       </c>
-      <c r="F4" s="352" t="s">
+      <c r="F4" s="356" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="356" t="s">
+      <c r="G4" s="439" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="358" t="s">
+      <c r="H4" s="404" t="s">
         <v>48</v>
       </c>
-      <c r="I4" s="360" t="s">
+      <c r="I4" s="441" t="s">
         <v>49</v>
       </c>
-      <c r="J4" s="352" t="s">
+      <c r="J4" s="356" t="s">
         <v>78</v>
       </c>
-      <c r="K4" s="358" t="s">
+      <c r="K4" s="404" t="s">
         <v>80</v>
       </c>
-      <c r="L4" s="362" t="s">
+      <c r="L4" s="408" t="s">
         <v>53</v>
       </c>
-      <c r="M4" s="348"/>
-      <c r="N4" s="362" t="s">
+      <c r="M4" s="407"/>
+      <c r="N4" s="408" t="s">
         <v>55</v>
       </c>
-      <c r="O4" s="348"/>
-      <c r="P4" s="362" t="s">
+      <c r="O4" s="407"/>
+      <c r="P4" s="408" t="s">
         <v>72</v>
       </c>
-      <c r="Q4" s="348"/>
-      <c r="R4" s="363" t="s">
+      <c r="Q4" s="407"/>
+      <c r="R4" s="406" t="s">
         <v>53</v>
       </c>
-      <c r="S4" s="363"/>
-      <c r="T4" s="348"/>
-      <c r="U4" s="362" t="s">
+      <c r="S4" s="406"/>
+      <c r="T4" s="407"/>
+      <c r="U4" s="408" t="s">
         <v>55</v>
       </c>
-      <c r="V4" s="363"/>
-      <c r="W4" s="363"/>
-      <c r="X4" s="366" t="s">
+      <c r="V4" s="406"/>
+      <c r="W4" s="406"/>
+      <c r="X4" s="350" t="s">
         <v>72</v>
       </c>
-      <c r="Y4" s="367"/>
-      <c r="Z4" s="348" t="s">
+      <c r="Y4" s="412"/>
+      <c r="Z4" s="407" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="72" customHeight="1">
-      <c r="A5" s="351"/>
-      <c r="B5" s="351"/>
-      <c r="C5" s="365"/>
-      <c r="D5" s="353"/>
-      <c r="E5" s="355"/>
-      <c r="F5" s="353"/>
-      <c r="G5" s="357"/>
-      <c r="H5" s="359"/>
-      <c r="I5" s="361"/>
-      <c r="J5" s="353"/>
-      <c r="K5" s="359"/>
+      <c r="A5" s="367"/>
+      <c r="B5" s="367"/>
+      <c r="C5" s="363"/>
+      <c r="D5" s="357"/>
+      <c r="E5" s="438"/>
+      <c r="F5" s="357"/>
+      <c r="G5" s="440"/>
+      <c r="H5" s="405"/>
+      <c r="I5" s="442"/>
+      <c r="J5" s="357"/>
+      <c r="K5" s="405"/>
       <c r="L5" s="79" t="s">
         <v>52</v>
       </c>
@@ -29996,7 +30018,7 @@
       <c r="Y5" s="260" t="s">
         <v>114</v>
       </c>
-      <c r="Z5" s="349"/>
+      <c r="Z5" s="403"/>
     </row>
     <row r="6" spans="1:26" ht="15" customHeight="1" thickBot="1">
       <c r="A6" s="78"/>
@@ -31823,7 +31845,7 @@
       <c r="Y29" s="19"/>
       <c r="Z29" s="92"/>
     </row>
-    <row r="30" spans="1:26" s="9" customFormat="1" ht="31.5">
+    <row r="30" spans="1:26" s="9" customFormat="1" ht="47.25">
       <c r="A30" s="33">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -34169,7 +34191,7 @@
       </c>
       <c r="Z59" s="92"/>
     </row>
-    <row r="60" spans="1:26" s="9" customFormat="1" ht="47.25">
+    <row r="60" spans="1:26" s="9" customFormat="1" ht="63">
       <c r="A60" s="33">
         <f t="shared" si="0"/>
         <v>54</v>
@@ -38948,7 +38970,7 @@
       <c r="X125" s="230"/>
       <c r="Y125" s="19"/>
       <c r="Z125" s="92" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="126" spans="1:26" s="9" customFormat="1" ht="78.75">
@@ -39019,7 +39041,7 @@
       <c r="X126" s="230"/>
       <c r="Y126" s="19"/>
       <c r="Z126" s="92" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="127" spans="1:26" s="9" customFormat="1" ht="47.25">
@@ -39088,7 +39110,7 @@
       <c r="X127" s="230"/>
       <c r="Y127" s="19"/>
       <c r="Z127" s="92" t="s">
-        <v>1096</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="128" spans="1:26" s="9" customFormat="1" ht="47.25">
@@ -39104,19 +39126,21 @@
         <v>621</v>
       </c>
       <c r="D128" s="25" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="E128" s="174">
         <f t="shared" si="23"/>
         <v>46330</v>
       </c>
       <c r="F128" s="31" t="s">
+        <v>1065</v>
+      </c>
+      <c r="G128" s="21" t="s">
         <v>1066</v>
       </c>
-      <c r="G128" s="21" t="s">
-        <v>1067</v>
-      </c>
-      <c r="H128" s="138"/>
+      <c r="H128" s="138" t="s">
+        <v>6</v>
+      </c>
       <c r="I128" s="164">
         <f t="shared" ca="1" si="24"/>
         <v>6</v>
@@ -39145,10 +39169,14 @@
       </c>
       <c r="U128" s="29"/>
       <c r="V128" s="211"/>
-      <c r="W128" s="235"/>
+      <c r="W128" s="235" t="s">
+        <v>240</v>
+      </c>
       <c r="X128" s="230"/>
       <c r="Y128" s="19"/>
-      <c r="Z128" s="92"/>
+      <c r="Z128" s="92" t="s">
+        <v>1100</v>
+      </c>
     </row>
     <row r="129" spans="1:26" s="9" customFormat="1" ht="63">
       <c r="A129" s="33">
@@ -39163,17 +39191,17 @@
         <v>195</v>
       </c>
       <c r="D129" s="25" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="E129" s="174">
         <f t="shared" si="23"/>
         <v>46332</v>
       </c>
       <c r="F129" s="31" t="s">
+        <v>1090</v>
+      </c>
+      <c r="G129" s="21" t="s">
         <v>1091</v>
-      </c>
-      <c r="G129" s="21" t="s">
-        <v>1092</v>
       </c>
       <c r="H129" s="138"/>
       <c r="I129" s="164">
@@ -39270,28 +39298,28 @@
       <c r="C133" s="207" t="s">
         <v>38</v>
       </c>
-      <c r="D133" s="390" t="s">
+      <c r="D133" s="428" t="s">
         <v>39</v>
       </c>
-      <c r="E133" s="391"/>
+      <c r="E133" s="429"/>
       <c r="F133" s="46"/>
       <c r="G133" s="68"/>
-      <c r="H133" s="392" t="s">
+      <c r="H133" s="377" t="s">
         <v>14</v>
       </c>
-      <c r="I133" s="393"/>
-      <c r="J133" s="393"/>
-      <c r="K133" s="393"/>
-      <c r="L133" s="393"/>
-      <c r="M133" s="394"/>
-      <c r="N133" s="388" t="s">
+      <c r="I133" s="378"/>
+      <c r="J133" s="378"/>
+      <c r="K133" s="378"/>
+      <c r="L133" s="378"/>
+      <c r="M133" s="379"/>
+      <c r="N133" s="348" t="s">
         <v>7</v>
       </c>
-      <c r="O133" s="389"/>
-      <c r="P133" s="388" t="s">
+      <c r="O133" s="349"/>
+      <c r="P133" s="348" t="s">
         <v>110</v>
       </c>
-      <c r="Q133" s="389"/>
+      <c r="Q133" s="349"/>
       <c r="R133" s="1"/>
       <c r="S133" s="1"/>
       <c r="T133" s="140"/>
@@ -39304,16 +39332,16 @@
       <c r="C134" s="208" t="s">
         <v>74</v>
       </c>
-      <c r="D134" s="380" t="s">
+      <c r="D134" s="435" t="s">
         <v>77</v>
       </c>
-      <c r="E134" s="381"/>
+      <c r="E134" s="436"/>
       <c r="F134" s="46"/>
       <c r="G134" s="46"/>
-      <c r="H134" s="368" t="s">
+      <c r="H134" s="430" t="s">
         <v>17</v>
       </c>
-      <c r="I134" s="369"/>
+      <c r="I134" s="431"/>
       <c r="J134" s="130"/>
       <c r="K134" s="210"/>
       <c r="L134" s="117">
@@ -39322,7 +39350,7 @@
       </c>
       <c r="M134" s="104">
         <f ca="1">SUM($M$135:$M$137)</f>
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="N134" s="118" t="s">
         <v>15</v>
@@ -39347,32 +39375,32 @@
       <c r="Y134" s="11"/>
     </row>
     <row r="135" spans="1:26">
-      <c r="C135" s="382" t="s">
+      <c r="C135" s="386" t="s">
         <v>6</v>
       </c>
-      <c r="D135" s="380" t="s">
+      <c r="D135" s="435" t="s">
         <v>40</v>
       </c>
-      <c r="E135" s="381"/>
+      <c r="E135" s="436"/>
       <c r="F135" s="69"/>
       <c r="G135" s="6"/>
-      <c r="H135" s="371" t="s">
+      <c r="H135" s="432" t="s">
         <v>69</v>
       </c>
-      <c r="I135" s="372"/>
-      <c r="J135" s="372"/>
-      <c r="K135" s="373"/>
+      <c r="I135" s="433"/>
+      <c r="J135" s="433"/>
+      <c r="K135" s="434"/>
       <c r="L135" s="122">
         <f t="shared" ref="L135:L137" ca="1" si="61">M135/$M$134</f>
-        <v>0.83464566929133854</v>
+        <v>0.8359375</v>
       </c>
       <c r="M135" s="123">
         <f>COUNTIF($H$7:$H$131,"RFCS")</f>
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="N135" s="121">
         <f ca="1">COUNTIFS($I$7:$I$131,"&lt;=21",$H$7:$H$131,"RFCS")</f>
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="O135" s="120">
         <f ca="1">COUNTIFS($I$7:$I$131,"&gt;21",$H$7:$H$131,"RFCS")</f>
@@ -39395,20 +39423,20 @@
       <c r="Y135" s="11"/>
     </row>
     <row r="136" spans="1:26">
-      <c r="C136" s="382"/>
-      <c r="D136" s="380"/>
-      <c r="E136" s="381"/>
+      <c r="C136" s="386"/>
+      <c r="D136" s="435"/>
+      <c r="E136" s="436"/>
       <c r="F136" s="72"/>
       <c r="G136" s="6"/>
-      <c r="H136" s="374" t="s">
+      <c r="H136" s="383" t="s">
         <v>70</v>
       </c>
-      <c r="I136" s="375"/>
-      <c r="J136" s="375"/>
-      <c r="K136" s="376"/>
+      <c r="I136" s="384"/>
+      <c r="J136" s="384"/>
+      <c r="K136" s="385"/>
       <c r="L136" s="124">
         <f t="shared" ca="1" si="61"/>
-        <v>5.5118110236220472E-2</v>
+        <v>5.46875E-2</v>
       </c>
       <c r="M136" s="125">
         <f ca="1">SUM(N136:O136)</f>
@@ -39441,22 +39469,22 @@
       <c r="Y136" s="11"/>
     </row>
     <row r="137" spans="1:26" ht="16.5" thickBot="1">
-      <c r="C137" s="382" t="s">
+      <c r="C137" s="386" t="s">
         <v>75</v>
       </c>
-      <c r="D137" s="384" t="s">
+      <c r="D137" s="388" t="s">
         <v>76</v>
       </c>
-      <c r="E137" s="385"/>
-      <c r="H137" s="377" t="s">
+      <c r="E137" s="389"/>
+      <c r="H137" s="400" t="s">
         <v>71</v>
       </c>
-      <c r="I137" s="378"/>
-      <c r="J137" s="378"/>
-      <c r="K137" s="379"/>
+      <c r="I137" s="401"/>
+      <c r="J137" s="401"/>
+      <c r="K137" s="402"/>
       <c r="L137" s="126">
         <f t="shared" ca="1" si="61"/>
-        <v>0.11023622047244094</v>
+        <v>0.109375</v>
       </c>
       <c r="M137" s="116">
         <f>COUNTIFS($K$7:$K$131,"X")</f>
@@ -39468,9 +39496,9 @@
       <c r="Q137" s="224"/>
     </row>
     <row r="138" spans="1:26" ht="16.5" thickBot="1">
-      <c r="C138" s="383"/>
-      <c r="D138" s="386"/>
-      <c r="E138" s="387"/>
+      <c r="C138" s="387"/>
+      <c r="D138" s="390"/>
+      <c r="E138" s="391"/>
     </row>
     <row r="140" spans="1:26">
       <c r="C140" s="370" t="s">
@@ -39510,22 +39538,6 @@
     </sortState>
   </autoFilter>
   <mergeCells count="32">
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="P133:Q133"/>
-    <mergeCell ref="J4:J5"/>
-    <mergeCell ref="D133:E133"/>
-    <mergeCell ref="H133:M133"/>
-    <mergeCell ref="N133:O133"/>
-    <mergeCell ref="H134:I134"/>
-    <mergeCell ref="C140:E140"/>
-    <mergeCell ref="H135:K135"/>
-    <mergeCell ref="H136:K136"/>
-    <mergeCell ref="H137:K137"/>
-    <mergeCell ref="D134:E134"/>
-    <mergeCell ref="C135:C136"/>
-    <mergeCell ref="D135:E136"/>
-    <mergeCell ref="C137:C138"/>
-    <mergeCell ref="D137:E138"/>
     <mergeCell ref="Z4:Z5"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="D4:D5"/>
@@ -39542,6 +39554,22 @@
     <mergeCell ref="K4:K5"/>
     <mergeCell ref="P4:Q4"/>
     <mergeCell ref="X4:Y4"/>
+    <mergeCell ref="H134:I134"/>
+    <mergeCell ref="C140:E140"/>
+    <mergeCell ref="H135:K135"/>
+    <mergeCell ref="H136:K136"/>
+    <mergeCell ref="H137:K137"/>
+    <mergeCell ref="D134:E134"/>
+    <mergeCell ref="C135:C136"/>
+    <mergeCell ref="D135:E136"/>
+    <mergeCell ref="C137:C138"/>
+    <mergeCell ref="D137:E138"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="P133:Q133"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="D133:E133"/>
+    <mergeCell ref="H133:M133"/>
+    <mergeCell ref="N133:O133"/>
   </mergeCells>
   <phoneticPr fontId="71"/>
   <conditionalFormatting sqref="A7:Z131">
@@ -40050,7 +40078,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75733AF3-96C4-423A-BD99-1E08B3C66916}">
-  <dimension ref="A1:Y24"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="13" customWidth="1"/>
@@ -40129,19 +40157,19 @@
       <c r="S3" s="281"/>
     </row>
     <row r="4" spans="1:25" ht="36" customHeight="1" thickBot="1">
-      <c r="A4" s="396" t="s">
+      <c r="A4" s="354" t="s">
         <v>123</v>
       </c>
-      <c r="B4" s="358" t="s">
+      <c r="B4" s="404" t="s">
         <v>45</v>
       </c>
-      <c r="C4" s="358" t="s">
+      <c r="C4" s="404" t="s">
         <v>95</v>
       </c>
-      <c r="D4" s="358" t="s">
+      <c r="D4" s="404" t="s">
         <v>46</v>
       </c>
-      <c r="E4" s="352" t="s">
+      <c r="E4" s="356" t="s">
         <v>4</v>
       </c>
       <c r="F4" s="449" t="s">
@@ -40170,12 +40198,12 @@
       <c r="S4" s="448"/>
     </row>
     <row r="5" spans="1:25" ht="78.75">
-      <c r="A5" s="397"/>
-      <c r="B5" s="359"/>
-      <c r="C5" s="359"/>
-      <c r="D5" s="359"/>
-      <c r="E5" s="353"/>
-      <c r="F5" s="399"/>
+      <c r="A5" s="355"/>
+      <c r="B5" s="405"/>
+      <c r="C5" s="405"/>
+      <c r="D5" s="405"/>
+      <c r="E5" s="357"/>
+      <c r="F5" s="361"/>
       <c r="G5" s="283" t="s">
         <v>56</v>
       </c>
@@ -40239,127 +40267,127 @@
     </row>
     <row r="7" spans="1:25" ht="45">
       <c r="A7" s="13" cm="1">
-        <f t="array" ref="A7:A24">IF(_xlfn.ANCHORARRAY(D7)="","",_xlfn.SEQUENCE(ROWS(_xlfn.ANCHORARRAY(D7))))</f>
+        <f t="array" ref="A7:A26">IF(_xlfn.ANCHORARRAY(D7)="","",_xlfn.SEQUENCE(ROWS(_xlfn.ANCHORARRAY(D7))))</f>
         <v>1</v>
       </c>
       <c r="B7" s="302" t="str" cm="1">
-        <f t="array" ref="B7:B24">_xlfn.LET(
+        <f t="array" ref="B7:B26">_xlfn.LET(
 _xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(D7),RFA!$E:$E,RFA!$C:$C,""),
 IF(_xlpm.x=0,"",_xlpm.x)
 )</f>
         <v>FAS</v>
       </c>
       <c r="C7" s="13" t="str" cm="1">
-        <f t="array" ref="C7:C24">_xlfn.LET(
+        <f t="array" ref="C7:C26">_xlfn.LET(
 _xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(D7),RFA!$E:$E,RFA!$D:$D,""),
 IF(_xlpm.x=0,"",_xlpm.x)
 )</f>
         <v>MAS</v>
       </c>
       <c r="D7" s="282" t="str" cm="1">
-        <f t="array" ref="D7:D24">_xlfn._xlws.FILTER(RFA!$E$5:$E$4578, RFA!$AI$5:$AI$4578="YES","")</f>
+        <f t="array" ref="D7:D26">_xlfn._xlws.FILTER(RFA!$E$5:$E$4578, RFA!$AI$5:$AI$4578="YES","")</f>
         <v>LTIA-5.10-VIETUR-70000-RFA-MAS-0088A</v>
       </c>
       <c r="E7" s="303" t="str" cm="1">
-        <f t="array" ref="E7:E24">_xlfn.LET(
+        <f t="array" ref="E7:E26">_xlfn.LET(
 _xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(D7),RFA!$E:$E,RFA!$G:$G,""),
 IF(_xlpm.x=0,"",_xlpm.x)
 )</f>
         <v>Request for approval material cable fire resistant shield for fire alarm system (Belden)</v>
       </c>
       <c r="F7" s="303" t="str" cm="1">
-        <f t="array" ref="F7:F24">_xlfn.LET(
+        <f t="array" ref="F7:F26">_xlfn.LET(
 _xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(D7),RFA!$E:$E,RFA!$H:$H,""),
 IF(_xlpm.x=0,"",_xlpm.x)
 )</f>
         <v>Đề nghị phê duyệt vật liệu cáp chống cháy cho hệ thống báo cháy (Belden)</v>
       </c>
       <c r="G7" s="270" cm="1">
-        <f t="array" ref="G7:G24">_xlfn.LET(
+        <f t="array" ref="G7:G26">_xlfn.LET(
 _xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(D7),RFA!$E:$E,RFA!$S:$S,""),
 IF(_xlpm.x=0,"",_xlpm.x)
 )</f>
         <v>45426</v>
       </c>
       <c r="H7" s="270" cm="1">
-        <f t="array" ref="H7:H24">_xlfn.LET(
+        <f t="array" ref="H7:H26">_xlfn.LET(
 _xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(D7),RFA!$E:$E,RFA!$T:$T,""),
 IF(_xlpm.x=0,"",_xlpm.x)
 )</f>
         <v>45426</v>
       </c>
       <c r="I7" s="264" cm="1">
-        <f t="array" ref="I7:I24">_xlfn.LET(
+        <f t="array" ref="I7:I26">_xlfn.LET(
 _xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(D7),RFA!$E:$E,RFA!$U:$U,""),
 IF(_xlpm.x=0,"",_xlpm.x)
 )</f>
         <v>45426</v>
       </c>
       <c r="J7" s="264" t="str" cm="1">
-        <f t="array" ref="J7:J24">_xlfn.LET(
+        <f t="array" ref="J7:J26">_xlfn.LET(
 _xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(D7),RFA!$E:$E,RFA!$I:$I,""),
 IF(_xlpm.x=0,"",_xlpm.x)
 )</f>
         <v>C</v>
       </c>
       <c r="K7" s="270" cm="1">
-        <f t="array" ref="K7:K24">_xlfn.LET(
+        <f t="array" ref="K7:K26">_xlfn.LET(
 _xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(D7),RFA!$E:$E,RFA!$V:$V,""),
 IF(_xlpm.x=0,"",_xlpm.x)
 )</f>
         <v>45454</v>
       </c>
       <c r="L7" s="264" cm="1">
-        <f t="array" ref="L7:L24">_xlfn.LET(
+        <f t="array" ref="L7:L26">_xlfn.LET(
 _xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(D7),RFA!$E:$E,RFA!$W:$W,""),
 IF(_xlpm.x=0,"",_xlpm.x)
 )</f>
         <v>45455</v>
       </c>
       <c r="M7" s="264" t="str" cm="1">
-        <f t="array" ref="M7:M24">_xlfn.LET(
+        <f t="array" ref="M7:M26">_xlfn.LET(
 _xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(D7),RFA!$E:$E,RFA!$R:$R,""),
 IF(_xlpm.x=0,"",_xlpm.x)
 )</f>
         <v>C</v>
       </c>
       <c r="N7" s="270" cm="1">
-        <f t="array" ref="N7:N24">_xlfn.LET(
+        <f t="array" ref="N7:N26">_xlfn.LET(
 _xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(D7),RFA!$E:$E,RFA!$Y:$Y,""),
 IF(_xlpm.x=0,"",_xlpm.x)
 )</f>
         <v>45456</v>
       </c>
       <c r="O7" s="264" cm="1">
-        <f t="array" ref="O7:O24">_xlfn.LET(
+        <f t="array" ref="O7:O26">_xlfn.LET(
 _xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(D7),RFA!$E:$E,RFA!$Z:$Z,""),
 IF(_xlpm.x=0,"",_xlpm.x)
 )</f>
         <v>45456</v>
       </c>
       <c r="P7" s="264" cm="1">
-        <f t="array" ref="P7:P24">_xlfn.LET(
+        <f t="array" ref="P7:P26">_xlfn.LET(
 _xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(D7),RFA!$E:$E,RFA!$AA:$AA,""),
 IF(_xlpm.x=0,"",_xlpm.x)
 )</f>
         <v>45463</v>
       </c>
       <c r="Q7" s="270" t="str" cm="1">
-        <f t="array" ref="Q7:Q24">_xlfn.LET(
+        <f t="array" ref="Q7:Q26">_xlfn.LET(
 _xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(D7),RFA!$E:$E,RFA!$AB:$AB,""),
 IF(_xlpm.x=0,"",_xlpm.x)
 )</f>
         <v/>
       </c>
       <c r="R7" s="13" t="str" cm="1">
-        <f t="array" aca="1" ref="R7:R24" ca="1">_xlfn.LET(
+        <f t="array" aca="1" ref="R7:R26" ca="1">_xlfn.LET(
 _xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(D7),RFA!$E:$E,RFA!$AC:$AC,""),
 IF(_xlpm.x=0,"",_xlpm.x)
 )</f>
         <v>Not submit yet</v>
       </c>
       <c r="S7" s="279" cm="1">
-        <f t="array" aca="1" ref="S7:S24" ca="1">_xlfn.LET(
+        <f t="array" aca="1" ref="S7:S26" ca="1">_xlfn.LET(
 _xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(D7),RFA!$E:$E,RFA!$AD:$AD,""),
 IF(_xlpm.x=0,"",_xlpm.x)
 )</f>
@@ -41407,6 +41435,128 @@
         <v/>
       </c>
       <c r="S24" s="279" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="1:19">
+      <c r="A25" s="13">
+        <v>19</v>
+      </c>
+      <c r="B25" s="302" t="str">
+        <v>CCTV</v>
+      </c>
+      <c r="C25" s="13" t="str">
+        <v>MSS</v>
+      </c>
+      <c r="D25" s="282" t="str">
+        <v>LTIA-5.11-LTICT- 72120 -RFA-MSS-0004</v>
+      </c>
+      <c r="E25" s="303" t="str">
+        <v>Request for Approval of the Method Statement for the CCTV System</v>
+      </c>
+      <c r="F25" s="303" t="str">
+        <v>Yêu cầu phê duyệt Biện pháp thi công cho hệ thống Camera giám sát (CCTV)</v>
+      </c>
+      <c r="G25" s="270">
+        <v>46300</v>
+      </c>
+      <c r="H25" s="270">
+        <v>46300</v>
+      </c>
+      <c r="I25" s="264">
+        <v>46300</v>
+      </c>
+      <c r="J25" s="264" t="str">
+        <v>C</v>
+      </c>
+      <c r="K25" s="270" t="str">
+        <v/>
+      </c>
+      <c r="L25" s="264" t="str">
+        <v/>
+      </c>
+      <c r="M25" s="264" t="str">
+        <v/>
+      </c>
+      <c r="N25" s="270" t="str">
+        <v/>
+      </c>
+      <c r="O25" s="264" t="str">
+        <v/>
+      </c>
+      <c r="P25" s="264" t="str">
+        <v/>
+      </c>
+      <c r="Q25" s="270" t="str">
+        <v/>
+      </c>
+      <c r="R25" s="13" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="S25" s="279" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="1:19">
+      <c r="A26" s="13">
+        <v>20</v>
+      </c>
+      <c r="B26" s="302" t="str">
+        <v>AGAC</v>
+      </c>
+      <c r="C26" s="13" t="str">
+        <v>MSS</v>
+      </c>
+      <c r="D26" s="282" t="str">
+        <v>LTIA-5.11-LTICT-70100-RFA-MSS-0007</v>
+      </c>
+      <c r="E26" s="303" t="str">
+        <v>Request for Approval of the Method Statement for the AGAC System</v>
+      </c>
+      <c r="F26" s="303" t="str">
+        <v>Yêu cầu phê duyệt Biện pháp thi công cho hệ thống cửa truy cập tự động (AGAC)</v>
+      </c>
+      <c r="G26" s="270">
+        <v>46301</v>
+      </c>
+      <c r="H26" s="270">
+        <v>46301</v>
+      </c>
+      <c r="I26" s="264">
+        <v>46301</v>
+      </c>
+      <c r="J26" s="264" t="str">
+        <v>C</v>
+      </c>
+      <c r="K26" s="270" t="str">
+        <v/>
+      </c>
+      <c r="L26" s="264" t="str">
+        <v/>
+      </c>
+      <c r="M26" s="264" t="str">
+        <v/>
+      </c>
+      <c r="N26" s="270" t="str">
+        <v/>
+      </c>
+      <c r="O26" s="264" t="str">
+        <v/>
+      </c>
+      <c r="P26" s="264" t="str">
+        <v/>
+      </c>
+      <c r="Q26" s="270" t="str">
+        <v/>
+      </c>
+      <c r="R26" s="13" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="S26" s="279" t="str">
         <f ca="1"/>
         <v/>
       </c>
@@ -41433,7 +41583,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42223A76-B79E-483C-82B7-07960417E780}">
-  <dimension ref="A1:R18"/>
+  <dimension ref="A1:R17"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="13" customWidth="1"/>
@@ -41508,16 +41658,16 @@
       <c r="R3" s="281"/>
     </row>
     <row r="4" spans="1:18" ht="16.5" thickBot="1">
-      <c r="A4" s="396" t="s">
+      <c r="A4" s="354" t="s">
         <v>123</v>
       </c>
-      <c r="B4" s="358" t="s">
+      <c r="B4" s="404" t="s">
         <v>45</v>
       </c>
-      <c r="C4" s="358" t="s">
+      <c r="C4" s="404" t="s">
         <v>46</v>
       </c>
-      <c r="D4" s="363" t="s">
+      <c r="D4" s="406" t="s">
         <v>4</v>
       </c>
       <c r="E4" s="449" t="s">
@@ -41546,11 +41696,11 @@
       <c r="R4" s="448"/>
     </row>
     <row r="5" spans="1:18" ht="78.75">
-      <c r="A5" s="397"/>
-      <c r="B5" s="359"/>
-      <c r="C5" s="359"/>
-      <c r="D5" s="357"/>
-      <c r="E5" s="353"/>
+      <c r="A5" s="355"/>
+      <c r="B5" s="405"/>
+      <c r="C5" s="405"/>
+      <c r="D5" s="440"/>
+      <c r="E5" s="357"/>
       <c r="F5" s="283" t="s">
         <v>56</v>
       </c>
@@ -42039,7 +42189,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="60">
+    <row r="14" spans="1:18" ht="45">
       <c r="A14" s="13">
         <v>8</v>
       </c>
@@ -42155,7 +42305,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="45">
+    <row r="16" spans="1:18" ht="60">
       <c r="A16" s="13">
         <v>10</v>
       </c>
@@ -42213,7 +42363,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="17" spans="1:18" ht="60">
+    <row r="17" spans="1:18" ht="45">
       <c r="A17" s="13">
         <v>11</v>
       </c>
@@ -42271,7 +42421,6 @@
         <v>309</v>
       </c>
     </row>
-    <row r="18" spans="1:18" ht="45"/>
   </sheetData>
   <autoFilter ref="A6:R6" xr:uid="{75733AF3-96C4-423A-BD99-1E08B3C66916}"/>
   <mergeCells count="9">

--- a/ICT-RFA-RFI-lists-New.xlsx
+++ b/ICT-RFA-RFI-lists-New.xlsx
@@ -9,9 +9,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project Airport\LTIA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{458764C3-D111-42DD-B0BC-919B4BC6EA75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D5D9B42-3847-43AA-A1FE-D3702FB82F3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="506" activeTab="2" xr2:uid="{CCA8147E-0981-4321-B87F-440A52C0DA59}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="506" activeTab="1" xr2:uid="{CCA8147E-0981-4321-B87F-440A52C0DA59}"/>
   </bookViews>
   <sheets>
     <sheet name="RFA" sheetId="1" r:id="rId1"/>
@@ -25,12 +25,12 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Need ReSub (RFA)'!$A$6:$S$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Need ReSub (RFA-SDS)'!$A$6:$R$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">RFA!$A$6:$AE$143</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'RFA-SDS'!$A$6:$AD$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'RFA-SDS'!$A$6:$AD$47</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">RFI!$A$6:$Z$127</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Need ReSub (RFA)'!$A$1:$S$77</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'Need ReSub (RFA-SDS)'!$A$1:$R$62</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">RFA!$A$1:$AE$143,RFA!$I$145:$R$151,RFA!$C$145:$F$155,RFA!$C$157:$F$160,RFA!$C$162:$F$173</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'RFA-SDS'!$A$1:$AD$43,'RFA-SDS'!$H$45:$Q$51,'RFA-SDS'!$C$45:$E$49,'RFA-SDS'!$C$51:$E$54</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'RFA-SDS'!$A$1:$AD$47,'RFA-SDS'!$H$49:$Q$55,'RFA-SDS'!$C$49:$E$53,'RFA-SDS'!$C$55:$E$58</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">RFI!$A$1:$Z$131,RFI!$H$133:$Q$137,RFI!$C$133:$E$138,RFI!$C$140:$E$143</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">RFA!$4:$5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'RFA-SDS'!$4:$5</definedName>
@@ -78,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3507" uniqueCount="1101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3528" uniqueCount="1111">
   <si>
     <t>TT</t>
   </si>
@@ -5160,6 +5160,36 @@
   <si>
     <t>10/16/2026: Đã comment và gửi CNC
 10/19/2026: Đã ký RFCS</t>
+  </si>
+  <si>
+    <t>LTIA-5.10-VIETUR-80000-RFA-SDS-0197C</t>
+  </si>
+  <si>
+    <t>Construction design drawing of  ICT system – part.1: ICT systems for 3F Level</t>
+  </si>
+  <si>
+    <t>LTIA-5.10-VIETUR-80000-RFA-SDS-0080B</t>
+  </si>
+  <si>
+    <t>Construction design drawing of  ICT system – part.4: ICT systems for PIT Level (Underground)</t>
+  </si>
+  <si>
+    <t>LTIA-5.10-VIETUR-80000-RFA-SDS-0122B</t>
+  </si>
+  <si>
+    <t>Construction design drawing of ICT system - part .1 : ICT system for 1F Level</t>
+  </si>
+  <si>
+    <t>LTIA-5.11-LTICT-71110-RFA-SDS-0002</t>
+  </si>
+  <si>
+    <t>Request for approval of the construction design of the ETC toll collection system</t>
+  </si>
+  <si>
+    <t>Yêu cầu phê duyệt thiết kế thi công hệ thống thu phí không dừng</t>
+  </si>
+  <si>
+    <t>10/22/2026 Update</t>
   </si>
 </sst>
 </file>
@@ -7596,138 +7626,222 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="51" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="52" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="55" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="55" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="55" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="51" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="52" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="55" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -7750,90 +7864,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="53" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -8455,7 +8485,7 @@
       </c>
       <c r="J1" s="176">
         <f ca="1">TODAY()</f>
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="K1" s="131"/>
       <c r="L1" s="197"/>
@@ -8542,92 +8572,92 @@
       <c r="AE3" s="159"/>
     </row>
     <row r="4" spans="1:35" s="5" customFormat="1" ht="36" customHeight="1" thickBot="1">
-      <c r="A4" s="354" t="s">
+      <c r="A4" s="408" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="366" t="s">
+      <c r="B4" s="348" t="s">
         <v>515</v>
       </c>
-      <c r="C4" s="362" t="s">
+      <c r="C4" s="414" t="s">
         <v>45</v>
       </c>
-      <c r="D4" s="404" t="s">
+      <c r="D4" s="366" t="s">
         <v>95</v>
       </c>
-      <c r="E4" s="356" t="s">
+      <c r="E4" s="369" t="s">
         <v>46</v>
       </c>
-      <c r="F4" s="358" t="s">
+      <c r="F4" s="412" t="s">
         <v>47</v>
       </c>
-      <c r="G4" s="356" t="s">
+      <c r="G4" s="369" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="360" t="s">
+      <c r="H4" s="410" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="404" t="s">
+      <c r="I4" s="366" t="s">
         <v>48</v>
       </c>
-      <c r="J4" s="404" t="s">
+      <c r="J4" s="366" t="s">
         <v>49</v>
       </c>
-      <c r="K4" s="356" t="s">
+      <c r="K4" s="369" t="s">
         <v>78</v>
       </c>
-      <c r="L4" s="404" t="s">
+      <c r="L4" s="366" t="s">
         <v>80</v>
       </c>
-      <c r="M4" s="406" t="s">
+      <c r="M4" s="364" t="s">
         <v>53</v>
       </c>
-      <c r="N4" s="407"/>
-      <c r="O4" s="406" t="s">
+      <c r="N4" s="365"/>
+      <c r="O4" s="364" t="s">
         <v>55</v>
       </c>
-      <c r="P4" s="407"/>
-      <c r="Q4" s="408" t="s">
+      <c r="P4" s="365"/>
+      <c r="Q4" s="368" t="s">
         <v>72</v>
       </c>
-      <c r="R4" s="407"/>
-      <c r="S4" s="406" t="s">
+      <c r="R4" s="365"/>
+      <c r="S4" s="364" t="s">
         <v>53</v>
       </c>
-      <c r="T4" s="406"/>
-      <c r="U4" s="407"/>
-      <c r="V4" s="408" t="s">
+      <c r="T4" s="364"/>
+      <c r="U4" s="365"/>
+      <c r="V4" s="368" t="s">
         <v>55</v>
       </c>
-      <c r="W4" s="406"/>
-      <c r="X4" s="407"/>
-      <c r="Y4" s="350" t="s">
+      <c r="W4" s="364"/>
+      <c r="X4" s="365"/>
+      <c r="Y4" s="371" t="s">
         <v>72</v>
       </c>
-      <c r="Z4" s="412"/>
-      <c r="AA4" s="411" t="s">
+      <c r="Z4" s="372"/>
+      <c r="AA4" s="359" t="s">
         <v>112</v>
       </c>
-      <c r="AB4" s="352"/>
-      <c r="AC4" s="352"/>
-      <c r="AD4" s="353"/>
-      <c r="AE4" s="356" t="s">
+      <c r="AB4" s="360"/>
+      <c r="AC4" s="360"/>
+      <c r="AD4" s="361"/>
+      <c r="AE4" s="369" t="s">
         <v>79</v>
       </c>
       <c r="AG4" s="236"/>
     </row>
     <row r="5" spans="1:35" ht="78.75">
-      <c r="A5" s="355"/>
-      <c r="B5" s="367"/>
-      <c r="C5" s="363"/>
-      <c r="D5" s="405"/>
-      <c r="E5" s="357"/>
-      <c r="F5" s="359"/>
-      <c r="G5" s="357"/>
-      <c r="H5" s="361"/>
-      <c r="I5" s="405"/>
-      <c r="J5" s="405"/>
-      <c r="K5" s="357"/>
-      <c r="L5" s="405"/>
+      <c r="A5" s="409"/>
+      <c r="B5" s="349"/>
+      <c r="C5" s="415"/>
+      <c r="D5" s="367"/>
+      <c r="E5" s="370"/>
+      <c r="F5" s="413"/>
+      <c r="G5" s="370"/>
+      <c r="H5" s="411"/>
+      <c r="I5" s="367"/>
+      <c r="J5" s="367"/>
+      <c r="K5" s="370"/>
+      <c r="L5" s="367"/>
       <c r="M5" s="79" t="s">
         <v>52</v>
       </c>
@@ -8682,14 +8712,14 @@
       <c r="AD5" s="336" t="s">
         <v>118</v>
       </c>
-      <c r="AE5" s="403"/>
-      <c r="AG5" s="356" t="s">
+      <c r="AE5" s="416"/>
+      <c r="AG5" s="369" t="s">
         <v>119</v>
       </c>
-      <c r="AH5" s="356" t="s">
+      <c r="AH5" s="369" t="s">
         <v>120</v>
       </c>
-      <c r="AI5" s="356" t="s">
+      <c r="AI5" s="369" t="s">
         <v>121</v>
       </c>
     </row>
@@ -8725,9 +8755,9 @@
       <c r="AC6" s="86"/>
       <c r="AD6" s="86"/>
       <c r="AE6" s="74"/>
-      <c r="AG6" s="427"/>
-      <c r="AH6" s="427"/>
-      <c r="AI6" s="427"/>
+      <c r="AG6" s="407"/>
+      <c r="AH6" s="407"/>
+      <c r="AI6" s="407"/>
     </row>
     <row r="7" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A7" s="33">
@@ -9646,7 +9676,7 @@
       </c>
       <c r="AD14" s="337">
         <f t="shared" ca="1" si="7"/>
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="AE14" s="92"/>
       <c r="AG14" s="238" t="str">
@@ -9762,7 +9792,7 @@
       </c>
       <c r="AD15" s="337">
         <f t="shared" ca="1" si="7"/>
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="AE15" s="92"/>
       <c r="AG15" s="238" t="str">
@@ -13150,7 +13180,7 @@
       </c>
       <c r="AD44" s="337">
         <f t="shared" ca="1" si="13"/>
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="AE44" s="92"/>
       <c r="AG44" s="238" t="str">
@@ -13384,7 +13414,7 @@
       </c>
       <c r="AD46" s="337">
         <f t="shared" ca="1" si="13"/>
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AE46" s="92"/>
       <c r="AG46" s="238" t="str">
@@ -13850,7 +13880,7 @@
       </c>
       <c r="AD50" s="337">
         <f t="shared" ca="1" si="13"/>
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="AE50" s="92"/>
       <c r="AG50" s="238" t="str">
@@ -13901,7 +13931,7 @@
       <c r="I51" s="138"/>
       <c r="J51" s="164">
         <f t="shared" ca="1" si="3"/>
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="K51" s="47"/>
       <c r="L51" s="164" t="s">
@@ -14758,7 +14788,7 @@
       </c>
       <c r="AD58" s="337">
         <f t="shared" ca="1" si="13"/>
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="AE58" s="92"/>
       <c r="AG58" s="238" t="str">
@@ -14809,7 +14839,7 @@
       <c r="I59" s="138"/>
       <c r="J59" s="164">
         <f t="shared" ca="1" si="3"/>
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="K59" s="47"/>
       <c r="L59" s="164" t="s">
@@ -15084,7 +15114,7 @@
       </c>
       <c r="AD61" s="337">
         <f t="shared" ca="1" si="13"/>
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AE61" s="92"/>
       <c r="AG61" s="238" t="str">
@@ -15904,7 +15934,7 @@
       </c>
       <c r="AD68" s="337">
         <f t="shared" ca="1" si="13"/>
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="AE68" s="92"/>
       <c r="AG68" s="238" t="str">
@@ -18526,11 +18556,11 @@
       <c r="I92" s="138"/>
       <c r="J92" s="164">
         <f t="shared" ca="1" si="27"/>
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="K92" s="47">
         <f t="shared" ca="1" si="28"/>
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L92" s="164" t="s">
         <v>1003</v>
@@ -18628,11 +18658,11 @@
       </c>
       <c r="J93" s="164">
         <f t="shared" ca="1" si="27"/>
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="K93" s="47">
         <f t="shared" ca="1" si="28"/>
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="L93" s="164" t="s">
         <v>13</v>
@@ -20528,11 +20558,11 @@
       <c r="I111" s="23"/>
       <c r="J111" s="164">
         <f t="shared" ca="1" si="30"/>
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="K111" s="47">
         <f t="shared" ca="1" si="31"/>
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="L111" s="164" t="s">
         <v>13</v>
@@ -21162,11 +21192,11 @@
       <c r="I117" s="138"/>
       <c r="J117" s="164">
         <f t="shared" ca="1" si="30"/>
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="K117" s="47">
         <f t="shared" ca="1" si="31"/>
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="L117" s="164" t="s">
         <v>1003</v>
@@ -22272,11 +22302,11 @@
       <c r="I128" s="138"/>
       <c r="J128" s="164">
         <f t="shared" ca="1" si="30"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K128" s="47">
         <f t="shared" ca="1" si="31"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L128" s="164"/>
       <c r="M128" s="40" t="s">
@@ -22349,7 +22379,7 @@
       </c>
       <c r="F129" s="174">
         <f t="shared" si="29"/>
-        <v>46319</v>
+        <v>46323</v>
       </c>
       <c r="G129" s="31" t="s">
         <v>1028</v>
@@ -22360,7 +22390,7 @@
       <c r="I129" s="138"/>
       <c r="J129" s="164">
         <f t="shared" ca="1" si="30"/>
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K129" s="47">
         <f t="shared" ca="1" si="31"/>
@@ -22382,7 +22412,7 @@
         <v>46298</v>
       </c>
       <c r="U129" s="188">
-        <v>46298</v>
+        <v>46302</v>
       </c>
       <c r="V129" s="29"/>
       <c r="W129" s="188"/>
@@ -22439,7 +22469,7 @@
       </c>
       <c r="F130" s="174">
         <f t="shared" si="29"/>
-        <v>46321</v>
+        <v>46323</v>
       </c>
       <c r="G130" s="31" t="s">
         <v>1033</v>
@@ -22472,7 +22502,7 @@
         <v>46300</v>
       </c>
       <c r="U130" s="188">
-        <v>46300</v>
+        <v>46302</v>
       </c>
       <c r="V130" s="29"/>
       <c r="W130" s="188"/>
@@ -22541,11 +22571,11 @@
         <v>1</v>
       </c>
       <c r="J131" s="164">
-        <f t="shared" ca="1" si="30"/>
-        <v>15</v>
+        <f t="shared" si="30"/>
+        <v>17</v>
       </c>
       <c r="K131" s="47">
-        <f t="shared" ca="1" si="31"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="L131" s="164"/>
@@ -22553,7 +22583,9 @@
         <v>8</v>
       </c>
       <c r="N131" s="41"/>
-      <c r="O131" s="40"/>
+      <c r="O131" s="40" t="s">
+        <v>8</v>
+      </c>
       <c r="P131" s="41"/>
       <c r="Q131" s="40"/>
       <c r="R131" s="155"/>
@@ -22566,16 +22598,20 @@
       <c r="U131" s="188">
         <v>46300</v>
       </c>
-      <c r="V131" s="29"/>
-      <c r="W131" s="188"/>
+      <c r="V131" s="29">
+        <v>46314</v>
+      </c>
+      <c r="W131" s="188">
+        <v>46317</v>
+      </c>
       <c r="X131" s="235" t="s">
         <v>240</v>
       </c>
       <c r="Y131" s="230"/>
       <c r="Z131" s="227"/>
-      <c r="AA131" s="29" t="str">
+      <c r="AA131" s="29">
         <f t="shared" si="68"/>
-        <v/>
+        <v>46324</v>
       </c>
       <c r="AB131" s="229"/>
       <c r="AC131" s="229"/>
@@ -22623,7 +22659,7 @@
       </c>
       <c r="F132" s="174">
         <f t="shared" si="29"/>
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="G132" s="31" t="s">
         <v>1040</v>
@@ -22635,11 +22671,11 @@
         <v>1</v>
       </c>
       <c r="J132" s="164">
-        <f t="shared" ca="1" si="30"/>
-        <v>14</v>
+        <f t="shared" si="30"/>
+        <v>15</v>
       </c>
       <c r="K132" s="47">
-        <f t="shared" ca="1" si="31"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="L132" s="164"/>
@@ -22647,7 +22683,9 @@
         <v>8</v>
       </c>
       <c r="N132" s="41"/>
-      <c r="O132" s="40"/>
+      <c r="O132" s="40" t="s">
+        <v>8</v>
+      </c>
       <c r="P132" s="41"/>
       <c r="Q132" s="40"/>
       <c r="R132" s="155"/>
@@ -22658,18 +22696,22 @@
         <v>46301</v>
       </c>
       <c r="U132" s="188">
-        <v>46301</v>
-      </c>
-      <c r="V132" s="29"/>
-      <c r="W132" s="188"/>
+        <v>46302</v>
+      </c>
+      <c r="V132" s="29">
+        <v>46314</v>
+      </c>
+      <c r="W132" s="188">
+        <v>46317</v>
+      </c>
       <c r="X132" s="235" t="s">
         <v>240</v>
       </c>
       <c r="Y132" s="230"/>
       <c r="Z132" s="227"/>
-      <c r="AA132" s="29" t="str">
+      <c r="AA132" s="29">
         <f t="shared" si="68"/>
-        <v/>
+        <v>46324</v>
       </c>
       <c r="AB132" s="229"/>
       <c r="AC132" s="229"/>
@@ -22728,7 +22770,7 @@
       <c r="I133" s="138"/>
       <c r="J133" s="164">
         <f t="shared" ca="1" si="30"/>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K133" s="47">
         <f t="shared" ca="1" si="31"/>
@@ -22818,7 +22860,7 @@
       <c r="I134" s="138"/>
       <c r="J134" s="164">
         <f t="shared" ca="1" si="30"/>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K134" s="47">
         <f t="shared" ca="1" si="31"/>
@@ -23008,7 +23050,7 @@
       <c r="I136" s="138"/>
       <c r="J136" s="164">
         <f t="shared" ca="1" si="30"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K136" s="47">
         <f t="shared" ca="1" si="31"/>
@@ -23096,7 +23138,7 @@
       <c r="I137" s="138"/>
       <c r="J137" s="164">
         <f t="shared" ca="1" si="30"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K137" s="47">
         <f t="shared" ca="1" si="31"/>
@@ -23184,7 +23226,7 @@
       <c r="I138" s="138"/>
       <c r="J138" s="164">
         <f t="shared" ca="1" si="30"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K138" s="47">
         <f t="shared" ca="1" si="31"/>
@@ -23272,7 +23314,7 @@
       <c r="I139" s="138"/>
       <c r="J139" s="164">
         <f t="shared" ca="1" si="30"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K139" s="47">
         <f t="shared" ca="1" si="31"/>
@@ -23360,7 +23402,7 @@
       <c r="I140" s="138"/>
       <c r="J140" s="164">
         <f t="shared" ca="1" si="30"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K140" s="47">
         <f t="shared" ca="1" si="31"/>
@@ -23448,7 +23490,7 @@
       <c r="I141" s="138"/>
       <c r="J141" s="164">
         <f t="shared" ca="1" si="30"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K141" s="47">
         <f t="shared" ca="1" si="31"/>
@@ -23596,29 +23638,29 @@
       <c r="C145" s="166" t="s">
         <v>20</v>
       </c>
-      <c r="D145" s="364" t="s">
+      <c r="D145" s="376" t="s">
         <v>21</v>
       </c>
-      <c r="E145" s="364"/>
-      <c r="F145" s="365"/>
+      <c r="E145" s="376"/>
+      <c r="F145" s="377"/>
       <c r="G145" s="46"/>
       <c r="H145" s="68"/>
-      <c r="I145" s="377" t="s">
+      <c r="I145" s="356" t="s">
         <v>14</v>
       </c>
-      <c r="J145" s="378"/>
-      <c r="K145" s="378"/>
-      <c r="L145" s="378"/>
-      <c r="M145" s="378"/>
-      <c r="N145" s="379"/>
-      <c r="O145" s="348" t="s">
+      <c r="J145" s="357"/>
+      <c r="K145" s="357"/>
+      <c r="L145" s="357"/>
+      <c r="M145" s="357"/>
+      <c r="N145" s="358"/>
+      <c r="O145" s="362" t="s">
         <v>7</v>
       </c>
-      <c r="P145" s="349"/>
-      <c r="Q145" s="348" t="s">
+      <c r="P145" s="363"/>
+      <c r="Q145" s="362" t="s">
         <v>109</v>
       </c>
-      <c r="R145" s="349"/>
+      <c r="R145" s="363"/>
       <c r="S145" s="1"/>
       <c r="T145" s="1"/>
       <c r="U145" s="140"/>
@@ -23640,26 +23682,26 @@
       <c r="C146" s="167" t="s">
         <v>109</v>
       </c>
-      <c r="D146" s="409" t="s">
+      <c r="D146" s="354" t="s">
         <v>111</v>
       </c>
-      <c r="E146" s="409"/>
-      <c r="F146" s="410"/>
+      <c r="E146" s="354"/>
+      <c r="F146" s="355"/>
       <c r="G146" s="46"/>
       <c r="H146" s="46"/>
-      <c r="I146" s="377" t="s">
+      <c r="I146" s="356" t="s">
         <v>19</v>
       </c>
-      <c r="J146" s="378"/>
-      <c r="K146" s="378"/>
-      <c r="L146" s="379"/>
+      <c r="J146" s="357"/>
+      <c r="K146" s="357"/>
+      <c r="L146" s="358"/>
       <c r="M146" s="105">
         <f t="shared" ref="M146:M151" ca="1" si="89">N146/$N$146</f>
         <v>1</v>
       </c>
       <c r="N146" s="106">
         <f ca="1">SUM($N$147:$N$151)</f>
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="O146" s="102" t="s">
         <v>15</v>
@@ -23696,22 +23738,22 @@
       <c r="C147" s="167" t="s">
         <v>22</v>
       </c>
-      <c r="D147" s="409" t="s">
+      <c r="D147" s="354" t="s">
         <v>23</v>
       </c>
-      <c r="E147" s="409"/>
-      <c r="F147" s="410"/>
+      <c r="E147" s="354"/>
+      <c r="F147" s="355"/>
       <c r="G147" s="70"/>
       <c r="H147" s="6"/>
-      <c r="I147" s="371" t="s">
+      <c r="I147" s="379" t="s">
         <v>66</v>
       </c>
-      <c r="J147" s="372"/>
-      <c r="K147" s="372"/>
-      <c r="L147" s="373"/>
+      <c r="J147" s="380"/>
+      <c r="K147" s="380"/>
+      <c r="L147" s="381"/>
       <c r="M147" s="107">
         <f t="shared" ca="1" si="89"/>
-        <v>0.4859154929577465</v>
+        <v>0.49285714285714288</v>
       </c>
       <c r="N147" s="108">
         <f>COUNTIF($I$7:$I$143,"A")</f>
@@ -23754,21 +23796,21 @@
       <c r="C148" s="167" t="s">
         <v>24</v>
       </c>
-      <c r="D148" s="409" t="s">
+      <c r="D148" s="354" t="s">
         <v>25</v>
       </c>
-      <c r="E148" s="409"/>
-      <c r="F148" s="410"/>
+      <c r="E148" s="354"/>
+      <c r="F148" s="355"/>
       <c r="H148" s="6"/>
-      <c r="I148" s="374" t="s">
+      <c r="I148" s="382" t="s">
         <v>67</v>
       </c>
-      <c r="J148" s="375"/>
-      <c r="K148" s="375"/>
-      <c r="L148" s="376"/>
+      <c r="J148" s="383"/>
+      <c r="K148" s="383"/>
+      <c r="L148" s="384"/>
       <c r="M148" s="109">
         <f t="shared" ca="1" si="89"/>
-        <v>9.8591549295774641E-2</v>
+        <v>0.1</v>
       </c>
       <c r="N148" s="110">
         <f>COUNTIF($I$7:$I$143,"B")</f>
@@ -23811,22 +23853,22 @@
       <c r="C149" s="167" t="s">
         <v>26</v>
       </c>
-      <c r="D149" s="409" t="s">
+      <c r="D149" s="354" t="s">
         <v>27</v>
       </c>
-      <c r="E149" s="409"/>
-      <c r="F149" s="410"/>
+      <c r="E149" s="354"/>
+      <c r="F149" s="355"/>
       <c r="G149" s="71"/>
       <c r="H149" s="6"/>
-      <c r="I149" s="380" t="s">
+      <c r="I149" s="385" t="s">
         <v>68</v>
       </c>
-      <c r="J149" s="381"/>
-      <c r="K149" s="381"/>
-      <c r="L149" s="382"/>
+      <c r="J149" s="386"/>
+      <c r="K149" s="386"/>
+      <c r="L149" s="387"/>
       <c r="M149" s="111">
         <f t="shared" ca="1" si="89"/>
-        <v>0.20422535211267606</v>
+        <v>0.20714285714285716</v>
       </c>
       <c r="N149" s="112">
         <f>COUNTIF($I$7:$I$143,"C")</f>
@@ -23869,33 +23911,33 @@
       <c r="C150" s="168" t="s">
         <v>28</v>
       </c>
-      <c r="D150" s="409" t="s">
+      <c r="D150" s="354" t="s">
         <v>29</v>
       </c>
-      <c r="E150" s="409"/>
-      <c r="F150" s="410"/>
+      <c r="E150" s="354"/>
+      <c r="F150" s="355"/>
       <c r="G150" s="72"/>
-      <c r="I150" s="383" t="s">
+      <c r="I150" s="388" t="s">
         <v>70</v>
       </c>
-      <c r="J150" s="384"/>
-      <c r="K150" s="384"/>
-      <c r="L150" s="385"/>
+      <c r="J150" s="389"/>
+      <c r="K150" s="389"/>
+      <c r="L150" s="390"/>
       <c r="M150" s="114">
         <f t="shared" ca="1" si="89"/>
-        <v>0.10563380281690141</v>
+        <v>9.285714285714286E-2</v>
       </c>
       <c r="N150" s="115">
         <f ca="1">SUM(O150:P150)</f>
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="O150" s="98">
         <f ca="1">COUNTIFS($J$7:$J$143,"&lt;=21",$V$7:$V$143,"",$L$7:$L$143,"&lt;&gt;X")</f>
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="P150" s="50">
         <f ca="1">COUNTIFS($J$7:$J$143,"&gt;21",$V$7:$V$143,"",$L$7:$L$143,"&lt;&gt;X")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q150" s="114">
         <f t="shared" ca="1" si="90"/>
@@ -23928,21 +23970,21 @@
       <c r="C151" s="168" t="s">
         <v>30</v>
       </c>
-      <c r="D151" s="409" t="s">
+      <c r="D151" s="354" t="s">
         <v>31</v>
       </c>
-      <c r="E151" s="409"/>
-      <c r="F151" s="410"/>
+      <c r="E151" s="354"/>
+      <c r="F151" s="355"/>
       <c r="H151" s="6"/>
-      <c r="I151" s="400" t="s">
+      <c r="I151" s="391" t="s">
         <v>71</v>
       </c>
-      <c r="J151" s="401"/>
-      <c r="K151" s="401"/>
-      <c r="L151" s="402"/>
+      <c r="J151" s="392"/>
+      <c r="K151" s="392"/>
+      <c r="L151" s="393"/>
       <c r="M151" s="113">
         <f t="shared" ca="1" si="89"/>
-        <v>0.10563380281690141</v>
+        <v>0.10714285714285714</v>
       </c>
       <c r="N151" s="97">
         <f>COUNTIFS($L$7:$L$143,"X")</f>
@@ -23959,11 +24001,11 @@
       <c r="C152" s="168" t="s">
         <v>32</v>
       </c>
-      <c r="D152" s="409" t="s">
+      <c r="D152" s="354" t="s">
         <v>33</v>
       </c>
-      <c r="E152" s="409"/>
-      <c r="F152" s="410"/>
+      <c r="E152" s="354"/>
+      <c r="F152" s="355"/>
       <c r="H152" s="1" t="s">
         <v>11</v>
       </c>
@@ -23972,11 +24014,11 @@
       <c r="C153" s="167" t="s">
         <v>34</v>
       </c>
-      <c r="D153" s="409" t="s">
+      <c r="D153" s="354" t="s">
         <v>35</v>
       </c>
-      <c r="E153" s="409"/>
-      <c r="F153" s="410"/>
+      <c r="E153" s="354"/>
+      <c r="F153" s="355"/>
       <c r="H153" s="13"/>
       <c r="I153" s="141"/>
       <c r="J153" s="141"/>
@@ -24004,14 +24046,14 @@
       <c r="AI153" s="1"/>
     </row>
     <row r="154" spans="1:35">
-      <c r="C154" s="386" t="s">
+      <c r="C154" s="394" t="s">
         <v>75</v>
       </c>
-      <c r="D154" s="388" t="s">
+      <c r="D154" s="350" t="s">
         <v>76</v>
       </c>
-      <c r="E154" s="388"/>
-      <c r="F154" s="389"/>
+      <c r="E154" s="350"/>
+      <c r="F154" s="351"/>
       <c r="H154" s="13"/>
       <c r="J154" s="141"/>
       <c r="K154" s="13"/>
@@ -24038,10 +24080,10 @@
       <c r="AI154" s="1"/>
     </row>
     <row r="155" spans="1:35" ht="16.5" thickBot="1">
-      <c r="C155" s="387"/>
-      <c r="D155" s="390"/>
-      <c r="E155" s="390"/>
-      <c r="F155" s="391"/>
+      <c r="C155" s="395"/>
+      <c r="D155" s="352"/>
+      <c r="E155" s="352"/>
+      <c r="F155" s="353"/>
       <c r="H155" s="13"/>
       <c r="I155" s="141"/>
       <c r="J155" s="141"/>
@@ -24096,12 +24138,12 @@
       <c r="AI156" s="1"/>
     </row>
     <row r="157" spans="1:35">
-      <c r="C157" s="370" t="s">
+      <c r="C157" s="378" t="s">
         <v>41</v>
       </c>
-      <c r="D157" s="370"/>
-      <c r="E157" s="370"/>
-      <c r="F157" s="370"/>
+      <c r="D157" s="378"/>
+      <c r="E157" s="378"/>
+      <c r="F157" s="378"/>
       <c r="H157" s="13"/>
       <c r="I157" s="141"/>
       <c r="J157" s="141"/>
@@ -24132,11 +24174,11 @@
       <c r="C158" s="169" t="s">
         <v>8</v>
       </c>
-      <c r="D158" s="416" t="s">
+      <c r="D158" s="396" t="s">
         <v>91</v>
       </c>
-      <c r="E158" s="416"/>
-      <c r="F158" s="416"/>
+      <c r="E158" s="396"/>
+      <c r="F158" s="396"/>
       <c r="H158" s="13"/>
       <c r="I158" s="141"/>
       <c r="J158" s="141"/>
@@ -24167,11 +24209,11 @@
       <c r="C159" s="169" t="s">
         <v>8</v>
       </c>
-      <c r="D159" s="416" t="s">
+      <c r="D159" s="396" t="s">
         <v>92</v>
       </c>
-      <c r="E159" s="416"/>
-      <c r="F159" s="416"/>
+      <c r="E159" s="396"/>
+      <c r="F159" s="396"/>
       <c r="H159" s="13"/>
       <c r="I159" s="141"/>
       <c r="J159" s="141"/>
@@ -24202,11 +24244,11 @@
       <c r="C160" s="169" t="s">
         <v>8</v>
       </c>
-      <c r="D160" s="416" t="s">
+      <c r="D160" s="396" t="s">
         <v>93</v>
       </c>
-      <c r="E160" s="416"/>
-      <c r="F160" s="416"/>
+      <c r="E160" s="396"/>
+      <c r="F160" s="396"/>
       <c r="H160" s="13"/>
       <c r="I160" s="141"/>
       <c r="J160" s="141"/>
@@ -24261,12 +24303,12 @@
       <c r="AI161" s="1"/>
     </row>
     <row r="162" spans="3:35" ht="16.5" thickBot="1">
-      <c r="C162" s="422" t="s">
+      <c r="C162" s="402" t="s">
         <v>96</v>
       </c>
-      <c r="D162" s="423"/>
-      <c r="E162" s="423"/>
-      <c r="F162" s="424"/>
+      <c r="D162" s="403"/>
+      <c r="E162" s="403"/>
+      <c r="F162" s="404"/>
       <c r="H162" s="13"/>
       <c r="I162" s="141"/>
       <c r="J162" s="141"/>
@@ -24297,11 +24339,11 @@
       <c r="C163" s="212" t="s">
         <v>81</v>
       </c>
-      <c r="D163" s="425" t="s">
+      <c r="D163" s="405" t="s">
         <v>97</v>
       </c>
-      <c r="E163" s="425"/>
-      <c r="F163" s="426"/>
+      <c r="E163" s="405"/>
+      <c r="F163" s="406"/>
       <c r="H163" s="13"/>
       <c r="I163" s="141"/>
       <c r="J163" s="141"/>
@@ -24332,101 +24374,101 @@
       <c r="C164" s="213" t="s">
         <v>82</v>
       </c>
-      <c r="D164" s="417" t="s">
+      <c r="D164" s="397" t="s">
         <v>98</v>
       </c>
-      <c r="E164" s="417"/>
-      <c r="F164" s="418"/>
+      <c r="E164" s="397"/>
+      <c r="F164" s="398"/>
     </row>
     <row r="165" spans="3:35">
       <c r="C165" s="213" t="s">
         <v>83</v>
       </c>
-      <c r="D165" s="417" t="s">
+      <c r="D165" s="397" t="s">
         <v>99</v>
       </c>
-      <c r="E165" s="417"/>
-      <c r="F165" s="418"/>
+      <c r="E165" s="397"/>
+      <c r="F165" s="398"/>
     </row>
     <row r="166" spans="3:35">
       <c r="C166" s="214" t="s">
         <v>84</v>
       </c>
-      <c r="D166" s="417" t="s">
+      <c r="D166" s="397" t="s">
         <v>100</v>
       </c>
-      <c r="E166" s="417"/>
-      <c r="F166" s="418"/>
+      <c r="E166" s="397"/>
+      <c r="F166" s="398"/>
     </row>
     <row r="167" spans="3:35">
       <c r="C167" s="214" t="s">
         <v>85</v>
       </c>
-      <c r="D167" s="417" t="s">
+      <c r="D167" s="397" t="s">
         <v>101</v>
       </c>
-      <c r="E167" s="417"/>
-      <c r="F167" s="418"/>
+      <c r="E167" s="397"/>
+      <c r="F167" s="398"/>
     </row>
     <row r="168" spans="3:35" ht="18.75">
       <c r="C168" s="214" t="s">
         <v>86</v>
       </c>
-      <c r="D168" s="417" t="s">
+      <c r="D168" s="397" t="s">
         <v>102</v>
       </c>
-      <c r="E168" s="417"/>
-      <c r="F168" s="418"/>
+      <c r="E168" s="397"/>
+      <c r="F168" s="398"/>
     </row>
     <row r="169" spans="3:35" ht="18.75">
       <c r="C169" s="213" t="s">
         <v>87</v>
       </c>
-      <c r="D169" s="417" t="s">
+      <c r="D169" s="397" t="s">
         <v>103</v>
       </c>
-      <c r="E169" s="417"/>
-      <c r="F169" s="418"/>
+      <c r="E169" s="397"/>
+      <c r="F169" s="398"/>
     </row>
     <row r="170" spans="3:35">
       <c r="C170" s="215" t="s">
         <v>88</v>
       </c>
-      <c r="D170" s="419" t="s">
+      <c r="D170" s="399" t="s">
         <v>104</v>
       </c>
-      <c r="E170" s="420"/>
-      <c r="F170" s="421"/>
+      <c r="E170" s="400"/>
+      <c r="F170" s="401"/>
     </row>
     <row r="171" spans="3:35" ht="18.75">
       <c r="C171" s="215" t="s">
         <v>89</v>
       </c>
-      <c r="D171" s="417" t="s">
+      <c r="D171" s="397" t="s">
         <v>105</v>
       </c>
-      <c r="E171" s="417"/>
-      <c r="F171" s="418"/>
+      <c r="E171" s="397"/>
+      <c r="F171" s="398"/>
     </row>
     <row r="172" spans="3:35">
       <c r="C172" s="213" t="s">
         <v>90</v>
       </c>
-      <c r="D172" s="417" t="s">
+      <c r="D172" s="397" t="s">
         <v>106</v>
       </c>
-      <c r="E172" s="417"/>
-      <c r="F172" s="418"/>
+      <c r="E172" s="397"/>
+      <c r="F172" s="398"/>
     </row>
     <row r="173" spans="3:35" ht="16.5" thickBot="1">
       <c r="C173" s="216" t="s">
         <v>94</v>
       </c>
-      <c r="D173" s="413" t="s">
+      <c r="D173" s="373" t="s">
         <v>107</v>
       </c>
-      <c r="E173" s="414"/>
-      <c r="F173" s="415"/>
+      <c r="E173" s="374"/>
+      <c r="F173" s="375"/>
     </row>
   </sheetData>
   <autoFilter ref="A6:AE143" xr:uid="{C724CDAB-378C-47DB-9F45-08EE3BFB6E8B}">
@@ -25025,9 +25067,11 @@
     <hyperlink ref="M140" r:id="rId503" xr:uid="{1BAE53B4-41B2-4955-9719-066BE2284B9D}"/>
     <hyperlink ref="M141" r:id="rId504" xr:uid="{1AD5278F-5E89-48A8-B214-0DE3CB9C250D}"/>
     <hyperlink ref="O135" r:id="rId505" xr:uid="{E415571E-9ABB-4838-B4BB-663A644C52E5}"/>
+    <hyperlink ref="O132" r:id="rId506" xr:uid="{98767DB8-64B4-4F62-AF4D-D1090D594B1A}"/>
+    <hyperlink ref="O131" r:id="rId507" xr:uid="{DE03DEA0-F484-427D-9D4A-E446F78CBEA0}"/>
   </hyperlinks>
   <pageMargins left="0.25" right="0.17" top="0.5" bottom="0.25" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="28" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId506"/>
+  <pageSetup paperSize="9" scale="28" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId508"/>
   <colBreaks count="1" manualBreakCount="1">
     <brk id="30" max="564" man="1"/>
   </colBreaks>
@@ -25036,7 +25080,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D8E8261-1CEF-42DB-8488-C430D415EC88}">
-  <dimension ref="A1:AI54"/>
+  <dimension ref="A1:AI58"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" customWidth="1"/>
@@ -25080,7 +25124,7 @@
       </c>
       <c r="I1" s="176">
         <f ca="1">TODAY()</f>
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="J1" s="131"/>
       <c r="K1" s="197"/>
@@ -25165,88 +25209,88 @@
       <c r="AD3" s="159"/>
     </row>
     <row r="4" spans="1:35" s="5" customFormat="1" ht="36" customHeight="1" thickBot="1">
-      <c r="A4" s="354" t="s">
+      <c r="A4" s="408" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="366" t="s">
+      <c r="B4" s="348" t="s">
         <v>515</v>
       </c>
-      <c r="C4" s="362" t="s">
+      <c r="C4" s="414" t="s">
         <v>45</v>
       </c>
-      <c r="D4" s="356" t="s">
+      <c r="D4" s="369" t="s">
         <v>46</v>
       </c>
-      <c r="E4" s="358" t="s">
+      <c r="E4" s="412" t="s">
         <v>47</v>
       </c>
-      <c r="F4" s="356" t="s">
+      <c r="F4" s="369" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="360" t="s">
+      <c r="G4" s="410" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="404" t="s">
+      <c r="H4" s="366" t="s">
         <v>48</v>
       </c>
-      <c r="I4" s="404" t="s">
+      <c r="I4" s="366" t="s">
         <v>49</v>
       </c>
-      <c r="J4" s="356" t="s">
+      <c r="J4" s="369" t="s">
         <v>78</v>
       </c>
-      <c r="K4" s="404" t="s">
+      <c r="K4" s="366" t="s">
         <v>80</v>
       </c>
-      <c r="L4" s="406" t="s">
+      <c r="L4" s="364" t="s">
         <v>53</v>
       </c>
-      <c r="M4" s="407"/>
-      <c r="N4" s="408" t="s">
+      <c r="M4" s="365"/>
+      <c r="N4" s="368" t="s">
         <v>55</v>
       </c>
-      <c r="O4" s="407"/>
-      <c r="P4" s="408" t="s">
+      <c r="O4" s="365"/>
+      <c r="P4" s="368" t="s">
         <v>72</v>
       </c>
-      <c r="Q4" s="407"/>
-      <c r="R4" s="406" t="s">
+      <c r="Q4" s="365"/>
+      <c r="R4" s="364" t="s">
         <v>53</v>
       </c>
-      <c r="S4" s="406"/>
-      <c r="T4" s="407"/>
-      <c r="U4" s="408" t="s">
+      <c r="S4" s="364"/>
+      <c r="T4" s="365"/>
+      <c r="U4" s="368" t="s">
         <v>55</v>
       </c>
-      <c r="V4" s="406"/>
-      <c r="W4" s="407"/>
-      <c r="X4" s="350" t="s">
+      <c r="V4" s="364"/>
+      <c r="W4" s="365"/>
+      <c r="X4" s="371" t="s">
         <v>72</v>
       </c>
-      <c r="Y4" s="351"/>
-      <c r="Z4" s="350" t="s">
+      <c r="Y4" s="417"/>
+      <c r="Z4" s="371" t="s">
         <v>112</v>
       </c>
-      <c r="AA4" s="352"/>
-      <c r="AB4" s="352"/>
-      <c r="AC4" s="353"/>
-      <c r="AD4" s="356" t="s">
+      <c r="AA4" s="360"/>
+      <c r="AB4" s="360"/>
+      <c r="AC4" s="361"/>
+      <c r="AD4" s="369" t="s">
         <v>79</v>
       </c>
       <c r="AG4" s="236"/>
     </row>
     <row r="5" spans="1:35" ht="78.75">
-      <c r="A5" s="355"/>
-      <c r="B5" s="367"/>
-      <c r="C5" s="363"/>
-      <c r="D5" s="357"/>
-      <c r="E5" s="359"/>
-      <c r="F5" s="357"/>
-      <c r="G5" s="361"/>
-      <c r="H5" s="405"/>
-      <c r="I5" s="405"/>
-      <c r="J5" s="357"/>
-      <c r="K5" s="405"/>
+      <c r="A5" s="409"/>
+      <c r="B5" s="349"/>
+      <c r="C5" s="415"/>
+      <c r="D5" s="370"/>
+      <c r="E5" s="413"/>
+      <c r="F5" s="370"/>
+      <c r="G5" s="411"/>
+      <c r="H5" s="367"/>
+      <c r="I5" s="367"/>
+      <c r="J5" s="370"/>
+      <c r="K5" s="367"/>
       <c r="L5" s="79" t="s">
         <v>52</v>
       </c>
@@ -25301,14 +25345,14 @@
       <c r="AC5" s="250" t="s">
         <v>118</v>
       </c>
-      <c r="AD5" s="403"/>
-      <c r="AG5" s="394" t="s">
+      <c r="AD5" s="416"/>
+      <c r="AG5" s="422" t="s">
         <v>119</v>
       </c>
-      <c r="AH5" s="396" t="s">
+      <c r="AH5" s="424" t="s">
         <v>120</v>
       </c>
-      <c r="AI5" s="398" t="s">
+      <c r="AI5" s="426" t="s">
         <v>121</v>
       </c>
     </row>
@@ -25343,13 +25387,13 @@
       <c r="AB6" s="86"/>
       <c r="AC6" s="86"/>
       <c r="AD6" s="74"/>
-      <c r="AG6" s="395"/>
-      <c r="AH6" s="397"/>
-      <c r="AI6" s="399"/>
+      <c r="AG6" s="423"/>
+      <c r="AH6" s="425"/>
+      <c r="AI6" s="427"/>
     </row>
     <row r="7" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A7" s="33">
-        <f t="shared" ref="A7:A41" si="0">A6+1</f>
+        <f t="shared" ref="A7:A45" si="0">A6+1</f>
         <v>1</v>
       </c>
       <c r="B7" s="33" t="str">
@@ -25363,7 +25407,7 @@
         <v>519</v>
       </c>
       <c r="E7" s="174">
-        <f t="shared" ref="E7:E41" si="2">IF($T7=0,$S7+22,$T7+21)</f>
+        <f t="shared" ref="E7:E45" si="2">IF($T7=0,$S7+22,$T7+21)</f>
         <v>45490</v>
       </c>
       <c r="F7" s="30" t="s">
@@ -25449,8 +25493,8 @@
       <c r="AH7" s="242" t="b" cm="1">
         <f t="array" ref="AH7">$D7=_xlfn.XLOOKUP(
 AG7,
-_xlfn._xlws.FILTER($AG$7:$AG$4870,$K$7:$K$4870&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4870,$K$7:$K$4870&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4874,$K$7:$K$4874&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4874,$K$7:$K$4874&lt;&gt;"X"),
 "",
 0,
 -1
@@ -25495,7 +25539,7 @@
         <v>25</v>
       </c>
       <c r="J8" s="47">
-        <f t="shared" ref="J8:J41" si="4">IF(($I8-21)&gt;0,$I8-21,0)</f>
+        <f t="shared" ref="J8:J45" si="4">IF(($I8-21)&gt;0,$I8-21,0)</f>
         <v>4</v>
       </c>
       <c r="K8" s="164"/>
@@ -25542,14 +25586,14 @@
         <v>45674</v>
       </c>
       <c r="Z8" s="29">
-        <f t="shared" ref="Z8:Z43" si="5">IF(AND($Q8="",$H8=""),"",IF(OR($Q8="B",$Q8="C"),IF($Y8&lt;&gt;"",$Y8+7,IF($X8&lt;&gt;"",$X8+8,"")),IF($Q8="",IF(OR($H8="B",$H8="C"),IF($V8&lt;&gt;"",$V8+7,IF($U8&lt;&gt;"",$U8+8,""))),"")))</f>
+        <f t="shared" ref="Z8:Z47" si="5">IF(AND($Q8="",$H8=""),"",IF(OR($Q8="B",$Q8="C"),IF($Y8&lt;&gt;"",$Y8+7,IF($X8&lt;&gt;"",$X8+8,"")),IF($Q8="",IF(OR($H8="B",$H8="C"),IF($V8&lt;&gt;"",$V8+7,IF($U8&lt;&gt;"",$U8+8,""))),"")))</f>
         <v>45681</v>
       </c>
       <c r="AA8" s="229">
         <v>45850</v>
       </c>
       <c r="AB8" s="229" t="str">
-        <f t="shared" ref="AB8:AB41" si="6">IF(OR($Q8="B",$Q8="C"),IF($Z8="","",IF($AA8="",IF($Z8&gt;=$I$1,"In progress","Not submit yet"),IF($Z8&gt;=$AA8,"Timely Response","Late Resubmission"))),"")</f>
+        <f t="shared" ref="AB8:AB45" si="6">IF(OR($Q8="B",$Q8="C"),IF($Z8="","",IF($AA8="",IF($Z8&gt;=$I$1,"In progress","Not submit yet"),IF($Z8&gt;=$AA8,"Timely Response","Late Resubmission"))),"")</f>
         <v>Late Resubmission</v>
       </c>
       <c r="AC8" s="183">
@@ -25558,14 +25602,14 @@
       </c>
       <c r="AD8" s="92"/>
       <c r="AG8" s="238" t="str">
-        <f t="shared" ref="AG8:AG41" si="8">IF(AND(RIGHT($D8,1)&gt;="A",RIGHT($D8,1)&lt;="Z"),LEFT($D8,LEN($D8)-1),$D8)</f>
+        <f t="shared" ref="AG8:AG45" si="8">IF(AND(RIGHT($D8,1)&gt;="A",RIGHT($D8,1)&lt;="Z"),LEFT($D8,LEN($D8)-1),$D8)</f>
         <v>LTIA-5.10-VIETUR-80000-RFA-SDS-0122</v>
       </c>
       <c r="AH8" s="243" t="b" cm="1">
         <f t="array" ref="AH8">$D8=_xlfn.XLOOKUP(
 AG8,
-_xlfn._xlws.FILTER($AG$7:$AG$4870,$K$7:$K$4870&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4870,$K$7:$K$4870&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4874,$K$7:$K$4874&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4874,$K$7:$K$4874&lt;&gt;"X"),
 "",
 0,
 -1
@@ -25686,8 +25730,8 @@
       <c r="AH9" s="243" t="b" cm="1">
         <f t="array" ref="AH9">$D9=_xlfn.XLOOKUP(
 AG9,
-_xlfn._xlws.FILTER($AG$7:$AG$4870,$K$7:$K$4870&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4870,$K$7:$K$4870&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4874,$K$7:$K$4874&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4874,$K$7:$K$4874&lt;&gt;"X"),
 "",
 0,
 -1
@@ -25801,8 +25845,8 @@
       <c r="AH10" s="243" t="b" cm="1">
         <f t="array" ref="AH10">$D10=_xlfn.XLOOKUP(
 AG10,
-_xlfn._xlws.FILTER($AG$7:$AG$4870,$K$7:$K$4870&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4870,$K$7:$K$4870&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4874,$K$7:$K$4874&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4874,$K$7:$K$4874&lt;&gt;"X"),
 "",
 0,
 -1
@@ -25918,8 +25962,8 @@
       <c r="AH11" s="243" t="b" cm="1">
         <f t="array" ref="AH11">$D11=_xlfn.XLOOKUP(
 AG11,
-_xlfn._xlws.FILTER($AG$7:$AG$4870,$K$7:$K$4870&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4870,$K$7:$K$4870&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4874,$K$7:$K$4874&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4874,$K$7:$K$4874&lt;&gt;"X"),
 "",
 0,
 -1
@@ -26021,7 +26065,7 @@
       </c>
       <c r="AC12" s="183">
         <f t="shared" ca="1" si="7"/>
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="AD12" s="92"/>
       <c r="AG12" s="238" t="str">
@@ -26031,8 +26075,8 @@
       <c r="AH12" s="243" t="b" cm="1">
         <f t="array" ref="AH12">$D12=_xlfn.XLOOKUP(
 AG12,
-_xlfn._xlws.FILTER($AG$7:$AG$4870,$K$7:$K$4870&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4870,$K$7:$K$4870&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4874,$K$7:$K$4874&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4874,$K$7:$K$4874&lt;&gt;"X"),
 "",
 0,
 -1
@@ -26144,8 +26188,8 @@
       <c r="AH13" s="243" t="b" cm="1">
         <f t="array" ref="AH13">$D13=_xlfn.XLOOKUP(
 AG13,
-_xlfn._xlws.FILTER($AG$7:$AG$4870,$K$7:$K$4870&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4870,$K$7:$K$4870&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4874,$K$7:$K$4874&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4874,$K$7:$K$4874&lt;&gt;"X"),
 "",
 0,
 -1
@@ -26186,7 +26230,7 @@
         <v>2</v>
       </c>
       <c r="I14" s="164">
-        <f t="shared" ref="I14:I41" si="10">IF(ISBLANK($V14),_xlfn.DAYS($I$1,$T14),_xlfn.DAYS($V14,$T14))</f>
+        <f t="shared" ref="I14:I45" si="10">IF(ISBLANK($V14),_xlfn.DAYS($I$1,$T14),_xlfn.DAYS($V14,$T14))</f>
         <v>25</v>
       </c>
       <c r="J14" s="47">
@@ -26247,7 +26291,7 @@
       </c>
       <c r="AC14" s="183">
         <f t="shared" ca="1" si="7"/>
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="AD14" s="92"/>
       <c r="AG14" s="238" t="str">
@@ -26257,8 +26301,8 @@
       <c r="AH14" s="243" t="b" cm="1">
         <f t="array" ref="AH14">$D14=_xlfn.XLOOKUP(
 AG14,
-_xlfn._xlws.FILTER($AG$7:$AG$4870,$K$7:$K$4870&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4870,$K$7:$K$4870&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4874,$K$7:$K$4874&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4874,$K$7:$K$4874&lt;&gt;"X"),
 "",
 0,
 -1
@@ -26370,8 +26414,8 @@
       <c r="AH15" s="243" t="b" cm="1">
         <f t="array" ref="AH15">$D15=_xlfn.XLOOKUP(
 AG15,
-_xlfn._xlws.FILTER($AG$7:$AG$4870,$K$7:$K$4870&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4870,$K$7:$K$4870&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4874,$K$7:$K$4874&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4874,$K$7:$K$4874&lt;&gt;"X"),
 "",
 0,
 -1
@@ -26473,7 +26517,7 @@
       </c>
       <c r="AC16" s="183">
         <f t="shared" ca="1" si="7"/>
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AD16" s="92"/>
       <c r="AG16" s="238" t="str">
@@ -26483,8 +26527,8 @@
       <c r="AH16" s="243" t="b" cm="1">
         <f t="array" ref="AH16">$D16=_xlfn.XLOOKUP(
 AG16,
-_xlfn._xlws.FILTER($AG$7:$AG$4870,$K$7:$K$4870&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4870,$K$7:$K$4870&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4874,$K$7:$K$4874&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4874,$K$7:$K$4874&lt;&gt;"X"),
 "",
 0,
 -1
@@ -26496,7 +26540,7 @@
         <v>YES</v>
       </c>
     </row>
-    <row r="17" spans="1:35" s="9" customFormat="1" ht="94.5">
+    <row r="17" spans="1:35" s="9" customFormat="1" ht="110.25">
       <c r="A17" s="33">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -26579,14 +26623,16 @@
         <f t="shared" si="5"/>
         <v>45964</v>
       </c>
-      <c r="AA17" s="229"/>
+      <c r="AA17" s="229">
+        <v>46316</v>
+      </c>
       <c r="AB17" s="229" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v>Not submit yet</v>
+        <f t="shared" si="6"/>
+        <v>Late Resubmission</v>
       </c>
       <c r="AC17" s="183">
-        <f t="shared" ca="1" si="7"/>
-        <v>351</v>
+        <f t="shared" si="7"/>
+        <v>352</v>
       </c>
       <c r="AD17" s="92"/>
       <c r="AG17" s="238" t="str">
@@ -26596,1159 +26642,1163 @@
       <c r="AH17" s="243" t="b" cm="1">
         <f t="array" ref="AH17">$D17=_xlfn.XLOOKUP(
 AG17,
-_xlfn._xlws.FILTER($AG$7:$AG$4870,$K$7:$K$4870&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4870,$K$7:$K$4870&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4874,$K$7:$K$4874&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4874,$K$7:$K$4874&lt;&gt;"X"),
+"",
+0,
+-1
+)</f>
+        <v>0</v>
+      </c>
+      <c r="AI17" s="75" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="1:35" s="9" customFormat="1" ht="47.25">
+      <c r="A18" s="33">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="B18" s="33" t="str">
+        <f t="shared" si="1"/>
+        <v>5.10</v>
+      </c>
+      <c r="C18" s="137" t="s">
+        <v>556</v>
+      </c>
+      <c r="D18" s="25" t="s">
+        <v>564</v>
+      </c>
+      <c r="E18" s="174">
+        <f t="shared" si="2"/>
+        <v>45887</v>
+      </c>
+      <c r="F18" s="31" t="s">
+        <v>520</v>
+      </c>
+      <c r="G18" s="21" t="s">
+        <v>521</v>
+      </c>
+      <c r="H18" s="138" t="s">
+        <v>2</v>
+      </c>
+      <c r="I18" s="164">
+        <f t="shared" si="10"/>
+        <v>42</v>
+      </c>
+      <c r="J18" s="47">
+        <f t="shared" si="4"/>
+        <v>21</v>
+      </c>
+      <c r="K18" s="164"/>
+      <c r="L18" s="54" t="s">
+        <v>8</v>
+      </c>
+      <c r="M18" s="65" t="s">
+        <v>8</v>
+      </c>
+      <c r="N18" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="O18" s="41" t="s">
+        <v>8</v>
+      </c>
+      <c r="P18" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q18" s="155" t="s">
+        <v>2</v>
+      </c>
+      <c r="R18" s="27">
+        <v>45861</v>
+      </c>
+      <c r="S18" s="27">
+        <v>45861</v>
+      </c>
+      <c r="T18" s="187">
+        <v>45866</v>
+      </c>
+      <c r="U18" s="29">
+        <v>45874</v>
+      </c>
+      <c r="V18" s="188">
+        <v>45908</v>
+      </c>
+      <c r="W18" s="235" t="s">
+        <v>559</v>
+      </c>
+      <c r="X18" s="230">
+        <v>45954</v>
+      </c>
+      <c r="Y18" s="227">
+        <v>45957</v>
+      </c>
+      <c r="Z18" s="29">
+        <f t="shared" si="5"/>
+        <v>45964</v>
+      </c>
+      <c r="AA18" s="229">
+        <v>46316</v>
+      </c>
+      <c r="AB18" s="229" t="str">
+        <f t="shared" si="6"/>
+        <v>Late Resubmission</v>
+      </c>
+      <c r="AC18" s="183">
+        <f t="shared" si="7"/>
+        <v>352</v>
+      </c>
+      <c r="AD18" s="92"/>
+      <c r="AG18" s="238" t="str">
+        <f t="shared" si="8"/>
+        <v>LTIA-5.10-VIETUR-80000-RFA-SDS-0080</v>
+      </c>
+      <c r="AH18" s="243" t="b" cm="1">
+        <f t="array" ref="AH18">$D18=_xlfn.XLOOKUP(
+AG18,
+_xlfn._xlws.FILTER($AG$7:$AG$4874,$K$7:$K$4874&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4874,$K$7:$K$4874&lt;&gt;"X"),
+"",
+0,
+-1
+)</f>
+        <v>0</v>
+      </c>
+      <c r="AI18" s="75" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:35" s="9" customFormat="1" ht="47.25">
+      <c r="A19" s="33">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="B19" s="33" t="str">
+        <f t="shared" si="1"/>
+        <v>5.10</v>
+      </c>
+      <c r="C19" s="137" t="s">
+        <v>556</v>
+      </c>
+      <c r="D19" s="25" t="s">
+        <v>565</v>
+      </c>
+      <c r="E19" s="174">
+        <f t="shared" si="2"/>
+        <v>45887</v>
+      </c>
+      <c r="F19" s="31" t="s">
+        <v>529</v>
+      </c>
+      <c r="G19" s="21" t="s">
+        <v>530</v>
+      </c>
+      <c r="H19" s="138" t="s">
+        <v>2</v>
+      </c>
+      <c r="I19" s="164">
+        <f t="shared" si="10"/>
+        <v>42</v>
+      </c>
+      <c r="J19" s="47">
+        <f t="shared" si="4"/>
+        <v>21</v>
+      </c>
+      <c r="K19" s="164"/>
+      <c r="L19" s="54" t="s">
+        <v>8</v>
+      </c>
+      <c r="M19" s="65" t="s">
+        <v>8</v>
+      </c>
+      <c r="N19" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="O19" s="41" t="s">
+        <v>8</v>
+      </c>
+      <c r="P19" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q19" s="155" t="s">
+        <v>2</v>
+      </c>
+      <c r="R19" s="27">
+        <v>45861</v>
+      </c>
+      <c r="S19" s="27">
+        <v>45861</v>
+      </c>
+      <c r="T19" s="187">
+        <v>45866</v>
+      </c>
+      <c r="U19" s="29">
+        <v>45628</v>
+      </c>
+      <c r="V19" s="188">
+        <v>45908</v>
+      </c>
+      <c r="W19" s="235" t="s">
+        <v>559</v>
+      </c>
+      <c r="X19" s="230">
+        <v>45954</v>
+      </c>
+      <c r="Y19" s="227">
+        <v>45957</v>
+      </c>
+      <c r="Z19" s="29">
+        <f t="shared" si="5"/>
+        <v>45964</v>
+      </c>
+      <c r="AA19" s="229">
+        <v>45908</v>
+      </c>
+      <c r="AB19" s="229" t="str">
+        <f t="shared" si="6"/>
+        <v>Timely Response</v>
+      </c>
+      <c r="AC19" s="183" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="AD19" s="92"/>
+      <c r="AG19" s="238" t="str">
+        <f t="shared" si="8"/>
+        <v>LTIA-5.10-VIETUR-80000-RFA-SDS-0140</v>
+      </c>
+      <c r="AH19" s="243" t="b" cm="1">
+        <f t="array" ref="AH19">$D19=_xlfn.XLOOKUP(
+AG19,
+_xlfn._xlws.FILTER($AG$7:$AG$4874,$K$7:$K$4874&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4874,$K$7:$K$4874&lt;&gt;"X"),
+"",
+0,
+-1
+)</f>
+        <v>0</v>
+      </c>
+      <c r="AI19" s="75" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:35" s="9" customFormat="1" ht="47.25">
+      <c r="A20" s="33">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="B20" s="33" t="str">
+        <f t="shared" si="1"/>
+        <v>5.10</v>
+      </c>
+      <c r="C20" s="137" t="s">
+        <v>556</v>
+      </c>
+      <c r="D20" s="25" t="s">
+        <v>566</v>
+      </c>
+      <c r="E20" s="174">
+        <f t="shared" si="2"/>
+        <v>45887</v>
+      </c>
+      <c r="F20" s="31" t="s">
+        <v>534</v>
+      </c>
+      <c r="G20" s="21" t="s">
+        <v>535</v>
+      </c>
+      <c r="H20" s="138" t="s">
+        <v>2</v>
+      </c>
+      <c r="I20" s="164">
+        <f t="shared" si="10"/>
+        <v>42</v>
+      </c>
+      <c r="J20" s="47">
+        <f t="shared" si="4"/>
+        <v>21</v>
+      </c>
+      <c r="K20" s="164"/>
+      <c r="L20" s="54" t="s">
+        <v>8</v>
+      </c>
+      <c r="M20" s="65" t="s">
+        <v>8</v>
+      </c>
+      <c r="N20" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="O20" s="41" t="s">
+        <v>8</v>
+      </c>
+      <c r="P20" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q20" s="155" t="s">
+        <v>2</v>
+      </c>
+      <c r="R20" s="27">
+        <v>45861</v>
+      </c>
+      <c r="S20" s="27">
+        <v>45861</v>
+      </c>
+      <c r="T20" s="187">
+        <v>45866</v>
+      </c>
+      <c r="U20" s="29">
+        <v>45646</v>
+      </c>
+      <c r="V20" s="188">
+        <v>45908</v>
+      </c>
+      <c r="W20" s="235" t="s">
+        <v>559</v>
+      </c>
+      <c r="X20" s="230">
+        <v>45954</v>
+      </c>
+      <c r="Y20" s="227">
+        <v>45957</v>
+      </c>
+      <c r="Z20" s="29">
+        <f t="shared" si="5"/>
+        <v>45964</v>
+      </c>
+      <c r="AA20" s="229">
+        <v>45972</v>
+      </c>
+      <c r="AB20" s="229" t="str">
+        <f t="shared" si="6"/>
+        <v>Late Resubmission</v>
+      </c>
+      <c r="AC20" s="183">
+        <f t="shared" si="7"/>
+        <v>8</v>
+      </c>
+      <c r="AD20" s="92"/>
+      <c r="AG20" s="238" t="str">
+        <f t="shared" si="8"/>
+        <v>LTIA-5.10-VIETUR-80000-RFA-SDS-0160</v>
+      </c>
+      <c r="AH20" s="243" t="b" cm="1">
+        <f t="array" ref="AH20">$D20=_xlfn.XLOOKUP(
+AG20,
+_xlfn._xlws.FILTER($AG$7:$AG$4874,$K$7:$K$4874&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4874,$K$7:$K$4874&lt;&gt;"X"),
+"",
+0,
+-1
+)</f>
+        <v>0</v>
+      </c>
+      <c r="AI20" s="75" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="1:35" s="9" customFormat="1" ht="47.25">
+      <c r="A21" s="33">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="B21" s="33" t="str">
+        <f t="shared" si="1"/>
+        <v>5.10</v>
+      </c>
+      <c r="C21" s="137" t="s">
+        <v>556</v>
+      </c>
+      <c r="D21" s="25" t="s">
+        <v>567</v>
+      </c>
+      <c r="E21" s="174">
+        <f t="shared" si="2"/>
+        <v>45887</v>
+      </c>
+      <c r="F21" s="31" t="s">
+        <v>537</v>
+      </c>
+      <c r="G21" s="21" t="s">
+        <v>538</v>
+      </c>
+      <c r="H21" s="138" t="s">
+        <v>2</v>
+      </c>
+      <c r="I21" s="164">
+        <f t="shared" si="10"/>
+        <v>42</v>
+      </c>
+      <c r="J21" s="47">
+        <f t="shared" si="4"/>
+        <v>21</v>
+      </c>
+      <c r="K21" s="164"/>
+      <c r="L21" s="54" t="s">
+        <v>8</v>
+      </c>
+      <c r="M21" s="65" t="s">
+        <v>8</v>
+      </c>
+      <c r="N21" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="O21" s="41" t="s">
+        <v>8</v>
+      </c>
+      <c r="P21" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q21" s="155" t="s">
+        <v>2</v>
+      </c>
+      <c r="R21" s="27">
+        <v>45861</v>
+      </c>
+      <c r="S21" s="27">
+        <v>45861</v>
+      </c>
+      <c r="T21" s="188">
+        <v>45866</v>
+      </c>
+      <c r="U21" s="29">
+        <v>45648</v>
+      </c>
+      <c r="V21" s="188">
+        <v>45908</v>
+      </c>
+      <c r="W21" s="235" t="s">
+        <v>559</v>
+      </c>
+      <c r="X21" s="230">
+        <v>45954</v>
+      </c>
+      <c r="Y21" s="227">
+        <v>45957</v>
+      </c>
+      <c r="Z21" s="29">
+        <f t="shared" si="5"/>
+        <v>45964</v>
+      </c>
+      <c r="AA21" s="229">
+        <v>45959</v>
+      </c>
+      <c r="AB21" s="229" t="str">
+        <f t="shared" si="6"/>
+        <v>Timely Response</v>
+      </c>
+      <c r="AC21" s="183" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="AD21" s="332" t="s">
+        <v>568</v>
+      </c>
+      <c r="AG21" s="238" t="str">
+        <f t="shared" si="8"/>
+        <v>LTIA-5.10-VIETUR-80000-RFA-SDS-0197</v>
+      </c>
+      <c r="AH21" s="243" t="b" cm="1">
+        <f t="array" ref="AH21">$D21=_xlfn.XLOOKUP(
+AG21,
+_xlfn._xlws.FILTER($AG$7:$AG$4874,$K$7:$K$4874&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4874,$K$7:$K$4874&lt;&gt;"X"),
+"",
+0,
+-1
+)</f>
+        <v>0</v>
+      </c>
+      <c r="AI21" s="75" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="1:35" s="9" customFormat="1" ht="63">
+      <c r="A22" s="33">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="B22" s="33" t="str">
+        <f t="shared" si="1"/>
+        <v>5.10</v>
+      </c>
+      <c r="C22" s="137" t="s">
+        <v>571</v>
+      </c>
+      <c r="D22" s="25" t="s">
+        <v>569</v>
+      </c>
+      <c r="E22" s="174">
+        <f t="shared" si="2"/>
+        <v>46009</v>
+      </c>
+      <c r="F22" s="31" t="s">
+        <v>552</v>
+      </c>
+      <c r="G22" s="21" t="s">
+        <v>570</v>
+      </c>
+      <c r="H22" s="138" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="164">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="J22" s="47">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K22" s="164"/>
+      <c r="L22" s="54" t="s">
+        <v>8</v>
+      </c>
+      <c r="M22" s="65" t="s">
+        <v>8</v>
+      </c>
+      <c r="N22" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="O22" s="41" t="s">
+        <v>8</v>
+      </c>
+      <c r="P22" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q22" s="155" t="s">
+        <v>3</v>
+      </c>
+      <c r="R22" s="27">
+        <v>45861</v>
+      </c>
+      <c r="S22" s="27">
+        <v>45861</v>
+      </c>
+      <c r="T22" s="188">
+        <v>45988</v>
+      </c>
+      <c r="U22" s="29">
+        <v>45880</v>
+      </c>
+      <c r="V22" s="188">
+        <v>45989</v>
+      </c>
+      <c r="W22" s="235" t="s">
+        <v>572</v>
+      </c>
+      <c r="X22" s="230">
+        <v>45994</v>
+      </c>
+      <c r="Y22" s="227">
+        <v>45995</v>
+      </c>
+      <c r="Z22" s="29" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="AA22" s="229"/>
+      <c r="AB22" s="229" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="AC22" s="183" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="AD22" s="92" t="s">
+        <v>886</v>
+      </c>
+      <c r="AG22" s="238" t="str">
+        <f t="shared" si="8"/>
+        <v>LTIA-5.10-VIETUR-80000-RFA-SDS-0310</v>
+      </c>
+      <c r="AH22" s="243" t="b" cm="1">
+        <f t="array" ref="AH22">$D22=_xlfn.XLOOKUP(
+AG22,
+_xlfn._xlws.FILTER($AG$7:$AG$4874,$K$7:$K$4874&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4874,$K$7:$K$4874&lt;&gt;"X"),
 "",
 0,
 -1
 )</f>
         <v>1</v>
       </c>
-      <c r="AI17" s="75" t="str">
+      <c r="AI22" s="75" t="str">
         <f t="shared" si="9"/>
-        <v>YES</v>
-      </c>
-    </row>
-    <row r="18" spans="1:35" s="9" customFormat="1" ht="47.25">
-      <c r="A18" s="33">
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:35" s="9" customFormat="1" ht="47.25">
+      <c r="A23" s="33">
         <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="B18" s="33" t="str">
+        <v>17</v>
+      </c>
+      <c r="B23" s="33" t="str">
         <f t="shared" si="1"/>
         <v>5.10</v>
       </c>
-      <c r="C18" s="137" t="s">
-        <v>556</v>
-      </c>
-      <c r="D18" s="25" t="s">
-        <v>564</v>
-      </c>
-      <c r="E18" s="174">
-        <f t="shared" si="2"/>
-        <v>45887</v>
-      </c>
-      <c r="F18" s="31" t="s">
-        <v>520</v>
-      </c>
-      <c r="G18" s="21" t="s">
-        <v>521</v>
-      </c>
-      <c r="H18" s="138" t="s">
+      <c r="C23" s="164" t="s">
+        <v>576</v>
+      </c>
+      <c r="D23" s="25" t="s">
+        <v>573</v>
+      </c>
+      <c r="E23" s="174">
+        <f>IF($T23=0,$S23+22,$T23+21)</f>
+        <v>45902</v>
+      </c>
+      <c r="F23" s="31" t="s">
+        <v>574</v>
+      </c>
+      <c r="G23" s="21" t="s">
+        <v>575</v>
+      </c>
+      <c r="H23" s="138" t="s">
         <v>2</v>
       </c>
-      <c r="I18" s="164">
-        <f t="shared" si="10"/>
-        <v>42</v>
-      </c>
-      <c r="J18" s="47">
+      <c r="I23" s="164">
+        <f>IF(ISBLANK($V23),_xlfn.DAYS($I$1,$T23),_xlfn.DAYS($V23,$T23))</f>
+        <v>27</v>
+      </c>
+      <c r="J23" s="47">
         <f t="shared" si="4"/>
-        <v>21</v>
-      </c>
-      <c r="K18" s="164"/>
-      <c r="L18" s="54" t="s">
-        <v>8</v>
-      </c>
-      <c r="M18" s="65" t="s">
-        <v>8</v>
-      </c>
-      <c r="N18" s="40" t="s">
-        <v>8</v>
-      </c>
-      <c r="O18" s="41" t="s">
-        <v>8</v>
-      </c>
-      <c r="P18" s="40" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q18" s="155" t="s">
+        <v>6</v>
+      </c>
+      <c r="K23" s="164"/>
+      <c r="L23" s="54" t="s">
+        <v>8</v>
+      </c>
+      <c r="M23" s="65" t="s">
+        <v>8</v>
+      </c>
+      <c r="N23" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="O23" s="41" t="s">
+        <v>8</v>
+      </c>
+      <c r="P23" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q23" s="155" t="s">
         <v>2</v>
       </c>
-      <c r="R18" s="27">
-        <v>45861</v>
-      </c>
-      <c r="S18" s="27">
-        <v>45861</v>
-      </c>
-      <c r="T18" s="187">
-        <v>45866</v>
-      </c>
-      <c r="U18" s="29">
-        <v>45874</v>
-      </c>
-      <c r="V18" s="188">
+      <c r="R23" s="27">
+        <v>45880</v>
+      </c>
+      <c r="S23" s="27">
+        <v>45880</v>
+      </c>
+      <c r="T23" s="188">
+        <v>45881</v>
+      </c>
+      <c r="U23" s="29">
+        <v>45891</v>
+      </c>
+      <c r="V23" s="188">
         <v>45908</v>
       </c>
-      <c r="W18" s="235" t="s">
+      <c r="W23" s="235" t="s">
         <v>559</v>
       </c>
-      <c r="X18" s="230">
+      <c r="X23" s="230">
         <v>45954</v>
       </c>
-      <c r="Y18" s="227">
+      <c r="Y23" s="227">
         <v>45957</v>
       </c>
-      <c r="Z18" s="29">
+      <c r="Z23" s="29">
         <f t="shared" si="5"/>
         <v>45964</v>
       </c>
-      <c r="AA18" s="229"/>
-      <c r="AB18" s="229" t="str">
+      <c r="AA23" s="229"/>
+      <c r="AB23" s="229" t="str">
         <f t="shared" ca="1" si="6"/>
         <v>Not submit yet</v>
       </c>
-      <c r="AC18" s="183">
+      <c r="AC23" s="183">
         <f t="shared" ca="1" si="7"/>
-        <v>351</v>
-      </c>
-      <c r="AD18" s="92"/>
-      <c r="AG18" s="238" t="str">
+        <v>353</v>
+      </c>
+      <c r="AD23" s="92"/>
+      <c r="AG23" s="238" t="str">
         <f t="shared" si="8"/>
-        <v>LTIA-5.10-VIETUR-80000-RFA-SDS-0080</v>
-      </c>
-      <c r="AH18" s="243" t="b" cm="1">
-        <f t="array" ref="AH18">$D18=_xlfn.XLOOKUP(
-AG18,
-_xlfn._xlws.FILTER($AG$7:$AG$4870,$K$7:$K$4870&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4870,$K$7:$K$4870&lt;&gt;"X"),
+        <v>LTIA-5.10-VIETUR-80000-RFA-SDS-0350</v>
+      </c>
+      <c r="AH23" s="243" t="b" cm="1">
+        <f t="array" ref="AH23">$D23=_xlfn.XLOOKUP(
+AG23,
+_xlfn._xlws.FILTER($AG$7:$AG$4874,$K$7:$K$4874&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4874,$K$7:$K$4874&lt;&gt;"X"),
 "",
 0,
 -1
 )</f>
         <v>1</v>
       </c>
-      <c r="AI18" s="75" t="str">
+      <c r="AI23" s="75" t="str">
         <f t="shared" si="9"/>
         <v>YES</v>
       </c>
     </row>
-    <row r="19" spans="1:35" s="9" customFormat="1" ht="47.25">
-      <c r="A19" s="33">
+    <row r="24" spans="1:35" s="9" customFormat="1" ht="78.75">
+      <c r="A24" s="33">
         <f t="shared" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="B19" s="33" t="str">
+        <v>18</v>
+      </c>
+      <c r="B24" s="33" t="str">
         <f t="shared" si="1"/>
         <v>5.10</v>
       </c>
-      <c r="C19" s="137" t="s">
-        <v>556</v>
-      </c>
-      <c r="D19" s="25" t="s">
-        <v>565</v>
-      </c>
-      <c r="E19" s="174">
-        <f t="shared" si="2"/>
-        <v>45887</v>
-      </c>
-      <c r="F19" s="31" t="s">
-        <v>529</v>
-      </c>
-      <c r="G19" s="21" t="s">
-        <v>530</v>
-      </c>
-      <c r="H19" s="138" t="s">
+      <c r="C24" s="137" t="s">
+        <v>131</v>
+      </c>
+      <c r="D24" s="25" t="s">
+        <v>577</v>
+      </c>
+      <c r="E24" s="174">
+        <f>IF($T24=0,$S24+22,$T24+21)</f>
+        <v>45930</v>
+      </c>
+      <c r="F24" s="31" t="s">
+        <v>578</v>
+      </c>
+      <c r="G24" s="21" t="s">
+        <v>579</v>
+      </c>
+      <c r="H24" s="138" t="s">
         <v>2</v>
       </c>
-      <c r="I19" s="164">
-        <f t="shared" si="10"/>
-        <v>42</v>
-      </c>
-      <c r="J19" s="47">
+      <c r="I24" s="164">
+        <f>IF(ISBLANK($V24),_xlfn.DAYS($I$1,$T24),_xlfn.DAYS($V24,$T24))</f>
+        <v>8</v>
+      </c>
+      <c r="J24" s="47">
         <f t="shared" si="4"/>
-        <v>21</v>
-      </c>
-      <c r="K19" s="164"/>
-      <c r="L19" s="54" t="s">
-        <v>8</v>
-      </c>
-      <c r="M19" s="65" t="s">
-        <v>8</v>
-      </c>
-      <c r="N19" s="40" t="s">
-        <v>8</v>
-      </c>
-      <c r="O19" s="41" t="s">
-        <v>8</v>
-      </c>
-      <c r="P19" s="40" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q19" s="155" t="s">
+        <v>0</v>
+      </c>
+      <c r="K24" s="164"/>
+      <c r="L24" s="54" t="s">
+        <v>8</v>
+      </c>
+      <c r="M24" s="65" t="s">
+        <v>8</v>
+      </c>
+      <c r="N24" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="O24" s="41" t="s">
+        <v>8</v>
+      </c>
+      <c r="P24" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q24" s="155" t="s">
         <v>2</v>
       </c>
-      <c r="R19" s="27">
-        <v>45861</v>
-      </c>
-      <c r="S19" s="27">
-        <v>45861</v>
-      </c>
-      <c r="T19" s="187">
-        <v>45866</v>
-      </c>
-      <c r="U19" s="29">
-        <v>45628</v>
-      </c>
-      <c r="V19" s="188">
+      <c r="R24" s="27">
         <v>45908</v>
       </c>
-      <c r="W19" s="235" t="s">
+      <c r="S24" s="27">
+        <v>45908</v>
+      </c>
+      <c r="T24" s="188">
+        <v>45909</v>
+      </c>
+      <c r="U24" s="29">
+        <v>45873</v>
+      </c>
+      <c r="V24" s="188">
+        <v>45917</v>
+      </c>
+      <c r="W24" s="235" t="s">
         <v>559</v>
       </c>
-      <c r="X19" s="230">
-        <v>45954</v>
-      </c>
-      <c r="Y19" s="227">
+      <c r="X24" s="230">
+        <v>46153</v>
+      </c>
+      <c r="Y24" s="227">
         <v>45957</v>
       </c>
-      <c r="Z19" s="29">
+      <c r="Z24" s="29">
         <f t="shared" si="5"/>
         <v>45964</v>
       </c>
-      <c r="AA19" s="229">
-        <v>45908</v>
-      </c>
-      <c r="AB19" s="229" t="str">
-        <f t="shared" si="6"/>
-        <v>Timely Response</v>
-      </c>
-      <c r="AC19" s="183" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="AD19" s="92"/>
-      <c r="AG19" s="238" t="str">
+      <c r="AA24" s="229"/>
+      <c r="AB24" s="229" t="str">
+        <f t="shared" ca="1" si="6"/>
+        <v>Not submit yet</v>
+      </c>
+      <c r="AC24" s="183">
+        <f t="shared" ca="1" si="7"/>
+        <v>353</v>
+      </c>
+      <c r="AD24" s="92"/>
+      <c r="AG24" s="238" t="str">
         <f t="shared" si="8"/>
         <v>LTIA-5.10-VIETUR-80000-RFA-SDS-0140</v>
       </c>
-      <c r="AH19" s="243" t="b" cm="1">
-        <f t="array" ref="AH19">$D19=_xlfn.XLOOKUP(
-AG19,
-_xlfn._xlws.FILTER($AG$7:$AG$4870,$K$7:$K$4870&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4870,$K$7:$K$4870&lt;&gt;"X"),
+      <c r="AH24" s="243" t="b" cm="1">
+        <f t="array" ref="AH24">$D24=_xlfn.XLOOKUP(
+AG24,
+_xlfn._xlws.FILTER($AG$7:$AG$4874,$K$7:$K$4874&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4874,$K$7:$K$4874&lt;&gt;"X"),
+"",
+0,
+-1
+)</f>
+        <v>1</v>
+      </c>
+      <c r="AI24" s="75" t="str">
+        <f t="shared" si="9"/>
+        <v>YES</v>
+      </c>
+    </row>
+    <row r="25" spans="1:35" s="9" customFormat="1" ht="63">
+      <c r="A25" s="33">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="B25" s="33" t="str">
+        <f t="shared" si="1"/>
+        <v>5.10</v>
+      </c>
+      <c r="C25" s="137"/>
+      <c r="D25" s="25" t="s">
+        <v>580</v>
+      </c>
+      <c r="E25" s="174">
+        <f>IF($T25=0,$S25+22,$T25+21)</f>
+        <v>45953</v>
+      </c>
+      <c r="F25" s="31" t="s">
+        <v>546</v>
+      </c>
+      <c r="G25" s="21" t="s">
+        <v>547</v>
+      </c>
+      <c r="H25" s="138" t="s">
+        <v>2</v>
+      </c>
+      <c r="I25" s="164">
+        <f>IF(ISBLANK($V25),_xlfn.DAYS($I$1,$T25),_xlfn.DAYS($V25,$T25))</f>
+        <v>13</v>
+      </c>
+      <c r="J25" s="47">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K25" s="164"/>
+      <c r="L25" s="54" t="s">
+        <v>8</v>
+      </c>
+      <c r="M25" s="65" t="s">
+        <v>8</v>
+      </c>
+      <c r="N25" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="O25" s="41" t="s">
+        <v>8</v>
+      </c>
+      <c r="P25" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q25" s="155" t="s">
+        <v>2</v>
+      </c>
+      <c r="R25" s="27">
+        <v>45919</v>
+      </c>
+      <c r="S25" s="27">
+        <v>45919</v>
+      </c>
+      <c r="T25" s="188">
+        <v>45932</v>
+      </c>
+      <c r="U25" s="29">
+        <v>45940</v>
+      </c>
+      <c r="V25" s="188">
+        <v>45945</v>
+      </c>
+      <c r="W25" s="235" t="s">
+        <v>581</v>
+      </c>
+      <c r="X25" s="230">
+        <v>46029</v>
+      </c>
+      <c r="Y25" s="227">
+        <v>46030</v>
+      </c>
+      <c r="Z25" s="29">
+        <f t="shared" si="5"/>
+        <v>46037</v>
+      </c>
+      <c r="AA25" s="229">
+        <v>46311</v>
+      </c>
+      <c r="AB25" s="229" t="str">
+        <f t="shared" si="6"/>
+        <v>Late Resubmission</v>
+      </c>
+      <c r="AC25" s="183">
+        <f t="shared" si="7"/>
+        <v>274</v>
+      </c>
+      <c r="AD25" s="92" t="s">
+        <v>887</v>
+      </c>
+      <c r="AG25" s="238" t="str">
+        <f t="shared" si="8"/>
+        <v>LTIA-5.10-VIETUR-80000-RFA-SDS-0222</v>
+      </c>
+      <c r="AH25" s="243" t="b" cm="1">
+        <f t="array" ref="AH25">$D25=_xlfn.XLOOKUP(
+AG25,
+_xlfn._xlws.FILTER($AG$7:$AG$4874,$K$7:$K$4874&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4874,$K$7:$K$4874&lt;&gt;"X"),
 "",
 0,
 -1
 )</f>
         <v>0</v>
       </c>
-      <c r="AI19" s="75" t="str">
+      <c r="AI25" s="75" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:35" s="9" customFormat="1" ht="47.25">
-      <c r="A20" s="33">
+    <row r="26" spans="1:35" s="9" customFormat="1" ht="47.25">
+      <c r="A26" s="33">
         <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="B20" s="33" t="str">
+        <v>20</v>
+      </c>
+      <c r="B26" s="33" t="str">
         <f t="shared" si="1"/>
         <v>5.10</v>
       </c>
-      <c r="C20" s="137" t="s">
-        <v>556</v>
-      </c>
-      <c r="D20" s="25" t="s">
-        <v>566</v>
-      </c>
-      <c r="E20" s="174">
+      <c r="C26" s="137" t="s">
+        <v>195</v>
+      </c>
+      <c r="D26" s="25" t="s">
+        <v>582</v>
+      </c>
+      <c r="E26" s="174">
         <f t="shared" si="2"/>
-        <v>45887</v>
-      </c>
-      <c r="F20" s="31" t="s">
-        <v>534</v>
-      </c>
-      <c r="G20" s="21" t="s">
-        <v>535</v>
-      </c>
-      <c r="H20" s="138" t="s">
+        <v>45953</v>
+      </c>
+      <c r="F26" s="31" t="s">
+        <v>583</v>
+      </c>
+      <c r="G26" s="21" t="s">
+        <v>584</v>
+      </c>
+      <c r="H26" s="138" t="s">
         <v>2</v>
       </c>
-      <c r="I20" s="164">
+      <c r="I26" s="164">
         <f t="shared" si="10"/>
-        <v>42</v>
-      </c>
-      <c r="J20" s="47">
+        <v>13</v>
+      </c>
+      <c r="J26" s="47">
         <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K26" s="164"/>
+      <c r="L26" s="54" t="s">
+        <v>8</v>
+      </c>
+      <c r="M26" s="65" t="s">
+        <v>8</v>
+      </c>
+      <c r="N26" s="40" t="s">
+        <v>12</v>
+      </c>
+      <c r="O26" s="41" t="s">
+        <v>8</v>
+      </c>
+      <c r="P26" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q26" s="155" t="s">
+        <v>2</v>
+      </c>
+      <c r="R26" s="27">
+        <v>45930</v>
+      </c>
+      <c r="S26" s="27">
+        <v>45930</v>
+      </c>
+      <c r="T26" s="188">
+        <v>45932</v>
+      </c>
+      <c r="U26" s="29">
+        <v>45940</v>
+      </c>
+      <c r="V26" s="188">
+        <v>45945</v>
+      </c>
+      <c r="W26" s="235" t="s">
+        <v>581</v>
+      </c>
+      <c r="X26" s="230">
+        <v>45978</v>
+      </c>
+      <c r="Y26" s="227">
+        <v>45979</v>
+      </c>
+      <c r="Z26" s="29">
+        <f t="shared" si="5"/>
+        <v>45986</v>
+      </c>
+      <c r="AA26" s="229"/>
+      <c r="AB26" s="229" t="str">
+        <f t="shared" ca="1" si="6"/>
+        <v>Not submit yet</v>
+      </c>
+      <c r="AC26" s="183">
+        <f t="shared" ca="1" si="7"/>
+        <v>331</v>
+      </c>
+      <c r="AD26" s="92"/>
+      <c r="AG26" s="238" t="str">
+        <f t="shared" si="8"/>
+        <v>LTIA-5.10-VIETUR-80000-RFA-SDS-0371</v>
+      </c>
+      <c r="AH26" s="243" t="b" cm="1">
+        <f t="array" ref="AH26">$D26=_xlfn.XLOOKUP(
+AG26,
+_xlfn._xlws.FILTER($AG$7:$AG$4874,$K$7:$K$4874&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4874,$K$7:$K$4874&lt;&gt;"X"),
+"",
+0,
+-1
+)</f>
+        <v>1</v>
+      </c>
+      <c r="AI26" s="75" t="str">
+        <f t="shared" si="9"/>
+        <v>YES</v>
+      </c>
+    </row>
+    <row r="27" spans="1:35" s="9" customFormat="1" ht="47.25">
+      <c r="A27" s="33">
+        <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="K20" s="164"/>
-      <c r="L20" s="54" t="s">
-        <v>8</v>
-      </c>
-      <c r="M20" s="65" t="s">
-        <v>8</v>
-      </c>
-      <c r="N20" s="40" t="s">
-        <v>8</v>
-      </c>
-      <c r="O20" s="41" t="s">
-        <v>8</v>
-      </c>
-      <c r="P20" s="40" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q20" s="155" t="s">
+      <c r="B27" s="33" t="str">
+        <f t="shared" si="1"/>
+        <v>5.10</v>
+      </c>
+      <c r="C27" s="137" t="s">
+        <v>131</v>
+      </c>
+      <c r="D27" s="25" t="s">
+        <v>585</v>
+      </c>
+      <c r="E27" s="174">
+        <f t="shared" si="2"/>
+        <v>45982</v>
+      </c>
+      <c r="F27" s="31" t="s">
+        <v>537</v>
+      </c>
+      <c r="G27" s="21" t="s">
+        <v>538</v>
+      </c>
+      <c r="H27" s="138" t="s">
         <v>2</v>
       </c>
-      <c r="R20" s="27">
-        <v>45861</v>
-      </c>
-      <c r="S20" s="27">
-        <v>45861</v>
-      </c>
-      <c r="T20" s="187">
-        <v>45866</v>
-      </c>
-      <c r="U20" s="29">
-        <v>45646</v>
-      </c>
-      <c r="V20" s="188">
-        <v>45908</v>
-      </c>
-      <c r="W20" s="235" t="s">
-        <v>559</v>
-      </c>
-      <c r="X20" s="230">
-        <v>45954</v>
-      </c>
-      <c r="Y20" s="227">
-        <v>45957</v>
-      </c>
-      <c r="Z20" s="29">
+      <c r="I27" s="164">
+        <f t="shared" si="10"/>
+        <v>19</v>
+      </c>
+      <c r="J27" s="47">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K27" s="164"/>
+      <c r="L27" s="54" t="s">
+        <v>8</v>
+      </c>
+      <c r="M27" s="65" t="s">
+        <v>8</v>
+      </c>
+      <c r="N27" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="O27" s="41" t="s">
+        <v>8</v>
+      </c>
+      <c r="P27" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q27" s="155" t="s">
+        <v>2</v>
+      </c>
+      <c r="R27" s="27">
+        <v>45959</v>
+      </c>
+      <c r="S27" s="27">
+        <v>45959</v>
+      </c>
+      <c r="T27" s="188">
+        <v>45961</v>
+      </c>
+      <c r="U27" s="29">
+        <v>45945</v>
+      </c>
+      <c r="V27" s="188">
+        <v>45980</v>
+      </c>
+      <c r="W27" s="235" t="s">
+        <v>190</v>
+      </c>
+      <c r="X27" s="230">
+        <v>45995</v>
+      </c>
+      <c r="Y27" s="227">
+        <v>45999</v>
+      </c>
+      <c r="Z27" s="29">
         <f t="shared" si="5"/>
-        <v>45964</v>
-      </c>
-      <c r="AA20" s="229">
-        <v>45972</v>
-      </c>
-      <c r="AB20" s="229" t="str">
+        <v>46006</v>
+      </c>
+      <c r="AA27" s="229">
+        <v>46316</v>
+      </c>
+      <c r="AB27" s="229" t="str">
         <f t="shared" si="6"/>
         <v>Late Resubmission</v>
       </c>
-      <c r="AC20" s="183">
+      <c r="AC27" s="183">
         <f t="shared" si="7"/>
-        <v>8</v>
-      </c>
-      <c r="AD20" s="92"/>
-      <c r="AG20" s="238" t="str">
+        <v>310</v>
+      </c>
+      <c r="AD27" s="92"/>
+      <c r="AG27" s="238" t="str">
         <f t="shared" si="8"/>
-        <v>LTIA-5.10-VIETUR-80000-RFA-SDS-0160</v>
-      </c>
-      <c r="AH20" s="243" t="b" cm="1">
-        <f t="array" ref="AH20">$D20=_xlfn.XLOOKUP(
-AG20,
-_xlfn._xlws.FILTER($AG$7:$AG$4870,$K$7:$K$4870&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4870,$K$7:$K$4870&lt;&gt;"X"),
+        <v>LTIA-5.10-VIETUR-80000-RFA-SDS-0197</v>
+      </c>
+      <c r="AH27" s="243" t="b" cm="1">
+        <f t="array" ref="AH27">$D27=_xlfn.XLOOKUP(
+AG27,
+_xlfn._xlws.FILTER($AG$7:$AG$4874,$K$7:$K$4874&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4874,$K$7:$K$4874&lt;&gt;"X"),
 "",
 0,
 -1
 )</f>
         <v>0</v>
       </c>
-      <c r="AI20" s="75" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="21" spans="1:35" s="9" customFormat="1" ht="47.25">
-      <c r="A21" s="33">
-        <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="B21" s="33" t="str">
-        <f t="shared" si="1"/>
-        <v>5.10</v>
-      </c>
-      <c r="C21" s="137" t="s">
-        <v>556</v>
-      </c>
-      <c r="D21" s="25" t="s">
-        <v>567</v>
-      </c>
-      <c r="E21" s="174">
-        <f t="shared" si="2"/>
-        <v>45887</v>
-      </c>
-      <c r="F21" s="31" t="s">
-        <v>537</v>
-      </c>
-      <c r="G21" s="21" t="s">
-        <v>538</v>
-      </c>
-      <c r="H21" s="138" t="s">
-        <v>2</v>
-      </c>
-      <c r="I21" s="164">
-        <f t="shared" si="10"/>
-        <v>42</v>
-      </c>
-      <c r="J21" s="47">
-        <f t="shared" si="4"/>
-        <v>21</v>
-      </c>
-      <c r="K21" s="164"/>
-      <c r="L21" s="54" t="s">
-        <v>8</v>
-      </c>
-      <c r="M21" s="65" t="s">
-        <v>8</v>
-      </c>
-      <c r="N21" s="40" t="s">
-        <v>8</v>
-      </c>
-      <c r="O21" s="41" t="s">
-        <v>8</v>
-      </c>
-      <c r="P21" s="40" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q21" s="155" t="s">
-        <v>2</v>
-      </c>
-      <c r="R21" s="27">
-        <v>45861</v>
-      </c>
-      <c r="S21" s="27">
-        <v>45861</v>
-      </c>
-      <c r="T21" s="188">
-        <v>45866</v>
-      </c>
-      <c r="U21" s="29">
-        <v>45648</v>
-      </c>
-      <c r="V21" s="188">
-        <v>45908</v>
-      </c>
-      <c r="W21" s="235" t="s">
-        <v>559</v>
-      </c>
-      <c r="X21" s="230">
-        <v>45954</v>
-      </c>
-      <c r="Y21" s="227">
-        <v>45957</v>
-      </c>
-      <c r="Z21" s="29">
-        <f t="shared" si="5"/>
-        <v>45964</v>
-      </c>
-      <c r="AA21" s="229">
-        <v>45959</v>
-      </c>
-      <c r="AB21" s="229" t="str">
-        <f t="shared" si="6"/>
-        <v>Timely Response</v>
-      </c>
-      <c r="AC21" s="183" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="AD21" s="332" t="s">
-        <v>568</v>
-      </c>
-      <c r="AG21" s="238" t="str">
-        <f t="shared" si="8"/>
-        <v>LTIA-5.10-VIETUR-80000-RFA-SDS-0197</v>
-      </c>
-      <c r="AH21" s="243" t="b" cm="1">
-        <f t="array" ref="AH21">$D21=_xlfn.XLOOKUP(
-AG21,
-_xlfn._xlws.FILTER($AG$7:$AG$4870,$K$7:$K$4870&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4870,$K$7:$K$4870&lt;&gt;"X"),
-"",
-0,
--1
-)</f>
-        <v>0</v>
-      </c>
-      <c r="AI21" s="75" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="22" spans="1:35" s="9" customFormat="1" ht="63">
-      <c r="A22" s="33">
-        <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="B22" s="33" t="str">
-        <f t="shared" si="1"/>
-        <v>5.10</v>
-      </c>
-      <c r="C22" s="137" t="s">
-        <v>571</v>
-      </c>
-      <c r="D22" s="25" t="s">
-        <v>569</v>
-      </c>
-      <c r="E22" s="174">
-        <f t="shared" si="2"/>
-        <v>46009</v>
-      </c>
-      <c r="F22" s="31" t="s">
-        <v>552</v>
-      </c>
-      <c r="G22" s="21" t="s">
-        <v>570</v>
-      </c>
-      <c r="H22" s="138" t="s">
-        <v>3</v>
-      </c>
-      <c r="I22" s="164">
-        <f t="shared" si="10"/>
-        <v>1</v>
-      </c>
-      <c r="J22" s="47">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="K22" s="164"/>
-      <c r="L22" s="54" t="s">
-        <v>8</v>
-      </c>
-      <c r="M22" s="65" t="s">
-        <v>8</v>
-      </c>
-      <c r="N22" s="40" t="s">
-        <v>8</v>
-      </c>
-      <c r="O22" s="41" t="s">
-        <v>8</v>
-      </c>
-      <c r="P22" s="40" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q22" s="155" t="s">
-        <v>3</v>
-      </c>
-      <c r="R22" s="27">
-        <v>45861</v>
-      </c>
-      <c r="S22" s="27">
-        <v>45861</v>
-      </c>
-      <c r="T22" s="188">
-        <v>45988</v>
-      </c>
-      <c r="U22" s="29">
-        <v>45880</v>
-      </c>
-      <c r="V22" s="188">
-        <v>45989</v>
-      </c>
-      <c r="W22" s="235" t="s">
-        <v>572</v>
-      </c>
-      <c r="X22" s="230">
-        <v>45994</v>
-      </c>
-      <c r="Y22" s="227">
-        <v>45995</v>
-      </c>
-      <c r="Z22" s="29" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AA22" s="229"/>
-      <c r="AB22" s="229" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="AC22" s="183" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="AD22" s="92" t="s">
-        <v>886</v>
-      </c>
-      <c r="AG22" s="238" t="str">
-        <f t="shared" si="8"/>
-        <v>LTIA-5.10-VIETUR-80000-RFA-SDS-0310</v>
-      </c>
-      <c r="AH22" s="243" t="b" cm="1">
-        <f t="array" ref="AH22">$D22=_xlfn.XLOOKUP(
-AG22,
-_xlfn._xlws.FILTER($AG$7:$AG$4870,$K$7:$K$4870&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4870,$K$7:$K$4870&lt;&gt;"X"),
-"",
-0,
--1
-)</f>
-        <v>1</v>
-      </c>
-      <c r="AI22" s="75" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="23" spans="1:35" s="9" customFormat="1" ht="47.25">
-      <c r="A23" s="33">
-        <f t="shared" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="B23" s="33" t="str">
-        <f t="shared" si="1"/>
-        <v>5.10</v>
-      </c>
-      <c r="C23" s="164" t="s">
-        <v>576</v>
-      </c>
-      <c r="D23" s="25" t="s">
-        <v>573</v>
-      </c>
-      <c r="E23" s="174">
-        <f>IF($T23=0,$S23+22,$T23+21)</f>
-        <v>45902</v>
-      </c>
-      <c r="F23" s="31" t="s">
-        <v>574</v>
-      </c>
-      <c r="G23" s="21" t="s">
-        <v>575</v>
-      </c>
-      <c r="H23" s="138" t="s">
-        <v>2</v>
-      </c>
-      <c r="I23" s="164">
-        <f>IF(ISBLANK($V23),_xlfn.DAYS($I$1,$T23),_xlfn.DAYS($V23,$T23))</f>
-        <v>27</v>
-      </c>
-      <c r="J23" s="47">
-        <f t="shared" si="4"/>
-        <v>6</v>
-      </c>
-      <c r="K23" s="164"/>
-      <c r="L23" s="54" t="s">
-        <v>8</v>
-      </c>
-      <c r="M23" s="65" t="s">
-        <v>8</v>
-      </c>
-      <c r="N23" s="40" t="s">
-        <v>8</v>
-      </c>
-      <c r="O23" s="41" t="s">
-        <v>8</v>
-      </c>
-      <c r="P23" s="40" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q23" s="155" t="s">
-        <v>2</v>
-      </c>
-      <c r="R23" s="27">
-        <v>45880</v>
-      </c>
-      <c r="S23" s="27">
-        <v>45880</v>
-      </c>
-      <c r="T23" s="188">
-        <v>45881</v>
-      </c>
-      <c r="U23" s="29">
-        <v>45891</v>
-      </c>
-      <c r="V23" s="188">
-        <v>45908</v>
-      </c>
-      <c r="W23" s="235" t="s">
-        <v>559</v>
-      </c>
-      <c r="X23" s="230">
-        <v>45954</v>
-      </c>
-      <c r="Y23" s="227">
-        <v>45957</v>
-      </c>
-      <c r="Z23" s="29">
-        <f t="shared" si="5"/>
-        <v>45964</v>
-      </c>
-      <c r="AA23" s="229"/>
-      <c r="AB23" s="229" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v>Not submit yet</v>
-      </c>
-      <c r="AC23" s="183">
-        <f t="shared" ca="1" si="7"/>
-        <v>351</v>
-      </c>
-      <c r="AD23" s="92"/>
-      <c r="AG23" s="238" t="str">
-        <f t="shared" si="8"/>
-        <v>LTIA-5.10-VIETUR-80000-RFA-SDS-0350</v>
-      </c>
-      <c r="AH23" s="243" t="b" cm="1">
-        <f t="array" ref="AH23">$D23=_xlfn.XLOOKUP(
-AG23,
-_xlfn._xlws.FILTER($AG$7:$AG$4870,$K$7:$K$4870&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4870,$K$7:$K$4870&lt;&gt;"X"),
-"",
-0,
--1
-)</f>
-        <v>1</v>
-      </c>
-      <c r="AI23" s="75" t="str">
-        <f t="shared" si="9"/>
-        <v>YES</v>
-      </c>
-    </row>
-    <row r="24" spans="1:35" s="9" customFormat="1" ht="78.75">
-      <c r="A24" s="33">
-        <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="B24" s="33" t="str">
-        <f t="shared" si="1"/>
-        <v>5.10</v>
-      </c>
-      <c r="C24" s="137" t="s">
-        <v>131</v>
-      </c>
-      <c r="D24" s="25" t="s">
-        <v>577</v>
-      </c>
-      <c r="E24" s="174">
-        <f>IF($T24=0,$S24+22,$T24+21)</f>
-        <v>45930</v>
-      </c>
-      <c r="F24" s="31" t="s">
-        <v>578</v>
-      </c>
-      <c r="G24" s="21" t="s">
-        <v>579</v>
-      </c>
-      <c r="H24" s="138" t="s">
-        <v>2</v>
-      </c>
-      <c r="I24" s="164">
-        <f>IF(ISBLANK($V24),_xlfn.DAYS($I$1,$T24),_xlfn.DAYS($V24,$T24))</f>
-        <v>8</v>
-      </c>
-      <c r="J24" s="47">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="K24" s="164"/>
-      <c r="L24" s="54" t="s">
-        <v>8</v>
-      </c>
-      <c r="M24" s="65" t="s">
-        <v>8</v>
-      </c>
-      <c r="N24" s="40" t="s">
-        <v>8</v>
-      </c>
-      <c r="O24" s="41" t="s">
-        <v>8</v>
-      </c>
-      <c r="P24" s="40" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q24" s="155" t="s">
-        <v>2</v>
-      </c>
-      <c r="R24" s="27">
-        <v>45908</v>
-      </c>
-      <c r="S24" s="27">
-        <v>45908</v>
-      </c>
-      <c r="T24" s="188">
-        <v>45909</v>
-      </c>
-      <c r="U24" s="29">
-        <v>45873</v>
-      </c>
-      <c r="V24" s="188">
-        <v>45917</v>
-      </c>
-      <c r="W24" s="235" t="s">
-        <v>559</v>
-      </c>
-      <c r="X24" s="230">
-        <v>46153</v>
-      </c>
-      <c r="Y24" s="227">
-        <v>45957</v>
-      </c>
-      <c r="Z24" s="29">
-        <f t="shared" si="5"/>
-        <v>45964</v>
-      </c>
-      <c r="AA24" s="229"/>
-      <c r="AB24" s="229" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v>Not submit yet</v>
-      </c>
-      <c r="AC24" s="183">
-        <f t="shared" ca="1" si="7"/>
-        <v>351</v>
-      </c>
-      <c r="AD24" s="92"/>
-      <c r="AG24" s="238" t="str">
-        <f t="shared" si="8"/>
-        <v>LTIA-5.10-VIETUR-80000-RFA-SDS-0140</v>
-      </c>
-      <c r="AH24" s="243" t="b" cm="1">
-        <f t="array" ref="AH24">$D24=_xlfn.XLOOKUP(
-AG24,
-_xlfn._xlws.FILTER($AG$7:$AG$4870,$K$7:$K$4870&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4870,$K$7:$K$4870&lt;&gt;"X"),
-"",
-0,
--1
-)</f>
-        <v>1</v>
-      </c>
-      <c r="AI24" s="75" t="str">
-        <f t="shared" si="9"/>
-        <v>YES</v>
-      </c>
-    </row>
-    <row r="25" spans="1:35" s="9" customFormat="1" ht="63">
-      <c r="A25" s="33">
-        <f t="shared" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="B25" s="33" t="str">
-        <f t="shared" si="1"/>
-        <v>5.10</v>
-      </c>
-      <c r="C25" s="137"/>
-      <c r="D25" s="25" t="s">
-        <v>580</v>
-      </c>
-      <c r="E25" s="174">
-        <f>IF($T25=0,$S25+22,$T25+21)</f>
-        <v>45953</v>
-      </c>
-      <c r="F25" s="31" t="s">
-        <v>546</v>
-      </c>
-      <c r="G25" s="21" t="s">
-        <v>547</v>
-      </c>
-      <c r="H25" s="138" t="s">
-        <v>2</v>
-      </c>
-      <c r="I25" s="164">
-        <f>IF(ISBLANK($V25),_xlfn.DAYS($I$1,$T25),_xlfn.DAYS($V25,$T25))</f>
-        <v>13</v>
-      </c>
-      <c r="J25" s="47">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="K25" s="164"/>
-      <c r="L25" s="54" t="s">
-        <v>8</v>
-      </c>
-      <c r="M25" s="65" t="s">
-        <v>8</v>
-      </c>
-      <c r="N25" s="40" t="s">
-        <v>8</v>
-      </c>
-      <c r="O25" s="41" t="s">
-        <v>8</v>
-      </c>
-      <c r="P25" s="40" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q25" s="155" t="s">
-        <v>2</v>
-      </c>
-      <c r="R25" s="27">
-        <v>45919</v>
-      </c>
-      <c r="S25" s="27">
-        <v>45919</v>
-      </c>
-      <c r="T25" s="188">
-        <v>45932</v>
-      </c>
-      <c r="U25" s="29">
-        <v>45940</v>
-      </c>
-      <c r="V25" s="188">
-        <v>45945</v>
-      </c>
-      <c r="W25" s="235" t="s">
-        <v>581</v>
-      </c>
-      <c r="X25" s="230">
-        <v>46029</v>
-      </c>
-      <c r="Y25" s="227">
-        <v>46030</v>
-      </c>
-      <c r="Z25" s="29">
-        <f t="shared" si="5"/>
-        <v>46037</v>
-      </c>
-      <c r="AA25" s="229">
-        <v>46311</v>
-      </c>
-      <c r="AB25" s="229" t="str">
-        <f t="shared" si="6"/>
-        <v>Late Resubmission</v>
-      </c>
-      <c r="AC25" s="183">
-        <f t="shared" si="7"/>
-        <v>274</v>
-      </c>
-      <c r="AD25" s="92" t="s">
-        <v>887</v>
-      </c>
-      <c r="AG25" s="238" t="str">
-        <f t="shared" si="8"/>
-        <v>LTIA-5.10-VIETUR-80000-RFA-SDS-0222</v>
-      </c>
-      <c r="AH25" s="243" t="b" cm="1">
-        <f t="array" ref="AH25">$D25=_xlfn.XLOOKUP(
-AG25,
-_xlfn._xlws.FILTER($AG$7:$AG$4870,$K$7:$K$4870&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4870,$K$7:$K$4870&lt;&gt;"X"),
-"",
-0,
--1
-)</f>
-        <v>0</v>
-      </c>
-      <c r="AI25" s="75" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="26" spans="1:35" s="9" customFormat="1" ht="47.25">
-      <c r="A26" s="33">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="B26" s="33" t="str">
-        <f t="shared" si="1"/>
-        <v>5.10</v>
-      </c>
-      <c r="C26" s="137" t="s">
-        <v>195</v>
-      </c>
-      <c r="D26" s="25" t="s">
-        <v>582</v>
-      </c>
-      <c r="E26" s="174">
-        <f t="shared" si="2"/>
-        <v>45953</v>
-      </c>
-      <c r="F26" s="31" t="s">
-        <v>583</v>
-      </c>
-      <c r="G26" s="21" t="s">
-        <v>584</v>
-      </c>
-      <c r="H26" s="138" t="s">
-        <v>2</v>
-      </c>
-      <c r="I26" s="164">
-        <f t="shared" si="10"/>
-        <v>13</v>
-      </c>
-      <c r="J26" s="47">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="K26" s="164"/>
-      <c r="L26" s="54" t="s">
-        <v>8</v>
-      </c>
-      <c r="M26" s="65" t="s">
-        <v>8</v>
-      </c>
-      <c r="N26" s="40" t="s">
-        <v>12</v>
-      </c>
-      <c r="O26" s="41" t="s">
-        <v>8</v>
-      </c>
-      <c r="P26" s="40" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q26" s="155" t="s">
-        <v>2</v>
-      </c>
-      <c r="R26" s="27">
-        <v>45930</v>
-      </c>
-      <c r="S26" s="27">
-        <v>45930</v>
-      </c>
-      <c r="T26" s="188">
-        <v>45932</v>
-      </c>
-      <c r="U26" s="29">
-        <v>45940</v>
-      </c>
-      <c r="V26" s="188">
-        <v>45945</v>
-      </c>
-      <c r="W26" s="235" t="s">
-        <v>581</v>
-      </c>
-      <c r="X26" s="230">
-        <v>45978</v>
-      </c>
-      <c r="Y26" s="227">
-        <v>45979</v>
-      </c>
-      <c r="Z26" s="29">
-        <f t="shared" si="5"/>
-        <v>45986</v>
-      </c>
-      <c r="AA26" s="229"/>
-      <c r="AB26" s="229" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v>Not submit yet</v>
-      </c>
-      <c r="AC26" s="183">
-        <f t="shared" ca="1" si="7"/>
-        <v>329</v>
-      </c>
-      <c r="AD26" s="92"/>
-      <c r="AG26" s="238" t="str">
-        <f t="shared" si="8"/>
-        <v>LTIA-5.10-VIETUR-80000-RFA-SDS-0371</v>
-      </c>
-      <c r="AH26" s="243" t="b" cm="1">
-        <f t="array" ref="AH26">$D26=_xlfn.XLOOKUP(
-AG26,
-_xlfn._xlws.FILTER($AG$7:$AG$4870,$K$7:$K$4870&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4870,$K$7:$K$4870&lt;&gt;"X"),
-"",
-0,
--1
-)</f>
-        <v>1</v>
-      </c>
-      <c r="AI26" s="75" t="str">
-        <f t="shared" si="9"/>
-        <v>YES</v>
-      </c>
-    </row>
-    <row r="27" spans="1:35" s="9" customFormat="1" ht="47.25">
-      <c r="A27" s="33">
-        <f t="shared" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="B27" s="33" t="str">
-        <f t="shared" si="1"/>
-        <v>5.10</v>
-      </c>
-      <c r="C27" s="137" t="s">
-        <v>131</v>
-      </c>
-      <c r="D27" s="25" t="s">
-        <v>585</v>
-      </c>
-      <c r="E27" s="174">
-        <f t="shared" si="2"/>
-        <v>45982</v>
-      </c>
-      <c r="F27" s="31" t="s">
-        <v>537</v>
-      </c>
-      <c r="G27" s="21" t="s">
-        <v>538</v>
-      </c>
-      <c r="H27" s="138" t="s">
-        <v>2</v>
-      </c>
-      <c r="I27" s="164">
-        <f t="shared" si="10"/>
-        <v>19</v>
-      </c>
-      <c r="J27" s="47">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="K27" s="164"/>
-      <c r="L27" s="54" t="s">
-        <v>8</v>
-      </c>
-      <c r="M27" s="65" t="s">
-        <v>8</v>
-      </c>
-      <c r="N27" s="40" t="s">
-        <v>8</v>
-      </c>
-      <c r="O27" s="41" t="s">
-        <v>8</v>
-      </c>
-      <c r="P27" s="40" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q27" s="155" t="s">
-        <v>2</v>
-      </c>
-      <c r="R27" s="27">
-        <v>45959</v>
-      </c>
-      <c r="S27" s="27">
-        <v>45959</v>
-      </c>
-      <c r="T27" s="188">
-        <v>45961</v>
-      </c>
-      <c r="U27" s="29">
-        <v>45945</v>
-      </c>
-      <c r="V27" s="188">
-        <v>45980</v>
-      </c>
-      <c r="W27" s="235" t="s">
-        <v>190</v>
-      </c>
-      <c r="X27" s="230">
-        <v>45995</v>
-      </c>
-      <c r="Y27" s="227">
-        <v>45999</v>
-      </c>
-      <c r="Z27" s="29">
-        <f t="shared" si="5"/>
-        <v>46006</v>
-      </c>
-      <c r="AA27" s="229"/>
-      <c r="AB27" s="229" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v>Not submit yet</v>
-      </c>
-      <c r="AC27" s="183">
-        <f t="shared" ca="1" si="7"/>
-        <v>309</v>
-      </c>
-      <c r="AD27" s="92"/>
-      <c r="AG27" s="238" t="str">
-        <f t="shared" si="8"/>
-        <v>LTIA-5.10-VIETUR-80000-RFA-SDS-0197</v>
-      </c>
-      <c r="AH27" s="243" t="b" cm="1">
-        <f t="array" ref="AH27">$D27=_xlfn.XLOOKUP(
-AG27,
-_xlfn._xlws.FILTER($AG$7:$AG$4870,$K$7:$K$4870&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4870,$K$7:$K$4870&lt;&gt;"X"),
-"",
-0,
--1
-)</f>
-        <v>1</v>
-      </c>
       <c r="AI27" s="75" t="str">
         <f t="shared" si="9"/>
-        <v>YES</v>
+        <v/>
       </c>
     </row>
     <row r="28" spans="1:35" s="9" customFormat="1" ht="63">
@@ -27853,8 +27903,8 @@
       <c r="AH28" s="243" t="b" cm="1">
         <f t="array" ref="AH28">$D28=_xlfn.XLOOKUP(
 AG28,
-_xlfn._xlws.FILTER($AG$7:$AG$4870,$K$7:$K$4870&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4870,$K$7:$K$4870&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4874,$K$7:$K$4874&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4874,$K$7:$K$4874&lt;&gt;"X"),
 "",
 0,
 -1
@@ -27944,8 +27994,8 @@
       <c r="AH29" s="243" t="b" cm="1">
         <f t="array" ref="AH29">$D29=_xlfn.XLOOKUP(
 AG29,
-_xlfn._xlws.FILTER($AG$7:$AG$4870,$K$7:$K$4870&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4870,$K$7:$K$4870&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4874,$K$7:$K$4874&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4874,$K$7:$K$4874&lt;&gt;"X"),
 "",
 0,
 -1
@@ -28047,7 +28097,7 @@
       </c>
       <c r="AC30" s="183">
         <f t="shared" ca="1" si="7"/>
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AD30" s="92" t="s">
         <v>593</v>
@@ -28059,8 +28109,8 @@
       <c r="AH30" s="243" t="b" cm="1">
         <f t="array" ref="AH30">$D30=_xlfn.XLOOKUP(
 AG30,
-_xlfn._xlws.FILTER($AG$7:$AG$4870,$K$7:$K$4870&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4870,$K$7:$K$4870&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4874,$K$7:$K$4874&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4874,$K$7:$K$4874&lt;&gt;"X"),
 "",
 0,
 -1
@@ -28102,11 +28152,11 @@
       </c>
       <c r="I31" s="164">
         <f ca="1">IF(ISBLANK($V31),_xlfn.DAYS($I$1,$T31),_xlfn.DAYS($V31,$T31))</f>
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="J31" s="47">
         <f t="shared" ca="1" si="4"/>
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="K31" s="164"/>
       <c r="L31" s="54" t="s">
@@ -28156,8 +28206,8 @@
       <c r="AH31" s="243" t="b" cm="1">
         <f t="array" ref="AH31">$D31=_xlfn.XLOOKUP(
 AG31,
-_xlfn._xlws.FILTER($AG$7:$AG$4870,$K$7:$K$4870&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4870,$K$7:$K$4870&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4874,$K$7:$K$4874&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4874,$K$7:$K$4874&lt;&gt;"X"),
 "",
 0,
 -1
@@ -28273,8 +28323,8 @@
       <c r="AH32" s="243" t="b" cm="1">
         <f t="array" ref="AH32">$D32=_xlfn.XLOOKUP(
 AG32,
-_xlfn._xlws.FILTER($AG$7:$AG$4870,$K$7:$K$4870&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4870,$K$7:$K$4870&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4874,$K$7:$K$4874&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4874,$K$7:$K$4874&lt;&gt;"X"),
 "",
 0,
 -1
@@ -28378,8 +28428,8 @@
       <c r="AH33" s="243" t="b" cm="1">
         <f t="array" ref="AH33">$D33=_xlfn.XLOOKUP(
 AG33,
-_xlfn._xlws.FILTER($AG$7:$AG$4870,$K$7:$K$4870&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4870,$K$7:$K$4870&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4874,$K$7:$K$4874&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4874,$K$7:$K$4874&lt;&gt;"X"),
 "",
 0,
 -1
@@ -28464,8 +28514,8 @@
       <c r="AH34" s="243" t="b" cm="1">
         <f t="array" ref="AH34">$D34=_xlfn.XLOOKUP(
 AG34,
-_xlfn._xlws.FILTER($AG$7:$AG$4870,$K$7:$K$4870&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4870,$K$7:$K$4870&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4874,$K$7:$K$4874&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4874,$K$7:$K$4874&lt;&gt;"X"),
 "",
 0,
 -1
@@ -28505,7 +28555,7 @@
       <c r="H35" s="138"/>
       <c r="I35" s="164">
         <f t="shared" ca="1" si="10"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J35" s="47">
         <f t="shared" ca="1" si="4"/>
@@ -28557,8 +28607,8 @@
       <c r="AH35" s="243" t="b" cm="1">
         <f t="array" ref="AH35">$D35=_xlfn.XLOOKUP(
 AG35,
-_xlfn._xlws.FILTER($AG$7:$AG$4870,$K$7:$K$4870&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4870,$K$7:$K$4870&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4874,$K$7:$K$4874&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4874,$K$7:$K$4874&lt;&gt;"X"),
 "",
 0,
 -1
@@ -28660,8 +28710,8 @@
       <c r="AH36" s="243" t="b" cm="1">
         <f t="array" ref="AH36">$D36=_xlfn.XLOOKUP(
 AG36,
-_xlfn._xlws.FILTER($AG$7:$AG$4870,$K$7:$K$4870&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4870,$K$7:$K$4870&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4874,$K$7:$K$4874&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4874,$K$7:$K$4874&lt;&gt;"X"),
 "",
 0,
 -1
@@ -28701,11 +28751,11 @@
       </c>
       <c r="I37" s="164">
         <f t="shared" ca="1" si="10"/>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J37" s="47">
         <f t="shared" ca="1" si="4"/>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K37" s="164"/>
       <c r="L37" s="54" t="s">
@@ -28755,8 +28805,8 @@
       <c r="AH37" s="243" t="b" cm="1">
         <f t="array" ref="AH37">$D37=_xlfn.XLOOKUP(
 AG37,
-_xlfn._xlws.FILTER($AG$7:$AG$4870,$K$7:$K$4870&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4870,$K$7:$K$4870&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4874,$K$7:$K$4874&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4874,$K$7:$K$4874&lt;&gt;"X"),
 "",
 0,
 -1
@@ -28858,8 +28908,8 @@
       <c r="AH38" s="243" t="b" cm="1">
         <f t="array" ref="AH38">$D38=_xlfn.XLOOKUP(
 AG38,
-_xlfn._xlws.FILTER($AG$7:$AG$4870,$K$7:$K$4870&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4870,$K$7:$K$4870&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4874,$K$7:$K$4874&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4874,$K$7:$K$4874&lt;&gt;"X"),
 "",
 0,
 -1
@@ -28899,7 +28949,7 @@
       <c r="H39" s="138"/>
       <c r="I39" s="164">
         <f t="shared" ca="1" si="10"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J39" s="47">
         <f t="shared" ca="1" si="4"/>
@@ -28951,8 +29001,8 @@
       <c r="AH39" s="243" t="b" cm="1">
         <f t="array" ref="AH39">$D39=_xlfn.XLOOKUP(
 AG39,
-_xlfn._xlws.FILTER($AG$7:$AG$4870,$K$7:$K$4870&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4870,$K$7:$K$4870&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4874,$K$7:$K$4874&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4874,$K$7:$K$4874&lt;&gt;"X"),
 "",
 0,
 -1
@@ -28990,7 +29040,7 @@
       <c r="H40" s="138"/>
       <c r="I40" s="164">
         <f t="shared" ca="1" si="10"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J40" s="47">
         <f t="shared" ca="1" si="4"/>
@@ -29040,8 +29090,8 @@
       <c r="AH40" s="243" t="b" cm="1">
         <f t="array" ref="AH40">$D40=_xlfn.XLOOKUP(
 AG40,
-_xlfn._xlws.FILTER($AG$7:$AG$4870,$K$7:$K$4870&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4870,$K$7:$K$4870&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4874,$K$7:$K$4874&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4874,$K$7:$K$4874&lt;&gt;"X"),
 "",
 0,
 -1
@@ -29079,7 +29129,7 @@
       <c r="H41" s="138"/>
       <c r="I41" s="164">
         <f t="shared" ca="1" si="10"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J41" s="47">
         <f t="shared" ca="1" si="4"/>
@@ -29129,8 +29179,8 @@
       <c r="AH41" s="243" t="b" cm="1">
         <f t="array" ref="AH41">$D41=_xlfn.XLOOKUP(
 AG41,
-_xlfn._xlws.FILTER($AG$7:$AG$4870,$K$7:$K$4870&lt;&gt;"X"),
-_xlfn._xlws.FILTER($D$7:$D$4870,$K$7:$K$4870&lt;&gt;"X"),
+_xlfn._xlws.FILTER($AG$7:$AG$4874,$K$7:$K$4874&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4874,$K$7:$K$4874&lt;&gt;"X"),
 "",
 0,
 -1
@@ -29142,30 +29192,59 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="1:35" s="9" customFormat="1">
-      <c r="A42" s="23"/>
-      <c r="B42" s="33"/>
-      <c r="C42" s="137"/>
-      <c r="D42" s="25"/>
-      <c r="E42" s="174"/>
-      <c r="F42" s="31"/>
-      <c r="G42" s="21"/>
+    <row r="42" spans="1:35" s="9" customFormat="1" ht="47.25">
+      <c r="A42" s="33">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="B42" s="33" t="str">
+        <f t="shared" ref="B42" si="25">MID(D42, FIND("-", D42) + 1, 4)</f>
+        <v>5.10</v>
+      </c>
+      <c r="C42" s="164"/>
+      <c r="D42" s="25" t="s">
+        <v>1101</v>
+      </c>
+      <c r="E42" s="174">
+        <f t="shared" si="2"/>
+        <v>46338</v>
+      </c>
+      <c r="F42" s="31" t="s">
+        <v>1102</v>
+      </c>
+      <c r="G42" s="21" t="s">
+        <v>538</v>
+      </c>
       <c r="H42" s="138"/>
-      <c r="I42" s="177"/>
-      <c r="J42" s="47"/>
+      <c r="I42" s="164">
+        <f t="shared" ca="1" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="J42" s="47">
+        <f t="shared" ca="1" si="4"/>
+        <v>0</v>
+      </c>
       <c r="K42" s="164"/>
-      <c r="L42" s="52"/>
-      <c r="M42" s="66"/>
+      <c r="L42" s="54" t="s">
+        <v>8</v>
+      </c>
+      <c r="M42" s="65"/>
       <c r="N42" s="40"/>
-      <c r="O42" s="37"/>
-      <c r="P42" s="17"/>
-      <c r="Q42" s="183"/>
-      <c r="R42" s="27"/>
-      <c r="S42" s="27"/>
-      <c r="T42" s="187"/>
+      <c r="O42" s="41"/>
+      <c r="P42" s="40"/>
+      <c r="Q42" s="155"/>
+      <c r="R42" s="27">
+        <v>46316</v>
+      </c>
+      <c r="S42" s="27">
+        <v>46316</v>
+      </c>
+      <c r="T42" s="188">
+        <v>46317</v>
+      </c>
       <c r="U42" s="29"/>
       <c r="V42" s="188"/>
-      <c r="W42" s="227"/>
+      <c r="W42" s="235"/>
       <c r="X42" s="230"/>
       <c r="Y42" s="227"/>
       <c r="Z42" s="29" t="str">
@@ -29173,291 +29252,409 @@
         <v/>
       </c>
       <c r="AA42" s="229"/>
-      <c r="AB42" s="229"/>
-      <c r="AC42" s="19"/>
-      <c r="AD42" s="92"/>
-      <c r="AG42" s="238"/>
-      <c r="AH42" s="243"/>
-      <c r="AI42" s="75"/>
-    </row>
-    <row r="43" spans="1:35" s="9" customFormat="1" ht="16.5" thickBot="1">
-      <c r="A43" s="24"/>
-      <c r="B43" s="329"/>
-      <c r="C43" s="165"/>
-      <c r="D43" s="45"/>
-      <c r="E43" s="175"/>
-      <c r="F43" s="32"/>
-      <c r="G43" s="22"/>
-      <c r="H43" s="139"/>
-      <c r="I43" s="178"/>
-      <c r="J43" s="132"/>
-      <c r="K43" s="199"/>
-      <c r="L43" s="53"/>
-      <c r="M43" s="67"/>
-      <c r="N43" s="18"/>
-      <c r="O43" s="38"/>
-      <c r="P43" s="18"/>
-      <c r="Q43" s="184"/>
-      <c r="R43" s="44"/>
-      <c r="S43" s="44"/>
-      <c r="T43" s="189"/>
-      <c r="U43" s="43"/>
-      <c r="V43" s="194"/>
-      <c r="W43" s="228"/>
-      <c r="X43" s="232"/>
-      <c r="Y43" s="228"/>
-      <c r="Z43" s="43" t="str">
+      <c r="AB42" s="229" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="AC42" s="183" t="str">
+        <f t="shared" ref="AC42" si="26">IF(AB42="Late Resubmission",IF(AA42="","",AA42-Z42),IF(AB42="Not submit yet",IF(Z42="","",$I$1-Z42),""))</f>
+        <v/>
+      </c>
+      <c r="AD42" s="92" t="s">
+        <v>1110</v>
+      </c>
+      <c r="AG42" s="238" t="str">
+        <f t="shared" si="8"/>
+        <v>LTIA-5.10-VIETUR-80000-RFA-SDS-0197</v>
+      </c>
+      <c r="AH42" s="243" t="b" cm="1">
+        <f t="array" ref="AH42">$D42=_xlfn.XLOOKUP(
+AG42,
+_xlfn._xlws.FILTER($AG$7:$AG$4874,$K$7:$K$4874&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4874,$K$7:$K$4874&lt;&gt;"X"),
+"",
+0,
+-1
+)</f>
+        <v>1</v>
+      </c>
+      <c r="AI42" s="75" t="str">
+        <f>IF(AND($AH42,OR($Q42="B",$Q42="C")),"YES","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" spans="1:35" s="9" customFormat="1" ht="47.25">
+      <c r="A43" s="33">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+      <c r="B43" s="33" t="str">
+        <f t="shared" ref="B43" si="27">MID(D43, FIND("-", D43) + 1, 4)</f>
+        <v>5.10</v>
+      </c>
+      <c r="C43" s="164"/>
+      <c r="D43" s="25" t="s">
+        <v>1103</v>
+      </c>
+      <c r="E43" s="174">
+        <f t="shared" si="2"/>
+        <v>46337</v>
+      </c>
+      <c r="F43" s="31" t="s">
+        <v>1104</v>
+      </c>
+      <c r="G43" s="21" t="s">
+        <v>521</v>
+      </c>
+      <c r="H43" s="138"/>
+      <c r="I43" s="164">
+        <f t="shared" ca="1" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="J43" s="47">
+        <f t="shared" ca="1" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K43" s="164"/>
+      <c r="L43" s="54" t="s">
+        <v>8</v>
+      </c>
+      <c r="M43" s="65"/>
+      <c r="N43" s="40"/>
+      <c r="O43" s="41"/>
+      <c r="P43" s="40"/>
+      <c r="Q43" s="155"/>
+      <c r="R43" s="27">
+        <v>46316</v>
+      </c>
+      <c r="S43" s="27">
+        <v>46316</v>
+      </c>
+      <c r="T43" s="188">
+        <v>46316</v>
+      </c>
+      <c r="U43" s="29"/>
+      <c r="V43" s="188"/>
+      <c r="W43" s="235"/>
+      <c r="X43" s="230"/>
+      <c r="Y43" s="227"/>
+      <c r="Z43" s="29" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AA43" s="233"/>
-      <c r="AB43" s="233"/>
-      <c r="AC43" s="20"/>
-      <c r="AD43" s="93"/>
-      <c r="AG43" s="239"/>
-      <c r="AH43" s="244"/>
-      <c r="AI43" s="241"/>
-    </row>
-    <row r="44" spans="1:35" ht="16.5" thickBot="1"/>
-    <row r="45" spans="1:35" ht="16.5" thickBot="1">
-      <c r="C45" s="166" t="s">
+      <c r="AA43" s="229"/>
+      <c r="AB43" s="229" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="AC43" s="183" t="str">
+        <f t="shared" ref="AC43" si="28">IF(AB43="Late Resubmission",IF(AA43="","",AA43-Z43),IF(AB43="Not submit yet",IF(Z43="","",$I$1-Z43),""))</f>
+        <v/>
+      </c>
+      <c r="AD43" s="92"/>
+      <c r="AG43" s="238" t="str">
+        <f t="shared" si="8"/>
+        <v>LTIA-5.10-VIETUR-80000-RFA-SDS-0080</v>
+      </c>
+      <c r="AH43" s="243" t="b" cm="1">
+        <f t="array" ref="AH43">$D43=_xlfn.XLOOKUP(
+AG43,
+_xlfn._xlws.FILTER($AG$7:$AG$4874,$K$7:$K$4874&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4874,$K$7:$K$4874&lt;&gt;"X"),
+"",
+0,
+-1
+)</f>
+        <v>1</v>
+      </c>
+      <c r="AI43" s="75" t="str">
+        <f>IF(AND($AH43,OR($Q43="B",$Q43="C")),"YES","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" spans="1:35" s="9" customFormat="1" ht="47.25">
+      <c r="A44" s="33">
+        <f t="shared" si="0"/>
+        <v>38</v>
+      </c>
+      <c r="B44" s="33" t="str">
+        <f t="shared" ref="B44" si="29">MID(D44, FIND("-", D44) + 1, 4)</f>
+        <v>5.10</v>
+      </c>
+      <c r="C44" s="164"/>
+      <c r="D44" s="25" t="s">
+        <v>1105</v>
+      </c>
+      <c r="E44" s="174">
+        <f t="shared" si="2"/>
+        <v>46337</v>
+      </c>
+      <c r="F44" s="31" t="s">
+        <v>1106</v>
+      </c>
+      <c r="G44" s="21" t="s">
+        <v>526</v>
+      </c>
+      <c r="H44" s="138"/>
+      <c r="I44" s="164">
+        <f t="shared" ca="1" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="J44" s="47">
+        <f t="shared" ca="1" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K44" s="164"/>
+      <c r="L44" s="54" t="s">
+        <v>8</v>
+      </c>
+      <c r="M44" s="65"/>
+      <c r="N44" s="40"/>
+      <c r="O44" s="41"/>
+      <c r="P44" s="40"/>
+      <c r="Q44" s="155"/>
+      <c r="R44" s="27">
+        <v>46316</v>
+      </c>
+      <c r="S44" s="27">
+        <v>46316</v>
+      </c>
+      <c r="T44" s="188">
+        <v>46316</v>
+      </c>
+      <c r="U44" s="29"/>
+      <c r="V44" s="188"/>
+      <c r="W44" s="235"/>
+      <c r="X44" s="230"/>
+      <c r="Y44" s="227"/>
+      <c r="Z44" s="29" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="AA44" s="229"/>
+      <c r="AB44" s="229" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="AC44" s="183" t="str">
+        <f t="shared" ref="AC44" si="30">IF(AB44="Late Resubmission",IF(AA44="","",AA44-Z44),IF(AB44="Not submit yet",IF(Z44="","",$I$1-Z44),""))</f>
+        <v/>
+      </c>
+      <c r="AD44" s="92"/>
+      <c r="AG44" s="238" t="str">
+        <f t="shared" si="8"/>
+        <v>LTIA-5.10-VIETUR-80000-RFA-SDS-0122</v>
+      </c>
+      <c r="AH44" s="243" t="b" cm="1">
+        <f t="array" ref="AH44">$D44=_xlfn.XLOOKUP(
+AG44,
+_xlfn._xlws.FILTER($AG$7:$AG$4874,$K$7:$K$4874&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4874,$K$7:$K$4874&lt;&gt;"X"),
+"",
+0,
+-1
+)</f>
+        <v>1</v>
+      </c>
+      <c r="AI44" s="75" t="str">
+        <f>IF(AND($AH44,OR($Q44="B",$Q44="C")),"YES","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45" spans="1:35" s="9" customFormat="1" ht="47.25">
+      <c r="A45" s="33">
+        <f t="shared" si="0"/>
+        <v>39</v>
+      </c>
+      <c r="B45" s="33" t="str">
+        <f t="shared" ref="B45" si="31">MID(D45, FIND("-", D45) + 1, 4)</f>
+        <v>5.11</v>
+      </c>
+      <c r="C45" s="164" t="s">
+        <v>656</v>
+      </c>
+      <c r="D45" s="25" t="s">
+        <v>1107</v>
+      </c>
+      <c r="E45" s="174">
+        <f t="shared" si="2"/>
+        <v>46337</v>
+      </c>
+      <c r="F45" s="31" t="s">
+        <v>1108</v>
+      </c>
+      <c r="G45" s="21" t="s">
+        <v>1109</v>
+      </c>
+      <c r="H45" s="138"/>
+      <c r="I45" s="164">
+        <f t="shared" ca="1" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="J45" s="47">
+        <f t="shared" ca="1" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K45" s="164"/>
+      <c r="L45" s="54" t="s">
+        <v>8</v>
+      </c>
+      <c r="M45" s="65"/>
+      <c r="N45" s="40"/>
+      <c r="O45" s="41"/>
+      <c r="P45" s="40"/>
+      <c r="Q45" s="155"/>
+      <c r="R45" s="27">
+        <v>46316</v>
+      </c>
+      <c r="S45" s="27">
+        <v>46316</v>
+      </c>
+      <c r="T45" s="188">
+        <v>46316</v>
+      </c>
+      <c r="U45" s="29"/>
+      <c r="V45" s="188"/>
+      <c r="W45" s="235"/>
+      <c r="X45" s="230"/>
+      <c r="Y45" s="227"/>
+      <c r="Z45" s="29" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="AA45" s="229"/>
+      <c r="AB45" s="229" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="AC45" s="183" t="str">
+        <f t="shared" ref="AC45" si="32">IF(AB45="Late Resubmission",IF(AA45="","",AA45-Z45),IF(AB45="Not submit yet",IF(Z45="","",$I$1-Z45),""))</f>
+        <v/>
+      </c>
+      <c r="AD45" s="92"/>
+      <c r="AG45" s="238" t="str">
+        <f t="shared" si="8"/>
+        <v>LTIA-5.11-LTICT-71110-RFA-SDS-0002</v>
+      </c>
+      <c r="AH45" s="243" t="b" cm="1">
+        <f t="array" ref="AH45">$D45=_xlfn.XLOOKUP(
+AG45,
+_xlfn._xlws.FILTER($AG$7:$AG$4874,$K$7:$K$4874&lt;&gt;"X"),
+_xlfn._xlws.FILTER($D$7:$D$4874,$K$7:$K$4874&lt;&gt;"X"),
+"",
+0,
+-1
+)</f>
+        <v>1</v>
+      </c>
+      <c r="AI45" s="75" t="str">
+        <f>IF(AND($AH45,OR($Q45="B",$Q45="C")),"YES","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" spans="1:35" s="9" customFormat="1">
+      <c r="A46" s="23"/>
+      <c r="B46" s="33"/>
+      <c r="C46" s="137"/>
+      <c r="D46" s="25"/>
+      <c r="E46" s="174"/>
+      <c r="F46" s="31"/>
+      <c r="G46" s="21"/>
+      <c r="H46" s="138"/>
+      <c r="I46" s="177"/>
+      <c r="J46" s="47"/>
+      <c r="K46" s="164"/>
+      <c r="L46" s="52"/>
+      <c r="M46" s="66"/>
+      <c r="N46" s="40"/>
+      <c r="O46" s="37"/>
+      <c r="P46" s="17"/>
+      <c r="Q46" s="183"/>
+      <c r="R46" s="27"/>
+      <c r="S46" s="27"/>
+      <c r="T46" s="187"/>
+      <c r="U46" s="29"/>
+      <c r="V46" s="188"/>
+      <c r="W46" s="227"/>
+      <c r="X46" s="230"/>
+      <c r="Y46" s="227"/>
+      <c r="Z46" s="29" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="AA46" s="229"/>
+      <c r="AB46" s="229"/>
+      <c r="AC46" s="19"/>
+      <c r="AD46" s="92"/>
+      <c r="AG46" s="238"/>
+      <c r="AH46" s="243"/>
+      <c r="AI46" s="75"/>
+    </row>
+    <row r="47" spans="1:35" s="9" customFormat="1" ht="16.5" thickBot="1">
+      <c r="A47" s="24"/>
+      <c r="B47" s="329"/>
+      <c r="C47" s="165"/>
+      <c r="D47" s="45"/>
+      <c r="E47" s="175"/>
+      <c r="F47" s="32"/>
+      <c r="G47" s="22"/>
+      <c r="H47" s="139"/>
+      <c r="I47" s="178"/>
+      <c r="J47" s="132"/>
+      <c r="K47" s="199"/>
+      <c r="L47" s="53"/>
+      <c r="M47" s="67"/>
+      <c r="N47" s="18"/>
+      <c r="O47" s="38"/>
+      <c r="P47" s="18"/>
+      <c r="Q47" s="184"/>
+      <c r="R47" s="44"/>
+      <c r="S47" s="44"/>
+      <c r="T47" s="189"/>
+      <c r="U47" s="43"/>
+      <c r="V47" s="194"/>
+      <c r="W47" s="228"/>
+      <c r="X47" s="232"/>
+      <c r="Y47" s="228"/>
+      <c r="Z47" s="43" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="AA47" s="233"/>
+      <c r="AB47" s="233"/>
+      <c r="AC47" s="20"/>
+      <c r="AD47" s="93"/>
+      <c r="AG47" s="239"/>
+      <c r="AH47" s="244"/>
+      <c r="AI47" s="241"/>
+    </row>
+    <row r="48" spans="1:35" ht="16.5" thickBot="1"/>
+    <row r="49" spans="3:35" ht="16.5" thickBot="1">
+      <c r="C49" s="166" t="s">
         <v>20</v>
       </c>
-      <c r="D45" s="364" t="s">
+      <c r="D49" s="376" t="s">
         <v>21</v>
       </c>
-      <c r="E45" s="365"/>
-      <c r="F45" s="46"/>
-      <c r="G45" s="46"/>
-      <c r="H45" s="377" t="s">
+      <c r="E49" s="377"/>
+      <c r="F49" s="46"/>
+      <c r="G49" s="46"/>
+      <c r="H49" s="356" t="s">
         <v>14</v>
       </c>
-      <c r="I45" s="378"/>
-      <c r="J45" s="378"/>
-      <c r="K45" s="378"/>
-      <c r="L45" s="378"/>
-      <c r="M45" s="379"/>
-      <c r="N45" s="348" t="s">
+      <c r="I49" s="357"/>
+      <c r="J49" s="357"/>
+      <c r="K49" s="357"/>
+      <c r="L49" s="357"/>
+      <c r="M49" s="358"/>
+      <c r="N49" s="362" t="s">
         <v>7</v>
       </c>
-      <c r="O45" s="349"/>
-      <c r="P45" s="348" t="s">
+      <c r="O49" s="363"/>
+      <c r="P49" s="362" t="s">
         <v>109</v>
       </c>
-      <c r="Q45" s="349"/>
-      <c r="R45" s="1"/>
-      <c r="S45" s="1"/>
-      <c r="T45" s="140"/>
-      <c r="U45" s="1"/>
-      <c r="W45" s="11"/>
-      <c r="X45" s="11"/>
-      <c r="Y45" s="11"/>
-      <c r="Z45" s="11"/>
-      <c r="AA45" s="11"/>
-      <c r="AB45" s="11"/>
-      <c r="AC45" s="11"/>
-      <c r="AG45" s="11"/>
-      <c r="AH45" s="11"/>
-      <c r="AI45" s="11"/>
-    </row>
-    <row r="46" spans="1:35" ht="16.5" thickBot="1">
-      <c r="C46" s="195" t="s">
-        <v>109</v>
-      </c>
-      <c r="D46" s="392" t="s">
-        <v>111</v>
-      </c>
-      <c r="E46" s="393"/>
-      <c r="F46" s="46"/>
-      <c r="H46" s="377" t="s">
-        <v>18</v>
-      </c>
-      <c r="I46" s="378"/>
-      <c r="J46" s="378"/>
-      <c r="K46" s="379"/>
-      <c r="L46" s="105">
-        <f ca="1">M46/$M$46</f>
-        <v>1</v>
-      </c>
-      <c r="M46" s="106">
-        <f ca="1">SUM($M$47:$M$51)</f>
-        <v>37</v>
-      </c>
-      <c r="N46" s="102" t="s">
-        <v>15</v>
-      </c>
-      <c r="O46" s="103" t="s">
-        <v>16</v>
-      </c>
-      <c r="P46" s="105">
-        <f ca="1">Q46/$Q$46</f>
-        <v>1</v>
-      </c>
-      <c r="Q46" s="220">
-        <f ca="1">SUM(Q47:Q50)</f>
-        <v>33</v>
-      </c>
-      <c r="R46" s="1"/>
-      <c r="S46" s="1"/>
-      <c r="T46" s="140"/>
-      <c r="U46" s="1"/>
-      <c r="W46" s="11"/>
-      <c r="X46" s="11"/>
-      <c r="Y46" s="11"/>
-      <c r="Z46" s="11"/>
-      <c r="AA46" s="11"/>
-      <c r="AB46" s="11"/>
-      <c r="AC46" s="11"/>
-      <c r="AG46" s="11"/>
-      <c r="AH46" s="11"/>
-      <c r="AI46" s="11"/>
-    </row>
-    <row r="47" spans="1:35">
-      <c r="C47" s="195" t="s">
-        <v>36</v>
-      </c>
-      <c r="D47" s="368" t="s">
-        <v>37</v>
-      </c>
-      <c r="E47" s="369"/>
-      <c r="F47" s="69"/>
-      <c r="G47" s="6"/>
-      <c r="H47" s="371" t="s">
-        <v>66</v>
-      </c>
-      <c r="I47" s="372"/>
-      <c r="J47" s="372"/>
-      <c r="K47" s="373"/>
-      <c r="L47" s="107">
-        <f ca="1">M47/$M$46</f>
-        <v>2.7027027027027029E-2</v>
-      </c>
-      <c r="M47" s="108">
-        <f>COUNTIF($H$7:$H$43,"A")</f>
-        <v>1</v>
-      </c>
-      <c r="N47" s="100">
-        <f ca="1">COUNTIFS($I$7:$I$43,"&lt;=21",$H$7:$H$43,"A")</f>
-        <v>1</v>
-      </c>
-      <c r="O47" s="101">
-        <f ca="1">COUNTIFS($I$7:$I$43,"&gt;21",$H$7:$H$43,"A")</f>
-        <v>0</v>
-      </c>
-      <c r="P47" s="107">
-        <f ca="1">Q47/$Q$46</f>
-        <v>3.0303030303030304E-2</v>
-      </c>
-      <c r="Q47" s="108">
-        <f>COUNTIF($Q$7:$Q$43,"A")</f>
-        <v>1</v>
-      </c>
-      <c r="R47" s="1"/>
-      <c r="S47" s="1"/>
-      <c r="T47" s="140"/>
-      <c r="U47" s="1"/>
-      <c r="W47" s="11"/>
-      <c r="X47" s="11"/>
-      <c r="Y47" s="11"/>
-      <c r="Z47" s="11"/>
-      <c r="AA47" s="11"/>
-      <c r="AB47" s="11"/>
-      <c r="AC47" s="11"/>
-      <c r="AG47" s="11"/>
-      <c r="AH47" s="11"/>
-      <c r="AI47" s="11"/>
-    </row>
-    <row r="48" spans="1:35">
-      <c r="C48" s="386" t="s">
-        <v>75</v>
-      </c>
-      <c r="D48" s="388" t="s">
-        <v>76</v>
-      </c>
-      <c r="E48" s="389"/>
-      <c r="F48" s="70"/>
-      <c r="G48" s="6"/>
-      <c r="H48" s="374" t="s">
-        <v>67</v>
-      </c>
-      <c r="I48" s="375"/>
-      <c r="J48" s="375"/>
-      <c r="K48" s="376"/>
-      <c r="L48" s="109">
-        <f t="shared" ref="L48:L51" ca="1" si="25">M48/$M$46</f>
-        <v>0.54054054054054057</v>
-      </c>
-      <c r="M48" s="110">
-        <f>COUNTIF($H$7:$H$43,"B")</f>
-        <v>20</v>
-      </c>
-      <c r="N48" s="98">
-        <f ca="1">COUNTIFS($I$7:$I$43,"&lt;=21",$H$7:$H$43,"B")</f>
-        <v>8</v>
-      </c>
-      <c r="O48" s="50">
-        <f ca="1">COUNTIFS($I$7:$I$43,"&gt;21",$H$7:$H$43,"B")</f>
-        <v>12</v>
-      </c>
-      <c r="P48" s="109">
-        <f t="shared" ref="P48:P50" ca="1" si="26">Q48/$Q$46</f>
-        <v>0.60606060606060608</v>
-      </c>
-      <c r="Q48" s="110">
-        <f>COUNTIF($Q$7:$Q$43,"B")</f>
-        <v>20</v>
-      </c>
-      <c r="R48" s="1"/>
-      <c r="S48" s="1"/>
-      <c r="T48" s="140"/>
-      <c r="U48" s="1"/>
-      <c r="W48" s="11"/>
-      <c r="X48" s="11"/>
-      <c r="Y48" s="11"/>
-      <c r="Z48" s="11"/>
-      <c r="AA48" s="11"/>
-      <c r="AB48" s="11"/>
-      <c r="AC48" s="11"/>
-      <c r="AG48" s="11"/>
-      <c r="AH48" s="11"/>
-      <c r="AI48" s="11"/>
-    </row>
-    <row r="49" spans="3:35" ht="16.5" thickBot="1">
-      <c r="C49" s="387"/>
-      <c r="D49" s="390"/>
-      <c r="E49" s="391"/>
-      <c r="F49" s="71"/>
-      <c r="G49" s="6"/>
-      <c r="H49" s="380" t="s">
-        <v>68</v>
-      </c>
-      <c r="I49" s="381"/>
-      <c r="J49" s="381"/>
-      <c r="K49" s="382"/>
-      <c r="L49" s="111">
-        <f t="shared" ca="1" si="25"/>
-        <v>0.21621621621621623</v>
-      </c>
-      <c r="M49" s="112">
-        <f>COUNTIF($H$7:$H$43,"C")</f>
-        <v>8</v>
-      </c>
-      <c r="N49" s="98">
-        <f ca="1">COUNTIFS($I$7:$I$43,"&lt;=21",$H$7:$H$43,"C")</f>
-        <v>3</v>
-      </c>
-      <c r="O49" s="50">
-        <f ca="1">COUNTIFS($I$7:$I$43,"&gt;21",$H$7:$H$43,"C")</f>
-        <v>5</v>
-      </c>
-      <c r="P49" s="111">
-        <f t="shared" ca="1" si="26"/>
-        <v>9.0909090909090912E-2</v>
-      </c>
-      <c r="Q49" s="112">
-        <f>COUNTIF($Q$7:$Q$43,"C")</f>
-        <v>3</v>
-      </c>
+      <c r="Q49" s="363"/>
       <c r="R49" s="1"/>
       <c r="S49" s="1"/>
       <c r="T49" s="140"/>
@@ -29473,42 +29670,44 @@
       <c r="AH49" s="11"/>
       <c r="AI49" s="11"/>
     </row>
-    <row r="50" spans="3:35">
-      <c r="F50" s="72"/>
-      <c r="G50" s="6"/>
-      <c r="H50" s="383" t="s">
-        <v>70</v>
-      </c>
-      <c r="I50" s="384"/>
-      <c r="J50" s="384"/>
-      <c r="K50" s="385"/>
-      <c r="L50" s="114">
-        <f t="shared" ca="1" si="25"/>
-        <v>0.16216216216216217</v>
-      </c>
-      <c r="M50" s="115">
-        <f ca="1">SUM(N50:O50)</f>
-        <v>6</v>
-      </c>
-      <c r="N50" s="98">
-        <f ca="1">COUNTIFS($I$7:$I$43,"&lt;=21",$U$7:$U$43,"",$K$7:$K$43,"&lt;&gt;X")</f>
-        <v>4</v>
-      </c>
-      <c r="O50" s="50">
-        <f ca="1">COUNTIFS($I$7:$I$43,"&gt;21",$U$7:$U$43,"",$K$7:$K$43,"&lt;&gt;X")</f>
-        <v>2</v>
-      </c>
-      <c r="P50" s="114">
-        <f t="shared" ca="1" si="26"/>
-        <v>0.27272727272727271</v>
-      </c>
-      <c r="Q50" s="115">
-        <f ca="1">COUNTIFS($I$7:$I$43,"&gt;=0",$P$7:$P$43,"",$K$7:$K$43,"&lt;&gt;X")</f>
-        <v>9</v>
-      </c>
-      <c r="R50" s="1" t="s">
-        <v>10</v>
-      </c>
+    <row r="50" spans="3:35" ht="16.5" thickBot="1">
+      <c r="C50" s="195" t="s">
+        <v>109</v>
+      </c>
+      <c r="D50" s="420" t="s">
+        <v>111</v>
+      </c>
+      <c r="E50" s="421"/>
+      <c r="F50" s="46"/>
+      <c r="H50" s="356" t="s">
+        <v>18</v>
+      </c>
+      <c r="I50" s="357"/>
+      <c r="J50" s="357"/>
+      <c r="K50" s="358"/>
+      <c r="L50" s="105">
+        <f ca="1">M50/$M$50</f>
+        <v>1</v>
+      </c>
+      <c r="M50" s="106">
+        <f ca="1">SUM($M$51:$M$55)</f>
+        <v>41</v>
+      </c>
+      <c r="N50" s="102" t="s">
+        <v>15</v>
+      </c>
+      <c r="O50" s="103" t="s">
+        <v>16</v>
+      </c>
+      <c r="P50" s="105">
+        <f ca="1">Q50/$Q$50</f>
+        <v>1</v>
+      </c>
+      <c r="Q50" s="220">
+        <f ca="1">SUM(Q51:Q54)</f>
+        <v>37</v>
+      </c>
+      <c r="R50" s="1"/>
       <c r="S50" s="1"/>
       <c r="T50" s="140"/>
       <c r="U50" s="1"/>
@@ -29523,57 +29722,268 @@
       <c r="AH50" s="11"/>
       <c r="AI50" s="11"/>
     </row>
-    <row r="51" spans="3:35" ht="16.5" thickBot="1">
-      <c r="C51" s="370" t="s">
+    <row r="51" spans="3:35">
+      <c r="C51" s="195" t="s">
+        <v>36</v>
+      </c>
+      <c r="D51" s="418" t="s">
+        <v>37</v>
+      </c>
+      <c r="E51" s="419"/>
+      <c r="F51" s="69"/>
+      <c r="G51" s="6"/>
+      <c r="H51" s="379" t="s">
+        <v>66</v>
+      </c>
+      <c r="I51" s="380"/>
+      <c r="J51" s="380"/>
+      <c r="K51" s="381"/>
+      <c r="L51" s="107">
+        <f ca="1">M51/$M$50</f>
+        <v>2.4390243902439025E-2</v>
+      </c>
+      <c r="M51" s="108">
+        <f>COUNTIF($H$7:$H$47,"A")</f>
+        <v>1</v>
+      </c>
+      <c r="N51" s="100">
+        <f ca="1">COUNTIFS($I$7:$I$47,"&lt;=21",$H$7:$H$47,"A")</f>
+        <v>1</v>
+      </c>
+      <c r="O51" s="101">
+        <f ca="1">COUNTIFS($I$7:$I$47,"&gt;21",$H$7:$H$47,"A")</f>
+        <v>0</v>
+      </c>
+      <c r="P51" s="107">
+        <f ca="1">Q51/$Q$50</f>
+        <v>2.7027027027027029E-2</v>
+      </c>
+      <c r="Q51" s="108">
+        <f>COUNTIF($Q$7:$Q$47,"A")</f>
+        <v>1</v>
+      </c>
+      <c r="R51" s="1"/>
+      <c r="S51" s="1"/>
+      <c r="T51" s="140"/>
+      <c r="U51" s="1"/>
+      <c r="W51" s="11"/>
+      <c r="X51" s="11"/>
+      <c r="Y51" s="11"/>
+      <c r="Z51" s="11"/>
+      <c r="AA51" s="11"/>
+      <c r="AB51" s="11"/>
+      <c r="AC51" s="11"/>
+      <c r="AG51" s="11"/>
+      <c r="AH51" s="11"/>
+      <c r="AI51" s="11"/>
+    </row>
+    <row r="52" spans="3:35">
+      <c r="C52" s="394" t="s">
+        <v>75</v>
+      </c>
+      <c r="D52" s="350" t="s">
+        <v>76</v>
+      </c>
+      <c r="E52" s="351"/>
+      <c r="F52" s="70"/>
+      <c r="G52" s="6"/>
+      <c r="H52" s="382" t="s">
+        <v>67</v>
+      </c>
+      <c r="I52" s="383"/>
+      <c r="J52" s="383"/>
+      <c r="K52" s="384"/>
+      <c r="L52" s="109">
+        <f t="shared" ref="L52:L55" ca="1" si="33">M52/$M$50</f>
+        <v>0.48780487804878048</v>
+      </c>
+      <c r="M52" s="110">
+        <f>COUNTIF($H$7:$H$47,"B")</f>
+        <v>20</v>
+      </c>
+      <c r="N52" s="98">
+        <f ca="1">COUNTIFS($I$7:$I$47,"&lt;=21",$H$7:$H$47,"B")</f>
+        <v>8</v>
+      </c>
+      <c r="O52" s="50">
+        <f ca="1">COUNTIFS($I$7:$I$47,"&gt;21",$H$7:$H$47,"B")</f>
+        <v>12</v>
+      </c>
+      <c r="P52" s="109">
+        <f t="shared" ref="P52:P54" ca="1" si="34">Q52/$Q$50</f>
+        <v>0.54054054054054057</v>
+      </c>
+      <c r="Q52" s="110">
+        <f>COUNTIF($Q$7:$Q$47,"B")</f>
+        <v>20</v>
+      </c>
+      <c r="R52" s="1"/>
+      <c r="S52" s="1"/>
+      <c r="T52" s="140"/>
+      <c r="U52" s="1"/>
+      <c r="W52" s="11"/>
+      <c r="X52" s="11"/>
+      <c r="Y52" s="11"/>
+      <c r="Z52" s="11"/>
+      <c r="AA52" s="11"/>
+      <c r="AB52" s="11"/>
+      <c r="AC52" s="11"/>
+      <c r="AG52" s="11"/>
+      <c r="AH52" s="11"/>
+      <c r="AI52" s="11"/>
+    </row>
+    <row r="53" spans="3:35" ht="16.5" thickBot="1">
+      <c r="C53" s="395"/>
+      <c r="D53" s="352"/>
+      <c r="E53" s="353"/>
+      <c r="F53" s="71"/>
+      <c r="G53" s="6"/>
+      <c r="H53" s="385" t="s">
+        <v>68</v>
+      </c>
+      <c r="I53" s="386"/>
+      <c r="J53" s="386"/>
+      <c r="K53" s="387"/>
+      <c r="L53" s="111">
+        <f t="shared" ca="1" si="33"/>
+        <v>0.1951219512195122</v>
+      </c>
+      <c r="M53" s="112">
+        <f>COUNTIF($H$7:$H$47,"C")</f>
+        <v>8</v>
+      </c>
+      <c r="N53" s="98">
+        <f ca="1">COUNTIFS($I$7:$I$47,"&lt;=21",$H$7:$H$47,"C")</f>
+        <v>3</v>
+      </c>
+      <c r="O53" s="50">
+        <f ca="1">COUNTIFS($I$7:$I$47,"&gt;21",$H$7:$H$47,"C")</f>
+        <v>5</v>
+      </c>
+      <c r="P53" s="111">
+        <f t="shared" ca="1" si="34"/>
+        <v>8.1081081081081086E-2</v>
+      </c>
+      <c r="Q53" s="112">
+        <f>COUNTIF($Q$7:$Q$47,"C")</f>
+        <v>3</v>
+      </c>
+      <c r="R53" s="1"/>
+      <c r="S53" s="1"/>
+      <c r="T53" s="140"/>
+      <c r="U53" s="1"/>
+      <c r="W53" s="11"/>
+      <c r="X53" s="11"/>
+      <c r="Y53" s="11"/>
+      <c r="Z53" s="11"/>
+      <c r="AA53" s="11"/>
+      <c r="AB53" s="11"/>
+      <c r="AC53" s="11"/>
+      <c r="AG53" s="11"/>
+      <c r="AH53" s="11"/>
+      <c r="AI53" s="11"/>
+    </row>
+    <row r="54" spans="3:35">
+      <c r="F54" s="72"/>
+      <c r="G54" s="6"/>
+      <c r="H54" s="388" t="s">
+        <v>70</v>
+      </c>
+      <c r="I54" s="389"/>
+      <c r="J54" s="389"/>
+      <c r="K54" s="390"/>
+      <c r="L54" s="114">
+        <f t="shared" ca="1" si="33"/>
+        <v>0.24390243902439024</v>
+      </c>
+      <c r="M54" s="115">
+        <f ca="1">SUM(N54:O54)</f>
+        <v>10</v>
+      </c>
+      <c r="N54" s="98">
+        <f ca="1">COUNTIFS($I$7:$I$47,"&lt;=21",$U$7:$U$47,"",$K$7:$K$47,"&lt;&gt;X")</f>
+        <v>8</v>
+      </c>
+      <c r="O54" s="50">
+        <f ca="1">COUNTIFS($I$7:$I$47,"&gt;21",$U$7:$U$47,"",$K$7:$K$47,"&lt;&gt;X")</f>
+        <v>2</v>
+      </c>
+      <c r="P54" s="114">
+        <f t="shared" ca="1" si="34"/>
+        <v>0.35135135135135137</v>
+      </c>
+      <c r="Q54" s="115">
+        <f ca="1">COUNTIFS($I$7:$I$47,"&gt;=0",$P$7:$P$47,"",$K$7:$K$47,"&lt;&gt;X")</f>
+        <v>13</v>
+      </c>
+      <c r="R54" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="S54" s="1"/>
+      <c r="T54" s="140"/>
+      <c r="U54" s="1"/>
+      <c r="W54" s="11"/>
+      <c r="X54" s="11"/>
+      <c r="Y54" s="11"/>
+      <c r="Z54" s="11"/>
+      <c r="AA54" s="11"/>
+      <c r="AB54" s="11"/>
+      <c r="AC54" s="11"/>
+      <c r="AG54" s="11"/>
+      <c r="AH54" s="11"/>
+      <c r="AI54" s="11"/>
+    </row>
+    <row r="55" spans="3:35" ht="16.5" thickBot="1">
+      <c r="C55" s="378" t="s">
         <v>41</v>
       </c>
-      <c r="D51" s="370"/>
-      <c r="E51" s="370"/>
-      <c r="H51" s="400" t="s">
+      <c r="D55" s="378"/>
+      <c r="E55" s="378"/>
+      <c r="H55" s="391" t="s">
         <v>71</v>
       </c>
-      <c r="I51" s="401"/>
-      <c r="J51" s="401"/>
-      <c r="K51" s="402"/>
-      <c r="L51" s="113">
-        <f t="shared" ca="1" si="25"/>
-        <v>5.4054054054054057E-2</v>
-      </c>
-      <c r="M51" s="97">
-        <f>COUNTIFS($K$7:$K$43,"X")</f>
+      <c r="I55" s="392"/>
+      <c r="J55" s="392"/>
+      <c r="K55" s="393"/>
+      <c r="L55" s="113">
+        <f t="shared" ca="1" si="33"/>
+        <v>4.878048780487805E-2</v>
+      </c>
+      <c r="M55" s="97">
+        <f>COUNTIFS($K$7:$K$47,"X")</f>
         <v>2</v>
       </c>
-      <c r="N51" s="99"/>
-      <c r="O51" s="51"/>
-      <c r="P51" s="221"/>
-      <c r="Q51" s="222"/>
-    </row>
-    <row r="52" spans="3:35">
-      <c r="C52" s="169" t="s">
-        <v>8</v>
-      </c>
-      <c r="D52" s="1" t="s">
+      <c r="N55" s="99"/>
+      <c r="O55" s="51"/>
+      <c r="P55" s="221"/>
+      <c r="Q55" s="222"/>
+    </row>
+    <row r="56" spans="3:35">
+      <c r="C56" s="169" t="s">
+        <v>8</v>
+      </c>
+      <c r="D56" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="53" spans="3:35">
-      <c r="C53" s="169" t="s">
-        <v>8</v>
-      </c>
-      <c r="D53" s="127" t="s">
+    <row r="57" spans="3:35">
+      <c r="C57" s="169" t="s">
+        <v>8</v>
+      </c>
+      <c r="D57" s="127" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="54" spans="3:35">
-      <c r="C54" s="169" t="s">
-        <v>8</v>
-      </c>
-      <c r="D54" s="1" t="s">
+    <row r="58" spans="3:35">
+      <c r="C58" s="169" t="s">
+        <v>8</v>
+      </c>
+      <c r="D58" s="1" t="s">
         <v>44</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A6:AD43" xr:uid="{4D8E8261-1CEF-42DB-8488-C430D415EC88}">
+  <autoFilter ref="A6:AD47" xr:uid="{4D8E8261-1CEF-42DB-8488-C430D415EC88}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A7:AD33">
       <sortCondition ref="S6:S33"/>
     </sortState>
@@ -29582,9 +29992,9 @@
     <mergeCell ref="AG5:AG6"/>
     <mergeCell ref="AH5:AH6"/>
     <mergeCell ref="AI5:AI6"/>
-    <mergeCell ref="H51:K51"/>
-    <mergeCell ref="H46:K46"/>
-    <mergeCell ref="N45:O45"/>
+    <mergeCell ref="H55:K55"/>
+    <mergeCell ref="H50:K50"/>
+    <mergeCell ref="N49:O49"/>
     <mergeCell ref="AD4:AD5"/>
     <mergeCell ref="H4:H5"/>
     <mergeCell ref="I4:I5"/>
@@ -29595,17 +30005,17 @@
     <mergeCell ref="K4:K5"/>
     <mergeCell ref="P4:Q4"/>
     <mergeCell ref="J4:J5"/>
-    <mergeCell ref="D47:E47"/>
-    <mergeCell ref="C51:E51"/>
-    <mergeCell ref="H47:K47"/>
-    <mergeCell ref="H48:K48"/>
-    <mergeCell ref="H45:M45"/>
-    <mergeCell ref="H49:K49"/>
-    <mergeCell ref="H50:K50"/>
-    <mergeCell ref="C48:C49"/>
-    <mergeCell ref="D48:E49"/>
-    <mergeCell ref="D46:E46"/>
-    <mergeCell ref="P45:Q45"/>
+    <mergeCell ref="D51:E51"/>
+    <mergeCell ref="C55:E55"/>
+    <mergeCell ref="H51:K51"/>
+    <mergeCell ref="H52:K52"/>
+    <mergeCell ref="H49:M49"/>
+    <mergeCell ref="H53:K53"/>
+    <mergeCell ref="H54:K54"/>
+    <mergeCell ref="C52:C53"/>
+    <mergeCell ref="D52:E53"/>
+    <mergeCell ref="D50:E50"/>
+    <mergeCell ref="P49:Q49"/>
     <mergeCell ref="X4:Y4"/>
     <mergeCell ref="Z4:AC4"/>
     <mergeCell ref="A4:A5"/>
@@ -29614,11 +30024,11 @@
     <mergeCell ref="F4:F5"/>
     <mergeCell ref="G4:G5"/>
     <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D45:E45"/>
+    <mergeCell ref="D49:E49"/>
     <mergeCell ref="B4:B5"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
-  <conditionalFormatting sqref="A7:AD43 AG7:AI43">
+  <conditionalFormatting sqref="A7:AD47 AG7:AI47">
     <cfRule type="expression" dxfId="11" priority="1">
       <formula>$K7="X"</formula>
     </cfRule>
@@ -29744,9 +30154,9 @@
     <hyperlink ref="O24" r:id="rId100" xr:uid="{26FEB876-D8E0-4A23-A9C5-C07952F599D7}"/>
     <hyperlink ref="O27" r:id="rId101" xr:uid="{51C15339-30E0-4EDA-A35A-162E28AC0D63}"/>
     <hyperlink ref="O33" r:id="rId102" xr:uid="{7E0883C0-4918-4433-937B-70D3D155F955}"/>
-    <hyperlink ref="C52" r:id="rId103" xr:uid="{BDBBB1AA-41DD-4769-B198-E0D4B6B569E2}"/>
-    <hyperlink ref="C53" r:id="rId104" xr:uid="{174B2EE8-A853-4328-A727-C5D3FC38F2B6}"/>
-    <hyperlink ref="C54" r:id="rId105" xr:uid="{6C349E79-11FF-4195-90FE-DE817F5EBEF8}"/>
+    <hyperlink ref="C56" r:id="rId103" xr:uid="{BDBBB1AA-41DD-4769-B198-E0D4B6B569E2}"/>
+    <hyperlink ref="C57" r:id="rId104" xr:uid="{174B2EE8-A853-4328-A727-C5D3FC38F2B6}"/>
+    <hyperlink ref="C58" r:id="rId105" xr:uid="{6C349E79-11FF-4195-90FE-DE817F5EBEF8}"/>
     <hyperlink ref="P7" r:id="rId106" xr:uid="{20D7A9F2-B509-4410-8C53-729666C026F8}"/>
     <hyperlink ref="P8" r:id="rId107" xr:uid="{BC5C2D57-7ED0-43E0-8C7C-0DF13280AE79}"/>
     <hyperlink ref="P9" r:id="rId108" xr:uid="{49C5EB74-800E-4CE6-82D1-E75C20991765}"/>
@@ -29783,9 +30193,13 @@
     <hyperlink ref="N38" r:id="rId139" xr:uid="{DBAA5DC8-908C-4ABF-AC05-BCE08D8BBB73}"/>
     <hyperlink ref="L40" r:id="rId140" xr:uid="{95929207-D5E2-4FFA-94DE-6961D7557694}"/>
     <hyperlink ref="L41" r:id="rId141" xr:uid="{4C22862D-00A5-4D76-A6A0-23BE29E9D691}"/>
+    <hyperlink ref="L42" r:id="rId142" xr:uid="{5058F1CC-A2A1-4682-93D1-9F212CA38D49}"/>
+    <hyperlink ref="L43" r:id="rId143" xr:uid="{78A29C5A-B38D-4480-9D00-419A29522F79}"/>
+    <hyperlink ref="L44" r:id="rId144" xr:uid="{8C138FAE-DE0F-4AE2-8DC0-AE6D1691EDA5}"/>
+    <hyperlink ref="L45" r:id="rId145" xr:uid="{27FD25C8-1BF4-4B08-A8C9-830AD37907F6}"/>
   </hyperlinks>
   <pageMargins left="0.25" right="0.17" top="0.5" bottom="0.25" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="29" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId142"/>
+  <pageSetup paperSize="9" scale="29" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId146"/>
 </worksheet>
 </file>
 
@@ -29830,7 +30244,7 @@
       </c>
       <c r="I1" s="176">
         <f ca="1">TODAY()</f>
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="J1" s="131"/>
       <c r="K1" s="197"/>
@@ -29901,81 +30315,81 @@
       <c r="Z3" s="159"/>
     </row>
     <row r="4" spans="1:26" s="5" customFormat="1" ht="35.1" customHeight="1" thickBot="1">
-      <c r="A4" s="366" t="s">
+      <c r="A4" s="348" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="366" t="s">
+      <c r="B4" s="348" t="s">
         <v>515</v>
       </c>
-      <c r="C4" s="362" t="s">
+      <c r="C4" s="414" t="s">
         <v>45</v>
       </c>
-      <c r="D4" s="356" t="s">
+      <c r="D4" s="369" t="s">
         <v>46</v>
       </c>
       <c r="E4" s="437" t="s">
         <v>47</v>
       </c>
-      <c r="F4" s="356" t="s">
+      <c r="F4" s="369" t="s">
         <v>4</v>
       </c>
       <c r="G4" s="439" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="404" t="s">
+      <c r="H4" s="366" t="s">
         <v>48</v>
       </c>
       <c r="I4" s="441" t="s">
         <v>49</v>
       </c>
-      <c r="J4" s="356" t="s">
+      <c r="J4" s="369" t="s">
         <v>78</v>
       </c>
-      <c r="K4" s="404" t="s">
+      <c r="K4" s="366" t="s">
         <v>80</v>
       </c>
-      <c r="L4" s="408" t="s">
+      <c r="L4" s="368" t="s">
         <v>53</v>
       </c>
-      <c r="M4" s="407"/>
-      <c r="N4" s="408" t="s">
+      <c r="M4" s="365"/>
+      <c r="N4" s="368" t="s">
         <v>55</v>
       </c>
-      <c r="O4" s="407"/>
-      <c r="P4" s="408" t="s">
+      <c r="O4" s="365"/>
+      <c r="P4" s="368" t="s">
         <v>72</v>
       </c>
-      <c r="Q4" s="407"/>
-      <c r="R4" s="406" t="s">
+      <c r="Q4" s="365"/>
+      <c r="R4" s="364" t="s">
         <v>53</v>
       </c>
-      <c r="S4" s="406"/>
-      <c r="T4" s="407"/>
-      <c r="U4" s="408" t="s">
+      <c r="S4" s="364"/>
+      <c r="T4" s="365"/>
+      <c r="U4" s="368" t="s">
         <v>55</v>
       </c>
-      <c r="V4" s="406"/>
-      <c r="W4" s="406"/>
-      <c r="X4" s="350" t="s">
+      <c r="V4" s="364"/>
+      <c r="W4" s="364"/>
+      <c r="X4" s="371" t="s">
         <v>72</v>
       </c>
-      <c r="Y4" s="412"/>
-      <c r="Z4" s="407" t="s">
+      <c r="Y4" s="372"/>
+      <c r="Z4" s="365" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="72" customHeight="1">
-      <c r="A5" s="367"/>
-      <c r="B5" s="367"/>
-      <c r="C5" s="363"/>
-      <c r="D5" s="357"/>
+      <c r="A5" s="349"/>
+      <c r="B5" s="349"/>
+      <c r="C5" s="415"/>
+      <c r="D5" s="370"/>
       <c r="E5" s="438"/>
-      <c r="F5" s="357"/>
+      <c r="F5" s="370"/>
       <c r="G5" s="440"/>
-      <c r="H5" s="405"/>
+      <c r="H5" s="367"/>
       <c r="I5" s="442"/>
-      <c r="J5" s="357"/>
-      <c r="K5" s="405"/>
+      <c r="J5" s="370"/>
+      <c r="K5" s="367"/>
       <c r="L5" s="79" t="s">
         <v>52</v>
       </c>
@@ -30018,7 +30432,7 @@
       <c r="Y5" s="260" t="s">
         <v>114</v>
       </c>
-      <c r="Z5" s="403"/>
+      <c r="Z5" s="416"/>
     </row>
     <row r="6" spans="1:26" ht="15" customHeight="1" thickBot="1">
       <c r="A6" s="78"/>
@@ -32575,11 +32989,11 @@
       <c r="H39" s="138"/>
       <c r="I39" s="164">
         <f t="shared" ca="1" si="9"/>
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="J39" s="47">
         <f t="shared" ca="1" si="10"/>
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="K39" s="164"/>
       <c r="L39" s="40"/>
@@ -34981,11 +35395,11 @@
       </c>
       <c r="I70" s="164">
         <f t="shared" ref="I70:I78" ca="1" si="14">IF(ISBLANK($V70),_xlfn.DAYS($I$1,$T70),_xlfn.DAYS($V70,$T70))</f>
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J70" s="47">
         <f t="shared" ref="J70:J78" ca="1" si="15">IF(($I70-21)&gt;0,$I70-21,0)</f>
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K70" s="164"/>
       <c r="L70" s="40"/>
@@ -36939,11 +37353,11 @@
       <c r="H97" s="138"/>
       <c r="I97" s="164">
         <f t="shared" ca="1" si="24"/>
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J97" s="47">
         <f t="shared" ca="1" si="25"/>
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="K97" s="164"/>
       <c r="L97" s="40" t="s">
@@ -38059,11 +38473,11 @@
       <c r="H112" s="138"/>
       <c r="I112" s="164">
         <f t="shared" ca="1" si="24"/>
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="J112" s="47">
         <f t="shared" ca="1" si="25"/>
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="K112" s="164" t="s">
         <v>13</v>
@@ -38126,11 +38540,11 @@
       </c>
       <c r="I113" s="164">
         <f t="shared" ca="1" si="24"/>
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="J113" s="47">
         <f t="shared" ca="1" si="25"/>
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K113" s="164"/>
       <c r="L113" s="40" t="s">
@@ -38262,11 +38676,11 @@
       <c r="H115" s="138"/>
       <c r="I115" s="164">
         <f t="shared" ca="1" si="24"/>
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="J115" s="47">
         <f t="shared" ca="1" si="25"/>
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K115" s="164"/>
       <c r="L115" s="40" t="s">
@@ -39142,11 +39556,11 @@
         <v>6</v>
       </c>
       <c r="I128" s="164">
-        <f t="shared" ca="1" si="24"/>
-        <v>6</v>
+        <f t="shared" si="24"/>
+        <v>8</v>
       </c>
       <c r="J128" s="47">
-        <f t="shared" ca="1" si="25"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="K128" s="164"/>
@@ -39154,7 +39568,9 @@
         <v>8</v>
       </c>
       <c r="M128" s="41"/>
-      <c r="N128" s="40"/>
+      <c r="N128" s="40" t="s">
+        <v>8</v>
+      </c>
       <c r="O128" s="41"/>
       <c r="P128" s="40"/>
       <c r="Q128" s="154"/>
@@ -39167,8 +39583,12 @@
       <c r="T128" s="188">
         <v>46309</v>
       </c>
-      <c r="U128" s="29"/>
-      <c r="V128" s="211"/>
+      <c r="U128" s="29">
+        <v>46316</v>
+      </c>
+      <c r="V128" s="211">
+        <v>46317</v>
+      </c>
       <c r="W128" s="235" t="s">
         <v>240</v>
       </c>
@@ -39206,7 +39626,7 @@
       <c r="H129" s="138"/>
       <c r="I129" s="164">
         <f t="shared" ca="1" si="24"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J129" s="47">
         <f t="shared" ca="1" si="25"/>
@@ -39304,22 +39724,22 @@
       <c r="E133" s="429"/>
       <c r="F133" s="46"/>
       <c r="G133" s="68"/>
-      <c r="H133" s="377" t="s">
+      <c r="H133" s="356" t="s">
         <v>14</v>
       </c>
-      <c r="I133" s="378"/>
-      <c r="J133" s="378"/>
-      <c r="K133" s="378"/>
-      <c r="L133" s="378"/>
-      <c r="M133" s="379"/>
-      <c r="N133" s="348" t="s">
+      <c r="I133" s="357"/>
+      <c r="J133" s="357"/>
+      <c r="K133" s="357"/>
+      <c r="L133" s="357"/>
+      <c r="M133" s="358"/>
+      <c r="N133" s="362" t="s">
         <v>7</v>
       </c>
-      <c r="O133" s="349"/>
-      <c r="P133" s="348" t="s">
+      <c r="O133" s="363"/>
+      <c r="P133" s="362" t="s">
         <v>110</v>
       </c>
-      <c r="Q133" s="349"/>
+      <c r="Q133" s="363"/>
       <c r="R133" s="1"/>
       <c r="S133" s="1"/>
       <c r="T133" s="140"/>
@@ -39350,7 +39770,7 @@
       </c>
       <c r="M134" s="104">
         <f ca="1">SUM($M$135:$M$137)</f>
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="N134" s="118" t="s">
         <v>15</v>
@@ -39375,7 +39795,7 @@
       <c r="Y134" s="11"/>
     </row>
     <row r="135" spans="1:26">
-      <c r="C135" s="386" t="s">
+      <c r="C135" s="394" t="s">
         <v>6</v>
       </c>
       <c r="D135" s="435" t="s">
@@ -39392,7 +39812,7 @@
       <c r="K135" s="434"/>
       <c r="L135" s="122">
         <f t="shared" ref="L135:L137" ca="1" si="61">M135/$M$134</f>
-        <v>0.8359375</v>
+        <v>0.84251968503937003</v>
       </c>
       <c r="M135" s="123">
         <f>COUNTIF($H$7:$H$131,"RFCS")</f>
@@ -39423,28 +39843,28 @@
       <c r="Y135" s="11"/>
     </row>
     <row r="136" spans="1:26">
-      <c r="C136" s="386"/>
+      <c r="C136" s="394"/>
       <c r="D136" s="435"/>
       <c r="E136" s="436"/>
       <c r="F136" s="72"/>
       <c r="G136" s="6"/>
-      <c r="H136" s="383" t="s">
+      <c r="H136" s="388" t="s">
         <v>70</v>
       </c>
-      <c r="I136" s="384"/>
-      <c r="J136" s="384"/>
-      <c r="K136" s="385"/>
+      <c r="I136" s="389"/>
+      <c r="J136" s="389"/>
+      <c r="K136" s="390"/>
       <c r="L136" s="124">
         <f t="shared" ca="1" si="61"/>
-        <v>5.46875E-2</v>
+        <v>4.7244094488188976E-2</v>
       </c>
       <c r="M136" s="125">
         <f ca="1">SUM(N136:O136)</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N136" s="98">
         <f ca="1">COUNTIFS($I$7:$I$131,"&lt;=21",$U$7:$U$131,"",$K$7:$K$131,"&lt;&gt;X")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O136" s="50">
         <f ca="1">COUNTIFS($I$7:$I$131,"&gt;21",$U$7:$U$131,"",$K$7:$K$131,"&lt;&gt;X")</f>
@@ -39469,22 +39889,22 @@
       <c r="Y136" s="11"/>
     </row>
     <row r="137" spans="1:26" ht="16.5" thickBot="1">
-      <c r="C137" s="386" t="s">
+      <c r="C137" s="394" t="s">
         <v>75</v>
       </c>
-      <c r="D137" s="388" t="s">
+      <c r="D137" s="350" t="s">
         <v>76</v>
       </c>
-      <c r="E137" s="389"/>
-      <c r="H137" s="400" t="s">
+      <c r="E137" s="351"/>
+      <c r="H137" s="391" t="s">
         <v>71</v>
       </c>
-      <c r="I137" s="401"/>
-      <c r="J137" s="401"/>
-      <c r="K137" s="402"/>
+      <c r="I137" s="392"/>
+      <c r="J137" s="392"/>
+      <c r="K137" s="393"/>
       <c r="L137" s="126">
         <f t="shared" ca="1" si="61"/>
-        <v>0.109375</v>
+        <v>0.11023622047244094</v>
       </c>
       <c r="M137" s="116">
         <f>COUNTIFS($K$7:$K$131,"X")</f>
@@ -39496,16 +39916,16 @@
       <c r="Q137" s="224"/>
     </row>
     <row r="138" spans="1:26" ht="16.5" thickBot="1">
-      <c r="C138" s="387"/>
-      <c r="D138" s="390"/>
-      <c r="E138" s="391"/>
+      <c r="C138" s="395"/>
+      <c r="D138" s="352"/>
+      <c r="E138" s="353"/>
     </row>
     <row r="140" spans="1:26">
-      <c r="C140" s="370" t="s">
+      <c r="C140" s="378" t="s">
         <v>41</v>
       </c>
-      <c r="D140" s="370"/>
-      <c r="E140" s="370"/>
+      <c r="D140" s="378"/>
+      <c r="E140" s="378"/>
     </row>
     <row r="141" spans="1:26">
       <c r="C141" s="169" t="s">
@@ -40070,9 +40490,10 @@
     <hyperlink ref="N126" r:id="rId478" xr:uid="{E0E300E4-A703-49B0-A1DF-0EC9F6DC050D}"/>
     <hyperlink ref="N127" r:id="rId479" xr:uid="{984FC4EC-B838-4F05-998C-F6897E6C0896}"/>
     <hyperlink ref="N125" r:id="rId480" xr:uid="{ECB0E570-ED5C-4126-9B31-6711B56E14D0}"/>
+    <hyperlink ref="N128" r:id="rId481" xr:uid="{1CA6C02A-5CE8-4BB3-A561-833347DA6DD6}"/>
   </hyperlinks>
   <pageMargins left="0.25" right="0.17" top="0.5" bottom="0.25" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="28" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId481"/>
+  <pageSetup paperSize="9" scale="28" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId482"/>
 </worksheet>
 </file>
 
@@ -40157,19 +40578,19 @@
       <c r="S3" s="281"/>
     </row>
     <row r="4" spans="1:25" ht="36" customHeight="1" thickBot="1">
-      <c r="A4" s="354" t="s">
+      <c r="A4" s="408" t="s">
         <v>123</v>
       </c>
-      <c r="B4" s="404" t="s">
+      <c r="B4" s="366" t="s">
         <v>45</v>
       </c>
-      <c r="C4" s="404" t="s">
+      <c r="C4" s="366" t="s">
         <v>95</v>
       </c>
-      <c r="D4" s="404" t="s">
+      <c r="D4" s="366" t="s">
         <v>46</v>
       </c>
-      <c r="E4" s="356" t="s">
+      <c r="E4" s="369" t="s">
         <v>4</v>
       </c>
       <c r="F4" s="449" t="s">
@@ -40198,12 +40619,12 @@
       <c r="S4" s="448"/>
     </row>
     <row r="5" spans="1:25" ht="78.75">
-      <c r="A5" s="355"/>
-      <c r="B5" s="405"/>
-      <c r="C5" s="405"/>
-      <c r="D5" s="405"/>
-      <c r="E5" s="357"/>
-      <c r="F5" s="361"/>
+      <c r="A5" s="409"/>
+      <c r="B5" s="367"/>
+      <c r="C5" s="367"/>
+      <c r="D5" s="367"/>
+      <c r="E5" s="370"/>
+      <c r="F5" s="411"/>
       <c r="G5" s="283" t="s">
         <v>56</v>
       </c>
@@ -40380,18 +40801,18 @@
         <v/>
       </c>
       <c r="R7" s="13" t="str" cm="1">
-        <f t="array" aca="1" ref="R7:R26" ca="1">_xlfn.LET(
+        <f t="array" ref="R7:R26">_xlfn.LET(
 _xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(D7),RFA!$E:$E,RFA!$AC:$AC,""),
 IF(_xlpm.x=0,"",_xlpm.x)
 )</f>
         <v>Not submit yet</v>
       </c>
       <c r="S7" s="279" cm="1">
-        <f t="array" aca="1" ref="S7:S26" ca="1">_xlfn.LET(
+        <f t="array" ref="S7:S26">_xlfn.LET(
 _xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(D7),RFA!$E:$E,RFA!$AD:$AD,""),
 IF(_xlpm.x=0,"",_xlpm.x)
 )</f>
-        <v>852</v>
+        <v>853</v>
       </c>
     </row>
     <row r="8" spans="1:25" ht="45">
@@ -40447,12 +40868,10 @@
         <v/>
       </c>
       <c r="R8" s="13" t="str">
-        <f ca="1"/>
         <v>Not submit yet</v>
       </c>
       <c r="S8" s="279">
-        <f ca="1"/>
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="Y8" t="s">
         <v>125</v>
@@ -40512,12 +40931,10 @@
         <v/>
       </c>
       <c r="R9" s="13" t="str">
-        <f ca="1"/>
         <v>Not submit yet</v>
       </c>
       <c r="S9" s="279">
-        <f ca="1"/>
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="10" spans="1:25" ht="45">
@@ -40573,12 +40990,10 @@
         <v/>
       </c>
       <c r="R10" s="13" t="str">
-        <f ca="1"/>
         <v>Not submit yet</v>
       </c>
       <c r="S10" s="279">
-        <f ca="1"/>
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="11" spans="1:25" ht="75">
@@ -40634,12 +41049,10 @@
         <v/>
       </c>
       <c r="R11" s="13" t="str">
-        <f ca="1"/>
         <v>Not submit yet</v>
       </c>
       <c r="S11" s="279">
-        <f ca="1"/>
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="12" spans="1:25" ht="45">
@@ -40695,12 +41108,10 @@
         <v/>
       </c>
       <c r="R12" s="13" t="str">
-        <f ca="1"/>
         <v>Not submit yet</v>
       </c>
       <c r="S12" s="279">
-        <f ca="1"/>
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="13" spans="1:25" ht="45">
@@ -40756,12 +41167,10 @@
         <v/>
       </c>
       <c r="R13" s="13" t="str">
-        <f ca="1"/>
         <v>Not submit yet</v>
       </c>
       <c r="S13" s="279">
-        <f ca="1"/>
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="14" spans="1:25" ht="45">
@@ -40817,12 +41226,10 @@
         <v/>
       </c>
       <c r="R14" s="13" t="str">
-        <f ca="1"/>
         <v>Not submit yet</v>
       </c>
       <c r="S14" s="279">
-        <f ca="1"/>
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15" spans="1:25" ht="60">
@@ -40878,11 +41285,9 @@
         <v/>
       </c>
       <c r="R15" s="13" t="str">
-        <f ca="1"/>
         <v/>
       </c>
       <c r="S15" s="279" t="str">
-        <f ca="1"/>
         <v/>
       </c>
     </row>
@@ -40939,11 +41344,9 @@
         <v/>
       </c>
       <c r="R16" s="13" t="str">
-        <f ca="1"/>
         <v/>
       </c>
       <c r="S16" s="279" t="str">
-        <f ca="1"/>
         <v/>
       </c>
     </row>
@@ -41000,11 +41403,9 @@
         <v/>
       </c>
       <c r="R17" s="13" t="str">
-        <f ca="1"/>
         <v/>
       </c>
       <c r="S17" s="279" t="str">
-        <f ca="1"/>
         <v/>
       </c>
     </row>
@@ -41061,11 +41462,9 @@
         <v/>
       </c>
       <c r="R18" s="13" t="str">
-        <f ca="1"/>
         <v/>
       </c>
       <c r="S18" s="279" t="str">
-        <f ca="1"/>
         <v/>
       </c>
     </row>
@@ -41126,11 +41525,9 @@
         <v/>
       </c>
       <c r="R19" s="13" t="str">
-        <f ca="1"/>
         <v/>
       </c>
       <c r="S19" s="279" t="str">
-        <f ca="1"/>
         <v/>
       </c>
     </row>
@@ -41187,11 +41584,9 @@
         <v>46312</v>
       </c>
       <c r="R20" s="13" t="str">
-        <f ca="1"/>
         <v/>
       </c>
       <c r="S20" s="279" t="str">
-        <f ca="1"/>
         <v/>
       </c>
     </row>
@@ -41248,11 +41643,9 @@
         <v/>
       </c>
       <c r="R21" s="13" t="str">
-        <f ca="1"/>
         <v/>
       </c>
       <c r="S21" s="279" t="str">
-        <f ca="1"/>
         <v/>
       </c>
     </row>
@@ -41309,11 +41702,9 @@
         <v/>
       </c>
       <c r="R22" s="13" t="str">
-        <f ca="1"/>
         <v/>
       </c>
       <c r="S22" s="279" t="str">
-        <f ca="1"/>
         <v/>
       </c>
     </row>
@@ -41370,11 +41761,9 @@
         <v/>
       </c>
       <c r="R23" s="13" t="str">
-        <f ca="1"/>
         <v/>
       </c>
       <c r="S23" s="279" t="str">
-        <f ca="1"/>
         <v/>
       </c>
     </row>
@@ -41431,15 +41820,13 @@
         <v/>
       </c>
       <c r="R24" s="13" t="str">
-        <f ca="1"/>
         <v/>
       </c>
       <c r="S24" s="279" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="25" spans="1:19">
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="1:19" ht="30">
       <c r="A25" s="13">
         <v>19</v>
       </c>
@@ -41470,11 +41857,11 @@
       <c r="J25" s="264" t="str">
         <v>C</v>
       </c>
-      <c r="K25" s="270" t="str">
-        <v/>
-      </c>
-      <c r="L25" s="264" t="str">
-        <v/>
+      <c r="K25" s="270">
+        <v>46314</v>
+      </c>
+      <c r="L25" s="264">
+        <v>46317</v>
       </c>
       <c r="M25" s="264" t="str">
         <v/>
@@ -41485,22 +41872,20 @@
       <c r="O25" s="264" t="str">
         <v/>
       </c>
-      <c r="P25" s="264" t="str">
-        <v/>
+      <c r="P25" s="264">
+        <v>46324</v>
       </c>
       <c r="Q25" s="270" t="str">
         <v/>
       </c>
       <c r="R25" s="13" t="str">
-        <f ca="1"/>
         <v/>
       </c>
       <c r="S25" s="279" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="26" spans="1:19">
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="1:19" ht="45">
       <c r="A26" s="13">
         <v>20</v>
       </c>
@@ -41526,16 +41911,16 @@
         <v>46301</v>
       </c>
       <c r="I26" s="264">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="J26" s="264" t="str">
         <v>C</v>
       </c>
-      <c r="K26" s="270" t="str">
-        <v/>
-      </c>
-      <c r="L26" s="264" t="str">
-        <v/>
+      <c r="K26" s="270">
+        <v>46314</v>
+      </c>
+      <c r="L26" s="264">
+        <v>46317</v>
       </c>
       <c r="M26" s="264" t="str">
         <v/>
@@ -41546,18 +41931,16 @@
       <c r="O26" s="264" t="str">
         <v/>
       </c>
-      <c r="P26" s="264" t="str">
-        <v/>
+      <c r="P26" s="264">
+        <v>46324</v>
       </c>
       <c r="Q26" s="270" t="str">
         <v/>
       </c>
       <c r="R26" s="13" t="str">
-        <f ca="1"/>
         <v/>
       </c>
       <c r="S26" s="279" t="str">
-        <f ca="1"/>
         <v/>
       </c>
     </row>
@@ -41658,16 +42041,16 @@
       <c r="R3" s="281"/>
     </row>
     <row r="4" spans="1:18" ht="16.5" thickBot="1">
-      <c r="A4" s="354" t="s">
+      <c r="A4" s="408" t="s">
         <v>123</v>
       </c>
-      <c r="B4" s="404" t="s">
+      <c r="B4" s="366" t="s">
         <v>45</v>
       </c>
-      <c r="C4" s="404" t="s">
+      <c r="C4" s="366" t="s">
         <v>46</v>
       </c>
-      <c r="D4" s="406" t="s">
+      <c r="D4" s="364" t="s">
         <v>4</v>
       </c>
       <c r="E4" s="449" t="s">
@@ -41696,11 +42079,11 @@
       <c r="R4" s="448"/>
     </row>
     <row r="5" spans="1:18" ht="78.75">
-      <c r="A5" s="355"/>
-      <c r="B5" s="405"/>
-      <c r="C5" s="405"/>
+      <c r="A5" s="409"/>
+      <c r="B5" s="367"/>
+      <c r="C5" s="367"/>
       <c r="D5" s="440"/>
-      <c r="E5" s="357"/>
+      <c r="E5" s="370"/>
       <c r="F5" s="283" t="s">
         <v>56</v>
       </c>
@@ -41763,11 +42146,11 @@
     </row>
     <row r="7" spans="1:18" ht="75">
       <c r="A7" s="13" cm="1">
-        <f t="array" ref="A7:A17">IF(_xlfn.ANCHORARRAY(C7)="","",_xlfn.SEQUENCE(ROWS(_xlfn.ANCHORARRAY(C7))))</f>
+        <f t="array" ref="A7:A14">IF(_xlfn.ANCHORARRAY(C7)="","",_xlfn.SEQUENCE(ROWS(_xlfn.ANCHORARRAY(C7))))</f>
         <v>1</v>
       </c>
       <c r="B7" s="302" t="str" cm="1">
-        <f t="array" ref="B7:B17">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$C:$C,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
+        <f t="array" ref="B7:B14">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$C:$C,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
         <v>FAS
 SCS
 SCN
@@ -41775,68 +42158,68 @@
 PAS</v>
       </c>
       <c r="C7" s="282" t="str" cm="1">
-        <f t="array" ref="C7:C17">_xlfn._xlws.FILTER('RFA-SDS'!$D$5:$D$4870,'RFA-SDS'!$AI$5:$AI$4870="YES","")</f>
+        <f t="array" ref="C7:C14">_xlfn._xlws.FILTER('RFA-SDS'!$D$5:$D$4874,'RFA-SDS'!$AI$5:$AI$4874="YES","")</f>
         <v>LTIA-5.10-VIETUR-80000-RFA-SDS-0214</v>
       </c>
       <c r="D7" s="303" t="str" cm="1">
-        <f t="array" ref="D7:D17">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$F:$F,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
+        <f t="array" ref="D7:D14">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$F:$F,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
         <v xml:space="preserve">Construction design drawing of  ICT system – part.1: ICT systems for FLB </v>
       </c>
       <c r="E7" s="303" t="str" cm="1">
-        <f t="array" ref="E7:E17">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$G:$G,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
+        <f t="array" ref="E7:E14">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$G:$G,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
         <v>Bản vẽ TKTC cho hệ thống ICT – phần 1 – Hệ thống ICT cho FLB</v>
       </c>
       <c r="F7" s="270" cm="1">
-        <f t="array" ref="F7:F17">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$R:$R,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
+        <f t="array" ref="F7:F14">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$R:$R,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
         <v>45673</v>
       </c>
       <c r="G7" s="270" cm="1">
-        <f t="array" ref="G7:G17">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$S:$S,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
+        <f t="array" ref="G7:G14">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$S:$S,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
         <v>45673</v>
       </c>
       <c r="H7" s="264" cm="1">
-        <f t="array" ref="H7:H17">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$T:$T,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
+        <f t="array" ref="H7:H14">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$T:$T,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
         <v>45699</v>
       </c>
       <c r="I7" s="264" t="str" cm="1">
-        <f t="array" ref="I7:I17">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$H:$H,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
+        <f t="array" ref="I7:I14">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$H:$H,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
         <v>B</v>
       </c>
       <c r="J7" s="270" cm="1">
-        <f t="array" ref="J7:J17">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$U:$U,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
+        <f t="array" ref="J7:J14">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$U:$U,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
         <v>45716</v>
       </c>
       <c r="K7" s="264" cm="1">
-        <f t="array" ref="K7:K17">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$V:$V,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
+        <f t="array" ref="K7:K14">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$V:$V,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
         <v>45741</v>
       </c>
       <c r="L7" s="264" t="str" cm="1">
-        <f t="array" ref="L7:L17">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$Q:$Q,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
+        <f t="array" ref="L7:L14">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$Q:$Q,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
         <v>B</v>
       </c>
       <c r="M7" s="270" cm="1">
-        <f t="array" ref="M7:M17">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$X:$X,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
+        <f t="array" ref="M7:M14">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$X:$X,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
         <v>45756</v>
       </c>
       <c r="N7" s="264" cm="1">
-        <f t="array" ref="N7:N17">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$Y:$Y,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
+        <f t="array" ref="N7:N14">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$Y:$Y,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
         <v>45756</v>
       </c>
       <c r="O7" s="264" cm="1">
-        <f t="array" ref="O7:O17">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$Z:$Z,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
+        <f t="array" ref="O7:O14">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$Z:$Z,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
         <v>45763</v>
       </c>
       <c r="P7" s="270" t="str" cm="1">
-        <f t="array" ref="P7:P17">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$AA:$AA,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
+        <f t="array" ref="P7:P14">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$AA:$AA,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
         <v/>
       </c>
       <c r="Q7" s="13" t="str" cm="1">
-        <f t="array" aca="1" ref="Q7:Q17" ca="1">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$AB:$AB,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
+        <f t="array" ref="Q7:Q14">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$AB:$AB,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
         <v>Not submit yet</v>
       </c>
       <c r="R7" s="279" cm="1">
-        <f t="array" aca="1" ref="R7:R17" ca="1">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$AC:$AC,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
-        <v>552</v>
+        <f t="array" ref="R7:R14">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$AC:$AC,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
+        <v>554</v>
       </c>
     </row>
     <row r="8" spans="1:18" ht="30">
@@ -41889,12 +42272,10 @@
         <v/>
       </c>
       <c r="Q8" s="13" t="str">
-        <f ca="1"/>
         <v>Not submit yet</v>
       </c>
       <c r="R8" s="279">
-        <f ca="1"/>
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="45">
@@ -41947,12 +42328,10 @@
         <v/>
       </c>
       <c r="Q9" s="13" t="str">
-        <f ca="1"/>
         <v>Not submit yet</v>
       </c>
       <c r="R9" s="279">
-        <f ca="1"/>
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="105">
@@ -41960,35 +42339,35 @@
         <v>4</v>
       </c>
       <c r="B10" s="302" t="str">
-        <v>SCN
-PAS</v>
+        <v>FAS
+BHS</v>
       </c>
       <c r="C10" s="282" t="str">
-        <v>LTIA-5.10-VIETUR-80000-RFA-SDS-0122A</v>
+        <v>LTIA-5.10-VIETUR-80000-RFA-SDS-0350</v>
       </c>
       <c r="D10" s="303" t="str">
-        <v>Construction design drawing of ICT system – part.1: ICT systems for 1F Level (Re-submission for attachment): 2. Structure Cable Network-level 1 (attachment 02). &amp; 5. Public Address Systems -level 1 (attachment 05).</v>
+        <v xml:space="preserve">Construction design drawing of  ICT system – part.1: ICT systems for FAS Under BHS Flatform. </v>
       </c>
       <c r="E10" s="303" t="str">
-        <v>Bản vẽ TKTC cho hệ thống ICT – phần 1 – Hệ thống ICT cho tầng 1 (Trình cho phần đính kèm số: 2. Hệ thống Mạng Cáp – tầng 1 (đính kèm 02) &amp; 5. Hệ Thống Phát Thanh Công Cộng - tầng 1 (đính kèm 05)</v>
+        <v>Bản vẽ TKTC cho hệ thống ICT – phần 1 – Hệ thống ICT cho Hệ Thống báo cháy dưới sàn thép BHS</v>
       </c>
       <c r="F10" s="270">
-        <v>45850</v>
+        <v>45880</v>
       </c>
       <c r="G10" s="270">
-        <v>45850</v>
+        <v>45880</v>
       </c>
       <c r="H10" s="264">
-        <v>45855</v>
+        <v>45881</v>
       </c>
       <c r="I10" s="264" t="str">
         <v>B</v>
       </c>
       <c r="J10" s="270">
-        <v>45862</v>
+        <v>45891</v>
       </c>
       <c r="K10" s="264">
-        <v>45870</v>
+        <v>45908</v>
       </c>
       <c r="L10" s="264" t="str">
         <v>B</v>
@@ -42006,12 +42385,10 @@
         <v/>
       </c>
       <c r="Q10" s="13" t="str">
-        <f ca="1"/>
         <v>Not submit yet</v>
       </c>
       <c r="R10" s="279">
-        <f ca="1"/>
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="45">
@@ -42019,40 +42396,40 @@
         <v>5</v>
       </c>
       <c r="B11" s="302" t="str">
-        <v>SCN</v>
+        <v>FAS</v>
       </c>
       <c r="C11" s="282" t="str">
-        <v>LTIA-5.10-VIETUR-80000-RFA-SDS-0080A</v>
+        <v>LTIA-5.10-VIETUR-80000-RFA-SDS-0140B</v>
       </c>
       <c r="D11" s="303" t="str">
-        <v>Construction design drawing of  ICT system – part.4: ICT systems for PIT Level (Underground)</v>
+        <v>Construction design drawing of  ICT system – part.1: ICT systems for 2F Level (Re-submission for attachment) 5. Public addressable system-level 2 (attachment 5)</v>
       </c>
       <c r="E11" s="303" t="str">
-        <v>Bản vẽ TKTC cho hệ thống ICT – phần 4 – Hệ thống ICT cho tầng PIT (phần ngầm)</v>
+        <v>Bản vẽ TKTC cho hệ thống ICT – phần 1 – Hệ thống ICT cho tầng 2 (trình cho phần đính kèm số: 5. Hệ thống phát thanh công cộng - tầng 2 (đính kèm 5)</v>
       </c>
       <c r="F11" s="270">
-        <v>45861</v>
+        <v>45908</v>
       </c>
       <c r="G11" s="270">
-        <v>45861</v>
+        <v>45908</v>
       </c>
       <c r="H11" s="264">
-        <v>45866</v>
+        <v>45909</v>
       </c>
       <c r="I11" s="264" t="str">
         <v>B</v>
       </c>
       <c r="J11" s="270">
-        <v>45874</v>
+        <v>45873</v>
       </c>
       <c r="K11" s="264">
-        <v>45908</v>
+        <v>45917</v>
       </c>
       <c r="L11" s="264" t="str">
         <v>B</v>
       </c>
       <c r="M11" s="270">
-        <v>45954</v>
+        <v>46153</v>
       </c>
       <c r="N11" s="264">
         <v>45957</v>
@@ -42064,12 +42441,10 @@
         <v/>
       </c>
       <c r="Q11" s="13" t="str">
-        <f ca="1"/>
         <v>Not submit yet</v>
       </c>
       <c r="R11" s="279">
-        <f ca="1"/>
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="12" spans="1:18" ht="45">
@@ -42077,58 +42452,55 @@
         <v>6</v>
       </c>
       <c r="B12" s="302" t="str">
-        <v>FAS
-BHS</v>
+        <v>ACS</v>
       </c>
       <c r="C12" s="282" t="str">
-        <v>LTIA-5.10-VIETUR-80000-RFA-SDS-0350</v>
+        <v>LTIA-5.10-VIETUR-80000-RFA-SDS-0371</v>
       </c>
       <c r="D12" s="303" t="str">
-        <v xml:space="preserve">Construction design drawing of  ICT system – part.1: ICT systems for FAS Under BHS Flatform. </v>
+        <v xml:space="preserve">Construction design drawing of  ICT system – part.1: ICT systems for Duress Button Drawings. </v>
       </c>
       <c r="E12" s="303" t="str">
-        <v>Bản vẽ TKTC cho hệ thống ICT – phần 1 – Hệ thống ICT cho Hệ Thống báo cháy dưới sàn thép BHS</v>
+        <v>Bản vẽ TKTC cho hệ thống ICT – phần 1 – Hệ thống ICT cho hệ thống nút nhấn khẩn cấp.</v>
       </c>
       <c r="F12" s="270">
-        <v>45880</v>
+        <v>45930</v>
       </c>
       <c r="G12" s="270">
-        <v>45880</v>
+        <v>45930</v>
       </c>
       <c r="H12" s="264">
-        <v>45881</v>
+        <v>45932</v>
       </c>
       <c r="I12" s="264" t="str">
         <v>B</v>
       </c>
       <c r="J12" s="270">
-        <v>45891</v>
+        <v>45940</v>
       </c>
       <c r="K12" s="264">
-        <v>45908</v>
+        <v>45945</v>
       </c>
       <c r="L12" s="264" t="str">
         <v>B</v>
       </c>
       <c r="M12" s="270">
-        <v>45954</v>
+        <v>45978</v>
       </c>
       <c r="N12" s="264">
-        <v>45957</v>
+        <v>45979</v>
       </c>
       <c r="O12" s="264">
-        <v>45964</v>
+        <v>45986</v>
       </c>
       <c r="P12" s="270" t="str">
         <v/>
       </c>
       <c r="Q12" s="13" t="str">
-        <f ca="1"/>
         <v>Not submit yet</v>
       </c>
       <c r="R12" s="279">
-        <f ca="1"/>
-        <v>351</v>
+        <v>331</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="75">
@@ -42136,57 +42508,55 @@
         <v>7</v>
       </c>
       <c r="B13" s="302" t="str">
-        <v>FAS</v>
+        <v>PAS</v>
       </c>
       <c r="C13" s="282" t="str">
-        <v>LTIA-5.10-VIETUR-80000-RFA-SDS-0140B</v>
+        <v>LTIA-5.10-VIETUR-80000-RFA-SDS-0394</v>
       </c>
       <c r="D13" s="303" t="str">
-        <v>Construction design drawing of  ICT system – part.1: ICT systems for 2F Level (Re-submission for attachment) 5. Public addressable system-level 2 (attachment 5)</v>
+        <v>Construction design drawing of  ICT system – part.1: ICT systems for Schematic Diagram Public Address System (PAS)</v>
       </c>
       <c r="E13" s="303" t="str">
-        <v>Bản vẽ TKTC cho hệ thống ICT – phần 1 – Hệ thống ICT cho tầng 2 (trình cho phần đính kèm số: 5. Hệ thống phát thanh công cộng - tầng 2 (đính kèm 5)</v>
+        <v>Bản vẽ TKTC cho hệ thống ICT – phần 1 – Hệ thống ICT cho SDNL hệ thống Phát Thanh</v>
       </c>
       <c r="F13" s="270">
-        <v>45908</v>
+        <v>45965</v>
       </c>
       <c r="G13" s="270">
-        <v>45908</v>
+        <v>45965</v>
       </c>
       <c r="H13" s="264">
-        <v>45909</v>
+        <v>45966</v>
       </c>
       <c r="I13" s="264" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
       <c r="J13" s="270">
-        <v>45873</v>
+        <v>45979</v>
       </c>
       <c r="K13" s="264">
-        <v>45917</v>
+        <v>45994</v>
       </c>
       <c r="L13" s="264" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
       <c r="M13" s="270">
-        <v>46153</v>
+        <v>46146</v>
       </c>
       <c r="N13" s="264">
-        <v>45957</v>
+        <v>46136</v>
       </c>
       <c r="O13" s="264">
-        <v>45964</v>
-      </c>
-      <c r="P13" s="270" t="str">
-        <v/>
+        <v>46143</v>
+      </c>
+      <c r="P13" s="270">
+        <v>46268</v>
       </c>
       <c r="Q13" s="13" t="str">
-        <f ca="1"/>
-        <v>Not submit yet</v>
+        <v>Late Resubmission</v>
       </c>
       <c r="R13" s="279">
-        <f ca="1"/>
-        <v>351</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14" spans="1:18" ht="45">
@@ -42194,233 +42564,60 @@
         <v>8</v>
       </c>
       <c r="B14" s="302" t="str">
-        <v>ACS</v>
+        <v>PAS</v>
       </c>
       <c r="C14" s="282" t="str">
-        <v>LTIA-5.10-VIETUR-80000-RFA-SDS-0371</v>
+        <v>LTIA-5.10-VIETUR-80000-RFA-SDS-0160B</v>
       </c>
       <c r="D14" s="303" t="str">
-        <v xml:space="preserve">Construction design drawing of  ICT system – part.1: ICT systems for Duress Button Drawings. </v>
+        <v xml:space="preserve">Construction design drawing of  ICT system – part.1: ICT systems for GF Level </v>
       </c>
       <c r="E14" s="303" t="str">
-        <v>Bản vẽ TKTC cho hệ thống ICT – phần 1 – Hệ thống ICT cho hệ thống nút nhấn khẩn cấp.</v>
+        <v>Bản vẽ TKTC cho hệ thống ICT – phần 1 – Hệ thống ICT cho tầng GF</v>
       </c>
       <c r="F14" s="270">
-        <v>45930</v>
+        <v>45972</v>
       </c>
       <c r="G14" s="270">
-        <v>45930</v>
+        <v>45972</v>
       </c>
       <c r="H14" s="264">
-        <v>45932</v>
+        <v>45972</v>
       </c>
       <c r="I14" s="264" t="str">
         <v>B</v>
       </c>
       <c r="J14" s="270">
-        <v>45940</v>
+        <v>45982</v>
       </c>
       <c r="K14" s="264">
-        <v>45945</v>
+        <v>45982</v>
       </c>
       <c r="L14" s="264" t="str">
         <v>B</v>
       </c>
       <c r="M14" s="270">
-        <v>45978</v>
+        <v>45995</v>
       </c>
       <c r="N14" s="264">
-        <v>45979</v>
+        <v>45999</v>
       </c>
       <c r="O14" s="264">
-        <v>45986</v>
+        <v>46006</v>
       </c>
       <c r="P14" s="270" t="str">
         <v/>
       </c>
       <c r="Q14" s="13" t="str">
-        <f ca="1"/>
         <v>Not submit yet</v>
       </c>
       <c r="R14" s="279">
-        <f ca="1"/>
-        <v>329</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" ht="45">
-      <c r="A15" s="13">
-        <v>9</v>
-      </c>
-      <c r="B15" s="302" t="str">
-        <v>FAS</v>
-      </c>
-      <c r="C15" s="282" t="str">
-        <v>LTIA-5.10-VIETUR-80000-RFA-SDS-0197B</v>
-      </c>
-      <c r="D15" s="303" t="str">
-        <v xml:space="preserve">Construction design drawing of  ICT system – part.1: ICT systems for 3F Level </v>
-      </c>
-      <c r="E15" s="303" t="str">
-        <v>Bản vẽ TKTC cho hệ thống ICT – phần 1 – Hệ thống ICT cho tầng 3F</v>
-      </c>
-      <c r="F15" s="270">
-        <v>45959</v>
-      </c>
-      <c r="G15" s="270">
-        <v>45959</v>
-      </c>
-      <c r="H15" s="264">
-        <v>45961</v>
-      </c>
-      <c r="I15" s="264" t="str">
-        <v>B</v>
-      </c>
-      <c r="J15" s="270">
-        <v>45945</v>
-      </c>
-      <c r="K15" s="264">
-        <v>45980</v>
-      </c>
-      <c r="L15" s="264" t="str">
-        <v>B</v>
-      </c>
-      <c r="M15" s="270">
-        <v>45995</v>
-      </c>
-      <c r="N15" s="264">
-        <v>45999</v>
-      </c>
-      <c r="O15" s="264">
-        <v>46006</v>
-      </c>
-      <c r="P15" s="270" t="str">
-        <v/>
-      </c>
-      <c r="Q15" s="13" t="str">
-        <f ca="1"/>
-        <v>Not submit yet</v>
-      </c>
-      <c r="R15" s="279">
-        <f ca="1"/>
-        <v>309</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" ht="60">
-      <c r="A16" s="13">
-        <v>10</v>
-      </c>
-      <c r="B16" s="302" t="str">
-        <v>PAS</v>
-      </c>
-      <c r="C16" s="282" t="str">
-        <v>LTIA-5.10-VIETUR-80000-RFA-SDS-0394</v>
-      </c>
-      <c r="D16" s="303" t="str">
-        <v>Construction design drawing of  ICT system – part.1: ICT systems for Schematic Diagram Public Address System (PAS)</v>
-      </c>
-      <c r="E16" s="303" t="str">
-        <v>Bản vẽ TKTC cho hệ thống ICT – phần 1 – Hệ thống ICT cho SDNL hệ thống Phát Thanh</v>
-      </c>
-      <c r="F16" s="270">
-        <v>45965</v>
-      </c>
-      <c r="G16" s="270">
-        <v>45965</v>
-      </c>
-      <c r="H16" s="264">
-        <v>45966</v>
-      </c>
-      <c r="I16" s="264" t="str">
-        <v>C</v>
-      </c>
-      <c r="J16" s="270">
-        <v>45979</v>
-      </c>
-      <c r="K16" s="264">
-        <v>45994</v>
-      </c>
-      <c r="L16" s="264" t="str">
-        <v>C</v>
-      </c>
-      <c r="M16" s="270">
-        <v>46146</v>
-      </c>
-      <c r="N16" s="264">
-        <v>46136</v>
-      </c>
-      <c r="O16" s="264">
-        <v>46143</v>
-      </c>
-      <c r="P16" s="270">
-        <v>46268</v>
-      </c>
-      <c r="Q16" s="13" t="str">
-        <f ca="1"/>
-        <v>Late Resubmission</v>
-      </c>
-      <c r="R16" s="279">
-        <f ca="1"/>
-        <v>125</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" ht="45">
-      <c r="A17" s="13">
-        <v>11</v>
-      </c>
-      <c r="B17" s="302" t="str">
-        <v>PAS</v>
-      </c>
-      <c r="C17" s="282" t="str">
-        <v>LTIA-5.10-VIETUR-80000-RFA-SDS-0160B</v>
-      </c>
-      <c r="D17" s="303" t="str">
-        <v xml:space="preserve">Construction design drawing of  ICT system – part.1: ICT systems for GF Level </v>
-      </c>
-      <c r="E17" s="303" t="str">
-        <v>Bản vẽ TKTC cho hệ thống ICT – phần 1 – Hệ thống ICT cho tầng GF</v>
-      </c>
-      <c r="F17" s="270">
-        <v>45972</v>
-      </c>
-      <c r="G17" s="270">
-        <v>45972</v>
-      </c>
-      <c r="H17" s="264">
-        <v>45972</v>
-      </c>
-      <c r="I17" s="264" t="str">
-        <v>B</v>
-      </c>
-      <c r="J17" s="270">
-        <v>45982</v>
-      </c>
-      <c r="K17" s="264">
-        <v>45982</v>
-      </c>
-      <c r="L17" s="264" t="str">
-        <v>B</v>
-      </c>
-      <c r="M17" s="270">
-        <v>45995</v>
-      </c>
-      <c r="N17" s="264">
-        <v>45999</v>
-      </c>
-      <c r="O17" s="264">
-        <v>46006</v>
-      </c>
-      <c r="P17" s="270" t="str">
-        <v/>
-      </c>
-      <c r="Q17" s="13" t="str">
-        <f ca="1"/>
-        <v>Not submit yet</v>
-      </c>
-      <c r="R17" s="279">
-        <f ca="1"/>
-        <v>309</v>
-      </c>
-    </row>
+        <v>311</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" ht="45"/>
+    <row r="16" spans="1:18" ht="60"/>
+    <row r="17" ht="45"/>
   </sheetData>
   <autoFilter ref="A6:R6" xr:uid="{75733AF3-96C4-423A-BD99-1E08B3C66916}"/>
   <mergeCells count="9">
@@ -42475,32 +42672,32 @@
     </row>
     <row r="3" spans="1:4" ht="15.75">
       <c r="A3" s="319">
-        <f ca="1">MAX('Need ReSub (RFA)'!S7:S76)</f>
-        <v>852</v>
+        <f>MAX('Need ReSub (RFA)'!S7:S76)</f>
+        <v>853</v>
       </c>
       <c r="B3" s="319">
-        <f ca="1">AVERAGEIF('Need ReSub (RFA)'!S7:S76,"&lt;&gt;0")</f>
-        <v>460.25</v>
+        <f>AVERAGEIF('Need ReSub (RFA)'!S7:S76,"&lt;&gt;0")</f>
+        <v>461.25</v>
       </c>
       <c r="C3" s="319">
-        <f ca="1">MAX(_xlfn.ANCHORARRAY('Need ReSub (RFA-SDS)'!R7))</f>
-        <v>552</v>
+        <f>MAX(_xlfn.ANCHORARRAY('Need ReSub (RFA-SDS)'!R7))</f>
+        <v>554</v>
       </c>
       <c r="D3" s="319">
-        <f ca="1">AVERAGEIF(_xlfn.ANCHORARRAY('Need ReSub (RFA-SDS)'!R7),"&lt;&gt;0")</f>
-        <v>349.18181818181819</v>
+        <f>AVERAGEIF(_xlfn.ANCHORARRAY('Need ReSub (RFA-SDS)'!R7),"&lt;&gt;0")</f>
+        <v>355.5</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="452" t="str">
-        <f ca="1">"In the RFA process, the average number of days elapsed since responding to an unapproved RFA was " &amp; ROUND($B$3,0) &amp; " days, with a maximum of " &amp; ROUND($A$3,0) &amp; " days, indicating that delays in the RFA approval process are contributing to delays in construction work.
+        <f>"In the RFA process, the average number of days elapsed since responding to an unapproved RFA was " &amp; ROUND($B$3,0) &amp; " days, with a maximum of " &amp; ROUND($A$3,0) &amp; " days, indicating that delays in the RFA approval process are contributing to delays in construction work.
 Furthermore, the RFA (SDS) is as follows:
 Avarage :  " &amp; ROUND($D$3,0) &amp; " days
 Maimum :  " &amp; ROUND($C$3,0) &amp; " days"</f>
-        <v>In the RFA process, the average number of days elapsed since responding to an unapproved RFA was 460 days, with a maximum of 852 days, indicating that delays in the RFA approval process are contributing to delays in construction work.
+        <v>In the RFA process, the average number of days elapsed since responding to an unapproved RFA was 461 days, with a maximum of 853 days, indicating that delays in the RFA approval process are contributing to delays in construction work.
 Furthermore, the RFA (SDS) is as follows:
-Avarage :  349 days
-Maimum :  552 days</v>
+Avarage :  356 days
+Maimum :  554 days</v>
       </c>
       <c r="B5" s="452"/>
     </row>

--- a/ICT-RFA-RFI-lists-New.xlsx
+++ b/ICT-RFA-RFI-lists-New.xlsx
@@ -9,9 +9,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project Airport\LTIA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D5D9B42-3847-43AA-A1FE-D3702FB82F3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DDD01A7-70A4-4C79-AE18-DC92C297D06E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="506" activeTab="1" xr2:uid="{CCA8147E-0981-4321-B87F-440A52C0DA59}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="506" activeTab="2" xr2:uid="{CCA8147E-0981-4321-B87F-440A52C0DA59}"/>
   </bookViews>
   <sheets>
     <sheet name="RFA" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="4">'Need ReSub (RFA-SDS)'!$A$1:$R$62</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">RFA!$A$1:$AE$143,RFA!$I$145:$R$151,RFA!$C$145:$F$155,RFA!$C$157:$F$160,RFA!$C$162:$F$173</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'RFA-SDS'!$A$1:$AD$47,'RFA-SDS'!$H$49:$Q$55,'RFA-SDS'!$C$49:$E$53,'RFA-SDS'!$C$55:$E$58</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">RFI!$A$1:$Z$131,RFI!$H$133:$Q$137,RFI!$C$133:$E$138,RFI!$C$140:$E$143</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">RFI!$A$1:$Z$132,RFI!$H$134:$Q$138,RFI!$C$134:$E$139,RFI!$C$141:$E$144</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">RFA!$4:$5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'RFA-SDS'!$4:$5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">RFI!$4:$5</definedName>
@@ -78,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3528" uniqueCount="1111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3543" uniqueCount="1116">
   <si>
     <t>TT</t>
   </si>
@@ -5190,6 +5190,21 @@
   </si>
   <si>
     <t>10/22/2026 Update</t>
+  </si>
+  <si>
+    <t>LTIA-5.10-VIETUR-70000-RFI-1015</t>
+  </si>
+  <si>
+    <t>Clarify the information: Supplement data outlets for the BHS system, including ATR, FLS, MES, EDS equipment, and CCC panels</t>
+  </si>
+  <si>
+    <t>Làm rõ thông tin : Bổ sung số lượng node mạng (data outlet) cho hệ thống BHS, bao gồm các thiết bị ATR, FLS, MES, EDS và tủ CCC</t>
+  </si>
+  <si>
+    <t>Mr Noise + Kuroda</t>
+  </si>
+  <si>
+    <t>10/20/2026: Đã ký RFCS</t>
   </si>
 </sst>
 </file>
@@ -7626,23 +7641,233 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="51" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="52" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="55" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="55" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -7650,266 +7875,56 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="51" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="52" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="45" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="55" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="55" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="53" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="47" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="45" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -8572,92 +8587,92 @@
       <c r="AE3" s="159"/>
     </row>
     <row r="4" spans="1:35" s="5" customFormat="1" ht="36" customHeight="1" thickBot="1">
-      <c r="A4" s="408" t="s">
+      <c r="A4" s="397" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="348" t="s">
+      <c r="B4" s="407" t="s">
         <v>515</v>
       </c>
-      <c r="C4" s="414" t="s">
+      <c r="C4" s="403" t="s">
         <v>45</v>
       </c>
-      <c r="D4" s="366" t="s">
+      <c r="D4" s="364" t="s">
         <v>95</v>
       </c>
-      <c r="E4" s="369" t="s">
+      <c r="E4" s="362" t="s">
         <v>46</v>
       </c>
-      <c r="F4" s="412" t="s">
+      <c r="F4" s="399" t="s">
         <v>47</v>
       </c>
-      <c r="G4" s="369" t="s">
+      <c r="G4" s="362" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="410" t="s">
+      <c r="H4" s="401" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="366" t="s">
+      <c r="I4" s="364" t="s">
         <v>48</v>
       </c>
-      <c r="J4" s="366" t="s">
+      <c r="J4" s="364" t="s">
         <v>49</v>
       </c>
-      <c r="K4" s="369" t="s">
+      <c r="K4" s="362" t="s">
         <v>78</v>
       </c>
-      <c r="L4" s="366" t="s">
+      <c r="L4" s="364" t="s">
         <v>80</v>
       </c>
-      <c r="M4" s="364" t="s">
+      <c r="M4" s="366" t="s">
         <v>53</v>
       </c>
-      <c r="N4" s="365"/>
-      <c r="O4" s="364" t="s">
+      <c r="N4" s="367"/>
+      <c r="O4" s="366" t="s">
         <v>55</v>
       </c>
-      <c r="P4" s="365"/>
+      <c r="P4" s="367"/>
       <c r="Q4" s="368" t="s">
         <v>72</v>
       </c>
-      <c r="R4" s="365"/>
-      <c r="S4" s="364" t="s">
+      <c r="R4" s="367"/>
+      <c r="S4" s="366" t="s">
         <v>53</v>
       </c>
-      <c r="T4" s="364"/>
-      <c r="U4" s="365"/>
+      <c r="T4" s="366"/>
+      <c r="U4" s="367"/>
       <c r="V4" s="368" t="s">
         <v>55</v>
       </c>
-      <c r="W4" s="364"/>
-      <c r="X4" s="365"/>
-      <c r="Y4" s="371" t="s">
+      <c r="W4" s="366"/>
+      <c r="X4" s="367"/>
+      <c r="Y4" s="393" t="s">
         <v>72</v>
       </c>
-      <c r="Z4" s="372"/>
-      <c r="AA4" s="359" t="s">
+      <c r="Z4" s="427"/>
+      <c r="AA4" s="426" t="s">
         <v>112</v>
       </c>
-      <c r="AB4" s="360"/>
-      <c r="AC4" s="360"/>
-      <c r="AD4" s="361"/>
-      <c r="AE4" s="369" t="s">
+      <c r="AB4" s="395"/>
+      <c r="AC4" s="395"/>
+      <c r="AD4" s="396"/>
+      <c r="AE4" s="362" t="s">
         <v>79</v>
       </c>
       <c r="AG4" s="236"/>
     </row>
     <row r="5" spans="1:35" ht="78.75">
-      <c r="A5" s="409"/>
-      <c r="B5" s="349"/>
-      <c r="C5" s="415"/>
-      <c r="D5" s="367"/>
-      <c r="E5" s="370"/>
-      <c r="F5" s="413"/>
-      <c r="G5" s="370"/>
-      <c r="H5" s="411"/>
-      <c r="I5" s="367"/>
-      <c r="J5" s="367"/>
-      <c r="K5" s="370"/>
-      <c r="L5" s="367"/>
+      <c r="A5" s="398"/>
+      <c r="B5" s="408"/>
+      <c r="C5" s="404"/>
+      <c r="D5" s="365"/>
+      <c r="E5" s="369"/>
+      <c r="F5" s="400"/>
+      <c r="G5" s="369"/>
+      <c r="H5" s="402"/>
+      <c r="I5" s="365"/>
+      <c r="J5" s="365"/>
+      <c r="K5" s="369"/>
+      <c r="L5" s="365"/>
       <c r="M5" s="79" t="s">
         <v>52</v>
       </c>
@@ -8712,14 +8727,14 @@
       <c r="AD5" s="336" t="s">
         <v>118</v>
       </c>
-      <c r="AE5" s="416"/>
-      <c r="AG5" s="369" t="s">
+      <c r="AE5" s="363"/>
+      <c r="AG5" s="362" t="s">
         <v>119</v>
       </c>
-      <c r="AH5" s="369" t="s">
+      <c r="AH5" s="362" t="s">
         <v>120</v>
       </c>
-      <c r="AI5" s="369" t="s">
+      <c r="AI5" s="362" t="s">
         <v>121</v>
       </c>
     </row>
@@ -8755,9 +8770,9 @@
       <c r="AC6" s="86"/>
       <c r="AD6" s="86"/>
       <c r="AE6" s="74"/>
-      <c r="AG6" s="407"/>
-      <c r="AH6" s="407"/>
-      <c r="AI6" s="407"/>
+      <c r="AG6" s="409"/>
+      <c r="AH6" s="409"/>
+      <c r="AI6" s="409"/>
     </row>
     <row r="7" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A7" s="33">
@@ -23638,29 +23653,29 @@
       <c r="C145" s="166" t="s">
         <v>20</v>
       </c>
-      <c r="D145" s="376" t="s">
+      <c r="D145" s="405" t="s">
         <v>21</v>
       </c>
-      <c r="E145" s="376"/>
-      <c r="F145" s="377"/>
+      <c r="E145" s="405"/>
+      <c r="F145" s="406"/>
       <c r="G145" s="46"/>
       <c r="H145" s="68"/>
-      <c r="I145" s="356" t="s">
+      <c r="I145" s="357" t="s">
         <v>14</v>
       </c>
-      <c r="J145" s="357"/>
-      <c r="K145" s="357"/>
-      <c r="L145" s="357"/>
-      <c r="M145" s="357"/>
-      <c r="N145" s="358"/>
-      <c r="O145" s="362" t="s">
+      <c r="J145" s="358"/>
+      <c r="K145" s="358"/>
+      <c r="L145" s="358"/>
+      <c r="M145" s="358"/>
+      <c r="N145" s="359"/>
+      <c r="O145" s="360" t="s">
         <v>7</v>
       </c>
-      <c r="P145" s="363"/>
-      <c r="Q145" s="362" t="s">
+      <c r="P145" s="361"/>
+      <c r="Q145" s="360" t="s">
         <v>109</v>
       </c>
-      <c r="R145" s="363"/>
+      <c r="R145" s="361"/>
       <c r="S145" s="1"/>
       <c r="T145" s="1"/>
       <c r="U145" s="140"/>
@@ -23682,19 +23697,19 @@
       <c r="C146" s="167" t="s">
         <v>109</v>
       </c>
-      <c r="D146" s="354" t="s">
+      <c r="D146" s="424" t="s">
         <v>111</v>
       </c>
-      <c r="E146" s="354"/>
-      <c r="F146" s="355"/>
+      <c r="E146" s="424"/>
+      <c r="F146" s="425"/>
       <c r="G146" s="46"/>
       <c r="H146" s="46"/>
-      <c r="I146" s="356" t="s">
+      <c r="I146" s="357" t="s">
         <v>19</v>
       </c>
-      <c r="J146" s="357"/>
-      <c r="K146" s="357"/>
-      <c r="L146" s="358"/>
+      <c r="J146" s="358"/>
+      <c r="K146" s="358"/>
+      <c r="L146" s="359"/>
       <c r="M146" s="105">
         <f t="shared" ref="M146:M151" ca="1" si="89">N146/$N$146</f>
         <v>1</v>
@@ -23738,19 +23753,19 @@
       <c r="C147" s="167" t="s">
         <v>22</v>
       </c>
-      <c r="D147" s="354" t="s">
+      <c r="D147" s="424" t="s">
         <v>23</v>
       </c>
-      <c r="E147" s="354"/>
-      <c r="F147" s="355"/>
+      <c r="E147" s="424"/>
+      <c r="F147" s="425"/>
       <c r="G147" s="70"/>
       <c r="H147" s="6"/>
-      <c r="I147" s="379" t="s">
+      <c r="I147" s="373" t="s">
         <v>66</v>
       </c>
-      <c r="J147" s="380"/>
-      <c r="K147" s="380"/>
-      <c r="L147" s="381"/>
+      <c r="J147" s="374"/>
+      <c r="K147" s="374"/>
+      <c r="L147" s="375"/>
       <c r="M147" s="107">
         <f t="shared" ca="1" si="89"/>
         <v>0.49285714285714288</v>
@@ -23796,18 +23811,18 @@
       <c r="C148" s="167" t="s">
         <v>24</v>
       </c>
-      <c r="D148" s="354" t="s">
+      <c r="D148" s="424" t="s">
         <v>25</v>
       </c>
-      <c r="E148" s="354"/>
-      <c r="F148" s="355"/>
+      <c r="E148" s="424"/>
+      <c r="F148" s="425"/>
       <c r="H148" s="6"/>
-      <c r="I148" s="382" t="s">
+      <c r="I148" s="376" t="s">
         <v>67</v>
       </c>
-      <c r="J148" s="383"/>
-      <c r="K148" s="383"/>
-      <c r="L148" s="384"/>
+      <c r="J148" s="377"/>
+      <c r="K148" s="377"/>
+      <c r="L148" s="378"/>
       <c r="M148" s="109">
         <f t="shared" ca="1" si="89"/>
         <v>0.1</v>
@@ -23853,19 +23868,19 @@
       <c r="C149" s="167" t="s">
         <v>26</v>
       </c>
-      <c r="D149" s="354" t="s">
+      <c r="D149" s="424" t="s">
         <v>27</v>
       </c>
-      <c r="E149" s="354"/>
-      <c r="F149" s="355"/>
+      <c r="E149" s="424"/>
+      <c r="F149" s="425"/>
       <c r="G149" s="71"/>
       <c r="H149" s="6"/>
-      <c r="I149" s="385" t="s">
+      <c r="I149" s="379" t="s">
         <v>68</v>
       </c>
-      <c r="J149" s="386"/>
-      <c r="K149" s="386"/>
-      <c r="L149" s="387"/>
+      <c r="J149" s="380"/>
+      <c r="K149" s="380"/>
+      <c r="L149" s="381"/>
       <c r="M149" s="111">
         <f t="shared" ca="1" si="89"/>
         <v>0.20714285714285716</v>
@@ -23911,18 +23926,18 @@
       <c r="C150" s="168" t="s">
         <v>28</v>
       </c>
-      <c r="D150" s="354" t="s">
+      <c r="D150" s="424" t="s">
         <v>29</v>
       </c>
-      <c r="E150" s="354"/>
-      <c r="F150" s="355"/>
+      <c r="E150" s="424"/>
+      <c r="F150" s="425"/>
       <c r="G150" s="72"/>
-      <c r="I150" s="388" t="s">
+      <c r="I150" s="382" t="s">
         <v>70</v>
       </c>
-      <c r="J150" s="389"/>
-      <c r="K150" s="389"/>
-      <c r="L150" s="390"/>
+      <c r="J150" s="383"/>
+      <c r="K150" s="383"/>
+      <c r="L150" s="384"/>
       <c r="M150" s="114">
         <f t="shared" ca="1" si="89"/>
         <v>9.285714285714286E-2</v>
@@ -23970,18 +23985,18 @@
       <c r="C151" s="168" t="s">
         <v>30</v>
       </c>
-      <c r="D151" s="354" t="s">
+      <c r="D151" s="424" t="s">
         <v>31</v>
       </c>
-      <c r="E151" s="354"/>
-      <c r="F151" s="355"/>
+      <c r="E151" s="424"/>
+      <c r="F151" s="425"/>
       <c r="H151" s="6"/>
-      <c r="I151" s="391" t="s">
+      <c r="I151" s="354" t="s">
         <v>71</v>
       </c>
-      <c r="J151" s="392"/>
-      <c r="K151" s="392"/>
-      <c r="L151" s="393"/>
+      <c r="J151" s="355"/>
+      <c r="K151" s="355"/>
+      <c r="L151" s="356"/>
       <c r="M151" s="113">
         <f t="shared" ca="1" si="89"/>
         <v>0.10714285714285714</v>
@@ -24001,11 +24016,11 @@
       <c r="C152" s="168" t="s">
         <v>32</v>
       </c>
-      <c r="D152" s="354" t="s">
+      <c r="D152" s="424" t="s">
         <v>33</v>
       </c>
-      <c r="E152" s="354"/>
-      <c r="F152" s="355"/>
+      <c r="E152" s="424"/>
+      <c r="F152" s="425"/>
       <c r="H152" s="1" t="s">
         <v>11</v>
       </c>
@@ -24014,11 +24029,11 @@
       <c r="C153" s="167" t="s">
         <v>34</v>
       </c>
-      <c r="D153" s="354" t="s">
+      <c r="D153" s="424" t="s">
         <v>35</v>
       </c>
-      <c r="E153" s="354"/>
-      <c r="F153" s="355"/>
+      <c r="E153" s="424"/>
+      <c r="F153" s="425"/>
       <c r="H153" s="13"/>
       <c r="I153" s="141"/>
       <c r="J153" s="141"/>
@@ -24046,14 +24061,14 @@
       <c r="AI153" s="1"/>
     </row>
     <row r="154" spans="1:35">
-      <c r="C154" s="394" t="s">
+      <c r="C154" s="385" t="s">
         <v>75</v>
       </c>
-      <c r="D154" s="350" t="s">
+      <c r="D154" s="387" t="s">
         <v>76</v>
       </c>
-      <c r="E154" s="350"/>
-      <c r="F154" s="351"/>
+      <c r="E154" s="387"/>
+      <c r="F154" s="388"/>
       <c r="H154" s="13"/>
       <c r="J154" s="141"/>
       <c r="K154" s="13"/>
@@ -24080,10 +24095,10 @@
       <c r="AI154" s="1"/>
     </row>
     <row r="155" spans="1:35" ht="16.5" thickBot="1">
-      <c r="C155" s="395"/>
-      <c r="D155" s="352"/>
-      <c r="E155" s="352"/>
-      <c r="F155" s="353"/>
+      <c r="C155" s="386"/>
+      <c r="D155" s="389"/>
+      <c r="E155" s="389"/>
+      <c r="F155" s="390"/>
       <c r="H155" s="13"/>
       <c r="I155" s="141"/>
       <c r="J155" s="141"/>
@@ -24138,12 +24153,12 @@
       <c r="AI156" s="1"/>
     </row>
     <row r="157" spans="1:35">
-      <c r="C157" s="378" t="s">
+      <c r="C157" s="372" t="s">
         <v>41</v>
       </c>
-      <c r="D157" s="378"/>
-      <c r="E157" s="378"/>
-      <c r="F157" s="378"/>
+      <c r="D157" s="372"/>
+      <c r="E157" s="372"/>
+      <c r="F157" s="372"/>
       <c r="H157" s="13"/>
       <c r="I157" s="141"/>
       <c r="J157" s="141"/>
@@ -24174,11 +24189,11 @@
       <c r="C158" s="169" t="s">
         <v>8</v>
       </c>
-      <c r="D158" s="396" t="s">
+      <c r="D158" s="412" t="s">
         <v>91</v>
       </c>
-      <c r="E158" s="396"/>
-      <c r="F158" s="396"/>
+      <c r="E158" s="412"/>
+      <c r="F158" s="412"/>
       <c r="H158" s="13"/>
       <c r="I158" s="141"/>
       <c r="J158" s="141"/>
@@ -24209,11 +24224,11 @@
       <c r="C159" s="169" t="s">
         <v>8</v>
       </c>
-      <c r="D159" s="396" t="s">
+      <c r="D159" s="412" t="s">
         <v>92</v>
       </c>
-      <c r="E159" s="396"/>
-      <c r="F159" s="396"/>
+      <c r="E159" s="412"/>
+      <c r="F159" s="412"/>
       <c r="H159" s="13"/>
       <c r="I159" s="141"/>
       <c r="J159" s="141"/>
@@ -24244,11 +24259,11 @@
       <c r="C160" s="169" t="s">
         <v>8</v>
       </c>
-      <c r="D160" s="396" t="s">
+      <c r="D160" s="412" t="s">
         <v>93</v>
       </c>
-      <c r="E160" s="396"/>
-      <c r="F160" s="396"/>
+      <c r="E160" s="412"/>
+      <c r="F160" s="412"/>
       <c r="H160" s="13"/>
       <c r="I160" s="141"/>
       <c r="J160" s="141"/>
@@ -24303,12 +24318,12 @@
       <c r="AI161" s="1"/>
     </row>
     <row r="162" spans="3:35" ht="16.5" thickBot="1">
-      <c r="C162" s="402" t="s">
+      <c r="C162" s="416" t="s">
         <v>96</v>
       </c>
-      <c r="D162" s="403"/>
-      <c r="E162" s="403"/>
-      <c r="F162" s="404"/>
+      <c r="D162" s="417"/>
+      <c r="E162" s="417"/>
+      <c r="F162" s="418"/>
       <c r="H162" s="13"/>
       <c r="I162" s="141"/>
       <c r="J162" s="141"/>
@@ -24339,11 +24354,11 @@
       <c r="C163" s="212" t="s">
         <v>81</v>
       </c>
-      <c r="D163" s="405" t="s">
+      <c r="D163" s="419" t="s">
         <v>97</v>
       </c>
-      <c r="E163" s="405"/>
-      <c r="F163" s="406"/>
+      <c r="E163" s="419"/>
+      <c r="F163" s="420"/>
       <c r="H163" s="13"/>
       <c r="I163" s="141"/>
       <c r="J163" s="141"/>
@@ -24374,101 +24389,101 @@
       <c r="C164" s="213" t="s">
         <v>82</v>
       </c>
-      <c r="D164" s="397" t="s">
+      <c r="D164" s="410" t="s">
         <v>98</v>
       </c>
-      <c r="E164" s="397"/>
-      <c r="F164" s="398"/>
+      <c r="E164" s="410"/>
+      <c r="F164" s="411"/>
     </row>
     <row r="165" spans="3:35">
       <c r="C165" s="213" t="s">
         <v>83</v>
       </c>
-      <c r="D165" s="397" t="s">
+      <c r="D165" s="410" t="s">
         <v>99</v>
       </c>
-      <c r="E165" s="397"/>
-      <c r="F165" s="398"/>
+      <c r="E165" s="410"/>
+      <c r="F165" s="411"/>
     </row>
     <row r="166" spans="3:35">
       <c r="C166" s="214" t="s">
         <v>84</v>
       </c>
-      <c r="D166" s="397" t="s">
+      <c r="D166" s="410" t="s">
         <v>100</v>
       </c>
-      <c r="E166" s="397"/>
-      <c r="F166" s="398"/>
+      <c r="E166" s="410"/>
+      <c r="F166" s="411"/>
     </row>
     <row r="167" spans="3:35">
       <c r="C167" s="214" t="s">
         <v>85</v>
       </c>
-      <c r="D167" s="397" t="s">
+      <c r="D167" s="410" t="s">
         <v>101</v>
       </c>
-      <c r="E167" s="397"/>
-      <c r="F167" s="398"/>
+      <c r="E167" s="410"/>
+      <c r="F167" s="411"/>
     </row>
     <row r="168" spans="3:35" ht="18.75">
       <c r="C168" s="214" t="s">
         <v>86</v>
       </c>
-      <c r="D168" s="397" t="s">
+      <c r="D168" s="410" t="s">
         <v>102</v>
       </c>
-      <c r="E168" s="397"/>
-      <c r="F168" s="398"/>
+      <c r="E168" s="410"/>
+      <c r="F168" s="411"/>
     </row>
     <row r="169" spans="3:35" ht="18.75">
       <c r="C169" s="213" t="s">
         <v>87</v>
       </c>
-      <c r="D169" s="397" t="s">
+      <c r="D169" s="410" t="s">
         <v>103</v>
       </c>
-      <c r="E169" s="397"/>
-      <c r="F169" s="398"/>
+      <c r="E169" s="410"/>
+      <c r="F169" s="411"/>
     </row>
     <row r="170" spans="3:35">
       <c r="C170" s="215" t="s">
         <v>88</v>
       </c>
-      <c r="D170" s="399" t="s">
+      <c r="D170" s="413" t="s">
         <v>104</v>
       </c>
-      <c r="E170" s="400"/>
-      <c r="F170" s="401"/>
+      <c r="E170" s="414"/>
+      <c r="F170" s="415"/>
     </row>
     <row r="171" spans="3:35" ht="18.75">
       <c r="C171" s="215" t="s">
         <v>89</v>
       </c>
-      <c r="D171" s="397" t="s">
+      <c r="D171" s="410" t="s">
         <v>105</v>
       </c>
-      <c r="E171" s="397"/>
-      <c r="F171" s="398"/>
+      <c r="E171" s="410"/>
+      <c r="F171" s="411"/>
     </row>
     <row r="172" spans="3:35">
       <c r="C172" s="213" t="s">
         <v>90</v>
       </c>
-      <c r="D172" s="397" t="s">
+      <c r="D172" s="410" t="s">
         <v>106</v>
       </c>
-      <c r="E172" s="397"/>
-      <c r="F172" s="398"/>
+      <c r="E172" s="410"/>
+      <c r="F172" s="411"/>
     </row>
     <row r="173" spans="3:35" ht="16.5" thickBot="1">
       <c r="C173" s="216" t="s">
         <v>94</v>
       </c>
-      <c r="D173" s="373" t="s">
+      <c r="D173" s="421" t="s">
         <v>107</v>
       </c>
-      <c r="E173" s="374"/>
-      <c r="F173" s="375"/>
+      <c r="E173" s="422"/>
+      <c r="F173" s="423"/>
     </row>
   </sheetData>
   <autoFilter ref="A6:AE143" xr:uid="{C724CDAB-378C-47DB-9F45-08EE3BFB6E8B}">
@@ -24477,6 +24492,49 @@
     </sortState>
   </autoFilter>
   <mergeCells count="59">
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="D154:F155"/>
+    <mergeCell ref="D146:F146"/>
+    <mergeCell ref="I146:L146"/>
+    <mergeCell ref="AA4:AD4"/>
+    <mergeCell ref="Q145:R145"/>
+    <mergeCell ref="D151:F151"/>
+    <mergeCell ref="D152:F152"/>
+    <mergeCell ref="D153:F153"/>
+    <mergeCell ref="S4:U4"/>
+    <mergeCell ref="L4:L5"/>
+    <mergeCell ref="Q4:R4"/>
+    <mergeCell ref="K4:K5"/>
+    <mergeCell ref="Y4:Z4"/>
+    <mergeCell ref="D173:F173"/>
+    <mergeCell ref="D145:F145"/>
+    <mergeCell ref="C157:F157"/>
+    <mergeCell ref="O145:P145"/>
+    <mergeCell ref="I145:N145"/>
+    <mergeCell ref="I147:L147"/>
+    <mergeCell ref="I148:L148"/>
+    <mergeCell ref="I149:L149"/>
+    <mergeCell ref="I150:L150"/>
+    <mergeCell ref="I151:L151"/>
+    <mergeCell ref="C154:C155"/>
+    <mergeCell ref="D147:F147"/>
+    <mergeCell ref="D148:F148"/>
+    <mergeCell ref="D149:F149"/>
+    <mergeCell ref="D150:F150"/>
+    <mergeCell ref="D158:F158"/>
+    <mergeCell ref="D172:F172"/>
+    <mergeCell ref="D159:F159"/>
+    <mergeCell ref="D160:F160"/>
+    <mergeCell ref="D167:F167"/>
+    <mergeCell ref="D168:F168"/>
+    <mergeCell ref="D169:F169"/>
+    <mergeCell ref="D170:F170"/>
+    <mergeCell ref="D171:F171"/>
+    <mergeCell ref="C162:F162"/>
+    <mergeCell ref="D163:F163"/>
+    <mergeCell ref="D164:F164"/>
+    <mergeCell ref="D165:F165"/>
+    <mergeCell ref="D166:F166"/>
     <mergeCell ref="AG5:AG6"/>
     <mergeCell ref="AH5:AH6"/>
     <mergeCell ref="AI5:AI6"/>
@@ -24493,49 +24551,6 @@
     <mergeCell ref="V4:X4"/>
     <mergeCell ref="M4:N4"/>
     <mergeCell ref="O4:P4"/>
-    <mergeCell ref="D172:F172"/>
-    <mergeCell ref="D159:F159"/>
-    <mergeCell ref="D160:F160"/>
-    <mergeCell ref="D167:F167"/>
-    <mergeCell ref="D168:F168"/>
-    <mergeCell ref="D169:F169"/>
-    <mergeCell ref="D170:F170"/>
-    <mergeCell ref="D171:F171"/>
-    <mergeCell ref="C162:F162"/>
-    <mergeCell ref="D163:F163"/>
-    <mergeCell ref="D164:F164"/>
-    <mergeCell ref="D165:F165"/>
-    <mergeCell ref="D166:F166"/>
-    <mergeCell ref="D173:F173"/>
-    <mergeCell ref="D145:F145"/>
-    <mergeCell ref="C157:F157"/>
-    <mergeCell ref="O145:P145"/>
-    <mergeCell ref="I145:N145"/>
-    <mergeCell ref="I147:L147"/>
-    <mergeCell ref="I148:L148"/>
-    <mergeCell ref="I149:L149"/>
-    <mergeCell ref="I150:L150"/>
-    <mergeCell ref="I151:L151"/>
-    <mergeCell ref="C154:C155"/>
-    <mergeCell ref="D147:F147"/>
-    <mergeCell ref="D148:F148"/>
-    <mergeCell ref="D149:F149"/>
-    <mergeCell ref="D150:F150"/>
-    <mergeCell ref="D158:F158"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="D154:F155"/>
-    <mergeCell ref="D146:F146"/>
-    <mergeCell ref="I146:L146"/>
-    <mergeCell ref="AA4:AD4"/>
-    <mergeCell ref="Q145:R145"/>
-    <mergeCell ref="D151:F151"/>
-    <mergeCell ref="D152:F152"/>
-    <mergeCell ref="D153:F153"/>
-    <mergeCell ref="S4:U4"/>
-    <mergeCell ref="L4:L5"/>
-    <mergeCell ref="Q4:R4"/>
-    <mergeCell ref="K4:K5"/>
-    <mergeCell ref="Y4:Z4"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="A7:AE143 AG7:AI143">
@@ -25209,88 +25224,88 @@
       <c r="AD3" s="159"/>
     </row>
     <row r="4" spans="1:35" s="5" customFormat="1" ht="36" customHeight="1" thickBot="1">
-      <c r="A4" s="408" t="s">
+      <c r="A4" s="397" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="348" t="s">
+      <c r="B4" s="407" t="s">
         <v>515</v>
       </c>
-      <c r="C4" s="414" t="s">
+      <c r="C4" s="403" t="s">
         <v>45</v>
       </c>
-      <c r="D4" s="369" t="s">
+      <c r="D4" s="362" t="s">
         <v>46</v>
       </c>
-      <c r="E4" s="412" t="s">
+      <c r="E4" s="399" t="s">
         <v>47</v>
       </c>
-      <c r="F4" s="369" t="s">
+      <c r="F4" s="362" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="410" t="s">
+      <c r="G4" s="401" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="366" t="s">
+      <c r="H4" s="364" t="s">
         <v>48</v>
       </c>
-      <c r="I4" s="366" t="s">
+      <c r="I4" s="364" t="s">
         <v>49</v>
       </c>
-      <c r="J4" s="369" t="s">
+      <c r="J4" s="362" t="s">
         <v>78</v>
       </c>
-      <c r="K4" s="366" t="s">
+      <c r="K4" s="364" t="s">
         <v>80</v>
       </c>
-      <c r="L4" s="364" t="s">
+      <c r="L4" s="366" t="s">
         <v>53</v>
       </c>
-      <c r="M4" s="365"/>
+      <c r="M4" s="367"/>
       <c r="N4" s="368" t="s">
         <v>55</v>
       </c>
-      <c r="O4" s="365"/>
+      <c r="O4" s="367"/>
       <c r="P4" s="368" t="s">
         <v>72</v>
       </c>
-      <c r="Q4" s="365"/>
-      <c r="R4" s="364" t="s">
+      <c r="Q4" s="367"/>
+      <c r="R4" s="366" t="s">
         <v>53</v>
       </c>
-      <c r="S4" s="364"/>
-      <c r="T4" s="365"/>
+      <c r="S4" s="366"/>
+      <c r="T4" s="367"/>
       <c r="U4" s="368" t="s">
         <v>55</v>
       </c>
-      <c r="V4" s="364"/>
-      <c r="W4" s="365"/>
-      <c r="X4" s="371" t="s">
+      <c r="V4" s="366"/>
+      <c r="W4" s="367"/>
+      <c r="X4" s="393" t="s">
         <v>72</v>
       </c>
-      <c r="Y4" s="417"/>
-      <c r="Z4" s="371" t="s">
+      <c r="Y4" s="394"/>
+      <c r="Z4" s="393" t="s">
         <v>112</v>
       </c>
-      <c r="AA4" s="360"/>
-      <c r="AB4" s="360"/>
-      <c r="AC4" s="361"/>
-      <c r="AD4" s="369" t="s">
+      <c r="AA4" s="395"/>
+      <c r="AB4" s="395"/>
+      <c r="AC4" s="396"/>
+      <c r="AD4" s="362" t="s">
         <v>79</v>
       </c>
       <c r="AG4" s="236"/>
     </row>
     <row r="5" spans="1:35" ht="78.75">
-      <c r="A5" s="409"/>
-      <c r="B5" s="349"/>
-      <c r="C5" s="415"/>
-      <c r="D5" s="370"/>
-      <c r="E5" s="413"/>
-      <c r="F5" s="370"/>
-      <c r="G5" s="411"/>
-      <c r="H5" s="367"/>
-      <c r="I5" s="367"/>
-      <c r="J5" s="370"/>
-      <c r="K5" s="367"/>
+      <c r="A5" s="398"/>
+      <c r="B5" s="408"/>
+      <c r="C5" s="404"/>
+      <c r="D5" s="369"/>
+      <c r="E5" s="400"/>
+      <c r="F5" s="369"/>
+      <c r="G5" s="402"/>
+      <c r="H5" s="365"/>
+      <c r="I5" s="365"/>
+      <c r="J5" s="369"/>
+      <c r="K5" s="365"/>
       <c r="L5" s="79" t="s">
         <v>52</v>
       </c>
@@ -25345,14 +25360,14 @@
       <c r="AC5" s="250" t="s">
         <v>118</v>
       </c>
-      <c r="AD5" s="416"/>
-      <c r="AG5" s="422" t="s">
+      <c r="AD5" s="363"/>
+      <c r="AG5" s="348" t="s">
         <v>119</v>
       </c>
-      <c r="AH5" s="424" t="s">
+      <c r="AH5" s="350" t="s">
         <v>120</v>
       </c>
-      <c r="AI5" s="426" t="s">
+      <c r="AI5" s="352" t="s">
         <v>121</v>
       </c>
     </row>
@@ -25387,9 +25402,9 @@
       <c r="AB6" s="86"/>
       <c r="AC6" s="86"/>
       <c r="AD6" s="74"/>
-      <c r="AG6" s="423"/>
-      <c r="AH6" s="425"/>
-      <c r="AI6" s="427"/>
+      <c r="AG6" s="349"/>
+      <c r="AH6" s="351"/>
+      <c r="AI6" s="353"/>
     </row>
     <row r="7" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A7" s="33">
@@ -26540,7 +26555,7 @@
         <v>YES</v>
       </c>
     </row>
-    <row r="17" spans="1:35" s="9" customFormat="1" ht="110.25">
+    <row r="17" spans="1:35" s="9" customFormat="1" ht="94.5">
       <c r="A17" s="33">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -28552,13 +28567,15 @@
       <c r="G35" s="21" t="s">
         <v>600</v>
       </c>
-      <c r="H35" s="138"/>
+      <c r="H35" s="138" t="s">
+        <v>3</v>
+      </c>
       <c r="I35" s="164">
-        <f t="shared" ca="1" si="10"/>
+        <f t="shared" si="10"/>
         <v>13</v>
       </c>
       <c r="J35" s="47">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K35" s="164"/>
@@ -28566,7 +28583,9 @@
         <v>8</v>
       </c>
       <c r="M35" s="65"/>
-      <c r="N35" s="40"/>
+      <c r="N35" s="40" t="s">
+        <v>8</v>
+      </c>
       <c r="O35" s="41"/>
       <c r="P35" s="40"/>
       <c r="Q35" s="155"/>
@@ -28579,14 +28598,20 @@
       <c r="T35" s="188">
         <v>46304</v>
       </c>
-      <c r="U35" s="29"/>
-      <c r="V35" s="188"/>
-      <c r="W35" s="235"/>
+      <c r="U35" s="29">
+        <v>46315</v>
+      </c>
+      <c r="V35" s="188">
+        <v>46317</v>
+      </c>
+      <c r="W35" s="235" t="s">
+        <v>240</v>
+      </c>
       <c r="X35" s="230"/>
       <c r="Y35" s="227"/>
-      <c r="Z35" s="29" t="str">
+      <c r="Z35" s="29" t="b">
         <f t="shared" si="5"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AA35" s="229"/>
       <c r="AB35" s="229" t="str">
@@ -28750,19 +28775,21 @@
         <v>1</v>
       </c>
       <c r="I37" s="164">
-        <f t="shared" ca="1" si="10"/>
-        <v>36</v>
+        <f t="shared" si="10"/>
+        <v>14</v>
       </c>
       <c r="J37" s="47">
-        <f t="shared" ca="1" si="4"/>
-        <v>15</v>
+        <f t="shared" si="4"/>
+        <v>0</v>
       </c>
       <c r="K37" s="164"/>
       <c r="L37" s="54" t="s">
         <v>8</v>
       </c>
       <c r="M37" s="65"/>
-      <c r="N37" s="40"/>
+      <c r="N37" s="40" t="s">
+        <v>8</v>
+      </c>
       <c r="O37" s="41"/>
       <c r="P37" s="40"/>
       <c r="Q37" s="155"/>
@@ -28775,16 +28802,20 @@
       <c r="T37" s="188">
         <v>46281</v>
       </c>
-      <c r="U37" s="29"/>
-      <c r="V37" s="188"/>
+      <c r="U37" s="29">
+        <v>46293</v>
+      </c>
+      <c r="V37" s="188">
+        <v>46295</v>
+      </c>
       <c r="W37" s="235" t="s">
         <v>240</v>
       </c>
       <c r="X37" s="230"/>
       <c r="Y37" s="227"/>
-      <c r="Z37" s="29" t="str">
+      <c r="Z37" s="29">
         <f t="shared" si="5"/>
-        <v/>
+        <v>46302</v>
       </c>
       <c r="AA37" s="229"/>
       <c r="AB37" s="229" t="str">
@@ -28946,13 +28977,15 @@
       <c r="G39" s="21" t="s">
         <v>588</v>
       </c>
-      <c r="H39" s="138"/>
+      <c r="H39" s="138" t="s">
+        <v>3</v>
+      </c>
       <c r="I39" s="164">
-        <f t="shared" ca="1" si="10"/>
+        <f t="shared" si="10"/>
         <v>13</v>
       </c>
       <c r="J39" s="47">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K39" s="164"/>
@@ -28960,7 +28993,9 @@
         <v>8</v>
       </c>
       <c r="M39" s="65"/>
-      <c r="N39" s="40"/>
+      <c r="N39" s="40" t="s">
+        <v>8</v>
+      </c>
       <c r="O39" s="41"/>
       <c r="P39" s="40"/>
       <c r="Q39" s="155"/>
@@ -28973,14 +29008,20 @@
       <c r="T39" s="188">
         <v>46304</v>
       </c>
-      <c r="U39" s="29"/>
-      <c r="V39" s="188"/>
-      <c r="W39" s="235"/>
+      <c r="U39" s="29">
+        <v>46315</v>
+      </c>
+      <c r="V39" s="188">
+        <v>46317</v>
+      </c>
+      <c r="W39" s="235" t="s">
+        <v>240</v>
+      </c>
       <c r="X39" s="230"/>
       <c r="Y39" s="227"/>
-      <c r="Z39" s="29" t="str">
+      <c r="Z39" s="29" t="b">
         <f t="shared" si="5"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AA39" s="229"/>
       <c r="AB39" s="229" t="str">
@@ -29010,7 +29051,7 @@
         <v>1</v>
       </c>
       <c r="AI39" s="75" t="str">
-        <f>IF(AND($AH39,OR($Q39="B",$Q39="C")),"YES","")</f>
+        <f t="shared" ref="AI39:AI45" si="21">IF(AND($AH39,OR($Q39="B",$Q39="C")),"YES","")</f>
         <v/>
       </c>
     </row>
@@ -29020,7 +29061,7 @@
         <v>34</v>
       </c>
       <c r="B40" s="33" t="str">
-        <f t="shared" ref="B40" si="21">MID(D40, FIND("-", D40) + 1, 4)</f>
+        <f t="shared" ref="B40" si="22">MID(D40, FIND("-", D40) + 1, 4)</f>
         <v>5.10</v>
       </c>
       <c r="C40" s="164"/>
@@ -29079,7 +29120,7 @@
         <v/>
       </c>
       <c r="AC40" s="183" t="str">
-        <f t="shared" ref="AC40" si="22">IF(AB40="Late Resubmission",IF(AA40="","",AA40-Z40),IF(AB40="Not submit yet",IF(Z40="","",$I$1-Z40),""))</f>
+        <f t="shared" ref="AC40" si="23">IF(AB40="Late Resubmission",IF(AA40="","",AA40-Z40),IF(AB40="Not submit yet",IF(Z40="","",$I$1-Z40),""))</f>
         <v/>
       </c>
       <c r="AD40" s="92"/>
@@ -29099,7 +29140,7 @@
         <v>1</v>
       </c>
       <c r="AI40" s="75" t="str">
-        <f>IF(AND($AH40,OR($Q40="B",$Q40="C")),"YES","")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -29109,7 +29150,7 @@
         <v>35</v>
       </c>
       <c r="B41" s="33" t="str">
-        <f t="shared" ref="B41" si="23">MID(D41, FIND("-", D41) + 1, 4)</f>
+        <f t="shared" ref="B41" si="24">MID(D41, FIND("-", D41) + 1, 4)</f>
         <v>5.10</v>
       </c>
       <c r="C41" s="164"/>
@@ -29168,7 +29209,7 @@
         <v/>
       </c>
       <c r="AC41" s="183" t="str">
-        <f t="shared" ref="AC41" si="24">IF(AB41="Late Resubmission",IF(AA41="","",AA41-Z41),IF(AB41="Not submit yet",IF(Z41="","",$I$1-Z41),""))</f>
+        <f t="shared" ref="AC41" si="25">IF(AB41="Late Resubmission",IF(AA41="","",AA41-Z41),IF(AB41="Not submit yet",IF(Z41="","",$I$1-Z41),""))</f>
         <v/>
       </c>
       <c r="AD41" s="92"/>
@@ -29188,7 +29229,7 @@
         <v>1</v>
       </c>
       <c r="AI41" s="75" t="str">
-        <f>IF(AND($AH41,OR($Q41="B",$Q41="C")),"YES","")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -29198,7 +29239,7 @@
         <v>36</v>
       </c>
       <c r="B42" s="33" t="str">
-        <f t="shared" ref="B42" si="25">MID(D42, FIND("-", D42) + 1, 4)</f>
+        <f t="shared" ref="B42" si="26">MID(D42, FIND("-", D42) + 1, 4)</f>
         <v>5.10</v>
       </c>
       <c r="C42" s="164"/>
@@ -29257,7 +29298,7 @@
         <v/>
       </c>
       <c r="AC42" s="183" t="str">
-        <f t="shared" ref="AC42" si="26">IF(AB42="Late Resubmission",IF(AA42="","",AA42-Z42),IF(AB42="Not submit yet",IF(Z42="","",$I$1-Z42),""))</f>
+        <f t="shared" ref="AC42" si="27">IF(AB42="Late Resubmission",IF(AA42="","",AA42-Z42),IF(AB42="Not submit yet",IF(Z42="","",$I$1-Z42),""))</f>
         <v/>
       </c>
       <c r="AD42" s="92" t="s">
@@ -29279,7 +29320,7 @@
         <v>1</v>
       </c>
       <c r="AI42" s="75" t="str">
-        <f>IF(AND($AH42,OR($Q42="B",$Q42="C")),"YES","")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -29289,7 +29330,7 @@
         <v>37</v>
       </c>
       <c r="B43" s="33" t="str">
-        <f t="shared" ref="B43" si="27">MID(D43, FIND("-", D43) + 1, 4)</f>
+        <f t="shared" ref="B43" si="28">MID(D43, FIND("-", D43) + 1, 4)</f>
         <v>5.10</v>
       </c>
       <c r="C43" s="164"/>
@@ -29348,7 +29389,7 @@
         <v/>
       </c>
       <c r="AC43" s="183" t="str">
-        <f t="shared" ref="AC43" si="28">IF(AB43="Late Resubmission",IF(AA43="","",AA43-Z43),IF(AB43="Not submit yet",IF(Z43="","",$I$1-Z43),""))</f>
+        <f t="shared" ref="AC43" si="29">IF(AB43="Late Resubmission",IF(AA43="","",AA43-Z43),IF(AB43="Not submit yet",IF(Z43="","",$I$1-Z43),""))</f>
         <v/>
       </c>
       <c r="AD43" s="92"/>
@@ -29368,7 +29409,7 @@
         <v>1</v>
       </c>
       <c r="AI43" s="75" t="str">
-        <f>IF(AND($AH43,OR($Q43="B",$Q43="C")),"YES","")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -29378,7 +29419,7 @@
         <v>38</v>
       </c>
       <c r="B44" s="33" t="str">
-        <f t="shared" ref="B44" si="29">MID(D44, FIND("-", D44) + 1, 4)</f>
+        <f t="shared" ref="B44" si="30">MID(D44, FIND("-", D44) + 1, 4)</f>
         <v>5.10</v>
       </c>
       <c r="C44" s="164"/>
@@ -29437,7 +29478,7 @@
         <v/>
       </c>
       <c r="AC44" s="183" t="str">
-        <f t="shared" ref="AC44" si="30">IF(AB44="Late Resubmission",IF(AA44="","",AA44-Z44),IF(AB44="Not submit yet",IF(Z44="","",$I$1-Z44),""))</f>
+        <f t="shared" ref="AC44" si="31">IF(AB44="Late Resubmission",IF(AA44="","",AA44-Z44),IF(AB44="Not submit yet",IF(Z44="","",$I$1-Z44),""))</f>
         <v/>
       </c>
       <c r="AD44" s="92"/>
@@ -29457,7 +29498,7 @@
         <v>1</v>
       </c>
       <c r="AI44" s="75" t="str">
-        <f>IF(AND($AH44,OR($Q44="B",$Q44="C")),"YES","")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -29467,7 +29508,7 @@
         <v>39</v>
       </c>
       <c r="B45" s="33" t="str">
-        <f t="shared" ref="B45" si="31">MID(D45, FIND("-", D45) + 1, 4)</f>
+        <f t="shared" ref="B45" si="32">MID(D45, FIND("-", D45) + 1, 4)</f>
         <v>5.11</v>
       </c>
       <c r="C45" s="164" t="s">
@@ -29528,7 +29569,7 @@
         <v/>
       </c>
       <c r="AC45" s="183" t="str">
-        <f t="shared" ref="AC45" si="32">IF(AB45="Late Resubmission",IF(AA45="","",AA45-Z45),IF(AB45="Not submit yet",IF(Z45="","",$I$1-Z45),""))</f>
+        <f t="shared" ref="AC45" si="33">IF(AB45="Late Resubmission",IF(AA45="","",AA45-Z45),IF(AB45="Not submit yet",IF(Z45="","",$I$1-Z45),""))</f>
         <v/>
       </c>
       <c r="AD45" s="92"/>
@@ -29548,7 +29589,7 @@
         <v>1</v>
       </c>
       <c r="AI45" s="75" t="str">
-        <f>IF(AND($AH45,OR($Q45="B",$Q45="C")),"YES","")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -29633,28 +29674,28 @@
       <c r="C49" s="166" t="s">
         <v>20</v>
       </c>
-      <c r="D49" s="376" t="s">
+      <c r="D49" s="405" t="s">
         <v>21</v>
       </c>
-      <c r="E49" s="377"/>
+      <c r="E49" s="406"/>
       <c r="F49" s="46"/>
       <c r="G49" s="46"/>
-      <c r="H49" s="356" t="s">
+      <c r="H49" s="357" t="s">
         <v>14</v>
       </c>
-      <c r="I49" s="357"/>
-      <c r="J49" s="357"/>
-      <c r="K49" s="357"/>
-      <c r="L49" s="357"/>
-      <c r="M49" s="358"/>
-      <c r="N49" s="362" t="s">
+      <c r="I49" s="358"/>
+      <c r="J49" s="358"/>
+      <c r="K49" s="358"/>
+      <c r="L49" s="358"/>
+      <c r="M49" s="359"/>
+      <c r="N49" s="360" t="s">
         <v>7</v>
       </c>
-      <c r="O49" s="363"/>
-      <c r="P49" s="362" t="s">
+      <c r="O49" s="361"/>
+      <c r="P49" s="360" t="s">
         <v>109</v>
       </c>
-      <c r="Q49" s="363"/>
+      <c r="Q49" s="361"/>
       <c r="R49" s="1"/>
       <c r="S49" s="1"/>
       <c r="T49" s="140"/>
@@ -29674,24 +29715,24 @@
       <c r="C50" s="195" t="s">
         <v>109</v>
       </c>
-      <c r="D50" s="420" t="s">
+      <c r="D50" s="391" t="s">
         <v>111</v>
       </c>
-      <c r="E50" s="421"/>
+      <c r="E50" s="392"/>
       <c r="F50" s="46"/>
-      <c r="H50" s="356" t="s">
+      <c r="H50" s="357" t="s">
         <v>18</v>
       </c>
-      <c r="I50" s="357"/>
-      <c r="J50" s="357"/>
-      <c r="K50" s="358"/>
+      <c r="I50" s="358"/>
+      <c r="J50" s="358"/>
+      <c r="K50" s="359"/>
       <c r="L50" s="105">
         <f ca="1">M50/$M$50</f>
         <v>1</v>
       </c>
       <c r="M50" s="106">
         <f ca="1">SUM($M$51:$M$55)</f>
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N50" s="102" t="s">
         <v>15</v>
@@ -29726,29 +29767,29 @@
       <c r="C51" s="195" t="s">
         <v>36</v>
       </c>
-      <c r="D51" s="418" t="s">
+      <c r="D51" s="370" t="s">
         <v>37</v>
       </c>
-      <c r="E51" s="419"/>
+      <c r="E51" s="371"/>
       <c r="F51" s="69"/>
       <c r="G51" s="6"/>
-      <c r="H51" s="379" t="s">
+      <c r="H51" s="373" t="s">
         <v>66</v>
       </c>
-      <c r="I51" s="380"/>
-      <c r="J51" s="380"/>
-      <c r="K51" s="381"/>
+      <c r="I51" s="374"/>
+      <c r="J51" s="374"/>
+      <c r="K51" s="375"/>
       <c r="L51" s="107">
         <f ca="1">M51/$M$50</f>
-        <v>2.4390243902439025E-2</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="M51" s="108">
         <f>COUNTIF($H$7:$H$47,"A")</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N51" s="100">
         <f ca="1">COUNTIFS($I$7:$I$47,"&lt;=21",$H$7:$H$47,"A")</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O51" s="101">
         <f ca="1">COUNTIFS($I$7:$I$47,"&gt;21",$H$7:$H$47,"A")</f>
@@ -29778,24 +29819,24 @@
       <c r="AI51" s="11"/>
     </row>
     <row r="52" spans="3:35">
-      <c r="C52" s="394" t="s">
+      <c r="C52" s="385" t="s">
         <v>75</v>
       </c>
-      <c r="D52" s="350" t="s">
+      <c r="D52" s="387" t="s">
         <v>76</v>
       </c>
-      <c r="E52" s="351"/>
+      <c r="E52" s="388"/>
       <c r="F52" s="70"/>
       <c r="G52" s="6"/>
-      <c r="H52" s="382" t="s">
+      <c r="H52" s="376" t="s">
         <v>67</v>
       </c>
-      <c r="I52" s="383"/>
-      <c r="J52" s="383"/>
-      <c r="K52" s="384"/>
+      <c r="I52" s="377"/>
+      <c r="J52" s="377"/>
+      <c r="K52" s="378"/>
       <c r="L52" s="109">
-        <f t="shared" ref="L52:L55" ca="1" si="33">M52/$M$50</f>
-        <v>0.48780487804878048</v>
+        <f t="shared" ref="L52:L55" ca="1" si="34">M52/$M$50</f>
+        <v>0.5</v>
       </c>
       <c r="M52" s="110">
         <f>COUNTIF($H$7:$H$47,"B")</f>
@@ -29810,7 +29851,7 @@
         <v>12</v>
       </c>
       <c r="P52" s="109">
-        <f t="shared" ref="P52:P54" ca="1" si="34">Q52/$Q$50</f>
+        <f t="shared" ref="P52:P54" ca="1" si="35">Q52/$Q$50</f>
         <v>0.54054054054054057</v>
       </c>
       <c r="Q52" s="110">
@@ -29833,20 +29874,20 @@
       <c r="AI52" s="11"/>
     </row>
     <row r="53" spans="3:35" ht="16.5" thickBot="1">
-      <c r="C53" s="395"/>
-      <c r="D53" s="352"/>
-      <c r="E53" s="353"/>
+      <c r="C53" s="386"/>
+      <c r="D53" s="389"/>
+      <c r="E53" s="390"/>
       <c r="F53" s="71"/>
       <c r="G53" s="6"/>
-      <c r="H53" s="385" t="s">
+      <c r="H53" s="379" t="s">
         <v>68</v>
       </c>
-      <c r="I53" s="386"/>
-      <c r="J53" s="386"/>
-      <c r="K53" s="387"/>
+      <c r="I53" s="380"/>
+      <c r="J53" s="380"/>
+      <c r="K53" s="381"/>
       <c r="L53" s="111">
-        <f t="shared" ca="1" si="33"/>
-        <v>0.1951219512195122</v>
+        <f t="shared" ca="1" si="34"/>
+        <v>0.2</v>
       </c>
       <c r="M53" s="112">
         <f>COUNTIF($H$7:$H$47,"C")</f>
@@ -29854,14 +29895,14 @@
       </c>
       <c r="N53" s="98">
         <f ca="1">COUNTIFS($I$7:$I$47,"&lt;=21",$H$7:$H$47,"C")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O53" s="50">
         <f ca="1">COUNTIFS($I$7:$I$47,"&gt;21",$H$7:$H$47,"C")</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P53" s="111">
-        <f t="shared" ca="1" si="34"/>
+        <f t="shared" ca="1" si="35"/>
         <v>8.1081081081081086E-2</v>
       </c>
       <c r="Q53" s="112">
@@ -29886,30 +29927,30 @@
     <row r="54" spans="3:35">
       <c r="F54" s="72"/>
       <c r="G54" s="6"/>
-      <c r="H54" s="388" t="s">
+      <c r="H54" s="382" t="s">
         <v>70</v>
       </c>
-      <c r="I54" s="389"/>
-      <c r="J54" s="389"/>
-      <c r="K54" s="390"/>
+      <c r="I54" s="383"/>
+      <c r="J54" s="383"/>
+      <c r="K54" s="384"/>
       <c r="L54" s="114">
-        <f t="shared" ca="1" si="33"/>
-        <v>0.24390243902439024</v>
+        <f t="shared" ca="1" si="34"/>
+        <v>0.17499999999999999</v>
       </c>
       <c r="M54" s="115">
         <f ca="1">SUM(N54:O54)</f>
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="N54" s="98">
         <f ca="1">COUNTIFS($I$7:$I$47,"&lt;=21",$U$7:$U$47,"",$K$7:$K$47,"&lt;&gt;X")</f>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O54" s="50">
         <f ca="1">COUNTIFS($I$7:$I$47,"&gt;21",$U$7:$U$47,"",$K$7:$K$47,"&lt;&gt;X")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P54" s="114">
-        <f t="shared" ca="1" si="34"/>
+        <f t="shared" ca="1" si="35"/>
         <v>0.35135135135135137</v>
       </c>
       <c r="Q54" s="115">
@@ -29934,20 +29975,20 @@
       <c r="AI54" s="11"/>
     </row>
     <row r="55" spans="3:35" ht="16.5" thickBot="1">
-      <c r="C55" s="378" t="s">
+      <c r="C55" s="372" t="s">
         <v>41</v>
       </c>
-      <c r="D55" s="378"/>
-      <c r="E55" s="378"/>
-      <c r="H55" s="391" t="s">
+      <c r="D55" s="372"/>
+      <c r="E55" s="372"/>
+      <c r="H55" s="354" t="s">
         <v>71</v>
       </c>
-      <c r="I55" s="392"/>
-      <c r="J55" s="392"/>
-      <c r="K55" s="393"/>
+      <c r="I55" s="355"/>
+      <c r="J55" s="355"/>
+      <c r="K55" s="356"/>
       <c r="L55" s="113">
-        <f t="shared" ca="1" si="33"/>
-        <v>4.878048780487805E-2</v>
+        <f t="shared" ca="1" si="34"/>
+        <v>0.05</v>
       </c>
       <c r="M55" s="97">
         <f>COUNTIFS($K$7:$K$47,"X")</f>
@@ -29989,6 +30030,27 @@
     </sortState>
   </autoFilter>
   <mergeCells count="37">
+    <mergeCell ref="P49:Q49"/>
+    <mergeCell ref="X4:Y4"/>
+    <mergeCell ref="Z4:AC4"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D49:E49"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="D51:E51"/>
+    <mergeCell ref="C55:E55"/>
+    <mergeCell ref="H51:K51"/>
+    <mergeCell ref="H52:K52"/>
+    <mergeCell ref="H49:M49"/>
+    <mergeCell ref="H53:K53"/>
+    <mergeCell ref="H54:K54"/>
+    <mergeCell ref="C52:C53"/>
+    <mergeCell ref="D52:E53"/>
+    <mergeCell ref="D50:E50"/>
     <mergeCell ref="AG5:AG6"/>
     <mergeCell ref="AH5:AH6"/>
     <mergeCell ref="AI5:AI6"/>
@@ -30005,27 +30067,6 @@
     <mergeCell ref="K4:K5"/>
     <mergeCell ref="P4:Q4"/>
     <mergeCell ref="J4:J5"/>
-    <mergeCell ref="D51:E51"/>
-    <mergeCell ref="C55:E55"/>
-    <mergeCell ref="H51:K51"/>
-    <mergeCell ref="H52:K52"/>
-    <mergeCell ref="H49:M49"/>
-    <mergeCell ref="H53:K53"/>
-    <mergeCell ref="H54:K54"/>
-    <mergeCell ref="C52:C53"/>
-    <mergeCell ref="D52:E53"/>
-    <mergeCell ref="D50:E50"/>
-    <mergeCell ref="P49:Q49"/>
-    <mergeCell ref="X4:Y4"/>
-    <mergeCell ref="Z4:AC4"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D49:E49"/>
-    <mergeCell ref="B4:B5"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="A7:AD47 AG7:AI47">
@@ -30197,15 +30238,18 @@
     <hyperlink ref="L43" r:id="rId143" xr:uid="{78A29C5A-B38D-4480-9D00-419A29522F79}"/>
     <hyperlink ref="L44" r:id="rId144" xr:uid="{8C138FAE-DE0F-4AE2-8DC0-AE6D1691EDA5}"/>
     <hyperlink ref="L45" r:id="rId145" xr:uid="{27FD25C8-1BF4-4B08-A8C9-830AD37907F6}"/>
+    <hyperlink ref="N35" r:id="rId146" xr:uid="{6B0F2654-6C47-4293-B5E0-0B9362535EF3}"/>
+    <hyperlink ref="N39" r:id="rId147" xr:uid="{B3CD6A53-FDFF-4D4E-A8B5-14FD90B4C9E2}"/>
+    <hyperlink ref="N37" r:id="rId148" xr:uid="{4E229929-49C0-4A6C-8225-9EBD5F9E6EEE}"/>
   </hyperlinks>
   <pageMargins left="0.25" right="0.17" top="0.5" bottom="0.25" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="29" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId146"/>
+  <pageSetup paperSize="9" scale="29" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId149"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C184EF3E-84BF-4DCF-951B-B90EB4B9D23F}">
-  <dimension ref="A1:Z143"/>
+  <dimension ref="A1:Z144"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" customWidth="1"/>
@@ -30315,81 +30359,81 @@
       <c r="Z3" s="159"/>
     </row>
     <row r="4" spans="1:26" s="5" customFormat="1" ht="35.1" customHeight="1" thickBot="1">
-      <c r="A4" s="348" t="s">
+      <c r="A4" s="407" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="348" t="s">
+      <c r="B4" s="407" t="s">
         <v>515</v>
       </c>
-      <c r="C4" s="414" t="s">
+      <c r="C4" s="403" t="s">
         <v>45</v>
       </c>
-      <c r="D4" s="369" t="s">
+      <c r="D4" s="362" t="s">
         <v>46</v>
       </c>
-      <c r="E4" s="437" t="s">
+      <c r="E4" s="428" t="s">
         <v>47</v>
       </c>
-      <c r="F4" s="369" t="s">
+      <c r="F4" s="362" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="439" t="s">
+      <c r="G4" s="430" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="366" t="s">
+      <c r="H4" s="364" t="s">
         <v>48</v>
       </c>
-      <c r="I4" s="441" t="s">
+      <c r="I4" s="432" t="s">
         <v>49</v>
       </c>
-      <c r="J4" s="369" t="s">
+      <c r="J4" s="362" t="s">
         <v>78</v>
       </c>
-      <c r="K4" s="366" t="s">
+      <c r="K4" s="364" t="s">
         <v>80</v>
       </c>
       <c r="L4" s="368" t="s">
         <v>53</v>
       </c>
-      <c r="M4" s="365"/>
+      <c r="M4" s="367"/>
       <c r="N4" s="368" t="s">
         <v>55</v>
       </c>
-      <c r="O4" s="365"/>
+      <c r="O4" s="367"/>
       <c r="P4" s="368" t="s">
         <v>72</v>
       </c>
-      <c r="Q4" s="365"/>
-      <c r="R4" s="364" t="s">
+      <c r="Q4" s="367"/>
+      <c r="R4" s="366" t="s">
         <v>53</v>
       </c>
-      <c r="S4" s="364"/>
-      <c r="T4" s="365"/>
+      <c r="S4" s="366"/>
+      <c r="T4" s="367"/>
       <c r="U4" s="368" t="s">
         <v>55</v>
       </c>
-      <c r="V4" s="364"/>
-      <c r="W4" s="364"/>
-      <c r="X4" s="371" t="s">
+      <c r="V4" s="366"/>
+      <c r="W4" s="366"/>
+      <c r="X4" s="393" t="s">
         <v>72</v>
       </c>
-      <c r="Y4" s="372"/>
-      <c r="Z4" s="365" t="s">
+      <c r="Y4" s="427"/>
+      <c r="Z4" s="367" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="72" customHeight="1">
-      <c r="A5" s="349"/>
-      <c r="B5" s="349"/>
-      <c r="C5" s="415"/>
-      <c r="D5" s="370"/>
-      <c r="E5" s="438"/>
-      <c r="F5" s="370"/>
-      <c r="G5" s="440"/>
-      <c r="H5" s="367"/>
-      <c r="I5" s="442"/>
-      <c r="J5" s="370"/>
-      <c r="K5" s="367"/>
+      <c r="A5" s="408"/>
+      <c r="B5" s="408"/>
+      <c r="C5" s="404"/>
+      <c r="D5" s="369"/>
+      <c r="E5" s="429"/>
+      <c r="F5" s="369"/>
+      <c r="G5" s="431"/>
+      <c r="H5" s="365"/>
+      <c r="I5" s="433"/>
+      <c r="J5" s="369"/>
+      <c r="K5" s="365"/>
       <c r="L5" s="79" t="s">
         <v>52</v>
       </c>
@@ -30432,7 +30476,7 @@
       <c r="Y5" s="260" t="s">
         <v>114</v>
       </c>
-      <c r="Z5" s="416"/>
+      <c r="Z5" s="363"/>
     </row>
     <row r="6" spans="1:26" ht="15" customHeight="1" thickBot="1">
       <c r="A6" s="78"/>
@@ -36116,7 +36160,7 @@
         <v>628</v>
       </c>
       <c r="E80" s="174">
-        <f t="shared" ref="E80:E129" si="23">IF($T80=0,$S80+22,$T80+21)</f>
+        <f t="shared" ref="E80:E130" si="23">IF($T80=0,$S80+22,$T80+21)</f>
         <v>45945</v>
       </c>
       <c r="F80" s="31" t="s">
@@ -36129,11 +36173,11 @@
         <v>6</v>
       </c>
       <c r="I80" s="164">
-        <f t="shared" ref="I80:I129" si="24">IF(ISBLANK($V80),_xlfn.DAYS($I$1,$T80),_xlfn.DAYS($V80,$T80))</f>
+        <f t="shared" ref="I80:I130" si="24">IF(ISBLANK($V80),_xlfn.DAYS($I$1,$T80),_xlfn.DAYS($V80,$T80))</f>
         <v>6</v>
       </c>
       <c r="J80" s="47">
-        <f t="shared" ref="J80:J129" si="25">IF(($I80-21)&gt;0,$I80-21,0)</f>
+        <f t="shared" ref="J80:J130" si="25">IF(($I80-21)&gt;0,$I80-21,0)</f>
         <v>0</v>
       </c>
       <c r="K80" s="164"/>
@@ -36476,7 +36520,7 @@
     </row>
     <row r="85" spans="1:26" s="9" customFormat="1" ht="47.25">
       <c r="A85" s="33">
-        <f t="shared" ref="A85:A129" si="29">A84+1</f>
+        <f t="shared" ref="A85:A130" si="29">A84+1</f>
         <v>79</v>
       </c>
       <c r="B85" s="33" t="str">
@@ -39657,135 +39701,158 @@
       <c r="Y129" s="19"/>
       <c r="Z129" s="92"/>
     </row>
-    <row r="130" spans="1:26" s="9" customFormat="1">
-      <c r="A130" s="23"/>
-      <c r="B130" s="33"/>
-      <c r="C130" s="137"/>
-      <c r="D130" s="25"/>
-      <c r="E130" s="174"/>
-      <c r="F130" s="31"/>
-      <c r="G130" s="21"/>
-      <c r="H130" s="138"/>
-      <c r="I130" s="177"/>
-      <c r="J130" s="48"/>
-      <c r="K130" s="177"/>
-      <c r="L130" s="59"/>
-      <c r="M130" s="60"/>
-      <c r="N130" s="61"/>
-      <c r="O130" s="144"/>
-      <c r="P130" s="146"/>
-      <c r="Q130" s="152"/>
-      <c r="R130" s="27"/>
-      <c r="S130" s="27"/>
-      <c r="T130" s="187"/>
-      <c r="U130" s="29"/>
-      <c r="V130" s="188"/>
-      <c r="W130" s="235"/>
+    <row r="130" spans="1:26" s="9" customFormat="1" ht="63">
+      <c r="A130" s="33">
+        <f t="shared" si="29"/>
+        <v>124</v>
+      </c>
+      <c r="B130" s="33" t="str">
+        <f t="shared" ref="B130" si="61">MID(D130, FIND("-", D130) + 1, 4)</f>
+        <v>5.10</v>
+      </c>
+      <c r="C130" s="164"/>
+      <c r="D130" s="25" t="s">
+        <v>1111</v>
+      </c>
+      <c r="E130" s="174">
+        <f t="shared" si="23"/>
+        <v>46314</v>
+      </c>
+      <c r="F130" s="31" t="s">
+        <v>1112</v>
+      </c>
+      <c r="G130" s="21" t="s">
+        <v>1113</v>
+      </c>
+      <c r="H130" s="138" t="s">
+        <v>6</v>
+      </c>
+      <c r="I130" s="164">
+        <f t="shared" si="24"/>
+        <v>24</v>
+      </c>
+      <c r="J130" s="47">
+        <f t="shared" si="25"/>
+        <v>3</v>
+      </c>
+      <c r="K130" s="164"/>
+      <c r="L130" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="M130" s="41"/>
+      <c r="N130" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="O130" s="41"/>
+      <c r="P130" s="40"/>
+      <c r="Q130" s="154"/>
+      <c r="R130" s="27">
+        <v>46293</v>
+      </c>
+      <c r="S130" s="27">
+        <v>46293</v>
+      </c>
+      <c r="T130" s="188">
+        <v>46293</v>
+      </c>
+      <c r="U130" s="29">
+        <v>46244</v>
+      </c>
+      <c r="V130" s="211">
+        <v>46317</v>
+      </c>
+      <c r="W130" s="235" t="s">
+        <v>1114</v>
+      </c>
       <c r="X130" s="230"/>
       <c r="Y130" s="19"/>
-      <c r="Z130" s="92"/>
-    </row>
-    <row r="131" spans="1:26" s="9" customFormat="1" ht="16.5" thickBot="1">
-      <c r="A131" s="24"/>
-      <c r="B131" s="329"/>
-      <c r="C131" s="165"/>
-      <c r="D131" s="45"/>
-      <c r="E131" s="175"/>
-      <c r="F131" s="32"/>
-      <c r="G131" s="22"/>
-      <c r="H131" s="139"/>
-      <c r="I131" s="178"/>
-      <c r="J131" s="49"/>
-      <c r="K131" s="178"/>
-      <c r="L131" s="62"/>
-      <c r="M131" s="63"/>
-      <c r="N131" s="64"/>
-      <c r="O131" s="145"/>
-      <c r="P131" s="147"/>
-      <c r="Q131" s="153"/>
-      <c r="R131" s="44"/>
-      <c r="S131" s="44"/>
-      <c r="T131" s="189"/>
-      <c r="U131" s="43"/>
-      <c r="V131" s="194"/>
-      <c r="W131" s="258"/>
-      <c r="X131" s="232"/>
-      <c r="Y131" s="20"/>
-      <c r="Z131" s="93"/>
-    </row>
-    <row r="132" spans="1:26" ht="16.5" thickBot="1"/>
-    <row r="133" spans="1:26" ht="16.5" thickBot="1">
-      <c r="C133" s="207" t="s">
+      <c r="Z130" s="92" t="s">
+        <v>1115</v>
+      </c>
+    </row>
+    <row r="131" spans="1:26" s="9" customFormat="1">
+      <c r="A131" s="23"/>
+      <c r="B131" s="33"/>
+      <c r="C131" s="137"/>
+      <c r="D131" s="25"/>
+      <c r="E131" s="174"/>
+      <c r="F131" s="31"/>
+      <c r="G131" s="21"/>
+      <c r="H131" s="138"/>
+      <c r="I131" s="177"/>
+      <c r="J131" s="48"/>
+      <c r="K131" s="177"/>
+      <c r="L131" s="59"/>
+      <c r="M131" s="60"/>
+      <c r="N131" s="61"/>
+      <c r="O131" s="144"/>
+      <c r="P131" s="146"/>
+      <c r="Q131" s="152"/>
+      <c r="R131" s="27"/>
+      <c r="S131" s="27"/>
+      <c r="T131" s="187"/>
+      <c r="U131" s="29"/>
+      <c r="V131" s="188"/>
+      <c r="W131" s="235"/>
+      <c r="X131" s="230"/>
+      <c r="Y131" s="19"/>
+      <c r="Z131" s="92"/>
+    </row>
+    <row r="132" spans="1:26" s="9" customFormat="1" ht="16.5" thickBot="1">
+      <c r="A132" s="24"/>
+      <c r="B132" s="329"/>
+      <c r="C132" s="165"/>
+      <c r="D132" s="45"/>
+      <c r="E132" s="175"/>
+      <c r="F132" s="32"/>
+      <c r="G132" s="22"/>
+      <c r="H132" s="139"/>
+      <c r="I132" s="178"/>
+      <c r="J132" s="49"/>
+      <c r="K132" s="178"/>
+      <c r="L132" s="62"/>
+      <c r="M132" s="63"/>
+      <c r="N132" s="64"/>
+      <c r="O132" s="145"/>
+      <c r="P132" s="147"/>
+      <c r="Q132" s="153"/>
+      <c r="R132" s="44"/>
+      <c r="S132" s="44"/>
+      <c r="T132" s="189"/>
+      <c r="U132" s="43"/>
+      <c r="V132" s="194"/>
+      <c r="W132" s="258"/>
+      <c r="X132" s="232"/>
+      <c r="Y132" s="20"/>
+      <c r="Z132" s="93"/>
+    </row>
+    <row r="133" spans="1:26" ht="16.5" thickBot="1"/>
+    <row r="134" spans="1:26" ht="16.5" thickBot="1">
+      <c r="C134" s="207" t="s">
         <v>38</v>
       </c>
-      <c r="D133" s="428" t="s">
+      <c r="D134" s="441" t="s">
         <v>39</v>
       </c>
-      <c r="E133" s="429"/>
-      <c r="F133" s="46"/>
-      <c r="G133" s="68"/>
-      <c r="H133" s="356" t="s">
+      <c r="E134" s="442"/>
+      <c r="F134" s="46"/>
+      <c r="G134" s="68"/>
+      <c r="H134" s="357" t="s">
         <v>14</v>
       </c>
-      <c r="I133" s="357"/>
-      <c r="J133" s="357"/>
-      <c r="K133" s="357"/>
-      <c r="L133" s="357"/>
-      <c r="M133" s="358"/>
-      <c r="N133" s="362" t="s">
+      <c r="I134" s="358"/>
+      <c r="J134" s="358"/>
+      <c r="K134" s="358"/>
+      <c r="L134" s="358"/>
+      <c r="M134" s="359"/>
+      <c r="N134" s="360" t="s">
         <v>7</v>
       </c>
-      <c r="O133" s="363"/>
-      <c r="P133" s="362" t="s">
+      <c r="O134" s="361"/>
+      <c r="P134" s="360" t="s">
         <v>110</v>
       </c>
-      <c r="Q133" s="363"/>
-      <c r="R133" s="1"/>
-      <c r="S133" s="1"/>
-      <c r="T133" s="140"/>
-      <c r="U133" s="1"/>
-      <c r="W133" s="11"/>
-      <c r="X133" s="11"/>
-      <c r="Y133" s="11"/>
-    </row>
-    <row r="134" spans="1:26" ht="16.5" customHeight="1" thickBot="1">
-      <c r="C134" s="208" t="s">
-        <v>74</v>
-      </c>
-      <c r="D134" s="435" t="s">
-        <v>77</v>
-      </c>
-      <c r="E134" s="436"/>
-      <c r="F134" s="46"/>
-      <c r="G134" s="46"/>
-      <c r="H134" s="430" t="s">
-        <v>17</v>
-      </c>
-      <c r="I134" s="431"/>
-      <c r="J134" s="130"/>
-      <c r="K134" s="210"/>
-      <c r="L134" s="117">
-        <f ca="1">M134/$M$134</f>
-        <v>1</v>
-      </c>
-      <c r="M134" s="104">
-        <f ca="1">SUM($M$135:$M$137)</f>
-        <v>127</v>
-      </c>
-      <c r="N134" s="118" t="s">
-        <v>15</v>
-      </c>
-      <c r="O134" s="119" t="s">
-        <v>16</v>
-      </c>
-      <c r="P134" s="117">
-        <f ca="1">Q134/$Q$134</f>
-        <v>1</v>
-      </c>
-      <c r="Q134" s="104">
-        <f ca="1">SUM(Q135:Q136)</f>
-        <v>109</v>
-      </c>
+      <c r="Q134" s="361"/>
       <c r="R134" s="1"/>
       <c r="S134" s="1"/>
       <c r="T134" s="140"/>
@@ -39794,45 +39861,43 @@
       <c r="X134" s="11"/>
       <c r="Y134" s="11"/>
     </row>
-    <row r="135" spans="1:26">
-      <c r="C135" s="394" t="s">
-        <v>6</v>
-      </c>
-      <c r="D135" s="435" t="s">
-        <v>40</v>
-      </c>
-      <c r="E135" s="436"/>
-      <c r="F135" s="69"/>
-      <c r="G135" s="6"/>
-      <c r="H135" s="432" t="s">
-        <v>69</v>
-      </c>
-      <c r="I135" s="433"/>
-      <c r="J135" s="433"/>
-      <c r="K135" s="434"/>
-      <c r="L135" s="122">
-        <f t="shared" ref="L135:L137" ca="1" si="61">M135/$M$134</f>
-        <v>0.84251968503937003</v>
-      </c>
-      <c r="M135" s="123">
-        <f>COUNTIF($H$7:$H$131,"RFCS")</f>
-        <v>107</v>
-      </c>
-      <c r="N135" s="121">
-        <f ca="1">COUNTIFS($I$7:$I$131,"&lt;=21",$H$7:$H$131,"RFCS")</f>
-        <v>65</v>
-      </c>
-      <c r="O135" s="120">
-        <f ca="1">COUNTIFS($I$7:$I$131,"&gt;21",$H$7:$H$131,"RFCS")</f>
-        <v>41</v>
-      </c>
-      <c r="P135" s="122">
-        <f ca="1">Q135/$Q$134</f>
-        <v>0.62385321100917435</v>
-      </c>
-      <c r="Q135" s="123">
-        <f>COUNTIF($Q$7:$Q$131,"RBE") + COUNTIF($Q$7:$Q$131,"SUP")</f>
-        <v>68</v>
+    <row r="135" spans="1:26" ht="16.5" customHeight="1" thickBot="1">
+      <c r="C135" s="208" t="s">
+        <v>74</v>
+      </c>
+      <c r="D135" s="439" t="s">
+        <v>77</v>
+      </c>
+      <c r="E135" s="440"/>
+      <c r="F135" s="46"/>
+      <c r="G135" s="46"/>
+      <c r="H135" s="434" t="s">
+        <v>17</v>
+      </c>
+      <c r="I135" s="435"/>
+      <c r="J135" s="130"/>
+      <c r="K135" s="210"/>
+      <c r="L135" s="117">
+        <f ca="1">M135/$M$135</f>
+        <v>1</v>
+      </c>
+      <c r="M135" s="104">
+        <f ca="1">SUM($M$136:$M$138)</f>
+        <v>128</v>
+      </c>
+      <c r="N135" s="118" t="s">
+        <v>15</v>
+      </c>
+      <c r="O135" s="119" t="s">
+        <v>16</v>
+      </c>
+      <c r="P135" s="117">
+        <f ca="1">Q135/$Q$135</f>
+        <v>1</v>
+      </c>
+      <c r="Q135" s="104">
+        <f ca="1">SUM(Q136:Q137)</f>
+        <v>110</v>
       </c>
       <c r="R135" s="1"/>
       <c r="S135" s="1"/>
@@ -39843,44 +39908,46 @@
       <c r="Y135" s="11"/>
     </row>
     <row r="136" spans="1:26">
-      <c r="C136" s="394"/>
-      <c r="D136" s="435"/>
-      <c r="E136" s="436"/>
-      <c r="F136" s="72"/>
+      <c r="C136" s="385" t="s">
+        <v>6</v>
+      </c>
+      <c r="D136" s="439" t="s">
+        <v>40</v>
+      </c>
+      <c r="E136" s="440"/>
+      <c r="F136" s="69"/>
       <c r="G136" s="6"/>
-      <c r="H136" s="388" t="s">
-        <v>70</v>
-      </c>
-      <c r="I136" s="389"/>
-      <c r="J136" s="389"/>
-      <c r="K136" s="390"/>
-      <c r="L136" s="124">
-        <f t="shared" ca="1" si="61"/>
-        <v>4.7244094488188976E-2</v>
-      </c>
-      <c r="M136" s="125">
-        <f ca="1">SUM(N136:O136)</f>
-        <v>6</v>
-      </c>
-      <c r="N136" s="98">
-        <f ca="1">COUNTIFS($I$7:$I$131,"&lt;=21",$U$7:$U$131,"",$K$7:$K$131,"&lt;&gt;X")</f>
-        <v>1</v>
-      </c>
-      <c r="O136" s="50">
-        <f ca="1">COUNTIFS($I$7:$I$131,"&gt;21",$U$7:$U$131,"",$K$7:$K$131,"&lt;&gt;X")</f>
-        <v>5</v>
-      </c>
-      <c r="P136" s="124">
-        <f ca="1">Q136/$Q$134</f>
-        <v>0.37614678899082571</v>
-      </c>
-      <c r="Q136" s="125">
-        <f ca="1">COUNTIFS($I$7:$I$131,"&gt;=0",$P$7:$P$131,"",$K$7:$K$131,"&lt;&gt;X")</f>
-        <v>41</v>
-      </c>
-      <c r="R136" s="1" t="s">
-        <v>10</v>
-      </c>
+      <c r="H136" s="436" t="s">
+        <v>69</v>
+      </c>
+      <c r="I136" s="437"/>
+      <c r="J136" s="437"/>
+      <c r="K136" s="438"/>
+      <c r="L136" s="122">
+        <f t="shared" ref="L136:L138" ca="1" si="62">M136/$M$135</f>
+        <v>0.84375</v>
+      </c>
+      <c r="M136" s="123">
+        <f>COUNTIF($H$7:$H$132,"RFCS")</f>
+        <v>108</v>
+      </c>
+      <c r="N136" s="121">
+        <f ca="1">COUNTIFS($I$7:$I$132,"&lt;=21",$H$7:$H$132,"RFCS")</f>
+        <v>65</v>
+      </c>
+      <c r="O136" s="120">
+        <f ca="1">COUNTIFS($I$7:$I$132,"&gt;21",$H$7:$H$132,"RFCS")</f>
+        <v>42</v>
+      </c>
+      <c r="P136" s="122">
+        <f ca="1">Q136/$Q$135</f>
+        <v>0.61818181818181817</v>
+      </c>
+      <c r="Q136" s="123">
+        <f>COUNTIF($Q$7:$Q$132,"RBE") + COUNTIF($Q$7:$Q$132,"SUP")</f>
+        <v>68</v>
+      </c>
+      <c r="R136" s="1"/>
       <c r="S136" s="1"/>
       <c r="T136" s="140"/>
       <c r="U136" s="1"/>
@@ -39888,66 +39955,112 @@
       <c r="X136" s="11"/>
       <c r="Y136" s="11"/>
     </row>
-    <row r="137" spans="1:26" ht="16.5" thickBot="1">
-      <c r="C137" s="394" t="s">
+    <row r="137" spans="1:26">
+      <c r="C137" s="385"/>
+      <c r="D137" s="439"/>
+      <c r="E137" s="440"/>
+      <c r="F137" s="72"/>
+      <c r="G137" s="6"/>
+      <c r="H137" s="382" t="s">
+        <v>70</v>
+      </c>
+      <c r="I137" s="383"/>
+      <c r="J137" s="383"/>
+      <c r="K137" s="384"/>
+      <c r="L137" s="124">
+        <f t="shared" ca="1" si="62"/>
+        <v>4.6875E-2</v>
+      </c>
+      <c r="M137" s="125">
+        <f ca="1">SUM(N137:O137)</f>
+        <v>6</v>
+      </c>
+      <c r="N137" s="98">
+        <f ca="1">COUNTIFS($I$7:$I$132,"&lt;=21",$U$7:$U$132,"",$K$7:$K$132,"&lt;&gt;X")</f>
+        <v>1</v>
+      </c>
+      <c r="O137" s="50">
+        <f ca="1">COUNTIFS($I$7:$I$132,"&gt;21",$U$7:$U$132,"",$K$7:$K$132,"&lt;&gt;X")</f>
+        <v>5</v>
+      </c>
+      <c r="P137" s="124">
+        <f ca="1">Q137/$Q$135</f>
+        <v>0.38181818181818183</v>
+      </c>
+      <c r="Q137" s="125">
+        <f ca="1">COUNTIFS($I$7:$I$132,"&gt;=0",$P$7:$P$132,"",$K$7:$K$132,"&lt;&gt;X")</f>
+        <v>42</v>
+      </c>
+      <c r="R137" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="S137" s="1"/>
+      <c r="T137" s="140"/>
+      <c r="U137" s="1"/>
+      <c r="W137" s="11"/>
+      <c r="X137" s="11"/>
+      <c r="Y137" s="11"/>
+    </row>
+    <row r="138" spans="1:26" ht="16.5" thickBot="1">
+      <c r="C138" s="385" t="s">
         <v>75</v>
       </c>
-      <c r="D137" s="350" t="s">
+      <c r="D138" s="387" t="s">
         <v>76</v>
       </c>
-      <c r="E137" s="351"/>
-      <c r="H137" s="391" t="s">
+      <c r="E138" s="388"/>
+      <c r="H138" s="354" t="s">
         <v>71</v>
       </c>
-      <c r="I137" s="392"/>
-      <c r="J137" s="392"/>
-      <c r="K137" s="393"/>
-      <c r="L137" s="126">
-        <f t="shared" ca="1" si="61"/>
-        <v>0.11023622047244094</v>
-      </c>
-      <c r="M137" s="116">
-        <f>COUNTIFS($K$7:$K$131,"X")</f>
+      <c r="I138" s="355"/>
+      <c r="J138" s="355"/>
+      <c r="K138" s="356"/>
+      <c r="L138" s="126">
+        <f t="shared" ca="1" si="62"/>
+        <v>0.109375</v>
+      </c>
+      <c r="M138" s="116">
+        <f>COUNTIFS($K$7:$K$132,"X")</f>
         <v>14</v>
       </c>
-      <c r="N137" s="99"/>
-      <c r="O137" s="51"/>
-      <c r="P137" s="223"/>
-      <c r="Q137" s="224"/>
-    </row>
-    <row r="138" spans="1:26" ht="16.5" thickBot="1">
-      <c r="C138" s="395"/>
-      <c r="D138" s="352"/>
-      <c r="E138" s="353"/>
-    </row>
-    <row r="140" spans="1:26">
-      <c r="C140" s="378" t="s">
+      <c r="N138" s="99"/>
+      <c r="O138" s="51"/>
+      <c r="P138" s="223"/>
+      <c r="Q138" s="224"/>
+    </row>
+    <row r="139" spans="1:26" ht="16.5" thickBot="1">
+      <c r="C139" s="386"/>
+      <c r="D139" s="389"/>
+      <c r="E139" s="390"/>
+    </row>
+    <row r="141" spans="1:26">
+      <c r="C141" s="372" t="s">
         <v>41</v>
       </c>
-      <c r="D140" s="378"/>
-      <c r="E140" s="378"/>
-    </row>
-    <row r="141" spans="1:26">
-      <c r="C141" s="169" t="s">
-        <v>8</v>
-      </c>
-      <c r="D141" s="1" t="s">
-        <v>42</v>
-      </c>
+      <c r="D141" s="372"/>
+      <c r="E141" s="372"/>
     </row>
     <row r="142" spans="1:26">
       <c r="C142" s="169" t="s">
         <v>8</v>
       </c>
-      <c r="D142" s="127" t="s">
-        <v>43</v>
+      <c r="D142" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="143" spans="1:26">
       <c r="C143" s="169" t="s">
         <v>8</v>
       </c>
-      <c r="D143" s="1" t="s">
+      <c r="D143" s="127" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="144" spans="1:26">
+      <c r="C144" s="169" t="s">
+        <v>8</v>
+      </c>
+      <c r="D144" s="1" t="s">
         <v>44</v>
       </c>
     </row>
@@ -39958,6 +40071,22 @@
     </sortState>
   </autoFilter>
   <mergeCells count="32">
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="P134:Q134"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="D134:E134"/>
+    <mergeCell ref="H134:M134"/>
+    <mergeCell ref="N134:O134"/>
+    <mergeCell ref="H135:I135"/>
+    <mergeCell ref="C141:E141"/>
+    <mergeCell ref="H136:K136"/>
+    <mergeCell ref="H137:K137"/>
+    <mergeCell ref="H138:K138"/>
+    <mergeCell ref="D135:E135"/>
+    <mergeCell ref="C136:C137"/>
+    <mergeCell ref="D136:E137"/>
+    <mergeCell ref="C138:C139"/>
+    <mergeCell ref="D138:E139"/>
     <mergeCell ref="Z4:Z5"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="D4:D5"/>
@@ -39974,25 +40103,9 @@
     <mergeCell ref="K4:K5"/>
     <mergeCell ref="P4:Q4"/>
     <mergeCell ref="X4:Y4"/>
-    <mergeCell ref="H134:I134"/>
-    <mergeCell ref="C140:E140"/>
-    <mergeCell ref="H135:K135"/>
-    <mergeCell ref="H136:K136"/>
-    <mergeCell ref="H137:K137"/>
-    <mergeCell ref="D134:E134"/>
-    <mergeCell ref="C135:C136"/>
-    <mergeCell ref="D135:E136"/>
-    <mergeCell ref="C137:C138"/>
-    <mergeCell ref="D137:E138"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="P133:Q133"/>
-    <mergeCell ref="J4:J5"/>
-    <mergeCell ref="D133:E133"/>
-    <mergeCell ref="H133:M133"/>
-    <mergeCell ref="N133:O133"/>
   </mergeCells>
   <phoneticPr fontId="71"/>
-  <conditionalFormatting sqref="A7:Z131">
+  <conditionalFormatting sqref="A7:Z132">
     <cfRule type="expression" dxfId="4" priority="1">
       <formula>$K7="X"</formula>
     </cfRule>
@@ -40137,9 +40250,9 @@
     <hyperlink ref="O43" r:id="rId125" xr:uid="{0E3F3A7F-DA9A-49F8-A93F-8337122FAE1A}"/>
     <hyperlink ref="N41" r:id="rId126" xr:uid="{3405D711-BDD4-4069-A376-D6B961D87010}"/>
     <hyperlink ref="N43" r:id="rId127" xr:uid="{525398A7-A7B1-41B1-88A2-7E7F9115541E}"/>
-    <hyperlink ref="C141" r:id="rId128" xr:uid="{F06CE902-4089-4B08-A7E9-420A16C9FF0E}"/>
-    <hyperlink ref="C142" r:id="rId129" xr:uid="{6D322F1B-B574-40E7-BED0-14ED893C19C5}"/>
-    <hyperlink ref="C143" r:id="rId130" xr:uid="{1845DEB0-969B-4FE7-B52A-52C25D3EC72E}"/>
+    <hyperlink ref="C142" r:id="rId128" xr:uid="{F06CE902-4089-4B08-A7E9-420A16C9FF0E}"/>
+    <hyperlink ref="C143" r:id="rId129" xr:uid="{6D322F1B-B574-40E7-BED0-14ED893C19C5}"/>
+    <hyperlink ref="C144" r:id="rId130" xr:uid="{1845DEB0-969B-4FE7-B52A-52C25D3EC72E}"/>
     <hyperlink ref="N42" r:id="rId131" xr:uid="{95D9F3CF-8EC0-4C96-9F49-34E6585C583B}"/>
     <hyperlink ref="L44" r:id="rId132" xr:uid="{255E79C1-4568-41F7-B71E-8301B034AA56}"/>
     <hyperlink ref="P8" r:id="rId133" xr:uid="{4339778F-2FA8-45DA-BD1F-0684B78D35ED}"/>
@@ -40491,9 +40604,11 @@
     <hyperlink ref="N127" r:id="rId479" xr:uid="{984FC4EC-B838-4F05-998C-F6897E6C0896}"/>
     <hyperlink ref="N125" r:id="rId480" xr:uid="{ECB0E570-ED5C-4126-9B31-6711B56E14D0}"/>
     <hyperlink ref="N128" r:id="rId481" xr:uid="{1CA6C02A-5CE8-4BB3-A561-833347DA6DD6}"/>
+    <hyperlink ref="L130" r:id="rId482" xr:uid="{7D960168-2434-4940-BEFA-A280CD48B60C}"/>
+    <hyperlink ref="N130" r:id="rId483" xr:uid="{B567A3B4-9E9F-477C-ACA4-EAD1E0777B05}"/>
   </hyperlinks>
   <pageMargins left="0.25" right="0.17" top="0.5" bottom="0.25" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="28" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId482"/>
+  <pageSetup paperSize="9" scale="28" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId484"/>
 </worksheet>
 </file>
 
@@ -40578,19 +40693,19 @@
       <c r="S3" s="281"/>
     </row>
     <row r="4" spans="1:25" ht="36" customHeight="1" thickBot="1">
-      <c r="A4" s="408" t="s">
+      <c r="A4" s="397" t="s">
         <v>123</v>
       </c>
-      <c r="B4" s="366" t="s">
+      <c r="B4" s="364" t="s">
         <v>45</v>
       </c>
-      <c r="C4" s="366" t="s">
+      <c r="C4" s="364" t="s">
         <v>95</v>
       </c>
-      <c r="D4" s="366" t="s">
+      <c r="D4" s="364" t="s">
         <v>46</v>
       </c>
-      <c r="E4" s="369" t="s">
+      <c r="E4" s="362" t="s">
         <v>4</v>
       </c>
       <c r="F4" s="449" t="s">
@@ -40619,12 +40734,12 @@
       <c r="S4" s="448"/>
     </row>
     <row r="5" spans="1:25" ht="78.75">
-      <c r="A5" s="409"/>
-      <c r="B5" s="367"/>
-      <c r="C5" s="367"/>
-      <c r="D5" s="367"/>
-      <c r="E5" s="370"/>
-      <c r="F5" s="411"/>
+      <c r="A5" s="398"/>
+      <c r="B5" s="365"/>
+      <c r="C5" s="365"/>
+      <c r="D5" s="365"/>
+      <c r="E5" s="369"/>
+      <c r="F5" s="402"/>
       <c r="G5" s="283" t="s">
         <v>56</v>
       </c>
@@ -41966,7 +42081,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42223A76-B79E-483C-82B7-07960417E780}">
-  <dimension ref="A1:R17"/>
+  <dimension ref="A1:R14"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="13" customWidth="1"/>
@@ -42041,16 +42156,16 @@
       <c r="R3" s="281"/>
     </row>
     <row r="4" spans="1:18" ht="16.5" thickBot="1">
-      <c r="A4" s="408" t="s">
+      <c r="A4" s="397" t="s">
         <v>123</v>
       </c>
-      <c r="B4" s="366" t="s">
+      <c r="B4" s="364" t="s">
         <v>45</v>
       </c>
-      <c r="C4" s="366" t="s">
+      <c r="C4" s="364" t="s">
         <v>46</v>
       </c>
-      <c r="D4" s="364" t="s">
+      <c r="D4" s="366" t="s">
         <v>4</v>
       </c>
       <c r="E4" s="449" t="s">
@@ -42079,11 +42194,11 @@
       <c r="R4" s="448"/>
     </row>
     <row r="5" spans="1:18" ht="78.75">
-      <c r="A5" s="409"/>
-      <c r="B5" s="367"/>
-      <c r="C5" s="367"/>
-      <c r="D5" s="440"/>
-      <c r="E5" s="370"/>
+      <c r="A5" s="398"/>
+      <c r="B5" s="365"/>
+      <c r="C5" s="365"/>
+      <c r="D5" s="431"/>
+      <c r="E5" s="369"/>
       <c r="F5" s="283" t="s">
         <v>56</v>
       </c>
@@ -42334,7 +42449,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="105">
+    <row r="10" spans="1:18" ht="45">
       <c r="A10" s="13">
         <v>4</v>
       </c>
@@ -42391,7 +42506,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="45">
+    <row r="11" spans="1:18" ht="75">
       <c r="A11" s="13">
         <v>5</v>
       </c>
@@ -42503,7 +42618,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="75">
+    <row r="13" spans="1:18" ht="60">
       <c r="A13" s="13">
         <v>7</v>
       </c>
@@ -42615,9 +42730,6 @@
         <v>311</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="45"/>
-    <row r="16" spans="1:18" ht="60"/>
-    <row r="17" ht="45"/>
   </sheetData>
   <autoFilter ref="A6:R6" xr:uid="{75733AF3-96C4-423A-BD99-1E08B3C66916}"/>
   <mergeCells count="9">

--- a/ICT-RFA-RFI-lists-New.xlsx
+++ b/ICT-RFA-RFI-lists-New.xlsx
@@ -9,9 +9,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project Airport\LTIA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DDD01A7-70A4-4C79-AE18-DC92C297D06E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF16DFFE-99A1-43A8-B745-71630EDB6E43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="506" activeTab="2" xr2:uid="{CCA8147E-0981-4321-B87F-440A52C0DA59}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="506" activeTab="1" xr2:uid="{CCA8147E-0981-4321-B87F-440A52C0DA59}"/>
   </bookViews>
   <sheets>
     <sheet name="RFA" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Need ReSub (RFA-SDS)'!$A$6:$R$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">RFA!$A$6:$AE$143</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'RFA-SDS'!$A$6:$AD$47</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">RFI!$A$6:$Z$127</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">RFI!$A$6:$Z$130</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Need ReSub (RFA)'!$A$1:$S$77</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'Need ReSub (RFA-SDS)'!$A$1:$R$62</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">RFA!$A$1:$AE$143,RFA!$I$145:$R$151,RFA!$C$145:$F$155,RFA!$C$157:$F$160,RFA!$C$162:$F$173</definedName>
@@ -78,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3543" uniqueCount="1116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3585" uniqueCount="1117">
   <si>
     <t>TT</t>
   </si>
@@ -4401,9 +4401,6 @@
     <t>Đề xuất phương án đi ông và kéo dây cho camera ô trống, biển chỉ dẫn, kiosk tự phục vụ và biển báo trống trong nhà xe khối P1 &amp; P2</t>
   </si>
   <si>
-    <t>18/6/2026 Đã ký</t>
-  </si>
-  <si>
     <t>LTIA-5.10-VIETUR-70000-RFA-OTH-0712</t>
   </si>
   <si>
@@ -4766,9 +4763,6 @@
 9/9/2026: Đã ký A</t>
   </si>
   <si>
-    <t xml:space="preserve">LTIA-5.10-VIETUR-70000-RFA-MAS-0821 </t>
-  </si>
-  <si>
     <t>Request for approval of additional ICT cable – ELV System</t>
   </si>
   <si>
@@ -4913,12 +4907,6 @@
   <si>
     <t>9/28/2026 Đã cmt và gửi cho CNC
 9/29/2026 Đã ký C</t>
-  </si>
-  <si>
-    <t>9/8/2026 Update
-9/24/2026 Update
-9/25/2026 Đã cmt và gửi cho CNC
-9/29/2026 Đã ký B</t>
   </si>
   <si>
     <t>LTIA-5.11- LTICT- 72100-RFA-MSS-0002</t>
@@ -5033,9 +5021,6 @@
     <t>Bản vẽ TKTC cho hệ thống ICT – phần 1 – Hệ thống ICT cho Bản Vẽ Phòng Kỹ Thuật Tầng GF, Tầng 3, FLB</t>
   </si>
   <si>
-    <t>10/12/2026: Đã comment</t>
-  </si>
-  <si>
     <t>LTIA-5.11-LTICT- 71110 -RFA-OTH-0012</t>
   </si>
   <si>
@@ -5145,9 +5130,6 @@
     <t>Construction design drawing of  ICT system – part.1: ICT systems for DATA CENTER 2 (DC2) &amp; TECHNICAL ROOM (EF,BD)</t>
   </si>
   <si>
-    <t>10/19/2026: Đã comment</t>
-  </si>
-  <si>
     <t>10/12/2026: Đã comment
 10/13/2026: Đã gửi comment qua CNC
 10/19/2026: Đã ký C</t>
@@ -5205,6 +5187,33 @@
   </si>
   <si>
     <t>10/20/2026: Đã ký RFCS</t>
+  </si>
+  <si>
+    <t>9/8/2026 Update
+9/24/2026 Update
+9/25/2026 Đã cmt và gửi cho CNC
+9/29/2026 Đã ký B
+10/22/2026: Bản ký duyệt B ngày 29/9/2026 đã rút</t>
+  </si>
+  <si>
+    <t>LTIA-5.10-VIETUR-70000-RFA-MAS-0821</t>
+  </si>
+  <si>
+    <t>10/1/2026: Đã comemnt
+Withdraw (nhưng không có mail)</t>
+  </si>
+  <si>
+    <t>10/12/2026: Đã comment
+10/22/2026: Đã gửi comment qua CNC
+10/22/2026: Đã ký C</t>
+  </si>
+  <si>
+    <t>10/19/2026: Đã comment
+10/22/2026: Đã gửi comment qua CNC
+10/22/2026: Đã ký C</t>
+  </si>
+  <si>
+    <t>18/6/2026 Đã ký RFCS</t>
   </si>
 </sst>
 </file>
@@ -7641,6 +7650,273 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="53" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="47" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="51" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="52" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="45" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="55" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="55" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -7658,273 +7934,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="51" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="52" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="55" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="55" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="45" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="53" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="47" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -8500,7 +8509,7 @@
       </c>
       <c r="J1" s="176">
         <f ca="1">TODAY()</f>
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="K1" s="131"/>
       <c r="L1" s="197"/>
@@ -8587,92 +8596,92 @@
       <c r="AE3" s="159"/>
     </row>
     <row r="4" spans="1:35" s="5" customFormat="1" ht="36" customHeight="1" thickBot="1">
-      <c r="A4" s="397" t="s">
+      <c r="A4" s="426" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="407" t="s">
+      <c r="B4" s="348" t="s">
         <v>515</v>
       </c>
-      <c r="C4" s="403" t="s">
+      <c r="C4" s="391" t="s">
         <v>45</v>
       </c>
-      <c r="D4" s="364" t="s">
+      <c r="D4" s="385" t="s">
         <v>95</v>
       </c>
-      <c r="E4" s="362" t="s">
+      <c r="E4" s="352" t="s">
         <v>46</v>
       </c>
-      <c r="F4" s="399" t="s">
+      <c r="F4" s="430" t="s">
         <v>47</v>
       </c>
-      <c r="G4" s="362" t="s">
+      <c r="G4" s="352" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="401" t="s">
+      <c r="H4" s="428" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="364" t="s">
+      <c r="I4" s="385" t="s">
         <v>48</v>
       </c>
-      <c r="J4" s="364" t="s">
+      <c r="J4" s="385" t="s">
         <v>49</v>
       </c>
-      <c r="K4" s="362" t="s">
+      <c r="K4" s="352" t="s">
         <v>78</v>
       </c>
-      <c r="L4" s="364" t="s">
+      <c r="L4" s="385" t="s">
         <v>80</v>
       </c>
-      <c r="M4" s="366" t="s">
+      <c r="M4" s="390" t="s">
         <v>53</v>
       </c>
-      <c r="N4" s="367"/>
-      <c r="O4" s="366" t="s">
+      <c r="N4" s="379"/>
+      <c r="O4" s="390" t="s">
         <v>55</v>
       </c>
-      <c r="P4" s="367"/>
-      <c r="Q4" s="368" t="s">
+      <c r="P4" s="379"/>
+      <c r="Q4" s="389" t="s">
         <v>72</v>
       </c>
-      <c r="R4" s="367"/>
-      <c r="S4" s="366" t="s">
+      <c r="R4" s="379"/>
+      <c r="S4" s="390" t="s">
         <v>53</v>
       </c>
-      <c r="T4" s="366"/>
-      <c r="U4" s="367"/>
-      <c r="V4" s="368" t="s">
+      <c r="T4" s="390"/>
+      <c r="U4" s="379"/>
+      <c r="V4" s="389" t="s">
         <v>55</v>
       </c>
-      <c r="W4" s="366"/>
-      <c r="X4" s="367"/>
+      <c r="W4" s="390"/>
+      <c r="X4" s="379"/>
       <c r="Y4" s="393" t="s">
         <v>72</v>
       </c>
-      <c r="Z4" s="427"/>
-      <c r="AA4" s="426" t="s">
+      <c r="Z4" s="394"/>
+      <c r="AA4" s="397" t="s">
         <v>112</v>
       </c>
-      <c r="AB4" s="395"/>
-      <c r="AC4" s="395"/>
-      <c r="AD4" s="396"/>
-      <c r="AE4" s="362" t="s">
+      <c r="AB4" s="398"/>
+      <c r="AC4" s="398"/>
+      <c r="AD4" s="399"/>
+      <c r="AE4" s="352" t="s">
         <v>79</v>
       </c>
       <c r="AG4" s="236"/>
     </row>
     <row r="5" spans="1:35" ht="78.75">
-      <c r="A5" s="398"/>
-      <c r="B5" s="408"/>
-      <c r="C5" s="404"/>
-      <c r="D5" s="365"/>
-      <c r="E5" s="369"/>
-      <c r="F5" s="400"/>
-      <c r="G5" s="369"/>
-      <c r="H5" s="402"/>
-      <c r="I5" s="365"/>
-      <c r="J5" s="365"/>
-      <c r="K5" s="369"/>
-      <c r="L5" s="365"/>
+      <c r="A5" s="427"/>
+      <c r="B5" s="349"/>
+      <c r="C5" s="392"/>
+      <c r="D5" s="386"/>
+      <c r="E5" s="353"/>
+      <c r="F5" s="431"/>
+      <c r="G5" s="353"/>
+      <c r="H5" s="429"/>
+      <c r="I5" s="386"/>
+      <c r="J5" s="386"/>
+      <c r="K5" s="353"/>
+      <c r="L5" s="386"/>
       <c r="M5" s="79" t="s">
         <v>52</v>
       </c>
@@ -8727,14 +8736,14 @@
       <c r="AD5" s="336" t="s">
         <v>118</v>
       </c>
-      <c r="AE5" s="363"/>
-      <c r="AG5" s="362" t="s">
+      <c r="AE5" s="380"/>
+      <c r="AG5" s="352" t="s">
         <v>119</v>
       </c>
-      <c r="AH5" s="362" t="s">
+      <c r="AH5" s="352" t="s">
         <v>120</v>
       </c>
-      <c r="AI5" s="362" t="s">
+      <c r="AI5" s="352" t="s">
         <v>121</v>
       </c>
     </row>
@@ -8770,9 +8779,9 @@
       <c r="AC6" s="86"/>
       <c r="AD6" s="86"/>
       <c r="AE6" s="74"/>
-      <c r="AG6" s="409"/>
-      <c r="AH6" s="409"/>
-      <c r="AI6" s="409"/>
+      <c r="AG6" s="425"/>
+      <c r="AH6" s="425"/>
+      <c r="AI6" s="425"/>
     </row>
     <row r="7" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A7" s="33">
@@ -9691,7 +9700,7 @@
       </c>
       <c r="AD14" s="337">
         <f t="shared" ca="1" si="7"/>
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="AE14" s="92"/>
       <c r="AG14" s="238" t="str">
@@ -9807,7 +9816,7 @@
       </c>
       <c r="AD15" s="337">
         <f t="shared" ca="1" si="7"/>
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="AE15" s="92"/>
       <c r="AG15" s="238" t="str">
@@ -10866,7 +10875,7 @@
         <v/>
       </c>
       <c r="AE24" s="92" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="AG24" s="238" t="str">
         <f t="shared" si="8"/>
@@ -13195,7 +13204,7 @@
       </c>
       <c r="AD44" s="337">
         <f t="shared" ca="1" si="13"/>
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AE44" s="92"/>
       <c r="AG44" s="238" t="str">
@@ -13429,7 +13438,7 @@
       </c>
       <c r="AD46" s="337">
         <f t="shared" ca="1" si="13"/>
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AE46" s="92"/>
       <c r="AG46" s="238" t="str">
@@ -13895,7 +13904,7 @@
       </c>
       <c r="AD50" s="337">
         <f t="shared" ca="1" si="13"/>
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AE50" s="92"/>
       <c r="AG50" s="238" t="str">
@@ -13946,7 +13955,7 @@
       <c r="I51" s="138"/>
       <c r="J51" s="164">
         <f t="shared" ca="1" si="3"/>
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="K51" s="47"/>
       <c r="L51" s="164" t="s">
@@ -14104,7 +14113,7 @@
         <v/>
       </c>
       <c r="AE52" s="92" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="AG52" s="238" t="str">
         <f t="shared" si="14"/>
@@ -14222,7 +14231,7 @@
         <v/>
       </c>
       <c r="AE53" s="92" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="AG53" s="238" t="str">
         <f t="shared" si="14"/>
@@ -14572,7 +14581,7 @@
         <v/>
       </c>
       <c r="AE56" s="92" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="AG56" s="238" t="str">
         <f t="shared" si="14"/>
@@ -14803,7 +14812,7 @@
       </c>
       <c r="AD58" s="337">
         <f t="shared" ca="1" si="13"/>
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AE58" s="92"/>
       <c r="AG58" s="238" t="str">
@@ -14854,7 +14863,7 @@
       <c r="I59" s="138"/>
       <c r="J59" s="164">
         <f t="shared" ca="1" si="3"/>
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="K59" s="47"/>
       <c r="L59" s="164" t="s">
@@ -15014,7 +15023,7 @@
         <v>203</v>
       </c>
       <c r="AE60" s="92" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="AG60" s="238" t="str">
         <f t="shared" si="14"/>
@@ -15029,11 +15038,11 @@
 0,
 -1
 )</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI60" s="75" t="str">
         <f t="shared" si="9"/>
-        <v/>
+        <v>YES</v>
       </c>
     </row>
     <row r="61" spans="1:35" s="9" customFormat="1" ht="47.25">
@@ -15129,7 +15138,7 @@
       </c>
       <c r="AD61" s="337">
         <f t="shared" ca="1" si="13"/>
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AE61" s="92"/>
       <c r="AG61" s="238" t="str">
@@ -15366,7 +15375,7 @@
         <v/>
       </c>
       <c r="AE63" s="92" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="AG63" s="238" t="str">
         <f t="shared" si="14"/>
@@ -15484,7 +15493,7 @@
         <v/>
       </c>
       <c r="AE64" s="92" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="AG64" s="238" t="str">
         <f t="shared" si="14"/>
@@ -15602,7 +15611,7 @@
         <v/>
       </c>
       <c r="AE65" s="92" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="AG65" s="238" t="str">
         <f t="shared" si="14"/>
@@ -15720,7 +15729,7 @@
         <v/>
       </c>
       <c r="AE66" s="92" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="AG66" s="238" t="str">
         <f t="shared" si="14"/>
@@ -15949,7 +15958,7 @@
       </c>
       <c r="AD68" s="337">
         <f t="shared" ca="1" si="13"/>
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AE68" s="92"/>
       <c r="AG68" s="238" t="str">
@@ -16024,8 +16033,12 @@
       <c r="P69" s="41" t="s">
         <v>8</v>
       </c>
-      <c r="Q69" s="40"/>
-      <c r="R69" s="155"/>
+      <c r="Q69" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="R69" s="155" t="s">
+        <v>3</v>
+      </c>
       <c r="S69" s="27">
         <v>46140</v>
       </c>
@@ -16044,11 +16057,15 @@
       <c r="X69" s="235" t="s">
         <v>190</v>
       </c>
-      <c r="Y69" s="230"/>
-      <c r="Z69" s="227"/>
-      <c r="AA69" s="29" t="b">
+      <c r="Y69" s="230">
+        <v>46191</v>
+      </c>
+      <c r="Z69" s="227">
+        <v>46199</v>
+      </c>
+      <c r="AA69" s="29" t="str">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AB69" s="229"/>
       <c r="AC69" s="229" t="str">
@@ -17330,7 +17347,7 @@
         <v/>
       </c>
       <c r="AE80" s="92" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="AG80" s="238" t="str">
         <f t="shared" si="14"/>
@@ -17751,7 +17768,7 @@
         <v/>
       </c>
       <c r="AE84" s="92" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="AG84" s="238" t="str">
         <f t="shared" si="14"/>
@@ -17869,7 +17886,7 @@
         <v/>
       </c>
       <c r="AE85" s="92" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="AG85" s="238" t="str">
         <f t="shared" si="14"/>
@@ -17979,7 +17996,7 @@
         <v/>
       </c>
       <c r="AE86" s="92" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="AG86" s="238" t="str">
         <f t="shared" si="14"/>
@@ -18571,14 +18588,14 @@
       <c r="I92" s="138"/>
       <c r="J92" s="164">
         <f t="shared" ca="1" si="27"/>
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="K92" s="47">
         <f t="shared" ca="1" si="28"/>
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="L92" s="164" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="M92" s="40" t="s">
         <v>8</v>
@@ -18673,11 +18690,11 @@
       </c>
       <c r="J93" s="164">
         <f t="shared" ca="1" si="27"/>
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="K93" s="47">
         <f t="shared" ca="1" si="28"/>
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L93" s="164" t="s">
         <v>13</v>
@@ -19465,7 +19482,7 @@
         <v/>
       </c>
       <c r="AE100" s="92" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="AG100" s="238" t="str">
         <f t="shared" si="14"/>
@@ -19663,7 +19680,7 @@
         <v/>
       </c>
       <c r="AE102" s="92" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="AG102" s="238" t="str">
         <f t="shared" si="14"/>
@@ -19701,17 +19718,17 @@
         <v>28</v>
       </c>
       <c r="E103" s="25" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="F103" s="174">
         <f t="shared" si="29"/>
         <v>46195</v>
       </c>
       <c r="G103" s="31" t="s">
+        <v>869</v>
+      </c>
+      <c r="H103" s="21" t="s">
         <v>870</v>
-      </c>
-      <c r="H103" s="21" t="s">
-        <v>871</v>
       </c>
       <c r="I103" s="138" t="s">
         <v>1</v>
@@ -19737,8 +19754,12 @@
       <c r="P103" s="41" t="s">
         <v>8</v>
       </c>
-      <c r="Q103" s="40"/>
-      <c r="R103" s="155"/>
+      <c r="Q103" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="R103" s="155" t="s">
+        <v>1</v>
+      </c>
       <c r="S103" s="27">
         <v>46174</v>
       </c>
@@ -19757,25 +19778,29 @@
       <c r="X103" s="235" t="s">
         <v>240</v>
       </c>
-      <c r="Y103" s="230"/>
-      <c r="Z103" s="227"/>
+      <c r="Y103" s="230">
+        <v>46212</v>
+      </c>
+      <c r="Z103" s="227">
+        <v>46213</v>
+      </c>
       <c r="AA103" s="29">
         <f t="shared" si="21"/>
-        <v>46204</v>
+        <v>46220</v>
       </c>
       <c r="AB103" s="229">
         <v>46247</v>
       </c>
       <c r="AC103" s="229" t="str">
         <f t="shared" si="22"/>
-        <v/>
-      </c>
-      <c r="AD103" s="337" t="str">
+        <v>Late Resubmission</v>
+      </c>
+      <c r="AD103" s="337">
         <f t="shared" ref="AD103" si="34">IF(AC103="Late Resubmission",IF(AB103="","",AB103-AA103),IF(AC103="Not submit yet",IF(AA103="","",$J$1-AA103),""))</f>
-        <v/>
+        <v>27</v>
       </c>
       <c r="AE103" s="92" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="AG103" s="238" t="str">
         <f t="shared" si="14"/>
@@ -19849,8 +19874,12 @@
       <c r="P104" s="41" t="s">
         <v>8</v>
       </c>
-      <c r="Q104" s="40"/>
-      <c r="R104" s="155"/>
+      <c r="Q104" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="R104" s="155" t="s">
+        <v>1</v>
+      </c>
       <c r="S104" s="27">
         <v>46188</v>
       </c>
@@ -19869,25 +19898,29 @@
       <c r="X104" s="235" t="s">
         <v>240</v>
       </c>
-      <c r="Y104" s="230"/>
-      <c r="Z104" s="227"/>
+      <c r="Y104" s="230">
+        <v>46212</v>
+      </c>
+      <c r="Z104" s="227">
+        <v>46213</v>
+      </c>
       <c r="AA104" s="29">
         <f t="shared" si="21"/>
-        <v>46204</v>
+        <v>46220</v>
       </c>
       <c r="AB104" s="229">
         <v>46262</v>
       </c>
       <c r="AC104" s="229" t="str">
         <f t="shared" si="22"/>
-        <v/>
-      </c>
-      <c r="AD104" s="337" t="str">
+        <v>Late Resubmission</v>
+      </c>
+      <c r="AD104" s="337">
         <f t="shared" si="32"/>
-        <v/>
+        <v>42</v>
       </c>
       <c r="AE104" s="92" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="AG104" s="238" t="str">
         <f t="shared" si="14"/>
@@ -19961,8 +19994,12 @@
       <c r="P105" s="41" t="s">
         <v>8</v>
       </c>
-      <c r="Q105" s="40"/>
-      <c r="R105" s="155"/>
+      <c r="Q105" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="R105" s="155" t="s">
+        <v>1</v>
+      </c>
       <c r="S105" s="27">
         <v>46188</v>
       </c>
@@ -19981,25 +20018,29 @@
       <c r="X105" s="235" t="s">
         <v>240</v>
       </c>
-      <c r="Y105" s="230"/>
-      <c r="Z105" s="227"/>
+      <c r="Y105" s="230">
+        <v>46204</v>
+      </c>
+      <c r="Z105" s="227">
+        <v>46206</v>
+      </c>
       <c r="AA105" s="29">
         <f t="shared" si="21"/>
-        <v>46204</v>
+        <v>46213</v>
       </c>
       <c r="AB105" s="229">
         <v>46247</v>
       </c>
       <c r="AC105" s="229" t="str">
         <f t="shared" si="22"/>
-        <v/>
-      </c>
-      <c r="AD105" s="337" t="str">
+        <v>Late Resubmission</v>
+      </c>
+      <c r="AD105" s="337">
         <f t="shared" si="32"/>
-        <v/>
+        <v>34</v>
       </c>
       <c r="AE105" s="92" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="AG105" s="238" t="str">
         <f t="shared" si="14"/>
@@ -20107,7 +20148,7 @@
         <v/>
       </c>
       <c r="AE106" s="92" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="AG106" s="238" t="str">
         <f t="shared" si="14"/>
@@ -20198,7 +20239,7 @@
         <v/>
       </c>
       <c r="AE107" s="92" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="AG107" s="238" t="str">
         <f t="shared" si="14"/>
@@ -20236,17 +20277,17 @@
         <v>28</v>
       </c>
       <c r="E108" s="25" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="F108" s="174">
         <f t="shared" si="29"/>
         <v>46219</v>
       </c>
       <c r="G108" s="31" t="s">
+        <v>883</v>
+      </c>
+      <c r="H108" s="21" t="s">
         <v>884</v>
-      </c>
-      <c r="H108" s="21" t="s">
-        <v>885</v>
       </c>
       <c r="I108" s="138" t="s">
         <v>1</v>
@@ -20308,7 +20349,7 @@
         <v/>
       </c>
       <c r="AE108" s="92" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="AG108" s="238" t="str">
         <f t="shared" si="14"/>
@@ -20346,17 +20387,17 @@
         <v>28</v>
       </c>
       <c r="E109" s="25" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="F109" s="174">
         <f t="shared" si="29"/>
         <v>46300</v>
       </c>
       <c r="G109" s="31" t="s">
+        <v>901</v>
+      </c>
+      <c r="H109" s="21" t="s">
         <v>902</v>
-      </c>
-      <c r="H109" s="21" t="s">
-        <v>903</v>
       </c>
       <c r="I109" s="23" t="s">
         <v>3</v>
@@ -20416,7 +20457,7 @@
         <v/>
       </c>
       <c r="AE109" s="92" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="AG109" s="238" t="str">
         <f t="shared" si="14"/>
@@ -20454,7 +20495,7 @@
         <v>30</v>
       </c>
       <c r="E110" s="25" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="F110" s="174">
         <f t="shared" si="29"/>
@@ -20464,7 +20505,7 @@
         <v>775</v>
       </c>
       <c r="H110" s="21" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="I110" s="138" t="s">
         <v>3</v>
@@ -20558,26 +20599,26 @@
         <v>85</v>
       </c>
       <c r="E111" s="25" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="F111" s="174">
         <f t="shared" si="29"/>
         <v>46224</v>
       </c>
       <c r="G111" s="31" t="s">
+        <v>914</v>
+      </c>
+      <c r="H111" s="21" t="s">
         <v>915</v>
-      </c>
-      <c r="H111" s="21" t="s">
-        <v>916</v>
       </c>
       <c r="I111" s="23"/>
       <c r="J111" s="164">
         <f t="shared" ca="1" si="30"/>
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K111" s="47">
         <f t="shared" ca="1" si="31"/>
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L111" s="164" t="s">
         <v>13</v>
@@ -20618,7 +20659,7 @@
         <v/>
       </c>
       <c r="AE111" s="92" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="AG111" s="238" t="str">
         <f t="shared" si="14"/>
@@ -20656,17 +20697,17 @@
         <v>28</v>
       </c>
       <c r="E112" s="25" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="F112" s="174">
         <f t="shared" si="29"/>
         <v>46231</v>
       </c>
       <c r="G112" s="31" t="s">
+        <v>919</v>
+      </c>
+      <c r="H112" s="21" t="s">
         <v>920</v>
-      </c>
-      <c r="H112" s="21" t="s">
-        <v>921</v>
       </c>
       <c r="I112" s="138" t="s">
         <v>2</v>
@@ -20724,7 +20765,7 @@
         <v/>
       </c>
       <c r="AE112" s="92" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="AG112" s="238" t="str">
         <f t="shared" si="14"/>
@@ -20762,17 +20803,17 @@
         <v>28</v>
       </c>
       <c r="E113" s="25" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="F113" s="174">
         <f t="shared" si="29"/>
         <v>46234</v>
       </c>
       <c r="G113" s="31" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="H113" s="21" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="I113" s="138" t="s">
         <v>1</v>
@@ -20794,8 +20835,12 @@
         <v>8</v>
       </c>
       <c r="P113" s="41"/>
-      <c r="Q113" s="40"/>
-      <c r="R113" s="155"/>
+      <c r="Q113" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="R113" s="155" t="s">
+        <v>1</v>
+      </c>
       <c r="S113" s="27">
         <v>46213</v>
       </c>
@@ -20814,22 +20859,26 @@
       <c r="X113" s="235" t="s">
         <v>670</v>
       </c>
-      <c r="Y113" s="230"/>
-      <c r="Z113" s="227"/>
+      <c r="Y113" s="230">
+        <v>46238</v>
+      </c>
+      <c r="Z113" s="227">
+        <v>46244</v>
+      </c>
       <c r="AA113" s="29">
         <f t="shared" si="21"/>
-        <v>46235</v>
+        <v>46251</v>
       </c>
       <c r="AB113" s="229">
         <v>46289</v>
       </c>
       <c r="AC113" s="229" t="str">
         <f t="shared" si="22"/>
-        <v/>
-      </c>
-      <c r="AD113" s="337" t="str">
+        <v>Late Resubmission</v>
+      </c>
+      <c r="AD113" s="337">
         <f t="shared" ref="AD113" si="50">IF(AC113="Late Resubmission",IF(AB113="","",AB113-AA113),IF(AC113="Not submit yet",IF(AA113="","",$J$1-AA113),""))</f>
-        <v/>
+        <v>38</v>
       </c>
       <c r="AE113" s="92"/>
       <c r="AG113" s="238" t="str">
@@ -20868,17 +20917,17 @@
         <v>30</v>
       </c>
       <c r="E114" s="25" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="F114" s="174">
         <f t="shared" si="29"/>
         <v>46251</v>
       </c>
       <c r="G114" s="31" t="s">
+        <v>946</v>
+      </c>
+      <c r="H114" s="21" t="s">
         <v>947</v>
-      </c>
-      <c r="H114" s="21" t="s">
-        <v>948</v>
       </c>
       <c r="I114" s="138" t="s">
         <v>3</v>
@@ -20936,7 +20985,7 @@
         <v/>
       </c>
       <c r="AE114" s="92" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="AG114" s="238" t="str">
         <f t="shared" si="14"/>
@@ -20958,7 +21007,7 @@
         <v/>
       </c>
     </row>
-    <row r="115" spans="1:35" s="9" customFormat="1" ht="63">
+    <row r="115" spans="1:35" s="9" customFormat="1" ht="94.5">
       <c r="A115" s="33">
         <f t="shared" si="19"/>
         <v>109</v>
@@ -20974,7 +21023,7 @@
         <v>28</v>
       </c>
       <c r="E115" s="25" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="F115" s="174">
         <f t="shared" si="29"/>
@@ -21006,7 +21055,9 @@
         <v>8</v>
       </c>
       <c r="P115" s="41"/>
-      <c r="Q115" s="40"/>
+      <c r="Q115" s="40" t="s">
+        <v>8</v>
+      </c>
       <c r="R115" s="155" t="s">
         <v>3</v>
       </c>
@@ -21028,8 +21079,12 @@
       <c r="X115" s="235" t="s">
         <v>240</v>
       </c>
-      <c r="Y115" s="230"/>
-      <c r="Z115" s="227"/>
+      <c r="Y115" s="230">
+        <v>46290</v>
+      </c>
+      <c r="Z115" s="227">
+        <v>46293</v>
+      </c>
       <c r="AA115" s="29" t="str">
         <f t="shared" si="21"/>
         <v/>
@@ -21044,7 +21099,7 @@
         <v/>
       </c>
       <c r="AE115" s="92" t="s">
-        <v>1026</v>
+        <v>1111</v>
       </c>
       <c r="AG115" s="238" t="str">
         <f t="shared" si="14"/>
@@ -21082,17 +21137,17 @@
         <v>28</v>
       </c>
       <c r="E116" s="25" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="F116" s="174">
         <f t="shared" si="29"/>
         <v>46268</v>
       </c>
       <c r="G116" s="31" t="s">
+        <v>869</v>
+      </c>
+      <c r="H116" s="21" t="s">
         <v>870</v>
-      </c>
-      <c r="H116" s="21" t="s">
-        <v>871</v>
       </c>
       <c r="I116" s="138" t="s">
         <v>2</v>
@@ -21114,7 +21169,9 @@
         <v>8</v>
       </c>
       <c r="P116" s="41"/>
-      <c r="Q116" s="40"/>
+      <c r="Q116" s="40" t="s">
+        <v>8</v>
+      </c>
       <c r="R116" s="155" t="s">
         <v>3</v>
       </c>
@@ -21156,7 +21213,7 @@
         <v/>
       </c>
       <c r="AE116" s="92" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="AG116" s="238" t="str">
         <f t="shared" si="14"/>
@@ -21192,29 +21249,29 @@
         <v>28</v>
       </c>
       <c r="E117" s="25" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="F117" s="174">
         <f t="shared" si="29"/>
         <v>46268</v>
       </c>
       <c r="G117" s="31" t="s">
+        <v>959</v>
+      </c>
+      <c r="H117" s="21" t="s">
         <v>960</v>
-      </c>
-      <c r="H117" s="21" t="s">
-        <v>961</v>
       </c>
       <c r="I117" s="138"/>
       <c r="J117" s="164">
         <f t="shared" ca="1" si="30"/>
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K117" s="47">
         <f t="shared" ca="1" si="31"/>
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L117" s="164" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="M117" s="40" t="s">
         <v>8</v>
@@ -21252,7 +21309,7 @@
         <v/>
       </c>
       <c r="AE117" s="92" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="AG117" s="238" t="str">
         <f t="shared" si="14"/>
@@ -21290,17 +21347,17 @@
         <v>30</v>
       </c>
       <c r="E118" s="25" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="F118" s="174">
         <f t="shared" si="29"/>
         <v>46268</v>
       </c>
       <c r="G118" s="31" t="s">
+        <v>962</v>
+      </c>
+      <c r="H118" s="21" t="s">
         <v>963</v>
-      </c>
-      <c r="H118" s="21" t="s">
-        <v>964</v>
       </c>
       <c r="I118" s="138"/>
       <c r="J118" s="164"/>
@@ -21382,17 +21439,17 @@
         <v>28</v>
       </c>
       <c r="E119" s="25" t="s">
-        <v>1063</v>
+        <v>1059</v>
       </c>
       <c r="F119" s="174">
         <f t="shared" si="29"/>
         <v>46275</v>
       </c>
       <c r="G119" s="31" t="s">
+        <v>964</v>
+      </c>
+      <c r="H119" s="21" t="s">
         <v>965</v>
-      </c>
-      <c r="H119" s="21" t="s">
-        <v>966</v>
       </c>
       <c r="I119" s="138" t="s">
         <v>3</v>
@@ -21452,7 +21509,7 @@
         <v/>
       </c>
       <c r="AE119" s="92" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="AG119" s="238" t="str">
         <f t="shared" si="14"/>
@@ -21490,17 +21547,17 @@
         <v>28</v>
       </c>
       <c r="E120" s="25" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="F120" s="174">
         <f t="shared" si="29"/>
         <v>46276</v>
       </c>
       <c r="G120" s="31" t="s">
+        <v>967</v>
+      </c>
+      <c r="H120" s="21" t="s">
         <v>968</v>
-      </c>
-      <c r="H120" s="21" t="s">
-        <v>969</v>
       </c>
       <c r="I120" s="138" t="s">
         <v>1</v>
@@ -21522,8 +21579,12 @@
         <v>8</v>
       </c>
       <c r="P120" s="41"/>
-      <c r="Q120" s="40"/>
-      <c r="R120" s="155"/>
+      <c r="Q120" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="R120" s="155" t="s">
+        <v>1</v>
+      </c>
       <c r="S120" s="27">
         <v>46255</v>
       </c>
@@ -21542,23 +21603,27 @@
       <c r="X120" s="235" t="s">
         <v>240</v>
       </c>
-      <c r="Y120" s="230"/>
-      <c r="Z120" s="227"/>
+      <c r="Y120" s="230">
+        <v>46282</v>
+      </c>
+      <c r="Z120" s="227">
+        <v>46283</v>
+      </c>
       <c r="AA120" s="29">
         <f t="shared" si="21"/>
-        <v>46282</v>
+        <v>46290</v>
       </c>
       <c r="AB120" s="229"/>
       <c r="AC120" s="229" t="str">
-        <f t="shared" si="22"/>
-        <v/>
-      </c>
-      <c r="AD120" s="337" t="str">
-        <f t="shared" ref="AD120" si="64">IF(AC120="Late Resubmission",IF(AB120="","",AB120-AA120),IF(AC120="Not submit yet",IF(AA120="","",$J$1-AA120),""))</f>
-        <v/>
+        <f t="shared" ca="1" si="22"/>
+        <v>Not submit yet</v>
+      </c>
+      <c r="AD120" s="337">
+        <f t="shared" ref="AD120" ca="1" si="64">IF(AC120="Late Resubmission",IF(AB120="","",AB120-AA120),IF(AC120="Not submit yet",IF(AA120="","",$J$1-AA120),""))</f>
+        <v>28</v>
       </c>
       <c r="AE120" s="92" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="AG120" s="238" t="str">
         <f t="shared" si="14"/>
@@ -21596,7 +21661,7 @@
         <v>28</v>
       </c>
       <c r="E121" s="25" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="F121" s="174">
         <f t="shared" si="29"/>
@@ -21650,7 +21715,7 @@
         <v/>
       </c>
       <c r="AE121" s="92" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="AG121" s="238" t="str">
         <f t="shared" si="14"/>
@@ -21688,7 +21753,7 @@
         <v>28</v>
       </c>
       <c r="E122" s="25" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="F122" s="174">
         <f t="shared" si="29"/>
@@ -21720,8 +21785,12 @@
         <v>8</v>
       </c>
       <c r="P122" s="41"/>
-      <c r="Q122" s="40"/>
-      <c r="R122" s="155"/>
+      <c r="Q122" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="R122" s="155" t="s">
+        <v>3</v>
+      </c>
       <c r="S122" s="27">
         <v>46262</v>
       </c>
@@ -21740,11 +21809,15 @@
       <c r="X122" s="235" t="s">
         <v>240</v>
       </c>
-      <c r="Y122" s="230"/>
-      <c r="Z122" s="227"/>
-      <c r="AA122" s="29">
+      <c r="Y122" s="230">
+        <v>46288</v>
+      </c>
+      <c r="Z122" s="227">
+        <v>46290</v>
+      </c>
+      <c r="AA122" s="29" t="str">
         <f t="shared" ref="AA122:AA143" si="68">IF(AND($R122="",$I122=""),"",IF(OR($R122="B",$R122="C"),IF($Z122&lt;&gt;"",$Z122+7,IF($Y122&lt;&gt;"",$Y122+8,"")),IF($R122="",IF(OR($I122="B",$I122="C"),IF($W122&lt;&gt;"",$W122+7,IF($V122&lt;&gt;"",$V122+8,""))),"")))</f>
-        <v>46286</v>
+        <v/>
       </c>
       <c r="AB122" s="229"/>
       <c r="AC122" s="229" t="str">
@@ -21773,7 +21846,7 @@
       </c>
       <c r="AI122" s="75" t="str">
         <f>IF($AH122,IF(OR($R122="B",$R122="C"),"YES",IF($R122="",IF(OR($I122="B",$I122="C"),"YES",""),"")),"")</f>
-        <v>YES</v>
+        <v/>
       </c>
     </row>
     <row r="123" spans="1:35" s="9" customFormat="1" ht="110.25">
@@ -21792,17 +21865,17 @@
         <v>28</v>
       </c>
       <c r="E123" s="25" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="F123" s="174">
         <f t="shared" si="29"/>
         <v>46293</v>
       </c>
       <c r="G123" s="31" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="H123" s="21" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="I123" s="138"/>
       <c r="J123" s="164"/>
@@ -21846,7 +21919,7 @@
         <v/>
       </c>
       <c r="AE123" s="92" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="AG123" s="238" t="str">
         <f t="shared" si="14"/>
@@ -21884,17 +21957,17 @@
         <v>30</v>
       </c>
       <c r="E124" s="25" t="s">
-        <v>981</v>
+        <v>1112</v>
       </c>
       <c r="F124" s="174">
         <f t="shared" si="29"/>
         <v>46324</v>
       </c>
       <c r="G124" s="31" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="H124" s="21" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="I124" s="138" t="s">
         <v>3</v>
@@ -21916,8 +21989,12 @@
         <v>8</v>
       </c>
       <c r="P124" s="41"/>
-      <c r="Q124" s="40"/>
-      <c r="R124" s="155"/>
+      <c r="Q124" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="R124" s="155" t="s">
+        <v>3</v>
+      </c>
       <c r="S124" s="27">
         <v>46280</v>
       </c>
@@ -21936,11 +22013,15 @@
       <c r="X124" s="235" t="s">
         <v>240</v>
       </c>
-      <c r="Y124" s="230"/>
-      <c r="Z124" s="227"/>
-      <c r="AA124" s="29" t="b">
+      <c r="Y124" s="230">
+        <v>46316</v>
+      </c>
+      <c r="Z124" s="227">
+        <v>46316</v>
+      </c>
+      <c r="AA124" s="29" t="str">
         <f t="shared" si="68"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AB124" s="229"/>
       <c r="AC124" s="229" t="str">
@@ -21952,11 +22033,11 @@
         <v/>
       </c>
       <c r="AE124" s="92" t="s">
-        <v>1055</v>
+        <v>1052</v>
       </c>
       <c r="AG124" s="238" t="str">
         <f t="shared" si="14"/>
-        <v xml:space="preserve">LTIA-5.10-VIETUR-70000-RFA-MAS-0821 </v>
+        <v>LTIA-5.10-VIETUR-70000-RFA-MAS-0821</v>
       </c>
       <c r="AH124" s="243" t="b" cm="1">
         <f t="array" ref="AH124">$E124=_xlfn.XLOOKUP(
@@ -21990,14 +22071,14 @@
         <v>30</v>
       </c>
       <c r="E125" s="25" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="F125" s="174">
         <f t="shared" si="29"/>
         <v>46310</v>
       </c>
       <c r="G125" s="31" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="H125" s="21" t="s">
         <v>776</v>
@@ -22058,7 +22139,7 @@
         <v/>
       </c>
       <c r="AE125" s="92" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="AG125" s="238" t="str">
         <f t="shared" ref="AG125:AG141" si="75">IF(AND(RIGHT($E125,1)&gt;="A",RIGHT($E125,1)&lt;="Z"),LEFT($E125,LEN($E125)-1),$E125)</f>
@@ -22096,17 +22177,17 @@
         <v>28</v>
       </c>
       <c r="E126" s="25" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="F126" s="174">
         <f t="shared" si="29"/>
         <v>46310</v>
       </c>
       <c r="G126" s="31" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="H126" s="21" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="I126" s="138" t="s">
         <v>1</v>
@@ -22164,7 +22245,7 @@
         <v/>
       </c>
       <c r="AE126" s="92" t="s">
-        <v>1032</v>
+        <v>1029</v>
       </c>
       <c r="AG126" s="238" t="str">
         <f t="shared" si="75"/>
@@ -22202,17 +22283,17 @@
         <v>30</v>
       </c>
       <c r="E127" s="25" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="F127" s="174">
         <f t="shared" si="29"/>
         <v>46314</v>
       </c>
       <c r="G127" s="31" t="s">
+        <v>962</v>
+      </c>
+      <c r="H127" s="21" t="s">
         <v>963</v>
-      </c>
-      <c r="H127" s="21" t="s">
-        <v>964</v>
       </c>
       <c r="I127" s="138" t="s">
         <v>3</v>
@@ -22264,7 +22345,7 @@
       <c r="AC127" s="229"/>
       <c r="AD127" s="337"/>
       <c r="AE127" s="92" t="s">
-        <v>1030</v>
+        <v>1027</v>
       </c>
       <c r="AG127" s="238" t="str">
         <f t="shared" si="75"/>
@@ -22302,28 +22383,24 @@
         <v>30</v>
       </c>
       <c r="E128" s="25" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="F128" s="174">
         <f t="shared" si="29"/>
         <v>46316</v>
       </c>
       <c r="G128" s="31" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="H128" s="21" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="I128" s="138"/>
-      <c r="J128" s="164">
-        <f t="shared" ca="1" si="30"/>
-        <v>22</v>
-      </c>
-      <c r="K128" s="47">
-        <f t="shared" ca="1" si="31"/>
-        <v>1</v>
-      </c>
-      <c r="L128" s="164"/>
+      <c r="J128" s="164"/>
+      <c r="K128" s="47"/>
+      <c r="L128" s="164" t="s">
+        <v>13</v>
+      </c>
       <c r="M128" s="40" t="s">
         <v>8</v>
       </c>
@@ -22353,7 +22430,9 @@
       <c r="AB128" s="229"/>
       <c r="AC128" s="229"/>
       <c r="AD128" s="337"/>
-      <c r="AE128" s="92"/>
+      <c r="AE128" s="92" t="s">
+        <v>1113</v>
+      </c>
       <c r="AG128" s="238" t="str">
         <f t="shared" si="75"/>
         <v>LTIA-5.10-VIETUR-70000-RFA-MAS-0696</v>
@@ -22367,7 +22446,7 @@
 0,
 -1
 )</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI128" s="75" t="str">
         <f t="shared" si="74"/>
@@ -22390,22 +22469,24 @@
         <v>32</v>
       </c>
       <c r="E129" s="25" t="s">
-        <v>1027</v>
+        <v>1024</v>
       </c>
       <c r="F129" s="174">
         <f t="shared" si="29"/>
         <v>46323</v>
       </c>
       <c r="G129" s="31" t="s">
-        <v>1028</v>
+        <v>1025</v>
       </c>
       <c r="H129" s="21" t="s">
-        <v>1029</v>
-      </c>
-      <c r="I129" s="138"/>
+        <v>1026</v>
+      </c>
+      <c r="I129" s="138" t="s">
+        <v>1</v>
+      </c>
       <c r="J129" s="164">
         <f t="shared" ca="1" si="30"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K129" s="47">
         <f t="shared" ca="1" si="31"/>
@@ -22431,7 +22512,9 @@
       </c>
       <c r="V129" s="29"/>
       <c r="W129" s="188"/>
-      <c r="X129" s="235"/>
+      <c r="X129" s="235" t="s">
+        <v>240</v>
+      </c>
       <c r="Y129" s="230"/>
       <c r="Z129" s="227"/>
       <c r="AA129" s="29" t="str">
@@ -22442,7 +22525,7 @@
       <c r="AC129" s="229"/>
       <c r="AD129" s="337"/>
       <c r="AE129" s="92" t="s">
-        <v>1062</v>
+        <v>1114</v>
       </c>
       <c r="AG129" s="238" t="str">
         <f t="shared" si="75"/>
@@ -22461,7 +22544,7 @@
       </c>
       <c r="AI129" s="75" t="str">
         <f t="shared" si="74"/>
-        <v/>
+        <v>YES</v>
       </c>
     </row>
     <row r="130" spans="1:35" s="9" customFormat="1" ht="47.25">
@@ -22480,22 +22563,24 @@
         <v>32</v>
       </c>
       <c r="E130" s="25" t="s">
-        <v>1035</v>
+        <v>1032</v>
       </c>
       <c r="F130" s="174">
         <f t="shared" si="29"/>
         <v>46323</v>
       </c>
       <c r="G130" s="31" t="s">
-        <v>1033</v>
+        <v>1030</v>
       </c>
       <c r="H130" s="21" t="s">
-        <v>1034</v>
-      </c>
-      <c r="I130" s="138"/>
+        <v>1031</v>
+      </c>
+      <c r="I130" s="138" t="s">
+        <v>1</v>
+      </c>
       <c r="J130" s="164">
         <f t="shared" ca="1" si="30"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K130" s="47">
         <f t="shared" ca="1" si="31"/>
@@ -22521,7 +22606,9 @@
       </c>
       <c r="V130" s="29"/>
       <c r="W130" s="188"/>
-      <c r="X130" s="235"/>
+      <c r="X130" s="235" t="s">
+        <v>240</v>
+      </c>
       <c r="Y130" s="230"/>
       <c r="Z130" s="227"/>
       <c r="AA130" s="29" t="str">
@@ -22532,7 +22619,7 @@
       <c r="AC130" s="229"/>
       <c r="AD130" s="337"/>
       <c r="AE130" s="92" t="s">
-        <v>1097</v>
+        <v>1115</v>
       </c>
       <c r="AG130" s="238" t="str">
         <f t="shared" si="75"/>
@@ -22551,7 +22638,7 @@
       </c>
       <c r="AI130" s="75" t="str">
         <f t="shared" si="74"/>
-        <v/>
+        <v>YES</v>
       </c>
     </row>
     <row r="131" spans="1:35" s="9" customFormat="1" ht="47.25">
@@ -22570,17 +22657,17 @@
         <v>32</v>
       </c>
       <c r="E131" s="25" t="s">
-        <v>1036</v>
+        <v>1033</v>
       </c>
       <c r="F131" s="174">
         <f t="shared" si="29"/>
         <v>46321</v>
       </c>
       <c r="G131" s="31" t="s">
-        <v>1037</v>
+        <v>1034</v>
       </c>
       <c r="H131" s="21" t="s">
-        <v>1038</v>
+        <v>1035</v>
       </c>
       <c r="I131" s="138" t="s">
         <v>1</v>
@@ -22632,7 +22719,7 @@
       <c r="AC131" s="229"/>
       <c r="AD131" s="337"/>
       <c r="AE131" s="92" t="s">
-        <v>1071</v>
+        <v>1067</v>
       </c>
       <c r="AG131" s="238" t="str">
         <f t="shared" si="75"/>
@@ -22670,17 +22757,17 @@
         <v>32</v>
       </c>
       <c r="E132" s="25" t="s">
-        <v>1039</v>
+        <v>1036</v>
       </c>
       <c r="F132" s="174">
         <f t="shared" si="29"/>
         <v>46323</v>
       </c>
       <c r="G132" s="31" t="s">
-        <v>1040</v>
+        <v>1037</v>
       </c>
       <c r="H132" s="21" t="s">
-        <v>1041</v>
+        <v>1038</v>
       </c>
       <c r="I132" s="138" t="s">
         <v>1</v>
@@ -22732,7 +22819,7 @@
       <c r="AC132" s="229"/>
       <c r="AD132" s="337"/>
       <c r="AE132" s="92" t="s">
-        <v>1098</v>
+        <v>1093</v>
       </c>
       <c r="AG132" s="238" t="str">
         <f t="shared" si="75"/>
@@ -22770,22 +22857,24 @@
         <v>32</v>
       </c>
       <c r="E133" s="25" t="s">
-        <v>1042</v>
+        <v>1039</v>
       </c>
       <c r="F133" s="174">
         <f t="shared" si="29"/>
         <v>46322</v>
       </c>
       <c r="G133" s="31" t="s">
-        <v>1043</v>
+        <v>1040</v>
       </c>
       <c r="H133" s="21" t="s">
-        <v>1044</v>
-      </c>
-      <c r="I133" s="138"/>
+        <v>1041</v>
+      </c>
+      <c r="I133" s="138" t="s">
+        <v>1</v>
+      </c>
       <c r="J133" s="164">
         <f t="shared" ca="1" si="30"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K133" s="47">
         <f t="shared" ca="1" si="31"/>
@@ -22811,7 +22900,9 @@
       </c>
       <c r="V133" s="29"/>
       <c r="W133" s="188"/>
-      <c r="X133" s="235"/>
+      <c r="X133" s="235" t="s">
+        <v>240</v>
+      </c>
       <c r="Y133" s="230"/>
       <c r="Z133" s="227"/>
       <c r="AA133" s="29" t="str">
@@ -22822,7 +22913,7 @@
       <c r="AC133" s="229"/>
       <c r="AD133" s="337"/>
       <c r="AE133" s="92" t="s">
-        <v>1097</v>
+        <v>1115</v>
       </c>
       <c r="AG133" s="238" t="str">
         <f t="shared" si="75"/>
@@ -22841,7 +22932,7 @@
       </c>
       <c r="AI133" s="75" t="str">
         <f t="shared" si="74"/>
-        <v/>
+        <v>YES</v>
       </c>
     </row>
     <row r="134" spans="1:35" s="9" customFormat="1" ht="47.25">
@@ -22860,22 +22951,24 @@
         <v>32</v>
       </c>
       <c r="E134" s="25" t="s">
-        <v>1045</v>
+        <v>1042</v>
       </c>
       <c r="F134" s="174">
         <f t="shared" si="29"/>
         <v>46322</v>
       </c>
       <c r="G134" s="31" t="s">
-        <v>1046</v>
+        <v>1043</v>
       </c>
       <c r="H134" s="21" t="s">
-        <v>1047</v>
-      </c>
-      <c r="I134" s="138"/>
+        <v>1044</v>
+      </c>
+      <c r="I134" s="138" t="s">
+        <v>1</v>
+      </c>
       <c r="J134" s="164">
         <f t="shared" ca="1" si="30"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K134" s="47">
         <f t="shared" ca="1" si="31"/>
@@ -22901,7 +22994,9 @@
       </c>
       <c r="V134" s="29"/>
       <c r="W134" s="188"/>
-      <c r="X134" s="235"/>
+      <c r="X134" s="235" t="s">
+        <v>240</v>
+      </c>
       <c r="Y134" s="230"/>
       <c r="Z134" s="227"/>
       <c r="AA134" s="29" t="str">
@@ -22912,7 +23007,7 @@
       <c r="AC134" s="229"/>
       <c r="AD134" s="337"/>
       <c r="AE134" s="92" t="s">
-        <v>1097</v>
+        <v>1115</v>
       </c>
       <c r="AG134" s="238" t="str">
         <f t="shared" si="75"/>
@@ -22931,7 +23026,7 @@
       </c>
       <c r="AI134" s="75" t="str">
         <f t="shared" si="74"/>
-        <v/>
+        <v>YES</v>
       </c>
     </row>
     <row r="135" spans="1:35" s="9" customFormat="1" ht="47.25">
@@ -22950,17 +23045,17 @@
         <v>28</v>
       </c>
       <c r="E135" s="25" t="s">
-        <v>1048</v>
+        <v>1045</v>
       </c>
       <c r="F135" s="174">
         <f t="shared" si="29"/>
         <v>46322</v>
       </c>
       <c r="G135" s="31" t="s">
-        <v>1049</v>
+        <v>1046</v>
       </c>
       <c r="H135" s="21" t="s">
-        <v>1050</v>
+        <v>1047</v>
       </c>
       <c r="I135" s="138" t="s">
         <v>3</v>
@@ -23012,7 +23107,7 @@
       <c r="AC135" s="229"/>
       <c r="AD135" s="337"/>
       <c r="AE135" s="92" t="s">
-        <v>1069</v>
+        <v>1065</v>
       </c>
       <c r="AG135" s="238" t="str">
         <f t="shared" si="75"/>
@@ -23050,22 +23145,22 @@
         <v>32</v>
       </c>
       <c r="E136" s="25" t="s">
-        <v>1072</v>
+        <v>1068</v>
       </c>
       <c r="F136" s="174">
         <f t="shared" si="29"/>
         <v>46330</v>
       </c>
       <c r="G136" s="31" t="s">
-        <v>1073</v>
+        <v>1069</v>
       </c>
       <c r="H136" s="21" t="s">
-        <v>1074</v>
+        <v>1070</v>
       </c>
       <c r="I136" s="138"/>
       <c r="J136" s="164">
         <f t="shared" ca="1" si="30"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K136" s="47">
         <f t="shared" ca="1" si="31"/>
@@ -23138,22 +23233,22 @@
         <v>32</v>
       </c>
       <c r="E137" s="25" t="s">
-        <v>1075</v>
+        <v>1071</v>
       </c>
       <c r="F137" s="174">
         <f t="shared" si="29"/>
         <v>46330</v>
       </c>
       <c r="G137" s="31" t="s">
-        <v>1076</v>
+        <v>1072</v>
       </c>
       <c r="H137" s="21" t="s">
-        <v>1077</v>
+        <v>1073</v>
       </c>
       <c r="I137" s="138"/>
       <c r="J137" s="164">
         <f t="shared" ca="1" si="30"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K137" s="47">
         <f t="shared" ca="1" si="31"/>
@@ -23220,28 +23315,28 @@
         <v>5.11</v>
       </c>
       <c r="C138" s="164" t="s">
-        <v>1081</v>
+        <v>1077</v>
       </c>
       <c r="D138" s="137" t="s">
         <v>32</v>
       </c>
       <c r="E138" s="25" t="s">
-        <v>1078</v>
+        <v>1074</v>
       </c>
       <c r="F138" s="174">
         <f t="shared" si="29"/>
         <v>46330</v>
       </c>
       <c r="G138" s="31" t="s">
-        <v>1079</v>
+        <v>1075</v>
       </c>
       <c r="H138" s="21" t="s">
-        <v>1080</v>
+        <v>1076</v>
       </c>
       <c r="I138" s="138"/>
       <c r="J138" s="164">
         <f t="shared" ca="1" si="30"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K138" s="47">
         <f t="shared" ca="1" si="31"/>
@@ -23308,28 +23403,28 @@
         <v>5.11</v>
       </c>
       <c r="C139" s="164" t="s">
-        <v>1085</v>
+        <v>1081</v>
       </c>
       <c r="D139" s="137" t="s">
         <v>32</v>
       </c>
       <c r="E139" s="25" t="s">
-        <v>1082</v>
+        <v>1078</v>
       </c>
       <c r="F139" s="174">
         <f t="shared" si="29"/>
         <v>46330</v>
       </c>
       <c r="G139" s="31" t="s">
-        <v>1083</v>
+        <v>1079</v>
       </c>
       <c r="H139" s="21" t="s">
-        <v>1084</v>
+        <v>1080</v>
       </c>
       <c r="I139" s="138"/>
       <c r="J139" s="164">
         <f t="shared" ca="1" si="30"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K139" s="47">
         <f t="shared" ca="1" si="31"/>
@@ -23402,22 +23497,22 @@
         <v>32</v>
       </c>
       <c r="E140" s="25" t="s">
-        <v>1086</v>
+        <v>1082</v>
       </c>
       <c r="F140" s="174">
         <f t="shared" si="29"/>
         <v>46331</v>
       </c>
       <c r="G140" s="31" t="s">
-        <v>1087</v>
+        <v>1083</v>
       </c>
       <c r="H140" s="21" t="s">
-        <v>1088</v>
+        <v>1084</v>
       </c>
       <c r="I140" s="138"/>
       <c r="J140" s="164">
         <f t="shared" ca="1" si="30"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K140" s="47">
         <f t="shared" ca="1" si="31"/>
@@ -23490,22 +23585,22 @@
         <v>28</v>
       </c>
       <c r="E141" s="25" t="s">
-        <v>1092</v>
+        <v>1088</v>
       </c>
       <c r="F141" s="174">
         <f t="shared" si="29"/>
         <v>46333</v>
       </c>
       <c r="G141" s="31" t="s">
-        <v>1093</v>
+        <v>1089</v>
       </c>
       <c r="H141" s="21" t="s">
-        <v>1094</v>
+        <v>1090</v>
       </c>
       <c r="I141" s="138"/>
       <c r="J141" s="164">
         <f t="shared" ca="1" si="30"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K141" s="47">
         <f t="shared" ca="1" si="31"/>
@@ -23653,29 +23748,29 @@
       <c r="C145" s="166" t="s">
         <v>20</v>
       </c>
-      <c r="D145" s="405" t="s">
+      <c r="D145" s="403" t="s">
         <v>21</v>
       </c>
-      <c r="E145" s="405"/>
-      <c r="F145" s="406"/>
+      <c r="E145" s="403"/>
+      <c r="F145" s="404"/>
       <c r="G145" s="46"/>
       <c r="H145" s="68"/>
-      <c r="I145" s="357" t="s">
+      <c r="I145" s="356" t="s">
         <v>14</v>
       </c>
-      <c r="J145" s="358"/>
-      <c r="K145" s="358"/>
-      <c r="L145" s="358"/>
-      <c r="M145" s="358"/>
-      <c r="N145" s="359"/>
-      <c r="O145" s="360" t="s">
+      <c r="J145" s="357"/>
+      <c r="K145" s="357"/>
+      <c r="L145" s="357"/>
+      <c r="M145" s="357"/>
+      <c r="N145" s="358"/>
+      <c r="O145" s="350" t="s">
         <v>7</v>
       </c>
-      <c r="P145" s="361"/>
-      <c r="Q145" s="360" t="s">
+      <c r="P145" s="351"/>
+      <c r="Q145" s="350" t="s">
         <v>109</v>
       </c>
-      <c r="R145" s="361"/>
+      <c r="R145" s="351"/>
       <c r="S145" s="1"/>
       <c r="T145" s="1"/>
       <c r="U145" s="140"/>
@@ -23697,26 +23792,26 @@
       <c r="C146" s="167" t="s">
         <v>109</v>
       </c>
-      <c r="D146" s="424" t="s">
+      <c r="D146" s="395" t="s">
         <v>111</v>
       </c>
-      <c r="E146" s="424"/>
-      <c r="F146" s="425"/>
+      <c r="E146" s="395"/>
+      <c r="F146" s="396"/>
       <c r="G146" s="46"/>
       <c r="H146" s="46"/>
-      <c r="I146" s="357" t="s">
+      <c r="I146" s="356" t="s">
         <v>19</v>
       </c>
-      <c r="J146" s="358"/>
-      <c r="K146" s="358"/>
-      <c r="L146" s="359"/>
+      <c r="J146" s="357"/>
+      <c r="K146" s="357"/>
+      <c r="L146" s="358"/>
       <c r="M146" s="105">
         <f t="shared" ref="M146:M151" ca="1" si="89">N146/$N$146</f>
         <v>1</v>
       </c>
       <c r="N146" s="106">
         <f ca="1">SUM($N$147:$N$151)</f>
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="O146" s="102" t="s">
         <v>15</v>
@@ -23730,7 +23825,7 @@
       </c>
       <c r="R146" s="220">
         <f ca="1">SUM(R147:R150)</f>
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="S146" s="1"/>
       <c r="T146" s="1"/>
@@ -23753,22 +23848,22 @@
       <c r="C147" s="167" t="s">
         <v>22</v>
       </c>
-      <c r="D147" s="424" t="s">
+      <c r="D147" s="395" t="s">
         <v>23</v>
       </c>
-      <c r="E147" s="424"/>
-      <c r="F147" s="425"/>
+      <c r="E147" s="395"/>
+      <c r="F147" s="396"/>
       <c r="G147" s="70"/>
       <c r="H147" s="6"/>
-      <c r="I147" s="373" t="s">
+      <c r="I147" s="405" t="s">
         <v>66</v>
       </c>
-      <c r="J147" s="374"/>
-      <c r="K147" s="374"/>
-      <c r="L147" s="375"/>
+      <c r="J147" s="406"/>
+      <c r="K147" s="406"/>
+      <c r="L147" s="407"/>
       <c r="M147" s="107">
         <f t="shared" ca="1" si="89"/>
-        <v>0.49285714285714288</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="N147" s="108">
         <f>COUNTIF($I$7:$I$143,"A")</f>
@@ -23784,11 +23879,11 @@
       </c>
       <c r="Q147" s="107">
         <f ca="1">R147/$R$146</f>
-        <v>0.4065040650406504</v>
+        <v>0.44166666666666665</v>
       </c>
       <c r="R147" s="108">
         <f>COUNTIF($R$7:$R$143,"A")</f>
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="S147" s="1"/>
       <c r="T147" s="1"/>
@@ -23811,21 +23906,21 @@
       <c r="C148" s="167" t="s">
         <v>24</v>
       </c>
-      <c r="D148" s="424" t="s">
+      <c r="D148" s="395" t="s">
         <v>25</v>
       </c>
-      <c r="E148" s="424"/>
-      <c r="F148" s="425"/>
+      <c r="E148" s="395"/>
+      <c r="F148" s="396"/>
       <c r="H148" s="6"/>
-      <c r="I148" s="376" t="s">
+      <c r="I148" s="408" t="s">
         <v>67</v>
       </c>
-      <c r="J148" s="377"/>
-      <c r="K148" s="377"/>
-      <c r="L148" s="378"/>
+      <c r="J148" s="409"/>
+      <c r="K148" s="409"/>
+      <c r="L148" s="410"/>
       <c r="M148" s="109">
         <f t="shared" ca="1" si="89"/>
-        <v>0.1</v>
+        <v>9.7222222222222224E-2</v>
       </c>
       <c r="N148" s="110">
         <f>COUNTIF($I$7:$I$143,"B")</f>
@@ -23841,7 +23936,7 @@
       </c>
       <c r="Q148" s="109">
         <f t="shared" ref="Q148:Q150" ca="1" si="90">R148/$R$146</f>
-        <v>7.3170731707317069E-2</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="R148" s="110">
         <f>COUNTIF($R$7:$R$143,"B")</f>
@@ -23868,30 +23963,30 @@
       <c r="C149" s="167" t="s">
         <v>26</v>
       </c>
-      <c r="D149" s="424" t="s">
+      <c r="D149" s="395" t="s">
         <v>27</v>
       </c>
-      <c r="E149" s="424"/>
-      <c r="F149" s="425"/>
+      <c r="E149" s="395"/>
+      <c r="F149" s="396"/>
       <c r="G149" s="71"/>
       <c r="H149" s="6"/>
-      <c r="I149" s="379" t="s">
+      <c r="I149" s="411" t="s">
         <v>68</v>
       </c>
-      <c r="J149" s="380"/>
-      <c r="K149" s="380"/>
-      <c r="L149" s="381"/>
+      <c r="J149" s="412"/>
+      <c r="K149" s="412"/>
+      <c r="L149" s="413"/>
       <c r="M149" s="111">
         <f t="shared" ca="1" si="89"/>
-        <v>0.20714285714285716</v>
+        <v>0.22916666666666666</v>
       </c>
       <c r="N149" s="112">
         <f>COUNTIF($I$7:$I$143,"C")</f>
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="O149" s="98">
         <f ca="1">COUNTIFS($J$7:$J$143,"&lt;=21",$I$7:$I$143,"C")</f>
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="P149" s="50">
         <f ca="1">COUNTIFS($J$7:$J$143,"&gt;21",$I$7:$I$143,"C")</f>
@@ -23899,11 +23994,11 @@
       </c>
       <c r="Q149" s="111">
         <f t="shared" ca="1" si="90"/>
-        <v>0.13821138211382114</v>
+        <v>0.18333333333333332</v>
       </c>
       <c r="R149" s="112">
         <f>COUNTIF($R$7:$R$143,"C")</f>
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="S149" s="1"/>
       <c r="T149" s="1"/>
@@ -23926,25 +24021,25 @@
       <c r="C150" s="168" t="s">
         <v>28</v>
       </c>
-      <c r="D150" s="424" t="s">
+      <c r="D150" s="395" t="s">
         <v>29</v>
       </c>
-      <c r="E150" s="424"/>
-      <c r="F150" s="425"/>
+      <c r="E150" s="395"/>
+      <c r="F150" s="396"/>
       <c r="G150" s="72"/>
-      <c r="I150" s="382" t="s">
+      <c r="I150" s="365" t="s">
         <v>70</v>
       </c>
-      <c r="J150" s="383"/>
-      <c r="K150" s="383"/>
-      <c r="L150" s="384"/>
+      <c r="J150" s="366"/>
+      <c r="K150" s="366"/>
+      <c r="L150" s="367"/>
       <c r="M150" s="114">
         <f t="shared" ca="1" si="89"/>
-        <v>9.285714285714286E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
       <c r="N150" s="115">
         <f ca="1">SUM(O150:P150)</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O150" s="98">
         <f ca="1">COUNTIFS($J$7:$J$143,"&lt;=21",$V$7:$V$143,"",$L$7:$L$143,"&lt;&gt;X")</f>
@@ -23952,15 +24047,15 @@
       </c>
       <c r="P150" s="50">
         <f ca="1">COUNTIFS($J$7:$J$143,"&gt;21",$V$7:$V$143,"",$L$7:$L$143,"&lt;&gt;X")</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q150" s="114">
         <f t="shared" ca="1" si="90"/>
-        <v>0.38211382113821141</v>
+        <v>0.3</v>
       </c>
       <c r="R150" s="115">
         <f ca="1">COUNTIFS($J$7:$J$143,"&gt;=0",$Q$7:$Q$143,"",$L$7:$L$143,"&lt;&gt;X")</f>
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="S150" s="1" t="s">
         <v>10</v>
@@ -23985,25 +24080,25 @@
       <c r="C151" s="168" t="s">
         <v>30</v>
       </c>
-      <c r="D151" s="424" t="s">
+      <c r="D151" s="395" t="s">
         <v>31</v>
       </c>
-      <c r="E151" s="424"/>
-      <c r="F151" s="425"/>
+      <c r="E151" s="395"/>
+      <c r="F151" s="396"/>
       <c r="H151" s="6"/>
-      <c r="I151" s="354" t="s">
+      <c r="I151" s="368" t="s">
         <v>71</v>
       </c>
-      <c r="J151" s="355"/>
-      <c r="K151" s="355"/>
-      <c r="L151" s="356"/>
+      <c r="J151" s="369"/>
+      <c r="K151" s="369"/>
+      <c r="L151" s="370"/>
       <c r="M151" s="113">
         <f t="shared" ca="1" si="89"/>
-        <v>0.10714285714285714</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="N151" s="97">
         <f>COUNTIFS($L$7:$L$143,"X")</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O151" s="99"/>
       <c r="P151" s="51"/>
@@ -24016,11 +24111,11 @@
       <c r="C152" s="168" t="s">
         <v>32</v>
       </c>
-      <c r="D152" s="424" t="s">
+      <c r="D152" s="395" t="s">
         <v>33</v>
       </c>
-      <c r="E152" s="424"/>
-      <c r="F152" s="425"/>
+      <c r="E152" s="395"/>
+      <c r="F152" s="396"/>
       <c r="H152" s="1" t="s">
         <v>11</v>
       </c>
@@ -24029,11 +24124,11 @@
       <c r="C153" s="167" t="s">
         <v>34</v>
       </c>
-      <c r="D153" s="424" t="s">
+      <c r="D153" s="395" t="s">
         <v>35</v>
       </c>
-      <c r="E153" s="424"/>
-      <c r="F153" s="425"/>
+      <c r="E153" s="395"/>
+      <c r="F153" s="396"/>
       <c r="H153" s="13"/>
       <c r="I153" s="141"/>
       <c r="J153" s="141"/>
@@ -24061,14 +24156,14 @@
       <c r="AI153" s="1"/>
     </row>
     <row r="154" spans="1:35">
-      <c r="C154" s="385" t="s">
+      <c r="C154" s="373" t="s">
         <v>75</v>
       </c>
-      <c r="D154" s="387" t="s">
+      <c r="D154" s="375" t="s">
         <v>76</v>
       </c>
-      <c r="E154" s="387"/>
-      <c r="F154" s="388"/>
+      <c r="E154" s="375"/>
+      <c r="F154" s="376"/>
       <c r="H154" s="13"/>
       <c r="J154" s="141"/>
       <c r="K154" s="13"/>
@@ -24095,10 +24190,10 @@
       <c r="AI154" s="1"/>
     </row>
     <row r="155" spans="1:35" ht="16.5" thickBot="1">
-      <c r="C155" s="386"/>
-      <c r="D155" s="389"/>
-      <c r="E155" s="389"/>
-      <c r="F155" s="390"/>
+      <c r="C155" s="374"/>
+      <c r="D155" s="377"/>
+      <c r="E155" s="377"/>
+      <c r="F155" s="378"/>
       <c r="H155" s="13"/>
       <c r="I155" s="141"/>
       <c r="J155" s="141"/>
@@ -24153,12 +24248,12 @@
       <c r="AI156" s="1"/>
     </row>
     <row r="157" spans="1:35">
-      <c r="C157" s="372" t="s">
+      <c r="C157" s="361" t="s">
         <v>41</v>
       </c>
-      <c r="D157" s="372"/>
-      <c r="E157" s="372"/>
-      <c r="F157" s="372"/>
+      <c r="D157" s="361"/>
+      <c r="E157" s="361"/>
+      <c r="F157" s="361"/>
       <c r="H157" s="13"/>
       <c r="I157" s="141"/>
       <c r="J157" s="141"/>
@@ -24189,11 +24284,11 @@
       <c r="C158" s="169" t="s">
         <v>8</v>
       </c>
-      <c r="D158" s="412" t="s">
+      <c r="D158" s="414" t="s">
         <v>91</v>
       </c>
-      <c r="E158" s="412"/>
-      <c r="F158" s="412"/>
+      <c r="E158" s="414"/>
+      <c r="F158" s="414"/>
       <c r="H158" s="13"/>
       <c r="I158" s="141"/>
       <c r="J158" s="141"/>
@@ -24224,11 +24319,11 @@
       <c r="C159" s="169" t="s">
         <v>8</v>
       </c>
-      <c r="D159" s="412" t="s">
+      <c r="D159" s="414" t="s">
         <v>92</v>
       </c>
-      <c r="E159" s="412"/>
-      <c r="F159" s="412"/>
+      <c r="E159" s="414"/>
+      <c r="F159" s="414"/>
       <c r="H159" s="13"/>
       <c r="I159" s="141"/>
       <c r="J159" s="141"/>
@@ -24259,11 +24354,11 @@
       <c r="C160" s="169" t="s">
         <v>8</v>
       </c>
-      <c r="D160" s="412" t="s">
+      <c r="D160" s="414" t="s">
         <v>93</v>
       </c>
-      <c r="E160" s="412"/>
-      <c r="F160" s="412"/>
+      <c r="E160" s="414"/>
+      <c r="F160" s="414"/>
       <c r="H160" s="13"/>
       <c r="I160" s="141"/>
       <c r="J160" s="141"/>
@@ -24318,12 +24413,12 @@
       <c r="AI161" s="1"/>
     </row>
     <row r="162" spans="3:35" ht="16.5" thickBot="1">
-      <c r="C162" s="416" t="s">
+      <c r="C162" s="420" t="s">
         <v>96</v>
       </c>
-      <c r="D162" s="417"/>
-      <c r="E162" s="417"/>
-      <c r="F162" s="418"/>
+      <c r="D162" s="421"/>
+      <c r="E162" s="421"/>
+      <c r="F162" s="422"/>
       <c r="H162" s="13"/>
       <c r="I162" s="141"/>
       <c r="J162" s="141"/>
@@ -24354,11 +24449,11 @@
       <c r="C163" s="212" t="s">
         <v>81</v>
       </c>
-      <c r="D163" s="419" t="s">
+      <c r="D163" s="423" t="s">
         <v>97</v>
       </c>
-      <c r="E163" s="419"/>
-      <c r="F163" s="420"/>
+      <c r="E163" s="423"/>
+      <c r="F163" s="424"/>
       <c r="H163" s="13"/>
       <c r="I163" s="141"/>
       <c r="J163" s="141"/>
@@ -24389,101 +24484,101 @@
       <c r="C164" s="213" t="s">
         <v>82</v>
       </c>
-      <c r="D164" s="410" t="s">
+      <c r="D164" s="415" t="s">
         <v>98</v>
       </c>
-      <c r="E164" s="410"/>
-      <c r="F164" s="411"/>
+      <c r="E164" s="415"/>
+      <c r="F164" s="416"/>
     </row>
     <row r="165" spans="3:35">
       <c r="C165" s="213" t="s">
         <v>83</v>
       </c>
-      <c r="D165" s="410" t="s">
+      <c r="D165" s="415" t="s">
         <v>99</v>
       </c>
-      <c r="E165" s="410"/>
-      <c r="F165" s="411"/>
+      <c r="E165" s="415"/>
+      <c r="F165" s="416"/>
     </row>
     <row r="166" spans="3:35">
       <c r="C166" s="214" t="s">
         <v>84</v>
       </c>
-      <c r="D166" s="410" t="s">
+      <c r="D166" s="415" t="s">
         <v>100</v>
       </c>
-      <c r="E166" s="410"/>
-      <c r="F166" s="411"/>
+      <c r="E166" s="415"/>
+      <c r="F166" s="416"/>
     </row>
     <row r="167" spans="3:35">
       <c r="C167" s="214" t="s">
         <v>85</v>
       </c>
-      <c r="D167" s="410" t="s">
+      <c r="D167" s="415" t="s">
         <v>101</v>
       </c>
-      <c r="E167" s="410"/>
-      <c r="F167" s="411"/>
+      <c r="E167" s="415"/>
+      <c r="F167" s="416"/>
     </row>
     <row r="168" spans="3:35" ht="18.75">
       <c r="C168" s="214" t="s">
         <v>86</v>
       </c>
-      <c r="D168" s="410" t="s">
+      <c r="D168" s="415" t="s">
         <v>102</v>
       </c>
-      <c r="E168" s="410"/>
-      <c r="F168" s="411"/>
+      <c r="E168" s="415"/>
+      <c r="F168" s="416"/>
     </row>
     <row r="169" spans="3:35" ht="18.75">
       <c r="C169" s="213" t="s">
         <v>87</v>
       </c>
-      <c r="D169" s="410" t="s">
+      <c r="D169" s="415" t="s">
         <v>103</v>
       </c>
-      <c r="E169" s="410"/>
-      <c r="F169" s="411"/>
+      <c r="E169" s="415"/>
+      <c r="F169" s="416"/>
     </row>
     <row r="170" spans="3:35">
       <c r="C170" s="215" t="s">
         <v>88</v>
       </c>
-      <c r="D170" s="413" t="s">
+      <c r="D170" s="417" t="s">
         <v>104</v>
       </c>
-      <c r="E170" s="414"/>
-      <c r="F170" s="415"/>
+      <c r="E170" s="418"/>
+      <c r="F170" s="419"/>
     </row>
     <row r="171" spans="3:35" ht="18.75">
       <c r="C171" s="215" t="s">
         <v>89</v>
       </c>
-      <c r="D171" s="410" t="s">
+      <c r="D171" s="415" t="s">
         <v>105</v>
       </c>
-      <c r="E171" s="410"/>
-      <c r="F171" s="411"/>
+      <c r="E171" s="415"/>
+      <c r="F171" s="416"/>
     </row>
     <row r="172" spans="3:35">
       <c r="C172" s="213" t="s">
         <v>90</v>
       </c>
-      <c r="D172" s="410" t="s">
+      <c r="D172" s="415" t="s">
         <v>106</v>
       </c>
-      <c r="E172" s="410"/>
-      <c r="F172" s="411"/>
+      <c r="E172" s="415"/>
+      <c r="F172" s="416"/>
     </row>
     <row r="173" spans="3:35" ht="16.5" thickBot="1">
       <c r="C173" s="216" t="s">
         <v>94</v>
       </c>
-      <c r="D173" s="421" t="s">
+      <c r="D173" s="400" t="s">
         <v>107</v>
       </c>
-      <c r="E173" s="422"/>
-      <c r="F173" s="423"/>
+      <c r="E173" s="401"/>
+      <c r="F173" s="402"/>
     </row>
   </sheetData>
   <autoFilter ref="A6:AE143" xr:uid="{C724CDAB-378C-47DB-9F45-08EE3BFB6E8B}">
@@ -24492,20 +24587,35 @@
     </sortState>
   </autoFilter>
   <mergeCells count="59">
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="D154:F155"/>
-    <mergeCell ref="D146:F146"/>
-    <mergeCell ref="I146:L146"/>
-    <mergeCell ref="AA4:AD4"/>
-    <mergeCell ref="Q145:R145"/>
-    <mergeCell ref="D151:F151"/>
-    <mergeCell ref="D152:F152"/>
-    <mergeCell ref="D153:F153"/>
-    <mergeCell ref="S4:U4"/>
-    <mergeCell ref="L4:L5"/>
-    <mergeCell ref="Q4:R4"/>
-    <mergeCell ref="K4:K5"/>
-    <mergeCell ref="Y4:Z4"/>
+    <mergeCell ref="AG5:AG6"/>
+    <mergeCell ref="AH5:AH6"/>
+    <mergeCell ref="AI5:AI6"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="AE4:AE5"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="V4:X4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="O4:P4"/>
+    <mergeCell ref="D172:F172"/>
+    <mergeCell ref="D159:F159"/>
+    <mergeCell ref="D160:F160"/>
+    <mergeCell ref="D167:F167"/>
+    <mergeCell ref="D168:F168"/>
+    <mergeCell ref="D169:F169"/>
+    <mergeCell ref="D170:F170"/>
+    <mergeCell ref="D171:F171"/>
+    <mergeCell ref="C162:F162"/>
+    <mergeCell ref="D163:F163"/>
+    <mergeCell ref="D164:F164"/>
+    <mergeCell ref="D165:F165"/>
+    <mergeCell ref="D166:F166"/>
     <mergeCell ref="D173:F173"/>
     <mergeCell ref="D145:F145"/>
     <mergeCell ref="C157:F157"/>
@@ -24522,35 +24632,20 @@
     <mergeCell ref="D149:F149"/>
     <mergeCell ref="D150:F150"/>
     <mergeCell ref="D158:F158"/>
-    <mergeCell ref="D172:F172"/>
-    <mergeCell ref="D159:F159"/>
-    <mergeCell ref="D160:F160"/>
-    <mergeCell ref="D167:F167"/>
-    <mergeCell ref="D168:F168"/>
-    <mergeCell ref="D169:F169"/>
-    <mergeCell ref="D170:F170"/>
-    <mergeCell ref="D171:F171"/>
-    <mergeCell ref="C162:F162"/>
-    <mergeCell ref="D163:F163"/>
-    <mergeCell ref="D164:F164"/>
-    <mergeCell ref="D165:F165"/>
-    <mergeCell ref="D166:F166"/>
-    <mergeCell ref="AG5:AG6"/>
-    <mergeCell ref="AH5:AH6"/>
-    <mergeCell ref="AI5:AI6"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="I4:I5"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="H4:H5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="AE4:AE5"/>
-    <mergeCell ref="J4:J5"/>
-    <mergeCell ref="V4:X4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="O4:P4"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="D154:F155"/>
+    <mergeCell ref="D146:F146"/>
+    <mergeCell ref="I146:L146"/>
+    <mergeCell ref="AA4:AD4"/>
+    <mergeCell ref="Q145:R145"/>
+    <mergeCell ref="D151:F151"/>
+    <mergeCell ref="D152:F152"/>
+    <mergeCell ref="D153:F153"/>
+    <mergeCell ref="S4:U4"/>
+    <mergeCell ref="L4:L5"/>
+    <mergeCell ref="Q4:R4"/>
+    <mergeCell ref="K4:K5"/>
+    <mergeCell ref="Y4:Z4"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="A7:AE143 AG7:AI143">
@@ -25084,9 +25179,19 @@
     <hyperlink ref="O135" r:id="rId505" xr:uid="{E415571E-9ABB-4838-B4BB-663A644C52E5}"/>
     <hyperlink ref="O132" r:id="rId506" xr:uid="{98767DB8-64B4-4F62-AF4D-D1090D594B1A}"/>
     <hyperlink ref="O131" r:id="rId507" xr:uid="{DE03DEA0-F484-427D-9D4A-E446F78CBEA0}"/>
+    <hyperlink ref="Q69" r:id="rId508" xr:uid="{C707341B-C732-4702-9ABA-7F958D07CDC4}"/>
+    <hyperlink ref="Q103" r:id="rId509" xr:uid="{308C595A-8E32-4C9B-9BB2-19EF13F06D0B}"/>
+    <hyperlink ref="Q116" r:id="rId510" xr:uid="{63F6A2D7-2F06-4811-A58D-5AC0A9C3B7AB}"/>
+    <hyperlink ref="Q104" r:id="rId511" xr:uid="{E501FC20-B408-4A40-8D12-562AAB9D1D05}"/>
+    <hyperlink ref="Q105" r:id="rId512" xr:uid="{48538F5F-CA57-4FAE-BB4E-300F1696CC2C}"/>
+    <hyperlink ref="Q113" r:id="rId513" xr:uid="{0C6C0B32-7CE1-4516-A3E7-247858363D3F}"/>
+    <hyperlink ref="Q115" r:id="rId514" xr:uid="{3E4D8F72-1AD4-4C25-9220-17068324D340}"/>
+    <hyperlink ref="Q120" r:id="rId515" xr:uid="{FADCE709-BF5F-432D-8C19-79AFA2F4F3E3}"/>
+    <hyperlink ref="Q122" r:id="rId516" xr:uid="{889D74CF-A66B-448A-989C-A2B7707E0520}"/>
+    <hyperlink ref="Q124" r:id="rId517" xr:uid="{B9A70A03-2E25-4243-9FDF-0D2FA60C4B00}"/>
   </hyperlinks>
   <pageMargins left="0.25" right="0.17" top="0.5" bottom="0.25" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="28" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId508"/>
+  <pageSetup paperSize="9" scale="28" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId518"/>
   <colBreaks count="1" manualBreakCount="1">
     <brk id="30" max="564" man="1"/>
   </colBreaks>
@@ -25139,7 +25244,7 @@
       </c>
       <c r="I1" s="176">
         <f ca="1">TODAY()</f>
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="J1" s="131"/>
       <c r="K1" s="197"/>
@@ -25224,88 +25329,88 @@
       <c r="AD3" s="159"/>
     </row>
     <row r="4" spans="1:35" s="5" customFormat="1" ht="36" customHeight="1" thickBot="1">
-      <c r="A4" s="397" t="s">
+      <c r="A4" s="426" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="407" t="s">
+      <c r="B4" s="348" t="s">
         <v>515</v>
       </c>
-      <c r="C4" s="403" t="s">
+      <c r="C4" s="391" t="s">
         <v>45</v>
       </c>
-      <c r="D4" s="362" t="s">
+      <c r="D4" s="352" t="s">
         <v>46</v>
       </c>
-      <c r="E4" s="399" t="s">
+      <c r="E4" s="430" t="s">
         <v>47</v>
       </c>
-      <c r="F4" s="362" t="s">
+      <c r="F4" s="352" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="401" t="s">
+      <c r="G4" s="428" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="364" t="s">
+      <c r="H4" s="385" t="s">
         <v>48</v>
       </c>
-      <c r="I4" s="364" t="s">
+      <c r="I4" s="385" t="s">
         <v>49</v>
       </c>
-      <c r="J4" s="362" t="s">
+      <c r="J4" s="352" t="s">
         <v>78</v>
       </c>
-      <c r="K4" s="364" t="s">
+      <c r="K4" s="385" t="s">
         <v>80</v>
       </c>
-      <c r="L4" s="366" t="s">
+      <c r="L4" s="390" t="s">
         <v>53</v>
       </c>
-      <c r="M4" s="367"/>
-      <c r="N4" s="368" t="s">
+      <c r="M4" s="379"/>
+      <c r="N4" s="389" t="s">
         <v>55</v>
       </c>
-      <c r="O4" s="367"/>
-      <c r="P4" s="368" t="s">
+      <c r="O4" s="379"/>
+      <c r="P4" s="389" t="s">
         <v>72</v>
       </c>
-      <c r="Q4" s="367"/>
-      <c r="R4" s="366" t="s">
+      <c r="Q4" s="379"/>
+      <c r="R4" s="390" t="s">
         <v>53</v>
       </c>
-      <c r="S4" s="366"/>
-      <c r="T4" s="367"/>
-      <c r="U4" s="368" t="s">
+      <c r="S4" s="390"/>
+      <c r="T4" s="379"/>
+      <c r="U4" s="389" t="s">
         <v>55</v>
       </c>
-      <c r="V4" s="366"/>
-      <c r="W4" s="367"/>
+      <c r="V4" s="390"/>
+      <c r="W4" s="379"/>
       <c r="X4" s="393" t="s">
         <v>72</v>
       </c>
-      <c r="Y4" s="394"/>
+      <c r="Y4" s="432"/>
       <c r="Z4" s="393" t="s">
         <v>112</v>
       </c>
-      <c r="AA4" s="395"/>
-      <c r="AB4" s="395"/>
-      <c r="AC4" s="396"/>
-      <c r="AD4" s="362" t="s">
+      <c r="AA4" s="398"/>
+      <c r="AB4" s="398"/>
+      <c r="AC4" s="399"/>
+      <c r="AD4" s="352" t="s">
         <v>79</v>
       </c>
       <c r="AG4" s="236"/>
     </row>
     <row r="5" spans="1:35" ht="78.75">
-      <c r="A5" s="398"/>
-      <c r="B5" s="408"/>
-      <c r="C5" s="404"/>
-      <c r="D5" s="369"/>
-      <c r="E5" s="400"/>
-      <c r="F5" s="369"/>
-      <c r="G5" s="402"/>
-      <c r="H5" s="365"/>
-      <c r="I5" s="365"/>
-      <c r="J5" s="369"/>
-      <c r="K5" s="365"/>
+      <c r="A5" s="427"/>
+      <c r="B5" s="349"/>
+      <c r="C5" s="392"/>
+      <c r="D5" s="353"/>
+      <c r="E5" s="431"/>
+      <c r="F5" s="353"/>
+      <c r="G5" s="429"/>
+      <c r="H5" s="386"/>
+      <c r="I5" s="386"/>
+      <c r="J5" s="353"/>
+      <c r="K5" s="386"/>
       <c r="L5" s="79" t="s">
         <v>52</v>
       </c>
@@ -25360,14 +25465,14 @@
       <c r="AC5" s="250" t="s">
         <v>118</v>
       </c>
-      <c r="AD5" s="363"/>
-      <c r="AG5" s="348" t="s">
+      <c r="AD5" s="380"/>
+      <c r="AG5" s="437" t="s">
         <v>119</v>
       </c>
-      <c r="AH5" s="350" t="s">
+      <c r="AH5" s="439" t="s">
         <v>120</v>
       </c>
-      <c r="AI5" s="352" t="s">
+      <c r="AI5" s="441" t="s">
         <v>121</v>
       </c>
     </row>
@@ -25402,9 +25507,9 @@
       <c r="AB6" s="86"/>
       <c r="AC6" s="86"/>
       <c r="AD6" s="74"/>
-      <c r="AG6" s="349"/>
-      <c r="AH6" s="351"/>
-      <c r="AI6" s="353"/>
+      <c r="AG6" s="438"/>
+      <c r="AH6" s="440"/>
+      <c r="AI6" s="442"/>
     </row>
     <row r="7" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A7" s="33">
@@ -26080,7 +26185,7 @@
       </c>
       <c r="AC12" s="183">
         <f t="shared" ca="1" si="7"/>
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AD12" s="92"/>
       <c r="AG12" s="238" t="str">
@@ -26306,7 +26411,7 @@
       </c>
       <c r="AC14" s="183">
         <f t="shared" ca="1" si="7"/>
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AD14" s="92"/>
       <c r="AG14" s="238" t="str">
@@ -26532,7 +26637,7 @@
       </c>
       <c r="AC16" s="183">
         <f t="shared" ca="1" si="7"/>
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AD16" s="92"/>
       <c r="AG16" s="238" t="str">
@@ -26555,7 +26660,7 @@
         <v>YES</v>
       </c>
     </row>
-    <row r="17" spans="1:35" s="9" customFormat="1" ht="94.5">
+    <row r="17" spans="1:35" s="9" customFormat="1" ht="110.25">
       <c r="A17" s="33">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -27225,7 +27330,7 @@
         <v/>
       </c>
       <c r="AD22" s="92" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="AG22" s="238" t="str">
         <f t="shared" si="8"/>
@@ -27337,7 +27442,7 @@
       </c>
       <c r="AC23" s="183">
         <f t="shared" ca="1" si="7"/>
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AD23" s="92"/>
       <c r="AG23" s="238" t="str">
@@ -27450,7 +27555,7 @@
       </c>
       <c r="AC24" s="183">
         <f t="shared" ca="1" si="7"/>
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AD24" s="92"/>
       <c r="AG24" s="238" t="str">
@@ -27566,7 +27671,7 @@
         <v>274</v>
       </c>
       <c r="AD25" s="92" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="AG25" s="238" t="str">
         <f t="shared" si="8"/>
@@ -27678,7 +27783,7 @@
       </c>
       <c r="AC26" s="183">
         <f t="shared" ca="1" si="7"/>
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AD26" s="92"/>
       <c r="AG26" s="238" t="str">
@@ -28000,7 +28105,7 @@
         <v/>
       </c>
       <c r="AD29" s="92" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="AG29" s="238" t="str">
         <f t="shared" si="8"/>
@@ -28112,7 +28217,7 @@
       </c>
       <c r="AC30" s="183">
         <f t="shared" ca="1" si="7"/>
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AD30" s="92" t="s">
         <v>593</v>
@@ -28166,12 +28271,12 @@
         <v>1</v>
       </c>
       <c r="I31" s="164">
-        <f ca="1">IF(ISBLANK($V31),_xlfn.DAYS($I$1,$T31),_xlfn.DAYS($V31,$T31))</f>
-        <v>176</v>
+        <f>IF(ISBLANK($V31),_xlfn.DAYS($I$1,$T31),_xlfn.DAYS($V31,$T31))</f>
+        <v>50</v>
       </c>
       <c r="J31" s="47">
-        <f t="shared" ca="1" si="4"/>
-        <v>155</v>
+        <f t="shared" si="4"/>
+        <v>29</v>
       </c>
       <c r="K31" s="164"/>
       <c r="L31" s="54" t="s">
@@ -28180,10 +28285,16 @@
       <c r="M31" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="N31" s="40"/>
+      <c r="N31" s="40" t="s">
+        <v>8</v>
+      </c>
       <c r="O31" s="41"/>
-      <c r="P31" s="40"/>
-      <c r="Q31" s="155"/>
+      <c r="P31" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q31" s="155" t="s">
+        <v>1</v>
+      </c>
       <c r="R31" s="27">
         <v>46014</v>
       </c>
@@ -28193,23 +28304,33 @@
       <c r="T31" s="188">
         <v>46141</v>
       </c>
-      <c r="U31" s="29"/>
-      <c r="V31" s="188"/>
-      <c r="W31" s="227"/>
-      <c r="X31" s="230"/>
-      <c r="Y31" s="227"/>
-      <c r="Z31" s="29" t="str">
+      <c r="U31" s="29">
+        <v>46150</v>
+      </c>
+      <c r="V31" s="188">
+        <v>46191</v>
+      </c>
+      <c r="W31" s="235" t="s">
+        <v>190</v>
+      </c>
+      <c r="X31" s="230">
+        <v>46206</v>
+      </c>
+      <c r="Y31" s="227">
+        <v>46212</v>
+      </c>
+      <c r="Z31" s="29">
         <f t="shared" si="5"/>
-        <v/>
+        <v>46219</v>
       </c>
       <c r="AA31" s="229"/>
       <c r="AB31" s="229" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="AC31" s="183" t="str">
-        <f t="shared" si="7"/>
-        <v/>
+        <f t="shared" ca="1" si="6"/>
+        <v>Not submit yet</v>
+      </c>
+      <c r="AC31" s="183">
+        <f t="shared" ca="1" si="7"/>
+        <v>99</v>
       </c>
       <c r="AD31" s="92" t="s">
         <v>597</v>
@@ -28231,7 +28352,7 @@
       </c>
       <c r="AI31" s="75" t="str">
         <f t="shared" si="9"/>
-        <v/>
+        <v>YES</v>
       </c>
     </row>
     <row r="32" spans="1:35" s="9" customFormat="1" ht="47.25">
@@ -28469,14 +28590,14 @@
         <v>342</v>
       </c>
       <c r="D34" s="25" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="E34" s="174"/>
       <c r="F34" s="31" t="s">
+        <v>909</v>
+      </c>
+      <c r="G34" s="21" t="s">
         <v>910</v>
-      </c>
-      <c r="G34" s="21" t="s">
-        <v>911</v>
       </c>
       <c r="H34" s="138"/>
       <c r="I34" s="164"/>
@@ -28520,7 +28641,7 @@
         <v/>
       </c>
       <c r="AD34" s="92" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="AG34" s="238" t="str">
         <f t="shared" si="8"/>
@@ -28555,14 +28676,14 @@
         <v>197</v>
       </c>
       <c r="D35" s="25" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="E35" s="174">
         <f t="shared" si="2"/>
         <v>46325</v>
       </c>
       <c r="F35" s="31" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="G35" s="21" t="s">
         <v>600</v>
@@ -28623,7 +28744,7 @@
         <v/>
       </c>
       <c r="AD35" s="92" t="s">
-        <v>1067</v>
+        <v>1063</v>
       </c>
       <c r="AG35" s="238" t="str">
         <f t="shared" si="8"/>
@@ -28665,10 +28786,10 @@
         <v>46302</v>
       </c>
       <c r="F36" s="31" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
       <c r="G36" s="21" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="H36" s="138" t="s">
         <v>1</v>
@@ -28726,7 +28847,7 @@
         <v/>
       </c>
       <c r="AD36" s="92" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="AG36" s="238" t="str">
         <f t="shared" si="8"/>
@@ -28759,17 +28880,17 @@
       </c>
       <c r="C37" s="164"/>
       <c r="D37" s="25" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="E37" s="174">
         <f t="shared" si="2"/>
         <v>46302</v>
       </c>
       <c r="F37" s="31" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="G37" s="21" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="H37" s="138" t="s">
         <v>1</v>
@@ -28827,7 +28948,7 @@
         <v/>
       </c>
       <c r="AD37" s="92" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="AG37" s="238" t="str">
         <f t="shared" si="8"/>
@@ -28862,17 +28983,17 @@
         <v>372</v>
       </c>
       <c r="D38" s="25" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="E38" s="174">
         <f t="shared" si="2"/>
         <v>46304</v>
       </c>
       <c r="F38" s="31" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="G38" s="21" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="H38" s="138" t="s">
         <v>1</v>
@@ -28894,8 +29015,12 @@
         <v>8</v>
       </c>
       <c r="O38" s="41"/>
-      <c r="P38" s="40"/>
-      <c r="Q38" s="155"/>
+      <c r="P38" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q38" s="155" t="s">
+        <v>1</v>
+      </c>
       <c r="R38" s="27">
         <v>46283</v>
       </c>
@@ -28914,23 +29039,25 @@
       <c r="W38" s="235" t="s">
         <v>240</v>
       </c>
-      <c r="X38" s="230"/>
+      <c r="X38" s="230">
+        <v>46317</v>
+      </c>
       <c r="Y38" s="227"/>
       <c r="Z38" s="29">
         <f t="shared" si="5"/>
-        <v>46311</v>
+        <v>46325</v>
       </c>
       <c r="AA38" s="229"/>
       <c r="AB38" s="229" t="str">
-        <f t="shared" si="6"/>
-        <v/>
+        <f t="shared" ca="1" si="6"/>
+        <v>In progress</v>
       </c>
       <c r="AC38" s="183" t="str">
-        <f t="shared" ref="AC38" si="18">IF(AB38="Late Resubmission",IF(AA38="","",AA38-Z38),IF(AB38="Not submit yet",IF(Z38="","",$I$1-Z38),""))</f>
+        <f t="shared" ref="AC38" ca="1" si="18">IF(AB38="Late Resubmission",IF(AA38="","",AA38-Z38),IF(AB38="Not submit yet",IF(Z38="","",$I$1-Z38),""))</f>
         <v/>
       </c>
       <c r="AD38" s="92" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
       <c r="AG38" s="238" t="str">
         <f t="shared" si="8"/>
@@ -28949,7 +29076,7 @@
       </c>
       <c r="AI38" s="75" t="str">
         <f t="shared" si="9"/>
-        <v/>
+        <v>YES</v>
       </c>
     </row>
     <row r="39" spans="1:35" s="9" customFormat="1" ht="63">
@@ -28965,14 +29092,14 @@
         <v>197</v>
       </c>
       <c r="D39" s="25" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="E39" s="174">
         <f t="shared" si="2"/>
         <v>46325</v>
       </c>
       <c r="F39" s="31" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="G39" s="21" t="s">
         <v>588</v>
@@ -29033,7 +29160,7 @@
         <v/>
       </c>
       <c r="AD39" s="92" t="s">
-        <v>1067</v>
+        <v>1063</v>
       </c>
       <c r="AG39" s="238" t="str">
         <f t="shared" si="8"/>
@@ -29066,22 +29193,22 @@
       </c>
       <c r="C40" s="164"/>
       <c r="D40" s="25" t="s">
-        <v>1059</v>
+        <v>1056</v>
       </c>
       <c r="E40" s="174">
         <f t="shared" si="2"/>
         <v>46330</v>
       </c>
       <c r="F40" s="31" t="s">
-        <v>1060</v>
+        <v>1057</v>
       </c>
       <c r="G40" s="21" t="s">
-        <v>1061</v>
+        <v>1058</v>
       </c>
       <c r="H40" s="138"/>
       <c r="I40" s="164">
         <f t="shared" ca="1" si="10"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J40" s="47">
         <f t="shared" ca="1" si="4"/>
@@ -29155,14 +29282,14 @@
       </c>
       <c r="C41" s="164"/>
       <c r="D41" s="25" t="s">
-        <v>1095</v>
+        <v>1091</v>
       </c>
       <c r="E41" s="174">
         <f t="shared" si="2"/>
         <v>46332</v>
       </c>
       <c r="F41" s="31" t="s">
-        <v>1096</v>
+        <v>1092</v>
       </c>
       <c r="G41" s="21" t="s">
         <v>547</v>
@@ -29170,7 +29297,7 @@
       <c r="H41" s="138"/>
       <c r="I41" s="164">
         <f t="shared" ca="1" si="10"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J41" s="47">
         <f t="shared" ca="1" si="4"/>
@@ -29244,14 +29371,14 @@
       </c>
       <c r="C42" s="164"/>
       <c r="D42" s="25" t="s">
-        <v>1101</v>
+        <v>1096</v>
       </c>
       <c r="E42" s="174">
         <f t="shared" si="2"/>
         <v>46338</v>
       </c>
       <c r="F42" s="31" t="s">
-        <v>1102</v>
+        <v>1097</v>
       </c>
       <c r="G42" s="21" t="s">
         <v>538</v>
@@ -29259,7 +29386,7 @@
       <c r="H42" s="138"/>
       <c r="I42" s="164">
         <f t="shared" ca="1" si="10"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J42" s="47">
         <f t="shared" ca="1" si="4"/>
@@ -29302,7 +29429,7 @@
         <v/>
       </c>
       <c r="AD42" s="92" t="s">
-        <v>1110</v>
+        <v>1105</v>
       </c>
       <c r="AG42" s="238" t="str">
         <f t="shared" si="8"/>
@@ -29335,14 +29462,14 @@
       </c>
       <c r="C43" s="164"/>
       <c r="D43" s="25" t="s">
-        <v>1103</v>
+        <v>1098</v>
       </c>
       <c r="E43" s="174">
         <f t="shared" si="2"/>
         <v>46337</v>
       </c>
       <c r="F43" s="31" t="s">
-        <v>1104</v>
+        <v>1099</v>
       </c>
       <c r="G43" s="21" t="s">
         <v>521</v>
@@ -29350,7 +29477,7 @@
       <c r="H43" s="138"/>
       <c r="I43" s="164">
         <f t="shared" ca="1" si="10"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J43" s="47">
         <f t="shared" ca="1" si="4"/>
@@ -29424,14 +29551,14 @@
       </c>
       <c r="C44" s="164"/>
       <c r="D44" s="25" t="s">
-        <v>1105</v>
+        <v>1100</v>
       </c>
       <c r="E44" s="174">
         <f t="shared" si="2"/>
         <v>46337</v>
       </c>
       <c r="F44" s="31" t="s">
-        <v>1106</v>
+        <v>1101</v>
       </c>
       <c r="G44" s="21" t="s">
         <v>526</v>
@@ -29439,7 +29566,7 @@
       <c r="H44" s="138"/>
       <c r="I44" s="164">
         <f t="shared" ca="1" si="10"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J44" s="47">
         <f t="shared" ca="1" si="4"/>
@@ -29515,22 +29642,22 @@
         <v>656</v>
       </c>
       <c r="D45" s="25" t="s">
-        <v>1107</v>
+        <v>1102</v>
       </c>
       <c r="E45" s="174">
         <f t="shared" si="2"/>
         <v>46337</v>
       </c>
       <c r="F45" s="31" t="s">
-        <v>1108</v>
+        <v>1103</v>
       </c>
       <c r="G45" s="21" t="s">
-        <v>1109</v>
+        <v>1104</v>
       </c>
       <c r="H45" s="138"/>
       <c r="I45" s="164">
         <f t="shared" ca="1" si="10"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J45" s="47">
         <f t="shared" ca="1" si="4"/>
@@ -29674,28 +29801,28 @@
       <c r="C49" s="166" t="s">
         <v>20</v>
       </c>
-      <c r="D49" s="405" t="s">
+      <c r="D49" s="403" t="s">
         <v>21</v>
       </c>
-      <c r="E49" s="406"/>
+      <c r="E49" s="404"/>
       <c r="F49" s="46"/>
       <c r="G49" s="46"/>
-      <c r="H49" s="357" t="s">
+      <c r="H49" s="356" t="s">
         <v>14</v>
       </c>
-      <c r="I49" s="358"/>
-      <c r="J49" s="358"/>
-      <c r="K49" s="358"/>
-      <c r="L49" s="358"/>
-      <c r="M49" s="359"/>
-      <c r="N49" s="360" t="s">
+      <c r="I49" s="357"/>
+      <c r="J49" s="357"/>
+      <c r="K49" s="357"/>
+      <c r="L49" s="357"/>
+      <c r="M49" s="358"/>
+      <c r="N49" s="350" t="s">
         <v>7</v>
       </c>
-      <c r="O49" s="361"/>
-      <c r="P49" s="360" t="s">
+      <c r="O49" s="351"/>
+      <c r="P49" s="350" t="s">
         <v>109</v>
       </c>
-      <c r="Q49" s="361"/>
+      <c r="Q49" s="351"/>
       <c r="R49" s="1"/>
       <c r="S49" s="1"/>
       <c r="T49" s="140"/>
@@ -29715,24 +29842,24 @@
       <c r="C50" s="195" t="s">
         <v>109</v>
       </c>
-      <c r="D50" s="391" t="s">
+      <c r="D50" s="435" t="s">
         <v>111</v>
       </c>
-      <c r="E50" s="392"/>
+      <c r="E50" s="436"/>
       <c r="F50" s="46"/>
-      <c r="H50" s="357" t="s">
+      <c r="H50" s="356" t="s">
         <v>18</v>
       </c>
-      <c r="I50" s="358"/>
-      <c r="J50" s="358"/>
-      <c r="K50" s="359"/>
+      <c r="I50" s="357"/>
+      <c r="J50" s="357"/>
+      <c r="K50" s="358"/>
       <c r="L50" s="105">
         <f ca="1">M50/$M$50</f>
         <v>1</v>
       </c>
       <c r="M50" s="106">
         <f ca="1">SUM($M$51:$M$55)</f>
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N50" s="102" t="s">
         <v>15</v>
@@ -29767,21 +29894,21 @@
       <c r="C51" s="195" t="s">
         <v>36</v>
       </c>
-      <c r="D51" s="370" t="s">
+      <c r="D51" s="433" t="s">
         <v>37</v>
       </c>
-      <c r="E51" s="371"/>
+      <c r="E51" s="434"/>
       <c r="F51" s="69"/>
       <c r="G51" s="6"/>
-      <c r="H51" s="373" t="s">
+      <c r="H51" s="405" t="s">
         <v>66</v>
       </c>
-      <c r="I51" s="374"/>
-      <c r="J51" s="374"/>
-      <c r="K51" s="375"/>
+      <c r="I51" s="406"/>
+      <c r="J51" s="406"/>
+      <c r="K51" s="407"/>
       <c r="L51" s="107">
         <f ca="1">M51/$M$50</f>
-        <v>7.4999999999999997E-2</v>
+        <v>7.6923076923076927E-2</v>
       </c>
       <c r="M51" s="108">
         <f>COUNTIF($H$7:$H$47,"A")</f>
@@ -29819,24 +29946,24 @@
       <c r="AI51" s="11"/>
     </row>
     <row r="52" spans="3:35">
-      <c r="C52" s="385" t="s">
+      <c r="C52" s="373" t="s">
         <v>75</v>
       </c>
-      <c r="D52" s="387" t="s">
+      <c r="D52" s="375" t="s">
         <v>76</v>
       </c>
-      <c r="E52" s="388"/>
+      <c r="E52" s="376"/>
       <c r="F52" s="70"/>
       <c r="G52" s="6"/>
-      <c r="H52" s="376" t="s">
+      <c r="H52" s="408" t="s">
         <v>67</v>
       </c>
-      <c r="I52" s="377"/>
-      <c r="J52" s="377"/>
-      <c r="K52" s="378"/>
+      <c r="I52" s="409"/>
+      <c r="J52" s="409"/>
+      <c r="K52" s="410"/>
       <c r="L52" s="109">
         <f t="shared" ref="L52:L55" ca="1" si="34">M52/$M$50</f>
-        <v>0.5</v>
+        <v>0.51282051282051277</v>
       </c>
       <c r="M52" s="110">
         <f>COUNTIF($H$7:$H$47,"B")</f>
@@ -29874,20 +30001,20 @@
       <c r="AI52" s="11"/>
     </row>
     <row r="53" spans="3:35" ht="16.5" thickBot="1">
-      <c r="C53" s="386"/>
-      <c r="D53" s="389"/>
-      <c r="E53" s="390"/>
+      <c r="C53" s="374"/>
+      <c r="D53" s="377"/>
+      <c r="E53" s="378"/>
       <c r="F53" s="71"/>
       <c r="G53" s="6"/>
-      <c r="H53" s="379" t="s">
+      <c r="H53" s="411" t="s">
         <v>68</v>
       </c>
-      <c r="I53" s="380"/>
-      <c r="J53" s="380"/>
-      <c r="K53" s="381"/>
+      <c r="I53" s="412"/>
+      <c r="J53" s="412"/>
+      <c r="K53" s="413"/>
       <c r="L53" s="111">
         <f t="shared" ca="1" si="34"/>
-        <v>0.2</v>
+        <v>0.20512820512820512</v>
       </c>
       <c r="M53" s="112">
         <f>COUNTIF($H$7:$H$47,"C")</f>
@@ -29903,11 +30030,11 @@
       </c>
       <c r="P53" s="111">
         <f t="shared" ca="1" si="35"/>
-        <v>8.1081081081081086E-2</v>
+        <v>0.13513513513513514</v>
       </c>
       <c r="Q53" s="112">
         <f>COUNTIF($Q$7:$Q$47,"C")</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R53" s="1"/>
       <c r="S53" s="1"/>
@@ -29927,19 +30054,19 @@
     <row r="54" spans="3:35">
       <c r="F54" s="72"/>
       <c r="G54" s="6"/>
-      <c r="H54" s="382" t="s">
+      <c r="H54" s="365" t="s">
         <v>70</v>
       </c>
-      <c r="I54" s="383"/>
-      <c r="J54" s="383"/>
-      <c r="K54" s="384"/>
+      <c r="I54" s="366"/>
+      <c r="J54" s="366"/>
+      <c r="K54" s="367"/>
       <c r="L54" s="114">
         <f t="shared" ca="1" si="34"/>
-        <v>0.17499999999999999</v>
+        <v>0.15384615384615385</v>
       </c>
       <c r="M54" s="115">
         <f ca="1">SUM(N54:O54)</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N54" s="98">
         <f ca="1">COUNTIFS($I$7:$I$47,"&lt;=21",$U$7:$U$47,"",$K$7:$K$47,"&lt;&gt;X")</f>
@@ -29947,15 +30074,15 @@
       </c>
       <c r="O54" s="50">
         <f ca="1">COUNTIFS($I$7:$I$47,"&gt;21",$U$7:$U$47,"",$K$7:$K$47,"&lt;&gt;X")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P54" s="114">
         <f t="shared" ca="1" si="35"/>
-        <v>0.35135135135135137</v>
+        <v>0.29729729729729731</v>
       </c>
       <c r="Q54" s="115">
         <f ca="1">COUNTIFS($I$7:$I$47,"&gt;=0",$P$7:$P$47,"",$K$7:$K$47,"&lt;&gt;X")</f>
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="R54" s="1" t="s">
         <v>10</v>
@@ -29975,20 +30102,20 @@
       <c r="AI54" s="11"/>
     </row>
     <row r="55" spans="3:35" ht="16.5" thickBot="1">
-      <c r="C55" s="372" t="s">
+      <c r="C55" s="361" t="s">
         <v>41</v>
       </c>
-      <c r="D55" s="372"/>
-      <c r="E55" s="372"/>
-      <c r="H55" s="354" t="s">
+      <c r="D55" s="361"/>
+      <c r="E55" s="361"/>
+      <c r="H55" s="368" t="s">
         <v>71</v>
       </c>
-      <c r="I55" s="355"/>
-      <c r="J55" s="355"/>
-      <c r="K55" s="356"/>
+      <c r="I55" s="369"/>
+      <c r="J55" s="369"/>
+      <c r="K55" s="370"/>
       <c r="L55" s="113">
         <f t="shared" ca="1" si="34"/>
-        <v>0.05</v>
+        <v>5.128205128205128E-2</v>
       </c>
       <c r="M55" s="97">
         <f>COUNTIFS($K$7:$K$47,"X")</f>
@@ -30030,27 +30157,6 @@
     </sortState>
   </autoFilter>
   <mergeCells count="37">
-    <mergeCell ref="P49:Q49"/>
-    <mergeCell ref="X4:Y4"/>
-    <mergeCell ref="Z4:AC4"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D49:E49"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="D51:E51"/>
-    <mergeCell ref="C55:E55"/>
-    <mergeCell ref="H51:K51"/>
-    <mergeCell ref="H52:K52"/>
-    <mergeCell ref="H49:M49"/>
-    <mergeCell ref="H53:K53"/>
-    <mergeCell ref="H54:K54"/>
-    <mergeCell ref="C52:C53"/>
-    <mergeCell ref="D52:E53"/>
-    <mergeCell ref="D50:E50"/>
     <mergeCell ref="AG5:AG6"/>
     <mergeCell ref="AH5:AH6"/>
     <mergeCell ref="AI5:AI6"/>
@@ -30067,6 +30173,27 @@
     <mergeCell ref="K4:K5"/>
     <mergeCell ref="P4:Q4"/>
     <mergeCell ref="J4:J5"/>
+    <mergeCell ref="D51:E51"/>
+    <mergeCell ref="C55:E55"/>
+    <mergeCell ref="H51:K51"/>
+    <mergeCell ref="H52:K52"/>
+    <mergeCell ref="H49:M49"/>
+    <mergeCell ref="H53:K53"/>
+    <mergeCell ref="H54:K54"/>
+    <mergeCell ref="C52:C53"/>
+    <mergeCell ref="D52:E53"/>
+    <mergeCell ref="D50:E50"/>
+    <mergeCell ref="P49:Q49"/>
+    <mergeCell ref="X4:Y4"/>
+    <mergeCell ref="Z4:AC4"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D49:E49"/>
+    <mergeCell ref="B4:B5"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="A7:AD47 AG7:AI47">
@@ -30241,9 +30368,12 @@
     <hyperlink ref="N35" r:id="rId146" xr:uid="{6B0F2654-6C47-4293-B5E0-0B9362535EF3}"/>
     <hyperlink ref="N39" r:id="rId147" xr:uid="{B3CD6A53-FDFF-4D4E-A8B5-14FD90B4C9E2}"/>
     <hyperlink ref="N37" r:id="rId148" xr:uid="{4E229929-49C0-4A6C-8225-9EBD5F9E6EEE}"/>
+    <hyperlink ref="P38" r:id="rId149" xr:uid="{91D3734C-8D09-4697-8831-21B6301767CF}"/>
+    <hyperlink ref="N31" r:id="rId150" xr:uid="{C4DD3B82-64DA-4546-88B1-E22DBB5B7042}"/>
+    <hyperlink ref="P31" r:id="rId151" xr:uid="{EABB05B7-96EF-481F-A292-B7E85DC0CCAB}"/>
   </hyperlinks>
   <pageMargins left="0.25" right="0.17" top="0.5" bottom="0.25" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="29" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId149"/>
+  <pageSetup paperSize="9" scale="29" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId152"/>
 </worksheet>
 </file>
 
@@ -30288,7 +30418,7 @@
       </c>
       <c r="I1" s="176">
         <f ca="1">TODAY()</f>
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="J1" s="131"/>
       <c r="K1" s="197"/>
@@ -30359,81 +30489,81 @@
       <c r="Z3" s="159"/>
     </row>
     <row r="4" spans="1:26" s="5" customFormat="1" ht="35.1" customHeight="1" thickBot="1">
-      <c r="A4" s="407" t="s">
+      <c r="A4" s="348" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="407" t="s">
+      <c r="B4" s="348" t="s">
         <v>515</v>
       </c>
-      <c r="C4" s="403" t="s">
+      <c r="C4" s="391" t="s">
         <v>45</v>
       </c>
-      <c r="D4" s="362" t="s">
+      <c r="D4" s="352" t="s">
         <v>46</v>
       </c>
-      <c r="E4" s="428" t="s">
+      <c r="E4" s="381" t="s">
         <v>47</v>
       </c>
-      <c r="F4" s="362" t="s">
+      <c r="F4" s="352" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="430" t="s">
+      <c r="G4" s="383" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="364" t="s">
+      <c r="H4" s="385" t="s">
         <v>48</v>
       </c>
-      <c r="I4" s="432" t="s">
+      <c r="I4" s="387" t="s">
         <v>49</v>
       </c>
-      <c r="J4" s="362" t="s">
+      <c r="J4" s="352" t="s">
         <v>78</v>
       </c>
-      <c r="K4" s="364" t="s">
+      <c r="K4" s="385" t="s">
         <v>80</v>
       </c>
-      <c r="L4" s="368" t="s">
+      <c r="L4" s="389" t="s">
         <v>53</v>
       </c>
-      <c r="M4" s="367"/>
-      <c r="N4" s="368" t="s">
+      <c r="M4" s="379"/>
+      <c r="N4" s="389" t="s">
         <v>55</v>
       </c>
-      <c r="O4" s="367"/>
-      <c r="P4" s="368" t="s">
+      <c r="O4" s="379"/>
+      <c r="P4" s="389" t="s">
         <v>72</v>
       </c>
-      <c r="Q4" s="367"/>
-      <c r="R4" s="366" t="s">
+      <c r="Q4" s="379"/>
+      <c r="R4" s="390" t="s">
         <v>53</v>
       </c>
-      <c r="S4" s="366"/>
-      <c r="T4" s="367"/>
-      <c r="U4" s="368" t="s">
+      <c r="S4" s="390"/>
+      <c r="T4" s="379"/>
+      <c r="U4" s="389" t="s">
         <v>55</v>
       </c>
-      <c r="V4" s="366"/>
-      <c r="W4" s="366"/>
+      <c r="V4" s="390"/>
+      <c r="W4" s="390"/>
       <c r="X4" s="393" t="s">
         <v>72</v>
       </c>
-      <c r="Y4" s="427"/>
-      <c r="Z4" s="367" t="s">
+      <c r="Y4" s="394"/>
+      <c r="Z4" s="379" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="72" customHeight="1">
-      <c r="A5" s="408"/>
-      <c r="B5" s="408"/>
-      <c r="C5" s="404"/>
-      <c r="D5" s="369"/>
-      <c r="E5" s="429"/>
-      <c r="F5" s="369"/>
-      <c r="G5" s="431"/>
-      <c r="H5" s="365"/>
-      <c r="I5" s="433"/>
-      <c r="J5" s="369"/>
-      <c r="K5" s="365"/>
+      <c r="A5" s="349"/>
+      <c r="B5" s="349"/>
+      <c r="C5" s="392"/>
+      <c r="D5" s="353"/>
+      <c r="E5" s="382"/>
+      <c r="F5" s="353"/>
+      <c r="G5" s="384"/>
+      <c r="H5" s="386"/>
+      <c r="I5" s="388"/>
+      <c r="J5" s="353"/>
+      <c r="K5" s="386"/>
       <c r="L5" s="79" t="s">
         <v>52</v>
       </c>
@@ -30476,7 +30606,7 @@
       <c r="Y5" s="260" t="s">
         <v>114</v>
       </c>
-      <c r="Z5" s="363"/>
+      <c r="Z5" s="380"/>
     </row>
     <row r="6" spans="1:26" ht="15" customHeight="1" thickBot="1">
       <c r="A6" s="78"/>
@@ -32840,7 +32970,7 @@
         <v>45840</v>
       </c>
       <c r="Z36" s="92" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
     </row>
     <row r="37" spans="1:26" s="9" customFormat="1" ht="47.25">
@@ -33033,11 +33163,11 @@
       <c r="H39" s="138"/>
       <c r="I39" s="164">
         <f t="shared" ca="1" si="9"/>
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="J39" s="47">
         <f t="shared" ca="1" si="10"/>
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="K39" s="164"/>
       <c r="L39" s="40"/>
@@ -33383,7 +33513,7 @@
         <v>45869</v>
       </c>
       <c r="Z43" s="188" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
     </row>
     <row r="44" spans="1:26" s="9" customFormat="1" ht="47.25">
@@ -33782,7 +33912,7 @@
         <v>45933</v>
       </c>
       <c r="Z48" s="92" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
     </row>
     <row r="49" spans="1:26" s="9" customFormat="1" ht="47.25">
@@ -34160,7 +34290,7 @@
         <v>45938</v>
       </c>
       <c r="Z53" s="92" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
     </row>
     <row r="54" spans="1:26" s="9" customFormat="1" ht="78.75">
@@ -34403,7 +34533,7 @@
         <v>45979</v>
       </c>
       <c r="Z56" s="92" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
     </row>
     <row r="57" spans="1:26" s="9" customFormat="1" ht="63">
@@ -34779,8 +34909,12 @@
       <c r="O61" s="41" t="s">
         <v>8</v>
       </c>
-      <c r="P61" s="40"/>
-      <c r="Q61" s="154"/>
+      <c r="P61" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q61" s="154" t="s">
+        <v>74</v>
+      </c>
       <c r="R61" s="27">
         <v>45958</v>
       </c>
@@ -34799,8 +34933,12 @@
       <c r="W61" s="235" t="s">
         <v>190</v>
       </c>
-      <c r="X61" s="230"/>
-      <c r="Y61" s="19"/>
+      <c r="X61" s="230">
+        <v>46248</v>
+      </c>
+      <c r="Y61" s="19">
+        <v>46311</v>
+      </c>
       <c r="Z61" s="92"/>
     </row>
     <row r="62" spans="1:26" s="9" customFormat="1" ht="47.25">
@@ -35439,11 +35577,11 @@
       </c>
       <c r="I70" s="164">
         <f t="shared" ref="I70:I78" ca="1" si="14">IF(ISBLANK($V70),_xlfn.DAYS($I$1,$T70),_xlfn.DAYS($V70,$T70))</f>
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="J70" s="47">
         <f t="shared" ref="J70:J78" ca="1" si="15">IF(($I70-21)&gt;0,$I70-21,0)</f>
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K70" s="164"/>
       <c r="L70" s="40"/>
@@ -35469,7 +35607,7 @@
       <c r="X70" s="230"/>
       <c r="Y70" s="19"/>
       <c r="Z70" s="92" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="71" spans="1:26" s="9" customFormat="1" ht="47.25">
@@ -35681,8 +35819,12 @@
       <c r="O73" s="41" t="s">
         <v>8</v>
       </c>
-      <c r="P73" s="40"/>
-      <c r="Q73" s="154"/>
+      <c r="P73" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q73" s="154" t="s">
+        <v>74</v>
+      </c>
       <c r="R73" s="27">
         <v>46178</v>
       </c>
@@ -35701,10 +35843,14 @@
       <c r="W73" s="235" t="s">
         <v>240</v>
       </c>
-      <c r="X73" s="230"/>
-      <c r="Y73" s="19"/>
+      <c r="X73" s="230">
+        <v>46204</v>
+      </c>
+      <c r="Y73" s="19">
+        <v>46206</v>
+      </c>
       <c r="Z73" s="92" t="s">
-        <v>868</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="74" spans="1:26" s="9" customFormat="1" ht="63">
@@ -36687,7 +36833,7 @@
         <v>372</v>
       </c>
       <c r="D87" s="25" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="E87" s="174">
         <f t="shared" si="23"/>
@@ -37389,19 +37535,19 @@
         <v>46217</v>
       </c>
       <c r="F97" s="31" t="s">
+        <v>895</v>
+      </c>
+      <c r="G97" s="21" t="s">
         <v>896</v>
-      </c>
-      <c r="G97" s="21" t="s">
-        <v>897</v>
       </c>
       <c r="H97" s="138"/>
       <c r="I97" s="164">
         <f t="shared" ca="1" si="24"/>
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J97" s="47">
         <f t="shared" ca="1" si="25"/>
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K97" s="164"/>
       <c r="L97" s="40" t="s">
@@ -37429,7 +37575,7 @@
       <c r="X97" s="230"/>
       <c r="Y97" s="19"/>
       <c r="Z97" s="92" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
     </row>
     <row r="98" spans="1:26" s="9" customFormat="1" ht="31.5">
@@ -38306,7 +38452,7 @@
         <v>0</v>
       </c>
       <c r="K109" s="164" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="L109" s="40" t="s">
         <v>8</v>
@@ -38343,7 +38489,7 @@
       <c r="X109" s="230"/>
       <c r="Y109" s="19"/>
       <c r="Z109" s="92" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
     </row>
     <row r="110" spans="1:26" s="9" customFormat="1" ht="94.5">
@@ -38416,7 +38562,7 @@
       <c r="X110" s="230"/>
       <c r="Y110" s="19"/>
       <c r="Z110" s="92" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
     </row>
     <row r="111" spans="1:26" s="9" customFormat="1" ht="47.25">
@@ -38489,7 +38635,7 @@
       <c r="X111" s="230"/>
       <c r="Y111" s="19"/>
       <c r="Z111" s="92" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
     </row>
     <row r="112" spans="1:26" s="9" customFormat="1" ht="47.25">
@@ -38517,11 +38663,11 @@
       <c r="H112" s="138"/>
       <c r="I112" s="164">
         <f t="shared" ca="1" si="24"/>
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="J112" s="47">
         <f t="shared" ca="1" si="25"/>
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K112" s="164" t="s">
         <v>13</v>
@@ -38551,7 +38697,7 @@
       <c r="X112" s="230"/>
       <c r="Y112" s="19"/>
       <c r="Z112" s="92" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
     </row>
     <row r="113" spans="1:26" s="9" customFormat="1" ht="78.75">
@@ -38584,11 +38730,11 @@
       </c>
       <c r="I113" s="164">
         <f t="shared" ca="1" si="24"/>
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J113" s="47">
         <f t="shared" ca="1" si="25"/>
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K113" s="164"/>
       <c r="L113" s="40" t="s">
@@ -38618,7 +38764,7 @@
       <c r="X113" s="230"/>
       <c r="Y113" s="19"/>
       <c r="Z113" s="92" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="114" spans="1:26" s="9" customFormat="1" ht="63">
@@ -38634,7 +38780,7 @@
         <v>621</v>
       </c>
       <c r="D114" s="25" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="E114" s="174">
         <f t="shared" si="23"/>
@@ -38644,7 +38790,7 @@
         <v>675</v>
       </c>
       <c r="G114" s="21" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="H114" s="138" t="s">
         <v>6</v>
@@ -38705,26 +38851,26 @@
         <v>621</v>
       </c>
       <c r="D115" s="25" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="E115" s="174">
         <f t="shared" si="23"/>
         <v>46266</v>
       </c>
       <c r="F115" s="31" t="s">
+        <v>904</v>
+      </c>
+      <c r="G115" s="21" t="s">
         <v>905</v>
-      </c>
-      <c r="G115" s="21" t="s">
-        <v>906</v>
       </c>
       <c r="H115" s="138"/>
       <c r="I115" s="164">
         <f t="shared" ca="1" si="24"/>
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J115" s="47">
         <f t="shared" ca="1" si="25"/>
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K115" s="164"/>
       <c r="L115" s="40" t="s">
@@ -38750,7 +38896,7 @@
       <c r="X115" s="230"/>
       <c r="Y115" s="19"/>
       <c r="Z115" s="92" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
     </row>
     <row r="116" spans="1:26" s="9" customFormat="1" ht="63">
@@ -38773,10 +38919,10 @@
         <v>46220</v>
       </c>
       <c r="F116" s="31" t="s">
+        <v>906</v>
+      </c>
+      <c r="G116" s="21" t="s">
         <v>907</v>
-      </c>
-      <c r="G116" s="21" t="s">
-        <v>908</v>
       </c>
       <c r="H116" s="138" t="s">
         <v>6</v>
@@ -38832,20 +38978,20 @@
         <v>5.10</v>
       </c>
       <c r="C117" s="164" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="D117" s="25" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="E117" s="174">
         <f t="shared" si="23"/>
         <v>46234</v>
       </c>
       <c r="F117" s="31" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="G117" s="21" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="H117" s="138" t="s">
         <v>6</v>
@@ -38890,7 +39036,7 @@
       <c r="X117" s="230"/>
       <c r="Y117" s="19"/>
       <c r="Z117" s="92" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="118" spans="1:26" s="9" customFormat="1" ht="94.5">
@@ -38906,17 +39052,17 @@
         <v>144</v>
       </c>
       <c r="D118" s="25" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="E118" s="174">
         <f t="shared" si="23"/>
         <v>46237</v>
       </c>
       <c r="F118" s="31" t="s">
+        <v>931</v>
+      </c>
+      <c r="G118" s="21" t="s">
         <v>932</v>
-      </c>
-      <c r="G118" s="21" t="s">
-        <v>933</v>
       </c>
       <c r="H118" s="138"/>
       <c r="I118" s="164"/>
@@ -38947,7 +39093,7 @@
       <c r="X118" s="230"/>
       <c r="Y118" s="19"/>
       <c r="Z118" s="92" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
     </row>
     <row r="119" spans="1:26" s="9" customFormat="1" ht="63">
@@ -38963,17 +39109,17 @@
         <v>131</v>
       </c>
       <c r="D119" s="25" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="E119" s="174">
         <f t="shared" si="23"/>
         <v>46239</v>
       </c>
       <c r="F119" s="31" t="s">
+        <v>939</v>
+      </c>
+      <c r="G119" s="21" t="s">
         <v>940</v>
-      </c>
-      <c r="G119" s="21" t="s">
-        <v>941</v>
       </c>
       <c r="H119" s="138" t="s">
         <v>6</v>
@@ -38995,8 +39141,12 @@
         <v>8</v>
       </c>
       <c r="O119" s="41"/>
-      <c r="P119" s="40"/>
-      <c r="Q119" s="154"/>
+      <c r="P119" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q119" s="154" t="s">
+        <v>74</v>
+      </c>
       <c r="R119" s="27">
         <v>46218</v>
       </c>
@@ -39015,10 +39165,14 @@
       <c r="W119" s="235" t="s">
         <v>240</v>
       </c>
-      <c r="X119" s="230"/>
-      <c r="Y119" s="19"/>
+      <c r="X119" s="230">
+        <v>46247</v>
+      </c>
+      <c r="Y119" s="19">
+        <v>46248</v>
+      </c>
       <c r="Z119" s="92" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="120" spans="1:26" s="9" customFormat="1" ht="110.25">
@@ -39031,7 +39185,7 @@
         <v>5.11</v>
       </c>
       <c r="C120" s="164" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="D120" s="25" t="s">
         <v>686</v>
@@ -39041,10 +39195,10 @@
         <v>46248</v>
       </c>
       <c r="F120" s="31" t="s">
+        <v>941</v>
+      </c>
+      <c r="G120" s="21" t="s">
         <v>942</v>
-      </c>
-      <c r="G120" s="21" t="s">
-        <v>943</v>
       </c>
       <c r="H120" s="138" t="s">
         <v>6</v>
@@ -39089,7 +39243,7 @@
       <c r="X120" s="230"/>
       <c r="Y120" s="19"/>
       <c r="Z120" s="92" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="121" spans="1:26" s="9" customFormat="1" ht="141.75">
@@ -39105,17 +39259,17 @@
         <v>656</v>
       </c>
       <c r="D121" s="25" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="E121" s="174">
         <f t="shared" si="23"/>
         <v>46265</v>
       </c>
       <c r="F121" s="31" t="s">
+        <v>949</v>
+      </c>
+      <c r="G121" s="21" t="s">
         <v>950</v>
-      </c>
-      <c r="G121" s="21" t="s">
-        <v>951</v>
       </c>
       <c r="H121" s="138" t="s">
         <v>6</v>
@@ -39137,8 +39291,12 @@
         <v>8</v>
       </c>
       <c r="O121" s="41"/>
-      <c r="P121" s="40"/>
-      <c r="Q121" s="154"/>
+      <c r="P121" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q121" s="154" t="s">
+        <v>74</v>
+      </c>
       <c r="R121" s="27">
         <v>46244</v>
       </c>
@@ -39155,12 +39313,12 @@
         <v>46274</v>
       </c>
       <c r="W121" s="235" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="X121" s="230"/>
       <c r="Y121" s="19"/>
       <c r="Z121" s="92" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="122" spans="1:26" s="9" customFormat="1" ht="31.5">
@@ -39174,17 +39332,17 @@
       </c>
       <c r="C122" s="164"/>
       <c r="D122" s="25" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="E122" s="174">
         <f t="shared" si="23"/>
         <v>46267</v>
       </c>
       <c r="F122" s="31" t="s">
+        <v>954</v>
+      </c>
+      <c r="G122" s="21" t="s">
         <v>955</v>
-      </c>
-      <c r="G122" s="21" t="s">
-        <v>956</v>
       </c>
       <c r="H122" s="138" t="s">
         <v>6</v>
@@ -39229,7 +39387,7 @@
       <c r="X122" s="230"/>
       <c r="Y122" s="19"/>
       <c r="Z122" s="92" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="123" spans="1:26" s="9" customFormat="1" ht="47.25">
@@ -39245,17 +39403,17 @@
         <v>131</v>
       </c>
       <c r="D123" s="25" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="E123" s="174">
         <f t="shared" si="23"/>
         <v>46280</v>
       </c>
       <c r="F123" s="31" t="s">
+        <v>970</v>
+      </c>
+      <c r="G123" s="21" t="s">
         <v>971</v>
-      </c>
-      <c r="G123" s="21" t="s">
-        <v>972</v>
       </c>
       <c r="H123" s="138"/>
       <c r="I123" s="164"/>
@@ -39302,17 +39460,17 @@
         <v>131</v>
       </c>
       <c r="D124" s="25" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="E124" s="174">
         <f t="shared" si="23"/>
         <v>46314</v>
       </c>
       <c r="F124" s="31" t="s">
+        <v>970</v>
+      </c>
+      <c r="G124" s="21" t="s">
         <v>971</v>
-      </c>
-      <c r="G124" s="21" t="s">
-        <v>972</v>
       </c>
       <c r="H124" s="138" t="s">
         <v>6</v>
@@ -39357,7 +39515,7 @@
       <c r="X124" s="230"/>
       <c r="Y124" s="19"/>
       <c r="Z124" s="92" t="s">
-        <v>1031</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="125" spans="1:26" s="9" customFormat="1" ht="63">
@@ -39373,17 +39531,17 @@
         <v>131</v>
       </c>
       <c r="D125" s="25" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="E125" s="174">
         <f t="shared" si="23"/>
         <v>46316</v>
       </c>
       <c r="F125" s="31" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="G125" s="21" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="H125" s="138" t="s">
         <v>6</v>
@@ -39428,7 +39586,7 @@
       <c r="X125" s="230"/>
       <c r="Y125" s="19"/>
       <c r="Z125" s="92" t="s">
-        <v>1068</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="126" spans="1:26" s="9" customFormat="1" ht="78.75">
@@ -39444,17 +39602,17 @@
         <v>621</v>
       </c>
       <c r="D126" s="25" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="E126" s="174">
         <f t="shared" si="23"/>
         <v>46323</v>
       </c>
       <c r="F126" s="31" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
       <c r="G126" s="21" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="H126" s="138" t="s">
         <v>6</v>
@@ -39499,7 +39657,7 @@
       <c r="X126" s="230"/>
       <c r="Y126" s="19"/>
       <c r="Z126" s="92" t="s">
-        <v>1070</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="127" spans="1:26" s="9" customFormat="1" ht="47.25">
@@ -39513,17 +39671,17 @@
       </c>
       <c r="C127" s="164"/>
       <c r="D127" s="25" t="s">
-        <v>1056</v>
+        <v>1053</v>
       </c>
       <c r="E127" s="174">
         <f t="shared" si="23"/>
         <v>46325</v>
       </c>
       <c r="F127" s="31" t="s">
-        <v>1057</v>
+        <v>1054</v>
       </c>
       <c r="G127" s="21" t="s">
-        <v>1058</v>
+        <v>1055</v>
       </c>
       <c r="H127" s="138" t="s">
         <v>6</v>
@@ -39568,7 +39726,7 @@
       <c r="X127" s="230"/>
       <c r="Y127" s="19"/>
       <c r="Z127" s="92" t="s">
-        <v>1099</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="128" spans="1:26" s="9" customFormat="1" ht="47.25">
@@ -39584,17 +39742,17 @@
         <v>621</v>
       </c>
       <c r="D128" s="25" t="s">
-        <v>1064</v>
+        <v>1060</v>
       </c>
       <c r="E128" s="174">
         <f t="shared" si="23"/>
         <v>46330</v>
       </c>
       <c r="F128" s="31" t="s">
-        <v>1065</v>
+        <v>1061</v>
       </c>
       <c r="G128" s="21" t="s">
-        <v>1066</v>
+        <v>1062</v>
       </c>
       <c r="H128" s="138" t="s">
         <v>6</v>
@@ -39639,7 +39797,7 @@
       <c r="X128" s="230"/>
       <c r="Y128" s="19"/>
       <c r="Z128" s="92" t="s">
-        <v>1100</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="129" spans="1:26" s="9" customFormat="1" ht="63">
@@ -39655,22 +39813,22 @@
         <v>195</v>
       </c>
       <c r="D129" s="25" t="s">
-        <v>1089</v>
+        <v>1085</v>
       </c>
       <c r="E129" s="174">
         <f t="shared" si="23"/>
         <v>46332</v>
       </c>
       <c r="F129" s="31" t="s">
-        <v>1090</v>
+        <v>1086</v>
       </c>
       <c r="G129" s="21" t="s">
-        <v>1091</v>
+        <v>1087</v>
       </c>
       <c r="H129" s="138"/>
       <c r="I129" s="164">
         <f t="shared" ca="1" si="24"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J129" s="47">
         <f t="shared" ca="1" si="25"/>
@@ -39712,17 +39870,17 @@
       </c>
       <c r="C130" s="164"/>
       <c r="D130" s="25" t="s">
-        <v>1111</v>
+        <v>1106</v>
       </c>
       <c r="E130" s="174">
         <f t="shared" si="23"/>
         <v>46314</v>
       </c>
       <c r="F130" s="31" t="s">
-        <v>1112</v>
+        <v>1107</v>
       </c>
       <c r="G130" s="21" t="s">
-        <v>1113</v>
+        <v>1108</v>
       </c>
       <c r="H130" s="138" t="s">
         <v>6</v>
@@ -39762,12 +39920,12 @@
         <v>46317</v>
       </c>
       <c r="W130" s="235" t="s">
-        <v>1114</v>
+        <v>1109</v>
       </c>
       <c r="X130" s="230"/>
       <c r="Y130" s="19"/>
       <c r="Z130" s="92" t="s">
-        <v>1115</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="131" spans="1:26" s="9" customFormat="1">
@@ -39831,28 +39989,28 @@
       <c r="C134" s="207" t="s">
         <v>38</v>
       </c>
-      <c r="D134" s="441" t="s">
+      <c r="D134" s="354" t="s">
         <v>39</v>
       </c>
-      <c r="E134" s="442"/>
+      <c r="E134" s="355"/>
       <c r="F134" s="46"/>
       <c r="G134" s="68"/>
-      <c r="H134" s="357" t="s">
+      <c r="H134" s="356" t="s">
         <v>14</v>
       </c>
-      <c r="I134" s="358"/>
-      <c r="J134" s="358"/>
-      <c r="K134" s="358"/>
-      <c r="L134" s="358"/>
-      <c r="M134" s="359"/>
-      <c r="N134" s="360" t="s">
+      <c r="I134" s="357"/>
+      <c r="J134" s="357"/>
+      <c r="K134" s="357"/>
+      <c r="L134" s="357"/>
+      <c r="M134" s="358"/>
+      <c r="N134" s="350" t="s">
         <v>7</v>
       </c>
-      <c r="O134" s="361"/>
-      <c r="P134" s="360" t="s">
+      <c r="O134" s="351"/>
+      <c r="P134" s="350" t="s">
         <v>110</v>
       </c>
-      <c r="Q134" s="361"/>
+      <c r="Q134" s="351"/>
       <c r="R134" s="1"/>
       <c r="S134" s="1"/>
       <c r="T134" s="140"/>
@@ -39865,16 +40023,16 @@
       <c r="C135" s="208" t="s">
         <v>74</v>
       </c>
-      <c r="D135" s="439" t="s">
+      <c r="D135" s="371" t="s">
         <v>77</v>
       </c>
-      <c r="E135" s="440"/>
+      <c r="E135" s="372"/>
       <c r="F135" s="46"/>
       <c r="G135" s="46"/>
-      <c r="H135" s="434" t="s">
+      <c r="H135" s="359" t="s">
         <v>17</v>
       </c>
-      <c r="I135" s="435"/>
+      <c r="I135" s="360"/>
       <c r="J135" s="130"/>
       <c r="K135" s="210"/>
       <c r="L135" s="117">
@@ -39908,21 +40066,21 @@
       <c r="Y135" s="11"/>
     </row>
     <row r="136" spans="1:26">
-      <c r="C136" s="385" t="s">
+      <c r="C136" s="373" t="s">
         <v>6</v>
       </c>
-      <c r="D136" s="439" t="s">
+      <c r="D136" s="371" t="s">
         <v>40</v>
       </c>
-      <c r="E136" s="440"/>
+      <c r="E136" s="372"/>
       <c r="F136" s="69"/>
       <c r="G136" s="6"/>
-      <c r="H136" s="436" t="s">
+      <c r="H136" s="362" t="s">
         <v>69</v>
       </c>
-      <c r="I136" s="437"/>
-      <c r="J136" s="437"/>
-      <c r="K136" s="438"/>
+      <c r="I136" s="363"/>
+      <c r="J136" s="363"/>
+      <c r="K136" s="364"/>
       <c r="L136" s="122">
         <f t="shared" ref="L136:L138" ca="1" si="62">M136/$M$135</f>
         <v>0.84375</v>
@@ -39941,11 +40099,11 @@
       </c>
       <c r="P136" s="122">
         <f ca="1">Q136/$Q$135</f>
-        <v>0.61818181818181817</v>
+        <v>0.65454545454545454</v>
       </c>
       <c r="Q136" s="123">
         <f>COUNTIF($Q$7:$Q$132,"RBE") + COUNTIF($Q$7:$Q$132,"SUP")</f>
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="R136" s="1"/>
       <c r="S136" s="1"/>
@@ -39956,17 +40114,17 @@
       <c r="Y136" s="11"/>
     </row>
     <row r="137" spans="1:26">
-      <c r="C137" s="385"/>
-      <c r="D137" s="439"/>
-      <c r="E137" s="440"/>
+      <c r="C137" s="373"/>
+      <c r="D137" s="371"/>
+      <c r="E137" s="372"/>
       <c r="F137" s="72"/>
       <c r="G137" s="6"/>
-      <c r="H137" s="382" t="s">
+      <c r="H137" s="365" t="s">
         <v>70</v>
       </c>
-      <c r="I137" s="383"/>
-      <c r="J137" s="383"/>
-      <c r="K137" s="384"/>
+      <c r="I137" s="366"/>
+      <c r="J137" s="366"/>
+      <c r="K137" s="367"/>
       <c r="L137" s="124">
         <f t="shared" ca="1" si="62"/>
         <v>4.6875E-2</v>
@@ -39985,11 +40143,11 @@
       </c>
       <c r="P137" s="124">
         <f ca="1">Q137/$Q$135</f>
-        <v>0.38181818181818183</v>
+        <v>0.34545454545454546</v>
       </c>
       <c r="Q137" s="125">
         <f ca="1">COUNTIFS($I$7:$I$132,"&gt;=0",$P$7:$P$132,"",$K$7:$K$132,"&lt;&gt;X")</f>
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="R137" s="1" t="s">
         <v>10</v>
@@ -40002,19 +40160,19 @@
       <c r="Y137" s="11"/>
     </row>
     <row r="138" spans="1:26" ht="16.5" thickBot="1">
-      <c r="C138" s="385" t="s">
+      <c r="C138" s="373" t="s">
         <v>75</v>
       </c>
-      <c r="D138" s="387" t="s">
+      <c r="D138" s="375" t="s">
         <v>76</v>
       </c>
-      <c r="E138" s="388"/>
-      <c r="H138" s="354" t="s">
+      <c r="E138" s="376"/>
+      <c r="H138" s="368" t="s">
         <v>71</v>
       </c>
-      <c r="I138" s="355"/>
-      <c r="J138" s="355"/>
-      <c r="K138" s="356"/>
+      <c r="I138" s="369"/>
+      <c r="J138" s="369"/>
+      <c r="K138" s="370"/>
       <c r="L138" s="126">
         <f t="shared" ca="1" si="62"/>
         <v>0.109375</v>
@@ -40029,16 +40187,16 @@
       <c r="Q138" s="224"/>
     </row>
     <row r="139" spans="1:26" ht="16.5" thickBot="1">
-      <c r="C139" s="386"/>
-      <c r="D139" s="389"/>
-      <c r="E139" s="390"/>
+      <c r="C139" s="374"/>
+      <c r="D139" s="377"/>
+      <c r="E139" s="378"/>
     </row>
     <row r="141" spans="1:26">
-      <c r="C141" s="372" t="s">
+      <c r="C141" s="361" t="s">
         <v>41</v>
       </c>
-      <c r="D141" s="372"/>
-      <c r="E141" s="372"/>
+      <c r="D141" s="361"/>
+      <c r="E141" s="361"/>
     </row>
     <row r="142" spans="1:26">
       <c r="C142" s="169" t="s">
@@ -40065,28 +40223,12 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A6:Z127" xr:uid="{C184EF3E-84BF-4DCF-951B-B90EB4B9D23F}">
+  <autoFilter ref="A6:Z130" xr:uid="{C184EF3E-84BF-4DCF-951B-B90EB4B9D23F}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A7:Z32">
       <sortCondition ref="S6"/>
     </sortState>
   </autoFilter>
   <mergeCells count="32">
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="P134:Q134"/>
-    <mergeCell ref="J4:J5"/>
-    <mergeCell ref="D134:E134"/>
-    <mergeCell ref="H134:M134"/>
-    <mergeCell ref="N134:O134"/>
-    <mergeCell ref="H135:I135"/>
-    <mergeCell ref="C141:E141"/>
-    <mergeCell ref="H136:K136"/>
-    <mergeCell ref="H137:K137"/>
-    <mergeCell ref="H138:K138"/>
-    <mergeCell ref="D135:E135"/>
-    <mergeCell ref="C136:C137"/>
-    <mergeCell ref="D136:E137"/>
-    <mergeCell ref="C138:C139"/>
-    <mergeCell ref="D138:E139"/>
     <mergeCell ref="Z4:Z5"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="D4:D5"/>
@@ -40103,6 +40245,22 @@
     <mergeCell ref="K4:K5"/>
     <mergeCell ref="P4:Q4"/>
     <mergeCell ref="X4:Y4"/>
+    <mergeCell ref="H135:I135"/>
+    <mergeCell ref="C141:E141"/>
+    <mergeCell ref="H136:K136"/>
+    <mergeCell ref="H137:K137"/>
+    <mergeCell ref="H138:K138"/>
+    <mergeCell ref="D135:E135"/>
+    <mergeCell ref="C136:C137"/>
+    <mergeCell ref="D136:E137"/>
+    <mergeCell ref="C138:C139"/>
+    <mergeCell ref="D138:E139"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="P134:Q134"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="D134:E134"/>
+    <mergeCell ref="H134:M134"/>
+    <mergeCell ref="N134:O134"/>
   </mergeCells>
   <phoneticPr fontId="71"/>
   <conditionalFormatting sqref="A7:Z132">
@@ -40606,15 +40764,19 @@
     <hyperlink ref="N128" r:id="rId481" xr:uid="{1CA6C02A-5CE8-4BB3-A561-833347DA6DD6}"/>
     <hyperlink ref="L130" r:id="rId482" xr:uid="{7D960168-2434-4940-BEFA-A280CD48B60C}"/>
     <hyperlink ref="N130" r:id="rId483" xr:uid="{B567A3B4-9E9F-477C-ACA4-EAD1E0777B05}"/>
+    <hyperlink ref="P121" r:id="rId484" xr:uid="{932A0C4D-563A-4ED3-99EE-72591862CEBC}"/>
+    <hyperlink ref="P61" r:id="rId485" xr:uid="{B7476E13-5509-4F98-A368-0F0149FCE838}"/>
+    <hyperlink ref="P73" r:id="rId486" xr:uid="{6610F5FD-75DB-40B9-A6E0-491FAB724084}"/>
+    <hyperlink ref="P119" r:id="rId487" xr:uid="{2F121870-B035-4D11-8EFC-0663ECEC1B47}"/>
   </hyperlinks>
   <pageMargins left="0.25" right="0.17" top="0.5" bottom="0.25" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="28" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId484"/>
+  <pageSetup paperSize="9" scale="28" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId488"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75733AF3-96C4-423A-BD99-1E08B3C66916}">
-  <dimension ref="A1:Y26"/>
+  <dimension ref="A1:Y30"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="13" customWidth="1"/>
@@ -40693,19 +40855,19 @@
       <c r="S3" s="281"/>
     </row>
     <row r="4" spans="1:25" ht="36" customHeight="1" thickBot="1">
-      <c r="A4" s="397" t="s">
+      <c r="A4" s="426" t="s">
         <v>123</v>
       </c>
-      <c r="B4" s="364" t="s">
+      <c r="B4" s="385" t="s">
         <v>45</v>
       </c>
-      <c r="C4" s="364" t="s">
+      <c r="C4" s="385" t="s">
         <v>95</v>
       </c>
-      <c r="D4" s="364" t="s">
+      <c r="D4" s="385" t="s">
         <v>46</v>
       </c>
-      <c r="E4" s="362" t="s">
+      <c r="E4" s="352" t="s">
         <v>4</v>
       </c>
       <c r="F4" s="449" t="s">
@@ -40734,12 +40896,12 @@
       <c r="S4" s="448"/>
     </row>
     <row r="5" spans="1:25" ht="78.75">
-      <c r="A5" s="398"/>
-      <c r="B5" s="365"/>
-      <c r="C5" s="365"/>
-      <c r="D5" s="365"/>
-      <c r="E5" s="369"/>
-      <c r="F5" s="402"/>
+      <c r="A5" s="427"/>
+      <c r="B5" s="386"/>
+      <c r="C5" s="386"/>
+      <c r="D5" s="386"/>
+      <c r="E5" s="353"/>
+      <c r="F5" s="429"/>
       <c r="G5" s="283" t="s">
         <v>56</v>
       </c>
@@ -40803,131 +40965,131 @@
     </row>
     <row r="7" spans="1:25" ht="45">
       <c r="A7" s="13" cm="1">
-        <f t="array" ref="A7:A26">IF(_xlfn.ANCHORARRAY(D7)="","",_xlfn.SEQUENCE(ROWS(_xlfn.ANCHORARRAY(D7))))</f>
+        <f t="array" ref="A7:A30">IF(_xlfn.ANCHORARRAY(D7)="","",_xlfn.SEQUENCE(ROWS(_xlfn.ANCHORARRAY(D7))))</f>
         <v>1</v>
       </c>
       <c r="B7" s="302" t="str" cm="1">
-        <f t="array" ref="B7:B26">_xlfn.LET(
+        <f t="array" ref="B7:B30">_xlfn.LET(
 _xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(D7),RFA!$E:$E,RFA!$C:$C,""),
 IF(_xlpm.x=0,"",_xlpm.x)
 )</f>
         <v>FAS</v>
       </c>
       <c r="C7" s="13" t="str" cm="1">
-        <f t="array" ref="C7:C26">_xlfn.LET(
+        <f t="array" ref="C7:C30">_xlfn.LET(
 _xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(D7),RFA!$E:$E,RFA!$D:$D,""),
 IF(_xlpm.x=0,"",_xlpm.x)
 )</f>
         <v>MAS</v>
       </c>
       <c r="D7" s="282" t="str" cm="1">
-        <f t="array" ref="D7:D26">_xlfn._xlws.FILTER(RFA!$E$5:$E$4578, RFA!$AI$5:$AI$4578="YES","")</f>
+        <f t="array" ref="D7:D30">_xlfn._xlws.FILTER(RFA!$E$5:$E$4578, RFA!$AI$5:$AI$4578="YES","")</f>
         <v>LTIA-5.10-VIETUR-70000-RFA-MAS-0088A</v>
       </c>
       <c r="E7" s="303" t="str" cm="1">
-        <f t="array" ref="E7:E26">_xlfn.LET(
+        <f t="array" ref="E7:E30">_xlfn.LET(
 _xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(D7),RFA!$E:$E,RFA!$G:$G,""),
 IF(_xlpm.x=0,"",_xlpm.x)
 )</f>
         <v>Request for approval material cable fire resistant shield for fire alarm system (Belden)</v>
       </c>
       <c r="F7" s="303" t="str" cm="1">
-        <f t="array" ref="F7:F26">_xlfn.LET(
+        <f t="array" ref="F7:F30">_xlfn.LET(
 _xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(D7),RFA!$E:$E,RFA!$H:$H,""),
 IF(_xlpm.x=0,"",_xlpm.x)
 )</f>
         <v>Đề nghị phê duyệt vật liệu cáp chống cháy cho hệ thống báo cháy (Belden)</v>
       </c>
       <c r="G7" s="270" cm="1">
-        <f t="array" ref="G7:G26">_xlfn.LET(
+        <f t="array" ref="G7:G30">_xlfn.LET(
 _xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(D7),RFA!$E:$E,RFA!$S:$S,""),
 IF(_xlpm.x=0,"",_xlpm.x)
 )</f>
         <v>45426</v>
       </c>
       <c r="H7" s="270" cm="1">
-        <f t="array" ref="H7:H26">_xlfn.LET(
+        <f t="array" ref="H7:H30">_xlfn.LET(
 _xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(D7),RFA!$E:$E,RFA!$T:$T,""),
 IF(_xlpm.x=0,"",_xlpm.x)
 )</f>
         <v>45426</v>
       </c>
       <c r="I7" s="264" cm="1">
-        <f t="array" ref="I7:I26">_xlfn.LET(
+        <f t="array" ref="I7:I30">_xlfn.LET(
 _xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(D7),RFA!$E:$E,RFA!$U:$U,""),
 IF(_xlpm.x=0,"",_xlpm.x)
 )</f>
         <v>45426</v>
       </c>
       <c r="J7" s="264" t="str" cm="1">
-        <f t="array" ref="J7:J26">_xlfn.LET(
+        <f t="array" ref="J7:J30">_xlfn.LET(
 _xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(D7),RFA!$E:$E,RFA!$I:$I,""),
 IF(_xlpm.x=0,"",_xlpm.x)
 )</f>
         <v>C</v>
       </c>
       <c r="K7" s="270" cm="1">
-        <f t="array" ref="K7:K26">_xlfn.LET(
+        <f t="array" ref="K7:K30">_xlfn.LET(
 _xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(D7),RFA!$E:$E,RFA!$V:$V,""),
 IF(_xlpm.x=0,"",_xlpm.x)
 )</f>
         <v>45454</v>
       </c>
       <c r="L7" s="264" cm="1">
-        <f t="array" ref="L7:L26">_xlfn.LET(
+        <f t="array" ref="L7:L30">_xlfn.LET(
 _xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(D7),RFA!$E:$E,RFA!$W:$W,""),
 IF(_xlpm.x=0,"",_xlpm.x)
 )</f>
         <v>45455</v>
       </c>
       <c r="M7" s="264" t="str" cm="1">
-        <f t="array" ref="M7:M26">_xlfn.LET(
+        <f t="array" ref="M7:M30">_xlfn.LET(
 _xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(D7),RFA!$E:$E,RFA!$R:$R,""),
 IF(_xlpm.x=0,"",_xlpm.x)
 )</f>
         <v>C</v>
       </c>
       <c r="N7" s="270" cm="1">
-        <f t="array" ref="N7:N26">_xlfn.LET(
+        <f t="array" ref="N7:N30">_xlfn.LET(
 _xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(D7),RFA!$E:$E,RFA!$Y:$Y,""),
 IF(_xlpm.x=0,"",_xlpm.x)
 )</f>
         <v>45456</v>
       </c>
       <c r="O7" s="264" cm="1">
-        <f t="array" ref="O7:O26">_xlfn.LET(
+        <f t="array" ref="O7:O30">_xlfn.LET(
 _xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(D7),RFA!$E:$E,RFA!$Z:$Z,""),
 IF(_xlpm.x=0,"",_xlpm.x)
 )</f>
         <v>45456</v>
       </c>
       <c r="P7" s="264" cm="1">
-        <f t="array" ref="P7:P26">_xlfn.LET(
+        <f t="array" ref="P7:P30">_xlfn.LET(
 _xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(D7),RFA!$E:$E,RFA!$AA:$AA,""),
 IF(_xlpm.x=0,"",_xlpm.x)
 )</f>
         <v>45463</v>
       </c>
       <c r="Q7" s="270" t="str" cm="1">
-        <f t="array" ref="Q7:Q26">_xlfn.LET(
+        <f t="array" ref="Q7:Q30">_xlfn.LET(
 _xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(D7),RFA!$E:$E,RFA!$AB:$AB,""),
 IF(_xlpm.x=0,"",_xlpm.x)
 )</f>
         <v/>
       </c>
       <c r="R7" s="13" t="str" cm="1">
-        <f t="array" ref="R7:R26">_xlfn.LET(
+        <f t="array" ref="R7:R30">_xlfn.LET(
 _xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(D7),RFA!$E:$E,RFA!$AC:$AC,""),
 IF(_xlpm.x=0,"",_xlpm.x)
 )</f>
         <v>Not submit yet</v>
       </c>
       <c r="S7" s="279" cm="1">
-        <f t="array" ref="S7:S26">_xlfn.LET(
+        <f t="array" ref="S7:S30">_xlfn.LET(
 _xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(D7),RFA!$E:$E,RFA!$AD:$AD,""),
 IF(_xlpm.x=0,"",_xlpm.x)
 )</f>
-        <v>853</v>
+        <v>855</v>
       </c>
     </row>
     <row r="8" spans="1:25" ht="45">
@@ -40986,7 +41148,7 @@
         <v>Not submit yet</v>
       </c>
       <c r="S8" s="279">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="Y8" t="s">
         <v>125</v>
@@ -41049,7 +41211,7 @@
         <v>Not submit yet</v>
       </c>
       <c r="S9" s="279">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="10" spans="1:25" ht="45">
@@ -41108,7 +41270,7 @@
         <v>Not submit yet</v>
       </c>
       <c r="S10" s="279">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="11" spans="1:25" ht="75">
@@ -41167,7 +41329,7 @@
         <v>Not submit yet</v>
       </c>
       <c r="S11" s="279">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="12" spans="1:25" ht="45">
@@ -41226,7 +41388,7 @@
         <v>Not submit yet</v>
       </c>
       <c r="S12" s="279">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="13" spans="1:25" ht="45">
@@ -41234,58 +41396,58 @@
         <v>7</v>
       </c>
       <c r="B13" s="302" t="str">
-        <v>SCS</v>
+        <v>FAS</v>
       </c>
       <c r="C13" s="13" t="str">
         <v>MAS</v>
       </c>
       <c r="D13" s="282" t="str">
-        <v>LTIA-5.10-VIETUR-70000-RFA-MAS-0706</v>
+        <v>LTIA-5.10-VIETUR-70000-RFA-MAS-0696</v>
       </c>
       <c r="E13" s="303" t="str">
-        <v>Request for approval of Floor-Mounted data outlets for Raised Floor Area</v>
+        <v>Request for approval Fire Alarm System (FAS) – Workstation.</v>
       </c>
       <c r="F13" s="303" t="str">
-        <v>Đề nghị phê duyệt Ổ cắm dữ liệu âm sàn cho khu vực sàn nâng</v>
+        <v>Đề nghị phê duyệt vật tư hệ thống báo cháy – Máy Trạm.</v>
       </c>
       <c r="G13" s="270">
-        <v>45960</v>
+        <v>45951</v>
       </c>
       <c r="H13" s="270">
-        <v>45960</v>
+        <v>45951</v>
       </c>
       <c r="I13" s="264">
-        <v>45960</v>
+        <v>46031</v>
       </c>
       <c r="J13" s="264" t="str">
         <v>A</v>
       </c>
       <c r="K13" s="270">
-        <v>45973</v>
+        <v>45965</v>
       </c>
       <c r="L13" s="264">
-        <v>45985</v>
+        <v>46032</v>
       </c>
       <c r="M13" s="264" t="str">
         <v>C</v>
       </c>
       <c r="N13" s="270">
-        <v>45999</v>
+        <v>46084</v>
       </c>
       <c r="O13" s="264">
-        <v>46000</v>
+        <v>46085</v>
       </c>
       <c r="P13" s="264">
-        <v>46007</v>
-      </c>
-      <c r="Q13" s="270" t="str">
-        <v/>
+        <v>46092</v>
+      </c>
+      <c r="Q13" s="270">
+        <v>46295</v>
       </c>
       <c r="R13" s="13" t="str">
-        <v>Not submit yet</v>
+        <v>Late Resubmission</v>
       </c>
       <c r="S13" s="279">
-        <v>309</v>
+        <v>203</v>
       </c>
     </row>
     <row r="14" spans="1:25" ht="45">
@@ -41296,46 +41458,46 @@
         <v>SCS</v>
       </c>
       <c r="C14" s="13" t="str">
-        <v>OTH</v>
+        <v>MAS</v>
       </c>
       <c r="D14" s="282" t="str">
-        <v>LTIA-5.10-VIETUR-70000-RFA-OTH-0654</v>
+        <v>LTIA-5.10-VIETUR-70000-RFA-MAS-0706</v>
       </c>
       <c r="E14" s="303" t="str">
-        <v>Request for approval for Measurement Equipment of ICT cable - ELV System</v>
+        <v>Request for approval of Floor-Mounted data outlets for Raised Floor Area</v>
       </c>
       <c r="F14" s="303" t="str">
-        <v>Đề nghị phê duyệt Thiết bị đo cáp điện nhẹ - Hệ thống điện nhẹ</v>
+        <v>Đề nghị phê duyệt Ổ cắm dữ liệu âm sàn cho khu vực sàn nâng</v>
       </c>
       <c r="G14" s="270">
-        <v>46009</v>
+        <v>45960</v>
       </c>
       <c r="H14" s="270">
-        <v>46009</v>
+        <v>45960</v>
       </c>
       <c r="I14" s="264">
-        <v>46009</v>
+        <v>45960</v>
       </c>
       <c r="J14" s="264" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="K14" s="270">
-        <v>46022</v>
+        <v>45973</v>
       </c>
       <c r="L14" s="264">
-        <v>46043</v>
+        <v>45985</v>
       </c>
       <c r="M14" s="264" t="str">
         <v>C</v>
       </c>
       <c r="N14" s="270">
-        <v>46162</v>
-      </c>
-      <c r="O14" s="264" t="str">
-        <v/>
+        <v>45999</v>
+      </c>
+      <c r="O14" s="264">
+        <v>46000</v>
       </c>
       <c r="P14" s="264">
-        <v>46170</v>
+        <v>46007</v>
       </c>
       <c r="Q14" s="270" t="str">
         <v/>
@@ -41344,7 +41506,7 @@
         <v>Not submit yet</v>
       </c>
       <c r="S14" s="279">
-        <v>146</v>
+        <v>311</v>
       </c>
     </row>
     <row r="15" spans="1:25" ht="60">
@@ -41352,58 +41514,58 @@
         <v>9</v>
       </c>
       <c r="B15" s="302" t="str">
-        <v>PPS</v>
+        <v>SCS</v>
       </c>
       <c r="C15" s="13" t="str">
-        <v>ICD</v>
+        <v>OTH</v>
       </c>
       <c r="D15" s="282" t="str">
-        <v>LTIA-5.11-LTICT-RFA-OTH-0002</v>
+        <v>LTIA-5.10-VIETUR-70000-RFA-OTH-0654</v>
       </c>
       <c r="E15" s="303" t="str">
-        <v>Request for Approval of Interface, Functionality, and Design Documents for the SBD-BHS Component under the PPS System (Package 5.11)</v>
+        <v>Request for approval for Measurement Equipment of ICT cable - ELV System</v>
       </c>
       <c r="F15" s="303" t="str">
-        <v>Yêu cầu phê duyệt các tài liệu giao tiếp, chức năng và thiết kế hạng mục SBD-BHS thuộc hệ thống PPS (Gói thầu 5.11)</v>
+        <v>Đề nghị phê duyệt Thiết bị đo cáp điện nhẹ - Hệ thống điện nhẹ</v>
       </c>
       <c r="G15" s="270">
-        <v>45974</v>
+        <v>46009</v>
       </c>
       <c r="H15" s="270">
-        <v>45974</v>
+        <v>46009</v>
       </c>
       <c r="I15" s="264">
-        <v>46107</v>
+        <v>46009</v>
       </c>
       <c r="J15" s="264" t="str">
         <v>B</v>
       </c>
       <c r="K15" s="270">
-        <v>46120</v>
+        <v>46022</v>
       </c>
       <c r="L15" s="264">
-        <v>46133</v>
+        <v>46043</v>
       </c>
       <c r="M15" s="264" t="str">
-        <v/>
-      </c>
-      <c r="N15" s="270" t="str">
-        <v/>
+        <v>C</v>
+      </c>
+      <c r="N15" s="270">
+        <v>46162</v>
       </c>
       <c r="O15" s="264" t="str">
         <v/>
       </c>
       <c r="P15" s="264">
-        <v>46140</v>
+        <v>46170</v>
       </c>
       <c r="Q15" s="270" t="str">
         <v/>
       </c>
       <c r="R15" s="13" t="str">
-        <v/>
-      </c>
-      <c r="S15" s="279" t="str">
-        <v/>
+        <v>Not submit yet</v>
+      </c>
+      <c r="S15" s="279">
+        <v>148</v>
       </c>
     </row>
     <row r="16" spans="1:25" ht="45">
@@ -41417,31 +41579,31 @@
         <v>ICD</v>
       </c>
       <c r="D16" s="282" t="str">
-        <v>LTIA-5.11-LTICT-RFA-OTH-0004</v>
+        <v>LTIA-5.11-LTICT-RFA-OTH-0002</v>
       </c>
       <c r="E16" s="303" t="str">
-        <v>Request approval of design models and IP/VLAN address allocation for the BHS system</v>
+        <v>Request for Approval of Interface, Functionality, and Design Documents for the SBD-BHS Component under the PPS System (Package 5.11)</v>
       </c>
       <c r="F16" s="303" t="str">
-        <v>Yêu cầu phê duyệt các mô hình thiết kế, phân bổ địa chỉ IP/Vlan cho hệ thống BHS</v>
+        <v>Yêu cầu phê duyệt các tài liệu giao tiếp, chức năng và thiết kế hạng mục SBD-BHS thuộc hệ thống PPS (Gói thầu 5.11)</v>
       </c>
       <c r="G16" s="270">
-        <v>46055</v>
+        <v>45974</v>
       </c>
       <c r="H16" s="270">
-        <v>46056</v>
+        <v>45974</v>
       </c>
       <c r="I16" s="264">
-        <v>46057</v>
+        <v>46107</v>
       </c>
       <c r="J16" s="264" t="str">
-        <v>C</v>
+        <v>B</v>
       </c>
       <c r="K16" s="270">
-        <v>46066</v>
+        <v>46120</v>
       </c>
       <c r="L16" s="264">
-        <v>46105</v>
+        <v>46133</v>
       </c>
       <c r="M16" s="264" t="str">
         <v/>
@@ -41453,7 +41615,7 @@
         <v/>
       </c>
       <c r="P16" s="264">
-        <v>46112</v>
+        <v>46140</v>
       </c>
       <c r="Q16" s="270" t="str">
         <v/>
@@ -41470,34 +41632,34 @@
         <v>11</v>
       </c>
       <c r="B17" s="302" t="str">
-        <v>CCTV</v>
+        <v>PPS</v>
       </c>
       <c r="C17" s="13" t="str">
         <v>ICD</v>
       </c>
       <c r="D17" s="282" t="str">
-        <v>LTIA-5.11-LTICT-RFA-OTH-0005</v>
+        <v>LTIA-5.11-LTICT-RFA-OTH-0004</v>
       </c>
       <c r="E17" s="303" t="str">
-        <v>Request for approval of the Interface Control Document (ICD) for the CCTV (Closed-Circuit Television) scope under the CCTV System (Package 5.11)</v>
+        <v>Request approval of design models and IP/VLAN address allocation for the BHS system</v>
       </c>
       <c r="F17" s="303" t="str">
-        <v>Yêu cầu phê duyệt tài liệu kiểm soát giao diện (ICD), cho hạng mục CCTV (Closed-Circuit Television) thuộc hệ thống CCTV (Gói thầu 5.11)</v>
+        <v>Yêu cầu phê duyệt các mô hình thiết kế, phân bổ địa chỉ IP/Vlan cho hệ thống BHS</v>
       </c>
       <c r="G17" s="270">
-        <v>46085</v>
+        <v>46055</v>
       </c>
       <c r="H17" s="270">
-        <v>46083</v>
+        <v>46056</v>
       </c>
       <c r="I17" s="264">
-        <v>46085</v>
+        <v>46057</v>
       </c>
       <c r="J17" s="264" t="str">
         <v>C</v>
       </c>
       <c r="K17" s="270">
-        <v>46098</v>
+        <v>46066</v>
       </c>
       <c r="L17" s="264">
         <v>46105</v>
@@ -41529,49 +41691,49 @@
         <v>12</v>
       </c>
       <c r="B18" s="302" t="str">
-        <v>AGAC</v>
+        <v>CCTV</v>
       </c>
       <c r="C18" s="13" t="str">
         <v>ICD</v>
       </c>
       <c r="D18" s="282" t="str">
-        <v>LTIA-5.11-LTICT-RFA-OTH-0006</v>
+        <v>LTIA-5.11-LTICT-RFA-OTH-0005</v>
       </c>
       <c r="E18" s="303" t="str">
-        <v>Request for Approval of the AGAC System Integration Document (ICD) - Package 5.11</v>
+        <v>Request for approval of the Interface Control Document (ICD) for the CCTV (Closed-Circuit Television) scope under the CCTV System (Package 5.11)</v>
       </c>
       <c r="F18" s="303" t="str">
-        <v>Yêu cầu phê duyệt tài liệu tích hợp hệ thống (ICD) AGAC (Gói thầu 5.11)</v>
+        <v>Yêu cầu phê duyệt tài liệu kiểm soát giao diện (ICD), cho hạng mục CCTV (Closed-Circuit Television) thuộc hệ thống CCTV (Gói thầu 5.11)</v>
       </c>
       <c r="G18" s="270">
-        <v>46086</v>
+        <v>46085</v>
       </c>
       <c r="H18" s="270">
-        <v>46086</v>
+        <v>46083</v>
       </c>
       <c r="I18" s="264">
-        <v>46094</v>
+        <v>46085</v>
       </c>
       <c r="J18" s="264" t="str">
         <v>C</v>
       </c>
       <c r="K18" s="270">
-        <v>46107</v>
+        <v>46098</v>
       </c>
       <c r="L18" s="264">
+        <v>46105</v>
+      </c>
+      <c r="M18" s="264" t="str">
+        <v/>
+      </c>
+      <c r="N18" s="270" t="str">
+        <v/>
+      </c>
+      <c r="O18" s="264" t="str">
+        <v/>
+      </c>
+      <c r="P18" s="264">
         <v>46112</v>
-      </c>
-      <c r="M18" s="264" t="str">
-        <v/>
-      </c>
-      <c r="N18" s="270" t="str">
-        <v/>
-      </c>
-      <c r="O18" s="264" t="str">
-        <v/>
-      </c>
-      <c r="P18" s="264">
-        <v>46119</v>
       </c>
       <c r="Q18" s="270" t="str">
         <v/>
@@ -41588,100 +41750,100 @@
         <v>13</v>
       </c>
       <c r="B19" s="302" t="str">
+        <v>AGAC</v>
+      </c>
+      <c r="C19" s="13" t="str">
+        <v>ICD</v>
+      </c>
+      <c r="D19" s="282" t="str">
+        <v>LTIA-5.11-LTICT-RFA-OTH-0006</v>
+      </c>
+      <c r="E19" s="303" t="str">
+        <v>Request for Approval of the AGAC System Integration Document (ICD) - Package 5.11</v>
+      </c>
+      <c r="F19" s="303" t="str">
+        <v>Yêu cầu phê duyệt tài liệu tích hợp hệ thống (ICD) AGAC (Gói thầu 5.11)</v>
+      </c>
+      <c r="G19" s="270">
+        <v>46086</v>
+      </c>
+      <c r="H19" s="270">
+        <v>46086</v>
+      </c>
+      <c r="I19" s="264">
+        <v>46094</v>
+      </c>
+      <c r="J19" s="264" t="str">
+        <v>C</v>
+      </c>
+      <c r="K19" s="270">
+        <v>46107</v>
+      </c>
+      <c r="L19" s="264">
+        <v>46112</v>
+      </c>
+      <c r="M19" s="264" t="str">
+        <v/>
+      </c>
+      <c r="N19" s="270" t="str">
+        <v/>
+      </c>
+      <c r="O19" s="264" t="str">
+        <v/>
+      </c>
+      <c r="P19" s="264">
+        <v>46119</v>
+      </c>
+      <c r="Q19" s="270" t="str">
+        <v/>
+      </c>
+      <c r="R19" s="13" t="str">
+        <v/>
+      </c>
+      <c r="S19" s="279" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:19" ht="45">
+      <c r="A20" s="13">
+        <v>14</v>
+      </c>
+      <c r="B20" s="302" t="str">
         <v>DCH
 DNE
 CCTV
 AGAC
 PPS</v>
       </c>
-      <c r="C19" s="13" t="str">
+      <c r="C20" s="13" t="str">
         <v>MSS</v>
       </c>
-      <c r="D19" s="282" t="str">
+      <c r="D20" s="282" t="str">
         <v>LTIA-5.11- LTICT-RFA-MSS-0001</v>
       </c>
-      <c r="E19" s="303" t="str">
+      <c r="E20" s="303" t="str">
         <v>Request for approval of construction methods for 05 systems serving the domestic T&amp;C plan</v>
       </c>
-      <c r="F19" s="303" t="str">
+      <c r="F20" s="303" t="str">
         <v>Yêu cầu phê duyệt Biện pháp thi công cho 05 hệ thống phục vụ kế hoạch T&amp;C Quốc nội</v>
       </c>
-      <c r="G19" s="270">
+      <c r="G20" s="270">
         <v>46094</v>
       </c>
-      <c r="H19" s="270">
+      <c r="H20" s="270">
         <v>46094</v>
       </c>
-      <c r="I19" s="264">
+      <c r="I20" s="264">
         <v>46094</v>
-      </c>
-      <c r="J19" s="264" t="str">
-        <v>C</v>
-      </c>
-      <c r="K19" s="270">
-        <v>46129</v>
-      </c>
-      <c r="L19" s="264">
-        <v>46129</v>
-      </c>
-      <c r="M19" s="264" t="str">
-        <v/>
-      </c>
-      <c r="N19" s="270" t="str">
-        <v/>
-      </c>
-      <c r="O19" s="264" t="str">
-        <v/>
-      </c>
-      <c r="P19" s="264">
-        <v>46136</v>
-      </c>
-      <c r="Q19" s="270" t="str">
-        <v/>
-      </c>
-      <c r="R19" s="13" t="str">
-        <v/>
-      </c>
-      <c r="S19" s="279" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="20" spans="1:19" ht="45">
-      <c r="A20" s="13">
-        <v>14</v>
-      </c>
-      <c r="B20" s="302" t="str">
-        <v>DNE</v>
-      </c>
-      <c r="C20" s="13" t="str">
-        <v>OTH</v>
-      </c>
-      <c r="D20" s="282" t="str">
-        <v>LTIA-5.11-LTICT-RFA-OTH-0009</v>
-      </c>
-      <c r="E20" s="303" t="str">
-        <v>Request for Approval of the Network IP Addressing and Allocation Plan for the T&amp;C Stage</v>
-      </c>
-      <c r="F20" s="303" t="str">
-        <v>Yêu cầu phê duyệt tài liệu quy hoạch và phân bổ địa chỉ IP mạng phục vụ giai đoạn T&amp;C</v>
-      </c>
-      <c r="G20" s="270">
-        <v>46195</v>
-      </c>
-      <c r="H20" s="270">
-        <v>46195</v>
-      </c>
-      <c r="I20" s="264">
-        <v>46198</v>
       </c>
       <c r="J20" s="264" t="str">
         <v>C</v>
       </c>
       <c r="K20" s="270">
-        <v>46209</v>
+        <v>46129</v>
       </c>
       <c r="L20" s="264">
-        <v>46219</v>
+        <v>46129</v>
       </c>
       <c r="M20" s="264" t="str">
         <v/>
@@ -41693,10 +41855,10 @@
         <v/>
       </c>
       <c r="P20" s="264">
-        <v>46226</v>
-      </c>
-      <c r="Q20" s="270">
-        <v>46312</v>
+        <v>46136</v>
+      </c>
+      <c r="Q20" s="270" t="str">
+        <v/>
       </c>
       <c r="R20" s="13" t="str">
         <v/>
@@ -41710,37 +41872,37 @@
         <v>15</v>
       </c>
       <c r="B21" s="302" t="str">
-        <v>HBMS</v>
+        <v>DNE</v>
       </c>
       <c r="C21" s="13" t="str">
         <v>OTH</v>
       </c>
       <c r="D21" s="282" t="str">
-        <v>LTIA-5.10-VIETUR-70000-RFA-OTH-0732</v>
+        <v>LTIA-5.11-LTICT-RFA-OTH-0009</v>
       </c>
       <c r="E21" s="303" t="str">
-        <v>Request for approval of Hight level building management system (HBMS) Graphic User Interface (GUI)</v>
+        <v>Request for Approval of the Network IP Addressing and Allocation Plan for the T&amp;C Stage</v>
       </c>
       <c r="F21" s="303" t="str">
-        <v>Đề nghị phê duyệt giao diện đồ họa người dùng (GUI) Hệ thống quản lý tòa nhà bậc cao (HBMS)</v>
+        <v>Yêu cầu phê duyệt tài liệu quy hoạch và phân bổ địa chỉ IP mạng phục vụ giai đoạn T&amp;C</v>
       </c>
       <c r="G21" s="270">
-        <v>46210</v>
+        <v>46195</v>
       </c>
       <c r="H21" s="270">
-        <v>46210</v>
+        <v>46195</v>
       </c>
       <c r="I21" s="264">
-        <v>46210</v>
+        <v>46198</v>
       </c>
       <c r="J21" s="264" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
       <c r="K21" s="270">
-        <v>46220</v>
+        <v>46209</v>
       </c>
       <c r="L21" s="264">
-        <v>46225</v>
+        <v>46219</v>
       </c>
       <c r="M21" s="264" t="str">
         <v/>
@@ -41752,10 +41914,10 @@
         <v/>
       </c>
       <c r="P21" s="264">
-        <v>46232</v>
-      </c>
-      <c r="Q21" s="270" t="str">
-        <v/>
+        <v>46226</v>
+      </c>
+      <c r="Q21" s="270">
+        <v>46312</v>
       </c>
       <c r="R21" s="13" t="str">
         <v/>
@@ -41769,37 +41931,37 @@
         <v>16</v>
       </c>
       <c r="B22" s="302" t="str">
-        <v>PAS</v>
+        <v>HBMS</v>
       </c>
       <c r="C22" s="13" t="str">
         <v>OTH</v>
       </c>
       <c r="D22" s="282" t="str">
-        <v>LTIA-5.10-VIETUR-72150-RFA-OTH-0750</v>
+        <v>LTIA-5.10-VIETUR-70000-RFA-OTH-0732</v>
       </c>
       <c r="E22" s="303" t="str">
-        <v>Request for Approval of the Pre-Completion Inspection, Testing, and Commissioning Procedure for the Public Address System (PAS)</v>
+        <v>Request for approval of Hight level building management system (HBMS) Graphic User Interface (GUI)</v>
       </c>
       <c r="F22" s="303" t="str">
-        <v>Đề nghị phê duyệt Quy trình kiểm tra trước khi hoàn thành, thử nghiệm, vận hành hệ thống Âm Thanh Thông báo</v>
+        <v>Đề nghị phê duyệt giao diện đồ họa người dùng (GUI) Hệ thống quản lý tòa nhà bậc cao (HBMS)</v>
       </c>
       <c r="G22" s="270">
-        <v>46255</v>
+        <v>46210</v>
       </c>
       <c r="H22" s="270">
-        <v>46255</v>
+        <v>46210</v>
       </c>
       <c r="I22" s="264">
-        <v>46255</v>
+        <v>46210</v>
       </c>
       <c r="J22" s="264" t="str">
-        <v>C</v>
+        <v>B</v>
       </c>
       <c r="K22" s="270">
-        <v>46272</v>
+        <v>46220</v>
       </c>
       <c r="L22" s="264">
-        <v>46275</v>
+        <v>46225</v>
       </c>
       <c r="M22" s="264" t="str">
         <v/>
@@ -41811,7 +41973,7 @@
         <v/>
       </c>
       <c r="P22" s="264">
-        <v>46282</v>
+        <v>46232</v>
       </c>
       <c r="Q22" s="270" t="str">
         <v/>
@@ -41828,58 +41990,58 @@
         <v>17</v>
       </c>
       <c r="B23" s="302" t="str">
-        <v>MCS</v>
+        <v>PAS</v>
       </c>
       <c r="C23" s="13" t="str">
         <v>OTH</v>
       </c>
       <c r="D23" s="282" t="str">
-        <v>LTIA-5.10-VIETUR-70000-RFA-OTH-0721A</v>
+        <v>LTIA-5.10-VIETUR-72150-RFA-OTH-0750</v>
       </c>
       <c r="E23" s="303" t="str">
-        <v>Request for approval of Pre-completion inspection, testing, commissioning of Master Clock System (MCS)</v>
+        <v>Request for Approval of the Pre-Completion Inspection, Testing, and Commissioning Procedure for the Public Address System (PAS)</v>
       </c>
       <c r="F23" s="303" t="str">
-        <v>Đề nghị phê duyệt Quy trình kiểm tra trước khi hoàn thành, thử nghiệm, vận hành của Hệ thống Đồng hồ chủ (MCS)</v>
+        <v>Đề nghị phê duyệt Quy trình kiểm tra trước khi hoàn thành, thử nghiệm, vận hành hệ thống Âm Thanh Thông báo</v>
       </c>
       <c r="G23" s="270">
-        <v>46262</v>
+        <v>46255</v>
       </c>
       <c r="H23" s="270">
-        <v>46262</v>
+        <v>46255</v>
       </c>
       <c r="I23" s="264">
-        <v>46262</v>
+        <v>46255</v>
       </c>
       <c r="J23" s="264" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
       <c r="K23" s="270">
-        <v>46276</v>
+        <v>46272</v>
       </c>
       <c r="L23" s="264">
-        <v>46279</v>
+        <v>46275</v>
       </c>
       <c r="M23" s="264" t="str">
-        <v/>
-      </c>
-      <c r="N23" s="270" t="str">
-        <v/>
-      </c>
-      <c r="O23" s="264" t="str">
-        <v/>
+        <v>C</v>
+      </c>
+      <c r="N23" s="270">
+        <v>46282</v>
+      </c>
+      <c r="O23" s="264">
+        <v>46283</v>
       </c>
       <c r="P23" s="264">
-        <v>46286</v>
+        <v>46290</v>
       </c>
       <c r="Q23" s="270" t="str">
         <v/>
       </c>
       <c r="R23" s="13" t="str">
-        <v/>
-      </c>
-      <c r="S23" s="279" t="str">
-        <v/>
+        <v>Not submit yet</v>
+      </c>
+      <c r="S23" s="279">
+        <v>28</v>
       </c>
     </row>
     <row r="24" spans="1:19" ht="105">
@@ -41946,37 +42108,37 @@
         <v>19</v>
       </c>
       <c r="B25" s="302" t="str">
-        <v>CCTV</v>
+        <v>PMR</v>
       </c>
       <c r="C25" s="13" t="str">
         <v>MSS</v>
       </c>
       <c r="D25" s="282" t="str">
-        <v>LTIA-5.11-LTICT- 72120 -RFA-MSS-0004</v>
+        <v>LTIA-5.11- LTICT- 72100-RFA-MSS-0002</v>
       </c>
       <c r="E25" s="303" t="str">
-        <v>Request for Approval of the Method Statement for the CCTV System</v>
+        <v>Request for Approval of the Method Statement for the PMR Radio System</v>
       </c>
       <c r="F25" s="303" t="str">
-        <v>Yêu cầu phê duyệt Biện pháp thi công cho hệ thống Camera giám sát (CCTV)</v>
+        <v>Yêu cầu phê duyệt Biện pháp thi công cho hệ thống Bộ đàm (PMR)</v>
       </c>
       <c r="G25" s="270">
-        <v>46300</v>
+        <v>46298</v>
       </c>
       <c r="H25" s="270">
-        <v>46300</v>
+        <v>46298</v>
       </c>
       <c r="I25" s="264">
-        <v>46300</v>
+        <v>46302</v>
       </c>
       <c r="J25" s="264" t="str">
         <v>C</v>
       </c>
-      <c r="K25" s="270">
-        <v>46314</v>
-      </c>
-      <c r="L25" s="264">
-        <v>46317</v>
+      <c r="K25" s="270" t="str">
+        <v/>
+      </c>
+      <c r="L25" s="264" t="str">
+        <v/>
       </c>
       <c r="M25" s="264" t="str">
         <v/>
@@ -41987,8 +42149,8 @@
       <c r="O25" s="264" t="str">
         <v/>
       </c>
-      <c r="P25" s="264">
-        <v>46324</v>
+      <c r="P25" s="264" t="str">
+        <v/>
       </c>
       <c r="Q25" s="270" t="str">
         <v/>
@@ -42005,25 +42167,25 @@
         <v>20</v>
       </c>
       <c r="B26" s="302" t="str">
-        <v>AGAC</v>
+        <v>SCS</v>
       </c>
       <c r="C26" s="13" t="str">
         <v>MSS</v>
       </c>
       <c r="D26" s="282" t="str">
-        <v>LTIA-5.11-LTICT-70100-RFA-MSS-0007</v>
+        <v>LTIA-5.11-LTICT- 72010 -RFA-MSS-0003</v>
       </c>
       <c r="E26" s="303" t="str">
-        <v>Request for Approval of the Method Statement for the AGAC System</v>
+        <v>Request for Approval of the Method Statement for the Structured Cable System</v>
       </c>
       <c r="F26" s="303" t="str">
-        <v>Yêu cầu phê duyệt Biện pháp thi công cho hệ thống cửa truy cập tự động (AGAC)</v>
+        <v>Yêu cầu phê duyệt Biện pháp thi công cho hệ thống Cáp cấu trúc (SCS)</v>
       </c>
       <c r="G26" s="270">
-        <v>46301</v>
+        <v>46300</v>
       </c>
       <c r="H26" s="270">
-        <v>46301</v>
+        <v>46300</v>
       </c>
       <c r="I26" s="264">
         <v>46302</v>
@@ -42031,31 +42193,267 @@
       <c r="J26" s="264" t="str">
         <v>C</v>
       </c>
-      <c r="K26" s="270">
+      <c r="K26" s="270" t="str">
+        <v/>
+      </c>
+      <c r="L26" s="264" t="str">
+        <v/>
+      </c>
+      <c r="M26" s="264" t="str">
+        <v/>
+      </c>
+      <c r="N26" s="270" t="str">
+        <v/>
+      </c>
+      <c r="O26" s="264" t="str">
+        <v/>
+      </c>
+      <c r="P26" s="264" t="str">
+        <v/>
+      </c>
+      <c r="Q26" s="270" t="str">
+        <v/>
+      </c>
+      <c r="R26" s="13" t="str">
+        <v/>
+      </c>
+      <c r="S26" s="279" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27" spans="1:19">
+      <c r="A27" s="13">
+        <v>21</v>
+      </c>
+      <c r="B27" s="302" t="str">
+        <v>CCTV</v>
+      </c>
+      <c r="C27" s="13" t="str">
+        <v>MSS</v>
+      </c>
+      <c r="D27" s="282" t="str">
+        <v>LTIA-5.11-LTICT- 72120 -RFA-MSS-0004</v>
+      </c>
+      <c r="E27" s="303" t="str">
+        <v>Request for Approval of the Method Statement for the CCTV System</v>
+      </c>
+      <c r="F27" s="303" t="str">
+        <v>Yêu cầu phê duyệt Biện pháp thi công cho hệ thống Camera giám sát (CCTV)</v>
+      </c>
+      <c r="G27" s="270">
+        <v>46300</v>
+      </c>
+      <c r="H27" s="270">
+        <v>46300</v>
+      </c>
+      <c r="I27" s="264">
+        <v>46300</v>
+      </c>
+      <c r="J27" s="264" t="str">
+        <v>C</v>
+      </c>
+      <c r="K27" s="270">
         <v>46314</v>
       </c>
-      <c r="L26" s="264">
+      <c r="L27" s="264">
         <v>46317</v>
       </c>
-      <c r="M26" s="264" t="str">
-        <v/>
-      </c>
-      <c r="N26" s="270" t="str">
-        <v/>
-      </c>
-      <c r="O26" s="264" t="str">
-        <v/>
-      </c>
-      <c r="P26" s="264">
+      <c r="M27" s="264" t="str">
+        <v/>
+      </c>
+      <c r="N27" s="270" t="str">
+        <v/>
+      </c>
+      <c r="O27" s="264" t="str">
+        <v/>
+      </c>
+      <c r="P27" s="264">
         <v>46324</v>
       </c>
-      <c r="Q26" s="270" t="str">
-        <v/>
-      </c>
-      <c r="R26" s="13" t="str">
-        <v/>
-      </c>
-      <c r="S26" s="279" t="str">
+      <c r="Q27" s="270" t="str">
+        <v/>
+      </c>
+      <c r="R27" s="13" t="str">
+        <v/>
+      </c>
+      <c r="S27" s="279" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="28" spans="1:19">
+      <c r="A28" s="13">
+        <v>22</v>
+      </c>
+      <c r="B28" s="302" t="str">
+        <v>AGAC</v>
+      </c>
+      <c r="C28" s="13" t="str">
+        <v>MSS</v>
+      </c>
+      <c r="D28" s="282" t="str">
+        <v>LTIA-5.11-LTICT-70100-RFA-MSS-0007</v>
+      </c>
+      <c r="E28" s="303" t="str">
+        <v>Request for Approval of the Method Statement for the AGAC System</v>
+      </c>
+      <c r="F28" s="303" t="str">
+        <v>Yêu cầu phê duyệt Biện pháp thi công cho hệ thống cửa truy cập tự động (AGAC)</v>
+      </c>
+      <c r="G28" s="270">
+        <v>46301</v>
+      </c>
+      <c r="H28" s="270">
+        <v>46301</v>
+      </c>
+      <c r="I28" s="264">
+        <v>46302</v>
+      </c>
+      <c r="J28" s="264" t="str">
+        <v>C</v>
+      </c>
+      <c r="K28" s="270">
+        <v>46314</v>
+      </c>
+      <c r="L28" s="264">
+        <v>46317</v>
+      </c>
+      <c r="M28" s="264" t="str">
+        <v/>
+      </c>
+      <c r="N28" s="270" t="str">
+        <v/>
+      </c>
+      <c r="O28" s="264" t="str">
+        <v/>
+      </c>
+      <c r="P28" s="264">
+        <v>46324</v>
+      </c>
+      <c r="Q28" s="270" t="str">
+        <v/>
+      </c>
+      <c r="R28" s="13" t="str">
+        <v/>
+      </c>
+      <c r="S28" s="279" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="29" spans="1:19">
+      <c r="A29" s="13">
+        <v>23</v>
+      </c>
+      <c r="B29" s="302" t="str">
+        <v>Smart Parking</v>
+      </c>
+      <c r="C29" s="13" t="str">
+        <v>MSS</v>
+      </c>
+      <c r="D29" s="282" t="str">
+        <v>LTIA-5.11-LTICT- 72190 -RFA-MSS-0005</v>
+      </c>
+      <c r="E29" s="303" t="str">
+        <v>Request for Approval of the Method Statement for the Smart Parking System</v>
+      </c>
+      <c r="F29" s="303" t="str">
+        <v>Yêu cầu phê duyệt Biện pháp thi công cho hệ thống Bãi đỗ xe thông minh</v>
+      </c>
+      <c r="G29" s="270">
+        <v>46301</v>
+      </c>
+      <c r="H29" s="270">
+        <v>46301</v>
+      </c>
+      <c r="I29" s="264">
+        <v>46301</v>
+      </c>
+      <c r="J29" s="264" t="str">
+        <v>C</v>
+      </c>
+      <c r="K29" s="270" t="str">
+        <v/>
+      </c>
+      <c r="L29" s="264" t="str">
+        <v/>
+      </c>
+      <c r="M29" s="264" t="str">
+        <v/>
+      </c>
+      <c r="N29" s="270" t="str">
+        <v/>
+      </c>
+      <c r="O29" s="264" t="str">
+        <v/>
+      </c>
+      <c r="P29" s="264" t="str">
+        <v/>
+      </c>
+      <c r="Q29" s="270" t="str">
+        <v/>
+      </c>
+      <c r="R29" s="13" t="str">
+        <v/>
+      </c>
+      <c r="S29" s="279" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="30" spans="1:19">
+      <c r="A30" s="13">
+        <v>24</v>
+      </c>
+      <c r="B30" s="302" t="str">
+        <v>TOLL</v>
+      </c>
+      <c r="C30" s="13" t="str">
+        <v>MSS</v>
+      </c>
+      <c r="D30" s="282" t="str">
+        <v>LTIA-5.11-LTICT- 71110 -RFA-MSS-0006</v>
+      </c>
+      <c r="E30" s="303" t="str">
+        <v>Request for Approval of the Method Statement for the Toll Collection System</v>
+      </c>
+      <c r="F30" s="303" t="str">
+        <v>Yêu cầu phê duyệt Biện pháp thi công cho hệ thống Thu phí</v>
+      </c>
+      <c r="G30" s="270">
+        <v>46301</v>
+      </c>
+      <c r="H30" s="270">
+        <v>46301</v>
+      </c>
+      <c r="I30" s="264">
+        <v>46301</v>
+      </c>
+      <c r="J30" s="264" t="str">
+        <v>C</v>
+      </c>
+      <c r="K30" s="270" t="str">
+        <v/>
+      </c>
+      <c r="L30" s="264" t="str">
+        <v/>
+      </c>
+      <c r="M30" s="264" t="str">
+        <v/>
+      </c>
+      <c r="N30" s="270" t="str">
+        <v/>
+      </c>
+      <c r="O30" s="264" t="str">
+        <v/>
+      </c>
+      <c r="P30" s="264" t="str">
+        <v/>
+      </c>
+      <c r="Q30" s="270" t="str">
+        <v/>
+      </c>
+      <c r="R30" s="13" t="str">
+        <v/>
+      </c>
+      <c r="S30" s="279" t="str">
         <v/>
       </c>
     </row>
@@ -42081,7 +42479,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42223A76-B79E-483C-82B7-07960417E780}">
-  <dimension ref="A1:R14"/>
+  <dimension ref="A1:R16"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="13" customWidth="1"/>
@@ -42156,16 +42554,16 @@
       <c r="R3" s="281"/>
     </row>
     <row r="4" spans="1:18" ht="16.5" thickBot="1">
-      <c r="A4" s="397" t="s">
+      <c r="A4" s="426" t="s">
         <v>123</v>
       </c>
-      <c r="B4" s="364" t="s">
+      <c r="B4" s="385" t="s">
         <v>45</v>
       </c>
-      <c r="C4" s="364" t="s">
+      <c r="C4" s="385" t="s">
         <v>46</v>
       </c>
-      <c r="D4" s="366" t="s">
+      <c r="D4" s="390" t="s">
         <v>4</v>
       </c>
       <c r="E4" s="449" t="s">
@@ -42194,11 +42592,11 @@
       <c r="R4" s="448"/>
     </row>
     <row r="5" spans="1:18" ht="78.75">
-      <c r="A5" s="398"/>
-      <c r="B5" s="365"/>
-      <c r="C5" s="365"/>
-      <c r="D5" s="431"/>
-      <c r="E5" s="369"/>
+      <c r="A5" s="427"/>
+      <c r="B5" s="386"/>
+      <c r="C5" s="386"/>
+      <c r="D5" s="384"/>
+      <c r="E5" s="353"/>
       <c r="F5" s="283" t="s">
         <v>56</v>
       </c>
@@ -42261,11 +42659,11 @@
     </row>
     <row r="7" spans="1:18" ht="75">
       <c r="A7" s="13" cm="1">
-        <f t="array" ref="A7:A14">IF(_xlfn.ANCHORARRAY(C7)="","",_xlfn.SEQUENCE(ROWS(_xlfn.ANCHORARRAY(C7))))</f>
+        <f t="array" ref="A7:A16">IF(_xlfn.ANCHORARRAY(C7)="","",_xlfn.SEQUENCE(ROWS(_xlfn.ANCHORARRAY(C7))))</f>
         <v>1</v>
       </c>
       <c r="B7" s="302" t="str" cm="1">
-        <f t="array" ref="B7:B14">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$C:$C,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
+        <f t="array" ref="B7:B16">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$C:$C,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
         <v>FAS
 SCS
 SCN
@@ -42273,68 +42671,68 @@
 PAS</v>
       </c>
       <c r="C7" s="282" t="str" cm="1">
-        <f t="array" ref="C7:C14">_xlfn._xlws.FILTER('RFA-SDS'!$D$5:$D$4874,'RFA-SDS'!$AI$5:$AI$4874="YES","")</f>
+        <f t="array" ref="C7:C16">_xlfn._xlws.FILTER('RFA-SDS'!$D$5:$D$4874,'RFA-SDS'!$AI$5:$AI$4874="YES","")</f>
         <v>LTIA-5.10-VIETUR-80000-RFA-SDS-0214</v>
       </c>
       <c r="D7" s="303" t="str" cm="1">
-        <f t="array" ref="D7:D14">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$F:$F,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
+        <f t="array" ref="D7:D16">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$F:$F,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
         <v xml:space="preserve">Construction design drawing of  ICT system – part.1: ICT systems for FLB </v>
       </c>
       <c r="E7" s="303" t="str" cm="1">
-        <f t="array" ref="E7:E14">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$G:$G,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
+        <f t="array" ref="E7:E16">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$G:$G,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
         <v>Bản vẽ TKTC cho hệ thống ICT – phần 1 – Hệ thống ICT cho FLB</v>
       </c>
       <c r="F7" s="270" cm="1">
-        <f t="array" ref="F7:F14">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$R:$R,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
+        <f t="array" ref="F7:F16">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$R:$R,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
         <v>45673</v>
       </c>
       <c r="G7" s="270" cm="1">
-        <f t="array" ref="G7:G14">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$S:$S,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
+        <f t="array" ref="G7:G16">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$S:$S,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
         <v>45673</v>
       </c>
       <c r="H7" s="264" cm="1">
-        <f t="array" ref="H7:H14">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$T:$T,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
+        <f t="array" ref="H7:H16">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$T:$T,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
         <v>45699</v>
       </c>
       <c r="I7" s="264" t="str" cm="1">
-        <f t="array" ref="I7:I14">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$H:$H,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
+        <f t="array" ref="I7:I16">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$H:$H,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
         <v>B</v>
       </c>
       <c r="J7" s="270" cm="1">
-        <f t="array" ref="J7:J14">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$U:$U,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
+        <f t="array" ref="J7:J16">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$U:$U,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
         <v>45716</v>
       </c>
       <c r="K7" s="264" cm="1">
-        <f t="array" ref="K7:K14">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$V:$V,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
+        <f t="array" ref="K7:K16">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$V:$V,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
         <v>45741</v>
       </c>
       <c r="L7" s="264" t="str" cm="1">
-        <f t="array" ref="L7:L14">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$Q:$Q,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
+        <f t="array" ref="L7:L16">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$Q:$Q,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
         <v>B</v>
       </c>
       <c r="M7" s="270" cm="1">
-        <f t="array" ref="M7:M14">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$X:$X,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
+        <f t="array" ref="M7:M16">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$X:$X,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
         <v>45756</v>
       </c>
       <c r="N7" s="264" cm="1">
-        <f t="array" ref="N7:N14">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$Y:$Y,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
+        <f t="array" ref="N7:N16">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$Y:$Y,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
         <v>45756</v>
       </c>
       <c r="O7" s="264" cm="1">
-        <f t="array" ref="O7:O14">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$Z:$Z,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
+        <f t="array" ref="O7:O16">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$Z:$Z,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
         <v>45763</v>
       </c>
       <c r="P7" s="270" t="str" cm="1">
-        <f t="array" ref="P7:P14">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$AA:$AA,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
+        <f t="array" ref="P7:P16">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$AA:$AA,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
         <v/>
       </c>
       <c r="Q7" s="13" t="str" cm="1">
-        <f t="array" ref="Q7:Q14">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$AB:$AB,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
+        <f t="array" ref="Q7:Q16">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$AB:$AB,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
         <v>Not submit yet</v>
       </c>
       <c r="R7" s="279" cm="1">
-        <f t="array" ref="R7:R14">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$AC:$AC,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
-        <v>554</v>
+        <f t="array" ref="R7:R16">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$AC:$AC,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
+        <v>555</v>
       </c>
     </row>
     <row r="8" spans="1:18" ht="30">
@@ -42390,7 +42788,7 @@
         <v>Not submit yet</v>
       </c>
       <c r="R8" s="279">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="45">
@@ -42446,7 +42844,7 @@
         <v>Not submit yet</v>
       </c>
       <c r="R9" s="279">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="45">
@@ -42503,7 +42901,7 @@
         <v>Not submit yet</v>
       </c>
       <c r="R10" s="279">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="75">
@@ -42559,7 +42957,7 @@
         <v>Not submit yet</v>
       </c>
       <c r="R11" s="279">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="12" spans="1:18" ht="45">
@@ -42615,7 +43013,7 @@
         <v>Not submit yet</v>
       </c>
       <c r="R12" s="279">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="60">
@@ -42727,7 +43125,119 @@
         <v>Not submit yet</v>
       </c>
       <c r="R14" s="279">
-        <v>311</v>
+        <v>312</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18">
+      <c r="A15" s="13">
+        <v>9</v>
+      </c>
+      <c r="B15" s="302" t="str">
+        <v>SCS</v>
+      </c>
+      <c r="C15" s="282" t="str">
+        <v>LTIA-5.10-VIETUR-80000-RFA-SDS-0415</v>
+      </c>
+      <c r="D15" s="303" t="str">
+        <v>Construction design drawing of  ICT system – part.1: ICT systems for Power and Loop Cable Layout on Cable Tray</v>
+      </c>
+      <c r="E15" s="303" t="str">
+        <v>Bản vẽ TKTC cho hệ thống ICT – phần 1 – Hệ thống ICT cho Bản Vẽ Dây Nguồn Và Dây Tín Hiệu Loop Trên Máng Cáp</v>
+      </c>
+      <c r="F15" s="270">
+        <v>46014</v>
+      </c>
+      <c r="G15" s="270">
+        <v>46014</v>
+      </c>
+      <c r="H15" s="264">
+        <v>46141</v>
+      </c>
+      <c r="I15" s="264" t="str">
+        <v>C</v>
+      </c>
+      <c r="J15" s="270">
+        <v>46150</v>
+      </c>
+      <c r="K15" s="264">
+        <v>46191</v>
+      </c>
+      <c r="L15" s="264" t="str">
+        <v>C</v>
+      </c>
+      <c r="M15" s="270">
+        <v>46206</v>
+      </c>
+      <c r="N15" s="264">
+        <v>46212</v>
+      </c>
+      <c r="O15" s="264">
+        <v>46219</v>
+      </c>
+      <c r="P15" s="270" t="str">
+        <v/>
+      </c>
+      <c r="Q15" s="13" t="str">
+        <v>Not submit yet</v>
+      </c>
+      <c r="R15" s="279">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18">
+      <c r="A16" s="13">
+        <v>10</v>
+      </c>
+      <c r="B16" s="302" t="str">
+        <v>PMR</v>
+      </c>
+      <c r="C16" s="282" t="str">
+        <v>LTIA-5.11-LTICT-72100-RFA-SDS-0001</v>
+      </c>
+      <c r="D16" s="303" t="str">
+        <v>Request for Approval of Construction Drawings for the PMR System</v>
+      </c>
+      <c r="E16" s="303" t="str">
+        <v>Đề nghị phê duyệt bản vẽ thi công cho hệ thống bộ đàm (PMR)</v>
+      </c>
+      <c r="F16" s="270">
+        <v>46283</v>
+      </c>
+      <c r="G16" s="270">
+        <v>46283</v>
+      </c>
+      <c r="H16" s="264">
+        <v>46283</v>
+      </c>
+      <c r="I16" s="264" t="str">
+        <v>C</v>
+      </c>
+      <c r="J16" s="270">
+        <v>46304</v>
+      </c>
+      <c r="K16" s="264">
+        <v>46304</v>
+      </c>
+      <c r="L16" s="264" t="str">
+        <v>C</v>
+      </c>
+      <c r="M16" s="270">
+        <v>46317</v>
+      </c>
+      <c r="N16" s="264" t="str">
+        <v/>
+      </c>
+      <c r="O16" s="264">
+        <v>46325</v>
+      </c>
+      <c r="P16" s="270" t="str">
+        <v/>
+      </c>
+      <c r="Q16" s="13" t="str">
+        <v>In progress</v>
+      </c>
+      <c r="R16" s="279" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -42785,19 +43295,19 @@
     <row r="3" spans="1:4" ht="15.75">
       <c r="A3" s="319">
         <f>MAX('Need ReSub (RFA)'!S7:S76)</f>
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="B3" s="319">
         <f>AVERAGEIF('Need ReSub (RFA)'!S7:S76,"&lt;&gt;0")</f>
-        <v>461.25</v>
+        <v>393.7</v>
       </c>
       <c r="C3" s="319">
         <f>MAX(_xlfn.ANCHORARRAY('Need ReSub (RFA-SDS)'!R7))</f>
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="D3" s="319">
         <f>AVERAGEIF(_xlfn.ANCHORARRAY('Need ReSub (RFA-SDS)'!R7),"&lt;&gt;0")</f>
-        <v>355.5</v>
+        <v>327.77777777777777</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -42806,10 +43316,10 @@
 Furthermore, the RFA (SDS) is as follows:
 Avarage :  " &amp; ROUND($D$3,0) &amp; " days
 Maimum :  " &amp; ROUND($C$3,0) &amp; " days"</f>
-        <v>In the RFA process, the average number of days elapsed since responding to an unapproved RFA was 461 days, with a maximum of 853 days, indicating that delays in the RFA approval process are contributing to delays in construction work.
+        <v>In the RFA process, the average number of days elapsed since responding to an unapproved RFA was 394 days, with a maximum of 855 days, indicating that delays in the RFA approval process are contributing to delays in construction work.
 Furthermore, the RFA (SDS) is as follows:
-Avarage :  356 days
-Maimum :  554 days</v>
+Avarage :  328 days
+Maimum :  555 days</v>
       </c>
       <c r="B5" s="452"/>
     </row>

--- a/ICT-RFA-RFI-lists-New.xlsx
+++ b/ICT-RFA-RFI-lists-New.xlsx
@@ -9,9 +9,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project Airport\LTIA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF16DFFE-99A1-43A8-B745-71630EDB6E43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE9A458C-01FA-4246-AEAB-9164D233D63C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="506" activeTab="1" xr2:uid="{CCA8147E-0981-4321-B87F-440A52C0DA59}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="506" activeTab="2" xr2:uid="{CCA8147E-0981-4321-B87F-440A52C0DA59}"/>
   </bookViews>
   <sheets>
     <sheet name="RFA" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="4">'Need ReSub (RFA-SDS)'!$A$1:$R$62</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">RFA!$A$1:$AE$143,RFA!$I$145:$R$151,RFA!$C$145:$F$155,RFA!$C$157:$F$160,RFA!$C$162:$F$173</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'RFA-SDS'!$A$1:$AD$47,'RFA-SDS'!$H$49:$Q$55,'RFA-SDS'!$C$49:$E$53,'RFA-SDS'!$C$55:$E$58</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">RFI!$A$1:$Z$132,RFI!$H$134:$Q$138,RFI!$C$134:$E$139,RFI!$C$141:$E$144</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">RFI!$A$1:$Z$133,RFI!$H$135:$Q$139,RFI!$C$135:$E$140,RFI!$C$142:$E$145</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">RFA!$4:$5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'RFA-SDS'!$4:$5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">RFI!$4:$5</definedName>
@@ -78,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3585" uniqueCount="1117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3593" uniqueCount="1121">
   <si>
     <t>TT</t>
   </si>
@@ -5171,9 +5171,6 @@
     <t>Yêu cầu phê duyệt thiết kế thi công hệ thống thu phí không dừng</t>
   </si>
   <si>
-    <t>10/22/2026 Update</t>
-  </si>
-  <si>
     <t>LTIA-5.10-VIETUR-70000-RFI-1015</t>
   </si>
   <si>
@@ -5214,6 +5211,21 @@
   </si>
   <si>
     <t>18/6/2026 Đã ký RFCS</t>
+  </si>
+  <si>
+    <t>LTIA-5.11-LTICT-70000 -RFI-0040</t>
+  </si>
+  <si>
+    <t>Proposal for the Design of the Passenger Flow Information Display System (55-inch Digital Signage Displays Integrated with the MagicINFO Centralized Management Platform) at the Immigration Control Areas on Level 1 (Arrivals) and Level 3 (Departures)</t>
+  </si>
+  <si>
+    <t>Đề xuất phương án thiết kế thống hiển thị thông tin phân luồng hành khách (màn hình Digital Signage 55 inch kết hợp nền tảng quản lý tập trung MagicINFO) tại khu vực kiểm soát xuất nhập cảnh tầng 1 (nhập cảnh) và tầng 3 (xuất cảnh)</t>
+  </si>
+  <si>
+    <t>10/23/2026: Đã comment</t>
+  </si>
+  <si>
+    <t>10/22/2026: Update</t>
   </si>
 </sst>
 </file>
@@ -7650,290 +7662,290 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="51" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="52" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="55" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="55" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="45" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="53" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="47" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="51" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="52" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="45" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="55" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="55" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -8596,92 +8608,92 @@
       <c r="AE3" s="159"/>
     </row>
     <row r="4" spans="1:35" s="5" customFormat="1" ht="36" customHeight="1" thickBot="1">
-      <c r="A4" s="426" t="s">
+      <c r="A4" s="397" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="348" t="s">
+      <c r="B4" s="407" t="s">
         <v>515</v>
       </c>
-      <c r="C4" s="391" t="s">
+      <c r="C4" s="403" t="s">
         <v>45</v>
       </c>
-      <c r="D4" s="385" t="s">
+      <c r="D4" s="364" t="s">
         <v>95</v>
       </c>
-      <c r="E4" s="352" t="s">
+      <c r="E4" s="362" t="s">
         <v>46</v>
       </c>
-      <c r="F4" s="430" t="s">
+      <c r="F4" s="399" t="s">
         <v>47</v>
       </c>
-      <c r="G4" s="352" t="s">
+      <c r="G4" s="362" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="428" t="s">
+      <c r="H4" s="401" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="385" t="s">
+      <c r="I4" s="364" t="s">
         <v>48</v>
       </c>
-      <c r="J4" s="385" t="s">
+      <c r="J4" s="364" t="s">
         <v>49</v>
       </c>
-      <c r="K4" s="352" t="s">
+      <c r="K4" s="362" t="s">
         <v>78</v>
       </c>
-      <c r="L4" s="385" t="s">
+      <c r="L4" s="364" t="s">
         <v>80</v>
       </c>
-      <c r="M4" s="390" t="s">
+      <c r="M4" s="366" t="s">
         <v>53</v>
       </c>
-      <c r="N4" s="379"/>
-      <c r="O4" s="390" t="s">
+      <c r="N4" s="367"/>
+      <c r="O4" s="366" t="s">
         <v>55</v>
       </c>
-      <c r="P4" s="379"/>
-      <c r="Q4" s="389" t="s">
+      <c r="P4" s="367"/>
+      <c r="Q4" s="368" t="s">
         <v>72</v>
       </c>
-      <c r="R4" s="379"/>
-      <c r="S4" s="390" t="s">
+      <c r="R4" s="367"/>
+      <c r="S4" s="366" t="s">
         <v>53</v>
       </c>
-      <c r="T4" s="390"/>
-      <c r="U4" s="379"/>
-      <c r="V4" s="389" t="s">
+      <c r="T4" s="366"/>
+      <c r="U4" s="367"/>
+      <c r="V4" s="368" t="s">
         <v>55</v>
       </c>
-      <c r="W4" s="390"/>
-      <c r="X4" s="379"/>
+      <c r="W4" s="366"/>
+      <c r="X4" s="367"/>
       <c r="Y4" s="393" t="s">
         <v>72</v>
       </c>
-      <c r="Z4" s="394"/>
-      <c r="AA4" s="397" t="s">
+      <c r="Z4" s="427"/>
+      <c r="AA4" s="426" t="s">
         <v>112</v>
       </c>
-      <c r="AB4" s="398"/>
-      <c r="AC4" s="398"/>
-      <c r="AD4" s="399"/>
-      <c r="AE4" s="352" t="s">
+      <c r="AB4" s="395"/>
+      <c r="AC4" s="395"/>
+      <c r="AD4" s="396"/>
+      <c r="AE4" s="362" t="s">
         <v>79</v>
       </c>
       <c r="AG4" s="236"/>
     </row>
     <row r="5" spans="1:35" ht="78.75">
-      <c r="A5" s="427"/>
-      <c r="B5" s="349"/>
-      <c r="C5" s="392"/>
-      <c r="D5" s="386"/>
-      <c r="E5" s="353"/>
-      <c r="F5" s="431"/>
-      <c r="G5" s="353"/>
-      <c r="H5" s="429"/>
-      <c r="I5" s="386"/>
-      <c r="J5" s="386"/>
-      <c r="K5" s="353"/>
-      <c r="L5" s="386"/>
+      <c r="A5" s="398"/>
+      <c r="B5" s="408"/>
+      <c r="C5" s="404"/>
+      <c r="D5" s="365"/>
+      <c r="E5" s="369"/>
+      <c r="F5" s="400"/>
+      <c r="G5" s="369"/>
+      <c r="H5" s="402"/>
+      <c r="I5" s="365"/>
+      <c r="J5" s="365"/>
+      <c r="K5" s="369"/>
+      <c r="L5" s="365"/>
       <c r="M5" s="79" t="s">
         <v>52</v>
       </c>
@@ -8736,14 +8748,14 @@
       <c r="AD5" s="336" t="s">
         <v>118</v>
       </c>
-      <c r="AE5" s="380"/>
-      <c r="AG5" s="352" t="s">
+      <c r="AE5" s="363"/>
+      <c r="AG5" s="362" t="s">
         <v>119</v>
       </c>
-      <c r="AH5" s="352" t="s">
+      <c r="AH5" s="362" t="s">
         <v>120</v>
       </c>
-      <c r="AI5" s="352" t="s">
+      <c r="AI5" s="362" t="s">
         <v>121</v>
       </c>
     </row>
@@ -8779,9 +8791,9 @@
       <c r="AC6" s="86"/>
       <c r="AD6" s="86"/>
       <c r="AE6" s="74"/>
-      <c r="AG6" s="425"/>
-      <c r="AH6" s="425"/>
-      <c r="AI6" s="425"/>
+      <c r="AG6" s="409"/>
+      <c r="AH6" s="409"/>
+      <c r="AI6" s="409"/>
     </row>
     <row r="7" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A7" s="33">
@@ -21099,7 +21111,7 @@
         <v/>
       </c>
       <c r="AE115" s="92" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="AG115" s="238" t="str">
         <f t="shared" si="14"/>
@@ -21957,7 +21969,7 @@
         <v>30</v>
       </c>
       <c r="E124" s="25" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="F124" s="174">
         <f t="shared" si="29"/>
@@ -22431,7 +22443,7 @@
       <c r="AC128" s="229"/>
       <c r="AD128" s="337"/>
       <c r="AE128" s="92" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="AG128" s="238" t="str">
         <f t="shared" si="75"/>
@@ -22525,7 +22537,7 @@
       <c r="AC129" s="229"/>
       <c r="AD129" s="337"/>
       <c r="AE129" s="92" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="AG129" s="238" t="str">
         <f t="shared" si="75"/>
@@ -22619,7 +22631,7 @@
       <c r="AC130" s="229"/>
       <c r="AD130" s="337"/>
       <c r="AE130" s="92" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="AG130" s="238" t="str">
         <f t="shared" si="75"/>
@@ -22913,7 +22925,7 @@
       <c r="AC133" s="229"/>
       <c r="AD133" s="337"/>
       <c r="AE133" s="92" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="AG133" s="238" t="str">
         <f t="shared" si="75"/>
@@ -23007,7 +23019,7 @@
       <c r="AC134" s="229"/>
       <c r="AD134" s="337"/>
       <c r="AE134" s="92" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="AG134" s="238" t="str">
         <f t="shared" si="75"/>
@@ -23748,29 +23760,29 @@
       <c r="C145" s="166" t="s">
         <v>20</v>
       </c>
-      <c r="D145" s="403" t="s">
+      <c r="D145" s="405" t="s">
         <v>21</v>
       </c>
-      <c r="E145" s="403"/>
-      <c r="F145" s="404"/>
+      <c r="E145" s="405"/>
+      <c r="F145" s="406"/>
       <c r="G145" s="46"/>
       <c r="H145" s="68"/>
-      <c r="I145" s="356" t="s">
+      <c r="I145" s="357" t="s">
         <v>14</v>
       </c>
-      <c r="J145" s="357"/>
-      <c r="K145" s="357"/>
-      <c r="L145" s="357"/>
-      <c r="M145" s="357"/>
-      <c r="N145" s="358"/>
-      <c r="O145" s="350" t="s">
+      <c r="J145" s="358"/>
+      <c r="K145" s="358"/>
+      <c r="L145" s="358"/>
+      <c r="M145" s="358"/>
+      <c r="N145" s="359"/>
+      <c r="O145" s="360" t="s">
         <v>7</v>
       </c>
-      <c r="P145" s="351"/>
-      <c r="Q145" s="350" t="s">
+      <c r="P145" s="361"/>
+      <c r="Q145" s="360" t="s">
         <v>109</v>
       </c>
-      <c r="R145" s="351"/>
+      <c r="R145" s="361"/>
       <c r="S145" s="1"/>
       <c r="T145" s="1"/>
       <c r="U145" s="140"/>
@@ -23792,19 +23804,19 @@
       <c r="C146" s="167" t="s">
         <v>109</v>
       </c>
-      <c r="D146" s="395" t="s">
+      <c r="D146" s="424" t="s">
         <v>111</v>
       </c>
-      <c r="E146" s="395"/>
-      <c r="F146" s="396"/>
+      <c r="E146" s="424"/>
+      <c r="F146" s="425"/>
       <c r="G146" s="46"/>
       <c r="H146" s="46"/>
-      <c r="I146" s="356" t="s">
+      <c r="I146" s="357" t="s">
         <v>19</v>
       </c>
-      <c r="J146" s="357"/>
-      <c r="K146" s="357"/>
-      <c r="L146" s="358"/>
+      <c r="J146" s="358"/>
+      <c r="K146" s="358"/>
+      <c r="L146" s="359"/>
       <c r="M146" s="105">
         <f t="shared" ref="M146:M151" ca="1" si="89">N146/$N$146</f>
         <v>1</v>
@@ -23848,19 +23860,19 @@
       <c r="C147" s="167" t="s">
         <v>22</v>
       </c>
-      <c r="D147" s="395" t="s">
+      <c r="D147" s="424" t="s">
         <v>23</v>
       </c>
-      <c r="E147" s="395"/>
-      <c r="F147" s="396"/>
+      <c r="E147" s="424"/>
+      <c r="F147" s="425"/>
       <c r="G147" s="70"/>
       <c r="H147" s="6"/>
-      <c r="I147" s="405" t="s">
+      <c r="I147" s="373" t="s">
         <v>66</v>
       </c>
-      <c r="J147" s="406"/>
-      <c r="K147" s="406"/>
-      <c r="L147" s="407"/>
+      <c r="J147" s="374"/>
+      <c r="K147" s="374"/>
+      <c r="L147" s="375"/>
       <c r="M147" s="107">
         <f t="shared" ca="1" si="89"/>
         <v>0.47916666666666669</v>
@@ -23906,18 +23918,18 @@
       <c r="C148" s="167" t="s">
         <v>24</v>
       </c>
-      <c r="D148" s="395" t="s">
+      <c r="D148" s="424" t="s">
         <v>25</v>
       </c>
-      <c r="E148" s="395"/>
-      <c r="F148" s="396"/>
+      <c r="E148" s="424"/>
+      <c r="F148" s="425"/>
       <c r="H148" s="6"/>
-      <c r="I148" s="408" t="s">
+      <c r="I148" s="376" t="s">
         <v>67</v>
       </c>
-      <c r="J148" s="409"/>
-      <c r="K148" s="409"/>
-      <c r="L148" s="410"/>
+      <c r="J148" s="377"/>
+      <c r="K148" s="377"/>
+      <c r="L148" s="378"/>
       <c r="M148" s="109">
         <f t="shared" ca="1" si="89"/>
         <v>9.7222222222222224E-2</v>
@@ -23963,19 +23975,19 @@
       <c r="C149" s="167" t="s">
         <v>26</v>
       </c>
-      <c r="D149" s="395" t="s">
+      <c r="D149" s="424" t="s">
         <v>27</v>
       </c>
-      <c r="E149" s="395"/>
-      <c r="F149" s="396"/>
+      <c r="E149" s="424"/>
+      <c r="F149" s="425"/>
       <c r="G149" s="71"/>
       <c r="H149" s="6"/>
-      <c r="I149" s="411" t="s">
+      <c r="I149" s="379" t="s">
         <v>68</v>
       </c>
-      <c r="J149" s="412"/>
-      <c r="K149" s="412"/>
-      <c r="L149" s="413"/>
+      <c r="J149" s="380"/>
+      <c r="K149" s="380"/>
+      <c r="L149" s="381"/>
       <c r="M149" s="111">
         <f t="shared" ca="1" si="89"/>
         <v>0.22916666666666666</v>
@@ -24021,18 +24033,18 @@
       <c r="C150" s="168" t="s">
         <v>28</v>
       </c>
-      <c r="D150" s="395" t="s">
+      <c r="D150" s="424" t="s">
         <v>29</v>
       </c>
-      <c r="E150" s="395"/>
-      <c r="F150" s="396"/>
+      <c r="E150" s="424"/>
+      <c r="F150" s="425"/>
       <c r="G150" s="72"/>
-      <c r="I150" s="365" t="s">
+      <c r="I150" s="382" t="s">
         <v>70</v>
       </c>
-      <c r="J150" s="366"/>
-      <c r="K150" s="366"/>
-      <c r="L150" s="367"/>
+      <c r="J150" s="383"/>
+      <c r="K150" s="383"/>
+      <c r="L150" s="384"/>
       <c r="M150" s="114">
         <f t="shared" ca="1" si="89"/>
         <v>8.3333333333333329E-2</v>
@@ -24080,18 +24092,18 @@
       <c r="C151" s="168" t="s">
         <v>30</v>
       </c>
-      <c r="D151" s="395" t="s">
+      <c r="D151" s="424" t="s">
         <v>31</v>
       </c>
-      <c r="E151" s="395"/>
-      <c r="F151" s="396"/>
+      <c r="E151" s="424"/>
+      <c r="F151" s="425"/>
       <c r="H151" s="6"/>
-      <c r="I151" s="368" t="s">
+      <c r="I151" s="354" t="s">
         <v>71</v>
       </c>
-      <c r="J151" s="369"/>
-      <c r="K151" s="369"/>
-      <c r="L151" s="370"/>
+      <c r="J151" s="355"/>
+      <c r="K151" s="355"/>
+      <c r="L151" s="356"/>
       <c r="M151" s="113">
         <f t="shared" ca="1" si="89"/>
         <v>0.1111111111111111</v>
@@ -24111,11 +24123,11 @@
       <c r="C152" s="168" t="s">
         <v>32</v>
       </c>
-      <c r="D152" s="395" t="s">
+      <c r="D152" s="424" t="s">
         <v>33</v>
       </c>
-      <c r="E152" s="395"/>
-      <c r="F152" s="396"/>
+      <c r="E152" s="424"/>
+      <c r="F152" s="425"/>
       <c r="H152" s="1" t="s">
         <v>11</v>
       </c>
@@ -24124,11 +24136,11 @@
       <c r="C153" s="167" t="s">
         <v>34</v>
       </c>
-      <c r="D153" s="395" t="s">
+      <c r="D153" s="424" t="s">
         <v>35</v>
       </c>
-      <c r="E153" s="395"/>
-      <c r="F153" s="396"/>
+      <c r="E153" s="424"/>
+      <c r="F153" s="425"/>
       <c r="H153" s="13"/>
       <c r="I153" s="141"/>
       <c r="J153" s="141"/>
@@ -24156,14 +24168,14 @@
       <c r="AI153" s="1"/>
     </row>
     <row r="154" spans="1:35">
-      <c r="C154" s="373" t="s">
+      <c r="C154" s="385" t="s">
         <v>75</v>
       </c>
-      <c r="D154" s="375" t="s">
+      <c r="D154" s="387" t="s">
         <v>76</v>
       </c>
-      <c r="E154" s="375"/>
-      <c r="F154" s="376"/>
+      <c r="E154" s="387"/>
+      <c r="F154" s="388"/>
       <c r="H154" s="13"/>
       <c r="J154" s="141"/>
       <c r="K154" s="13"/>
@@ -24190,10 +24202,10 @@
       <c r="AI154" s="1"/>
     </row>
     <row r="155" spans="1:35" ht="16.5" thickBot="1">
-      <c r="C155" s="374"/>
-      <c r="D155" s="377"/>
-      <c r="E155" s="377"/>
-      <c r="F155" s="378"/>
+      <c r="C155" s="386"/>
+      <c r="D155" s="389"/>
+      <c r="E155" s="389"/>
+      <c r="F155" s="390"/>
       <c r="H155" s="13"/>
       <c r="I155" s="141"/>
       <c r="J155" s="141"/>
@@ -24248,12 +24260,12 @@
       <c r="AI156" s="1"/>
     </row>
     <row r="157" spans="1:35">
-      <c r="C157" s="361" t="s">
+      <c r="C157" s="372" t="s">
         <v>41</v>
       </c>
-      <c r="D157" s="361"/>
-      <c r="E157" s="361"/>
-      <c r="F157" s="361"/>
+      <c r="D157" s="372"/>
+      <c r="E157" s="372"/>
+      <c r="F157" s="372"/>
       <c r="H157" s="13"/>
       <c r="I157" s="141"/>
       <c r="J157" s="141"/>
@@ -24284,11 +24296,11 @@
       <c r="C158" s="169" t="s">
         <v>8</v>
       </c>
-      <c r="D158" s="414" t="s">
+      <c r="D158" s="412" t="s">
         <v>91</v>
       </c>
-      <c r="E158" s="414"/>
-      <c r="F158" s="414"/>
+      <c r="E158" s="412"/>
+      <c r="F158" s="412"/>
       <c r="H158" s="13"/>
       <c r="I158" s="141"/>
       <c r="J158" s="141"/>
@@ -24319,11 +24331,11 @@
       <c r="C159" s="169" t="s">
         <v>8</v>
       </c>
-      <c r="D159" s="414" t="s">
+      <c r="D159" s="412" t="s">
         <v>92</v>
       </c>
-      <c r="E159" s="414"/>
-      <c r="F159" s="414"/>
+      <c r="E159" s="412"/>
+      <c r="F159" s="412"/>
       <c r="H159" s="13"/>
       <c r="I159" s="141"/>
       <c r="J159" s="141"/>
@@ -24354,11 +24366,11 @@
       <c r="C160" s="169" t="s">
         <v>8</v>
       </c>
-      <c r="D160" s="414" t="s">
+      <c r="D160" s="412" t="s">
         <v>93</v>
       </c>
-      <c r="E160" s="414"/>
-      <c r="F160" s="414"/>
+      <c r="E160" s="412"/>
+      <c r="F160" s="412"/>
       <c r="H160" s="13"/>
       <c r="I160" s="141"/>
       <c r="J160" s="141"/>
@@ -24413,12 +24425,12 @@
       <c r="AI161" s="1"/>
     </row>
     <row r="162" spans="3:35" ht="16.5" thickBot="1">
-      <c r="C162" s="420" t="s">
+      <c r="C162" s="416" t="s">
         <v>96</v>
       </c>
-      <c r="D162" s="421"/>
-      <c r="E162" s="421"/>
-      <c r="F162" s="422"/>
+      <c r="D162" s="417"/>
+      <c r="E162" s="417"/>
+      <c r="F162" s="418"/>
       <c r="H162" s="13"/>
       <c r="I162" s="141"/>
       <c r="J162" s="141"/>
@@ -24449,11 +24461,11 @@
       <c r="C163" s="212" t="s">
         <v>81</v>
       </c>
-      <c r="D163" s="423" t="s">
+      <c r="D163" s="419" t="s">
         <v>97</v>
       </c>
-      <c r="E163" s="423"/>
-      <c r="F163" s="424"/>
+      <c r="E163" s="419"/>
+      <c r="F163" s="420"/>
       <c r="H163" s="13"/>
       <c r="I163" s="141"/>
       <c r="J163" s="141"/>
@@ -24484,101 +24496,101 @@
       <c r="C164" s="213" t="s">
         <v>82</v>
       </c>
-      <c r="D164" s="415" t="s">
+      <c r="D164" s="410" t="s">
         <v>98</v>
       </c>
-      <c r="E164" s="415"/>
-      <c r="F164" s="416"/>
+      <c r="E164" s="410"/>
+      <c r="F164" s="411"/>
     </row>
     <row r="165" spans="3:35">
       <c r="C165" s="213" t="s">
         <v>83</v>
       </c>
-      <c r="D165" s="415" t="s">
+      <c r="D165" s="410" t="s">
         <v>99</v>
       </c>
-      <c r="E165" s="415"/>
-      <c r="F165" s="416"/>
+      <c r="E165" s="410"/>
+      <c r="F165" s="411"/>
     </row>
     <row r="166" spans="3:35">
       <c r="C166" s="214" t="s">
         <v>84</v>
       </c>
-      <c r="D166" s="415" t="s">
+      <c r="D166" s="410" t="s">
         <v>100</v>
       </c>
-      <c r="E166" s="415"/>
-      <c r="F166" s="416"/>
+      <c r="E166" s="410"/>
+      <c r="F166" s="411"/>
     </row>
     <row r="167" spans="3:35">
       <c r="C167" s="214" t="s">
         <v>85</v>
       </c>
-      <c r="D167" s="415" t="s">
+      <c r="D167" s="410" t="s">
         <v>101</v>
       </c>
-      <c r="E167" s="415"/>
-      <c r="F167" s="416"/>
+      <c r="E167" s="410"/>
+      <c r="F167" s="411"/>
     </row>
     <row r="168" spans="3:35" ht="18.75">
       <c r="C168" s="214" t="s">
         <v>86</v>
       </c>
-      <c r="D168" s="415" t="s">
+      <c r="D168" s="410" t="s">
         <v>102</v>
       </c>
-      <c r="E168" s="415"/>
-      <c r="F168" s="416"/>
+      <c r="E168" s="410"/>
+      <c r="F168" s="411"/>
     </row>
     <row r="169" spans="3:35" ht="18.75">
       <c r="C169" s="213" t="s">
         <v>87</v>
       </c>
-      <c r="D169" s="415" t="s">
+      <c r="D169" s="410" t="s">
         <v>103</v>
       </c>
-      <c r="E169" s="415"/>
-      <c r="F169" s="416"/>
+      <c r="E169" s="410"/>
+      <c r="F169" s="411"/>
     </row>
     <row r="170" spans="3:35">
       <c r="C170" s="215" t="s">
         <v>88</v>
       </c>
-      <c r="D170" s="417" t="s">
+      <c r="D170" s="413" t="s">
         <v>104</v>
       </c>
-      <c r="E170" s="418"/>
-      <c r="F170" s="419"/>
+      <c r="E170" s="414"/>
+      <c r="F170" s="415"/>
     </row>
     <row r="171" spans="3:35" ht="18.75">
       <c r="C171" s="215" t="s">
         <v>89</v>
       </c>
-      <c r="D171" s="415" t="s">
+      <c r="D171" s="410" t="s">
         <v>105</v>
       </c>
-      <c r="E171" s="415"/>
-      <c r="F171" s="416"/>
+      <c r="E171" s="410"/>
+      <c r="F171" s="411"/>
     </row>
     <row r="172" spans="3:35">
       <c r="C172" s="213" t="s">
         <v>90</v>
       </c>
-      <c r="D172" s="415" t="s">
+      <c r="D172" s="410" t="s">
         <v>106</v>
       </c>
-      <c r="E172" s="415"/>
-      <c r="F172" s="416"/>
+      <c r="E172" s="410"/>
+      <c r="F172" s="411"/>
     </row>
     <row r="173" spans="3:35" ht="16.5" thickBot="1">
       <c r="C173" s="216" t="s">
         <v>94</v>
       </c>
-      <c r="D173" s="400" t="s">
+      <c r="D173" s="421" t="s">
         <v>107</v>
       </c>
-      <c r="E173" s="401"/>
-      <c r="F173" s="402"/>
+      <c r="E173" s="422"/>
+      <c r="F173" s="423"/>
     </row>
   </sheetData>
   <autoFilter ref="A6:AE143" xr:uid="{C724CDAB-378C-47DB-9F45-08EE3BFB6E8B}">
@@ -24587,6 +24599,49 @@
     </sortState>
   </autoFilter>
   <mergeCells count="59">
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="D154:F155"/>
+    <mergeCell ref="D146:F146"/>
+    <mergeCell ref="I146:L146"/>
+    <mergeCell ref="AA4:AD4"/>
+    <mergeCell ref="Q145:R145"/>
+    <mergeCell ref="D151:F151"/>
+    <mergeCell ref="D152:F152"/>
+    <mergeCell ref="D153:F153"/>
+    <mergeCell ref="S4:U4"/>
+    <mergeCell ref="L4:L5"/>
+    <mergeCell ref="Q4:R4"/>
+    <mergeCell ref="K4:K5"/>
+    <mergeCell ref="Y4:Z4"/>
+    <mergeCell ref="D173:F173"/>
+    <mergeCell ref="D145:F145"/>
+    <mergeCell ref="C157:F157"/>
+    <mergeCell ref="O145:P145"/>
+    <mergeCell ref="I145:N145"/>
+    <mergeCell ref="I147:L147"/>
+    <mergeCell ref="I148:L148"/>
+    <mergeCell ref="I149:L149"/>
+    <mergeCell ref="I150:L150"/>
+    <mergeCell ref="I151:L151"/>
+    <mergeCell ref="C154:C155"/>
+    <mergeCell ref="D147:F147"/>
+    <mergeCell ref="D148:F148"/>
+    <mergeCell ref="D149:F149"/>
+    <mergeCell ref="D150:F150"/>
+    <mergeCell ref="D158:F158"/>
+    <mergeCell ref="D172:F172"/>
+    <mergeCell ref="D159:F159"/>
+    <mergeCell ref="D160:F160"/>
+    <mergeCell ref="D167:F167"/>
+    <mergeCell ref="D168:F168"/>
+    <mergeCell ref="D169:F169"/>
+    <mergeCell ref="D170:F170"/>
+    <mergeCell ref="D171:F171"/>
+    <mergeCell ref="C162:F162"/>
+    <mergeCell ref="D163:F163"/>
+    <mergeCell ref="D164:F164"/>
+    <mergeCell ref="D165:F165"/>
+    <mergeCell ref="D166:F166"/>
     <mergeCell ref="AG5:AG6"/>
     <mergeCell ref="AH5:AH6"/>
     <mergeCell ref="AI5:AI6"/>
@@ -24603,49 +24658,6 @@
     <mergeCell ref="V4:X4"/>
     <mergeCell ref="M4:N4"/>
     <mergeCell ref="O4:P4"/>
-    <mergeCell ref="D172:F172"/>
-    <mergeCell ref="D159:F159"/>
-    <mergeCell ref="D160:F160"/>
-    <mergeCell ref="D167:F167"/>
-    <mergeCell ref="D168:F168"/>
-    <mergeCell ref="D169:F169"/>
-    <mergeCell ref="D170:F170"/>
-    <mergeCell ref="D171:F171"/>
-    <mergeCell ref="C162:F162"/>
-    <mergeCell ref="D163:F163"/>
-    <mergeCell ref="D164:F164"/>
-    <mergeCell ref="D165:F165"/>
-    <mergeCell ref="D166:F166"/>
-    <mergeCell ref="D173:F173"/>
-    <mergeCell ref="D145:F145"/>
-    <mergeCell ref="C157:F157"/>
-    <mergeCell ref="O145:P145"/>
-    <mergeCell ref="I145:N145"/>
-    <mergeCell ref="I147:L147"/>
-    <mergeCell ref="I148:L148"/>
-    <mergeCell ref="I149:L149"/>
-    <mergeCell ref="I150:L150"/>
-    <mergeCell ref="I151:L151"/>
-    <mergeCell ref="C154:C155"/>
-    <mergeCell ref="D147:F147"/>
-    <mergeCell ref="D148:F148"/>
-    <mergeCell ref="D149:F149"/>
-    <mergeCell ref="D150:F150"/>
-    <mergeCell ref="D158:F158"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="D154:F155"/>
-    <mergeCell ref="D146:F146"/>
-    <mergeCell ref="I146:L146"/>
-    <mergeCell ref="AA4:AD4"/>
-    <mergeCell ref="Q145:R145"/>
-    <mergeCell ref="D151:F151"/>
-    <mergeCell ref="D152:F152"/>
-    <mergeCell ref="D153:F153"/>
-    <mergeCell ref="S4:U4"/>
-    <mergeCell ref="L4:L5"/>
-    <mergeCell ref="Q4:R4"/>
-    <mergeCell ref="K4:K5"/>
-    <mergeCell ref="Y4:Z4"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="A7:AE143 AG7:AI143">
@@ -25329,88 +25341,88 @@
       <c r="AD3" s="159"/>
     </row>
     <row r="4" spans="1:35" s="5" customFormat="1" ht="36" customHeight="1" thickBot="1">
-      <c r="A4" s="426" t="s">
+      <c r="A4" s="397" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="348" t="s">
+      <c r="B4" s="407" t="s">
         <v>515</v>
       </c>
-      <c r="C4" s="391" t="s">
+      <c r="C4" s="403" t="s">
         <v>45</v>
       </c>
-      <c r="D4" s="352" t="s">
+      <c r="D4" s="362" t="s">
         <v>46</v>
       </c>
-      <c r="E4" s="430" t="s">
+      <c r="E4" s="399" t="s">
         <v>47</v>
       </c>
-      <c r="F4" s="352" t="s">
+      <c r="F4" s="362" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="428" t="s">
+      <c r="G4" s="401" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="385" t="s">
+      <c r="H4" s="364" t="s">
         <v>48</v>
       </c>
-      <c r="I4" s="385" t="s">
+      <c r="I4" s="364" t="s">
         <v>49</v>
       </c>
-      <c r="J4" s="352" t="s">
+      <c r="J4" s="362" t="s">
         <v>78</v>
       </c>
-      <c r="K4" s="385" t="s">
+      <c r="K4" s="364" t="s">
         <v>80</v>
       </c>
-      <c r="L4" s="390" t="s">
+      <c r="L4" s="366" t="s">
         <v>53</v>
       </c>
-      <c r="M4" s="379"/>
-      <c r="N4" s="389" t="s">
+      <c r="M4" s="367"/>
+      <c r="N4" s="368" t="s">
         <v>55</v>
       </c>
-      <c r="O4" s="379"/>
-      <c r="P4" s="389" t="s">
+      <c r="O4" s="367"/>
+      <c r="P4" s="368" t="s">
         <v>72</v>
       </c>
-      <c r="Q4" s="379"/>
-      <c r="R4" s="390" t="s">
+      <c r="Q4" s="367"/>
+      <c r="R4" s="366" t="s">
         <v>53</v>
       </c>
-      <c r="S4" s="390"/>
-      <c r="T4" s="379"/>
-      <c r="U4" s="389" t="s">
+      <c r="S4" s="366"/>
+      <c r="T4" s="367"/>
+      <c r="U4" s="368" t="s">
         <v>55</v>
       </c>
-      <c r="V4" s="390"/>
-      <c r="W4" s="379"/>
+      <c r="V4" s="366"/>
+      <c r="W4" s="367"/>
       <c r="X4" s="393" t="s">
         <v>72</v>
       </c>
-      <c r="Y4" s="432"/>
+      <c r="Y4" s="394"/>
       <c r="Z4" s="393" t="s">
         <v>112</v>
       </c>
-      <c r="AA4" s="398"/>
-      <c r="AB4" s="398"/>
-      <c r="AC4" s="399"/>
-      <c r="AD4" s="352" t="s">
+      <c r="AA4" s="395"/>
+      <c r="AB4" s="395"/>
+      <c r="AC4" s="396"/>
+      <c r="AD4" s="362" t="s">
         <v>79</v>
       </c>
       <c r="AG4" s="236"/>
     </row>
     <row r="5" spans="1:35" ht="78.75">
-      <c r="A5" s="427"/>
-      <c r="B5" s="349"/>
-      <c r="C5" s="392"/>
-      <c r="D5" s="353"/>
-      <c r="E5" s="431"/>
-      <c r="F5" s="353"/>
-      <c r="G5" s="429"/>
-      <c r="H5" s="386"/>
-      <c r="I5" s="386"/>
-      <c r="J5" s="353"/>
-      <c r="K5" s="386"/>
+      <c r="A5" s="398"/>
+      <c r="B5" s="408"/>
+      <c r="C5" s="404"/>
+      <c r="D5" s="369"/>
+      <c r="E5" s="400"/>
+      <c r="F5" s="369"/>
+      <c r="G5" s="402"/>
+      <c r="H5" s="365"/>
+      <c r="I5" s="365"/>
+      <c r="J5" s="369"/>
+      <c r="K5" s="365"/>
       <c r="L5" s="79" t="s">
         <v>52</v>
       </c>
@@ -25465,14 +25477,14 @@
       <c r="AC5" s="250" t="s">
         <v>118</v>
       </c>
-      <c r="AD5" s="380"/>
-      <c r="AG5" s="437" t="s">
+      <c r="AD5" s="363"/>
+      <c r="AG5" s="348" t="s">
         <v>119</v>
       </c>
-      <c r="AH5" s="439" t="s">
+      <c r="AH5" s="350" t="s">
         <v>120</v>
       </c>
-      <c r="AI5" s="441" t="s">
+      <c r="AI5" s="352" t="s">
         <v>121</v>
       </c>
     </row>
@@ -25507,9 +25519,9 @@
       <c r="AB6" s="86"/>
       <c r="AC6" s="86"/>
       <c r="AD6" s="74"/>
-      <c r="AG6" s="438"/>
-      <c r="AH6" s="440"/>
-      <c r="AI6" s="442"/>
+      <c r="AG6" s="349"/>
+      <c r="AH6" s="351"/>
+      <c r="AI6" s="353"/>
     </row>
     <row r="7" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A7" s="33">
@@ -26660,7 +26672,7 @@
         <v>YES</v>
       </c>
     </row>
-    <row r="17" spans="1:35" s="9" customFormat="1" ht="110.25">
+    <row r="17" spans="1:35" s="9" customFormat="1" ht="94.5">
       <c r="A17" s="33">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -29250,7 +29262,9 @@
         <f t="shared" ref="AC40" si="23">IF(AB40="Late Resubmission",IF(AA40="","",AA40-Z40),IF(AB40="Not submit yet",IF(Z40="","",$I$1-Z40),""))</f>
         <v/>
       </c>
-      <c r="AD40" s="92"/>
+      <c r="AD40" s="92" t="s">
+        <v>1119</v>
+      </c>
       <c r="AG40" s="238" t="str">
         <f t="shared" si="8"/>
         <v>LTIA-5.10-VIETUR-80000-RFA-SDS-0493</v>
@@ -29339,7 +29353,9 @@
         <f t="shared" ref="AC41" si="25">IF(AB41="Late Resubmission",IF(AA41="","",AA41-Z41),IF(AB41="Not submit yet",IF(Z41="","",$I$1-Z41),""))</f>
         <v/>
       </c>
-      <c r="AD41" s="92"/>
+      <c r="AD41" s="92" t="s">
+        <v>1119</v>
+      </c>
       <c r="AG41" s="238" t="str">
         <f t="shared" si="8"/>
         <v>LTIA-5.10-VIETUR-80000-RFA-SDS-0222</v>
@@ -29429,7 +29445,7 @@
         <v/>
       </c>
       <c r="AD42" s="92" t="s">
-        <v>1105</v>
+        <v>1120</v>
       </c>
       <c r="AG42" s="238" t="str">
         <f t="shared" si="8"/>
@@ -29801,28 +29817,28 @@
       <c r="C49" s="166" t="s">
         <v>20</v>
       </c>
-      <c r="D49" s="403" t="s">
+      <c r="D49" s="405" t="s">
         <v>21</v>
       </c>
-      <c r="E49" s="404"/>
+      <c r="E49" s="406"/>
       <c r="F49" s="46"/>
       <c r="G49" s="46"/>
-      <c r="H49" s="356" t="s">
+      <c r="H49" s="357" t="s">
         <v>14</v>
       </c>
-      <c r="I49" s="357"/>
-      <c r="J49" s="357"/>
-      <c r="K49" s="357"/>
-      <c r="L49" s="357"/>
-      <c r="M49" s="358"/>
-      <c r="N49" s="350" t="s">
+      <c r="I49" s="358"/>
+      <c r="J49" s="358"/>
+      <c r="K49" s="358"/>
+      <c r="L49" s="358"/>
+      <c r="M49" s="359"/>
+      <c r="N49" s="360" t="s">
         <v>7</v>
       </c>
-      <c r="O49" s="351"/>
-      <c r="P49" s="350" t="s">
+      <c r="O49" s="361"/>
+      <c r="P49" s="360" t="s">
         <v>109</v>
       </c>
-      <c r="Q49" s="351"/>
+      <c r="Q49" s="361"/>
       <c r="R49" s="1"/>
       <c r="S49" s="1"/>
       <c r="T49" s="140"/>
@@ -29842,17 +29858,17 @@
       <c r="C50" s="195" t="s">
         <v>109</v>
       </c>
-      <c r="D50" s="435" t="s">
+      <c r="D50" s="391" t="s">
         <v>111</v>
       </c>
-      <c r="E50" s="436"/>
+      <c r="E50" s="392"/>
       <c r="F50" s="46"/>
-      <c r="H50" s="356" t="s">
+      <c r="H50" s="357" t="s">
         <v>18</v>
       </c>
-      <c r="I50" s="357"/>
-      <c r="J50" s="357"/>
-      <c r="K50" s="358"/>
+      <c r="I50" s="358"/>
+      <c r="J50" s="358"/>
+      <c r="K50" s="359"/>
       <c r="L50" s="105">
         <f ca="1">M50/$M$50</f>
         <v>1</v>
@@ -29894,18 +29910,18 @@
       <c r="C51" s="195" t="s">
         <v>36</v>
       </c>
-      <c r="D51" s="433" t="s">
+      <c r="D51" s="370" t="s">
         <v>37</v>
       </c>
-      <c r="E51" s="434"/>
+      <c r="E51" s="371"/>
       <c r="F51" s="69"/>
       <c r="G51" s="6"/>
-      <c r="H51" s="405" t="s">
+      <c r="H51" s="373" t="s">
         <v>66</v>
       </c>
-      <c r="I51" s="406"/>
-      <c r="J51" s="406"/>
-      <c r="K51" s="407"/>
+      <c r="I51" s="374"/>
+      <c r="J51" s="374"/>
+      <c r="K51" s="375"/>
       <c r="L51" s="107">
         <f ca="1">M51/$M$50</f>
         <v>7.6923076923076927E-2</v>
@@ -29946,21 +29962,21 @@
       <c r="AI51" s="11"/>
     </row>
     <row r="52" spans="3:35">
-      <c r="C52" s="373" t="s">
+      <c r="C52" s="385" t="s">
         <v>75</v>
       </c>
-      <c r="D52" s="375" t="s">
+      <c r="D52" s="387" t="s">
         <v>76</v>
       </c>
-      <c r="E52" s="376"/>
+      <c r="E52" s="388"/>
       <c r="F52" s="70"/>
       <c r="G52" s="6"/>
-      <c r="H52" s="408" t="s">
+      <c r="H52" s="376" t="s">
         <v>67</v>
       </c>
-      <c r="I52" s="409"/>
-      <c r="J52" s="409"/>
-      <c r="K52" s="410"/>
+      <c r="I52" s="377"/>
+      <c r="J52" s="377"/>
+      <c r="K52" s="378"/>
       <c r="L52" s="109">
         <f t="shared" ref="L52:L55" ca="1" si="34">M52/$M$50</f>
         <v>0.51282051282051277</v>
@@ -30001,17 +30017,17 @@
       <c r="AI52" s="11"/>
     </row>
     <row r="53" spans="3:35" ht="16.5" thickBot="1">
-      <c r="C53" s="374"/>
-      <c r="D53" s="377"/>
-      <c r="E53" s="378"/>
+      <c r="C53" s="386"/>
+      <c r="D53" s="389"/>
+      <c r="E53" s="390"/>
       <c r="F53" s="71"/>
       <c r="G53" s="6"/>
-      <c r="H53" s="411" t="s">
+      <c r="H53" s="379" t="s">
         <v>68</v>
       </c>
-      <c r="I53" s="412"/>
-      <c r="J53" s="412"/>
-      <c r="K53" s="413"/>
+      <c r="I53" s="380"/>
+      <c r="J53" s="380"/>
+      <c r="K53" s="381"/>
       <c r="L53" s="111">
         <f t="shared" ca="1" si="34"/>
         <v>0.20512820512820512</v>
@@ -30054,12 +30070,12 @@
     <row r="54" spans="3:35">
       <c r="F54" s="72"/>
       <c r="G54" s="6"/>
-      <c r="H54" s="365" t="s">
+      <c r="H54" s="382" t="s">
         <v>70</v>
       </c>
-      <c r="I54" s="366"/>
-      <c r="J54" s="366"/>
-      <c r="K54" s="367"/>
+      <c r="I54" s="383"/>
+      <c r="J54" s="383"/>
+      <c r="K54" s="384"/>
       <c r="L54" s="114">
         <f t="shared" ca="1" si="34"/>
         <v>0.15384615384615385</v>
@@ -30102,17 +30118,17 @@
       <c r="AI54" s="11"/>
     </row>
     <row r="55" spans="3:35" ht="16.5" thickBot="1">
-      <c r="C55" s="361" t="s">
+      <c r="C55" s="372" t="s">
         <v>41</v>
       </c>
-      <c r="D55" s="361"/>
-      <c r="E55" s="361"/>
-      <c r="H55" s="368" t="s">
+      <c r="D55" s="372"/>
+      <c r="E55" s="372"/>
+      <c r="H55" s="354" t="s">
         <v>71</v>
       </c>
-      <c r="I55" s="369"/>
-      <c r="J55" s="369"/>
-      <c r="K55" s="370"/>
+      <c r="I55" s="355"/>
+      <c r="J55" s="355"/>
+      <c r="K55" s="356"/>
       <c r="L55" s="113">
         <f t="shared" ca="1" si="34"/>
         <v>5.128205128205128E-2</v>
@@ -30157,6 +30173,27 @@
     </sortState>
   </autoFilter>
   <mergeCells count="37">
+    <mergeCell ref="P49:Q49"/>
+    <mergeCell ref="X4:Y4"/>
+    <mergeCell ref="Z4:AC4"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D49:E49"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="D51:E51"/>
+    <mergeCell ref="C55:E55"/>
+    <mergeCell ref="H51:K51"/>
+    <mergeCell ref="H52:K52"/>
+    <mergeCell ref="H49:M49"/>
+    <mergeCell ref="H53:K53"/>
+    <mergeCell ref="H54:K54"/>
+    <mergeCell ref="C52:C53"/>
+    <mergeCell ref="D52:E53"/>
+    <mergeCell ref="D50:E50"/>
     <mergeCell ref="AG5:AG6"/>
     <mergeCell ref="AH5:AH6"/>
     <mergeCell ref="AI5:AI6"/>
@@ -30173,27 +30210,6 @@
     <mergeCell ref="K4:K5"/>
     <mergeCell ref="P4:Q4"/>
     <mergeCell ref="J4:J5"/>
-    <mergeCell ref="D51:E51"/>
-    <mergeCell ref="C55:E55"/>
-    <mergeCell ref="H51:K51"/>
-    <mergeCell ref="H52:K52"/>
-    <mergeCell ref="H49:M49"/>
-    <mergeCell ref="H53:K53"/>
-    <mergeCell ref="H54:K54"/>
-    <mergeCell ref="C52:C53"/>
-    <mergeCell ref="D52:E53"/>
-    <mergeCell ref="D50:E50"/>
-    <mergeCell ref="P49:Q49"/>
-    <mergeCell ref="X4:Y4"/>
-    <mergeCell ref="Z4:AC4"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D49:E49"/>
-    <mergeCell ref="B4:B5"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="A7:AD47 AG7:AI47">
@@ -30379,7 +30395,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C184EF3E-84BF-4DCF-951B-B90EB4B9D23F}">
-  <dimension ref="A1:Z144"/>
+  <dimension ref="A1:Z145"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" customWidth="1"/>
@@ -30489,81 +30505,81 @@
       <c r="Z3" s="159"/>
     </row>
     <row r="4" spans="1:26" s="5" customFormat="1" ht="35.1" customHeight="1" thickBot="1">
-      <c r="A4" s="348" t="s">
+      <c r="A4" s="407" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="348" t="s">
+      <c r="B4" s="407" t="s">
         <v>515</v>
       </c>
-      <c r="C4" s="391" t="s">
+      <c r="C4" s="403" t="s">
         <v>45</v>
       </c>
-      <c r="D4" s="352" t="s">
+      <c r="D4" s="362" t="s">
         <v>46</v>
       </c>
-      <c r="E4" s="381" t="s">
+      <c r="E4" s="428" t="s">
         <v>47</v>
       </c>
-      <c r="F4" s="352" t="s">
+      <c r="F4" s="362" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="383" t="s">
+      <c r="G4" s="430" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="385" t="s">
+      <c r="H4" s="364" t="s">
         <v>48</v>
       </c>
-      <c r="I4" s="387" t="s">
+      <c r="I4" s="432" t="s">
         <v>49</v>
       </c>
-      <c r="J4" s="352" t="s">
+      <c r="J4" s="362" t="s">
         <v>78</v>
       </c>
-      <c r="K4" s="385" t="s">
+      <c r="K4" s="364" t="s">
         <v>80</v>
       </c>
-      <c r="L4" s="389" t="s">
+      <c r="L4" s="368" t="s">
         <v>53</v>
       </c>
-      <c r="M4" s="379"/>
-      <c r="N4" s="389" t="s">
+      <c r="M4" s="367"/>
+      <c r="N4" s="368" t="s">
         <v>55</v>
       </c>
-      <c r="O4" s="379"/>
-      <c r="P4" s="389" t="s">
+      <c r="O4" s="367"/>
+      <c r="P4" s="368" t="s">
         <v>72</v>
       </c>
-      <c r="Q4" s="379"/>
-      <c r="R4" s="390" t="s">
+      <c r="Q4" s="367"/>
+      <c r="R4" s="366" t="s">
         <v>53</v>
       </c>
-      <c r="S4" s="390"/>
-      <c r="T4" s="379"/>
-      <c r="U4" s="389" t="s">
+      <c r="S4" s="366"/>
+      <c r="T4" s="367"/>
+      <c r="U4" s="368" t="s">
         <v>55</v>
       </c>
-      <c r="V4" s="390"/>
-      <c r="W4" s="390"/>
+      <c r="V4" s="366"/>
+      <c r="W4" s="366"/>
       <c r="X4" s="393" t="s">
         <v>72</v>
       </c>
-      <c r="Y4" s="394"/>
-      <c r="Z4" s="379" t="s">
+      <c r="Y4" s="427"/>
+      <c r="Z4" s="367" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="72" customHeight="1">
-      <c r="A5" s="349"/>
-      <c r="B5" s="349"/>
-      <c r="C5" s="392"/>
-      <c r="D5" s="353"/>
-      <c r="E5" s="382"/>
-      <c r="F5" s="353"/>
-      <c r="G5" s="384"/>
-      <c r="H5" s="386"/>
-      <c r="I5" s="388"/>
-      <c r="J5" s="353"/>
-      <c r="K5" s="386"/>
+      <c r="A5" s="408"/>
+      <c r="B5" s="408"/>
+      <c r="C5" s="404"/>
+      <c r="D5" s="369"/>
+      <c r="E5" s="429"/>
+      <c r="F5" s="369"/>
+      <c r="G5" s="431"/>
+      <c r="H5" s="365"/>
+      <c r="I5" s="433"/>
+      <c r="J5" s="369"/>
+      <c r="K5" s="365"/>
       <c r="L5" s="79" t="s">
         <v>52</v>
       </c>
@@ -30606,7 +30622,7 @@
       <c r="Y5" s="260" t="s">
         <v>114</v>
       </c>
-      <c r="Z5" s="380"/>
+      <c r="Z5" s="363"/>
     </row>
     <row r="6" spans="1:26" ht="15" customHeight="1" thickBot="1">
       <c r="A6" s="78"/>
@@ -35850,7 +35866,7 @@
         <v>46206</v>
       </c>
       <c r="Z73" s="92" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="74" spans="1:26" s="9" customFormat="1" ht="63">
@@ -36306,7 +36322,7 @@
         <v>628</v>
       </c>
       <c r="E80" s="174">
-        <f t="shared" ref="E80:E130" si="23">IF($T80=0,$S80+22,$T80+21)</f>
+        <f t="shared" ref="E80:E131" si="23">IF($T80=0,$S80+22,$T80+21)</f>
         <v>45945</v>
       </c>
       <c r="F80" s="31" t="s">
@@ -36319,11 +36335,11 @@
         <v>6</v>
       </c>
       <c r="I80" s="164">
-        <f t="shared" ref="I80:I130" si="24">IF(ISBLANK($V80),_xlfn.DAYS($I$1,$T80),_xlfn.DAYS($V80,$T80))</f>
+        <f t="shared" ref="I80:I131" si="24">IF(ISBLANK($V80),_xlfn.DAYS($I$1,$T80),_xlfn.DAYS($V80,$T80))</f>
         <v>6</v>
       </c>
       <c r="J80" s="47">
-        <f t="shared" ref="J80:J130" si="25">IF(($I80-21)&gt;0,$I80-21,0)</f>
+        <f t="shared" ref="J80:J131" si="25">IF(($I80-21)&gt;0,$I80-21,0)</f>
         <v>0</v>
       </c>
       <c r="K80" s="164"/>
@@ -36666,7 +36682,7 @@
     </row>
     <row r="85" spans="1:26" s="9" customFormat="1" ht="47.25">
       <c r="A85" s="33">
-        <f t="shared" ref="A85:A130" si="29">A84+1</f>
+        <f t="shared" ref="A85:A131" si="29">A84+1</f>
         <v>79</v>
       </c>
       <c r="B85" s="33" t="str">
@@ -39857,7 +39873,9 @@
       <c r="W129" s="235"/>
       <c r="X129" s="230"/>
       <c r="Y129" s="19"/>
-      <c r="Z129" s="92"/>
+      <c r="Z129" s="92" t="s">
+        <v>1119</v>
+      </c>
     </row>
     <row r="130" spans="1:26" s="9" customFormat="1" ht="63">
       <c r="A130" s="33">
@@ -39870,17 +39888,17 @@
       </c>
       <c r="C130" s="164"/>
       <c r="D130" s="25" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="E130" s="174">
         <f t="shared" si="23"/>
         <v>46314</v>
       </c>
       <c r="F130" s="31" t="s">
+        <v>1106</v>
+      </c>
+      <c r="G130" s="21" t="s">
         <v>1107</v>
-      </c>
-      <c r="G130" s="21" t="s">
-        <v>1108</v>
       </c>
       <c r="H130" s="138" t="s">
         <v>6</v>
@@ -39920,143 +39938,156 @@
         <v>46317</v>
       </c>
       <c r="W130" s="235" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="X130" s="230"/>
       <c r="Y130" s="19"/>
       <c r="Z130" s="92" t="s">
-        <v>1110</v>
-      </c>
-    </row>
-    <row r="131" spans="1:26" s="9" customFormat="1">
-      <c r="A131" s="23"/>
-      <c r="B131" s="33"/>
-      <c r="C131" s="137"/>
-      <c r="D131" s="25"/>
-      <c r="E131" s="174"/>
-      <c r="F131" s="31"/>
-      <c r="G131" s="21"/>
-      <c r="H131" s="138"/>
-      <c r="I131" s="177"/>
-      <c r="J131" s="48"/>
-      <c r="K131" s="177"/>
-      <c r="L131" s="59"/>
-      <c r="M131" s="60"/>
-      <c r="N131" s="61"/>
-      <c r="O131" s="144"/>
-      <c r="P131" s="146"/>
-      <c r="Q131" s="152"/>
-      <c r="R131" s="27"/>
-      <c r="S131" s="27"/>
-      <c r="T131" s="187"/>
+        <v>1109</v>
+      </c>
+    </row>
+    <row r="131" spans="1:26" s="9" customFormat="1" ht="126">
+      <c r="A131" s="33">
+        <f t="shared" si="29"/>
+        <v>125</v>
+      </c>
+      <c r="B131" s="33" t="str">
+        <f t="shared" ref="B131" si="62">MID(D131, FIND("-", D131) + 1, 4)</f>
+        <v>5.11</v>
+      </c>
+      <c r="C131" s="164"/>
+      <c r="D131" s="25" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E131" s="174">
+        <f t="shared" si="23"/>
+        <v>46339</v>
+      </c>
+      <c r="F131" s="31" t="s">
+        <v>1117</v>
+      </c>
+      <c r="G131" s="21" t="s">
+        <v>1118</v>
+      </c>
+      <c r="H131" s="138" t="s">
+        <v>6</v>
+      </c>
+      <c r="I131" s="164">
+        <f t="shared" ca="1" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="J131" s="47">
+        <f t="shared" ca="1" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="K131" s="164"/>
+      <c r="L131" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="M131" s="41"/>
+      <c r="N131" s="40"/>
+      <c r="O131" s="41"/>
+      <c r="P131" s="40"/>
+      <c r="Q131" s="154"/>
+      <c r="R131" s="27">
+        <v>46318</v>
+      </c>
+      <c r="S131" s="27">
+        <v>46318</v>
+      </c>
+      <c r="T131" s="188">
+        <v>46318</v>
+      </c>
       <c r="U131" s="29"/>
-      <c r="V131" s="188"/>
+      <c r="V131" s="211"/>
       <c r="W131" s="235"/>
       <c r="X131" s="230"/>
       <c r="Y131" s="19"/>
       <c r="Z131" s="92"/>
     </row>
-    <row r="132" spans="1:26" s="9" customFormat="1" ht="16.5" thickBot="1">
-      <c r="A132" s="24"/>
-      <c r="B132" s="329"/>
-      <c r="C132" s="165"/>
-      <c r="D132" s="45"/>
-      <c r="E132" s="175"/>
-      <c r="F132" s="32"/>
-      <c r="G132" s="22"/>
-      <c r="H132" s="139"/>
-      <c r="I132" s="178"/>
-      <c r="J132" s="49"/>
-      <c r="K132" s="178"/>
-      <c r="L132" s="62"/>
-      <c r="M132" s="63"/>
-      <c r="N132" s="64"/>
-      <c r="O132" s="145"/>
-      <c r="P132" s="147"/>
-      <c r="Q132" s="153"/>
-      <c r="R132" s="44"/>
-      <c r="S132" s="44"/>
-      <c r="T132" s="189"/>
-      <c r="U132" s="43"/>
-      <c r="V132" s="194"/>
-      <c r="W132" s="258"/>
-      <c r="X132" s="232"/>
-      <c r="Y132" s="20"/>
-      <c r="Z132" s="93"/>
-    </row>
-    <row r="133" spans="1:26" ht="16.5" thickBot="1"/>
-    <row r="134" spans="1:26" ht="16.5" thickBot="1">
-      <c r="C134" s="207" t="s">
+    <row r="132" spans="1:26" s="9" customFormat="1">
+      <c r="A132" s="23"/>
+      <c r="B132" s="33"/>
+      <c r="C132" s="137"/>
+      <c r="D132" s="25"/>
+      <c r="E132" s="174"/>
+      <c r="F132" s="31"/>
+      <c r="G132" s="21"/>
+      <c r="H132" s="138"/>
+      <c r="I132" s="177"/>
+      <c r="J132" s="48"/>
+      <c r="K132" s="177"/>
+      <c r="L132" s="59"/>
+      <c r="M132" s="60"/>
+      <c r="N132" s="61"/>
+      <c r="O132" s="144"/>
+      <c r="P132" s="146"/>
+      <c r="Q132" s="152"/>
+      <c r="R132" s="27"/>
+      <c r="S132" s="27"/>
+      <c r="T132" s="187"/>
+      <c r="U132" s="29"/>
+      <c r="V132" s="188"/>
+      <c r="W132" s="235"/>
+      <c r="X132" s="230"/>
+      <c r="Y132" s="19"/>
+      <c r="Z132" s="92"/>
+    </row>
+    <row r="133" spans="1:26" s="9" customFormat="1" ht="16.5" thickBot="1">
+      <c r="A133" s="24"/>
+      <c r="B133" s="329"/>
+      <c r="C133" s="165"/>
+      <c r="D133" s="45"/>
+      <c r="E133" s="175"/>
+      <c r="F133" s="32"/>
+      <c r="G133" s="22"/>
+      <c r="H133" s="139"/>
+      <c r="I133" s="178"/>
+      <c r="J133" s="49"/>
+      <c r="K133" s="178"/>
+      <c r="L133" s="62"/>
+      <c r="M133" s="63"/>
+      <c r="N133" s="64"/>
+      <c r="O133" s="145"/>
+      <c r="P133" s="147"/>
+      <c r="Q133" s="153"/>
+      <c r="R133" s="44"/>
+      <c r="S133" s="44"/>
+      <c r="T133" s="189"/>
+      <c r="U133" s="43"/>
+      <c r="V133" s="194"/>
+      <c r="W133" s="258"/>
+      <c r="X133" s="232"/>
+      <c r="Y133" s="20"/>
+      <c r="Z133" s="93"/>
+    </row>
+    <row r="134" spans="1:26" ht="16.5" thickBot="1"/>
+    <row r="135" spans="1:26" ht="16.5" thickBot="1">
+      <c r="C135" s="207" t="s">
         <v>38</v>
       </c>
-      <c r="D134" s="354" t="s">
+      <c r="D135" s="441" t="s">
         <v>39</v>
       </c>
-      <c r="E134" s="355"/>
-      <c r="F134" s="46"/>
-      <c r="G134" s="68"/>
-      <c r="H134" s="356" t="s">
+      <c r="E135" s="442"/>
+      <c r="F135" s="46"/>
+      <c r="G135" s="68"/>
+      <c r="H135" s="357" t="s">
         <v>14</v>
       </c>
-      <c r="I134" s="357"/>
-      <c r="J134" s="357"/>
-      <c r="K134" s="357"/>
-      <c r="L134" s="357"/>
-      <c r="M134" s="358"/>
-      <c r="N134" s="350" t="s">
+      <c r="I135" s="358"/>
+      <c r="J135" s="358"/>
+      <c r="K135" s="358"/>
+      <c r="L135" s="358"/>
+      <c r="M135" s="359"/>
+      <c r="N135" s="360" t="s">
         <v>7</v>
       </c>
-      <c r="O134" s="351"/>
-      <c r="P134" s="350" t="s">
+      <c r="O135" s="361"/>
+      <c r="P135" s="360" t="s">
         <v>110</v>
       </c>
-      <c r="Q134" s="351"/>
-      <c r="R134" s="1"/>
-      <c r="S134" s="1"/>
-      <c r="T134" s="140"/>
-      <c r="U134" s="1"/>
-      <c r="W134" s="11"/>
-      <c r="X134" s="11"/>
-      <c r="Y134" s="11"/>
-    </row>
-    <row r="135" spans="1:26" ht="16.5" customHeight="1" thickBot="1">
-      <c r="C135" s="208" t="s">
-        <v>74</v>
-      </c>
-      <c r="D135" s="371" t="s">
-        <v>77</v>
-      </c>
-      <c r="E135" s="372"/>
-      <c r="F135" s="46"/>
-      <c r="G135" s="46"/>
-      <c r="H135" s="359" t="s">
-        <v>17</v>
-      </c>
-      <c r="I135" s="360"/>
-      <c r="J135" s="130"/>
-      <c r="K135" s="210"/>
-      <c r="L135" s="117">
-        <f ca="1">M135/$M$135</f>
-        <v>1</v>
-      </c>
-      <c r="M135" s="104">
-        <f ca="1">SUM($M$136:$M$138)</f>
-        <v>128</v>
-      </c>
-      <c r="N135" s="118" t="s">
-        <v>15</v>
-      </c>
-      <c r="O135" s="119" t="s">
-        <v>16</v>
-      </c>
-      <c r="P135" s="117">
-        <f ca="1">Q135/$Q$135</f>
-        <v>1</v>
-      </c>
-      <c r="Q135" s="104">
-        <f ca="1">SUM(Q136:Q137)</f>
-        <v>110</v>
-      </c>
+      <c r="Q135" s="361"/>
       <c r="R135" s="1"/>
       <c r="S135" s="1"/>
       <c r="T135" s="140"/>
@@ -40065,45 +40096,43 @@
       <c r="X135" s="11"/>
       <c r="Y135" s="11"/>
     </row>
-    <row r="136" spans="1:26">
-      <c r="C136" s="373" t="s">
-        <v>6</v>
-      </c>
-      <c r="D136" s="371" t="s">
-        <v>40</v>
-      </c>
-      <c r="E136" s="372"/>
-      <c r="F136" s="69"/>
-      <c r="G136" s="6"/>
-      <c r="H136" s="362" t="s">
-        <v>69</v>
-      </c>
-      <c r="I136" s="363"/>
-      <c r="J136" s="363"/>
-      <c r="K136" s="364"/>
-      <c r="L136" s="122">
-        <f t="shared" ref="L136:L138" ca="1" si="62">M136/$M$135</f>
-        <v>0.84375</v>
-      </c>
-      <c r="M136" s="123">
-        <f>COUNTIF($H$7:$H$132,"RFCS")</f>
-        <v>108</v>
-      </c>
-      <c r="N136" s="121">
-        <f ca="1">COUNTIFS($I$7:$I$132,"&lt;=21",$H$7:$H$132,"RFCS")</f>
-        <v>65</v>
-      </c>
-      <c r="O136" s="120">
-        <f ca="1">COUNTIFS($I$7:$I$132,"&gt;21",$H$7:$H$132,"RFCS")</f>
-        <v>42</v>
-      </c>
-      <c r="P136" s="122">
-        <f ca="1">Q136/$Q$135</f>
-        <v>0.65454545454545454</v>
-      </c>
-      <c r="Q136" s="123">
-        <f>COUNTIF($Q$7:$Q$132,"RBE") + COUNTIF($Q$7:$Q$132,"SUP")</f>
-        <v>72</v>
+    <row r="136" spans="1:26" ht="16.5" customHeight="1" thickBot="1">
+      <c r="C136" s="208" t="s">
+        <v>74</v>
+      </c>
+      <c r="D136" s="439" t="s">
+        <v>77</v>
+      </c>
+      <c r="E136" s="440"/>
+      <c r="F136" s="46"/>
+      <c r="G136" s="46"/>
+      <c r="H136" s="434" t="s">
+        <v>17</v>
+      </c>
+      <c r="I136" s="435"/>
+      <c r="J136" s="130"/>
+      <c r="K136" s="210"/>
+      <c r="L136" s="117">
+        <f ca="1">M136/$M$136</f>
+        <v>1</v>
+      </c>
+      <c r="M136" s="104">
+        <f ca="1">SUM($M$137:$M$139)</f>
+        <v>130</v>
+      </c>
+      <c r="N136" s="118" t="s">
+        <v>15</v>
+      </c>
+      <c r="O136" s="119" t="s">
+        <v>16</v>
+      </c>
+      <c r="P136" s="117">
+        <f ca="1">Q136/$Q$136</f>
+        <v>1</v>
+      </c>
+      <c r="Q136" s="104">
+        <f ca="1">SUM(Q137:Q138)</f>
+        <v>111</v>
       </c>
       <c r="R136" s="1"/>
       <c r="S136" s="1"/>
@@ -40114,44 +40143,46 @@
       <c r="Y136" s="11"/>
     </row>
     <row r="137" spans="1:26">
-      <c r="C137" s="373"/>
-      <c r="D137" s="371"/>
-      <c r="E137" s="372"/>
-      <c r="F137" s="72"/>
+      <c r="C137" s="385" t="s">
+        <v>6</v>
+      </c>
+      <c r="D137" s="439" t="s">
+        <v>40</v>
+      </c>
+      <c r="E137" s="440"/>
+      <c r="F137" s="69"/>
       <c r="G137" s="6"/>
-      <c r="H137" s="365" t="s">
-        <v>70</v>
-      </c>
-      <c r="I137" s="366"/>
-      <c r="J137" s="366"/>
-      <c r="K137" s="367"/>
-      <c r="L137" s="124">
-        <f t="shared" ca="1" si="62"/>
-        <v>4.6875E-2</v>
-      </c>
-      <c r="M137" s="125">
-        <f ca="1">SUM(N137:O137)</f>
-        <v>6</v>
-      </c>
-      <c r="N137" s="98">
-        <f ca="1">COUNTIFS($I$7:$I$132,"&lt;=21",$U$7:$U$132,"",$K$7:$K$132,"&lt;&gt;X")</f>
-        <v>1</v>
-      </c>
-      <c r="O137" s="50">
-        <f ca="1">COUNTIFS($I$7:$I$132,"&gt;21",$U$7:$U$132,"",$K$7:$K$132,"&lt;&gt;X")</f>
-        <v>5</v>
-      </c>
-      <c r="P137" s="124">
-        <f ca="1">Q137/$Q$135</f>
-        <v>0.34545454545454546</v>
-      </c>
-      <c r="Q137" s="125">
-        <f ca="1">COUNTIFS($I$7:$I$132,"&gt;=0",$P$7:$P$132,"",$K$7:$K$132,"&lt;&gt;X")</f>
-        <v>38</v>
-      </c>
-      <c r="R137" s="1" t="s">
-        <v>10</v>
-      </c>
+      <c r="H137" s="436" t="s">
+        <v>69</v>
+      </c>
+      <c r="I137" s="437"/>
+      <c r="J137" s="437"/>
+      <c r="K137" s="438"/>
+      <c r="L137" s="122">
+        <f t="shared" ref="L137:L139" ca="1" si="63">M137/$M$136</f>
+        <v>0.83846153846153848</v>
+      </c>
+      <c r="M137" s="123">
+        <f>COUNTIF($H$7:$H$133,"RFCS")</f>
+        <v>109</v>
+      </c>
+      <c r="N137" s="121">
+        <f ca="1">COUNTIFS($I$7:$I$133,"&lt;=21",$H$7:$H$133,"RFCS")</f>
+        <v>66</v>
+      </c>
+      <c r="O137" s="120">
+        <f ca="1">COUNTIFS($I$7:$I$133,"&gt;21",$H$7:$H$133,"RFCS")</f>
+        <v>42</v>
+      </c>
+      <c r="P137" s="122">
+        <f ca="1">Q137/$Q$136</f>
+        <v>0.64864864864864868</v>
+      </c>
+      <c r="Q137" s="123">
+        <f>COUNTIF($Q$7:$Q$133,"RBE") + COUNTIF($Q$7:$Q$133,"SUP")</f>
+        <v>72</v>
+      </c>
+      <c r="R137" s="1"/>
       <c r="S137" s="1"/>
       <c r="T137" s="140"/>
       <c r="U137" s="1"/>
@@ -40159,66 +40190,112 @@
       <c r="X137" s="11"/>
       <c r="Y137" s="11"/>
     </row>
-    <row r="138" spans="1:26" ht="16.5" thickBot="1">
-      <c r="C138" s="373" t="s">
+    <row r="138" spans="1:26">
+      <c r="C138" s="385"/>
+      <c r="D138" s="439"/>
+      <c r="E138" s="440"/>
+      <c r="F138" s="72"/>
+      <c r="G138" s="6"/>
+      <c r="H138" s="382" t="s">
+        <v>70</v>
+      </c>
+      <c r="I138" s="383"/>
+      <c r="J138" s="383"/>
+      <c r="K138" s="384"/>
+      <c r="L138" s="124">
+        <f t="shared" ca="1" si="63"/>
+        <v>5.3846153846153849E-2</v>
+      </c>
+      <c r="M138" s="125">
+        <f ca="1">SUM(N138:O138)</f>
+        <v>7</v>
+      </c>
+      <c r="N138" s="98">
+        <f ca="1">COUNTIFS($I$7:$I$133,"&lt;=21",$U$7:$U$133,"",$K$7:$K$133,"&lt;&gt;X")</f>
+        <v>2</v>
+      </c>
+      <c r="O138" s="50">
+        <f ca="1">COUNTIFS($I$7:$I$133,"&gt;21",$U$7:$U$133,"",$K$7:$K$133,"&lt;&gt;X")</f>
+        <v>5</v>
+      </c>
+      <c r="P138" s="124">
+        <f ca="1">Q138/$Q$136</f>
+        <v>0.35135135135135137</v>
+      </c>
+      <c r="Q138" s="125">
+        <f ca="1">COUNTIFS($I$7:$I$133,"&gt;=0",$P$7:$P$133,"",$K$7:$K$133,"&lt;&gt;X")</f>
+        <v>39</v>
+      </c>
+      <c r="R138" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="S138" s="1"/>
+      <c r="T138" s="140"/>
+      <c r="U138" s="1"/>
+      <c r="W138" s="11"/>
+      <c r="X138" s="11"/>
+      <c r="Y138" s="11"/>
+    </row>
+    <row r="139" spans="1:26" ht="16.5" thickBot="1">
+      <c r="C139" s="385" t="s">
         <v>75</v>
       </c>
-      <c r="D138" s="375" t="s">
+      <c r="D139" s="387" t="s">
         <v>76</v>
       </c>
-      <c r="E138" s="376"/>
-      <c r="H138" s="368" t="s">
+      <c r="E139" s="388"/>
+      <c r="H139" s="354" t="s">
         <v>71</v>
       </c>
-      <c r="I138" s="369"/>
-      <c r="J138" s="369"/>
-      <c r="K138" s="370"/>
-      <c r="L138" s="126">
-        <f t="shared" ca="1" si="62"/>
-        <v>0.109375</v>
-      </c>
-      <c r="M138" s="116">
-        <f>COUNTIFS($K$7:$K$132,"X")</f>
+      <c r="I139" s="355"/>
+      <c r="J139" s="355"/>
+      <c r="K139" s="356"/>
+      <c r="L139" s="126">
+        <f t="shared" ca="1" si="63"/>
+        <v>0.1076923076923077</v>
+      </c>
+      <c r="M139" s="116">
+        <f>COUNTIFS($K$7:$K$133,"X")</f>
         <v>14</v>
       </c>
-      <c r="N138" s="99"/>
-      <c r="O138" s="51"/>
-      <c r="P138" s="223"/>
-      <c r="Q138" s="224"/>
-    </row>
-    <row r="139" spans="1:26" ht="16.5" thickBot="1">
-      <c r="C139" s="374"/>
-      <c r="D139" s="377"/>
-      <c r="E139" s="378"/>
-    </row>
-    <row r="141" spans="1:26">
-      <c r="C141" s="361" t="s">
+      <c r="N139" s="99"/>
+      <c r="O139" s="51"/>
+      <c r="P139" s="223"/>
+      <c r="Q139" s="224"/>
+    </row>
+    <row r="140" spans="1:26" ht="16.5" thickBot="1">
+      <c r="C140" s="386"/>
+      <c r="D140" s="389"/>
+      <c r="E140" s="390"/>
+    </row>
+    <row r="142" spans="1:26">
+      <c r="C142" s="372" t="s">
         <v>41</v>
       </c>
-      <c r="D141" s="361"/>
-      <c r="E141" s="361"/>
-    </row>
-    <row r="142" spans="1:26">
-      <c r="C142" s="169" t="s">
-        <v>8</v>
-      </c>
-      <c r="D142" s="1" t="s">
-        <v>42</v>
-      </c>
+      <c r="D142" s="372"/>
+      <c r="E142" s="372"/>
     </row>
     <row r="143" spans="1:26">
       <c r="C143" s="169" t="s">
         <v>8</v>
       </c>
-      <c r="D143" s="127" t="s">
-        <v>43</v>
+      <c r="D143" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="144" spans="1:26">
       <c r="C144" s="169" t="s">
         <v>8</v>
       </c>
-      <c r="D144" s="1" t="s">
+      <c r="D144" s="127" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="145" spans="3:4">
+      <c r="C145" s="169" t="s">
+        <v>8</v>
+      </c>
+      <c r="D145" s="1" t="s">
         <v>44</v>
       </c>
     </row>
@@ -40229,6 +40306,22 @@
     </sortState>
   </autoFilter>
   <mergeCells count="32">
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="P135:Q135"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="D135:E135"/>
+    <mergeCell ref="H135:M135"/>
+    <mergeCell ref="N135:O135"/>
+    <mergeCell ref="H136:I136"/>
+    <mergeCell ref="C142:E142"/>
+    <mergeCell ref="H137:K137"/>
+    <mergeCell ref="H138:K138"/>
+    <mergeCell ref="H139:K139"/>
+    <mergeCell ref="D136:E136"/>
+    <mergeCell ref="C137:C138"/>
+    <mergeCell ref="D137:E138"/>
+    <mergeCell ref="C139:C140"/>
+    <mergeCell ref="D139:E140"/>
     <mergeCell ref="Z4:Z5"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="D4:D5"/>
@@ -40245,25 +40338,9 @@
     <mergeCell ref="K4:K5"/>
     <mergeCell ref="P4:Q4"/>
     <mergeCell ref="X4:Y4"/>
-    <mergeCell ref="H135:I135"/>
-    <mergeCell ref="C141:E141"/>
-    <mergeCell ref="H136:K136"/>
-    <mergeCell ref="H137:K137"/>
-    <mergeCell ref="H138:K138"/>
-    <mergeCell ref="D135:E135"/>
-    <mergeCell ref="C136:C137"/>
-    <mergeCell ref="D136:E137"/>
-    <mergeCell ref="C138:C139"/>
-    <mergeCell ref="D138:E139"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="P134:Q134"/>
-    <mergeCell ref="J4:J5"/>
-    <mergeCell ref="D134:E134"/>
-    <mergeCell ref="H134:M134"/>
-    <mergeCell ref="N134:O134"/>
   </mergeCells>
   <phoneticPr fontId="71"/>
-  <conditionalFormatting sqref="A7:Z132">
+  <conditionalFormatting sqref="A7:Z133">
     <cfRule type="expression" dxfId="4" priority="1">
       <formula>$K7="X"</formula>
     </cfRule>
@@ -40408,9 +40485,9 @@
     <hyperlink ref="O43" r:id="rId125" xr:uid="{0E3F3A7F-DA9A-49F8-A93F-8337122FAE1A}"/>
     <hyperlink ref="N41" r:id="rId126" xr:uid="{3405D711-BDD4-4069-A376-D6B961D87010}"/>
     <hyperlink ref="N43" r:id="rId127" xr:uid="{525398A7-A7B1-41B1-88A2-7E7F9115541E}"/>
-    <hyperlink ref="C142" r:id="rId128" xr:uid="{F06CE902-4089-4B08-A7E9-420A16C9FF0E}"/>
-    <hyperlink ref="C143" r:id="rId129" xr:uid="{6D322F1B-B574-40E7-BED0-14ED893C19C5}"/>
-    <hyperlink ref="C144" r:id="rId130" xr:uid="{1845DEB0-969B-4FE7-B52A-52C25D3EC72E}"/>
+    <hyperlink ref="C143" r:id="rId128" xr:uid="{F06CE902-4089-4B08-A7E9-420A16C9FF0E}"/>
+    <hyperlink ref="C144" r:id="rId129" xr:uid="{6D322F1B-B574-40E7-BED0-14ED893C19C5}"/>
+    <hyperlink ref="C145" r:id="rId130" xr:uid="{1845DEB0-969B-4FE7-B52A-52C25D3EC72E}"/>
     <hyperlink ref="N42" r:id="rId131" xr:uid="{95D9F3CF-8EC0-4C96-9F49-34E6585C583B}"/>
     <hyperlink ref="L44" r:id="rId132" xr:uid="{255E79C1-4568-41F7-B71E-8301B034AA56}"/>
     <hyperlink ref="P8" r:id="rId133" xr:uid="{4339778F-2FA8-45DA-BD1F-0684B78D35ED}"/>
@@ -40768,9 +40845,10 @@
     <hyperlink ref="P61" r:id="rId485" xr:uid="{B7476E13-5509-4F98-A368-0F0149FCE838}"/>
     <hyperlink ref="P73" r:id="rId486" xr:uid="{6610F5FD-75DB-40B9-A6E0-491FAB724084}"/>
     <hyperlink ref="P119" r:id="rId487" xr:uid="{2F121870-B035-4D11-8EFC-0663ECEC1B47}"/>
+    <hyperlink ref="L131" r:id="rId488" xr:uid="{94164395-7664-4D29-826A-1481F8D07F22}"/>
   </hyperlinks>
   <pageMargins left="0.25" right="0.17" top="0.5" bottom="0.25" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="28" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId488"/>
+  <pageSetup paperSize="9" scale="28" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId489"/>
 </worksheet>
 </file>
 
@@ -40855,19 +40933,19 @@
       <c r="S3" s="281"/>
     </row>
     <row r="4" spans="1:25" ht="36" customHeight="1" thickBot="1">
-      <c r="A4" s="426" t="s">
+      <c r="A4" s="397" t="s">
         <v>123</v>
       </c>
-      <c r="B4" s="385" t="s">
+      <c r="B4" s="364" t="s">
         <v>45</v>
       </c>
-      <c r="C4" s="385" t="s">
+      <c r="C4" s="364" t="s">
         <v>95</v>
       </c>
-      <c r="D4" s="385" t="s">
+      <c r="D4" s="364" t="s">
         <v>46</v>
       </c>
-      <c r="E4" s="352" t="s">
+      <c r="E4" s="362" t="s">
         <v>4</v>
       </c>
       <c r="F4" s="449" t="s">
@@ -40896,12 +40974,12 @@
       <c r="S4" s="448"/>
     </row>
     <row r="5" spans="1:25" ht="78.75">
-      <c r="A5" s="427"/>
-      <c r="B5" s="386"/>
-      <c r="C5" s="386"/>
-      <c r="D5" s="386"/>
-      <c r="E5" s="353"/>
-      <c r="F5" s="429"/>
+      <c r="A5" s="398"/>
+      <c r="B5" s="365"/>
+      <c r="C5" s="365"/>
+      <c r="D5" s="365"/>
+      <c r="E5" s="369"/>
+      <c r="F5" s="402"/>
       <c r="G5" s="283" t="s">
         <v>56</v>
       </c>
@@ -41391,7 +41469,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="13" spans="1:25" ht="45">
+    <row r="13" spans="1:25" ht="30">
       <c r="A13" s="13">
         <v>7</v>
       </c>
@@ -41509,7 +41587,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="15" spans="1:25" ht="60">
+    <row r="15" spans="1:25" ht="45">
       <c r="A15" s="13">
         <v>9</v>
       </c>
@@ -41568,7 +41646,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="16" spans="1:25" ht="45">
+    <row r="16" spans="1:25" ht="60">
       <c r="A16" s="13">
         <v>10</v>
       </c>
@@ -41627,7 +41705,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:19" ht="60">
+    <row r="17" spans="1:19" ht="45">
       <c r="A17" s="13">
         <v>11</v>
       </c>
@@ -41686,7 +41764,7 @@
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:19" ht="45">
+    <row r="18" spans="1:19" ht="60">
       <c r="A18" s="13">
         <v>12</v>
       </c>
@@ -41745,7 +41823,7 @@
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:19" ht="75">
+    <row r="19" spans="1:19" ht="45">
       <c r="A19" s="13">
         <v>13</v>
       </c>
@@ -41804,7 +41882,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:19" ht="45">
+    <row r="20" spans="1:19" ht="75">
       <c r="A20" s="13">
         <v>14</v>
       </c>
@@ -41926,7 +42004,7 @@
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:19" ht="60">
+    <row r="22" spans="1:19" ht="45">
       <c r="A22" s="13">
         <v>16</v>
       </c>
@@ -42221,7 +42299,7 @@
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:19">
+    <row r="27" spans="1:19" ht="30">
       <c r="A27" s="13">
         <v>21</v>
       </c>
@@ -42280,7 +42358,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" spans="1:19">
+    <row r="28" spans="1:19" ht="45">
       <c r="A28" s="13">
         <v>22</v>
       </c>
@@ -42339,7 +42417,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:19">
+    <row r="29" spans="1:19" ht="45">
       <c r="A29" s="13">
         <v>23</v>
       </c>
@@ -42398,7 +42476,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:19">
+    <row r="30" spans="1:19" ht="45">
       <c r="A30" s="13">
         <v>24</v>
       </c>
@@ -42554,16 +42632,16 @@
       <c r="R3" s="281"/>
     </row>
     <row r="4" spans="1:18" ht="16.5" thickBot="1">
-      <c r="A4" s="426" t="s">
+      <c r="A4" s="397" t="s">
         <v>123</v>
       </c>
-      <c r="B4" s="385" t="s">
+      <c r="B4" s="364" t="s">
         <v>45</v>
       </c>
-      <c r="C4" s="385" t="s">
+      <c r="C4" s="364" t="s">
         <v>46</v>
       </c>
-      <c r="D4" s="390" t="s">
+      <c r="D4" s="366" t="s">
         <v>4</v>
       </c>
       <c r="E4" s="449" t="s">
@@ -42592,11 +42670,11 @@
       <c r="R4" s="448"/>
     </row>
     <row r="5" spans="1:18" ht="78.75">
-      <c r="A5" s="427"/>
-      <c r="B5" s="386"/>
-      <c r="C5" s="386"/>
-      <c r="D5" s="384"/>
-      <c r="E5" s="353"/>
+      <c r="A5" s="398"/>
+      <c r="B5" s="365"/>
+      <c r="C5" s="365"/>
+      <c r="D5" s="431"/>
+      <c r="E5" s="369"/>
       <c r="F5" s="283" t="s">
         <v>56</v>
       </c>
@@ -43128,7 +43206,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="15" spans="1:18">
+    <row r="15" spans="1:18" ht="60">
       <c r="A15" s="13">
         <v>9</v>
       </c>
@@ -43184,7 +43262,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="16" spans="1:18">
+    <row r="16" spans="1:18" ht="30">
       <c r="A16" s="13">
         <v>10</v>
       </c>

--- a/ICT-RFA-RFI-lists-New.xlsx
+++ b/ICT-RFA-RFI-lists-New.xlsx
@@ -9,9 +9,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project Airport\LTIA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F2C222F-F9C1-402A-8803-184FFE24C466}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAF7253C-8783-4870-B0CF-3210D98A6521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="506" xr2:uid="{CCA8147E-0981-4321-B87F-440A52C0DA59}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="506" activeTab="1" xr2:uid="{CCA8147E-0981-4321-B87F-440A52C0DA59}"/>
   </bookViews>
   <sheets>
     <sheet name="RFA" sheetId="1" r:id="rId1"/>
@@ -78,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3616" uniqueCount="1135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3620" uniqueCount="1137">
   <si>
     <t>TT</t>
   </si>
@@ -5278,6 +5278,16 @@
   </si>
   <si>
     <t>10/27/2026: Đã phát hành letter</t>
+  </si>
+  <si>
+    <t>10/23/2026: Đã comment
+10/26/2026: Đã gửi CNC
+10/27/2026: Đã ký C</t>
+  </si>
+  <si>
+    <t>10/23/2026: Đã comment
+10/26/2026: Đã gửi CNC
+10/27/2026: Đã ký RFCS</t>
   </si>
 </sst>
 </file>
@@ -7714,31 +7724,28 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -7750,16 +7757,25 @@
     <xf numFmtId="0" fontId="17" fillId="2" borderId="52" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -7768,22 +7784,34 @@
     <xf numFmtId="0" fontId="56" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -7825,89 +7853,29 @@
     <xf numFmtId="0" fontId="32" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -7933,44 +7901,74 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="53" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="47" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -7993,11 +7991,23 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="53" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="47" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -8660,92 +8670,92 @@
       <c r="AE3" s="159"/>
     </row>
     <row r="4" spans="1:35" s="5" customFormat="1" ht="36" customHeight="1" thickBot="1">
-      <c r="A4" s="397" t="s">
+      <c r="A4" s="408" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="407" t="s">
+      <c r="B4" s="348" t="s">
         <v>515</v>
       </c>
-      <c r="C4" s="403" t="s">
+      <c r="C4" s="414" t="s">
         <v>45</v>
       </c>
-      <c r="D4" s="364" t="s">
+      <c r="D4" s="366" t="s">
         <v>95</v>
       </c>
-      <c r="E4" s="362" t="s">
+      <c r="E4" s="369" t="s">
         <v>46</v>
       </c>
-      <c r="F4" s="399" t="s">
+      <c r="F4" s="412" t="s">
         <v>47</v>
       </c>
-      <c r="G4" s="362" t="s">
+      <c r="G4" s="369" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="401" t="s">
+      <c r="H4" s="410" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="364" t="s">
+      <c r="I4" s="366" t="s">
         <v>48</v>
       </c>
-      <c r="J4" s="364" t="s">
+      <c r="J4" s="366" t="s">
         <v>49</v>
       </c>
-      <c r="K4" s="362" t="s">
+      <c r="K4" s="369" t="s">
         <v>78</v>
       </c>
-      <c r="L4" s="364" t="s">
+      <c r="L4" s="366" t="s">
         <v>80</v>
       </c>
-      <c r="M4" s="366" t="s">
+      <c r="M4" s="364" t="s">
         <v>53</v>
       </c>
-      <c r="N4" s="367"/>
-      <c r="O4" s="366" t="s">
+      <c r="N4" s="365"/>
+      <c r="O4" s="364" t="s">
         <v>55</v>
       </c>
-      <c r="P4" s="367"/>
+      <c r="P4" s="365"/>
       <c r="Q4" s="368" t="s">
         <v>72</v>
       </c>
-      <c r="R4" s="367"/>
-      <c r=